--- a/jogos_2026-08-02.xlsx
+++ b/jogos_2026-08-02.xlsx
@@ -635,13 +635,13 @@
         </is>
       </c>
       <c r="N2">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="O2">
-        <v>0</v>
+        <v>5.15</v>
       </c>
       <c r="P2">
-        <v>0</v>
+        <v>8.050000000000001</v>
       </c>
       <c r="Q2">
         <v>0</v>
@@ -1092,12 +1092,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Marconi Stallions</t>
+          <t>Rockdale City Suns</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>St George City FA</t>
+          <t>Manly United</t>
         </is>
       </c>
       <c r="G5">
@@ -1255,12 +1255,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Rockdale City Suns</t>
+          <t>Marconi Stallions</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Manly United</t>
+          <t>St George City FA</t>
         </is>
       </c>
       <c r="G6">
@@ -2070,12 +2070,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Daejeon Citizen</t>
+          <t>Ulsan</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Gwangju</t>
+          <t>Anyang</t>
         </is>
       </c>
       <c r="G11">
@@ -2396,12 +2396,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Ulsan</t>
+          <t>Daejeon Citizen</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Anyang</t>
+          <t>Gwangju</t>
         </is>
       </c>
       <c r="G13">
@@ -2885,12 +2885,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Jeonnam Dragons</t>
+          <t>Ansan Greeners</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Paju Citizen</t>
+          <t>Gimhae City</t>
         </is>
       </c>
       <c r="G16">
@@ -3048,12 +3048,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Ansan Greeners</t>
+          <t>Jeonnam Dragons</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Gimhae City</t>
+          <t>Paju Citizen</t>
         </is>
       </c>
       <c r="G17">
@@ -3374,12 +3374,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Suzhou Dongwu</t>
+          <t>Changchun Yatai</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Meizhou Hakka</t>
+          <t>Hebei Kungfu</t>
         </is>
       </c>
       <c r="G19">
@@ -3537,12 +3537,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Changchun Yatai</t>
+          <t>Suzhou Dongwu</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Hebei Kungfu</t>
+          <t>Meizhou Hakka</t>
         </is>
       </c>
       <c r="G20">
@@ -8590,12 +8590,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Sion</t>
+          <t>Grasshopper</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Luzern</t>
+          <t>Lugano</t>
         </is>
       </c>
       <c r="G51">
@@ -8753,12 +8753,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Grasshopper</t>
+          <t>Sion</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Lugano</t>
+          <t>Luzern</t>
         </is>
       </c>
       <c r="G52">
@@ -9568,12 +9568,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Molde</t>
+          <t>Aalesund</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Sarpsborg 08</t>
+          <t>Tromsø</t>
         </is>
       </c>
       <c r="G57">
@@ -9731,12 +9731,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Aalesund</t>
+          <t>Molde</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Tromsø</t>
+          <t>Sarpsborg 08</t>
         </is>
       </c>
       <c r="G58">
@@ -10709,12 +10709,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Kongsvinger</t>
+          <t>Lyn</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Strømmen</t>
+          <t>Sogndal</t>
         </is>
       </c>
       <c r="G64">
@@ -10872,12 +10872,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Lyn</t>
+          <t>Raufoss</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Sogndal</t>
+          <t>Stabæk</t>
         </is>
       </c>
       <c r="G65">
@@ -11035,12 +11035,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Raufoss</t>
+          <t>Hødd</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Stabæk</t>
+          <t>Moss</t>
         </is>
       </c>
       <c r="G66">
@@ -11198,12 +11198,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Hødd</t>
+          <t>Kongsvinger</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Moss</t>
+          <t>Strømmen</t>
         </is>
       </c>
       <c r="G67">
@@ -17066,12 +17066,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Ciudad de Bolívar</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Club Atlético Mitre</t>
+          <t>Midland</t>
         </is>
       </c>
       <c r="G103">
@@ -17229,12 +17229,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>Ciudad de Bolívar</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Midland</t>
+          <t>Club Atlético Mitre</t>
         </is>
       </c>
       <c r="G104">
@@ -17718,12 +17718,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Dečić</t>
+          <t>Sutjeska</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Arsenal Tivat</t>
+          <t>Budućnost</t>
         </is>
       </c>
       <c r="G107">
@@ -17881,12 +17881,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Petrovac</t>
+          <t>Dečić</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Bokelj</t>
+          <t>Arsenal Tivat</t>
         </is>
       </c>
       <c r="G108">
@@ -18044,12 +18044,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Sutjeska</t>
+          <t>Petrovac</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Budućnost</t>
+          <t>Bokelj</t>
         </is>
       </c>
       <c r="G109">
@@ -18207,12 +18207,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>FK Jezero Plav</t>
+          <t>Mladost DG</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Mornar</t>
+          <t>Otrant-Olympic</t>
         </is>
       </c>
       <c r="G110">
@@ -18370,12 +18370,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Mladost DG</t>
+          <t>FK Jezero Plav</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Otrant-Olympic</t>
+          <t>Mornar</t>
         </is>
       </c>
       <c r="G111">
@@ -19348,12 +19348,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Deportivo Maipú</t>
+          <t>Patronato</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Atlanta</t>
+          <t>Quilmes</t>
         </is>
       </c>
       <c r="G117">
@@ -19511,12 +19511,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Patronato</t>
+          <t>Temperley</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Quilmes</t>
+          <t>Gimnasia y Tiro</t>
         </is>
       </c>
       <c r="G118">
@@ -19674,12 +19674,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Temperley</t>
+          <t>Deportivo Maipú</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Gimnasia y Tiro</t>
+          <t>Atlanta</t>
         </is>
       </c>
       <c r="G119">

--- a/jogos_2026-08-02.xlsx
+++ b/jogos_2026-08-02.xlsx
@@ -2070,12 +2070,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Ulsan</t>
+          <t>Jeju United</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Anyang</t>
+          <t>Incheon United</t>
         </is>
       </c>
       <c r="G11">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Jeju United</t>
+          <t>Daejeon Citizen</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Incheon United</t>
+          <t>Gwangju</t>
         </is>
       </c>
       <c r="G12">
@@ -2396,12 +2396,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Daejeon Citizen</t>
+          <t>Ulsan</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Gwangju</t>
+          <t>Anyang</t>
         </is>
       </c>
       <c r="G13">
@@ -16903,12 +16903,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Almirante Brown</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Racing Córdoba</t>
+          <t>Midland</t>
         </is>
       </c>
       <c r="G102">
@@ -17066,12 +17066,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>Ciudad de Bolívar</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Midland</t>
+          <t>Club Atlético Mitre</t>
         </is>
       </c>
       <c r="G103">
@@ -17229,12 +17229,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Ciudad de Bolívar</t>
+          <t>Almirante Brown</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Club Atlético Mitre</t>
+          <t>Racing Córdoba</t>
         </is>
       </c>
       <c r="G104">
@@ -17881,12 +17881,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Dečić</t>
+          <t>FK Jezero Plav</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Arsenal Tivat</t>
+          <t>Mornar</t>
         </is>
       </c>
       <c r="G108">
@@ -18207,12 +18207,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Mladost DG</t>
+          <t>Dečić</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Otrant-Olympic</t>
+          <t>Arsenal Tivat</t>
         </is>
       </c>
       <c r="G110">
@@ -18370,12 +18370,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>FK Jezero Plav</t>
+          <t>Mladost DG</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Mornar</t>
+          <t>Otrant-Olympic</t>
         </is>
       </c>
       <c r="G111">
@@ -19511,12 +19511,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Temperley</t>
+          <t>Deportivo Maipú</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Gimnasia y Tiro</t>
+          <t>Atlanta</t>
         </is>
       </c>
       <c r="G118">
@@ -19674,12 +19674,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Deportivo Maipú</t>
+          <t>Temperley</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Atlanta</t>
+          <t>Gimnasia y Tiro</t>
         </is>
       </c>
       <c r="G119">
@@ -20652,12 +20652,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Deportivo Madryn</t>
+          <t>Club Atlético Güemes</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>All Boys</t>
+          <t>Tristán Suárez</t>
         </is>
       </c>
       <c r="G125">
@@ -20815,12 +20815,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Club Atlético Güemes</t>
+          <t>Deportivo Madryn</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Tristán Suárez</t>
+          <t>All Boys</t>
         </is>
       </c>
       <c r="G126">

--- a/jogos_2026-08-02.xlsx
+++ b/jogos_2026-08-02.xlsx
@@ -929,12 +929,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Blacktown City</t>
+          <t>Rockdale City Suns</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Sydney II</t>
+          <t>Manly United</t>
         </is>
       </c>
       <c r="G4">
@@ -1092,12 +1092,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Rockdale City Suns</t>
+          <t>Blacktown City</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Manly United</t>
+          <t>Sydney II</t>
         </is>
       </c>
       <c r="G5">
@@ -3211,12 +3211,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Shenzhen Juniors</t>
+          <t>Changchun Yatai</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Wuxi Wugou</t>
+          <t>Hebei Kungfu</t>
         </is>
       </c>
       <c r="G18">
@@ -3374,12 +3374,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Changchun Yatai</t>
+          <t>Suzhou Dongwu</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Hebei Kungfu</t>
+          <t>Meizhou Hakka</t>
         </is>
       </c>
       <c r="G19">
@@ -3537,12 +3537,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Suzhou Dongwu</t>
+          <t>Shenzhen Juniors</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Meizhou Hakka</t>
+          <t>Wuxi Wugou</t>
         </is>
       </c>
       <c r="G20">
@@ -4352,12 +4352,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>IFK Göteborg</t>
+          <t>Brommapojkarna</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Degerfors</t>
+          <t>Malmö FF</t>
         </is>
       </c>
       <c r="G25">
@@ -4515,12 +4515,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Brommapojkarna</t>
+          <t>IFK Göteborg</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Malmö FF</t>
+          <t>Degerfors</t>
         </is>
       </c>
       <c r="G26">
@@ -8590,12 +8590,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Grasshopper</t>
+          <t>Sion</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Lugano</t>
+          <t>Luzern</t>
         </is>
       </c>
       <c r="G51">
@@ -8753,12 +8753,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Sion</t>
+          <t>Grasshopper</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Luzern</t>
+          <t>Lugano</t>
         </is>
       </c>
       <c r="G52">
@@ -19511,12 +19511,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Deportivo Maipú</t>
+          <t>Temperley</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Atlanta</t>
+          <t>Gimnasia y Tiro</t>
         </is>
       </c>
       <c r="G118">
@@ -19674,12 +19674,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Temperley</t>
+          <t>Deportivo Maipú</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Gimnasia y Tiro</t>
+          <t>Atlanta</t>
         </is>
       </c>
       <c r="G119">

--- a/jogos_2026-08-02.xlsx
+++ b/jogos_2026-08-02.xlsx
@@ -1613,13 +1613,13 @@
         </is>
       </c>
       <c r="N8">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="O8">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="P8">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="Q8">
         <v>0</v>
@@ -1652,10 +1652,10 @@
         <v>0</v>
       </c>
       <c r="AA8">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AB8">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC8">
         <v>0</v>
@@ -2102,13 +2102,13 @@
         </is>
       </c>
       <c r="N11">
-        <v>0</v>
+        <v>3.11</v>
       </c>
       <c r="O11">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="P11">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="Q11">
         <v>0</v>
@@ -2265,13 +2265,13 @@
         </is>
       </c>
       <c r="N12">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="O12">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="P12">
-        <v>0</v>
+        <v>6.41</v>
       </c>
       <c r="Q12">
         <v>0</v>
@@ -2304,10 +2304,10 @@
         <v>0</v>
       </c>
       <c r="AA12">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB12">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AC12">
         <v>0</v>
@@ -2428,13 +2428,13 @@
         </is>
       </c>
       <c r="N13">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="O13">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="P13">
-        <v>0</v>
+        <v>3.81</v>
       </c>
       <c r="Q13">
         <v>0</v>
@@ -2467,10 +2467,10 @@
         <v>0</v>
       </c>
       <c r="AA13">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AB13">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AC13">
         <v>0</v>
@@ -2591,13 +2591,13 @@
         </is>
       </c>
       <c r="N14">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="O14">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="P14">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Q14">
         <v>0</v>
@@ -2754,13 +2754,13 @@
         </is>
       </c>
       <c r="N15">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="O15">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="P15">
-        <v>0</v>
+        <v>3.51</v>
       </c>
       <c r="Q15">
         <v>0</v>
@@ -2793,10 +2793,10 @@
         <v>0</v>
       </c>
       <c r="AA15">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AB15">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC15">
         <v>0</v>
@@ -2917,13 +2917,13 @@
         </is>
       </c>
       <c r="N16">
-        <v>0</v>
+        <v>2.91</v>
       </c>
       <c r="O16">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="P16">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="Q16">
         <v>0</v>
@@ -2956,10 +2956,10 @@
         <v>0</v>
       </c>
       <c r="AA16">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AB16">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AC16">
         <v>0</v>
@@ -3732,13 +3732,13 @@
         </is>
       </c>
       <c r="N21">
-        <v>0</v>
+        <v>3.46</v>
       </c>
       <c r="O21">
-        <v>0</v>
+        <v>3.92</v>
       </c>
       <c r="P21">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="Q21">
         <v>0</v>
@@ -4221,13 +4221,13 @@
         </is>
       </c>
       <c r="N24">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="O24">
-        <v>0</v>
+        <v>3.19</v>
       </c>
       <c r="P24">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="Q24">
         <v>0</v>
@@ -4384,13 +4384,13 @@
         </is>
       </c>
       <c r="N25">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="O25">
-        <v>0</v>
+        <v>3.72</v>
       </c>
       <c r="P25">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="Q25">
         <v>0</v>
@@ -4547,13 +4547,13 @@
         </is>
       </c>
       <c r="N26">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="O26">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="P26">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="Q26">
         <v>0</v>
@@ -6014,13 +6014,13 @@
         </is>
       </c>
       <c r="N35">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="O35">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="P35">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="Q35">
         <v>0</v>
@@ -8785,13 +8785,13 @@
         </is>
       </c>
       <c r="N52">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="O52">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="P52">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="Q52">
         <v>0</v>
@@ -8824,10 +8824,10 @@
         <v>0</v>
       </c>
       <c r="AA52">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AB52">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="AC52">
         <v>0</v>
@@ -10415,13 +10415,13 @@
         </is>
       </c>
       <c r="N62">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="O62">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="P62">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="Q62">
         <v>0</v>
@@ -10578,13 +10578,13 @@
         </is>
       </c>
       <c r="N63">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="O63">
-        <v>0</v>
+        <v>4.85</v>
       </c>
       <c r="P63">
-        <v>0</v>
+        <v>5.55</v>
       </c>
       <c r="Q63">
         <v>0</v>
@@ -10623,10 +10623,10 @@
         <v>0</v>
       </c>
       <c r="AC63">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AD63">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AE63">
         <v>0</v>
@@ -10709,12 +10709,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Lyn</t>
+          <t>Hødd</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Sogndal</t>
+          <t>Moss</t>
         </is>
       </c>
       <c r="G64">
@@ -10872,12 +10872,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Raufoss</t>
+          <t>Kongsvinger</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Stabæk</t>
+          <t>Strømmen</t>
         </is>
       </c>
       <c r="G65">
@@ -10904,13 +10904,13 @@
         </is>
       </c>
       <c r="N65">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="O65">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="P65">
-        <v>0</v>
+        <v>4.85</v>
       </c>
       <c r="Q65">
         <v>0</v>
@@ -10949,10 +10949,10 @@
         <v>0</v>
       </c>
       <c r="AC65">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AD65">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AE65">
         <v>0</v>
@@ -11035,12 +11035,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Hødd</t>
+          <t>Raufoss</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Moss</t>
+          <t>Stabæk</t>
         </is>
       </c>
       <c r="G66">
@@ -11198,12 +11198,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Kongsvinger</t>
+          <t>Lyn</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Strømmen</t>
+          <t>Sogndal</t>
         </is>
       </c>
       <c r="G67">
@@ -11230,13 +11230,13 @@
         </is>
       </c>
       <c r="N67">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="O67">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="P67">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="Q67">
         <v>0</v>
@@ -11275,10 +11275,10 @@
         <v>0</v>
       </c>
       <c r="AC67">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AD67">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AE67">
         <v>0</v>
@@ -12534,13 +12534,13 @@
         </is>
       </c>
       <c r="N75">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="O75">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="P75">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="Q75">
         <v>0</v>
@@ -14164,13 +14164,13 @@
         </is>
       </c>
       <c r="N85">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="O85">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="P85">
-        <v>0</v>
+        <v>14.5</v>
       </c>
       <c r="Q85">
         <v>0</v>
@@ -19217,13 +19217,13 @@
         </is>
       </c>
       <c r="N116">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="O116">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="P116">
-        <v>0</v>
+        <v>13.8</v>
       </c>
       <c r="Q116">
         <v>0</v>
@@ -19256,10 +19256,10 @@
         <v>0</v>
       </c>
       <c r="AA116">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AB116">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC116">
         <v>0</v>
@@ -19869,13 +19869,13 @@
         </is>
       </c>
       <c r="N120">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="O120">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="P120">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="Q120">
         <v>0</v>

--- a/jogos_2026-08-02.xlsx
+++ b/jogos_2026-08-02.xlsx
@@ -2885,12 +2885,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Ansan Greeners</t>
+          <t>Jeonnam Dragons</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Gimhae City</t>
+          <t>Paju Citizen</t>
         </is>
       </c>
       <c r="G16">
@@ -2917,13 +2917,13 @@
         </is>
       </c>
       <c r="N16">
-        <v>2.91</v>
+        <v>0</v>
       </c>
       <c r="O16">
-        <v>3.38</v>
+        <v>0</v>
       </c>
       <c r="P16">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="Q16">
         <v>0</v>
@@ -2956,10 +2956,10 @@
         <v>0</v>
       </c>
       <c r="AA16">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AB16">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AC16">
         <v>0</v>
@@ -3048,12 +3048,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Jeonnam Dragons</t>
+          <t>Ansan Greeners</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Paju Citizen</t>
+          <t>Gimhae City</t>
         </is>
       </c>
       <c r="G17">
@@ -3080,13 +3080,13 @@
         </is>
       </c>
       <c r="N17">
-        <v>0</v>
+        <v>2.91</v>
       </c>
       <c r="O17">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="P17">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="Q17">
         <v>0</v>
@@ -3119,10 +3119,10 @@
         <v>0</v>
       </c>
       <c r="AA17">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AB17">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AC17">
         <v>0</v>
@@ -10546,12 +10546,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Odd</t>
+          <t>Hødd</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Åsane</t>
+          <t>Moss</t>
         </is>
       </c>
       <c r="G63">
@@ -10578,13 +10578,13 @@
         </is>
       </c>
       <c r="N63">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="O63">
-        <v>4.85</v>
+        <v>0</v>
       </c>
       <c r="P63">
-        <v>5.55</v>
+        <v>0</v>
       </c>
       <c r="Q63">
         <v>0</v>
@@ -10623,10 +10623,10 @@
         <v>0</v>
       </c>
       <c r="AC63">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AD63">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AE63">
         <v>0</v>
@@ -10709,12 +10709,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Hødd</t>
+          <t>Kongsvinger</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Moss</t>
+          <t>Strømmen</t>
         </is>
       </c>
       <c r="G64">
@@ -10741,13 +10741,13 @@
         </is>
       </c>
       <c r="N64">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="O64">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="P64">
-        <v>0</v>
+        <v>4.85</v>
       </c>
       <c r="Q64">
         <v>0</v>
@@ -10786,10 +10786,10 @@
         <v>0</v>
       </c>
       <c r="AC64">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AD64">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AE64">
         <v>0</v>
@@ -10872,12 +10872,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Kongsvinger</t>
+          <t>Raufoss</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Strømmen</t>
+          <t>Stabæk</t>
         </is>
       </c>
       <c r="G65">
@@ -10904,13 +10904,13 @@
         </is>
       </c>
       <c r="N65">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="O65">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="P65">
-        <v>4.85</v>
+        <v>0</v>
       </c>
       <c r="Q65">
         <v>0</v>
@@ -10949,10 +10949,10 @@
         <v>0</v>
       </c>
       <c r="AC65">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AD65">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AE65">
         <v>0</v>
@@ -11035,12 +11035,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Raufoss</t>
+          <t>Lyn</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Stabæk</t>
+          <t>Sogndal</t>
         </is>
       </c>
       <c r="G66">
@@ -11067,13 +11067,13 @@
         </is>
       </c>
       <c r="N66">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="O66">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="P66">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="Q66">
         <v>0</v>
@@ -11112,10 +11112,10 @@
         <v>0</v>
       </c>
       <c r="AC66">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AD66">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AE66">
         <v>0</v>
@@ -11198,12 +11198,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Lyn</t>
+          <t>Odd</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Sogndal</t>
+          <t>Åsane</t>
         </is>
       </c>
       <c r="G67">
@@ -11230,13 +11230,13 @@
         </is>
       </c>
       <c r="N67">
-        <v>2.14</v>
+        <v>1.39</v>
       </c>
       <c r="O67">
-        <v>3.65</v>
+        <v>4.85</v>
       </c>
       <c r="P67">
-        <v>2.8</v>
+        <v>5.55</v>
       </c>
       <c r="Q67">
         <v>0</v>
@@ -11275,10 +11275,10 @@
         <v>0</v>
       </c>
       <c r="AC67">
-        <v>1.91</v>
+        <v>1.88</v>
       </c>
       <c r="AD67">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="AE67">
         <v>0</v>

--- a/jogos_2026-08-02.xlsx
+++ b/jogos_2026-08-02.xlsx
@@ -15957,13 +15957,13 @@
         </is>
       </c>
       <c r="N96">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="O96">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="P96">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Q96">
         <v>0</v>
@@ -15996,10 +15996,10 @@
         <v>0</v>
       </c>
       <c r="AA96">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AB96">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AC96">
         <v>0</v>

--- a/jogos_2026-08-02.xlsx
+++ b/jogos_2026-08-02.xlsx
@@ -8622,13 +8622,13 @@
         </is>
       </c>
       <c r="N51">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="O51">
-        <v>0</v>
+        <v>3.98</v>
       </c>
       <c r="P51">
-        <v>0</v>
+        <v>3.98</v>
       </c>
       <c r="Q51">
         <v>0</v>
@@ -11035,12 +11035,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Lyn</t>
+          <t>Odd</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Sogndal</t>
+          <t>Åsane</t>
         </is>
       </c>
       <c r="G66">
@@ -11067,13 +11067,13 @@
         </is>
       </c>
       <c r="N66">
-        <v>2.14</v>
+        <v>1.39</v>
       </c>
       <c r="O66">
-        <v>3.65</v>
+        <v>4.85</v>
       </c>
       <c r="P66">
-        <v>2.8</v>
+        <v>5.55</v>
       </c>
       <c r="Q66">
         <v>0</v>
@@ -11112,10 +11112,10 @@
         <v>0</v>
       </c>
       <c r="AC66">
-        <v>1.91</v>
+        <v>1.88</v>
       </c>
       <c r="AD66">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="AE66">
         <v>0</v>
@@ -11198,12 +11198,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Odd</t>
+          <t>Lyn</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Åsane</t>
+          <t>Sogndal</t>
         </is>
       </c>
       <c r="G67">
@@ -11230,13 +11230,13 @@
         </is>
       </c>
       <c r="N67">
-        <v>1.39</v>
+        <v>2.14</v>
       </c>
       <c r="O67">
-        <v>4.85</v>
+        <v>3.65</v>
       </c>
       <c r="P67">
-        <v>5.55</v>
+        <v>2.8</v>
       </c>
       <c r="Q67">
         <v>0</v>
@@ -11275,10 +11275,10 @@
         <v>0</v>
       </c>
       <c r="AC67">
-        <v>1.88</v>
+        <v>1.91</v>
       </c>
       <c r="AD67">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="AE67">
         <v>0</v>
@@ -13349,13 +13349,13 @@
         </is>
       </c>
       <c r="N80">
-        <v>0</v>
+        <v>3.78</v>
       </c>
       <c r="O80">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="P80">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="Q80">
         <v>0</v>
@@ -18728,13 +18728,13 @@
         </is>
       </c>
       <c r="N113">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="O113">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="P113">
-        <v>0</v>
+        <v>5.27</v>
       </c>
       <c r="Q113">
         <v>0</v>
@@ -18891,13 +18891,13 @@
         </is>
       </c>
       <c r="N114">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="O114">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="P114">
-        <v>0</v>
+        <v>3.88</v>
       </c>
       <c r="Q114">
         <v>0</v>
@@ -18930,10 +18930,10 @@
         <v>0</v>
       </c>
       <c r="AA114">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AB114">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AC114">
         <v>0</v>

--- a/jogos_2026-08-02.xlsx
+++ b/jogos_2026-08-02.xlsx
@@ -17587,13 +17587,13 @@
         </is>
       </c>
       <c r="N106">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="O106">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="P106">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="Q106">
         <v>0</v>

--- a/jogos_2026-08-02.xlsx
+++ b/jogos_2026-08-02.xlsx
@@ -8948,13 +8948,13 @@
         </is>
       </c>
       <c r="N53">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="O53">
-        <v>0</v>
+        <v>4.65</v>
       </c>
       <c r="P53">
-        <v>0</v>
+        <v>7.28</v>
       </c>
       <c r="Q53">
         <v>0</v>
@@ -9437,13 +9437,13 @@
         </is>
       </c>
       <c r="N56">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="O56">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="P56">
-        <v>0</v>
+        <v>5.73</v>
       </c>
       <c r="Q56">
         <v>0</v>
@@ -9600,13 +9600,13 @@
         </is>
       </c>
       <c r="N57">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="O57">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="P57">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="Q57">
         <v>0</v>
@@ -9763,13 +9763,13 @@
         </is>
       </c>
       <c r="N58">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="O58">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="P58">
-        <v>0</v>
+        <v>4.43</v>
       </c>
       <c r="Q58">
         <v>0</v>
@@ -15794,13 +15794,13 @@
         </is>
       </c>
       <c r="N95">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="O95">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="P95">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="Q95">
         <v>0</v>
@@ -16772,13 +16772,13 @@
         </is>
       </c>
       <c r="N101">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="O101">
-        <v>0</v>
+        <v>2.67</v>
       </c>
       <c r="P101">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="Q101">
         <v>0</v>
@@ -16805,10 +16805,10 @@
         <v>0</v>
       </c>
       <c r="Y101">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="Z101">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AA101">
         <v>0</v>
@@ -17098,13 +17098,13 @@
         </is>
       </c>
       <c r="N103">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="O103">
-        <v>0</v>
+        <v>2.76</v>
       </c>
       <c r="P103">
-        <v>0</v>
+        <v>3.77</v>
       </c>
       <c r="Q103">
         <v>0</v>
@@ -17131,10 +17131,10 @@
         <v>0</v>
       </c>
       <c r="Y103">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="Z103">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AA103">
         <v>0</v>
@@ -17261,13 +17261,13 @@
         </is>
       </c>
       <c r="N104">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="O104">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="P104">
-        <v>0</v>
+        <v>3.56</v>
       </c>
       <c r="Q104">
         <v>0</v>
@@ -17294,10 +17294,10 @@
         <v>0</v>
       </c>
       <c r="Y104">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="Z104">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AA104">
         <v>0</v>
@@ -19380,13 +19380,13 @@
         </is>
       </c>
       <c r="N117">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="O117">
-        <v>0</v>
+        <v>2.71</v>
       </c>
       <c r="P117">
-        <v>0</v>
+        <v>3.26</v>
       </c>
       <c r="Q117">
         <v>0</v>
@@ -19413,10 +19413,10 @@
         <v>0</v>
       </c>
       <c r="Y117">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="Z117">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AA117">
         <v>0</v>
@@ -19543,13 +19543,13 @@
         </is>
       </c>
       <c r="N118">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="O118">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="P118">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="Q118">
         <v>0</v>
@@ -19576,10 +19576,10 @@
         <v>0</v>
       </c>
       <c r="Y118">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="Z118">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AA118">
         <v>0</v>
@@ -20521,13 +20521,13 @@
         </is>
       </c>
       <c r="N124">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="O124">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="P124">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="Q124">
         <v>0</v>
@@ -20554,10 +20554,10 @@
         <v>0</v>
       </c>
       <c r="Y124">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="Z124">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AA124">
         <v>0</v>
@@ -20684,13 +20684,13 @@
         </is>
       </c>
       <c r="N125">
-        <v>0</v>
+        <v>3.26</v>
       </c>
       <c r="O125">
-        <v>0</v>
+        <v>2.67</v>
       </c>
       <c r="P125">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="Q125">
         <v>0</v>
@@ -20717,10 +20717,10 @@
         <v>0</v>
       </c>
       <c r="Y125">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="Z125">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AA125">
         <v>0</v>
@@ -20847,13 +20847,13 @@
         </is>
       </c>
       <c r="N126">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="O126">
-        <v>0</v>
+        <v>2.71</v>
       </c>
       <c r="P126">
-        <v>0</v>
+        <v>3.87</v>
       </c>
       <c r="Q126">
         <v>0</v>
@@ -20880,10 +20880,10 @@
         <v>0</v>
       </c>
       <c r="Y126">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="Z126">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AA126">
         <v>0</v>
@@ -21173,13 +21173,13 @@
         </is>
       </c>
       <c r="N128">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="O128">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="P128">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="Q128">
         <v>0</v>
@@ -21206,10 +21206,10 @@
         <v>0</v>
       </c>
       <c r="Y128">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="Z128">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AA128">
         <v>0</v>
@@ -22803,13 +22803,13 @@
         </is>
       </c>
       <c r="N138">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="O138">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="P138">
-        <v>0</v>
+        <v>3.67</v>
       </c>
       <c r="Q138">
         <v>0</v>

--- a/jogos_2026-08-02.xlsx
+++ b/jogos_2026-08-02.xlsx
@@ -2722,12 +2722,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Gimpo Citizen</t>
+          <t>Ansan Greeners</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Gyeongnam</t>
+          <t>Gimhae City</t>
         </is>
       </c>
       <c r="G15">
@@ -2754,13 +2754,13 @@
         </is>
       </c>
       <c r="N15">
-        <v>1.94</v>
+        <v>2.91</v>
       </c>
       <c r="O15">
-        <v>3.34</v>
+        <v>3.38</v>
       </c>
       <c r="P15">
-        <v>3.51</v>
+        <v>2.18</v>
       </c>
       <c r="Q15">
         <v>0</v>
@@ -2793,10 +2793,10 @@
         <v>0</v>
       </c>
       <c r="AA15">
-        <v>1.95</v>
+        <v>1.81</v>
       </c>
       <c r="AB15">
-        <v>1.75</v>
+        <v>1.88</v>
       </c>
       <c r="AC15">
         <v>0</v>
@@ -2885,12 +2885,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Jeonnam Dragons</t>
+          <t>Gimpo Citizen</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Paju Citizen</t>
+          <t>Gyeongnam</t>
         </is>
       </c>
       <c r="G16">
@@ -2917,13 +2917,13 @@
         </is>
       </c>
       <c r="N16">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="O16">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="P16">
-        <v>0</v>
+        <v>3.51</v>
       </c>
       <c r="Q16">
         <v>0</v>
@@ -2956,10 +2956,10 @@
         <v>0</v>
       </c>
       <c r="AA16">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AB16">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC16">
         <v>0</v>
@@ -3048,12 +3048,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Ansan Greeners</t>
+          <t>Jeonnam Dragons</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Gimhae City</t>
+          <t>Paju Citizen</t>
         </is>
       </c>
       <c r="G17">
@@ -3080,13 +3080,13 @@
         </is>
       </c>
       <c r="N17">
-        <v>2.91</v>
+        <v>0</v>
       </c>
       <c r="O17">
-        <v>3.38</v>
+        <v>0</v>
       </c>
       <c r="P17">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="Q17">
         <v>0</v>
@@ -3119,10 +3119,10 @@
         <v>0</v>
       </c>
       <c r="AA17">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AB17">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AC17">
         <v>0</v>
@@ -3374,12 +3374,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Suzhou Dongwu</t>
+          <t>Shenzhen Juniors</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Meizhou Hakka</t>
+          <t>Wuxi Wugou</t>
         </is>
       </c>
       <c r="G19">
@@ -3537,12 +3537,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Shenzhen Juniors</t>
+          <t>Suzhou Dongwu</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Wuxi Wugou</t>
+          <t>Meizhou Hakka</t>
         </is>
       </c>
       <c r="G20">
@@ -5036,13 +5036,13 @@
         </is>
       </c>
       <c r="N29">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="O29">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="P29">
-        <v>0</v>
+        <v>7.24</v>
       </c>
       <c r="Q29">
         <v>0</v>
@@ -5199,13 +5199,13 @@
         </is>
       </c>
       <c r="N30">
-        <v>0</v>
+        <v>4.43</v>
       </c>
       <c r="O30">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="P30">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="Q30">
         <v>0</v>
@@ -6829,13 +6829,13 @@
         </is>
       </c>
       <c r="N40">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="O40">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="P40">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="Q40">
         <v>0</v>
@@ -11393,13 +11393,13 @@
         </is>
       </c>
       <c r="N68">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="O68">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="P68">
-        <v>0</v>
+        <v>4.63</v>
       </c>
       <c r="Q68">
         <v>0</v>

--- a/jogos_2026-08-02.xlsx
+++ b/jogos_2026-08-02.xlsx
@@ -4058,13 +4058,13 @@
         </is>
       </c>
       <c r="N23">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="O23">
-        <v>0</v>
+        <v>3.76</v>
       </c>
       <c r="P23">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="Q23">
         <v>0</v>
@@ -4103,10 +4103,10 @@
         <v>0</v>
       </c>
       <c r="AC23">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AD23">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AE23">
         <v>0</v>
@@ -7318,13 +7318,13 @@
         </is>
       </c>
       <c r="N43">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="O43">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="P43">
-        <v>0</v>
+        <v>4.59</v>
       </c>
       <c r="Q43">
         <v>0</v>
@@ -16446,13 +16446,13 @@
         </is>
       </c>
       <c r="N99">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="O99">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="P99">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="Q99">
         <v>0</v>
@@ -16609,13 +16609,13 @@
         </is>
       </c>
       <c r="N100">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="O100">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="P100">
-        <v>0</v>
+        <v>6.28</v>
       </c>
       <c r="Q100">
         <v>0</v>
@@ -18565,13 +18565,13 @@
         </is>
       </c>
       <c r="N112">
-        <v>0</v>
+        <v>6.11</v>
       </c>
       <c r="O112">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="P112">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="Q112">
         <v>0</v>
@@ -18604,10 +18604,10 @@
         <v>0</v>
       </c>
       <c r="AA112">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AB112">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AC112">
         <v>0</v>
@@ -22151,13 +22151,13 @@
         </is>
       </c>
       <c r="N134">
-        <v>0</v>
+        <v>4.37</v>
       </c>
       <c r="O134">
-        <v>0</v>
+        <v>3.72</v>
       </c>
       <c r="P134">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="Q134">
         <v>0</v>

--- a/jogos_2026-08-02.xlsx
+++ b/jogos_2026-08-02.xlsx
@@ -10578,13 +10578,13 @@
         </is>
       </c>
       <c r="N63">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="O63">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="P63">
-        <v>0</v>
+        <v>3.13</v>
       </c>
       <c r="Q63">
         <v>0</v>
@@ -10623,10 +10623,10 @@
         <v>0</v>
       </c>
       <c r="AC63">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AD63">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AE63">
         <v>0</v>
@@ -10904,13 +10904,13 @@
         </is>
       </c>
       <c r="N65">
-        <v>0</v>
+        <v>4.79</v>
       </c>
       <c r="O65">
-        <v>0</v>
+        <v>4.55</v>
       </c>
       <c r="P65">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="Q65">
         <v>0</v>
@@ -10949,10 +10949,10 @@
         <v>0</v>
       </c>
       <c r="AC65">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AD65">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AE65">
         <v>0</v>
@@ -21499,13 +21499,13 @@
         </is>
       </c>
       <c r="N130">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="O130">
-        <v>0</v>
+        <v>3.61</v>
       </c>
       <c r="P130">
-        <v>0</v>
+        <v>5.34</v>
       </c>
       <c r="Q130">
         <v>0</v>

--- a/jogos_2026-08-02.xlsx
+++ b/jogos_2026-08-02.xlsx
@@ -5525,13 +5525,13 @@
         </is>
       </c>
       <c r="N32">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="O32">
-        <v>0</v>
+        <v>3.98</v>
       </c>
       <c r="P32">
-        <v>0</v>
+        <v>5.59</v>
       </c>
       <c r="Q32">
         <v>0</v>
@@ -5564,10 +5564,10 @@
         <v>0</v>
       </c>
       <c r="AA32">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AB32">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AC32">
         <v>0</v>
@@ -16935,13 +16935,13 @@
         </is>
       </c>
       <c r="N102">
-        <v>0</v>
+        <v>2.76</v>
       </c>
       <c r="O102">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="P102">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="Q102">
         <v>0</v>
@@ -16968,10 +16968,10 @@
         <v>0</v>
       </c>
       <c r="Y102">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="Z102">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AA102">
         <v>0</v>
@@ -19706,13 +19706,13 @@
         </is>
       </c>
       <c r="N119">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="O119">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="P119">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="Q119">
         <v>0</v>
@@ -19739,10 +19739,10 @@
         <v>0</v>
       </c>
       <c r="Y119">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="Z119">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AA119">
         <v>0</v>

--- a/jogos_2026-08-02.xlsx
+++ b/jogos_2026-08-02.xlsx
@@ -340,7 +340,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AU138"/>
+  <dimension ref="A1:AU139"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -644,55 +644,55 @@
         <v>8.050000000000001</v>
       </c>
       <c r="Q2">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="S2">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="T2">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="U2">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="V2">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="W2">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X2">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y2">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="Z2">
-        <v>0</v>
+        <v>4.98</v>
       </c>
       <c r="AA2">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AB2">
-        <v>0</v>
+        <v>2.51</v>
       </c>
       <c r="AC2">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="AD2">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AE2">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AF2">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AG2">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
@@ -705,10 +705,10 @@
         </is>
       </c>
       <c r="AJ2">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AK2">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -2885,12 +2885,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Gimpo Citizen</t>
+          <t>Jeonnam Dragons</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Gyeongnam</t>
+          <t>Paju Citizen</t>
         </is>
       </c>
       <c r="G16">
@@ -2917,13 +2917,13 @@
         </is>
       </c>
       <c r="N16">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="O16">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="P16">
-        <v>3.51</v>
+        <v>0</v>
       </c>
       <c r="Q16">
         <v>0</v>
@@ -2956,10 +2956,10 @@
         <v>0</v>
       </c>
       <c r="AA16">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AB16">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AC16">
         <v>0</v>
@@ -3048,12 +3048,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Jeonnam Dragons</t>
+          <t>Gimpo Citizen</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Paju Citizen</t>
+          <t>Gyeongnam</t>
         </is>
       </c>
       <c r="G17">
@@ -3080,13 +3080,13 @@
         </is>
       </c>
       <c r="N17">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="O17">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="P17">
-        <v>0</v>
+        <v>3.51</v>
       </c>
       <c r="Q17">
         <v>0</v>
@@ -3119,10 +3119,10 @@
         <v>0</v>
       </c>
       <c r="AA17">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AB17">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC17">
         <v>0</v>
@@ -7938,12 +7938,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>KÍ</t>
+          <t>EB - Streymur</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>B36</t>
+          <t>Víkingur</t>
         </is>
       </c>
       <c r="G47">
@@ -8101,12 +8101,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>EB - Streymur</t>
+          <t>KÍ</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Víkingur</t>
+          <t>B36</t>
         </is>
       </c>
       <c r="G48">
@@ -10872,12 +10872,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Raufoss</t>
+          <t>Odd</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Stabæk</t>
+          <t>Åsane</t>
         </is>
       </c>
       <c r="G65">
@@ -10904,13 +10904,13 @@
         </is>
       </c>
       <c r="N65">
-        <v>4.79</v>
+        <v>1.39</v>
       </c>
       <c r="O65">
-        <v>4.55</v>
+        <v>4.85</v>
       </c>
       <c r="P65">
-        <v>1.55</v>
+        <v>5.55</v>
       </c>
       <c r="Q65">
         <v>0</v>
@@ -10949,10 +10949,10 @@
         <v>0</v>
       </c>
       <c r="AC65">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="AD65">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="AE65">
         <v>0</v>
@@ -11035,12 +11035,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Odd</t>
+          <t>Lyn</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Åsane</t>
+          <t>Sogndal</t>
         </is>
       </c>
       <c r="G66">
@@ -11067,13 +11067,13 @@
         </is>
       </c>
       <c r="N66">
-        <v>1.39</v>
+        <v>2.14</v>
       </c>
       <c r="O66">
-        <v>4.85</v>
+        <v>3.65</v>
       </c>
       <c r="P66">
-        <v>5.55</v>
+        <v>2.8</v>
       </c>
       <c r="Q66">
         <v>0</v>
@@ -11112,10 +11112,10 @@
         <v>0</v>
       </c>
       <c r="AC66">
-        <v>1.88</v>
+        <v>1.91</v>
       </c>
       <c r="AD66">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="AE66">
         <v>0</v>
@@ -11198,12 +11198,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Lyn</t>
+          <t>Raufoss</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Sogndal</t>
+          <t>Stabæk</t>
         </is>
       </c>
       <c r="G67">
@@ -11230,13 +11230,13 @@
         </is>
       </c>
       <c r="N67">
-        <v>2.14</v>
+        <v>4.79</v>
       </c>
       <c r="O67">
-        <v>3.65</v>
+        <v>4.55</v>
       </c>
       <c r="P67">
-        <v>2.8</v>
+        <v>1.55</v>
       </c>
       <c r="Q67">
         <v>0</v>
@@ -11275,10 +11275,10 @@
         <v>0</v>
       </c>
       <c r="AC67">
-        <v>1.91</v>
+        <v>1.87</v>
       </c>
       <c r="AD67">
-        <v>1.85</v>
+        <v>1.81</v>
       </c>
       <c r="AE67">
         <v>0</v>
@@ -15589,7 +15589,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -15599,12 +15599,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Csákvári TK</t>
+          <t>Napredak</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Nagykanizsai TE</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="G94">
@@ -15747,27 +15747,27 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Brann</t>
+          <t>Csákvári TK</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Rosenborg</t>
+          <t>Nagykanizsai TE</t>
         </is>
       </c>
       <c r="G95">
@@ -15794,13 +15794,13 @@
         </is>
       </c>
       <c r="N95">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="O95">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="P95">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="Q95">
         <v>0</v>
@@ -15898,7 +15898,7 @@
       </c>
       <c r="AU95" t="inlineStr">
         <is>
-          <t>2026-08-02 14:15:00</t>
+          <t>2026-08-02 14:00:00</t>
         </is>
       </c>
     </row>
@@ -15910,27 +15910,27 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Pogoń Grod. Mazowiecki</t>
+          <t>Brann</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Puszcza Niepołomice</t>
+          <t>Rosenborg</t>
         </is>
       </c>
       <c r="G96">
@@ -15957,13 +15957,13 @@
         </is>
       </c>
       <c r="N96">
-        <v>2.6</v>
+        <v>1.71</v>
       </c>
       <c r="O96">
-        <v>3.05</v>
+        <v>4.2</v>
       </c>
       <c r="P96">
-        <v>2.5</v>
+        <v>4.5</v>
       </c>
       <c r="Q96">
         <v>0</v>
@@ -15996,10 +15996,10 @@
         <v>0</v>
       </c>
       <c r="AA96">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AB96">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AC96">
         <v>0</v>
@@ -16061,7 +16061,7 @@
       </c>
       <c r="AU96" t="inlineStr">
         <is>
-          <t>2026-08-02 14:30:00</t>
+          <t>2026-08-02 14:15:00</t>
         </is>
       </c>
     </row>
@@ -16078,7 +16078,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -16088,12 +16088,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Akhmat Grozny</t>
+          <t>Pogoń Grod. Mazowiecki</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Spartak Moskva</t>
+          <t>Puszcza Niepołomice</t>
         </is>
       </c>
       <c r="G97">
@@ -16120,13 +16120,13 @@
         </is>
       </c>
       <c r="N97">
-        <v>3.5</v>
+        <v>2.6</v>
       </c>
       <c r="O97">
-        <v>3.67</v>
+        <v>3.05</v>
       </c>
       <c r="P97">
-        <v>2.19</v>
+        <v>2.5</v>
       </c>
       <c r="Q97">
         <v>0</v>
@@ -16159,10 +16159,10 @@
         <v>0</v>
       </c>
       <c r="AA97">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AB97">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AC97">
         <v>0</v>
@@ -16236,27 +16236,27 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Akhmat Grozny</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Spartak Moskva</t>
         </is>
       </c>
       <c r="G98">
@@ -16283,13 +16283,13 @@
         </is>
       </c>
       <c r="N98">
-        <v>1.54</v>
+        <v>3.5</v>
       </c>
       <c r="O98">
-        <v>4.2</v>
+        <v>3.67</v>
       </c>
       <c r="P98">
-        <v>5.33</v>
+        <v>2.19</v>
       </c>
       <c r="Q98">
         <v>0</v>
@@ -16387,7 +16387,7 @@
       </c>
       <c r="AU98" t="inlineStr">
         <is>
-          <t>2026-08-02 15:00:00</t>
+          <t>2026-08-02 14:30:00</t>
         </is>
       </c>
     </row>
@@ -16404,22 +16404,22 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Zemun</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Radnički Niš</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="G99">
@@ -16446,13 +16446,13 @@
         </is>
       </c>
       <c r="N99">
-        <v>2.46</v>
+        <v>1.54</v>
       </c>
       <c r="O99">
-        <v>3.14</v>
+        <v>4.2</v>
       </c>
       <c r="P99">
-        <v>2.59</v>
+        <v>5.33</v>
       </c>
       <c r="Q99">
         <v>0</v>
@@ -16577,12 +16577,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Partizan</t>
+          <t>Zemun</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>IMT Novi Beograd</t>
+          <t>Radnički Niš</t>
         </is>
       </c>
       <c r="G100">
@@ -16609,13 +16609,13 @@
         </is>
       </c>
       <c r="N100">
-        <v>1.43</v>
+        <v>2.46</v>
       </c>
       <c r="O100">
-        <v>4.15</v>
+        <v>3.14</v>
       </c>
       <c r="P100">
-        <v>6.28</v>
+        <v>2.59</v>
       </c>
       <c r="Q100">
         <v>0</v>
@@ -16730,22 +16730,22 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Partizan</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>San Miguel</t>
+          <t>IMT Novi Beograd</t>
         </is>
       </c>
       <c r="G101">
@@ -16772,13 +16772,13 @@
         </is>
       </c>
       <c r="N101">
-        <v>2.66</v>
+        <v>1.43</v>
       </c>
       <c r="O101">
-        <v>2.67</v>
+        <v>4.15</v>
       </c>
       <c r="P101">
-        <v>2.78</v>
+        <v>6.28</v>
       </c>
       <c r="Q101">
         <v>0</v>
@@ -16805,10 +16805,10 @@
         <v>0</v>
       </c>
       <c r="Y101">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="Z101">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AA101">
         <v>0</v>
@@ -16903,12 +16903,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Midland</t>
+          <t>San Miguel</t>
         </is>
       </c>
       <c r="G102">
@@ -16935,13 +16935,13 @@
         </is>
       </c>
       <c r="N102">
-        <v>2.76</v>
+        <v>2.66</v>
       </c>
       <c r="O102">
-        <v>2.7</v>
+        <v>2.67</v>
       </c>
       <c r="P102">
-        <v>2.65</v>
+        <v>2.78</v>
       </c>
       <c r="Q102">
         <v>0</v>
@@ -16968,7 +16968,7 @@
         <v>0</v>
       </c>
       <c r="Y102">
-        <v>1.65</v>
+        <v>1.63</v>
       </c>
       <c r="Z102">
         <v>2.1</v>
@@ -17066,12 +17066,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Ciudad de Bolívar</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Club Atlético Mitre</t>
+          <t>Midland</t>
         </is>
       </c>
       <c r="G103">
@@ -17098,13 +17098,13 @@
         </is>
       </c>
       <c r="N103">
-        <v>2.12</v>
+        <v>2.76</v>
       </c>
       <c r="O103">
-        <v>2.76</v>
+        <v>2.7</v>
       </c>
       <c r="P103">
-        <v>3.77</v>
+        <v>2.65</v>
       </c>
       <c r="Q103">
         <v>0</v>
@@ -17229,12 +17229,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Almirante Brown</t>
+          <t>Ciudad de Bolívar</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Racing Córdoba</t>
+          <t>Club Atlético Mitre</t>
         </is>
       </c>
       <c r="G104">
@@ -17261,13 +17261,13 @@
         </is>
       </c>
       <c r="N104">
-        <v>2.22</v>
+        <v>2.12</v>
       </c>
       <c r="O104">
-        <v>2.72</v>
+        <v>2.76</v>
       </c>
       <c r="P104">
-        <v>3.56</v>
+        <v>3.77</v>
       </c>
       <c r="Q104">
         <v>0</v>
@@ -17294,10 +17294,10 @@
         <v>0</v>
       </c>
       <c r="Y104">
-        <v>1.72</v>
+        <v>1.65</v>
       </c>
       <c r="Z104">
-        <v>1.96</v>
+        <v>2.1</v>
       </c>
       <c r="AA104">
         <v>0</v>
@@ -17382,22 +17382,22 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Pardubice</t>
+          <t>Almirante Brown</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Jablonec</t>
+          <t>Racing Córdoba</t>
         </is>
       </c>
       <c r="G105">
@@ -17424,13 +17424,13 @@
         </is>
       </c>
       <c r="N105">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="O105">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="P105">
-        <v>0</v>
+        <v>3.56</v>
       </c>
       <c r="Q105">
         <v>0</v>
@@ -17457,10 +17457,10 @@
         <v>0</v>
       </c>
       <c r="Y105">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="Z105">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AA105">
         <v>0</v>
@@ -17545,22 +17545,22 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>CSD Independiente del Valle</t>
+          <t>Pardubice</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Deportivo Cuenca</t>
+          <t>Jablonec</t>
         </is>
       </c>
       <c r="G106">
@@ -17587,13 +17587,13 @@
         </is>
       </c>
       <c r="N106">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="O106">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="P106">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="Q106">
         <v>0</v>
@@ -17708,22 +17708,22 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Sutjeska</t>
+          <t>CSD Independiente del Valle</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Budućnost</t>
+          <t>Deportivo Cuenca</t>
         </is>
       </c>
       <c r="G107">
@@ -17750,13 +17750,13 @@
         </is>
       </c>
       <c r="N107">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="O107">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="P107">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="Q107">
         <v>0</v>
@@ -17881,12 +17881,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>FK Jezero Plav</t>
+          <t>Sutjeska</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Mornar</t>
+          <t>Budućnost</t>
         </is>
       </c>
       <c r="G108">
@@ -18044,12 +18044,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Petrovac</t>
+          <t>FK Jezero Plav</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Bokelj</t>
+          <t>Mornar</t>
         </is>
       </c>
       <c r="G109">
@@ -18207,12 +18207,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Dečić</t>
+          <t>Petrovac</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Arsenal Tivat</t>
+          <t>Bokelj</t>
         </is>
       </c>
       <c r="G110">
@@ -18370,12 +18370,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Mladost DG</t>
+          <t>Dečić</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Otrant-Olympic</t>
+          <t>Arsenal Tivat</t>
         </is>
       </c>
       <c r="G111">
@@ -18518,12 +18518,12 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -18533,12 +18533,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Brinje-Grosuplje</t>
+          <t>Mladost DG</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Koper</t>
+          <t>Otrant-Olympic</t>
         </is>
       </c>
       <c r="G112">
@@ -18565,13 +18565,13 @@
         </is>
       </c>
       <c r="N112">
-        <v>6.11</v>
+        <v>0</v>
       </c>
       <c r="O112">
-        <v>4.15</v>
+        <v>0</v>
       </c>
       <c r="P112">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="Q112">
         <v>0</v>
@@ -18604,10 +18604,10 @@
         <v>0</v>
       </c>
       <c r="AA112">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AB112">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AC112">
         <v>0</v>
@@ -18669,7 +18669,7 @@
       </c>
       <c r="AU112" t="inlineStr">
         <is>
-          <t>2026-08-02 15:15:00</t>
+          <t>2026-08-02 15:00:00</t>
         </is>
       </c>
     </row>
@@ -18696,12 +18696,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Olimpija</t>
+          <t>Brinje-Grosuplje</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Aluminij</t>
+          <t>Koper</t>
         </is>
       </c>
       <c r="G113">
@@ -18728,13 +18728,13 @@
         </is>
       </c>
       <c r="N113">
-        <v>1.51</v>
+        <v>6.11</v>
       </c>
       <c r="O113">
-        <v>4.05</v>
+        <v>4.15</v>
       </c>
       <c r="P113">
-        <v>5.27</v>
+        <v>1.44</v>
       </c>
       <c r="Q113">
         <v>0</v>
@@ -18767,10 +18767,10 @@
         <v>0</v>
       </c>
       <c r="AA113">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AB113">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AC113">
         <v>0</v>
@@ -18849,7 +18849,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -18859,12 +18859,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>GKS Katowice</t>
+          <t>Olimpija</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Radomiak Radom</t>
+          <t>Aluminij</t>
         </is>
       </c>
       <c r="G114">
@@ -18891,13 +18891,13 @@
         </is>
       </c>
       <c r="N114">
-        <v>1.88</v>
+        <v>1.51</v>
       </c>
       <c r="O114">
-        <v>3.52</v>
+        <v>4.05</v>
       </c>
       <c r="P114">
-        <v>3.88</v>
+        <v>5.27</v>
       </c>
       <c r="Q114">
         <v>0</v>
@@ -18930,10 +18930,10 @@
         <v>0</v>
       </c>
       <c r="AA114">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AB114">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AC114">
         <v>0</v>
@@ -19012,7 +19012,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -19022,12 +19022,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Ferencváros</t>
+          <t>GKS Katowice</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Vasas</t>
+          <t>Radomiak Radom</t>
         </is>
       </c>
       <c r="G115">
@@ -19054,13 +19054,13 @@
         </is>
       </c>
       <c r="N115">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="O115">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="P115">
-        <v>0</v>
+        <v>3.88</v>
       </c>
       <c r="Q115">
         <v>0</v>
@@ -19093,10 +19093,10 @@
         <v>0</v>
       </c>
       <c r="AA115">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AB115">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AC115">
         <v>0</v>
@@ -19175,7 +19175,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -19185,12 +19185,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>CSKA Sofia</t>
+          <t>Ferencváros</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Dunav 2010</t>
+          <t>Vasas</t>
         </is>
       </c>
       <c r="G116">
@@ -19217,13 +19217,13 @@
         </is>
       </c>
       <c r="N116">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="O116">
-        <v>5.3</v>
+        <v>0</v>
       </c>
       <c r="P116">
-        <v>13.8</v>
+        <v>0</v>
       </c>
       <c r="Q116">
         <v>0</v>
@@ -19256,10 +19256,10 @@
         <v>0</v>
       </c>
       <c r="AA116">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AB116">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AC116">
         <v>0</v>
@@ -19333,27 +19333,27 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Patronato</t>
+          <t>CSKA Sofia</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Quilmes</t>
+          <t>Dunav 2010</t>
         </is>
       </c>
       <c r="G117">
@@ -19380,13 +19380,13 @@
         </is>
       </c>
       <c r="N117">
-        <v>2.36</v>
+        <v>1.23</v>
       </c>
       <c r="O117">
-        <v>2.71</v>
+        <v>5.3</v>
       </c>
       <c r="P117">
-        <v>3.26</v>
+        <v>13.8</v>
       </c>
       <c r="Q117">
         <v>0</v>
@@ -19413,16 +19413,16 @@
         <v>0</v>
       </c>
       <c r="Y117">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="Z117">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AA117">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AB117">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC117">
         <v>0</v>
@@ -19484,7 +19484,7 @@
       </c>
       <c r="AU117" t="inlineStr">
         <is>
-          <t>2026-08-02 15:30:00</t>
+          <t>2026-08-02 15:15:00</t>
         </is>
       </c>
     </row>
@@ -19511,12 +19511,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Temperley</t>
+          <t>Patronato</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Gimnasia y Tiro</t>
+          <t>Quilmes</t>
         </is>
       </c>
       <c r="G118">
@@ -19543,43 +19543,43 @@
         </is>
       </c>
       <c r="N118">
+        <v>2.36</v>
+      </c>
+      <c r="O118">
+        <v>2.71</v>
+      </c>
+      <c r="P118">
+        <v>3.26</v>
+      </c>
+      <c r="Q118">
+        <v>0</v>
+      </c>
+      <c r="R118">
+        <v>0</v>
+      </c>
+      <c r="S118">
+        <v>0</v>
+      </c>
+      <c r="T118">
+        <v>0</v>
+      </c>
+      <c r="U118">
+        <v>0</v>
+      </c>
+      <c r="V118">
+        <v>0</v>
+      </c>
+      <c r="W118">
+        <v>0</v>
+      </c>
+      <c r="X118">
+        <v>0</v>
+      </c>
+      <c r="Y118">
+        <v>1.72</v>
+      </c>
+      <c r="Z118">
         <v>1.96</v>
-      </c>
-      <c r="O118">
-        <v>2.85</v>
-      </c>
-      <c r="P118">
-        <v>4.2</v>
-      </c>
-      <c r="Q118">
-        <v>0</v>
-      </c>
-      <c r="R118">
-        <v>0</v>
-      </c>
-      <c r="S118">
-        <v>0</v>
-      </c>
-      <c r="T118">
-        <v>0</v>
-      </c>
-      <c r="U118">
-        <v>0</v>
-      </c>
-      <c r="V118">
-        <v>0</v>
-      </c>
-      <c r="W118">
-        <v>0</v>
-      </c>
-      <c r="X118">
-        <v>0</v>
-      </c>
-      <c r="Y118">
-        <v>1.6</v>
-      </c>
-      <c r="Z118">
-        <v>2.15</v>
       </c>
       <c r="AA118">
         <v>0</v>
@@ -19674,12 +19674,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Deportivo Maipú</t>
+          <t>Temperley</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Atlanta</t>
+          <t>Gimnasia y Tiro</t>
         </is>
       </c>
       <c r="G119">
@@ -19706,13 +19706,13 @@
         </is>
       </c>
       <c r="N119">
-        <v>2.75</v>
+        <v>1.96</v>
       </c>
       <c r="O119">
-        <v>2.73</v>
+        <v>2.85</v>
       </c>
       <c r="P119">
-        <v>2.63</v>
+        <v>4.2</v>
       </c>
       <c r="Q119">
         <v>0</v>
@@ -19739,10 +19739,10 @@
         <v>0</v>
       </c>
       <c r="Y119">
-        <v>1.55</v>
+        <v>1.6</v>
       </c>
       <c r="Z119">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="AA119">
         <v>0</v>
@@ -19827,22 +19827,22 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Rapid Bucureşti</t>
+          <t>Deportivo Maipú</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>CFR Cluj</t>
+          <t>Atlanta</t>
         </is>
       </c>
       <c r="G120">
@@ -19869,13 +19869,13 @@
         </is>
       </c>
       <c r="N120">
-        <v>2.16</v>
+        <v>2.75</v>
       </c>
       <c r="O120">
-        <v>3.24</v>
+        <v>2.73</v>
       </c>
       <c r="P120">
-        <v>3.32</v>
+        <v>2.63</v>
       </c>
       <c r="Q120">
         <v>0</v>
@@ -19902,10 +19902,10 @@
         <v>0</v>
       </c>
       <c r="Y120">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="Z120">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AA120">
         <v>0</v>
@@ -19985,27 +19985,27 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Recoleta</t>
+          <t>Rapid Bucureşti</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Puerto Montt</t>
+          <t>CFR Cluj</t>
         </is>
       </c>
       <c r="G121">
@@ -20032,13 +20032,13 @@
         </is>
       </c>
       <c r="N121">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="O121">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="P121">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="Q121">
         <v>0</v>
@@ -20136,7 +20136,7 @@
       </c>
       <c r="AU121" t="inlineStr">
         <is>
-          <t>2026-08-02 16:00:00</t>
+          <t>2026-08-02 15:30:00</t>
         </is>
       </c>
     </row>
@@ -20153,7 +20153,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -20163,12 +20163,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>La Serena</t>
+          <t>Recoleta</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Puerto Montt</t>
         </is>
       </c>
       <c r="G122">
@@ -20316,7 +20316,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -20326,12 +20326,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Real Potosí</t>
+          <t>La Serena</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Gualberto Villarroel SJ</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="G123">
@@ -20479,7 +20479,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -20489,12 +20489,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Chaco For Ever</t>
+          <t>Real Potosí</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Deportivo Morón</t>
+          <t>Gualberto Villarroel SJ</t>
         </is>
       </c>
       <c r="G124">
@@ -20521,13 +20521,13 @@
         </is>
       </c>
       <c r="N124">
-        <v>2.72</v>
+        <v>0</v>
       </c>
       <c r="O124">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="P124">
-        <v>2.69</v>
+        <v>0</v>
       </c>
       <c r="Q124">
         <v>0</v>
@@ -20554,10 +20554,10 @@
         <v>0</v>
       </c>
       <c r="Y124">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="Z124">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AA124">
         <v>0</v>
@@ -20652,12 +20652,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Club Atlético Güemes</t>
+          <t>Chaco For Ever</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Tristán Suárez</t>
+          <t>Deportivo Morón</t>
         </is>
       </c>
       <c r="G125">
@@ -20684,13 +20684,13 @@
         </is>
       </c>
       <c r="N125">
-        <v>3.26</v>
+        <v>2.72</v>
       </c>
       <c r="O125">
-        <v>2.67</v>
+        <v>2.7</v>
       </c>
       <c r="P125">
-        <v>2.4</v>
+        <v>2.69</v>
       </c>
       <c r="Q125">
         <v>0</v>
@@ -20717,10 +20717,10 @@
         <v>0</v>
       </c>
       <c r="Y125">
-        <v>1.71</v>
+        <v>1.58</v>
       </c>
       <c r="Z125">
-        <v>1.98</v>
+        <v>2.2</v>
       </c>
       <c r="AA125">
         <v>0</v>
@@ -20815,12 +20815,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Deportivo Madryn</t>
+          <t>Club Atlético Güemes</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>All Boys</t>
+          <t>Tristán Suárez</t>
         </is>
       </c>
       <c r="G126">
@@ -20847,13 +20847,13 @@
         </is>
       </c>
       <c r="N126">
-        <v>2.12</v>
+        <v>3.26</v>
       </c>
       <c r="O126">
-        <v>2.71</v>
+        <v>2.67</v>
       </c>
       <c r="P126">
-        <v>3.87</v>
+        <v>2.4</v>
       </c>
       <c r="Q126">
         <v>0</v>
@@ -20880,10 +20880,10 @@
         <v>0</v>
       </c>
       <c r="Y126">
-        <v>1.63</v>
+        <v>1.71</v>
       </c>
       <c r="Z126">
-        <v>2.1</v>
+        <v>1.98</v>
       </c>
       <c r="AA126">
         <v>0</v>
@@ -20968,22 +20968,22 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Rijeka</t>
+          <t>Deportivo Madryn</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Rudeš</t>
+          <t>All Boys</t>
         </is>
       </c>
       <c r="G127">
@@ -21010,13 +21010,13 @@
         </is>
       </c>
       <c r="N127">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="O127">
-        <v>0</v>
+        <v>2.71</v>
       </c>
       <c r="P127">
-        <v>0</v>
+        <v>3.87</v>
       </c>
       <c r="Q127">
         <v>0</v>
@@ -21043,10 +21043,10 @@
         <v>0</v>
       </c>
       <c r="Y127">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="Z127">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AA127">
         <v>0</v>
@@ -21126,27 +21126,27 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Central Norte</t>
+          <t>Rijeka</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Los Andes</t>
+          <t>Rudeš</t>
         </is>
       </c>
       <c r="G128">
@@ -21173,13 +21173,13 @@
         </is>
       </c>
       <c r="N128">
-        <v>2.72</v>
+        <v>0</v>
       </c>
       <c r="O128">
-        <v>2.68</v>
+        <v>0</v>
       </c>
       <c r="P128">
-        <v>2.72</v>
+        <v>0</v>
       </c>
       <c r="Q128">
         <v>0</v>
@@ -21206,10 +21206,10 @@
         <v>0</v>
       </c>
       <c r="Y128">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="Z128">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AA128">
         <v>0</v>
@@ -21277,7 +21277,7 @@
       </c>
       <c r="AU128" t="inlineStr">
         <is>
-          <t>2026-08-02 16:30:00</t>
+          <t>2026-08-02 16:00:00</t>
         </is>
       </c>
     </row>
@@ -21289,12 +21289,12 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -21304,12 +21304,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Washington Spirit</t>
+          <t>Central Norte</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>San Diego Wave</t>
+          <t>Los Andes</t>
         </is>
       </c>
       <c r="G129">
@@ -21336,13 +21336,13 @@
         </is>
       </c>
       <c r="N129">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="O129">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="P129">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="Q129">
         <v>0</v>
@@ -21369,10 +21369,10 @@
         <v>0</v>
       </c>
       <c r="Y129">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="Z129">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AA129">
         <v>0</v>
@@ -21440,7 +21440,7 @@
       </c>
       <c r="AU129" t="inlineStr">
         <is>
-          <t>2026-08-02 17:00:00</t>
+          <t>2026-08-02 16:30:00</t>
         </is>
       </c>
     </row>
@@ -21452,12 +21452,12 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -21467,12 +21467,12 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Macará</t>
+          <t>Washington Spirit</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Guayaquil City FC</t>
+          <t>San Diego Wave</t>
         </is>
       </c>
       <c r="G130">
@@ -21499,13 +21499,13 @@
         </is>
       </c>
       <c r="N130">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="O130">
-        <v>3.61</v>
+        <v>0</v>
       </c>
       <c r="P130">
-        <v>5.34</v>
+        <v>0</v>
       </c>
       <c r="Q130">
         <v>0</v>
@@ -21603,7 +21603,7 @@
       </c>
       <c r="AU130" t="inlineStr">
         <is>
-          <t>2026-08-02 17:30:00</t>
+          <t>2026-08-02 17:00:00</t>
         </is>
       </c>
     </row>
@@ -21615,12 +21615,12 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>18:15</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -21630,12 +21630,12 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Club Always Ready</t>
+          <t>Macará</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Bolívar</t>
+          <t>Guayaquil City FC</t>
         </is>
       </c>
       <c r="G131">
@@ -21662,13 +21662,13 @@
         </is>
       </c>
       <c r="N131">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="O131">
-        <v>0</v>
+        <v>3.61</v>
       </c>
       <c r="P131">
-        <v>0</v>
+        <v>5.34</v>
       </c>
       <c r="Q131">
         <v>0</v>
@@ -21766,7 +21766,7 @@
       </c>
       <c r="AU131" t="inlineStr">
         <is>
-          <t>2026-08-02 18:15:00</t>
+          <t>2026-08-02 17:30:00</t>
         </is>
       </c>
     </row>
@@ -21778,12 +21778,12 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>18:15</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -21793,12 +21793,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Deportes Santa Cruz</t>
+          <t>Club Always Ready</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Santiago Wanderers</t>
+          <t>Bolívar</t>
         </is>
       </c>
       <c r="G132">
@@ -21929,7 +21929,7 @@
       </c>
       <c r="AU132" t="inlineStr">
         <is>
-          <t>2026-08-02 18:30:00</t>
+          <t>2026-08-02 18:15:00</t>
         </is>
       </c>
     </row>
@@ -21946,7 +21946,7 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -21956,12 +21956,12 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Universidad Chile</t>
+          <t>Deportes Santa Cruz</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Huachipato</t>
+          <t>Santiago Wanderers</t>
         </is>
       </c>
       <c r="G133">
@@ -22104,12 +22104,12 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -22119,12 +22119,12 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>HFX Wanderers FC</t>
+          <t>Universidad Chile</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Forge FC</t>
+          <t>Huachipato</t>
         </is>
       </c>
       <c r="G134">
@@ -22151,13 +22151,13 @@
         </is>
       </c>
       <c r="N134">
-        <v>4.37</v>
+        <v>0</v>
       </c>
       <c r="O134">
-        <v>3.72</v>
+        <v>0</v>
       </c>
       <c r="P134">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="Q134">
         <v>0</v>
@@ -22255,7 +22255,7 @@
       </c>
       <c r="AU134" t="inlineStr">
         <is>
-          <t>2026-08-02 19:00:00</t>
+          <t>2026-08-02 18:30:00</t>
         </is>
       </c>
     </row>
@@ -22267,12 +22267,12 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -22282,12 +22282,12 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Utah Royals</t>
+          <t>HFX Wanderers FC</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Portland Thorns</t>
+          <t>Forge FC</t>
         </is>
       </c>
       <c r="G135">
@@ -22314,13 +22314,13 @@
         </is>
       </c>
       <c r="N135">
-        <v>0</v>
+        <v>4.37</v>
       </c>
       <c r="O135">
-        <v>0</v>
+        <v>3.72</v>
       </c>
       <c r="P135">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="Q135">
         <v>0</v>
@@ -22418,7 +22418,7 @@
       </c>
       <c r="AU135" t="inlineStr">
         <is>
-          <t>2026-08-02 20:00:00</t>
+          <t>2026-08-02 19:00:00</t>
         </is>
       </c>
     </row>
@@ -22430,12 +22430,12 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>20:10</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
@@ -22445,12 +22445,12 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Leones del Norte</t>
+          <t>Utah Royals</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Barcelona</t>
+          <t>Portland Thorns</t>
         </is>
       </c>
       <c r="G136">
@@ -22581,7 +22581,7 @@
       </c>
       <c r="AU136" t="inlineStr">
         <is>
-          <t>2026-08-02 20:10:00</t>
+          <t>2026-08-02 20:00:00</t>
         </is>
       </c>
     </row>
@@ -22593,12 +22593,12 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>20:10</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
@@ -22608,12 +22608,12 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Oriente Petrolero</t>
+          <t>Leones del Norte</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Nacional Potosí</t>
+          <t>Barcelona</t>
         </is>
       </c>
       <c r="G137">
@@ -22744,7 +22744,7 @@
       </c>
       <c r="AU137" t="inlineStr">
         <is>
-          <t>2026-08-02 20:30:00</t>
+          <t>2026-08-02 20:10:00</t>
         </is>
       </c>
     </row>
@@ -22756,156 +22756,319 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
+          <t>20:30</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>Bolivia LFPB</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>Oriente Petrolero</t>
+        </is>
+      </c>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>Nacional Potosí</t>
+        </is>
+      </c>
+      <c r="G138">
+        <v>0</v>
+      </c>
+      <c r="H138">
+        <v>0</v>
+      </c>
+      <c r="I138">
+        <v>0</v>
+      </c>
+      <c r="J138">
+        <v>0</v>
+      </c>
+      <c r="K138">
+        <v>0</v>
+      </c>
+      <c r="L138">
+        <v>0</v>
+      </c>
+      <c r="M138" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N138">
+        <v>0</v>
+      </c>
+      <c r="O138">
+        <v>0</v>
+      </c>
+      <c r="P138">
+        <v>0</v>
+      </c>
+      <c r="Q138">
+        <v>0</v>
+      </c>
+      <c r="R138">
+        <v>0</v>
+      </c>
+      <c r="S138">
+        <v>0</v>
+      </c>
+      <c r="T138">
+        <v>0</v>
+      </c>
+      <c r="U138">
+        <v>0</v>
+      </c>
+      <c r="V138">
+        <v>0</v>
+      </c>
+      <c r="W138">
+        <v>0</v>
+      </c>
+      <c r="X138">
+        <v>0</v>
+      </c>
+      <c r="Y138">
+        <v>0</v>
+      </c>
+      <c r="Z138">
+        <v>0</v>
+      </c>
+      <c r="AA138">
+        <v>0</v>
+      </c>
+      <c r="AB138">
+        <v>0</v>
+      </c>
+      <c r="AC138">
+        <v>0</v>
+      </c>
+      <c r="AD138">
+        <v>0</v>
+      </c>
+      <c r="AE138">
+        <v>0</v>
+      </c>
+      <c r="AF138">
+        <v>0</v>
+      </c>
+      <c r="AG138">
+        <v>0</v>
+      </c>
+      <c r="AH138" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI138" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ138">
+        <v>0</v>
+      </c>
+      <c r="AK138">
+        <v>0</v>
+      </c>
+      <c r="AL138">
+        <v>0</v>
+      </c>
+      <c r="AM138">
+        <v>-1</v>
+      </c>
+      <c r="AN138">
+        <v>-1</v>
+      </c>
+      <c r="AO138">
+        <v>-1</v>
+      </c>
+      <c r="AP138">
+        <v>-1</v>
+      </c>
+      <c r="AQ138">
+        <v>0</v>
+      </c>
+      <c r="AR138">
+        <v>0</v>
+      </c>
+      <c r="AS138">
+        <v>0</v>
+      </c>
+      <c r="AT138">
+        <v>0</v>
+      </c>
+      <c r="AU138" t="inlineStr">
+        <is>
+          <t>2026-08-02 20:30:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
           <t>22:00</t>
         </is>
       </c>
-      <c r="C138" t="inlineStr">
+      <c r="C139" t="inlineStr">
         <is>
           <t>USA NWSL</t>
         </is>
       </c>
-      <c r="D138" t="inlineStr">
+      <c r="D139" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="E138" t="inlineStr">
+      <c r="E139" t="inlineStr">
         <is>
           <t>Denver Summit W</t>
         </is>
       </c>
-      <c r="F138" t="inlineStr">
+      <c r="F139" t="inlineStr">
         <is>
           <t>Boston Legacy W</t>
         </is>
       </c>
-      <c r="G138">
-        <v>0</v>
-      </c>
-      <c r="H138">
-        <v>0</v>
-      </c>
-      <c r="I138">
-        <v>0</v>
-      </c>
-      <c r="J138">
-        <v>0</v>
-      </c>
-      <c r="K138">
-        <v>0</v>
-      </c>
-      <c r="L138">
-        <v>0</v>
-      </c>
-      <c r="M138" t="inlineStr">
+      <c r="G139">
+        <v>0</v>
+      </c>
+      <c r="H139">
+        <v>0</v>
+      </c>
+      <c r="I139">
+        <v>0</v>
+      </c>
+      <c r="J139">
+        <v>0</v>
+      </c>
+      <c r="K139">
+        <v>0</v>
+      </c>
+      <c r="L139">
+        <v>0</v>
+      </c>
+      <c r="M139" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="N138">
+      <c r="N139">
         <v>1.82</v>
       </c>
-      <c r="O138">
+      <c r="O139">
         <v>3.6</v>
       </c>
-      <c r="P138">
+      <c r="P139">
         <v>3.67</v>
       </c>
-      <c r="Q138">
-        <v>0</v>
-      </c>
-      <c r="R138">
-        <v>0</v>
-      </c>
-      <c r="S138">
-        <v>0</v>
-      </c>
-      <c r="T138">
-        <v>0</v>
-      </c>
-      <c r="U138">
-        <v>0</v>
-      </c>
-      <c r="V138">
-        <v>0</v>
-      </c>
-      <c r="W138">
-        <v>0</v>
-      </c>
-      <c r="X138">
-        <v>0</v>
-      </c>
-      <c r="Y138">
-        <v>0</v>
-      </c>
-      <c r="Z138">
-        <v>0</v>
-      </c>
-      <c r="AA138">
-        <v>0</v>
-      </c>
-      <c r="AB138">
-        <v>0</v>
-      </c>
-      <c r="AC138">
-        <v>0</v>
-      </c>
-      <c r="AD138">
-        <v>0</v>
-      </c>
-      <c r="AE138">
-        <v>0</v>
-      </c>
-      <c r="AF138">
-        <v>0</v>
-      </c>
-      <c r="AG138">
-        <v>0</v>
-      </c>
-      <c r="AH138" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI138" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ138">
-        <v>0</v>
-      </c>
-      <c r="AK138">
-        <v>0</v>
-      </c>
-      <c r="AL138">
-        <v>0</v>
-      </c>
-      <c r="AM138">
-        <v>-1</v>
-      </c>
-      <c r="AN138">
-        <v>-1</v>
-      </c>
-      <c r="AO138">
-        <v>-1</v>
-      </c>
-      <c r="AP138">
-        <v>-1</v>
-      </c>
-      <c r="AQ138">
-        <v>0</v>
-      </c>
-      <c r="AR138">
-        <v>0</v>
-      </c>
-      <c r="AS138">
-        <v>0</v>
-      </c>
-      <c r="AT138">
-        <v>0</v>
-      </c>
-      <c r="AU138" t="inlineStr">
+      <c r="Q139">
+        <v>0</v>
+      </c>
+      <c r="R139">
+        <v>0</v>
+      </c>
+      <c r="S139">
+        <v>0</v>
+      </c>
+      <c r="T139">
+        <v>0</v>
+      </c>
+      <c r="U139">
+        <v>0</v>
+      </c>
+      <c r="V139">
+        <v>0</v>
+      </c>
+      <c r="W139">
+        <v>0</v>
+      </c>
+      <c r="X139">
+        <v>0</v>
+      </c>
+      <c r="Y139">
+        <v>0</v>
+      </c>
+      <c r="Z139">
+        <v>0</v>
+      </c>
+      <c r="AA139">
+        <v>0</v>
+      </c>
+      <c r="AB139">
+        <v>0</v>
+      </c>
+      <c r="AC139">
+        <v>0</v>
+      </c>
+      <c r="AD139">
+        <v>0</v>
+      </c>
+      <c r="AE139">
+        <v>0</v>
+      </c>
+      <c r="AF139">
+        <v>0</v>
+      </c>
+      <c r="AG139">
+        <v>0</v>
+      </c>
+      <c r="AH139" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI139" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ139">
+        <v>0</v>
+      </c>
+      <c r="AK139">
+        <v>0</v>
+      </c>
+      <c r="AL139">
+        <v>0</v>
+      </c>
+      <c r="AM139">
+        <v>-1</v>
+      </c>
+      <c r="AN139">
+        <v>-1</v>
+      </c>
+      <c r="AO139">
+        <v>-1</v>
+      </c>
+      <c r="AP139">
+        <v>-1</v>
+      </c>
+      <c r="AQ139">
+        <v>0</v>
+      </c>
+      <c r="AR139">
+        <v>0</v>
+      </c>
+      <c r="AS139">
+        <v>0</v>
+      </c>
+      <c r="AT139">
+        <v>0</v>
+      </c>
+      <c r="AU139" t="inlineStr">
         <is>
           <t>2026-08-02 22:00:00</t>
         </is>

--- a/jogos_2026-08-02.xlsx
+++ b/jogos_2026-08-02.xlsx
@@ -5004,12 +5004,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Okzhetpes</t>
+          <t>Ulytau</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Altay</t>
+          <t>Astana</t>
         </is>
       </c>
       <c r="G29">
@@ -5036,13 +5036,13 @@
         </is>
       </c>
       <c r="N29">
-        <v>1.56</v>
+        <v>4.43</v>
       </c>
       <c r="O29">
-        <v>3.52</v>
+        <v>3.42</v>
       </c>
       <c r="P29">
-        <v>7.24</v>
+        <v>1.83</v>
       </c>
       <c r="Q29">
         <v>0</v>
@@ -5167,12 +5167,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Ulytau</t>
+          <t>Okzhetpes</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Astana</t>
+          <t>Altay</t>
         </is>
       </c>
       <c r="G30">
@@ -5199,13 +5199,13 @@
         </is>
       </c>
       <c r="N30">
-        <v>4.43</v>
+        <v>1.56</v>
       </c>
       <c r="O30">
-        <v>3.42</v>
+        <v>3.52</v>
       </c>
       <c r="P30">
-        <v>1.83</v>
+        <v>7.24</v>
       </c>
       <c r="Q30">
         <v>0</v>

--- a/jogos_2026-08-02.xlsx
+++ b/jogos_2026-08-02.xlsx
@@ -11728,55 +11728,55 @@
         <v>0</v>
       </c>
       <c r="Q70">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="R70">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="S70">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T70">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="U70">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="V70">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="W70">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X70">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y70">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Z70">
-        <v>0</v>
+        <v>3.84</v>
       </c>
       <c r="AA70">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AB70">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="AC70">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AD70">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AE70">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AF70">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AG70">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AH70" t="inlineStr">
         <is>
@@ -11789,10 +11789,10 @@
         </is>
       </c>
       <c r="AJ70">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK70">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AL70">
         <v>0</v>

--- a/jogos_2026-08-02.xlsx
+++ b/jogos_2026-08-02.xlsx
@@ -1459,55 +1459,55 @@
         <v>0</v>
       </c>
       <c r="Q7">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="R7">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="S7">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="T7">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="U7">
-        <v>0</v>
+        <v>3.13</v>
       </c>
       <c r="V7">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="W7">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X7">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y7">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Z7">
-        <v>0</v>
+        <v>3.06</v>
       </c>
       <c r="AA7">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="AB7">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AC7">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="AD7">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AE7">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF7">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AG7">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1520,10 +1520,10 @@
         </is>
       </c>
       <c r="AJ7">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AK7">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AL7">
         <v>0</v>
@@ -1948,55 +1948,55 @@
         <v>0</v>
       </c>
       <c r="Q10">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="R10">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S10">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="T10">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="U10">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="V10">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="W10">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X10">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y10">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Z10">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="AA10">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AB10">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AC10">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="AD10">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AE10">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AF10">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AG10">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2009,10 +2009,10 @@
         </is>
       </c>
       <c r="AJ10">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AK10">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AL10">
         <v>0</v>
@@ -2111,55 +2111,55 @@
         <v>2.44</v>
       </c>
       <c r="Q11">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R11">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="S11">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="T11">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="U11">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="V11">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="W11">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X11">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y11">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="Z11">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="AA11">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AB11">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AC11">
-        <v>0</v>
+        <v>4.63</v>
       </c>
       <c r="AD11">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AE11">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AF11">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AG11">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2172,10 +2172,10 @@
         </is>
       </c>
       <c r="AJ11">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AK11">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AL11">
         <v>0</v>
@@ -2274,34 +2274,34 @@
         <v>6.41</v>
       </c>
       <c r="Q12">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="R12">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="S12">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="T12">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="U12">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="V12">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W12">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X12">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y12">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z12">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="AA12">
         <v>1.85</v>
@@ -2310,19 +2310,19 @@
         <v>1.87</v>
       </c>
       <c r="AC12">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="AD12">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AE12">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AF12">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AG12">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2335,10 +2335,10 @@
         </is>
       </c>
       <c r="AJ12">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AK12">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AL12">
         <v>0</v>
@@ -2437,34 +2437,34 @@
         <v>3.81</v>
       </c>
       <c r="Q13">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="R13">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="S13">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="T13">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="U13">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="V13">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="W13">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y13">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z13">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AA13">
         <v>1.84</v>
@@ -2473,19 +2473,19 @@
         <v>1.87</v>
       </c>
       <c r="AC13">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="AD13">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AE13">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AF13">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AG13">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2498,10 +2498,10 @@
         </is>
       </c>
       <c r="AJ13">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK13">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AL13">
         <v>0</v>
@@ -2600,55 +2600,55 @@
         <v>2.25</v>
       </c>
       <c r="Q14">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R14">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="S14">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="T14">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="U14">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="V14">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="W14">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X14">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y14">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="Z14">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="AA14">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AB14">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AC14">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="AD14">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AE14">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AF14">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AG14">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2661,10 +2661,10 @@
         </is>
       </c>
       <c r="AJ14">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AK14">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AL14">
         <v>0</v>
@@ -2763,34 +2763,34 @@
         <v>2.18</v>
       </c>
       <c r="Q15">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="R15">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="S15">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="T15">
-        <v>0</v>
+        <v>3.09</v>
       </c>
       <c r="U15">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="V15">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="W15">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X15">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y15">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="Z15">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="AA15">
         <v>1.81</v>
@@ -2799,19 +2799,19 @@
         <v>1.88</v>
       </c>
       <c r="AC15">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="AD15">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AE15">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AF15">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AG15">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2824,10 +2824,10 @@
         </is>
       </c>
       <c r="AJ15">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AK15">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AL15">
         <v>0</v>
@@ -3089,34 +3089,34 @@
         <v>3.51</v>
       </c>
       <c r="Q17">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="R17">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="S17">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="T17">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="U17">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V17">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="W17">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X17">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y17">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="Z17">
-        <v>0</v>
+        <v>2.93</v>
       </c>
       <c r="AA17">
         <v>1.95</v>
@@ -3125,19 +3125,19 @@
         <v>1.75</v>
       </c>
       <c r="AC17">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AD17">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AE17">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF17">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AG17">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3150,10 +3150,10 @@
         </is>
       </c>
       <c r="AJ17">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK17">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AL17">
         <v>0</v>
@@ -3741,55 +3741,55 @@
         <v>1.99</v>
       </c>
       <c r="Q21">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="R21">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="S21">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="T21">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="U21">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="V21">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="W21">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="X21">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y21">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="Z21">
-        <v>0</v>
+        <v>5.35</v>
       </c>
       <c r="AA21">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AB21">
-        <v>0</v>
+        <v>2.61</v>
       </c>
       <c r="AC21">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AD21">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AE21">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AF21">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AG21">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
@@ -3802,10 +3802,10 @@
         </is>
       </c>
       <c r="AJ21">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AK21">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AL21">
         <v>0</v>
@@ -3904,55 +3904,55 @@
         <v>0</v>
       </c>
       <c r="Q22">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="R22">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="S22">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="T22">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="U22">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="V22">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W22">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X22">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y22">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="Z22">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="AA22">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AB22">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AC22">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AD22">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AE22">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AF22">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AG22">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
@@ -3965,10 +3965,10 @@
         </is>
       </c>
       <c r="AJ22">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AK22">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AL22">
         <v>0</v>
@@ -4067,40 +4067,40 @@
         <v>2.48</v>
       </c>
       <c r="Q23">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="R23">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="S23">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="T23">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="U23">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="V23">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="W23">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="X23">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y23">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="Z23">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="AA23">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AB23">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="AC23">
         <v>2.2</v>
@@ -4109,13 +4109,13 @@
         <v>1.58</v>
       </c>
       <c r="AE23">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AF23">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AG23">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
@@ -4128,10 +4128,10 @@
         </is>
       </c>
       <c r="AJ23">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK23">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AL23">
         <v>0</v>
@@ -4230,55 +4230,55 @@
         <v>2.33</v>
       </c>
       <c r="Q24">
-        <v>0</v>
+        <v>3.33</v>
       </c>
       <c r="R24">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="S24">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="T24">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="U24">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="V24">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="W24">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X24">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y24">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Z24">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AA24">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="AB24">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AC24">
-        <v>0</v>
+        <v>3.86</v>
       </c>
       <c r="AD24">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AE24">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF24">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AG24">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AH24" t="inlineStr">
         <is>
@@ -4291,10 +4291,10 @@
         </is>
       </c>
       <c r="AJ24">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AK24">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AL24">
         <v>0</v>
@@ -4393,55 +4393,55 @@
         <v>2.18</v>
       </c>
       <c r="Q25">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R25">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="S25">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T25">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="U25">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="V25">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="W25">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X25">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y25">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="Z25">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AA25">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AB25">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AC25">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="AD25">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AE25">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AF25">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AG25">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="AH25" t="inlineStr">
         <is>
@@ -4454,10 +4454,10 @@
         </is>
       </c>
       <c r="AJ25">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AK25">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AL25">
         <v>0</v>
@@ -4556,55 +4556,55 @@
         <v>4.7</v>
       </c>
       <c r="Q26">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="R26">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="S26">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T26">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="U26">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="V26">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="W26">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X26">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y26">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z26">
-        <v>0</v>
+        <v>3.78</v>
       </c>
       <c r="AA26">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB26">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC26">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AD26">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AE26">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AF26">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AG26">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AH26" t="inlineStr">
         <is>
@@ -4617,10 +4617,10 @@
         </is>
       </c>
       <c r="AJ26">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK26">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AL26">
         <v>0</v>
@@ -4719,55 +4719,55 @@
         <v>2.35</v>
       </c>
       <c r="Q27">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="R27">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="S27">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="T27">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="U27">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="V27">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="W27">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="X27">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y27">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="Z27">
-        <v>0</v>
+        <v>5.11</v>
       </c>
       <c r="AA27">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AB27">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AC27">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="AD27">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AE27">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AF27">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AG27">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AH27" t="inlineStr">
         <is>
@@ -4780,10 +4780,10 @@
         </is>
       </c>
       <c r="AJ27">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AK27">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AL27">
         <v>0</v>
@@ -4882,55 +4882,55 @@
         <v>3.87</v>
       </c>
       <c r="Q28">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="R28">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="S28">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T28">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="U28">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="V28">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="W28">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X28">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y28">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="Z28">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="AA28">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AB28">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AC28">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="AD28">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AE28">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AF28">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AG28">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AH28" t="inlineStr">
         <is>
@@ -4943,10 +4943,10 @@
         </is>
       </c>
       <c r="AJ28">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AK28">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AL28">
         <v>0</v>
@@ -5045,55 +5045,55 @@
         <v>1.83</v>
       </c>
       <c r="Q29">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="R29">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="S29">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="T29">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="U29">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="V29">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="W29">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X29">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y29">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Z29">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AA29">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AB29">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AC29">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AD29">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AE29">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AF29">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AG29">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AH29" t="inlineStr">
         <is>
@@ -5106,10 +5106,10 @@
         </is>
       </c>
       <c r="AJ29">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AK29">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AL29">
         <v>0</v>
@@ -5362,64 +5362,64 @@
         </is>
       </c>
       <c r="N31">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="O31">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P31">
-        <v>0</v>
+        <v>2.91</v>
       </c>
       <c r="Q31">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="R31">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="S31">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="T31">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="U31">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="V31">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="W31">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="X31">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y31">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="Z31">
-        <v>0</v>
+        <v>3.94</v>
       </c>
       <c r="AA31">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AB31">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AC31">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="AD31">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AE31">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AF31">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AG31">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="AH31" t="inlineStr">
         <is>
@@ -5432,10 +5432,10 @@
         </is>
       </c>
       <c r="AJ31">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK31">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AL31">
         <v>0</v>
@@ -5534,34 +5534,34 @@
         <v>5.59</v>
       </c>
       <c r="Q32">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="R32">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="S32">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="T32">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="U32">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="V32">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="W32">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X32">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y32">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="Z32">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="AA32">
         <v>1.82</v>
@@ -5570,19 +5570,19 @@
         <v>1.88</v>
       </c>
       <c r="AC32">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="AD32">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AE32">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AF32">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AG32">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AH32" t="inlineStr">
         <is>
@@ -5595,10 +5595,10 @@
         </is>
       </c>
       <c r="AJ32">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AK32">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AL32">
         <v>0</v>
@@ -5697,55 +5697,55 @@
         <v>0</v>
       </c>
       <c r="Q33">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="R33">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="S33">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="T33">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="U33">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="V33">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="W33">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X33">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y33">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z33">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="AA33">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AB33">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC33">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="AD33">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AE33">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF33">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AG33">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AH33" t="inlineStr">
         <is>
@@ -5758,10 +5758,10 @@
         </is>
       </c>
       <c r="AJ33">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AK33">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AL33">
         <v>0</v>
@@ -5851,64 +5851,64 @@
         </is>
       </c>
       <c r="N34">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="O34">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="P34">
-        <v>0</v>
+        <v>4.03</v>
       </c>
       <c r="Q34">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="R34">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="S34">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="T34">
-        <v>0</v>
+        <v>3.11</v>
       </c>
       <c r="U34">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="V34">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="W34">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X34">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y34">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="Z34">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AA34">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AB34">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC34">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AD34">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AE34">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AF34">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AG34">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AH34" t="inlineStr">
         <is>
@@ -5921,10 +5921,10 @@
         </is>
       </c>
       <c r="AJ34">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AK34">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AL34">
         <v>0</v>
@@ -6023,55 +6023,55 @@
         <v>2.98</v>
       </c>
       <c r="Q35">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="R35">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="S35">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="T35">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="U35">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="V35">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="W35">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X35">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y35">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="Z35">
-        <v>0</v>
+        <v>4.96</v>
       </c>
       <c r="AA35">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AB35">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AC35">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="AD35">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AE35">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AF35">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AG35">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AH35" t="inlineStr">
         <is>
@@ -6084,10 +6084,10 @@
         </is>
       </c>
       <c r="AJ35">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AK35">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AL35">
         <v>0</v>
@@ -6349,10 +6349,10 @@
         <v>0</v>
       </c>
       <c r="Q37">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="R37">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="S37">
         <v>0</v>
@@ -6361,10 +6361,10 @@
         <v>0</v>
       </c>
       <c r="U37">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="V37">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="W37">
         <v>0</v>
@@ -6373,31 +6373,31 @@
         <v>0</v>
       </c>
       <c r="Y37">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="Z37">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="AA37">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AB37">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AC37">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AD37">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AE37">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AF37">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AG37">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AH37" t="inlineStr">
         <is>
@@ -6410,10 +6410,10 @@
         </is>
       </c>
       <c r="AJ37">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AK37">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AL37">
         <v>0</v>
@@ -6512,55 +6512,55 @@
         <v>1.38</v>
       </c>
       <c r="Q38">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="R38">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="S38">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="T38">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="U38">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="V38">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="W38">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="X38">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y38">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z38">
-        <v>0</v>
+        <v>3.84</v>
       </c>
       <c r="AA38">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AB38">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="AC38">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="AD38">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AE38">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AF38">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AG38">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AH38" t="inlineStr">
         <is>
@@ -6573,10 +6573,10 @@
         </is>
       </c>
       <c r="AJ38">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AK38">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AL38">
         <v>0</v>
@@ -6675,34 +6675,34 @@
         <v>2.71</v>
       </c>
       <c r="Q39">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="R39">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="S39">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="T39">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="U39">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="V39">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="W39">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X39">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y39">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="Z39">
-        <v>0</v>
+        <v>3.62</v>
       </c>
       <c r="AA39">
         <v>1.7</v>
@@ -6711,19 +6711,19 @@
         <v>2</v>
       </c>
       <c r="AC39">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="AD39">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AE39">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AF39">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AG39">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AH39" t="inlineStr">
         <is>
@@ -6736,10 +6736,10 @@
         </is>
       </c>
       <c r="AJ39">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AK39">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AL39">
         <v>0</v>
@@ -6838,55 +6838,55 @@
         <v>2.37</v>
       </c>
       <c r="Q40">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="R40">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="S40">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="T40">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="U40">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="V40">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="W40">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X40">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y40">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="Z40">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AA40">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AB40">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AC40">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="AD40">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AE40">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AF40">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AG40">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AH40" t="inlineStr">
         <is>
@@ -6899,10 +6899,10 @@
         </is>
       </c>
       <c r="AJ40">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AK40">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AL40">
         <v>0</v>
@@ -6992,64 +6992,64 @@
         </is>
       </c>
       <c r="N41">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="O41">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="P41">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="Q41">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="R41">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="S41">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="T41">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="U41">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="V41">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="W41">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X41">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y41">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Z41">
-        <v>0</v>
+        <v>3.92</v>
       </c>
       <c r="AA41">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AB41">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AC41">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="AD41">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AE41">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AF41">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AG41">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="AH41" t="inlineStr">
         <is>
@@ -7062,10 +7062,10 @@
         </is>
       </c>
       <c r="AJ41">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK41">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AL41">
         <v>0</v>
@@ -7164,55 +7164,55 @@
         <v>1.86</v>
       </c>
       <c r="Q42">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="R42">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="S42">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T42">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="U42">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="V42">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="W42">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X42">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y42">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z42">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="AA42">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AB42">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AC42">
-        <v>0</v>
+        <v>2.61</v>
       </c>
       <c r="AD42">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AE42">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AF42">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AG42">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AH42" t="inlineStr">
         <is>
@@ -7225,10 +7225,10 @@
         </is>
       </c>
       <c r="AJ42">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AK42">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AL42">
         <v>0</v>
@@ -7327,55 +7327,55 @@
         <v>4.59</v>
       </c>
       <c r="Q43">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="R43">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="S43">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="T43">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="U43">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="V43">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="W43">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X43">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y43">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="Z43">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="AA43">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="AB43">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AC43">
-        <v>0</v>
+        <v>3.82</v>
       </c>
       <c r="AD43">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AE43">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF43">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AG43">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AH43" t="inlineStr">
         <is>
@@ -7388,10 +7388,10 @@
         </is>
       </c>
       <c r="AJ43">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AK43">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="AL43">
         <v>0</v>
@@ -7490,55 +7490,55 @@
         <v>5.75</v>
       </c>
       <c r="Q44">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="R44">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="S44">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="T44">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="U44">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="V44">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="W44">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="X44">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y44">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="Z44">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="AA44">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AB44">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AC44">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AD44">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AE44">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AF44">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AG44">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AH44" t="inlineStr">
         <is>
@@ -7551,10 +7551,10 @@
         </is>
       </c>
       <c r="AJ44">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AK44">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AL44">
         <v>0</v>
@@ -7653,55 +7653,55 @@
         <v>6.53</v>
       </c>
       <c r="Q45">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="R45">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="S45">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="T45">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="U45">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="V45">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="W45">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X45">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y45">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="Z45">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AA45">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AB45">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AC45">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AD45">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AE45">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AF45">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AG45">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AH45" t="inlineStr">
         <is>
@@ -7714,10 +7714,10 @@
         </is>
       </c>
       <c r="AJ45">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AK45">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AL45">
         <v>0</v>
@@ -7816,10 +7816,10 @@
         <v>0</v>
       </c>
       <c r="Q46">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="R46">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="S46">
         <v>0</v>
@@ -7828,10 +7828,10 @@
         <v>0</v>
       </c>
       <c r="U46">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="V46">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="W46">
         <v>0</v>
@@ -7840,31 +7840,31 @@
         <v>0</v>
       </c>
       <c r="Y46">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="Z46">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AA46">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AB46">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC46">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AD46">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AE46">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AF46">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AG46">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AH46" t="inlineStr">
         <is>
@@ -7877,10 +7877,10 @@
         </is>
       </c>
       <c r="AJ46">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK46">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AL46">
         <v>0</v>
@@ -8305,55 +8305,55 @@
         <v>3.19</v>
       </c>
       <c r="Q49">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="R49">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="S49">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="T49">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="U49">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="V49">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="W49">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X49">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y49">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z49">
-        <v>0</v>
+        <v>3.94</v>
       </c>
       <c r="AA49">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AB49">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AC49">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="AD49">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AE49">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AF49">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AG49">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AH49" t="inlineStr">
         <is>
@@ -8366,10 +8366,10 @@
         </is>
       </c>
       <c r="AJ49">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AK49">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AL49">
         <v>0</v>
@@ -8590,12 +8590,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Sion</t>
+          <t>Grasshopper</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Luzern</t>
+          <t>Lugano</t>
         </is>
       </c>
       <c r="G51">
@@ -8622,64 +8622,64 @@
         </is>
       </c>
       <c r="N51">
-        <v>1.77</v>
+        <v>3.48</v>
       </c>
       <c r="O51">
-        <v>3.98</v>
+        <v>3.52</v>
       </c>
       <c r="P51">
-        <v>3.98</v>
+        <v>2.04</v>
       </c>
       <c r="Q51">
-        <v>0</v>
+        <v>4.16</v>
       </c>
       <c r="R51">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="S51">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T51">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="U51">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="V51">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="W51">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X51">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y51">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z51">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AA51">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AB51">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="AC51">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="AD51">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AE51">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AF51">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AG51">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AH51" t="inlineStr">
         <is>
@@ -8692,10 +8692,10 @@
         </is>
       </c>
       <c r="AJ51">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AK51">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AL51">
         <v>0</v>
@@ -8753,12 +8753,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Grasshopper</t>
+          <t>Sion</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Lugano</t>
+          <t>Luzern</t>
         </is>
       </c>
       <c r="G52">
@@ -8785,64 +8785,64 @@
         </is>
       </c>
       <c r="N52">
-        <v>3.48</v>
+        <v>1.77</v>
       </c>
       <c r="O52">
-        <v>3.52</v>
+        <v>3.98</v>
       </c>
       <c r="P52">
-        <v>2.04</v>
+        <v>3.98</v>
       </c>
       <c r="Q52">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="R52">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="S52">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T52">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="U52">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="V52">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="W52">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="X52">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y52">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="Z52">
-        <v>0</v>
+        <v>4.55</v>
       </c>
       <c r="AA52">
-        <v>1.81</v>
+        <v>1.5</v>
       </c>
       <c r="AB52">
-        <v>2.01</v>
+        <v>2.29</v>
       </c>
       <c r="AC52">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="AD52">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AE52">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AF52">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AG52">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="AH52" t="inlineStr">
         <is>
@@ -8855,10 +8855,10 @@
         </is>
       </c>
       <c r="AJ52">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK52">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AL52">
         <v>0</v>
@@ -8957,55 +8957,55 @@
         <v>7.28</v>
       </c>
       <c r="Q53">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="R53">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="S53">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T53">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="U53">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="V53">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="W53">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X53">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y53">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="Z53">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="AA53">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AB53">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AC53">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="AD53">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AE53">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AF53">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AG53">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AH53" t="inlineStr">
         <is>
@@ -9018,10 +9018,10 @@
         </is>
       </c>
       <c r="AJ53">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AK53">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AL53">
         <v>0</v>
@@ -9405,12 +9405,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>KFUM</t>
+          <t>Aalesund</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Kristiansund</t>
+          <t>Tromsø</t>
         </is>
       </c>
       <c r="G56">
@@ -9437,64 +9437,64 @@
         </is>
       </c>
       <c r="N56">
+        <v>3.52</v>
+      </c>
+      <c r="O56">
+        <v>3.74</v>
+      </c>
+      <c r="P56">
+        <v>2.02</v>
+      </c>
+      <c r="Q56">
+        <v>3.74</v>
+      </c>
+      <c r="R56">
+        <v>2.23</v>
+      </c>
+      <c r="S56">
+        <v>1.3</v>
+      </c>
+      <c r="T56">
+        <v>3.3</v>
+      </c>
+      <c r="U56">
+        <v>2.52</v>
+      </c>
+      <c r="V56">
+        <v>1.49</v>
+      </c>
+      <c r="W56">
+        <v>1.08</v>
+      </c>
+      <c r="X56">
+        <v>1.02</v>
+      </c>
+      <c r="Y56">
+        <v>1.18</v>
+      </c>
+      <c r="Z56">
+        <v>4.33</v>
+      </c>
+      <c r="AA56">
+        <v>1.65</v>
+      </c>
+      <c r="AB56">
+        <v>2.14</v>
+      </c>
+      <c r="AC56">
+        <v>2.57</v>
+      </c>
+      <c r="AD56">
+        <v>1.44</v>
+      </c>
+      <c r="AE56">
+        <v>1.13</v>
+      </c>
+      <c r="AF56">
         <v>1.57</v>
       </c>
-      <c r="O56">
-        <v>4.25</v>
-      </c>
-      <c r="P56">
-        <v>5.73</v>
-      </c>
-      <c r="Q56">
-        <v>0</v>
-      </c>
-      <c r="R56">
-        <v>0</v>
-      </c>
-      <c r="S56">
-        <v>0</v>
-      </c>
-      <c r="T56">
-        <v>0</v>
-      </c>
-      <c r="U56">
-        <v>0</v>
-      </c>
-      <c r="V56">
-        <v>0</v>
-      </c>
-      <c r="W56">
-        <v>0</v>
-      </c>
-      <c r="X56">
-        <v>0</v>
-      </c>
-      <c r="Y56">
-        <v>0</v>
-      </c>
-      <c r="Z56">
-        <v>0</v>
-      </c>
-      <c r="AA56">
-        <v>0</v>
-      </c>
-      <c r="AB56">
-        <v>0</v>
-      </c>
-      <c r="AC56">
-        <v>0</v>
-      </c>
-      <c r="AD56">
-        <v>0</v>
-      </c>
-      <c r="AE56">
-        <v>0</v>
-      </c>
-      <c r="AF56">
-        <v>0</v>
-      </c>
       <c r="AG56">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AH56" t="inlineStr">
         <is>
@@ -9507,10 +9507,10 @@
         </is>
       </c>
       <c r="AJ56">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AK56">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AL56">
         <v>0</v>
@@ -9568,12 +9568,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Aalesund</t>
+          <t>Molde</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Tromsø</t>
+          <t>Sarpsborg 08</t>
         </is>
       </c>
       <c r="G57">
@@ -9600,64 +9600,64 @@
         </is>
       </c>
       <c r="N57">
-        <v>3.52</v>
+        <v>1.7</v>
       </c>
       <c r="O57">
-        <v>3.74</v>
+        <v>4.3</v>
       </c>
       <c r="P57">
-        <v>2.02</v>
+        <v>4.43</v>
       </c>
       <c r="Q57">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="R57">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="S57">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="T57">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="U57">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="V57">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="W57">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="X57">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y57">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="Z57">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="AA57">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AB57">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AC57">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="AD57">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AE57">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AF57">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AG57">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AH57" t="inlineStr">
         <is>
@@ -9670,10 +9670,10 @@
         </is>
       </c>
       <c r="AJ57">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AK57">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AL57">
         <v>0</v>
@@ -9731,12 +9731,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Molde</t>
+          <t>KFUM</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Sarpsborg 08</t>
+          <t>Kristiansund</t>
         </is>
       </c>
       <c r="G58">
@@ -9763,64 +9763,64 @@
         </is>
       </c>
       <c r="N58">
-        <v>1.7</v>
+        <v>1.57</v>
       </c>
       <c r="O58">
-        <v>4.3</v>
+        <v>4.25</v>
       </c>
       <c r="P58">
-        <v>4.43</v>
+        <v>5.73</v>
       </c>
       <c r="Q58">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="R58">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="S58">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="T58">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="U58">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="V58">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="W58">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X58">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y58">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="Z58">
-        <v>0</v>
+        <v>3.84</v>
       </c>
       <c r="AA58">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AB58">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AC58">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="AD58">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AE58">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AF58">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AG58">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AH58" t="inlineStr">
         <is>
@@ -9833,10 +9833,10 @@
         </is>
       </c>
       <c r="AJ58">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AK58">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AL58">
         <v>0</v>
@@ -9926,64 +9926,64 @@
         </is>
       </c>
       <c r="N59">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="O59">
-        <v>0</v>
+        <v>8.1</v>
       </c>
       <c r="P59">
-        <v>0</v>
+        <v>16.5</v>
       </c>
       <c r="Q59">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="R59">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="S59">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="T59">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="U59">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="V59">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="W59">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="X59">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y59">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="Z59">
-        <v>0</v>
+        <v>5.65</v>
       </c>
       <c r="AA59">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AB59">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="AC59">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AD59">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AE59">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AF59">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="AG59">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AH59" t="inlineStr">
         <is>
@@ -9996,10 +9996,10 @@
         </is>
       </c>
       <c r="AJ59">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AK59">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AL59">
         <v>0</v>
@@ -10098,34 +10098,34 @@
         <v>2.74</v>
       </c>
       <c r="Q60">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="R60">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="S60">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="T60">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="U60">
-        <v>0</v>
+        <v>3.01</v>
       </c>
       <c r="V60">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W60">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X60">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y60">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z60">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="AA60">
         <v>1.98</v>
@@ -10134,19 +10134,19 @@
         <v>1.71</v>
       </c>
       <c r="AC60">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="AD60">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AE60">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AF60">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AG60">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AH60" t="inlineStr">
         <is>
@@ -10159,10 +10159,10 @@
         </is>
       </c>
       <c r="AJ60">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AK60">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AL60">
         <v>0</v>
@@ -10261,34 +10261,34 @@
         <v>2.48</v>
       </c>
       <c r="Q61">
-        <v>0</v>
+        <v>2.71</v>
       </c>
       <c r="R61">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="S61">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="T61">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="U61">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="V61">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="W61">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X61">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y61">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z61">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="AA61">
         <v>1.81</v>
@@ -10297,19 +10297,19 @@
         <v>1.91</v>
       </c>
       <c r="AC61">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AD61">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AE61">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AF61">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AG61">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="AH61" t="inlineStr">
         <is>
@@ -10322,10 +10322,10 @@
         </is>
       </c>
       <c r="AJ61">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AK61">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AL61">
         <v>0</v>
@@ -10383,12 +10383,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Egersund</t>
+          <t>Hødd</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Sandnes Ulf</t>
+          <t>Moss</t>
         </is>
       </c>
       <c r="G62">
@@ -10415,64 +10415,64 @@
         </is>
       </c>
       <c r="N62">
-        <v>1.89</v>
+        <v>2.02</v>
       </c>
       <c r="O62">
-        <v>3.75</v>
+        <v>3.85</v>
       </c>
       <c r="P62">
-        <v>3.3</v>
+        <v>3.13</v>
       </c>
       <c r="Q62">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="R62">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="S62">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="T62">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="U62">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="V62">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="W62">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="X62">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y62">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="Z62">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="AA62">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AB62">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="AC62">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AD62">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AE62">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AF62">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AG62">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AH62" t="inlineStr">
         <is>
@@ -10485,10 +10485,10 @@
         </is>
       </c>
       <c r="AJ62">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK62">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AL62">
         <v>0</v>
@@ -10546,12 +10546,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Hødd</t>
+          <t>Kongsvinger</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Moss</t>
+          <t>Strømmen</t>
         </is>
       </c>
       <c r="G63">
@@ -10578,64 +10578,64 @@
         </is>
       </c>
       <c r="N63">
-        <v>2.02</v>
+        <v>1.45</v>
       </c>
       <c r="O63">
-        <v>3.85</v>
+        <v>4.7</v>
       </c>
       <c r="P63">
-        <v>3.13</v>
+        <v>4.85</v>
       </c>
       <c r="Q63">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="R63">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="S63">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="T63">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="U63">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="V63">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="W63">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="X63">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y63">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="Z63">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="AA63">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AB63">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AC63">
-        <v>1.98</v>
+        <v>1.79</v>
       </c>
       <c r="AD63">
-        <v>1.83</v>
+        <v>1.89</v>
       </c>
       <c r="AE63">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AF63">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AG63">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AH63" t="inlineStr">
         <is>
@@ -10648,10 +10648,10 @@
         </is>
       </c>
       <c r="AJ63">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AK63">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AL63">
         <v>0</v>
@@ -10709,12 +10709,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Kongsvinger</t>
+          <t>Lyn</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Strømmen</t>
+          <t>Sogndal</t>
         </is>
       </c>
       <c r="G64">
@@ -10741,64 +10741,64 @@
         </is>
       </c>
       <c r="N64">
-        <v>1.45</v>
+        <v>2.14</v>
       </c>
       <c r="O64">
-        <v>4.7</v>
+        <v>3.65</v>
       </c>
       <c r="P64">
-        <v>4.85</v>
+        <v>2.8</v>
       </c>
       <c r="Q64">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="R64">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="S64">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="T64">
-        <v>0</v>
+        <v>3.84</v>
       </c>
       <c r="U64">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="V64">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="W64">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="X64">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y64">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="Z64">
-        <v>0</v>
+        <v>6.47</v>
       </c>
       <c r="AA64">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AB64">
-        <v>0</v>
+        <v>2.91</v>
       </c>
       <c r="AC64">
-        <v>1.79</v>
+        <v>1.91</v>
       </c>
       <c r="AD64">
-        <v>1.89</v>
+        <v>1.85</v>
       </c>
       <c r="AE64">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AF64">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AG64">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AH64" t="inlineStr">
         <is>
@@ -10811,10 +10811,10 @@
         </is>
       </c>
       <c r="AJ64">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AK64">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AL64">
         <v>0</v>
@@ -10872,12 +10872,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Odd</t>
+          <t>Egersund</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Åsane</t>
+          <t>Sandnes Ulf</t>
         </is>
       </c>
       <c r="G65">
@@ -10904,64 +10904,64 @@
         </is>
       </c>
       <c r="N65">
-        <v>1.39</v>
+        <v>1.89</v>
       </c>
       <c r="O65">
-        <v>4.85</v>
+        <v>3.75</v>
       </c>
       <c r="P65">
-        <v>5.55</v>
+        <v>3.3</v>
       </c>
       <c r="Q65">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="R65">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="S65">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T65">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="U65">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="V65">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="W65">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X65">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y65">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="Z65">
-        <v>0</v>
+        <v>4.87</v>
       </c>
       <c r="AA65">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AB65">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AC65">
-        <v>1.88</v>
+        <v>2.35</v>
       </c>
       <c r="AD65">
-        <v>1.8</v>
+        <v>1.52</v>
       </c>
       <c r="AE65">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AF65">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AG65">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="AH65" t="inlineStr">
         <is>
@@ -10974,10 +10974,10 @@
         </is>
       </c>
       <c r="AJ65">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AK65">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AL65">
         <v>0</v>
@@ -11035,12 +11035,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Lyn</t>
+          <t>Odd</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Sogndal</t>
+          <t>Åsane</t>
         </is>
       </c>
       <c r="G66">
@@ -11067,64 +11067,64 @@
         </is>
       </c>
       <c r="N66">
-        <v>2.14</v>
+        <v>1.39</v>
       </c>
       <c r="O66">
-        <v>3.65</v>
+        <v>4.85</v>
       </c>
       <c r="P66">
-        <v>2.8</v>
+        <v>5.55</v>
       </c>
       <c r="Q66">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="R66">
-        <v>0</v>
+        <v>2.51</v>
       </c>
       <c r="S66">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="T66">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="U66">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="V66">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="W66">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="X66">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y66">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="Z66">
-        <v>0</v>
+        <v>6.6</v>
       </c>
       <c r="AA66">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AB66">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AC66">
-        <v>1.91</v>
+        <v>1.88</v>
       </c>
       <c r="AD66">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="AE66">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AF66">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AG66">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AH66" t="inlineStr">
         <is>
@@ -11137,10 +11137,10 @@
         </is>
       </c>
       <c r="AJ66">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AK66">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="AL66">
         <v>0</v>
@@ -11239,40 +11239,40 @@
         <v>1.55</v>
       </c>
       <c r="Q67">
-        <v>0</v>
+        <v>4.09</v>
       </c>
       <c r="R67">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="S67">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="T67">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="U67">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="V67">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="W67">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="X67">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y67">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Z67">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="AA67">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AB67">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AC67">
         <v>1.87</v>
@@ -11281,13 +11281,13 @@
         <v>1.81</v>
       </c>
       <c r="AE67">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AF67">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AG67">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="AH67" t="inlineStr">
         <is>
@@ -11300,10 +11300,10 @@
         </is>
       </c>
       <c r="AJ67">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AK67">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AL67">
         <v>0</v>
@@ -11402,55 +11402,55 @@
         <v>4.63</v>
       </c>
       <c r="Q68">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="R68">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="S68">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="T68">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="U68">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="V68">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="W68">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X68">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y68">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="Z68">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="AA68">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="AB68">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC68">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AD68">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AE68">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AF68">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AG68">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AH68" t="inlineStr">
         <is>
@@ -11463,10 +11463,10 @@
         </is>
       </c>
       <c r="AJ68">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AK68">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AL68">
         <v>0</v>
@@ -11565,55 +11565,55 @@
         <v>11.4</v>
       </c>
       <c r="Q69">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="R69">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="S69">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="T69">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="U69">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="V69">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="W69">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X69">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y69">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Z69">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="AA69">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AB69">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC69">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="AD69">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AE69">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AF69">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AG69">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AH69" t="inlineStr">
         <is>
@@ -11626,10 +11626,10 @@
         </is>
       </c>
       <c r="AJ69">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AK69">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AL69">
         <v>0</v>
@@ -12045,64 +12045,64 @@
         </is>
       </c>
       <c r="N72">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="O72">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P72">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="Q72">
-        <v>0</v>
+        <v>3.09</v>
       </c>
       <c r="R72">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="S72">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="T72">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="U72">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="V72">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="W72">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X72">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y72">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="Z72">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="AA72">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AB72">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC72">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AD72">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AE72">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AF72">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AG72">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AH72" t="inlineStr">
         <is>
@@ -12115,10 +12115,10 @@
         </is>
       </c>
       <c r="AJ72">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AK72">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AL72">
         <v>0</v>
@@ -12208,64 +12208,64 @@
         </is>
       </c>
       <c r="N73">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="O73">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="P73">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Q73">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="R73">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="S73">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="T73">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="U73">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="V73">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W73">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X73">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y73">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="Z73">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="AA73">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AB73">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AC73">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="AD73">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AE73">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AF73">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AG73">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AH73" t="inlineStr">
         <is>
@@ -12278,10 +12278,10 @@
         </is>
       </c>
       <c r="AJ73">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AK73">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AL73">
         <v>0</v>
@@ -12380,34 +12380,34 @@
         <v>3.07</v>
       </c>
       <c r="Q74">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="R74">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="S74">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="T74">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="U74">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="V74">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="W74">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X74">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y74">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="Z74">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="AA74">
         <v>1.72</v>
@@ -12416,19 +12416,19 @@
         <v>1.98</v>
       </c>
       <c r="AC74">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="AD74">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AE74">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AF74">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AG74">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AH74" t="inlineStr">
         <is>
@@ -12441,10 +12441,10 @@
         </is>
       </c>
       <c r="AJ74">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK74">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AL74">
         <v>0</v>
@@ -12543,55 +12543,55 @@
         <v>3.24</v>
       </c>
       <c r="Q75">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="R75">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="S75">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="T75">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="U75">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="V75">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="W75">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X75">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y75">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="Z75">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AA75">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AB75">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AC75">
-        <v>0</v>
+        <v>4.38</v>
       </c>
       <c r="AD75">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AE75">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AF75">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AG75">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AH75" t="inlineStr">
         <is>
@@ -12604,10 +12604,10 @@
         </is>
       </c>
       <c r="AJ75">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK75">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AL75">
         <v>0</v>
@@ -13032,55 +13032,55 @@
         <v>4.45</v>
       </c>
       <c r="Q78">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="R78">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="S78">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="T78">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="U78">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="V78">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W78">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X78">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y78">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z78">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="AA78">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AB78">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AC78">
-        <v>0</v>
+        <v>3.62</v>
       </c>
       <c r="AD78">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AE78">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AF78">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG78">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AH78" t="inlineStr">
         <is>
@@ -13093,10 +13093,10 @@
         </is>
       </c>
       <c r="AJ78">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AK78">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AL78">
         <v>0</v>
@@ -13186,64 +13186,64 @@
         </is>
       </c>
       <c r="N79">
-        <v>0</v>
+        <v>3.89</v>
       </c>
       <c r="O79">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="P79">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="Q79">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="R79">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="S79">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="T79">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="U79">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="V79">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="W79">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X79">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y79">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="Z79">
-        <v>0</v>
+        <v>3.78</v>
       </c>
       <c r="AA79">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AB79">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AC79">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="AD79">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AE79">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AF79">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AG79">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AH79" t="inlineStr">
         <is>
@@ -13256,10 +13256,10 @@
         </is>
       </c>
       <c r="AJ79">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AK79">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AL79">
         <v>0</v>
@@ -13358,55 +13358,55 @@
         <v>1.76</v>
       </c>
       <c r="Q80">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="R80">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="S80">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="T80">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="U80">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="V80">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="W80">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X80">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y80">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="Z80">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="AA80">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AB80">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AC80">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="AD80">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AE80">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AF80">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AG80">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="AH80" t="inlineStr">
         <is>
@@ -13419,10 +13419,10 @@
         </is>
       </c>
       <c r="AJ80">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AK80">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AL80">
         <v>0</v>
@@ -13512,13 +13512,13 @@
         </is>
       </c>
       <c r="N81">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="O81">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="P81">
-        <v>0</v>
+        <v>6.3</v>
       </c>
       <c r="Q81">
         <v>0</v>
@@ -13643,12 +13643,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Vaprus</t>
+          <t>Tallinna FC Flora</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Tallinna FC Levadia</t>
+          <t>Harju Jalgpallikool</t>
         </is>
       </c>
       <c r="G82">
@@ -13675,64 +13675,64 @@
         </is>
       </c>
       <c r="N82">
-        <v>10.9</v>
+        <v>1.38</v>
       </c>
       <c r="O82">
-        <v>5.8</v>
+        <v>4.45</v>
       </c>
       <c r="P82">
+        <v>6.64</v>
+      </c>
+      <c r="Q82">
+        <v>1.85</v>
+      </c>
+      <c r="R82">
+        <v>2.5</v>
+      </c>
+      <c r="S82">
         <v>1.2</v>
       </c>
-      <c r="Q82">
-        <v>0</v>
-      </c>
-      <c r="R82">
-        <v>0</v>
-      </c>
-      <c r="S82">
-        <v>0</v>
-      </c>
       <c r="T82">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="U82">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="V82">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="W82">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="X82">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y82">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="Z82">
-        <v>0</v>
+        <v>5.55</v>
       </c>
       <c r="AA82">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AB82">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="AC82">
-        <v>1.98</v>
+        <v>1.9</v>
       </c>
       <c r="AD82">
-        <v>1.83</v>
+        <v>1.72</v>
       </c>
       <c r="AE82">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AF82">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AG82">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="AH82" t="inlineStr">
         <is>
@@ -13745,10 +13745,10 @@
         </is>
       </c>
       <c r="AJ82">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AK82">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="AL82">
         <v>0</v>
@@ -13806,12 +13806,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Tallinna FC Flora</t>
+          <t>Vaprus</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Harju Jalgpallikool</t>
+          <t>Tallinna FC Levadia</t>
         </is>
       </c>
       <c r="G83">
@@ -13838,64 +13838,64 @@
         </is>
       </c>
       <c r="N83">
-        <v>1.38</v>
+        <v>10.9</v>
       </c>
       <c r="O83">
-        <v>4.45</v>
+        <v>5.8</v>
       </c>
       <c r="P83">
-        <v>6.64</v>
+        <v>1.2</v>
       </c>
       <c r="Q83">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="R83">
-        <v>0</v>
+        <v>2.67</v>
       </c>
       <c r="S83">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="T83">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="U83">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="V83">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="W83">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="X83">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y83">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="Z83">
-        <v>0</v>
+        <v>5.9</v>
       </c>
       <c r="AA83">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AB83">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="AC83">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AD83">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AE83">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AF83">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AG83">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AH83" t="inlineStr">
         <is>
@@ -13908,10 +13908,10 @@
         </is>
       </c>
       <c r="AJ83">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AK83">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AL83">
         <v>0</v>
@@ -14010,55 +14010,55 @@
         <v>1.49</v>
       </c>
       <c r="Q84">
-        <v>0</v>
+        <v>4.43</v>
       </c>
       <c r="R84">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="S84">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="T84">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="U84">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="V84">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="W84">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X84">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y84">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="Z84">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="AA84">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AB84">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AC84">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AD84">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AE84">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AF84">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AG84">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="AH84" t="inlineStr">
         <is>
@@ -14071,10 +14071,10 @@
         </is>
       </c>
       <c r="AJ84">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AK84">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AL84">
         <v>0</v>
@@ -14173,55 +14173,55 @@
         <v>14.5</v>
       </c>
       <c r="Q85">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="R85">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="S85">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="T85">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="U85">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="V85">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="W85">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X85">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y85">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="Z85">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="AA85">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB85">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC85">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="AD85">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AE85">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AF85">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AG85">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AH85" t="inlineStr">
         <is>
@@ -14234,10 +14234,10 @@
         </is>
       </c>
       <c r="AJ85">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AK85">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AL85">
         <v>0</v>
@@ -14816,64 +14816,64 @@
         </is>
       </c>
       <c r="N89">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="O89">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="P89">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Q89">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="R89">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="S89">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T89">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="U89">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="V89">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="W89">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X89">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y89">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="Z89">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="AA89">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AB89">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AC89">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="AD89">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AE89">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AF89">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AG89">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AH89" t="inlineStr">
         <is>
@@ -14886,10 +14886,10 @@
         </is>
       </c>
       <c r="AJ89">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AK89">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AL89">
         <v>0</v>
@@ -15966,55 +15966,55 @@
         <v>4.5</v>
       </c>
       <c r="Q96">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="R96">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="S96">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="T96">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="U96">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="V96">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="W96">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="X96">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y96">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="Z96">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="AA96">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AB96">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AC96">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AD96">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AE96">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AF96">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AG96">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="AH96" t="inlineStr">
         <is>
@@ -16027,10 +16027,10 @@
         </is>
       </c>
       <c r="AJ96">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AK96">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AL96">
         <v>0</v>
@@ -18696,12 +18696,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Brinje-Grosuplje</t>
+          <t>Olimpija</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Koper</t>
+          <t>Aluminij</t>
         </is>
       </c>
       <c r="G113">
@@ -18728,13 +18728,13 @@
         </is>
       </c>
       <c r="N113">
-        <v>6.11</v>
+        <v>1.51</v>
       </c>
       <c r="O113">
-        <v>4.15</v>
+        <v>4.05</v>
       </c>
       <c r="P113">
-        <v>1.44</v>
+        <v>5.27</v>
       </c>
       <c r="Q113">
         <v>0</v>
@@ -18767,10 +18767,10 @@
         <v>0</v>
       </c>
       <c r="AA113">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AB113">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AC113">
         <v>0</v>
@@ -18859,12 +18859,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Olimpija</t>
+          <t>Brinje-Grosuplje</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Aluminij</t>
+          <t>Koper</t>
         </is>
       </c>
       <c r="G114">
@@ -18891,13 +18891,13 @@
         </is>
       </c>
       <c r="N114">
-        <v>1.51</v>
+        <v>6.11</v>
       </c>
       <c r="O114">
-        <v>4.05</v>
+        <v>4.15</v>
       </c>
       <c r="P114">
-        <v>5.27</v>
+        <v>1.44</v>
       </c>
       <c r="Q114">
         <v>0</v>
@@ -18930,10 +18930,10 @@
         <v>0</v>
       </c>
       <c r="AA114">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AB114">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AC114">
         <v>0</v>
@@ -19674,12 +19674,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Temperley</t>
+          <t>Deportivo Maipú</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Gimnasia y Tiro</t>
+          <t>Atlanta</t>
         </is>
       </c>
       <c r="G119">
@@ -19706,13 +19706,13 @@
         </is>
       </c>
       <c r="N119">
-        <v>1.96</v>
+        <v>2.75</v>
       </c>
       <c r="O119">
-        <v>2.85</v>
+        <v>2.73</v>
       </c>
       <c r="P119">
-        <v>4.2</v>
+        <v>2.63</v>
       </c>
       <c r="Q119">
         <v>0</v>
@@ -19739,10 +19739,10 @@
         <v>0</v>
       </c>
       <c r="Y119">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="Z119">
-        <v>2.15</v>
+        <v>2.25</v>
       </c>
       <c r="AA119">
         <v>0</v>
@@ -19837,12 +19837,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Deportivo Maipú</t>
+          <t>Temperley</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Atlanta</t>
+          <t>Gimnasia y Tiro</t>
         </is>
       </c>
       <c r="G120">
@@ -19869,13 +19869,13 @@
         </is>
       </c>
       <c r="N120">
-        <v>2.75</v>
+        <v>1.96</v>
       </c>
       <c r="O120">
-        <v>2.73</v>
+        <v>2.85</v>
       </c>
       <c r="P120">
-        <v>2.63</v>
+        <v>4.2</v>
       </c>
       <c r="Q120">
         <v>0</v>
@@ -19902,10 +19902,10 @@
         <v>0</v>
       </c>
       <c r="Y120">
-        <v>1.55</v>
+        <v>1.6</v>
       </c>
       <c r="Z120">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="AA120">
         <v>0</v>

--- a/jogos_2026-08-02.xlsx
+++ b/jogos_2026-08-02.xlsx
@@ -2233,12 +2233,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Daejeon Citizen</t>
+          <t>Ulsan</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Gwangju</t>
+          <t>Anyang</t>
         </is>
       </c>
       <c r="G12">
@@ -2265,80 +2265,80 @@
         </is>
       </c>
       <c r="N12">
-        <v>1.49</v>
+        <v>1.91</v>
       </c>
       <c r="O12">
-        <v>4.15</v>
+        <v>3.55</v>
       </c>
       <c r="P12">
-        <v>6.41</v>
+        <v>3.81</v>
       </c>
       <c r="Q12">
-        <v>1.95</v>
+        <v>2.28</v>
       </c>
       <c r="R12">
-        <v>2.28</v>
+        <v>2.06</v>
       </c>
       <c r="S12">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="T12">
-        <v>2.9</v>
+        <v>2.94</v>
       </c>
       <c r="U12">
-        <v>2.7</v>
+        <v>2.75</v>
       </c>
       <c r="V12">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="W12">
         <v>1.07</v>
       </c>
       <c r="X12">
-        <v>1.05</v>
+        <v>1</v>
       </c>
       <c r="Y12">
         <v>1.22</v>
       </c>
       <c r="Z12">
-        <v>3.54</v>
+        <v>3.4</v>
       </c>
       <c r="AA12">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="AB12">
         <v>1.87</v>
       </c>
       <c r="AC12">
-        <v>2.89</v>
+        <v>2.94</v>
       </c>
       <c r="AD12">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="AE12">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="AF12">
+        <v>1.7</v>
+      </c>
+      <c r="AG12">
+        <v>2.04</v>
+      </c>
+      <c r="AH12" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI12" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ12">
+        <v>1.22</v>
+      </c>
+      <c r="AK12">
         <v>1.9</v>
-      </c>
-      <c r="AG12">
-        <v>1.8</v>
-      </c>
-      <c r="AH12" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI12" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ12">
-        <v>1.19</v>
-      </c>
-      <c r="AK12">
-        <v>2.7</v>
       </c>
       <c r="AL12">
         <v>0</v>
@@ -2396,12 +2396,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Ulsan</t>
+          <t>Daejeon Citizen</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Anyang</t>
+          <t>Gwangju</t>
         </is>
       </c>
       <c r="G13">
@@ -2428,64 +2428,64 @@
         </is>
       </c>
       <c r="N13">
-        <v>1.91</v>
+        <v>1.49</v>
       </c>
       <c r="O13">
-        <v>3.55</v>
+        <v>4.15</v>
       </c>
       <c r="P13">
-        <v>3.81</v>
+        <v>6.41</v>
       </c>
       <c r="Q13">
+        <v>1.95</v>
+      </c>
+      <c r="R13">
         <v>2.28</v>
       </c>
-      <c r="R13">
-        <v>2.06</v>
-      </c>
       <c r="S13">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="T13">
-        <v>2.94</v>
+        <v>2.9</v>
       </c>
       <c r="U13">
-        <v>2.75</v>
+        <v>2.7</v>
       </c>
       <c r="V13">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="W13">
         <v>1.07</v>
       </c>
       <c r="X13">
-        <v>1</v>
+        <v>1.05</v>
       </c>
       <c r="Y13">
         <v>1.22</v>
       </c>
       <c r="Z13">
-        <v>3.4</v>
+        <v>3.54</v>
       </c>
       <c r="AA13">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="AB13">
         <v>1.87</v>
       </c>
       <c r="AC13">
-        <v>2.94</v>
+        <v>2.89</v>
       </c>
       <c r="AD13">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="AE13">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="AF13">
-        <v>1.7</v>
+        <v>1.9</v>
       </c>
       <c r="AG13">
-        <v>2.04</v>
+        <v>1.8</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2498,10 +2498,10 @@
         </is>
       </c>
       <c r="AJ13">
-        <v>1.22</v>
+        <v>1.19</v>
       </c>
       <c r="AK13">
-        <v>1.9</v>
+        <v>2.7</v>
       </c>
       <c r="AL13">
         <v>0</v>
@@ -2559,12 +2559,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Busan I'Park</t>
+          <t>Ansan Greeners</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Seoul E-Land</t>
+          <t>Gimhae City</t>
         </is>
       </c>
       <c r="G14">
@@ -2591,80 +2591,80 @@
         </is>
       </c>
       <c r="N14">
-        <v>2.74</v>
+        <v>2.91</v>
       </c>
       <c r="O14">
-        <v>3.44</v>
+        <v>3.38</v>
       </c>
       <c r="P14">
-        <v>2.25</v>
+        <v>2.18</v>
       </c>
       <c r="Q14">
-        <v>3.1</v>
+        <v>3.28</v>
       </c>
       <c r="R14">
-        <v>2.16</v>
+        <v>2.05</v>
       </c>
       <c r="S14">
+        <v>1.34</v>
+      </c>
+      <c r="T14">
+        <v>3.09</v>
+      </c>
+      <c r="U14">
+        <v>2.66</v>
+      </c>
+      <c r="V14">
+        <v>1.39</v>
+      </c>
+      <c r="W14">
+        <v>1.08</v>
+      </c>
+      <c r="X14">
+        <v>1.05</v>
+      </c>
+      <c r="Y14">
+        <v>1.23</v>
+      </c>
+      <c r="Z14">
+        <v>3.42</v>
+      </c>
+      <c r="AA14">
+        <v>1.81</v>
+      </c>
+      <c r="AB14">
+        <v>1.88</v>
+      </c>
+      <c r="AC14">
+        <v>2.97</v>
+      </c>
+      <c r="AD14">
+        <v>1.3</v>
+      </c>
+      <c r="AE14">
+        <v>1.08</v>
+      </c>
+      <c r="AF14">
+        <v>1.67</v>
+      </c>
+      <c r="AG14">
+        <v>2.1</v>
+      </c>
+      <c r="AH14" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI14" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ14">
+        <v>1.57</v>
+      </c>
+      <c r="AK14">
         <v>1.29</v>
-      </c>
-      <c r="T14">
-        <v>3.25</v>
-      </c>
-      <c r="U14">
-        <v>2.5</v>
-      </c>
-      <c r="V14">
-        <v>1.5</v>
-      </c>
-      <c r="W14">
-        <v>1.06</v>
-      </c>
-      <c r="X14">
-        <v>1.03</v>
-      </c>
-      <c r="Y14">
-        <v>1.16</v>
-      </c>
-      <c r="Z14">
-        <v>4.05</v>
-      </c>
-      <c r="AA14">
-        <v>1.69</v>
-      </c>
-      <c r="AB14">
-        <v>2.07</v>
-      </c>
-      <c r="AC14">
-        <v>2.66</v>
-      </c>
-      <c r="AD14">
-        <v>1.37</v>
-      </c>
-      <c r="AE14">
-        <v>1.11</v>
-      </c>
-      <c r="AF14">
-        <v>1.55</v>
-      </c>
-      <c r="AG14">
-        <v>2.27</v>
-      </c>
-      <c r="AH14" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI14" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ14">
-        <v>1.23</v>
-      </c>
-      <c r="AK14">
-        <v>1.31</v>
       </c>
       <c r="AL14">
         <v>0</v>
@@ -2722,12 +2722,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Ansan Greeners</t>
+          <t>Jeonnam Dragons</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Gimhae City</t>
+          <t>Paju Citizen</t>
         </is>
       </c>
       <c r="G15">
@@ -2754,64 +2754,64 @@
         </is>
       </c>
       <c r="N15">
-        <v>2.91</v>
+        <v>0</v>
       </c>
       <c r="O15">
-        <v>3.38</v>
+        <v>0</v>
       </c>
       <c r="P15">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="Q15">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="R15">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="S15">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="T15">
-        <v>3.09</v>
+        <v>0</v>
       </c>
       <c r="U15">
-        <v>2.66</v>
+        <v>0</v>
       </c>
       <c r="V15">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="W15">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="X15">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="Y15">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="Z15">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="AA15">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AB15">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AC15">
-        <v>2.97</v>
+        <v>0</v>
       </c>
       <c r="AD15">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AE15">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AF15">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AG15">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2824,10 +2824,10 @@
         </is>
       </c>
       <c r="AJ15">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AK15">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AL15">
         <v>0</v>
@@ -2885,12 +2885,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Jeonnam Dragons</t>
+          <t>Gimpo Citizen</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Paju Citizen</t>
+          <t>Gyeongnam</t>
         </is>
       </c>
       <c r="G16">
@@ -2917,64 +2917,64 @@
         </is>
       </c>
       <c r="N16">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="O16">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="P16">
-        <v>0</v>
+        <v>3.51</v>
       </c>
       <c r="Q16">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="R16">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="S16">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="T16">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="U16">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V16">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="W16">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X16">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y16">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="Z16">
-        <v>0</v>
+        <v>2.93</v>
       </c>
       <c r="AA16">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AB16">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC16">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AD16">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AE16">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF16">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AG16">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -2987,10 +2987,10 @@
         </is>
       </c>
       <c r="AJ16">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK16">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AL16">
         <v>0</v>
@@ -3048,12 +3048,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Gimpo Citizen</t>
+          <t>Busan I'Park</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Gyeongnam</t>
+          <t>Seoul E-Land</t>
         </is>
       </c>
       <c r="G17">
@@ -3080,31 +3080,31 @@
         </is>
       </c>
       <c r="N17">
-        <v>1.94</v>
+        <v>2.74</v>
       </c>
       <c r="O17">
-        <v>3.34</v>
+        <v>3.44</v>
       </c>
       <c r="P17">
-        <v>3.51</v>
+        <v>2.25</v>
       </c>
       <c r="Q17">
-        <v>2.48</v>
+        <v>3.1</v>
       </c>
       <c r="R17">
-        <v>2.03</v>
+        <v>2.16</v>
       </c>
       <c r="S17">
-        <v>1.4</v>
+        <v>1.29</v>
       </c>
       <c r="T17">
-        <v>2.75</v>
+        <v>3.25</v>
       </c>
       <c r="U17">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="V17">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
       <c r="W17">
         <v>1.06</v>
@@ -3113,31 +3113,31 @@
         <v>1.03</v>
       </c>
       <c r="Y17">
-        <v>1.38</v>
+        <v>1.16</v>
       </c>
       <c r="Z17">
-        <v>2.93</v>
+        <v>4.05</v>
       </c>
       <c r="AA17">
-        <v>1.95</v>
+        <v>1.69</v>
       </c>
       <c r="AB17">
-        <v>1.75</v>
+        <v>2.07</v>
       </c>
       <c r="AC17">
-        <v>3.2</v>
+        <v>2.66</v>
       </c>
       <c r="AD17">
-        <v>1.27</v>
+        <v>1.37</v>
       </c>
       <c r="AE17">
-        <v>1.03</v>
+        <v>1.11</v>
       </c>
       <c r="AF17">
-        <v>1.93</v>
+        <v>1.55</v>
       </c>
       <c r="AG17">
-        <v>1.76</v>
+        <v>2.27</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3150,10 +3150,10 @@
         </is>
       </c>
       <c r="AJ17">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="AK17">
-        <v>1.83</v>
+        <v>1.31</v>
       </c>
       <c r="AL17">
         <v>0</v>
@@ -9405,12 +9405,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Aalesund</t>
+          <t>KFUM</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Tromsø</t>
+          <t>Kristiansund</t>
         </is>
       </c>
       <c r="G56">
@@ -9437,64 +9437,64 @@
         </is>
       </c>
       <c r="N56">
-        <v>3.52</v>
+        <v>1.57</v>
       </c>
       <c r="O56">
-        <v>3.74</v>
+        <v>4.25</v>
       </c>
       <c r="P56">
-        <v>2.02</v>
+        <v>5.73</v>
       </c>
       <c r="Q56">
-        <v>3.74</v>
+        <v>2.04</v>
       </c>
       <c r="R56">
-        <v>2.23</v>
+        <v>2.22</v>
       </c>
       <c r="S56">
-        <v>1.3</v>
+        <v>1.34</v>
       </c>
       <c r="T56">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="U56">
-        <v>2.52</v>
+        <v>2.38</v>
       </c>
       <c r="V56">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="W56">
         <v>1.08</v>
       </c>
       <c r="X56">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y56">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="Z56">
-        <v>4.33</v>
+        <v>3.84</v>
       </c>
       <c r="AA56">
-        <v>1.65</v>
+        <v>1.72</v>
       </c>
       <c r="AB56">
-        <v>2.14</v>
+        <v>2.07</v>
       </c>
       <c r="AC56">
         <v>2.57</v>
       </c>
       <c r="AD56">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AE56">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="AF56">
-        <v>1.57</v>
+        <v>1.74</v>
       </c>
       <c r="AG56">
-        <v>2.25</v>
+        <v>2</v>
       </c>
       <c r="AH56" t="inlineStr">
         <is>
@@ -9507,10 +9507,10 @@
         </is>
       </c>
       <c r="AJ56">
-        <v>1.19</v>
+        <v>1.15</v>
       </c>
       <c r="AK56">
-        <v>1.22</v>
+        <v>2.04</v>
       </c>
       <c r="AL56">
         <v>0</v>
@@ -9731,12 +9731,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>KFUM</t>
+          <t>Aalesund</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Kristiansund</t>
+          <t>Tromsø</t>
         </is>
       </c>
       <c r="G58">
@@ -9763,64 +9763,64 @@
         </is>
       </c>
       <c r="N58">
-        <v>1.57</v>
+        <v>3.52</v>
       </c>
       <c r="O58">
-        <v>4.25</v>
+        <v>3.74</v>
       </c>
       <c r="P58">
-        <v>5.73</v>
+        <v>2.02</v>
       </c>
       <c r="Q58">
-        <v>2.04</v>
+        <v>3.74</v>
       </c>
       <c r="R58">
-        <v>2.22</v>
+        <v>2.23</v>
       </c>
       <c r="S58">
-        <v>1.34</v>
+        <v>1.3</v>
       </c>
       <c r="T58">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="U58">
-        <v>2.38</v>
+        <v>2.52</v>
       </c>
       <c r="V58">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="W58">
         <v>1.08</v>
       </c>
       <c r="X58">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y58">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="Z58">
-        <v>3.84</v>
+        <v>4.33</v>
       </c>
       <c r="AA58">
-        <v>1.72</v>
+        <v>1.65</v>
       </c>
       <c r="AB58">
-        <v>2.07</v>
+        <v>2.14</v>
       </c>
       <c r="AC58">
         <v>2.57</v>
       </c>
       <c r="AD58">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="AE58">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AF58">
-        <v>1.74</v>
+        <v>1.57</v>
       </c>
       <c r="AG58">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="AH58" t="inlineStr">
         <is>
@@ -9833,10 +9833,10 @@
         </is>
       </c>
       <c r="AJ58">
-        <v>1.15</v>
+        <v>1.19</v>
       </c>
       <c r="AK58">
-        <v>2.04</v>
+        <v>1.22</v>
       </c>
       <c r="AL58">
         <v>0</v>
@@ -10057,12 +10057,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Austria Lustenau</t>
+          <t>Wolfsberger AC</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Ried</t>
+          <t>Austria Wien</t>
         </is>
       </c>
       <c r="G60">
@@ -10089,16 +10089,16 @@
         </is>
       </c>
       <c r="N60">
-        <v>2.41</v>
+        <v>2.72</v>
       </c>
       <c r="O60">
-        <v>3.42</v>
+        <v>3.32</v>
       </c>
       <c r="P60">
-        <v>2.74</v>
+        <v>2.48</v>
       </c>
       <c r="Q60">
-        <v>3.25</v>
+        <v>2.71</v>
       </c>
       <c r="R60">
         <v>2.1</v>
@@ -10107,46 +10107,46 @@
         <v>1.36</v>
       </c>
       <c r="T60">
-        <v>2.69</v>
+        <v>2.88</v>
       </c>
       <c r="U60">
-        <v>3.01</v>
+        <v>2.5</v>
       </c>
       <c r="V60">
-        <v>1.36</v>
+        <v>1.44</v>
       </c>
       <c r="W60">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="X60">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y60">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="Z60">
-        <v>2.99</v>
+        <v>3.65</v>
       </c>
       <c r="AA60">
-        <v>1.98</v>
+        <v>1.81</v>
       </c>
       <c r="AB60">
-        <v>1.71</v>
+        <v>1.91</v>
       </c>
       <c r="AC60">
-        <v>3.55</v>
+        <v>3.1</v>
       </c>
       <c r="AD60">
-        <v>1.25</v>
+        <v>1.32</v>
       </c>
       <c r="AE60">
-        <v>1.06</v>
+        <v>1.09</v>
       </c>
       <c r="AF60">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="AG60">
-        <v>1.96</v>
+        <v>2.13</v>
       </c>
       <c r="AH60" t="inlineStr">
         <is>
@@ -10159,10 +10159,10 @@
         </is>
       </c>
       <c r="AJ60">
-        <v>1.32</v>
+        <v>1.39</v>
       </c>
       <c r="AK60">
-        <v>1.45</v>
+        <v>1.53</v>
       </c>
       <c r="AL60">
         <v>0</v>
@@ -10220,12 +10220,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Wolfsberger AC</t>
+          <t>Austria Lustenau</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Austria Wien</t>
+          <t>Ried</t>
         </is>
       </c>
       <c r="G61">
@@ -10252,16 +10252,16 @@
         </is>
       </c>
       <c r="N61">
-        <v>2.72</v>
+        <v>2.41</v>
       </c>
       <c r="O61">
-        <v>3.32</v>
+        <v>3.42</v>
       </c>
       <c r="P61">
-        <v>2.48</v>
+        <v>2.74</v>
       </c>
       <c r="Q61">
-        <v>2.71</v>
+        <v>3.25</v>
       </c>
       <c r="R61">
         <v>2.1</v>
@@ -10270,62 +10270,62 @@
         <v>1.36</v>
       </c>
       <c r="T61">
-        <v>2.88</v>
+        <v>2.69</v>
       </c>
       <c r="U61">
-        <v>2.5</v>
+        <v>3.01</v>
       </c>
       <c r="V61">
-        <v>1.44</v>
+        <v>1.36</v>
       </c>
       <c r="W61">
+        <v>1.05</v>
+      </c>
+      <c r="X61">
+        <v>1.04</v>
+      </c>
+      <c r="Y61">
+        <v>1.33</v>
+      </c>
+      <c r="Z61">
+        <v>2.99</v>
+      </c>
+      <c r="AA61">
+        <v>1.98</v>
+      </c>
+      <c r="AB61">
+        <v>1.71</v>
+      </c>
+      <c r="AC61">
+        <v>3.55</v>
+      </c>
+      <c r="AD61">
+        <v>1.25</v>
+      </c>
+      <c r="AE61">
         <v>1.06</v>
       </c>
-      <c r="X61">
-        <v>1.03</v>
-      </c>
-      <c r="Y61">
-        <v>1.25</v>
-      </c>
-      <c r="Z61">
-        <v>3.65</v>
-      </c>
-      <c r="AA61">
-        <v>1.81</v>
-      </c>
-      <c r="AB61">
-        <v>1.91</v>
-      </c>
-      <c r="AC61">
-        <v>3.1</v>
-      </c>
-      <c r="AD61">
+      <c r="AF61">
+        <v>1.73</v>
+      </c>
+      <c r="AG61">
+        <v>1.96</v>
+      </c>
+      <c r="AH61" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI61" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ61">
         <v>1.32</v>
       </c>
-      <c r="AE61">
-        <v>1.09</v>
-      </c>
-      <c r="AF61">
-        <v>1.67</v>
-      </c>
-      <c r="AG61">
-        <v>2.13</v>
-      </c>
-      <c r="AH61" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI61" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ61">
-        <v>1.39</v>
-      </c>
       <c r="AK61">
-        <v>1.53</v>
+        <v>1.45</v>
       </c>
       <c r="AL61">
         <v>0</v>
@@ -10709,12 +10709,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Lyn</t>
+          <t>Egersund</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Sogndal</t>
+          <t>Sandnes Ulf</t>
         </is>
       </c>
       <c r="G64">
@@ -10741,64 +10741,64 @@
         </is>
       </c>
       <c r="N64">
-        <v>2.14</v>
+        <v>1.89</v>
       </c>
       <c r="O64">
-        <v>3.65</v>
+        <v>3.75</v>
       </c>
       <c r="P64">
-        <v>2.8</v>
+        <v>3.3</v>
       </c>
       <c r="Q64">
-        <v>2.66</v>
+        <v>2.5</v>
       </c>
       <c r="R64">
-        <v>2.42</v>
+        <v>2.5</v>
       </c>
       <c r="S64">
-        <v>1.19</v>
+        <v>1.25</v>
       </c>
       <c r="T64">
-        <v>3.84</v>
+        <v>3.75</v>
       </c>
       <c r="U64">
-        <v>2.02</v>
+        <v>2.29</v>
       </c>
       <c r="V64">
-        <v>1.8</v>
+        <v>1.6</v>
       </c>
       <c r="W64">
-        <v>1.19</v>
+        <v>1.13</v>
       </c>
       <c r="X64">
         <v>1.01</v>
       </c>
       <c r="Y64">
-        <v>1.07</v>
+        <v>1.17</v>
       </c>
       <c r="Z64">
-        <v>6.47</v>
+        <v>4.87</v>
       </c>
       <c r="AA64">
-        <v>1.39</v>
+        <v>1.57</v>
       </c>
       <c r="AB64">
-        <v>2.91</v>
+        <v>2.35</v>
       </c>
       <c r="AC64">
-        <v>1.91</v>
+        <v>2.35</v>
       </c>
       <c r="AD64">
-        <v>1.85</v>
+        <v>1.52</v>
       </c>
       <c r="AE64">
-        <v>1.35</v>
+        <v>1.22</v>
       </c>
       <c r="AF64">
-        <v>1.33</v>
+        <v>1.49</v>
       </c>
       <c r="AG64">
-        <v>2.7</v>
+        <v>2.44</v>
       </c>
       <c r="AH64" t="inlineStr">
         <is>
@@ -10814,7 +10814,7 @@
         <v>1.2</v>
       </c>
       <c r="AK64">
-        <v>1.47</v>
+        <v>1.79</v>
       </c>
       <c r="AL64">
         <v>0</v>
@@ -10872,12 +10872,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Egersund</t>
+          <t>Odd</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Sandnes Ulf</t>
+          <t>Åsane</t>
         </is>
       </c>
       <c r="G65">
@@ -10904,64 +10904,64 @@
         </is>
       </c>
       <c r="N65">
-        <v>1.89</v>
+        <v>1.39</v>
       </c>
       <c r="O65">
-        <v>3.75</v>
+        <v>4.85</v>
       </c>
       <c r="P65">
-        <v>3.3</v>
+        <v>5.55</v>
       </c>
       <c r="Q65">
-        <v>2.5</v>
+        <v>1.87</v>
       </c>
       <c r="R65">
-        <v>2.5</v>
+        <v>2.51</v>
       </c>
       <c r="S65">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="T65">
-        <v>3.75</v>
+        <v>4.4</v>
       </c>
       <c r="U65">
-        <v>2.29</v>
+        <v>1.99</v>
       </c>
       <c r="V65">
-        <v>1.6</v>
+        <v>1.77</v>
       </c>
       <c r="W65">
-        <v>1.13</v>
+        <v>1.2</v>
       </c>
       <c r="X65">
         <v>1.01</v>
       </c>
       <c r="Y65">
-        <v>1.17</v>
+        <v>1.1</v>
       </c>
       <c r="Z65">
-        <v>4.87</v>
+        <v>6.6</v>
       </c>
       <c r="AA65">
-        <v>1.57</v>
+        <v>1.36</v>
       </c>
       <c r="AB65">
-        <v>2.35</v>
+        <v>3.1</v>
       </c>
       <c r="AC65">
-        <v>2.35</v>
+        <v>1.88</v>
       </c>
       <c r="AD65">
-        <v>1.52</v>
+        <v>1.8</v>
       </c>
       <c r="AE65">
-        <v>1.22</v>
+        <v>1.33</v>
       </c>
       <c r="AF65">
-        <v>1.49</v>
+        <v>1.45</v>
       </c>
       <c r="AG65">
-        <v>2.44</v>
+        <v>2.25</v>
       </c>
       <c r="AH65" t="inlineStr">
         <is>
@@ -10974,10 +10974,10 @@
         </is>
       </c>
       <c r="AJ65">
-        <v>1.2</v>
+        <v>1.13</v>
       </c>
       <c r="AK65">
-        <v>1.79</v>
+        <v>2.83</v>
       </c>
       <c r="AL65">
         <v>0</v>
@@ -11035,12 +11035,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Odd</t>
+          <t>Lyn</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Åsane</t>
+          <t>Sogndal</t>
         </is>
       </c>
       <c r="G66">
@@ -11067,64 +11067,64 @@
         </is>
       </c>
       <c r="N66">
-        <v>1.39</v>
+        <v>2.14</v>
       </c>
       <c r="O66">
-        <v>4.85</v>
+        <v>3.65</v>
       </c>
       <c r="P66">
-        <v>5.55</v>
+        <v>2.8</v>
       </c>
       <c r="Q66">
-        <v>1.87</v>
+        <v>2.66</v>
       </c>
       <c r="R66">
-        <v>2.51</v>
+        <v>2.42</v>
       </c>
       <c r="S66">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="T66">
-        <v>4.4</v>
+        <v>3.84</v>
       </c>
       <c r="U66">
-        <v>1.99</v>
+        <v>2.02</v>
       </c>
       <c r="V66">
-        <v>1.77</v>
+        <v>1.8</v>
       </c>
       <c r="W66">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="X66">
         <v>1.01</v>
       </c>
       <c r="Y66">
-        <v>1.1</v>
+        <v>1.07</v>
       </c>
       <c r="Z66">
-        <v>6.6</v>
+        <v>6.47</v>
       </c>
       <c r="AA66">
-        <v>1.36</v>
+        <v>1.39</v>
       </c>
       <c r="AB66">
-        <v>3.1</v>
+        <v>2.91</v>
       </c>
       <c r="AC66">
-        <v>1.88</v>
+        <v>1.91</v>
       </c>
       <c r="AD66">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="AE66">
+        <v>1.35</v>
+      </c>
+      <c r="AF66">
         <v>1.33</v>
       </c>
-      <c r="AF66">
-        <v>1.45</v>
-      </c>
       <c r="AG66">
-        <v>2.25</v>
+        <v>2.7</v>
       </c>
       <c r="AH66" t="inlineStr">
         <is>
@@ -11137,10 +11137,10 @@
         </is>
       </c>
       <c r="AJ66">
-        <v>1.13</v>
+        <v>1.2</v>
       </c>
       <c r="AK66">
-        <v>2.83</v>
+        <v>1.47</v>
       </c>
       <c r="AL66">
         <v>0</v>

--- a/jogos_2026-08-02.xlsx
+++ b/jogos_2026-08-02.xlsx
@@ -2070,12 +2070,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Jeju United</t>
+          <t>Ulsan</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Incheon United</t>
+          <t>Anyang</t>
         </is>
       </c>
       <c r="G11">
@@ -2102,64 +2102,64 @@
         </is>
       </c>
       <c r="N11">
-        <v>3.11</v>
+        <v>1.91</v>
       </c>
       <c r="O11">
-        <v>2.98</v>
+        <v>3.55</v>
       </c>
       <c r="P11">
-        <v>2.44</v>
+        <v>3.81</v>
       </c>
       <c r="Q11">
-        <v>3.6</v>
+        <v>2.28</v>
       </c>
       <c r="R11">
-        <v>1.93</v>
+        <v>2.06</v>
       </c>
       <c r="S11">
-        <v>1.48</v>
+        <v>1.35</v>
       </c>
       <c r="T11">
-        <v>2.34</v>
+        <v>2.94</v>
       </c>
       <c r="U11">
+        <v>2.75</v>
+      </c>
+      <c r="V11">
+        <v>1.41</v>
+      </c>
+      <c r="W11">
+        <v>1.07</v>
+      </c>
+      <c r="X11">
+        <v>1</v>
+      </c>
+      <c r="Y11">
+        <v>1.22</v>
+      </c>
+      <c r="Z11">
         <v>3.4</v>
       </c>
-      <c r="V11">
-        <v>1.3</v>
-      </c>
-      <c r="W11">
-        <v>1.01</v>
-      </c>
-      <c r="X11">
-        <v>1.05</v>
-      </c>
-      <c r="Y11">
-        <v>1.4</v>
-      </c>
-      <c r="Z11">
-        <v>2.57</v>
-      </c>
       <c r="AA11">
-        <v>2.38</v>
+        <v>1.84</v>
       </c>
       <c r="AB11">
-        <v>1.56</v>
+        <v>1.87</v>
       </c>
       <c r="AC11">
-        <v>4.63</v>
+        <v>2.94</v>
       </c>
       <c r="AD11">
-        <v>1.19</v>
+        <v>1.31</v>
       </c>
       <c r="AE11">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="AF11">
-        <v>1.82</v>
+        <v>1.7</v>
       </c>
       <c r="AG11">
-        <v>1.78</v>
+        <v>2.04</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2172,10 +2172,10 @@
         </is>
       </c>
       <c r="AJ11">
-        <v>1.33</v>
+        <v>1.22</v>
       </c>
       <c r="AK11">
-        <v>1.36</v>
+        <v>1.9</v>
       </c>
       <c r="AL11">
         <v>0</v>
@@ -2233,12 +2233,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Ulsan</t>
+          <t>Daejeon Citizen</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Anyang</t>
+          <t>Gwangju</t>
         </is>
       </c>
       <c r="G12">
@@ -2265,64 +2265,64 @@
         </is>
       </c>
       <c r="N12">
-        <v>1.91</v>
+        <v>1.49</v>
       </c>
       <c r="O12">
-        <v>3.55</v>
+        <v>4.15</v>
       </c>
       <c r="P12">
-        <v>3.81</v>
+        <v>6.41</v>
       </c>
       <c r="Q12">
+        <v>1.95</v>
+      </c>
+      <c r="R12">
         <v>2.28</v>
       </c>
-      <c r="R12">
-        <v>2.06</v>
-      </c>
       <c r="S12">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="T12">
-        <v>2.94</v>
+        <v>2.9</v>
       </c>
       <c r="U12">
-        <v>2.75</v>
+        <v>2.7</v>
       </c>
       <c r="V12">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="W12">
         <v>1.07</v>
       </c>
       <c r="X12">
-        <v>1</v>
+        <v>1.05</v>
       </c>
       <c r="Y12">
         <v>1.22</v>
       </c>
       <c r="Z12">
-        <v>3.4</v>
+        <v>3.54</v>
       </c>
       <c r="AA12">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="AB12">
         <v>1.87</v>
       </c>
       <c r="AC12">
-        <v>2.94</v>
+        <v>2.89</v>
       </c>
       <c r="AD12">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="AE12">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="AF12">
-        <v>1.7</v>
+        <v>1.9</v>
       </c>
       <c r="AG12">
-        <v>2.04</v>
+        <v>1.8</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2335,10 +2335,10 @@
         </is>
       </c>
       <c r="AJ12">
-        <v>1.22</v>
+        <v>1.19</v>
       </c>
       <c r="AK12">
-        <v>1.9</v>
+        <v>2.7</v>
       </c>
       <c r="AL12">
         <v>0</v>
@@ -2396,12 +2396,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Daejeon Citizen</t>
+          <t>Jeju United</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Gwangju</t>
+          <t>Incheon United</t>
         </is>
       </c>
       <c r="G13">
@@ -2428,64 +2428,64 @@
         </is>
       </c>
       <c r="N13">
-        <v>1.49</v>
+        <v>3.11</v>
       </c>
       <c r="O13">
-        <v>4.15</v>
+        <v>2.98</v>
       </c>
       <c r="P13">
-        <v>6.41</v>
+        <v>2.44</v>
       </c>
       <c r="Q13">
-        <v>1.95</v>
+        <v>3.6</v>
       </c>
       <c r="R13">
-        <v>2.28</v>
+        <v>1.93</v>
       </c>
       <c r="S13">
-        <v>1.33</v>
+        <v>1.48</v>
       </c>
       <c r="T13">
-        <v>2.9</v>
+        <v>2.34</v>
       </c>
       <c r="U13">
-        <v>2.7</v>
+        <v>3.4</v>
       </c>
       <c r="V13">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="W13">
-        <v>1.07</v>
+        <v>1.01</v>
       </c>
       <c r="X13">
         <v>1.05</v>
       </c>
       <c r="Y13">
-        <v>1.22</v>
+        <v>1.4</v>
       </c>
       <c r="Z13">
-        <v>3.54</v>
+        <v>2.57</v>
       </c>
       <c r="AA13">
-        <v>1.85</v>
+        <v>2.38</v>
       </c>
       <c r="AB13">
-        <v>1.87</v>
+        <v>1.56</v>
       </c>
       <c r="AC13">
-        <v>2.89</v>
+        <v>4.63</v>
       </c>
       <c r="AD13">
-        <v>1.32</v>
+        <v>1.19</v>
       </c>
       <c r="AE13">
-        <v>1.09</v>
+        <v>1.05</v>
       </c>
       <c r="AF13">
-        <v>1.9</v>
+        <v>1.82</v>
       </c>
       <c r="AG13">
-        <v>1.8</v>
+        <v>1.78</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2498,10 +2498,10 @@
         </is>
       </c>
       <c r="AJ13">
-        <v>1.19</v>
+        <v>1.33</v>
       </c>
       <c r="AK13">
-        <v>2.7</v>
+        <v>1.36</v>
       </c>
       <c r="AL13">
         <v>0</v>
@@ -2559,12 +2559,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Ansan Greeners</t>
+          <t>Jeonnam Dragons</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Gimhae City</t>
+          <t>Paju Citizen</t>
         </is>
       </c>
       <c r="G14">
@@ -2591,64 +2591,64 @@
         </is>
       </c>
       <c r="N14">
-        <v>2.91</v>
+        <v>0</v>
       </c>
       <c r="O14">
-        <v>3.38</v>
+        <v>0</v>
       </c>
       <c r="P14">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="Q14">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="R14">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="S14">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="T14">
-        <v>3.09</v>
+        <v>0</v>
       </c>
       <c r="U14">
-        <v>2.66</v>
+        <v>0</v>
       </c>
       <c r="V14">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="W14">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="X14">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="Y14">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="Z14">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="AA14">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AB14">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AC14">
-        <v>2.97</v>
+        <v>0</v>
       </c>
       <c r="AD14">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AE14">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AF14">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AG14">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2661,10 +2661,10 @@
         </is>
       </c>
       <c r="AJ14">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AK14">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AL14">
         <v>0</v>
@@ -2722,12 +2722,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Jeonnam Dragons</t>
+          <t>Ansan Greeners</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Paju Citizen</t>
+          <t>Gimhae City</t>
         </is>
       </c>
       <c r="G15">
@@ -2754,64 +2754,64 @@
         </is>
       </c>
       <c r="N15">
-        <v>0</v>
+        <v>2.91</v>
       </c>
       <c r="O15">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="P15">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="Q15">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="R15">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="S15">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="T15">
-        <v>0</v>
+        <v>3.09</v>
       </c>
       <c r="U15">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="V15">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="W15">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X15">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y15">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="Z15">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="AA15">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AB15">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AC15">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="AD15">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AE15">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AF15">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AG15">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2824,10 +2824,10 @@
         </is>
       </c>
       <c r="AJ15">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AK15">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AL15">
         <v>0</v>
@@ -2885,12 +2885,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Gimpo Citizen</t>
+          <t>Busan I'Park</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Gyeongnam</t>
+          <t>Seoul E-Land</t>
         </is>
       </c>
       <c r="G16">
@@ -2917,31 +2917,31 @@
         </is>
       </c>
       <c r="N16">
-        <v>1.94</v>
+        <v>2.74</v>
       </c>
       <c r="O16">
-        <v>3.34</v>
+        <v>3.44</v>
       </c>
       <c r="P16">
-        <v>3.51</v>
+        <v>2.25</v>
       </c>
       <c r="Q16">
-        <v>2.48</v>
+        <v>3.1</v>
       </c>
       <c r="R16">
-        <v>2.03</v>
+        <v>2.16</v>
       </c>
       <c r="S16">
-        <v>1.4</v>
+        <v>1.29</v>
       </c>
       <c r="T16">
-        <v>2.75</v>
+        <v>3.25</v>
       </c>
       <c r="U16">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="V16">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
       <c r="W16">
         <v>1.06</v>
@@ -2950,31 +2950,31 @@
         <v>1.03</v>
       </c>
       <c r="Y16">
-        <v>1.38</v>
+        <v>1.16</v>
       </c>
       <c r="Z16">
-        <v>2.93</v>
+        <v>4.05</v>
       </c>
       <c r="AA16">
-        <v>1.95</v>
+        <v>1.69</v>
       </c>
       <c r="AB16">
-        <v>1.75</v>
+        <v>2.07</v>
       </c>
       <c r="AC16">
-        <v>3.2</v>
+        <v>2.66</v>
       </c>
       <c r="AD16">
-        <v>1.27</v>
+        <v>1.37</v>
       </c>
       <c r="AE16">
-        <v>1.03</v>
+        <v>1.11</v>
       </c>
       <c r="AF16">
-        <v>1.93</v>
+        <v>1.55</v>
       </c>
       <c r="AG16">
-        <v>1.76</v>
+        <v>2.27</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -2987,10 +2987,10 @@
         </is>
       </c>
       <c r="AJ16">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="AK16">
-        <v>1.83</v>
+        <v>1.31</v>
       </c>
       <c r="AL16">
         <v>0</v>
@@ -3048,12 +3048,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Busan I'Park</t>
+          <t>Gimpo Citizen</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Seoul E-Land</t>
+          <t>Gyeongnam</t>
         </is>
       </c>
       <c r="G17">
@@ -3080,31 +3080,31 @@
         </is>
       </c>
       <c r="N17">
-        <v>2.74</v>
+        <v>1.94</v>
       </c>
       <c r="O17">
-        <v>3.44</v>
+        <v>3.34</v>
       </c>
       <c r="P17">
-        <v>2.25</v>
+        <v>3.51</v>
       </c>
       <c r="Q17">
-        <v>3.1</v>
+        <v>2.48</v>
       </c>
       <c r="R17">
-        <v>2.16</v>
+        <v>2.03</v>
       </c>
       <c r="S17">
-        <v>1.29</v>
+        <v>1.4</v>
       </c>
       <c r="T17">
-        <v>3.25</v>
+        <v>2.75</v>
       </c>
       <c r="U17">
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="V17">
-        <v>1.5</v>
+        <v>1.33</v>
       </c>
       <c r="W17">
         <v>1.06</v>
@@ -3113,31 +3113,31 @@
         <v>1.03</v>
       </c>
       <c r="Y17">
-        <v>1.16</v>
+        <v>1.38</v>
       </c>
       <c r="Z17">
-        <v>4.05</v>
+        <v>2.93</v>
       </c>
       <c r="AA17">
-        <v>1.69</v>
+        <v>1.95</v>
       </c>
       <c r="AB17">
-        <v>2.07</v>
+        <v>1.75</v>
       </c>
       <c r="AC17">
-        <v>2.66</v>
+        <v>3.2</v>
       </c>
       <c r="AD17">
-        <v>1.37</v>
+        <v>1.27</v>
       </c>
       <c r="AE17">
-        <v>1.11</v>
+        <v>1.03</v>
       </c>
       <c r="AF17">
-        <v>1.55</v>
+        <v>1.93</v>
       </c>
       <c r="AG17">
-        <v>2.27</v>
+        <v>1.76</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3150,10 +3150,10 @@
         </is>
       </c>
       <c r="AJ17">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="AK17">
-        <v>1.31</v>
+        <v>1.83</v>
       </c>
       <c r="AL17">
         <v>0</v>
@@ -10709,12 +10709,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Egersund</t>
+          <t>Odd</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Sandnes Ulf</t>
+          <t>Åsane</t>
         </is>
       </c>
       <c r="G64">
@@ -10741,64 +10741,64 @@
         </is>
       </c>
       <c r="N64">
-        <v>1.89</v>
+        <v>1.39</v>
       </c>
       <c r="O64">
-        <v>3.75</v>
+        <v>4.85</v>
       </c>
       <c r="P64">
-        <v>3.3</v>
+        <v>5.55</v>
       </c>
       <c r="Q64">
-        <v>2.5</v>
+        <v>1.87</v>
       </c>
       <c r="R64">
-        <v>2.5</v>
+        <v>2.51</v>
       </c>
       <c r="S64">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="T64">
-        <v>3.75</v>
+        <v>4.4</v>
       </c>
       <c r="U64">
-        <v>2.29</v>
+        <v>1.99</v>
       </c>
       <c r="V64">
-        <v>1.6</v>
+        <v>1.77</v>
       </c>
       <c r="W64">
-        <v>1.13</v>
+        <v>1.2</v>
       </c>
       <c r="X64">
         <v>1.01</v>
       </c>
       <c r="Y64">
-        <v>1.17</v>
+        <v>1.1</v>
       </c>
       <c r="Z64">
-        <v>4.87</v>
+        <v>6.6</v>
       </c>
       <c r="AA64">
-        <v>1.57</v>
+        <v>1.36</v>
       </c>
       <c r="AB64">
-        <v>2.35</v>
+        <v>3.1</v>
       </c>
       <c r="AC64">
-        <v>2.35</v>
+        <v>1.88</v>
       </c>
       <c r="AD64">
-        <v>1.52</v>
+        <v>1.8</v>
       </c>
       <c r="AE64">
-        <v>1.22</v>
+        <v>1.33</v>
       </c>
       <c r="AF64">
-        <v>1.49</v>
+        <v>1.45</v>
       </c>
       <c r="AG64">
-        <v>2.44</v>
+        <v>2.25</v>
       </c>
       <c r="AH64" t="inlineStr">
         <is>
@@ -10811,10 +10811,10 @@
         </is>
       </c>
       <c r="AJ64">
-        <v>1.2</v>
+        <v>1.13</v>
       </c>
       <c r="AK64">
-        <v>1.79</v>
+        <v>2.83</v>
       </c>
       <c r="AL64">
         <v>0</v>
@@ -10872,12 +10872,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Odd</t>
+          <t>Raufoss</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Åsane</t>
+          <t>Stabæk</t>
         </is>
       </c>
       <c r="G65">
@@ -10904,43 +10904,43 @@
         </is>
       </c>
       <c r="N65">
-        <v>1.39</v>
+        <v>4.79</v>
       </c>
       <c r="O65">
-        <v>4.85</v>
+        <v>4.55</v>
       </c>
       <c r="P65">
-        <v>5.55</v>
+        <v>1.55</v>
       </c>
       <c r="Q65">
-        <v>1.87</v>
+        <v>4.09</v>
       </c>
       <c r="R65">
-        <v>2.51</v>
+        <v>2.56</v>
       </c>
       <c r="S65">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="T65">
-        <v>4.4</v>
+        <v>4.2</v>
       </c>
       <c r="U65">
         <v>1.99</v>
       </c>
       <c r="V65">
-        <v>1.77</v>
+        <v>1.83</v>
       </c>
       <c r="W65">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="X65">
         <v>1.01</v>
       </c>
       <c r="Y65">
-        <v>1.1</v>
+        <v>1.05</v>
       </c>
       <c r="Z65">
-        <v>6.6</v>
+        <v>6.5</v>
       </c>
       <c r="AA65">
         <v>1.36</v>
@@ -10949,19 +10949,19 @@
         <v>3.1</v>
       </c>
       <c r="AC65">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="AD65">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="AE65">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
       <c r="AF65">
-        <v>1.45</v>
+        <v>1.4</v>
       </c>
       <c r="AG65">
-        <v>2.25</v>
+        <v>2.73</v>
       </c>
       <c r="AH65" t="inlineStr">
         <is>
@@ -10974,10 +10974,10 @@
         </is>
       </c>
       <c r="AJ65">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="AK65">
-        <v>2.83</v>
+        <v>1.15</v>
       </c>
       <c r="AL65">
         <v>0</v>
@@ -11035,12 +11035,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Lyn</t>
+          <t>Egersund</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Sogndal</t>
+          <t>Sandnes Ulf</t>
         </is>
       </c>
       <c r="G66">
@@ -11067,64 +11067,64 @@
         </is>
       </c>
       <c r="N66">
-        <v>2.14</v>
+        <v>1.89</v>
       </c>
       <c r="O66">
-        <v>3.65</v>
+        <v>3.75</v>
       </c>
       <c r="P66">
-        <v>2.8</v>
+        <v>3.3</v>
       </c>
       <c r="Q66">
-        <v>2.66</v>
+        <v>2.5</v>
       </c>
       <c r="R66">
-        <v>2.42</v>
+        <v>2.5</v>
       </c>
       <c r="S66">
-        <v>1.19</v>
+        <v>1.25</v>
       </c>
       <c r="T66">
-        <v>3.84</v>
+        <v>3.75</v>
       </c>
       <c r="U66">
-        <v>2.02</v>
+        <v>2.29</v>
       </c>
       <c r="V66">
-        <v>1.8</v>
+        <v>1.6</v>
       </c>
       <c r="W66">
-        <v>1.19</v>
+        <v>1.13</v>
       </c>
       <c r="X66">
         <v>1.01</v>
       </c>
       <c r="Y66">
-        <v>1.07</v>
+        <v>1.17</v>
       </c>
       <c r="Z66">
-        <v>6.47</v>
+        <v>4.87</v>
       </c>
       <c r="AA66">
-        <v>1.39</v>
+        <v>1.57</v>
       </c>
       <c r="AB66">
-        <v>2.91</v>
+        <v>2.35</v>
       </c>
       <c r="AC66">
-        <v>1.91</v>
+        <v>2.35</v>
       </c>
       <c r="AD66">
-        <v>1.85</v>
+        <v>1.52</v>
       </c>
       <c r="AE66">
-        <v>1.35</v>
+        <v>1.22</v>
       </c>
       <c r="AF66">
-        <v>1.33</v>
+        <v>1.49</v>
       </c>
       <c r="AG66">
-        <v>2.7</v>
+        <v>2.44</v>
       </c>
       <c r="AH66" t="inlineStr">
         <is>
@@ -11140,7 +11140,7 @@
         <v>1.2</v>
       </c>
       <c r="AK66">
-        <v>1.47</v>
+        <v>1.79</v>
       </c>
       <c r="AL66">
         <v>0</v>
@@ -11198,12 +11198,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Raufoss</t>
+          <t>Lyn</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Stabæk</t>
+          <t>Sogndal</t>
         </is>
       </c>
       <c r="G67">
@@ -11230,64 +11230,64 @@
         </is>
       </c>
       <c r="N67">
-        <v>4.79</v>
+        <v>2.14</v>
       </c>
       <c r="O67">
-        <v>4.55</v>
+        <v>3.65</v>
       </c>
       <c r="P67">
-        <v>1.55</v>
+        <v>2.8</v>
       </c>
       <c r="Q67">
-        <v>4.09</v>
+        <v>2.66</v>
       </c>
       <c r="R67">
-        <v>2.56</v>
+        <v>2.42</v>
       </c>
       <c r="S67">
-        <v>1.17</v>
+        <v>1.19</v>
       </c>
       <c r="T67">
-        <v>4.2</v>
+        <v>3.84</v>
       </c>
       <c r="U67">
-        <v>1.99</v>
+        <v>2.02</v>
       </c>
       <c r="V67">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="W67">
-        <v>1.22</v>
+        <v>1.19</v>
       </c>
       <c r="X67">
         <v>1.01</v>
       </c>
       <c r="Y67">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="Z67">
-        <v>6.5</v>
+        <v>6.47</v>
       </c>
       <c r="AA67">
-        <v>1.36</v>
+        <v>1.39</v>
       </c>
       <c r="AB67">
-        <v>3.1</v>
+        <v>2.91</v>
       </c>
       <c r="AC67">
-        <v>1.87</v>
+        <v>1.91</v>
       </c>
       <c r="AD67">
-        <v>1.81</v>
+        <v>1.85</v>
       </c>
       <c r="AE67">
-        <v>1.28</v>
+        <v>1.35</v>
       </c>
       <c r="AF67">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="AG67">
-        <v>2.73</v>
+        <v>2.7</v>
       </c>
       <c r="AH67" t="inlineStr">
         <is>
@@ -11300,10 +11300,10 @@
         </is>
       </c>
       <c r="AJ67">
-        <v>1.15</v>
+        <v>1.2</v>
       </c>
       <c r="AK67">
-        <v>1.15</v>
+        <v>1.47</v>
       </c>
       <c r="AL67">
         <v>0</v>
@@ -12697,13 +12697,13 @@
         </is>
       </c>
       <c r="N76">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="O76">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="P76">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="Q76">
         <v>0</v>
@@ -15794,13 +15794,13 @@
         </is>
       </c>
       <c r="N95">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="O95">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="P95">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="Q95">
         <v>0</v>
@@ -15833,10 +15833,10 @@
         <v>0</v>
       </c>
       <c r="AA95">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB95">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC95">
         <v>0</v>
@@ -17913,13 +17913,13 @@
         </is>
       </c>
       <c r="N108">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="O108">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="P108">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="Q108">
         <v>0</v>
@@ -18076,13 +18076,13 @@
         </is>
       </c>
       <c r="N109">
-        <v>0</v>
+        <v>3.81</v>
       </c>
       <c r="O109">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="P109">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q109">
         <v>0</v>
@@ -18239,13 +18239,13 @@
         </is>
       </c>
       <c r="N110">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="O110">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="P110">
-        <v>0</v>
+        <v>3.82</v>
       </c>
       <c r="Q110">
         <v>0</v>
@@ -18402,13 +18402,13 @@
         </is>
       </c>
       <c r="N111">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="O111">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="P111">
-        <v>0</v>
+        <v>3.82</v>
       </c>
       <c r="Q111">
         <v>0</v>
@@ -18565,13 +18565,13 @@
         </is>
       </c>
       <c r="N112">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="O112">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="P112">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="Q112">
         <v>0</v>
@@ -18604,10 +18604,10 @@
         <v>0</v>
       </c>
       <c r="AA112">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AB112">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC112">
         <v>0</v>
@@ -19511,12 +19511,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Patronato</t>
+          <t>Deportivo Maipú</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Quilmes</t>
+          <t>Atlanta</t>
         </is>
       </c>
       <c r="G118">
@@ -19543,13 +19543,13 @@
         </is>
       </c>
       <c r="N118">
-        <v>2.36</v>
+        <v>2.75</v>
       </c>
       <c r="O118">
-        <v>2.71</v>
+        <v>2.73</v>
       </c>
       <c r="P118">
-        <v>3.26</v>
+        <v>2.63</v>
       </c>
       <c r="Q118">
         <v>0</v>
@@ -19576,10 +19576,10 @@
         <v>0</v>
       </c>
       <c r="Y118">
-        <v>1.72</v>
+        <v>1.55</v>
       </c>
       <c r="Z118">
-        <v>1.96</v>
+        <v>2.25</v>
       </c>
       <c r="AA118">
         <v>0</v>
@@ -19674,12 +19674,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Deportivo Maipú</t>
+          <t>Temperley</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Atlanta</t>
+          <t>Gimnasia y Tiro</t>
         </is>
       </c>
       <c r="G119">
@@ -19706,13 +19706,13 @@
         </is>
       </c>
       <c r="N119">
-        <v>2.75</v>
+        <v>1.96</v>
       </c>
       <c r="O119">
-        <v>2.73</v>
+        <v>2.85</v>
       </c>
       <c r="P119">
-        <v>2.63</v>
+        <v>4.2</v>
       </c>
       <c r="Q119">
         <v>0</v>
@@ -19739,10 +19739,10 @@
         <v>0</v>
       </c>
       <c r="Y119">
-        <v>1.55</v>
+        <v>1.6</v>
       </c>
       <c r="Z119">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="AA119">
         <v>0</v>
@@ -19837,12 +19837,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Temperley</t>
+          <t>Patronato</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Gimnasia y Tiro</t>
+          <t>Quilmes</t>
         </is>
       </c>
       <c r="G120">
@@ -19869,43 +19869,43 @@
         </is>
       </c>
       <c r="N120">
+        <v>2.36</v>
+      </c>
+      <c r="O120">
+        <v>2.71</v>
+      </c>
+      <c r="P120">
+        <v>3.26</v>
+      </c>
+      <c r="Q120">
+        <v>0</v>
+      </c>
+      <c r="R120">
+        <v>0</v>
+      </c>
+      <c r="S120">
+        <v>0</v>
+      </c>
+      <c r="T120">
+        <v>0</v>
+      </c>
+      <c r="U120">
+        <v>0</v>
+      </c>
+      <c r="V120">
+        <v>0</v>
+      </c>
+      <c r="W120">
+        <v>0</v>
+      </c>
+      <c r="X120">
+        <v>0</v>
+      </c>
+      <c r="Y120">
+        <v>1.72</v>
+      </c>
+      <c r="Z120">
         <v>1.96</v>
-      </c>
-      <c r="O120">
-        <v>2.85</v>
-      </c>
-      <c r="P120">
-        <v>4.2</v>
-      </c>
-      <c r="Q120">
-        <v>0</v>
-      </c>
-      <c r="R120">
-        <v>0</v>
-      </c>
-      <c r="S120">
-        <v>0</v>
-      </c>
-      <c r="T120">
-        <v>0</v>
-      </c>
-      <c r="U120">
-        <v>0</v>
-      </c>
-      <c r="V120">
-        <v>0</v>
-      </c>
-      <c r="W120">
-        <v>0</v>
-      </c>
-      <c r="X120">
-        <v>0</v>
-      </c>
-      <c r="Y120">
-        <v>1.6</v>
-      </c>
-      <c r="Z120">
-        <v>2.15</v>
       </c>
       <c r="AA120">
         <v>0</v>

--- a/jogos_2026-08-02.xlsx
+++ b/jogos_2026-08-02.xlsx
@@ -2233,12 +2233,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Daejeon Citizen</t>
+          <t>Jeju United</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Gwangju</t>
+          <t>Incheon United</t>
         </is>
       </c>
       <c r="G12">
@@ -2265,64 +2265,64 @@
         </is>
       </c>
       <c r="N12">
-        <v>1.49</v>
+        <v>3.11</v>
       </c>
       <c r="O12">
-        <v>4.15</v>
+        <v>2.98</v>
       </c>
       <c r="P12">
-        <v>6.41</v>
+        <v>2.44</v>
       </c>
       <c r="Q12">
-        <v>1.95</v>
+        <v>3.6</v>
       </c>
       <c r="R12">
-        <v>2.28</v>
+        <v>1.93</v>
       </c>
       <c r="S12">
-        <v>1.33</v>
+        <v>1.48</v>
       </c>
       <c r="T12">
-        <v>2.9</v>
+        <v>2.34</v>
       </c>
       <c r="U12">
-        <v>2.7</v>
+        <v>3.4</v>
       </c>
       <c r="V12">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="W12">
-        <v>1.07</v>
+        <v>1.01</v>
       </c>
       <c r="X12">
         <v>1.05</v>
       </c>
       <c r="Y12">
-        <v>1.22</v>
+        <v>1.4</v>
       </c>
       <c r="Z12">
-        <v>3.54</v>
+        <v>2.57</v>
       </c>
       <c r="AA12">
-        <v>1.85</v>
+        <v>2.38</v>
       </c>
       <c r="AB12">
-        <v>1.87</v>
+        <v>1.56</v>
       </c>
       <c r="AC12">
-        <v>2.89</v>
+        <v>4.63</v>
       </c>
       <c r="AD12">
-        <v>1.32</v>
+        <v>1.19</v>
       </c>
       <c r="AE12">
-        <v>1.09</v>
+        <v>1.05</v>
       </c>
       <c r="AF12">
-        <v>1.9</v>
+        <v>1.82</v>
       </c>
       <c r="AG12">
-        <v>1.8</v>
+        <v>1.78</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2335,10 +2335,10 @@
         </is>
       </c>
       <c r="AJ12">
-        <v>1.19</v>
+        <v>1.33</v>
       </c>
       <c r="AK12">
-        <v>2.7</v>
+        <v>1.36</v>
       </c>
       <c r="AL12">
         <v>0</v>
@@ -2396,12 +2396,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Jeju United</t>
+          <t>Daejeon Citizen</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Incheon United</t>
+          <t>Gwangju</t>
         </is>
       </c>
       <c r="G13">
@@ -2428,80 +2428,80 @@
         </is>
       </c>
       <c r="N13">
-        <v>3.11</v>
+        <v>1.49</v>
       </c>
       <c r="O13">
-        <v>2.98</v>
+        <v>4.15</v>
       </c>
       <c r="P13">
-        <v>2.44</v>
+        <v>6.41</v>
       </c>
       <c r="Q13">
-        <v>3.6</v>
+        <v>1.95</v>
       </c>
       <c r="R13">
-        <v>1.93</v>
+        <v>2.28</v>
       </c>
       <c r="S13">
-        <v>1.48</v>
+        <v>1.33</v>
       </c>
       <c r="T13">
-        <v>2.34</v>
+        <v>2.9</v>
       </c>
       <c r="U13">
-        <v>3.4</v>
+        <v>2.7</v>
       </c>
       <c r="V13">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="W13">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="X13">
         <v>1.05</v>
       </c>
       <c r="Y13">
-        <v>1.4</v>
+        <v>1.22</v>
       </c>
       <c r="Z13">
-        <v>2.57</v>
+        <v>3.54</v>
       </c>
       <c r="AA13">
-        <v>2.38</v>
+        <v>1.85</v>
       </c>
       <c r="AB13">
-        <v>1.56</v>
+        <v>1.87</v>
       </c>
       <c r="AC13">
-        <v>4.63</v>
+        <v>2.89</v>
       </c>
       <c r="AD13">
+        <v>1.32</v>
+      </c>
+      <c r="AE13">
+        <v>1.09</v>
+      </c>
+      <c r="AF13">
+        <v>1.9</v>
+      </c>
+      <c r="AG13">
+        <v>1.8</v>
+      </c>
+      <c r="AH13" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI13" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ13">
         <v>1.19</v>
       </c>
-      <c r="AE13">
-        <v>1.05</v>
-      </c>
-      <c r="AF13">
-        <v>1.82</v>
-      </c>
-      <c r="AG13">
-        <v>1.78</v>
-      </c>
-      <c r="AH13" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI13" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ13">
-        <v>1.33</v>
-      </c>
       <c r="AK13">
-        <v>1.36</v>
+        <v>2.7</v>
       </c>
       <c r="AL13">
         <v>0</v>
@@ -2722,12 +2722,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Ansan Greeners</t>
+          <t>Busan I'Park</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Gimhae City</t>
+          <t>Seoul E-Land</t>
         </is>
       </c>
       <c r="G15">
@@ -2754,80 +2754,80 @@
         </is>
       </c>
       <c r="N15">
-        <v>2.91</v>
+        <v>2.74</v>
       </c>
       <c r="O15">
-        <v>3.38</v>
+        <v>3.44</v>
       </c>
       <c r="P15">
-        <v>2.18</v>
+        <v>2.25</v>
       </c>
       <c r="Q15">
-        <v>3.28</v>
+        <v>3.1</v>
       </c>
       <c r="R15">
-        <v>2.05</v>
+        <v>2.16</v>
       </c>
       <c r="S15">
-        <v>1.34</v>
+        <v>1.29</v>
       </c>
       <c r="T15">
-        <v>3.09</v>
+        <v>3.25</v>
       </c>
       <c r="U15">
+        <v>2.5</v>
+      </c>
+      <c r="V15">
+        <v>1.5</v>
+      </c>
+      <c r="W15">
+        <v>1.06</v>
+      </c>
+      <c r="X15">
+        <v>1.03</v>
+      </c>
+      <c r="Y15">
+        <v>1.16</v>
+      </c>
+      <c r="Z15">
+        <v>4.05</v>
+      </c>
+      <c r="AA15">
+        <v>1.69</v>
+      </c>
+      <c r="AB15">
+        <v>2.07</v>
+      </c>
+      <c r="AC15">
         <v>2.66</v>
       </c>
-      <c r="V15">
-        <v>1.39</v>
-      </c>
-      <c r="W15">
-        <v>1.08</v>
-      </c>
-      <c r="X15">
-        <v>1.05</v>
-      </c>
-      <c r="Y15">
+      <c r="AD15">
+        <v>1.37</v>
+      </c>
+      <c r="AE15">
+        <v>1.11</v>
+      </c>
+      <c r="AF15">
+        <v>1.55</v>
+      </c>
+      <c r="AG15">
+        <v>2.27</v>
+      </c>
+      <c r="AH15" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI15" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ15">
         <v>1.23</v>
       </c>
-      <c r="Z15">
-        <v>3.42</v>
-      </c>
-      <c r="AA15">
-        <v>1.81</v>
-      </c>
-      <c r="AB15">
-        <v>1.88</v>
-      </c>
-      <c r="AC15">
-        <v>2.97</v>
-      </c>
-      <c r="AD15">
-        <v>1.3</v>
-      </c>
-      <c r="AE15">
-        <v>1.08</v>
-      </c>
-      <c r="AF15">
-        <v>1.67</v>
-      </c>
-      <c r="AG15">
-        <v>2.1</v>
-      </c>
-      <c r="AH15" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI15" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ15">
-        <v>1.57</v>
-      </c>
       <c r="AK15">
-        <v>1.29</v>
+        <v>1.31</v>
       </c>
       <c r="AL15">
         <v>0</v>
@@ -2885,12 +2885,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Busan I'Park</t>
+          <t>Gimpo Citizen</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Seoul E-Land</t>
+          <t>Gyeongnam</t>
         </is>
       </c>
       <c r="G16">
@@ -2917,31 +2917,31 @@
         </is>
       </c>
       <c r="N16">
-        <v>2.74</v>
+        <v>1.94</v>
       </c>
       <c r="O16">
-        <v>3.44</v>
+        <v>3.34</v>
       </c>
       <c r="P16">
-        <v>2.25</v>
+        <v>3.51</v>
       </c>
       <c r="Q16">
-        <v>3.1</v>
+        <v>2.48</v>
       </c>
       <c r="R16">
-        <v>2.16</v>
+        <v>2.03</v>
       </c>
       <c r="S16">
-        <v>1.29</v>
+        <v>1.4</v>
       </c>
       <c r="T16">
-        <v>3.25</v>
+        <v>2.75</v>
       </c>
       <c r="U16">
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="V16">
-        <v>1.5</v>
+        <v>1.33</v>
       </c>
       <c r="W16">
         <v>1.06</v>
@@ -2950,31 +2950,31 @@
         <v>1.03</v>
       </c>
       <c r="Y16">
-        <v>1.16</v>
+        <v>1.38</v>
       </c>
       <c r="Z16">
-        <v>4.05</v>
+        <v>2.93</v>
       </c>
       <c r="AA16">
-        <v>1.69</v>
+        <v>1.95</v>
       </c>
       <c r="AB16">
-        <v>2.07</v>
+        <v>1.75</v>
       </c>
       <c r="AC16">
-        <v>2.66</v>
+        <v>3.2</v>
       </c>
       <c r="AD16">
-        <v>1.37</v>
+        <v>1.27</v>
       </c>
       <c r="AE16">
-        <v>1.11</v>
+        <v>1.03</v>
       </c>
       <c r="AF16">
-        <v>1.55</v>
+        <v>1.93</v>
       </c>
       <c r="AG16">
-        <v>2.27</v>
+        <v>1.76</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -2987,10 +2987,10 @@
         </is>
       </c>
       <c r="AJ16">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="AK16">
-        <v>1.31</v>
+        <v>1.83</v>
       </c>
       <c r="AL16">
         <v>0</v>
@@ -3048,12 +3048,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Gimpo Citizen</t>
+          <t>Ansan Greeners</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Gyeongnam</t>
+          <t>Gimhae City</t>
         </is>
       </c>
       <c r="G17">
@@ -3080,64 +3080,64 @@
         </is>
       </c>
       <c r="N17">
-        <v>1.94</v>
+        <v>2.91</v>
       </c>
       <c r="O17">
-        <v>3.34</v>
+        <v>3.38</v>
       </c>
       <c r="P17">
-        <v>3.51</v>
+        <v>2.18</v>
       </c>
       <c r="Q17">
-        <v>2.48</v>
+        <v>3.28</v>
       </c>
       <c r="R17">
-        <v>2.03</v>
+        <v>2.05</v>
       </c>
       <c r="S17">
-        <v>1.4</v>
+        <v>1.34</v>
       </c>
       <c r="T17">
-        <v>2.75</v>
+        <v>3.09</v>
       </c>
       <c r="U17">
-        <v>3</v>
+        <v>2.66</v>
       </c>
       <c r="V17">
-        <v>1.33</v>
+        <v>1.39</v>
       </c>
       <c r="W17">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="X17">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="Y17">
-        <v>1.38</v>
+        <v>1.23</v>
       </c>
       <c r="Z17">
-        <v>2.93</v>
+        <v>3.42</v>
       </c>
       <c r="AA17">
-        <v>1.95</v>
+        <v>1.81</v>
       </c>
       <c r="AB17">
-        <v>1.75</v>
+        <v>1.88</v>
       </c>
       <c r="AC17">
-        <v>3.2</v>
+        <v>2.97</v>
       </c>
       <c r="AD17">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="AE17">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="AF17">
-        <v>1.93</v>
+        <v>1.67</v>
       </c>
       <c r="AG17">
-        <v>1.76</v>
+        <v>2.1</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3150,10 +3150,10 @@
         </is>
       </c>
       <c r="AJ17">
-        <v>1.25</v>
+        <v>1.57</v>
       </c>
       <c r="AK17">
-        <v>1.83</v>
+        <v>1.29</v>
       </c>
       <c r="AL17">
         <v>0</v>
@@ -4352,12 +4352,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Brommapojkarna</t>
+          <t>IFK Göteborg</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Malmö FF</t>
+          <t>Degerfors</t>
         </is>
       </c>
       <c r="G25">
@@ -4384,64 +4384,64 @@
         </is>
       </c>
       <c r="N25">
-        <v>2.95</v>
+        <v>1.69</v>
       </c>
       <c r="O25">
-        <v>3.72</v>
+        <v>3.8</v>
       </c>
       <c r="P25">
-        <v>2.18</v>
+        <v>4.7</v>
       </c>
       <c r="Q25">
-        <v>3.3</v>
+        <v>2.27</v>
       </c>
       <c r="R25">
-        <v>2.21</v>
+        <v>2.38</v>
       </c>
       <c r="S25">
         <v>1.3</v>
       </c>
       <c r="T25">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="U25">
-        <v>2.3</v>
+        <v>2.47</v>
       </c>
       <c r="V25">
-        <v>1.53</v>
+        <v>1.44</v>
       </c>
       <c r="W25">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="X25">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y25">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="Z25">
-        <v>4.2</v>
+        <v>3.78</v>
       </c>
       <c r="AA25">
-        <v>1.61</v>
+        <v>1.8</v>
       </c>
       <c r="AB25">
-        <v>2.25</v>
+        <v>2</v>
       </c>
       <c r="AC25">
-        <v>2.56</v>
+        <v>2.9</v>
       </c>
       <c r="AD25">
-        <v>1.5</v>
+        <v>1.39</v>
       </c>
       <c r="AE25">
-        <v>1.16</v>
+        <v>1.09</v>
       </c>
       <c r="AF25">
-        <v>1.51</v>
+        <v>1.7</v>
       </c>
       <c r="AG25">
-        <v>2.39</v>
+        <v>2.05</v>
       </c>
       <c r="AH25" t="inlineStr">
         <is>
@@ -4454,10 +4454,10 @@
         </is>
       </c>
       <c r="AJ25">
-        <v>1.66</v>
+        <v>1.22</v>
       </c>
       <c r="AK25">
-        <v>1.34</v>
+        <v>1.99</v>
       </c>
       <c r="AL25">
         <v>0</v>
@@ -4515,12 +4515,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>IFK Göteborg</t>
+          <t>Brommapojkarna</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Degerfors</t>
+          <t>Malmö FF</t>
         </is>
       </c>
       <c r="G26">
@@ -4547,64 +4547,64 @@
         </is>
       </c>
       <c r="N26">
-        <v>1.69</v>
+        <v>2.95</v>
       </c>
       <c r="O26">
-        <v>3.8</v>
+        <v>3.72</v>
       </c>
       <c r="P26">
-        <v>4.7</v>
+        <v>2.18</v>
       </c>
       <c r="Q26">
-        <v>2.27</v>
+        <v>3.3</v>
       </c>
       <c r="R26">
-        <v>2.38</v>
+        <v>2.21</v>
       </c>
       <c r="S26">
         <v>1.3</v>
       </c>
       <c r="T26">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="U26">
-        <v>2.47</v>
+        <v>2.3</v>
       </c>
       <c r="V26">
-        <v>1.44</v>
+        <v>1.53</v>
       </c>
       <c r="W26">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="X26">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y26">
-        <v>1.22</v>
+        <v>1.19</v>
       </c>
       <c r="Z26">
-        <v>3.78</v>
+        <v>4.2</v>
       </c>
       <c r="AA26">
-        <v>1.8</v>
+        <v>1.61</v>
       </c>
       <c r="AB26">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="AC26">
-        <v>2.9</v>
+        <v>2.56</v>
       </c>
       <c r="AD26">
-        <v>1.39</v>
+        <v>1.5</v>
       </c>
       <c r="AE26">
-        <v>1.09</v>
+        <v>1.16</v>
       </c>
       <c r="AF26">
-        <v>1.7</v>
+        <v>1.51</v>
       </c>
       <c r="AG26">
-        <v>2.05</v>
+        <v>2.39</v>
       </c>
       <c r="AH26" t="inlineStr">
         <is>
@@ -4617,10 +4617,10 @@
         </is>
       </c>
       <c r="AJ26">
-        <v>1.22</v>
+        <v>1.66</v>
       </c>
       <c r="AK26">
-        <v>1.99</v>
+        <v>1.34</v>
       </c>
       <c r="AL26">
         <v>0</v>
@@ -6349,10 +6349,10 @@
         <v>0</v>
       </c>
       <c r="Q37">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="R37">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="S37">
         <v>0</v>
@@ -6361,10 +6361,10 @@
         <v>0</v>
       </c>
       <c r="U37">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="V37">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="W37">
         <v>0</v>
@@ -6373,31 +6373,31 @@
         <v>0</v>
       </c>
       <c r="Y37">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="Z37">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="AA37">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AB37">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="AC37">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AD37">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AE37">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AF37">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="AG37">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="AH37" t="inlineStr">
         <is>
@@ -6410,10 +6410,10 @@
         </is>
       </c>
       <c r="AJ37">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AK37">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AL37">
         <v>0</v>
@@ -12706,55 +12706,55 @@
         <v>2.72</v>
       </c>
       <c r="Q76">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="R76">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S76">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="T76">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="U76">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="V76">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="W76">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X76">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y76">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="Z76">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="AA76">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AB76">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AC76">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="AD76">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AE76">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AF76">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AG76">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AH76" t="inlineStr">
         <is>
@@ -12767,10 +12767,10 @@
         </is>
       </c>
       <c r="AJ76">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AK76">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AL76">
         <v>0</v>
@@ -16903,12 +16903,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>San Miguel</t>
+          <t>Midland</t>
         </is>
       </c>
       <c r="G102">
@@ -16935,13 +16935,13 @@
         </is>
       </c>
       <c r="N102">
-        <v>2.66</v>
+        <v>2.76</v>
       </c>
       <c r="O102">
-        <v>2.67</v>
+        <v>2.7</v>
       </c>
       <c r="P102">
-        <v>2.78</v>
+        <v>2.65</v>
       </c>
       <c r="Q102">
         <v>0</v>
@@ -16968,7 +16968,7 @@
         <v>0</v>
       </c>
       <c r="Y102">
-        <v>1.63</v>
+        <v>1.65</v>
       </c>
       <c r="Z102">
         <v>2.1</v>
@@ -17066,12 +17066,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>Ciudad de Bolívar</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Midland</t>
+          <t>Club Atlético Mitre</t>
         </is>
       </c>
       <c r="G103">
@@ -17098,13 +17098,13 @@
         </is>
       </c>
       <c r="N103">
+        <v>2.12</v>
+      </c>
+      <c r="O103">
         <v>2.76</v>
       </c>
-      <c r="O103">
-        <v>2.7</v>
-      </c>
       <c r="P103">
-        <v>2.65</v>
+        <v>3.77</v>
       </c>
       <c r="Q103">
         <v>0</v>
@@ -17229,12 +17229,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Ciudad de Bolívar</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Club Atlético Mitre</t>
+          <t>San Miguel</t>
         </is>
       </c>
       <c r="G104">
@@ -17261,13 +17261,13 @@
         </is>
       </c>
       <c r="N104">
-        <v>2.12</v>
+        <v>2.66</v>
       </c>
       <c r="O104">
-        <v>2.76</v>
+        <v>2.67</v>
       </c>
       <c r="P104">
-        <v>3.77</v>
+        <v>2.78</v>
       </c>
       <c r="Q104">
         <v>0</v>
@@ -17294,7 +17294,7 @@
         <v>0</v>
       </c>
       <c r="Y104">
-        <v>1.65</v>
+        <v>1.63</v>
       </c>
       <c r="Z104">
         <v>2.1</v>
@@ -17952,10 +17952,10 @@
         <v>0</v>
       </c>
       <c r="AA108">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AB108">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AC108">
         <v>0</v>
@@ -18115,10 +18115,10 @@
         <v>0</v>
       </c>
       <c r="AA109">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AB109">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AC109">
         <v>0</v>
@@ -18278,10 +18278,10 @@
         <v>0</v>
       </c>
       <c r="AA110">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="AB110">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AC110">
         <v>0</v>
@@ -18441,10 +18441,10 @@
         <v>0</v>
       </c>
       <c r="AA111">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AB111">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AC111">
         <v>0</v>

--- a/jogos_2026-08-02.xlsx
+++ b/jogos_2026-08-02.xlsx
@@ -340,7 +340,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AU141"/>
+  <dimension ref="A1:AU140"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2559,12 +2559,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Jeonnam Dragons</t>
+          <t>Busan I'Park</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Paju Citizen</t>
+          <t>Seoul E-Land</t>
         </is>
       </c>
       <c r="G14">
@@ -2591,64 +2591,64 @@
         </is>
       </c>
       <c r="N14">
-        <v>1.97</v>
+        <v>2.74</v>
       </c>
       <c r="O14">
-        <v>3.32</v>
+        <v>3.44</v>
       </c>
       <c r="P14">
-        <v>3.45</v>
+        <v>2.25</v>
       </c>
       <c r="Q14">
-        <v>2.62</v>
+        <v>3.1</v>
       </c>
       <c r="R14">
-        <v>2.25</v>
+        <v>2.16</v>
       </c>
       <c r="S14">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="T14">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="U14">
         <v>2.5</v>
       </c>
       <c r="V14">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="W14">
-        <v>1.1</v>
+        <v>1.06</v>
       </c>
       <c r="X14">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="Y14">
-        <v>1.26</v>
+        <v>1.16</v>
       </c>
       <c r="Z14">
-        <v>3.71</v>
+        <v>4.05</v>
       </c>
       <c r="AA14">
-        <v>1.79</v>
+        <v>1.69</v>
       </c>
       <c r="AB14">
-        <v>1.9</v>
+        <v>2.07</v>
       </c>
       <c r="AC14">
-        <v>3.07</v>
+        <v>2.66</v>
       </c>
       <c r="AD14">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="AE14">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="AF14">
-        <v>1.73</v>
+        <v>1.55</v>
       </c>
       <c r="AG14">
-        <v>2</v>
+        <v>2.27</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2661,10 +2661,10 @@
         </is>
       </c>
       <c r="AJ14">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="AK14">
-        <v>1.58</v>
+        <v>1.31</v>
       </c>
       <c r="AL14">
         <v>0</v>
@@ -2722,12 +2722,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Busan I'Park</t>
+          <t>Jeonnam Dragons</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Seoul E-Land</t>
+          <t>Paju Citizen</t>
         </is>
       </c>
       <c r="G15">
@@ -2754,64 +2754,64 @@
         </is>
       </c>
       <c r="N15">
-        <v>2.74</v>
+        <v>1.97</v>
       </c>
       <c r="O15">
-        <v>3.44</v>
+        <v>3.32</v>
       </c>
       <c r="P15">
+        <v>3.45</v>
+      </c>
+      <c r="Q15">
+        <v>2.62</v>
+      </c>
+      <c r="R15">
         <v>2.25</v>
       </c>
-      <c r="Q15">
+      <c r="S15">
+        <v>1.3</v>
+      </c>
+      <c r="T15">
         <v>3.1</v>
-      </c>
-      <c r="R15">
-        <v>2.16</v>
-      </c>
-      <c r="S15">
-        <v>1.29</v>
-      </c>
-      <c r="T15">
-        <v>3.25</v>
       </c>
       <c r="U15">
         <v>2.5</v>
       </c>
       <c r="V15">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="W15">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="X15">
-        <v>1.03</v>
+        <v>1</v>
       </c>
       <c r="Y15">
-        <v>1.16</v>
+        <v>1.26</v>
       </c>
       <c r="Z15">
-        <v>4.05</v>
+        <v>3.71</v>
       </c>
       <c r="AA15">
-        <v>1.69</v>
+        <v>1.79</v>
       </c>
       <c r="AB15">
-        <v>2.07</v>
+        <v>1.9</v>
       </c>
       <c r="AC15">
-        <v>2.66</v>
+        <v>3.07</v>
       </c>
       <c r="AD15">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="AE15">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="AF15">
-        <v>1.55</v>
+        <v>1.73</v>
       </c>
       <c r="AG15">
-        <v>2.27</v>
+        <v>2</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2824,10 +2824,10 @@
         </is>
       </c>
       <c r="AJ15">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="AK15">
-        <v>1.31</v>
+        <v>1.58</v>
       </c>
       <c r="AL15">
         <v>0</v>
@@ -2885,12 +2885,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Ansan Greeners</t>
+          <t>Gimpo Citizen</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Gimhae City</t>
+          <t>Gyeongnam</t>
         </is>
       </c>
       <c r="G16">
@@ -2917,64 +2917,64 @@
         </is>
       </c>
       <c r="N16">
-        <v>2.91</v>
+        <v>1.94</v>
       </c>
       <c r="O16">
-        <v>3.38</v>
+        <v>3.34</v>
       </c>
       <c r="P16">
-        <v>2.18</v>
+        <v>3.51</v>
       </c>
       <c r="Q16">
-        <v>3.28</v>
+        <v>2.48</v>
       </c>
       <c r="R16">
-        <v>2.05</v>
+        <v>2.03</v>
       </c>
       <c r="S16">
-        <v>1.34</v>
+        <v>1.4</v>
       </c>
       <c r="T16">
-        <v>3.09</v>
+        <v>2.75</v>
       </c>
       <c r="U16">
-        <v>2.66</v>
+        <v>3</v>
       </c>
       <c r="V16">
-        <v>1.39</v>
+        <v>1.33</v>
       </c>
       <c r="W16">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="X16">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="Y16">
-        <v>1.23</v>
+        <v>1.38</v>
       </c>
       <c r="Z16">
-        <v>3.42</v>
+        <v>2.93</v>
       </c>
       <c r="AA16">
-        <v>1.81</v>
+        <v>1.95</v>
       </c>
       <c r="AB16">
-        <v>1.88</v>
+        <v>1.75</v>
       </c>
       <c r="AC16">
-        <v>2.97</v>
+        <v>3.2</v>
       </c>
       <c r="AD16">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="AE16">
-        <v>1.08</v>
+        <v>1.03</v>
       </c>
       <c r="AF16">
-        <v>1.67</v>
+        <v>1.93</v>
       </c>
       <c r="AG16">
-        <v>2.1</v>
+        <v>1.76</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -2987,10 +2987,10 @@
         </is>
       </c>
       <c r="AJ16">
-        <v>1.57</v>
+        <v>1.25</v>
       </c>
       <c r="AK16">
-        <v>1.29</v>
+        <v>1.83</v>
       </c>
       <c r="AL16">
         <v>0</v>
@@ -3048,12 +3048,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Gimpo Citizen</t>
+          <t>Ansan Greeners</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Gyeongnam</t>
+          <t>Gimhae City</t>
         </is>
       </c>
       <c r="G17">
@@ -3080,64 +3080,64 @@
         </is>
       </c>
       <c r="N17">
-        <v>1.94</v>
+        <v>2.91</v>
       </c>
       <c r="O17">
-        <v>3.34</v>
+        <v>3.38</v>
       </c>
       <c r="P17">
-        <v>3.51</v>
+        <v>2.18</v>
       </c>
       <c r="Q17">
-        <v>2.48</v>
+        <v>3.28</v>
       </c>
       <c r="R17">
-        <v>2.03</v>
+        <v>2.05</v>
       </c>
       <c r="S17">
-        <v>1.4</v>
+        <v>1.34</v>
       </c>
       <c r="T17">
-        <v>2.75</v>
+        <v>3.09</v>
       </c>
       <c r="U17">
-        <v>3</v>
+        <v>2.66</v>
       </c>
       <c r="V17">
-        <v>1.33</v>
+        <v>1.39</v>
       </c>
       <c r="W17">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="X17">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="Y17">
-        <v>1.38</v>
+        <v>1.23</v>
       </c>
       <c r="Z17">
-        <v>2.93</v>
+        <v>3.42</v>
       </c>
       <c r="AA17">
-        <v>1.95</v>
+        <v>1.81</v>
       </c>
       <c r="AB17">
-        <v>1.75</v>
+        <v>1.88</v>
       </c>
       <c r="AC17">
-        <v>3.2</v>
+        <v>2.97</v>
       </c>
       <c r="AD17">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="AE17">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="AF17">
-        <v>1.93</v>
+        <v>1.67</v>
       </c>
       <c r="AG17">
-        <v>1.76</v>
+        <v>2.1</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3150,10 +3150,10 @@
         </is>
       </c>
       <c r="AJ17">
-        <v>1.25</v>
+        <v>1.57</v>
       </c>
       <c r="AK17">
-        <v>1.83</v>
+        <v>1.29</v>
       </c>
       <c r="AL17">
         <v>0</v>
@@ -14621,12 +14621,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>HB</t>
+          <t>B68</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>NSÍ</t>
+          <t>07 Vestur</t>
         </is>
       </c>
       <c r="G88">
@@ -14769,12 +14769,12 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -14784,12 +14784,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>B68</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>07 Vestur</t>
+          <t>Unión Española</t>
         </is>
       </c>
       <c r="G89">
@@ -14920,7 +14920,7 @@
       </c>
       <c r="AU89" t="inlineStr">
         <is>
-          <t>2026-08-02 13:15:00</t>
+          <t>2026-08-02 13:30:00</t>
         </is>
       </c>
     </row>
@@ -14937,7 +14937,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -14947,12 +14947,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Magallanes</t>
+          <t>Concepción</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Unión Española</t>
+          <t>Universidad Católica</t>
         </is>
       </c>
       <c r="G90">
@@ -14979,64 +14979,64 @@
         </is>
       </c>
       <c r="N90">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="O90">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="P90">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Q90">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="R90">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="S90">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T90">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="U90">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="V90">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="W90">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X90">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y90">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="Z90">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="AA90">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AB90">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AC90">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="AD90">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AE90">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AF90">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AG90">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AH90" t="inlineStr">
         <is>
@@ -15049,10 +15049,10 @@
         </is>
       </c>
       <c r="AJ90">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AK90">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AL90">
         <v>0</v>
@@ -15100,7 +15100,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -15110,12 +15110,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Concepción</t>
+          <t>Sūduva</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Universidad Católica</t>
+          <t>Trakai</t>
         </is>
       </c>
       <c r="G91">
@@ -15138,68 +15138,68 @@
       </c>
       <c r="M91" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="N91">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="O91">
-        <v>3.68</v>
+        <v>0</v>
       </c>
       <c r="P91">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="Q91">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="R91">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="S91">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="T91">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="U91">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="V91">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="W91">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="X91">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y91">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="Z91">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="AA91">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AB91">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AC91">
-        <v>2.97</v>
+        <v>0</v>
       </c>
       <c r="AD91">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AE91">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AF91">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AG91">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AH91" t="inlineStr">
         <is>
@@ -15212,10 +15212,10 @@
         </is>
       </c>
       <c r="AJ91">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AK91">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AL91">
         <v>0</v>
@@ -15263,22 +15263,22 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Sūduva</t>
+          <t>Varaždin</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Trakai</t>
+          <t>Hajduk Split</t>
         </is>
       </c>
       <c r="G92">
@@ -15301,68 +15301,68 @@
       </c>
       <c r="M92" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N92">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="O92">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="P92">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="Q92">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R92">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="S92">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="T92">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="U92">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="V92">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="W92">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X92">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y92">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z92">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AA92">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB92">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AC92">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AD92">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AE92">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AF92">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AG92">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="AH92" t="inlineStr">
         <is>
@@ -15375,10 +15375,10 @@
         </is>
       </c>
       <c r="AJ92">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AK92">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AL92">
         <v>0</v>
@@ -15421,27 +15421,27 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Varaždin</t>
+          <t>Rīgas FS</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Hajduk Split</t>
+          <t>Super Nova</t>
         </is>
       </c>
       <c r="G93">
@@ -15468,64 +15468,64 @@
         </is>
       </c>
       <c r="N93">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="O93">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="P93">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="Q93">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="R93">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="S93">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="T93">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="U93">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="V93">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="W93">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="X93">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y93">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="Z93">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="AA93">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AB93">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AC93">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="AD93">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AE93">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="AF93">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AG93">
-        <v>2.11</v>
+        <v>0</v>
       </c>
       <c r="AH93" t="inlineStr">
         <is>
@@ -15538,10 +15538,10 @@
         </is>
       </c>
       <c r="AJ93">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AK93">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AL93">
         <v>0</v>
@@ -15572,7 +15572,7 @@
       </c>
       <c r="AU93" t="inlineStr">
         <is>
-          <t>2026-08-02 13:30:00</t>
+          <t>2026-08-02 14:00:00</t>
         </is>
       </c>
     </row>
@@ -15589,22 +15589,22 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Rīgas FS</t>
+          <t>Rapid Wien</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Super Nova</t>
+          <t>Rheindorf Altach</t>
         </is>
       </c>
       <c r="G94">
@@ -15631,64 +15631,64 @@
         </is>
       </c>
       <c r="N94">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="O94">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="P94">
-        <v>0</v>
+        <v>3.72</v>
       </c>
       <c r="Q94">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="R94">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="S94">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="T94">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="U94">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="V94">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="W94">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X94">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y94">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="Z94">
-        <v>0</v>
+        <v>3.39</v>
       </c>
       <c r="AA94">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AB94">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AC94">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AD94">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AE94">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AF94">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AG94">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AH94" t="inlineStr">
         <is>
@@ -15701,10 +15701,10 @@
         </is>
       </c>
       <c r="AJ94">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AK94">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AL94">
         <v>0</v>
@@ -15752,7 +15752,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -15762,12 +15762,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Rapid Wien</t>
+          <t>Napredak</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Rheindorf Altach</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="G95">
@@ -15794,64 +15794,64 @@
         </is>
       </c>
       <c r="N95">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="O95">
-        <v>3.44</v>
+        <v>0</v>
       </c>
       <c r="P95">
-        <v>3.72</v>
+        <v>0</v>
       </c>
       <c r="Q95">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="R95">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="S95">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="T95">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="U95">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="V95">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="W95">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="X95">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y95">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="Z95">
-        <v>3.39</v>
+        <v>0</v>
       </c>
       <c r="AA95">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AB95">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AC95">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="AD95">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AE95">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AF95">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AG95">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AH95" t="inlineStr">
         <is>
@@ -15864,10 +15864,10 @@
         </is>
       </c>
       <c r="AJ95">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AK95">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AL95">
         <v>0</v>
@@ -15915,7 +15915,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -15925,12 +15925,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Napredak</t>
+          <t>Csákvári TK</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>Nagykanizsai TE</t>
         </is>
       </c>
       <c r="G96">
@@ -15957,13 +15957,13 @@
         </is>
       </c>
       <c r="N96">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="O96">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="P96">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="Q96">
         <v>0</v>
@@ -15996,10 +15996,10 @@
         <v>0</v>
       </c>
       <c r="AA96">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB96">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC96">
         <v>0</v>
@@ -16073,27 +16073,27 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Csákvári TK</t>
+          <t>Brann</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Nagykanizsai TE</t>
+          <t>Rosenborg</t>
         </is>
       </c>
       <c r="G97">
@@ -16120,64 +16120,64 @@
         </is>
       </c>
       <c r="N97">
+        <v>1.71</v>
+      </c>
+      <c r="O97">
+        <v>4.2</v>
+      </c>
+      <c r="P97">
+        <v>4.5</v>
+      </c>
+      <c r="Q97">
+        <v>2.22</v>
+      </c>
+      <c r="R97">
+        <v>2.39</v>
+      </c>
+      <c r="S97">
+        <v>1.22</v>
+      </c>
+      <c r="T97">
+        <v>4</v>
+      </c>
+      <c r="U97">
+        <v>2.1</v>
+      </c>
+      <c r="V97">
+        <v>1.63</v>
+      </c>
+      <c r="W97">
+        <v>1.14</v>
+      </c>
+      <c r="X97">
+        <v>1.02</v>
+      </c>
+      <c r="Y97">
+        <v>1.13</v>
+      </c>
+      <c r="Z97">
+        <v>5.25</v>
+      </c>
+      <c r="AA97">
+        <v>1.5</v>
+      </c>
+      <c r="AB97">
+        <v>2.5</v>
+      </c>
+      <c r="AC97">
         <v>2.25</v>
       </c>
-      <c r="O97">
-        <v>3.5</v>
-      </c>
-      <c r="P97">
-        <v>2.6</v>
-      </c>
-      <c r="Q97">
-        <v>0</v>
-      </c>
-      <c r="R97">
-        <v>0</v>
-      </c>
-      <c r="S97">
-        <v>0</v>
-      </c>
-      <c r="T97">
-        <v>0</v>
-      </c>
-      <c r="U97">
-        <v>0</v>
-      </c>
-      <c r="V97">
-        <v>0</v>
-      </c>
-      <c r="W97">
-        <v>0</v>
-      </c>
-      <c r="X97">
-        <v>0</v>
-      </c>
-      <c r="Y97">
-        <v>0</v>
-      </c>
-      <c r="Z97">
-        <v>0</v>
-      </c>
-      <c r="AA97">
-        <v>1.85</v>
-      </c>
-      <c r="AB97">
-        <v>1.95</v>
-      </c>
-      <c r="AC97">
-        <v>0</v>
-      </c>
       <c r="AD97">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AE97">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AF97">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AG97">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="AH97" t="inlineStr">
         <is>
@@ -16190,10 +16190,10 @@
         </is>
       </c>
       <c r="AJ97">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AK97">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AL97">
         <v>0</v>
@@ -16224,7 +16224,7 @@
       </c>
       <c r="AU97" t="inlineStr">
         <is>
-          <t>2026-08-02 14:00:00</t>
+          <t>2026-08-02 14:15:00</t>
         </is>
       </c>
     </row>
@@ -16236,27 +16236,27 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Brann</t>
+          <t>Pogoń Grod. Mazowiecki</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Rosenborg</t>
+          <t>Puszcza Niepołomice</t>
         </is>
       </c>
       <c r="G98">
@@ -16283,64 +16283,64 @@
         </is>
       </c>
       <c r="N98">
-        <v>1.71</v>
+        <v>2.6</v>
       </c>
       <c r="O98">
-        <v>4.2</v>
+        <v>3.05</v>
       </c>
       <c r="P98">
-        <v>4.5</v>
+        <v>2.5</v>
       </c>
       <c r="Q98">
-        <v>2.22</v>
+        <v>3.2</v>
       </c>
       <c r="R98">
-        <v>2.39</v>
+        <v>2.2</v>
       </c>
       <c r="S98">
-        <v>1.22</v>
+        <v>1.35</v>
       </c>
       <c r="T98">
-        <v>4</v>
+        <v>2.86</v>
       </c>
       <c r="U98">
-        <v>2.1</v>
+        <v>2.63</v>
       </c>
       <c r="V98">
-        <v>1.63</v>
+        <v>1.48</v>
       </c>
       <c r="W98">
-        <v>1.14</v>
+        <v>1.1</v>
       </c>
       <c r="X98">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="Y98">
+        <v>1.21</v>
+      </c>
+      <c r="Z98">
+        <v>3.76</v>
+      </c>
+      <c r="AA98">
+        <v>1.81</v>
+      </c>
+      <c r="AB98">
+        <v>1.86</v>
+      </c>
+      <c r="AC98">
+        <v>2.78</v>
+      </c>
+      <c r="AD98">
+        <v>1.41</v>
+      </c>
+      <c r="AE98">
         <v>1.13</v>
       </c>
-      <c r="Z98">
-        <v>5.25</v>
-      </c>
-      <c r="AA98">
-        <v>1.5</v>
-      </c>
-      <c r="AB98">
-        <v>2.5</v>
-      </c>
-      <c r="AC98">
-        <v>2.25</v>
-      </c>
-      <c r="AD98">
-        <v>1.66</v>
-      </c>
-      <c r="AE98">
-        <v>1.21</v>
-      </c>
       <c r="AF98">
-        <v>1.45</v>
+        <v>1.55</v>
       </c>
       <c r="AG98">
-        <v>2.56</v>
+        <v>2.23</v>
       </c>
       <c r="AH98" t="inlineStr">
         <is>
@@ -16353,10 +16353,10 @@
         </is>
       </c>
       <c r="AJ98">
-        <v>1.21</v>
+        <v>1.42</v>
       </c>
       <c r="AK98">
-        <v>1.86</v>
+        <v>1.44</v>
       </c>
       <c r="AL98">
         <v>0</v>
@@ -16387,7 +16387,7 @@
       </c>
       <c r="AU98" t="inlineStr">
         <is>
-          <t>2026-08-02 14:15:00</t>
+          <t>2026-08-02 14:30:00</t>
         </is>
       </c>
     </row>
@@ -16404,7 +16404,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -16414,12 +16414,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Pogoń Grod. Mazowiecki</t>
+          <t>Akhmat Grozny</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Puszcza Niepołomice</t>
+          <t>Spartak Moskva</t>
         </is>
       </c>
       <c r="G99">
@@ -16446,64 +16446,64 @@
         </is>
       </c>
       <c r="N99">
-        <v>2.6</v>
+        <v>3.5</v>
       </c>
       <c r="O99">
-        <v>3.05</v>
+        <v>3.67</v>
       </c>
       <c r="P99">
-        <v>2.5</v>
+        <v>2.19</v>
       </c>
       <c r="Q99">
-        <v>3.2</v>
+        <v>3.76</v>
       </c>
       <c r="R99">
-        <v>2.2</v>
+        <v>2.29</v>
       </c>
       <c r="S99">
-        <v>1.35</v>
+        <v>1.38</v>
       </c>
       <c r="T99">
-        <v>2.86</v>
+        <v>2.93</v>
       </c>
       <c r="U99">
-        <v>2.63</v>
+        <v>2.79</v>
       </c>
       <c r="V99">
-        <v>1.48</v>
+        <v>1.41</v>
       </c>
       <c r="W99">
-        <v>1.1</v>
+        <v>1.07</v>
       </c>
       <c r="X99">
         <v>1</v>
       </c>
       <c r="Y99">
-        <v>1.21</v>
+        <v>1.26</v>
       </c>
       <c r="Z99">
-        <v>3.76</v>
+        <v>3.5</v>
       </c>
       <c r="AA99">
-        <v>1.81</v>
+        <v>1.91</v>
       </c>
       <c r="AB99">
-        <v>1.86</v>
+        <v>1.93</v>
       </c>
       <c r="AC99">
-        <v>2.78</v>
+        <v>3.18</v>
       </c>
       <c r="AD99">
-        <v>1.41</v>
+        <v>1.33</v>
       </c>
       <c r="AE99">
-        <v>1.13</v>
+        <v>1.08</v>
       </c>
       <c r="AF99">
-        <v>1.55</v>
+        <v>1.73</v>
       </c>
       <c r="AG99">
-        <v>2.23</v>
+        <v>2.02</v>
       </c>
       <c r="AH99" t="inlineStr">
         <is>
@@ -16516,10 +16516,10 @@
         </is>
       </c>
       <c r="AJ99">
-        <v>1.42</v>
+        <v>1.31</v>
       </c>
       <c r="AK99">
-        <v>1.44</v>
+        <v>1.3</v>
       </c>
       <c r="AL99">
         <v>0</v>
@@ -16562,27 +16562,27 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Akhmat Grozny</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Spartak Moskva</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="G100">
@@ -16609,64 +16609,64 @@
         </is>
       </c>
       <c r="N100">
-        <v>3.5</v>
+        <v>1.54</v>
       </c>
       <c r="O100">
-        <v>3.67</v>
+        <v>4.2</v>
       </c>
       <c r="P100">
-        <v>2.19</v>
+        <v>5.33</v>
       </c>
       <c r="Q100">
-        <v>3.76</v>
+        <v>1.99</v>
       </c>
       <c r="R100">
+        <v>2.4</v>
+      </c>
+      <c r="S100">
+        <v>1.25</v>
+      </c>
+      <c r="T100">
+        <v>3.6</v>
+      </c>
+      <c r="U100">
+        <v>2.25</v>
+      </c>
+      <c r="V100">
+        <v>1.57</v>
+      </c>
+      <c r="W100">
+        <v>1.11</v>
+      </c>
+      <c r="X100">
+        <v>1.03</v>
+      </c>
+      <c r="Y100">
+        <v>1.14</v>
+      </c>
+      <c r="Z100">
+        <v>4.5</v>
+      </c>
+      <c r="AA100">
+        <v>1.6</v>
+      </c>
+      <c r="AB100">
         <v>2.29</v>
       </c>
-      <c r="S100">
-        <v>1.38</v>
-      </c>
-      <c r="T100">
-        <v>2.93</v>
-      </c>
-      <c r="U100">
-        <v>2.79</v>
-      </c>
-      <c r="V100">
-        <v>1.41</v>
-      </c>
-      <c r="W100">
-        <v>1.07</v>
-      </c>
-      <c r="X100">
-        <v>1</v>
-      </c>
-      <c r="Y100">
-        <v>1.26</v>
-      </c>
-      <c r="Z100">
-        <v>3.5</v>
-      </c>
-      <c r="AA100">
-        <v>1.91</v>
-      </c>
-      <c r="AB100">
-        <v>1.93</v>
-      </c>
       <c r="AC100">
-        <v>3.18</v>
+        <v>2.56</v>
       </c>
       <c r="AD100">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
       <c r="AE100">
-        <v>1.08</v>
+        <v>1.14</v>
       </c>
       <c r="AF100">
         <v>1.73</v>
       </c>
       <c r="AG100">
-        <v>2.02</v>
+        <v>1.92</v>
       </c>
       <c r="AH100" t="inlineStr">
         <is>
@@ -16679,10 +16679,10 @@
         </is>
       </c>
       <c r="AJ100">
-        <v>1.31</v>
+        <v>1.22</v>
       </c>
       <c r="AK100">
-        <v>1.3</v>
+        <v>2.45</v>
       </c>
       <c r="AL100">
         <v>0</v>
@@ -16713,7 +16713,7 @@
       </c>
       <c r="AU100" t="inlineStr">
         <is>
-          <t>2026-08-02 14:30:00</t>
+          <t>2026-08-02 15:00:00</t>
         </is>
       </c>
     </row>
@@ -16730,22 +16730,22 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Partizan</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>IMT Novi Beograd</t>
         </is>
       </c>
       <c r="G101">
@@ -16772,64 +16772,64 @@
         </is>
       </c>
       <c r="N101">
-        <v>1.54</v>
+        <v>1.43</v>
       </c>
       <c r="O101">
-        <v>4.2</v>
+        <v>4.15</v>
       </c>
       <c r="P101">
-        <v>5.33</v>
+        <v>6.28</v>
       </c>
       <c r="Q101">
-        <v>1.99</v>
+        <v>1.91</v>
       </c>
       <c r="R101">
         <v>2.4</v>
       </c>
       <c r="S101">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="T101">
-        <v>3.6</v>
+        <v>3.15</v>
       </c>
       <c r="U101">
-        <v>2.25</v>
+        <v>2.4</v>
       </c>
       <c r="V101">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="W101">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="X101">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y101">
-        <v>1.14</v>
+        <v>1.22</v>
       </c>
       <c r="Z101">
-        <v>4.5</v>
+        <v>4</v>
       </c>
       <c r="AA101">
         <v>1.6</v>
       </c>
       <c r="AB101">
-        <v>2.29</v>
+        <v>2.19</v>
       </c>
       <c r="AC101">
-        <v>2.56</v>
+        <v>2.62</v>
       </c>
       <c r="AD101">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="AE101">
         <v>1.14</v>
       </c>
       <c r="AF101">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="AG101">
-        <v>1.92</v>
+        <v>1.95</v>
       </c>
       <c r="AH101" t="inlineStr">
         <is>
@@ -16842,10 +16842,10 @@
         </is>
       </c>
       <c r="AJ101">
-        <v>1.22</v>
+        <v>1.1</v>
       </c>
       <c r="AK101">
-        <v>2.45</v>
+        <v>2.7</v>
       </c>
       <c r="AL101">
         <v>0</v>
@@ -17056,22 +17056,22 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Partizan</t>
+          <t>Ciudad de Bolívar</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>IMT Novi Beograd</t>
+          <t>Club Atlético Mitre</t>
         </is>
       </c>
       <c r="G103">
@@ -17098,64 +17098,64 @@
         </is>
       </c>
       <c r="N103">
-        <v>1.43</v>
+        <v>2.12</v>
       </c>
       <c r="O103">
-        <v>4.15</v>
+        <v>2.76</v>
       </c>
       <c r="P103">
-        <v>6.28</v>
+        <v>3.77</v>
       </c>
       <c r="Q103">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="R103">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="S103">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="T103">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="U103">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="V103">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="W103">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="X103">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="Y103">
-        <v>1.22</v>
+        <v>1.65</v>
       </c>
       <c r="Z103">
-        <v>4</v>
+        <v>2.1</v>
       </c>
       <c r="AA103">
-        <v>1.6</v>
+        <v>3.1</v>
       </c>
       <c r="AB103">
-        <v>2.19</v>
+        <v>1.36</v>
       </c>
       <c r="AC103">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="AD103">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="AE103">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AF103">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AG103">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AH103" t="inlineStr">
         <is>
@@ -17168,10 +17168,10 @@
         </is>
       </c>
       <c r="AJ103">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AK103">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="AL103">
         <v>0</v>
@@ -17229,12 +17229,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Ciudad de Bolívar</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Club Atlético Mitre</t>
+          <t>San Miguel</t>
         </is>
       </c>
       <c r="G104">
@@ -17261,13 +17261,13 @@
         </is>
       </c>
       <c r="N104">
-        <v>2.12</v>
+        <v>2.66</v>
       </c>
       <c r="O104">
-        <v>2.76</v>
+        <v>2.67</v>
       </c>
       <c r="P104">
-        <v>3.77</v>
+        <v>2.78</v>
       </c>
       <c r="Q104">
         <v>0</v>
@@ -17294,16 +17294,16 @@
         <v>0</v>
       </c>
       <c r="Y104">
-        <v>1.65</v>
+        <v>1.63</v>
       </c>
       <c r="Z104">
         <v>2.1</v>
       </c>
       <c r="AA104">
-        <v>3.1</v>
+        <v>3.4</v>
       </c>
       <c r="AB104">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AC104">
         <v>0</v>
@@ -17392,12 +17392,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Almirante Brown</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>San Miguel</t>
+          <t>Racing Córdoba</t>
         </is>
       </c>
       <c r="G105">
@@ -17424,64 +17424,64 @@
         </is>
       </c>
       <c r="N105">
-        <v>2.66</v>
+        <v>2.22</v>
       </c>
       <c r="O105">
-        <v>2.67</v>
+        <v>2.72</v>
       </c>
       <c r="P105">
-        <v>2.78</v>
+        <v>3.56</v>
       </c>
       <c r="Q105">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R105">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="S105">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="T105">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="U105">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="V105">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="W105">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X105">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Y105">
-        <v>1.63</v>
+        <v>1.72</v>
       </c>
       <c r="Z105">
-        <v>2.1</v>
+        <v>1.96</v>
       </c>
       <c r="AA105">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="AB105">
-        <v>1.33</v>
+        <v>1.27</v>
       </c>
       <c r="AC105">
-        <v>0</v>
+        <v>7.1</v>
       </c>
       <c r="AD105">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AE105">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AF105">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="AG105">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AH105" t="inlineStr">
         <is>
@@ -17494,10 +17494,10 @@
         </is>
       </c>
       <c r="AJ105">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK105">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AL105">
         <v>0</v>
@@ -17555,12 +17555,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Almirante Brown</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Racing Córdoba</t>
+          <t>Midland</t>
         </is>
       </c>
       <c r="G106">
@@ -17587,28 +17587,28 @@
         </is>
       </c>
       <c r="N106">
-        <v>2.22</v>
+        <v>2.76</v>
       </c>
       <c r="O106">
-        <v>2.72</v>
+        <v>2.7</v>
       </c>
       <c r="P106">
-        <v>3.56</v>
+        <v>2.65</v>
       </c>
       <c r="Q106">
-        <v>3.3</v>
+        <v>3.74</v>
       </c>
       <c r="R106">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="S106">
-        <v>1.81</v>
+        <v>1.7</v>
       </c>
       <c r="T106">
-        <v>1.89</v>
+        <v>2.1</v>
       </c>
       <c r="U106">
-        <v>4.33</v>
+        <v>4.2</v>
       </c>
       <c r="V106">
         <v>1.2</v>
@@ -17617,34 +17617,34 @@
         <v>1.03</v>
       </c>
       <c r="X106">
-        <v>1.18</v>
+        <v>1.16</v>
       </c>
       <c r="Y106">
-        <v>1.72</v>
+        <v>1.65</v>
       </c>
       <c r="Z106">
-        <v>1.96</v>
+        <v>2.1</v>
       </c>
       <c r="AA106">
-        <v>3.5</v>
+        <v>3.04</v>
       </c>
       <c r="AB106">
-        <v>1.27</v>
+        <v>1.32</v>
       </c>
       <c r="AC106">
-        <v>7.1</v>
+        <v>6.55</v>
       </c>
       <c r="AD106">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="AE106">
         <v>1.02</v>
       </c>
       <c r="AF106">
-        <v>2.54</v>
+        <v>2.07</v>
       </c>
       <c r="AG106">
-        <v>1.44</v>
+        <v>1.57</v>
       </c>
       <c r="AH106" t="inlineStr">
         <is>
@@ -17657,10 +17657,10 @@
         </is>
       </c>
       <c r="AJ106">
-        <v>1.25</v>
+        <v>1.34</v>
       </c>
       <c r="AK106">
-        <v>1.57</v>
+        <v>1.36</v>
       </c>
       <c r="AL106">
         <v>0</v>
@@ -17708,22 +17708,22 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>Pardubice</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Midland</t>
+          <t>Jablonec</t>
         </is>
       </c>
       <c r="G107">
@@ -17750,64 +17750,64 @@
         </is>
       </c>
       <c r="N107">
-        <v>2.76</v>
+        <v>2.5</v>
       </c>
       <c r="O107">
+        <v>3.15</v>
+      </c>
+      <c r="P107">
         <v>2.7</v>
       </c>
-      <c r="P107">
-        <v>2.65</v>
-      </c>
       <c r="Q107">
-        <v>3.74</v>
+        <v>3.14</v>
       </c>
       <c r="R107">
-        <v>1.7</v>
+        <v>2.05</v>
       </c>
       <c r="S107">
-        <v>1.7</v>
+        <v>1.36</v>
       </c>
       <c r="T107">
-        <v>2.1</v>
+        <v>2.85</v>
       </c>
       <c r="U107">
-        <v>4.2</v>
+        <v>2.62</v>
       </c>
       <c r="V107">
-        <v>1.2</v>
+        <v>1.38</v>
       </c>
       <c r="W107">
+        <v>1.06</v>
+      </c>
+      <c r="X107">
         <v>1.03</v>
       </c>
-      <c r="X107">
-        <v>1.16</v>
-      </c>
       <c r="Y107">
-        <v>1.65</v>
+        <v>1.29</v>
       </c>
       <c r="Z107">
-        <v>2.1</v>
+        <v>3.45</v>
       </c>
       <c r="AA107">
-        <v>3.04</v>
+        <v>1.96</v>
       </c>
       <c r="AB107">
-        <v>1.32</v>
+        <v>1.8</v>
       </c>
       <c r="AC107">
-        <v>6.55</v>
+        <v>2.97</v>
       </c>
       <c r="AD107">
-        <v>1.05</v>
+        <v>1.3</v>
       </c>
       <c r="AE107">
-        <v>1.02</v>
+        <v>1.07</v>
       </c>
       <c r="AF107">
-        <v>2.07</v>
+        <v>1.74</v>
       </c>
       <c r="AG107">
-        <v>1.57</v>
+        <v>1.92</v>
       </c>
       <c r="AH107" t="inlineStr">
         <is>
@@ -17820,10 +17820,10 @@
         </is>
       </c>
       <c r="AJ107">
-        <v>1.34</v>
+        <v>1.41</v>
       </c>
       <c r="AK107">
-        <v>1.36</v>
+        <v>1.5</v>
       </c>
       <c r="AL107">
         <v>0</v>
@@ -17871,22 +17871,22 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Pardubice</t>
+          <t>CSD Independiente del Valle</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Jablonec</t>
+          <t>Deportivo Cuenca</t>
         </is>
       </c>
       <c r="G108">
@@ -17913,64 +17913,64 @@
         </is>
       </c>
       <c r="N108">
-        <v>2.5</v>
+        <v>1.22</v>
       </c>
       <c r="O108">
-        <v>3.15</v>
+        <v>5</v>
       </c>
       <c r="P108">
-        <v>2.7</v>
+        <v>10</v>
       </c>
       <c r="Q108">
-        <v>3.14</v>
+        <v>1.67</v>
       </c>
       <c r="R108">
-        <v>2.05</v>
+        <v>2.34</v>
       </c>
       <c r="S108">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="T108">
-        <v>2.85</v>
+        <v>3.25</v>
       </c>
       <c r="U108">
-        <v>2.62</v>
+        <v>2.3</v>
       </c>
       <c r="V108">
+        <v>1.55</v>
+      </c>
+      <c r="W108">
+        <v>1.11</v>
+      </c>
+      <c r="X108">
+        <v>1.04</v>
+      </c>
+      <c r="Y108">
+        <v>1.19</v>
+      </c>
+      <c r="Z108">
+        <v>3.8</v>
+      </c>
+      <c r="AA108">
+        <v>1.76</v>
+      </c>
+      <c r="AB108">
+        <v>2.04</v>
+      </c>
+      <c r="AC108">
+        <v>2.8</v>
+      </c>
+      <c r="AD108">
         <v>1.38</v>
       </c>
-      <c r="W108">
-        <v>1.06</v>
-      </c>
-      <c r="X108">
-        <v>1.03</v>
-      </c>
-      <c r="Y108">
-        <v>1.29</v>
-      </c>
-      <c r="Z108">
-        <v>3.45</v>
-      </c>
-      <c r="AA108">
-        <v>1.96</v>
-      </c>
-      <c r="AB108">
-        <v>1.8</v>
-      </c>
-      <c r="AC108">
-        <v>2.97</v>
-      </c>
-      <c r="AD108">
-        <v>1.3</v>
-      </c>
       <c r="AE108">
-        <v>1.07</v>
+        <v>1.13</v>
       </c>
       <c r="AF108">
-        <v>1.74</v>
+        <v>2.1</v>
       </c>
       <c r="AG108">
-        <v>1.92</v>
+        <v>1.62</v>
       </c>
       <c r="AH108" t="inlineStr">
         <is>
@@ -17983,10 +17983,10 @@
         </is>
       </c>
       <c r="AJ108">
-        <v>1.41</v>
+        <v>1.14</v>
       </c>
       <c r="AK108">
-        <v>1.5</v>
+        <v>3.35</v>
       </c>
       <c r="AL108">
         <v>0</v>
@@ -18034,22 +18034,22 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>CSD Independiente del Valle</t>
+          <t>Sutjeska</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Deportivo Cuenca</t>
+          <t>Budućnost</t>
         </is>
       </c>
       <c r="G109">
@@ -18076,64 +18076,64 @@
         </is>
       </c>
       <c r="N109">
-        <v>1.22</v>
+        <v>2.1</v>
       </c>
       <c r="O109">
-        <v>5</v>
+        <v>3.2</v>
       </c>
       <c r="P109">
-        <v>10</v>
+        <v>3.52</v>
       </c>
       <c r="Q109">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="R109">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="S109">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="T109">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="U109">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="V109">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="W109">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="X109">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="Y109">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="Z109">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="AA109">
-        <v>1.76</v>
+        <v>2.15</v>
       </c>
       <c r="AB109">
-        <v>2.04</v>
+        <v>1.66</v>
       </c>
       <c r="AC109">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="AD109">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AE109">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AF109">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AG109">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AH109" t="inlineStr">
         <is>
@@ -18146,10 +18146,10 @@
         </is>
       </c>
       <c r="AJ109">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AK109">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="AL109">
         <v>0</v>
@@ -18207,12 +18207,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Sutjeska</t>
+          <t>FK Jezero Plav</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Budućnost</t>
+          <t>Mornar</t>
         </is>
       </c>
       <c r="G110">
@@ -18239,13 +18239,13 @@
         </is>
       </c>
       <c r="N110">
-        <v>2.1</v>
+        <v>3.81</v>
       </c>
       <c r="O110">
         <v>3.2</v>
       </c>
       <c r="P110">
-        <v>3.52</v>
+        <v>2</v>
       </c>
       <c r="Q110">
         <v>0</v>
@@ -18278,10 +18278,10 @@
         <v>0</v>
       </c>
       <c r="AA110">
-        <v>2.15</v>
+        <v>2.35</v>
       </c>
       <c r="AB110">
-        <v>1.66</v>
+        <v>1.57</v>
       </c>
       <c r="AC110">
         <v>0</v>
@@ -18370,12 +18370,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>FK Jezero Plav</t>
+          <t>Petrovac</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Mornar</t>
+          <t>Bokelj</t>
         </is>
       </c>
       <c r="G111">
@@ -18402,13 +18402,13 @@
         </is>
       </c>
       <c r="N111">
-        <v>3.81</v>
+        <v>1.99</v>
       </c>
       <c r="O111">
         <v>3.2</v>
       </c>
       <c r="P111">
-        <v>2</v>
+        <v>3.82</v>
       </c>
       <c r="Q111">
         <v>0</v>
@@ -18441,10 +18441,10 @@
         <v>0</v>
       </c>
       <c r="AA111">
-        <v>2.35</v>
+        <v>2.37</v>
       </c>
       <c r="AB111">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="AC111">
         <v>0</v>
@@ -18533,12 +18533,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Petrovac</t>
+          <t>Dečić</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Bokelj</t>
+          <t>Arsenal Tivat</t>
         </is>
       </c>
       <c r="G112">
@@ -18604,10 +18604,10 @@
         <v>0</v>
       </c>
       <c r="AA112">
-        <v>2.37</v>
+        <v>2.35</v>
       </c>
       <c r="AB112">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="AC112">
         <v>0</v>
@@ -18696,12 +18696,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Dečić</t>
+          <t>Mladost DG</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Arsenal Tivat</t>
+          <t>Otrant-Olympic</t>
         </is>
       </c>
       <c r="G113">
@@ -18728,13 +18728,13 @@
         </is>
       </c>
       <c r="N113">
-        <v>1.99</v>
+        <v>2.12</v>
       </c>
       <c r="O113">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="P113">
-        <v>3.82</v>
+        <v>3.32</v>
       </c>
       <c r="Q113">
         <v>0</v>
@@ -18767,10 +18767,10 @@
         <v>0</v>
       </c>
       <c r="AA113">
-        <v>2.35</v>
+        <v>1.95</v>
       </c>
       <c r="AB113">
-        <v>1.57</v>
+        <v>1.85</v>
       </c>
       <c r="AC113">
         <v>0</v>
@@ -18844,12 +18844,12 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -18859,12 +18859,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Mladost DG</t>
+          <t>Olimpija</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Otrant-Olympic</t>
+          <t>Aluminij</t>
         </is>
       </c>
       <c r="G114">
@@ -18891,64 +18891,64 @@
         </is>
       </c>
       <c r="N114">
-        <v>2.12</v>
+        <v>1.51</v>
       </c>
       <c r="O114">
-        <v>3.3</v>
+        <v>4.05</v>
       </c>
       <c r="P114">
-        <v>3.32</v>
+        <v>5.27</v>
       </c>
       <c r="Q114">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="R114">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S114">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T114">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="U114">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="V114">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="W114">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X114">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y114">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="Z114">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AA114">
-        <v>1.95</v>
+        <v>1.7</v>
       </c>
       <c r="AB114">
-        <v>1.85</v>
+        <v>2.1</v>
       </c>
       <c r="AC114">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="AD114">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AE114">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AF114">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AG114">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AH114" t="inlineStr">
         <is>
@@ -18961,10 +18961,10 @@
         </is>
       </c>
       <c r="AJ114">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AK114">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AL114">
         <v>0</v>
@@ -18995,7 +18995,7 @@
       </c>
       <c r="AU114" t="inlineStr">
         <is>
-          <t>2026-08-02 15:00:00</t>
+          <t>2026-08-02 15:15:00</t>
         </is>
       </c>
     </row>
@@ -19022,12 +19022,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Olimpija</t>
+          <t>Brinje-Grosuplje</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Aluminij</t>
+          <t>Koper</t>
         </is>
       </c>
       <c r="G115">
@@ -19054,64 +19054,64 @@
         </is>
       </c>
       <c r="N115">
-        <v>1.51</v>
+        <v>6.11</v>
       </c>
       <c r="O115">
-        <v>4.05</v>
+        <v>4.15</v>
       </c>
       <c r="P115">
-        <v>5.27</v>
+        <v>1.44</v>
       </c>
       <c r="Q115">
-        <v>2.1</v>
+        <v>5.15</v>
       </c>
       <c r="R115">
         <v>2.3</v>
       </c>
       <c r="S115">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="T115">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="U115">
-        <v>2.5</v>
+        <v>2.55</v>
       </c>
       <c r="V115">
-        <v>1.53</v>
+        <v>1.45</v>
       </c>
       <c r="W115">
         <v>1.1</v>
       </c>
       <c r="X115">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="Y115">
         <v>1.21</v>
       </c>
       <c r="Z115">
-        <v>4</v>
+        <v>3.74</v>
       </c>
       <c r="AA115">
-        <v>1.7</v>
+        <v>1.79</v>
       </c>
       <c r="AB115">
-        <v>2.1</v>
+        <v>1.91</v>
       </c>
       <c r="AC115">
-        <v>2.59</v>
+        <v>2.96</v>
       </c>
       <c r="AD115">
-        <v>1.42</v>
+        <v>1.37</v>
       </c>
       <c r="AE115">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="AF115">
-        <v>1.71</v>
+        <v>1.78</v>
       </c>
       <c r="AG115">
-        <v>2</v>
+        <v>1.88</v>
       </c>
       <c r="AH115" t="inlineStr">
         <is>
@@ -19124,10 +19124,10 @@
         </is>
       </c>
       <c r="AJ115">
-        <v>1.1</v>
+        <v>1.18</v>
       </c>
       <c r="AK115">
-        <v>2.4</v>
+        <v>1.09</v>
       </c>
       <c r="AL115">
         <v>0</v>
@@ -19175,7 +19175,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -19185,12 +19185,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Brinje-Grosuplje</t>
+          <t>GKS Katowice</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Koper</t>
+          <t>Radomiak Radom</t>
         </is>
       </c>
       <c r="G116">
@@ -19217,64 +19217,64 @@
         </is>
       </c>
       <c r="N116">
-        <v>6.11</v>
+        <v>1.88</v>
       </c>
       <c r="O116">
-        <v>4.15</v>
+        <v>3.52</v>
       </c>
       <c r="P116">
-        <v>1.44</v>
+        <v>3.88</v>
       </c>
       <c r="Q116">
-        <v>5.15</v>
+        <v>2.5</v>
       </c>
       <c r="R116">
         <v>2.3</v>
       </c>
       <c r="S116">
-        <v>1.33</v>
+        <v>1.37</v>
       </c>
       <c r="T116">
         <v>3</v>
       </c>
       <c r="U116">
-        <v>2.55</v>
+        <v>2.62</v>
       </c>
       <c r="V116">
-        <v>1.45</v>
+        <v>1.41</v>
       </c>
       <c r="W116">
-        <v>1.1</v>
+        <v>1.06</v>
       </c>
       <c r="X116">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="Y116">
-        <v>1.21</v>
+        <v>1.26</v>
       </c>
       <c r="Z116">
-        <v>3.74</v>
+        <v>3.76</v>
       </c>
       <c r="AA116">
         <v>1.79</v>
       </c>
       <c r="AB116">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="AC116">
-        <v>2.96</v>
+        <v>2.88</v>
       </c>
       <c r="AD116">
-        <v>1.37</v>
+        <v>1.32</v>
       </c>
       <c r="AE116">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="AF116">
-        <v>1.78</v>
+        <v>1.69</v>
       </c>
       <c r="AG116">
-        <v>1.88</v>
+        <v>2.05</v>
       </c>
       <c r="AH116" t="inlineStr">
         <is>
@@ -19287,10 +19287,10 @@
         </is>
       </c>
       <c r="AJ116">
-        <v>1.18</v>
+        <v>1.27</v>
       </c>
       <c r="AK116">
-        <v>1.09</v>
+        <v>1.82</v>
       </c>
       <c r="AL116">
         <v>0</v>
@@ -19338,7 +19338,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -19348,12 +19348,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>GKS Katowice</t>
+          <t>Ferencváros</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Radomiak Radom</t>
+          <t>Vasas</t>
         </is>
       </c>
       <c r="G117">
@@ -19380,64 +19380,64 @@
         </is>
       </c>
       <c r="N117">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="O117">
-        <v>3.52</v>
+        <v>0</v>
       </c>
       <c r="P117">
-        <v>3.88</v>
+        <v>0</v>
       </c>
       <c r="Q117">
+        <v>1.95</v>
+      </c>
+      <c r="R117">
         <v>2.5</v>
       </c>
-      <c r="R117">
-        <v>2.3</v>
-      </c>
       <c r="S117">
-        <v>1.37</v>
+        <v>1.27</v>
       </c>
       <c r="T117">
-        <v>3</v>
+        <v>3.25</v>
       </c>
       <c r="U117">
-        <v>2.62</v>
+        <v>2.25</v>
       </c>
       <c r="V117">
-        <v>1.41</v>
+        <v>1.6</v>
       </c>
       <c r="W117">
-        <v>1.06</v>
+        <v>1.15</v>
       </c>
       <c r="X117">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y117">
-        <v>1.26</v>
+        <v>1.18</v>
       </c>
       <c r="Z117">
-        <v>3.76</v>
+        <v>4.5</v>
       </c>
       <c r="AA117">
-        <v>1.79</v>
+        <v>1.6</v>
       </c>
       <c r="AB117">
-        <v>1.92</v>
+        <v>2.14</v>
       </c>
       <c r="AC117">
-        <v>2.88</v>
+        <v>2.5</v>
       </c>
       <c r="AD117">
-        <v>1.32</v>
+        <v>1.45</v>
       </c>
       <c r="AE117">
-        <v>1.13</v>
+        <v>1.17</v>
       </c>
       <c r="AF117">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="AG117">
-        <v>2.05</v>
+        <v>2.01</v>
       </c>
       <c r="AH117" t="inlineStr">
         <is>
@@ -19450,10 +19450,10 @@
         </is>
       </c>
       <c r="AJ117">
-        <v>1.27</v>
+        <v>1.07</v>
       </c>
       <c r="AK117">
-        <v>1.82</v>
+        <v>2.5</v>
       </c>
       <c r="AL117">
         <v>0</v>
@@ -19501,7 +19501,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -19511,12 +19511,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Ferencváros</t>
+          <t>CSKA Sofia</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Vasas</t>
+          <t>Dunav 2010</t>
         </is>
       </c>
       <c r="G118">
@@ -19543,64 +19543,64 @@
         </is>
       </c>
       <c r="N118">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="O118">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="P118">
-        <v>0</v>
+        <v>13.8</v>
       </c>
       <c r="Q118">
-        <v>1.95</v>
+        <v>1.57</v>
       </c>
       <c r="R118">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="S118">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="T118">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="U118">
-        <v>2.25</v>
+        <v>2.47</v>
       </c>
       <c r="V118">
-        <v>1.6</v>
+        <v>1.44</v>
       </c>
       <c r="W118">
-        <v>1.15</v>
+        <v>1.08</v>
       </c>
       <c r="X118">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y118">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="Z118">
-        <v>4.5</v>
+        <v>4.1</v>
       </c>
       <c r="AA118">
-        <v>1.6</v>
+        <v>1.9</v>
       </c>
       <c r="AB118">
-        <v>2.14</v>
+        <v>1.9</v>
       </c>
       <c r="AC118">
-        <v>2.5</v>
+        <v>2.62</v>
       </c>
       <c r="AD118">
-        <v>1.45</v>
+        <v>1.38</v>
       </c>
       <c r="AE118">
-        <v>1.17</v>
+        <v>1.13</v>
       </c>
       <c r="AF118">
-        <v>1.7</v>
+        <v>2.45</v>
       </c>
       <c r="AG118">
-        <v>2.01</v>
+        <v>1.5</v>
       </c>
       <c r="AH118" t="inlineStr">
         <is>
@@ -19613,10 +19613,10 @@
         </is>
       </c>
       <c r="AJ118">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="AK118">
-        <v>2.5</v>
+        <v>4.33</v>
       </c>
       <c r="AL118">
         <v>0</v>
@@ -19659,27 +19659,27 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>CSKA Sofia</t>
+          <t>Temperley</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Dunav 2010</t>
+          <t>Gimnasia y Tiro</t>
         </is>
       </c>
       <c r="G119">
@@ -19706,64 +19706,64 @@
         </is>
       </c>
       <c r="N119">
-        <v>1.23</v>
+        <v>1.96</v>
       </c>
       <c r="O119">
-        <v>5.3</v>
+        <v>2.85</v>
       </c>
       <c r="P119">
-        <v>13.8</v>
+        <v>4.2</v>
       </c>
       <c r="Q119">
-        <v>1.57</v>
+        <v>2.91</v>
       </c>
       <c r="R119">
-        <v>2.6</v>
+        <v>1.89</v>
       </c>
       <c r="S119">
-        <v>1.3</v>
+        <v>1.62</v>
       </c>
       <c r="T119">
-        <v>3.1</v>
+        <v>2.01</v>
       </c>
       <c r="U119">
-        <v>2.47</v>
+        <v>4.15</v>
       </c>
       <c r="V119">
-        <v>1.44</v>
+        <v>1.16</v>
       </c>
       <c r="W119">
-        <v>1.08</v>
+        <v>1.03</v>
       </c>
       <c r="X119">
-        <v>1.01</v>
+        <v>1.15</v>
       </c>
       <c r="Y119">
-        <v>1.2</v>
+        <v>1.6</v>
       </c>
       <c r="Z119">
-        <v>4.1</v>
+        <v>2.15</v>
       </c>
       <c r="AA119">
-        <v>1.9</v>
+        <v>2.88</v>
       </c>
       <c r="AB119">
-        <v>1.9</v>
+        <v>1.32</v>
       </c>
       <c r="AC119">
-        <v>2.62</v>
+        <v>6.05</v>
       </c>
       <c r="AD119">
-        <v>1.38</v>
+        <v>1.06</v>
       </c>
       <c r="AE119">
-        <v>1.13</v>
+        <v>1.02</v>
       </c>
       <c r="AF119">
-        <v>2.45</v>
+        <v>2.3</v>
       </c>
       <c r="AG119">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="AH119" t="inlineStr">
         <is>
@@ -19776,10 +19776,10 @@
         </is>
       </c>
       <c r="AJ119">
-        <v>1.1</v>
+        <v>1.36</v>
       </c>
       <c r="AK119">
-        <v>4.33</v>
+        <v>1.64</v>
       </c>
       <c r="AL119">
         <v>0</v>
@@ -19810,7 +19810,7 @@
       </c>
       <c r="AU119" t="inlineStr">
         <is>
-          <t>2026-08-02 15:15:00</t>
+          <t>2026-08-02 15:30:00</t>
         </is>
       </c>
     </row>
@@ -19837,12 +19837,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Temperley</t>
+          <t>Deportivo Maipú</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Gimnasia y Tiro</t>
+          <t>Atlanta</t>
         </is>
       </c>
       <c r="G120">
@@ -19869,64 +19869,64 @@
         </is>
       </c>
       <c r="N120">
-        <v>1.96</v>
+        <v>2.75</v>
       </c>
       <c r="O120">
-        <v>2.85</v>
+        <v>2.73</v>
       </c>
       <c r="P120">
-        <v>4.2</v>
+        <v>2.63</v>
       </c>
       <c r="Q120">
-        <v>2.91</v>
+        <v>3.51</v>
       </c>
       <c r="R120">
-        <v>1.89</v>
+        <v>1.92</v>
       </c>
       <c r="S120">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="T120">
-        <v>2.01</v>
+        <v>2.25</v>
       </c>
       <c r="U120">
-        <v>4.15</v>
+        <v>3.5</v>
       </c>
       <c r="V120">
-        <v>1.16</v>
+        <v>1.22</v>
       </c>
       <c r="W120">
         <v>1.03</v>
       </c>
       <c r="X120">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="Y120">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="Z120">
-        <v>2.15</v>
+        <v>2.25</v>
       </c>
       <c r="AA120">
-        <v>2.88</v>
+        <v>2.52</v>
       </c>
       <c r="AB120">
-        <v>1.32</v>
+        <v>1.41</v>
       </c>
       <c r="AC120">
-        <v>6.05</v>
+        <v>5.31</v>
       </c>
       <c r="AD120">
-        <v>1.06</v>
+        <v>1.11</v>
       </c>
       <c r="AE120">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="AF120">
-        <v>2.3</v>
+        <v>2.09</v>
       </c>
       <c r="AG120">
-        <v>1.48</v>
+        <v>1.65</v>
       </c>
       <c r="AH120" t="inlineStr">
         <is>
@@ -19939,10 +19939,10 @@
         </is>
       </c>
       <c r="AJ120">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="AK120">
-        <v>1.64</v>
+        <v>1.39</v>
       </c>
       <c r="AL120">
         <v>0</v>
@@ -20153,22 +20153,22 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Deportivo Maipú</t>
+          <t>Rapid Bucureşti</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Atlanta</t>
+          <t>CFR Cluj</t>
         </is>
       </c>
       <c r="G122">
@@ -20195,64 +20195,64 @@
         </is>
       </c>
       <c r="N122">
-        <v>2.75</v>
+        <v>2.16</v>
       </c>
       <c r="O122">
+        <v>3.24</v>
+      </c>
+      <c r="P122">
+        <v>3.32</v>
+      </c>
+      <c r="Q122">
+        <v>2.55</v>
+      </c>
+      <c r="R122">
+        <v>2.1</v>
+      </c>
+      <c r="S122">
+        <v>1.42</v>
+      </c>
+      <c r="T122">
+        <v>2.59</v>
+      </c>
+      <c r="U122">
         <v>2.73</v>
       </c>
-      <c r="P122">
-        <v>2.63</v>
-      </c>
-      <c r="Q122">
-        <v>3.51</v>
-      </c>
-      <c r="R122">
-        <v>1.92</v>
-      </c>
-      <c r="S122">
-        <v>1.57</v>
-      </c>
-      <c r="T122">
-        <v>2.25</v>
-      </c>
-      <c r="U122">
-        <v>3.5</v>
-      </c>
       <c r="V122">
-        <v>1.22</v>
+        <v>1.35</v>
       </c>
       <c r="W122">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="X122">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="Y122">
-        <v>1.55</v>
+        <v>1.3</v>
       </c>
       <c r="Z122">
-        <v>2.25</v>
+        <v>2.97</v>
       </c>
       <c r="AA122">
-        <v>2.52</v>
+        <v>2.06</v>
       </c>
       <c r="AB122">
-        <v>1.41</v>
+        <v>1.72</v>
       </c>
       <c r="AC122">
-        <v>5.31</v>
+        <v>3.65</v>
       </c>
       <c r="AD122">
-        <v>1.11</v>
+        <v>1.28</v>
       </c>
       <c r="AE122">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="AF122">
-        <v>2.09</v>
+        <v>1.83</v>
       </c>
       <c r="AG122">
-        <v>1.65</v>
+        <v>1.88</v>
       </c>
       <c r="AH122" t="inlineStr">
         <is>
@@ -20265,10 +20265,10 @@
         </is>
       </c>
       <c r="AJ122">
-        <v>1.4</v>
+        <v>1.25</v>
       </c>
       <c r="AK122">
-        <v>1.39</v>
+        <v>1.72</v>
       </c>
       <c r="AL122">
         <v>0</v>
@@ -20311,27 +20311,27 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Rapid Bucureşti</t>
+          <t>Recoleta</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>CFR Cluj</t>
+          <t>Puerto Montt</t>
         </is>
       </c>
       <c r="G123">
@@ -20358,64 +20358,64 @@
         </is>
       </c>
       <c r="N123">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="O123">
-        <v>3.24</v>
+        <v>0</v>
       </c>
       <c r="P123">
-        <v>3.32</v>
+        <v>0</v>
       </c>
       <c r="Q123">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="R123">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="S123">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="T123">
-        <v>2.59</v>
+        <v>0</v>
       </c>
       <c r="U123">
-        <v>2.73</v>
+        <v>0</v>
       </c>
       <c r="V123">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="W123">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="X123">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="Y123">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="Z123">
-        <v>2.97</v>
+        <v>0</v>
       </c>
       <c r="AA123">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="AB123">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AC123">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="AD123">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AE123">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AF123">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AG123">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AH123" t="inlineStr">
         <is>
@@ -20428,10 +20428,10 @@
         </is>
       </c>
       <c r="AJ123">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AK123">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AL123">
         <v>0</v>
@@ -20462,7 +20462,7 @@
       </c>
       <c r="AU123" t="inlineStr">
         <is>
-          <t>2026-08-02 15:30:00</t>
+          <t>2026-08-02 16:00:00</t>
         </is>
       </c>
     </row>
@@ -20479,7 +20479,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -20489,12 +20489,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Recoleta</t>
+          <t>La Serena</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Puerto Montt</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="G124">
@@ -20521,64 +20521,64 @@
         </is>
       </c>
       <c r="N124">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="O124">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="P124">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="Q124">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="R124">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="S124">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T124">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="U124">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="V124">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="W124">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X124">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y124">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="Z124">
-        <v>0</v>
+        <v>3.96</v>
       </c>
       <c r="AA124">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AB124">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AC124">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="AD124">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AE124">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AF124">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AG124">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AH124" t="inlineStr">
         <is>
@@ -20591,10 +20591,10 @@
         </is>
       </c>
       <c r="AJ124">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AK124">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AL124">
         <v>0</v>
@@ -20642,7 +20642,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -20652,12 +20652,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>La Serena</t>
+          <t>Real Potosí</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Gualberto Villarroel SJ</t>
         </is>
       </c>
       <c r="G125">
@@ -20684,64 +20684,64 @@
         </is>
       </c>
       <c r="N125">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="O125">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="P125">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="Q125">
-        <v>2.99</v>
+        <v>0</v>
       </c>
       <c r="R125">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="S125">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="T125">
-        <v>2.99</v>
+        <v>0</v>
       </c>
       <c r="U125">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="V125">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="W125">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="X125">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="Y125">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="Z125">
-        <v>3.96</v>
+        <v>0</v>
       </c>
       <c r="AA125">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AB125">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AC125">
-        <v>2.94</v>
+        <v>0</v>
       </c>
       <c r="AD125">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AE125">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AF125">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AG125">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AH125" t="inlineStr">
         <is>
@@ -20754,10 +20754,10 @@
         </is>
       </c>
       <c r="AJ125">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AK125">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="AL125">
         <v>0</v>
@@ -20805,7 +20805,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -20815,12 +20815,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Real Potosí</t>
+          <t>Chaco For Ever</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Gualberto Villarroel SJ</t>
+          <t>Deportivo Morón</t>
         </is>
       </c>
       <c r="G126">
@@ -20847,64 +20847,64 @@
         </is>
       </c>
       <c r="N126">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="O126">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="P126">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="Q126">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R126">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="S126">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="T126">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="U126">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="V126">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="W126">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X126">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="Y126">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="Z126">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AA126">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="AB126">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AC126">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="AD126">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AE126">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF126">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AG126">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AH126" t="inlineStr">
         <is>
@@ -20917,10 +20917,10 @@
         </is>
       </c>
       <c r="AJ126">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AK126">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AL126">
         <v>0</v>
@@ -20978,12 +20978,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Chaco For Ever</t>
+          <t>Deportivo Madryn</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Deportivo Morón</t>
+          <t>All Boys</t>
         </is>
       </c>
       <c r="G127">
@@ -21010,64 +21010,64 @@
         </is>
       </c>
       <c r="N127">
-        <v>2.72</v>
+        <v>2.12</v>
       </c>
       <c r="O127">
-        <v>2.7</v>
+        <v>2.71</v>
       </c>
       <c r="P127">
-        <v>2.69</v>
+        <v>3.87</v>
       </c>
       <c r="Q127">
-        <v>3.6</v>
+        <v>2.63</v>
       </c>
       <c r="R127">
-        <v>1.77</v>
+        <v>1.83</v>
       </c>
       <c r="S127">
-        <v>1.64</v>
+        <v>1.66</v>
       </c>
       <c r="T127">
-        <v>2.2</v>
+        <v>2.16</v>
       </c>
       <c r="U127">
-        <v>3.9</v>
+        <v>3.98</v>
       </c>
       <c r="V127">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="W127">
         <v>1.03</v>
       </c>
       <c r="X127">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="Y127">
-        <v>1.58</v>
+        <v>1.63</v>
       </c>
       <c r="Z127">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="AA127">
-        <v>2.97</v>
+        <v>3.4</v>
       </c>
       <c r="AB127">
         <v>1.35</v>
       </c>
       <c r="AC127">
-        <v>5.5</v>
+        <v>5.65</v>
       </c>
       <c r="AD127">
         <v>1.08</v>
       </c>
       <c r="AE127">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AF127">
-        <v>2.2</v>
+        <v>2.16</v>
       </c>
       <c r="AG127">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="AH127" t="inlineStr">
         <is>
@@ -21080,10 +21080,10 @@
         </is>
       </c>
       <c r="AJ127">
-        <v>1.36</v>
+        <v>1.32</v>
       </c>
       <c r="AK127">
-        <v>1.35</v>
+        <v>1.7</v>
       </c>
       <c r="AL127">
         <v>0</v>
@@ -21141,12 +21141,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Deportivo Madryn</t>
+          <t>Club Atlético Güemes</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>All Boys</t>
+          <t>Tristán Suárez</t>
         </is>
       </c>
       <c r="G128">
@@ -21173,64 +21173,64 @@
         </is>
       </c>
       <c r="N128">
-        <v>2.12</v>
+        <v>3.26</v>
       </c>
       <c r="O128">
-        <v>2.71</v>
+        <v>2.67</v>
       </c>
       <c r="P128">
+        <v>2.4</v>
+      </c>
+      <c r="Q128">
         <v>3.87</v>
       </c>
-      <c r="Q128">
-        <v>2.63</v>
-      </c>
       <c r="R128">
-        <v>1.83</v>
+        <v>1.62</v>
       </c>
       <c r="S128">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="T128">
-        <v>2.16</v>
+        <v>2.05</v>
       </c>
       <c r="U128">
-        <v>3.98</v>
+        <v>4.33</v>
       </c>
       <c r="V128">
         <v>1.17</v>
       </c>
       <c r="W128">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="X128">
-        <v>1.1</v>
+        <v>1.14</v>
       </c>
       <c r="Y128">
-        <v>1.63</v>
+        <v>1.71</v>
       </c>
       <c r="Z128">
-        <v>2.1</v>
+        <v>1.98</v>
       </c>
       <c r="AA128">
-        <v>3.4</v>
+        <v>3.08</v>
       </c>
       <c r="AB128">
-        <v>1.35</v>
+        <v>1.28</v>
       </c>
       <c r="AC128">
-        <v>5.65</v>
+        <v>6.3</v>
       </c>
       <c r="AD128">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="AE128">
         <v>1.02</v>
       </c>
       <c r="AF128">
-        <v>2.16</v>
+        <v>2.38</v>
       </c>
       <c r="AG128">
-        <v>1.57</v>
+        <v>1.51</v>
       </c>
       <c r="AH128" t="inlineStr">
         <is>
@@ -21243,10 +21243,10 @@
         </is>
       </c>
       <c r="AJ128">
+        <v>1.44</v>
+      </c>
+      <c r="AK128">
         <v>1.32</v>
-      </c>
-      <c r="AK128">
-        <v>1.7</v>
       </c>
       <c r="AL128">
         <v>0</v>
@@ -21294,22 +21294,22 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Club Atlético Güemes</t>
+          <t>Rijeka</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Tristán Suárez</t>
+          <t>Rudeš</t>
         </is>
       </c>
       <c r="G129">
@@ -21336,64 +21336,64 @@
         </is>
       </c>
       <c r="N129">
-        <v>3.26</v>
+        <v>0</v>
       </c>
       <c r="O129">
-        <v>2.67</v>
+        <v>0</v>
       </c>
       <c r="P129">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="Q129">
-        <v>3.87</v>
+        <v>0</v>
       </c>
       <c r="R129">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="S129">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="T129">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="U129">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="V129">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="W129">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="X129">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="Y129">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="Z129">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AA129">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="AB129">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AC129">
-        <v>6.3</v>
+        <v>0</v>
       </c>
       <c r="AD129">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AE129">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AF129">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="AG129">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="AH129" t="inlineStr">
         <is>
@@ -21406,10 +21406,10 @@
         </is>
       </c>
       <c r="AJ129">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AK129">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AL129">
         <v>0</v>
@@ -21452,27 +21452,27 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Rijeka</t>
+          <t>Central Norte</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Rudeš</t>
+          <t>Los Andes</t>
         </is>
       </c>
       <c r="G130">
@@ -21499,13 +21499,13 @@
         </is>
       </c>
       <c r="N130">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="O130">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="P130">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="Q130">
         <v>0</v>
@@ -21532,16 +21532,16 @@
         <v>0</v>
       </c>
       <c r="Y130">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="Z130">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AA130">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AB130">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AC130">
         <v>0</v>
@@ -21603,7 +21603,7 @@
       </c>
       <c r="AU130" t="inlineStr">
         <is>
-          <t>2026-08-02 16:00:00</t>
+          <t>2026-08-02 16:30:00</t>
         </is>
       </c>
     </row>
@@ -21615,12 +21615,12 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -21630,12 +21630,12 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Central Norte</t>
+          <t>Washington Spirit</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Los Andes</t>
+          <t>San Diego Wave</t>
         </is>
       </c>
       <c r="G131">
@@ -21662,13 +21662,13 @@
         </is>
       </c>
       <c r="N131">
-        <v>2.72</v>
+        <v>0</v>
       </c>
       <c r="O131">
-        <v>2.68</v>
+        <v>0</v>
       </c>
       <c r="P131">
-        <v>2.72</v>
+        <v>0</v>
       </c>
       <c r="Q131">
         <v>0</v>
@@ -21695,16 +21695,16 @@
         <v>0</v>
       </c>
       <c r="Y131">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="Z131">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AA131">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="AB131">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AC131">
         <v>0</v>
@@ -21766,7 +21766,7 @@
       </c>
       <c r="AU131" t="inlineStr">
         <is>
-          <t>2026-08-02 16:30:00</t>
+          <t>2026-08-02 17:00:00</t>
         </is>
       </c>
     </row>
@@ -21778,12 +21778,12 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -21793,12 +21793,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Washington Spirit</t>
+          <t>Macará</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>San Diego Wave</t>
+          <t>Guayaquil City FC</t>
         </is>
       </c>
       <c r="G132">
@@ -21825,64 +21825,64 @@
         </is>
       </c>
       <c r="N132">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="O132">
-        <v>0</v>
+        <v>3.61</v>
       </c>
       <c r="P132">
-        <v>0</v>
+        <v>5.34</v>
       </c>
       <c r="Q132">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="R132">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="S132">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="T132">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="U132">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="V132">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="W132">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X132">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="Y132">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Z132">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="AA132">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AB132">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AC132">
-        <v>0</v>
+        <v>3.94</v>
       </c>
       <c r="AD132">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AE132">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AF132">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AG132">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AH132" t="inlineStr">
         <is>
@@ -21895,10 +21895,10 @@
         </is>
       </c>
       <c r="AJ132">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AK132">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="AL132">
         <v>0</v>
@@ -21929,7 +21929,7 @@
       </c>
       <c r="AU132" t="inlineStr">
         <is>
-          <t>2026-08-02 17:00:00</t>
+          <t>2026-08-02 17:30:00</t>
         </is>
       </c>
     </row>
@@ -21941,12 +21941,12 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>18:15</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -21956,12 +21956,12 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Macará</t>
+          <t>Club Always Ready</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Guayaquil City FC</t>
+          <t>Bolívar</t>
         </is>
       </c>
       <c r="G133">
@@ -21988,64 +21988,64 @@
         </is>
       </c>
       <c r="N133">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="O133">
-        <v>3.61</v>
+        <v>0</v>
       </c>
       <c r="P133">
-        <v>5.34</v>
+        <v>0</v>
       </c>
       <c r="Q133">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="R133">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="S133">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="T133">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="U133">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="V133">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="W133">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="X133">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="Y133">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="Z133">
-        <v>2.83</v>
+        <v>0</v>
       </c>
       <c r="AA133">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AB133">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AC133">
-        <v>3.94</v>
+        <v>0</v>
       </c>
       <c r="AD133">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AE133">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AF133">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="AG133">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AH133" t="inlineStr">
         <is>
@@ -22058,10 +22058,10 @@
         </is>
       </c>
       <c r="AJ133">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AK133">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="AL133">
         <v>0</v>
@@ -22092,7 +22092,7 @@
       </c>
       <c r="AU133" t="inlineStr">
         <is>
-          <t>2026-08-02 17:30:00</t>
+          <t>2026-08-02 18:15:00</t>
         </is>
       </c>
     </row>
@@ -22104,12 +22104,12 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>18:15</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -22119,12 +22119,12 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Club Always Ready</t>
+          <t>Deportes Santa Cruz</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Bolívar</t>
+          <t>Santiago Wanderers</t>
         </is>
       </c>
       <c r="G134">
@@ -22255,7 +22255,7 @@
       </c>
       <c r="AU134" t="inlineStr">
         <is>
-          <t>2026-08-02 18:15:00</t>
+          <t>2026-08-02 18:30:00</t>
         </is>
       </c>
     </row>
@@ -22272,7 +22272,7 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -22282,12 +22282,12 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Deportes Santa Cruz</t>
+          <t>Universidad Chile</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Santiago Wanderers</t>
+          <t>Huachipato</t>
         </is>
       </c>
       <c r="G135">
@@ -22314,64 +22314,64 @@
         </is>
       </c>
       <c r="N135">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="O135">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="P135">
-        <v>0</v>
+        <v>5.15</v>
       </c>
       <c r="Q135">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="R135">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="S135">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="T135">
-        <v>0</v>
+        <v>3.07</v>
       </c>
       <c r="U135">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="V135">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W135">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X135">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y135">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="Z135">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="AA135">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AB135">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AC135">
-        <v>0</v>
+        <v>3.19</v>
       </c>
       <c r="AD135">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AE135">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AF135">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AG135">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AH135" t="inlineStr">
         <is>
@@ -22384,10 +22384,10 @@
         </is>
       </c>
       <c r="AJ135">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AK135">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="AL135">
         <v>0</v>
@@ -22430,12 +22430,12 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
@@ -22445,12 +22445,12 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Universidad Chile</t>
+          <t>HFX Wanderers FC</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Huachipato</t>
+          <t>Forge FC</t>
         </is>
       </c>
       <c r="G136">
@@ -22477,64 +22477,64 @@
         </is>
       </c>
       <c r="N136">
-        <v>1.63</v>
+        <v>4.37</v>
       </c>
       <c r="O136">
-        <v>3.7</v>
+        <v>3.72</v>
       </c>
       <c r="P136">
-        <v>5.15</v>
+        <v>1.66</v>
       </c>
       <c r="Q136">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="R136">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="S136">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="T136">
-        <v>3.07</v>
+        <v>0</v>
       </c>
       <c r="U136">
-        <v>2.69</v>
+        <v>0</v>
       </c>
       <c r="V136">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="W136">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="X136">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y136">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="Z136">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="AA136">
-        <v>1.88</v>
+        <v>1.65</v>
       </c>
       <c r="AB136">
-        <v>1.89</v>
+        <v>2.2</v>
       </c>
       <c r="AC136">
-        <v>3.19</v>
+        <v>0</v>
       </c>
       <c r="AD136">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="AE136">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AF136">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AG136">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AH136" t="inlineStr">
         <is>
@@ -22547,10 +22547,10 @@
         </is>
       </c>
       <c r="AJ136">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AK136">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="AL136">
         <v>0</v>
@@ -22581,7 +22581,7 @@
       </c>
       <c r="AU136" t="inlineStr">
         <is>
-          <t>2026-08-02 18:30:00</t>
+          <t>2026-08-02 19:00:00</t>
         </is>
       </c>
     </row>
@@ -22593,12 +22593,12 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
@@ -22608,12 +22608,12 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>HFX Wanderers FC</t>
+          <t>Utah Royals</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Forge FC</t>
+          <t>Portland Thorns</t>
         </is>
       </c>
       <c r="G137">
@@ -22640,13 +22640,13 @@
         </is>
       </c>
       <c r="N137">
-        <v>4.37</v>
+        <v>0</v>
       </c>
       <c r="O137">
-        <v>3.72</v>
+        <v>0</v>
       </c>
       <c r="P137">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="Q137">
         <v>0</v>
@@ -22679,10 +22679,10 @@
         <v>0</v>
       </c>
       <c r="AA137">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AB137">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AC137">
         <v>0</v>
@@ -22744,7 +22744,7 @@
       </c>
       <c r="AU137" t="inlineStr">
         <is>
-          <t>2026-08-02 19:00:00</t>
+          <t>2026-08-02 20:00:00</t>
         </is>
       </c>
     </row>
@@ -22756,12 +22756,12 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>20:10</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -22771,12 +22771,12 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Utah Royals</t>
+          <t>Leones del Norte</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Portland Thorns</t>
+          <t>Barcelona</t>
         </is>
       </c>
       <c r="G138">
@@ -22812,55 +22812,55 @@
         <v>0</v>
       </c>
       <c r="Q138">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R138">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="S138">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="T138">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="U138">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V138">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="W138">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X138">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="Y138">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="Z138">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="AA138">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="AB138">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AC138">
-        <v>0</v>
+        <v>4.24</v>
       </c>
       <c r="AD138">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AE138">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AF138">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AG138">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AH138" t="inlineStr">
         <is>
@@ -22873,10 +22873,10 @@
         </is>
       </c>
       <c r="AJ138">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AK138">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AL138">
         <v>0</v>
@@ -22907,7 +22907,7 @@
       </c>
       <c r="AU138" t="inlineStr">
         <is>
-          <t>2026-08-02 20:00:00</t>
+          <t>2026-08-02 20:10:00</t>
         </is>
       </c>
     </row>
@@ -22919,12 +22919,12 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>20:10</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
@@ -22934,12 +22934,12 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Leones del Norte</t>
+          <t>Oriente Petrolero</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Barcelona</t>
+          <t>Nacional Potosí</t>
         </is>
       </c>
       <c r="G139">
@@ -22975,55 +22975,55 @@
         <v>0</v>
       </c>
       <c r="Q139">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="R139">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="S139">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="T139">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="U139">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="V139">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="W139">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="X139">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="Y139">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="Z139">
-        <v>2.59</v>
+        <v>0</v>
       </c>
       <c r="AA139">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="AB139">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AC139">
-        <v>4.24</v>
+        <v>0</v>
       </c>
       <c r="AD139">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AE139">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AF139">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AG139">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AH139" t="inlineStr">
         <is>
@@ -23036,10 +23036,10 @@
         </is>
       </c>
       <c r="AJ139">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="AK139">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AL139">
         <v>0</v>
@@ -23070,7 +23070,7 @@
       </c>
       <c r="AU139" t="inlineStr">
         <is>
-          <t>2026-08-02 20:10:00</t>
+          <t>2026-08-02 20:30:00</t>
         </is>
       </c>
     </row>
@@ -23082,12 +23082,12 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>22:00</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
@@ -23097,12 +23097,12 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Oriente Petrolero</t>
+          <t>Denver Summit W</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Nacional Potosí</t>
+          <t>Boston Legacy W</t>
         </is>
       </c>
       <c r="G140">
@@ -23129,13 +23129,13 @@
         </is>
       </c>
       <c r="N140">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="O140">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="P140">
-        <v>0</v>
+        <v>3.67</v>
       </c>
       <c r="Q140">
         <v>0</v>
@@ -23232,169 +23232,6 @@
         <v>0</v>
       </c>
       <c r="AU140" t="inlineStr">
-        <is>
-          <t>2026-08-02 20:30:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="141">
-      <c r="A141" t="inlineStr">
-        <is>
-          <t>2026-08-02</t>
-        </is>
-      </c>
-      <c r="B141" t="inlineStr">
-        <is>
-          <t>22:00</t>
-        </is>
-      </c>
-      <c r="C141" t="inlineStr">
-        <is>
-          <t>USA NWSL</t>
-        </is>
-      </c>
-      <c r="D141" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="E141" t="inlineStr">
-        <is>
-          <t>Denver Summit W</t>
-        </is>
-      </c>
-      <c r="F141" t="inlineStr">
-        <is>
-          <t>Boston Legacy W</t>
-        </is>
-      </c>
-      <c r="G141">
-        <v>0</v>
-      </c>
-      <c r="H141">
-        <v>0</v>
-      </c>
-      <c r="I141">
-        <v>0</v>
-      </c>
-      <c r="J141">
-        <v>0</v>
-      </c>
-      <c r="K141">
-        <v>0</v>
-      </c>
-      <c r="L141">
-        <v>0</v>
-      </c>
-      <c r="M141" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="N141">
-        <v>1.82</v>
-      </c>
-      <c r="O141">
-        <v>3.6</v>
-      </c>
-      <c r="P141">
-        <v>3.67</v>
-      </c>
-      <c r="Q141">
-        <v>0</v>
-      </c>
-      <c r="R141">
-        <v>0</v>
-      </c>
-      <c r="S141">
-        <v>0</v>
-      </c>
-      <c r="T141">
-        <v>0</v>
-      </c>
-      <c r="U141">
-        <v>0</v>
-      </c>
-      <c r="V141">
-        <v>0</v>
-      </c>
-      <c r="W141">
-        <v>0</v>
-      </c>
-      <c r="X141">
-        <v>0</v>
-      </c>
-      <c r="Y141">
-        <v>0</v>
-      </c>
-      <c r="Z141">
-        <v>0</v>
-      </c>
-      <c r="AA141">
-        <v>0</v>
-      </c>
-      <c r="AB141">
-        <v>0</v>
-      </c>
-      <c r="AC141">
-        <v>0</v>
-      </c>
-      <c r="AD141">
-        <v>0</v>
-      </c>
-      <c r="AE141">
-        <v>0</v>
-      </c>
-      <c r="AF141">
-        <v>0</v>
-      </c>
-      <c r="AG141">
-        <v>0</v>
-      </c>
-      <c r="AH141" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI141" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ141">
-        <v>0</v>
-      </c>
-      <c r="AK141">
-        <v>0</v>
-      </c>
-      <c r="AL141">
-        <v>0</v>
-      </c>
-      <c r="AM141">
-        <v>-1</v>
-      </c>
-      <c r="AN141">
-        <v>-1</v>
-      </c>
-      <c r="AO141">
-        <v>-1</v>
-      </c>
-      <c r="AP141">
-        <v>-1</v>
-      </c>
-      <c r="AQ141">
-        <v>0</v>
-      </c>
-      <c r="AR141">
-        <v>0</v>
-      </c>
-      <c r="AS141">
-        <v>0</v>
-      </c>
-      <c r="AT141">
-        <v>0</v>
-      </c>
-      <c r="AU141" t="inlineStr">
         <is>
           <t>2026-08-02 22:00:00</t>
         </is>

--- a/jogos_2026-08-02.xlsx
+++ b/jogos_2026-08-02.xlsx
@@ -2233,12 +2233,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Daejeon Citizen</t>
+          <t>Jeju United</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Gwangju</t>
+          <t>Incheon United</t>
         </is>
       </c>
       <c r="G12">
@@ -2265,64 +2265,64 @@
         </is>
       </c>
       <c r="N12">
-        <v>1.49</v>
+        <v>3.11</v>
       </c>
       <c r="O12">
-        <v>4.15</v>
+        <v>2.98</v>
       </c>
       <c r="P12">
-        <v>6.41</v>
+        <v>2.44</v>
       </c>
       <c r="Q12">
-        <v>1.95</v>
+        <v>3.6</v>
       </c>
       <c r="R12">
-        <v>2.28</v>
+        <v>1.93</v>
       </c>
       <c r="S12">
-        <v>1.33</v>
+        <v>1.48</v>
       </c>
       <c r="T12">
-        <v>2.9</v>
+        <v>2.34</v>
       </c>
       <c r="U12">
-        <v>2.7</v>
+        <v>3.4</v>
       </c>
       <c r="V12">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="W12">
-        <v>1.07</v>
+        <v>1.01</v>
       </c>
       <c r="X12">
         <v>1.05</v>
       </c>
       <c r="Y12">
-        <v>1.22</v>
+        <v>1.4</v>
       </c>
       <c r="Z12">
-        <v>3.54</v>
+        <v>2.57</v>
       </c>
       <c r="AA12">
-        <v>1.85</v>
+        <v>2.38</v>
       </c>
       <c r="AB12">
-        <v>1.87</v>
+        <v>1.56</v>
       </c>
       <c r="AC12">
-        <v>2.89</v>
+        <v>4.63</v>
       </c>
       <c r="AD12">
-        <v>1.32</v>
+        <v>1.19</v>
       </c>
       <c r="AE12">
-        <v>1.09</v>
+        <v>1.05</v>
       </c>
       <c r="AF12">
-        <v>1.9</v>
+        <v>1.82</v>
       </c>
       <c r="AG12">
-        <v>1.8</v>
+        <v>1.78</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2335,10 +2335,10 @@
         </is>
       </c>
       <c r="AJ12">
-        <v>1.19</v>
+        <v>1.33</v>
       </c>
       <c r="AK12">
-        <v>2.7</v>
+        <v>1.36</v>
       </c>
       <c r="AL12">
         <v>0</v>
@@ -2396,12 +2396,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Jeju United</t>
+          <t>Daejeon Citizen</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Incheon United</t>
+          <t>Gwangju</t>
         </is>
       </c>
       <c r="G13">
@@ -2428,80 +2428,80 @@
         </is>
       </c>
       <c r="N13">
-        <v>3.11</v>
+        <v>1.49</v>
       </c>
       <c r="O13">
-        <v>2.98</v>
+        <v>4.15</v>
       </c>
       <c r="P13">
-        <v>2.44</v>
+        <v>6.41</v>
       </c>
       <c r="Q13">
-        <v>3.6</v>
+        <v>1.95</v>
       </c>
       <c r="R13">
-        <v>1.93</v>
+        <v>2.28</v>
       </c>
       <c r="S13">
-        <v>1.48</v>
+        <v>1.33</v>
       </c>
       <c r="T13">
-        <v>2.34</v>
+        <v>2.9</v>
       </c>
       <c r="U13">
-        <v>3.4</v>
+        <v>2.7</v>
       </c>
       <c r="V13">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="W13">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="X13">
         <v>1.05</v>
       </c>
       <c r="Y13">
-        <v>1.4</v>
+        <v>1.22</v>
       </c>
       <c r="Z13">
-        <v>2.57</v>
+        <v>3.54</v>
       </c>
       <c r="AA13">
-        <v>2.38</v>
+        <v>1.85</v>
       </c>
       <c r="AB13">
-        <v>1.56</v>
+        <v>1.87</v>
       </c>
       <c r="AC13">
-        <v>4.63</v>
+        <v>2.89</v>
       </c>
       <c r="AD13">
+        <v>1.32</v>
+      </c>
+      <c r="AE13">
+        <v>1.09</v>
+      </c>
+      <c r="AF13">
+        <v>1.9</v>
+      </c>
+      <c r="AG13">
+        <v>1.8</v>
+      </c>
+      <c r="AH13" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI13" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ13">
         <v>1.19</v>
       </c>
-      <c r="AE13">
-        <v>1.05</v>
-      </c>
-      <c r="AF13">
-        <v>1.82</v>
-      </c>
-      <c r="AG13">
-        <v>1.78</v>
-      </c>
-      <c r="AH13" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI13" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ13">
-        <v>1.33</v>
-      </c>
       <c r="AK13">
-        <v>1.36</v>
+        <v>2.7</v>
       </c>
       <c r="AL13">
         <v>0</v>
@@ -2559,12 +2559,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Busan I'Park</t>
+          <t>Gimpo Citizen</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Seoul E-Land</t>
+          <t>Gyeongnam</t>
         </is>
       </c>
       <c r="G14">
@@ -2591,31 +2591,31 @@
         </is>
       </c>
       <c r="N14">
-        <v>2.74</v>
+        <v>1.94</v>
       </c>
       <c r="O14">
-        <v>3.44</v>
+        <v>3.34</v>
       </c>
       <c r="P14">
-        <v>2.25</v>
+        <v>3.51</v>
       </c>
       <c r="Q14">
-        <v>3.1</v>
+        <v>2.48</v>
       </c>
       <c r="R14">
-        <v>2.16</v>
+        <v>2.03</v>
       </c>
       <c r="S14">
-        <v>1.29</v>
+        <v>1.4</v>
       </c>
       <c r="T14">
-        <v>3.25</v>
+        <v>2.75</v>
       </c>
       <c r="U14">
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="V14">
-        <v>1.5</v>
+        <v>1.33</v>
       </c>
       <c r="W14">
         <v>1.06</v>
@@ -2624,31 +2624,31 @@
         <v>1.03</v>
       </c>
       <c r="Y14">
-        <v>1.16</v>
+        <v>1.38</v>
       </c>
       <c r="Z14">
-        <v>4.05</v>
+        <v>2.93</v>
       </c>
       <c r="AA14">
-        <v>1.69</v>
+        <v>1.95</v>
       </c>
       <c r="AB14">
-        <v>2.07</v>
+        <v>1.75</v>
       </c>
       <c r="AC14">
-        <v>2.66</v>
+        <v>3.2</v>
       </c>
       <c r="AD14">
-        <v>1.37</v>
+        <v>1.27</v>
       </c>
       <c r="AE14">
-        <v>1.11</v>
+        <v>1.03</v>
       </c>
       <c r="AF14">
-        <v>1.55</v>
+        <v>1.93</v>
       </c>
       <c r="AG14">
-        <v>2.27</v>
+        <v>1.76</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2661,10 +2661,10 @@
         </is>
       </c>
       <c r="AJ14">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="AK14">
-        <v>1.31</v>
+        <v>1.83</v>
       </c>
       <c r="AL14">
         <v>0</v>
@@ -2722,12 +2722,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Jeonnam Dragons</t>
+          <t>Ansan Greeners</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Paju Citizen</t>
+          <t>Gimhae City</t>
         </is>
       </c>
       <c r="G15">
@@ -2754,64 +2754,64 @@
         </is>
       </c>
       <c r="N15">
-        <v>1.97</v>
+        <v>2.91</v>
       </c>
       <c r="O15">
-        <v>3.32</v>
+        <v>3.38</v>
       </c>
       <c r="P15">
-        <v>3.45</v>
+        <v>2.18</v>
       </c>
       <c r="Q15">
-        <v>2.62</v>
+        <v>3.28</v>
       </c>
       <c r="R15">
-        <v>2.25</v>
+        <v>2.05</v>
       </c>
       <c r="S15">
+        <v>1.34</v>
+      </c>
+      <c r="T15">
+        <v>3.09</v>
+      </c>
+      <c r="U15">
+        <v>2.66</v>
+      </c>
+      <c r="V15">
+        <v>1.39</v>
+      </c>
+      <c r="W15">
+        <v>1.08</v>
+      </c>
+      <c r="X15">
+        <v>1.05</v>
+      </c>
+      <c r="Y15">
+        <v>1.23</v>
+      </c>
+      <c r="Z15">
+        <v>3.42</v>
+      </c>
+      <c r="AA15">
+        <v>1.81</v>
+      </c>
+      <c r="AB15">
+        <v>1.88</v>
+      </c>
+      <c r="AC15">
+        <v>2.97</v>
+      </c>
+      <c r="AD15">
         <v>1.3</v>
       </c>
-      <c r="T15">
-        <v>3.1</v>
-      </c>
-      <c r="U15">
-        <v>2.5</v>
-      </c>
-      <c r="V15">
-        <v>1.44</v>
-      </c>
-      <c r="W15">
-        <v>1.1</v>
-      </c>
-      <c r="X15">
-        <v>1</v>
-      </c>
-      <c r="Y15">
-        <v>1.26</v>
-      </c>
-      <c r="Z15">
-        <v>3.71</v>
-      </c>
-      <c r="AA15">
-        <v>1.79</v>
-      </c>
-      <c r="AB15">
-        <v>1.9</v>
-      </c>
-      <c r="AC15">
-        <v>3.07</v>
-      </c>
-      <c r="AD15">
-        <v>1.36</v>
-      </c>
       <c r="AE15">
-        <v>1.13</v>
+        <v>1.08</v>
       </c>
       <c r="AF15">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="AG15">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2824,10 +2824,10 @@
         </is>
       </c>
       <c r="AJ15">
-        <v>1.25</v>
+        <v>1.57</v>
       </c>
       <c r="AK15">
-        <v>1.58</v>
+        <v>1.29</v>
       </c>
       <c r="AL15">
         <v>0</v>
@@ -2885,12 +2885,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Gimpo Citizen</t>
+          <t>Busan I'Park</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Gyeongnam</t>
+          <t>Seoul E-Land</t>
         </is>
       </c>
       <c r="G16">
@@ -2917,31 +2917,31 @@
         </is>
       </c>
       <c r="N16">
-        <v>1.94</v>
+        <v>2.74</v>
       </c>
       <c r="O16">
-        <v>3.34</v>
+        <v>3.44</v>
       </c>
       <c r="P16">
-        <v>3.51</v>
+        <v>2.25</v>
       </c>
       <c r="Q16">
-        <v>2.48</v>
+        <v>3.1</v>
       </c>
       <c r="R16">
-        <v>2.03</v>
+        <v>2.16</v>
       </c>
       <c r="S16">
-        <v>1.4</v>
+        <v>1.29</v>
       </c>
       <c r="T16">
-        <v>2.75</v>
+        <v>3.25</v>
       </c>
       <c r="U16">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="V16">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
       <c r="W16">
         <v>1.06</v>
@@ -2950,31 +2950,31 @@
         <v>1.03</v>
       </c>
       <c r="Y16">
-        <v>1.38</v>
+        <v>1.16</v>
       </c>
       <c r="Z16">
-        <v>2.93</v>
+        <v>4.05</v>
       </c>
       <c r="AA16">
-        <v>1.95</v>
+        <v>1.69</v>
       </c>
       <c r="AB16">
-        <v>1.75</v>
+        <v>2.07</v>
       </c>
       <c r="AC16">
-        <v>3.2</v>
+        <v>2.66</v>
       </c>
       <c r="AD16">
-        <v>1.27</v>
+        <v>1.37</v>
       </c>
       <c r="AE16">
-        <v>1.03</v>
+        <v>1.11</v>
       </c>
       <c r="AF16">
-        <v>1.93</v>
+        <v>1.55</v>
       </c>
       <c r="AG16">
-        <v>1.76</v>
+        <v>2.27</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -2987,10 +2987,10 @@
         </is>
       </c>
       <c r="AJ16">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="AK16">
-        <v>1.83</v>
+        <v>1.31</v>
       </c>
       <c r="AL16">
         <v>0</v>
@@ -3048,12 +3048,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Ansan Greeners</t>
+          <t>Jeonnam Dragons</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Gimhae City</t>
+          <t>Paju Citizen</t>
         </is>
       </c>
       <c r="G17">
@@ -3080,64 +3080,64 @@
         </is>
       </c>
       <c r="N17">
-        <v>2.91</v>
+        <v>1.97</v>
       </c>
       <c r="O17">
-        <v>3.38</v>
+        <v>3.32</v>
       </c>
       <c r="P17">
-        <v>2.18</v>
+        <v>3.45</v>
       </c>
       <c r="Q17">
-        <v>3.28</v>
+        <v>2.62</v>
       </c>
       <c r="R17">
-        <v>2.05</v>
+        <v>2.25</v>
       </c>
       <c r="S17">
-        <v>1.34</v>
+        <v>1.3</v>
       </c>
       <c r="T17">
-        <v>3.09</v>
+        <v>3.1</v>
       </c>
       <c r="U17">
-        <v>2.66</v>
+        <v>2.5</v>
       </c>
       <c r="V17">
-        <v>1.39</v>
+        <v>1.44</v>
       </c>
       <c r="W17">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="X17">
-        <v>1.05</v>
+        <v>1</v>
       </c>
       <c r="Y17">
-        <v>1.23</v>
+        <v>1.26</v>
       </c>
       <c r="Z17">
-        <v>3.42</v>
+        <v>3.71</v>
       </c>
       <c r="AA17">
-        <v>1.81</v>
+        <v>1.79</v>
       </c>
       <c r="AB17">
-        <v>1.88</v>
+        <v>1.9</v>
       </c>
       <c r="AC17">
-        <v>2.97</v>
+        <v>3.07</v>
       </c>
       <c r="AD17">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="AE17">
-        <v>1.08</v>
+        <v>1.13</v>
       </c>
       <c r="AF17">
-        <v>1.67</v>
+        <v>1.73</v>
       </c>
       <c r="AG17">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3150,10 +3150,10 @@
         </is>
       </c>
       <c r="AJ17">
-        <v>1.57</v>
+        <v>1.25</v>
       </c>
       <c r="AK17">
-        <v>1.29</v>
+        <v>1.58</v>
       </c>
       <c r="AL17">
         <v>0</v>
@@ -8753,12 +8753,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Grasshopper</t>
+          <t>Sion</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Lugano</t>
+          <t>Luzern</t>
         </is>
       </c>
       <c r="G52">
@@ -8785,64 +8785,64 @@
         </is>
       </c>
       <c r="N52">
-        <v>3.48</v>
+        <v>1.77</v>
       </c>
       <c r="O52">
-        <v>3.52</v>
+        <v>3.98</v>
       </c>
       <c r="P52">
-        <v>2.04</v>
+        <v>3.98</v>
       </c>
       <c r="Q52">
-        <v>4.16</v>
+        <v>2.38</v>
       </c>
       <c r="R52">
-        <v>2.23</v>
+        <v>2.36</v>
       </c>
       <c r="S52">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="T52">
-        <v>3.3</v>
+        <v>3.7</v>
       </c>
       <c r="U52">
-        <v>2.47</v>
+        <v>2.2</v>
       </c>
       <c r="V52">
-        <v>1.45</v>
+        <v>1.62</v>
       </c>
       <c r="W52">
-        <v>1.11</v>
+        <v>1.17</v>
       </c>
       <c r="X52">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y52">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="Z52">
-        <v>4</v>
+        <v>4.55</v>
       </c>
       <c r="AA52">
-        <v>1.81</v>
+        <v>1.5</v>
       </c>
       <c r="AB52">
-        <v>2.01</v>
+        <v>2.29</v>
       </c>
       <c r="AC52">
-        <v>2.68</v>
+        <v>2.41</v>
       </c>
       <c r="AD52">
-        <v>1.37</v>
+        <v>1.57</v>
       </c>
       <c r="AE52">
-        <v>1.11</v>
+        <v>1.19</v>
       </c>
       <c r="AF52">
-        <v>1.61</v>
+        <v>1.5</v>
       </c>
       <c r="AG52">
-        <v>2.18</v>
+        <v>2.42</v>
       </c>
       <c r="AH52" t="inlineStr">
         <is>
@@ -8855,10 +8855,10 @@
         </is>
       </c>
       <c r="AJ52">
-        <v>1.85</v>
+        <v>1.25</v>
       </c>
       <c r="AK52">
-        <v>1.25</v>
+        <v>1.87</v>
       </c>
       <c r="AL52">
         <v>0</v>
@@ -8916,12 +8916,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Sion</t>
+          <t>Grasshopper</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Luzern</t>
+          <t>Lugano</t>
         </is>
       </c>
       <c r="G53">
@@ -8948,80 +8948,80 @@
         </is>
       </c>
       <c r="N53">
-        <v>1.77</v>
+        <v>3.48</v>
       </c>
       <c r="O53">
-        <v>3.98</v>
+        <v>3.52</v>
       </c>
       <c r="P53">
-        <v>3.98</v>
+        <v>2.04</v>
       </c>
       <c r="Q53">
-        <v>2.38</v>
+        <v>4.16</v>
       </c>
       <c r="R53">
-        <v>2.36</v>
+        <v>2.23</v>
       </c>
       <c r="S53">
+        <v>1.3</v>
+      </c>
+      <c r="T53">
+        <v>3.3</v>
+      </c>
+      <c r="U53">
+        <v>2.47</v>
+      </c>
+      <c r="V53">
+        <v>1.45</v>
+      </c>
+      <c r="W53">
+        <v>1.11</v>
+      </c>
+      <c r="X53">
+        <v>1.04</v>
+      </c>
+      <c r="Y53">
+        <v>1.22</v>
+      </c>
+      <c r="Z53">
+        <v>4</v>
+      </c>
+      <c r="AA53">
+        <v>1.81</v>
+      </c>
+      <c r="AB53">
+        <v>2.01</v>
+      </c>
+      <c r="AC53">
+        <v>2.68</v>
+      </c>
+      <c r="AD53">
+        <v>1.37</v>
+      </c>
+      <c r="AE53">
+        <v>1.11</v>
+      </c>
+      <c r="AF53">
+        <v>1.61</v>
+      </c>
+      <c r="AG53">
+        <v>2.18</v>
+      </c>
+      <c r="AH53" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI53" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ53">
+        <v>1.85</v>
+      </c>
+      <c r="AK53">
         <v>1.25</v>
-      </c>
-      <c r="T53">
-        <v>3.7</v>
-      </c>
-      <c r="U53">
-        <v>2.2</v>
-      </c>
-      <c r="V53">
-        <v>1.62</v>
-      </c>
-      <c r="W53">
-        <v>1.17</v>
-      </c>
-      <c r="X53">
-        <v>1.02</v>
-      </c>
-      <c r="Y53">
-        <v>1.17</v>
-      </c>
-      <c r="Z53">
-        <v>4.55</v>
-      </c>
-      <c r="AA53">
-        <v>1.5</v>
-      </c>
-      <c r="AB53">
-        <v>2.29</v>
-      </c>
-      <c r="AC53">
-        <v>2.41</v>
-      </c>
-      <c r="AD53">
-        <v>1.57</v>
-      </c>
-      <c r="AE53">
-        <v>1.19</v>
-      </c>
-      <c r="AF53">
-        <v>1.5</v>
-      </c>
-      <c r="AG53">
-        <v>2.42</v>
-      </c>
-      <c r="AH53" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI53" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ53">
-        <v>1.25</v>
-      </c>
-      <c r="AK53">
-        <v>1.87</v>
       </c>
       <c r="AL53">
         <v>0</v>
@@ -16740,12 +16740,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Partizan</t>
+          <t>Zemun</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>IMT Novi Beograd</t>
+          <t>Radnički Niš</t>
         </is>
       </c>
       <c r="G101">
@@ -16772,80 +16772,80 @@
         </is>
       </c>
       <c r="N101">
+        <v>2.46</v>
+      </c>
+      <c r="O101">
+        <v>3.14</v>
+      </c>
+      <c r="P101">
+        <v>2.59</v>
+      </c>
+      <c r="Q101">
+        <v>3.1</v>
+      </c>
+      <c r="R101">
+        <v>2.1</v>
+      </c>
+      <c r="S101">
+        <v>1.36</v>
+      </c>
+      <c r="T101">
+        <v>2.77</v>
+      </c>
+      <c r="U101">
+        <v>2.78</v>
+      </c>
+      <c r="V101">
+        <v>1.36</v>
+      </c>
+      <c r="W101">
+        <v>1.03</v>
+      </c>
+      <c r="X101">
+        <v>1.06</v>
+      </c>
+      <c r="Y101">
+        <v>1.25</v>
+      </c>
+      <c r="Z101">
+        <v>3.28</v>
+      </c>
+      <c r="AA101">
+        <v>1.89</v>
+      </c>
+      <c r="AB101">
+        <v>1.81</v>
+      </c>
+      <c r="AC101">
+        <v>3.2</v>
+      </c>
+      <c r="AD101">
+        <v>1.26</v>
+      </c>
+      <c r="AE101">
+        <v>1.06</v>
+      </c>
+      <c r="AF101">
+        <v>1.68</v>
+      </c>
+      <c r="AG101">
+        <v>2.04</v>
+      </c>
+      <c r="AH101" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI101" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ101">
+        <v>1.26</v>
+      </c>
+      <c r="AK101">
         <v>1.43</v>
-      </c>
-      <c r="O101">
-        <v>4.15</v>
-      </c>
-      <c r="P101">
-        <v>6.28</v>
-      </c>
-      <c r="Q101">
-        <v>1.91</v>
-      </c>
-      <c r="R101">
-        <v>2.4</v>
-      </c>
-      <c r="S101">
-        <v>1.28</v>
-      </c>
-      <c r="T101">
-        <v>3.15</v>
-      </c>
-      <c r="U101">
-        <v>2.4</v>
-      </c>
-      <c r="V101">
-        <v>1.5</v>
-      </c>
-      <c r="W101">
-        <v>1.08</v>
-      </c>
-      <c r="X101">
-        <v>1.04</v>
-      </c>
-      <c r="Y101">
-        <v>1.22</v>
-      </c>
-      <c r="Z101">
-        <v>4</v>
-      </c>
-      <c r="AA101">
-        <v>1.6</v>
-      </c>
-      <c r="AB101">
-        <v>2.19</v>
-      </c>
-      <c r="AC101">
-        <v>2.62</v>
-      </c>
-      <c r="AD101">
-        <v>1.45</v>
-      </c>
-      <c r="AE101">
-        <v>1.14</v>
-      </c>
-      <c r="AF101">
-        <v>1.72</v>
-      </c>
-      <c r="AG101">
-        <v>1.95</v>
-      </c>
-      <c r="AH101" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI101" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ101">
-        <v>1.1</v>
-      </c>
-      <c r="AK101">
-        <v>2.7</v>
       </c>
       <c r="AL101">
         <v>0</v>
@@ -16903,12 +16903,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Zemun</t>
+          <t>Partizan</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Radnički Niš</t>
+          <t>IMT Novi Beograd</t>
         </is>
       </c>
       <c r="G102">
@@ -16935,64 +16935,64 @@
         </is>
       </c>
       <c r="N102">
-        <v>2.46</v>
+        <v>1.43</v>
       </c>
       <c r="O102">
-        <v>3.14</v>
+        <v>4.15</v>
       </c>
       <c r="P102">
-        <v>2.59</v>
+        <v>6.28</v>
       </c>
       <c r="Q102">
-        <v>3.1</v>
+        <v>1.91</v>
       </c>
       <c r="R102">
-        <v>2.1</v>
+        <v>2.4</v>
       </c>
       <c r="S102">
-        <v>1.36</v>
+        <v>1.28</v>
       </c>
       <c r="T102">
-        <v>2.77</v>
+        <v>3.15</v>
       </c>
       <c r="U102">
-        <v>2.78</v>
+        <v>2.4</v>
       </c>
       <c r="V102">
-        <v>1.36</v>
+        <v>1.5</v>
       </c>
       <c r="W102">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="X102">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="Y102">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="Z102">
-        <v>3.28</v>
+        <v>4</v>
       </c>
       <c r="AA102">
-        <v>1.89</v>
+        <v>1.6</v>
       </c>
       <c r="AB102">
-        <v>1.81</v>
+        <v>2.19</v>
       </c>
       <c r="AC102">
-        <v>3.2</v>
+        <v>2.62</v>
       </c>
       <c r="AD102">
-        <v>1.26</v>
+        <v>1.45</v>
       </c>
       <c r="AE102">
-        <v>1.06</v>
+        <v>1.14</v>
       </c>
       <c r="AF102">
-        <v>1.68</v>
+        <v>1.72</v>
       </c>
       <c r="AG102">
-        <v>2.04</v>
+        <v>1.95</v>
       </c>
       <c r="AH102" t="inlineStr">
         <is>
@@ -17005,10 +17005,10 @@
         </is>
       </c>
       <c r="AJ102">
-        <v>1.26</v>
+        <v>1.1</v>
       </c>
       <c r="AK102">
-        <v>1.43</v>
+        <v>2.7</v>
       </c>
       <c r="AL102">
         <v>0</v>
@@ -20815,12 +20815,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Chaco For Ever</t>
+          <t>Club Atlético Güemes</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Deportivo Morón</t>
+          <t>Tristán Suárez</t>
         </is>
       </c>
       <c r="G126">
@@ -20847,64 +20847,64 @@
         </is>
       </c>
       <c r="N126">
-        <v>2.72</v>
+        <v>3.26</v>
       </c>
       <c r="O126">
-        <v>2.7</v>
+        <v>2.67</v>
       </c>
       <c r="P126">
-        <v>2.69</v>
+        <v>2.4</v>
       </c>
       <c r="Q126">
-        <v>3.6</v>
+        <v>3.87</v>
       </c>
       <c r="R126">
-        <v>1.77</v>
+        <v>1.62</v>
       </c>
       <c r="S126">
-        <v>1.64</v>
+        <v>1.67</v>
       </c>
       <c r="T126">
-        <v>2.2</v>
+        <v>2.05</v>
       </c>
       <c r="U126">
-        <v>3.9</v>
+        <v>4.33</v>
       </c>
       <c r="V126">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="W126">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="X126">
-        <v>1.09</v>
+        <v>1.14</v>
       </c>
       <c r="Y126">
-        <v>1.58</v>
+        <v>1.71</v>
       </c>
       <c r="Z126">
-        <v>2.2</v>
+        <v>1.98</v>
       </c>
       <c r="AA126">
-        <v>2.97</v>
+        <v>3.08</v>
       </c>
       <c r="AB126">
-        <v>1.35</v>
+        <v>1.28</v>
       </c>
       <c r="AC126">
-        <v>5.5</v>
+        <v>6.3</v>
       </c>
       <c r="AD126">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="AE126">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AF126">
-        <v>2.2</v>
+        <v>2.38</v>
       </c>
       <c r="AG126">
-        <v>1.55</v>
+        <v>1.51</v>
       </c>
       <c r="AH126" t="inlineStr">
         <is>
@@ -20917,10 +20917,10 @@
         </is>
       </c>
       <c r="AJ126">
-        <v>1.36</v>
+        <v>1.44</v>
       </c>
       <c r="AK126">
-        <v>1.35</v>
+        <v>1.32</v>
       </c>
       <c r="AL126">
         <v>0</v>
@@ -21141,12 +21141,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Club Atlético Güemes</t>
+          <t>Chaco For Ever</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Tristán Suárez</t>
+          <t>Deportivo Morón</t>
         </is>
       </c>
       <c r="G128">
@@ -21173,64 +21173,64 @@
         </is>
       </c>
       <c r="N128">
-        <v>3.26</v>
+        <v>2.72</v>
       </c>
       <c r="O128">
-        <v>2.67</v>
+        <v>2.7</v>
       </c>
       <c r="P128">
-        <v>2.4</v>
+        <v>2.69</v>
       </c>
       <c r="Q128">
-        <v>3.87</v>
+        <v>3.6</v>
       </c>
       <c r="R128">
-        <v>1.62</v>
+        <v>1.77</v>
       </c>
       <c r="S128">
-        <v>1.67</v>
+        <v>1.64</v>
       </c>
       <c r="T128">
-        <v>2.05</v>
+        <v>2.2</v>
       </c>
       <c r="U128">
-        <v>4.33</v>
+        <v>3.9</v>
       </c>
       <c r="V128">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="W128">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="X128">
-        <v>1.14</v>
+        <v>1.09</v>
       </c>
       <c r="Y128">
-        <v>1.71</v>
+        <v>1.58</v>
       </c>
       <c r="Z128">
-        <v>1.98</v>
+        <v>2.2</v>
       </c>
       <c r="AA128">
-        <v>3.08</v>
+        <v>2.97</v>
       </c>
       <c r="AB128">
-        <v>1.28</v>
+        <v>1.35</v>
       </c>
       <c r="AC128">
-        <v>6.3</v>
+        <v>5.5</v>
       </c>
       <c r="AD128">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="AE128">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="AF128">
-        <v>2.38</v>
+        <v>2.2</v>
       </c>
       <c r="AG128">
-        <v>1.51</v>
+        <v>1.55</v>
       </c>
       <c r="AH128" t="inlineStr">
         <is>
@@ -21243,10 +21243,10 @@
         </is>
       </c>
       <c r="AJ128">
-        <v>1.44</v>
+        <v>1.36</v>
       </c>
       <c r="AK128">
-        <v>1.32</v>
+        <v>1.35</v>
       </c>
       <c r="AL128">
         <v>0</v>

--- a/jogos_2026-08-02.xlsx
+++ b/jogos_2026-08-02.xlsx
@@ -1474,7 +1474,7 @@
         <v>3.13</v>
       </c>
       <c r="V7">
-        <v>1.34</v>
+        <v>1.32</v>
       </c>
       <c r="W7">
         <v>1.02</v>
@@ -1486,7 +1486,7 @@
         <v>1.3</v>
       </c>
       <c r="Z7">
-        <v>3.06</v>
+        <v>2.97</v>
       </c>
       <c r="AA7">
         <v>2.11</v>
@@ -1523,7 +1523,7 @@
         <v>1.96</v>
       </c>
       <c r="AK7">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AL7">
         <v>0</v>
@@ -2559,12 +2559,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Gimpo Citizen</t>
+          <t>Ansan Greeners</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Gyeongnam</t>
+          <t>Gimhae City</t>
         </is>
       </c>
       <c r="G14">
@@ -2591,64 +2591,64 @@
         </is>
       </c>
       <c r="N14">
-        <v>1.94</v>
+        <v>2.91</v>
       </c>
       <c r="O14">
-        <v>3.34</v>
+        <v>3.38</v>
       </c>
       <c r="P14">
-        <v>3.51</v>
+        <v>2.18</v>
       </c>
       <c r="Q14">
-        <v>2.48</v>
+        <v>3.28</v>
       </c>
       <c r="R14">
-        <v>2.03</v>
+        <v>2.05</v>
       </c>
       <c r="S14">
-        <v>1.4</v>
+        <v>1.34</v>
       </c>
       <c r="T14">
-        <v>2.75</v>
+        <v>3.09</v>
       </c>
       <c r="U14">
-        <v>3</v>
+        <v>2.66</v>
       </c>
       <c r="V14">
-        <v>1.33</v>
+        <v>1.39</v>
       </c>
       <c r="W14">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="X14">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="Y14">
-        <v>1.38</v>
+        <v>1.23</v>
       </c>
       <c r="Z14">
-        <v>2.93</v>
+        <v>3.42</v>
       </c>
       <c r="AA14">
-        <v>1.95</v>
+        <v>1.81</v>
       </c>
       <c r="AB14">
-        <v>1.75</v>
+        <v>1.88</v>
       </c>
       <c r="AC14">
-        <v>3.2</v>
+        <v>2.97</v>
       </c>
       <c r="AD14">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="AE14">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="AF14">
-        <v>1.93</v>
+        <v>1.67</v>
       </c>
       <c r="AG14">
-        <v>1.76</v>
+        <v>2.1</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2661,10 +2661,10 @@
         </is>
       </c>
       <c r="AJ14">
-        <v>1.25</v>
+        <v>1.57</v>
       </c>
       <c r="AK14">
-        <v>1.83</v>
+        <v>1.29</v>
       </c>
       <c r="AL14">
         <v>0</v>
@@ -2722,12 +2722,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Ansan Greeners</t>
+          <t>Jeonnam Dragons</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Gimhae City</t>
+          <t>Paju Citizen</t>
         </is>
       </c>
       <c r="G15">
@@ -2754,64 +2754,64 @@
         </is>
       </c>
       <c r="N15">
-        <v>2.91</v>
+        <v>1.97</v>
       </c>
       <c r="O15">
-        <v>3.38</v>
+        <v>3.32</v>
       </c>
       <c r="P15">
-        <v>2.18</v>
+        <v>3.45</v>
       </c>
       <c r="Q15">
-        <v>3.28</v>
+        <v>2.62</v>
       </c>
       <c r="R15">
-        <v>2.05</v>
+        <v>2.25</v>
       </c>
       <c r="S15">
-        <v>1.34</v>
+        <v>1.3</v>
       </c>
       <c r="T15">
-        <v>3.09</v>
+        <v>3.1</v>
       </c>
       <c r="U15">
-        <v>2.66</v>
+        <v>2.5</v>
       </c>
       <c r="V15">
-        <v>1.39</v>
+        <v>1.44</v>
       </c>
       <c r="W15">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="X15">
-        <v>1.05</v>
+        <v>1</v>
       </c>
       <c r="Y15">
-        <v>1.23</v>
+        <v>1.26</v>
       </c>
       <c r="Z15">
-        <v>3.42</v>
+        <v>3.71</v>
       </c>
       <c r="AA15">
-        <v>1.81</v>
+        <v>1.79</v>
       </c>
       <c r="AB15">
-        <v>1.88</v>
+        <v>1.9</v>
       </c>
       <c r="AC15">
-        <v>2.97</v>
+        <v>3.07</v>
       </c>
       <c r="AD15">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="AE15">
-        <v>1.08</v>
+        <v>1.13</v>
       </c>
       <c r="AF15">
-        <v>1.67</v>
+        <v>1.73</v>
       </c>
       <c r="AG15">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2824,10 +2824,10 @@
         </is>
       </c>
       <c r="AJ15">
-        <v>1.57</v>
+        <v>1.25</v>
       </c>
       <c r="AK15">
-        <v>1.29</v>
+        <v>1.58</v>
       </c>
       <c r="AL15">
         <v>0</v>
@@ -3048,12 +3048,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Jeonnam Dragons</t>
+          <t>Gimpo Citizen</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Paju Citizen</t>
+          <t>Gyeongnam</t>
         </is>
       </c>
       <c r="G17">
@@ -3080,64 +3080,64 @@
         </is>
       </c>
       <c r="N17">
-        <v>1.97</v>
+        <v>1.94</v>
       </c>
       <c r="O17">
-        <v>3.32</v>
+        <v>3.34</v>
       </c>
       <c r="P17">
-        <v>3.45</v>
+        <v>3.51</v>
       </c>
       <c r="Q17">
-        <v>2.62</v>
+        <v>2.48</v>
       </c>
       <c r="R17">
-        <v>2.25</v>
+        <v>2.03</v>
       </c>
       <c r="S17">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="T17">
-        <v>3.1</v>
+        <v>2.75</v>
       </c>
       <c r="U17">
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="V17">
-        <v>1.44</v>
+        <v>1.33</v>
       </c>
       <c r="W17">
-        <v>1.1</v>
+        <v>1.06</v>
       </c>
       <c r="X17">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="Y17">
-        <v>1.26</v>
+        <v>1.38</v>
       </c>
       <c r="Z17">
-        <v>3.71</v>
+        <v>2.93</v>
       </c>
       <c r="AA17">
-        <v>1.79</v>
+        <v>1.95</v>
       </c>
       <c r="AB17">
-        <v>1.9</v>
+        <v>1.75</v>
       </c>
       <c r="AC17">
-        <v>3.07</v>
+        <v>3.2</v>
       </c>
       <c r="AD17">
-        <v>1.36</v>
+        <v>1.27</v>
       </c>
       <c r="AE17">
-        <v>1.13</v>
+        <v>1.03</v>
       </c>
       <c r="AF17">
-        <v>1.73</v>
+        <v>1.93</v>
       </c>
       <c r="AG17">
-        <v>2</v>
+        <v>1.76</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3153,7 +3153,7 @@
         <v>1.25</v>
       </c>
       <c r="AK17">
-        <v>1.58</v>
+        <v>1.83</v>
       </c>
       <c r="AL17">
         <v>0</v>
@@ -4058,28 +4058,28 @@
         </is>
       </c>
       <c r="N23">
-        <v>2.48</v>
+        <v>2.7</v>
       </c>
       <c r="O23">
-        <v>3.76</v>
+        <v>3.61</v>
       </c>
       <c r="P23">
-        <v>2.48</v>
+        <v>2.03</v>
       </c>
       <c r="Q23">
-        <v>3.48</v>
+        <v>3.3</v>
       </c>
       <c r="R23">
-        <v>2.31</v>
+        <v>2.45</v>
       </c>
       <c r="S23">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="T23">
-        <v>3.5</v>
+        <v>3.8</v>
       </c>
       <c r="U23">
-        <v>2.1</v>
+        <v>2.18</v>
       </c>
       <c r="V23">
         <v>1.64</v>
@@ -4091,7 +4091,7 @@
         <v>1.02</v>
       </c>
       <c r="Y23">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="Z23">
         <v>4.8</v>
@@ -4103,10 +4103,10 @@
         <v>2.39</v>
       </c>
       <c r="AC23">
-        <v>2.2</v>
+        <v>2.17</v>
       </c>
       <c r="AD23">
-        <v>1.58</v>
+        <v>1.64</v>
       </c>
       <c r="AE23">
         <v>1.22</v>
@@ -4115,7 +4115,7 @@
         <v>1.44</v>
       </c>
       <c r="AG23">
-        <v>2.55</v>
+        <v>2.63</v>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
@@ -4128,10 +4128,10 @@
         </is>
       </c>
       <c r="AJ23">
-        <v>1.22</v>
+        <v>1.62</v>
       </c>
       <c r="AK23">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="AL23">
         <v>0</v>
@@ -4221,19 +4221,19 @@
         </is>
       </c>
       <c r="N24">
-        <v>3.05</v>
+        <v>2.31</v>
       </c>
       <c r="O24">
-        <v>3.19</v>
+        <v>3</v>
       </c>
       <c r="P24">
-        <v>2.33</v>
+        <v>2.65</v>
       </c>
       <c r="Q24">
-        <v>3.33</v>
+        <v>3</v>
       </c>
       <c r="R24">
-        <v>2.07</v>
+        <v>1.96</v>
       </c>
       <c r="S24">
         <v>1.46</v>
@@ -4242,10 +4242,10 @@
         <v>2.5</v>
       </c>
       <c r="U24">
-        <v>3.16</v>
+        <v>3.29</v>
       </c>
       <c r="V24">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="W24">
         <v>1.02</v>
@@ -4263,7 +4263,7 @@
         <v>2.21</v>
       </c>
       <c r="AB24">
-        <v>1.66</v>
+        <v>1.63</v>
       </c>
       <c r="AC24">
         <v>3.86</v>
@@ -4291,7 +4291,7 @@
         </is>
       </c>
       <c r="AJ24">
-        <v>1.44</v>
+        <v>1.27</v>
       </c>
       <c r="AK24">
         <v>1.48</v>
@@ -4710,34 +4710,34 @@
         </is>
       </c>
       <c r="N27">
-        <v>2.35</v>
+        <v>1.29</v>
       </c>
       <c r="O27">
-        <v>4.7</v>
+        <v>5.4</v>
       </c>
       <c r="P27">
-        <v>2.35</v>
+        <v>7.95</v>
       </c>
       <c r="Q27">
-        <v>1.76</v>
+        <v>1.71</v>
       </c>
       <c r="R27">
-        <v>2.47</v>
+        <v>2.63</v>
       </c>
       <c r="S27">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="T27">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="U27">
-        <v>2.1</v>
+        <v>2.16</v>
       </c>
       <c r="V27">
-        <v>1.65</v>
+        <v>1.6</v>
       </c>
       <c r="W27">
-        <v>1.15</v>
+        <v>1.13</v>
       </c>
       <c r="X27">
         <v>1.02</v>
@@ -4746,13 +4746,13 @@
         <v>1.12</v>
       </c>
       <c r="Z27">
-        <v>5.11</v>
+        <v>4.75</v>
       </c>
       <c r="AA27">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="AB27">
-        <v>2.35</v>
+        <v>2.38</v>
       </c>
       <c r="AC27">
         <v>2.21</v>
@@ -4764,10 +4764,10 @@
         <v>1.25</v>
       </c>
       <c r="AF27">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="AG27">
-        <v>2</v>
+        <v>1.92</v>
       </c>
       <c r="AH27" t="inlineStr">
         <is>
@@ -4780,10 +4780,10 @@
         </is>
       </c>
       <c r="AJ27">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="AK27">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="AL27">
         <v>0</v>
@@ -4873,16 +4873,16 @@
         </is>
       </c>
       <c r="N28">
-        <v>1.86</v>
+        <v>1.68</v>
       </c>
       <c r="O28">
+        <v>3.9</v>
+      </c>
+      <c r="P28">
         <v>3.8</v>
       </c>
-      <c r="P28">
-        <v>3.87</v>
-      </c>
       <c r="Q28">
-        <v>2.23</v>
+        <v>2.18</v>
       </c>
       <c r="R28">
         <v>2.38</v>
@@ -4891,28 +4891,28 @@
         <v>1.3</v>
       </c>
       <c r="T28">
-        <v>3.6</v>
+        <v>3.22</v>
       </c>
       <c r="U28">
-        <v>2.36</v>
+        <v>2.42</v>
       </c>
       <c r="V28">
-        <v>1.52</v>
+        <v>1.55</v>
       </c>
       <c r="W28">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="X28">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y28">
-        <v>1.16</v>
+        <v>1.2</v>
       </c>
       <c r="Z28">
-        <v>4.33</v>
+        <v>4.57</v>
       </c>
       <c r="AA28">
-        <v>1.63</v>
+        <v>1.66</v>
       </c>
       <c r="AB28">
         <v>2.15</v>
@@ -4921,16 +4921,16 @@
         <v>2.65</v>
       </c>
       <c r="AD28">
-        <v>1.44</v>
+        <v>1.51</v>
       </c>
       <c r="AE28">
-        <v>1.14</v>
+        <v>1.2</v>
       </c>
       <c r="AF28">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="AG28">
-        <v>2.16</v>
+        <v>2.19</v>
       </c>
       <c r="AH28" t="inlineStr">
         <is>
@@ -4943,10 +4943,10 @@
         </is>
       </c>
       <c r="AJ28">
-        <v>1.18</v>
+        <v>1.23</v>
       </c>
       <c r="AK28">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="AL28">
         <v>0</v>
@@ -5045,7 +5045,7 @@
         <v>1.83</v>
       </c>
       <c r="Q29">
-        <v>3.95</v>
+        <v>4.9</v>
       </c>
       <c r="R29">
         <v>2.1</v>
@@ -5057,13 +5057,13 @@
         <v>2.7</v>
       </c>
       <c r="U29">
-        <v>2.48</v>
+        <v>2.88</v>
       </c>
       <c r="V29">
-        <v>1.41</v>
+        <v>1.36</v>
       </c>
       <c r="W29">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="X29">
         <v>1.02</v>
@@ -5078,7 +5078,7 @@
         <v>1.79</v>
       </c>
       <c r="AB29">
-        <v>1.77</v>
+        <v>1.91</v>
       </c>
       <c r="AC29">
         <v>3.3</v>
@@ -5106,7 +5106,7 @@
         </is>
       </c>
       <c r="AJ29">
-        <v>1.91</v>
+        <v>1.73</v>
       </c>
       <c r="AK29">
         <v>1.18</v>
@@ -5199,7 +5199,7 @@
         </is>
       </c>
       <c r="N30">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="O30">
         <v>3.52</v>
@@ -5869,13 +5869,13 @@
         <v>1.44</v>
       </c>
       <c r="T34">
-        <v>2.54</v>
+        <v>2.7</v>
       </c>
       <c r="U34">
         <v>3.1</v>
       </c>
       <c r="V34">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="W34">
         <v>1.02</v>
@@ -5884,16 +5884,16 @@
         <v>1.02</v>
       </c>
       <c r="Y34">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="Z34">
-        <v>2.83</v>
+        <v>2.98</v>
       </c>
       <c r="AA34">
         <v>2.15</v>
       </c>
       <c r="AB34">
-        <v>1.7</v>
+        <v>1.66</v>
       </c>
       <c r="AC34">
         <v>3.74</v>
@@ -5921,10 +5921,10 @@
         </is>
       </c>
       <c r="AJ34">
-        <v>1.34</v>
+        <v>1.32</v>
       </c>
       <c r="AK34">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="AL34">
         <v>0</v>
@@ -6014,7 +6014,7 @@
         </is>
       </c>
       <c r="N35">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="O35">
         <v>3.6</v>
@@ -6023,55 +6023,55 @@
         <v>4.03</v>
       </c>
       <c r="Q35">
-        <v>2.2</v>
+        <v>2.29</v>
       </c>
       <c r="R35">
-        <v>2.21</v>
+        <v>2.31</v>
       </c>
       <c r="S35">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="T35">
-        <v>3.11</v>
+        <v>3.6</v>
       </c>
       <c r="U35">
-        <v>2.35</v>
+        <v>2.38</v>
       </c>
       <c r="V35">
-        <v>1.48</v>
+        <v>1.53</v>
       </c>
       <c r="W35">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="X35">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y35">
-        <v>1.19</v>
+        <v>1.14</v>
       </c>
       <c r="Z35">
-        <v>4</v>
+        <v>4.4</v>
       </c>
       <c r="AA35">
-        <v>1.63</v>
+        <v>1.59</v>
       </c>
       <c r="AB35">
-        <v>2.1</v>
+        <v>2.29</v>
       </c>
       <c r="AC35">
-        <v>2.7</v>
+        <v>2.38</v>
       </c>
       <c r="AD35">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="AE35">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="AF35">
         <v>1.56</v>
       </c>
       <c r="AG35">
-        <v>2.28</v>
+        <v>2.2</v>
       </c>
       <c r="AH35" t="inlineStr">
         <is>
@@ -6084,7 +6084,7 @@
         </is>
       </c>
       <c r="AJ35">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AK35">
         <v>1.95</v>
@@ -6666,19 +6666,19 @@
         </is>
       </c>
       <c r="N39">
-        <v>9.25</v>
+        <v>7.4</v>
       </c>
       <c r="O39">
-        <v>5.55</v>
+        <v>4.65</v>
       </c>
       <c r="P39">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="Q39">
-        <v>7.2</v>
+        <v>7.1</v>
       </c>
       <c r="R39">
-        <v>2.49</v>
+        <v>2.48</v>
       </c>
       <c r="S39">
         <v>1.33</v>
@@ -6690,7 +6690,7 @@
         <v>2.6</v>
       </c>
       <c r="V39">
-        <v>1.45</v>
+        <v>1.47</v>
       </c>
       <c r="W39">
         <v>1.09</v>
@@ -6702,7 +6702,7 @@
         <v>1.22</v>
       </c>
       <c r="Z39">
-        <v>3.84</v>
+        <v>3.82</v>
       </c>
       <c r="AA39">
         <v>1.83</v>
@@ -6711,7 +6711,7 @@
         <v>2.13</v>
       </c>
       <c r="AC39">
-        <v>2.82</v>
+        <v>2.86</v>
       </c>
       <c r="AD39">
         <v>1.4</v>
@@ -6723,7 +6723,7 @@
         <v>2.03</v>
       </c>
       <c r="AG39">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="AH39" t="inlineStr">
         <is>
@@ -6736,10 +6736,10 @@
         </is>
       </c>
       <c r="AJ39">
-        <v>1.14</v>
+        <v>3.2</v>
       </c>
       <c r="AK39">
-        <v>1.03</v>
+        <v>1.09</v>
       </c>
       <c r="AL39">
         <v>0</v>
@@ -6829,16 +6829,16 @@
         </is>
       </c>
       <c r="N40">
-        <v>2.41</v>
+        <v>2.17</v>
       </c>
       <c r="O40">
-        <v>3.48</v>
+        <v>3.47</v>
       </c>
       <c r="P40">
-        <v>2.71</v>
+        <v>2.83</v>
       </c>
       <c r="Q40">
-        <v>2.48</v>
+        <v>2.73</v>
       </c>
       <c r="R40">
         <v>2.2</v>
@@ -6850,43 +6850,43 @@
         <v>2.94</v>
       </c>
       <c r="U40">
-        <v>2.48</v>
+        <v>2.45</v>
       </c>
       <c r="V40">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="W40">
         <v>1.06</v>
       </c>
       <c r="X40">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="Y40">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="Z40">
-        <v>3.62</v>
+        <v>3.85</v>
       </c>
       <c r="AA40">
-        <v>1.7</v>
+        <v>1.79</v>
       </c>
       <c r="AB40">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="AC40">
-        <v>2.92</v>
+        <v>3</v>
       </c>
       <c r="AD40">
-        <v>1.39</v>
+        <v>1.36</v>
       </c>
       <c r="AE40">
-        <v>1.11</v>
+        <v>1.15</v>
       </c>
       <c r="AF40">
         <v>1.62</v>
       </c>
       <c r="AG40">
-        <v>2.2</v>
+        <v>2.17</v>
       </c>
       <c r="AH40" t="inlineStr">
         <is>
@@ -6899,10 +6899,10 @@
         </is>
       </c>
       <c r="AJ40">
-        <v>1.24</v>
+        <v>1.3</v>
       </c>
       <c r="AK40">
-        <v>1.6</v>
+        <v>1.67</v>
       </c>
       <c r="AL40">
         <v>0</v>
@@ -7001,10 +7001,10 @@
         <v>2.37</v>
       </c>
       <c r="Q41">
-        <v>4.2</v>
+        <v>3.45</v>
       </c>
       <c r="R41">
-        <v>2.1</v>
+        <v>2.04</v>
       </c>
       <c r="S41">
         <v>1.41</v>
@@ -7025,22 +7025,22 @@
         <v>1.02</v>
       </c>
       <c r="Y41">
-        <v>1.37</v>
+        <v>1.3</v>
       </c>
       <c r="Z41">
-        <v>2.8</v>
+        <v>3.2</v>
       </c>
       <c r="AA41">
         <v>2.15</v>
       </c>
       <c r="AB41">
-        <v>1.61</v>
+        <v>1.77</v>
       </c>
       <c r="AC41">
-        <v>3.85</v>
+        <v>3.3</v>
       </c>
       <c r="AD41">
-        <v>1.21</v>
+        <v>1.27</v>
       </c>
       <c r="AE41">
         <v>1.06</v>
@@ -7049,7 +7049,7 @@
         <v>1.82</v>
       </c>
       <c r="AG41">
-        <v>1.9</v>
+        <v>1.78</v>
       </c>
       <c r="AH41" t="inlineStr">
         <is>
@@ -7065,7 +7065,7 @@
         <v>1.27</v>
       </c>
       <c r="AK41">
-        <v>1.37</v>
+        <v>1.3</v>
       </c>
       <c r="AL41">
         <v>0</v>
@@ -7155,64 +7155,64 @@
         </is>
       </c>
       <c r="N42">
-        <v>2.45</v>
+        <v>2.16</v>
       </c>
       <c r="O42">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="P42">
-        <v>2.55</v>
+        <v>3</v>
       </c>
       <c r="Q42">
-        <v>3.02</v>
+        <v>2.6</v>
       </c>
       <c r="R42">
-        <v>2.09</v>
+        <v>2.13</v>
       </c>
       <c r="S42">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="T42">
-        <v>2.96</v>
+        <v>3.3</v>
       </c>
       <c r="U42">
         <v>2.5</v>
       </c>
       <c r="V42">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="W42">
-        <v>1.11</v>
+        <v>1.06</v>
       </c>
       <c r="X42">
         <v>1.02</v>
       </c>
       <c r="Y42">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="Z42">
-        <v>3.92</v>
+        <v>3.96</v>
       </c>
       <c r="AA42">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="AB42">
-        <v>2.03</v>
+        <v>2.04</v>
       </c>
       <c r="AC42">
-        <v>2.66</v>
+        <v>2.75</v>
       </c>
       <c r="AD42">
         <v>1.37</v>
       </c>
       <c r="AE42">
-        <v>1.1</v>
+        <v>1.16</v>
       </c>
       <c r="AF42">
-        <v>1.55</v>
+        <v>1.6</v>
       </c>
       <c r="AG42">
-        <v>2.27</v>
+        <v>2.25</v>
       </c>
       <c r="AH42" t="inlineStr">
         <is>
@@ -7225,10 +7225,10 @@
         </is>
       </c>
       <c r="AJ42">
-        <v>1.25</v>
+        <v>1.36</v>
       </c>
       <c r="AK42">
-        <v>1.44</v>
+        <v>1.65</v>
       </c>
       <c r="AL42">
         <v>0</v>
@@ -7490,16 +7490,16 @@
         <v>4.59</v>
       </c>
       <c r="Q44">
-        <v>2.24</v>
+        <v>2.17</v>
       </c>
       <c r="R44">
-        <v>2.07</v>
+        <v>2.13</v>
       </c>
       <c r="S44">
-        <v>1.44</v>
+        <v>1.41</v>
       </c>
       <c r="T44">
-        <v>2.56</v>
+        <v>2.66</v>
       </c>
       <c r="U44">
         <v>3.1</v>
@@ -7511,7 +7511,7 @@
         <v>1.03</v>
       </c>
       <c r="X44">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y44">
         <v>1.35</v>
@@ -7523,10 +7523,10 @@
         <v>2.21</v>
       </c>
       <c r="AB44">
-        <v>1.68</v>
+        <v>1.65</v>
       </c>
       <c r="AC44">
-        <v>3.82</v>
+        <v>3.88</v>
       </c>
       <c r="AD44">
         <v>1.18</v>
@@ -7535,10 +7535,10 @@
         <v>1.03</v>
       </c>
       <c r="AF44">
-        <v>2.06</v>
+        <v>2.1</v>
       </c>
       <c r="AG44">
-        <v>1.68</v>
+        <v>1.66</v>
       </c>
       <c r="AH44" t="inlineStr">
         <is>
@@ -7551,10 +7551,10 @@
         </is>
       </c>
       <c r="AJ44">
-        <v>1.28</v>
+        <v>1.24</v>
       </c>
       <c r="AK44">
-        <v>2.13</v>
+        <v>2.16</v>
       </c>
       <c r="AL44">
         <v>0</v>
@@ -8459,22 +8459,22 @@
         </is>
       </c>
       <c r="N50">
-        <v>2.14</v>
+        <v>1.87</v>
       </c>
       <c r="O50">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="P50">
-        <v>3.19</v>
+        <v>3.4</v>
       </c>
       <c r="Q50">
-        <v>2.27</v>
+        <v>2.33</v>
       </c>
       <c r="R50">
-        <v>2.22</v>
+        <v>2.35</v>
       </c>
       <c r="S50">
-        <v>1.29</v>
+        <v>1.32</v>
       </c>
       <c r="T50">
         <v>3.3</v>
@@ -8486,7 +8486,7 @@
         <v>1.5</v>
       </c>
       <c r="W50">
-        <v>1.11</v>
+        <v>1.09</v>
       </c>
       <c r="X50">
         <v>1</v>
@@ -8495,22 +8495,22 @@
         <v>1.22</v>
       </c>
       <c r="Z50">
-        <v>3.94</v>
+        <v>4.28</v>
       </c>
       <c r="AA50">
-        <v>1.66</v>
+        <v>1.71</v>
       </c>
       <c r="AB50">
-        <v>2.15</v>
+        <v>2.16</v>
       </c>
       <c r="AC50">
         <v>2.65</v>
       </c>
       <c r="AD50">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="AE50">
-        <v>1.17</v>
+        <v>1.13</v>
       </c>
       <c r="AF50">
         <v>1.55</v>
@@ -8529,10 +8529,10 @@
         </is>
       </c>
       <c r="AJ50">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="AK50">
-        <v>1.92</v>
+        <v>1.86</v>
       </c>
       <c r="AL50">
         <v>0</v>
@@ -8785,64 +8785,64 @@
         </is>
       </c>
       <c r="N52">
-        <v>1.77</v>
+        <v>2.07</v>
       </c>
       <c r="O52">
-        <v>3.98</v>
+        <v>3.75</v>
       </c>
       <c r="P52">
-        <v>3.98</v>
+        <v>2.8</v>
       </c>
       <c r="Q52">
+        <v>2.22</v>
+      </c>
+      <c r="R52">
         <v>2.38</v>
-      </c>
-      <c r="R52">
-        <v>2.36</v>
       </c>
       <c r="S52">
         <v>1.25</v>
       </c>
       <c r="T52">
-        <v>3.7</v>
+        <v>3.42</v>
       </c>
       <c r="U52">
-        <v>2.2</v>
+        <v>2.31</v>
       </c>
       <c r="V52">
-        <v>1.62</v>
+        <v>1.59</v>
       </c>
       <c r="W52">
-        <v>1.17</v>
+        <v>1.13</v>
       </c>
       <c r="X52">
         <v>1.02</v>
       </c>
       <c r="Y52">
-        <v>1.17</v>
+        <v>1.13</v>
       </c>
       <c r="Z52">
-        <v>4.55</v>
+        <v>4.75</v>
       </c>
       <c r="AA52">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="AB52">
-        <v>2.29</v>
+        <v>2.28</v>
       </c>
       <c r="AC52">
-        <v>2.41</v>
+        <v>2.38</v>
       </c>
       <c r="AD52">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="AE52">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="AF52">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="AG52">
-        <v>2.42</v>
+        <v>2.44</v>
       </c>
       <c r="AH52" t="inlineStr">
         <is>
@@ -8855,10 +8855,10 @@
         </is>
       </c>
       <c r="AJ52">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AK52">
-        <v>1.87</v>
+        <v>1.8</v>
       </c>
       <c r="AL52">
         <v>0</v>
@@ -8948,13 +8948,13 @@
         </is>
       </c>
       <c r="N53">
-        <v>3.48</v>
+        <v>3.59</v>
       </c>
       <c r="O53">
-        <v>3.52</v>
+        <v>3.62</v>
       </c>
       <c r="P53">
-        <v>2.04</v>
+        <v>1.96</v>
       </c>
       <c r="Q53">
         <v>4.16</v>
@@ -8963,49 +8963,49 @@
         <v>2.23</v>
       </c>
       <c r="S53">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="T53">
-        <v>3.3</v>
+        <v>3.15</v>
       </c>
       <c r="U53">
-        <v>2.47</v>
+        <v>2.45</v>
       </c>
       <c r="V53">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="W53">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="X53">
         <v>1.04</v>
       </c>
       <c r="Y53">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="Z53">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="AA53">
-        <v>1.81</v>
+        <v>1.7</v>
       </c>
       <c r="AB53">
-        <v>2.01</v>
+        <v>2.1</v>
       </c>
       <c r="AC53">
         <v>2.68</v>
       </c>
       <c r="AD53">
-        <v>1.37</v>
+        <v>1.44</v>
       </c>
       <c r="AE53">
-        <v>1.11</v>
+        <v>1.17</v>
       </c>
       <c r="AF53">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="AG53">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="AH53" t="inlineStr">
         <is>
@@ -10252,58 +10252,58 @@
         </is>
       </c>
       <c r="N61">
-        <v>2.72</v>
+        <v>2.25</v>
       </c>
       <c r="O61">
-        <v>3.32</v>
+        <v>3.2</v>
       </c>
       <c r="P61">
-        <v>2.48</v>
+        <v>3</v>
       </c>
       <c r="Q61">
-        <v>2.71</v>
+        <v>2.9</v>
       </c>
       <c r="R61">
-        <v>2.1</v>
+        <v>2.13</v>
       </c>
       <c r="S61">
         <v>1.36</v>
       </c>
       <c r="T61">
-        <v>2.88</v>
+        <v>2.89</v>
       </c>
       <c r="U61">
         <v>2.5</v>
       </c>
       <c r="V61">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="W61">
         <v>1.06</v>
       </c>
       <c r="X61">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="Y61">
         <v>1.25</v>
       </c>
       <c r="Z61">
-        <v>3.65</v>
+        <v>3.81</v>
       </c>
       <c r="AA61">
-        <v>1.81</v>
+        <v>1.79</v>
       </c>
       <c r="AB61">
-        <v>1.91</v>
+        <v>1.88</v>
       </c>
       <c r="AC61">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="AD61">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="AE61">
-        <v>1.09</v>
+        <v>1.14</v>
       </c>
       <c r="AF61">
         <v>1.67</v>
@@ -10322,10 +10322,10 @@
         </is>
       </c>
       <c r="AJ61">
-        <v>1.39</v>
+        <v>1.3</v>
       </c>
       <c r="AK61">
-        <v>1.53</v>
+        <v>1.56</v>
       </c>
       <c r="AL61">
         <v>0</v>
@@ -10415,13 +10415,13 @@
         </is>
       </c>
       <c r="N62">
-        <v>2.41</v>
+        <v>2.62</v>
       </c>
       <c r="O62">
-        <v>3.42</v>
+        <v>3.18</v>
       </c>
       <c r="P62">
-        <v>2.74</v>
+        <v>2.5</v>
       </c>
       <c r="Q62">
         <v>3.25</v>
@@ -10430,46 +10430,46 @@
         <v>2.1</v>
       </c>
       <c r="S62">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="T62">
-        <v>2.69</v>
+        <v>2.85</v>
       </c>
       <c r="U62">
-        <v>3.01</v>
+        <v>2.88</v>
       </c>
       <c r="V62">
         <v>1.36</v>
       </c>
       <c r="W62">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="X62">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y62">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="Z62">
-        <v>2.99</v>
+        <v>3.2</v>
       </c>
       <c r="AA62">
-        <v>1.98</v>
+        <v>2.06</v>
       </c>
       <c r="AB62">
-        <v>1.71</v>
+        <v>1.76</v>
       </c>
       <c r="AC62">
         <v>3.55</v>
       </c>
       <c r="AD62">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="AE62">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="AF62">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="AG62">
         <v>1.96</v>
@@ -10485,7 +10485,7 @@
         </is>
       </c>
       <c r="AJ62">
-        <v>1.32</v>
+        <v>1.43</v>
       </c>
       <c r="AK62">
         <v>1.45</v>
@@ -11556,13 +11556,13 @@
         </is>
       </c>
       <c r="N69">
-        <v>1.86</v>
+        <v>1.62</v>
       </c>
       <c r="O69">
-        <v>3.22</v>
+        <v>3.42</v>
       </c>
       <c r="P69">
-        <v>4.63</v>
+        <v>6.33</v>
       </c>
       <c r="Q69">
         <v>2.17</v>
@@ -11571,16 +11571,16 @@
         <v>2.07</v>
       </c>
       <c r="S69">
-        <v>1.45</v>
+        <v>1.36</v>
       </c>
       <c r="T69">
         <v>2.55</v>
       </c>
       <c r="U69">
-        <v>2.35</v>
+        <v>2.75</v>
       </c>
       <c r="V69">
-        <v>1.45</v>
+        <v>1.4</v>
       </c>
       <c r="W69">
         <v>1.06</v>
@@ -11592,25 +11592,25 @@
         <v>1.21</v>
       </c>
       <c r="Z69">
-        <v>3.85</v>
+        <v>3</v>
       </c>
       <c r="AA69">
-        <v>2.11</v>
+        <v>1.7</v>
       </c>
       <c r="AB69">
         <v>1.7</v>
       </c>
       <c r="AC69">
-        <v>2.75</v>
+        <v>3.5</v>
       </c>
       <c r="AD69">
-        <v>1.38</v>
+        <v>1.24</v>
       </c>
       <c r="AE69">
         <v>1.14</v>
       </c>
       <c r="AF69">
-        <v>2.1</v>
+        <v>1.62</v>
       </c>
       <c r="AG69">
         <v>1.67</v>
@@ -11626,10 +11626,10 @@
         </is>
       </c>
       <c r="AJ69">
-        <v>1.2</v>
+        <v>1.29</v>
       </c>
       <c r="AK69">
-        <v>1.85</v>
+        <v>2.19</v>
       </c>
       <c r="AL69">
         <v>0</v>
@@ -11882,13 +11882,13 @@
         </is>
       </c>
       <c r="N71">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="O71">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="P71">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="Q71">
         <v>3.12</v>
@@ -16740,12 +16740,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Zemun</t>
+          <t>Partizan</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Radnički Niš</t>
+          <t>IMT Novi Beograd</t>
         </is>
       </c>
       <c r="G101">
@@ -16772,64 +16772,64 @@
         </is>
       </c>
       <c r="N101">
-        <v>2.46</v>
+        <v>1.43</v>
       </c>
       <c r="O101">
-        <v>3.14</v>
+        <v>4.15</v>
       </c>
       <c r="P101">
-        <v>2.59</v>
+        <v>6.28</v>
       </c>
       <c r="Q101">
-        <v>3.1</v>
+        <v>1.91</v>
       </c>
       <c r="R101">
-        <v>2.1</v>
+        <v>2.4</v>
       </c>
       <c r="S101">
-        <v>1.36</v>
+        <v>1.28</v>
       </c>
       <c r="T101">
-        <v>2.77</v>
+        <v>3.15</v>
       </c>
       <c r="U101">
-        <v>2.78</v>
+        <v>2.4</v>
       </c>
       <c r="V101">
-        <v>1.36</v>
+        <v>1.5</v>
       </c>
       <c r="W101">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="X101">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="Y101">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="Z101">
-        <v>3.28</v>
+        <v>4</v>
       </c>
       <c r="AA101">
-        <v>1.89</v>
+        <v>1.6</v>
       </c>
       <c r="AB101">
-        <v>1.81</v>
+        <v>2.19</v>
       </c>
       <c r="AC101">
-        <v>3.2</v>
+        <v>2.62</v>
       </c>
       <c r="AD101">
-        <v>1.26</v>
+        <v>1.45</v>
       </c>
       <c r="AE101">
-        <v>1.06</v>
+        <v>1.14</v>
       </c>
       <c r="AF101">
-        <v>1.68</v>
+        <v>1.72</v>
       </c>
       <c r="AG101">
-        <v>2.04</v>
+        <v>1.95</v>
       </c>
       <c r="AH101" t="inlineStr">
         <is>
@@ -16842,10 +16842,10 @@
         </is>
       </c>
       <c r="AJ101">
-        <v>1.26</v>
+        <v>1.1</v>
       </c>
       <c r="AK101">
-        <v>1.43</v>
+        <v>2.7</v>
       </c>
       <c r="AL101">
         <v>0</v>
@@ -16903,12 +16903,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Partizan</t>
+          <t>Zemun</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>IMT Novi Beograd</t>
+          <t>Radnički Niš</t>
         </is>
       </c>
       <c r="G102">
@@ -16935,80 +16935,80 @@
         </is>
       </c>
       <c r="N102">
+        <v>2.46</v>
+      </c>
+      <c r="O102">
+        <v>3.14</v>
+      </c>
+      <c r="P102">
+        <v>2.59</v>
+      </c>
+      <c r="Q102">
+        <v>3.1</v>
+      </c>
+      <c r="R102">
+        <v>2.1</v>
+      </c>
+      <c r="S102">
+        <v>1.36</v>
+      </c>
+      <c r="T102">
+        <v>2.77</v>
+      </c>
+      <c r="U102">
+        <v>2.78</v>
+      </c>
+      <c r="V102">
+        <v>1.36</v>
+      </c>
+      <c r="W102">
+        <v>1.03</v>
+      </c>
+      <c r="X102">
+        <v>1.06</v>
+      </c>
+      <c r="Y102">
+        <v>1.25</v>
+      </c>
+      <c r="Z102">
+        <v>3.28</v>
+      </c>
+      <c r="AA102">
+        <v>1.89</v>
+      </c>
+      <c r="AB102">
+        <v>1.81</v>
+      </c>
+      <c r="AC102">
+        <v>3.2</v>
+      </c>
+      <c r="AD102">
+        <v>1.26</v>
+      </c>
+      <c r="AE102">
+        <v>1.06</v>
+      </c>
+      <c r="AF102">
+        <v>1.68</v>
+      </c>
+      <c r="AG102">
+        <v>2.04</v>
+      </c>
+      <c r="AH102" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI102" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ102">
+        <v>1.26</v>
+      </c>
+      <c r="AK102">
         <v>1.43</v>
-      </c>
-      <c r="O102">
-        <v>4.15</v>
-      </c>
-      <c r="P102">
-        <v>6.28</v>
-      </c>
-      <c r="Q102">
-        <v>1.91</v>
-      </c>
-      <c r="R102">
-        <v>2.4</v>
-      </c>
-      <c r="S102">
-        <v>1.28</v>
-      </c>
-      <c r="T102">
-        <v>3.15</v>
-      </c>
-      <c r="U102">
-        <v>2.4</v>
-      </c>
-      <c r="V102">
-        <v>1.5</v>
-      </c>
-      <c r="W102">
-        <v>1.08</v>
-      </c>
-      <c r="X102">
-        <v>1.04</v>
-      </c>
-      <c r="Y102">
-        <v>1.22</v>
-      </c>
-      <c r="Z102">
-        <v>4</v>
-      </c>
-      <c r="AA102">
-        <v>1.6</v>
-      </c>
-      <c r="AB102">
-        <v>2.19</v>
-      </c>
-      <c r="AC102">
-        <v>2.62</v>
-      </c>
-      <c r="AD102">
-        <v>1.45</v>
-      </c>
-      <c r="AE102">
-        <v>1.14</v>
-      </c>
-      <c r="AF102">
-        <v>1.72</v>
-      </c>
-      <c r="AG102">
-        <v>1.95</v>
-      </c>
-      <c r="AH102" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI102" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ102">
-        <v>1.1</v>
-      </c>
-      <c r="AK102">
-        <v>2.7</v>
       </c>
       <c r="AL102">
         <v>0</v>
@@ -19380,13 +19380,13 @@
         </is>
       </c>
       <c r="N117">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="O117">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="P117">
-        <v>0</v>
+        <v>5.79</v>
       </c>
       <c r="Q117">
         <v>1.95</v>
@@ -19410,25 +19410,25 @@
         <v>1.15</v>
       </c>
       <c r="X117">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y117">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="Z117">
-        <v>4.5</v>
+        <v>4.33</v>
       </c>
       <c r="AA117">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="AB117">
-        <v>2.14</v>
+        <v>2.25</v>
       </c>
       <c r="AC117">
         <v>2.5</v>
       </c>
       <c r="AD117">
-        <v>1.45</v>
+        <v>1.5</v>
       </c>
       <c r="AE117">
         <v>1.17</v>
@@ -19437,7 +19437,7 @@
         <v>1.7</v>
       </c>
       <c r="AG117">
-        <v>2.01</v>
+        <v>2</v>
       </c>
       <c r="AH117" t="inlineStr">
         <is>
@@ -19450,7 +19450,7 @@
         </is>
       </c>
       <c r="AJ117">
-        <v>1.07</v>
+        <v>1.2</v>
       </c>
       <c r="AK117">
         <v>2.5</v>
@@ -20978,12 +20978,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Deportivo Madryn</t>
+          <t>Chaco For Ever</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>All Boys</t>
+          <t>Deportivo Morón</t>
         </is>
       </c>
       <c r="G127">
@@ -21010,64 +21010,64 @@
         </is>
       </c>
       <c r="N127">
-        <v>2.12</v>
+        <v>2.72</v>
       </c>
       <c r="O127">
-        <v>2.71</v>
+        <v>2.7</v>
       </c>
       <c r="P127">
-        <v>3.87</v>
+        <v>2.69</v>
       </c>
       <c r="Q127">
-        <v>2.63</v>
+        <v>3.6</v>
       </c>
       <c r="R127">
-        <v>1.83</v>
+        <v>1.77</v>
       </c>
       <c r="S127">
-        <v>1.66</v>
+        <v>1.64</v>
       </c>
       <c r="T127">
-        <v>2.16</v>
+        <v>2.2</v>
       </c>
       <c r="U127">
-        <v>3.98</v>
+        <v>3.9</v>
       </c>
       <c r="V127">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="W127">
         <v>1.03</v>
       </c>
       <c r="X127">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="Y127">
-        <v>1.63</v>
+        <v>1.58</v>
       </c>
       <c r="Z127">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="AA127">
-        <v>3.4</v>
+        <v>2.97</v>
       </c>
       <c r="AB127">
         <v>1.35</v>
       </c>
       <c r="AC127">
-        <v>5.65</v>
+        <v>5.5</v>
       </c>
       <c r="AD127">
         <v>1.08</v>
       </c>
       <c r="AE127">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="AF127">
-        <v>2.16</v>
+        <v>2.2</v>
       </c>
       <c r="AG127">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="AH127" t="inlineStr">
         <is>
@@ -21080,10 +21080,10 @@
         </is>
       </c>
       <c r="AJ127">
-        <v>1.32</v>
+        <v>1.36</v>
       </c>
       <c r="AK127">
-        <v>1.7</v>
+        <v>1.35</v>
       </c>
       <c r="AL127">
         <v>0</v>
@@ -21141,12 +21141,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Chaco For Ever</t>
+          <t>Deportivo Madryn</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Deportivo Morón</t>
+          <t>All Boys</t>
         </is>
       </c>
       <c r="G128">
@@ -21173,64 +21173,64 @@
         </is>
       </c>
       <c r="N128">
-        <v>2.72</v>
+        <v>2.12</v>
       </c>
       <c r="O128">
-        <v>2.7</v>
+        <v>2.71</v>
       </c>
       <c r="P128">
-        <v>2.69</v>
+        <v>3.87</v>
       </c>
       <c r="Q128">
-        <v>3.6</v>
+        <v>2.63</v>
       </c>
       <c r="R128">
-        <v>1.77</v>
+        <v>1.83</v>
       </c>
       <c r="S128">
-        <v>1.64</v>
+        <v>1.66</v>
       </c>
       <c r="T128">
-        <v>2.2</v>
+        <v>2.16</v>
       </c>
       <c r="U128">
-        <v>3.9</v>
+        <v>3.98</v>
       </c>
       <c r="V128">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="W128">
         <v>1.03</v>
       </c>
       <c r="X128">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="Y128">
-        <v>1.58</v>
+        <v>1.63</v>
       </c>
       <c r="Z128">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="AA128">
-        <v>2.97</v>
+        <v>3.4</v>
       </c>
       <c r="AB128">
         <v>1.35</v>
       </c>
       <c r="AC128">
-        <v>5.5</v>
+        <v>5.65</v>
       </c>
       <c r="AD128">
         <v>1.08</v>
       </c>
       <c r="AE128">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AF128">
-        <v>2.2</v>
+        <v>2.16</v>
       </c>
       <c r="AG128">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="AH128" t="inlineStr">
         <is>
@@ -21243,10 +21243,10 @@
         </is>
       </c>
       <c r="AJ128">
-        <v>1.36</v>
+        <v>1.32</v>
       </c>
       <c r="AK128">
-        <v>1.35</v>
+        <v>1.7</v>
       </c>
       <c r="AL128">
         <v>0</v>

--- a/jogos_2026-08-02.xlsx
+++ b/jogos_2026-08-02.xlsx
@@ -635,13 +635,13 @@
         </is>
       </c>
       <c r="N2">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="O2">
-        <v>5.45</v>
+        <v>4.8</v>
       </c>
       <c r="P2">
-        <v>7</v>
+        <v>6.9</v>
       </c>
       <c r="Q2">
         <v>1.67</v>
@@ -650,13 +650,13 @@
         <v>2.7</v>
       </c>
       <c r="S2">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="T2">
         <v>3.6</v>
       </c>
       <c r="U2">
-        <v>2.29</v>
+        <v>2.2</v>
       </c>
       <c r="V2">
         <v>1.59</v>
@@ -665,7 +665,7 @@
         <v>1.14</v>
       </c>
       <c r="X2">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y2">
         <v>1.15</v>
@@ -680,19 +680,19 @@
         <v>2.51</v>
       </c>
       <c r="AC2">
-        <v>2.34</v>
+        <v>2.4</v>
       </c>
       <c r="AD2">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="AE2">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="AF2">
         <v>1.82</v>
       </c>
       <c r="AG2">
-        <v>1.91</v>
+        <v>1.95</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
@@ -705,10 +705,10 @@
         </is>
       </c>
       <c r="AJ2">
-        <v>1.15</v>
+        <v>1.1</v>
       </c>
       <c r="AK2">
-        <v>3.3</v>
+        <v>3.05</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -1954,34 +1954,34 @@
         <v>2.3</v>
       </c>
       <c r="S10">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="T10">
-        <v>3.28</v>
+        <v>3.6</v>
       </c>
       <c r="U10">
-        <v>2.4</v>
+        <v>2.33</v>
       </c>
       <c r="V10">
-        <v>1.53</v>
+        <v>1.51</v>
       </c>
       <c r="W10">
-        <v>1.08</v>
+        <v>1.12</v>
       </c>
       <c r="X10">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y10">
-        <v>1.18</v>
+        <v>1.14</v>
       </c>
       <c r="Z10">
-        <v>4.1</v>
+        <v>4.53</v>
       </c>
       <c r="AA10">
-        <v>1.66</v>
+        <v>1.62</v>
       </c>
       <c r="AB10">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="AC10">
         <v>2.52</v>
@@ -1990,7 +1990,7 @@
         <v>1.46</v>
       </c>
       <c r="AE10">
-        <v>1.15</v>
+        <v>1.19</v>
       </c>
       <c r="AF10">
         <v>1.67</v>
@@ -2009,10 +2009,10 @@
         </is>
       </c>
       <c r="AJ10">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="AK10">
-        <v>2</v>
+        <v>2.12</v>
       </c>
       <c r="AL10">
         <v>0</v>
@@ -2111,10 +2111,10 @@
         <v>3.81</v>
       </c>
       <c r="Q11">
-        <v>2.28</v>
+        <v>2.38</v>
       </c>
       <c r="R11">
-        <v>2.06</v>
+        <v>2.16</v>
       </c>
       <c r="S11">
         <v>1.35</v>
@@ -2126,13 +2126,13 @@
         <v>2.75</v>
       </c>
       <c r="V11">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="W11">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="X11">
-        <v>1</v>
+        <v>1.05</v>
       </c>
       <c r="Y11">
         <v>1.22</v>
@@ -2141,19 +2141,19 @@
         <v>3.4</v>
       </c>
       <c r="AA11">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="AB11">
-        <v>1.87</v>
+        <v>1.83</v>
       </c>
       <c r="AC11">
-        <v>2.94</v>
+        <v>3.05</v>
       </c>
       <c r="AD11">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="AE11">
-        <v>1.08</v>
+        <v>1.13</v>
       </c>
       <c r="AF11">
         <v>1.7</v>
@@ -2172,10 +2172,10 @@
         </is>
       </c>
       <c r="AJ11">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AK11">
-        <v>1.9</v>
+        <v>1.87</v>
       </c>
       <c r="AL11">
         <v>0</v>
@@ -2265,22 +2265,22 @@
         </is>
       </c>
       <c r="N12">
-        <v>3.11</v>
+        <v>2.88</v>
       </c>
       <c r="O12">
-        <v>2.98</v>
+        <v>2.88</v>
       </c>
       <c r="P12">
-        <v>2.44</v>
+        <v>2.4</v>
       </c>
       <c r="Q12">
         <v>3.6</v>
       </c>
       <c r="R12">
-        <v>1.93</v>
+        <v>1.87</v>
       </c>
       <c r="S12">
-        <v>1.48</v>
+        <v>1.45</v>
       </c>
       <c r="T12">
         <v>2.34</v>
@@ -2289,40 +2289,40 @@
         <v>3.4</v>
       </c>
       <c r="V12">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="W12">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="X12">
-        <v>1.05</v>
+        <v>1.1</v>
       </c>
       <c r="Y12">
-        <v>1.4</v>
+        <v>1.45</v>
       </c>
       <c r="Z12">
-        <v>2.57</v>
+        <v>2.79</v>
       </c>
       <c r="AA12">
         <v>2.38</v>
       </c>
       <c r="AB12">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="AC12">
-        <v>4.63</v>
+        <v>4.5</v>
       </c>
       <c r="AD12">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="AE12">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="AF12">
         <v>1.82</v>
       </c>
       <c r="AG12">
-        <v>1.78</v>
+        <v>1.73</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2335,10 +2335,10 @@
         </is>
       </c>
       <c r="AJ12">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AK12">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="AL12">
         <v>0</v>
@@ -2428,49 +2428,49 @@
         </is>
       </c>
       <c r="N13">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="O13">
-        <v>4.15</v>
+        <v>4</v>
       </c>
       <c r="P13">
-        <v>6.41</v>
+        <v>5.25</v>
       </c>
       <c r="Q13">
-        <v>1.95</v>
+        <v>2.05</v>
       </c>
       <c r="R13">
         <v>2.28</v>
       </c>
       <c r="S13">
-        <v>1.33</v>
+        <v>1.37</v>
       </c>
       <c r="T13">
-        <v>2.9</v>
+        <v>2.99</v>
       </c>
       <c r="U13">
-        <v>2.7</v>
+        <v>2.65</v>
       </c>
       <c r="V13">
         <v>1.4</v>
       </c>
       <c r="W13">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="X13">
-        <v>1.05</v>
+        <v>1</v>
       </c>
       <c r="Y13">
-        <v>1.22</v>
+        <v>1.28</v>
       </c>
       <c r="Z13">
-        <v>3.54</v>
+        <v>3.8</v>
       </c>
       <c r="AA13">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="AB13">
-        <v>1.87</v>
+        <v>1.8</v>
       </c>
       <c r="AC13">
         <v>2.89</v>
@@ -2482,10 +2482,10 @@
         <v>1.09</v>
       </c>
       <c r="AF13">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="AG13">
-        <v>1.8</v>
+        <v>1.77</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2498,10 +2498,10 @@
         </is>
       </c>
       <c r="AJ13">
-        <v>1.19</v>
+        <v>1.16</v>
       </c>
       <c r="AK13">
-        <v>2.7</v>
+        <v>2.6</v>
       </c>
       <c r="AL13">
         <v>0</v>
@@ -2559,12 +2559,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Ansan Greeners</t>
+          <t>Gimpo Citizen</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Gimhae City</t>
+          <t>Gyeongnam</t>
         </is>
       </c>
       <c r="G14">
@@ -2591,64 +2591,64 @@
         </is>
       </c>
       <c r="N14">
-        <v>2.91</v>
+        <v>1.85</v>
       </c>
       <c r="O14">
-        <v>3.38</v>
+        <v>2.98</v>
       </c>
       <c r="P14">
+        <v>3.28</v>
+      </c>
+      <c r="Q14">
+        <v>2.47</v>
+      </c>
+      <c r="R14">
         <v>2.18</v>
       </c>
-      <c r="Q14">
+      <c r="S14">
+        <v>1.4</v>
+      </c>
+      <c r="T14">
+        <v>2.5</v>
+      </c>
+      <c r="U14">
         <v>3.28</v>
       </c>
-      <c r="R14">
-        <v>2.05</v>
-      </c>
-      <c r="S14">
-        <v>1.34</v>
-      </c>
-      <c r="T14">
-        <v>3.09</v>
-      </c>
-      <c r="U14">
-        <v>2.66</v>
-      </c>
       <c r="V14">
-        <v>1.39</v>
+        <v>1.33</v>
       </c>
       <c r="W14">
-        <v>1.08</v>
+        <v>1.03</v>
       </c>
       <c r="X14">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="Y14">
-        <v>1.23</v>
+        <v>1.35</v>
       </c>
       <c r="Z14">
-        <v>3.42</v>
+        <v>2.74</v>
       </c>
       <c r="AA14">
-        <v>1.81</v>
+        <v>2.14</v>
       </c>
       <c r="AB14">
-        <v>1.88</v>
+        <v>1.73</v>
       </c>
       <c r="AC14">
-        <v>2.97</v>
+        <v>3.2</v>
       </c>
       <c r="AD14">
-        <v>1.3</v>
+        <v>1.22</v>
       </c>
       <c r="AE14">
-        <v>1.08</v>
+        <v>1.03</v>
       </c>
       <c r="AF14">
-        <v>1.67</v>
+        <v>1.85</v>
       </c>
       <c r="AG14">
-        <v>2.1</v>
+        <v>1.8</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2661,10 +2661,10 @@
         </is>
       </c>
       <c r="AJ14">
-        <v>1.57</v>
+        <v>1.22</v>
       </c>
       <c r="AK14">
-        <v>1.29</v>
+        <v>1.84</v>
       </c>
       <c r="AL14">
         <v>0</v>
@@ -2763,55 +2763,55 @@
         <v>3.45</v>
       </c>
       <c r="Q15">
-        <v>2.62</v>
+        <v>2.66</v>
       </c>
       <c r="R15">
         <v>2.25</v>
       </c>
       <c r="S15">
-        <v>1.3</v>
+        <v>1.34</v>
       </c>
       <c r="T15">
-        <v>3.1</v>
+        <v>3.12</v>
       </c>
       <c r="U15">
-        <v>2.5</v>
+        <v>2.71</v>
       </c>
       <c r="V15">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="W15">
-        <v>1.1</v>
+        <v>1.05</v>
       </c>
       <c r="X15">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y15">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="Z15">
-        <v>3.71</v>
+        <v>3.55</v>
       </c>
       <c r="AA15">
-        <v>1.79</v>
+        <v>1.9</v>
       </c>
       <c r="AB15">
         <v>1.9</v>
       </c>
       <c r="AC15">
-        <v>3.07</v>
+        <v>3</v>
       </c>
       <c r="AD15">
         <v>1.36</v>
       </c>
       <c r="AE15">
-        <v>1.13</v>
+        <v>1.08</v>
       </c>
       <c r="AF15">
-        <v>1.73</v>
+        <v>1.58</v>
       </c>
       <c r="AG15">
-        <v>2</v>
+        <v>2.07</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2824,10 +2824,10 @@
         </is>
       </c>
       <c r="AJ15">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AK15">
-        <v>1.58</v>
+        <v>1.63</v>
       </c>
       <c r="AL15">
         <v>0</v>
@@ -2917,10 +2917,10 @@
         </is>
       </c>
       <c r="N16">
-        <v>2.74</v>
+        <v>2.75</v>
       </c>
       <c r="O16">
-        <v>3.44</v>
+        <v>3.4</v>
       </c>
       <c r="P16">
         <v>2.25</v>
@@ -2929,25 +2929,25 @@
         <v>3.1</v>
       </c>
       <c r="R16">
-        <v>2.16</v>
+        <v>2.36</v>
       </c>
       <c r="S16">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="T16">
-        <v>3.25</v>
+        <v>3.15</v>
       </c>
       <c r="U16">
         <v>2.5</v>
       </c>
       <c r="V16">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="W16">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="X16">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y16">
         <v>1.16</v>
@@ -2956,19 +2956,19 @@
         <v>4.05</v>
       </c>
       <c r="AA16">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="AB16">
-        <v>2.07</v>
+        <v>2.1</v>
       </c>
       <c r="AC16">
-        <v>2.66</v>
+        <v>2.62</v>
       </c>
       <c r="AD16">
-        <v>1.37</v>
+        <v>1.44</v>
       </c>
       <c r="AE16">
-        <v>1.11</v>
+        <v>1.17</v>
       </c>
       <c r="AF16">
         <v>1.55</v>
@@ -2990,7 +2990,7 @@
         <v>1.23</v>
       </c>
       <c r="AK16">
-        <v>1.31</v>
+        <v>1.38</v>
       </c>
       <c r="AL16">
         <v>0</v>
@@ -3048,12 +3048,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Gimpo Citizen</t>
+          <t>Ansan Greeners</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Gyeongnam</t>
+          <t>Gimhae City</t>
         </is>
       </c>
       <c r="G17">
@@ -3080,64 +3080,64 @@
         </is>
       </c>
       <c r="N17">
-        <v>1.94</v>
+        <v>2.91</v>
       </c>
       <c r="O17">
-        <v>3.34</v>
+        <v>3.38</v>
       </c>
       <c r="P17">
-        <v>3.51</v>
+        <v>2.18</v>
       </c>
       <c r="Q17">
-        <v>2.48</v>
+        <v>3.4</v>
       </c>
       <c r="R17">
-        <v>2.03</v>
+        <v>2.2</v>
       </c>
       <c r="S17">
+        <v>1.36</v>
+      </c>
+      <c r="T17">
+        <v>2.88</v>
+      </c>
+      <c r="U17">
+        <v>2.66</v>
+      </c>
+      <c r="V17">
         <v>1.4</v>
       </c>
-      <c r="T17">
-        <v>2.75</v>
-      </c>
-      <c r="U17">
-        <v>3</v>
-      </c>
-      <c r="V17">
-        <v>1.33</v>
-      </c>
       <c r="W17">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="X17">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="Y17">
-        <v>1.38</v>
+        <v>1.26</v>
       </c>
       <c r="Z17">
-        <v>2.93</v>
+        <v>3.68</v>
       </c>
       <c r="AA17">
-        <v>1.95</v>
+        <v>1.82</v>
       </c>
       <c r="AB17">
-        <v>1.75</v>
+        <v>1.88</v>
       </c>
       <c r="AC17">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="AD17">
         <v>1.27</v>
       </c>
       <c r="AE17">
-        <v>1.03</v>
+        <v>1.13</v>
       </c>
       <c r="AF17">
-        <v>1.93</v>
+        <v>1.67</v>
       </c>
       <c r="AG17">
-        <v>1.76</v>
+        <v>2.1</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3150,10 +3150,10 @@
         </is>
       </c>
       <c r="AJ17">
-        <v>1.25</v>
+        <v>1.62</v>
       </c>
       <c r="AK17">
-        <v>1.83</v>
+        <v>1.36</v>
       </c>
       <c r="AL17">
         <v>0</v>
@@ -3741,10 +3741,10 @@
         <v>1.99</v>
       </c>
       <c r="Q21">
-        <v>3.65</v>
+        <v>3.3</v>
       </c>
       <c r="R21">
-        <v>2.45</v>
+        <v>2.58</v>
       </c>
       <c r="S21">
         <v>1.21</v>
@@ -3753,7 +3753,7 @@
         <v>3.68</v>
       </c>
       <c r="U21">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="V21">
         <v>1.63</v>
@@ -3768,28 +3768,28 @@
         <v>1.1</v>
       </c>
       <c r="Z21">
-        <v>5.35</v>
+        <v>5</v>
       </c>
       <c r="AA21">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="AB21">
-        <v>2.61</v>
+        <v>2.6</v>
       </c>
       <c r="AC21">
-        <v>2.08</v>
+        <v>2.23</v>
       </c>
       <c r="AD21">
         <v>1.64</v>
       </c>
       <c r="AE21">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="AF21">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="AG21">
-        <v>2.55</v>
+        <v>2.6</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
@@ -3802,10 +3802,10 @@
         </is>
       </c>
       <c r="AJ21">
-        <v>1.18</v>
+        <v>1.25</v>
       </c>
       <c r="AK21">
-        <v>1.29</v>
+        <v>1.23</v>
       </c>
       <c r="AL21">
         <v>0</v>
@@ -3904,10 +3904,10 @@
         <v>0</v>
       </c>
       <c r="Q22">
-        <v>2.63</v>
+        <v>2.7</v>
       </c>
       <c r="R22">
-        <v>2.09</v>
+        <v>2.07</v>
       </c>
       <c r="S22">
         <v>1.38</v>
@@ -3916,43 +3916,43 @@
         <v>2.77</v>
       </c>
       <c r="U22">
-        <v>2.86</v>
+        <v>2.69</v>
       </c>
       <c r="V22">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="W22">
         <v>1.06</v>
       </c>
       <c r="X22">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="Y22">
-        <v>1.23</v>
+        <v>1.28</v>
       </c>
       <c r="Z22">
-        <v>3.55</v>
+        <v>3.26</v>
       </c>
       <c r="AA22">
-        <v>1.77</v>
+        <v>1.94</v>
       </c>
       <c r="AB22">
-        <v>1.91</v>
+        <v>1.88</v>
       </c>
       <c r="AC22">
-        <v>2.88</v>
+        <v>3.51</v>
       </c>
       <c r="AD22">
-        <v>1.35</v>
+        <v>1.31</v>
       </c>
       <c r="AE22">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="AF22">
-        <v>1.64</v>
+        <v>1.71</v>
       </c>
       <c r="AG22">
-        <v>2.08</v>
+        <v>2</v>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
@@ -3965,10 +3965,10 @@
         </is>
       </c>
       <c r="AJ22">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="AK22">
-        <v>1.69</v>
+        <v>1.67</v>
       </c>
       <c r="AL22">
         <v>0</v>
@@ -4384,40 +4384,40 @@
         </is>
       </c>
       <c r="N25">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="O25">
-        <v>3.8</v>
+        <v>3.5</v>
       </c>
       <c r="P25">
-        <v>4.7</v>
+        <v>3.9</v>
       </c>
       <c r="Q25">
-        <v>2.27</v>
+        <v>2.3</v>
       </c>
       <c r="R25">
         <v>2.38</v>
       </c>
       <c r="S25">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="T25">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="U25">
         <v>2.47</v>
       </c>
       <c r="V25">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="W25">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="X25">
         <v>1.01</v>
       </c>
       <c r="Y25">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="Z25">
         <v>3.78</v>
@@ -4435,7 +4435,7 @@
         <v>1.39</v>
       </c>
       <c r="AE25">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="AF25">
         <v>1.7</v>
@@ -4454,10 +4454,10 @@
         </is>
       </c>
       <c r="AJ25">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="AK25">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="AL25">
         <v>0</v>
@@ -4547,40 +4547,40 @@
         </is>
       </c>
       <c r="N26">
-        <v>2.95</v>
+        <v>3</v>
       </c>
       <c r="O26">
-        <v>3.72</v>
+        <v>3.4</v>
       </c>
       <c r="P26">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="Q26">
         <v>3.3</v>
       </c>
       <c r="R26">
-        <v>2.21</v>
+        <v>2.22</v>
       </c>
       <c r="S26">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="T26">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="U26">
-        <v>2.3</v>
+        <v>2.23</v>
       </c>
       <c r="V26">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="W26">
-        <v>1.1</v>
+        <v>1.14</v>
       </c>
       <c r="X26">
         <v>1.02</v>
       </c>
       <c r="Y26">
-        <v>1.19</v>
+        <v>1.16</v>
       </c>
       <c r="Z26">
         <v>4.2</v>
@@ -4589,19 +4589,19 @@
         <v>1.61</v>
       </c>
       <c r="AB26">
-        <v>2.25</v>
+        <v>2.26</v>
       </c>
       <c r="AC26">
-        <v>2.56</v>
+        <v>2.39</v>
       </c>
       <c r="AD26">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="AE26">
         <v>1.16</v>
       </c>
       <c r="AF26">
-        <v>1.51</v>
+        <v>1.44</v>
       </c>
       <c r="AG26">
         <v>2.39</v>
@@ -4617,10 +4617,10 @@
         </is>
       </c>
       <c r="AJ26">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="AK26">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="AL26">
         <v>0</v>
@@ -5525,58 +5525,58 @@
         </is>
       </c>
       <c r="N32">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="O32">
-        <v>3.98</v>
+        <v>3.95</v>
       </c>
       <c r="P32">
-        <v>5.59</v>
+        <v>5.4</v>
       </c>
       <c r="Q32">
-        <v>1.98</v>
+        <v>2.1</v>
       </c>
       <c r="R32">
-        <v>2.16</v>
+        <v>2.22</v>
       </c>
       <c r="S32">
-        <v>1.33</v>
+        <v>1.37</v>
       </c>
       <c r="T32">
-        <v>2.77</v>
+        <v>2.9</v>
       </c>
       <c r="U32">
         <v>2.75</v>
       </c>
       <c r="V32">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="W32">
-        <v>1.1</v>
+        <v>1.07</v>
       </c>
       <c r="X32">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="Y32">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="Z32">
         <v>3.42</v>
       </c>
       <c r="AA32">
-        <v>1.82</v>
+        <v>1.88</v>
       </c>
       <c r="AB32">
-        <v>1.88</v>
+        <v>1.94</v>
       </c>
       <c r="AC32">
         <v>2.97</v>
       </c>
       <c r="AD32">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="AE32">
-        <v>1.08</v>
+        <v>1.12</v>
       </c>
       <c r="AF32">
         <v>1.86</v>
@@ -5595,7 +5595,7 @@
         </is>
       </c>
       <c r="AJ32">
-        <v>1.2</v>
+        <v>1.11</v>
       </c>
       <c r="AK32">
         <v>2.25</v>
@@ -6186,19 +6186,19 @@
         <v>2.98</v>
       </c>
       <c r="Q36">
-        <v>2.52</v>
+        <v>2.66</v>
       </c>
       <c r="R36">
-        <v>2.45</v>
+        <v>2.28</v>
       </c>
       <c r="S36">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="T36">
-        <v>3.6</v>
+        <v>3.36</v>
       </c>
       <c r="U36">
-        <v>2.27</v>
+        <v>2.29</v>
       </c>
       <c r="V36">
         <v>1.57</v>
@@ -6207,34 +6207,34 @@
         <v>1.11</v>
       </c>
       <c r="X36">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y36">
-        <v>1.15</v>
+        <v>1.13</v>
       </c>
       <c r="Z36">
-        <v>4.96</v>
+        <v>4.6</v>
       </c>
       <c r="AA36">
-        <v>1.54</v>
+        <v>1.66</v>
       </c>
       <c r="AB36">
         <v>2.15</v>
       </c>
       <c r="AC36">
-        <v>2.37</v>
+        <v>2.5</v>
       </c>
       <c r="AD36">
-        <v>1.55</v>
+        <v>1.49</v>
       </c>
       <c r="AE36">
-        <v>1.21</v>
+        <v>1.17</v>
       </c>
       <c r="AF36">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="AG36">
-        <v>2.35</v>
+        <v>2.4</v>
       </c>
       <c r="AH36" t="inlineStr">
         <is>
@@ -6247,10 +6247,10 @@
         </is>
       </c>
       <c r="AJ36">
-        <v>1.31</v>
+        <v>1.24</v>
       </c>
       <c r="AK36">
-        <v>1.63</v>
+        <v>1.65</v>
       </c>
       <c r="AL36">
         <v>0</v>
@@ -7318,43 +7318,43 @@
         </is>
       </c>
       <c r="N43">
-        <v>3.8</v>
+        <v>3.15</v>
       </c>
       <c r="O43">
-        <v>3.65</v>
+        <v>3.55</v>
       </c>
       <c r="P43">
-        <v>1.86</v>
+        <v>2.03</v>
       </c>
       <c r="Q43">
-        <v>3.75</v>
+        <v>3.6</v>
       </c>
       <c r="R43">
-        <v>2.22</v>
+        <v>2.23</v>
       </c>
       <c r="S43">
         <v>1.3</v>
       </c>
       <c r="T43">
-        <v>3.22</v>
+        <v>3.2</v>
       </c>
       <c r="U43">
-        <v>2.47</v>
+        <v>2.55</v>
       </c>
       <c r="V43">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="W43">
         <v>1.07</v>
       </c>
       <c r="X43">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y43">
-        <v>1.22</v>
+        <v>1.16</v>
       </c>
       <c r="Z43">
-        <v>3.95</v>
+        <v>4.2</v>
       </c>
       <c r="AA43">
         <v>1.66</v>
@@ -7363,16 +7363,16 @@
         <v>2.05</v>
       </c>
       <c r="AC43">
-        <v>2.61</v>
+        <v>2.7</v>
       </c>
       <c r="AD43">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="AE43">
         <v>1.12</v>
       </c>
       <c r="AF43">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="AG43">
         <v>2.28</v>
@@ -7388,10 +7388,10 @@
         </is>
       </c>
       <c r="AJ43">
+        <v>1.22</v>
+      </c>
+      <c r="AK43">
         <v>1.26</v>
-      </c>
-      <c r="AK43">
-        <v>1.31</v>
       </c>
       <c r="AL43">
         <v>0</v>
@@ -7644,13 +7644,13 @@
         </is>
       </c>
       <c r="N45">
-        <v>1.45</v>
+        <v>1.48</v>
       </c>
       <c r="O45">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="P45">
-        <v>5.75</v>
+        <v>5.25</v>
       </c>
       <c r="Q45">
         <v>1.98</v>
@@ -7665,7 +7665,7 @@
         <v>3.25</v>
       </c>
       <c r="U45">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="V45">
         <v>1.57</v>
@@ -7701,7 +7701,7 @@
         <v>1.66</v>
       </c>
       <c r="AG45">
-        <v>2.04</v>
+        <v>2.07</v>
       </c>
       <c r="AH45" t="inlineStr">
         <is>
@@ -7714,10 +7714,10 @@
         </is>
       </c>
       <c r="AJ45">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="AK45">
-        <v>2.08</v>
+        <v>2.39</v>
       </c>
       <c r="AL45">
         <v>0</v>
@@ -7807,25 +7807,25 @@
         </is>
       </c>
       <c r="N46">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="O46">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="P46">
-        <v>6.53</v>
+        <v>5.75</v>
       </c>
       <c r="Q46">
-        <v>1.83</v>
+        <v>2.02</v>
       </c>
       <c r="R46">
         <v>2.39</v>
       </c>
       <c r="S46">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="T46">
-        <v>3.75</v>
+        <v>3.34</v>
       </c>
       <c r="U46">
         <v>2.24</v>
@@ -7843,13 +7843,13 @@
         <v>1.11</v>
       </c>
       <c r="Z46">
-        <v>4.2</v>
+        <v>4.9</v>
       </c>
       <c r="AA46">
-        <v>1.53</v>
+        <v>1.47</v>
       </c>
       <c r="AB46">
-        <v>2.17</v>
+        <v>2.35</v>
       </c>
       <c r="AC46">
         <v>2.25</v>
@@ -7858,13 +7858,13 @@
         <v>1.57</v>
       </c>
       <c r="AE46">
-        <v>1.15</v>
+        <v>1.19</v>
       </c>
       <c r="AF46">
-        <v>1.64</v>
+        <v>1.66</v>
       </c>
       <c r="AG46">
-        <v>2.04</v>
+        <v>2.07</v>
       </c>
       <c r="AH46" t="inlineStr">
         <is>
@@ -7877,10 +7877,10 @@
         </is>
       </c>
       <c r="AJ46">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AK46">
-        <v>2.23</v>
+        <v>2.66</v>
       </c>
       <c r="AL46">
         <v>0</v>
@@ -7985,10 +7985,10 @@
         <v>2.28</v>
       </c>
       <c r="S47">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T47">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="U47">
         <v>2.33</v>
@@ -7997,10 +7997,10 @@
         <v>1.46</v>
       </c>
       <c r="W47">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X47">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y47">
         <v>1.19</v>
@@ -8142,55 +8142,55 @@
         <v>0</v>
       </c>
       <c r="Q48">
-        <v>0</v>
+        <v>6.15</v>
       </c>
       <c r="R48">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="S48">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="T48">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="U48">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="V48">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="W48">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="X48">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y48">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="Z48">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AA48">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AB48">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AC48">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AD48">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AE48">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AF48">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AG48">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="AH48" t="inlineStr">
         <is>
@@ -8203,10 +8203,10 @@
         </is>
       </c>
       <c r="AJ48">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AK48">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AL48">
         <v>0</v>
@@ -8305,55 +8305,55 @@
         <v>0</v>
       </c>
       <c r="Q49">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="R49">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S49">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T49">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="U49">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="V49">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="W49">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X49">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y49">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z49">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="AA49">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AB49">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC49">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AD49">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AE49">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AF49">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AG49">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AH49" t="inlineStr">
         <is>
@@ -8366,10 +8366,10 @@
         </is>
       </c>
       <c r="AJ49">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AK49">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AL49">
         <v>0</v>
@@ -9111,19 +9111,19 @@
         </is>
       </c>
       <c r="N54">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="O54">
         <v>4.65</v>
       </c>
       <c r="P54">
-        <v>7.28</v>
+        <v>5.7</v>
       </c>
       <c r="Q54">
-        <v>1.83</v>
+        <v>1.93</v>
       </c>
       <c r="R54">
-        <v>2.63</v>
+        <v>2.52</v>
       </c>
       <c r="S54">
         <v>1.25</v>
@@ -9132,10 +9132,10 @@
         <v>3.6</v>
       </c>
       <c r="U54">
-        <v>2.23</v>
+        <v>2.18</v>
       </c>
       <c r="V54">
-        <v>1.61</v>
+        <v>1.58</v>
       </c>
       <c r="W54">
         <v>1.13</v>
@@ -9147,28 +9147,28 @@
         <v>1.15</v>
       </c>
       <c r="Z54">
-        <v>4.5</v>
+        <v>4.85</v>
       </c>
       <c r="AA54">
         <v>1.53</v>
       </c>
       <c r="AB54">
-        <v>2.4</v>
+        <v>2.53</v>
       </c>
       <c r="AC54">
         <v>2.33</v>
       </c>
       <c r="AD54">
-        <v>1.5</v>
+        <v>1.59</v>
       </c>
       <c r="AE54">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="AF54">
         <v>1.63</v>
       </c>
       <c r="AG54">
-        <v>2.06</v>
+        <v>2.2</v>
       </c>
       <c r="AH54" t="inlineStr">
         <is>
@@ -9181,10 +9181,10 @@
         </is>
       </c>
       <c r="AJ54">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="AK54">
-        <v>2.62</v>
+        <v>2.75</v>
       </c>
       <c r="AL54">
         <v>0</v>
@@ -9600,64 +9600,64 @@
         </is>
       </c>
       <c r="N57">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="O57">
-        <v>4.25</v>
+        <v>3.78</v>
       </c>
       <c r="P57">
-        <v>5.73</v>
+        <v>4.2</v>
       </c>
       <c r="Q57">
-        <v>2.04</v>
+        <v>2.21</v>
       </c>
       <c r="R57">
-        <v>2.22</v>
+        <v>2.21</v>
       </c>
       <c r="S57">
-        <v>1.34</v>
+        <v>1.29</v>
       </c>
       <c r="T57">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="U57">
-        <v>2.38</v>
+        <v>2.39</v>
       </c>
       <c r="V57">
-        <v>1.48</v>
+        <v>1.45</v>
       </c>
       <c r="W57">
         <v>1.08</v>
       </c>
       <c r="X57">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y57">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="Z57">
-        <v>3.84</v>
+        <v>3.85</v>
       </c>
       <c r="AA57">
         <v>1.72</v>
       </c>
       <c r="AB57">
-        <v>2.07</v>
+        <v>2.04</v>
       </c>
       <c r="AC57">
-        <v>2.57</v>
+        <v>2.8</v>
       </c>
       <c r="AD57">
         <v>1.4</v>
       </c>
       <c r="AE57">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="AF57">
-        <v>1.74</v>
+        <v>1.67</v>
       </c>
       <c r="AG57">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="AH57" t="inlineStr">
         <is>
@@ -9670,10 +9670,10 @@
         </is>
       </c>
       <c r="AJ57">
-        <v>1.15</v>
+        <v>1.2</v>
       </c>
       <c r="AK57">
-        <v>2.04</v>
+        <v>2.1</v>
       </c>
       <c r="AL57">
         <v>0</v>
@@ -9772,10 +9772,10 @@
         <v>4.43</v>
       </c>
       <c r="Q58">
-        <v>2.01</v>
+        <v>2</v>
       </c>
       <c r="R58">
-        <v>2.44</v>
+        <v>2.36</v>
       </c>
       <c r="S58">
         <v>1.22</v>
@@ -9784,7 +9784,7 @@
         <v>4</v>
       </c>
       <c r="U58">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="V58">
         <v>1.68</v>
@@ -9796,31 +9796,31 @@
         <v>1.02</v>
       </c>
       <c r="Y58">
-        <v>1.14</v>
+        <v>1.08</v>
       </c>
       <c r="Z58">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="AA58">
         <v>1.44</v>
       </c>
       <c r="AB58">
-        <v>2.7</v>
+        <v>2.63</v>
       </c>
       <c r="AC58">
-        <v>2.01</v>
+        <v>2.12</v>
       </c>
       <c r="AD58">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="AE58">
-        <v>1.3</v>
+        <v>1.26</v>
       </c>
       <c r="AF58">
         <v>1.44</v>
       </c>
       <c r="AG58">
-        <v>2.5</v>
+        <v>2.56</v>
       </c>
       <c r="AH58" t="inlineStr">
         <is>
@@ -9833,10 +9833,10 @@
         </is>
       </c>
       <c r="AJ58">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AK58">
-        <v>2.2</v>
+        <v>2.13</v>
       </c>
       <c r="AL58">
         <v>0</v>
@@ -9926,25 +9926,25 @@
         </is>
       </c>
       <c r="N59">
-        <v>3.52</v>
+        <v>3.31</v>
       </c>
       <c r="O59">
-        <v>3.74</v>
+        <v>3.61</v>
       </c>
       <c r="P59">
-        <v>2.02</v>
+        <v>1.87</v>
       </c>
       <c r="Q59">
-        <v>3.74</v>
+        <v>3.7</v>
       </c>
       <c r="R59">
-        <v>2.23</v>
+        <v>2.3</v>
       </c>
       <c r="S59">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="T59">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="U59">
         <v>2.52</v>
@@ -9953,7 +9953,7 @@
         <v>1.49</v>
       </c>
       <c r="W59">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="X59">
         <v>1.02</v>
@@ -9962,28 +9962,28 @@
         <v>1.18</v>
       </c>
       <c r="Z59">
-        <v>4.33</v>
+        <v>4.44</v>
       </c>
       <c r="AA59">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="AB59">
-        <v>2.14</v>
+        <v>2.18</v>
       </c>
       <c r="AC59">
         <v>2.57</v>
       </c>
       <c r="AD59">
-        <v>1.44</v>
+        <v>1.41</v>
       </c>
       <c r="AE59">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="AF59">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="AG59">
-        <v>2.25</v>
+        <v>2.18</v>
       </c>
       <c r="AH59" t="inlineStr">
         <is>
@@ -9996,7 +9996,7 @@
         </is>
       </c>
       <c r="AJ59">
-        <v>1.19</v>
+        <v>1.85</v>
       </c>
       <c r="AK59">
         <v>1.22</v>
@@ -10098,55 +10098,55 @@
         <v>16.5</v>
       </c>
       <c r="Q60">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="R60">
-        <v>2.83</v>
+        <v>2.88</v>
       </c>
       <c r="S60">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="T60">
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="U60">
-        <v>1.99</v>
+        <v>1.8</v>
       </c>
       <c r="V60">
-        <v>1.71</v>
+        <v>1.91</v>
       </c>
       <c r="W60">
-        <v>1.18</v>
+        <v>1.25</v>
       </c>
       <c r="X60">
         <v>1.01</v>
       </c>
       <c r="Y60">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="Z60">
-        <v>5.65</v>
+        <v>5.3</v>
       </c>
       <c r="AA60">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AB60">
-        <v>2.83</v>
+        <v>2.75</v>
       </c>
       <c r="AC60">
-        <v>1.83</v>
+        <v>1.94</v>
       </c>
       <c r="AD60">
-        <v>1.98</v>
+        <v>1.7</v>
       </c>
       <c r="AE60">
-        <v>1.35</v>
+        <v>1.29</v>
       </c>
       <c r="AF60">
-        <v>2.24</v>
+        <v>2.08</v>
       </c>
       <c r="AG60">
-        <v>1.55</v>
+        <v>1.64</v>
       </c>
       <c r="AH60" t="inlineStr">
         <is>
@@ -10159,10 +10159,10 @@
         </is>
       </c>
       <c r="AJ60">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="AK60">
-        <v>7</v>
+        <v>5.1</v>
       </c>
       <c r="AL60">
         <v>0</v>
@@ -10578,28 +10578,28 @@
         </is>
       </c>
       <c r="N63">
-        <v>2.02</v>
+        <v>2.18</v>
       </c>
       <c r="O63">
-        <v>3.85</v>
+        <v>3.45</v>
       </c>
       <c r="P63">
-        <v>3.13</v>
+        <v>2.7</v>
       </c>
       <c r="Q63">
-        <v>2.7</v>
+        <v>2.8</v>
       </c>
       <c r="R63">
-        <v>2.34</v>
+        <v>2.5</v>
       </c>
       <c r="S63">
         <v>1.2</v>
       </c>
       <c r="T63">
-        <v>3.68</v>
+        <v>3.9</v>
       </c>
       <c r="U63">
-        <v>2.09</v>
+        <v>2.1</v>
       </c>
       <c r="V63">
         <v>1.67</v>
@@ -10617,25 +10617,25 @@
         <v>5.75</v>
       </c>
       <c r="AA63">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="AB63">
-        <v>2.56</v>
+        <v>2.63</v>
       </c>
       <c r="AC63">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="AD63">
-        <v>1.83</v>
+        <v>1.7</v>
       </c>
       <c r="AE63">
-        <v>1.28</v>
+        <v>1.24</v>
       </c>
       <c r="AF63">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="AG63">
-        <v>2.88</v>
+        <v>2.75</v>
       </c>
       <c r="AH63" t="inlineStr">
         <is>
@@ -10651,7 +10651,7 @@
         <v>1.25</v>
       </c>
       <c r="AK63">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="AL63">
         <v>0</v>
@@ -10741,28 +10741,28 @@
         </is>
       </c>
       <c r="N64">
-        <v>1.45</v>
+        <v>1.33</v>
       </c>
       <c r="O64">
-        <v>4.7</v>
+        <v>5.35</v>
       </c>
       <c r="P64">
-        <v>4.85</v>
+        <v>5.35</v>
       </c>
       <c r="Q64">
-        <v>1.78</v>
+        <v>1.76</v>
       </c>
       <c r="R64">
-        <v>2.82</v>
+        <v>2.6</v>
       </c>
       <c r="S64">
-        <v>1.14</v>
+        <v>1.18</v>
       </c>
       <c r="T64">
-        <v>5</v>
+        <v>4.5</v>
       </c>
       <c r="U64">
-        <v>1.8</v>
+        <v>1.86</v>
       </c>
       <c r="V64">
         <v>1.87</v>
@@ -10774,25 +10774,25 @@
         <v>1.01</v>
       </c>
       <c r="Y64">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="Z64">
-        <v>6.5</v>
+        <v>7.5</v>
       </c>
       <c r="AA64">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="AB64">
-        <v>3.4</v>
+        <v>3.08</v>
       </c>
       <c r="AC64">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="AD64">
         <v>1.89</v>
       </c>
       <c r="AE64">
-        <v>1.41</v>
+        <v>1.38</v>
       </c>
       <c r="AF64">
         <v>1.44</v>
@@ -10904,31 +10904,31 @@
         </is>
       </c>
       <c r="N65">
-        <v>1.39</v>
+        <v>1.33</v>
       </c>
       <c r="O65">
+        <v>4.55</v>
+      </c>
+      <c r="P65">
         <v>4.85</v>
       </c>
-      <c r="P65">
-        <v>5.55</v>
-      </c>
       <c r="Q65">
-        <v>1.87</v>
+        <v>1.79</v>
       </c>
       <c r="R65">
-        <v>2.51</v>
+        <v>2.75</v>
       </c>
       <c r="S65">
         <v>1.18</v>
       </c>
       <c r="T65">
-        <v>4.4</v>
+        <v>4.33</v>
       </c>
       <c r="U65">
         <v>1.99</v>
       </c>
       <c r="V65">
-        <v>1.77</v>
+        <v>1.83</v>
       </c>
       <c r="W65">
         <v>1.2</v>
@@ -10937,31 +10937,31 @@
         <v>1.01</v>
       </c>
       <c r="Y65">
-        <v>1.1</v>
+        <v>1.05</v>
       </c>
       <c r="Z65">
-        <v>6.6</v>
+        <v>6.45</v>
       </c>
       <c r="AA65">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="AB65">
-        <v>3.1</v>
+        <v>2.97</v>
       </c>
       <c r="AC65">
         <v>1.88</v>
       </c>
       <c r="AD65">
-        <v>1.8</v>
+        <v>1.91</v>
       </c>
       <c r="AE65">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AF65">
         <v>1.45</v>
       </c>
       <c r="AG65">
-        <v>2.25</v>
+        <v>2.44</v>
       </c>
       <c r="AH65" t="inlineStr">
         <is>
@@ -10974,10 +10974,10 @@
         </is>
       </c>
       <c r="AJ65">
-        <v>1.13</v>
+        <v>1.09</v>
       </c>
       <c r="AK65">
-        <v>2.83</v>
+        <v>2.7</v>
       </c>
       <c r="AL65">
         <v>0</v>
@@ -11067,16 +11067,16 @@
         </is>
       </c>
       <c r="N66">
-        <v>1.89</v>
+        <v>1.93</v>
       </c>
       <c r="O66">
-        <v>3.75</v>
+        <v>3.33</v>
       </c>
       <c r="P66">
-        <v>3.3</v>
+        <v>2.78</v>
       </c>
       <c r="Q66">
-        <v>2.5</v>
+        <v>2.42</v>
       </c>
       <c r="R66">
         <v>2.5</v>
@@ -11085,40 +11085,40 @@
         <v>1.25</v>
       </c>
       <c r="T66">
-        <v>3.75</v>
+        <v>3.6</v>
       </c>
       <c r="U66">
-        <v>2.29</v>
+        <v>2.25</v>
       </c>
       <c r="V66">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="W66">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="X66">
         <v>1.01</v>
       </c>
       <c r="Y66">
-        <v>1.17</v>
+        <v>1.13</v>
       </c>
       <c r="Z66">
-        <v>4.87</v>
+        <v>4.55</v>
       </c>
       <c r="AA66">
+        <v>1.45</v>
+      </c>
+      <c r="AB66">
+        <v>2.41</v>
+      </c>
+      <c r="AC66">
+        <v>2.37</v>
+      </c>
+      <c r="AD66">
         <v>1.57</v>
       </c>
-      <c r="AB66">
-        <v>2.35</v>
-      </c>
-      <c r="AC66">
-        <v>2.35</v>
-      </c>
-      <c r="AD66">
-        <v>1.52</v>
-      </c>
       <c r="AE66">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="AF66">
         <v>1.49</v>
@@ -11137,10 +11137,10 @@
         </is>
       </c>
       <c r="AJ66">
-        <v>1.2</v>
+        <v>1.27</v>
       </c>
       <c r="AK66">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="AL66">
         <v>0</v>
@@ -11230,19 +11230,19 @@
         </is>
       </c>
       <c r="N67">
-        <v>2.14</v>
+        <v>2.21</v>
       </c>
       <c r="O67">
-        <v>3.65</v>
+        <v>3.73</v>
       </c>
       <c r="P67">
-        <v>2.8</v>
+        <v>2.18</v>
       </c>
       <c r="Q67">
-        <v>2.66</v>
+        <v>2.9</v>
       </c>
       <c r="R67">
-        <v>2.42</v>
+        <v>2.5</v>
       </c>
       <c r="S67">
         <v>1.19</v>
@@ -11251,10 +11251,10 @@
         <v>3.84</v>
       </c>
       <c r="U67">
-        <v>2.02</v>
+        <v>2.06</v>
       </c>
       <c r="V67">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="W67">
         <v>1.19</v>
@@ -11266,28 +11266,28 @@
         <v>1.07</v>
       </c>
       <c r="Z67">
-        <v>6.47</v>
+        <v>5.8</v>
       </c>
       <c r="AA67">
-        <v>1.39</v>
+        <v>1.36</v>
       </c>
       <c r="AB67">
-        <v>2.91</v>
+        <v>3</v>
       </c>
       <c r="AC67">
-        <v>1.91</v>
+        <v>1.93</v>
       </c>
       <c r="AD67">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="AE67">
-        <v>1.35</v>
+        <v>1.32</v>
       </c>
       <c r="AF67">
         <v>1.33</v>
       </c>
       <c r="AG67">
-        <v>2.7</v>
+        <v>2.98</v>
       </c>
       <c r="AH67" t="inlineStr">
         <is>
@@ -11303,7 +11303,7 @@
         <v>1.2</v>
       </c>
       <c r="AK67">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="AL67">
         <v>0</v>
@@ -11393,19 +11393,19 @@
         </is>
       </c>
       <c r="N68">
-        <v>4.79</v>
+        <v>4.6</v>
       </c>
       <c r="O68">
-        <v>4.55</v>
+        <v>4.4</v>
       </c>
       <c r="P68">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="Q68">
-        <v>4.09</v>
+        <v>4.2</v>
       </c>
       <c r="R68">
-        <v>2.56</v>
+        <v>2.53</v>
       </c>
       <c r="S68">
         <v>1.17</v>
@@ -11414,43 +11414,43 @@
         <v>4.2</v>
       </c>
       <c r="U68">
-        <v>1.99</v>
+        <v>1.94</v>
       </c>
       <c r="V68">
-        <v>1.83</v>
+        <v>1.79</v>
       </c>
       <c r="W68">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="X68">
         <v>1.01</v>
       </c>
       <c r="Y68">
-        <v>1.05</v>
+        <v>1.1</v>
       </c>
       <c r="Z68">
-        <v>6.5</v>
+        <v>7</v>
       </c>
       <c r="AA68">
+        <v>1.31</v>
+      </c>
+      <c r="AB68">
+        <v>2.92</v>
+      </c>
+      <c r="AC68">
+        <v>1.98</v>
+      </c>
+      <c r="AD68">
+        <v>1.71</v>
+      </c>
+      <c r="AE68">
         <v>1.36</v>
       </c>
-      <c r="AB68">
-        <v>3.1</v>
-      </c>
-      <c r="AC68">
-        <v>1.87</v>
-      </c>
-      <c r="AD68">
-        <v>1.81</v>
-      </c>
-      <c r="AE68">
-        <v>1.28</v>
-      </c>
       <c r="AF68">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="AG68">
-        <v>2.73</v>
+        <v>2.7</v>
       </c>
       <c r="AH68" t="inlineStr">
         <is>
@@ -11463,7 +11463,7 @@
         </is>
       </c>
       <c r="AJ68">
-        <v>1.15</v>
+        <v>1.18</v>
       </c>
       <c r="AK68">
         <v>1.15</v>
@@ -14662,55 +14662,55 @@
         <v>0</v>
       </c>
       <c r="Q88">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="R88">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S88">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="T88">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="U88">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="V88">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="W88">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X88">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y88">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="Z88">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="AA88">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AB88">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AC88">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AD88">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AE88">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AF88">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AG88">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AH88" t="inlineStr">
         <is>
@@ -14723,10 +14723,10 @@
         </is>
       </c>
       <c r="AJ88">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK88">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AL88">
         <v>0</v>

--- a/jogos_2026-08-02.xlsx
+++ b/jogos_2026-08-02.xlsx
@@ -2559,12 +2559,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Gimpo Citizen</t>
+          <t>Ansan Greeners</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Gyeongnam</t>
+          <t>Gimhae City</t>
         </is>
       </c>
       <c r="G14">
@@ -2591,64 +2591,64 @@
         </is>
       </c>
       <c r="N14">
-        <v>1.85</v>
+        <v>2.91</v>
       </c>
       <c r="O14">
-        <v>2.98</v>
+        <v>3.38</v>
       </c>
       <c r="P14">
-        <v>3.28</v>
+        <v>2.18</v>
       </c>
       <c r="Q14">
-        <v>2.47</v>
+        <v>3.4</v>
       </c>
       <c r="R14">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="S14">
+        <v>1.36</v>
+      </c>
+      <c r="T14">
+        <v>2.88</v>
+      </c>
+      <c r="U14">
+        <v>2.66</v>
+      </c>
+      <c r="V14">
         <v>1.4</v>
       </c>
-      <c r="T14">
-        <v>2.5</v>
-      </c>
-      <c r="U14">
-        <v>3.28</v>
-      </c>
-      <c r="V14">
-        <v>1.33</v>
-      </c>
       <c r="W14">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="X14">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="Y14">
-        <v>1.35</v>
+        <v>1.26</v>
       </c>
       <c r="Z14">
-        <v>2.74</v>
+        <v>3.68</v>
       </c>
       <c r="AA14">
-        <v>2.14</v>
+        <v>1.82</v>
       </c>
       <c r="AB14">
-        <v>1.73</v>
+        <v>1.88</v>
       </c>
       <c r="AC14">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="AD14">
-        <v>1.22</v>
+        <v>1.27</v>
       </c>
       <c r="AE14">
-        <v>1.03</v>
+        <v>1.13</v>
       </c>
       <c r="AF14">
-        <v>1.85</v>
+        <v>1.67</v>
       </c>
       <c r="AG14">
-        <v>1.8</v>
+        <v>2.1</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2661,10 +2661,10 @@
         </is>
       </c>
       <c r="AJ14">
-        <v>1.22</v>
+        <v>1.62</v>
       </c>
       <c r="AK14">
-        <v>1.84</v>
+        <v>1.36</v>
       </c>
       <c r="AL14">
         <v>0</v>
@@ -2722,12 +2722,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Jeonnam Dragons</t>
+          <t>Gimpo Citizen</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Paju Citizen</t>
+          <t>Gyeongnam</t>
         </is>
       </c>
       <c r="G15">
@@ -2754,64 +2754,64 @@
         </is>
       </c>
       <c r="N15">
-        <v>1.97</v>
+        <v>1.85</v>
       </c>
       <c r="O15">
-        <v>3.32</v>
+        <v>2.98</v>
       </c>
       <c r="P15">
-        <v>3.45</v>
+        <v>3.28</v>
       </c>
       <c r="Q15">
-        <v>2.66</v>
+        <v>2.47</v>
       </c>
       <c r="R15">
-        <v>2.25</v>
+        <v>2.18</v>
       </c>
       <c r="S15">
-        <v>1.34</v>
+        <v>1.4</v>
       </c>
       <c r="T15">
-        <v>3.12</v>
+        <v>2.5</v>
       </c>
       <c r="U15">
-        <v>2.71</v>
+        <v>3.28</v>
       </c>
       <c r="V15">
-        <v>1.43</v>
+        <v>1.33</v>
       </c>
       <c r="W15">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="X15">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y15">
-        <v>1.28</v>
+        <v>1.35</v>
       </c>
       <c r="Z15">
-        <v>3.55</v>
+        <v>2.74</v>
       </c>
       <c r="AA15">
-        <v>1.9</v>
+        <v>2.14</v>
       </c>
       <c r="AB15">
-        <v>1.9</v>
+        <v>1.73</v>
       </c>
       <c r="AC15">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="AD15">
-        <v>1.36</v>
+        <v>1.22</v>
       </c>
       <c r="AE15">
-        <v>1.08</v>
+        <v>1.03</v>
       </c>
       <c r="AF15">
-        <v>1.58</v>
+        <v>1.85</v>
       </c>
       <c r="AG15">
-        <v>2.07</v>
+        <v>1.8</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2827,7 +2827,7 @@
         <v>1.22</v>
       </c>
       <c r="AK15">
-        <v>1.63</v>
+        <v>1.84</v>
       </c>
       <c r="AL15">
         <v>0</v>
@@ -3048,12 +3048,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Ansan Greeners</t>
+          <t>Jeonnam Dragons</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Gimhae City</t>
+          <t>Paju Citizen</t>
         </is>
       </c>
       <c r="G17">
@@ -3080,64 +3080,64 @@
         </is>
       </c>
       <c r="N17">
-        <v>2.91</v>
+        <v>1.97</v>
       </c>
       <c r="O17">
-        <v>3.38</v>
+        <v>3.32</v>
       </c>
       <c r="P17">
-        <v>2.18</v>
+        <v>3.45</v>
       </c>
       <c r="Q17">
-        <v>3.4</v>
+        <v>2.66</v>
       </c>
       <c r="R17">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="S17">
+        <v>1.34</v>
+      </c>
+      <c r="T17">
+        <v>3.12</v>
+      </c>
+      <c r="U17">
+        <v>2.71</v>
+      </c>
+      <c r="V17">
+        <v>1.43</v>
+      </c>
+      <c r="W17">
+        <v>1.05</v>
+      </c>
+      <c r="X17">
+        <v>1.01</v>
+      </c>
+      <c r="Y17">
+        <v>1.28</v>
+      </c>
+      <c r="Z17">
+        <v>3.55</v>
+      </c>
+      <c r="AA17">
+        <v>1.9</v>
+      </c>
+      <c r="AB17">
+        <v>1.9</v>
+      </c>
+      <c r="AC17">
+        <v>3</v>
+      </c>
+      <c r="AD17">
         <v>1.36</v>
       </c>
-      <c r="T17">
-        <v>2.88</v>
-      </c>
-      <c r="U17">
-        <v>2.66</v>
-      </c>
-      <c r="V17">
-        <v>1.4</v>
-      </c>
-      <c r="W17">
+      <c r="AE17">
         <v>1.08</v>
       </c>
-      <c r="X17">
-        <v>1.05</v>
-      </c>
-      <c r="Y17">
-        <v>1.26</v>
-      </c>
-      <c r="Z17">
-        <v>3.68</v>
-      </c>
-      <c r="AA17">
-        <v>1.82</v>
-      </c>
-      <c r="AB17">
-        <v>1.88</v>
-      </c>
-      <c r="AC17">
-        <v>3.1</v>
-      </c>
-      <c r="AD17">
-        <v>1.27</v>
-      </c>
-      <c r="AE17">
-        <v>1.13</v>
-      </c>
       <c r="AF17">
-        <v>1.67</v>
+        <v>1.58</v>
       </c>
       <c r="AG17">
-        <v>2.1</v>
+        <v>2.07</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3150,10 +3150,10 @@
         </is>
       </c>
       <c r="AJ17">
-        <v>1.62</v>
+        <v>1.22</v>
       </c>
       <c r="AK17">
-        <v>1.36</v>
+        <v>1.63</v>
       </c>
       <c r="AL17">
         <v>0</v>
@@ -7979,10 +7979,10 @@
         <v>2.79</v>
       </c>
       <c r="Q47">
-        <v>2.75</v>
+        <v>2.8</v>
       </c>
       <c r="R47">
-        <v>2.28</v>
+        <v>2.2</v>
       </c>
       <c r="S47">
         <v>1.3</v>
@@ -7991,10 +7991,10 @@
         <v>3.2</v>
       </c>
       <c r="U47">
-        <v>2.33</v>
+        <v>2.5</v>
       </c>
       <c r="V47">
-        <v>1.46</v>
+        <v>1.5</v>
       </c>
       <c r="W47">
         <v>1.11</v>
@@ -8003,16 +8003,16 @@
         <v>1.02</v>
       </c>
       <c r="Y47">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="Z47">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="AA47">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="AB47">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AC47">
         <v>2.6</v>
@@ -8024,10 +8024,10 @@
         <v>1.14</v>
       </c>
       <c r="AF47">
-        <v>1.55</v>
+        <v>1.6</v>
       </c>
       <c r="AG47">
-        <v>2.25</v>
+        <v>2.22</v>
       </c>
       <c r="AH47" t="inlineStr">
         <is>
@@ -8040,10 +8040,10 @@
         </is>
       </c>
       <c r="AJ47">
-        <v>1.32</v>
+        <v>1.22</v>
       </c>
       <c r="AK47">
-        <v>1.48</v>
+        <v>1.57</v>
       </c>
       <c r="AL47">
         <v>0</v>
@@ -8157,7 +8157,7 @@
         <v>2.25</v>
       </c>
       <c r="V48">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="W48">
         <v>1.14</v>
@@ -10872,12 +10872,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Odd</t>
+          <t>Egersund</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Åsane</t>
+          <t>Sandnes Ulf</t>
         </is>
       </c>
       <c r="G65">
@@ -10904,61 +10904,61 @@
         </is>
       </c>
       <c r="N65">
-        <v>1.33</v>
+        <v>1.93</v>
       </c>
       <c r="O65">
-        <v>4.55</v>
+        <v>3.33</v>
       </c>
       <c r="P65">
-        <v>4.85</v>
+        <v>2.78</v>
       </c>
       <c r="Q65">
-        <v>1.79</v>
+        <v>2.42</v>
       </c>
       <c r="R65">
-        <v>2.75</v>
+        <v>2.5</v>
       </c>
       <c r="S65">
-        <v>1.18</v>
+        <v>1.25</v>
       </c>
       <c r="T65">
-        <v>4.33</v>
+        <v>3.6</v>
       </c>
       <c r="U65">
-        <v>1.99</v>
+        <v>2.25</v>
       </c>
       <c r="V65">
-        <v>1.83</v>
+        <v>1.57</v>
       </c>
       <c r="W65">
-        <v>1.2</v>
+        <v>1.14</v>
       </c>
       <c r="X65">
         <v>1.01</v>
       </c>
       <c r="Y65">
-        <v>1.05</v>
+        <v>1.13</v>
       </c>
       <c r="Z65">
-        <v>6.45</v>
+        <v>4.55</v>
       </c>
       <c r="AA65">
-        <v>1.3</v>
+        <v>1.45</v>
       </c>
       <c r="AB65">
-        <v>2.97</v>
+        <v>2.41</v>
       </c>
       <c r="AC65">
-        <v>1.88</v>
+        <v>2.37</v>
       </c>
       <c r="AD65">
-        <v>1.91</v>
+        <v>1.57</v>
       </c>
       <c r="AE65">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="AF65">
-        <v>1.45</v>
+        <v>1.49</v>
       </c>
       <c r="AG65">
         <v>2.44</v>
@@ -10974,10 +10974,10 @@
         </is>
       </c>
       <c r="AJ65">
-        <v>1.09</v>
+        <v>1.27</v>
       </c>
       <c r="AK65">
-        <v>2.7</v>
+        <v>1.8</v>
       </c>
       <c r="AL65">
         <v>0</v>
@@ -11035,12 +11035,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Egersund</t>
+          <t>Raufoss</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Sandnes Ulf</t>
+          <t>Stabæk</t>
         </is>
       </c>
       <c r="G66">
@@ -11067,80 +11067,80 @@
         </is>
       </c>
       <c r="N66">
-        <v>1.93</v>
+        <v>4.6</v>
       </c>
       <c r="O66">
-        <v>3.33</v>
+        <v>4.4</v>
       </c>
       <c r="P66">
-        <v>2.78</v>
+        <v>1.54</v>
       </c>
       <c r="Q66">
-        <v>2.42</v>
+        <v>4.2</v>
       </c>
       <c r="R66">
-        <v>2.5</v>
+        <v>2.53</v>
       </c>
       <c r="S66">
-        <v>1.25</v>
+        <v>1.17</v>
       </c>
       <c r="T66">
-        <v>3.6</v>
+        <v>4.2</v>
       </c>
       <c r="U66">
-        <v>2.25</v>
+        <v>1.94</v>
       </c>
       <c r="V66">
-        <v>1.57</v>
+        <v>1.79</v>
       </c>
       <c r="W66">
-        <v>1.14</v>
+        <v>1.18</v>
       </c>
       <c r="X66">
         <v>1.01</v>
       </c>
       <c r="Y66">
-        <v>1.13</v>
+        <v>1.1</v>
       </c>
       <c r="Z66">
-        <v>4.55</v>
+        <v>7</v>
       </c>
       <c r="AA66">
-        <v>1.45</v>
+        <v>1.31</v>
       </c>
       <c r="AB66">
-        <v>2.41</v>
+        <v>2.92</v>
       </c>
       <c r="AC66">
-        <v>2.37</v>
+        <v>1.98</v>
       </c>
       <c r="AD66">
-        <v>1.57</v>
+        <v>1.71</v>
       </c>
       <c r="AE66">
+        <v>1.36</v>
+      </c>
+      <c r="AF66">
+        <v>1.42</v>
+      </c>
+      <c r="AG66">
+        <v>2.7</v>
+      </c>
+      <c r="AH66" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI66" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ66">
         <v>1.18</v>
       </c>
-      <c r="AF66">
-        <v>1.49</v>
-      </c>
-      <c r="AG66">
-        <v>2.44</v>
-      </c>
-      <c r="AH66" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI66" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ66">
-        <v>1.27</v>
-      </c>
       <c r="AK66">
-        <v>1.8</v>
+        <v>1.15</v>
       </c>
       <c r="AL66">
         <v>0</v>
@@ -11361,12 +11361,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Raufoss</t>
+          <t>Odd</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Stabæk</t>
+          <t>Åsane</t>
         </is>
       </c>
       <c r="G68">
@@ -11393,80 +11393,80 @@
         </is>
       </c>
       <c r="N68">
-        <v>4.6</v>
+        <v>1.33</v>
       </c>
       <c r="O68">
-        <v>4.4</v>
+        <v>4.55</v>
       </c>
       <c r="P68">
-        <v>1.54</v>
+        <v>4.85</v>
       </c>
       <c r="Q68">
-        <v>4.2</v>
+        <v>1.79</v>
       </c>
       <c r="R68">
-        <v>2.53</v>
+        <v>2.75</v>
       </c>
       <c r="S68">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="T68">
-        <v>4.2</v>
+        <v>4.33</v>
       </c>
       <c r="U68">
-        <v>1.94</v>
+        <v>1.99</v>
       </c>
       <c r="V68">
-        <v>1.79</v>
+        <v>1.83</v>
       </c>
       <c r="W68">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="X68">
         <v>1.01</v>
       </c>
       <c r="Y68">
-        <v>1.1</v>
+        <v>1.05</v>
       </c>
       <c r="Z68">
-        <v>7</v>
+        <v>6.45</v>
       </c>
       <c r="AA68">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="AB68">
-        <v>2.92</v>
+        <v>2.97</v>
       </c>
       <c r="AC68">
-        <v>1.98</v>
+        <v>1.88</v>
       </c>
       <c r="AD68">
-        <v>1.71</v>
+        <v>1.91</v>
       </c>
       <c r="AE68">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="AF68">
-        <v>1.42</v>
+        <v>1.45</v>
       </c>
       <c r="AG68">
+        <v>2.44</v>
+      </c>
+      <c r="AH68" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI68" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ68">
+        <v>1.09</v>
+      </c>
+      <c r="AK68">
         <v>2.7</v>
-      </c>
-      <c r="AH68" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI68" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ68">
-        <v>1.18</v>
-      </c>
-      <c r="AK68">
-        <v>1.15</v>
       </c>
       <c r="AL68">
         <v>0</v>
@@ -14680,7 +14680,7 @@
         <v>1.53</v>
       </c>
       <c r="W88">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="X88">
         <v>1.02</v>
@@ -16740,12 +16740,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Partizan</t>
+          <t>Zemun</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>IMT Novi Beograd</t>
+          <t>Radnički Niš</t>
         </is>
       </c>
       <c r="G101">
@@ -16772,80 +16772,80 @@
         </is>
       </c>
       <c r="N101">
+        <v>2.46</v>
+      </c>
+      <c r="O101">
+        <v>3.14</v>
+      </c>
+      <c r="P101">
+        <v>2.59</v>
+      </c>
+      <c r="Q101">
+        <v>3.1</v>
+      </c>
+      <c r="R101">
+        <v>2.1</v>
+      </c>
+      <c r="S101">
+        <v>1.36</v>
+      </c>
+      <c r="T101">
+        <v>2.77</v>
+      </c>
+      <c r="U101">
+        <v>2.78</v>
+      </c>
+      <c r="V101">
+        <v>1.36</v>
+      </c>
+      <c r="W101">
+        <v>1.03</v>
+      </c>
+      <c r="X101">
+        <v>1.06</v>
+      </c>
+      <c r="Y101">
+        <v>1.25</v>
+      </c>
+      <c r="Z101">
+        <v>3.28</v>
+      </c>
+      <c r="AA101">
+        <v>1.89</v>
+      </c>
+      <c r="AB101">
+        <v>1.81</v>
+      </c>
+      <c r="AC101">
+        <v>3.2</v>
+      </c>
+      <c r="AD101">
+        <v>1.26</v>
+      </c>
+      <c r="AE101">
+        <v>1.06</v>
+      </c>
+      <c r="AF101">
+        <v>1.68</v>
+      </c>
+      <c r="AG101">
+        <v>2.04</v>
+      </c>
+      <c r="AH101" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI101" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ101">
+        <v>1.26</v>
+      </c>
+      <c r="AK101">
         <v>1.43</v>
-      </c>
-      <c r="O101">
-        <v>4.15</v>
-      </c>
-      <c r="P101">
-        <v>6.28</v>
-      </c>
-      <c r="Q101">
-        <v>1.91</v>
-      </c>
-      <c r="R101">
-        <v>2.4</v>
-      </c>
-      <c r="S101">
-        <v>1.28</v>
-      </c>
-      <c r="T101">
-        <v>3.15</v>
-      </c>
-      <c r="U101">
-        <v>2.4</v>
-      </c>
-      <c r="V101">
-        <v>1.5</v>
-      </c>
-      <c r="W101">
-        <v>1.08</v>
-      </c>
-      <c r="X101">
-        <v>1.04</v>
-      </c>
-      <c r="Y101">
-        <v>1.22</v>
-      </c>
-      <c r="Z101">
-        <v>4</v>
-      </c>
-      <c r="AA101">
-        <v>1.6</v>
-      </c>
-      <c r="AB101">
-        <v>2.19</v>
-      </c>
-      <c r="AC101">
-        <v>2.62</v>
-      </c>
-      <c r="AD101">
-        <v>1.45</v>
-      </c>
-      <c r="AE101">
-        <v>1.14</v>
-      </c>
-      <c r="AF101">
-        <v>1.72</v>
-      </c>
-      <c r="AG101">
-        <v>1.95</v>
-      </c>
-      <c r="AH101" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI101" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ101">
-        <v>1.1</v>
-      </c>
-      <c r="AK101">
-        <v>2.7</v>
       </c>
       <c r="AL101">
         <v>0</v>
@@ -16903,12 +16903,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Zemun</t>
+          <t>Partizan</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Radnički Niš</t>
+          <t>IMT Novi Beograd</t>
         </is>
       </c>
       <c r="G102">
@@ -16935,64 +16935,64 @@
         </is>
       </c>
       <c r="N102">
-        <v>2.46</v>
+        <v>1.43</v>
       </c>
       <c r="O102">
-        <v>3.14</v>
+        <v>4.15</v>
       </c>
       <c r="P102">
-        <v>2.59</v>
+        <v>6.28</v>
       </c>
       <c r="Q102">
-        <v>3.1</v>
+        <v>1.91</v>
       </c>
       <c r="R102">
-        <v>2.1</v>
+        <v>2.4</v>
       </c>
       <c r="S102">
-        <v>1.36</v>
+        <v>1.28</v>
       </c>
       <c r="T102">
-        <v>2.77</v>
+        <v>3.15</v>
       </c>
       <c r="U102">
-        <v>2.78</v>
+        <v>2.4</v>
       </c>
       <c r="V102">
-        <v>1.36</v>
+        <v>1.5</v>
       </c>
       <c r="W102">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="X102">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="Y102">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="Z102">
-        <v>3.28</v>
+        <v>4</v>
       </c>
       <c r="AA102">
-        <v>1.89</v>
+        <v>1.6</v>
       </c>
       <c r="AB102">
-        <v>1.81</v>
+        <v>2.19</v>
       </c>
       <c r="AC102">
-        <v>3.2</v>
+        <v>2.62</v>
       </c>
       <c r="AD102">
-        <v>1.26</v>
+        <v>1.45</v>
       </c>
       <c r="AE102">
-        <v>1.06</v>
+        <v>1.14</v>
       </c>
       <c r="AF102">
-        <v>1.68</v>
+        <v>1.72</v>
       </c>
       <c r="AG102">
-        <v>2.04</v>
+        <v>1.95</v>
       </c>
       <c r="AH102" t="inlineStr">
         <is>
@@ -17005,10 +17005,10 @@
         </is>
       </c>
       <c r="AJ102">
-        <v>1.26</v>
+        <v>1.1</v>
       </c>
       <c r="AK102">
-        <v>1.43</v>
+        <v>2.7</v>
       </c>
       <c r="AL102">
         <v>0</v>

--- a/jogos_2026-08-02.xlsx
+++ b/jogos_2026-08-02.xlsx
@@ -2233,12 +2233,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Jeju United</t>
+          <t>Daejeon Citizen</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Incheon United</t>
+          <t>Gwangju</t>
         </is>
       </c>
       <c r="G12">
@@ -2265,64 +2265,64 @@
         </is>
       </c>
       <c r="N12">
-        <v>2.88</v>
+        <v>1.48</v>
       </c>
       <c r="O12">
-        <v>2.88</v>
+        <v>4</v>
       </c>
       <c r="P12">
-        <v>2.4</v>
+        <v>5.25</v>
       </c>
       <c r="Q12">
-        <v>3.6</v>
+        <v>2.05</v>
       </c>
       <c r="R12">
-        <v>1.87</v>
+        <v>2.28</v>
       </c>
       <c r="S12">
-        <v>1.45</v>
+        <v>1.37</v>
       </c>
       <c r="T12">
-        <v>2.34</v>
+        <v>2.99</v>
       </c>
       <c r="U12">
-        <v>3.4</v>
+        <v>2.65</v>
       </c>
       <c r="V12">
-        <v>1.29</v>
+        <v>1.4</v>
       </c>
       <c r="W12">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="X12">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="Y12">
-        <v>1.45</v>
+        <v>1.28</v>
       </c>
       <c r="Z12">
-        <v>2.79</v>
+        <v>3.8</v>
       </c>
       <c r="AA12">
-        <v>2.38</v>
+        <v>1.84</v>
       </c>
       <c r="AB12">
-        <v>1.57</v>
+        <v>1.8</v>
       </c>
       <c r="AC12">
-        <v>4.5</v>
+        <v>2.89</v>
       </c>
       <c r="AD12">
-        <v>1.2</v>
+        <v>1.32</v>
       </c>
       <c r="AE12">
-        <v>1.01</v>
+        <v>1.09</v>
       </c>
       <c r="AF12">
-        <v>1.82</v>
+        <v>1.91</v>
       </c>
       <c r="AG12">
-        <v>1.73</v>
+        <v>1.77</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2335,10 +2335,10 @@
         </is>
       </c>
       <c r="AJ12">
-        <v>1.3</v>
+        <v>1.16</v>
       </c>
       <c r="AK12">
-        <v>1.38</v>
+        <v>2.6</v>
       </c>
       <c r="AL12">
         <v>0</v>
@@ -2396,12 +2396,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Daejeon Citizen</t>
+          <t>Jeju United</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Gwangju</t>
+          <t>Incheon United</t>
         </is>
       </c>
       <c r="G13">
@@ -2428,64 +2428,64 @@
         </is>
       </c>
       <c r="N13">
-        <v>1.48</v>
+        <v>2.88</v>
       </c>
       <c r="O13">
-        <v>4</v>
+        <v>2.88</v>
       </c>
       <c r="P13">
-        <v>5.25</v>
+        <v>2.4</v>
       </c>
       <c r="Q13">
-        <v>2.05</v>
+        <v>3.6</v>
       </c>
       <c r="R13">
-        <v>2.28</v>
+        <v>1.87</v>
       </c>
       <c r="S13">
-        <v>1.37</v>
+        <v>1.45</v>
       </c>
       <c r="T13">
-        <v>2.99</v>
+        <v>2.34</v>
       </c>
       <c r="U13">
-        <v>2.65</v>
+        <v>3.4</v>
       </c>
       <c r="V13">
-        <v>1.4</v>
+        <v>1.29</v>
       </c>
       <c r="W13">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="X13">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="Y13">
-        <v>1.28</v>
+        <v>1.45</v>
       </c>
       <c r="Z13">
-        <v>3.8</v>
+        <v>2.79</v>
       </c>
       <c r="AA13">
-        <v>1.84</v>
+        <v>2.38</v>
       </c>
       <c r="AB13">
-        <v>1.8</v>
+        <v>1.57</v>
       </c>
       <c r="AC13">
-        <v>2.89</v>
+        <v>4.5</v>
       </c>
       <c r="AD13">
-        <v>1.32</v>
+        <v>1.2</v>
       </c>
       <c r="AE13">
-        <v>1.09</v>
+        <v>1.01</v>
       </c>
       <c r="AF13">
-        <v>1.91</v>
+        <v>1.82</v>
       </c>
       <c r="AG13">
-        <v>1.77</v>
+        <v>1.73</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2498,10 +2498,10 @@
         </is>
       </c>
       <c r="AJ13">
-        <v>1.16</v>
+        <v>1.3</v>
       </c>
       <c r="AK13">
-        <v>2.6</v>
+        <v>1.38</v>
       </c>
       <c r="AL13">
         <v>0</v>
@@ -2559,12 +2559,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Ansan Greeners</t>
+          <t>Busan I'Park</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Gimhae City</t>
+          <t>Seoul E-Land</t>
         </is>
       </c>
       <c r="G14">
@@ -2591,64 +2591,64 @@
         </is>
       </c>
       <c r="N14">
-        <v>2.91</v>
+        <v>2.75</v>
       </c>
       <c r="O14">
-        <v>3.38</v>
+        <v>3.4</v>
       </c>
       <c r="P14">
-        <v>2.18</v>
+        <v>2.25</v>
       </c>
       <c r="Q14">
-        <v>3.4</v>
+        <v>3.1</v>
       </c>
       <c r="R14">
-        <v>2.2</v>
+        <v>2.36</v>
       </c>
       <c r="S14">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="T14">
-        <v>2.88</v>
+        <v>3.15</v>
       </c>
       <c r="U14">
-        <v>2.66</v>
+        <v>2.5</v>
       </c>
       <c r="V14">
-        <v>1.4</v>
+        <v>1.45</v>
       </c>
       <c r="W14">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="X14">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="Y14">
-        <v>1.26</v>
+        <v>1.16</v>
       </c>
       <c r="Z14">
-        <v>3.68</v>
+        <v>4.05</v>
       </c>
       <c r="AA14">
-        <v>1.82</v>
+        <v>1.7</v>
       </c>
       <c r="AB14">
-        <v>1.88</v>
+        <v>2.1</v>
       </c>
       <c r="AC14">
-        <v>3.1</v>
+        <v>2.62</v>
       </c>
       <c r="AD14">
-        <v>1.27</v>
+        <v>1.44</v>
       </c>
       <c r="AE14">
-        <v>1.13</v>
+        <v>1.17</v>
       </c>
       <c r="AF14">
-        <v>1.67</v>
+        <v>1.55</v>
       </c>
       <c r="AG14">
-        <v>2.1</v>
+        <v>2.27</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2661,10 +2661,10 @@
         </is>
       </c>
       <c r="AJ14">
-        <v>1.62</v>
+        <v>1.23</v>
       </c>
       <c r="AK14">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="AL14">
         <v>0</v>
@@ -2885,12 +2885,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Busan I'Park</t>
+          <t>Jeonnam Dragons</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Seoul E-Land</t>
+          <t>Paju Citizen</t>
         </is>
       </c>
       <c r="G16">
@@ -2917,64 +2917,64 @@
         </is>
       </c>
       <c r="N16">
-        <v>2.75</v>
+        <v>1.97</v>
       </c>
       <c r="O16">
-        <v>3.4</v>
+        <v>3.32</v>
       </c>
       <c r="P16">
+        <v>3.45</v>
+      </c>
+      <c r="Q16">
+        <v>2.66</v>
+      </c>
+      <c r="R16">
         <v>2.25</v>
       </c>
-      <c r="Q16">
-        <v>3.1</v>
-      </c>
-      <c r="R16">
-        <v>2.36</v>
-      </c>
       <c r="S16">
-        <v>1.3</v>
+        <v>1.34</v>
       </c>
       <c r="T16">
-        <v>3.15</v>
+        <v>3.12</v>
       </c>
       <c r="U16">
-        <v>2.5</v>
+        <v>2.71</v>
       </c>
       <c r="V16">
-        <v>1.45</v>
+        <v>1.43</v>
       </c>
       <c r="W16">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="X16">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y16">
-        <v>1.16</v>
+        <v>1.28</v>
       </c>
       <c r="Z16">
-        <v>4.05</v>
+        <v>3.55</v>
       </c>
       <c r="AA16">
-        <v>1.7</v>
+        <v>1.9</v>
       </c>
       <c r="AB16">
-        <v>2.1</v>
+        <v>1.9</v>
       </c>
       <c r="AC16">
-        <v>2.62</v>
+        <v>3</v>
       </c>
       <c r="AD16">
-        <v>1.44</v>
+        <v>1.36</v>
       </c>
       <c r="AE16">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="AF16">
-        <v>1.55</v>
+        <v>1.58</v>
       </c>
       <c r="AG16">
-        <v>2.27</v>
+        <v>2.07</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -2987,10 +2987,10 @@
         </is>
       </c>
       <c r="AJ16">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="AK16">
-        <v>1.38</v>
+        <v>1.63</v>
       </c>
       <c r="AL16">
         <v>0</v>
@@ -3048,12 +3048,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Jeonnam Dragons</t>
+          <t>Ansan Greeners</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Paju Citizen</t>
+          <t>Gimhae City</t>
         </is>
       </c>
       <c r="G17">
@@ -3080,80 +3080,80 @@
         </is>
       </c>
       <c r="N17">
-        <v>1.97</v>
+        <v>2.91</v>
       </c>
       <c r="O17">
-        <v>3.32</v>
+        <v>3.38</v>
       </c>
       <c r="P17">
-        <v>3.45</v>
+        <v>2.18</v>
       </c>
       <c r="Q17">
+        <v>3.4</v>
+      </c>
+      <c r="R17">
+        <v>2.2</v>
+      </c>
+      <c r="S17">
+        <v>1.36</v>
+      </c>
+      <c r="T17">
+        <v>2.88</v>
+      </c>
+      <c r="U17">
         <v>2.66</v>
       </c>
-      <c r="R17">
-        <v>2.25</v>
-      </c>
-      <c r="S17">
-        <v>1.34</v>
-      </c>
-      <c r="T17">
-        <v>3.12</v>
-      </c>
-      <c r="U17">
-        <v>2.71</v>
-      </c>
       <c r="V17">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="W17">
+        <v>1.08</v>
+      </c>
+      <c r="X17">
         <v>1.05</v>
       </c>
-      <c r="X17">
-        <v>1.01</v>
-      </c>
       <c r="Y17">
-        <v>1.28</v>
+        <v>1.26</v>
       </c>
       <c r="Z17">
-        <v>3.55</v>
+        <v>3.68</v>
       </c>
       <c r="AA17">
-        <v>1.9</v>
+        <v>1.82</v>
       </c>
       <c r="AB17">
-        <v>1.9</v>
+        <v>1.88</v>
       </c>
       <c r="AC17">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="AD17">
+        <v>1.27</v>
+      </c>
+      <c r="AE17">
+        <v>1.13</v>
+      </c>
+      <c r="AF17">
+        <v>1.67</v>
+      </c>
+      <c r="AG17">
+        <v>2.1</v>
+      </c>
+      <c r="AH17" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI17" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ17">
+        <v>1.62</v>
+      </c>
+      <c r="AK17">
         <v>1.36</v>
-      </c>
-      <c r="AE17">
-        <v>1.08</v>
-      </c>
-      <c r="AF17">
-        <v>1.58</v>
-      </c>
-      <c r="AG17">
-        <v>2.07</v>
-      </c>
-      <c r="AH17" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI17" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ17">
-        <v>1.22</v>
-      </c>
-      <c r="AK17">
-        <v>1.63</v>
       </c>
       <c r="AL17">
         <v>0</v>
@@ -10546,12 +10546,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Hødd</t>
+          <t>Kongsvinger</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Moss</t>
+          <t>Strømmen</t>
         </is>
       </c>
       <c r="G63">
@@ -10578,80 +10578,80 @@
         </is>
       </c>
       <c r="N63">
-        <v>2.18</v>
+        <v>1.33</v>
       </c>
       <c r="O63">
-        <v>3.45</v>
+        <v>5.35</v>
       </c>
       <c r="P63">
-        <v>2.7</v>
+        <v>5.35</v>
       </c>
       <c r="Q63">
-        <v>2.8</v>
+        <v>1.76</v>
       </c>
       <c r="R63">
+        <v>2.6</v>
+      </c>
+      <c r="S63">
+        <v>1.18</v>
+      </c>
+      <c r="T63">
+        <v>4.5</v>
+      </c>
+      <c r="U63">
+        <v>1.86</v>
+      </c>
+      <c r="V63">
+        <v>1.87</v>
+      </c>
+      <c r="W63">
+        <v>1.23</v>
+      </c>
+      <c r="X63">
+        <v>1.01</v>
+      </c>
+      <c r="Y63">
+        <v>1.06</v>
+      </c>
+      <c r="Z63">
+        <v>7.5</v>
+      </c>
+      <c r="AA63">
+        <v>1.28</v>
+      </c>
+      <c r="AB63">
+        <v>3.08</v>
+      </c>
+      <c r="AC63">
+        <v>1.78</v>
+      </c>
+      <c r="AD63">
+        <v>1.89</v>
+      </c>
+      <c r="AE63">
+        <v>1.38</v>
+      </c>
+      <c r="AF63">
+        <v>1.44</v>
+      </c>
+      <c r="AG63">
         <v>2.5</v>
       </c>
-      <c r="S63">
-        <v>1.2</v>
-      </c>
-      <c r="T63">
-        <v>3.9</v>
-      </c>
-      <c r="U63">
-        <v>2.1</v>
-      </c>
-      <c r="V63">
-        <v>1.67</v>
-      </c>
-      <c r="W63">
-        <v>1.15</v>
-      </c>
-      <c r="X63">
-        <v>1.02</v>
-      </c>
-      <c r="Y63">
+      <c r="AH63" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI63" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ63">
         <v>1.11</v>
       </c>
-      <c r="Z63">
-        <v>5.75</v>
-      </c>
-      <c r="AA63">
-        <v>1.44</v>
-      </c>
-      <c r="AB63">
-        <v>2.63</v>
-      </c>
-      <c r="AC63">
-        <v>2</v>
-      </c>
-      <c r="AD63">
-        <v>1.7</v>
-      </c>
-      <c r="AE63">
-        <v>1.24</v>
-      </c>
-      <c r="AF63">
-        <v>1.39</v>
-      </c>
-      <c r="AG63">
-        <v>2.75</v>
-      </c>
-      <c r="AH63" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI63" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ63">
-        <v>1.25</v>
-      </c>
       <c r="AK63">
-        <v>1.53</v>
+        <v>3</v>
       </c>
       <c r="AL63">
         <v>0</v>
@@ -10709,12 +10709,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Kongsvinger</t>
+          <t>Egersund</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Strømmen</t>
+          <t>Sandnes Ulf</t>
         </is>
       </c>
       <c r="G64">
@@ -10741,64 +10741,64 @@
         </is>
       </c>
       <c r="N64">
-        <v>1.33</v>
+        <v>1.93</v>
       </c>
       <c r="O64">
-        <v>5.35</v>
+        <v>3.33</v>
       </c>
       <c r="P64">
-        <v>5.35</v>
+        <v>2.78</v>
       </c>
       <c r="Q64">
-        <v>1.76</v>
+        <v>2.42</v>
       </c>
       <c r="R64">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="S64">
-        <v>1.18</v>
+        <v>1.25</v>
       </c>
       <c r="T64">
-        <v>4.5</v>
+        <v>3.6</v>
       </c>
       <c r="U64">
-        <v>1.86</v>
+        <v>2.25</v>
       </c>
       <c r="V64">
-        <v>1.87</v>
+        <v>1.57</v>
       </c>
       <c r="W64">
-        <v>1.23</v>
+        <v>1.14</v>
       </c>
       <c r="X64">
         <v>1.01</v>
       </c>
       <c r="Y64">
-        <v>1.06</v>
+        <v>1.13</v>
       </c>
       <c r="Z64">
-        <v>7.5</v>
+        <v>4.55</v>
       </c>
       <c r="AA64">
-        <v>1.28</v>
+        <v>1.45</v>
       </c>
       <c r="AB64">
-        <v>3.08</v>
+        <v>2.41</v>
       </c>
       <c r="AC64">
-        <v>1.78</v>
+        <v>2.37</v>
       </c>
       <c r="AD64">
-        <v>1.89</v>
+        <v>1.57</v>
       </c>
       <c r="AE64">
-        <v>1.38</v>
+        <v>1.18</v>
       </c>
       <c r="AF64">
-        <v>1.44</v>
+        <v>1.49</v>
       </c>
       <c r="AG64">
-        <v>2.5</v>
+        <v>2.44</v>
       </c>
       <c r="AH64" t="inlineStr">
         <is>
@@ -10811,10 +10811,10 @@
         </is>
       </c>
       <c r="AJ64">
-        <v>1.11</v>
+        <v>1.27</v>
       </c>
       <c r="AK64">
-        <v>3</v>
+        <v>1.8</v>
       </c>
       <c r="AL64">
         <v>0</v>
@@ -10872,12 +10872,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Egersund</t>
+          <t>Lyn</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Sandnes Ulf</t>
+          <t>Sogndal</t>
         </is>
       </c>
       <c r="G65">
@@ -10904,64 +10904,64 @@
         </is>
       </c>
       <c r="N65">
-        <v>1.93</v>
+        <v>2.21</v>
       </c>
       <c r="O65">
-        <v>3.33</v>
+        <v>3.73</v>
       </c>
       <c r="P65">
-        <v>2.78</v>
+        <v>2.18</v>
       </c>
       <c r="Q65">
-        <v>2.42</v>
+        <v>2.9</v>
       </c>
       <c r="R65">
         <v>2.5</v>
       </c>
       <c r="S65">
-        <v>1.25</v>
+        <v>1.19</v>
       </c>
       <c r="T65">
-        <v>3.6</v>
+        <v>3.84</v>
       </c>
       <c r="U65">
-        <v>2.25</v>
+        <v>2.06</v>
       </c>
       <c r="V65">
-        <v>1.57</v>
+        <v>1.75</v>
       </c>
       <c r="W65">
-        <v>1.14</v>
+        <v>1.19</v>
       </c>
       <c r="X65">
         <v>1.01</v>
       </c>
       <c r="Y65">
-        <v>1.13</v>
+        <v>1.07</v>
       </c>
       <c r="Z65">
-        <v>4.55</v>
+        <v>5.8</v>
       </c>
       <c r="AA65">
-        <v>1.45</v>
+        <v>1.36</v>
       </c>
       <c r="AB65">
-        <v>2.41</v>
+        <v>3</v>
       </c>
       <c r="AC65">
-        <v>2.37</v>
+        <v>1.93</v>
       </c>
       <c r="AD65">
-        <v>1.57</v>
+        <v>1.83</v>
       </c>
       <c r="AE65">
-        <v>1.18</v>
+        <v>1.32</v>
       </c>
       <c r="AF65">
-        <v>1.49</v>
+        <v>1.33</v>
       </c>
       <c r="AG65">
-        <v>2.44</v>
+        <v>2.98</v>
       </c>
       <c r="AH65" t="inlineStr">
         <is>
@@ -10974,10 +10974,10 @@
         </is>
       </c>
       <c r="AJ65">
-        <v>1.27</v>
+        <v>1.2</v>
       </c>
       <c r="AK65">
-        <v>1.8</v>
+        <v>1.48</v>
       </c>
       <c r="AL65">
         <v>0</v>
@@ -11035,12 +11035,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Raufoss</t>
+          <t>Odd</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Stabæk</t>
+          <t>Åsane</t>
         </is>
       </c>
       <c r="G66">
@@ -11067,80 +11067,80 @@
         </is>
       </c>
       <c r="N66">
-        <v>4.6</v>
+        <v>1.33</v>
       </c>
       <c r="O66">
-        <v>4.4</v>
+        <v>4.55</v>
       </c>
       <c r="P66">
-        <v>1.54</v>
+        <v>4.85</v>
       </c>
       <c r="Q66">
-        <v>4.2</v>
+        <v>1.79</v>
       </c>
       <c r="R66">
-        <v>2.53</v>
+        <v>2.75</v>
       </c>
       <c r="S66">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="T66">
-        <v>4.2</v>
+        <v>4.33</v>
       </c>
       <c r="U66">
-        <v>1.94</v>
+        <v>1.99</v>
       </c>
       <c r="V66">
-        <v>1.79</v>
+        <v>1.83</v>
       </c>
       <c r="W66">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="X66">
         <v>1.01</v>
       </c>
       <c r="Y66">
-        <v>1.1</v>
+        <v>1.05</v>
       </c>
       <c r="Z66">
-        <v>7</v>
+        <v>6.45</v>
       </c>
       <c r="AA66">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="AB66">
-        <v>2.92</v>
+        <v>2.97</v>
       </c>
       <c r="AC66">
-        <v>1.98</v>
+        <v>1.88</v>
       </c>
       <c r="AD66">
-        <v>1.71</v>
+        <v>1.91</v>
       </c>
       <c r="AE66">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="AF66">
-        <v>1.42</v>
+        <v>1.45</v>
       </c>
       <c r="AG66">
+        <v>2.44</v>
+      </c>
+      <c r="AH66" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI66" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ66">
+        <v>1.09</v>
+      </c>
+      <c r="AK66">
         <v>2.7</v>
-      </c>
-      <c r="AH66" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI66" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ66">
-        <v>1.18</v>
-      </c>
-      <c r="AK66">
-        <v>1.15</v>
       </c>
       <c r="AL66">
         <v>0</v>
@@ -11198,12 +11198,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Lyn</t>
+          <t>Hødd</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Sogndal</t>
+          <t>Moss</t>
         </is>
       </c>
       <c r="G67">
@@ -11230,64 +11230,64 @@
         </is>
       </c>
       <c r="N67">
-        <v>2.21</v>
+        <v>2.18</v>
       </c>
       <c r="O67">
-        <v>3.73</v>
+        <v>3.45</v>
       </c>
       <c r="P67">
-        <v>2.18</v>
+        <v>2.7</v>
       </c>
       <c r="Q67">
-        <v>2.9</v>
+        <v>2.8</v>
       </c>
       <c r="R67">
         <v>2.5</v>
       </c>
       <c r="S67">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="T67">
-        <v>3.84</v>
+        <v>3.9</v>
       </c>
       <c r="U67">
-        <v>2.06</v>
+        <v>2.1</v>
       </c>
       <c r="V67">
-        <v>1.75</v>
+        <v>1.67</v>
       </c>
       <c r="W67">
-        <v>1.19</v>
+        <v>1.15</v>
       </c>
       <c r="X67">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y67">
-        <v>1.07</v>
+        <v>1.11</v>
       </c>
       <c r="Z67">
-        <v>5.8</v>
+        <v>5.75</v>
       </c>
       <c r="AA67">
-        <v>1.36</v>
+        <v>1.44</v>
       </c>
       <c r="AB67">
-        <v>3</v>
+        <v>2.63</v>
       </c>
       <c r="AC67">
-        <v>1.93</v>
+        <v>2</v>
       </c>
       <c r="AD67">
-        <v>1.83</v>
+        <v>1.7</v>
       </c>
       <c r="AE67">
-        <v>1.32</v>
+        <v>1.24</v>
       </c>
       <c r="AF67">
-        <v>1.33</v>
+        <v>1.39</v>
       </c>
       <c r="AG67">
-        <v>2.98</v>
+        <v>2.75</v>
       </c>
       <c r="AH67" t="inlineStr">
         <is>
@@ -11300,10 +11300,10 @@
         </is>
       </c>
       <c r="AJ67">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="AK67">
-        <v>1.48</v>
+        <v>1.53</v>
       </c>
       <c r="AL67">
         <v>0</v>
@@ -11361,12 +11361,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Odd</t>
+          <t>Raufoss</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Åsane</t>
+          <t>Stabæk</t>
         </is>
       </c>
       <c r="G68">
@@ -11393,64 +11393,64 @@
         </is>
       </c>
       <c r="N68">
-        <v>1.33</v>
+        <v>4.6</v>
       </c>
       <c r="O68">
-        <v>4.55</v>
+        <v>4.4</v>
       </c>
       <c r="P68">
-        <v>4.85</v>
+        <v>1.54</v>
       </c>
       <c r="Q68">
+        <v>4.2</v>
+      </c>
+      <c r="R68">
+        <v>2.53</v>
+      </c>
+      <c r="S68">
+        <v>1.17</v>
+      </c>
+      <c r="T68">
+        <v>4.2</v>
+      </c>
+      <c r="U68">
+        <v>1.94</v>
+      </c>
+      <c r="V68">
         <v>1.79</v>
       </c>
-      <c r="R68">
-        <v>2.75</v>
-      </c>
-      <c r="S68">
+      <c r="W68">
         <v>1.18</v>
-      </c>
-      <c r="T68">
-        <v>4.33</v>
-      </c>
-      <c r="U68">
-        <v>1.99</v>
-      </c>
-      <c r="V68">
-        <v>1.83</v>
-      </c>
-      <c r="W68">
-        <v>1.2</v>
       </c>
       <c r="X68">
         <v>1.01</v>
       </c>
       <c r="Y68">
-        <v>1.05</v>
+        <v>1.1</v>
       </c>
       <c r="Z68">
-        <v>6.45</v>
+        <v>7</v>
       </c>
       <c r="AA68">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="AB68">
-        <v>2.97</v>
+        <v>2.92</v>
       </c>
       <c r="AC68">
-        <v>1.88</v>
+        <v>1.98</v>
       </c>
       <c r="AD68">
-        <v>1.91</v>
+        <v>1.71</v>
       </c>
       <c r="AE68">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="AF68">
-        <v>1.45</v>
+        <v>1.42</v>
       </c>
       <c r="AG68">
-        <v>2.44</v>
+        <v>2.7</v>
       </c>
       <c r="AH68" t="inlineStr">
         <is>
@@ -11463,10 +11463,10 @@
         </is>
       </c>
       <c r="AJ68">
-        <v>1.09</v>
+        <v>1.18</v>
       </c>
       <c r="AK68">
-        <v>2.7</v>
+        <v>1.15</v>
       </c>
       <c r="AL68">
         <v>0</v>

--- a/jogos_2026-08-02.xlsx
+++ b/jogos_2026-08-02.xlsx
@@ -638,22 +638,22 @@
         <v>1.3</v>
       </c>
       <c r="O2">
-        <v>4.8</v>
+        <v>4.75</v>
       </c>
       <c r="P2">
-        <v>6.9</v>
+        <v>7.95</v>
       </c>
       <c r="Q2">
         <v>1.67</v>
       </c>
       <c r="R2">
-        <v>2.7</v>
+        <v>2.77</v>
       </c>
       <c r="S2">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="T2">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="U2">
         <v>2.2</v>
@@ -662,7 +662,7 @@
         <v>1.59</v>
       </c>
       <c r="W2">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="X2">
         <v>1.01</v>
@@ -674,16 +674,16 @@
         <v>4.55</v>
       </c>
       <c r="AA2">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="AB2">
         <v>2.51</v>
       </c>
       <c r="AC2">
-        <v>2.4</v>
+        <v>2.34</v>
       </c>
       <c r="AD2">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="AE2">
         <v>1.2</v>
@@ -1468,10 +1468,10 @@
         <v>1.43</v>
       </c>
       <c r="T7">
-        <v>2.75</v>
+        <v>2.59</v>
       </c>
       <c r="U7">
-        <v>3.13</v>
+        <v>3.05</v>
       </c>
       <c r="V7">
         <v>1.32</v>
@@ -1492,7 +1492,7 @@
         <v>2.11</v>
       </c>
       <c r="AB7">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="AC7">
         <v>3.68</v>
@@ -1523,7 +1523,7 @@
         <v>1.96</v>
       </c>
       <c r="AK7">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="AL7">
         <v>0</v>
@@ -2559,12 +2559,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Busan I'Park</t>
+          <t>Jeonnam Dragons</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Seoul E-Land</t>
+          <t>Paju Citizen</t>
         </is>
       </c>
       <c r="G14">
@@ -2591,64 +2591,64 @@
         </is>
       </c>
       <c r="N14">
-        <v>2.75</v>
+        <v>1.97</v>
       </c>
       <c r="O14">
-        <v>3.4</v>
+        <v>3.32</v>
       </c>
       <c r="P14">
+        <v>3.45</v>
+      </c>
+      <c r="Q14">
+        <v>2.66</v>
+      </c>
+      <c r="R14">
         <v>2.25</v>
       </c>
-      <c r="Q14">
-        <v>3.1</v>
-      </c>
-      <c r="R14">
-        <v>2.36</v>
-      </c>
       <c r="S14">
-        <v>1.3</v>
+        <v>1.34</v>
       </c>
       <c r="T14">
-        <v>3.15</v>
+        <v>3.12</v>
       </c>
       <c r="U14">
-        <v>2.5</v>
+        <v>2.71</v>
       </c>
       <c r="V14">
-        <v>1.45</v>
+        <v>1.43</v>
       </c>
       <c r="W14">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="X14">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y14">
-        <v>1.16</v>
+        <v>1.28</v>
       </c>
       <c r="Z14">
-        <v>4.05</v>
+        <v>3.55</v>
       </c>
       <c r="AA14">
-        <v>1.7</v>
+        <v>1.9</v>
       </c>
       <c r="AB14">
-        <v>2.1</v>
+        <v>1.9</v>
       </c>
       <c r="AC14">
-        <v>2.62</v>
+        <v>3</v>
       </c>
       <c r="AD14">
-        <v>1.44</v>
+        <v>1.36</v>
       </c>
       <c r="AE14">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="AF14">
-        <v>1.55</v>
+        <v>1.58</v>
       </c>
       <c r="AG14">
-        <v>2.27</v>
+        <v>2.07</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2661,10 +2661,10 @@
         </is>
       </c>
       <c r="AJ14">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="AK14">
-        <v>1.38</v>
+        <v>1.63</v>
       </c>
       <c r="AL14">
         <v>0</v>
@@ -2722,12 +2722,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Gimpo Citizen</t>
+          <t>Busan I'Park</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Gyeongnam</t>
+          <t>Seoul E-Land</t>
         </is>
       </c>
       <c r="G15">
@@ -2754,64 +2754,64 @@
         </is>
       </c>
       <c r="N15">
-        <v>1.85</v>
+        <v>2.75</v>
       </c>
       <c r="O15">
-        <v>2.98</v>
+        <v>3.4</v>
       </c>
       <c r="P15">
-        <v>3.28</v>
+        <v>2.25</v>
       </c>
       <c r="Q15">
-        <v>2.47</v>
+        <v>3.1</v>
       </c>
       <c r="R15">
-        <v>2.18</v>
+        <v>2.36</v>
       </c>
       <c r="S15">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="T15">
+        <v>3.15</v>
+      </c>
+      <c r="U15">
         <v>2.5</v>
       </c>
-      <c r="U15">
-        <v>3.28</v>
-      </c>
       <c r="V15">
-        <v>1.33</v>
+        <v>1.45</v>
       </c>
       <c r="W15">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="X15">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y15">
-        <v>1.35</v>
+        <v>1.16</v>
       </c>
       <c r="Z15">
-        <v>2.74</v>
+        <v>4.05</v>
       </c>
       <c r="AA15">
-        <v>2.14</v>
+        <v>1.7</v>
       </c>
       <c r="AB15">
-        <v>1.73</v>
+        <v>2.1</v>
       </c>
       <c r="AC15">
-        <v>3.2</v>
+        <v>2.62</v>
       </c>
       <c r="AD15">
-        <v>1.22</v>
+        <v>1.44</v>
       </c>
       <c r="AE15">
-        <v>1.03</v>
+        <v>1.17</v>
       </c>
       <c r="AF15">
-        <v>1.85</v>
+        <v>1.55</v>
       </c>
       <c r="AG15">
-        <v>1.8</v>
+        <v>2.27</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2824,10 +2824,10 @@
         </is>
       </c>
       <c r="AJ15">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="AK15">
-        <v>1.84</v>
+        <v>1.38</v>
       </c>
       <c r="AL15">
         <v>0</v>
@@ -2885,12 +2885,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Jeonnam Dragons</t>
+          <t>Gimpo Citizen</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Paju Citizen</t>
+          <t>Gyeongnam</t>
         </is>
       </c>
       <c r="G16">
@@ -2917,64 +2917,64 @@
         </is>
       </c>
       <c r="N16">
-        <v>1.97</v>
+        <v>1.85</v>
       </c>
       <c r="O16">
-        <v>3.32</v>
+        <v>2.98</v>
       </c>
       <c r="P16">
-        <v>3.45</v>
+        <v>3.28</v>
       </c>
       <c r="Q16">
-        <v>2.66</v>
+        <v>2.47</v>
       </c>
       <c r="R16">
-        <v>2.25</v>
+        <v>2.18</v>
       </c>
       <c r="S16">
-        <v>1.34</v>
+        <v>1.4</v>
       </c>
       <c r="T16">
-        <v>3.12</v>
+        <v>2.5</v>
       </c>
       <c r="U16">
-        <v>2.71</v>
+        <v>3.28</v>
       </c>
       <c r="V16">
-        <v>1.43</v>
+        <v>1.33</v>
       </c>
       <c r="W16">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="X16">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y16">
-        <v>1.28</v>
+        <v>1.35</v>
       </c>
       <c r="Z16">
-        <v>3.55</v>
+        <v>2.74</v>
       </c>
       <c r="AA16">
-        <v>1.9</v>
+        <v>2.14</v>
       </c>
       <c r="AB16">
-        <v>1.9</v>
+        <v>1.73</v>
       </c>
       <c r="AC16">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="AD16">
-        <v>1.36</v>
+        <v>1.22</v>
       </c>
       <c r="AE16">
-        <v>1.08</v>
+        <v>1.03</v>
       </c>
       <c r="AF16">
-        <v>1.58</v>
+        <v>1.85</v>
       </c>
       <c r="AG16">
-        <v>2.07</v>
+        <v>1.8</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -2990,7 +2990,7 @@
         <v>1.22</v>
       </c>
       <c r="AK16">
-        <v>1.63</v>
+        <v>1.84</v>
       </c>
       <c r="AL16">
         <v>0</v>
@@ -4058,19 +4058,19 @@
         </is>
       </c>
       <c r="N23">
-        <v>2.7</v>
+        <v>2.97</v>
       </c>
       <c r="O23">
-        <v>3.61</v>
+        <v>3.8</v>
       </c>
       <c r="P23">
-        <v>2.03</v>
+        <v>2.15</v>
       </c>
       <c r="Q23">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="R23">
-        <v>2.45</v>
+        <v>2.4</v>
       </c>
       <c r="S23">
         <v>1.22</v>
@@ -4091,10 +4091,10 @@
         <v>1.02</v>
       </c>
       <c r="Y23">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="Z23">
-        <v>4.8</v>
+        <v>5.38</v>
       </c>
       <c r="AA23">
         <v>1.46</v>
@@ -4115,7 +4115,7 @@
         <v>1.44</v>
       </c>
       <c r="AG23">
-        <v>2.63</v>
+        <v>2.5</v>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
@@ -4221,31 +4221,31 @@
         </is>
       </c>
       <c r="N24">
-        <v>2.31</v>
+        <v>2.8</v>
       </c>
       <c r="O24">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="P24">
-        <v>2.65</v>
+        <v>2.47</v>
       </c>
       <c r="Q24">
         <v>3</v>
       </c>
       <c r="R24">
-        <v>1.96</v>
+        <v>1.93</v>
       </c>
       <c r="S24">
-        <v>1.46</v>
+        <v>1.48</v>
       </c>
       <c r="T24">
-        <v>2.5</v>
+        <v>2.44</v>
       </c>
       <c r="U24">
         <v>3.29</v>
       </c>
       <c r="V24">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="W24">
         <v>1.02</v>
@@ -4254,7 +4254,7 @@
         <v>1.04</v>
       </c>
       <c r="Y24">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="Z24">
         <v>2.7</v>
@@ -4266,7 +4266,7 @@
         <v>1.63</v>
       </c>
       <c r="AC24">
-        <v>3.86</v>
+        <v>3.84</v>
       </c>
       <c r="AD24">
         <v>1.18</v>
@@ -4294,7 +4294,7 @@
         <v>1.27</v>
       </c>
       <c r="AK24">
-        <v>1.48</v>
+        <v>1.41</v>
       </c>
       <c r="AL24">
         <v>0</v>
@@ -4722,13 +4722,13 @@
         <v>1.71</v>
       </c>
       <c r="R27">
-        <v>2.63</v>
+        <v>2.62</v>
       </c>
       <c r="S27">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="T27">
-        <v>4</v>
+        <v>3.65</v>
       </c>
       <c r="U27">
         <v>2.16</v>
@@ -4746,7 +4746,7 @@
         <v>1.12</v>
       </c>
       <c r="Z27">
-        <v>4.75</v>
+        <v>4.7</v>
       </c>
       <c r="AA27">
         <v>1.47</v>
@@ -4761,13 +4761,13 @@
         <v>1.57</v>
       </c>
       <c r="AE27">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="AF27">
-        <v>1.78</v>
+        <v>1.76</v>
       </c>
       <c r="AG27">
-        <v>1.92</v>
+        <v>1.9</v>
       </c>
       <c r="AH27" t="inlineStr">
         <is>
@@ -4783,7 +4783,7 @@
         <v>1.05</v>
       </c>
       <c r="AK27">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="AL27">
         <v>0</v>
@@ -4873,13 +4873,13 @@
         </is>
       </c>
       <c r="N28">
-        <v>1.68</v>
+        <v>1.71</v>
       </c>
       <c r="O28">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="P28">
-        <v>3.8</v>
+        <v>4.33</v>
       </c>
       <c r="Q28">
         <v>2.18</v>
@@ -4894,7 +4894,7 @@
         <v>3.22</v>
       </c>
       <c r="U28">
-        <v>2.42</v>
+        <v>2.46</v>
       </c>
       <c r="V28">
         <v>1.55</v>
@@ -4909,28 +4909,28 @@
         <v>1.2</v>
       </c>
       <c r="Z28">
-        <v>4.57</v>
+        <v>4.53</v>
       </c>
       <c r="AA28">
-        <v>1.66</v>
+        <v>1.57</v>
       </c>
       <c r="AB28">
-        <v>2.15</v>
+        <v>2.26</v>
       </c>
       <c r="AC28">
         <v>2.65</v>
       </c>
       <c r="AD28">
-        <v>1.51</v>
+        <v>1.44</v>
       </c>
       <c r="AE28">
         <v>1.2</v>
       </c>
       <c r="AF28">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="AG28">
-        <v>2.19</v>
+        <v>2.23</v>
       </c>
       <c r="AH28" t="inlineStr">
         <is>
@@ -4946,7 +4946,7 @@
         <v>1.23</v>
       </c>
       <c r="AK28">
-        <v>2.1</v>
+        <v>2.07</v>
       </c>
       <c r="AL28">
         <v>0</v>
@@ -5057,13 +5057,13 @@
         <v>2.7</v>
       </c>
       <c r="U29">
-        <v>2.88</v>
+        <v>2.75</v>
       </c>
       <c r="V29">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="W29">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="X29">
         <v>1.02</v>
@@ -5081,7 +5081,7 @@
         <v>1.91</v>
       </c>
       <c r="AC29">
-        <v>3.3</v>
+        <v>2.95</v>
       </c>
       <c r="AD29">
         <v>1.27</v>
@@ -5090,10 +5090,10 @@
         <v>1.06</v>
       </c>
       <c r="AF29">
-        <v>1.64</v>
+        <v>1.9</v>
       </c>
       <c r="AG29">
-        <v>1.98</v>
+        <v>1.82</v>
       </c>
       <c r="AH29" t="inlineStr">
         <is>
@@ -5109,7 +5109,7 @@
         <v>1.73</v>
       </c>
       <c r="AK29">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="AL29">
         <v>0</v>
@@ -5202,10 +5202,10 @@
         <v>1.55</v>
       </c>
       <c r="O30">
-        <v>3.52</v>
+        <v>3.8</v>
       </c>
       <c r="P30">
-        <v>7.24</v>
+        <v>5.5</v>
       </c>
       <c r="Q30">
         <v>0</v>
@@ -5362,19 +5362,19 @@
         </is>
       </c>
       <c r="N31">
-        <v>2.17</v>
+        <v>2</v>
       </c>
       <c r="O31">
         <v>3.4</v>
       </c>
       <c r="P31">
-        <v>2.91</v>
+        <v>3.05</v>
       </c>
       <c r="Q31">
-        <v>2.75</v>
+        <v>2.62</v>
       </c>
       <c r="R31">
-        <v>2.18</v>
+        <v>2.19</v>
       </c>
       <c r="S31">
         <v>1.29</v>
@@ -5383,7 +5383,7 @@
         <v>3.12</v>
       </c>
       <c r="U31">
-        <v>2.5</v>
+        <v>2.59</v>
       </c>
       <c r="V31">
         <v>1.44</v>
@@ -5395,28 +5395,28 @@
         <v>1.03</v>
       </c>
       <c r="Y31">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="Z31">
-        <v>3.94</v>
+        <v>3.97</v>
       </c>
       <c r="AA31">
         <v>1.72</v>
       </c>
       <c r="AB31">
-        <v>2.04</v>
+        <v>2</v>
       </c>
       <c r="AC31">
-        <v>2.84</v>
+        <v>2.82</v>
       </c>
       <c r="AD31">
         <v>1.4</v>
       </c>
       <c r="AE31">
-        <v>1.15</v>
+        <v>1.09</v>
       </c>
       <c r="AF31">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="AG31">
         <v>2.19</v>
@@ -5432,10 +5432,10 @@
         </is>
       </c>
       <c r="AJ31">
-        <v>1.22</v>
+        <v>1.33</v>
       </c>
       <c r="AK31">
-        <v>1.56</v>
+        <v>1.67</v>
       </c>
       <c r="AL31">
         <v>0</v>
@@ -5528,10 +5528,10 @@
         <v>1.55</v>
       </c>
       <c r="O32">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="P32">
-        <v>5.4</v>
+        <v>5.59</v>
       </c>
       <c r="Q32">
         <v>2.1</v>
@@ -5540,7 +5540,7 @@
         <v>2.22</v>
       </c>
       <c r="S32">
-        <v>1.37</v>
+        <v>1.35</v>
       </c>
       <c r="T32">
         <v>2.9</v>
@@ -5549,10 +5549,10 @@
         <v>2.75</v>
       </c>
       <c r="V32">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="W32">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="X32">
         <v>1.03</v>
@@ -5579,10 +5579,10 @@
         <v>1.12</v>
       </c>
       <c r="AF32">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="AG32">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="AH32" t="inlineStr">
         <is>
@@ -5598,7 +5598,7 @@
         <v>1.11</v>
       </c>
       <c r="AK32">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="AL32">
         <v>0</v>
@@ -5688,7 +5688,7 @@
         </is>
       </c>
       <c r="N33">
-        <v>2.7</v>
+        <v>2.6</v>
       </c>
       <c r="O33">
         <v>2.6</v>
@@ -5700,52 +5700,52 @@
         <v>3.5</v>
       </c>
       <c r="R33">
-        <v>1.83</v>
+        <v>1.73</v>
       </c>
       <c r="S33">
-        <v>1.68</v>
+        <v>1.62</v>
       </c>
       <c r="T33">
-        <v>2.05</v>
+        <v>2.07</v>
       </c>
       <c r="U33">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="V33">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="W33">
         <v>1.02</v>
       </c>
       <c r="X33">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="Y33">
-        <v>1.67</v>
+        <v>1.61</v>
       </c>
       <c r="Z33">
-        <v>2.15</v>
+        <v>2.17</v>
       </c>
       <c r="AA33">
-        <v>2.83</v>
+        <v>2.78</v>
       </c>
       <c r="AB33">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="AC33">
         <v>6.25</v>
       </c>
       <c r="AD33">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="AE33">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AF33">
-        <v>2.3</v>
+        <v>2.23</v>
       </c>
       <c r="AG33">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="AH33" t="inlineStr">
         <is>
@@ -5863,7 +5863,7 @@
         <v>3.02</v>
       </c>
       <c r="R34">
-        <v>2.09</v>
+        <v>1.96</v>
       </c>
       <c r="S34">
         <v>1.44</v>
@@ -5890,10 +5890,10 @@
         <v>2.98</v>
       </c>
       <c r="AA34">
-        <v>2.15</v>
+        <v>2.18</v>
       </c>
       <c r="AB34">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="AC34">
         <v>3.74</v>
@@ -5924,7 +5924,7 @@
         <v>1.32</v>
       </c>
       <c r="AK34">
-        <v>1.52</v>
+        <v>1.56</v>
       </c>
       <c r="AL34">
         <v>0</v>
@@ -6014,10 +6014,10 @@
         </is>
       </c>
       <c r="N35">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="O35">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="P35">
         <v>4.03</v>
@@ -6026,10 +6026,10 @@
         <v>2.29</v>
       </c>
       <c r="R35">
-        <v>2.31</v>
+        <v>2.3</v>
       </c>
       <c r="S35">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="T35">
         <v>3.6</v>
@@ -6044,7 +6044,7 @@
         <v>1.12</v>
       </c>
       <c r="X35">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y35">
         <v>1.14</v>
@@ -6087,7 +6087,7 @@
         <v>1.17</v>
       </c>
       <c r="AK35">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="AL35">
         <v>0</v>
@@ -6666,19 +6666,19 @@
         </is>
       </c>
       <c r="N39">
-        <v>7.4</v>
+        <v>8.050000000000001</v>
       </c>
       <c r="O39">
-        <v>4.65</v>
+        <v>4.8</v>
       </c>
       <c r="P39">
-        <v>1.37</v>
+        <v>1.33</v>
       </c>
       <c r="Q39">
         <v>7.1</v>
       </c>
       <c r="R39">
-        <v>2.48</v>
+        <v>2.24</v>
       </c>
       <c r="S39">
         <v>1.33</v>
@@ -6693,34 +6693,34 @@
         <v>1.47</v>
       </c>
       <c r="W39">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="X39">
         <v>1.01</v>
       </c>
       <c r="Y39">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="Z39">
-        <v>3.82</v>
+        <v>3.74</v>
       </c>
       <c r="AA39">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="AB39">
-        <v>2.13</v>
+        <v>2.11</v>
       </c>
       <c r="AC39">
         <v>2.86</v>
       </c>
       <c r="AD39">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="AE39">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="AF39">
-        <v>2.03</v>
+        <v>2.02</v>
       </c>
       <c r="AG39">
         <v>1.72</v>
@@ -6736,10 +6736,10 @@
         </is>
       </c>
       <c r="AJ39">
-        <v>3.2</v>
+        <v>1.2</v>
       </c>
       <c r="AK39">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="AL39">
         <v>0</v>
@@ -6832,13 +6832,13 @@
         <v>2.17</v>
       </c>
       <c r="O40">
-        <v>3.47</v>
+        <v>3.4</v>
       </c>
       <c r="P40">
-        <v>2.83</v>
+        <v>3.1</v>
       </c>
       <c r="Q40">
-        <v>2.73</v>
+        <v>2.5</v>
       </c>
       <c r="R40">
         <v>2.2</v>
@@ -6850,34 +6850,34 @@
         <v>2.94</v>
       </c>
       <c r="U40">
-        <v>2.45</v>
+        <v>2.75</v>
       </c>
       <c r="V40">
-        <v>1.45</v>
+        <v>1.43</v>
       </c>
       <c r="W40">
         <v>1.06</v>
       </c>
       <c r="X40">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="Y40">
         <v>1.24</v>
       </c>
       <c r="Z40">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="AA40">
-        <v>1.79</v>
+        <v>1.77</v>
       </c>
       <c r="AB40">
         <v>1.99</v>
       </c>
       <c r="AC40">
-        <v>3</v>
+        <v>2.95</v>
       </c>
       <c r="AD40">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="AE40">
         <v>1.15</v>
@@ -6886,7 +6886,7 @@
         <v>1.62</v>
       </c>
       <c r="AG40">
-        <v>2.17</v>
+        <v>2.15</v>
       </c>
       <c r="AH40" t="inlineStr">
         <is>
@@ -7001,13 +7001,13 @@
         <v>2.37</v>
       </c>
       <c r="Q41">
-        <v>3.45</v>
+        <v>4.2</v>
       </c>
       <c r="R41">
-        <v>2.04</v>
+        <v>2.1</v>
       </c>
       <c r="S41">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="T41">
         <v>2.45</v>
@@ -7028,25 +7028,25 @@
         <v>1.3</v>
       </c>
       <c r="Z41">
-        <v>3.2</v>
+        <v>2.8</v>
       </c>
       <c r="AA41">
         <v>2.15</v>
       </c>
       <c r="AB41">
-        <v>1.77</v>
+        <v>1.61</v>
       </c>
       <c r="AC41">
-        <v>3.3</v>
+        <v>3.85</v>
       </c>
       <c r="AD41">
-        <v>1.27</v>
+        <v>1.21</v>
       </c>
       <c r="AE41">
         <v>1.06</v>
       </c>
       <c r="AF41">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="AG41">
         <v>1.78</v>
@@ -7062,10 +7062,10 @@
         </is>
       </c>
       <c r="AJ41">
-        <v>1.27</v>
+        <v>1.73</v>
       </c>
       <c r="AK41">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AL41">
         <v>0</v>
@@ -7155,22 +7155,22 @@
         </is>
       </c>
       <c r="N42">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="O42">
         <v>3.35</v>
       </c>
       <c r="P42">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="Q42">
         <v>2.6</v>
       </c>
       <c r="R42">
-        <v>2.13</v>
+        <v>2.25</v>
       </c>
       <c r="S42">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="T42">
         <v>3.3</v>
@@ -7551,10 +7551,10 @@
         </is>
       </c>
       <c r="AJ44">
-        <v>1.24</v>
+        <v>1.26</v>
       </c>
       <c r="AK44">
-        <v>2.16</v>
+        <v>2.19</v>
       </c>
       <c r="AL44">
         <v>0</v>
@@ -8468,10 +8468,10 @@
         <v>3.4</v>
       </c>
       <c r="Q50">
-        <v>2.33</v>
+        <v>2.4</v>
       </c>
       <c r="R50">
-        <v>2.35</v>
+        <v>2.23</v>
       </c>
       <c r="S50">
         <v>1.32</v>
@@ -8785,7 +8785,7 @@
         </is>
       </c>
       <c r="N52">
-        <v>2.07</v>
+        <v>1.91</v>
       </c>
       <c r="O52">
         <v>3.75</v>
@@ -8797,13 +8797,13 @@
         <v>2.22</v>
       </c>
       <c r="R52">
-        <v>2.38</v>
+        <v>2.31</v>
       </c>
       <c r="S52">
         <v>1.25</v>
       </c>
       <c r="T52">
-        <v>3.42</v>
+        <v>3.55</v>
       </c>
       <c r="U52">
         <v>2.31</v>
@@ -8821,13 +8821,13 @@
         <v>1.13</v>
       </c>
       <c r="Z52">
-        <v>4.75</v>
+        <v>4.55</v>
       </c>
       <c r="AA52">
         <v>1.51</v>
       </c>
       <c r="AB52">
-        <v>2.28</v>
+        <v>2.41</v>
       </c>
       <c r="AC52">
         <v>2.38</v>
@@ -8842,7 +8842,7 @@
         <v>1.49</v>
       </c>
       <c r="AG52">
-        <v>2.44</v>
+        <v>2.45</v>
       </c>
       <c r="AH52" t="inlineStr">
         <is>
@@ -8954,13 +8954,13 @@
         <v>3.62</v>
       </c>
       <c r="P53">
-        <v>1.96</v>
+        <v>2.01</v>
       </c>
       <c r="Q53">
-        <v>4.16</v>
+        <v>3.85</v>
       </c>
       <c r="R53">
-        <v>2.23</v>
+        <v>2.38</v>
       </c>
       <c r="S53">
         <v>1.31</v>
@@ -8972,7 +8972,7 @@
         <v>2.45</v>
       </c>
       <c r="V53">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="W53">
         <v>1.08</v>
@@ -8981,25 +8981,25 @@
         <v>1.04</v>
       </c>
       <c r="Y53">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="Z53">
         <v>3.9</v>
       </c>
       <c r="AA53">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="AB53">
-        <v>2.1</v>
+        <v>1.96</v>
       </c>
       <c r="AC53">
-        <v>2.68</v>
+        <v>2.78</v>
       </c>
       <c r="AD53">
-        <v>1.44</v>
+        <v>1.37</v>
       </c>
       <c r="AE53">
-        <v>1.17</v>
+        <v>1.11</v>
       </c>
       <c r="AF53">
         <v>1.6</v>
@@ -9274,64 +9274,64 @@
         </is>
       </c>
       <c r="N55">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="O55">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="P55">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Q55">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R55">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="S55">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="T55">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="U55">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="V55">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="W55">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X55">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y55">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="Z55">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="AA55">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AB55">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AC55">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AD55">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AE55">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AF55">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AG55">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="AH55" t="inlineStr">
         <is>
@@ -9344,10 +9344,10 @@
         </is>
       </c>
       <c r="AJ55">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK55">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AL55">
         <v>0</v>
@@ -9568,12 +9568,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>KFUM</t>
+          <t>Aalesund</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Kristiansund</t>
+          <t>Tromsø</t>
         </is>
       </c>
       <c r="G57">
@@ -9600,64 +9600,64 @@
         </is>
       </c>
       <c r="N57">
-        <v>1.67</v>
+        <v>3.31</v>
       </c>
       <c r="O57">
-        <v>3.78</v>
+        <v>3.61</v>
       </c>
       <c r="P57">
-        <v>4.2</v>
+        <v>1.87</v>
       </c>
       <c r="Q57">
-        <v>2.21</v>
+        <v>3.7</v>
       </c>
       <c r="R57">
-        <v>2.21</v>
+        <v>2.3</v>
       </c>
       <c r="S57">
         <v>1.29</v>
       </c>
       <c r="T57">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="U57">
-        <v>2.39</v>
+        <v>2.52</v>
       </c>
       <c r="V57">
-        <v>1.45</v>
+        <v>1.49</v>
       </c>
       <c r="W57">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="X57">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y57">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="Z57">
-        <v>3.85</v>
+        <v>4.44</v>
       </c>
       <c r="AA57">
-        <v>1.72</v>
+        <v>1.66</v>
       </c>
       <c r="AB57">
-        <v>2.04</v>
+        <v>2.18</v>
       </c>
       <c r="AC57">
-        <v>2.8</v>
+        <v>2.57</v>
       </c>
       <c r="AD57">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="AE57">
-        <v>1.17</v>
+        <v>1.12</v>
       </c>
       <c r="AF57">
-        <v>1.67</v>
+        <v>1.58</v>
       </c>
       <c r="AG57">
-        <v>2.05</v>
+        <v>2.18</v>
       </c>
       <c r="AH57" t="inlineStr">
         <is>
@@ -9670,10 +9670,10 @@
         </is>
       </c>
       <c r="AJ57">
-        <v>1.2</v>
+        <v>1.85</v>
       </c>
       <c r="AK57">
-        <v>2.1</v>
+        <v>1.22</v>
       </c>
       <c r="AL57">
         <v>0</v>
@@ -9731,12 +9731,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Molde</t>
+          <t>KFUM</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Sarpsborg 08</t>
+          <t>Kristiansund</t>
         </is>
       </c>
       <c r="G58">
@@ -9763,64 +9763,64 @@
         </is>
       </c>
       <c r="N58">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="O58">
-        <v>4.3</v>
+        <v>3.78</v>
       </c>
       <c r="P58">
-        <v>4.43</v>
+        <v>4.2</v>
       </c>
       <c r="Q58">
-        <v>2</v>
+        <v>2.21</v>
       </c>
       <c r="R58">
-        <v>2.36</v>
+        <v>2.21</v>
       </c>
       <c r="S58">
-        <v>1.22</v>
+        <v>1.29</v>
       </c>
       <c r="T58">
-        <v>4</v>
+        <v>3.25</v>
       </c>
       <c r="U58">
-        <v>2</v>
+        <v>2.39</v>
       </c>
       <c r="V58">
-        <v>1.68</v>
+        <v>1.45</v>
       </c>
       <c r="W58">
+        <v>1.08</v>
+      </c>
+      <c r="X58">
+        <v>1.01</v>
+      </c>
+      <c r="Y58">
+        <v>1.2</v>
+      </c>
+      <c r="Z58">
+        <v>3.85</v>
+      </c>
+      <c r="AA58">
+        <v>1.72</v>
+      </c>
+      <c r="AB58">
+        <v>2.04</v>
+      </c>
+      <c r="AC58">
+        <v>2.8</v>
+      </c>
+      <c r="AD58">
+        <v>1.4</v>
+      </c>
+      <c r="AE58">
         <v>1.17</v>
       </c>
-      <c r="X58">
-        <v>1.02</v>
-      </c>
-      <c r="Y58">
-        <v>1.08</v>
-      </c>
-      <c r="Z58">
-        <v>5.7</v>
-      </c>
-      <c r="AA58">
-        <v>1.44</v>
-      </c>
-      <c r="AB58">
-        <v>2.63</v>
-      </c>
-      <c r="AC58">
-        <v>2.12</v>
-      </c>
-      <c r="AD58">
-        <v>1.73</v>
-      </c>
-      <c r="AE58">
-        <v>1.26</v>
-      </c>
       <c r="AF58">
-        <v>1.44</v>
+        <v>1.67</v>
       </c>
       <c r="AG58">
-        <v>2.56</v>
+        <v>2.05</v>
       </c>
       <c r="AH58" t="inlineStr">
         <is>
@@ -9833,10 +9833,10 @@
         </is>
       </c>
       <c r="AJ58">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="AK58">
-        <v>2.13</v>
+        <v>2.1</v>
       </c>
       <c r="AL58">
         <v>0</v>
@@ -9894,12 +9894,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Aalesund</t>
+          <t>Molde</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Tromsø</t>
+          <t>Sarpsborg 08</t>
         </is>
       </c>
       <c r="G59">
@@ -9926,64 +9926,64 @@
         </is>
       </c>
       <c r="N59">
-        <v>3.31</v>
+        <v>1.7</v>
       </c>
       <c r="O59">
-        <v>3.61</v>
+        <v>4.3</v>
       </c>
       <c r="P59">
-        <v>1.87</v>
+        <v>4.43</v>
       </c>
       <c r="Q59">
-        <v>3.7</v>
+        <v>2</v>
       </c>
       <c r="R59">
-        <v>2.3</v>
+        <v>2.36</v>
       </c>
       <c r="S59">
-        <v>1.29</v>
+        <v>1.22</v>
       </c>
       <c r="T59">
-        <v>3.2</v>
+        <v>4</v>
       </c>
       <c r="U59">
-        <v>2.52</v>
+        <v>2</v>
       </c>
       <c r="V59">
-        <v>1.49</v>
+        <v>1.68</v>
       </c>
       <c r="W59">
-        <v>1.11</v>
+        <v>1.17</v>
       </c>
       <c r="X59">
         <v>1.02</v>
       </c>
       <c r="Y59">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="Z59">
-        <v>4.44</v>
+        <v>5.7</v>
       </c>
       <c r="AA59">
-        <v>1.66</v>
+        <v>1.44</v>
       </c>
       <c r="AB59">
-        <v>2.18</v>
+        <v>2.63</v>
       </c>
       <c r="AC59">
-        <v>2.57</v>
+        <v>2.12</v>
       </c>
       <c r="AD59">
-        <v>1.41</v>
+        <v>1.73</v>
       </c>
       <c r="AE59">
-        <v>1.12</v>
+        <v>1.26</v>
       </c>
       <c r="AF59">
-        <v>1.58</v>
+        <v>1.44</v>
       </c>
       <c r="AG59">
-        <v>2.18</v>
+        <v>2.56</v>
       </c>
       <c r="AH59" t="inlineStr">
         <is>
@@ -9996,10 +9996,10 @@
         </is>
       </c>
       <c r="AJ59">
-        <v>1.85</v>
+        <v>1.17</v>
       </c>
       <c r="AK59">
-        <v>1.22</v>
+        <v>2.13</v>
       </c>
       <c r="AL59">
         <v>0</v>
@@ -10220,12 +10220,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Wolfsberger AC</t>
+          <t>Austria Lustenau</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Austria Wien</t>
+          <t>Ried</t>
         </is>
       </c>
       <c r="G61">
@@ -10252,64 +10252,64 @@
         </is>
       </c>
       <c r="N61">
-        <v>2.25</v>
+        <v>2.62</v>
       </c>
       <c r="O61">
-        <v>3.2</v>
+        <v>3.18</v>
       </c>
       <c r="P61">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="Q61">
-        <v>2.9</v>
+        <v>3.25</v>
       </c>
       <c r="R61">
-        <v>2.13</v>
+        <v>2.1</v>
       </c>
       <c r="S61">
+        <v>1.4</v>
+      </c>
+      <c r="T61">
+        <v>2.85</v>
+      </c>
+      <c r="U61">
+        <v>2.85</v>
+      </c>
+      <c r="V61">
         <v>1.36</v>
       </c>
-      <c r="T61">
-        <v>2.89</v>
-      </c>
-      <c r="U61">
-        <v>2.5</v>
-      </c>
-      <c r="V61">
-        <v>1.4</v>
-      </c>
       <c r="W61">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="X61">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="Y61">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="Z61">
-        <v>3.81</v>
+        <v>2.99</v>
       </c>
       <c r="AA61">
-        <v>1.79</v>
+        <v>2.06</v>
       </c>
       <c r="AB61">
-        <v>1.88</v>
+        <v>1.76</v>
       </c>
       <c r="AC61">
-        <v>3.05</v>
+        <v>3.55</v>
       </c>
       <c r="AD61">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
       <c r="AE61">
-        <v>1.14</v>
+        <v>1.1</v>
       </c>
       <c r="AF61">
-        <v>1.67</v>
+        <v>1.75</v>
       </c>
       <c r="AG61">
-        <v>2.13</v>
+        <v>1.96</v>
       </c>
       <c r="AH61" t="inlineStr">
         <is>
@@ -10322,10 +10322,10 @@
         </is>
       </c>
       <c r="AJ61">
-        <v>1.3</v>
+        <v>1.45</v>
       </c>
       <c r="AK61">
-        <v>1.56</v>
+        <v>1.48</v>
       </c>
       <c r="AL61">
         <v>0</v>
@@ -10383,12 +10383,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Austria Lustenau</t>
+          <t>Wolfsberger AC</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Ried</t>
+          <t>Austria Wien</t>
         </is>
       </c>
       <c r="G62">
@@ -10415,64 +10415,64 @@
         </is>
       </c>
       <c r="N62">
-        <v>2.62</v>
+        <v>2.3</v>
       </c>
       <c r="O62">
-        <v>3.18</v>
+        <v>3.2</v>
       </c>
       <c r="P62">
+        <v>2.85</v>
+      </c>
+      <c r="Q62">
+        <v>2.95</v>
+      </c>
+      <c r="R62">
+        <v>2.13</v>
+      </c>
+      <c r="S62">
+        <v>1.36</v>
+      </c>
+      <c r="T62">
+        <v>2.89</v>
+      </c>
+      <c r="U62">
         <v>2.5</v>
       </c>
-      <c r="Q62">
-        <v>3.25</v>
-      </c>
-      <c r="R62">
-        <v>2.1</v>
-      </c>
-      <c r="S62">
+      <c r="V62">
         <v>1.4</v>
       </c>
-      <c r="T62">
-        <v>2.85</v>
-      </c>
-      <c r="U62">
-        <v>2.88</v>
-      </c>
-      <c r="V62">
-        <v>1.36</v>
-      </c>
       <c r="W62">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="X62">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="Y62">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="Z62">
-        <v>3.2</v>
+        <v>3.81</v>
       </c>
       <c r="AA62">
-        <v>2.06</v>
+        <v>1.79</v>
       </c>
       <c r="AB62">
-        <v>1.76</v>
+        <v>1.88</v>
       </c>
       <c r="AC62">
-        <v>3.55</v>
+        <v>3.05</v>
       </c>
       <c r="AD62">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="AE62">
         <v>1.1</v>
       </c>
       <c r="AF62">
-        <v>1.75</v>
+        <v>1.67</v>
       </c>
       <c r="AG62">
-        <v>1.96</v>
+        <v>2.15</v>
       </c>
       <c r="AH62" t="inlineStr">
         <is>
@@ -10485,10 +10485,10 @@
         </is>
       </c>
       <c r="AJ62">
-        <v>1.43</v>
+        <v>1.3</v>
       </c>
       <c r="AK62">
-        <v>1.45</v>
+        <v>1.56</v>
       </c>
       <c r="AL62">
         <v>0</v>
@@ -11035,12 +11035,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Odd</t>
+          <t>Hødd</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Åsane</t>
+          <t>Moss</t>
         </is>
       </c>
       <c r="G66">
@@ -11067,65 +11067,65 @@
         </is>
       </c>
       <c r="N66">
-        <v>1.33</v>
+        <v>2.18</v>
       </c>
       <c r="O66">
-        <v>4.55</v>
+        <v>3.45</v>
       </c>
       <c r="P66">
-        <v>4.85</v>
+        <v>2.7</v>
       </c>
       <c r="Q66">
-        <v>1.79</v>
+        <v>2.8</v>
       </c>
       <c r="R66">
+        <v>2.5</v>
+      </c>
+      <c r="S66">
+        <v>1.2</v>
+      </c>
+      <c r="T66">
+        <v>3.9</v>
+      </c>
+      <c r="U66">
+        <v>2.1</v>
+      </c>
+      <c r="V66">
+        <v>1.67</v>
+      </c>
+      <c r="W66">
+        <v>1.15</v>
+      </c>
+      <c r="X66">
+        <v>1.02</v>
+      </c>
+      <c r="Y66">
+        <v>1.11</v>
+      </c>
+      <c r="Z66">
+        <v>5.75</v>
+      </c>
+      <c r="AA66">
+        <v>1.44</v>
+      </c>
+      <c r="AB66">
+        <v>2.63</v>
+      </c>
+      <c r="AC66">
+        <v>2</v>
+      </c>
+      <c r="AD66">
+        <v>1.7</v>
+      </c>
+      <c r="AE66">
+        <v>1.24</v>
+      </c>
+      <c r="AF66">
+        <v>1.39</v>
+      </c>
+      <c r="AG66">
         <v>2.75</v>
       </c>
-      <c r="S66">
-        <v>1.18</v>
-      </c>
-      <c r="T66">
-        <v>4.33</v>
-      </c>
-      <c r="U66">
-        <v>1.99</v>
-      </c>
-      <c r="V66">
-        <v>1.83</v>
-      </c>
-      <c r="W66">
-        <v>1.2</v>
-      </c>
-      <c r="X66">
-        <v>1.01</v>
-      </c>
-      <c r="Y66">
-        <v>1.05</v>
-      </c>
-      <c r="Z66">
-        <v>6.45</v>
-      </c>
-      <c r="AA66">
-        <v>1.3</v>
-      </c>
-      <c r="AB66">
-        <v>2.97</v>
-      </c>
-      <c r="AC66">
-        <v>1.88</v>
-      </c>
-      <c r="AD66">
-        <v>1.91</v>
-      </c>
-      <c r="AE66">
-        <v>1.3</v>
-      </c>
-      <c r="AF66">
-        <v>1.45</v>
-      </c>
-      <c r="AG66">
-        <v>2.44</v>
-      </c>
       <c r="AH66" t="inlineStr">
         <is>
           <t>[]</t>
@@ -11137,10 +11137,10 @@
         </is>
       </c>
       <c r="AJ66">
-        <v>1.09</v>
+        <v>1.25</v>
       </c>
       <c r="AK66">
-        <v>2.7</v>
+        <v>1.53</v>
       </c>
       <c r="AL66">
         <v>0</v>
@@ -11198,12 +11198,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Hødd</t>
+          <t>Odd</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Moss</t>
+          <t>Åsane</t>
         </is>
       </c>
       <c r="G67">
@@ -11230,80 +11230,80 @@
         </is>
       </c>
       <c r="N67">
-        <v>2.18</v>
+        <v>1.33</v>
       </c>
       <c r="O67">
-        <v>3.45</v>
+        <v>4.55</v>
       </c>
       <c r="P67">
+        <v>4.85</v>
+      </c>
+      <c r="Q67">
+        <v>1.79</v>
+      </c>
+      <c r="R67">
+        <v>2.75</v>
+      </c>
+      <c r="S67">
+        <v>1.18</v>
+      </c>
+      <c r="T67">
+        <v>4.33</v>
+      </c>
+      <c r="U67">
+        <v>1.99</v>
+      </c>
+      <c r="V67">
+        <v>1.83</v>
+      </c>
+      <c r="W67">
+        <v>1.2</v>
+      </c>
+      <c r="X67">
+        <v>1.01</v>
+      </c>
+      <c r="Y67">
+        <v>1.05</v>
+      </c>
+      <c r="Z67">
+        <v>6.45</v>
+      </c>
+      <c r="AA67">
+        <v>1.3</v>
+      </c>
+      <c r="AB67">
+        <v>2.97</v>
+      </c>
+      <c r="AC67">
+        <v>1.88</v>
+      </c>
+      <c r="AD67">
+        <v>1.91</v>
+      </c>
+      <c r="AE67">
+        <v>1.3</v>
+      </c>
+      <c r="AF67">
+        <v>1.45</v>
+      </c>
+      <c r="AG67">
+        <v>2.44</v>
+      </c>
+      <c r="AH67" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI67" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ67">
+        <v>1.09</v>
+      </c>
+      <c r="AK67">
         <v>2.7</v>
-      </c>
-      <c r="Q67">
-        <v>2.8</v>
-      </c>
-      <c r="R67">
-        <v>2.5</v>
-      </c>
-      <c r="S67">
-        <v>1.2</v>
-      </c>
-      <c r="T67">
-        <v>3.9</v>
-      </c>
-      <c r="U67">
-        <v>2.1</v>
-      </c>
-      <c r="V67">
-        <v>1.67</v>
-      </c>
-      <c r="W67">
-        <v>1.15</v>
-      </c>
-      <c r="X67">
-        <v>1.02</v>
-      </c>
-      <c r="Y67">
-        <v>1.11</v>
-      </c>
-      <c r="Z67">
-        <v>5.75</v>
-      </c>
-      <c r="AA67">
-        <v>1.44</v>
-      </c>
-      <c r="AB67">
-        <v>2.63</v>
-      </c>
-      <c r="AC67">
-        <v>2</v>
-      </c>
-      <c r="AD67">
-        <v>1.7</v>
-      </c>
-      <c r="AE67">
-        <v>1.24</v>
-      </c>
-      <c r="AF67">
-        <v>1.39</v>
-      </c>
-      <c r="AG67">
-        <v>2.75</v>
-      </c>
-      <c r="AH67" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI67" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ67">
-        <v>1.25</v>
-      </c>
-      <c r="AK67">
-        <v>1.53</v>
       </c>
       <c r="AL67">
         <v>0</v>
@@ -11571,40 +11571,40 @@
         <v>2.07</v>
       </c>
       <c r="S69">
-        <v>1.36</v>
+        <v>1.45</v>
       </c>
       <c r="T69">
         <v>2.55</v>
       </c>
       <c r="U69">
-        <v>2.75</v>
+        <v>2.95</v>
       </c>
       <c r="V69">
-        <v>1.4</v>
+        <v>1.35</v>
       </c>
       <c r="W69">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="X69">
         <v>1.04</v>
       </c>
       <c r="Y69">
-        <v>1.21</v>
+        <v>1.33</v>
       </c>
       <c r="Z69">
         <v>3</v>
       </c>
       <c r="AA69">
-        <v>1.7</v>
+        <v>2.11</v>
       </c>
       <c r="AB69">
         <v>1.7</v>
       </c>
       <c r="AC69">
-        <v>3.5</v>
+        <v>2.75</v>
       </c>
       <c r="AD69">
-        <v>1.24</v>
+        <v>1.38</v>
       </c>
       <c r="AE69">
         <v>1.14</v>
@@ -11626,10 +11626,10 @@
         </is>
       </c>
       <c r="AJ69">
-        <v>1.29</v>
+        <v>1.1</v>
       </c>
       <c r="AK69">
-        <v>2.19</v>
+        <v>2.2</v>
       </c>
       <c r="AL69">
         <v>0</v>
@@ -11728,22 +11728,22 @@
         <v>11.4</v>
       </c>
       <c r="Q70">
-        <v>1.83</v>
+        <v>1.81</v>
       </c>
       <c r="R70">
-        <v>2.47</v>
+        <v>2.4</v>
       </c>
       <c r="S70">
         <v>1.37</v>
       </c>
       <c r="T70">
-        <v>2.99</v>
+        <v>3.02</v>
       </c>
       <c r="U70">
-        <v>2.88</v>
+        <v>2.77</v>
       </c>
       <c r="V70">
-        <v>1.39</v>
+        <v>1.42</v>
       </c>
       <c r="W70">
         <v>1.07</v>
@@ -11755,28 +11755,28 @@
         <v>1.3</v>
       </c>
       <c r="Z70">
-        <v>3.44</v>
+        <v>3.49</v>
       </c>
       <c r="AA70">
+        <v>1.96</v>
+      </c>
+      <c r="AB70">
         <v>1.93</v>
-      </c>
-      <c r="AB70">
-        <v>1.9</v>
       </c>
       <c r="AC70">
         <v>3.16</v>
       </c>
       <c r="AD70">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="AE70">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="AF70">
-        <v>2.25</v>
+        <v>2.27</v>
       </c>
       <c r="AG70">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="AH70" t="inlineStr">
         <is>
@@ -11789,10 +11789,10 @@
         </is>
       </c>
       <c r="AJ70">
-        <v>1.12</v>
+        <v>1.2</v>
       </c>
       <c r="AK70">
-        <v>3.3</v>
+        <v>3.36</v>
       </c>
       <c r="AL70">
         <v>0</v>
@@ -11882,25 +11882,25 @@
         </is>
       </c>
       <c r="N71">
-        <v>2.42</v>
+        <v>2.41</v>
       </c>
       <c r="O71">
-        <v>3.16</v>
+        <v>3.15</v>
       </c>
       <c r="P71">
-        <v>2.42</v>
+        <v>2.44</v>
       </c>
       <c r="Q71">
-        <v>3.12</v>
+        <v>3</v>
       </c>
       <c r="R71">
-        <v>2.15</v>
+        <v>2.25</v>
       </c>
       <c r="S71">
         <v>1.3</v>
       </c>
       <c r="T71">
-        <v>3.04</v>
+        <v>2.97</v>
       </c>
       <c r="U71">
         <v>2.47</v>
@@ -11921,25 +11921,25 @@
         <v>3.84</v>
       </c>
       <c r="AA71">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="AB71">
         <v>2.01</v>
       </c>
       <c r="AC71">
-        <v>2.7</v>
+        <v>2.66</v>
       </c>
       <c r="AD71">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="AE71">
         <v>1.11</v>
       </c>
       <c r="AF71">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="AG71">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="AH71" t="inlineStr">
         <is>
@@ -11952,10 +11952,10 @@
         </is>
       </c>
       <c r="AJ71">
-        <v>1.3</v>
+        <v>1.41</v>
       </c>
       <c r="AK71">
-        <v>1.4</v>
+        <v>1.43</v>
       </c>
       <c r="AL71">
         <v>0</v>
@@ -12208,13 +12208,13 @@
         </is>
       </c>
       <c r="N73">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="O73">
-        <v>2.85</v>
+        <v>2.9</v>
       </c>
       <c r="P73">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="Q73">
         <v>2.8</v>
@@ -12226,46 +12226,46 @@
         <v>1.5</v>
       </c>
       <c r="T73">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="U73">
         <v>3.42</v>
       </c>
       <c r="V73">
-        <v>1.22</v>
+        <v>1.28</v>
       </c>
       <c r="W73">
         <v>1.02</v>
       </c>
       <c r="X73">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="Y73">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="Z73">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="AA73">
-        <v>2.59</v>
+        <v>2.43</v>
       </c>
       <c r="AB73">
         <v>1.48</v>
       </c>
       <c r="AC73">
-        <v>4.75</v>
+        <v>5.25</v>
       </c>
       <c r="AD73">
-        <v>1.12</v>
+        <v>1.15</v>
       </c>
       <c r="AE73">
         <v>1.04</v>
       </c>
       <c r="AF73">
-        <v>2.08</v>
+        <v>2.09</v>
       </c>
       <c r="AG73">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="AH73" t="inlineStr">
         <is>
@@ -12281,7 +12281,7 @@
         <v>1.23</v>
       </c>
       <c r="AK73">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="AL73">
         <v>0</v>
@@ -12374,19 +12374,19 @@
         <v>2.3</v>
       </c>
       <c r="O74">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="P74">
-        <v>2.6</v>
+        <v>2.7</v>
       </c>
       <c r="Q74">
-        <v>3.09</v>
+        <v>2.88</v>
       </c>
       <c r="R74">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="S74">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="T74">
         <v>2.99</v>
@@ -12401,34 +12401,34 @@
         <v>1.1</v>
       </c>
       <c r="X74">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="Y74">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="Z74">
-        <v>3.68</v>
+        <v>3.6</v>
       </c>
       <c r="AA74">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="AB74">
-        <v>2</v>
+        <v>1.93</v>
       </c>
       <c r="AC74">
-        <v>3.1</v>
+        <v>3.18</v>
       </c>
       <c r="AD74">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="AE74">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="AF74">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="AG74">
-        <v>2.18</v>
+        <v>2.15</v>
       </c>
       <c r="AH74" t="inlineStr">
         <is>
@@ -12534,37 +12534,37 @@
         </is>
       </c>
       <c r="N75">
-        <v>2.75</v>
+        <v>2.78</v>
       </c>
       <c r="O75">
-        <v>3.25</v>
+        <v>3.24</v>
       </c>
       <c r="P75">
-        <v>2.25</v>
+        <v>2.43</v>
       </c>
       <c r="Q75">
         <v>3.54</v>
       </c>
       <c r="R75">
-        <v>2.12</v>
+        <v>2.04</v>
       </c>
       <c r="S75">
         <v>1.36</v>
       </c>
       <c r="T75">
-        <v>2.85</v>
+        <v>2.9</v>
       </c>
       <c r="U75">
-        <v>2.85</v>
+        <v>2.8</v>
       </c>
       <c r="V75">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="W75">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="X75">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y75">
         <v>1.27</v>
@@ -12573,25 +12573,25 @@
         <v>3.14</v>
       </c>
       <c r="AA75">
-        <v>1.97</v>
+        <v>2</v>
       </c>
       <c r="AB75">
-        <v>1.79</v>
+        <v>1.83</v>
       </c>
       <c r="AC75">
-        <v>3.34</v>
+        <v>3.4</v>
       </c>
       <c r="AD75">
-        <v>1.24</v>
+        <v>1.3</v>
       </c>
       <c r="AE75">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="AF75">
         <v>1.75</v>
       </c>
       <c r="AG75">
-        <v>1.97</v>
+        <v>2.05</v>
       </c>
       <c r="AH75" t="inlineStr">
         <is>
@@ -12604,10 +12604,10 @@
         </is>
       </c>
       <c r="AJ75">
-        <v>1.27</v>
+        <v>1.33</v>
       </c>
       <c r="AK75">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="AL75">
         <v>0</v>
@@ -12697,13 +12697,13 @@
         </is>
       </c>
       <c r="N76">
-        <v>2.19</v>
+        <v>2.17</v>
       </c>
       <c r="O76">
-        <v>3.52</v>
+        <v>3.5</v>
       </c>
       <c r="P76">
-        <v>3.07</v>
+        <v>3</v>
       </c>
       <c r="Q76">
         <v>2.81</v>
@@ -12715,7 +12715,7 @@
         <v>1.33</v>
       </c>
       <c r="T76">
-        <v>2.95</v>
+        <v>2.78</v>
       </c>
       <c r="U76">
         <v>2.62</v>
@@ -12727,31 +12727,31 @@
         <v>1.11</v>
       </c>
       <c r="X76">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="Y76">
-        <v>1.21</v>
+        <v>1.24</v>
       </c>
       <c r="Z76">
         <v>3.7</v>
       </c>
       <c r="AA76">
-        <v>1.72</v>
+        <v>1.8</v>
       </c>
       <c r="AB76">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="AC76">
-        <v>2.97</v>
+        <v>2.85</v>
       </c>
       <c r="AD76">
         <v>1.33</v>
       </c>
       <c r="AE76">
-        <v>1.13</v>
+        <v>1.08</v>
       </c>
       <c r="AF76">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="AG76">
         <v>2.15</v>
@@ -12767,10 +12767,10 @@
         </is>
       </c>
       <c r="AJ76">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AK76">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="AL76">
         <v>0</v>
@@ -12869,40 +12869,40 @@
         <v>3.24</v>
       </c>
       <c r="Q77">
-        <v>2.88</v>
+        <v>3.08</v>
       </c>
       <c r="R77">
-        <v>2.04</v>
+        <v>2.05</v>
       </c>
       <c r="S77">
-        <v>1.47</v>
+        <v>1.42</v>
       </c>
       <c r="T77">
-        <v>2.58</v>
+        <v>2.39</v>
       </c>
       <c r="U77">
         <v>2.9</v>
       </c>
       <c r="V77">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="W77">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="X77">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="Y77">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="Z77">
-        <v>2.62</v>
+        <v>2.75</v>
       </c>
       <c r="AA77">
-        <v>2.35</v>
+        <v>2.29</v>
       </c>
       <c r="AB77">
-        <v>1.57</v>
+        <v>1.59</v>
       </c>
       <c r="AC77">
         <v>4.38</v>
@@ -12911,13 +12911,13 @@
         <v>1.16</v>
       </c>
       <c r="AE77">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="AF77">
-        <v>1.95</v>
+        <v>1.93</v>
       </c>
       <c r="AG77">
-        <v>1.76</v>
+        <v>1.78</v>
       </c>
       <c r="AH77" t="inlineStr">
         <is>
@@ -12930,10 +12930,10 @@
         </is>
       </c>
       <c r="AJ77">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="AK77">
-        <v>1.56</v>
+        <v>1.59</v>
       </c>
       <c r="AL77">
         <v>0</v>
@@ -13044,13 +13044,13 @@
         <v>2.6</v>
       </c>
       <c r="U78">
-        <v>2.92</v>
+        <v>3</v>
       </c>
       <c r="V78">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="W78">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="X78">
         <v>1.01</v>
@@ -13080,7 +13080,7 @@
         <v>1.78</v>
       </c>
       <c r="AG78">
-        <v>1.86</v>
+        <v>1.89</v>
       </c>
       <c r="AH78" t="inlineStr">
         <is>
@@ -13675,19 +13675,19 @@
         </is>
       </c>
       <c r="N82">
-        <v>3.78</v>
+        <v>3.1</v>
       </c>
       <c r="O82">
-        <v>3.74</v>
+        <v>3.4</v>
       </c>
       <c r="P82">
-        <v>1.76</v>
+        <v>1.98</v>
       </c>
       <c r="Q82">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="R82">
-        <v>2.24</v>
+        <v>2.38</v>
       </c>
       <c r="S82">
         <v>1.27</v>
@@ -13696,10 +13696,10 @@
         <v>3.25</v>
       </c>
       <c r="U82">
-        <v>2.4</v>
+        <v>2.2</v>
       </c>
       <c r="V82">
-        <v>1.54</v>
+        <v>1.51</v>
       </c>
       <c r="W82">
         <v>1.12</v>
@@ -13711,28 +13711,28 @@
         <v>1.14</v>
       </c>
       <c r="Z82">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="AA82">
-        <v>1.61</v>
+        <v>1.55</v>
       </c>
       <c r="AB82">
         <v>2.17</v>
       </c>
       <c r="AC82">
-        <v>2.44</v>
+        <v>2.39</v>
       </c>
       <c r="AD82">
         <v>1.49</v>
       </c>
       <c r="AE82">
-        <v>1.17</v>
+        <v>1.19</v>
       </c>
       <c r="AF82">
         <v>1.5</v>
       </c>
       <c r="AG82">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="AH82" t="inlineStr">
         <is>
@@ -13745,10 +13745,10 @@
         </is>
       </c>
       <c r="AJ82">
-        <v>1.18</v>
+        <v>1.25</v>
       </c>
       <c r="AK82">
-        <v>1.22</v>
+        <v>1.27</v>
       </c>
       <c r="AL82">
         <v>0</v>
@@ -13838,52 +13838,52 @@
         </is>
       </c>
       <c r="N83">
-        <v>1.37</v>
+        <v>1.46</v>
       </c>
       <c r="O83">
         <v>4.4</v>
       </c>
       <c r="P83">
-        <v>6.3</v>
+        <v>5.3</v>
       </c>
       <c r="Q83">
-        <v>1.91</v>
+        <v>1.83</v>
       </c>
       <c r="R83">
-        <v>2.43</v>
+        <v>2.5</v>
       </c>
       <c r="S83">
         <v>1.25</v>
       </c>
       <c r="T83">
-        <v>3.55</v>
+        <v>3.45</v>
       </c>
       <c r="U83">
-        <v>2.24</v>
+        <v>2.25</v>
       </c>
       <c r="V83">
-        <v>1.56</v>
+        <v>1.6</v>
       </c>
       <c r="W83">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="X83">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y83">
         <v>1.14</v>
       </c>
       <c r="Z83">
-        <v>4.5</v>
+        <v>4.45</v>
       </c>
       <c r="AA83">
-        <v>1.51</v>
+        <v>1.49</v>
       </c>
       <c r="AB83">
-        <v>2.38</v>
+        <v>2.35</v>
       </c>
       <c r="AC83">
-        <v>2.34</v>
+        <v>2.4</v>
       </c>
       <c r="AD83">
         <v>1.53</v>
@@ -13892,10 +13892,10 @@
         <v>1.19</v>
       </c>
       <c r="AF83">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="AG83">
-        <v>2.06</v>
+        <v>2.1</v>
       </c>
       <c r="AH83" t="inlineStr">
         <is>
@@ -13908,10 +13908,10 @@
         </is>
       </c>
       <c r="AJ83">
-        <v>1.13</v>
+        <v>1.08</v>
       </c>
       <c r="AK83">
-        <v>2.46</v>
+        <v>2.41</v>
       </c>
       <c r="AL83">
         <v>0</v>
@@ -14327,31 +14327,31 @@
         </is>
       </c>
       <c r="N86">
-        <v>5.87</v>
+        <v>3.8</v>
       </c>
       <c r="O86">
+        <v>3.8</v>
+      </c>
+      <c r="P86">
+        <v>1.65</v>
+      </c>
+      <c r="Q86">
         <v>4.6</v>
       </c>
-      <c r="P86">
-        <v>1.49</v>
-      </c>
-      <c r="Q86">
-        <v>4.43</v>
-      </c>
       <c r="R86">
-        <v>2.39</v>
+        <v>2.48</v>
       </c>
       <c r="S86">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="T86">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="U86">
-        <v>2.29</v>
+        <v>2.31</v>
       </c>
       <c r="V86">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="W86">
         <v>1.11</v>
@@ -14360,31 +14360,31 @@
         <v>1.01</v>
       </c>
       <c r="Y86">
-        <v>1.12</v>
+        <v>1.2</v>
       </c>
       <c r="Z86">
-        <v>4.8</v>
+        <v>4.33</v>
       </c>
       <c r="AA86">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="AB86">
         <v>2.4</v>
       </c>
       <c r="AC86">
-        <v>2.38</v>
+        <v>2.42</v>
       </c>
       <c r="AD86">
+        <v>1.54</v>
+      </c>
+      <c r="AE86">
+        <v>1.16</v>
+      </c>
+      <c r="AF86">
         <v>1.56</v>
       </c>
-      <c r="AE86">
-        <v>1.18</v>
-      </c>
-      <c r="AF86">
-        <v>1.57</v>
-      </c>
       <c r="AG86">
-        <v>2.26</v>
+        <v>2.1</v>
       </c>
       <c r="AH86" t="inlineStr">
         <is>
@@ -14397,10 +14397,10 @@
         </is>
       </c>
       <c r="AJ86">
-        <v>1.2</v>
+        <v>2.15</v>
       </c>
       <c r="AK86">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="AL86">
         <v>0</v>
@@ -14493,61 +14493,61 @@
         <v>1.22</v>
       </c>
       <c r="O87">
-        <v>5.4</v>
+        <v>4.6</v>
       </c>
       <c r="P87">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="Q87">
         <v>1.73</v>
       </c>
       <c r="R87">
-        <v>2.5</v>
+        <v>2.34</v>
       </c>
       <c r="S87">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="T87">
-        <v>3.05</v>
+        <v>2.98</v>
       </c>
       <c r="U87">
-        <v>2.5</v>
+        <v>2.62</v>
       </c>
       <c r="V87">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="W87">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="X87">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="Y87">
-        <v>1.19</v>
+        <v>1.27</v>
       </c>
       <c r="Z87">
-        <v>3.74</v>
+        <v>3.7</v>
       </c>
       <c r="AA87">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="AB87">
         <v>2</v>
       </c>
       <c r="AC87">
-        <v>2.89</v>
+        <v>3.1</v>
       </c>
       <c r="AD87">
-        <v>1.38</v>
+        <v>1.3</v>
       </c>
       <c r="AE87">
-        <v>1.13</v>
+        <v>1.08</v>
       </c>
       <c r="AF87">
-        <v>2.3</v>
+        <v>2.15</v>
       </c>
       <c r="AG87">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="AH87" t="inlineStr">
         <is>
@@ -14560,10 +14560,10 @@
         </is>
       </c>
       <c r="AJ87">
-        <v>1.13</v>
+        <v>1.05</v>
       </c>
       <c r="AK87">
-        <v>3.5</v>
+        <v>3.24</v>
       </c>
       <c r="AL87">
         <v>0</v>
@@ -15305,22 +15305,22 @@
         </is>
       </c>
       <c r="N92">
-        <v>3.3</v>
+        <v>4</v>
       </c>
       <c r="O92">
         <v>3.2</v>
       </c>
       <c r="P92">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="Q92">
-        <v>4</v>
+        <v>3.75</v>
       </c>
       <c r="R92">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="S92">
-        <v>1.36</v>
+        <v>1.42</v>
       </c>
       <c r="T92">
         <v>2.9</v>
@@ -15341,25 +15341,25 @@
         <v>1.22</v>
       </c>
       <c r="Z92">
-        <v>3.5</v>
+        <v>3.35</v>
       </c>
       <c r="AA92">
         <v>1.85</v>
       </c>
       <c r="AB92">
-        <v>1.83</v>
+        <v>1.87</v>
       </c>
       <c r="AC92">
         <v>3.3</v>
       </c>
       <c r="AD92">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AE92">
         <v>1.09</v>
       </c>
       <c r="AF92">
-        <v>1.7</v>
+        <v>1.65</v>
       </c>
       <c r="AG92">
         <v>2.11</v>
@@ -15375,10 +15375,10 @@
         </is>
       </c>
       <c r="AJ92">
+        <v>1.33</v>
+      </c>
+      <c r="AK92">
         <v>1.29</v>
-      </c>
-      <c r="AK92">
-        <v>1.22</v>
       </c>
       <c r="AL92">
         <v>0</v>
@@ -15631,22 +15631,22 @@
         </is>
       </c>
       <c r="N94">
-        <v>1.97</v>
+        <v>1.75</v>
       </c>
       <c r="O94">
-        <v>3.44</v>
+        <v>3.55</v>
       </c>
       <c r="P94">
-        <v>3.72</v>
+        <v>4.3</v>
       </c>
       <c r="Q94">
         <v>2.4</v>
       </c>
       <c r="R94">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="S94">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="T94">
         <v>2.75</v>
@@ -15658,22 +15658,22 @@
         <v>1.37</v>
       </c>
       <c r="W94">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="X94">
         <v>1.01</v>
       </c>
       <c r="Y94">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="Z94">
-        <v>3.39</v>
+        <v>3.25</v>
       </c>
       <c r="AA94">
-        <v>1.96</v>
+        <v>1.92</v>
       </c>
       <c r="AB94">
-        <v>1.77</v>
+        <v>1.8</v>
       </c>
       <c r="AC94">
         <v>3.5</v>
@@ -15682,7 +15682,7 @@
         <v>1.25</v>
       </c>
       <c r="AE94">
-        <v>1.06</v>
+        <v>1.09</v>
       </c>
       <c r="AF94">
         <v>1.84</v>
@@ -15704,7 +15704,7 @@
         <v>1.27</v>
       </c>
       <c r="AK94">
-        <v>1.97</v>
+        <v>1.95</v>
       </c>
       <c r="AL94">
         <v>0</v>
@@ -16292,22 +16292,22 @@
         <v>2.5</v>
       </c>
       <c r="Q98">
-        <v>3.2</v>
+        <v>3.13</v>
       </c>
       <c r="R98">
         <v>2.2</v>
       </c>
       <c r="S98">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="T98">
-        <v>2.86</v>
+        <v>2.9</v>
       </c>
       <c r="U98">
-        <v>2.63</v>
+        <v>2.57</v>
       </c>
       <c r="V98">
-        <v>1.48</v>
+        <v>1.46</v>
       </c>
       <c r="W98">
         <v>1.1</v>
@@ -16322,25 +16322,25 @@
         <v>3.76</v>
       </c>
       <c r="AA98">
-        <v>1.81</v>
+        <v>1.71</v>
       </c>
       <c r="AB98">
-        <v>1.86</v>
+        <v>2.02</v>
       </c>
       <c r="AC98">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="AD98">
-        <v>1.41</v>
+        <v>1.39</v>
       </c>
       <c r="AE98">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="AF98">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="AG98">
-        <v>2.23</v>
+        <v>2.27</v>
       </c>
       <c r="AH98" t="inlineStr">
         <is>
@@ -16356,7 +16356,7 @@
         <v>1.42</v>
       </c>
       <c r="AK98">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AL98">
         <v>0</v>
@@ -16446,19 +16446,19 @@
         </is>
       </c>
       <c r="N99">
-        <v>3.5</v>
+        <v>3.7</v>
       </c>
       <c r="O99">
-        <v>3.67</v>
+        <v>3.64</v>
       </c>
       <c r="P99">
-        <v>2.19</v>
+        <v>1.93</v>
       </c>
       <c r="Q99">
-        <v>3.76</v>
+        <v>4.33</v>
       </c>
       <c r="R99">
-        <v>2.29</v>
+        <v>2.08</v>
       </c>
       <c r="S99">
         <v>1.38</v>
@@ -16467,7 +16467,7 @@
         <v>2.93</v>
       </c>
       <c r="U99">
-        <v>2.79</v>
+        <v>2.77</v>
       </c>
       <c r="V99">
         <v>1.41</v>
@@ -16476,34 +16476,34 @@
         <v>1.07</v>
       </c>
       <c r="X99">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y99">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="Z99">
-        <v>3.5</v>
+        <v>3.42</v>
       </c>
       <c r="AA99">
         <v>1.91</v>
       </c>
       <c r="AB99">
-        <v>1.93</v>
+        <v>1.97</v>
       </c>
       <c r="AC99">
-        <v>3.18</v>
+        <v>3.24</v>
       </c>
       <c r="AD99">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="AE99">
         <v>1.08</v>
       </c>
       <c r="AF99">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="AG99">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="AH99" t="inlineStr">
         <is>
@@ -16519,7 +16519,7 @@
         <v>1.31</v>
       </c>
       <c r="AK99">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="AL99">
         <v>0</v>
@@ -16784,52 +16784,52 @@
         <v>3.1</v>
       </c>
       <c r="R101">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="S101">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="T101">
-        <v>2.77</v>
+        <v>2.7</v>
       </c>
       <c r="U101">
-        <v>2.78</v>
+        <v>2.82</v>
       </c>
       <c r="V101">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="W101">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="X101">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="Y101">
+        <v>1.33</v>
+      </c>
+      <c r="Z101">
+        <v>3.1</v>
+      </c>
+      <c r="AA101">
+        <v>1.92</v>
+      </c>
+      <c r="AB101">
+        <v>1.79</v>
+      </c>
+      <c r="AC101">
+        <v>3.28</v>
+      </c>
+      <c r="AD101">
         <v>1.25</v>
       </c>
-      <c r="Z101">
-        <v>3.28</v>
-      </c>
-      <c r="AA101">
-        <v>1.89</v>
-      </c>
-      <c r="AB101">
-        <v>1.81</v>
-      </c>
-      <c r="AC101">
-        <v>3.2</v>
-      </c>
-      <c r="AD101">
-        <v>1.26</v>
-      </c>
       <c r="AE101">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="AF101">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="AG101">
-        <v>2.04</v>
+        <v>2.01</v>
       </c>
       <c r="AH101" t="inlineStr">
         <is>
@@ -16842,7 +16842,7 @@
         </is>
       </c>
       <c r="AJ101">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="AK101">
         <v>1.43</v>
@@ -16953,13 +16953,13 @@
         <v>1.28</v>
       </c>
       <c r="T102">
-        <v>3.15</v>
+        <v>3.6</v>
       </c>
       <c r="U102">
-        <v>2.4</v>
+        <v>2.36</v>
       </c>
       <c r="V102">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="W102">
         <v>1.08</v>
@@ -16974,10 +16974,10 @@
         <v>4</v>
       </c>
       <c r="AA102">
-        <v>1.6</v>
+        <v>1.67</v>
       </c>
       <c r="AB102">
-        <v>2.19</v>
+        <v>2.17</v>
       </c>
       <c r="AC102">
         <v>2.62</v>
@@ -16989,7 +16989,7 @@
         <v>1.14</v>
       </c>
       <c r="AF102">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="AG102">
         <v>1.95</v>
@@ -17005,7 +17005,7 @@
         </is>
       </c>
       <c r="AJ102">
-        <v>1.1</v>
+        <v>1.06</v>
       </c>
       <c r="AK102">
         <v>2.7</v>
@@ -17750,16 +17750,16 @@
         </is>
       </c>
       <c r="N107">
-        <v>2.5</v>
+        <v>2.35</v>
       </c>
       <c r="O107">
         <v>3.15</v>
       </c>
       <c r="P107">
-        <v>2.7</v>
+        <v>2.8</v>
       </c>
       <c r="Q107">
-        <v>3.14</v>
+        <v>3.03</v>
       </c>
       <c r="R107">
         <v>2.05</v>
@@ -17768,46 +17768,46 @@
         <v>1.36</v>
       </c>
       <c r="T107">
-        <v>2.85</v>
+        <v>2.84</v>
       </c>
       <c r="U107">
-        <v>2.62</v>
+        <v>2.8</v>
       </c>
       <c r="V107">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="W107">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="X107">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y107">
+        <v>1.28</v>
+      </c>
+      <c r="Z107">
+        <v>3.49</v>
+      </c>
+      <c r="AA107">
+        <v>1.88</v>
+      </c>
+      <c r="AB107">
+        <v>1.88</v>
+      </c>
+      <c r="AC107">
+        <v>3.4</v>
+      </c>
+      <c r="AD107">
         <v>1.29</v>
       </c>
-      <c r="Z107">
-        <v>3.45</v>
-      </c>
-      <c r="AA107">
-        <v>1.96</v>
-      </c>
-      <c r="AB107">
-        <v>1.8</v>
-      </c>
-      <c r="AC107">
-        <v>2.97</v>
-      </c>
-      <c r="AD107">
-        <v>1.3</v>
-      </c>
       <c r="AE107">
-        <v>1.07</v>
+        <v>1.11</v>
       </c>
       <c r="AF107">
-        <v>1.74</v>
+        <v>1.66</v>
       </c>
       <c r="AG107">
-        <v>1.92</v>
+        <v>2.09</v>
       </c>
       <c r="AH107" t="inlineStr">
         <is>
@@ -17820,10 +17820,10 @@
         </is>
       </c>
       <c r="AJ107">
-        <v>1.41</v>
+        <v>1.39</v>
       </c>
       <c r="AK107">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="AL107">
         <v>0</v>
@@ -18076,13 +18076,13 @@
         </is>
       </c>
       <c r="N109">
-        <v>2.1</v>
+        <v>2.04</v>
       </c>
       <c r="O109">
-        <v>3.2</v>
+        <v>3.16</v>
       </c>
       <c r="P109">
-        <v>3.52</v>
+        <v>3.39</v>
       </c>
       <c r="Q109">
         <v>0</v>
@@ -18239,13 +18239,13 @@
         </is>
       </c>
       <c r="N110">
-        <v>3.81</v>
+        <v>3.8</v>
       </c>
       <c r="O110">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="P110">
-        <v>2</v>
+        <v>1.92</v>
       </c>
       <c r="Q110">
         <v>0</v>
@@ -18402,13 +18402,13 @@
         </is>
       </c>
       <c r="N111">
-        <v>1.99</v>
+        <v>1.91</v>
       </c>
       <c r="O111">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="P111">
-        <v>3.82</v>
+        <v>3.8</v>
       </c>
       <c r="Q111">
         <v>0</v>
@@ -18565,13 +18565,13 @@
         </is>
       </c>
       <c r="N112">
-        <v>1.99</v>
+        <v>1.94</v>
       </c>
       <c r="O112">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="P112">
-        <v>3.82</v>
+        <v>3.76</v>
       </c>
       <c r="Q112">
         <v>0</v>
@@ -18891,80 +18891,80 @@
         </is>
       </c>
       <c r="N114">
-        <v>1.51</v>
+        <v>1.61</v>
       </c>
       <c r="O114">
-        <v>4.05</v>
+        <v>3.6</v>
       </c>
       <c r="P114">
-        <v>5.27</v>
+        <v>4.1</v>
       </c>
       <c r="Q114">
-        <v>2.1</v>
+        <v>2.17</v>
       </c>
       <c r="R114">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="S114">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="T114">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="U114">
         <v>2.5</v>
       </c>
       <c r="V114">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="W114">
         <v>1.1</v>
       </c>
       <c r="X114">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y114">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="Z114">
         <v>4</v>
       </c>
       <c r="AA114">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="AB114">
-        <v>2.1</v>
+        <v>2.03</v>
       </c>
       <c r="AC114">
-        <v>2.59</v>
+        <v>2.66</v>
       </c>
       <c r="AD114">
         <v>1.42</v>
       </c>
       <c r="AE114">
+        <v>1.13</v>
+      </c>
+      <c r="AF114">
+        <v>1.68</v>
+      </c>
+      <c r="AG114">
+        <v>2.01</v>
+      </c>
+      <c r="AH114" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI114" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ114">
         <v>1.11</v>
       </c>
-      <c r="AF114">
-        <v>1.71</v>
-      </c>
-      <c r="AG114">
-        <v>2</v>
-      </c>
-      <c r="AH114" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI114" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ114">
-        <v>1.1</v>
-      </c>
       <c r="AK114">
-        <v>2.4</v>
+        <v>2.1</v>
       </c>
       <c r="AL114">
         <v>0</v>
@@ -19054,19 +19054,19 @@
         </is>
       </c>
       <c r="N115">
-        <v>6.11</v>
+        <v>4.35</v>
       </c>
       <c r="O115">
-        <v>4.15</v>
+        <v>3.65</v>
       </c>
       <c r="P115">
-        <v>1.44</v>
+        <v>1.63</v>
       </c>
       <c r="Q115">
-        <v>5.15</v>
+        <v>5</v>
       </c>
       <c r="R115">
-        <v>2.3</v>
+        <v>2.18</v>
       </c>
       <c r="S115">
         <v>1.33</v>
@@ -19084,34 +19084,34 @@
         <v>1.1</v>
       </c>
       <c r="X115">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="Y115">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="Z115">
-        <v>3.74</v>
+        <v>3.5</v>
       </c>
       <c r="AA115">
         <v>1.79</v>
       </c>
       <c r="AB115">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="AC115">
-        <v>2.96</v>
+        <v>3.01</v>
       </c>
       <c r="AD115">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="AE115">
         <v>1.1</v>
       </c>
       <c r="AF115">
-        <v>1.78</v>
+        <v>1.75</v>
       </c>
       <c r="AG115">
-        <v>1.88</v>
+        <v>1.95</v>
       </c>
       <c r="AH115" t="inlineStr">
         <is>
@@ -19124,10 +19124,10 @@
         </is>
       </c>
       <c r="AJ115">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="AK115">
-        <v>1.09</v>
+        <v>1.13</v>
       </c>
       <c r="AL115">
         <v>0</v>
@@ -19217,52 +19217,52 @@
         </is>
       </c>
       <c r="N116">
-        <v>1.88</v>
+        <v>1.83</v>
       </c>
       <c r="O116">
-        <v>3.52</v>
+        <v>3.3</v>
       </c>
       <c r="P116">
-        <v>3.88</v>
+        <v>3.65</v>
       </c>
       <c r="Q116">
-        <v>2.5</v>
+        <v>2.54</v>
       </c>
       <c r="R116">
         <v>2.3</v>
       </c>
       <c r="S116">
-        <v>1.37</v>
+        <v>1.34</v>
       </c>
       <c r="T116">
-        <v>3</v>
+        <v>2.88</v>
       </c>
       <c r="U116">
-        <v>2.62</v>
+        <v>2.66</v>
       </c>
       <c r="V116">
         <v>1.41</v>
       </c>
       <c r="W116">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="X116">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="Y116">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="Z116">
-        <v>3.76</v>
+        <v>3.75</v>
       </c>
       <c r="AA116">
-        <v>1.79</v>
+        <v>1.87</v>
       </c>
       <c r="AB116">
-        <v>1.92</v>
+        <v>1.97</v>
       </c>
       <c r="AC116">
-        <v>2.88</v>
+        <v>3.1</v>
       </c>
       <c r="AD116">
         <v>1.32</v>
@@ -19287,10 +19287,10 @@
         </is>
       </c>
       <c r="AJ116">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="AK116">
-        <v>1.82</v>
+        <v>1.85</v>
       </c>
       <c r="AL116">
         <v>0</v>
@@ -19413,31 +19413,31 @@
         <v>1.01</v>
       </c>
       <c r="Y117">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="Z117">
-        <v>4.33</v>
+        <v>4.2</v>
       </c>
       <c r="AA117">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="AB117">
         <v>2.25</v>
       </c>
       <c r="AC117">
-        <v>2.5</v>
+        <v>2.43</v>
       </c>
       <c r="AD117">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="AE117">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="AF117">
         <v>1.7</v>
       </c>
       <c r="AG117">
-        <v>2</v>
+        <v>2.01</v>
       </c>
       <c r="AH117" t="inlineStr">
         <is>
@@ -19450,10 +19450,10 @@
         </is>
       </c>
       <c r="AJ117">
-        <v>1.2</v>
+        <v>1.11</v>
       </c>
       <c r="AK117">
-        <v>2.5</v>
+        <v>2.33</v>
       </c>
       <c r="AL117">
         <v>0</v>
@@ -19543,64 +19543,64 @@
         </is>
       </c>
       <c r="N118">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="O118">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="P118">
-        <v>13.8</v>
+        <v>8.5</v>
       </c>
       <c r="Q118">
-        <v>1.57</v>
+        <v>1.64</v>
       </c>
       <c r="R118">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="S118">
-        <v>1.3</v>
+        <v>1.34</v>
       </c>
       <c r="T118">
         <v>3.1</v>
       </c>
       <c r="U118">
-        <v>2.47</v>
+        <v>2.56</v>
       </c>
       <c r="V118">
         <v>1.44</v>
       </c>
       <c r="W118">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="X118">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y118">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="Z118">
-        <v>4.1</v>
+        <v>3.65</v>
       </c>
       <c r="AA118">
-        <v>1.9</v>
+        <v>1.78</v>
       </c>
       <c r="AB118">
-        <v>1.9</v>
+        <v>1.98</v>
       </c>
       <c r="AC118">
-        <v>2.62</v>
+        <v>2.97</v>
       </c>
       <c r="AD118">
-        <v>1.38</v>
+        <v>1.35</v>
       </c>
       <c r="AE118">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="AF118">
         <v>2.45</v>
       </c>
       <c r="AG118">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="AH118" t="inlineStr">
         <is>
@@ -19613,10 +19613,10 @@
         </is>
       </c>
       <c r="AJ118">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="AK118">
-        <v>4.33</v>
+        <v>3.88</v>
       </c>
       <c r="AL118">
         <v>0</v>
@@ -20195,52 +20195,52 @@
         </is>
       </c>
       <c r="N122">
-        <v>2.16</v>
+        <v>1.95</v>
       </c>
       <c r="O122">
-        <v>3.24</v>
+        <v>3.25</v>
       </c>
       <c r="P122">
-        <v>3.32</v>
+        <v>3.3</v>
       </c>
       <c r="Q122">
         <v>2.55</v>
       </c>
       <c r="R122">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="S122">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="T122">
-        <v>2.59</v>
+        <v>2.56</v>
       </c>
       <c r="U122">
-        <v>2.73</v>
+        <v>2.9</v>
       </c>
       <c r="V122">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="W122">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="X122">
         <v>1.06</v>
       </c>
       <c r="Y122">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="Z122">
-        <v>2.97</v>
+        <v>2.92</v>
       </c>
       <c r="AA122">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="AB122">
-        <v>1.72</v>
+        <v>1.7</v>
       </c>
       <c r="AC122">
-        <v>3.65</v>
+        <v>3.42</v>
       </c>
       <c r="AD122">
         <v>1.28</v>
@@ -20252,7 +20252,7 @@
         <v>1.83</v>
       </c>
       <c r="AG122">
-        <v>1.88</v>
+        <v>1.8</v>
       </c>
       <c r="AH122" t="inlineStr">
         <is>
@@ -20268,7 +20268,7 @@
         <v>1.25</v>
       </c>
       <c r="AK122">
-        <v>1.72</v>
+        <v>1.7</v>
       </c>
       <c r="AL122">
         <v>0</v>

--- a/jogos_2026-08-02.xlsx
+++ b/jogos_2026-08-02.xlsx
@@ -340,7 +340,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AU140"/>
+  <dimension ref="A1:AU138"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -751,7 +751,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>01:30</t>
+          <t>01:00</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -766,12 +766,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Sydney United</t>
+          <t>Sydney Olympic</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>NWS Spirit</t>
+          <t>APIA Leichhardt Tigers</t>
         </is>
       </c>
       <c r="G3">
@@ -798,64 +798,64 @@
         </is>
       </c>
       <c r="N3">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="O3">
-        <v>0</v>
+        <v>4.95</v>
       </c>
       <c r="P3">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Q3">
-        <v>2.53</v>
+        <v>5.2</v>
       </c>
       <c r="R3">
-        <v>2.25</v>
+        <v>2.43</v>
       </c>
       <c r="S3">
-        <v>1.3</v>
+        <v>1.22</v>
       </c>
       <c r="T3">
-        <v>2.97</v>
+        <v>3.5</v>
       </c>
       <c r="U3">
-        <v>2.5</v>
+        <v>2.07</v>
       </c>
       <c r="V3">
-        <v>1.43</v>
+        <v>1.67</v>
       </c>
       <c r="W3">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="X3">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y3">
-        <v>1.21</v>
+        <v>1.1</v>
       </c>
       <c r="Z3">
-        <v>3.58</v>
+        <v>5.1</v>
       </c>
       <c r="AA3">
-        <v>1.75</v>
+        <v>1.4</v>
       </c>
       <c r="AB3">
-        <v>2.05</v>
+        <v>2.68</v>
       </c>
       <c r="AC3">
-        <v>2.74</v>
+        <v>2.09</v>
       </c>
       <c r="AD3">
-        <v>1.35</v>
+        <v>1.67</v>
       </c>
       <c r="AE3">
-        <v>1.1</v>
+        <v>1.22</v>
       </c>
       <c r="AF3">
-        <v>1.61</v>
+        <v>1.56</v>
       </c>
       <c r="AG3">
-        <v>2.13</v>
+        <v>2.18</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -868,10 +868,10 @@
         </is>
       </c>
       <c r="AJ3">
-        <v>1.22</v>
+        <v>2.43</v>
       </c>
       <c r="AK3">
-        <v>1.66</v>
+        <v>1.07</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -902,7 +902,7 @@
       </c>
       <c r="AU3" t="inlineStr">
         <is>
-          <t>2026-08-02 01:30:00</t>
+          <t>2026-08-02 01:00:00</t>
         </is>
       </c>
     </row>
@@ -914,7 +914,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>02:00</t>
+          <t>01:30</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -929,12 +929,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Rockdale City Suns</t>
+          <t>Sydney United</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Manly United</t>
+          <t>NWS Spirit</t>
         </is>
       </c>
       <c r="G4">
@@ -961,64 +961,64 @@
         </is>
       </c>
       <c r="N4">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="O4">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P4">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="Q4">
-        <v>2.23</v>
+        <v>2.42</v>
       </c>
       <c r="R4">
-        <v>2.32</v>
+        <v>2.11</v>
       </c>
       <c r="S4">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="T4">
-        <v>3.5</v>
+        <v>2.75</v>
       </c>
       <c r="U4">
-        <v>2.2</v>
+        <v>2.71</v>
       </c>
       <c r="V4">
-        <v>1.57</v>
+        <v>1.37</v>
       </c>
       <c r="W4">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="X4">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y4">
+        <v>1.26</v>
+      </c>
+      <c r="Z4">
+        <v>3.2</v>
+      </c>
+      <c r="AA4">
+        <v>1.75</v>
+      </c>
+      <c r="AB4">
+        <v>2.05</v>
+      </c>
+      <c r="AC4">
+        <v>3.08</v>
+      </c>
+      <c r="AD4">
+        <v>1.28</v>
+      </c>
+      <c r="AE4">
         <v>1.1</v>
       </c>
-      <c r="Z4">
-        <v>5.1</v>
-      </c>
-      <c r="AA4">
-        <v>1.45</v>
-      </c>
-      <c r="AB4">
-        <v>2.41</v>
-      </c>
-      <c r="AC4">
-        <v>2.21</v>
-      </c>
-      <c r="AD4">
-        <v>1.58</v>
-      </c>
-      <c r="AE4">
-        <v>1.19</v>
-      </c>
       <c r="AF4">
-        <v>1.54</v>
+        <v>1.74</v>
       </c>
       <c r="AG4">
-        <v>2.28</v>
+        <v>1.91</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1031,10 +1031,10 @@
         </is>
       </c>
       <c r="AJ4">
-        <v>1.2</v>
+        <v>1.23</v>
       </c>
       <c r="AK4">
-        <v>1.94</v>
+        <v>1.64</v>
       </c>
       <c r="AL4">
         <v>0</v>
@@ -1065,7 +1065,7 @@
       </c>
       <c r="AU4" t="inlineStr">
         <is>
-          <t>2026-08-02 02:00:00</t>
+          <t>2026-08-02 01:30:00</t>
         </is>
       </c>
     </row>
@@ -1092,12 +1092,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Blacktown City</t>
+          <t>Rockdale City Suns</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Sydney II</t>
+          <t>Manly United</t>
         </is>
       </c>
       <c r="G5">
@@ -1124,16 +1124,16 @@
         </is>
       </c>
       <c r="N5">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="O5">
-        <v>0</v>
+        <v>3.84</v>
       </c>
       <c r="P5">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="Q5">
-        <v>2.4</v>
+        <v>2.24</v>
       </c>
       <c r="R5">
         <v>2.26</v>
@@ -1145,43 +1145,43 @@
         <v>3.28</v>
       </c>
       <c r="U5">
-        <v>2.31</v>
+        <v>2.2</v>
       </c>
       <c r="V5">
-        <v>1.5</v>
+        <v>1.59</v>
       </c>
       <c r="W5">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="X5">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y5">
-        <v>1.15</v>
+        <v>1.13</v>
       </c>
       <c r="Z5">
-        <v>4.3</v>
+        <v>5.1</v>
       </c>
       <c r="AA5">
-        <v>1.59</v>
+        <v>1.53</v>
       </c>
       <c r="AB5">
-        <v>2.19</v>
+        <v>2.37</v>
       </c>
       <c r="AC5">
-        <v>2.43</v>
+        <v>2.21</v>
       </c>
       <c r="AD5">
-        <v>1.44</v>
+        <v>1.58</v>
       </c>
       <c r="AE5">
-        <v>1.14</v>
+        <v>1.19</v>
       </c>
       <c r="AF5">
-        <v>1.52</v>
+        <v>1.54</v>
       </c>
       <c r="AG5">
-        <v>2.27</v>
+        <v>2.28</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1194,10 +1194,10 @@
         </is>
       </c>
       <c r="AJ5">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="AK5">
-        <v>1.74</v>
+        <v>1.93</v>
       </c>
       <c r="AL5">
         <v>0</v>
@@ -1287,13 +1287,13 @@
         </is>
       </c>
       <c r="N6">
-        <v>1.44</v>
+        <v>1.26</v>
       </c>
       <c r="O6">
-        <v>4.2</v>
+        <v>5.25</v>
       </c>
       <c r="P6">
-        <v>5.92</v>
+        <v>8.35</v>
       </c>
       <c r="Q6">
         <v>0</v>
@@ -1403,27 +1403,27 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>05:00</t>
+          <t>02:00</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Australia New South Wales NPL</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>SKA Khabarovsk</t>
+          <t>Blacktown City</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ural</t>
+          <t>Sydney II</t>
         </is>
       </c>
       <c r="G7">
@@ -1450,80 +1450,80 @@
         </is>
       </c>
       <c r="N7">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="O7">
-        <v>0</v>
+        <v>3.62</v>
       </c>
       <c r="P7">
-        <v>0</v>
+        <v>3.47</v>
       </c>
       <c r="Q7">
-        <v>5</v>
+        <v>2.41</v>
       </c>
       <c r="R7">
-        <v>2.02</v>
+        <v>2.21</v>
       </c>
       <c r="S7">
-        <v>1.43</v>
+        <v>1.28</v>
       </c>
       <c r="T7">
-        <v>2.59</v>
+        <v>3.12</v>
       </c>
       <c r="U7">
-        <v>3.05</v>
+        <v>2.31</v>
       </c>
       <c r="V7">
-        <v>1.32</v>
+        <v>1.5</v>
       </c>
       <c r="W7">
-        <v>1.02</v>
+        <v>1.09</v>
       </c>
       <c r="X7">
         <v>1.01</v>
       </c>
       <c r="Y7">
-        <v>1.3</v>
+        <v>1.17</v>
       </c>
       <c r="Z7">
-        <v>2.97</v>
+        <v>4.3</v>
       </c>
       <c r="AA7">
-        <v>2.11</v>
+        <v>1.61</v>
       </c>
       <c r="AB7">
-        <v>1.7</v>
+        <v>2.25</v>
       </c>
       <c r="AC7">
-        <v>3.68</v>
+        <v>2.43</v>
       </c>
       <c r="AD7">
+        <v>1.44</v>
+      </c>
+      <c r="AE7">
+        <v>1.14</v>
+      </c>
+      <c r="AF7">
+        <v>1.58</v>
+      </c>
+      <c r="AG7">
+        <v>2.15</v>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ7">
         <v>1.2</v>
       </c>
-      <c r="AE7">
-        <v>1.03</v>
-      </c>
-      <c r="AF7">
-        <v>1.92</v>
-      </c>
-      <c r="AG7">
-        <v>1.79</v>
-      </c>
-      <c r="AH7" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI7" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ7">
-        <v>1.96</v>
-      </c>
       <c r="AK7">
-        <v>1.2</v>
+        <v>1.74</v>
       </c>
       <c r="AL7">
         <v>0</v>
@@ -1554,7 +1554,7 @@
       </c>
       <c r="AU7" t="inlineStr">
         <is>
-          <t>2026-08-02 05:00:00</t>
+          <t>2026-08-02 02:00:00</t>
         </is>
       </c>
     </row>
@@ -1566,12 +1566,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>05:30</t>
+          <t>05:00</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1581,12 +1581,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>WSPG Wels</t>
+          <t>SKA Khabarovsk</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Austria Salzburg</t>
+          <t>Ural</t>
         </is>
       </c>
       <c r="G8">
@@ -1613,64 +1613,64 @@
         </is>
       </c>
       <c r="N8">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="O8">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="P8">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="Q8">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="R8">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="S8">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="T8">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="U8">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="V8">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="W8">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y8">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Z8">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="AA8">
-        <v>1.94</v>
+        <v>2.11</v>
       </c>
       <c r="AB8">
-        <v>1.75</v>
+        <v>1.7</v>
       </c>
       <c r="AC8">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="AD8">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AE8">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF8">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AG8">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1683,10 +1683,10 @@
         </is>
       </c>
       <c r="AJ8">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AK8">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AL8">
         <v>0</v>
@@ -1717,7 +1717,7 @@
       </c>
       <c r="AU8" t="inlineStr">
         <is>
-          <t>2026-08-02 05:30:00</t>
+          <t>2026-08-02 05:00:00</t>
         </is>
       </c>
     </row>
@@ -1729,27 +1729,27 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>05:30</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Australia New South Wales NPL</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Sydney Olympic</t>
+          <t>WSPG Wels</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>APIA Leichhardt Tigers</t>
+          <t>Austria Salzburg</t>
         </is>
       </c>
       <c r="G9">
@@ -1776,64 +1776,64 @@
         </is>
       </c>
       <c r="N9">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="O9">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="P9">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="Q9">
-        <v>5.69</v>
+        <v>0</v>
       </c>
       <c r="R9">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="S9">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="T9">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="U9">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="V9">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="W9">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="X9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y9">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="Z9">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AA9">
-        <v>1.4</v>
+        <v>1.94</v>
       </c>
       <c r="AB9">
-        <v>2.75</v>
+        <v>1.75</v>
       </c>
       <c r="AC9">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AD9">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AE9">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AF9">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="AG9">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1846,10 +1846,10 @@
         </is>
       </c>
       <c r="AJ9">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="AK9">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="AL9">
         <v>0</v>
@@ -1880,7 +1880,7 @@
       </c>
       <c r="AU9" t="inlineStr">
         <is>
-          <t>2026-08-02 06:00:00</t>
+          <t>2026-08-02 05:30:00</t>
         </is>
       </c>
     </row>
@@ -2559,12 +2559,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Gimpo Citizen</t>
+          <t>Ansan Greeners</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Gyeongnam</t>
+          <t>Gimhae City</t>
         </is>
       </c>
       <c r="G14">
@@ -2591,64 +2591,64 @@
         </is>
       </c>
       <c r="N14">
-        <v>1.85</v>
+        <v>2.91</v>
       </c>
       <c r="O14">
-        <v>2.98</v>
+        <v>3.38</v>
       </c>
       <c r="P14">
-        <v>3.28</v>
+        <v>2.18</v>
       </c>
       <c r="Q14">
-        <v>2.47</v>
+        <v>3.4</v>
       </c>
       <c r="R14">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="S14">
+        <v>1.34</v>
+      </c>
+      <c r="T14">
+        <v>2.88</v>
+      </c>
+      <c r="U14">
+        <v>2.66</v>
+      </c>
+      <c r="V14">
         <v>1.4</v>
       </c>
-      <c r="T14">
-        <v>2.5</v>
-      </c>
-      <c r="U14">
-        <v>3.28</v>
-      </c>
-      <c r="V14">
-        <v>1.33</v>
-      </c>
       <c r="W14">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="X14">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y14">
-        <v>1.35</v>
+        <v>1.23</v>
       </c>
       <c r="Z14">
-        <v>2.74</v>
+        <v>3.68</v>
       </c>
       <c r="AA14">
-        <v>2.14</v>
+        <v>1.84</v>
       </c>
       <c r="AB14">
-        <v>1.73</v>
+        <v>1.95</v>
       </c>
       <c r="AC14">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="AD14">
-        <v>1.25</v>
+        <v>1.34</v>
       </c>
       <c r="AE14">
-        <v>1.03</v>
+        <v>1.13</v>
       </c>
       <c r="AF14">
-        <v>1.85</v>
+        <v>1.67</v>
       </c>
       <c r="AG14">
-        <v>1.8</v>
+        <v>2.1</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2661,10 +2661,10 @@
         </is>
       </c>
       <c r="AJ14">
-        <v>1.22</v>
+        <v>1.62</v>
       </c>
       <c r="AK14">
-        <v>1.84</v>
+        <v>1.36</v>
       </c>
       <c r="AL14">
         <v>0</v>
@@ -2722,12 +2722,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Ansan Greeners</t>
+          <t>Busan I'Park</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Gimhae City</t>
+          <t>Seoul E-Land</t>
         </is>
       </c>
       <c r="G15">
@@ -2754,80 +2754,80 @@
         </is>
       </c>
       <c r="N15">
-        <v>2.91</v>
+        <v>2.75</v>
       </c>
       <c r="O15">
-        <v>3.38</v>
+        <v>3.5</v>
       </c>
       <c r="P15">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="Q15">
-        <v>3.4</v>
+        <v>3.1</v>
       </c>
       <c r="R15">
-        <v>2.2</v>
+        <v>2.36</v>
       </c>
       <c r="S15">
-        <v>1.34</v>
+        <v>1.3</v>
       </c>
       <c r="T15">
-        <v>2.88</v>
+        <v>3.25</v>
       </c>
       <c r="U15">
+        <v>2.5</v>
+      </c>
+      <c r="V15">
+        <v>1.5</v>
+      </c>
+      <c r="W15">
+        <v>1.11</v>
+      </c>
+      <c r="X15">
+        <v>1.03</v>
+      </c>
+      <c r="Y15">
+        <v>1.16</v>
+      </c>
+      <c r="Z15">
+        <v>4.05</v>
+      </c>
+      <c r="AA15">
+        <v>1.7</v>
+      </c>
+      <c r="AB15">
+        <v>1.96</v>
+      </c>
+      <c r="AC15">
         <v>2.66</v>
       </c>
-      <c r="V15">
-        <v>1.4</v>
-      </c>
-      <c r="W15">
-        <v>1.08</v>
-      </c>
-      <c r="X15">
-        <v>1.01</v>
-      </c>
-      <c r="Y15">
+      <c r="AD15">
+        <v>1.44</v>
+      </c>
+      <c r="AE15">
+        <v>1.17</v>
+      </c>
+      <c r="AF15">
+        <v>1.57</v>
+      </c>
+      <c r="AG15">
+        <v>2.27</v>
+      </c>
+      <c r="AH15" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI15" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ15">
         <v>1.23</v>
       </c>
-      <c r="Z15">
-        <v>3.68</v>
-      </c>
-      <c r="AA15">
-        <v>1.84</v>
-      </c>
-      <c r="AB15">
-        <v>1.95</v>
-      </c>
-      <c r="AC15">
-        <v>3.1</v>
-      </c>
-      <c r="AD15">
-        <v>1.34</v>
-      </c>
-      <c r="AE15">
-        <v>1.13</v>
-      </c>
-      <c r="AF15">
-        <v>1.67</v>
-      </c>
-      <c r="AG15">
-        <v>2.1</v>
-      </c>
-      <c r="AH15" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI15" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ15">
-        <v>1.62</v>
-      </c>
       <c r="AK15">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="AL15">
         <v>0</v>
@@ -2885,12 +2885,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Busan I'Park</t>
+          <t>Gimpo Citizen</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Seoul E-Land</t>
+          <t>Gyeongnam</t>
         </is>
       </c>
       <c r="G16">
@@ -2917,64 +2917,64 @@
         </is>
       </c>
       <c r="N16">
-        <v>2.75</v>
+        <v>1.85</v>
       </c>
       <c r="O16">
-        <v>3.5</v>
+        <v>2.98</v>
       </c>
       <c r="P16">
-        <v>2.2</v>
+        <v>3.28</v>
       </c>
       <c r="Q16">
-        <v>3.1</v>
+        <v>2.47</v>
       </c>
       <c r="R16">
-        <v>2.36</v>
+        <v>2.18</v>
       </c>
       <c r="S16">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="T16">
-        <v>3.25</v>
+        <v>2.5</v>
       </c>
       <c r="U16">
-        <v>2.5</v>
+        <v>3.28</v>
       </c>
       <c r="V16">
-        <v>1.5</v>
+        <v>1.33</v>
       </c>
       <c r="W16">
-        <v>1.11</v>
+        <v>1.06</v>
       </c>
       <c r="X16">
         <v>1.03</v>
       </c>
       <c r="Y16">
-        <v>1.16</v>
+        <v>1.35</v>
       </c>
       <c r="Z16">
-        <v>4.05</v>
+        <v>2.74</v>
       </c>
       <c r="AA16">
-        <v>1.7</v>
+        <v>2.14</v>
       </c>
       <c r="AB16">
-        <v>1.96</v>
+        <v>1.73</v>
       </c>
       <c r="AC16">
-        <v>2.66</v>
+        <v>3.2</v>
       </c>
       <c r="AD16">
-        <v>1.44</v>
+        <v>1.25</v>
       </c>
       <c r="AE16">
-        <v>1.17</v>
+        <v>1.03</v>
       </c>
       <c r="AF16">
-        <v>1.57</v>
+        <v>1.85</v>
       </c>
       <c r="AG16">
-        <v>2.27</v>
+        <v>1.8</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -2987,10 +2987,10 @@
         </is>
       </c>
       <c r="AJ16">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="AK16">
-        <v>1.38</v>
+        <v>1.84</v>
       </c>
       <c r="AL16">
         <v>0</v>
@@ -7375,7 +7375,7 @@
         <v>1.56</v>
       </c>
       <c r="AG43">
-        <v>2.28</v>
+        <v>2.17</v>
       </c>
       <c r="AH43" t="inlineStr">
         <is>
@@ -7391,7 +7391,7 @@
         <v>1.22</v>
       </c>
       <c r="AK43">
-        <v>1.29</v>
+        <v>1.26</v>
       </c>
       <c r="AL43">
         <v>0</v>
@@ -9894,12 +9894,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Molde</t>
+          <t>KFUM</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Sarpsborg 08</t>
+          <t>Kristiansund</t>
         </is>
       </c>
       <c r="G59">
@@ -9926,65 +9926,65 @@
         </is>
       </c>
       <c r="N59">
+        <v>1.65</v>
+      </c>
+      <c r="O59">
+        <v>3.78</v>
+      </c>
+      <c r="P59">
+        <v>4.1</v>
+      </c>
+      <c r="Q59">
+        <v>2.04</v>
+      </c>
+      <c r="R59">
+        <v>2.21</v>
+      </c>
+      <c r="S59">
+        <v>1.29</v>
+      </c>
+      <c r="T59">
+        <v>3.25</v>
+      </c>
+      <c r="U59">
+        <v>2.39</v>
+      </c>
+      <c r="V59">
+        <v>1.45</v>
+      </c>
+      <c r="W59">
+        <v>1.08</v>
+      </c>
+      <c r="X59">
+        <v>1.01</v>
+      </c>
+      <c r="Y59">
+        <v>1.2</v>
+      </c>
+      <c r="Z59">
+        <v>4.1</v>
+      </c>
+      <c r="AA59">
         <v>1.7</v>
       </c>
-      <c r="O59">
-        <v>4.3</v>
-      </c>
-      <c r="P59">
-        <v>4.43</v>
-      </c>
-      <c r="Q59">
+      <c r="AB59">
+        <v>2.04</v>
+      </c>
+      <c r="AC59">
+        <v>2.8</v>
+      </c>
+      <c r="AD59">
+        <v>1.4</v>
+      </c>
+      <c r="AE59">
+        <v>1.17</v>
+      </c>
+      <c r="AF59">
+        <v>1.67</v>
+      </c>
+      <c r="AG59">
         <v>2</v>
       </c>
-      <c r="R59">
-        <v>2.36</v>
-      </c>
-      <c r="S59">
-        <v>1.22</v>
-      </c>
-      <c r="T59">
-        <v>4</v>
-      </c>
-      <c r="U59">
-        <v>2</v>
-      </c>
-      <c r="V59">
-        <v>1.68</v>
-      </c>
-      <c r="W59">
-        <v>1.17</v>
-      </c>
-      <c r="X59">
-        <v>1.02</v>
-      </c>
-      <c r="Y59">
-        <v>1.14</v>
-      </c>
-      <c r="Z59">
-        <v>5.75</v>
-      </c>
-      <c r="AA59">
-        <v>1.4</v>
-      </c>
-      <c r="AB59">
-        <v>2.75</v>
-      </c>
-      <c r="AC59">
-        <v>2.12</v>
-      </c>
-      <c r="AD59">
-        <v>1.73</v>
-      </c>
-      <c r="AE59">
-        <v>1.26</v>
-      </c>
-      <c r="AF59">
-        <v>1.44</v>
-      </c>
-      <c r="AG59">
-        <v>2.5</v>
-      </c>
       <c r="AH59" t="inlineStr">
         <is>
           <t>[]</t>
@@ -9996,10 +9996,10 @@
         </is>
       </c>
       <c r="AJ59">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="AK59">
-        <v>2.13</v>
+        <v>2.1</v>
       </c>
       <c r="AL59">
         <v>0</v>
@@ -10057,12 +10057,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>KFUM</t>
+          <t>Molde</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Kristiansund</t>
+          <t>Sarpsborg 08</t>
         </is>
       </c>
       <c r="G60">
@@ -10089,80 +10089,80 @@
         </is>
       </c>
       <c r="N60">
-        <v>1.65</v>
+        <v>1.7</v>
       </c>
       <c r="O60">
-        <v>3.78</v>
+        <v>4.3</v>
       </c>
       <c r="P60">
-        <v>4.1</v>
+        <v>4.43</v>
       </c>
       <c r="Q60">
-        <v>2.04</v>
+        <v>2</v>
       </c>
       <c r="R60">
-        <v>2.21</v>
+        <v>2.36</v>
       </c>
       <c r="S60">
-        <v>1.29</v>
+        <v>1.22</v>
       </c>
       <c r="T60">
-        <v>3.25</v>
+        <v>4</v>
       </c>
       <c r="U60">
-        <v>2.39</v>
+        <v>2</v>
       </c>
       <c r="V60">
-        <v>1.45</v>
+        <v>1.68</v>
       </c>
       <c r="W60">
-        <v>1.08</v>
+        <v>1.17</v>
       </c>
       <c r="X60">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y60">
-        <v>1.2</v>
+        <v>1.14</v>
       </c>
       <c r="Z60">
-        <v>4.1</v>
+        <v>5.75</v>
       </c>
       <c r="AA60">
-        <v>1.7</v>
+        <v>1.4</v>
       </c>
       <c r="AB60">
-        <v>2.04</v>
+        <v>2.75</v>
       </c>
       <c r="AC60">
-        <v>2.8</v>
+        <v>2.12</v>
       </c>
       <c r="AD60">
-        <v>1.4</v>
+        <v>1.73</v>
       </c>
       <c r="AE60">
+        <v>1.26</v>
+      </c>
+      <c r="AF60">
+        <v>1.44</v>
+      </c>
+      <c r="AG60">
+        <v>2.5</v>
+      </c>
+      <c r="AH60" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI60" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ60">
         <v>1.17</v>
       </c>
-      <c r="AF60">
-        <v>1.67</v>
-      </c>
-      <c r="AG60">
-        <v>2</v>
-      </c>
-      <c r="AH60" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI60" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ60">
-        <v>1.2</v>
-      </c>
       <c r="AK60">
-        <v>2.1</v>
+        <v>2.13</v>
       </c>
       <c r="AL60">
         <v>0</v>
@@ -10255,7 +10255,7 @@
         <v>1.11</v>
       </c>
       <c r="O61">
-        <v>8</v>
+        <v>8.25</v>
       </c>
       <c r="P61">
         <v>13</v>
@@ -10306,10 +10306,10 @@
         <v>1.29</v>
       </c>
       <c r="AF61">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="AG61">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="AH61" t="inlineStr">
         <is>
@@ -10325,7 +10325,7 @@
         <v>1.05</v>
       </c>
       <c r="AK61">
-        <v>5.1</v>
+        <v>5.05</v>
       </c>
       <c r="AL61">
         <v>0</v>
@@ -11361,12 +11361,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Odd</t>
+          <t>Raufoss</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Åsane</t>
+          <t>Stabæk</t>
         </is>
       </c>
       <c r="G68">
@@ -11393,34 +11393,34 @@
         </is>
       </c>
       <c r="N68">
-        <v>1.39</v>
+        <v>4.5</v>
       </c>
       <c r="O68">
-        <v>4.75</v>
+        <v>4</v>
       </c>
       <c r="P68">
-        <v>5.3</v>
+        <v>1.54</v>
       </c>
       <c r="Q68">
-        <v>1.79</v>
+        <v>4.74</v>
       </c>
       <c r="R68">
-        <v>2.75</v>
+        <v>2.53</v>
       </c>
       <c r="S68">
+        <v>1.17</v>
+      </c>
+      <c r="T68">
+        <v>4.2</v>
+      </c>
+      <c r="U68">
+        <v>1.94</v>
+      </c>
+      <c r="V68">
+        <v>1.76</v>
+      </c>
+      <c r="W68">
         <v>1.18</v>
-      </c>
-      <c r="T68">
-        <v>4.33</v>
-      </c>
-      <c r="U68">
-        <v>1.99</v>
-      </c>
-      <c r="V68">
-        <v>1.83</v>
-      </c>
-      <c r="W68">
-        <v>1.2</v>
       </c>
       <c r="X68">
         <v>1.01</v>
@@ -11429,28 +11429,28 @@
         <v>1.1</v>
       </c>
       <c r="Z68">
-        <v>6.6</v>
+        <v>6.47</v>
       </c>
       <c r="AA68">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="AB68">
-        <v>2.85</v>
+        <v>2.92</v>
       </c>
       <c r="AC68">
-        <v>1.88</v>
+        <v>1.98</v>
       </c>
       <c r="AD68">
-        <v>1.91</v>
+        <v>1.71</v>
       </c>
       <c r="AE68">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="AF68">
-        <v>1.49</v>
+        <v>1.4</v>
       </c>
       <c r="AG68">
-        <v>2.45</v>
+        <v>2.73</v>
       </c>
       <c r="AH68" t="inlineStr">
         <is>
@@ -11463,10 +11463,10 @@
         </is>
       </c>
       <c r="AJ68">
-        <v>1.13</v>
+        <v>1.18</v>
       </c>
       <c r="AK68">
-        <v>2.7</v>
+        <v>1.15</v>
       </c>
       <c r="AL68">
         <v>0</v>
@@ -11524,12 +11524,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Raufoss</t>
+          <t>Odd</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Stabæk</t>
+          <t>Åsane</t>
         </is>
       </c>
       <c r="G69">
@@ -11556,34 +11556,34 @@
         </is>
       </c>
       <c r="N69">
-        <v>4.5</v>
+        <v>1.39</v>
       </c>
       <c r="O69">
-        <v>4</v>
+        <v>4.75</v>
       </c>
       <c r="P69">
-        <v>1.54</v>
+        <v>5.3</v>
       </c>
       <c r="Q69">
-        <v>4.74</v>
+        <v>1.79</v>
       </c>
       <c r="R69">
-        <v>2.53</v>
+        <v>2.75</v>
       </c>
       <c r="S69">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="T69">
-        <v>4.2</v>
+        <v>4.33</v>
       </c>
       <c r="U69">
-        <v>1.94</v>
+        <v>1.99</v>
       </c>
       <c r="V69">
-        <v>1.76</v>
+        <v>1.83</v>
       </c>
       <c r="W69">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="X69">
         <v>1.01</v>
@@ -11592,28 +11592,28 @@
         <v>1.1</v>
       </c>
       <c r="Z69">
-        <v>6.47</v>
+        <v>6.6</v>
       </c>
       <c r="AA69">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="AB69">
-        <v>2.92</v>
+        <v>2.85</v>
       </c>
       <c r="AC69">
-        <v>1.98</v>
+        <v>1.88</v>
       </c>
       <c r="AD69">
-        <v>1.71</v>
+        <v>1.91</v>
       </c>
       <c r="AE69">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="AF69">
-        <v>1.4</v>
+        <v>1.49</v>
       </c>
       <c r="AG69">
-        <v>2.73</v>
+        <v>2.45</v>
       </c>
       <c r="AH69" t="inlineStr">
         <is>
@@ -11626,10 +11626,10 @@
         </is>
       </c>
       <c r="AJ69">
-        <v>1.18</v>
+        <v>1.13</v>
       </c>
       <c r="AK69">
-        <v>1.15</v>
+        <v>2.7</v>
       </c>
       <c r="AL69">
         <v>0</v>
@@ -13465,12 +13465,12 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -13480,12 +13480,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Hegelmann Litauen</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>TransINVEST Vilnius</t>
         </is>
       </c>
       <c r="G81">
@@ -13512,64 +13512,64 @@
         </is>
       </c>
       <c r="N81">
-        <v>1.79</v>
+        <v>3.6</v>
       </c>
       <c r="O81">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="P81">
-        <v>4.46</v>
+        <v>1.83</v>
       </c>
       <c r="Q81">
-        <v>2.38</v>
+        <v>4.2</v>
       </c>
       <c r="R81">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="S81">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="T81">
-        <v>2.8</v>
+        <v>2.88</v>
       </c>
       <c r="U81">
-        <v>2.99</v>
+        <v>2.5</v>
       </c>
       <c r="V81">
-        <v>1.34</v>
+        <v>1.43</v>
       </c>
       <c r="W81">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="X81">
         <v>1.01</v>
       </c>
       <c r="Y81">
-        <v>1.32</v>
+        <v>1.25</v>
       </c>
       <c r="Z81">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="AA81">
-        <v>2.03</v>
+        <v>1.82</v>
       </c>
       <c r="AB81">
-        <v>1.76</v>
+        <v>1.81</v>
       </c>
       <c r="AC81">
-        <v>3.55</v>
+        <v>2.83</v>
       </c>
       <c r="AD81">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="AE81">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="AF81">
-        <v>1.89</v>
+        <v>1.65</v>
       </c>
       <c r="AG81">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="AH81" t="inlineStr">
         <is>
@@ -13582,10 +13582,10 @@
         </is>
       </c>
       <c r="AJ81">
-        <v>1.17</v>
+        <v>1.82</v>
       </c>
       <c r="AK81">
-        <v>2.02</v>
+        <v>1.23</v>
       </c>
       <c r="AL81">
         <v>0</v>
@@ -13616,7 +13616,7 @@
       </c>
       <c r="AU81" t="inlineStr">
         <is>
-          <t>2026-08-02 13:00:00</t>
+          <t>2026-08-02 12:45:00</t>
         </is>
       </c>
     </row>
@@ -13633,7 +13633,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -13643,12 +13643,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Hegelmann Litauen</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>TransINVEST Vilnius</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="G82">
@@ -13675,64 +13675,64 @@
         </is>
       </c>
       <c r="N82">
-        <v>3.6</v>
+        <v>1.79</v>
       </c>
       <c r="O82">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="P82">
-        <v>1.78</v>
+        <v>4.46</v>
       </c>
       <c r="Q82">
-        <v>4.2</v>
+        <v>2.38</v>
       </c>
       <c r="R82">
-        <v>2.25</v>
+        <v>2.1</v>
       </c>
       <c r="S82">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="T82">
-        <v>3.08</v>
+        <v>2.8</v>
       </c>
       <c r="U82">
-        <v>2.5</v>
+        <v>2.99</v>
       </c>
       <c r="V82">
-        <v>1.43</v>
+        <v>1.34</v>
       </c>
       <c r="W82">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="X82">
         <v>1.01</v>
       </c>
       <c r="Y82">
-        <v>1.25</v>
+        <v>1.32</v>
       </c>
       <c r="Z82">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="AA82">
-        <v>1.74</v>
+        <v>2.03</v>
       </c>
       <c r="AB82">
-        <v>1.96</v>
+        <v>1.76</v>
       </c>
       <c r="AC82">
-        <v>2.83</v>
+        <v>3.55</v>
       </c>
       <c r="AD82">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
       <c r="AE82">
-        <v>1.09</v>
+        <v>1.04</v>
       </c>
       <c r="AF82">
-        <v>1.65</v>
+        <v>1.89</v>
       </c>
       <c r="AG82">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="AH82" t="inlineStr">
         <is>
@@ -13745,10 +13745,10 @@
         </is>
       </c>
       <c r="AJ82">
-        <v>1.23</v>
+        <v>1.17</v>
       </c>
       <c r="AK82">
-        <v>1.23</v>
+        <v>1.95</v>
       </c>
       <c r="AL82">
         <v>0</v>
@@ -16775,7 +16775,7 @@
         <v>1.54</v>
       </c>
       <c r="O101">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="P101">
         <v>4.75</v>
@@ -16845,7 +16845,7 @@
         <v>1.19</v>
       </c>
       <c r="AK101">
-        <v>2.5</v>
+        <v>2.47</v>
       </c>
       <c r="AL101">
         <v>0</v>
@@ -17623,7 +17623,7 @@
         <v>1.74</v>
       </c>
       <c r="Z106">
-        <v>1.98</v>
+        <v>2.02</v>
       </c>
       <c r="AA106">
         <v>3.5</v>
@@ -17644,7 +17644,7 @@
         <v>2.54</v>
       </c>
       <c r="AG106">
-        <v>1.45</v>
+        <v>1.43</v>
       </c>
       <c r="AH106" t="inlineStr">
         <is>
@@ -17660,7 +17660,7 @@
         <v>1.25</v>
       </c>
       <c r="AK106">
-        <v>1.57</v>
+        <v>1.48</v>
       </c>
       <c r="AL106">
         <v>0</v>
@@ -17718,12 +17718,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>Chacarita Juniors</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Midland</t>
+          <t>Agropecuario</t>
         </is>
       </c>
       <c r="G107">
@@ -17750,64 +17750,64 @@
         </is>
       </c>
       <c r="N107">
-        <v>2.8</v>
+        <v>2.25</v>
       </c>
       <c r="O107">
-        <v>2.64</v>
+        <v>2.7</v>
       </c>
       <c r="P107">
-        <v>2.75</v>
+        <v>3.3</v>
       </c>
       <c r="Q107">
-        <v>3.7</v>
+        <v>3.01</v>
       </c>
       <c r="R107">
-        <v>1.71</v>
+        <v>1.85</v>
       </c>
       <c r="S107">
-        <v>1.68</v>
+        <v>1.65</v>
       </c>
       <c r="T107">
-        <v>2.05</v>
+        <v>2.19</v>
       </c>
       <c r="U107">
-        <v>4.5</v>
+        <v>3.9</v>
       </c>
       <c r="V107">
-        <v>1.15</v>
+        <v>1.2</v>
       </c>
       <c r="W107">
         <v>1.03</v>
       </c>
       <c r="X107">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="Y107">
-        <v>1.5</v>
+        <v>1.61</v>
       </c>
       <c r="Z107">
-        <v>2.12</v>
+        <v>2.17</v>
       </c>
       <c r="AA107">
-        <v>2.97</v>
+        <v>2.78</v>
       </c>
       <c r="AB107">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="AC107">
-        <v>6.4</v>
+        <v>6.12</v>
       </c>
       <c r="AD107">
-        <v>1.05</v>
+        <v>1.11</v>
       </c>
       <c r="AE107">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="AF107">
-        <v>2.07</v>
+        <v>2.3</v>
       </c>
       <c r="AG107">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="AH107" t="inlineStr">
         <is>
@@ -17820,10 +17820,10 @@
         </is>
       </c>
       <c r="AJ107">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="AK107">
-        <v>1.36</v>
+        <v>1.53</v>
       </c>
       <c r="AL107">
         <v>0</v>
@@ -19730,7 +19730,7 @@
         <v>4</v>
       </c>
       <c r="V119">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="W119">
         <v>1.03</v>
@@ -19763,7 +19763,7 @@
         <v>2.3</v>
       </c>
       <c r="AG119">
-        <v>1.48</v>
+        <v>1.46</v>
       </c>
       <c r="AH119" t="inlineStr">
         <is>
@@ -19887,7 +19887,7 @@
         <v>1.57</v>
       </c>
       <c r="T120">
-        <v>2.18</v>
+        <v>2.33</v>
       </c>
       <c r="U120">
         <v>3.75</v>
@@ -19926,7 +19926,7 @@
         <v>2.1</v>
       </c>
       <c r="AG120">
-        <v>1.64</v>
+        <v>1.62</v>
       </c>
       <c r="AH120" t="inlineStr">
         <is>
@@ -19942,7 +19942,7 @@
         <v>1.4</v>
       </c>
       <c r="AK120">
-        <v>1.39</v>
+        <v>1.41</v>
       </c>
       <c r="AL120">
         <v>0</v>
@@ -19990,22 +19990,22 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Patronato</t>
+          <t>Rapid Bucureşti</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Quilmes</t>
+          <t>CFR Cluj</t>
         </is>
       </c>
       <c r="G121">
@@ -20032,64 +20032,64 @@
         </is>
       </c>
       <c r="N121">
-        <v>2.5</v>
+        <v>1.95</v>
       </c>
       <c r="O121">
-        <v>2.7</v>
+        <v>3.25</v>
       </c>
       <c r="P121">
+        <v>3.3</v>
+      </c>
+      <c r="Q121">
+        <v>2.55</v>
+      </c>
+      <c r="R121">
+        <v>2.05</v>
+      </c>
+      <c r="S121">
+        <v>1.44</v>
+      </c>
+      <c r="T121">
+        <v>2.56</v>
+      </c>
+      <c r="U121">
         <v>2.9</v>
       </c>
-      <c r="Q121">
-        <v>3.5</v>
-      </c>
-      <c r="R121">
-        <v>1.93</v>
-      </c>
-      <c r="S121">
-        <v>1.64</v>
-      </c>
-      <c r="T121">
-        <v>2.19</v>
-      </c>
-      <c r="U121">
-        <v>4</v>
-      </c>
       <c r="V121">
-        <v>1.2</v>
+        <v>1.34</v>
       </c>
       <c r="W121">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="X121">
-        <v>1.13</v>
+        <v>1.06</v>
       </c>
       <c r="Y121">
-        <v>1.58</v>
+        <v>1.33</v>
       </c>
       <c r="Z121">
-        <v>2.23</v>
+        <v>2.92</v>
       </c>
       <c r="AA121">
-        <v>2.7</v>
+        <v>2.08</v>
       </c>
       <c r="AB121">
-        <v>1.36</v>
+        <v>1.7</v>
       </c>
       <c r="AC121">
-        <v>5.2</v>
+        <v>3.42</v>
       </c>
       <c r="AD121">
-        <v>1.08</v>
+        <v>1.28</v>
       </c>
       <c r="AE121">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="AF121">
-        <v>2.15</v>
+        <v>1.83</v>
       </c>
       <c r="AG121">
-        <v>1.56</v>
+        <v>1.8</v>
       </c>
       <c r="AH121" t="inlineStr">
         <is>
@@ -20102,10 +20102,10 @@
         </is>
       </c>
       <c r="AJ121">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="AK121">
-        <v>1.4</v>
+        <v>1.7</v>
       </c>
       <c r="AL121">
         <v>0</v>
@@ -20148,27 +20148,27 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Rapid Bucureşti</t>
+          <t>Recoleta</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>CFR Cluj</t>
+          <t>Puerto Montt</t>
         </is>
       </c>
       <c r="G122">
@@ -20195,64 +20195,64 @@
         </is>
       </c>
       <c r="N122">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="O122">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="P122">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="Q122">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="R122">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="S122">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="T122">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="U122">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="V122">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="W122">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="X122">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="Y122">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="Z122">
-        <v>2.92</v>
+        <v>0</v>
       </c>
       <c r="AA122">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="AB122">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AC122">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="AD122">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AE122">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AF122">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AG122">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AH122" t="inlineStr">
         <is>
@@ -20265,10 +20265,10 @@
         </is>
       </c>
       <c r="AJ122">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AK122">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AL122">
         <v>0</v>
@@ -20299,7 +20299,7 @@
       </c>
       <c r="AU122" t="inlineStr">
         <is>
-          <t>2026-08-02 15:30:00</t>
+          <t>2026-08-02 16:00:00</t>
         </is>
       </c>
     </row>
@@ -20316,7 +20316,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -20326,12 +20326,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Recoleta</t>
+          <t>La Serena</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Puerto Montt</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="G123">
@@ -20358,64 +20358,64 @@
         </is>
       </c>
       <c r="N123">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="O123">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="P123">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="Q123">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="R123">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="S123">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T123">
-        <v>0</v>
+        <v>3.21</v>
       </c>
       <c r="U123">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="V123">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="W123">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="X123">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y123">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="Z123">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="AA123">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB123">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AC123">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AD123">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AE123">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AF123">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AG123">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AH123" t="inlineStr">
         <is>
@@ -20428,10 +20428,10 @@
         </is>
       </c>
       <c r="AJ123">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AK123">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AL123">
         <v>0</v>
@@ -20479,7 +20479,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -20489,12 +20489,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>La Serena</t>
+          <t>Real Potosí</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Gualberto Villarroel SJ</t>
         </is>
       </c>
       <c r="G124">
@@ -20521,64 +20521,64 @@
         </is>
       </c>
       <c r="N124">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="O124">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="P124">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="Q124">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="R124">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="S124">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="T124">
-        <v>3.21</v>
+        <v>0</v>
       </c>
       <c r="U124">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="V124">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="W124">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="X124">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y124">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="Z124">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="AA124">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AB124">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AC124">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="AD124">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AE124">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AF124">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AG124">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AH124" t="inlineStr">
         <is>
@@ -20591,10 +20591,10 @@
         </is>
       </c>
       <c r="AJ124">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AK124">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="AL124">
         <v>0</v>
@@ -20642,7 +20642,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -20652,12 +20652,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Real Potosí</t>
+          <t>Deportivo Madryn</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Gualberto Villarroel SJ</t>
+          <t>All Boys</t>
         </is>
       </c>
       <c r="G125">
@@ -20684,64 +20684,64 @@
         </is>
       </c>
       <c r="N125">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="O125">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="P125">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="Q125">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="R125">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="S125">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="T125">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="U125">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="V125">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="W125">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X125">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="Y125">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="Z125">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="AA125">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AB125">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AC125">
-        <v>0</v>
+        <v>6.28</v>
       </c>
       <c r="AD125">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AE125">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AF125">
-        <v>0</v>
+        <v>2.51</v>
       </c>
       <c r="AG125">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AH125" t="inlineStr">
         <is>
@@ -20754,10 +20754,10 @@
         </is>
       </c>
       <c r="AJ125">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AK125">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AL125">
         <v>0</v>
@@ -20815,12 +20815,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Club Atlético Güemes</t>
+          <t>Chaco For Ever</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Tristán Suárez</t>
+          <t>Deportivo Morón</t>
         </is>
       </c>
       <c r="G126">
@@ -20847,64 +20847,64 @@
         </is>
       </c>
       <c r="N126">
-        <v>2.9</v>
+        <v>2.87</v>
       </c>
       <c r="O126">
-        <v>2.4</v>
+        <v>2.7</v>
       </c>
       <c r="P126">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="Q126">
-        <v>3.92</v>
+        <v>3.45</v>
       </c>
       <c r="R126">
-        <v>1.62</v>
+        <v>1.82</v>
       </c>
       <c r="S126">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="T126">
-        <v>1.91</v>
+        <v>2.14</v>
       </c>
       <c r="U126">
-        <v>4.33</v>
+        <v>4</v>
       </c>
       <c r="V126">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="W126">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="X126">
         <v>1.14</v>
       </c>
       <c r="Y126">
-        <v>1.74</v>
+        <v>1.57</v>
       </c>
       <c r="Z126">
-        <v>2.06</v>
+        <v>2.11</v>
       </c>
       <c r="AA126">
-        <v>3.08</v>
+        <v>3.4</v>
       </c>
       <c r="AB126">
-        <v>1.28</v>
+        <v>1.32</v>
       </c>
       <c r="AC126">
-        <v>6.3</v>
+        <v>6.27</v>
       </c>
       <c r="AD126">
-        <v>1.06</v>
+        <v>1.11</v>
       </c>
       <c r="AE126">
         <v>1.02</v>
       </c>
       <c r="AF126">
-        <v>2.38</v>
+        <v>2.3</v>
       </c>
       <c r="AG126">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="AH126" t="inlineStr">
         <is>
@@ -20917,10 +20917,10 @@
         </is>
       </c>
       <c r="AJ126">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="AK126">
-        <v>1.43</v>
+        <v>1.38</v>
       </c>
       <c r="AL126">
         <v>0</v>
@@ -20968,22 +20968,22 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Chaco For Ever</t>
+          <t>Rijeka</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Deportivo Morón</t>
+          <t>Rudeš</t>
         </is>
       </c>
       <c r="G127">
@@ -21010,64 +21010,64 @@
         </is>
       </c>
       <c r="N127">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="O127">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="P127">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="Q127">
-        <v>4.05</v>
+        <v>0</v>
       </c>
       <c r="R127">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="S127">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="T127">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="U127">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="V127">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="W127">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="X127">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="Y127">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="Z127">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AA127">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="AB127">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AC127">
-        <v>5.8</v>
+        <v>0</v>
       </c>
       <c r="AD127">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AE127">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AF127">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AG127">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AH127" t="inlineStr">
         <is>
@@ -21080,10 +21080,10 @@
         </is>
       </c>
       <c r="AJ127">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="AK127">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AL127">
         <v>0</v>
@@ -21126,7 +21126,7 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
@@ -21141,12 +21141,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Deportivo Madryn</t>
+          <t>Central Norte</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>All Boys</t>
+          <t>Los Andes</t>
         </is>
       </c>
       <c r="G128">
@@ -21173,64 +21173,64 @@
         </is>
       </c>
       <c r="N128">
-        <v>1.91</v>
+        <v>2.83</v>
       </c>
       <c r="O128">
-        <v>2.75</v>
+        <v>2.53</v>
       </c>
       <c r="P128">
-        <v>4.4</v>
+        <v>2.87</v>
       </c>
       <c r="Q128">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="R128">
+        <v>0</v>
+      </c>
+      <c r="S128">
+        <v>0</v>
+      </c>
+      <c r="T128">
+        <v>0</v>
+      </c>
+      <c r="U128">
+        <v>0</v>
+      </c>
+      <c r="V128">
+        <v>0</v>
+      </c>
+      <c r="W128">
+        <v>0</v>
+      </c>
+      <c r="X128">
+        <v>0</v>
+      </c>
+      <c r="Y128">
         <v>1.83</v>
       </c>
-      <c r="S128">
-        <v>1.7</v>
-      </c>
-      <c r="T128">
-        <v>2.25</v>
-      </c>
-      <c r="U128">
-        <v>4.1</v>
-      </c>
-      <c r="V128">
-        <v>1.2</v>
-      </c>
-      <c r="W128">
-        <v>1.03</v>
-      </c>
-      <c r="X128">
-        <v>1.12</v>
-      </c>
-      <c r="Y128">
-        <v>1.68</v>
-      </c>
       <c r="Z128">
-        <v>2.09</v>
+        <v>1.84</v>
       </c>
       <c r="AA128">
-        <v>3.4</v>
+        <v>4</v>
       </c>
       <c r="AB128">
-        <v>1.42</v>
+        <v>1.25</v>
       </c>
       <c r="AC128">
-        <v>6.28</v>
+        <v>0</v>
       </c>
       <c r="AD128">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AE128">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AF128">
-        <v>2.51</v>
+        <v>0</v>
       </c>
       <c r="AG128">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="AH128" t="inlineStr">
         <is>
@@ -21243,10 +21243,10 @@
         </is>
       </c>
       <c r="AJ128">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AK128">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AL128">
         <v>0</v>
@@ -21277,7 +21277,7 @@
       </c>
       <c r="AU128" t="inlineStr">
         <is>
-          <t>2026-08-02 16:00:00</t>
+          <t>2026-08-02 16:30:00</t>
         </is>
       </c>
     </row>
@@ -21289,27 +21289,27 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Rijeka</t>
+          <t>Washington Spirit</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Rudeš</t>
+          <t>San Diego Wave</t>
         </is>
       </c>
       <c r="G129">
@@ -21336,64 +21336,64 @@
         </is>
       </c>
       <c r="N129">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="O129">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="P129">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="Q129">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="R129">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="S129">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="T129">
-        <v>0</v>
+        <v>2.71</v>
       </c>
       <c r="U129">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="V129">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W129">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X129">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y129">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="Z129">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="AA129">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AB129">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AC129">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="AD129">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AE129">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AF129">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AG129">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AH129" t="inlineStr">
         <is>
@@ -21406,10 +21406,10 @@
         </is>
       </c>
       <c r="AJ129">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AK129">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AL129">
         <v>0</v>
@@ -21440,7 +21440,7 @@
       </c>
       <c r="AU129" t="inlineStr">
         <is>
-          <t>2026-08-02 16:00:00</t>
+          <t>2026-08-02 17:00:00</t>
         </is>
       </c>
     </row>
@@ -21452,12 +21452,12 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -21467,12 +21467,12 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Central Norte</t>
+          <t>Macará</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Los Andes</t>
+          <t>Guayaquil City FC</t>
         </is>
       </c>
       <c r="G130">
@@ -21499,64 +21499,64 @@
         </is>
       </c>
       <c r="N130">
-        <v>2.81</v>
+        <v>1.64</v>
       </c>
       <c r="O130">
+        <v>3.5</v>
+      </c>
+      <c r="P130">
+        <v>4.45</v>
+      </c>
+      <c r="Q130">
+        <v>2.2</v>
+      </c>
+      <c r="R130">
+        <v>2.1</v>
+      </c>
+      <c r="S130">
+        <v>1.4</v>
+      </c>
+      <c r="T130">
         <v>2.5</v>
       </c>
-      <c r="P130">
-        <v>2.9</v>
-      </c>
-      <c r="Q130">
-        <v>0</v>
-      </c>
-      <c r="R130">
-        <v>0</v>
-      </c>
-      <c r="S130">
-        <v>0</v>
-      </c>
-      <c r="T130">
-        <v>0</v>
-      </c>
       <c r="U130">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V130">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="W130">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X130">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y130">
-        <v>1.83</v>
+        <v>1.4</v>
       </c>
       <c r="Z130">
-        <v>1.84</v>
+        <v>2.83</v>
       </c>
       <c r="AA130">
-        <v>3.5</v>
+        <v>2.25</v>
       </c>
       <c r="AB130">
-        <v>1.3</v>
+        <v>1.54</v>
       </c>
       <c r="AC130">
-        <v>0</v>
+        <v>3.96</v>
       </c>
       <c r="AD130">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AE130">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF130">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AG130">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AH130" t="inlineStr">
         <is>
@@ -21569,10 +21569,10 @@
         </is>
       </c>
       <c r="AJ130">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AK130">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="AL130">
         <v>0</v>
@@ -21603,7 +21603,7 @@
       </c>
       <c r="AU130" t="inlineStr">
         <is>
-          <t>2026-08-02 16:30:00</t>
+          <t>2026-08-02 17:30:00</t>
         </is>
       </c>
     </row>
@@ -21615,12 +21615,12 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>18:15</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -21630,12 +21630,12 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Washington Spirit</t>
+          <t>Club Always Ready</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>San Diego Wave</t>
+          <t>Bolívar</t>
         </is>
       </c>
       <c r="G131">
@@ -21662,64 +21662,64 @@
         </is>
       </c>
       <c r="N131">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="O131">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="P131">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="Q131">
-        <v>2.66</v>
+        <v>0</v>
       </c>
       <c r="R131">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="S131">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="T131">
-        <v>2.71</v>
+        <v>0</v>
       </c>
       <c r="U131">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="V131">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="W131">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="X131">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y131">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="Z131">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="AA131">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AB131">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AC131">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="AD131">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AE131">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AF131">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AG131">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AH131" t="inlineStr">
         <is>
@@ -21732,10 +21732,10 @@
         </is>
       </c>
       <c r="AJ131">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AK131">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AL131">
         <v>0</v>
@@ -21766,7 +21766,7 @@
       </c>
       <c r="AU131" t="inlineStr">
         <is>
-          <t>2026-08-02 17:00:00</t>
+          <t>2026-08-02 18:15:00</t>
         </is>
       </c>
     </row>
@@ -21778,12 +21778,12 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -21793,12 +21793,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Macará</t>
+          <t>Deportes Santa Cruz</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Guayaquil City FC</t>
+          <t>Santiago Wanderers</t>
         </is>
       </c>
       <c r="G132">
@@ -21825,64 +21825,64 @@
         </is>
       </c>
       <c r="N132">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="O132">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="P132">
-        <v>4.45</v>
+        <v>0</v>
       </c>
       <c r="Q132">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="R132">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="S132">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="T132">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="U132">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="V132">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="W132">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="X132">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y132">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="Z132">
-        <v>2.83</v>
+        <v>0</v>
       </c>
       <c r="AA132">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AB132">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="AC132">
-        <v>3.96</v>
+        <v>0</v>
       </c>
       <c r="AD132">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AE132">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AF132">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="AG132">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AH132" t="inlineStr">
         <is>
@@ -21895,10 +21895,10 @@
         </is>
       </c>
       <c r="AJ132">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AK132">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="AL132">
         <v>0</v>
@@ -21929,7 +21929,7 @@
       </c>
       <c r="AU132" t="inlineStr">
         <is>
-          <t>2026-08-02 17:30:00</t>
+          <t>2026-08-02 18:30:00</t>
         </is>
       </c>
     </row>
@@ -21941,12 +21941,12 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>18:15</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -21956,12 +21956,12 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Club Always Ready</t>
+          <t>Universidad Chile</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Bolívar</t>
+          <t>Huachipato</t>
         </is>
       </c>
       <c r="G133">
@@ -21988,64 +21988,64 @@
         </is>
       </c>
       <c r="N133">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="O133">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="P133">
-        <v>0</v>
+        <v>4.65</v>
       </c>
       <c r="Q133">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="R133">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="S133">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="T133">
-        <v>0</v>
+        <v>3.07</v>
       </c>
       <c r="U133">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="V133">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="W133">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X133">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y133">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z133">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AA133">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AB133">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AC133">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AD133">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AE133">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AF133">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AG133">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AH133" t="inlineStr">
         <is>
@@ -22058,10 +22058,10 @@
         </is>
       </c>
       <c r="AJ133">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AK133">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AL133">
         <v>0</v>
@@ -22092,7 +22092,7 @@
       </c>
       <c r="AU133" t="inlineStr">
         <is>
-          <t>2026-08-02 18:15:00</t>
+          <t>2026-08-02 18:30:00</t>
         </is>
       </c>
     </row>
@@ -22104,12 +22104,12 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -22119,12 +22119,12 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Deportes Santa Cruz</t>
+          <t>HFX Wanderers FC</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Santiago Wanderers</t>
+          <t>Forge FC</t>
         </is>
       </c>
       <c r="G134">
@@ -22151,13 +22151,13 @@
         </is>
       </c>
       <c r="N134">
-        <v>0</v>
+        <v>4.37</v>
       </c>
       <c r="O134">
-        <v>0</v>
+        <v>3.72</v>
       </c>
       <c r="P134">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="Q134">
         <v>0</v>
@@ -22190,10 +22190,10 @@
         <v>0</v>
       </c>
       <c r="AA134">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AB134">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AC134">
         <v>0</v>
@@ -22255,7 +22255,7 @@
       </c>
       <c r="AU134" t="inlineStr">
         <is>
-          <t>2026-08-02 18:30:00</t>
+          <t>2026-08-02 19:00:00</t>
         </is>
       </c>
     </row>
@@ -22267,12 +22267,12 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -22282,12 +22282,12 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Universidad Chile</t>
+          <t>Utah Royals</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Huachipato</t>
+          <t>Portland Thorns</t>
         </is>
       </c>
       <c r="G135">
@@ -22314,64 +22314,64 @@
         </is>
       </c>
       <c r="N135">
-        <v>1.62</v>
+        <v>1.95</v>
       </c>
       <c r="O135">
-        <v>3.9</v>
+        <v>3.54</v>
       </c>
       <c r="P135">
-        <v>4.65</v>
+        <v>3.27</v>
       </c>
       <c r="Q135">
-        <v>2.1</v>
+        <v>2.47</v>
       </c>
       <c r="R135">
         <v>2.25</v>
       </c>
       <c r="S135">
-        <v>1.35</v>
+        <v>1.26</v>
       </c>
       <c r="T135">
-        <v>3.07</v>
+        <v>3.28</v>
       </c>
       <c r="U135">
-        <v>2.6</v>
+        <v>2.31</v>
       </c>
       <c r="V135">
-        <v>1.43</v>
+        <v>1.5</v>
       </c>
       <c r="W135">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="X135">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y135">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="Z135">
-        <v>3.5</v>
+        <v>4.2</v>
       </c>
       <c r="AA135">
-        <v>1.83</v>
+        <v>1.61</v>
       </c>
       <c r="AB135">
-        <v>1.87</v>
+        <v>2.15</v>
       </c>
       <c r="AC135">
-        <v>3.2</v>
+        <v>2.49</v>
       </c>
       <c r="AD135">
-        <v>1.33</v>
+        <v>1.42</v>
       </c>
       <c r="AE135">
-        <v>1.09</v>
+        <v>1.13</v>
       </c>
       <c r="AF135">
-        <v>1.83</v>
+        <v>1.53</v>
       </c>
       <c r="AG135">
-        <v>1.85</v>
+        <v>2.24</v>
       </c>
       <c r="AH135" t="inlineStr">
         <is>
@@ -22384,10 +22384,10 @@
         </is>
       </c>
       <c r="AJ135">
-        <v>1.19</v>
+        <v>1.21</v>
       </c>
       <c r="AK135">
-        <v>2.08</v>
+        <v>1.69</v>
       </c>
       <c r="AL135">
         <v>0</v>
@@ -22418,7 +22418,7 @@
       </c>
       <c r="AU135" t="inlineStr">
         <is>
-          <t>2026-08-02 18:30:00</t>
+          <t>2026-08-02 20:00:00</t>
         </is>
       </c>
     </row>
@@ -22430,12 +22430,12 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>20:10</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
@@ -22445,12 +22445,12 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>HFX Wanderers FC</t>
+          <t>Leones del Norte</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Forge FC</t>
+          <t>Barcelona</t>
         </is>
       </c>
       <c r="G136">
@@ -22477,64 +22477,64 @@
         </is>
       </c>
       <c r="N136">
-        <v>4.37</v>
+        <v>0</v>
       </c>
       <c r="O136">
-        <v>3.72</v>
+        <v>0</v>
       </c>
       <c r="P136">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="Q136">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="R136">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="S136">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="T136">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="U136">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V136">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="W136">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X136">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y136">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="Z136">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AA136">
-        <v>1.65</v>
+        <v>2.3</v>
       </c>
       <c r="AB136">
-        <v>2.2</v>
+        <v>1.58</v>
       </c>
       <c r="AC136">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="AD136">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AE136">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AF136">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AG136">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AH136" t="inlineStr">
         <is>
@@ -22547,10 +22547,10 @@
         </is>
       </c>
       <c r="AJ136">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AK136">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AL136">
         <v>0</v>
@@ -22581,7 +22581,7 @@
       </c>
       <c r="AU136" t="inlineStr">
         <is>
-          <t>2026-08-02 19:00:00</t>
+          <t>2026-08-02 20:10:00</t>
         </is>
       </c>
     </row>
@@ -22593,12 +22593,12 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
@@ -22608,12 +22608,12 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Utah Royals</t>
+          <t>Oriente Petrolero</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Portland Thorns</t>
+          <t>Nacional Potosí</t>
         </is>
       </c>
       <c r="G137">
@@ -22640,64 +22640,64 @@
         </is>
       </c>
       <c r="N137">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="O137">
-        <v>3.54</v>
+        <v>0</v>
       </c>
       <c r="P137">
-        <v>3.27</v>
+        <v>0</v>
       </c>
       <c r="Q137">
-        <v>2.47</v>
+        <v>0</v>
       </c>
       <c r="R137">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="S137">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="T137">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="U137">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="V137">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="W137">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="X137">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y137">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="Z137">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="AA137">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AB137">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AC137">
-        <v>2.49</v>
+        <v>0</v>
       </c>
       <c r="AD137">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AE137">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AF137">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AG137">
-        <v>2.24</v>
+        <v>0</v>
       </c>
       <c r="AH137" t="inlineStr">
         <is>
@@ -22710,10 +22710,10 @@
         </is>
       </c>
       <c r="AJ137">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AK137">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="AL137">
         <v>0</v>
@@ -22744,7 +22744,7 @@
       </c>
       <c r="AU137" t="inlineStr">
         <is>
-          <t>2026-08-02 20:00:00</t>
+          <t>2026-08-02 20:30:00</t>
         </is>
       </c>
     </row>
@@ -22756,12 +22756,12 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>20:10</t>
+          <t>22:00</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -22771,12 +22771,12 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Leones del Norte</t>
+          <t>Denver Summit W</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Barcelona</t>
+          <t>Boston Legacy W</t>
         </is>
       </c>
       <c r="G138">
@@ -22803,64 +22803,64 @@
         </is>
       </c>
       <c r="N138">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="O138">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="P138">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="Q138">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="R138">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="S138">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="T138">
-        <v>2.44</v>
+        <v>0</v>
       </c>
       <c r="U138">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="V138">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="W138">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="X138">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="Y138">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="Z138">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="AA138">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AB138">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AC138">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="AD138">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AE138">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AF138">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="AG138">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AH138" t="inlineStr">
         <is>
@@ -22873,10 +22873,10 @@
         </is>
       </c>
       <c r="AJ138">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AK138">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AL138">
         <v>0</v>
@@ -22906,332 +22906,6 @@
         <v>0</v>
       </c>
       <c r="AU138" t="inlineStr">
-        <is>
-          <t>2026-08-02 20:10:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="139">
-      <c r="A139" t="inlineStr">
-        <is>
-          <t>2026-08-02</t>
-        </is>
-      </c>
-      <c r="B139" t="inlineStr">
-        <is>
-          <t>20:30</t>
-        </is>
-      </c>
-      <c r="C139" t="inlineStr">
-        <is>
-          <t>Bolivia LFPB</t>
-        </is>
-      </c>
-      <c r="D139" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="E139" t="inlineStr">
-        <is>
-          <t>Oriente Petrolero</t>
-        </is>
-      </c>
-      <c r="F139" t="inlineStr">
-        <is>
-          <t>Nacional Potosí</t>
-        </is>
-      </c>
-      <c r="G139">
-        <v>0</v>
-      </c>
-      <c r="H139">
-        <v>0</v>
-      </c>
-      <c r="I139">
-        <v>0</v>
-      </c>
-      <c r="J139">
-        <v>0</v>
-      </c>
-      <c r="K139">
-        <v>0</v>
-      </c>
-      <c r="L139">
-        <v>0</v>
-      </c>
-      <c r="M139" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="N139">
-        <v>0</v>
-      </c>
-      <c r="O139">
-        <v>0</v>
-      </c>
-      <c r="P139">
-        <v>0</v>
-      </c>
-      <c r="Q139">
-        <v>0</v>
-      </c>
-      <c r="R139">
-        <v>0</v>
-      </c>
-      <c r="S139">
-        <v>0</v>
-      </c>
-      <c r="T139">
-        <v>0</v>
-      </c>
-      <c r="U139">
-        <v>0</v>
-      </c>
-      <c r="V139">
-        <v>0</v>
-      </c>
-      <c r="W139">
-        <v>0</v>
-      </c>
-      <c r="X139">
-        <v>0</v>
-      </c>
-      <c r="Y139">
-        <v>0</v>
-      </c>
-      <c r="Z139">
-        <v>0</v>
-      </c>
-      <c r="AA139">
-        <v>0</v>
-      </c>
-      <c r="AB139">
-        <v>0</v>
-      </c>
-      <c r="AC139">
-        <v>0</v>
-      </c>
-      <c r="AD139">
-        <v>0</v>
-      </c>
-      <c r="AE139">
-        <v>0</v>
-      </c>
-      <c r="AF139">
-        <v>0</v>
-      </c>
-      <c r="AG139">
-        <v>0</v>
-      </c>
-      <c r="AH139" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI139" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ139">
-        <v>0</v>
-      </c>
-      <c r="AK139">
-        <v>0</v>
-      </c>
-      <c r="AL139">
-        <v>0</v>
-      </c>
-      <c r="AM139">
-        <v>-1</v>
-      </c>
-      <c r="AN139">
-        <v>-1</v>
-      </c>
-      <c r="AO139">
-        <v>-1</v>
-      </c>
-      <c r="AP139">
-        <v>-1</v>
-      </c>
-      <c r="AQ139">
-        <v>0</v>
-      </c>
-      <c r="AR139">
-        <v>0</v>
-      </c>
-      <c r="AS139">
-        <v>0</v>
-      </c>
-      <c r="AT139">
-        <v>0</v>
-      </c>
-      <c r="AU139" t="inlineStr">
-        <is>
-          <t>2026-08-02 20:30:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="140">
-      <c r="A140" t="inlineStr">
-        <is>
-          <t>2026-08-02</t>
-        </is>
-      </c>
-      <c r="B140" t="inlineStr">
-        <is>
-          <t>22:00</t>
-        </is>
-      </c>
-      <c r="C140" t="inlineStr">
-        <is>
-          <t>USA NWSL</t>
-        </is>
-      </c>
-      <c r="D140" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="E140" t="inlineStr">
-        <is>
-          <t>Denver Summit W</t>
-        </is>
-      </c>
-      <c r="F140" t="inlineStr">
-        <is>
-          <t>Boston Legacy W</t>
-        </is>
-      </c>
-      <c r="G140">
-        <v>0</v>
-      </c>
-      <c r="H140">
-        <v>0</v>
-      </c>
-      <c r="I140">
-        <v>0</v>
-      </c>
-      <c r="J140">
-        <v>0</v>
-      </c>
-      <c r="K140">
-        <v>0</v>
-      </c>
-      <c r="L140">
-        <v>0</v>
-      </c>
-      <c r="M140" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="N140">
-        <v>1.84</v>
-      </c>
-      <c r="O140">
-        <v>3.6</v>
-      </c>
-      <c r="P140">
-        <v>3.5</v>
-      </c>
-      <c r="Q140">
-        <v>0</v>
-      </c>
-      <c r="R140">
-        <v>0</v>
-      </c>
-      <c r="S140">
-        <v>0</v>
-      </c>
-      <c r="T140">
-        <v>0</v>
-      </c>
-      <c r="U140">
-        <v>0</v>
-      </c>
-      <c r="V140">
-        <v>0</v>
-      </c>
-      <c r="W140">
-        <v>0</v>
-      </c>
-      <c r="X140">
-        <v>0</v>
-      </c>
-      <c r="Y140">
-        <v>0</v>
-      </c>
-      <c r="Z140">
-        <v>0</v>
-      </c>
-      <c r="AA140">
-        <v>0</v>
-      </c>
-      <c r="AB140">
-        <v>0</v>
-      </c>
-      <c r="AC140">
-        <v>0</v>
-      </c>
-      <c r="AD140">
-        <v>0</v>
-      </c>
-      <c r="AE140">
-        <v>0</v>
-      </c>
-      <c r="AF140">
-        <v>0</v>
-      </c>
-      <c r="AG140">
-        <v>0</v>
-      </c>
-      <c r="AH140" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI140" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ140">
-        <v>0</v>
-      </c>
-      <c r="AK140">
-        <v>0</v>
-      </c>
-      <c r="AL140">
-        <v>0</v>
-      </c>
-      <c r="AM140">
-        <v>-1</v>
-      </c>
-      <c r="AN140">
-        <v>-1</v>
-      </c>
-      <c r="AO140">
-        <v>-1</v>
-      </c>
-      <c r="AP140">
-        <v>-1</v>
-      </c>
-      <c r="AQ140">
-        <v>0</v>
-      </c>
-      <c r="AR140">
-        <v>0</v>
-      </c>
-      <c r="AS140">
-        <v>0</v>
-      </c>
-      <c r="AT140">
-        <v>0</v>
-      </c>
-      <c r="AU140" t="inlineStr">
         <is>
           <t>2026-08-02 22:00:00</t>
         </is>

--- a/jogos_2026-08-02.xlsx
+++ b/jogos_2026-08-02.xlsx
@@ -11361,12 +11361,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Raufoss</t>
+          <t>Odd</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Stabæk</t>
+          <t>Åsane</t>
         </is>
       </c>
       <c r="G68">
@@ -11393,34 +11393,34 @@
         </is>
       </c>
       <c r="N68">
-        <v>4.5</v>
+        <v>1.39</v>
       </c>
       <c r="O68">
-        <v>4</v>
+        <v>4.75</v>
       </c>
       <c r="P68">
-        <v>1.54</v>
+        <v>5.3</v>
       </c>
       <c r="Q68">
-        <v>4.74</v>
+        <v>1.79</v>
       </c>
       <c r="R68">
-        <v>2.53</v>
+        <v>2.75</v>
       </c>
       <c r="S68">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="T68">
-        <v>4.2</v>
+        <v>4.33</v>
       </c>
       <c r="U68">
-        <v>1.94</v>
+        <v>1.99</v>
       </c>
       <c r="V68">
-        <v>1.76</v>
+        <v>1.83</v>
       </c>
       <c r="W68">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="X68">
         <v>1.01</v>
@@ -11429,28 +11429,28 @@
         <v>1.1</v>
       </c>
       <c r="Z68">
-        <v>6.47</v>
+        <v>6.6</v>
       </c>
       <c r="AA68">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="AB68">
-        <v>2.92</v>
+        <v>2.85</v>
       </c>
       <c r="AC68">
-        <v>1.98</v>
+        <v>1.88</v>
       </c>
       <c r="AD68">
-        <v>1.71</v>
+        <v>1.91</v>
       </c>
       <c r="AE68">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="AF68">
-        <v>1.4</v>
+        <v>1.49</v>
       </c>
       <c r="AG68">
-        <v>2.73</v>
+        <v>2.45</v>
       </c>
       <c r="AH68" t="inlineStr">
         <is>
@@ -11463,10 +11463,10 @@
         </is>
       </c>
       <c r="AJ68">
-        <v>1.18</v>
+        <v>1.13</v>
       </c>
       <c r="AK68">
-        <v>1.15</v>
+        <v>2.7</v>
       </c>
       <c r="AL68">
         <v>0</v>
@@ -11524,12 +11524,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Odd</t>
+          <t>Raufoss</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Åsane</t>
+          <t>Stabæk</t>
         </is>
       </c>
       <c r="G69">
@@ -11556,34 +11556,34 @@
         </is>
       </c>
       <c r="N69">
-        <v>1.39</v>
+        <v>4.5</v>
       </c>
       <c r="O69">
-        <v>4.75</v>
+        <v>4</v>
       </c>
       <c r="P69">
-        <v>5.3</v>
+        <v>1.54</v>
       </c>
       <c r="Q69">
-        <v>1.79</v>
+        <v>4.74</v>
       </c>
       <c r="R69">
-        <v>2.75</v>
+        <v>2.53</v>
       </c>
       <c r="S69">
+        <v>1.17</v>
+      </c>
+      <c r="T69">
+        <v>4.2</v>
+      </c>
+      <c r="U69">
+        <v>1.94</v>
+      </c>
+      <c r="V69">
+        <v>1.76</v>
+      </c>
+      <c r="W69">
         <v>1.18</v>
-      </c>
-      <c r="T69">
-        <v>4.33</v>
-      </c>
-      <c r="U69">
-        <v>1.99</v>
-      </c>
-      <c r="V69">
-        <v>1.83</v>
-      </c>
-      <c r="W69">
-        <v>1.2</v>
       </c>
       <c r="X69">
         <v>1.01</v>
@@ -11592,28 +11592,28 @@
         <v>1.1</v>
       </c>
       <c r="Z69">
-        <v>6.6</v>
+        <v>6.47</v>
       </c>
       <c r="AA69">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="AB69">
-        <v>2.85</v>
+        <v>2.92</v>
       </c>
       <c r="AC69">
-        <v>1.88</v>
+        <v>1.98</v>
       </c>
       <c r="AD69">
-        <v>1.91</v>
+        <v>1.71</v>
       </c>
       <c r="AE69">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="AF69">
-        <v>1.49</v>
+        <v>1.4</v>
       </c>
       <c r="AG69">
-        <v>2.45</v>
+        <v>2.73</v>
       </c>
       <c r="AH69" t="inlineStr">
         <is>
@@ -11626,10 +11626,10 @@
         </is>
       </c>
       <c r="AJ69">
-        <v>1.13</v>
+        <v>1.18</v>
       </c>
       <c r="AK69">
-        <v>2.7</v>
+        <v>1.15</v>
       </c>
       <c r="AL69">
         <v>0</v>

--- a/jogos_2026-08-02.xlsx
+++ b/jogos_2026-08-02.xlsx
@@ -1652,10 +1652,10 @@
         <v>2.97</v>
       </c>
       <c r="AA8">
-        <v>2.11</v>
+        <v>2.13</v>
       </c>
       <c r="AB8">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="AC8">
         <v>3.68</v>
@@ -1670,7 +1670,7 @@
         <v>1.92</v>
       </c>
       <c r="AG8">
-        <v>1.79</v>
+        <v>1.77</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1948,55 +1948,55 @@
         <v>0</v>
       </c>
       <c r="Q10">
-        <v>2.27</v>
+        <v>2.2</v>
       </c>
       <c r="R10">
-        <v>2.3</v>
+        <v>2.38</v>
       </c>
       <c r="S10">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="T10">
-        <v>3.6</v>
+        <v>3.35</v>
       </c>
       <c r="U10">
         <v>2.33</v>
       </c>
       <c r="V10">
-        <v>1.51</v>
+        <v>1.53</v>
       </c>
       <c r="W10">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="X10">
         <v>1.03</v>
       </c>
       <c r="Y10">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="Z10">
-        <v>4.53</v>
+        <v>4.74</v>
       </c>
       <c r="AA10">
-        <v>1.63</v>
+        <v>1.65</v>
       </c>
       <c r="AB10">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="AC10">
-        <v>2.57</v>
+        <v>2.44</v>
       </c>
       <c r="AD10">
-        <v>1.46</v>
+        <v>1.5</v>
       </c>
       <c r="AE10">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="AF10">
-        <v>1.67</v>
+        <v>1.57</v>
       </c>
       <c r="AG10">
-        <v>2.18</v>
+        <v>2.22</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2012,7 +2012,7 @@
         <v>1.22</v>
       </c>
       <c r="AK10">
-        <v>2</v>
+        <v>2.09</v>
       </c>
       <c r="AL10">
         <v>0</v>
@@ -2559,12 +2559,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Ansan Greeners</t>
+          <t>Gimpo Citizen</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Gimhae City</t>
+          <t>Gyeongnam</t>
         </is>
       </c>
       <c r="G14">
@@ -2591,80 +2591,80 @@
         </is>
       </c>
       <c r="N14">
-        <v>2.91</v>
+        <v>1.94</v>
       </c>
       <c r="O14">
-        <v>3.38</v>
+        <v>2.98</v>
       </c>
       <c r="P14">
+        <v>3.05</v>
+      </c>
+      <c r="Q14">
+        <v>2.62</v>
+      </c>
+      <c r="R14">
         <v>2.18</v>
       </c>
-      <c r="Q14">
-        <v>3.4</v>
-      </c>
-      <c r="R14">
-        <v>2.2</v>
-      </c>
       <c r="S14">
-        <v>1.34</v>
+        <v>1.4</v>
       </c>
       <c r="T14">
-        <v>2.88</v>
+        <v>2.47</v>
       </c>
       <c r="U14">
-        <v>2.66</v>
+        <v>3.12</v>
       </c>
       <c r="V14">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="W14">
-        <v>1.08</v>
+        <v>1.02</v>
       </c>
       <c r="X14">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y14">
-        <v>1.23</v>
+        <v>1.36</v>
       </c>
       <c r="Z14">
-        <v>3.68</v>
+        <v>2.7</v>
       </c>
       <c r="AA14">
+        <v>2.03</v>
+      </c>
+      <c r="AB14">
+        <v>1.73</v>
+      </c>
+      <c r="AC14">
+        <v>3.2</v>
+      </c>
+      <c r="AD14">
+        <v>1.18</v>
+      </c>
+      <c r="AE14">
+        <v>1.03</v>
+      </c>
+      <c r="AF14">
+        <v>1.85</v>
+      </c>
+      <c r="AG14">
+        <v>1.8</v>
+      </c>
+      <c r="AH14" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI14" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ14">
+        <v>1.22</v>
+      </c>
+      <c r="AK14">
         <v>1.84</v>
-      </c>
-      <c r="AB14">
-        <v>1.95</v>
-      </c>
-      <c r="AC14">
-        <v>3.1</v>
-      </c>
-      <c r="AD14">
-        <v>1.34</v>
-      </c>
-      <c r="AE14">
-        <v>1.13</v>
-      </c>
-      <c r="AF14">
-        <v>1.67</v>
-      </c>
-      <c r="AG14">
-        <v>2.1</v>
-      </c>
-      <c r="AH14" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI14" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ14">
-        <v>1.62</v>
-      </c>
-      <c r="AK14">
-        <v>1.36</v>
       </c>
       <c r="AL14">
         <v>0</v>
@@ -2754,13 +2754,13 @@
         </is>
       </c>
       <c r="N15">
-        <v>2.75</v>
+        <v>2.42</v>
       </c>
       <c r="O15">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="P15">
-        <v>2.2</v>
+        <v>2.17</v>
       </c>
       <c r="Q15">
         <v>3.1</v>
@@ -2772,13 +2772,13 @@
         <v>1.3</v>
       </c>
       <c r="T15">
-        <v>3.25</v>
+        <v>3.15</v>
       </c>
       <c r="U15">
         <v>2.5</v>
       </c>
       <c r="V15">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="W15">
         <v>1.11</v>
@@ -2793,13 +2793,13 @@
         <v>4.05</v>
       </c>
       <c r="AA15">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="AB15">
         <v>1.96</v>
       </c>
       <c r="AC15">
-        <v>2.66</v>
+        <v>2.62</v>
       </c>
       <c r="AD15">
         <v>1.44</v>
@@ -2885,12 +2885,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Gimpo Citizen</t>
+          <t>Jeonnam Dragons</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Gyeongnam</t>
+          <t>Paju Citizen</t>
         </is>
       </c>
       <c r="G16">
@@ -2917,64 +2917,64 @@
         </is>
       </c>
       <c r="N16">
-        <v>1.85</v>
+        <v>1.97</v>
       </c>
       <c r="O16">
-        <v>2.98</v>
+        <v>3.32</v>
       </c>
       <c r="P16">
-        <v>3.28</v>
+        <v>3.45</v>
       </c>
       <c r="Q16">
-        <v>2.47</v>
+        <v>2.68</v>
       </c>
       <c r="R16">
-        <v>2.18</v>
+        <v>2.09</v>
       </c>
       <c r="S16">
+        <v>1.33</v>
+      </c>
+      <c r="T16">
+        <v>2.9</v>
+      </c>
+      <c r="U16">
+        <v>2.71</v>
+      </c>
+      <c r="V16">
         <v>1.4</v>
       </c>
-      <c r="T16">
-        <v>2.5</v>
-      </c>
-      <c r="U16">
-        <v>3.28</v>
-      </c>
-      <c r="V16">
-        <v>1.33</v>
-      </c>
       <c r="W16">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="X16">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y16">
-        <v>1.35</v>
+        <v>1.28</v>
       </c>
       <c r="Z16">
-        <v>2.74</v>
+        <v>3.55</v>
       </c>
       <c r="AA16">
-        <v>2.14</v>
+        <v>1.8</v>
       </c>
       <c r="AB16">
-        <v>1.73</v>
+        <v>1.93</v>
       </c>
       <c r="AC16">
-        <v>3.2</v>
+        <v>2.7</v>
       </c>
       <c r="AD16">
-        <v>1.25</v>
+        <v>1.31</v>
       </c>
       <c r="AE16">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="AF16">
-        <v>1.85</v>
+        <v>1.64</v>
       </c>
       <c r="AG16">
-        <v>1.8</v>
+        <v>2.1</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -2987,10 +2987,10 @@
         </is>
       </c>
       <c r="AJ16">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="AK16">
-        <v>1.84</v>
+        <v>1.63</v>
       </c>
       <c r="AL16">
         <v>0</v>
@@ -3048,12 +3048,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Jeonnam Dragons</t>
+          <t>Ansan Greeners</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Paju Citizen</t>
+          <t>Gimhae City</t>
         </is>
       </c>
       <c r="G17">
@@ -3080,16 +3080,16 @@
         </is>
       </c>
       <c r="N17">
-        <v>1.97</v>
+        <v>2.91</v>
       </c>
       <c r="O17">
-        <v>3.32</v>
+        <v>3.38</v>
       </c>
       <c r="P17">
-        <v>3.45</v>
+        <v>2.18</v>
       </c>
       <c r="Q17">
-        <v>2.68</v>
+        <v>3.28</v>
       </c>
       <c r="R17">
         <v>2.2</v>
@@ -3098,62 +3098,62 @@
         <v>1.35</v>
       </c>
       <c r="T17">
-        <v>2.88</v>
+        <v>2.82</v>
       </c>
       <c r="U17">
-        <v>2.62</v>
+        <v>2.74</v>
       </c>
       <c r="V17">
         <v>1.4</v>
       </c>
       <c r="W17">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="X17">
         <v>1.01</v>
       </c>
       <c r="Y17">
+        <v>1.24</v>
+      </c>
+      <c r="Z17">
+        <v>3.34</v>
+      </c>
+      <c r="AA17">
+        <v>1.86</v>
+      </c>
+      <c r="AB17">
+        <v>1.85</v>
+      </c>
+      <c r="AC17">
+        <v>3.2</v>
+      </c>
+      <c r="AD17">
         <v>1.28</v>
       </c>
-      <c r="Z17">
-        <v>3.55</v>
-      </c>
-      <c r="AA17">
-        <v>1.8</v>
-      </c>
-      <c r="AB17">
-        <v>1.93</v>
-      </c>
-      <c r="AC17">
-        <v>2.7</v>
-      </c>
-      <c r="AD17">
+      <c r="AE17">
+        <v>1.11</v>
+      </c>
+      <c r="AF17">
+        <v>1.67</v>
+      </c>
+      <c r="AG17">
+        <v>2.1</v>
+      </c>
+      <c r="AH17" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI17" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ17">
+        <v>1.62</v>
+      </c>
+      <c r="AK17">
         <v>1.36</v>
-      </c>
-      <c r="AE17">
-        <v>1.08</v>
-      </c>
-      <c r="AF17">
-        <v>1.58</v>
-      </c>
-      <c r="AG17">
-        <v>2.07</v>
-      </c>
-      <c r="AH17" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI17" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ17">
-        <v>1.3</v>
-      </c>
-      <c r="AK17">
-        <v>1.67</v>
       </c>
       <c r="AL17">
         <v>0</v>
@@ -3747,7 +3747,7 @@
         <v>2.5</v>
       </c>
       <c r="S21">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="T21">
         <v>3.68</v>
@@ -3771,7 +3771,7 @@
         <v>5</v>
       </c>
       <c r="AA21">
-        <v>1.44</v>
+        <v>1.48</v>
       </c>
       <c r="AB21">
         <v>2.6</v>
@@ -3780,10 +3780,10 @@
         <v>2.15</v>
       </c>
       <c r="AD21">
-        <v>1.66</v>
+        <v>1.69</v>
       </c>
       <c r="AE21">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="AF21">
         <v>1.44</v>
@@ -3919,7 +3919,7 @@
         <v>2.69</v>
       </c>
       <c r="V22">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="W22">
         <v>1.06</v>
@@ -3928,13 +3928,13 @@
         <v>1.03</v>
       </c>
       <c r="Y22">
-        <v>1.28</v>
+        <v>1.23</v>
       </c>
       <c r="Z22">
-        <v>3.4</v>
+        <v>3.55</v>
       </c>
       <c r="AA22">
-        <v>1.94</v>
+        <v>1.77</v>
       </c>
       <c r="AB22">
         <v>1.83</v>
@@ -3949,7 +3949,7 @@
         <v>1.08</v>
       </c>
       <c r="AF22">
-        <v>1.73</v>
+        <v>1.71</v>
       </c>
       <c r="AG22">
         <v>2</v>
@@ -3965,10 +3965,10 @@
         </is>
       </c>
       <c r="AJ22">
-        <v>1.26</v>
+        <v>1.32</v>
       </c>
       <c r="AK22">
-        <v>1.66</v>
+        <v>1.68</v>
       </c>
       <c r="AL22">
         <v>0</v>
@@ -4058,19 +4058,19 @@
         </is>
       </c>
       <c r="N23">
-        <v>2.97</v>
+        <v>2.7</v>
       </c>
       <c r="O23">
         <v>3.8</v>
       </c>
       <c r="P23">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="Q23">
-        <v>3.4</v>
+        <v>3.48</v>
       </c>
       <c r="R23">
-        <v>2.4</v>
+        <v>2.35</v>
       </c>
       <c r="S23">
         <v>1.22</v>
@@ -4109,13 +4109,13 @@
         <v>1.64</v>
       </c>
       <c r="AE23">
-        <v>1.22</v>
+        <v>1.27</v>
       </c>
       <c r="AF23">
         <v>1.44</v>
       </c>
       <c r="AG23">
-        <v>2.5</v>
+        <v>2.63</v>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
@@ -4221,19 +4221,19 @@
         </is>
       </c>
       <c r="N24">
-        <v>2.8</v>
+        <v>2.31</v>
       </c>
       <c r="O24">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="P24">
-        <v>2.47</v>
+        <v>2.43</v>
       </c>
       <c r="Q24">
-        <v>3</v>
+        <v>3.58</v>
       </c>
       <c r="R24">
-        <v>1.93</v>
+        <v>2.07</v>
       </c>
       <c r="S24">
         <v>1.48</v>
@@ -4245,7 +4245,7 @@
         <v>3.29</v>
       </c>
       <c r="V24">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="W24">
         <v>1.02</v>
@@ -4254,7 +4254,7 @@
         <v>1.04</v>
       </c>
       <c r="Y24">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="Z24">
         <v>2.7</v>
@@ -4294,7 +4294,7 @@
         <v>1.27</v>
       </c>
       <c r="AK24">
-        <v>1.41</v>
+        <v>1.38</v>
       </c>
       <c r="AL24">
         <v>0</v>
@@ -4710,19 +4710,19 @@
         </is>
       </c>
       <c r="N27">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="O27">
-        <v>5.4</v>
+        <v>4.95</v>
       </c>
       <c r="P27">
         <v>7.95</v>
       </c>
       <c r="Q27">
-        <v>1.71</v>
+        <v>1.73</v>
       </c>
       <c r="R27">
-        <v>2.62</v>
+        <v>2.83</v>
       </c>
       <c r="S27">
         <v>1.24</v>
@@ -4731,7 +4731,7 @@
         <v>3.65</v>
       </c>
       <c r="U27">
-        <v>2.16</v>
+        <v>2.15</v>
       </c>
       <c r="V27">
         <v>1.6</v>
@@ -4749,7 +4749,7 @@
         <v>4.7</v>
       </c>
       <c r="AA27">
-        <v>1.47</v>
+        <v>1.53</v>
       </c>
       <c r="AB27">
         <v>2.38</v>
@@ -4764,10 +4764,10 @@
         <v>1.24</v>
       </c>
       <c r="AF27">
-        <v>1.76</v>
+        <v>1.79</v>
       </c>
       <c r="AG27">
-        <v>1.9</v>
+        <v>1.92</v>
       </c>
       <c r="AH27" t="inlineStr">
         <is>
@@ -4783,7 +4783,7 @@
         <v>1.05</v>
       </c>
       <c r="AK27">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="AL27">
         <v>0</v>
@@ -4873,13 +4873,13 @@
         </is>
       </c>
       <c r="N28">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="O28">
-        <v>3.8</v>
+        <v>3.88</v>
       </c>
       <c r="P28">
-        <v>4.33</v>
+        <v>4.15</v>
       </c>
       <c r="Q28">
         <v>2.18</v>
@@ -4900,10 +4900,10 @@
         <v>1.55</v>
       </c>
       <c r="W28">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="X28">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y28">
         <v>1.2</v>
@@ -4912,16 +4912,16 @@
         <v>4.53</v>
       </c>
       <c r="AA28">
-        <v>1.57</v>
+        <v>1.66</v>
       </c>
       <c r="AB28">
-        <v>2.26</v>
+        <v>2.15</v>
       </c>
       <c r="AC28">
-        <v>2.65</v>
+        <v>2.62</v>
       </c>
       <c r="AD28">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="AE28">
         <v>1.2</v>
@@ -4930,7 +4930,7 @@
         <v>1.57</v>
       </c>
       <c r="AG28">
-        <v>2.23</v>
+        <v>2.18</v>
       </c>
       <c r="AH28" t="inlineStr">
         <is>
@@ -5051,7 +5051,7 @@
         <v>2.1</v>
       </c>
       <c r="S29">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="T29">
         <v>2.7</v>
@@ -5072,10 +5072,10 @@
         <v>1.3</v>
       </c>
       <c r="Z29">
-        <v>3.1</v>
+        <v>3.55</v>
       </c>
       <c r="AA29">
-        <v>1.79</v>
+        <v>2.01</v>
       </c>
       <c r="AB29">
         <v>1.77</v>
@@ -5090,7 +5090,7 @@
         <v>1.06</v>
       </c>
       <c r="AF29">
-        <v>1.9</v>
+        <v>1.64</v>
       </c>
       <c r="AG29">
         <v>1.82</v>
@@ -5202,10 +5202,10 @@
         <v>1.55</v>
       </c>
       <c r="O30">
-        <v>3.8</v>
+        <v>3.52</v>
       </c>
       <c r="P30">
-        <v>5.5</v>
+        <v>7.24</v>
       </c>
       <c r="Q30">
         <v>0</v>
@@ -5362,13 +5362,13 @@
         </is>
       </c>
       <c r="N31">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="O31">
         <v>3.4</v>
       </c>
       <c r="P31">
-        <v>3.05</v>
+        <v>3.15</v>
       </c>
       <c r="Q31">
         <v>2.62</v>
@@ -5377,7 +5377,7 @@
         <v>2.19</v>
       </c>
       <c r="S31">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="T31">
         <v>3.12</v>
@@ -5386,7 +5386,7 @@
         <v>2.59</v>
       </c>
       <c r="V31">
-        <v>1.44</v>
+        <v>1.47</v>
       </c>
       <c r="W31">
         <v>1.09</v>
@@ -5419,7 +5419,7 @@
         <v>1.6</v>
       </c>
       <c r="AG31">
-        <v>2.19</v>
+        <v>2.2</v>
       </c>
       <c r="AH31" t="inlineStr">
         <is>
@@ -5528,16 +5528,16 @@
         <v>1.55</v>
       </c>
       <c r="O32">
-        <v>3.9</v>
+        <v>3.7</v>
       </c>
       <c r="P32">
-        <v>5.59</v>
+        <v>4.7</v>
       </c>
       <c r="Q32">
         <v>2.1</v>
       </c>
       <c r="R32">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="S32">
         <v>1.35</v>
@@ -5549,13 +5549,13 @@
         <v>2.75</v>
       </c>
       <c r="V32">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="W32">
         <v>1.05</v>
       </c>
       <c r="X32">
-        <v>1.03</v>
+        <v>1</v>
       </c>
       <c r="Y32">
         <v>1.25</v>
@@ -5570,13 +5570,13 @@
         <v>1.94</v>
       </c>
       <c r="AC32">
-        <v>2.97</v>
+        <v>3.2</v>
       </c>
       <c r="AD32">
         <v>1.33</v>
       </c>
       <c r="AE32">
-        <v>1.12</v>
+        <v>1.08</v>
       </c>
       <c r="AF32">
         <v>1.87</v>
@@ -5598,7 +5598,7 @@
         <v>1.11</v>
       </c>
       <c r="AK32">
-        <v>2.3</v>
+        <v>2.31</v>
       </c>
       <c r="AL32">
         <v>0</v>
@@ -5691,7 +5691,7 @@
         <v>2.6</v>
       </c>
       <c r="O33">
-        <v>2.6</v>
+        <v>2.7</v>
       </c>
       <c r="P33">
         <v>2.95</v>
@@ -5706,25 +5706,25 @@
         <v>1.62</v>
       </c>
       <c r="T33">
-        <v>2.07</v>
+        <v>2.2</v>
       </c>
       <c r="U33">
-        <v>3.9</v>
+        <v>4.33</v>
       </c>
       <c r="V33">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="W33">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="X33">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="Y33">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="Z33">
-        <v>2.17</v>
+        <v>2.16</v>
       </c>
       <c r="AA33">
         <v>2.78</v>
@@ -5739,7 +5739,7 @@
         <v>1.11</v>
       </c>
       <c r="AE33">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AF33">
         <v>2.23</v>
@@ -5758,10 +5758,10 @@
         </is>
       </c>
       <c r="AJ33">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="AK33">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="AL33">
         <v>0</v>
@@ -5860,7 +5860,7 @@
         <v>0</v>
       </c>
       <c r="Q34">
-        <v>3.02</v>
+        <v>2.7</v>
       </c>
       <c r="R34">
         <v>1.96</v>
@@ -5890,10 +5890,10 @@
         <v>2.98</v>
       </c>
       <c r="AA34">
-        <v>2.18</v>
+        <v>2.19</v>
       </c>
       <c r="AB34">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="AC34">
         <v>3.74</v>
@@ -6014,10 +6014,10 @@
         </is>
       </c>
       <c r="N35">
-        <v>1.78</v>
+        <v>1.76</v>
       </c>
       <c r="O35">
-        <v>3.65</v>
+        <v>3.88</v>
       </c>
       <c r="P35">
         <v>4.03</v>
@@ -6029,10 +6029,10 @@
         <v>2.3</v>
       </c>
       <c r="S35">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="T35">
-        <v>3.6</v>
+        <v>3.35</v>
       </c>
       <c r="U35">
         <v>2.38</v>
@@ -6044,7 +6044,7 @@
         <v>1.12</v>
       </c>
       <c r="X35">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y35">
         <v>1.14</v>
@@ -6056,13 +6056,13 @@
         <v>1.59</v>
       </c>
       <c r="AB35">
-        <v>2.29</v>
+        <v>2.15</v>
       </c>
       <c r="AC35">
         <v>2.38</v>
       </c>
       <c r="AD35">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="AE35">
         <v>1.15</v>
@@ -6087,7 +6087,7 @@
         <v>1.17</v>
       </c>
       <c r="AK35">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="AL35">
         <v>0</v>
@@ -6669,16 +6669,16 @@
         <v>8.050000000000001</v>
       </c>
       <c r="O39">
-        <v>4.8</v>
+        <v>4.4</v>
       </c>
       <c r="P39">
-        <v>1.33</v>
+        <v>1.37</v>
       </c>
       <c r="Q39">
         <v>7.1</v>
       </c>
       <c r="R39">
-        <v>2.24</v>
+        <v>2.47</v>
       </c>
       <c r="S39">
         <v>1.33</v>
@@ -6829,19 +6829,19 @@
         </is>
       </c>
       <c r="N40">
-        <v>2.17</v>
+        <v>2.18</v>
       </c>
       <c r="O40">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="P40">
-        <v>3.1</v>
+        <v>2.83</v>
       </c>
       <c r="Q40">
-        <v>2.5</v>
+        <v>2.75</v>
       </c>
       <c r="R40">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="S40">
         <v>1.35</v>
@@ -6850,16 +6850,16 @@
         <v>2.94</v>
       </c>
       <c r="U40">
-        <v>2.75</v>
+        <v>2.49</v>
       </c>
       <c r="V40">
-        <v>1.43</v>
+        <v>1.45</v>
       </c>
       <c r="W40">
         <v>1.06</v>
       </c>
       <c r="X40">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="Y40">
         <v>1.24</v>
@@ -6886,7 +6886,7 @@
         <v>1.62</v>
       </c>
       <c r="AG40">
-        <v>2.15</v>
+        <v>2.14</v>
       </c>
       <c r="AH40" t="inlineStr">
         <is>
@@ -6902,7 +6902,7 @@
         <v>1.3</v>
       </c>
       <c r="AK40">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="AL40">
         <v>0</v>
@@ -7028,19 +7028,19 @@
         <v>1.3</v>
       </c>
       <c r="Z41">
-        <v>2.8</v>
+        <v>3.2</v>
       </c>
       <c r="AA41">
         <v>2.15</v>
       </c>
       <c r="AB41">
-        <v>1.61</v>
+        <v>1.77</v>
       </c>
       <c r="AC41">
-        <v>3.85</v>
+        <v>3.3</v>
       </c>
       <c r="AD41">
-        <v>1.21</v>
+        <v>1.27</v>
       </c>
       <c r="AE41">
         <v>1.06</v>
@@ -7062,10 +7062,10 @@
         </is>
       </c>
       <c r="AJ41">
-        <v>1.29</v>
+        <v>1.73</v>
       </c>
       <c r="AK41">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AL41">
         <v>0</v>
@@ -7167,7 +7167,7 @@
         <v>2.6</v>
       </c>
       <c r="R42">
-        <v>2.25</v>
+        <v>2.13</v>
       </c>
       <c r="S42">
         <v>1.31</v>
@@ -7191,7 +7191,7 @@
         <v>1.17</v>
       </c>
       <c r="Z42">
-        <v>3.96</v>
+        <v>3.8</v>
       </c>
       <c r="AA42">
         <v>1.69</v>
@@ -7206,10 +7206,10 @@
         <v>1.37</v>
       </c>
       <c r="AE42">
-        <v>1.16</v>
+        <v>1.14</v>
       </c>
       <c r="AF42">
-        <v>1.6</v>
+        <v>1.56</v>
       </c>
       <c r="AG42">
         <v>2.25</v>
@@ -7225,7 +7225,7 @@
         </is>
       </c>
       <c r="AJ42">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AK42">
         <v>1.65</v>
@@ -7520,7 +7520,7 @@
         <v>2.74</v>
       </c>
       <c r="AA44">
-        <v>2.21</v>
+        <v>2.17</v>
       </c>
       <c r="AB44">
         <v>1.65</v>
@@ -7551,10 +7551,10 @@
         </is>
       </c>
       <c r="AJ44">
-        <v>1.26</v>
+        <v>1.24</v>
       </c>
       <c r="AK44">
-        <v>2.19</v>
+        <v>2.16</v>
       </c>
       <c r="AL44">
         <v>0</v>
@@ -7644,25 +7644,25 @@
         </is>
       </c>
       <c r="N45">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="O45">
-        <v>4</v>
+        <v>4.15</v>
       </c>
       <c r="P45">
-        <v>5.25</v>
+        <v>5.75</v>
       </c>
       <c r="Q45">
-        <v>1.98</v>
+        <v>2.02</v>
       </c>
       <c r="R45">
         <v>2.5</v>
       </c>
       <c r="S45">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="T45">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="U45">
         <v>2.25</v>
@@ -7671,7 +7671,7 @@
         <v>1.57</v>
       </c>
       <c r="W45">
-        <v>1.14</v>
+        <v>1.11</v>
       </c>
       <c r="X45">
         <v>1.01</v>
@@ -7680,28 +7680,28 @@
         <v>1.14</v>
       </c>
       <c r="Z45">
-        <v>4.4</v>
+        <v>4.45</v>
       </c>
       <c r="AA45">
+        <v>1.55</v>
+      </c>
+      <c r="AB45">
+        <v>2.35</v>
+      </c>
+      <c r="AC45">
+        <v>2.28</v>
+      </c>
+      <c r="AD45">
+        <v>1.5</v>
+      </c>
+      <c r="AE45">
+        <v>1.18</v>
+      </c>
+      <c r="AF45">
         <v>1.56</v>
       </c>
-      <c r="AB45">
-        <v>2.27</v>
-      </c>
-      <c r="AC45">
-        <v>2.3</v>
-      </c>
-      <c r="AD45">
-        <v>1.49</v>
-      </c>
-      <c r="AE45">
-        <v>1.17</v>
-      </c>
-      <c r="AF45">
-        <v>1.66</v>
-      </c>
       <c r="AG45">
-        <v>2.04</v>
+        <v>2.18</v>
       </c>
       <c r="AH45" t="inlineStr">
         <is>
@@ -7717,7 +7717,7 @@
         <v>1.15</v>
       </c>
       <c r="AK45">
-        <v>2.39</v>
+        <v>2.31</v>
       </c>
       <c r="AL45">
         <v>0</v>
@@ -7810,61 +7810,61 @@
         <v>1.37</v>
       </c>
       <c r="O46">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="P46">
-        <v>5.75</v>
+        <v>6.5</v>
       </c>
       <c r="Q46">
-        <v>2.02</v>
+        <v>1.84</v>
       </c>
       <c r="R46">
-        <v>2.39</v>
+        <v>2.38</v>
       </c>
       <c r="S46">
         <v>1.22</v>
       </c>
       <c r="T46">
-        <v>3.34</v>
+        <v>3.32</v>
       </c>
       <c r="U46">
-        <v>2.24</v>
+        <v>2.27</v>
       </c>
       <c r="V46">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="W46">
         <v>1.1</v>
       </c>
       <c r="X46">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y46">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="Z46">
-        <v>4.9</v>
+        <v>4.7</v>
       </c>
       <c r="AA46">
         <v>1.53</v>
       </c>
       <c r="AB46">
-        <v>2.37</v>
+        <v>2.34</v>
       </c>
       <c r="AC46">
-        <v>2.25</v>
+        <v>2.34</v>
       </c>
       <c r="AD46">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="AE46">
-        <v>1.19</v>
+        <v>1.17</v>
       </c>
       <c r="AF46">
-        <v>1.64</v>
+        <v>1.67</v>
       </c>
       <c r="AG46">
-        <v>2.04</v>
+        <v>1.93</v>
       </c>
       <c r="AH46" t="inlineStr">
         <is>
@@ -7877,10 +7877,10 @@
         </is>
       </c>
       <c r="AJ46">
-        <v>1.04</v>
+        <v>1.13</v>
       </c>
       <c r="AK46">
-        <v>2.8</v>
+        <v>3</v>
       </c>
       <c r="AL46">
         <v>0</v>
@@ -7979,55 +7979,55 @@
         <v>2.79</v>
       </c>
       <c r="Q47">
-        <v>2.82</v>
+        <v>2.8</v>
       </c>
       <c r="R47">
-        <v>2.28</v>
+        <v>2.18</v>
       </c>
       <c r="S47">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="T47">
-        <v>3.2</v>
+        <v>3.02</v>
       </c>
       <c r="U47">
-        <v>2.5</v>
+        <v>2.44</v>
       </c>
       <c r="V47">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="W47">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="X47">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="Y47">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="Z47">
-        <v>3.8</v>
+        <v>3.84</v>
       </c>
       <c r="AA47">
-        <v>1.65</v>
+        <v>1.68</v>
       </c>
       <c r="AB47">
-        <v>2</v>
+        <v>2.06</v>
       </c>
       <c r="AC47">
-        <v>2.6</v>
+        <v>2.59</v>
       </c>
       <c r="AD47">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="AE47">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="AF47">
-        <v>1.6</v>
+        <v>1.56</v>
       </c>
       <c r="AG47">
-        <v>2.22</v>
+        <v>2.25</v>
       </c>
       <c r="AH47" t="inlineStr">
         <is>
@@ -8040,10 +8040,10 @@
         </is>
       </c>
       <c r="AJ47">
-        <v>1.22</v>
+        <v>1.35</v>
       </c>
       <c r="AK47">
-        <v>1.57</v>
+        <v>1.48</v>
       </c>
       <c r="AL47">
         <v>0</v>
@@ -8142,55 +8142,55 @@
         <v>0</v>
       </c>
       <c r="Q48">
-        <v>5.75</v>
+        <v>0</v>
       </c>
       <c r="R48">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="S48">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="T48">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="U48">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="V48">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="W48">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="X48">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y48">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="Z48">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AA48">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AB48">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="AC48">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="AD48">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AE48">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AF48">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AG48">
-        <v>2.01</v>
+        <v>0</v>
       </c>
       <c r="AH48" t="inlineStr">
         <is>
@@ -8203,10 +8203,10 @@
         </is>
       </c>
       <c r="AJ48">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AK48">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AL48">
         <v>0</v>
@@ -8305,55 +8305,55 @@
         <v>5.02</v>
       </c>
       <c r="Q49">
-        <v>2.08</v>
+        <v>2.15</v>
       </c>
       <c r="R49">
-        <v>2.3</v>
+        <v>2.17</v>
       </c>
       <c r="S49">
-        <v>1.3</v>
+        <v>1.34</v>
       </c>
       <c r="T49">
-        <v>3.2</v>
+        <v>2.88</v>
       </c>
       <c r="U49">
-        <v>2.62</v>
+        <v>2.63</v>
       </c>
       <c r="V49">
         <v>1.44</v>
       </c>
       <c r="W49">
-        <v>1.1</v>
+        <v>1.06</v>
       </c>
       <c r="X49">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="Y49">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="Z49">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="AA49">
-        <v>1.75</v>
+        <v>1.79</v>
       </c>
       <c r="AB49">
-        <v>2</v>
+        <v>1.92</v>
       </c>
       <c r="AC49">
         <v>2.88</v>
       </c>
       <c r="AD49">
-        <v>1.36</v>
+        <v>1.32</v>
       </c>
       <c r="AE49">
-        <v>1.12</v>
+        <v>1.09</v>
       </c>
       <c r="AF49">
-        <v>1.75</v>
+        <v>1.81</v>
       </c>
       <c r="AG49">
-        <v>1.98</v>
+        <v>1.88</v>
       </c>
       <c r="AH49" t="inlineStr">
         <is>
@@ -8366,10 +8366,10 @@
         </is>
       </c>
       <c r="AJ49">
-        <v>1.12</v>
+        <v>1.09</v>
       </c>
       <c r="AK49">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="AL49">
         <v>0</v>
@@ -8459,16 +8459,16 @@
         </is>
       </c>
       <c r="N50">
-        <v>1.87</v>
+        <v>1.91</v>
       </c>
       <c r="O50">
-        <v>3.65</v>
+        <v>3.5</v>
       </c>
       <c r="P50">
         <v>3.4</v>
       </c>
       <c r="Q50">
-        <v>2.4</v>
+        <v>2.41</v>
       </c>
       <c r="R50">
         <v>2.23</v>
@@ -8477,7 +8477,7 @@
         <v>1.32</v>
       </c>
       <c r="T50">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="U50">
         <v>2.4</v>
@@ -8529,7 +8529,7 @@
         </is>
       </c>
       <c r="AJ50">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="AK50">
         <v>1.86</v>
@@ -8628,7 +8628,7 @@
         <v>3.2</v>
       </c>
       <c r="P51">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="Q51">
         <v>5</v>
@@ -8637,10 +8637,10 @@
         <v>1.98</v>
       </c>
       <c r="S51">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="T51">
-        <v>2.55</v>
+        <v>2.75</v>
       </c>
       <c r="U51">
         <v>2.9</v>
@@ -8655,10 +8655,10 @@
         <v>1.03</v>
       </c>
       <c r="Y51">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="Z51">
-        <v>2.95</v>
+        <v>3.1</v>
       </c>
       <c r="AA51">
         <v>2.06</v>
@@ -8667,7 +8667,7 @@
         <v>1.67</v>
       </c>
       <c r="AC51">
-        <v>3.5</v>
+        <v>4.1</v>
       </c>
       <c r="AD51">
         <v>1.24</v>
@@ -8679,7 +8679,7 @@
         <v>1.94</v>
       </c>
       <c r="AG51">
-        <v>1.79</v>
+        <v>1.73</v>
       </c>
       <c r="AH51" t="inlineStr">
         <is>
@@ -8948,7 +8948,7 @@
         </is>
       </c>
       <c r="N53">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="O53">
         <v>3.75</v>
@@ -8957,16 +8957,16 @@
         <v>2.8</v>
       </c>
       <c r="Q53">
-        <v>2.22</v>
+        <v>2.5</v>
       </c>
       <c r="R53">
-        <v>2.31</v>
+        <v>2.39</v>
       </c>
       <c r="S53">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="T53">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="U53">
         <v>2.31</v>
@@ -8987,7 +8987,7 @@
         <v>4.55</v>
       </c>
       <c r="AA53">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="AB53">
         <v>2.41</v>
@@ -9002,7 +9002,7 @@
         <v>1.18</v>
       </c>
       <c r="AF53">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="AG53">
         <v>2.45</v>
@@ -9018,10 +9018,10 @@
         </is>
       </c>
       <c r="AJ53">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="AK53">
-        <v>1.8</v>
+        <v>1.77</v>
       </c>
       <c r="AL53">
         <v>0</v>
@@ -9117,7 +9117,7 @@
         <v>3.62</v>
       </c>
       <c r="P54">
-        <v>2.01</v>
+        <v>1.93</v>
       </c>
       <c r="Q54">
         <v>3.85</v>
@@ -9132,10 +9132,10 @@
         <v>3.15</v>
       </c>
       <c r="U54">
-        <v>2.45</v>
+        <v>2.47</v>
       </c>
       <c r="V54">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="W54">
         <v>1.08</v>
@@ -9144,16 +9144,16 @@
         <v>1.04</v>
       </c>
       <c r="Y54">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="Z54">
-        <v>3.9</v>
+        <v>4.2</v>
       </c>
       <c r="AA54">
         <v>1.72</v>
       </c>
       <c r="AB54">
-        <v>1.96</v>
+        <v>2.1</v>
       </c>
       <c r="AC54">
         <v>2.78</v>
@@ -9184,7 +9184,7 @@
         <v>1.85</v>
       </c>
       <c r="AK54">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="AL54">
         <v>0</v>
@@ -9446,56 +9446,56 @@
         <v>2.5</v>
       </c>
       <c r="Q56">
-        <v>3</v>
+        <v>3.06</v>
       </c>
       <c r="R56">
-        <v>2.34</v>
+        <v>2.18</v>
       </c>
       <c r="S56">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="T56">
-        <v>3.35</v>
+        <v>3.25</v>
       </c>
       <c r="U56">
-        <v>2.3</v>
+        <v>2.33</v>
       </c>
       <c r="V56">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="W56">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="X56">
         <v>1.02</v>
       </c>
       <c r="Y56">
-        <v>1.16</v>
+        <v>1.14</v>
       </c>
       <c r="Z56">
-        <v>4.5</v>
+        <v>4.33</v>
       </c>
       <c r="AA56">
         <v>1.6</v>
       </c>
       <c r="AB56">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="AC56">
+        <v>2.55</v>
+      </c>
+      <c r="AD56">
+        <v>1.49</v>
+      </c>
+      <c r="AE56">
+        <v>1.13</v>
+      </c>
+      <c r="AF56">
+        <v>1.5</v>
+      </c>
+      <c r="AG56">
         <v>2.4</v>
       </c>
-      <c r="AD56">
-        <v>1.5</v>
-      </c>
-      <c r="AE56">
-        <v>1.18</v>
-      </c>
-      <c r="AF56">
-        <v>1.53</v>
-      </c>
-      <c r="AG56">
-        <v>2.37</v>
-      </c>
       <c r="AH56" t="inlineStr">
         <is>
           <t>[]</t>
@@ -9507,10 +9507,10 @@
         </is>
       </c>
       <c r="AJ56">
-        <v>1.22</v>
+        <v>1.43</v>
       </c>
       <c r="AK56">
-        <v>1.49</v>
+        <v>1.47</v>
       </c>
       <c r="AL56">
         <v>0</v>
@@ -10252,19 +10252,19 @@
         </is>
       </c>
       <c r="N61">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="O61">
-        <v>8.25</v>
+        <v>8</v>
       </c>
       <c r="P61">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="Q61">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="R61">
-        <v>2.88</v>
+        <v>2.85</v>
       </c>
       <c r="S61">
         <v>1.14</v>
@@ -10306,10 +10306,10 @@
         <v>1.29</v>
       </c>
       <c r="AF61">
-        <v>2.06</v>
+        <v>2.01</v>
       </c>
       <c r="AG61">
-        <v>1.65</v>
+        <v>1.68</v>
       </c>
       <c r="AH61" t="inlineStr">
         <is>
@@ -10322,10 +10322,10 @@
         </is>
       </c>
       <c r="AJ61">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="AK61">
-        <v>5.05</v>
+        <v>4.95</v>
       </c>
       <c r="AL61">
         <v>0</v>
@@ -10418,10 +10418,10 @@
         <v>2.62</v>
       </c>
       <c r="O62">
-        <v>3.18</v>
+        <v>3.25</v>
       </c>
       <c r="P62">
-        <v>2.5</v>
+        <v>2.45</v>
       </c>
       <c r="Q62">
         <v>3.25</v>
@@ -10436,7 +10436,7 @@
         <v>2.85</v>
       </c>
       <c r="U62">
-        <v>2.85</v>
+        <v>2.88</v>
       </c>
       <c r="V62">
         <v>1.36</v>
@@ -10472,7 +10472,7 @@
         <v>1.75</v>
       </c>
       <c r="AG62">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="AH62" t="inlineStr">
         <is>
@@ -10488,7 +10488,7 @@
         <v>1.45</v>
       </c>
       <c r="AK62">
-        <v>1.48</v>
+        <v>1.45</v>
       </c>
       <c r="AL62">
         <v>0</v>
@@ -10578,13 +10578,13 @@
         </is>
       </c>
       <c r="N63">
-        <v>2.3</v>
+        <v>2.31</v>
       </c>
       <c r="O63">
         <v>3.2</v>
       </c>
       <c r="P63">
-        <v>2.85</v>
+        <v>2.88</v>
       </c>
       <c r="Q63">
         <v>2.95</v>
@@ -10608,7 +10608,7 @@
         <v>1.06</v>
       </c>
       <c r="X63">
-        <v>1.05</v>
+        <v>1</v>
       </c>
       <c r="Y63">
         <v>1.25</v>
@@ -10629,7 +10629,7 @@
         <v>1.33</v>
       </c>
       <c r="AE63">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="AF63">
         <v>1.67</v>
@@ -11361,12 +11361,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Odd</t>
+          <t>Raufoss</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Åsane</t>
+          <t>Stabæk</t>
         </is>
       </c>
       <c r="G68">
@@ -11393,34 +11393,34 @@
         </is>
       </c>
       <c r="N68">
-        <v>1.39</v>
+        <v>4.5</v>
       </c>
       <c r="O68">
-        <v>4.75</v>
+        <v>4</v>
       </c>
       <c r="P68">
-        <v>5.3</v>
+        <v>1.54</v>
       </c>
       <c r="Q68">
-        <v>1.79</v>
+        <v>4.74</v>
       </c>
       <c r="R68">
-        <v>2.75</v>
+        <v>2.53</v>
       </c>
       <c r="S68">
+        <v>1.17</v>
+      </c>
+      <c r="T68">
+        <v>4.2</v>
+      </c>
+      <c r="U68">
+        <v>1.94</v>
+      </c>
+      <c r="V68">
+        <v>1.76</v>
+      </c>
+      <c r="W68">
         <v>1.18</v>
-      </c>
-      <c r="T68">
-        <v>4.33</v>
-      </c>
-      <c r="U68">
-        <v>1.99</v>
-      </c>
-      <c r="V68">
-        <v>1.83</v>
-      </c>
-      <c r="W68">
-        <v>1.2</v>
       </c>
       <c r="X68">
         <v>1.01</v>
@@ -11429,28 +11429,28 @@
         <v>1.1</v>
       </c>
       <c r="Z68">
-        <v>6.6</v>
+        <v>6.47</v>
       </c>
       <c r="AA68">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="AB68">
-        <v>2.85</v>
+        <v>2.92</v>
       </c>
       <c r="AC68">
-        <v>1.88</v>
+        <v>1.98</v>
       </c>
       <c r="AD68">
-        <v>1.91</v>
+        <v>1.71</v>
       </c>
       <c r="AE68">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="AF68">
-        <v>1.49</v>
+        <v>1.4</v>
       </c>
       <c r="AG68">
-        <v>2.45</v>
+        <v>2.73</v>
       </c>
       <c r="AH68" t="inlineStr">
         <is>
@@ -11463,10 +11463,10 @@
         </is>
       </c>
       <c r="AJ68">
-        <v>1.13</v>
+        <v>1.18</v>
       </c>
       <c r="AK68">
-        <v>2.7</v>
+        <v>1.15</v>
       </c>
       <c r="AL68">
         <v>0</v>
@@ -11524,12 +11524,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Raufoss</t>
+          <t>Odd</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Stabæk</t>
+          <t>Åsane</t>
         </is>
       </c>
       <c r="G69">
@@ -11556,34 +11556,34 @@
         </is>
       </c>
       <c r="N69">
-        <v>4.5</v>
+        <v>1.39</v>
       </c>
       <c r="O69">
-        <v>4</v>
+        <v>4.75</v>
       </c>
       <c r="P69">
-        <v>1.54</v>
+        <v>5.3</v>
       </c>
       <c r="Q69">
-        <v>4.74</v>
+        <v>1.79</v>
       </c>
       <c r="R69">
-        <v>2.53</v>
+        <v>2.75</v>
       </c>
       <c r="S69">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="T69">
-        <v>4.2</v>
+        <v>4.33</v>
       </c>
       <c r="U69">
-        <v>1.94</v>
+        <v>1.99</v>
       </c>
       <c r="V69">
-        <v>1.76</v>
+        <v>1.83</v>
       </c>
       <c r="W69">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="X69">
         <v>1.01</v>
@@ -11592,28 +11592,28 @@
         <v>1.1</v>
       </c>
       <c r="Z69">
-        <v>6.47</v>
+        <v>6.6</v>
       </c>
       <c r="AA69">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="AB69">
-        <v>2.92</v>
+        <v>2.85</v>
       </c>
       <c r="AC69">
-        <v>1.98</v>
+        <v>1.88</v>
       </c>
       <c r="AD69">
-        <v>1.71</v>
+        <v>1.91</v>
       </c>
       <c r="AE69">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="AF69">
-        <v>1.4</v>
+        <v>1.49</v>
       </c>
       <c r="AG69">
-        <v>2.73</v>
+        <v>2.45</v>
       </c>
       <c r="AH69" t="inlineStr">
         <is>
@@ -11626,10 +11626,10 @@
         </is>
       </c>
       <c r="AJ69">
-        <v>1.18</v>
+        <v>1.13</v>
       </c>
       <c r="AK69">
-        <v>1.15</v>
+        <v>2.7</v>
       </c>
       <c r="AL69">
         <v>0</v>
@@ -11764,16 +11764,16 @@
         <v>1.7</v>
       </c>
       <c r="AC70">
-        <v>2.75</v>
+        <v>3.5</v>
       </c>
       <c r="AD70">
-        <v>1.38</v>
+        <v>1.24</v>
       </c>
       <c r="AE70">
-        <v>1.14</v>
+        <v>1.04</v>
       </c>
       <c r="AF70">
-        <v>1.62</v>
+        <v>2.1</v>
       </c>
       <c r="AG70">
         <v>1.67</v>
@@ -11789,10 +11789,10 @@
         </is>
       </c>
       <c r="AJ70">
-        <v>1.22</v>
+        <v>1.29</v>
       </c>
       <c r="AK70">
-        <v>2.2</v>
+        <v>2.19</v>
       </c>
       <c r="AL70">
         <v>0</v>
@@ -11900,7 +11900,7 @@
         <v>1.37</v>
       </c>
       <c r="T71">
-        <v>3.02</v>
+        <v>2.98</v>
       </c>
       <c r="U71">
         <v>2.77</v>
@@ -11915,19 +11915,19 @@
         <v>1</v>
       </c>
       <c r="Y71">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="Z71">
         <v>3.49</v>
       </c>
       <c r="AA71">
-        <v>1.96</v>
+        <v>1.86</v>
       </c>
       <c r="AB71">
-        <v>1.93</v>
+        <v>1.98</v>
       </c>
       <c r="AC71">
-        <v>3.16</v>
+        <v>3.28</v>
       </c>
       <c r="AD71">
         <v>1.33</v>
@@ -11939,7 +11939,7 @@
         <v>2.27</v>
       </c>
       <c r="AG71">
-        <v>1.56</v>
+        <v>1.58</v>
       </c>
       <c r="AH71" t="inlineStr">
         <is>
@@ -12045,16 +12045,16 @@
         </is>
       </c>
       <c r="N72">
-        <v>2.41</v>
+        <v>2.37</v>
       </c>
       <c r="O72">
-        <v>3.15</v>
+        <v>3.4</v>
       </c>
       <c r="P72">
-        <v>2.44</v>
+        <v>2.47</v>
       </c>
       <c r="Q72">
-        <v>3</v>
+        <v>3.02</v>
       </c>
       <c r="R72">
         <v>2.25</v>
@@ -12063,46 +12063,46 @@
         <v>1.3</v>
       </c>
       <c r="T72">
-        <v>2.97</v>
+        <v>2.92</v>
       </c>
       <c r="U72">
-        <v>2.47</v>
+        <v>2.5</v>
       </c>
       <c r="V72">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="W72">
         <v>1.07</v>
       </c>
       <c r="X72">
-        <v>1.03</v>
+        <v>1</v>
       </c>
       <c r="Y72">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="Z72">
-        <v>3.84</v>
+        <v>3.8</v>
       </c>
       <c r="AA72">
         <v>1.72</v>
       </c>
       <c r="AB72">
-        <v>2.01</v>
+        <v>2.07</v>
       </c>
       <c r="AC72">
-        <v>2.66</v>
+        <v>2.7</v>
       </c>
       <c r="AD72">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="AE72">
         <v>1.11</v>
       </c>
       <c r="AF72">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="AG72">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="AH72" t="inlineStr">
         <is>
@@ -12115,7 +12115,7 @@
         </is>
       </c>
       <c r="AJ72">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="AK72">
         <v>1.43</v>
@@ -12371,13 +12371,13 @@
         </is>
       </c>
       <c r="N74">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="O74">
-        <v>2.9</v>
+        <v>2.95</v>
       </c>
       <c r="P74">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="Q74">
         <v>2.8</v>
@@ -12386,7 +12386,7 @@
         <v>1.83</v>
       </c>
       <c r="S74">
-        <v>1.5</v>
+        <v>1.56</v>
       </c>
       <c r="T74">
         <v>2.5</v>
@@ -12395,7 +12395,7 @@
         <v>3.42</v>
       </c>
       <c r="V74">
-        <v>1.28</v>
+        <v>1.23</v>
       </c>
       <c r="W74">
         <v>1.02</v>
@@ -12407,7 +12407,7 @@
         <v>1.49</v>
       </c>
       <c r="Z74">
-        <v>2.45</v>
+        <v>2.44</v>
       </c>
       <c r="AA74">
         <v>2.43</v>
@@ -12419,16 +12419,16 @@
         <v>5.25</v>
       </c>
       <c r="AD74">
-        <v>1.15</v>
+        <v>1.13</v>
       </c>
       <c r="AE74">
         <v>1.04</v>
       </c>
       <c r="AF74">
-        <v>2.09</v>
+        <v>2.08</v>
       </c>
       <c r="AG74">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="AH74" t="inlineStr">
         <is>
@@ -12555,7 +12555,7 @@
         <v>2.99</v>
       </c>
       <c r="U75">
-        <v>2.56</v>
+        <v>2.76</v>
       </c>
       <c r="V75">
         <v>1.44</v>
@@ -12570,13 +12570,13 @@
         <v>1.25</v>
       </c>
       <c r="Z75">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="AA75">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="AB75">
-        <v>1.93</v>
+        <v>1.95</v>
       </c>
       <c r="AC75">
         <v>3.18</v>
@@ -12585,10 +12585,10 @@
         <v>1.33</v>
       </c>
       <c r="AE75">
-        <v>1.12</v>
+        <v>1.08</v>
       </c>
       <c r="AF75">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="AG75">
         <v>2.15</v>
@@ -12697,16 +12697,16 @@
         </is>
       </c>
       <c r="N76">
-        <v>2.78</v>
+        <v>2.7</v>
       </c>
       <c r="O76">
-        <v>3.24</v>
+        <v>3.25</v>
       </c>
       <c r="P76">
         <v>2.43</v>
       </c>
       <c r="Q76">
-        <v>3.54</v>
+        <v>3.4</v>
       </c>
       <c r="R76">
         <v>2.04</v>
@@ -12724,7 +12724,7 @@
         <v>1.4</v>
       </c>
       <c r="W76">
-        <v>1.08</v>
+        <v>1.04</v>
       </c>
       <c r="X76">
         <v>1.03</v>
@@ -12748,7 +12748,7 @@
         <v>1.3</v>
       </c>
       <c r="AE76">
-        <v>1.06</v>
+        <v>1.11</v>
       </c>
       <c r="AF76">
         <v>1.75</v>
@@ -12860,13 +12860,13 @@
         </is>
       </c>
       <c r="N77">
-        <v>2.17</v>
+        <v>2.26</v>
       </c>
       <c r="O77">
-        <v>3.5</v>
+        <v>3.35</v>
       </c>
       <c r="P77">
-        <v>3</v>
+        <v>2.73</v>
       </c>
       <c r="Q77">
         <v>2.81</v>
@@ -12878,7 +12878,7 @@
         <v>1.33</v>
       </c>
       <c r="T77">
-        <v>2.78</v>
+        <v>2.89</v>
       </c>
       <c r="U77">
         <v>2.62</v>
@@ -12896,7 +12896,7 @@
         <v>1.24</v>
       </c>
       <c r="Z77">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="AA77">
         <v>1.8</v>
@@ -12930,7 +12930,7 @@
         </is>
       </c>
       <c r="AJ77">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AK77">
         <v>1.62</v>
@@ -13044,16 +13044,16 @@
         <v>2.39</v>
       </c>
       <c r="U78">
-        <v>2.9</v>
+        <v>2.95</v>
       </c>
       <c r="V78">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="W78">
         <v>1.01</v>
       </c>
       <c r="X78">
-        <v>1.08</v>
+        <v>1.04</v>
       </c>
       <c r="Y78">
         <v>1.4</v>
@@ -13096,7 +13096,7 @@
         <v>1.28</v>
       </c>
       <c r="AK78">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="AL78">
         <v>0</v>
@@ -13195,7 +13195,7 @@
         <v>2.72</v>
       </c>
       <c r="Q79">
-        <v>3.04</v>
+        <v>3.06</v>
       </c>
       <c r="R79">
         <v>2</v>
@@ -13204,10 +13204,10 @@
         <v>1.4</v>
       </c>
       <c r="T79">
-        <v>2.6</v>
+        <v>2.88</v>
       </c>
       <c r="U79">
-        <v>3</v>
+        <v>2.92</v>
       </c>
       <c r="V79">
         <v>1.33</v>
@@ -13259,7 +13259,7 @@
         <v>1.26</v>
       </c>
       <c r="AK79">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="AL79">
         <v>0</v>
@@ -13512,7 +13512,7 @@
         </is>
       </c>
       <c r="N81">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="O81">
         <v>3.4</v>
@@ -13533,40 +13533,40 @@
         <v>2.88</v>
       </c>
       <c r="U81">
-        <v>2.5</v>
+        <v>2.63</v>
       </c>
       <c r="V81">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="W81">
-        <v>1.11</v>
+        <v>1.09</v>
       </c>
       <c r="X81">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y81">
         <v>1.25</v>
       </c>
       <c r="Z81">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="AA81">
-        <v>1.82</v>
+        <v>1.86</v>
       </c>
       <c r="AB81">
-        <v>1.81</v>
+        <v>1.89</v>
       </c>
       <c r="AC81">
-        <v>2.83</v>
+        <v>2.97</v>
       </c>
       <c r="AD81">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AE81">
-        <v>1.09</v>
+        <v>1.07</v>
       </c>
       <c r="AF81">
-        <v>1.65</v>
+        <v>1.69</v>
       </c>
       <c r="AG81">
         <v>2</v>
@@ -13582,10 +13582,10 @@
         </is>
       </c>
       <c r="AJ81">
-        <v>1.82</v>
+        <v>1.22</v>
       </c>
       <c r="AK81">
-        <v>1.23</v>
+        <v>1.2</v>
       </c>
       <c r="AL81">
         <v>0</v>
@@ -13838,28 +13838,28 @@
         </is>
       </c>
       <c r="N83">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="O83">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="P83">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="Q83">
-        <v>3.45</v>
+        <v>3.3</v>
       </c>
       <c r="R83">
+        <v>2.35</v>
+      </c>
+      <c r="S83">
+        <v>1.28</v>
+      </c>
+      <c r="T83">
+        <v>3.18</v>
+      </c>
+      <c r="U83">
         <v>2.38</v>
-      </c>
-      <c r="S83">
-        <v>1.27</v>
-      </c>
-      <c r="T83">
-        <v>3.25</v>
-      </c>
-      <c r="U83">
-        <v>2.2</v>
       </c>
       <c r="V83">
         <v>1.51</v>
@@ -13874,28 +13874,28 @@
         <v>1.14</v>
       </c>
       <c r="Z83">
-        <v>4.5</v>
+        <v>4.45</v>
       </c>
       <c r="AA83">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="AB83">
-        <v>2.17</v>
+        <v>2.15</v>
       </c>
       <c r="AC83">
-        <v>2.39</v>
+        <v>2.55</v>
       </c>
       <c r="AD83">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="AE83">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="AF83">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="AG83">
-        <v>2.34</v>
+        <v>2.32</v>
       </c>
       <c r="AH83" t="inlineStr">
         <is>
@@ -14001,13 +14001,13 @@
         </is>
       </c>
       <c r="N84">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="O84">
-        <v>4.4</v>
+        <v>4.1</v>
       </c>
       <c r="P84">
-        <v>5.3</v>
+        <v>5.1</v>
       </c>
       <c r="Q84">
         <v>1.83</v>
@@ -14019,13 +14019,13 @@
         <v>1.25</v>
       </c>
       <c r="T84">
-        <v>3.45</v>
+        <v>3.28</v>
       </c>
       <c r="U84">
-        <v>2.25</v>
+        <v>2.26</v>
       </c>
       <c r="V84">
-        <v>1.6</v>
+        <v>1.56</v>
       </c>
       <c r="W84">
         <v>1.14</v>
@@ -14167,62 +14167,62 @@
         <v>11.7</v>
       </c>
       <c r="O85">
-        <v>5.7</v>
+        <v>6</v>
       </c>
       <c r="P85">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="Q85">
-        <v>8.800000000000001</v>
+        <v>9.25</v>
       </c>
       <c r="R85">
-        <v>2.67</v>
+        <v>2.77</v>
       </c>
       <c r="S85">
-        <v>1.17</v>
+        <v>1.19</v>
       </c>
       <c r="T85">
-        <v>3.68</v>
+        <v>3.74</v>
       </c>
       <c r="U85">
-        <v>2.01</v>
+        <v>2.05</v>
       </c>
       <c r="V85">
         <v>1.73</v>
       </c>
       <c r="W85">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="X85">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y85">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="Z85">
-        <v>5.9</v>
+        <v>5.6</v>
       </c>
       <c r="AA85">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="AB85">
-        <v>2.78</v>
+        <v>2.75</v>
       </c>
       <c r="AC85">
-        <v>1.9</v>
+        <v>1.99</v>
       </c>
       <c r="AD85">
+        <v>1.73</v>
+      </c>
+      <c r="AE85">
+        <v>1.28</v>
+      </c>
+      <c r="AF85">
+        <v>1.89</v>
+      </c>
+      <c r="AG85">
         <v>1.8</v>
       </c>
-      <c r="AE85">
-        <v>1.24</v>
-      </c>
-      <c r="AF85">
-        <v>1.78</v>
-      </c>
-      <c r="AG85">
-        <v>1.91</v>
-      </c>
       <c r="AH85" t="inlineStr">
         <is>
           <t>[]</t>
@@ -14234,10 +14234,10 @@
         </is>
       </c>
       <c r="AJ85">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="AK85">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="AL85">
         <v>0</v>
@@ -14327,64 +14327,64 @@
         </is>
       </c>
       <c r="N86">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="O86">
-        <v>4.6</v>
+        <v>4.55</v>
       </c>
       <c r="P86">
-        <v>5</v>
+        <v>6.5</v>
       </c>
       <c r="Q86">
-        <v>1.74</v>
+        <v>1.78</v>
       </c>
       <c r="R86">
-        <v>2.9</v>
+        <v>2.56</v>
       </c>
       <c r="S86">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="T86">
-        <v>3.58</v>
+        <v>3.72</v>
       </c>
       <c r="U86">
-        <v>2.05</v>
+        <v>2.02</v>
       </c>
       <c r="V86">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="W86">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="X86">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y86">
         <v>1.07</v>
       </c>
       <c r="Z86">
-        <v>5.55</v>
+        <v>5.75</v>
       </c>
       <c r="AA86">
         <v>1.44</v>
       </c>
       <c r="AB86">
-        <v>2.62</v>
+        <v>2.74</v>
       </c>
       <c r="AC86">
-        <v>2</v>
+        <v>2.01</v>
       </c>
       <c r="AD86">
         <v>1.78</v>
       </c>
       <c r="AE86">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="AF86">
-        <v>1.55</v>
+        <v>1.58</v>
       </c>
       <c r="AG86">
-        <v>2.27</v>
+        <v>2.21</v>
       </c>
       <c r="AH86" t="inlineStr">
         <is>
@@ -14397,10 +14397,10 @@
         </is>
       </c>
       <c r="AJ86">
-        <v>1.05</v>
+        <v>1.11</v>
       </c>
       <c r="AK86">
-        <v>2.88</v>
+        <v>3.2</v>
       </c>
       <c r="AL86">
         <v>0</v>
@@ -14505,10 +14505,10 @@
         <v>2.48</v>
       </c>
       <c r="S87">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="T87">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="U87">
         <v>2.31</v>
@@ -14520,13 +14520,13 @@
         <v>1.11</v>
       </c>
       <c r="X87">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y87">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="Z87">
-        <v>4.33</v>
+        <v>4.8</v>
       </c>
       <c r="AA87">
         <v>1.57</v>
@@ -14541,13 +14541,13 @@
         <v>1.54</v>
       </c>
       <c r="AE87">
-        <v>1.16</v>
+        <v>1.21</v>
       </c>
       <c r="AF87">
         <v>1.56</v>
       </c>
       <c r="AG87">
-        <v>2.1</v>
+        <v>2.28</v>
       </c>
       <c r="AH87" t="inlineStr">
         <is>
@@ -14563,7 +14563,7 @@
         <v>2.15</v>
       </c>
       <c r="AK87">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="AL87">
         <v>0</v>
@@ -14653,31 +14653,31 @@
         </is>
       </c>
       <c r="N88">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="O88">
-        <v>4.6</v>
+        <v>4.3</v>
       </c>
       <c r="P88">
-        <v>15</v>
+        <v>6.8</v>
       </c>
       <c r="Q88">
         <v>1.73</v>
       </c>
       <c r="R88">
-        <v>2.34</v>
+        <v>2.32</v>
       </c>
       <c r="S88">
         <v>1.3</v>
       </c>
       <c r="T88">
-        <v>2.98</v>
+        <v>2.95</v>
       </c>
       <c r="U88">
-        <v>2.62</v>
+        <v>2.66</v>
       </c>
       <c r="V88">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="W88">
         <v>1.05</v>
@@ -14689,28 +14689,28 @@
         <v>1.27</v>
       </c>
       <c r="Z88">
-        <v>3.7</v>
+        <v>3.5</v>
       </c>
       <c r="AA88">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="AB88">
-        <v>2</v>
+        <v>1.93</v>
       </c>
       <c r="AC88">
-        <v>3.1</v>
+        <v>3.06</v>
       </c>
       <c r="AD88">
         <v>1.3</v>
       </c>
       <c r="AE88">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="AF88">
         <v>2.15</v>
       </c>
       <c r="AG88">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="AH88" t="inlineStr">
         <is>
@@ -14726,7 +14726,7 @@
         <v>1.05</v>
       </c>
       <c r="AK88">
-        <v>3.24</v>
+        <v>2.91</v>
       </c>
       <c r="AL88">
         <v>0</v>
@@ -14825,55 +14825,55 @@
         <v>0</v>
       </c>
       <c r="Q89">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="R89">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="S89">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="T89">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="U89">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="V89">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="W89">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="X89">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y89">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="Z89">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="AA89">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AB89">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="AC89">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="AD89">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AE89">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AF89">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AG89">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="AH89" t="inlineStr">
         <is>
@@ -14886,10 +14886,10 @@
         </is>
       </c>
       <c r="AJ89">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AK89">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AL89">
         <v>0</v>
@@ -15504,7 +15504,7 @@
         <v>1.22</v>
       </c>
       <c r="Z93">
-        <v>3.35</v>
+        <v>3.74</v>
       </c>
       <c r="AA93">
         <v>1.85</v>
@@ -15794,13 +15794,13 @@
         </is>
       </c>
       <c r="N95">
-        <v>1.75</v>
+        <v>1.78</v>
       </c>
       <c r="O95">
-        <v>3.55</v>
+        <v>3.35</v>
       </c>
       <c r="P95">
-        <v>4.3</v>
+        <v>3.73</v>
       </c>
       <c r="Q95">
         <v>2.4</v>
@@ -15815,13 +15815,13 @@
         <v>2.75</v>
       </c>
       <c r="U95">
-        <v>2.8</v>
+        <v>2.88</v>
       </c>
       <c r="V95">
         <v>1.37</v>
       </c>
       <c r="W95">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="X95">
         <v>1.01</v>
@@ -15851,7 +15851,7 @@
         <v>1.84</v>
       </c>
       <c r="AG95">
-        <v>1.84</v>
+        <v>1.86</v>
       </c>
       <c r="AH95" t="inlineStr">
         <is>
@@ -16455,19 +16455,19 @@
         <v>2.5</v>
       </c>
       <c r="Q99">
-        <v>3.13</v>
+        <v>3.2</v>
       </c>
       <c r="R99">
-        <v>2.2</v>
+        <v>2.32</v>
       </c>
       <c r="S99">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="T99">
         <v>2.9</v>
       </c>
       <c r="U99">
-        <v>2.57</v>
+        <v>2.44</v>
       </c>
       <c r="V99">
         <v>1.46</v>
@@ -16519,7 +16519,7 @@
         <v>1.42</v>
       </c>
       <c r="AK99">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="AL99">
         <v>0</v>
@@ -16612,22 +16612,22 @@
         <v>3.7</v>
       </c>
       <c r="O100">
-        <v>3.64</v>
+        <v>3.4</v>
       </c>
       <c r="P100">
-        <v>1.93</v>
+        <v>1.88</v>
       </c>
       <c r="Q100">
-        <v>4.33</v>
+        <v>3.76</v>
       </c>
       <c r="R100">
         <v>2.08</v>
       </c>
       <c r="S100">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="T100">
-        <v>2.93</v>
+        <v>3.03</v>
       </c>
       <c r="U100">
         <v>2.77</v>
@@ -16642,19 +16642,19 @@
         <v>1.01</v>
       </c>
       <c r="Y100">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="Z100">
-        <v>3.42</v>
+        <v>3.59</v>
       </c>
       <c r="AA100">
         <v>1.91</v>
       </c>
       <c r="AB100">
-        <v>1.97</v>
+        <v>1.93</v>
       </c>
       <c r="AC100">
-        <v>3.24</v>
+        <v>3.1</v>
       </c>
       <c r="AD100">
         <v>1.32</v>
@@ -16679,7 +16679,7 @@
         </is>
       </c>
       <c r="AJ100">
-        <v>1.31</v>
+        <v>1.22</v>
       </c>
       <c r="AK100">
         <v>1.29</v>
@@ -16944,55 +16944,55 @@
         <v>2.59</v>
       </c>
       <c r="Q102">
-        <v>3.1</v>
+        <v>3.9</v>
       </c>
       <c r="R102">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="S102">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="T102">
-        <v>2.7</v>
+        <v>2.88</v>
       </c>
       <c r="U102">
-        <v>2.82</v>
+        <v>2.91</v>
       </c>
       <c r="V102">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="W102">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="X102">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y102">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
       <c r="Z102">
-        <v>3.1</v>
+        <v>3.08</v>
       </c>
       <c r="AA102">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AB102">
+        <v>1.72</v>
+      </c>
+      <c r="AC102">
+        <v>3.5</v>
+      </c>
+      <c r="AD102">
+        <v>1.22</v>
+      </c>
+      <c r="AE102">
+        <v>1.04</v>
+      </c>
+      <c r="AF102">
         <v>1.79</v>
       </c>
-      <c r="AC102">
-        <v>3.28</v>
-      </c>
-      <c r="AD102">
-        <v>1.25</v>
-      </c>
-      <c r="AE102">
-        <v>1.05</v>
-      </c>
-      <c r="AF102">
-        <v>1.7</v>
-      </c>
       <c r="AG102">
-        <v>2.01</v>
+        <v>1.9</v>
       </c>
       <c r="AH102" t="inlineStr">
         <is>
@@ -17005,10 +17005,10 @@
         </is>
       </c>
       <c r="AJ102">
-        <v>1.25</v>
+        <v>1.64</v>
       </c>
       <c r="AK102">
-        <v>1.43</v>
+        <v>1.24</v>
       </c>
       <c r="AL102">
         <v>0</v>
@@ -17098,31 +17098,31 @@
         </is>
       </c>
       <c r="N103">
-        <v>1.43</v>
+        <v>1.58</v>
       </c>
       <c r="O103">
-        <v>4.15</v>
+        <v>4</v>
       </c>
       <c r="P103">
-        <v>6.28</v>
+        <v>4.2</v>
       </c>
       <c r="Q103">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="R103">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="S103">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="T103">
-        <v>3.6</v>
+        <v>3.25</v>
       </c>
       <c r="U103">
-        <v>2.36</v>
+        <v>2.44</v>
       </c>
       <c r="V103">
-        <v>1.49</v>
+        <v>1.46</v>
       </c>
       <c r="W103">
         <v>1.08</v>
@@ -17134,28 +17134,28 @@
         <v>1.22</v>
       </c>
       <c r="Z103">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="AA103">
-        <v>1.67</v>
+        <v>1.73</v>
       </c>
       <c r="AB103">
-        <v>2.17</v>
+        <v>2.09</v>
       </c>
       <c r="AC103">
-        <v>2.62</v>
+        <v>2.8</v>
       </c>
       <c r="AD103">
-        <v>1.45</v>
+        <v>1.4</v>
       </c>
       <c r="AE103">
-        <v>1.14</v>
+        <v>1.11</v>
       </c>
       <c r="AF103">
-        <v>1.73</v>
+        <v>1.68</v>
       </c>
       <c r="AG103">
-        <v>1.95</v>
+        <v>2.01</v>
       </c>
       <c r="AH103" t="inlineStr">
         <is>
@@ -17168,10 +17168,10 @@
         </is>
       </c>
       <c r="AJ103">
-        <v>1.06</v>
+        <v>1.16</v>
       </c>
       <c r="AK103">
-        <v>2.7</v>
+        <v>2.4</v>
       </c>
       <c r="AL103">
         <v>0</v>
@@ -17913,19 +17913,19 @@
         </is>
       </c>
       <c r="N108">
-        <v>2.35</v>
+        <v>2.3</v>
       </c>
       <c r="O108">
         <v>3.15</v>
       </c>
       <c r="P108">
-        <v>2.8</v>
+        <v>2.7</v>
       </c>
       <c r="Q108">
         <v>3.03</v>
       </c>
       <c r="R108">
-        <v>2.05</v>
+        <v>2.08</v>
       </c>
       <c r="S108">
         <v>1.36</v>
@@ -17934,7 +17934,7 @@
         <v>2.84</v>
       </c>
       <c r="U108">
-        <v>2.8</v>
+        <v>2.69</v>
       </c>
       <c r="V108">
         <v>1.4</v>
@@ -17943,7 +17943,7 @@
         <v>1.05</v>
       </c>
       <c r="X108">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y108">
         <v>1.28</v>
@@ -18076,40 +18076,40 @@
         </is>
       </c>
       <c r="N109">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="O109">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="P109">
-        <v>6.8</v>
+        <v>7.5</v>
       </c>
       <c r="Q109">
-        <v>1.7</v>
+        <v>1.75</v>
       </c>
       <c r="R109">
-        <v>2.57</v>
+        <v>2.59</v>
       </c>
       <c r="S109">
         <v>1.3</v>
       </c>
       <c r="T109">
-        <v>3.2</v>
+        <v>3.02</v>
       </c>
       <c r="U109">
-        <v>2.64</v>
+        <v>2.32</v>
       </c>
       <c r="V109">
-        <v>1.43</v>
+        <v>1.46</v>
       </c>
       <c r="W109">
-        <v>1.11</v>
+        <v>1.09</v>
       </c>
       <c r="X109">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y109">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="Z109">
         <v>4</v>
@@ -18118,22 +18118,22 @@
         <v>1.75</v>
       </c>
       <c r="AB109">
-        <v>2.01</v>
+        <v>2.04</v>
       </c>
       <c r="AC109">
-        <v>2.7</v>
+        <v>2.84</v>
       </c>
       <c r="AD109">
         <v>1.39</v>
       </c>
       <c r="AE109">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="AF109">
-        <v>2.11</v>
+        <v>1.98</v>
       </c>
       <c r="AG109">
-        <v>1.62</v>
+        <v>1.7</v>
       </c>
       <c r="AH109" t="inlineStr">
         <is>
@@ -18239,13 +18239,13 @@
         </is>
       </c>
       <c r="N110">
-        <v>2.04</v>
+        <v>2</v>
       </c>
       <c r="O110">
-        <v>3.16</v>
+        <v>3.25</v>
       </c>
       <c r="P110">
-        <v>3.39</v>
+        <v>3.4</v>
       </c>
       <c r="Q110">
         <v>0</v>
@@ -18402,13 +18402,13 @@
         </is>
       </c>
       <c r="N111">
-        <v>3.8</v>
+        <v>4.6</v>
       </c>
       <c r="O111">
-        <v>3.15</v>
+        <v>3.08</v>
       </c>
       <c r="P111">
-        <v>1.92</v>
+        <v>1.79</v>
       </c>
       <c r="Q111">
         <v>0</v>
@@ -18565,13 +18565,13 @@
         </is>
       </c>
       <c r="N112">
-        <v>1.94</v>
+        <v>1.76</v>
       </c>
       <c r="O112">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="P112">
-        <v>3.76</v>
+        <v>4.5</v>
       </c>
       <c r="Q112">
         <v>0</v>
@@ -18891,19 +18891,19 @@
         </is>
       </c>
       <c r="N114">
-        <v>1.61</v>
+        <v>1.63</v>
       </c>
       <c r="O114">
-        <v>3.6</v>
+        <v>3.9</v>
       </c>
       <c r="P114">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="Q114">
-        <v>2.17</v>
+        <v>2.14</v>
       </c>
       <c r="R114">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="S114">
         <v>1.29</v>
@@ -18915,7 +18915,7 @@
         <v>2.5</v>
       </c>
       <c r="V114">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="W114">
         <v>1.1</v>
@@ -18924,16 +18924,16 @@
         <v>1.01</v>
       </c>
       <c r="Y114">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="Z114">
-        <v>4</v>
+        <v>4.12</v>
       </c>
       <c r="AA114">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="AB114">
-        <v>2.03</v>
+        <v>2.11</v>
       </c>
       <c r="AC114">
         <v>2.66</v>
@@ -18942,13 +18942,13 @@
         <v>1.42</v>
       </c>
       <c r="AE114">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="AF114">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="AG114">
-        <v>2.01</v>
+        <v>2</v>
       </c>
       <c r="AH114" t="inlineStr">
         <is>
@@ -18964,7 +18964,7 @@
         <v>1.11</v>
       </c>
       <c r="AK114">
-        <v>2.1</v>
+        <v>2.14</v>
       </c>
       <c r="AL114">
         <v>0</v>
@@ -19054,25 +19054,25 @@
         </is>
       </c>
       <c r="N115">
-        <v>4.35</v>
+        <v>3.4</v>
       </c>
       <c r="O115">
-        <v>3.65</v>
+        <v>3.55</v>
       </c>
       <c r="P115">
-        <v>1.63</v>
+        <v>1.75</v>
       </c>
       <c r="Q115">
-        <v>5</v>
+        <v>4.65</v>
       </c>
       <c r="R115">
-        <v>2.18</v>
+        <v>2.15</v>
       </c>
       <c r="S115">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="T115">
-        <v>3</v>
+        <v>2.95</v>
       </c>
       <c r="U115">
         <v>2.55</v>
@@ -19081,7 +19081,7 @@
         <v>1.45</v>
       </c>
       <c r="W115">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="X115">
         <v>1.02</v>
@@ -19096,22 +19096,22 @@
         <v>1.79</v>
       </c>
       <c r="AB115">
-        <v>1.92</v>
+        <v>1.89</v>
       </c>
       <c r="AC115">
-        <v>3.01</v>
+        <v>3</v>
       </c>
       <c r="AD115">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AE115">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="AF115">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="AG115">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="AH115" t="inlineStr">
         <is>
@@ -19124,10 +19124,10 @@
         </is>
       </c>
       <c r="AJ115">
-        <v>1.2</v>
+        <v>1.29</v>
       </c>
       <c r="AK115">
-        <v>1.13</v>
+        <v>1.17</v>
       </c>
       <c r="AL115">
         <v>0</v>
@@ -19217,13 +19217,13 @@
         </is>
       </c>
       <c r="N116">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="O116">
-        <v>3.3</v>
+        <v>3.12</v>
       </c>
       <c r="P116">
-        <v>3.65</v>
+        <v>3.28</v>
       </c>
       <c r="Q116">
         <v>2.54</v>
@@ -19232,25 +19232,25 @@
         <v>2.3</v>
       </c>
       <c r="S116">
-        <v>1.34</v>
+        <v>1.37</v>
       </c>
       <c r="T116">
         <v>2.88</v>
       </c>
       <c r="U116">
-        <v>2.66</v>
+        <v>2.6</v>
       </c>
       <c r="V116">
-        <v>1.41</v>
+        <v>1.43</v>
       </c>
       <c r="W116">
         <v>1.1</v>
       </c>
       <c r="X116">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="Y116">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="Z116">
         <v>3.75</v>
@@ -19274,7 +19274,7 @@
         <v>1.69</v>
       </c>
       <c r="AG116">
-        <v>2.05</v>
+        <v>2.02</v>
       </c>
       <c r="AH116" t="inlineStr">
         <is>
@@ -19413,10 +19413,10 @@
         <v>1.01</v>
       </c>
       <c r="Y117">
-        <v>1.18</v>
+        <v>1.14</v>
       </c>
       <c r="Z117">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="AA117">
         <v>1.6</v>
@@ -19431,7 +19431,7 @@
         <v>1.44</v>
       </c>
       <c r="AE117">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="AF117">
         <v>1.7</v>
@@ -19543,58 +19543,58 @@
         </is>
       </c>
       <c r="N118">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="O118">
-        <v>5.5</v>
+        <v>5.75</v>
       </c>
       <c r="P118">
-        <v>8.5</v>
+        <v>14.3</v>
       </c>
       <c r="Q118">
-        <v>1.64</v>
+        <v>1.68</v>
       </c>
       <c r="R118">
         <v>2.5</v>
       </c>
       <c r="S118">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="T118">
         <v>3.1</v>
       </c>
       <c r="U118">
-        <v>2.56</v>
+        <v>2.59</v>
       </c>
       <c r="V118">
         <v>1.44</v>
       </c>
       <c r="W118">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="X118">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="Y118">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="Z118">
-        <v>3.65</v>
+        <v>3.56</v>
       </c>
       <c r="AA118">
-        <v>1.78</v>
+        <v>1.81</v>
       </c>
       <c r="AB118">
-        <v>1.98</v>
+        <v>2.05</v>
       </c>
       <c r="AC118">
-        <v>2.97</v>
+        <v>2.83</v>
       </c>
       <c r="AD118">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="AE118">
-        <v>1.12</v>
+        <v>1.1</v>
       </c>
       <c r="AF118">
         <v>2.45</v>
@@ -19613,10 +19613,10 @@
         </is>
       </c>
       <c r="AJ118">
-        <v>1</v>
+        <v>1.13</v>
       </c>
       <c r="AK118">
-        <v>3.88</v>
+        <v>3.68</v>
       </c>
       <c r="AL118">
         <v>0</v>
@@ -20035,16 +20035,16 @@
         <v>1.95</v>
       </c>
       <c r="O121">
-        <v>3.25</v>
+        <v>3.24</v>
       </c>
       <c r="P121">
-        <v>3.3</v>
+        <v>3.31</v>
       </c>
       <c r="Q121">
         <v>2.55</v>
       </c>
       <c r="R121">
-        <v>2.05</v>
+        <v>1.99</v>
       </c>
       <c r="S121">
         <v>1.44</v>
@@ -20053,13 +20053,13 @@
         <v>2.56</v>
       </c>
       <c r="U121">
-        <v>2.9</v>
+        <v>3.07</v>
       </c>
       <c r="V121">
         <v>1.34</v>
       </c>
       <c r="W121">
-        <v>1.08</v>
+        <v>1.03</v>
       </c>
       <c r="X121">
         <v>1.06</v>
@@ -20086,7 +20086,7 @@
         <v>1.05</v>
       </c>
       <c r="AF121">
-        <v>1.83</v>
+        <v>1.87</v>
       </c>
       <c r="AG121">
         <v>1.8</v>
@@ -20105,7 +20105,7 @@
         <v>1.25</v>
       </c>
       <c r="AK121">
-        <v>1.7</v>
+        <v>1.84</v>
       </c>
       <c r="AL121">
         <v>0</v>
@@ -21499,43 +21499,43 @@
         </is>
       </c>
       <c r="N130">
-        <v>1.64</v>
+        <v>1.55</v>
       </c>
       <c r="O130">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="P130">
-        <v>4.45</v>
+        <v>5.2</v>
       </c>
       <c r="Q130">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="R130">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="S130">
         <v>1.4</v>
       </c>
       <c r="T130">
-        <v>2.5</v>
+        <v>2.62</v>
       </c>
       <c r="U130">
-        <v>3</v>
+        <v>3.08</v>
       </c>
       <c r="V130">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="W130">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="X130">
         <v>1.03</v>
       </c>
       <c r="Y130">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="Z130">
-        <v>2.83</v>
+        <v>2.63</v>
       </c>
       <c r="AA130">
         <v>2.25</v>
@@ -21544,16 +21544,16 @@
         <v>1.54</v>
       </c>
       <c r="AC130">
-        <v>3.96</v>
+        <v>3.86</v>
       </c>
       <c r="AD130">
-        <v>1.18</v>
+        <v>1.23</v>
       </c>
       <c r="AE130">
         <v>1.03</v>
       </c>
       <c r="AF130">
-        <v>2.12</v>
+        <v>2.17</v>
       </c>
       <c r="AG130">
         <v>1.65</v>
@@ -21569,10 +21569,10 @@
         </is>
       </c>
       <c r="AJ130">
-        <v>1.13</v>
+        <v>1.1</v>
       </c>
       <c r="AK130">
-        <v>2.13</v>
+        <v>2.28</v>
       </c>
       <c r="AL130">
         <v>0</v>
@@ -22492,7 +22492,7 @@
         <v>2.03</v>
       </c>
       <c r="S136">
-        <v>1.48</v>
+        <v>1.46</v>
       </c>
       <c r="T136">
         <v>2.44</v>
@@ -22522,7 +22522,7 @@
         <v>1.58</v>
       </c>
       <c r="AC136">
-        <v>4.8</v>
+        <v>4.2</v>
       </c>
       <c r="AD136">
         <v>1.17</v>

--- a/jogos_2026-08-02.xlsx
+++ b/jogos_2026-08-02.xlsx
@@ -641,13 +641,13 @@
         <v>4.75</v>
       </c>
       <c r="P2">
-        <v>6.9</v>
+        <v>7</v>
       </c>
       <c r="Q2">
-        <v>1.67</v>
+        <v>1.72</v>
       </c>
       <c r="R2">
-        <v>2.77</v>
+        <v>2.64</v>
       </c>
       <c r="S2">
         <v>1.25</v>
@@ -674,7 +674,7 @@
         <v>4.55</v>
       </c>
       <c r="AA2">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="AB2">
         <v>2.51</v>
@@ -683,7 +683,7 @@
         <v>2.34</v>
       </c>
       <c r="AD2">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="AE2">
         <v>1.2</v>
@@ -705,7 +705,7 @@
         </is>
       </c>
       <c r="AJ2">
-        <v>1.1</v>
+        <v>1.15</v>
       </c>
       <c r="AK2">
         <v>3.05</v>
@@ -807,55 +807,55 @@
         <v>1.33</v>
       </c>
       <c r="Q3">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="R3">
-        <v>2.43</v>
+        <v>2.55</v>
       </c>
       <c r="S3">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="T3">
-        <v>3.5</v>
+        <v>3.58</v>
       </c>
       <c r="U3">
-        <v>2.07</v>
+        <v>2.1</v>
       </c>
       <c r="V3">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="W3">
-        <v>1.12</v>
+        <v>1.17</v>
       </c>
       <c r="X3">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="Y3">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="Z3">
-        <v>5.1</v>
+        <v>5.25</v>
       </c>
       <c r="AA3">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="AB3">
-        <v>2.68</v>
+        <v>2.49</v>
       </c>
       <c r="AC3">
-        <v>2.09</v>
+        <v>2.12</v>
       </c>
       <c r="AD3">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="AE3">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="AF3">
-        <v>1.56</v>
+        <v>1.6</v>
       </c>
       <c r="AG3">
-        <v>2.18</v>
+        <v>2.25</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -868,10 +868,10 @@
         </is>
       </c>
       <c r="AJ3">
-        <v>2.43</v>
+        <v>1.14</v>
       </c>
       <c r="AK3">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -961,34 +961,34 @@
         </is>
       </c>
       <c r="N4">
-        <v>1.81</v>
+        <v>1.86</v>
       </c>
       <c r="O4">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="P4">
-        <v>3.65</v>
+        <v>3.55</v>
       </c>
       <c r="Q4">
-        <v>2.42</v>
+        <v>2.41</v>
       </c>
       <c r="R4">
-        <v>2.11</v>
+        <v>2.1</v>
       </c>
       <c r="S4">
-        <v>1.3</v>
+        <v>1.38</v>
       </c>
       <c r="T4">
         <v>2.75</v>
       </c>
       <c r="U4">
-        <v>2.71</v>
+        <v>2.78</v>
       </c>
       <c r="V4">
-        <v>1.37</v>
+        <v>1.39</v>
       </c>
       <c r="W4">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="X4">
         <v>1.01</v>
@@ -1000,25 +1000,25 @@
         <v>3.2</v>
       </c>
       <c r="AA4">
+        <v>1.94</v>
+      </c>
+      <c r="AB4">
+        <v>1.81</v>
+      </c>
+      <c r="AC4">
+        <v>3.14</v>
+      </c>
+      <c r="AD4">
+        <v>1.34</v>
+      </c>
+      <c r="AE4">
+        <v>1.07</v>
+      </c>
+      <c r="AF4">
         <v>1.75</v>
       </c>
-      <c r="AB4">
-        <v>2.05</v>
-      </c>
-      <c r="AC4">
-        <v>3.08</v>
-      </c>
-      <c r="AD4">
-        <v>1.28</v>
-      </c>
-      <c r="AE4">
-        <v>1.1</v>
-      </c>
-      <c r="AF4">
-        <v>1.74</v>
-      </c>
       <c r="AG4">
-        <v>1.91</v>
+        <v>1.93</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1031,7 +1031,7 @@
         </is>
       </c>
       <c r="AJ4">
-        <v>1.23</v>
+        <v>1.19</v>
       </c>
       <c r="AK4">
         <v>1.64</v>
@@ -1124,19 +1124,19 @@
         </is>
       </c>
       <c r="N5">
-        <v>1.76</v>
+        <v>1.78</v>
       </c>
       <c r="O5">
-        <v>3.84</v>
+        <v>3.7</v>
       </c>
       <c r="P5">
-        <v>3.74</v>
+        <v>3.5</v>
       </c>
       <c r="Q5">
-        <v>2.24</v>
+        <v>2.16</v>
       </c>
       <c r="R5">
-        <v>2.26</v>
+        <v>2.25</v>
       </c>
       <c r="S5">
         <v>1.26</v>
@@ -1145,34 +1145,34 @@
         <v>3.28</v>
       </c>
       <c r="U5">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="V5">
-        <v>1.59</v>
+        <v>1.57</v>
       </c>
       <c r="W5">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="X5">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="Y5">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="Z5">
-        <v>5.1</v>
+        <v>4.35</v>
       </c>
       <c r="AA5">
-        <v>1.53</v>
+        <v>1.62</v>
       </c>
       <c r="AB5">
-        <v>2.37</v>
+        <v>2.17</v>
       </c>
       <c r="AC5">
-        <v>2.21</v>
+        <v>2.52</v>
       </c>
       <c r="AD5">
-        <v>1.58</v>
+        <v>1.48</v>
       </c>
       <c r="AE5">
         <v>1.19</v>
@@ -1181,7 +1181,7 @@
         <v>1.54</v>
       </c>
       <c r="AG5">
-        <v>2.28</v>
+        <v>2.26</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1197,7 +1197,7 @@
         <v>1.19</v>
       </c>
       <c r="AK5">
-        <v>1.93</v>
+        <v>1.87</v>
       </c>
       <c r="AL5">
         <v>0</v>
@@ -1287,13 +1287,13 @@
         </is>
       </c>
       <c r="N6">
-        <v>1.26</v>
+        <v>1.32</v>
       </c>
       <c r="O6">
-        <v>5.25</v>
+        <v>4.65</v>
       </c>
       <c r="P6">
-        <v>8.35</v>
+        <v>6.8</v>
       </c>
       <c r="Q6">
         <v>0</v>
@@ -1326,10 +1326,10 @@
         <v>0</v>
       </c>
       <c r="AA6">
-        <v>1.66</v>
+        <v>1.72</v>
       </c>
       <c r="AB6">
-        <v>2.15</v>
+        <v>2.07</v>
       </c>
       <c r="AC6">
         <v>0</v>
@@ -1450,64 +1450,64 @@
         </is>
       </c>
       <c r="N7">
-        <v>1.89</v>
+        <v>1.91</v>
       </c>
       <c r="O7">
-        <v>3.62</v>
+        <v>3.5</v>
       </c>
       <c r="P7">
-        <v>3.47</v>
+        <v>3.2</v>
       </c>
       <c r="Q7">
-        <v>2.41</v>
+        <v>2.46</v>
       </c>
       <c r="R7">
-        <v>2.21</v>
+        <v>2.18</v>
       </c>
       <c r="S7">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="T7">
-        <v>3.12</v>
+        <v>3.04</v>
       </c>
       <c r="U7">
-        <v>2.31</v>
+        <v>2.44</v>
       </c>
       <c r="V7">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="W7">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="X7">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y7">
+        <v>1.16</v>
+      </c>
+      <c r="Z7">
+        <v>4.2</v>
+      </c>
+      <c r="AA7">
+        <v>1.67</v>
+      </c>
+      <c r="AB7">
+        <v>2.08</v>
+      </c>
+      <c r="AC7">
+        <v>2.38</v>
+      </c>
+      <c r="AD7">
+        <v>1.38</v>
+      </c>
+      <c r="AE7">
         <v>1.17</v>
-      </c>
-      <c r="Z7">
-        <v>4.3</v>
-      </c>
-      <c r="AA7">
-        <v>1.61</v>
-      </c>
-      <c r="AB7">
-        <v>2.25</v>
-      </c>
-      <c r="AC7">
-        <v>2.43</v>
-      </c>
-      <c r="AD7">
-        <v>1.44</v>
-      </c>
-      <c r="AE7">
-        <v>1.14</v>
       </c>
       <c r="AF7">
         <v>1.58</v>
       </c>
       <c r="AG7">
-        <v>2.15</v>
+        <v>2.19</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1523,7 +1523,7 @@
         <v>1.2</v>
       </c>
       <c r="AK7">
-        <v>1.74</v>
+        <v>1.6</v>
       </c>
       <c r="AL7">
         <v>0</v>
@@ -2175,7 +2175,7 @@
         <v>1.25</v>
       </c>
       <c r="AK11">
-        <v>1.9</v>
+        <v>1.87</v>
       </c>
       <c r="AL11">
         <v>0</v>
@@ -2265,13 +2265,13 @@
         </is>
       </c>
       <c r="N12">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="O12">
-        <v>4.33</v>
+        <v>4.25</v>
       </c>
       <c r="P12">
-        <v>5.25</v>
+        <v>5.9</v>
       </c>
       <c r="Q12">
         <v>2.05</v>
@@ -2283,7 +2283,7 @@
         <v>1.36</v>
       </c>
       <c r="T12">
-        <v>2.9</v>
+        <v>2.99</v>
       </c>
       <c r="U12">
         <v>2.65</v>
@@ -2304,7 +2304,7 @@
         <v>3.8</v>
       </c>
       <c r="AA12">
-        <v>1.84</v>
+        <v>1.82</v>
       </c>
       <c r="AB12">
         <v>1.95</v>
@@ -2319,7 +2319,7 @@
         <v>1.08</v>
       </c>
       <c r="AF12">
-        <v>2.05</v>
+        <v>1.92</v>
       </c>
       <c r="AG12">
         <v>1.77</v>
@@ -2467,7 +2467,7 @@
         <v>2.79</v>
       </c>
       <c r="AA13">
-        <v>2.43</v>
+        <v>2.38</v>
       </c>
       <c r="AB13">
         <v>1.57</v>
@@ -2498,10 +2498,10 @@
         </is>
       </c>
       <c r="AJ13">
-        <v>1.36</v>
+        <v>1.52</v>
       </c>
       <c r="AK13">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="AL13">
         <v>0</v>
@@ -2559,12 +2559,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Gimpo Citizen</t>
+          <t>Jeonnam Dragons</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Gyeongnam</t>
+          <t>Paju Citizen</t>
         </is>
       </c>
       <c r="G14">
@@ -2591,64 +2591,64 @@
         </is>
       </c>
       <c r="N14">
-        <v>1.94</v>
+        <v>1.97</v>
       </c>
       <c r="O14">
-        <v>2.98</v>
+        <v>3.32</v>
       </c>
       <c r="P14">
-        <v>3.05</v>
+        <v>3.45</v>
       </c>
       <c r="Q14">
-        <v>2.62</v>
+        <v>2.68</v>
       </c>
       <c r="R14">
-        <v>2.18</v>
+        <v>2.09</v>
       </c>
       <c r="S14">
+        <v>1.33</v>
+      </c>
+      <c r="T14">
+        <v>2.9</v>
+      </c>
+      <c r="U14">
+        <v>2.71</v>
+      </c>
+      <c r="V14">
         <v>1.4</v>
       </c>
-      <c r="T14">
-        <v>2.47</v>
-      </c>
-      <c r="U14">
-        <v>3.12</v>
-      </c>
-      <c r="V14">
-        <v>1.33</v>
-      </c>
       <c r="W14">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="X14">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y14">
-        <v>1.36</v>
+        <v>1.28</v>
       </c>
       <c r="Z14">
+        <v>3.55</v>
+      </c>
+      <c r="AA14">
+        <v>1.8</v>
+      </c>
+      <c r="AB14">
+        <v>1.93</v>
+      </c>
+      <c r="AC14">
         <v>2.7</v>
       </c>
-      <c r="AA14">
-        <v>2.03</v>
-      </c>
-      <c r="AB14">
-        <v>1.73</v>
-      </c>
-      <c r="AC14">
-        <v>3.2</v>
-      </c>
       <c r="AD14">
-        <v>1.18</v>
+        <v>1.31</v>
       </c>
       <c r="AE14">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="AF14">
-        <v>1.85</v>
+        <v>1.64</v>
       </c>
       <c r="AG14">
-        <v>1.8</v>
+        <v>2.1</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2661,10 +2661,10 @@
         </is>
       </c>
       <c r="AJ14">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="AK14">
-        <v>1.84</v>
+        <v>1.63</v>
       </c>
       <c r="AL14">
         <v>0</v>
@@ -2885,12 +2885,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Jeonnam Dragons</t>
+          <t>Gimpo Citizen</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Paju Citizen</t>
+          <t>Gyeongnam</t>
         </is>
       </c>
       <c r="G16">
@@ -2917,65 +2917,65 @@
         </is>
       </c>
       <c r="N16">
-        <v>1.97</v>
+        <v>1.94</v>
       </c>
       <c r="O16">
-        <v>3.32</v>
+        <v>2.98</v>
       </c>
       <c r="P16">
-        <v>3.45</v>
+        <v>3.05</v>
       </c>
       <c r="Q16">
-        <v>2.68</v>
+        <v>2.62</v>
       </c>
       <c r="R16">
-        <v>2.09</v>
+        <v>2.18</v>
       </c>
       <c r="S16">
+        <v>1.4</v>
+      </c>
+      <c r="T16">
+        <v>2.47</v>
+      </c>
+      <c r="U16">
+        <v>3.12</v>
+      </c>
+      <c r="V16">
         <v>1.33</v>
       </c>
-      <c r="T16">
-        <v>2.9</v>
-      </c>
-      <c r="U16">
-        <v>2.71</v>
-      </c>
-      <c r="V16">
-        <v>1.4</v>
-      </c>
       <c r="W16">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="X16">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y16">
-        <v>1.28</v>
+        <v>1.36</v>
       </c>
       <c r="Z16">
-        <v>3.55</v>
+        <v>2.7</v>
       </c>
       <c r="AA16">
+        <v>2.03</v>
+      </c>
+      <c r="AB16">
+        <v>1.73</v>
+      </c>
+      <c r="AC16">
+        <v>3.2</v>
+      </c>
+      <c r="AD16">
+        <v>1.18</v>
+      </c>
+      <c r="AE16">
+        <v>1.03</v>
+      </c>
+      <c r="AF16">
+        <v>1.85</v>
+      </c>
+      <c r="AG16">
         <v>1.8</v>
       </c>
-      <c r="AB16">
-        <v>1.93</v>
-      </c>
-      <c r="AC16">
-        <v>2.7</v>
-      </c>
-      <c r="AD16">
-        <v>1.31</v>
-      </c>
-      <c r="AE16">
-        <v>1.08</v>
-      </c>
-      <c r="AF16">
-        <v>1.64</v>
-      </c>
-      <c r="AG16">
-        <v>2.1</v>
-      </c>
       <c r="AH16" t="inlineStr">
         <is>
           <t>[]</t>
@@ -2987,10 +2987,10 @@
         </is>
       </c>
       <c r="AJ16">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="AK16">
-        <v>1.63</v>
+        <v>1.84</v>
       </c>
       <c r="AL16">
         <v>0</v>
@@ -4390,16 +4390,16 @@
         <v>3.5</v>
       </c>
       <c r="P25">
-        <v>4.05</v>
+        <v>4.5</v>
       </c>
       <c r="Q25">
-        <v>2.2</v>
+        <v>2.28</v>
       </c>
       <c r="R25">
-        <v>2.38</v>
+        <v>2.39</v>
       </c>
       <c r="S25">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="T25">
         <v>3.3</v>
@@ -4411,34 +4411,34 @@
         <v>1.46</v>
       </c>
       <c r="W25">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="X25">
         <v>1.01</v>
       </c>
       <c r="Y25">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="Z25">
-        <v>3.78</v>
+        <v>3.82</v>
       </c>
       <c r="AA25">
         <v>1.8</v>
       </c>
       <c r="AB25">
-        <v>2</v>
+        <v>2.03</v>
       </c>
       <c r="AC25">
-        <v>2.9</v>
+        <v>2.88</v>
       </c>
       <c r="AD25">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="AE25">
-        <v>1.11</v>
+        <v>1.09</v>
       </c>
       <c r="AF25">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="AG25">
         <v>2.05</v>
@@ -4454,7 +4454,7 @@
         </is>
       </c>
       <c r="AJ25">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AK25">
         <v>2</v>
@@ -4550,10 +4550,10 @@
         <v>3</v>
       </c>
       <c r="O26">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="P26">
-        <v>2.11</v>
+        <v>2.1</v>
       </c>
       <c r="Q26">
         <v>3.3</v>
@@ -4565,10 +4565,10 @@
         <v>1.3</v>
       </c>
       <c r="T26">
-        <v>3.6</v>
+        <v>3.22</v>
       </c>
       <c r="U26">
-        <v>2.3</v>
+        <v>2.34</v>
       </c>
       <c r="V26">
         <v>1.5</v>
@@ -4601,7 +4601,7 @@
         <v>1.16</v>
       </c>
       <c r="AF26">
-        <v>1.44</v>
+        <v>1.51</v>
       </c>
       <c r="AG26">
         <v>2.39</v>
@@ -6192,13 +6192,13 @@
         <v>2.28</v>
       </c>
       <c r="S36">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="T36">
-        <v>3.8</v>
+        <v>3.36</v>
       </c>
       <c r="U36">
-        <v>2.45</v>
+        <v>2.25</v>
       </c>
       <c r="V36">
         <v>1.56</v>
@@ -6219,7 +6219,7 @@
         <v>1.57</v>
       </c>
       <c r="AB36">
-        <v>2.33</v>
+        <v>2.35</v>
       </c>
       <c r="AC36">
         <v>2.5</v>
@@ -6250,7 +6250,7 @@
         <v>1.24</v>
       </c>
       <c r="AK36">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="AL36">
         <v>0</v>
@@ -6349,55 +6349,55 @@
         <v>0</v>
       </c>
       <c r="Q37">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="R37">
-        <v>0</v>
+        <v>2.76</v>
       </c>
       <c r="S37">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="T37">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="U37">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="V37">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="W37">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="X37">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y37">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="Z37">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="AA37">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AB37">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="AC37">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AD37">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AE37">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AF37">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AG37">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AH37" t="inlineStr">
         <is>
@@ -6410,10 +6410,10 @@
         </is>
       </c>
       <c r="AJ37">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AK37">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AL37">
         <v>0</v>
@@ -7366,7 +7366,7 @@
         <v>2.7</v>
       </c>
       <c r="AD43">
-        <v>1.41</v>
+        <v>1.45</v>
       </c>
       <c r="AE43">
         <v>1.12</v>
@@ -7375,7 +7375,7 @@
         <v>1.56</v>
       </c>
       <c r="AG43">
-        <v>2.17</v>
+        <v>2.24</v>
       </c>
       <c r="AH43" t="inlineStr">
         <is>
@@ -7391,7 +7391,7 @@
         <v>1.22</v>
       </c>
       <c r="AK43">
-        <v>1.26</v>
+        <v>1.29</v>
       </c>
       <c r="AL43">
         <v>0</v>
@@ -8101,12 +8101,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>EB - Streymur</t>
+          <t>KÍ</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Víkingur</t>
+          <t>B36</t>
         </is>
       </c>
       <c r="G48">
@@ -8133,64 +8133,64 @@
         </is>
       </c>
       <c r="N48">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="O48">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="P48">
-        <v>0</v>
+        <v>5.02</v>
       </c>
       <c r="Q48">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="R48">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="S48">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="T48">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="U48">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="V48">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="W48">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X48">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y48">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z48">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AA48">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AB48">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AC48">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AD48">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AE48">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AF48">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AG48">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AH48" t="inlineStr">
         <is>
@@ -8203,10 +8203,10 @@
         </is>
       </c>
       <c r="AJ48">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AK48">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AL48">
         <v>0</v>
@@ -8264,12 +8264,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>KÍ</t>
+          <t>EB - Streymur</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>B36</t>
+          <t>Víkingur</t>
         </is>
       </c>
       <c r="G49">
@@ -8296,80 +8296,80 @@
         </is>
       </c>
       <c r="N49">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="O49">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="P49">
-        <v>5.02</v>
+        <v>0</v>
       </c>
       <c r="Q49">
-        <v>2.15</v>
+        <v>5.75</v>
       </c>
       <c r="R49">
-        <v>2.17</v>
+        <v>2.36</v>
       </c>
       <c r="S49">
-        <v>1.34</v>
+        <v>1.27</v>
       </c>
       <c r="T49">
-        <v>2.88</v>
+        <v>3.25</v>
       </c>
       <c r="U49">
-        <v>2.63</v>
+        <v>2.25</v>
       </c>
       <c r="V49">
-        <v>1.44</v>
+        <v>1.57</v>
       </c>
       <c r="W49">
+        <v>1.14</v>
+      </c>
+      <c r="X49">
+        <v>1.01</v>
+      </c>
+      <c r="Y49">
+        <v>1.12</v>
+      </c>
+      <c r="Z49">
+        <v>4.65</v>
+      </c>
+      <c r="AA49">
+        <v>1.55</v>
+      </c>
+      <c r="AB49">
+        <v>2.29</v>
+      </c>
+      <c r="AC49">
+        <v>2.28</v>
+      </c>
+      <c r="AD49">
+        <v>1.5</v>
+      </c>
+      <c r="AE49">
+        <v>1.19</v>
+      </c>
+      <c r="AF49">
+        <v>1.72</v>
+      </c>
+      <c r="AG49">
+        <v>1.98</v>
+      </c>
+      <c r="AH49" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI49" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ49">
+        <v>1.13</v>
+      </c>
+      <c r="AK49">
         <v>1.06</v>
-      </c>
-      <c r="X49">
-        <v>1</v>
-      </c>
-      <c r="Y49">
-        <v>1.22</v>
-      </c>
-      <c r="Z49">
-        <v>3.5</v>
-      </c>
-      <c r="AA49">
-        <v>1.79</v>
-      </c>
-      <c r="AB49">
-        <v>1.92</v>
-      </c>
-      <c r="AC49">
-        <v>2.88</v>
-      </c>
-      <c r="AD49">
-        <v>1.32</v>
-      </c>
-      <c r="AE49">
-        <v>1.09</v>
-      </c>
-      <c r="AF49">
-        <v>1.81</v>
-      </c>
-      <c r="AG49">
-        <v>1.88</v>
-      </c>
-      <c r="AH49" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI49" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ49">
-        <v>1.09</v>
-      </c>
-      <c r="AK49">
-        <v>2.3</v>
       </c>
       <c r="AL49">
         <v>0</v>
@@ -9274,19 +9274,19 @@
         </is>
       </c>
       <c r="N55">
-        <v>1.49</v>
+        <v>1.42</v>
       </c>
       <c r="O55">
-        <v>4.6</v>
+        <v>4.45</v>
       </c>
       <c r="P55">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="Q55">
         <v>1.94</v>
       </c>
       <c r="R55">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="S55">
         <v>1.25</v>
@@ -9310,28 +9310,28 @@
         <v>1.15</v>
       </c>
       <c r="Z55">
-        <v>5.09</v>
+        <v>4.8</v>
       </c>
       <c r="AA55">
         <v>1.57</v>
       </c>
       <c r="AB55">
-        <v>2.52</v>
+        <v>2.35</v>
       </c>
       <c r="AC55">
-        <v>2.36</v>
+        <v>2.33</v>
       </c>
       <c r="AD55">
         <v>1.58</v>
       </c>
       <c r="AE55">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="AF55">
-        <v>1.57</v>
+        <v>1.63</v>
       </c>
       <c r="AG55">
-        <v>2.2</v>
+        <v>2.14</v>
       </c>
       <c r="AH55" t="inlineStr">
         <is>
@@ -9347,7 +9347,7 @@
         <v>1.17</v>
       </c>
       <c r="AK55">
-        <v>2.75</v>
+        <v>2.7</v>
       </c>
       <c r="AL55">
         <v>0</v>
@@ -9766,16 +9766,16 @@
         <v>3.4</v>
       </c>
       <c r="O58">
-        <v>3.61</v>
+        <v>3.5</v>
       </c>
       <c r="P58">
         <v>1.87</v>
       </c>
       <c r="Q58">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="R58">
-        <v>2.25</v>
+        <v>2.24</v>
       </c>
       <c r="S58">
         <v>1.29</v>
@@ -9793,7 +9793,7 @@
         <v>1.11</v>
       </c>
       <c r="X58">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y58">
         <v>1.18</v>
@@ -9805,7 +9805,7 @@
         <v>1.66</v>
       </c>
       <c r="AB58">
-        <v>2.18</v>
+        <v>2.15</v>
       </c>
       <c r="AC58">
         <v>2.57</v>
@@ -9926,7 +9926,7 @@
         </is>
       </c>
       <c r="N59">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="O59">
         <v>3.78</v>
@@ -9956,7 +9956,7 @@
         <v>1.08</v>
       </c>
       <c r="X59">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y59">
         <v>1.2</v>
@@ -9983,7 +9983,7 @@
         <v>1.67</v>
       </c>
       <c r="AG59">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="AH59" t="inlineStr">
         <is>
@@ -10101,7 +10101,7 @@
         <v>2</v>
       </c>
       <c r="R60">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="S60">
         <v>1.22</v>
@@ -10119,10 +10119,10 @@
         <v>1.17</v>
       </c>
       <c r="X60">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y60">
-        <v>1.14</v>
+        <v>1.08</v>
       </c>
       <c r="Z60">
         <v>5.75</v>
@@ -10137,7 +10137,7 @@
         <v>2.12</v>
       </c>
       <c r="AD60">
-        <v>1.73</v>
+        <v>1.69</v>
       </c>
       <c r="AE60">
         <v>1.26</v>
@@ -10162,7 +10162,7 @@
         <v>1.17</v>
       </c>
       <c r="AK60">
-        <v>2.13</v>
+        <v>2.18</v>
       </c>
       <c r="AL60">
         <v>0</v>
@@ -10741,34 +10741,34 @@
         </is>
       </c>
       <c r="N64">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="O64">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="P64">
         <v>5.35</v>
       </c>
       <c r="Q64">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="R64">
         <v>2.6</v>
       </c>
       <c r="S64">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="T64">
         <v>4.45</v>
       </c>
       <c r="U64">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="V64">
-        <v>1.9</v>
+        <v>1.88</v>
       </c>
       <c r="W64">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="X64">
         <v>1.01</v>
@@ -10777,7 +10777,7 @@
         <v>1.05</v>
       </c>
       <c r="Z64">
-        <v>6.55</v>
+        <v>8</v>
       </c>
       <c r="AA64">
         <v>1.27</v>
@@ -10786,19 +10786,19 @@
         <v>3.14</v>
       </c>
       <c r="AC64">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="AD64">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="AE64">
-        <v>1.41</v>
+        <v>1.39</v>
       </c>
       <c r="AF64">
-        <v>1.44</v>
+        <v>1.47</v>
       </c>
       <c r="AG64">
-        <v>2.46</v>
+        <v>2.5</v>
       </c>
       <c r="AH64" t="inlineStr">
         <is>
@@ -10814,7 +10814,7 @@
         <v>1.11</v>
       </c>
       <c r="AK64">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="AL64">
         <v>0</v>
@@ -10904,13 +10904,13 @@
         </is>
       </c>
       <c r="N65">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="O65">
-        <v>3.33</v>
+        <v>3.75</v>
       </c>
       <c r="P65">
-        <v>2.78</v>
+        <v>2.84</v>
       </c>
       <c r="Q65">
         <v>2.42</v>
@@ -10922,7 +10922,7 @@
         <v>1.25</v>
       </c>
       <c r="T65">
-        <v>3.36</v>
+        <v>3.6</v>
       </c>
       <c r="U65">
         <v>2.25</v>
@@ -10937,28 +10937,28 @@
         <v>1.01</v>
       </c>
       <c r="Y65">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="Z65">
-        <v>4.55</v>
+        <v>4.65</v>
       </c>
       <c r="AA65">
         <v>1.45</v>
       </c>
       <c r="AB65">
-        <v>2.41</v>
+        <v>2.45</v>
       </c>
       <c r="AC65">
-        <v>2.37</v>
+        <v>2.32</v>
       </c>
       <c r="AD65">
-        <v>1.57</v>
+        <v>1.59</v>
       </c>
       <c r="AE65">
         <v>1.2</v>
       </c>
       <c r="AF65">
-        <v>1.45</v>
+        <v>1.47</v>
       </c>
       <c r="AG65">
         <v>2.55</v>
@@ -10974,7 +10974,7 @@
         </is>
       </c>
       <c r="AJ65">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="AK65">
         <v>1.8</v>
@@ -11079,52 +11079,52 @@
         <v>3</v>
       </c>
       <c r="R66">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="S66">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="T66">
-        <v>3.84</v>
+        <v>3.95</v>
       </c>
       <c r="U66">
-        <v>2.02</v>
+        <v>1.92</v>
       </c>
       <c r="V66">
-        <v>1.75</v>
+        <v>1.78</v>
       </c>
       <c r="W66">
-        <v>1.19</v>
+        <v>1.21</v>
       </c>
       <c r="X66">
         <v>1.01</v>
       </c>
       <c r="Y66">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="Z66">
-        <v>5</v>
+        <v>6.59</v>
       </c>
       <c r="AA66">
         <v>1.36</v>
       </c>
       <c r="AB66">
-        <v>2.78</v>
+        <v>2.88</v>
       </c>
       <c r="AC66">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="AD66">
-        <v>1.85</v>
+        <v>1.93</v>
       </c>
       <c r="AE66">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="AF66">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="AG66">
-        <v>2.98</v>
+        <v>3.08</v>
       </c>
       <c r="AH66" t="inlineStr">
         <is>
@@ -11140,7 +11140,7 @@
         <v>1.2</v>
       </c>
       <c r="AK66">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="AL66">
         <v>0</v>
@@ -11236,10 +11236,10 @@
         <v>3.75</v>
       </c>
       <c r="P67">
-        <v>2.75</v>
+        <v>2.3</v>
       </c>
       <c r="Q67">
-        <v>2.64</v>
+        <v>2.66</v>
       </c>
       <c r="R67">
         <v>2.38</v>
@@ -11251,13 +11251,13 @@
         <v>3.9</v>
       </c>
       <c r="U67">
-        <v>2.04</v>
+        <v>2.13</v>
       </c>
       <c r="V67">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="W67">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="X67">
         <v>1.02</v>
@@ -11272,19 +11272,19 @@
         <v>1.46</v>
       </c>
       <c r="AB67">
-        <v>2.63</v>
+        <v>2.64</v>
       </c>
       <c r="AC67">
-        <v>2</v>
+        <v>2.07</v>
       </c>
       <c r="AD67">
-        <v>1.7</v>
+        <v>1.68</v>
       </c>
       <c r="AE67">
-        <v>1.28</v>
+        <v>1.24</v>
       </c>
       <c r="AF67">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="AG67">
         <v>2.75</v>
@@ -11300,10 +11300,10 @@
         </is>
       </c>
       <c r="AJ67">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="AK67">
-        <v>1.53</v>
+        <v>1.6</v>
       </c>
       <c r="AL67">
         <v>0</v>
@@ -11393,16 +11393,16 @@
         </is>
       </c>
       <c r="N68">
-        <v>4.5</v>
+        <v>3.97</v>
       </c>
       <c r="O68">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="P68">
-        <v>1.54</v>
+        <v>1.45</v>
       </c>
       <c r="Q68">
-        <v>4.74</v>
+        <v>4.78</v>
       </c>
       <c r="R68">
         <v>2.53</v>
@@ -11417,7 +11417,7 @@
         <v>1.94</v>
       </c>
       <c r="V68">
-        <v>1.76</v>
+        <v>1.79</v>
       </c>
       <c r="W68">
         <v>1.18</v>
@@ -11463,7 +11463,7 @@
         </is>
       </c>
       <c r="AJ68">
-        <v>1.18</v>
+        <v>1.15</v>
       </c>
       <c r="AK68">
         <v>1.15</v>
@@ -11562,7 +11562,7 @@
         <v>4.75</v>
       </c>
       <c r="P69">
-        <v>5.3</v>
+        <v>4.85</v>
       </c>
       <c r="Q69">
         <v>1.79</v>
@@ -11595,7 +11595,7 @@
         <v>6.6</v>
       </c>
       <c r="AA69">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="AB69">
         <v>2.85</v>
@@ -11607,13 +11607,13 @@
         <v>1.91</v>
       </c>
       <c r="AE69">
-        <v>1.37</v>
+        <v>1.33</v>
       </c>
       <c r="AF69">
         <v>1.49</v>
       </c>
       <c r="AG69">
-        <v>2.45</v>
+        <v>2.44</v>
       </c>
       <c r="AH69" t="inlineStr">
         <is>
@@ -13748,7 +13748,7 @@
         <v>1.17</v>
       </c>
       <c r="AK82">
-        <v>1.95</v>
+        <v>2.02</v>
       </c>
       <c r="AL82">
         <v>0</v>
@@ -14825,55 +14825,55 @@
         <v>0</v>
       </c>
       <c r="Q89">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="R89">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S89">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="T89">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="U89">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="V89">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="W89">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X89">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y89">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="Z89">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="AA89">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AB89">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AC89">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="AD89">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AE89">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AF89">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AG89">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AH89" t="inlineStr">
         <is>
@@ -14886,10 +14886,10 @@
         </is>
       </c>
       <c r="AJ89">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK89">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AL89">
         <v>0</v>
@@ -14979,64 +14979,64 @@
         </is>
       </c>
       <c r="N90">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="O90">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P90">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="Q90">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="R90">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="S90">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="T90">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="U90">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="V90">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="W90">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="X90">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y90">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="Z90">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="AA90">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AB90">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC90">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="AD90">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AE90">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AF90">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AG90">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="AH90" t="inlineStr">
         <is>
@@ -15049,10 +15049,10 @@
         </is>
       </c>
       <c r="AJ90">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK90">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AL90">
         <v>0</v>
@@ -15142,7 +15142,7 @@
         </is>
       </c>
       <c r="N91">
-        <v>3.05</v>
+        <v>3.08</v>
       </c>
       <c r="O91">
         <v>3.5</v>
@@ -15160,10 +15160,10 @@
         <v>1.33</v>
       </c>
       <c r="T91">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="U91">
-        <v>2.69</v>
+        <v>2.55</v>
       </c>
       <c r="V91">
         <v>1.44</v>
@@ -15178,16 +15178,16 @@
         <v>1.27</v>
       </c>
       <c r="Z91">
-        <v>3.5</v>
+        <v>3.71</v>
       </c>
       <c r="AA91">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="AB91">
-        <v>1.93</v>
+        <v>1.95</v>
       </c>
       <c r="AC91">
-        <v>3.04</v>
+        <v>3</v>
       </c>
       <c r="AD91">
         <v>1.35</v>
@@ -15196,7 +15196,7 @@
         <v>1.13</v>
       </c>
       <c r="AF91">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="AG91">
         <v>2.05</v>
@@ -16316,7 +16316,7 @@
         <v>1.02</v>
       </c>
       <c r="Y98">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="Z98">
         <v>5.25</v>
@@ -16328,13 +16328,13 @@
         <v>2.55</v>
       </c>
       <c r="AC98">
-        <v>2.27</v>
+        <v>2.24</v>
       </c>
       <c r="AD98">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="AE98">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="AF98">
         <v>1.44</v>
@@ -16775,13 +16775,13 @@
         <v>1.54</v>
       </c>
       <c r="O101">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="P101">
         <v>4.75</v>
       </c>
       <c r="Q101">
-        <v>2</v>
+        <v>2.01</v>
       </c>
       <c r="R101">
         <v>2.38</v>
@@ -16802,13 +16802,13 @@
         <v>1.11</v>
       </c>
       <c r="X101">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y101">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="Z101">
-        <v>3.9</v>
+        <v>4.69</v>
       </c>
       <c r="AA101">
         <v>1.62</v>
@@ -16845,7 +16845,7 @@
         <v>1.19</v>
       </c>
       <c r="AK101">
-        <v>2.47</v>
+        <v>2.5</v>
       </c>
       <c r="AL101">
         <v>0</v>
@@ -17261,13 +17261,13 @@
         </is>
       </c>
       <c r="N104">
-        <v>2.25</v>
+        <v>2.17</v>
       </c>
       <c r="O104">
         <v>2.7</v>
       </c>
       <c r="P104">
-        <v>3.69</v>
+        <v>3.65</v>
       </c>
       <c r="Q104">
         <v>0</v>
@@ -17602,10 +17602,10 @@
         <v>1.73</v>
       </c>
       <c r="S106">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="T106">
-        <v>2.1</v>
+        <v>1.9</v>
       </c>
       <c r="U106">
         <v>4.6</v>
@@ -17614,7 +17614,7 @@
         <v>1.13</v>
       </c>
       <c r="W106">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="X106">
         <v>1.18</v>
@@ -17623,7 +17623,7 @@
         <v>1.74</v>
       </c>
       <c r="Z106">
-        <v>2.02</v>
+        <v>1.98</v>
       </c>
       <c r="AA106">
         <v>3.5</v>
@@ -17644,7 +17644,7 @@
         <v>2.54</v>
       </c>
       <c r="AG106">
-        <v>1.43</v>
+        <v>1.45</v>
       </c>
       <c r="AH106" t="inlineStr">
         <is>
@@ -17660,7 +17660,7 @@
         <v>1.25</v>
       </c>
       <c r="AK106">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="AL106">
         <v>0</v>
@@ -17750,7 +17750,7 @@
         </is>
       </c>
       <c r="N107">
-        <v>2.25</v>
+        <v>2.17</v>
       </c>
       <c r="O107">
         <v>2.7</v>
@@ -19706,13 +19706,13 @@
         </is>
       </c>
       <c r="N119">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="O119">
-        <v>2.65</v>
+        <v>2.75</v>
       </c>
       <c r="P119">
-        <v>4.35</v>
+        <v>3.9</v>
       </c>
       <c r="Q119">
         <v>3</v>
@@ -19721,7 +19721,7 @@
         <v>1.7</v>
       </c>
       <c r="S119">
-        <v>1.62</v>
+        <v>1.58</v>
       </c>
       <c r="T119">
         <v>1.99</v>
@@ -19763,7 +19763,7 @@
         <v>2.3</v>
       </c>
       <c r="AG119">
-        <v>1.46</v>
+        <v>1.48</v>
       </c>
       <c r="AH119" t="inlineStr">
         <is>
@@ -19776,10 +19776,10 @@
         </is>
       </c>
       <c r="AJ119">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="AK119">
-        <v>1.67</v>
+        <v>1.58</v>
       </c>
       <c r="AL119">
         <v>0</v>
@@ -19869,13 +19869,13 @@
         </is>
       </c>
       <c r="N120">
-        <v>2.62</v>
+        <v>2.46</v>
       </c>
       <c r="O120">
-        <v>2.75</v>
+        <v>2.8</v>
       </c>
       <c r="P120">
-        <v>2.85</v>
+        <v>2.73</v>
       </c>
       <c r="Q120">
         <v>3.51</v>
@@ -19887,7 +19887,7 @@
         <v>1.57</v>
       </c>
       <c r="T120">
-        <v>2.33</v>
+        <v>2.2</v>
       </c>
       <c r="U120">
         <v>3.75</v>
@@ -19911,13 +19911,13 @@
         <v>2.56</v>
       </c>
       <c r="AB120">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="AC120">
         <v>5.44</v>
       </c>
       <c r="AD120">
-        <v>1.13</v>
+        <v>1.1</v>
       </c>
       <c r="AE120">
         <v>1.01</v>
@@ -19926,7 +19926,7 @@
         <v>2.1</v>
       </c>
       <c r="AG120">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="AH120" t="inlineStr">
         <is>
@@ -19942,7 +19942,7 @@
         <v>1.4</v>
       </c>
       <c r="AK120">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="AL120">
         <v>0</v>
@@ -20195,64 +20195,64 @@
         </is>
       </c>
       <c r="N122">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="O122">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="P122">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="Q122">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="R122">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="S122">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="T122">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="U122">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="V122">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="W122">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X122">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y122">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Z122">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AA122">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AB122">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AC122">
-        <v>0</v>
+        <v>3.86</v>
       </c>
       <c r="AD122">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AE122">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF122">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AG122">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AH122" t="inlineStr">
         <is>
@@ -20265,10 +20265,10 @@
         </is>
       </c>
       <c r="AJ122">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AK122">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AL122">
         <v>0</v>
@@ -20358,16 +20358,16 @@
         </is>
       </c>
       <c r="N123">
-        <v>2.55</v>
+        <v>2.37</v>
       </c>
       <c r="O123">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="P123">
-        <v>2.45</v>
+        <v>2.54</v>
       </c>
       <c r="Q123">
-        <v>2.9</v>
+        <v>2.85</v>
       </c>
       <c r="R123">
         <v>2.25</v>
@@ -20376,7 +20376,7 @@
         <v>1.3</v>
       </c>
       <c r="T123">
-        <v>3.21</v>
+        <v>3.2</v>
       </c>
       <c r="U123">
         <v>2.6</v>
@@ -20394,19 +20394,19 @@
         <v>1.24</v>
       </c>
       <c r="Z123">
-        <v>3.55</v>
+        <v>3.7</v>
       </c>
       <c r="AA123">
         <v>1.8</v>
       </c>
       <c r="AB123">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="AC123">
         <v>2.8</v>
       </c>
       <c r="AD123">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AE123">
         <v>1.15</v>
@@ -20431,7 +20431,7 @@
         <v>1.5</v>
       </c>
       <c r="AK123">
-        <v>1.39</v>
+        <v>1.45</v>
       </c>
       <c r="AL123">
         <v>0</v>
@@ -20687,19 +20687,19 @@
         <v>1.91</v>
       </c>
       <c r="O125">
-        <v>2.75</v>
+        <v>2.8</v>
       </c>
       <c r="P125">
-        <v>4.4</v>
+        <v>4.2</v>
       </c>
       <c r="Q125">
         <v>2.7</v>
       </c>
       <c r="R125">
+        <v>1.83</v>
+      </c>
+      <c r="S125">
         <v>1.72</v>
-      </c>
-      <c r="S125">
-        <v>1.7</v>
       </c>
       <c r="T125">
         <v>2.25</v>
@@ -20714,10 +20714,10 @@
         <v>1.03</v>
       </c>
       <c r="X125">
-        <v>1.12</v>
+        <v>1.16</v>
       </c>
       <c r="Y125">
-        <v>1.71</v>
+        <v>1.68</v>
       </c>
       <c r="Z125">
         <v>2.09</v>
@@ -20726,13 +20726,13 @@
         <v>3.4</v>
       </c>
       <c r="AB125">
-        <v>1.42</v>
+        <v>1.33</v>
       </c>
       <c r="AC125">
-        <v>6.28</v>
+        <v>4.9</v>
       </c>
       <c r="AD125">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="AE125">
         <v>1.02</v>
@@ -20847,25 +20847,25 @@
         </is>
       </c>
       <c r="N126">
-        <v>2.87</v>
+        <v>2.91</v>
       </c>
       <c r="O126">
         <v>2.7</v>
       </c>
       <c r="P126">
-        <v>2.5</v>
+        <v>2.44</v>
       </c>
       <c r="Q126">
-        <v>3.45</v>
+        <v>4.15</v>
       </c>
       <c r="R126">
-        <v>1.82</v>
+        <v>1.74</v>
       </c>
       <c r="S126">
         <v>1.67</v>
       </c>
       <c r="T126">
-        <v>2.14</v>
+        <v>2.07</v>
       </c>
       <c r="U126">
         <v>4</v>
@@ -20877,13 +20877,13 @@
         <v>1.03</v>
       </c>
       <c r="X126">
-        <v>1.14</v>
+        <v>1.1</v>
       </c>
       <c r="Y126">
-        <v>1.57</v>
+        <v>1.65</v>
       </c>
       <c r="Z126">
-        <v>2.11</v>
+        <v>2.2</v>
       </c>
       <c r="AA126">
         <v>3.4</v>
@@ -20892,19 +20892,19 @@
         <v>1.32</v>
       </c>
       <c r="AC126">
-        <v>6.27</v>
+        <v>5.9</v>
       </c>
       <c r="AD126">
-        <v>1.11</v>
+        <v>1.07</v>
       </c>
       <c r="AE126">
         <v>1.02</v>
       </c>
       <c r="AF126">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="AG126">
-        <v>1.52</v>
+        <v>1.57</v>
       </c>
       <c r="AH126" t="inlineStr">
         <is>
@@ -20917,10 +20917,10 @@
         </is>
       </c>
       <c r="AJ126">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="AK126">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="AL126">
         <v>0</v>
@@ -21173,10 +21173,10 @@
         </is>
       </c>
       <c r="N128">
-        <v>2.83</v>
+        <v>2.87</v>
       </c>
       <c r="O128">
-        <v>2.53</v>
+        <v>2.5</v>
       </c>
       <c r="P128">
         <v>2.87</v>
@@ -21345,10 +21345,10 @@
         <v>3.25</v>
       </c>
       <c r="Q129">
-        <v>2.66</v>
+        <v>2.7</v>
       </c>
       <c r="R129">
-        <v>2.06</v>
+        <v>2.1</v>
       </c>
       <c r="S129">
         <v>1.37</v>
@@ -21369,25 +21369,25 @@
         <v>1.03</v>
       </c>
       <c r="Y129">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="Z129">
         <v>3.08</v>
       </c>
       <c r="AA129">
-        <v>1.94</v>
+        <v>1.76</v>
       </c>
       <c r="AB129">
-        <v>1.73</v>
+        <v>1.87</v>
       </c>
       <c r="AC129">
         <v>3.34</v>
       </c>
       <c r="AD129">
-        <v>1.18</v>
+        <v>1.33</v>
       </c>
       <c r="AE129">
-        <v>1.08</v>
+        <v>1.04</v>
       </c>
       <c r="AF129">
         <v>1.62</v>
@@ -21988,13 +21988,13 @@
         </is>
       </c>
       <c r="N133">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="O133">
-        <v>3.9</v>
+        <v>3.7</v>
       </c>
       <c r="P133">
-        <v>4.65</v>
+        <v>5.17</v>
       </c>
       <c r="Q133">
         <v>2.1</v>
@@ -22326,31 +22326,31 @@
         <v>2.47</v>
       </c>
       <c r="R135">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="S135">
-        <v>1.26</v>
+        <v>1.29</v>
       </c>
       <c r="T135">
-        <v>3.28</v>
+        <v>3.3</v>
       </c>
       <c r="U135">
-        <v>2.31</v>
+        <v>2.4</v>
       </c>
       <c r="V135">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="W135">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="X135">
         <v>1.03</v>
       </c>
       <c r="Y135">
-        <v>1.15</v>
+        <v>1.21</v>
       </c>
       <c r="Z135">
-        <v>4.2</v>
+        <v>3.6</v>
       </c>
       <c r="AA135">
         <v>1.61</v>
@@ -22368,10 +22368,10 @@
         <v>1.13</v>
       </c>
       <c r="AF135">
-        <v>1.53</v>
+        <v>1.62</v>
       </c>
       <c r="AG135">
-        <v>2.24</v>
+        <v>2.1</v>
       </c>
       <c r="AH135" t="inlineStr">
         <is>
@@ -22384,10 +22384,10 @@
         </is>
       </c>
       <c r="AJ135">
-        <v>1.21</v>
+        <v>1.26</v>
       </c>
       <c r="AK135">
-        <v>1.69</v>
+        <v>1.8</v>
       </c>
       <c r="AL135">
         <v>0</v>
@@ -22809,7 +22809,7 @@
         <v>3.6</v>
       </c>
       <c r="P138">
-        <v>3.5</v>
+        <v>3.56</v>
       </c>
       <c r="Q138">
         <v>0</v>

--- a/jogos_2026-08-02.xlsx
+++ b/jogos_2026-08-02.xlsx
@@ -2559,12 +2559,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Jeonnam Dragons</t>
+          <t>Gimpo Citizen</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Paju Citizen</t>
+          <t>Gyeongnam</t>
         </is>
       </c>
       <c r="G14">
@@ -2591,65 +2591,65 @@
         </is>
       </c>
       <c r="N14">
-        <v>1.97</v>
+        <v>1.94</v>
       </c>
       <c r="O14">
-        <v>3.32</v>
+        <v>2.98</v>
       </c>
       <c r="P14">
-        <v>3.45</v>
+        <v>3.05</v>
       </c>
       <c r="Q14">
-        <v>2.68</v>
+        <v>2.62</v>
       </c>
       <c r="R14">
-        <v>2.09</v>
+        <v>2.18</v>
       </c>
       <c r="S14">
+        <v>1.4</v>
+      </c>
+      <c r="T14">
+        <v>2.47</v>
+      </c>
+      <c r="U14">
+        <v>3.12</v>
+      </c>
+      <c r="V14">
         <v>1.33</v>
       </c>
-      <c r="T14">
-        <v>2.9</v>
-      </c>
-      <c r="U14">
-        <v>2.71</v>
-      </c>
-      <c r="V14">
-        <v>1.4</v>
-      </c>
       <c r="W14">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="X14">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y14">
-        <v>1.28</v>
+        <v>1.36</v>
       </c>
       <c r="Z14">
-        <v>3.55</v>
+        <v>2.7</v>
       </c>
       <c r="AA14">
+        <v>2.03</v>
+      </c>
+      <c r="AB14">
+        <v>1.73</v>
+      </c>
+      <c r="AC14">
+        <v>3.2</v>
+      </c>
+      <c r="AD14">
+        <v>1.18</v>
+      </c>
+      <c r="AE14">
+        <v>1.03</v>
+      </c>
+      <c r="AF14">
+        <v>1.85</v>
+      </c>
+      <c r="AG14">
         <v>1.8</v>
       </c>
-      <c r="AB14">
-        <v>1.93</v>
-      </c>
-      <c r="AC14">
-        <v>2.7</v>
-      </c>
-      <c r="AD14">
-        <v>1.31</v>
-      </c>
-      <c r="AE14">
-        <v>1.08</v>
-      </c>
-      <c r="AF14">
-        <v>1.64</v>
-      </c>
-      <c r="AG14">
-        <v>2.1</v>
-      </c>
       <c r="AH14" t="inlineStr">
         <is>
           <t>[]</t>
@@ -2661,10 +2661,10 @@
         </is>
       </c>
       <c r="AJ14">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="AK14">
-        <v>1.63</v>
+        <v>1.84</v>
       </c>
       <c r="AL14">
         <v>0</v>
@@ -2885,12 +2885,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Gimpo Citizen</t>
+          <t>Jeonnam Dragons</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Gyeongnam</t>
+          <t>Paju Citizen</t>
         </is>
       </c>
       <c r="G16">
@@ -2917,64 +2917,64 @@
         </is>
       </c>
       <c r="N16">
-        <v>1.94</v>
+        <v>1.97</v>
       </c>
       <c r="O16">
-        <v>2.98</v>
+        <v>3.32</v>
       </c>
       <c r="P16">
-        <v>3.05</v>
+        <v>3.45</v>
       </c>
       <c r="Q16">
-        <v>2.62</v>
+        <v>2.68</v>
       </c>
       <c r="R16">
-        <v>2.18</v>
+        <v>2.09</v>
       </c>
       <c r="S16">
+        <v>1.33</v>
+      </c>
+      <c r="T16">
+        <v>2.9</v>
+      </c>
+      <c r="U16">
+        <v>2.71</v>
+      </c>
+      <c r="V16">
         <v>1.4</v>
       </c>
-      <c r="T16">
-        <v>2.47</v>
-      </c>
-      <c r="U16">
-        <v>3.12</v>
-      </c>
-      <c r="V16">
-        <v>1.33</v>
-      </c>
       <c r="W16">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="X16">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y16">
-        <v>1.36</v>
+        <v>1.28</v>
       </c>
       <c r="Z16">
+        <v>3.55</v>
+      </c>
+      <c r="AA16">
+        <v>1.8</v>
+      </c>
+      <c r="AB16">
+        <v>1.93</v>
+      </c>
+      <c r="AC16">
         <v>2.7</v>
       </c>
-      <c r="AA16">
-        <v>2.03</v>
-      </c>
-      <c r="AB16">
-        <v>1.73</v>
-      </c>
-      <c r="AC16">
-        <v>3.2</v>
-      </c>
       <c r="AD16">
-        <v>1.18</v>
+        <v>1.31</v>
       </c>
       <c r="AE16">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="AF16">
-        <v>1.85</v>
+        <v>1.64</v>
       </c>
       <c r="AG16">
-        <v>1.8</v>
+        <v>2.1</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -2987,10 +2987,10 @@
         </is>
       </c>
       <c r="AJ16">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="AK16">
-        <v>1.84</v>
+        <v>1.63</v>
       </c>
       <c r="AL16">
         <v>0</v>

--- a/jogos_2026-08-02.xlsx
+++ b/jogos_2026-08-02.xlsx
@@ -635,28 +635,28 @@
         </is>
       </c>
       <c r="N2">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="O2">
-        <v>4.75</v>
+        <v>5.45</v>
       </c>
       <c r="P2">
-        <v>7</v>
+        <v>7.95</v>
       </c>
       <c r="Q2">
         <v>1.72</v>
       </c>
       <c r="R2">
-        <v>2.64</v>
+        <v>2.77</v>
       </c>
       <c r="S2">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="T2">
-        <v>3.5</v>
+        <v>3.75</v>
       </c>
       <c r="U2">
-        <v>2.2</v>
+        <v>2.29</v>
       </c>
       <c r="V2">
         <v>1.59</v>
@@ -674,7 +674,7 @@
         <v>4.55</v>
       </c>
       <c r="AA2">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="AB2">
         <v>2.51</v>
@@ -683,7 +683,7 @@
         <v>2.34</v>
       </c>
       <c r="AD2">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="AE2">
         <v>1.2</v>
@@ -692,7 +692,7 @@
         <v>1.82</v>
       </c>
       <c r="AG2">
-        <v>1.95</v>
+        <v>1.87</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
@@ -705,7 +705,7 @@
         </is>
       </c>
       <c r="AJ2">
-        <v>1.15</v>
+        <v>1.1</v>
       </c>
       <c r="AK2">
         <v>3.05</v>
@@ -2559,12 +2559,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Gimpo Citizen</t>
+          <t>Ansan Greeners</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Gyeongnam</t>
+          <t>Gimhae City</t>
         </is>
       </c>
       <c r="G14">
@@ -2591,64 +2591,64 @@
         </is>
       </c>
       <c r="N14">
-        <v>1.94</v>
+        <v>2.91</v>
       </c>
       <c r="O14">
-        <v>2.98</v>
+        <v>3.38</v>
       </c>
       <c r="P14">
-        <v>3.05</v>
+        <v>2.18</v>
       </c>
       <c r="Q14">
-        <v>2.62</v>
+        <v>3.28</v>
       </c>
       <c r="R14">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="S14">
+        <v>1.35</v>
+      </c>
+      <c r="T14">
+        <v>2.82</v>
+      </c>
+      <c r="U14">
+        <v>2.74</v>
+      </c>
+      <c r="V14">
         <v>1.4</v>
       </c>
-      <c r="T14">
-        <v>2.47</v>
-      </c>
-      <c r="U14">
-        <v>3.12</v>
-      </c>
-      <c r="V14">
-        <v>1.33</v>
-      </c>
       <c r="W14">
-        <v>1.02</v>
+        <v>1.08</v>
       </c>
       <c r="X14">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y14">
-        <v>1.36</v>
+        <v>1.24</v>
       </c>
       <c r="Z14">
-        <v>2.7</v>
+        <v>3.34</v>
       </c>
       <c r="AA14">
-        <v>2.03</v>
+        <v>1.86</v>
       </c>
       <c r="AB14">
-        <v>1.73</v>
+        <v>1.85</v>
       </c>
       <c r="AC14">
         <v>3.2</v>
       </c>
       <c r="AD14">
-        <v>1.18</v>
+        <v>1.28</v>
       </c>
       <c r="AE14">
-        <v>1.03</v>
+        <v>1.11</v>
       </c>
       <c r="AF14">
-        <v>1.85</v>
+        <v>1.67</v>
       </c>
       <c r="AG14">
-        <v>1.8</v>
+        <v>2.1</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2661,10 +2661,10 @@
         </is>
       </c>
       <c r="AJ14">
-        <v>1.22</v>
+        <v>1.62</v>
       </c>
       <c r="AK14">
-        <v>1.84</v>
+        <v>1.36</v>
       </c>
       <c r="AL14">
         <v>0</v>
@@ -2885,12 +2885,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Jeonnam Dragons</t>
+          <t>Gimpo Citizen</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Paju Citizen</t>
+          <t>Gyeongnam</t>
         </is>
       </c>
       <c r="G16">
@@ -2917,65 +2917,65 @@
         </is>
       </c>
       <c r="N16">
-        <v>1.97</v>
+        <v>1.94</v>
       </c>
       <c r="O16">
-        <v>3.32</v>
+        <v>2.98</v>
       </c>
       <c r="P16">
-        <v>3.45</v>
+        <v>3.05</v>
       </c>
       <c r="Q16">
-        <v>2.68</v>
+        <v>2.62</v>
       </c>
       <c r="R16">
-        <v>2.09</v>
+        <v>2.18</v>
       </c>
       <c r="S16">
+        <v>1.4</v>
+      </c>
+      <c r="T16">
+        <v>2.47</v>
+      </c>
+      <c r="U16">
+        <v>3.12</v>
+      </c>
+      <c r="V16">
         <v>1.33</v>
       </c>
-      <c r="T16">
-        <v>2.9</v>
-      </c>
-      <c r="U16">
-        <v>2.71</v>
-      </c>
-      <c r="V16">
-        <v>1.4</v>
-      </c>
       <c r="W16">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="X16">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y16">
-        <v>1.28</v>
+        <v>1.36</v>
       </c>
       <c r="Z16">
-        <v>3.55</v>
+        <v>2.7</v>
       </c>
       <c r="AA16">
+        <v>2.03</v>
+      </c>
+      <c r="AB16">
+        <v>1.73</v>
+      </c>
+      <c r="AC16">
+        <v>3.2</v>
+      </c>
+      <c r="AD16">
+        <v>1.18</v>
+      </c>
+      <c r="AE16">
+        <v>1.03</v>
+      </c>
+      <c r="AF16">
+        <v>1.85</v>
+      </c>
+      <c r="AG16">
         <v>1.8</v>
       </c>
-      <c r="AB16">
-        <v>1.93</v>
-      </c>
-      <c r="AC16">
-        <v>2.7</v>
-      </c>
-      <c r="AD16">
-        <v>1.31</v>
-      </c>
-      <c r="AE16">
-        <v>1.08</v>
-      </c>
-      <c r="AF16">
-        <v>1.64</v>
-      </c>
-      <c r="AG16">
-        <v>2.1</v>
-      </c>
       <c r="AH16" t="inlineStr">
         <is>
           <t>[]</t>
@@ -2987,10 +2987,10 @@
         </is>
       </c>
       <c r="AJ16">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="AK16">
-        <v>1.63</v>
+        <v>1.84</v>
       </c>
       <c r="AL16">
         <v>0</v>
@@ -3048,12 +3048,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Ansan Greeners</t>
+          <t>Jeonnam Dragons</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Gimhae City</t>
+          <t>Paju Citizen</t>
         </is>
       </c>
       <c r="G17">
@@ -3080,61 +3080,61 @@
         </is>
       </c>
       <c r="N17">
-        <v>2.91</v>
+        <v>1.97</v>
       </c>
       <c r="O17">
-        <v>3.38</v>
+        <v>3.32</v>
       </c>
       <c r="P17">
-        <v>2.18</v>
+        <v>3.45</v>
       </c>
       <c r="Q17">
-        <v>3.28</v>
+        <v>2.68</v>
       </c>
       <c r="R17">
-        <v>2.2</v>
+        <v>2.09</v>
       </c>
       <c r="S17">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="T17">
-        <v>2.82</v>
+        <v>2.9</v>
       </c>
       <c r="U17">
-        <v>2.74</v>
+        <v>2.71</v>
       </c>
       <c r="V17">
         <v>1.4</v>
       </c>
       <c r="W17">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="X17">
         <v>1.01</v>
       </c>
       <c r="Y17">
-        <v>1.24</v>
+        <v>1.28</v>
       </c>
       <c r="Z17">
-        <v>3.34</v>
+        <v>3.55</v>
       </c>
       <c r="AA17">
-        <v>1.86</v>
+        <v>1.8</v>
       </c>
       <c r="AB17">
-        <v>1.85</v>
+        <v>1.93</v>
       </c>
       <c r="AC17">
-        <v>3.2</v>
+        <v>2.7</v>
       </c>
       <c r="AD17">
-        <v>1.28</v>
+        <v>1.31</v>
       </c>
       <c r="AE17">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="AF17">
-        <v>1.67</v>
+        <v>1.64</v>
       </c>
       <c r="AG17">
         <v>2.1</v>
@@ -3150,10 +3150,10 @@
         </is>
       </c>
       <c r="AJ17">
-        <v>1.62</v>
+        <v>1.24</v>
       </c>
       <c r="AK17">
-        <v>1.36</v>
+        <v>1.63</v>
       </c>
       <c r="AL17">
         <v>0</v>
@@ -6666,7 +6666,7 @@
         </is>
       </c>
       <c r="N39">
-        <v>8.050000000000001</v>
+        <v>7.6</v>
       </c>
       <c r="O39">
         <v>4.4</v>
@@ -6690,7 +6690,7 @@
         <v>2.6</v>
       </c>
       <c r="V39">
-        <v>1.47</v>
+        <v>1.45</v>
       </c>
       <c r="W39">
         <v>1.08</v>
@@ -6723,7 +6723,7 @@
         <v>2.02</v>
       </c>
       <c r="AG39">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="AH39" t="inlineStr">
         <is>
@@ -6736,7 +6736,7 @@
         </is>
       </c>
       <c r="AJ39">
-        <v>1.2</v>
+        <v>3.08</v>
       </c>
       <c r="AK39">
         <v>1.1</v>
@@ -11361,12 +11361,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Raufoss</t>
+          <t>Odd</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Stabæk</t>
+          <t>Åsane</t>
         </is>
       </c>
       <c r="G68">
@@ -11393,34 +11393,34 @@
         </is>
       </c>
       <c r="N68">
-        <v>3.97</v>
+        <v>1.39</v>
       </c>
       <c r="O68">
-        <v>4.2</v>
+        <v>4.75</v>
       </c>
       <c r="P68">
-        <v>1.45</v>
+        <v>4.85</v>
       </c>
       <c r="Q68">
-        <v>4.78</v>
+        <v>1.79</v>
       </c>
       <c r="R68">
-        <v>2.53</v>
+        <v>2.75</v>
       </c>
       <c r="S68">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="T68">
-        <v>4.2</v>
+        <v>4.33</v>
       </c>
       <c r="U68">
-        <v>1.94</v>
+        <v>1.99</v>
       </c>
       <c r="V68">
-        <v>1.79</v>
+        <v>1.83</v>
       </c>
       <c r="W68">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="X68">
         <v>1.01</v>
@@ -11429,28 +11429,28 @@
         <v>1.1</v>
       </c>
       <c r="Z68">
-        <v>6.47</v>
+        <v>6.6</v>
       </c>
       <c r="AA68">
         <v>1.36</v>
       </c>
       <c r="AB68">
-        <v>2.92</v>
+        <v>2.85</v>
       </c>
       <c r="AC68">
-        <v>1.98</v>
+        <v>1.88</v>
       </c>
       <c r="AD68">
-        <v>1.71</v>
+        <v>1.91</v>
       </c>
       <c r="AE68">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AF68">
-        <v>1.4</v>
+        <v>1.49</v>
       </c>
       <c r="AG68">
-        <v>2.73</v>
+        <v>2.44</v>
       </c>
       <c r="AH68" t="inlineStr">
         <is>
@@ -11463,10 +11463,10 @@
         </is>
       </c>
       <c r="AJ68">
-        <v>1.15</v>
+        <v>1.13</v>
       </c>
       <c r="AK68">
-        <v>1.15</v>
+        <v>2.7</v>
       </c>
       <c r="AL68">
         <v>0</v>
@@ -11524,12 +11524,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Odd</t>
+          <t>Raufoss</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Åsane</t>
+          <t>Stabæk</t>
         </is>
       </c>
       <c r="G69">
@@ -11556,34 +11556,34 @@
         </is>
       </c>
       <c r="N69">
-        <v>1.39</v>
+        <v>3.97</v>
       </c>
       <c r="O69">
-        <v>4.75</v>
+        <v>4.2</v>
       </c>
       <c r="P69">
-        <v>4.85</v>
+        <v>1.45</v>
       </c>
       <c r="Q69">
+        <v>4.78</v>
+      </c>
+      <c r="R69">
+        <v>2.53</v>
+      </c>
+      <c r="S69">
+        <v>1.17</v>
+      </c>
+      <c r="T69">
+        <v>4.2</v>
+      </c>
+      <c r="U69">
+        <v>1.94</v>
+      </c>
+      <c r="V69">
         <v>1.79</v>
       </c>
-      <c r="R69">
-        <v>2.75</v>
-      </c>
-      <c r="S69">
+      <c r="W69">
         <v>1.18</v>
-      </c>
-      <c r="T69">
-        <v>4.33</v>
-      </c>
-      <c r="U69">
-        <v>1.99</v>
-      </c>
-      <c r="V69">
-        <v>1.83</v>
-      </c>
-      <c r="W69">
-        <v>1.2</v>
       </c>
       <c r="X69">
         <v>1.01</v>
@@ -11592,28 +11592,28 @@
         <v>1.1</v>
       </c>
       <c r="Z69">
-        <v>6.6</v>
+        <v>6.47</v>
       </c>
       <c r="AA69">
         <v>1.36</v>
       </c>
       <c r="AB69">
-        <v>2.85</v>
+        <v>2.92</v>
       </c>
       <c r="AC69">
-        <v>1.88</v>
+        <v>1.98</v>
       </c>
       <c r="AD69">
-        <v>1.91</v>
+        <v>1.71</v>
       </c>
       <c r="AE69">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AF69">
-        <v>1.49</v>
+        <v>1.4</v>
       </c>
       <c r="AG69">
-        <v>2.44</v>
+        <v>2.73</v>
       </c>
       <c r="AH69" t="inlineStr">
         <is>
@@ -11626,10 +11626,10 @@
         </is>
       </c>
       <c r="AJ69">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="AK69">
-        <v>2.7</v>
+        <v>1.15</v>
       </c>
       <c r="AL69">
         <v>0</v>
@@ -11891,16 +11891,16 @@
         <v>11.4</v>
       </c>
       <c r="Q71">
-        <v>1.81</v>
+        <v>1.83</v>
       </c>
       <c r="R71">
         <v>2.4</v>
       </c>
       <c r="S71">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="T71">
-        <v>2.98</v>
+        <v>3.02</v>
       </c>
       <c r="U71">
         <v>2.77</v>
@@ -11918,7 +11918,7 @@
         <v>1.27</v>
       </c>
       <c r="Z71">
-        <v>3.49</v>
+        <v>3.42</v>
       </c>
       <c r="AA71">
         <v>1.86</v>
@@ -11952,10 +11952,10 @@
         </is>
       </c>
       <c r="AJ71">
-        <v>1.2</v>
+        <v>1.07</v>
       </c>
       <c r="AK71">
-        <v>3.36</v>
+        <v>3.08</v>
       </c>
       <c r="AL71">
         <v>0</v>
@@ -14132,12 +14132,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Vaprus</t>
+          <t>Tallinna FC Flora</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Tallinna FC Levadia</t>
+          <t>Harju Jalgpallikool</t>
         </is>
       </c>
       <c r="G85">
@@ -14164,64 +14164,64 @@
         </is>
       </c>
       <c r="N85">
-        <v>11.7</v>
+        <v>1.33</v>
       </c>
       <c r="O85">
-        <v>6</v>
+        <v>4.55</v>
       </c>
       <c r="P85">
-        <v>1.18</v>
+        <v>6.5</v>
       </c>
       <c r="Q85">
-        <v>9.25</v>
+        <v>1.78</v>
       </c>
       <c r="R85">
-        <v>2.77</v>
+        <v>2.56</v>
       </c>
       <c r="S85">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="T85">
-        <v>3.74</v>
+        <v>3.72</v>
       </c>
       <c r="U85">
-        <v>2.05</v>
+        <v>2.02</v>
       </c>
       <c r="V85">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="W85">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="X85">
         <v>1.01</v>
       </c>
       <c r="Y85">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="Z85">
-        <v>5.6</v>
+        <v>5.75</v>
       </c>
       <c r="AA85">
-        <v>1.36</v>
+        <v>1.44</v>
       </c>
       <c r="AB85">
-        <v>2.75</v>
+        <v>2.74</v>
       </c>
       <c r="AC85">
-        <v>1.99</v>
+        <v>2.01</v>
       </c>
       <c r="AD85">
-        <v>1.73</v>
+        <v>1.78</v>
       </c>
       <c r="AE85">
         <v>1.28</v>
       </c>
       <c r="AF85">
-        <v>1.89</v>
+        <v>1.58</v>
       </c>
       <c r="AG85">
-        <v>1.8</v>
+        <v>2.21</v>
       </c>
       <c r="AH85" t="inlineStr">
         <is>
@@ -14234,10 +14234,10 @@
         </is>
       </c>
       <c r="AJ85">
-        <v>1.06</v>
+        <v>1.11</v>
       </c>
       <c r="AK85">
-        <v>1.04</v>
+        <v>3.2</v>
       </c>
       <c r="AL85">
         <v>0</v>
@@ -14295,12 +14295,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Tallinna FC Flora</t>
+          <t>Vaprus</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Harju Jalgpallikool</t>
+          <t>Tallinna FC Levadia</t>
         </is>
       </c>
       <c r="G86">
@@ -14327,64 +14327,64 @@
         </is>
       </c>
       <c r="N86">
-        <v>1.33</v>
+        <v>11.7</v>
       </c>
       <c r="O86">
-        <v>4.55</v>
+        <v>6</v>
       </c>
       <c r="P86">
-        <v>6.5</v>
+        <v>1.18</v>
       </c>
       <c r="Q86">
-        <v>1.78</v>
+        <v>9.25</v>
       </c>
       <c r="R86">
-        <v>2.56</v>
+        <v>2.77</v>
       </c>
       <c r="S86">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="T86">
-        <v>3.72</v>
+        <v>3.74</v>
       </c>
       <c r="U86">
-        <v>2.02</v>
+        <v>2.05</v>
       </c>
       <c r="V86">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="W86">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="X86">
         <v>1.01</v>
       </c>
       <c r="Y86">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="Z86">
-        <v>5.75</v>
+        <v>5.6</v>
       </c>
       <c r="AA86">
-        <v>1.44</v>
+        <v>1.36</v>
       </c>
       <c r="AB86">
-        <v>2.74</v>
+        <v>2.75</v>
       </c>
       <c r="AC86">
-        <v>2.01</v>
+        <v>1.99</v>
       </c>
       <c r="AD86">
-        <v>1.78</v>
+        <v>1.73</v>
       </c>
       <c r="AE86">
         <v>1.28</v>
       </c>
       <c r="AF86">
-        <v>1.58</v>
+        <v>1.89</v>
       </c>
       <c r="AG86">
-        <v>2.21</v>
+        <v>1.8</v>
       </c>
       <c r="AH86" t="inlineStr">
         <is>
@@ -14397,10 +14397,10 @@
         </is>
       </c>
       <c r="AJ86">
-        <v>1.11</v>
+        <v>1.06</v>
       </c>
       <c r="AK86">
-        <v>3.2</v>
+        <v>1.04</v>
       </c>
       <c r="AL86">
         <v>0</v>
@@ -16612,22 +16612,22 @@
         <v>3.7</v>
       </c>
       <c r="O100">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="P100">
-        <v>1.88</v>
+        <v>1.94</v>
       </c>
       <c r="Q100">
-        <v>3.76</v>
+        <v>4.33</v>
       </c>
       <c r="R100">
-        <v>2.08</v>
+        <v>2.19</v>
       </c>
       <c r="S100">
         <v>1.36</v>
       </c>
       <c r="T100">
-        <v>3.03</v>
+        <v>2.93</v>
       </c>
       <c r="U100">
         <v>2.77</v>
@@ -16645,13 +16645,13 @@
         <v>1.28</v>
       </c>
       <c r="Z100">
-        <v>3.59</v>
+        <v>3.42</v>
       </c>
       <c r="AA100">
         <v>1.91</v>
       </c>
       <c r="AB100">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="AC100">
         <v>3.1</v>
@@ -20652,12 +20652,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Deportivo Madryn</t>
+          <t>Chaco For Ever</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>All Boys</t>
+          <t>Deportivo Morón</t>
         </is>
       </c>
       <c r="G125">
@@ -20684,64 +20684,64 @@
         </is>
       </c>
       <c r="N125">
-        <v>1.91</v>
+        <v>2.91</v>
       </c>
       <c r="O125">
-        <v>2.8</v>
+        <v>2.7</v>
       </c>
       <c r="P125">
-        <v>4.2</v>
+        <v>2.44</v>
       </c>
       <c r="Q125">
-        <v>2.7</v>
+        <v>4.15</v>
       </c>
       <c r="R125">
-        <v>1.83</v>
+        <v>1.74</v>
       </c>
       <c r="S125">
-        <v>1.72</v>
+        <v>1.67</v>
       </c>
       <c r="T125">
-        <v>2.25</v>
+        <v>2.07</v>
       </c>
       <c r="U125">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="V125">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="W125">
         <v>1.03</v>
       </c>
       <c r="X125">
-        <v>1.16</v>
+        <v>1.1</v>
       </c>
       <c r="Y125">
-        <v>1.68</v>
+        <v>1.65</v>
       </c>
       <c r="Z125">
-        <v>2.09</v>
+        <v>2.2</v>
       </c>
       <c r="AA125">
         <v>3.4</v>
       </c>
       <c r="AB125">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="AC125">
-        <v>4.9</v>
+        <v>5.9</v>
       </c>
       <c r="AD125">
-        <v>1.1</v>
+        <v>1.07</v>
       </c>
       <c r="AE125">
         <v>1.02</v>
       </c>
       <c r="AF125">
-        <v>2.51</v>
+        <v>2.32</v>
       </c>
       <c r="AG125">
-        <v>1.46</v>
+        <v>1.57</v>
       </c>
       <c r="AH125" t="inlineStr">
         <is>
@@ -20754,10 +20754,10 @@
         </is>
       </c>
       <c r="AJ125">
-        <v>1.35</v>
+        <v>1.4</v>
       </c>
       <c r="AK125">
-        <v>1.8</v>
+        <v>1.36</v>
       </c>
       <c r="AL125">
         <v>0</v>
@@ -20815,12 +20815,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Chaco For Ever</t>
+          <t>Deportivo Madryn</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Deportivo Morón</t>
+          <t>All Boys</t>
         </is>
       </c>
       <c r="G126">
@@ -20847,64 +20847,64 @@
         </is>
       </c>
       <c r="N126">
-        <v>2.91</v>
+        <v>1.91</v>
       </c>
       <c r="O126">
+        <v>2.8</v>
+      </c>
+      <c r="P126">
+        <v>4.2</v>
+      </c>
+      <c r="Q126">
         <v>2.7</v>
       </c>
-      <c r="P126">
-        <v>2.44</v>
-      </c>
-      <c r="Q126">
-        <v>4.15</v>
-      </c>
       <c r="R126">
-        <v>1.74</v>
+        <v>1.83</v>
       </c>
       <c r="S126">
-        <v>1.67</v>
+        <v>1.72</v>
       </c>
       <c r="T126">
-        <v>2.07</v>
+        <v>2.25</v>
       </c>
       <c r="U126">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="V126">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="W126">
         <v>1.03</v>
       </c>
       <c r="X126">
-        <v>1.1</v>
+        <v>1.16</v>
       </c>
       <c r="Y126">
-        <v>1.65</v>
+        <v>1.68</v>
       </c>
       <c r="Z126">
-        <v>2.2</v>
+        <v>2.09</v>
       </c>
       <c r="AA126">
         <v>3.4</v>
       </c>
       <c r="AB126">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="AC126">
-        <v>5.9</v>
+        <v>4.9</v>
       </c>
       <c r="AD126">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="AE126">
         <v>1.02</v>
       </c>
       <c r="AF126">
-        <v>2.32</v>
+        <v>2.51</v>
       </c>
       <c r="AG126">
-        <v>1.57</v>
+        <v>1.46</v>
       </c>
       <c r="AH126" t="inlineStr">
         <is>
@@ -20917,10 +20917,10 @@
         </is>
       </c>
       <c r="AJ126">
-        <v>1.4</v>
+        <v>1.35</v>
       </c>
       <c r="AK126">
-        <v>1.36</v>
+        <v>1.8</v>
       </c>
       <c r="AL126">
         <v>0</v>
@@ -21345,10 +21345,10 @@
         <v>3.25</v>
       </c>
       <c r="Q129">
-        <v>2.7</v>
+        <v>2.43</v>
       </c>
       <c r="R129">
-        <v>2.1</v>
+        <v>2.25</v>
       </c>
       <c r="S129">
         <v>1.37</v>
@@ -21357,43 +21357,43 @@
         <v>2.71</v>
       </c>
       <c r="U129">
-        <v>2.9</v>
+        <v>2.45</v>
       </c>
       <c r="V129">
-        <v>1.36</v>
+        <v>1.42</v>
       </c>
       <c r="W129">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="X129">
         <v>1.03</v>
       </c>
       <c r="Y129">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="Z129">
-        <v>3.08</v>
+        <v>3.12</v>
       </c>
       <c r="AA129">
-        <v>1.76</v>
+        <v>1.96</v>
       </c>
       <c r="AB129">
-        <v>1.87</v>
+        <v>1.75</v>
       </c>
       <c r="AC129">
         <v>3.34</v>
       </c>
       <c r="AD129">
-        <v>1.33</v>
+        <v>1.24</v>
       </c>
       <c r="AE129">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="AF129">
-        <v>1.62</v>
+        <v>1.75</v>
       </c>
       <c r="AG129">
-        <v>1.73</v>
+        <v>1.95</v>
       </c>
       <c r="AH129" t="inlineStr">
         <is>
@@ -21409,7 +21409,7 @@
         <v>1.1</v>
       </c>
       <c r="AK129">
-        <v>1.61</v>
+        <v>1.72</v>
       </c>
       <c r="AL129">
         <v>0</v>
@@ -22323,28 +22323,28 @@
         <v>3.27</v>
       </c>
       <c r="Q135">
-        <v>2.47</v>
+        <v>2.49</v>
       </c>
       <c r="R135">
         <v>2.3</v>
       </c>
       <c r="S135">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="T135">
-        <v>3.3</v>
+        <v>3.14</v>
       </c>
       <c r="U135">
-        <v>2.4</v>
+        <v>2.48</v>
       </c>
       <c r="V135">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
       <c r="W135">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="X135">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y135">
         <v>1.21</v>
@@ -22353,22 +22353,22 @@
         <v>3.6</v>
       </c>
       <c r="AA135">
-        <v>1.61</v>
+        <v>1.7</v>
       </c>
       <c r="AB135">
-        <v>2.15</v>
+        <v>1.94</v>
       </c>
       <c r="AC135">
-        <v>2.49</v>
+        <v>2.62</v>
       </c>
       <c r="AD135">
-        <v>1.42</v>
+        <v>1.36</v>
       </c>
       <c r="AE135">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="AF135">
-        <v>1.62</v>
+        <v>1.55</v>
       </c>
       <c r="AG135">
         <v>2.1</v>
@@ -22384,10 +22384,10 @@
         </is>
       </c>
       <c r="AJ135">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="AK135">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="AL135">
         <v>0</v>
@@ -22803,13 +22803,13 @@
         </is>
       </c>
       <c r="N138">
-        <v>1.84</v>
+        <v>1.9</v>
       </c>
       <c r="O138">
-        <v>3.6</v>
+        <v>3.45</v>
       </c>
       <c r="P138">
-        <v>3.56</v>
+        <v>3.25</v>
       </c>
       <c r="Q138">
         <v>0</v>

--- a/jogos_2026-08-02.xlsx
+++ b/jogos_2026-08-02.xlsx
@@ -1625,7 +1625,7 @@
         <v>5</v>
       </c>
       <c r="R8">
-        <v>2.02</v>
+        <v>2.01</v>
       </c>
       <c r="S8">
         <v>1.43</v>
@@ -1652,10 +1652,10 @@
         <v>2.97</v>
       </c>
       <c r="AA8">
-        <v>2.13</v>
+        <v>2.09</v>
       </c>
       <c r="AB8">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="AC8">
         <v>3.68</v>
@@ -1670,7 +1670,7 @@
         <v>1.92</v>
       </c>
       <c r="AG8">
-        <v>1.77</v>
+        <v>1.79</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1683,7 +1683,7 @@
         </is>
       </c>
       <c r="AJ8">
-        <v>1.96</v>
+        <v>1.3</v>
       </c>
       <c r="AK8">
         <v>1.2</v>
@@ -1954,7 +1954,7 @@
         <v>2.38</v>
       </c>
       <c r="S10">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="T10">
         <v>3.35</v>
@@ -1963,10 +1963,10 @@
         <v>2.33</v>
       </c>
       <c r="V10">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="W10">
-        <v>1.11</v>
+        <v>1.09</v>
       </c>
       <c r="X10">
         <v>1.03</v>
@@ -1975,22 +1975,22 @@
         <v>1.13</v>
       </c>
       <c r="Z10">
-        <v>4.74</v>
+        <v>4.5</v>
       </c>
       <c r="AA10">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="AB10">
         <v>2.2</v>
       </c>
       <c r="AC10">
-        <v>2.44</v>
+        <v>2.37</v>
       </c>
       <c r="AD10">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="AE10">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="AF10">
         <v>1.57</v>
@@ -2600,7 +2600,7 @@
         <v>2.18</v>
       </c>
       <c r="Q14">
-        <v>3.28</v>
+        <v>3.4</v>
       </c>
       <c r="R14">
         <v>2.2</v>
@@ -2612,7 +2612,7 @@
         <v>2.82</v>
       </c>
       <c r="U14">
-        <v>2.74</v>
+        <v>2.75</v>
       </c>
       <c r="V14">
         <v>1.4</v>
@@ -2621,25 +2621,25 @@
         <v>1.08</v>
       </c>
       <c r="X14">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="Y14">
-        <v>1.24</v>
+        <v>1.29</v>
       </c>
       <c r="Z14">
-        <v>3.34</v>
+        <v>3.28</v>
       </c>
       <c r="AA14">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="AB14">
-        <v>1.85</v>
+        <v>1.87</v>
       </c>
       <c r="AC14">
         <v>3.2</v>
       </c>
       <c r="AD14">
-        <v>1.28</v>
+        <v>1.31</v>
       </c>
       <c r="AE14">
         <v>1.11</v>
@@ -2664,7 +2664,7 @@
         <v>1.62</v>
       </c>
       <c r="AK14">
-        <v>1.36</v>
+        <v>1.32</v>
       </c>
       <c r="AL14">
         <v>0</v>
@@ -2722,12 +2722,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Busan I'Park</t>
+          <t>Jeonnam Dragons</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Seoul E-Land</t>
+          <t>Paju Citizen</t>
         </is>
       </c>
       <c r="G15">
@@ -2754,64 +2754,64 @@
         </is>
       </c>
       <c r="N15">
-        <v>2.42</v>
+        <v>1.97</v>
       </c>
       <c r="O15">
-        <v>3.3</v>
+        <v>3.32</v>
       </c>
       <c r="P15">
-        <v>2.17</v>
+        <v>3.45</v>
       </c>
       <c r="Q15">
-        <v>3.1</v>
+        <v>2.66</v>
       </c>
       <c r="R15">
-        <v>2.36</v>
+        <v>2.09</v>
       </c>
       <c r="S15">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="T15">
-        <v>3.15</v>
+        <v>2.9</v>
       </c>
       <c r="U15">
-        <v>2.5</v>
+        <v>2.71</v>
       </c>
       <c r="V15">
-        <v>1.45</v>
+        <v>1.43</v>
       </c>
       <c r="W15">
-        <v>1.11</v>
+        <v>1.05</v>
       </c>
       <c r="X15">
-        <v>1.03</v>
+        <v>1</v>
       </c>
       <c r="Y15">
-        <v>1.16</v>
+        <v>1.21</v>
       </c>
       <c r="Z15">
-        <v>4.05</v>
+        <v>3.58</v>
       </c>
       <c r="AA15">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="AB15">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="AC15">
-        <v>2.62</v>
+        <v>2.92</v>
       </c>
       <c r="AD15">
-        <v>1.44</v>
+        <v>1.31</v>
       </c>
       <c r="AE15">
-        <v>1.17</v>
+        <v>1.13</v>
       </c>
       <c r="AF15">
-        <v>1.57</v>
+        <v>1.65</v>
       </c>
       <c r="AG15">
-        <v>2.27</v>
+        <v>2.1</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2824,10 +2824,10 @@
         </is>
       </c>
       <c r="AJ15">
-        <v>1.23</v>
+        <v>1.33</v>
       </c>
       <c r="AK15">
-        <v>1.38</v>
+        <v>1.7</v>
       </c>
       <c r="AL15">
         <v>0</v>
@@ -2885,12 +2885,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Gimpo Citizen</t>
+          <t>Busan I'Park</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Gyeongnam</t>
+          <t>Seoul E-Land</t>
         </is>
       </c>
       <c r="G16">
@@ -2917,64 +2917,64 @@
         </is>
       </c>
       <c r="N16">
-        <v>1.94</v>
+        <v>2.65</v>
       </c>
       <c r="O16">
-        <v>2.98</v>
+        <v>3.5</v>
       </c>
       <c r="P16">
-        <v>3.05</v>
+        <v>2.2</v>
       </c>
       <c r="Q16">
-        <v>2.62</v>
+        <v>3.1</v>
       </c>
       <c r="R16">
-        <v>2.18</v>
+        <v>2.36</v>
       </c>
       <c r="S16">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="T16">
-        <v>2.47</v>
+        <v>3.25</v>
       </c>
       <c r="U16">
-        <v>3.12</v>
+        <v>2.5</v>
       </c>
       <c r="V16">
-        <v>1.33</v>
+        <v>1.45</v>
       </c>
       <c r="W16">
-        <v>1.02</v>
+        <v>1.11</v>
       </c>
       <c r="X16">
         <v>1.04</v>
       </c>
       <c r="Y16">
-        <v>1.36</v>
+        <v>1.21</v>
       </c>
       <c r="Z16">
-        <v>2.7</v>
+        <v>4.23</v>
       </c>
       <c r="AA16">
-        <v>2.03</v>
+        <v>1.7</v>
       </c>
       <c r="AB16">
-        <v>1.73</v>
+        <v>2.1</v>
       </c>
       <c r="AC16">
-        <v>3.2</v>
+        <v>2.66</v>
       </c>
       <c r="AD16">
-        <v>1.18</v>
+        <v>1.37</v>
       </c>
       <c r="AE16">
-        <v>1.03</v>
+        <v>1.11</v>
       </c>
       <c r="AF16">
-        <v>1.85</v>
+        <v>1.57</v>
       </c>
       <c r="AG16">
-        <v>1.8</v>
+        <v>2.2</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -2987,10 +2987,10 @@
         </is>
       </c>
       <c r="AJ16">
-        <v>1.22</v>
+        <v>1.51</v>
       </c>
       <c r="AK16">
-        <v>1.84</v>
+        <v>1.4</v>
       </c>
       <c r="AL16">
         <v>0</v>
@@ -3048,12 +3048,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Jeonnam Dragons</t>
+          <t>Gimpo Citizen</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Paju Citizen</t>
+          <t>Gyeongnam</t>
         </is>
       </c>
       <c r="G17">
@@ -3080,65 +3080,65 @@
         </is>
       </c>
       <c r="N17">
-        <v>1.97</v>
+        <v>1.95</v>
       </c>
       <c r="O17">
-        <v>3.32</v>
+        <v>3.2</v>
       </c>
       <c r="P17">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="Q17">
-        <v>2.68</v>
+        <v>2.62</v>
       </c>
       <c r="R17">
-        <v>2.09</v>
+        <v>2.18</v>
       </c>
       <c r="S17">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="T17">
-        <v>2.9</v>
+        <v>2.47</v>
       </c>
       <c r="U17">
-        <v>2.71</v>
+        <v>3.12</v>
       </c>
       <c r="V17">
-        <v>1.4</v>
+        <v>1.29</v>
       </c>
       <c r="W17">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="X17">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y17">
-        <v>1.28</v>
+        <v>1.39</v>
       </c>
       <c r="Z17">
-        <v>3.55</v>
+        <v>2.95</v>
       </c>
       <c r="AA17">
+        <v>2.12</v>
+      </c>
+      <c r="AB17">
+        <v>1.62</v>
+      </c>
+      <c r="AC17">
+        <v>3.2</v>
+      </c>
+      <c r="AD17">
+        <v>1.21</v>
+      </c>
+      <c r="AE17">
+        <v>1.03</v>
+      </c>
+      <c r="AF17">
+        <v>1.92</v>
+      </c>
+      <c r="AG17">
         <v>1.8</v>
       </c>
-      <c r="AB17">
-        <v>1.93</v>
-      </c>
-      <c r="AC17">
-        <v>2.7</v>
-      </c>
-      <c r="AD17">
-        <v>1.31</v>
-      </c>
-      <c r="AE17">
-        <v>1.08</v>
-      </c>
-      <c r="AF17">
-        <v>1.64</v>
-      </c>
-      <c r="AG17">
-        <v>2.1</v>
-      </c>
       <c r="AH17" t="inlineStr">
         <is>
           <t>[]</t>
@@ -3150,10 +3150,10 @@
         </is>
       </c>
       <c r="AJ17">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="AK17">
-        <v>1.63</v>
+        <v>1.84</v>
       </c>
       <c r="AL17">
         <v>0</v>
@@ -3741,19 +3741,19 @@
         <v>1.99</v>
       </c>
       <c r="Q21">
-        <v>3.88</v>
+        <v>3.81</v>
       </c>
       <c r="R21">
-        <v>2.5</v>
+        <v>2.49</v>
       </c>
       <c r="S21">
         <v>1.2</v>
       </c>
       <c r="T21">
-        <v>3.68</v>
+        <v>4.05</v>
       </c>
       <c r="U21">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="V21">
         <v>1.63</v>
@@ -3765,13 +3765,13 @@
         <v>1.02</v>
       </c>
       <c r="Y21">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="Z21">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="AA21">
-        <v>1.48</v>
+        <v>1.43</v>
       </c>
       <c r="AB21">
         <v>2.6</v>
@@ -3780,16 +3780,16 @@
         <v>2.15</v>
       </c>
       <c r="AD21">
-        <v>1.69</v>
+        <v>1.65</v>
       </c>
       <c r="AE21">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="AF21">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="AG21">
-        <v>2.6</v>
+        <v>2.63</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
@@ -3802,10 +3802,10 @@
         </is>
       </c>
       <c r="AJ21">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AK21">
-        <v>1.28</v>
+        <v>1.2</v>
       </c>
       <c r="AL21">
         <v>0</v>
@@ -3904,7 +3904,7 @@
         <v>0</v>
       </c>
       <c r="Q22">
-        <v>2.55</v>
+        <v>2.69</v>
       </c>
       <c r="R22">
         <v>2.07</v>
@@ -3916,10 +3916,10 @@
         <v>2.77</v>
       </c>
       <c r="U22">
-        <v>2.69</v>
+        <v>2.86</v>
       </c>
       <c r="V22">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="W22">
         <v>1.06</v>
@@ -3928,16 +3928,16 @@
         <v>1.03</v>
       </c>
       <c r="Y22">
-        <v>1.23</v>
+        <v>1.28</v>
       </c>
       <c r="Z22">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="AA22">
-        <v>1.77</v>
+        <v>1.89</v>
       </c>
       <c r="AB22">
-        <v>1.83</v>
+        <v>1.86</v>
       </c>
       <c r="AC22">
         <v>3.4</v>
@@ -3946,7 +3946,7 @@
         <v>1.29</v>
       </c>
       <c r="AE22">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="AF22">
         <v>1.71</v>
@@ -3965,10 +3965,10 @@
         </is>
       </c>
       <c r="AJ22">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="AK22">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="AL22">
         <v>0</v>
@@ -4058,25 +4058,25 @@
         </is>
       </c>
       <c r="N23">
-        <v>2.7</v>
+        <v>2.95</v>
       </c>
       <c r="O23">
         <v>3.8</v>
       </c>
       <c r="P23">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="Q23">
-        <v>3.48</v>
+        <v>3.25</v>
       </c>
       <c r="R23">
-        <v>2.35</v>
+        <v>2.38</v>
       </c>
       <c r="S23">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="T23">
-        <v>3.8</v>
+        <v>3.5</v>
       </c>
       <c r="U23">
         <v>2.18</v>
@@ -4091,10 +4091,10 @@
         <v>1.02</v>
       </c>
       <c r="Y23">
-        <v>1.15</v>
+        <v>1.12</v>
       </c>
       <c r="Z23">
-        <v>5.38</v>
+        <v>4.8</v>
       </c>
       <c r="AA23">
         <v>1.46</v>
@@ -4109,7 +4109,7 @@
         <v>1.64</v>
       </c>
       <c r="AE23">
-        <v>1.27</v>
+        <v>1.23</v>
       </c>
       <c r="AF23">
         <v>1.44</v>
@@ -4128,10 +4128,10 @@
         </is>
       </c>
       <c r="AJ23">
-        <v>1.62</v>
+        <v>1.25</v>
       </c>
       <c r="AK23">
-        <v>1.32</v>
+        <v>1.36</v>
       </c>
       <c r="AL23">
         <v>0</v>
@@ -4221,31 +4221,31 @@
         </is>
       </c>
       <c r="N24">
-        <v>2.31</v>
+        <v>2.82</v>
       </c>
       <c r="O24">
         <v>3</v>
       </c>
       <c r="P24">
-        <v>2.43</v>
+        <v>2.25</v>
       </c>
       <c r="Q24">
-        <v>3.58</v>
+        <v>3.7</v>
       </c>
       <c r="R24">
-        <v>2.07</v>
+        <v>1.95</v>
       </c>
       <c r="S24">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="T24">
-        <v>2.44</v>
+        <v>2.41</v>
       </c>
       <c r="U24">
         <v>3.29</v>
       </c>
       <c r="V24">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="W24">
         <v>1.02</v>
@@ -4254,22 +4254,22 @@
         <v>1.04</v>
       </c>
       <c r="Y24">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="Z24">
         <v>2.7</v>
       </c>
       <c r="AA24">
-        <v>2.21</v>
+        <v>2.23</v>
       </c>
       <c r="AB24">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="AC24">
-        <v>3.84</v>
+        <v>4.04</v>
       </c>
       <c r="AD24">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="AE24">
         <v>1.03</v>
@@ -4291,10 +4291,10 @@
         </is>
       </c>
       <c r="AJ24">
-        <v>1.27</v>
+        <v>1.52</v>
       </c>
       <c r="AK24">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="AL24">
         <v>0</v>
@@ -4713,28 +4713,28 @@
         <v>1.33</v>
       </c>
       <c r="O27">
-        <v>4.95</v>
+        <v>4.8</v>
       </c>
       <c r="P27">
-        <v>7.95</v>
+        <v>6.8</v>
       </c>
       <c r="Q27">
-        <v>1.73</v>
+        <v>1.77</v>
       </c>
       <c r="R27">
-        <v>2.83</v>
+        <v>2.55</v>
       </c>
       <c r="S27">
         <v>1.24</v>
       </c>
       <c r="T27">
-        <v>3.65</v>
+        <v>4</v>
       </c>
       <c r="U27">
-        <v>2.15</v>
+        <v>2.23</v>
       </c>
       <c r="V27">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="W27">
         <v>1.13</v>
@@ -4743,13 +4743,13 @@
         <v>1.02</v>
       </c>
       <c r="Y27">
-        <v>1.12</v>
+        <v>1.18</v>
       </c>
       <c r="Z27">
-        <v>4.7</v>
+        <v>4.75</v>
       </c>
       <c r="AA27">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="AB27">
         <v>2.38</v>
@@ -4761,10 +4761,10 @@
         <v>1.57</v>
       </c>
       <c r="AE27">
-        <v>1.24</v>
+        <v>1.2</v>
       </c>
       <c r="AF27">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="AG27">
         <v>1.92</v>
@@ -4783,7 +4783,7 @@
         <v>1.05</v>
       </c>
       <c r="AK27">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="AL27">
         <v>0</v>
@@ -4876,13 +4876,13 @@
         <v>1.72</v>
       </c>
       <c r="O28">
-        <v>3.88</v>
+        <v>3.75</v>
       </c>
       <c r="P28">
-        <v>4.15</v>
+        <v>3.8</v>
       </c>
       <c r="Q28">
-        <v>2.18</v>
+        <v>2.1</v>
       </c>
       <c r="R28">
         <v>2.38</v>
@@ -4891,10 +4891,10 @@
         <v>1.3</v>
       </c>
       <c r="T28">
-        <v>3.22</v>
+        <v>3.6</v>
       </c>
       <c r="U28">
-        <v>2.46</v>
+        <v>2.45</v>
       </c>
       <c r="V28">
         <v>1.55</v>
@@ -4909,28 +4909,28 @@
         <v>1.2</v>
       </c>
       <c r="Z28">
-        <v>4.53</v>
+        <v>4.15</v>
       </c>
       <c r="AA28">
-        <v>1.66</v>
+        <v>1.63</v>
       </c>
       <c r="AB28">
-        <v>2.15</v>
+        <v>2.23</v>
       </c>
       <c r="AC28">
-        <v>2.62</v>
+        <v>2.63</v>
       </c>
       <c r="AD28">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="AE28">
-        <v>1.2</v>
+        <v>1.14</v>
       </c>
       <c r="AF28">
         <v>1.57</v>
       </c>
       <c r="AG28">
-        <v>2.18</v>
+        <v>2.23</v>
       </c>
       <c r="AH28" t="inlineStr">
         <is>
@@ -4946,7 +4946,7 @@
         <v>1.23</v>
       </c>
       <c r="AK28">
-        <v>2.07</v>
+        <v>2.12</v>
       </c>
       <c r="AL28">
         <v>0</v>
@@ -5075,10 +5075,10 @@
         <v>3.55</v>
       </c>
       <c r="AA29">
-        <v>2.01</v>
+        <v>1.9</v>
       </c>
       <c r="AB29">
-        <v>1.77</v>
+        <v>1.87</v>
       </c>
       <c r="AC29">
         <v>2.95</v>
@@ -5106,10 +5106,10 @@
         </is>
       </c>
       <c r="AJ29">
-        <v>1.73</v>
+        <v>1.91</v>
       </c>
       <c r="AK29">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AL29">
         <v>0</v>
@@ -5238,10 +5238,10 @@
         <v>0</v>
       </c>
       <c r="AA30">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB30">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC30">
         <v>0</v>
@@ -5362,7 +5362,7 @@
         </is>
       </c>
       <c r="N31">
-        <v>1.99</v>
+        <v>2.04</v>
       </c>
       <c r="O31">
         <v>3.4</v>
@@ -5371,7 +5371,7 @@
         <v>3.15</v>
       </c>
       <c r="Q31">
-        <v>2.62</v>
+        <v>2.6</v>
       </c>
       <c r="R31">
         <v>2.19</v>
@@ -5383,40 +5383,40 @@
         <v>3.12</v>
       </c>
       <c r="U31">
-        <v>2.59</v>
+        <v>2.5</v>
       </c>
       <c r="V31">
-        <v>1.47</v>
+        <v>1.49</v>
       </c>
       <c r="W31">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="X31">
         <v>1.03</v>
       </c>
       <c r="Y31">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="Z31">
-        <v>3.97</v>
+        <v>3.86</v>
       </c>
       <c r="AA31">
-        <v>1.72</v>
+        <v>1.74</v>
       </c>
       <c r="AB31">
         <v>2</v>
       </c>
       <c r="AC31">
-        <v>2.82</v>
+        <v>2.74</v>
       </c>
       <c r="AD31">
-        <v>1.4</v>
+        <v>1.35</v>
       </c>
       <c r="AE31">
         <v>1.09</v>
       </c>
       <c r="AF31">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="AG31">
         <v>2.2</v>
@@ -5432,10 +5432,10 @@
         </is>
       </c>
       <c r="AJ31">
-        <v>1.33</v>
+        <v>1.22</v>
       </c>
       <c r="AK31">
-        <v>1.67</v>
+        <v>1.63</v>
       </c>
       <c r="AL31">
         <v>0</v>
@@ -5525,7 +5525,7 @@
         </is>
       </c>
       <c r="N32">
-        <v>1.55</v>
+        <v>1.6</v>
       </c>
       <c r="O32">
         <v>3.7</v>
@@ -5534,7 +5534,7 @@
         <v>4.7</v>
       </c>
       <c r="Q32">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="R32">
         <v>2.2</v>
@@ -5546,19 +5546,19 @@
         <v>2.9</v>
       </c>
       <c r="U32">
-        <v>2.75</v>
+        <v>2.55</v>
       </c>
       <c r="V32">
-        <v>1.4</v>
+        <v>1.43</v>
       </c>
       <c r="W32">
-        <v>1.05</v>
+        <v>1.09</v>
       </c>
       <c r="X32">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y32">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="Z32">
         <v>3.42</v>
@@ -5570,13 +5570,13 @@
         <v>1.94</v>
       </c>
       <c r="AC32">
-        <v>3.2</v>
+        <v>2.97</v>
       </c>
       <c r="AD32">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AE32">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="AF32">
         <v>1.87</v>
@@ -5688,49 +5688,49 @@
         </is>
       </c>
       <c r="N33">
+        <v>2.7</v>
+      </c>
+      <c r="O33">
         <v>2.6</v>
       </c>
-      <c r="O33">
-        <v>2.7</v>
-      </c>
       <c r="P33">
-        <v>2.95</v>
+        <v>2.8</v>
       </c>
       <c r="Q33">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="R33">
-        <v>1.73</v>
+        <v>1.85</v>
       </c>
       <c r="S33">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="T33">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="U33">
-        <v>4.33</v>
+        <v>3.82</v>
       </c>
       <c r="V33">
         <v>1.18</v>
       </c>
       <c r="W33">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="X33">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="Y33">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
       <c r="Z33">
-        <v>2.16</v>
+        <v>2.15</v>
       </c>
       <c r="AA33">
         <v>2.78</v>
       </c>
       <c r="AB33">
-        <v>1.34</v>
+        <v>1.38</v>
       </c>
       <c r="AC33">
         <v>6.25</v>
@@ -5742,10 +5742,10 @@
         <v>1.03</v>
       </c>
       <c r="AF33">
-        <v>2.23</v>
+        <v>2.25</v>
       </c>
       <c r="AG33">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="AH33" t="inlineStr">
         <is>
@@ -5758,10 +5758,10 @@
         </is>
       </c>
       <c r="AJ33">
-        <v>1.38</v>
+        <v>1.31</v>
       </c>
       <c r="AK33">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="AL33">
         <v>0</v>
@@ -5860,16 +5860,16 @@
         <v>0</v>
       </c>
       <c r="Q34">
-        <v>2.7</v>
+        <v>3.18</v>
       </c>
       <c r="R34">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="S34">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="T34">
-        <v>2.7</v>
+        <v>2.53</v>
       </c>
       <c r="U34">
         <v>3.1</v>
@@ -5881,22 +5881,22 @@
         <v>1.02</v>
       </c>
       <c r="X34">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y34">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="Z34">
-        <v>2.98</v>
+        <v>2.81</v>
       </c>
       <c r="AA34">
         <v>2.19</v>
       </c>
       <c r="AB34">
-        <v>1.7</v>
+        <v>1.66</v>
       </c>
       <c r="AC34">
-        <v>3.74</v>
+        <v>3.94</v>
       </c>
       <c r="AD34">
         <v>1.19</v>
@@ -5908,7 +5908,7 @@
         <v>1.84</v>
       </c>
       <c r="AG34">
-        <v>1.86</v>
+        <v>1.84</v>
       </c>
       <c r="AH34" t="inlineStr">
         <is>
@@ -5921,10 +5921,10 @@
         </is>
       </c>
       <c r="AJ34">
-        <v>1.32</v>
+        <v>1.4</v>
       </c>
       <c r="AK34">
-        <v>1.56</v>
+        <v>1.52</v>
       </c>
       <c r="AL34">
         <v>0</v>
@@ -6014,37 +6014,37 @@
         </is>
       </c>
       <c r="N35">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="O35">
-        <v>3.88</v>
+        <v>3.7</v>
       </c>
       <c r="P35">
         <v>4.03</v>
       </c>
       <c r="Q35">
-        <v>2.29</v>
+        <v>2.2</v>
       </c>
       <c r="R35">
         <v>2.3</v>
       </c>
       <c r="S35">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="T35">
-        <v>3.35</v>
+        <v>3.6</v>
       </c>
       <c r="U35">
-        <v>2.38</v>
+        <v>2.45</v>
       </c>
       <c r="V35">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="W35">
-        <v>1.12</v>
+        <v>1.1</v>
       </c>
       <c r="X35">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y35">
         <v>1.14</v>
@@ -6056,22 +6056,22 @@
         <v>1.59</v>
       </c>
       <c r="AB35">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="AC35">
         <v>2.38</v>
       </c>
       <c r="AD35">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="AE35">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="AF35">
         <v>1.56</v>
       </c>
       <c r="AG35">
-        <v>2.2</v>
+        <v>2.28</v>
       </c>
       <c r="AH35" t="inlineStr">
         <is>
@@ -6087,7 +6087,7 @@
         <v>1.17</v>
       </c>
       <c r="AK35">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="AL35">
         <v>0</v>
@@ -6829,19 +6829,19 @@
         </is>
       </c>
       <c r="N40">
-        <v>2.18</v>
+        <v>2.17</v>
       </c>
       <c r="O40">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="P40">
-        <v>2.83</v>
+        <v>3.15</v>
       </c>
       <c r="Q40">
         <v>2.75</v>
       </c>
       <c r="R40">
-        <v>2.3</v>
+        <v>2.12</v>
       </c>
       <c r="S40">
         <v>1.35</v>
@@ -6850,7 +6850,7 @@
         <v>2.94</v>
       </c>
       <c r="U40">
-        <v>2.49</v>
+        <v>2.75</v>
       </c>
       <c r="V40">
         <v>1.45</v>
@@ -6859,34 +6859,34 @@
         <v>1.06</v>
       </c>
       <c r="X40">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="Y40">
-        <v>1.24</v>
+        <v>1.21</v>
       </c>
       <c r="Z40">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="AA40">
-        <v>1.77</v>
+        <v>1.79</v>
       </c>
       <c r="AB40">
-        <v>1.99</v>
+        <v>1.97</v>
       </c>
       <c r="AC40">
         <v>2.95</v>
       </c>
       <c r="AD40">
-        <v>1.37</v>
+        <v>1.34</v>
       </c>
       <c r="AE40">
-        <v>1.15</v>
+        <v>1.11</v>
       </c>
       <c r="AF40">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="AG40">
-        <v>2.14</v>
+        <v>2.2</v>
       </c>
       <c r="AH40" t="inlineStr">
         <is>
@@ -6899,10 +6899,10 @@
         </is>
       </c>
       <c r="AJ40">
-        <v>1.3</v>
+        <v>1.24</v>
       </c>
       <c r="AK40">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="AL40">
         <v>0</v>
@@ -7001,22 +7001,22 @@
         <v>2.37</v>
       </c>
       <c r="Q41">
-        <v>4.2</v>
+        <v>3.75</v>
       </c>
       <c r="R41">
-        <v>2.1</v>
+        <v>2.04</v>
       </c>
       <c r="S41">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="T41">
         <v>2.45</v>
       </c>
       <c r="U41">
-        <v>2.85</v>
+        <v>3</v>
       </c>
       <c r="V41">
-        <v>1.37</v>
+        <v>1.33</v>
       </c>
       <c r="W41">
         <v>1.06</v>
@@ -7025,16 +7025,16 @@
         <v>1.02</v>
       </c>
       <c r="Y41">
-        <v>1.3</v>
+        <v>1.37</v>
       </c>
       <c r="Z41">
-        <v>3.2</v>
+        <v>2.8</v>
       </c>
       <c r="AA41">
         <v>2.15</v>
       </c>
       <c r="AB41">
-        <v>1.77</v>
+        <v>1.73</v>
       </c>
       <c r="AC41">
         <v>3.3</v>
@@ -7062,10 +7062,10 @@
         </is>
       </c>
       <c r="AJ41">
-        <v>1.73</v>
+        <v>1.45</v>
       </c>
       <c r="AK41">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AL41">
         <v>0</v>
@@ -7155,28 +7155,28 @@
         </is>
       </c>
       <c r="N42">
-        <v>2.14</v>
+        <v>2.1</v>
       </c>
       <c r="O42">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="P42">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="Q42">
-        <v>2.6</v>
+        <v>2.47</v>
       </c>
       <c r="R42">
-        <v>2.13</v>
+        <v>2.18</v>
       </c>
       <c r="S42">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="T42">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="U42">
-        <v>2.5</v>
+        <v>2.55</v>
       </c>
       <c r="V42">
         <v>1.5</v>
@@ -7185,7 +7185,7 @@
         <v>1.06</v>
       </c>
       <c r="X42">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y42">
         <v>1.17</v>
@@ -7194,13 +7194,13 @@
         <v>3.8</v>
       </c>
       <c r="AA42">
-        <v>1.69</v>
+        <v>1.66</v>
       </c>
       <c r="AB42">
         <v>2.04</v>
       </c>
       <c r="AC42">
-        <v>2.75</v>
+        <v>2.63</v>
       </c>
       <c r="AD42">
         <v>1.37</v>
@@ -7644,25 +7644,25 @@
         </is>
       </c>
       <c r="N45">
-        <v>1.46</v>
+        <v>1.53</v>
       </c>
       <c r="O45">
-        <v>4.15</v>
+        <v>4</v>
       </c>
       <c r="P45">
-        <v>5.75</v>
+        <v>4.6</v>
       </c>
       <c r="Q45">
         <v>2.02</v>
       </c>
       <c r="R45">
-        <v>2.5</v>
+        <v>2.36</v>
       </c>
       <c r="S45">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="T45">
-        <v>3.2</v>
+        <v>3.5</v>
       </c>
       <c r="U45">
         <v>2.25</v>
@@ -7680,22 +7680,22 @@
         <v>1.14</v>
       </c>
       <c r="Z45">
-        <v>4.45</v>
+        <v>4.4</v>
       </c>
       <c r="AA45">
         <v>1.55</v>
       </c>
       <c r="AB45">
-        <v>2.35</v>
+        <v>2.45</v>
       </c>
       <c r="AC45">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="AD45">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="AE45">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AF45">
         <v>1.56</v>
@@ -7714,7 +7714,7 @@
         </is>
       </c>
       <c r="AJ45">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="AK45">
         <v>2.31</v>
@@ -7810,61 +7810,61 @@
         <v>1.37</v>
       </c>
       <c r="O46">
-        <v>4.5</v>
+        <v>4.2</v>
       </c>
       <c r="P46">
-        <v>6.5</v>
+        <v>5</v>
       </c>
       <c r="Q46">
-        <v>1.84</v>
+        <v>1.93</v>
       </c>
       <c r="R46">
-        <v>2.38</v>
+        <v>2.6</v>
       </c>
       <c r="S46">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="T46">
-        <v>3.32</v>
+        <v>3.42</v>
       </c>
       <c r="U46">
-        <v>2.27</v>
+        <v>2.2</v>
       </c>
       <c r="V46">
-        <v>1.53</v>
+        <v>1.59</v>
       </c>
       <c r="W46">
-        <v>1.1</v>
+        <v>1.17</v>
       </c>
       <c r="X46">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y46">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="Z46">
-        <v>4.7</v>
+        <v>5.05</v>
       </c>
       <c r="AA46">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="AB46">
-        <v>2.34</v>
+        <v>2.48</v>
       </c>
       <c r="AC46">
-        <v>2.34</v>
+        <v>2.25</v>
       </c>
       <c r="AD46">
-        <v>1.53</v>
+        <v>1.6</v>
       </c>
       <c r="AE46">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="AF46">
-        <v>1.67</v>
+        <v>1.57</v>
       </c>
       <c r="AG46">
-        <v>1.93</v>
+        <v>2.19</v>
       </c>
       <c r="AH46" t="inlineStr">
         <is>
@@ -7877,10 +7877,10 @@
         </is>
       </c>
       <c r="AJ46">
-        <v>1.13</v>
+        <v>1.08</v>
       </c>
       <c r="AK46">
-        <v>3</v>
+        <v>2.4</v>
       </c>
       <c r="AL46">
         <v>0</v>
@@ -8459,19 +8459,19 @@
         </is>
       </c>
       <c r="N50">
-        <v>1.91</v>
+        <v>1.85</v>
       </c>
       <c r="O50">
-        <v>3.5</v>
+        <v>3.65</v>
       </c>
       <c r="P50">
         <v>3.4</v>
       </c>
       <c r="Q50">
-        <v>2.41</v>
+        <v>2.38</v>
       </c>
       <c r="R50">
-        <v>2.23</v>
+        <v>2.22</v>
       </c>
       <c r="S50">
         <v>1.32</v>
@@ -8486,10 +8486,10 @@
         <v>1.5</v>
       </c>
       <c r="W50">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="X50">
-        <v>1</v>
+        <v>1.04</v>
       </c>
       <c r="Y50">
         <v>1.22</v>
@@ -8529,10 +8529,10 @@
         </is>
       </c>
       <c r="AJ50">
-        <v>1.26</v>
+        <v>1.29</v>
       </c>
       <c r="AK50">
-        <v>1.86</v>
+        <v>1.92</v>
       </c>
       <c r="AL50">
         <v>0</v>
@@ -8658,7 +8658,7 @@
         <v>1.36</v>
       </c>
       <c r="Z51">
-        <v>3.1</v>
+        <v>2.95</v>
       </c>
       <c r="AA51">
         <v>2.06</v>
@@ -8676,7 +8676,7 @@
         <v>1.04</v>
       </c>
       <c r="AF51">
-        <v>1.94</v>
+        <v>2</v>
       </c>
       <c r="AG51">
         <v>1.73</v>
@@ -8692,7 +8692,7 @@
         </is>
       </c>
       <c r="AJ51">
-        <v>1.32</v>
+        <v>1.25</v>
       </c>
       <c r="AK51">
         <v>1.19</v>
@@ -8948,34 +8948,34 @@
         </is>
       </c>
       <c r="N53">
-        <v>2</v>
+        <v>2.01</v>
       </c>
       <c r="O53">
-        <v>3.75</v>
+        <v>3.95</v>
       </c>
       <c r="P53">
-        <v>2.8</v>
+        <v>3.05</v>
       </c>
       <c r="Q53">
+        <v>2.54</v>
+      </c>
+      <c r="R53">
         <v>2.5</v>
-      </c>
-      <c r="R53">
-        <v>2.39</v>
       </c>
       <c r="S53">
         <v>1.24</v>
       </c>
       <c r="T53">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="U53">
-        <v>2.31</v>
+        <v>2.2</v>
       </c>
       <c r="V53">
-        <v>1.59</v>
+        <v>1.62</v>
       </c>
       <c r="W53">
-        <v>1.13</v>
+        <v>1.17</v>
       </c>
       <c r="X53">
         <v>1.02</v>
@@ -8984,19 +8984,19 @@
         <v>1.13</v>
       </c>
       <c r="Z53">
-        <v>4.55</v>
+        <v>4.25</v>
       </c>
       <c r="AA53">
-        <v>1.5</v>
+        <v>1.56</v>
       </c>
       <c r="AB53">
-        <v>2.41</v>
+        <v>2.28</v>
       </c>
       <c r="AC53">
-        <v>2.38</v>
+        <v>2.27</v>
       </c>
       <c r="AD53">
-        <v>1.56</v>
+        <v>1.54</v>
       </c>
       <c r="AE53">
         <v>1.18</v>
@@ -9005,7 +9005,7 @@
         <v>1.48</v>
       </c>
       <c r="AG53">
-        <v>2.45</v>
+        <v>2.47</v>
       </c>
       <c r="AH53" t="inlineStr">
         <is>
@@ -9018,10 +9018,10 @@
         </is>
       </c>
       <c r="AJ53">
-        <v>1.32</v>
+        <v>1.24</v>
       </c>
       <c r="AK53">
-        <v>1.77</v>
+        <v>1.75</v>
       </c>
       <c r="AL53">
         <v>0</v>
@@ -9111,13 +9111,13 @@
         </is>
       </c>
       <c r="N54">
-        <v>3.59</v>
+        <v>3.5</v>
       </c>
       <c r="O54">
-        <v>3.62</v>
+        <v>3.55</v>
       </c>
       <c r="P54">
-        <v>1.93</v>
+        <v>1.85</v>
       </c>
       <c r="Q54">
         <v>3.85</v>
@@ -9126,10 +9126,10 @@
         <v>2.38</v>
       </c>
       <c r="S54">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="T54">
-        <v>3.15</v>
+        <v>3.23</v>
       </c>
       <c r="U54">
         <v>2.47</v>
@@ -9144,31 +9144,31 @@
         <v>1.04</v>
       </c>
       <c r="Y54">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="Z54">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="AA54">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="AB54">
         <v>2.1</v>
       </c>
       <c r="AC54">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="AD54">
-        <v>1.37</v>
+        <v>1.44</v>
       </c>
       <c r="AE54">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="AF54">
         <v>1.6</v>
       </c>
       <c r="AG54">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="AH54" t="inlineStr">
         <is>
@@ -9437,31 +9437,31 @@
         </is>
       </c>
       <c r="N56">
-        <v>2.5</v>
+        <v>2.41</v>
       </c>
       <c r="O56">
-        <v>3.35</v>
+        <v>3.5</v>
       </c>
       <c r="P56">
-        <v>2.5</v>
+        <v>2.39</v>
       </c>
       <c r="Q56">
-        <v>3.06</v>
+        <v>3.04</v>
       </c>
       <c r="R56">
-        <v>2.18</v>
+        <v>2.3</v>
       </c>
       <c r="S56">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="T56">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="U56">
-        <v>2.33</v>
+        <v>2.31</v>
       </c>
       <c r="V56">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="W56">
         <v>1.11</v>
@@ -9470,31 +9470,31 @@
         <v>1.02</v>
       </c>
       <c r="Y56">
-        <v>1.14</v>
+        <v>1.18</v>
       </c>
       <c r="Z56">
         <v>4.33</v>
       </c>
       <c r="AA56">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="AB56">
         <v>2.3</v>
       </c>
       <c r="AC56">
-        <v>2.55</v>
+        <v>2.6</v>
       </c>
       <c r="AD56">
+        <v>1.44</v>
+      </c>
+      <c r="AE56">
+        <v>1.19</v>
+      </c>
+      <c r="AF56">
         <v>1.49</v>
       </c>
-      <c r="AE56">
-        <v>1.13</v>
-      </c>
-      <c r="AF56">
-        <v>1.5</v>
-      </c>
       <c r="AG56">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="AH56" t="inlineStr">
         <is>
@@ -9507,7 +9507,7 @@
         </is>
       </c>
       <c r="AJ56">
-        <v>1.43</v>
+        <v>1.25</v>
       </c>
       <c r="AK56">
         <v>1.47</v>
@@ -10252,10 +10252,10 @@
         </is>
       </c>
       <c r="N61">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="O61">
-        <v>8</v>
+        <v>7.5</v>
       </c>
       <c r="P61">
         <v>12</v>
@@ -10267,16 +10267,16 @@
         <v>2.85</v>
       </c>
       <c r="S61">
-        <v>1.14</v>
+        <v>1.21</v>
       </c>
       <c r="T61">
-        <v>5</v>
+        <v>3.58</v>
       </c>
       <c r="U61">
-        <v>1.8</v>
+        <v>1.92</v>
       </c>
       <c r="V61">
-        <v>1.91</v>
+        <v>1.77</v>
       </c>
       <c r="W61">
         <v>1.25</v>
@@ -10291,19 +10291,19 @@
         <v>5.3</v>
       </c>
       <c r="AA61">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="AB61">
-        <v>2.75</v>
+        <v>3.5</v>
       </c>
       <c r="AC61">
         <v>1.94</v>
       </c>
       <c r="AD61">
-        <v>1.7</v>
+        <v>1.92</v>
       </c>
       <c r="AE61">
-        <v>1.29</v>
+        <v>1.39</v>
       </c>
       <c r="AF61">
         <v>2.01</v>
@@ -10322,10 +10322,10 @@
         </is>
       </c>
       <c r="AJ61">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="AK61">
-        <v>4.95</v>
+        <v>4</v>
       </c>
       <c r="AL61">
         <v>0</v>
@@ -10418,22 +10418,22 @@
         <v>2.62</v>
       </c>
       <c r="O62">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="P62">
         <v>2.45</v>
       </c>
       <c r="Q62">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="R62">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="S62">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="T62">
-        <v>2.85</v>
+        <v>2.56</v>
       </c>
       <c r="U62">
         <v>2.88</v>
@@ -10442,31 +10442,31 @@
         <v>1.36</v>
       </c>
       <c r="W62">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="X62">
         <v>1.02</v>
       </c>
       <c r="Y62">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="Z62">
         <v>2.99</v>
       </c>
       <c r="AA62">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="AB62">
         <v>1.76</v>
       </c>
       <c r="AC62">
-        <v>3.55</v>
+        <v>3.38</v>
       </c>
       <c r="AD62">
-        <v>1.28</v>
+        <v>1.24</v>
       </c>
       <c r="AE62">
-        <v>1.1</v>
+        <v>1.06</v>
       </c>
       <c r="AF62">
         <v>1.75</v>
@@ -10485,7 +10485,7 @@
         </is>
       </c>
       <c r="AJ62">
-        <v>1.45</v>
+        <v>1.29</v>
       </c>
       <c r="AK62">
         <v>1.45</v>
@@ -10578,22 +10578,22 @@
         </is>
       </c>
       <c r="N63">
-        <v>2.31</v>
+        <v>2.3</v>
       </c>
       <c r="O63">
         <v>3.2</v>
       </c>
       <c r="P63">
-        <v>2.88</v>
+        <v>2.85</v>
       </c>
       <c r="Q63">
-        <v>2.95</v>
+        <v>2.9</v>
       </c>
       <c r="R63">
         <v>2.13</v>
       </c>
       <c r="S63">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="T63">
         <v>2.89</v>
@@ -10605,37 +10605,37 @@
         <v>1.4</v>
       </c>
       <c r="W63">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="X63">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="Y63">
         <v>1.25</v>
       </c>
       <c r="Z63">
-        <v>3.81</v>
+        <v>3.44</v>
       </c>
       <c r="AA63">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="AB63">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="AC63">
-        <v>3.05</v>
+        <v>3.14</v>
       </c>
       <c r="AD63">
         <v>1.33</v>
       </c>
       <c r="AE63">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="AF63">
         <v>1.67</v>
       </c>
       <c r="AG63">
-        <v>2.15</v>
+        <v>2.13</v>
       </c>
       <c r="AH63" t="inlineStr">
         <is>
@@ -10648,10 +10648,10 @@
         </is>
       </c>
       <c r="AJ63">
-        <v>1.3</v>
+        <v>1.34</v>
       </c>
       <c r="AK63">
-        <v>1.56</v>
+        <v>1.53</v>
       </c>
       <c r="AL63">
         <v>0</v>
@@ -10741,25 +10741,25 @@
         </is>
       </c>
       <c r="N64">
-        <v>1.34</v>
+        <v>1.31</v>
       </c>
       <c r="O64">
-        <v>5.1</v>
+        <v>5.55</v>
       </c>
       <c r="P64">
-        <v>5.35</v>
+        <v>5.8</v>
       </c>
       <c r="Q64">
-        <v>1.74</v>
+        <v>1.67</v>
       </c>
       <c r="R64">
-        <v>2.6</v>
+        <v>2.88</v>
       </c>
       <c r="S64">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="T64">
-        <v>4.45</v>
+        <v>4.75</v>
       </c>
       <c r="U64">
         <v>1.85</v>
@@ -10777,19 +10777,19 @@
         <v>1.05</v>
       </c>
       <c r="Z64">
-        <v>8</v>
+        <v>6.5</v>
       </c>
       <c r="AA64">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="AB64">
-        <v>3.14</v>
+        <v>3.25</v>
       </c>
       <c r="AC64">
         <v>1.77</v>
       </c>
       <c r="AD64">
-        <v>1.9</v>
+        <v>1.95</v>
       </c>
       <c r="AE64">
         <v>1.39</v>
@@ -10910,10 +10910,10 @@
         <v>3.75</v>
       </c>
       <c r="P65">
-        <v>2.84</v>
+        <v>3.35</v>
       </c>
       <c r="Q65">
-        <v>2.42</v>
+        <v>2.28</v>
       </c>
       <c r="R65">
         <v>2.5</v>
@@ -10922,16 +10922,16 @@
         <v>1.25</v>
       </c>
       <c r="T65">
-        <v>3.6</v>
+        <v>3.44</v>
       </c>
       <c r="U65">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="V65">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="W65">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="X65">
         <v>1.01</v>
@@ -10940,10 +10940,10 @@
         <v>1.12</v>
       </c>
       <c r="Z65">
-        <v>4.65</v>
+        <v>5.25</v>
       </c>
       <c r="AA65">
-        <v>1.45</v>
+        <v>1.48</v>
       </c>
       <c r="AB65">
         <v>2.45</v>
@@ -10955,13 +10955,13 @@
         <v>1.59</v>
       </c>
       <c r="AE65">
-        <v>1.2</v>
+        <v>1.23</v>
       </c>
       <c r="AF65">
-        <v>1.47</v>
+        <v>1.43</v>
       </c>
       <c r="AG65">
-        <v>2.55</v>
+        <v>2.5</v>
       </c>
       <c r="AH65" t="inlineStr">
         <is>
@@ -10974,10 +10974,10 @@
         </is>
       </c>
       <c r="AJ65">
-        <v>1.28</v>
+        <v>1.21</v>
       </c>
       <c r="AK65">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="AL65">
         <v>0</v>
@@ -11067,34 +11067,34 @@
         </is>
       </c>
       <c r="N66">
+        <v>2.21</v>
+      </c>
+      <c r="O66">
+        <v>3.73</v>
+      </c>
+      <c r="P66">
+        <v>2.18</v>
+      </c>
+      <c r="Q66">
+        <v>2.8</v>
+      </c>
+      <c r="R66">
         <v>2.45</v>
       </c>
-      <c r="O66">
-        <v>3.85</v>
-      </c>
-      <c r="P66">
-        <v>2.3</v>
-      </c>
-      <c r="Q66">
-        <v>3</v>
-      </c>
-      <c r="R66">
-        <v>2.6</v>
-      </c>
       <c r="S66">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="T66">
-        <v>3.95</v>
+        <v>4.5</v>
       </c>
       <c r="U66">
-        <v>1.92</v>
+        <v>1.9</v>
       </c>
       <c r="V66">
         <v>1.78</v>
       </c>
       <c r="W66">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="X66">
         <v>1.01</v>
@@ -11106,22 +11106,22 @@
         <v>6.59</v>
       </c>
       <c r="AA66">
-        <v>1.36</v>
+        <v>1.32</v>
       </c>
       <c r="AB66">
-        <v>2.88</v>
+        <v>2.75</v>
       </c>
       <c r="AC66">
-        <v>1.86</v>
+        <v>1.94</v>
       </c>
       <c r="AD66">
-        <v>1.93</v>
+        <v>1.84</v>
       </c>
       <c r="AE66">
-        <v>1.34</v>
+        <v>1.3</v>
       </c>
       <c r="AF66">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="AG66">
         <v>3.08</v>
@@ -11230,16 +11230,16 @@
         </is>
       </c>
       <c r="N67">
-        <v>2.17</v>
+        <v>2.15</v>
       </c>
       <c r="O67">
-        <v>3.75</v>
+        <v>3.6</v>
       </c>
       <c r="P67">
-        <v>2.3</v>
+        <v>2.75</v>
       </c>
       <c r="Q67">
-        <v>2.66</v>
+        <v>2.55</v>
       </c>
       <c r="R67">
         <v>2.38</v>
@@ -11257,13 +11257,13 @@
         <v>1.67</v>
       </c>
       <c r="W67">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="X67">
         <v>1.02</v>
       </c>
       <c r="Y67">
-        <v>1.11</v>
+        <v>1.09</v>
       </c>
       <c r="Z67">
         <v>5.75</v>
@@ -11272,10 +11272,10 @@
         <v>1.46</v>
       </c>
       <c r="AB67">
-        <v>2.64</v>
+        <v>2.52</v>
       </c>
       <c r="AC67">
-        <v>2.07</v>
+        <v>2.12</v>
       </c>
       <c r="AD67">
         <v>1.68</v>
@@ -11284,7 +11284,7 @@
         <v>1.24</v>
       </c>
       <c r="AF67">
-        <v>1.36</v>
+        <v>1.39</v>
       </c>
       <c r="AG67">
         <v>2.75</v>
@@ -11396,16 +11396,16 @@
         <v>1.39</v>
       </c>
       <c r="O68">
-        <v>4.75</v>
+        <v>4.55</v>
       </c>
       <c r="P68">
         <v>4.85</v>
       </c>
       <c r="Q68">
-        <v>1.79</v>
+        <v>1.77</v>
       </c>
       <c r="R68">
-        <v>2.75</v>
+        <v>2.8</v>
       </c>
       <c r="S68">
         <v>1.18</v>
@@ -11420,7 +11420,7 @@
         <v>1.83</v>
       </c>
       <c r="W68">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="X68">
         <v>1.01</v>
@@ -11429,7 +11429,7 @@
         <v>1.1</v>
       </c>
       <c r="Z68">
-        <v>6.6</v>
+        <v>5.6</v>
       </c>
       <c r="AA68">
         <v>1.36</v>
@@ -11441,13 +11441,13 @@
         <v>1.88</v>
       </c>
       <c r="AD68">
-        <v>1.91</v>
+        <v>1.87</v>
       </c>
       <c r="AE68">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AF68">
-        <v>1.49</v>
+        <v>1.47</v>
       </c>
       <c r="AG68">
         <v>2.44</v>
@@ -11463,7 +11463,7 @@
         </is>
       </c>
       <c r="AJ68">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="AK68">
         <v>2.7</v>
@@ -11556,31 +11556,31 @@
         </is>
       </c>
       <c r="N69">
-        <v>3.97</v>
+        <v>4.6</v>
       </c>
       <c r="O69">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="P69">
-        <v>1.45</v>
+        <v>1.54</v>
       </c>
       <c r="Q69">
         <v>4.78</v>
       </c>
       <c r="R69">
-        <v>2.53</v>
+        <v>2.79</v>
       </c>
       <c r="S69">
         <v>1.17</v>
       </c>
       <c r="T69">
-        <v>4.2</v>
+        <v>4.15</v>
       </c>
       <c r="U69">
-        <v>1.94</v>
+        <v>1.92</v>
       </c>
       <c r="V69">
-        <v>1.79</v>
+        <v>1.76</v>
       </c>
       <c r="W69">
         <v>1.18</v>
@@ -11595,7 +11595,7 @@
         <v>6.47</v>
       </c>
       <c r="AA69">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="AB69">
         <v>2.92</v>
@@ -11607,13 +11607,13 @@
         <v>1.71</v>
       </c>
       <c r="AE69">
-        <v>1.36</v>
+        <v>1.31</v>
       </c>
       <c r="AF69">
         <v>1.4</v>
       </c>
       <c r="AG69">
-        <v>2.73</v>
+        <v>2.55</v>
       </c>
       <c r="AH69" t="inlineStr">
         <is>
@@ -11626,10 +11626,10 @@
         </is>
       </c>
       <c r="AJ69">
-        <v>1.15</v>
+        <v>1.18</v>
       </c>
       <c r="AK69">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="AL69">
         <v>0</v>
@@ -11719,49 +11719,49 @@
         </is>
       </c>
       <c r="N70">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="O70">
-        <v>3.42</v>
+        <v>3.51</v>
       </c>
       <c r="P70">
-        <v>6.33</v>
+        <v>6.83</v>
       </c>
       <c r="Q70">
-        <v>2.17</v>
+        <v>2.1</v>
       </c>
       <c r="R70">
-        <v>2.07</v>
+        <v>2.1</v>
       </c>
       <c r="S70">
-        <v>1.45</v>
+        <v>1.42</v>
       </c>
       <c r="T70">
-        <v>2.55</v>
+        <v>2.65</v>
       </c>
       <c r="U70">
-        <v>2.35</v>
+        <v>2.75</v>
       </c>
       <c r="V70">
-        <v>1.45</v>
+        <v>1.35</v>
       </c>
       <c r="W70">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="X70">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y70">
         <v>1.33</v>
       </c>
       <c r="Z70">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="AA70">
-        <v>2.11</v>
+        <v>1.9</v>
       </c>
       <c r="AB70">
-        <v>1.7</v>
+        <v>1.87</v>
       </c>
       <c r="AC70">
         <v>3.5</v>
@@ -11770,13 +11770,13 @@
         <v>1.24</v>
       </c>
       <c r="AE70">
-        <v>1.04</v>
+        <v>1.15</v>
       </c>
       <c r="AF70">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="AG70">
-        <v>1.67</v>
+        <v>1.64</v>
       </c>
       <c r="AH70" t="inlineStr">
         <is>
@@ -11789,10 +11789,10 @@
         </is>
       </c>
       <c r="AJ70">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="AK70">
-        <v>2.19</v>
+        <v>2.3</v>
       </c>
       <c r="AL70">
         <v>0</v>
@@ -12051,10 +12051,10 @@
         <v>3.4</v>
       </c>
       <c r="P72">
-        <v>2.47</v>
+        <v>2.55</v>
       </c>
       <c r="Q72">
-        <v>3.02</v>
+        <v>3</v>
       </c>
       <c r="R72">
         <v>2.25</v>
@@ -12063,13 +12063,13 @@
         <v>1.3</v>
       </c>
       <c r="T72">
-        <v>2.92</v>
+        <v>3.2</v>
       </c>
       <c r="U72">
-        <v>2.5</v>
+        <v>2.54</v>
       </c>
       <c r="V72">
-        <v>1.43</v>
+        <v>1.49</v>
       </c>
       <c r="W72">
         <v>1.07</v>
@@ -12084,10 +12084,10 @@
         <v>3.8</v>
       </c>
       <c r="AA72">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="AB72">
-        <v>2.07</v>
+        <v>2</v>
       </c>
       <c r="AC72">
         <v>2.7</v>
@@ -12371,64 +12371,64 @@
         </is>
       </c>
       <c r="N74">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="O74">
-        <v>2.95</v>
+        <v>2.99</v>
       </c>
       <c r="P74">
         <v>3.25</v>
       </c>
       <c r="Q74">
-        <v>2.8</v>
+        <v>2.9</v>
       </c>
       <c r="R74">
         <v>1.83</v>
       </c>
       <c r="S74">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="T74">
         <v>2.5</v>
       </c>
       <c r="U74">
-        <v>3.42</v>
+        <v>3.48</v>
       </c>
       <c r="V74">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="W74">
         <v>1.02</v>
       </c>
       <c r="X74">
-        <v>1.11</v>
+        <v>1.06</v>
       </c>
       <c r="Y74">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="Z74">
         <v>2.44</v>
       </c>
       <c r="AA74">
-        <v>2.43</v>
+        <v>2.59</v>
       </c>
       <c r="AB74">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="AC74">
         <v>5.25</v>
       </c>
       <c r="AD74">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="AE74">
         <v>1.04</v>
       </c>
       <c r="AF74">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="AG74">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="AH74" t="inlineStr">
         <is>
@@ -12441,7 +12441,7 @@
         </is>
       </c>
       <c r="AJ74">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="AK74">
         <v>1.56</v>
@@ -12537,16 +12537,16 @@
         <v>2.3</v>
       </c>
       <c r="O75">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="P75">
         <v>2.7</v>
       </c>
       <c r="Q75">
-        <v>2.88</v>
+        <v>2.76</v>
       </c>
       <c r="R75">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="S75">
         <v>1.3</v>
@@ -12555,7 +12555,7 @@
         <v>2.99</v>
       </c>
       <c r="U75">
-        <v>2.76</v>
+        <v>2.55</v>
       </c>
       <c r="V75">
         <v>1.44</v>
@@ -12564,34 +12564,34 @@
         <v>1.1</v>
       </c>
       <c r="X75">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="Y75">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="Z75">
-        <v>3.7</v>
+        <v>3.58</v>
       </c>
       <c r="AA75">
-        <v>1.83</v>
+        <v>1.86</v>
       </c>
       <c r="AB75">
         <v>1.95</v>
       </c>
       <c r="AC75">
-        <v>3.18</v>
+        <v>3.25</v>
       </c>
       <c r="AD75">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AE75">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="AF75">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="AG75">
-        <v>2.15</v>
+        <v>2.18</v>
       </c>
       <c r="AH75" t="inlineStr">
         <is>
@@ -12697,34 +12697,34 @@
         </is>
       </c>
       <c r="N76">
-        <v>2.7</v>
+        <v>2.75</v>
       </c>
       <c r="O76">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="P76">
-        <v>2.43</v>
+        <v>2.45</v>
       </c>
       <c r="Q76">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="R76">
-        <v>2.04</v>
+        <v>2.1</v>
       </c>
       <c r="S76">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="T76">
-        <v>2.9</v>
+        <v>2.95</v>
       </c>
       <c r="U76">
-        <v>2.8</v>
+        <v>2.95</v>
       </c>
       <c r="V76">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="W76">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="X76">
         <v>1.03</v>
@@ -12733,28 +12733,28 @@
         <v>1.27</v>
       </c>
       <c r="Z76">
-        <v>3.14</v>
+        <v>3.35</v>
       </c>
       <c r="AA76">
         <v>2</v>
       </c>
       <c r="AB76">
-        <v>1.83</v>
+        <v>1.76</v>
       </c>
       <c r="AC76">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="AD76">
-        <v>1.3</v>
+        <v>1.23</v>
       </c>
       <c r="AE76">
-        <v>1.11</v>
+        <v>1.06</v>
       </c>
       <c r="AF76">
         <v>1.75</v>
       </c>
       <c r="AG76">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="AH76" t="inlineStr">
         <is>
@@ -12767,10 +12767,10 @@
         </is>
       </c>
       <c r="AJ76">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
       <c r="AK76">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="AL76">
         <v>0</v>
@@ -12860,13 +12860,13 @@
         </is>
       </c>
       <c r="N77">
-        <v>2.26</v>
+        <v>2.15</v>
       </c>
       <c r="O77">
-        <v>3.35</v>
+        <v>3.43</v>
       </c>
       <c r="P77">
-        <v>2.73</v>
+        <v>3</v>
       </c>
       <c r="Q77">
         <v>2.81</v>
@@ -12890,22 +12890,22 @@
         <v>1.11</v>
       </c>
       <c r="X77">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y77">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="Z77">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="AA77">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="AB77">
         <v>2</v>
       </c>
       <c r="AC77">
-        <v>2.85</v>
+        <v>3</v>
       </c>
       <c r="AD77">
         <v>1.33</v>
@@ -12914,10 +12914,10 @@
         <v>1.08</v>
       </c>
       <c r="AF77">
-        <v>1.6</v>
+        <v>1.63</v>
       </c>
       <c r="AG77">
-        <v>2.15</v>
+        <v>2.14</v>
       </c>
       <c r="AH77" t="inlineStr">
         <is>
@@ -12930,10 +12930,10 @@
         </is>
       </c>
       <c r="AJ77">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="AK77">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="AL77">
         <v>0</v>
@@ -13032,25 +13032,25 @@
         <v>3.24</v>
       </c>
       <c r="Q78">
-        <v>3.08</v>
+        <v>2.8</v>
       </c>
       <c r="R78">
         <v>2.05</v>
       </c>
       <c r="S78">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="T78">
-        <v>2.39</v>
+        <v>2.75</v>
       </c>
       <c r="U78">
         <v>2.95</v>
       </c>
       <c r="V78">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="W78">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X78">
         <v>1.04</v>
@@ -13062,13 +13062,13 @@
         <v>2.75</v>
       </c>
       <c r="AA78">
-        <v>2.29</v>
+        <v>2.25</v>
       </c>
       <c r="AB78">
-        <v>1.59</v>
+        <v>1.61</v>
       </c>
       <c r="AC78">
-        <v>4.38</v>
+        <v>4.2</v>
       </c>
       <c r="AD78">
         <v>1.16</v>
@@ -13077,10 +13077,10 @@
         <v>1.02</v>
       </c>
       <c r="AF78">
-        <v>1.93</v>
+        <v>1.9</v>
       </c>
       <c r="AG78">
-        <v>1.78</v>
+        <v>1.76</v>
       </c>
       <c r="AH78" t="inlineStr">
         <is>
@@ -13093,7 +13093,7 @@
         </is>
       </c>
       <c r="AJ78">
-        <v>1.28</v>
+        <v>1.34</v>
       </c>
       <c r="AK78">
         <v>1.58</v>
@@ -13225,10 +13225,10 @@
         <v>2.92</v>
       </c>
       <c r="AA79">
-        <v>2.04</v>
+        <v>2.1</v>
       </c>
       <c r="AB79">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="AC79">
         <v>3.58</v>
@@ -13521,22 +13521,22 @@
         <v>1.83</v>
       </c>
       <c r="Q81">
-        <v>4.2</v>
+        <v>4.25</v>
       </c>
       <c r="R81">
-        <v>2.2</v>
+        <v>2.26</v>
       </c>
       <c r="S81">
         <v>1.33</v>
       </c>
       <c r="T81">
-        <v>2.88</v>
+        <v>2.98</v>
       </c>
       <c r="U81">
         <v>2.63</v>
       </c>
       <c r="V81">
-        <v>1.44</v>
+        <v>1.38</v>
       </c>
       <c r="W81">
         <v>1.09</v>
@@ -13548,13 +13548,13 @@
         <v>1.25</v>
       </c>
       <c r="Z81">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="AA81">
         <v>1.86</v>
       </c>
       <c r="AB81">
-        <v>1.89</v>
+        <v>1.81</v>
       </c>
       <c r="AC81">
         <v>2.97</v>
@@ -13566,7 +13566,7 @@
         <v>1.07</v>
       </c>
       <c r="AF81">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="AG81">
         <v>2</v>
@@ -13585,7 +13585,7 @@
         <v>1.22</v>
       </c>
       <c r="AK81">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="AL81">
         <v>0</v>
@@ -13847,10 +13847,10 @@
         <v>2</v>
       </c>
       <c r="Q83">
-        <v>3.3</v>
+        <v>3.81</v>
       </c>
       <c r="R83">
-        <v>2.35</v>
+        <v>2.22</v>
       </c>
       <c r="S83">
         <v>1.28</v>
@@ -13859,7 +13859,7 @@
         <v>3.18</v>
       </c>
       <c r="U83">
-        <v>2.38</v>
+        <v>2.43</v>
       </c>
       <c r="V83">
         <v>1.51</v>
@@ -13886,13 +13886,13 @@
         <v>2.55</v>
       </c>
       <c r="AD83">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="AE83">
-        <v>1.18</v>
+        <v>1.15</v>
       </c>
       <c r="AF83">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="AG83">
         <v>2.32</v>
@@ -13908,10 +13908,10 @@
         </is>
       </c>
       <c r="AJ83">
-        <v>1.25</v>
+        <v>1.73</v>
       </c>
       <c r="AK83">
-        <v>1.27</v>
+        <v>1.35</v>
       </c>
       <c r="AL83">
         <v>0</v>
@@ -14001,13 +14001,13 @@
         </is>
       </c>
       <c r="N84">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="O84">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="P84">
-        <v>5.1</v>
+        <v>5.25</v>
       </c>
       <c r="Q84">
         <v>1.83</v>
@@ -14022,13 +14022,13 @@
         <v>3.28</v>
       </c>
       <c r="U84">
-        <v>2.26</v>
+        <v>2.25</v>
       </c>
       <c r="V84">
         <v>1.56</v>
       </c>
       <c r="W84">
-        <v>1.14</v>
+        <v>1.11</v>
       </c>
       <c r="X84">
         <v>1.03</v>
@@ -14037,19 +14037,19 @@
         <v>1.14</v>
       </c>
       <c r="Z84">
-        <v>4.45</v>
+        <v>4.6</v>
       </c>
       <c r="AA84">
-        <v>1.49</v>
+        <v>1.57</v>
       </c>
       <c r="AB84">
-        <v>2.35</v>
+        <v>2.38</v>
       </c>
       <c r="AC84">
         <v>2.4</v>
       </c>
       <c r="AD84">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="AE84">
         <v>1.19</v>
@@ -14058,7 +14058,7 @@
         <v>1.65</v>
       </c>
       <c r="AG84">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="AH84" t="inlineStr">
         <is>
@@ -14071,10 +14071,10 @@
         </is>
       </c>
       <c r="AJ84">
-        <v>1.08</v>
+        <v>1.14</v>
       </c>
       <c r="AK84">
-        <v>2.41</v>
+        <v>2.62</v>
       </c>
       <c r="AL84">
         <v>0</v>
@@ -14132,12 +14132,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Tallinna FC Flora</t>
+          <t>Vaprus</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Harju Jalgpallikool</t>
+          <t>Tallinna FC Levadia</t>
         </is>
       </c>
       <c r="G85">
@@ -14164,64 +14164,64 @@
         </is>
       </c>
       <c r="N85">
-        <v>1.33</v>
+        <v>11.7</v>
       </c>
       <c r="O85">
-        <v>4.55</v>
+        <v>5.75</v>
       </c>
       <c r="P85">
-        <v>6.5</v>
+        <v>1.22</v>
       </c>
       <c r="Q85">
-        <v>1.78</v>
+        <v>8.91</v>
       </c>
       <c r="R85">
-        <v>2.56</v>
+        <v>3.02</v>
       </c>
       <c r="S85">
         <v>1.2</v>
       </c>
       <c r="T85">
-        <v>3.72</v>
+        <v>3.9</v>
       </c>
       <c r="U85">
-        <v>2.02</v>
+        <v>2.05</v>
       </c>
       <c r="V85">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="W85">
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
       <c r="X85">
         <v>1.01</v>
       </c>
       <c r="Y85">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="Z85">
-        <v>5.75</v>
+        <v>5.25</v>
       </c>
       <c r="AA85">
-        <v>1.44</v>
+        <v>1.41</v>
       </c>
       <c r="AB85">
-        <v>2.74</v>
+        <v>2.52</v>
       </c>
       <c r="AC85">
-        <v>2.01</v>
+        <v>2.11</v>
       </c>
       <c r="AD85">
-        <v>1.78</v>
+        <v>1.65</v>
       </c>
       <c r="AE85">
-        <v>1.28</v>
+        <v>1.24</v>
       </c>
       <c r="AF85">
-        <v>1.58</v>
+        <v>1.85</v>
       </c>
       <c r="AG85">
-        <v>2.21</v>
+        <v>1.85</v>
       </c>
       <c r="AH85" t="inlineStr">
         <is>
@@ -14234,10 +14234,10 @@
         </is>
       </c>
       <c r="AJ85">
-        <v>1.11</v>
+        <v>3.66</v>
       </c>
       <c r="AK85">
-        <v>3.2</v>
+        <v>1.05</v>
       </c>
       <c r="AL85">
         <v>0</v>
@@ -14295,12 +14295,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Vaprus</t>
+          <t>Tallinna FC Flora</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Tallinna FC Levadia</t>
+          <t>Harju Jalgpallikool</t>
         </is>
       </c>
       <c r="G86">
@@ -14327,64 +14327,64 @@
         </is>
       </c>
       <c r="N86">
-        <v>11.7</v>
+        <v>1.48</v>
       </c>
       <c r="O86">
-        <v>6</v>
+        <v>4.2</v>
       </c>
       <c r="P86">
-        <v>1.18</v>
+        <v>5.25</v>
       </c>
       <c r="Q86">
-        <v>9.25</v>
+        <v>1.83</v>
       </c>
       <c r="R86">
-        <v>2.77</v>
+        <v>2.8</v>
       </c>
       <c r="S86">
-        <v>1.19</v>
+        <v>1.21</v>
       </c>
       <c r="T86">
-        <v>3.74</v>
+        <v>3.58</v>
       </c>
       <c r="U86">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="V86">
-        <v>1.73</v>
+        <v>1.69</v>
       </c>
       <c r="W86">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="X86">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y86">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="Z86">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="AA86">
-        <v>1.36</v>
+        <v>1.44</v>
       </c>
       <c r="AB86">
-        <v>2.75</v>
+        <v>2.7</v>
       </c>
       <c r="AC86">
-        <v>1.99</v>
+        <v>2.11</v>
       </c>
       <c r="AD86">
         <v>1.73</v>
       </c>
       <c r="AE86">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="AF86">
-        <v>1.89</v>
+        <v>1.5</v>
       </c>
       <c r="AG86">
-        <v>1.8</v>
+        <v>2.3</v>
       </c>
       <c r="AH86" t="inlineStr">
         <is>
@@ -14397,10 +14397,10 @@
         </is>
       </c>
       <c r="AJ86">
-        <v>1.06</v>
+        <v>1.14</v>
       </c>
       <c r="AK86">
-        <v>1.04</v>
+        <v>2.63</v>
       </c>
       <c r="AL86">
         <v>0</v>
@@ -14490,25 +14490,25 @@
         </is>
       </c>
       <c r="N87">
-        <v>3.8</v>
+        <v>4.3</v>
       </c>
       <c r="O87">
-        <v>3.8</v>
+        <v>3.95</v>
       </c>
       <c r="P87">
-        <v>1.65</v>
+        <v>1.68</v>
       </c>
       <c r="Q87">
-        <v>4.6</v>
+        <v>4.4</v>
       </c>
       <c r="R87">
-        <v>2.48</v>
+        <v>2.4</v>
       </c>
       <c r="S87">
         <v>1.26</v>
       </c>
       <c r="T87">
-        <v>3.45</v>
+        <v>3.34</v>
       </c>
       <c r="U87">
         <v>2.31</v>
@@ -14517,19 +14517,19 @@
         <v>1.57</v>
       </c>
       <c r="W87">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="X87">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y87">
-        <v>1.18</v>
+        <v>1.15</v>
       </c>
       <c r="Z87">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="AA87">
-        <v>1.57</v>
+        <v>1.65</v>
       </c>
       <c r="AB87">
         <v>2.4</v>
@@ -14538,16 +14538,16 @@
         <v>2.42</v>
       </c>
       <c r="AD87">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="AE87">
-        <v>1.21</v>
+        <v>1.18</v>
       </c>
       <c r="AF87">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="AG87">
-        <v>2.28</v>
+        <v>2.1</v>
       </c>
       <c r="AH87" t="inlineStr">
         <is>
@@ -14560,10 +14560,10 @@
         </is>
       </c>
       <c r="AJ87">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="AK87">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="AL87">
         <v>0</v>
@@ -14653,34 +14653,34 @@
         </is>
       </c>
       <c r="N88">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="O88">
-        <v>4.3</v>
+        <v>4.8</v>
       </c>
       <c r="P88">
-        <v>6.8</v>
+        <v>7.75</v>
       </c>
       <c r="Q88">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="R88">
-        <v>2.32</v>
+        <v>2.29</v>
       </c>
       <c r="S88">
         <v>1.3</v>
       </c>
       <c r="T88">
-        <v>2.95</v>
+        <v>3.2</v>
       </c>
       <c r="U88">
-        <v>2.66</v>
+        <v>2.54</v>
       </c>
       <c r="V88">
         <v>1.41</v>
       </c>
       <c r="W88">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="X88">
         <v>1</v>
@@ -14692,13 +14692,13 @@
         <v>3.5</v>
       </c>
       <c r="AA88">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="AB88">
         <v>1.93</v>
       </c>
       <c r="AC88">
-        <v>3.06</v>
+        <v>3.1</v>
       </c>
       <c r="AD88">
         <v>1.3</v>
@@ -14707,10 +14707,10 @@
         <v>1.07</v>
       </c>
       <c r="AF88">
-        <v>2.15</v>
+        <v>2.18</v>
       </c>
       <c r="AG88">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="AH88" t="inlineStr">
         <is>
@@ -14726,7 +14726,7 @@
         <v>1.05</v>
       </c>
       <c r="AK88">
-        <v>2.91</v>
+        <v>3.12</v>
       </c>
       <c r="AL88">
         <v>0</v>
@@ -14979,64 +14979,64 @@
         </is>
       </c>
       <c r="N90">
-        <v>2.11</v>
+        <v>2.16</v>
       </c>
       <c r="O90">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="P90">
-        <v>2.85</v>
+        <v>2.7</v>
       </c>
       <c r="Q90">
         <v>2.7</v>
       </c>
       <c r="R90">
-        <v>2.19</v>
+        <v>2.22</v>
       </c>
       <c r="S90">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="T90">
-        <v>3.18</v>
+        <v>3.25</v>
       </c>
       <c r="U90">
-        <v>2.38</v>
+        <v>2.25</v>
       </c>
       <c r="V90">
-        <v>1.48</v>
+        <v>1.44</v>
       </c>
       <c r="W90">
-        <v>1.09</v>
+        <v>1.12</v>
       </c>
       <c r="X90">
         <v>1.01</v>
       </c>
       <c r="Y90">
-        <v>1.15</v>
+        <v>1.13</v>
       </c>
       <c r="Z90">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="AA90">
-        <v>1.7</v>
+        <v>1.56</v>
       </c>
       <c r="AB90">
-        <v>2.1</v>
+        <v>2.31</v>
       </c>
       <c r="AC90">
-        <v>2.49</v>
+        <v>2.38</v>
       </c>
       <c r="AD90">
-        <v>1.42</v>
+        <v>1.46</v>
       </c>
       <c r="AE90">
-        <v>1.13</v>
+        <v>1.2</v>
       </c>
       <c r="AF90">
-        <v>1.51</v>
+        <v>1.48</v>
       </c>
       <c r="AG90">
-        <v>2.36</v>
+        <v>2.4</v>
       </c>
       <c r="AH90" t="inlineStr">
         <is>
@@ -15049,10 +15049,10 @@
         </is>
       </c>
       <c r="AJ90">
-        <v>1.22</v>
+        <v>1.36</v>
       </c>
       <c r="AK90">
-        <v>1.58</v>
+        <v>1.68</v>
       </c>
       <c r="AL90">
         <v>0</v>
@@ -15468,13 +15468,13 @@
         </is>
       </c>
       <c r="N93">
-        <v>4</v>
+        <v>3.4</v>
       </c>
       <c r="O93">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="P93">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="Q93">
         <v>3.75</v>
@@ -15483,7 +15483,7 @@
         <v>2.1</v>
       </c>
       <c r="S93">
-        <v>1.42</v>
+        <v>1.36</v>
       </c>
       <c r="T93">
         <v>2.9</v>
@@ -15495,7 +15495,7 @@
         <v>1.42</v>
       </c>
       <c r="W93">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="X93">
         <v>1.01</v>
@@ -15504,13 +15504,13 @@
         <v>1.22</v>
       </c>
       <c r="Z93">
-        <v>3.74</v>
+        <v>3.5</v>
       </c>
       <c r="AA93">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="AB93">
-        <v>1.87</v>
+        <v>1.8</v>
       </c>
       <c r="AC93">
         <v>3.3</v>
@@ -15538,10 +15538,10 @@
         </is>
       </c>
       <c r="AJ93">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="AK93">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="AL93">
         <v>0</v>
@@ -15800,28 +15800,28 @@
         <v>3.35</v>
       </c>
       <c r="P95">
-        <v>3.73</v>
+        <v>4.3</v>
       </c>
       <c r="Q95">
         <v>2.4</v>
       </c>
       <c r="R95">
-        <v>2.15</v>
+        <v>2.11</v>
       </c>
       <c r="S95">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="T95">
-        <v>2.75</v>
+        <v>2.9</v>
       </c>
       <c r="U95">
-        <v>2.88</v>
+        <v>2.7</v>
       </c>
       <c r="V95">
         <v>1.37</v>
       </c>
       <c r="W95">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="X95">
         <v>1.01</v>
@@ -15842,10 +15842,10 @@
         <v>3.5</v>
       </c>
       <c r="AD95">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AE95">
-        <v>1.09</v>
+        <v>1.05</v>
       </c>
       <c r="AF95">
         <v>1.84</v>
@@ -16455,22 +16455,22 @@
         <v>2.5</v>
       </c>
       <c r="Q99">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="R99">
-        <v>2.32</v>
+        <v>2.11</v>
       </c>
       <c r="S99">
         <v>1.33</v>
       </c>
       <c r="T99">
-        <v>2.9</v>
+        <v>3.09</v>
       </c>
       <c r="U99">
-        <v>2.44</v>
+        <v>2.45</v>
       </c>
       <c r="V99">
-        <v>1.46</v>
+        <v>1.5</v>
       </c>
       <c r="W99">
         <v>1.1</v>
@@ -16479,31 +16479,31 @@
         <v>1</v>
       </c>
       <c r="Y99">
-        <v>1.21</v>
+        <v>1.19</v>
       </c>
       <c r="Z99">
-        <v>3.76</v>
+        <v>3.78</v>
       </c>
       <c r="AA99">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="AB99">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="AC99">
-        <v>2.8</v>
+        <v>2.59</v>
       </c>
       <c r="AD99">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="AE99">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="AF99">
         <v>1.57</v>
       </c>
       <c r="AG99">
-        <v>2.27</v>
+        <v>2.21</v>
       </c>
       <c r="AH99" t="inlineStr">
         <is>
@@ -16516,10 +16516,10 @@
         </is>
       </c>
       <c r="AJ99">
-        <v>1.42</v>
+        <v>1.36</v>
       </c>
       <c r="AK99">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="AL99">
         <v>0</v>
@@ -16657,10 +16657,10 @@
         <v>3.1</v>
       </c>
       <c r="AD100">
-        <v>1.32</v>
+        <v>1.34</v>
       </c>
       <c r="AE100">
-        <v>1.08</v>
+        <v>1.12</v>
       </c>
       <c r="AF100">
         <v>1.74</v>
@@ -16944,25 +16944,25 @@
         <v>2.59</v>
       </c>
       <c r="Q102">
-        <v>3.9</v>
+        <v>4.1</v>
       </c>
       <c r="R102">
         <v>2</v>
       </c>
       <c r="S102">
+        <v>1.42</v>
+      </c>
+      <c r="T102">
+        <v>2.62</v>
+      </c>
+      <c r="U102">
+        <v>2.85</v>
+      </c>
+      <c r="V102">
         <v>1.36</v>
       </c>
-      <c r="T102">
-        <v>2.88</v>
-      </c>
-      <c r="U102">
-        <v>2.91</v>
-      </c>
-      <c r="V102">
-        <v>1.33</v>
-      </c>
       <c r="W102">
-        <v>1.02</v>
+        <v>1.07</v>
       </c>
       <c r="X102">
         <v>1.01</v>
@@ -16983,7 +16983,7 @@
         <v>3.5</v>
       </c>
       <c r="AD102">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AE102">
         <v>1.04</v>
@@ -17005,10 +17005,10 @@
         </is>
       </c>
       <c r="AJ102">
-        <v>1.64</v>
+        <v>1.26</v>
       </c>
       <c r="AK102">
-        <v>1.24</v>
+        <v>1.3</v>
       </c>
       <c r="AL102">
         <v>0</v>
@@ -17107,25 +17107,25 @@
         <v>4.2</v>
       </c>
       <c r="Q103">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="R103">
         <v>2.3</v>
       </c>
       <c r="S103">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="T103">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="U103">
-        <v>2.44</v>
+        <v>2.54</v>
       </c>
       <c r="V103">
         <v>1.46</v>
       </c>
       <c r="W103">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="X103">
         <v>1.04</v>
@@ -17143,10 +17143,10 @@
         <v>2.09</v>
       </c>
       <c r="AC103">
-        <v>2.8</v>
+        <v>2.62</v>
       </c>
       <c r="AD103">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="AE103">
         <v>1.11</v>
@@ -17155,7 +17155,7 @@
         <v>1.68</v>
       </c>
       <c r="AG103">
-        <v>2.01</v>
+        <v>2</v>
       </c>
       <c r="AH103" t="inlineStr">
         <is>
@@ -17171,7 +17171,7 @@
         <v>1.16</v>
       </c>
       <c r="AK103">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="AL103">
         <v>0</v>
@@ -17913,28 +17913,28 @@
         </is>
       </c>
       <c r="N108">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="O108">
-        <v>3.15</v>
+        <v>3.32</v>
       </c>
       <c r="P108">
-        <v>2.7</v>
+        <v>2.81</v>
       </c>
       <c r="Q108">
-        <v>3.03</v>
+        <v>2.81</v>
       </c>
       <c r="R108">
-        <v>2.08</v>
+        <v>2.04</v>
       </c>
       <c r="S108">
         <v>1.36</v>
       </c>
       <c r="T108">
-        <v>2.84</v>
+        <v>2.85</v>
       </c>
       <c r="U108">
-        <v>2.69</v>
+        <v>2.85</v>
       </c>
       <c r="V108">
         <v>1.4</v>
@@ -17943,19 +17943,19 @@
         <v>1.05</v>
       </c>
       <c r="X108">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y108">
         <v>1.28</v>
       </c>
       <c r="Z108">
-        <v>3.49</v>
+        <v>3.5</v>
       </c>
       <c r="AA108">
-        <v>1.88</v>
+        <v>1.86</v>
       </c>
       <c r="AB108">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="AC108">
         <v>3.4</v>
@@ -17986,7 +17986,7 @@
         <v>1.39</v>
       </c>
       <c r="AK108">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="AL108">
         <v>0</v>
@@ -18079,25 +18079,25 @@
         <v>1.29</v>
       </c>
       <c r="O109">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="P109">
-        <v>7.5</v>
+        <v>8.4</v>
       </c>
       <c r="Q109">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="R109">
-        <v>2.59</v>
+        <v>2.63</v>
       </c>
       <c r="S109">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="T109">
         <v>3.02</v>
       </c>
       <c r="U109">
-        <v>2.32</v>
+        <v>2.63</v>
       </c>
       <c r="V109">
         <v>1.46</v>
@@ -18106,7 +18106,7 @@
         <v>1.09</v>
       </c>
       <c r="X109">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y109">
         <v>1.21</v>
@@ -18121,19 +18121,19 @@
         <v>2.04</v>
       </c>
       <c r="AC109">
-        <v>2.84</v>
+        <v>2.7</v>
       </c>
       <c r="AD109">
-        <v>1.39</v>
+        <v>1.43</v>
       </c>
       <c r="AE109">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="AF109">
-        <v>1.98</v>
+        <v>2.12</v>
       </c>
       <c r="AG109">
-        <v>1.7</v>
+        <v>1.62</v>
       </c>
       <c r="AH109" t="inlineStr">
         <is>
@@ -18146,10 +18146,10 @@
         </is>
       </c>
       <c r="AJ109">
-        <v>1.17</v>
+        <v>1.1</v>
       </c>
       <c r="AK109">
-        <v>3.4</v>
+        <v>3.18</v>
       </c>
       <c r="AL109">
         <v>0</v>
@@ -18239,13 +18239,13 @@
         </is>
       </c>
       <c r="N110">
-        <v>2</v>
+        <v>1.91</v>
       </c>
       <c r="O110">
         <v>3.25</v>
       </c>
       <c r="P110">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="Q110">
         <v>0</v>
@@ -18408,7 +18408,7 @@
         <v>3.08</v>
       </c>
       <c r="P111">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="Q111">
         <v>0</v>
@@ -18568,10 +18568,10 @@
         <v>1.76</v>
       </c>
       <c r="O112">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="P112">
-        <v>4.5</v>
+        <v>4.3</v>
       </c>
       <c r="Q112">
         <v>0</v>
@@ -18894,61 +18894,61 @@
         <v>1.63</v>
       </c>
       <c r="O114">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="P114">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="Q114">
-        <v>2.14</v>
+        <v>2.15</v>
       </c>
       <c r="R114">
-        <v>2.42</v>
+        <v>2.28</v>
       </c>
       <c r="S114">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="T114">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="U114">
         <v>2.5</v>
       </c>
       <c r="V114">
-        <v>1.45</v>
+        <v>1.5</v>
       </c>
       <c r="W114">
+        <v>1.12</v>
+      </c>
+      <c r="X114">
+        <v>1.04</v>
+      </c>
+      <c r="Y114">
+        <v>1.22</v>
+      </c>
+      <c r="Z114">
+        <v>4.06</v>
+      </c>
+      <c r="AA114">
+        <v>1.72</v>
+      </c>
+      <c r="AB114">
+        <v>2.09</v>
+      </c>
+      <c r="AC114">
+        <v>2.69</v>
+      </c>
+      <c r="AD114">
+        <v>1.4</v>
+      </c>
+      <c r="AE114">
         <v>1.1</v>
       </c>
-      <c r="X114">
-        <v>1.01</v>
-      </c>
-      <c r="Y114">
-        <v>1.21</v>
-      </c>
-      <c r="Z114">
-        <v>4.12</v>
-      </c>
-      <c r="AA114">
+      <c r="AF114">
         <v>1.7</v>
       </c>
-      <c r="AB114">
-        <v>2.11</v>
-      </c>
-      <c r="AC114">
-        <v>2.66</v>
-      </c>
-      <c r="AD114">
-        <v>1.42</v>
-      </c>
-      <c r="AE114">
-        <v>1.11</v>
-      </c>
-      <c r="AF114">
-        <v>1.67</v>
-      </c>
       <c r="AG114">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="AH114" t="inlineStr">
         <is>
@@ -18961,10 +18961,10 @@
         </is>
       </c>
       <c r="AJ114">
-        <v>1.11</v>
+        <v>1.18</v>
       </c>
       <c r="AK114">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="AL114">
         <v>0</v>
@@ -19054,19 +19054,19 @@
         </is>
       </c>
       <c r="N115">
+        <v>3.85</v>
+      </c>
+      <c r="O115">
         <v>3.4</v>
       </c>
-      <c r="O115">
-        <v>3.55</v>
-      </c>
       <c r="P115">
-        <v>1.75</v>
+        <v>1.89</v>
       </c>
       <c r="Q115">
-        <v>4.65</v>
+        <v>4.49</v>
       </c>
       <c r="R115">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="S115">
         <v>1.35</v>
@@ -19075,13 +19075,13 @@
         <v>2.95</v>
       </c>
       <c r="U115">
-        <v>2.55</v>
+        <v>2.63</v>
       </c>
       <c r="V115">
-        <v>1.45</v>
+        <v>1.48</v>
       </c>
       <c r="W115">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="X115">
         <v>1.02</v>
@@ -19090,10 +19090,10 @@
         <v>1.22</v>
       </c>
       <c r="Z115">
-        <v>3.5</v>
+        <v>3.69</v>
       </c>
       <c r="AA115">
-        <v>1.79</v>
+        <v>1.83</v>
       </c>
       <c r="AB115">
         <v>1.89</v>
@@ -19108,7 +19108,7 @@
         <v>1.08</v>
       </c>
       <c r="AF115">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="AG115">
         <v>2</v>
@@ -19124,7 +19124,7 @@
         </is>
       </c>
       <c r="AJ115">
-        <v>1.29</v>
+        <v>1.22</v>
       </c>
       <c r="AK115">
         <v>1.17</v>
@@ -19217,31 +19217,31 @@
         </is>
       </c>
       <c r="N116">
-        <v>1.8</v>
+        <v>1.94</v>
       </c>
       <c r="O116">
-        <v>3.12</v>
+        <v>3.44</v>
       </c>
       <c r="P116">
-        <v>3.28</v>
+        <v>3.74</v>
       </c>
       <c r="Q116">
-        <v>2.54</v>
+        <v>2.47</v>
       </c>
       <c r="R116">
-        <v>2.3</v>
+        <v>2.11</v>
       </c>
       <c r="S116">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="T116">
         <v>2.88</v>
       </c>
       <c r="U116">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="V116">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="W116">
         <v>1.1</v>
@@ -19250,31 +19250,31 @@
         <v>1.01</v>
       </c>
       <c r="Y116">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="Z116">
-        <v>3.75</v>
+        <v>3.76</v>
       </c>
       <c r="AA116">
-        <v>1.87</v>
+        <v>1.83</v>
       </c>
       <c r="AB116">
         <v>1.97</v>
       </c>
       <c r="AC116">
-        <v>3.1</v>
+        <v>2.88</v>
       </c>
       <c r="AD116">
         <v>1.32</v>
       </c>
       <c r="AE116">
-        <v>1.13</v>
+        <v>1.09</v>
       </c>
       <c r="AF116">
         <v>1.69</v>
       </c>
       <c r="AG116">
-        <v>2.02</v>
+        <v>2.05</v>
       </c>
       <c r="AH116" t="inlineStr">
         <is>
@@ -19287,10 +19287,10 @@
         </is>
       </c>
       <c r="AJ116">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="AK116">
-        <v>1.85</v>
+        <v>1.75</v>
       </c>
       <c r="AL116">
         <v>0</v>
@@ -19422,16 +19422,16 @@
         <v>1.6</v>
       </c>
       <c r="AB117">
-        <v>2.25</v>
+        <v>2.14</v>
       </c>
       <c r="AC117">
         <v>2.43</v>
       </c>
       <c r="AD117">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="AE117">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="AF117">
         <v>1.7</v>
@@ -19450,10 +19450,10 @@
         </is>
       </c>
       <c r="AJ117">
-        <v>1.11</v>
+        <v>1.07</v>
       </c>
       <c r="AK117">
-        <v>2.33</v>
+        <v>2.4</v>
       </c>
       <c r="AL117">
         <v>0</v>
@@ -19543,13 +19543,13 @@
         </is>
       </c>
       <c r="N118">
-        <v>1.23</v>
+        <v>1.17</v>
       </c>
       <c r="O118">
-        <v>5.75</v>
+        <v>5.5</v>
       </c>
       <c r="P118">
-        <v>14.3</v>
+        <v>9.5</v>
       </c>
       <c r="Q118">
         <v>1.68</v>
@@ -19582,25 +19582,25 @@
         <v>3.56</v>
       </c>
       <c r="AA118">
-        <v>1.81</v>
+        <v>1.72</v>
       </c>
       <c r="AB118">
-        <v>2.05</v>
+        <v>1.96</v>
       </c>
       <c r="AC118">
-        <v>2.83</v>
+        <v>2.8</v>
       </c>
       <c r="AD118">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AE118">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="AF118">
-        <v>2.45</v>
+        <v>2.49</v>
       </c>
       <c r="AG118">
-        <v>1.44</v>
+        <v>1.48</v>
       </c>
       <c r="AH118" t="inlineStr">
         <is>
@@ -19613,7 +19613,7 @@
         </is>
       </c>
       <c r="AJ118">
-        <v>1.13</v>
+        <v>1.03</v>
       </c>
       <c r="AK118">
         <v>3.68</v>
@@ -20032,49 +20032,49 @@
         </is>
       </c>
       <c r="N121">
-        <v>1.95</v>
+        <v>2.03</v>
       </c>
       <c r="O121">
-        <v>3.24</v>
+        <v>3.1</v>
       </c>
       <c r="P121">
         <v>3.31</v>
       </c>
       <c r="Q121">
-        <v>2.55</v>
+        <v>2.64</v>
       </c>
       <c r="R121">
-        <v>1.99</v>
+        <v>2.15</v>
       </c>
       <c r="S121">
-        <v>1.44</v>
+        <v>1.41</v>
       </c>
       <c r="T121">
-        <v>2.56</v>
+        <v>2.8</v>
       </c>
       <c r="U121">
-        <v>3.07</v>
+        <v>2.88</v>
       </c>
       <c r="V121">
         <v>1.34</v>
       </c>
       <c r="W121">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="X121">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="Y121">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="Z121">
         <v>2.92</v>
       </c>
       <c r="AA121">
-        <v>2.08</v>
+        <v>2</v>
       </c>
       <c r="AB121">
-        <v>1.7</v>
+        <v>1.77</v>
       </c>
       <c r="AC121">
         <v>3.42</v>
@@ -20086,10 +20086,10 @@
         <v>1.05</v>
       </c>
       <c r="AF121">
-        <v>1.87</v>
+        <v>1.83</v>
       </c>
       <c r="AG121">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="AH121" t="inlineStr">
         <is>
@@ -20102,10 +20102,10 @@
         </is>
       </c>
       <c r="AJ121">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AK121">
-        <v>1.84</v>
+        <v>1.77</v>
       </c>
       <c r="AL121">
         <v>0</v>
@@ -20195,64 +20195,64 @@
         </is>
       </c>
       <c r="N122">
-        <v>2.25</v>
+        <v>2.12</v>
       </c>
       <c r="O122">
-        <v>2.95</v>
+        <v>3.1</v>
       </c>
       <c r="P122">
-        <v>2.95</v>
+        <v>3.05</v>
       </c>
       <c r="Q122">
-        <v>2.98</v>
+        <v>2.84</v>
       </c>
       <c r="R122">
-        <v>1.94</v>
+        <v>1.97</v>
       </c>
       <c r="S122">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="T122">
-        <v>2.44</v>
+        <v>2.48</v>
       </c>
       <c r="U122">
-        <v>3.12</v>
+        <v>3.09</v>
       </c>
       <c r="V122">
-        <v>1.29</v>
+        <v>1.35</v>
       </c>
       <c r="W122">
-        <v>1.02</v>
+        <v>1.07</v>
       </c>
       <c r="X122">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y122">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="Z122">
-        <v>2.7</v>
+        <v>2.74</v>
       </c>
       <c r="AA122">
-        <v>2.15</v>
+        <v>2.18</v>
       </c>
       <c r="AB122">
-        <v>1.66</v>
+        <v>1.62</v>
       </c>
       <c r="AC122">
-        <v>3.86</v>
+        <v>4.2</v>
       </c>
       <c r="AD122">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="AE122">
         <v>1.03</v>
       </c>
       <c r="AF122">
-        <v>1.87</v>
+        <v>2</v>
       </c>
       <c r="AG122">
-        <v>1.82</v>
+        <v>1.68</v>
       </c>
       <c r="AH122" t="inlineStr">
         <is>
@@ -20268,7 +20268,7 @@
         <v>1.28</v>
       </c>
       <c r="AK122">
-        <v>1.5</v>
+        <v>1.55</v>
       </c>
       <c r="AL122">
         <v>0</v>
@@ -20652,12 +20652,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Chaco For Ever</t>
+          <t>Deportivo Madryn</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Deportivo Morón</t>
+          <t>All Boys</t>
         </is>
       </c>
       <c r="G125">
@@ -20684,64 +20684,64 @@
         </is>
       </c>
       <c r="N125">
-        <v>2.91</v>
+        <v>1.91</v>
       </c>
       <c r="O125">
+        <v>2.8</v>
+      </c>
+      <c r="P125">
+        <v>4.2</v>
+      </c>
+      <c r="Q125">
         <v>2.7</v>
       </c>
-      <c r="P125">
-        <v>2.44</v>
-      </c>
-      <c r="Q125">
-        <v>4.15</v>
-      </c>
       <c r="R125">
-        <v>1.74</v>
+        <v>1.83</v>
       </c>
       <c r="S125">
-        <v>1.67</v>
+        <v>1.72</v>
       </c>
       <c r="T125">
-        <v>2.07</v>
+        <v>2.25</v>
       </c>
       <c r="U125">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="V125">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="W125">
         <v>1.03</v>
       </c>
       <c r="X125">
-        <v>1.1</v>
+        <v>1.16</v>
       </c>
       <c r="Y125">
-        <v>1.65</v>
+        <v>1.68</v>
       </c>
       <c r="Z125">
-        <v>2.2</v>
+        <v>2.09</v>
       </c>
       <c r="AA125">
         <v>3.4</v>
       </c>
       <c r="AB125">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="AC125">
-        <v>5.9</v>
+        <v>4.9</v>
       </c>
       <c r="AD125">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="AE125">
         <v>1.02</v>
       </c>
       <c r="AF125">
-        <v>2.32</v>
+        <v>2.51</v>
       </c>
       <c r="AG125">
-        <v>1.57</v>
+        <v>1.46</v>
       </c>
       <c r="AH125" t="inlineStr">
         <is>
@@ -20754,10 +20754,10 @@
         </is>
       </c>
       <c r="AJ125">
-        <v>1.4</v>
+        <v>1.35</v>
       </c>
       <c r="AK125">
-        <v>1.36</v>
+        <v>1.8</v>
       </c>
       <c r="AL125">
         <v>0</v>
@@ -20815,12 +20815,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Deportivo Madryn</t>
+          <t>Chaco For Ever</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>All Boys</t>
+          <t>Deportivo Morón</t>
         </is>
       </c>
       <c r="G126">
@@ -20847,64 +20847,64 @@
         </is>
       </c>
       <c r="N126">
-        <v>1.91</v>
+        <v>2.91</v>
       </c>
       <c r="O126">
-        <v>2.8</v>
+        <v>2.7</v>
       </c>
       <c r="P126">
-        <v>4.2</v>
+        <v>2.44</v>
       </c>
       <c r="Q126">
-        <v>2.7</v>
+        <v>4.15</v>
       </c>
       <c r="R126">
-        <v>1.83</v>
+        <v>1.74</v>
       </c>
       <c r="S126">
-        <v>1.72</v>
+        <v>1.67</v>
       </c>
       <c r="T126">
-        <v>2.25</v>
+        <v>2.07</v>
       </c>
       <c r="U126">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="V126">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="W126">
         <v>1.03</v>
       </c>
       <c r="X126">
-        <v>1.16</v>
+        <v>1.1</v>
       </c>
       <c r="Y126">
-        <v>1.68</v>
+        <v>1.65</v>
       </c>
       <c r="Z126">
-        <v>2.09</v>
+        <v>2.2</v>
       </c>
       <c r="AA126">
         <v>3.4</v>
       </c>
       <c r="AB126">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="AC126">
-        <v>4.9</v>
+        <v>5.9</v>
       </c>
       <c r="AD126">
-        <v>1.1</v>
+        <v>1.07</v>
       </c>
       <c r="AE126">
         <v>1.02</v>
       </c>
       <c r="AF126">
-        <v>2.51</v>
+        <v>2.32</v>
       </c>
       <c r="AG126">
-        <v>1.46</v>
+        <v>1.57</v>
       </c>
       <c r="AH126" t="inlineStr">
         <is>
@@ -20917,10 +20917,10 @@
         </is>
       </c>
       <c r="AJ126">
-        <v>1.35</v>
+        <v>1.4</v>
       </c>
       <c r="AK126">
-        <v>1.8</v>
+        <v>1.36</v>
       </c>
       <c r="AL126">
         <v>0</v>
@@ -21351,10 +21351,10 @@
         <v>2.25</v>
       </c>
       <c r="S129">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="T129">
-        <v>2.71</v>
+        <v>2.73</v>
       </c>
       <c r="U129">
         <v>2.45</v>
@@ -21372,13 +21372,13 @@
         <v>1.33</v>
       </c>
       <c r="Z129">
-        <v>3.12</v>
+        <v>3.11</v>
       </c>
       <c r="AA129">
         <v>1.96</v>
       </c>
       <c r="AB129">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="AC129">
         <v>3.34</v>
@@ -21409,7 +21409,7 @@
         <v>1.1</v>
       </c>
       <c r="AK129">
-        <v>1.72</v>
+        <v>1.58</v>
       </c>
       <c r="AL129">
         <v>0</v>
@@ -21499,31 +21499,31 @@
         </is>
       </c>
       <c r="N130">
-        <v>1.55</v>
+        <v>1.49</v>
       </c>
       <c r="O130">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="P130">
-        <v>5.2</v>
+        <v>5.25</v>
       </c>
       <c r="Q130">
-        <v>2.1</v>
+        <v>1.98</v>
       </c>
       <c r="R130">
-        <v>2.15</v>
+        <v>2.07</v>
       </c>
       <c r="S130">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="T130">
-        <v>2.62</v>
+        <v>2.5</v>
       </c>
       <c r="U130">
-        <v>3.08</v>
+        <v>3.25</v>
       </c>
       <c r="V130">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="W130">
         <v>1.04</v>
@@ -21532,19 +21532,19 @@
         <v>1.03</v>
       </c>
       <c r="Y130">
-        <v>1.38</v>
+        <v>1.42</v>
       </c>
       <c r="Z130">
-        <v>2.63</v>
+        <v>2.74</v>
       </c>
       <c r="AA130">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="AB130">
-        <v>1.54</v>
+        <v>1.62</v>
       </c>
       <c r="AC130">
-        <v>3.86</v>
+        <v>3.84</v>
       </c>
       <c r="AD130">
         <v>1.23</v>
@@ -21553,10 +21553,10 @@
         <v>1.03</v>
       </c>
       <c r="AF130">
-        <v>2.17</v>
+        <v>2.19</v>
       </c>
       <c r="AG130">
-        <v>1.65</v>
+        <v>1.59</v>
       </c>
       <c r="AH130" t="inlineStr">
         <is>
@@ -21569,10 +21569,10 @@
         </is>
       </c>
       <c r="AJ130">
-        <v>1.1</v>
+        <v>1.06</v>
       </c>
       <c r="AK130">
-        <v>2.28</v>
+        <v>2.18</v>
       </c>
       <c r="AL130">
         <v>0</v>
@@ -21825,64 +21825,64 @@
         </is>
       </c>
       <c r="N132">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="O132">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="P132">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="Q132">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="R132">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="S132">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="T132">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="U132">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="V132">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="W132">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X132">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y132">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z132">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AA132">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AB132">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AC132">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="AD132">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AE132">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AF132">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AG132">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AH132" t="inlineStr">
         <is>
@@ -21895,10 +21895,10 @@
         </is>
       </c>
       <c r="AJ132">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK132">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AL132">
         <v>0</v>
@@ -22190,10 +22190,10 @@
         <v>0</v>
       </c>
       <c r="AA134">
-        <v>1.65</v>
+        <v>1.8</v>
       </c>
       <c r="AB134">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="AC134">
         <v>0</v>
@@ -22486,16 +22486,16 @@
         <v>0</v>
       </c>
       <c r="Q136">
-        <v>3.55</v>
+        <v>3.71</v>
       </c>
       <c r="R136">
-        <v>2.03</v>
+        <v>1.95</v>
       </c>
       <c r="S136">
-        <v>1.46</v>
+        <v>1.48</v>
       </c>
       <c r="T136">
-        <v>2.44</v>
+        <v>2.63</v>
       </c>
       <c r="U136">
         <v>3</v>
@@ -22504,10 +22504,10 @@
         <v>1.27</v>
       </c>
       <c r="W136">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="X136">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="Y136">
         <v>1.49</v>
@@ -22528,13 +22528,13 @@
         <v>1.17</v>
       </c>
       <c r="AE136">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="AF136">
-        <v>2.08</v>
+        <v>1.91</v>
       </c>
       <c r="AG136">
-        <v>1.73</v>
+        <v>1.64</v>
       </c>
       <c r="AH136" t="inlineStr">
         <is>

--- a/jogos_2026-08-02.xlsx
+++ b/jogos_2026-08-02.xlsx
@@ -340,7 +340,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AU138"/>
+  <dimension ref="A1:AU137"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -638,7 +638,7 @@
         <v>1.3</v>
       </c>
       <c r="O2">
-        <v>5.45</v>
+        <v>4.75</v>
       </c>
       <c r="P2">
         <v>7.95</v>
@@ -689,7 +689,7 @@
         <v>1.2</v>
       </c>
       <c r="AF2">
-        <v>1.82</v>
+        <v>1.73</v>
       </c>
       <c r="AG2">
         <v>1.87</v>
@@ -751,7 +751,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>01:00</t>
+          <t>01:30</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -766,12 +766,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Sydney Olympic</t>
+          <t>Sydney United</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>APIA Leichhardt Tigers</t>
+          <t>NWS Spirit</t>
         </is>
       </c>
       <c r="G3">
@@ -798,64 +798,64 @@
         </is>
       </c>
       <c r="N3">
-        <v>6</v>
+        <v>1.86</v>
       </c>
       <c r="O3">
-        <v>4.95</v>
+        <v>3.13</v>
       </c>
       <c r="P3">
-        <v>1.33</v>
+        <v>3.52</v>
       </c>
       <c r="Q3">
-        <v>5.1</v>
+        <v>2.45</v>
       </c>
       <c r="R3">
-        <v>2.55</v>
+        <v>2.1</v>
       </c>
       <c r="S3">
-        <v>1.21</v>
+        <v>1.36</v>
       </c>
       <c r="T3">
-        <v>3.58</v>
+        <v>2.75</v>
       </c>
       <c r="U3">
-        <v>2.1</v>
+        <v>2.73</v>
       </c>
       <c r="V3">
-        <v>1.68</v>
+        <v>1.42</v>
       </c>
       <c r="W3">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="X3">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y3">
-        <v>1.09</v>
+        <v>1.26</v>
       </c>
       <c r="Z3">
-        <v>5.25</v>
+        <v>3.2</v>
       </c>
       <c r="AA3">
-        <v>1.42</v>
+        <v>1.95</v>
       </c>
       <c r="AB3">
-        <v>2.49</v>
+        <v>1.81</v>
       </c>
       <c r="AC3">
-        <v>2.12</v>
+        <v>3.14</v>
       </c>
       <c r="AD3">
-        <v>1.68</v>
+        <v>1.27</v>
       </c>
       <c r="AE3">
-        <v>1.23</v>
+        <v>1.07</v>
       </c>
       <c r="AF3">
-        <v>1.6</v>
+        <v>1.75</v>
       </c>
       <c r="AG3">
-        <v>2.25</v>
+        <v>1.9</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -868,10 +868,10 @@
         </is>
       </c>
       <c r="AJ3">
-        <v>1.14</v>
+        <v>1.22</v>
       </c>
       <c r="AK3">
-        <v>1.08</v>
+        <v>1.83</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -902,7 +902,7 @@
       </c>
       <c r="AU3" t="inlineStr">
         <is>
-          <t>2026-08-02 01:00:00</t>
+          <t>2026-08-02 01:30:00</t>
         </is>
       </c>
     </row>
@@ -914,7 +914,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>01:30</t>
+          <t>02:00</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -929,12 +929,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Sydney United</t>
+          <t>Rockdale City Suns</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>NWS Spirit</t>
+          <t>Manly United</t>
         </is>
       </c>
       <c r="G4">
@@ -961,64 +961,64 @@
         </is>
       </c>
       <c r="N4">
-        <v>1.86</v>
+        <v>1.76</v>
       </c>
       <c r="O4">
-        <v>3.35</v>
+        <v>3.8</v>
       </c>
       <c r="P4">
         <v>3.55</v>
       </c>
       <c r="Q4">
-        <v>2.41</v>
+        <v>2.2</v>
       </c>
       <c r="R4">
-        <v>2.1</v>
+        <v>2.25</v>
       </c>
       <c r="S4">
-        <v>1.38</v>
+        <v>1.25</v>
       </c>
       <c r="T4">
-        <v>2.75</v>
+        <v>3.28</v>
       </c>
       <c r="U4">
-        <v>2.78</v>
+        <v>2.37</v>
       </c>
       <c r="V4">
-        <v>1.39</v>
+        <v>1.57</v>
       </c>
       <c r="W4">
-        <v>1.08</v>
+        <v>1.13</v>
       </c>
       <c r="X4">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y4">
-        <v>1.26</v>
+        <v>1.15</v>
       </c>
       <c r="Z4">
-        <v>3.2</v>
+        <v>4.35</v>
       </c>
       <c r="AA4">
-        <v>1.94</v>
+        <v>1.6</v>
       </c>
       <c r="AB4">
-        <v>1.81</v>
+        <v>2.25</v>
       </c>
       <c r="AC4">
-        <v>3.14</v>
+        <v>2.28</v>
       </c>
       <c r="AD4">
-        <v>1.34</v>
+        <v>1.48</v>
       </c>
       <c r="AE4">
-        <v>1.07</v>
+        <v>1.14</v>
       </c>
       <c r="AF4">
-        <v>1.75</v>
+        <v>1.54</v>
       </c>
       <c r="AG4">
-        <v>1.93</v>
+        <v>2.26</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1034,7 +1034,7 @@
         <v>1.19</v>
       </c>
       <c r="AK4">
-        <v>1.64</v>
+        <v>1.91</v>
       </c>
       <c r="AL4">
         <v>0</v>
@@ -1065,7 +1065,7 @@
       </c>
       <c r="AU4" t="inlineStr">
         <is>
-          <t>2026-08-02 01:30:00</t>
+          <t>2026-08-02 02:00:00</t>
         </is>
       </c>
     </row>
@@ -1092,12 +1092,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Rockdale City Suns</t>
+          <t>Marconi Stallions</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Manly United</t>
+          <t>St George City FA</t>
         </is>
       </c>
       <c r="G5">
@@ -1124,64 +1124,64 @@
         </is>
       </c>
       <c r="N5">
-        <v>1.78</v>
+        <v>1.32</v>
       </c>
       <c r="O5">
-        <v>3.7</v>
+        <v>4.65</v>
       </c>
       <c r="P5">
-        <v>3.5</v>
+        <v>6.7</v>
       </c>
       <c r="Q5">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="R5">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="S5">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="T5">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="U5">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="V5">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="W5">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="X5">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y5">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="Z5">
-        <v>4.35</v>
+        <v>0</v>
       </c>
       <c r="AA5">
-        <v>1.62</v>
+        <v>1.72</v>
       </c>
       <c r="AB5">
-        <v>2.17</v>
+        <v>2.07</v>
       </c>
       <c r="AC5">
-        <v>2.52</v>
+        <v>0</v>
       </c>
       <c r="AD5">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="AE5">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AF5">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="AG5">
-        <v>2.26</v>
+        <v>0</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1194,10 +1194,10 @@
         </is>
       </c>
       <c r="AJ5">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AK5">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AL5">
         <v>0</v>
@@ -1255,12 +1255,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Marconi Stallions</t>
+          <t>Blacktown City</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>St George City FA</t>
+          <t>Sydney II</t>
         </is>
       </c>
       <c r="G6">
@@ -1287,64 +1287,64 @@
         </is>
       </c>
       <c r="N6">
-        <v>1.32</v>
+        <v>1.85</v>
       </c>
       <c r="O6">
-        <v>4.65</v>
+        <v>3.5</v>
       </c>
       <c r="P6">
-        <v>6.8</v>
+        <v>3.2</v>
       </c>
       <c r="Q6">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="R6">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="S6">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T6">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="U6">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="V6">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="W6">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X6">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y6">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="Z6">
-        <v>0</v>
+        <v>3.92</v>
       </c>
       <c r="AA6">
-        <v>1.72</v>
+        <v>1.67</v>
       </c>
       <c r="AB6">
-        <v>2.07</v>
+        <v>2.05</v>
       </c>
       <c r="AC6">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AD6">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AE6">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AF6">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AG6">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1357,10 +1357,10 @@
         </is>
       </c>
       <c r="AJ6">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AK6">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AL6">
         <v>0</v>
@@ -1403,7 +1403,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>02:00</t>
+          <t>03:00</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1418,12 +1418,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Blacktown City</t>
+          <t>Sydney Olympic</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Sydney II</t>
+          <t>APIA Leichhardt Tigers</t>
         </is>
       </c>
       <c r="G7">
@@ -1450,64 +1450,64 @@
         </is>
       </c>
       <c r="N7">
-        <v>1.91</v>
+        <v>5.5</v>
       </c>
       <c r="O7">
-        <v>3.5</v>
+        <v>4.39</v>
       </c>
       <c r="P7">
-        <v>3.2</v>
+        <v>1.36</v>
       </c>
       <c r="Q7">
-        <v>2.46</v>
+        <v>5.79</v>
       </c>
       <c r="R7">
-        <v>2.18</v>
+        <v>2.55</v>
       </c>
       <c r="S7">
-        <v>1.3</v>
+        <v>1.19</v>
       </c>
       <c r="T7">
-        <v>3.04</v>
+        <v>3.74</v>
       </c>
       <c r="U7">
-        <v>2.44</v>
+        <v>2.1</v>
       </c>
       <c r="V7">
-        <v>1.45</v>
+        <v>1.64</v>
       </c>
       <c r="W7">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="X7">
         <v>1.02</v>
       </c>
       <c r="Y7">
-        <v>1.16</v>
+        <v>1.09</v>
       </c>
       <c r="Z7">
-        <v>4.2</v>
+        <v>5.35</v>
       </c>
       <c r="AA7">
-        <v>1.67</v>
+        <v>1.4</v>
       </c>
       <c r="AB7">
-        <v>2.08</v>
+        <v>2.56</v>
       </c>
       <c r="AC7">
-        <v>2.38</v>
+        <v>2.15</v>
       </c>
       <c r="AD7">
-        <v>1.38</v>
+        <v>1.65</v>
       </c>
       <c r="AE7">
-        <v>1.17</v>
+        <v>1.24</v>
       </c>
       <c r="AF7">
-        <v>1.58</v>
+        <v>1.6</v>
       </c>
       <c r="AG7">
-        <v>2.19</v>
+        <v>2.1</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1520,10 +1520,10 @@
         </is>
       </c>
       <c r="AJ7">
-        <v>1.2</v>
+        <v>2.66</v>
       </c>
       <c r="AK7">
-        <v>1.6</v>
+        <v>1.06</v>
       </c>
       <c r="AL7">
         <v>0</v>
@@ -1554,7 +1554,7 @@
       </c>
       <c r="AU7" t="inlineStr">
         <is>
-          <t>2026-08-02 02:00:00</t>
+          <t>2026-08-02 03:00:00</t>
         </is>
       </c>
     </row>
@@ -2114,7 +2114,7 @@
         <v>2.38</v>
       </c>
       <c r="R11">
-        <v>2.16</v>
+        <v>2.25</v>
       </c>
       <c r="S11">
         <v>1.35</v>
@@ -2123,7 +2123,7 @@
         <v>2.94</v>
       </c>
       <c r="U11">
-        <v>2.75</v>
+        <v>2.65</v>
       </c>
       <c r="V11">
         <v>1.42</v>
@@ -2132,28 +2132,28 @@
         <v>1.1</v>
       </c>
       <c r="X11">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="Y11">
         <v>1.22</v>
       </c>
       <c r="Z11">
-        <v>3.4</v>
+        <v>3.82</v>
       </c>
       <c r="AA11">
-        <v>1.83</v>
+        <v>1.89</v>
       </c>
       <c r="AB11">
-        <v>1.83</v>
+        <v>1.94</v>
       </c>
       <c r="AC11">
-        <v>3.05</v>
+        <v>2.94</v>
       </c>
       <c r="AD11">
-        <v>1.3</v>
+        <v>1.37</v>
       </c>
       <c r="AE11">
-        <v>1.13</v>
+        <v>1.08</v>
       </c>
       <c r="AF11">
         <v>1.7</v>
@@ -2265,16 +2265,16 @@
         </is>
       </c>
       <c r="N12">
-        <v>1.38</v>
+        <v>1.46</v>
       </c>
       <c r="O12">
-        <v>4.25</v>
+        <v>4.2</v>
       </c>
       <c r="P12">
-        <v>5.9</v>
+        <v>5.1</v>
       </c>
       <c r="Q12">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="R12">
         <v>2.28</v>
@@ -2283,7 +2283,7 @@
         <v>1.36</v>
       </c>
       <c r="T12">
-        <v>2.99</v>
+        <v>2.77</v>
       </c>
       <c r="U12">
         <v>2.65</v>
@@ -2304,10 +2304,10 @@
         <v>3.8</v>
       </c>
       <c r="AA12">
-        <v>1.82</v>
+        <v>1.89</v>
       </c>
       <c r="AB12">
-        <v>1.95</v>
+        <v>1.93</v>
       </c>
       <c r="AC12">
         <v>2.89</v>
@@ -2319,7 +2319,7 @@
         <v>1.08</v>
       </c>
       <c r="AF12">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="AG12">
         <v>1.77</v>
@@ -2338,7 +2338,7 @@
         <v>1.16</v>
       </c>
       <c r="AK12">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="AL12">
         <v>0</v>
@@ -2437,13 +2437,13 @@
         <v>2.4</v>
       </c>
       <c r="Q13">
-        <v>3.6</v>
+        <v>3.2</v>
       </c>
       <c r="R13">
-        <v>1.87</v>
+        <v>1.98</v>
       </c>
       <c r="S13">
-        <v>1.45</v>
+        <v>1.53</v>
       </c>
       <c r="T13">
         <v>2.34</v>
@@ -2452,37 +2452,37 @@
         <v>3.4</v>
       </c>
       <c r="V13">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="W13">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="X13">
         <v>1.1</v>
       </c>
       <c r="Y13">
-        <v>1.45</v>
+        <v>1.4</v>
       </c>
       <c r="Z13">
-        <v>2.79</v>
+        <v>2.57</v>
       </c>
       <c r="AA13">
         <v>2.38</v>
       </c>
       <c r="AB13">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="AC13">
         <v>4.5</v>
       </c>
       <c r="AD13">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="AE13">
         <v>1.01</v>
       </c>
       <c r="AF13">
-        <v>1.82</v>
+        <v>1.97</v>
       </c>
       <c r="AG13">
         <v>1.73</v>
@@ -2498,10 +2498,10 @@
         </is>
       </c>
       <c r="AJ13">
-        <v>1.52</v>
+        <v>1.31</v>
       </c>
       <c r="AK13">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="AL13">
         <v>0</v>
@@ -2559,12 +2559,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Ansan Greeners</t>
+          <t>Jeonnam Dragons</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Gimhae City</t>
+          <t>Paju Citizen</t>
         </is>
       </c>
       <c r="G14">
@@ -2591,61 +2591,61 @@
         </is>
       </c>
       <c r="N14">
-        <v>2.91</v>
+        <v>1.97</v>
       </c>
       <c r="O14">
-        <v>3.38</v>
+        <v>3.32</v>
       </c>
       <c r="P14">
-        <v>2.18</v>
+        <v>3.45</v>
       </c>
       <c r="Q14">
-        <v>3.4</v>
+        <v>2.66</v>
       </c>
       <c r="R14">
-        <v>2.2</v>
+        <v>2.09</v>
       </c>
       <c r="S14">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="T14">
-        <v>2.82</v>
+        <v>2.9</v>
       </c>
       <c r="U14">
-        <v>2.75</v>
+        <v>2.71</v>
       </c>
       <c r="V14">
-        <v>1.4</v>
+        <v>1.43</v>
       </c>
       <c r="W14">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="X14">
-        <v>1.05</v>
+        <v>1</v>
       </c>
       <c r="Y14">
-        <v>1.29</v>
+        <v>1.21</v>
       </c>
       <c r="Z14">
-        <v>3.28</v>
+        <v>3.58</v>
       </c>
       <c r="AA14">
-        <v>1.87</v>
+        <v>1.68</v>
       </c>
       <c r="AB14">
-        <v>1.87</v>
+        <v>1.95</v>
       </c>
       <c r="AC14">
-        <v>3.2</v>
+        <v>2.92</v>
       </c>
       <c r="AD14">
         <v>1.31</v>
       </c>
       <c r="AE14">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="AF14">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="AG14">
         <v>2.1</v>
@@ -2661,10 +2661,10 @@
         </is>
       </c>
       <c r="AJ14">
-        <v>1.62</v>
+        <v>1.33</v>
       </c>
       <c r="AK14">
-        <v>1.32</v>
+        <v>1.7</v>
       </c>
       <c r="AL14">
         <v>0</v>
@@ -2722,12 +2722,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Jeonnam Dragons</t>
+          <t>Busan I'Park</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Paju Citizen</t>
+          <t>Seoul E-Land</t>
         </is>
       </c>
       <c r="G15">
@@ -2754,64 +2754,64 @@
         </is>
       </c>
       <c r="N15">
-        <v>1.97</v>
+        <v>2.65</v>
       </c>
       <c r="O15">
-        <v>3.32</v>
+        <v>3.5</v>
       </c>
       <c r="P15">
-        <v>3.45</v>
+        <v>2.2</v>
       </c>
       <c r="Q15">
-        <v>2.66</v>
+        <v>3.1</v>
       </c>
       <c r="R15">
-        <v>2.09</v>
+        <v>2.36</v>
       </c>
       <c r="S15">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="T15">
-        <v>2.9</v>
+        <v>3.25</v>
       </c>
       <c r="U15">
-        <v>2.71</v>
+        <v>2.5</v>
       </c>
       <c r="V15">
-        <v>1.43</v>
+        <v>1.45</v>
       </c>
       <c r="W15">
-        <v>1.05</v>
+        <v>1.11</v>
       </c>
       <c r="X15">
-        <v>1</v>
+        <v>1.04</v>
       </c>
       <c r="Y15">
         <v>1.21</v>
       </c>
       <c r="Z15">
-        <v>3.58</v>
+        <v>4.23</v>
       </c>
       <c r="AA15">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="AB15">
-        <v>1.95</v>
+        <v>2.1</v>
       </c>
       <c r="AC15">
-        <v>2.92</v>
+        <v>2.66</v>
       </c>
       <c r="AD15">
-        <v>1.31</v>
+        <v>1.37</v>
       </c>
       <c r="AE15">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="AF15">
-        <v>1.65</v>
+        <v>1.57</v>
       </c>
       <c r="AG15">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2824,10 +2824,10 @@
         </is>
       </c>
       <c r="AJ15">
-        <v>1.33</v>
+        <v>1.51</v>
       </c>
       <c r="AK15">
-        <v>1.7</v>
+        <v>1.4</v>
       </c>
       <c r="AL15">
         <v>0</v>
@@ -2885,12 +2885,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Busan I'Park</t>
+          <t>Ansan Greeners</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Seoul E-Land</t>
+          <t>Gimhae City</t>
         </is>
       </c>
       <c r="G16">
@@ -2917,64 +2917,64 @@
         </is>
       </c>
       <c r="N16">
-        <v>2.65</v>
+        <v>2.91</v>
       </c>
       <c r="O16">
-        <v>3.5</v>
+        <v>3.38</v>
       </c>
       <c r="P16">
+        <v>2.18</v>
+      </c>
+      <c r="Q16">
+        <v>3.4</v>
+      </c>
+      <c r="R16">
         <v>2.2</v>
       </c>
-      <c r="Q16">
-        <v>3.1</v>
-      </c>
-      <c r="R16">
-        <v>2.36</v>
-      </c>
       <c r="S16">
-        <v>1.3</v>
+        <v>1.35</v>
       </c>
       <c r="T16">
-        <v>3.25</v>
+        <v>2.82</v>
       </c>
       <c r="U16">
-        <v>2.5</v>
+        <v>2.75</v>
       </c>
       <c r="V16">
-        <v>1.45</v>
+        <v>1.4</v>
       </c>
       <c r="W16">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="X16">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="Y16">
-        <v>1.21</v>
+        <v>1.29</v>
       </c>
       <c r="Z16">
-        <v>4.23</v>
+        <v>3.28</v>
       </c>
       <c r="AA16">
-        <v>1.7</v>
+        <v>1.87</v>
       </c>
       <c r="AB16">
-        <v>2.1</v>
+        <v>1.87</v>
       </c>
       <c r="AC16">
-        <v>2.66</v>
+        <v>3.2</v>
       </c>
       <c r="AD16">
-        <v>1.37</v>
+        <v>1.31</v>
       </c>
       <c r="AE16">
         <v>1.11</v>
       </c>
       <c r="AF16">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="AG16">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -2987,10 +2987,10 @@
         </is>
       </c>
       <c r="AJ16">
-        <v>1.51</v>
+        <v>1.62</v>
       </c>
       <c r="AK16">
-        <v>1.4</v>
+        <v>1.32</v>
       </c>
       <c r="AL16">
         <v>0</v>
@@ -4384,13 +4384,13 @@
         </is>
       </c>
       <c r="N25">
-        <v>1.68</v>
+        <v>1.74</v>
       </c>
       <c r="O25">
-        <v>3.5</v>
+        <v>3.7</v>
       </c>
       <c r="P25">
-        <v>4.5</v>
+        <v>4.35</v>
       </c>
       <c r="Q25">
         <v>2.28</v>
@@ -4399,7 +4399,7 @@
         <v>2.39</v>
       </c>
       <c r="S25">
-        <v>1.32</v>
+        <v>1.29</v>
       </c>
       <c r="T25">
         <v>3.3</v>
@@ -4411,22 +4411,22 @@
         <v>1.46</v>
       </c>
       <c r="W25">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="X25">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y25">
         <v>1.24</v>
       </c>
       <c r="Z25">
-        <v>3.82</v>
+        <v>3.8</v>
       </c>
       <c r="AA25">
         <v>1.8</v>
       </c>
       <c r="AB25">
-        <v>2.03</v>
+        <v>1.91</v>
       </c>
       <c r="AC25">
         <v>2.88</v>
@@ -4438,7 +4438,7 @@
         <v>1.09</v>
       </c>
       <c r="AF25">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="AG25">
         <v>2.05</v>
@@ -4454,10 +4454,10 @@
         </is>
       </c>
       <c r="AJ25">
-        <v>1.17</v>
+        <v>1.25</v>
       </c>
       <c r="AK25">
-        <v>2</v>
+        <v>2.04</v>
       </c>
       <c r="AL25">
         <v>0</v>
@@ -4556,55 +4556,55 @@
         <v>2.1</v>
       </c>
       <c r="Q26">
-        <v>3.3</v>
+        <v>3.23</v>
       </c>
       <c r="R26">
-        <v>2.22</v>
+        <v>2.3</v>
       </c>
       <c r="S26">
         <v>1.3</v>
       </c>
       <c r="T26">
-        <v>3.22</v>
+        <v>3.6</v>
       </c>
       <c r="U26">
-        <v>2.34</v>
+        <v>2.4</v>
       </c>
       <c r="V26">
-        <v>1.5</v>
+        <v>1.56</v>
       </c>
       <c r="W26">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="X26">
         <v>1.04</v>
       </c>
       <c r="Y26">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="Z26">
-        <v>4.5</v>
+        <v>4.25</v>
       </c>
       <c r="AA26">
         <v>1.61</v>
       </c>
       <c r="AB26">
-        <v>2.28</v>
+        <v>2.25</v>
       </c>
       <c r="AC26">
-        <v>2.55</v>
+        <v>2.3</v>
       </c>
       <c r="AD26">
-        <v>1.45</v>
+        <v>1.52</v>
       </c>
       <c r="AE26">
         <v>1.16</v>
       </c>
       <c r="AF26">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="AG26">
-        <v>2.39</v>
+        <v>2.45</v>
       </c>
       <c r="AH26" t="inlineStr">
         <is>
@@ -4617,10 +4617,10 @@
         </is>
       </c>
       <c r="AJ26">
-        <v>1.65</v>
+        <v>1.23</v>
       </c>
       <c r="AK26">
-        <v>1.36</v>
+        <v>1.29</v>
       </c>
       <c r="AL26">
         <v>0</v>
@@ -5004,12 +5004,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Ulytau</t>
+          <t>Okzhetpes</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Astana</t>
+          <t>Altay</t>
         </is>
       </c>
       <c r="G29">
@@ -5036,64 +5036,64 @@
         </is>
       </c>
       <c r="N29">
-        <v>4.43</v>
+        <v>1.65</v>
       </c>
       <c r="O29">
-        <v>3.42</v>
+        <v>3.52</v>
       </c>
       <c r="P29">
-        <v>1.83</v>
+        <v>7.24</v>
       </c>
       <c r="Q29">
-        <v>4.9</v>
+        <v>0</v>
       </c>
       <c r="R29">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="S29">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="T29">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="U29">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="V29">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="W29">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="X29">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y29">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="Z29">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="AA29">
-        <v>1.9</v>
+        <v>1.8</v>
       </c>
       <c r="AB29">
-        <v>1.87</v>
+        <v>2</v>
       </c>
       <c r="AC29">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="AD29">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AE29">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AF29">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="AG29">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AH29" t="inlineStr">
         <is>
@@ -5106,10 +5106,10 @@
         </is>
       </c>
       <c r="AJ29">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AK29">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AL29">
         <v>0</v>
@@ -5152,27 +5152,27 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Okzhetpes</t>
+          <t>Ruch Chorzów</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Altay</t>
+          <t>Miedź Legnica</t>
         </is>
       </c>
       <c r="G30">
@@ -5199,64 +5199,64 @@
         </is>
       </c>
       <c r="N30">
-        <v>1.55</v>
+        <v>2.04</v>
       </c>
       <c r="O30">
-        <v>3.52</v>
+        <v>3.4</v>
       </c>
       <c r="P30">
-        <v>7.24</v>
+        <v>3.15</v>
       </c>
       <c r="Q30">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="R30">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="S30">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T30">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="U30">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="V30">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="W30">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X30">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y30">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Z30">
-        <v>0</v>
+        <v>3.86</v>
       </c>
       <c r="AA30">
-        <v>1.8</v>
+        <v>1.74</v>
       </c>
       <c r="AB30">
         <v>2</v>
       </c>
       <c r="AC30">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="AD30">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AE30">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AF30">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AG30">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AH30" t="inlineStr">
         <is>
@@ -5269,10 +5269,10 @@
         </is>
       </c>
       <c r="AJ30">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK30">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AL30">
         <v>0</v>
@@ -5303,7 +5303,7 @@
       </c>
       <c r="AU30" t="inlineStr">
         <is>
-          <t>2026-08-02 09:00:00</t>
+          <t>2026-08-02 09:30:00</t>
         </is>
       </c>
     </row>
@@ -5315,12 +5315,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -5330,12 +5330,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Ruch Chorzów</t>
+          <t>Legia Warszawa</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Miedź Legnica</t>
+          <t>Zagłębie Lubin</t>
         </is>
       </c>
       <c r="G31">
@@ -5362,64 +5362,64 @@
         </is>
       </c>
       <c r="N31">
-        <v>2.04</v>
+        <v>1.6</v>
       </c>
       <c r="O31">
-        <v>3.4</v>
+        <v>3.7</v>
       </c>
       <c r="P31">
-        <v>3.15</v>
+        <v>4.7</v>
       </c>
       <c r="Q31">
-        <v>2.6</v>
+        <v>2.12</v>
       </c>
       <c r="R31">
-        <v>2.19</v>
+        <v>2.37</v>
       </c>
       <c r="S31">
-        <v>1.3</v>
+        <v>1.35</v>
       </c>
       <c r="T31">
-        <v>3.12</v>
+        <v>2.9</v>
       </c>
       <c r="U31">
-        <v>2.5</v>
+        <v>2.55</v>
       </c>
       <c r="V31">
-        <v>1.49</v>
+        <v>1.43</v>
       </c>
       <c r="W31">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="X31">
         <v>1.03</v>
       </c>
       <c r="Y31">
-        <v>1.18</v>
+        <v>1.23</v>
       </c>
       <c r="Z31">
-        <v>3.86</v>
+        <v>3.42</v>
       </c>
       <c r="AA31">
-        <v>1.74</v>
+        <v>1.88</v>
       </c>
       <c r="AB31">
-        <v>2</v>
+        <v>1.94</v>
       </c>
       <c r="AC31">
-        <v>2.74</v>
+        <v>2.97</v>
       </c>
       <c r="AD31">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="AE31">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="AF31">
-        <v>1.59</v>
+        <v>1.91</v>
       </c>
       <c r="AG31">
-        <v>2.2</v>
+        <v>1.84</v>
       </c>
       <c r="AH31" t="inlineStr">
         <is>
@@ -5435,7 +5435,7 @@
         <v>1.22</v>
       </c>
       <c r="AK31">
-        <v>1.63</v>
+        <v>2.31</v>
       </c>
       <c r="AL31">
         <v>0</v>
@@ -5466,7 +5466,7 @@
       </c>
       <c r="AU31" t="inlineStr">
         <is>
-          <t>2026-08-02 09:30:00</t>
+          <t>2026-08-02 09:45:00</t>
         </is>
       </c>
     </row>
@@ -5478,12 +5478,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>09:45</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -5493,12 +5493,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Legia Warszawa</t>
+          <t>Richards Bay</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Zagłębie Lubin</t>
+          <t>Polokwane City</t>
         </is>
       </c>
       <c r="G32">
@@ -5525,64 +5525,64 @@
         </is>
       </c>
       <c r="N32">
+        <v>2.7</v>
+      </c>
+      <c r="O32">
+        <v>2.6</v>
+      </c>
+      <c r="P32">
+        <v>2.8</v>
+      </c>
+      <c r="Q32">
+        <v>3.45</v>
+      </c>
+      <c r="R32">
+        <v>1.85</v>
+      </c>
+      <c r="S32">
         <v>1.6</v>
       </c>
-      <c r="O32">
-        <v>3.7</v>
-      </c>
-      <c r="P32">
-        <v>4.7</v>
-      </c>
-      <c r="Q32">
-        <v>2.12</v>
-      </c>
-      <c r="R32">
-        <v>2.2</v>
-      </c>
-      <c r="S32">
-        <v>1.35</v>
-      </c>
       <c r="T32">
-        <v>2.9</v>
+        <v>2.1</v>
       </c>
       <c r="U32">
-        <v>2.55</v>
+        <v>3.82</v>
       </c>
       <c r="V32">
-        <v>1.43</v>
+        <v>1.18</v>
       </c>
       <c r="W32">
-        <v>1.09</v>
+        <v>1.01</v>
       </c>
       <c r="X32">
-        <v>1.01</v>
+        <v>1.15</v>
       </c>
       <c r="Y32">
-        <v>1.23</v>
+        <v>1.67</v>
       </c>
       <c r="Z32">
-        <v>3.42</v>
+        <v>2.15</v>
       </c>
       <c r="AA32">
-        <v>1.88</v>
+        <v>2.78</v>
       </c>
       <c r="AB32">
-        <v>1.94</v>
+        <v>1.38</v>
       </c>
       <c r="AC32">
-        <v>2.97</v>
+        <v>6.25</v>
       </c>
       <c r="AD32">
-        <v>1.3</v>
+        <v>1.11</v>
       </c>
       <c r="AE32">
-        <v>1.1</v>
+        <v>1.03</v>
       </c>
       <c r="AF32">
-        <v>1.87</v>
+        <v>2.25</v>
       </c>
       <c r="AG32">
-        <v>1.83</v>
+        <v>1.6</v>
       </c>
       <c r="AH32" t="inlineStr">
         <is>
@@ -5595,10 +5595,10 @@
         </is>
       </c>
       <c r="AJ32">
-        <v>1.11</v>
+        <v>1.31</v>
       </c>
       <c r="AK32">
-        <v>2.31</v>
+        <v>1.4</v>
       </c>
       <c r="AL32">
         <v>0</v>
@@ -5629,7 +5629,7 @@
       </c>
       <c r="AU32" t="inlineStr">
         <is>
-          <t>2026-08-02 09:45:00</t>
+          <t>2026-08-02 10:00:00</t>
         </is>
       </c>
     </row>
@@ -5646,7 +5646,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Richards Bay</t>
+          <t>Volga Ulyanovsk</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Polokwane City</t>
+          <t>Chelyabinsk</t>
         </is>
       </c>
       <c r="G33">
@@ -5688,64 +5688,64 @@
         </is>
       </c>
       <c r="N33">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="O33">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="P33">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="Q33">
-        <v>3.45</v>
+        <v>3.18</v>
       </c>
       <c r="R33">
-        <v>1.85</v>
+        <v>1.95</v>
       </c>
       <c r="S33">
-        <v>1.6</v>
+        <v>1.43</v>
       </c>
       <c r="T33">
-        <v>2.1</v>
+        <v>2.53</v>
       </c>
       <c r="U33">
-        <v>3.82</v>
+        <v>3.1</v>
       </c>
       <c r="V33">
-        <v>1.18</v>
+        <v>1.32</v>
       </c>
       <c r="W33">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X33">
-        <v>1.15</v>
+        <v>1.03</v>
       </c>
       <c r="Y33">
-        <v>1.67</v>
+        <v>1.33</v>
       </c>
       <c r="Z33">
-        <v>2.15</v>
+        <v>2.81</v>
       </c>
       <c r="AA33">
-        <v>2.78</v>
+        <v>2.19</v>
       </c>
       <c r="AB33">
-        <v>1.38</v>
+        <v>1.66</v>
       </c>
       <c r="AC33">
-        <v>6.25</v>
+        <v>3.94</v>
       </c>
       <c r="AD33">
-        <v>1.11</v>
+        <v>1.19</v>
       </c>
       <c r="AE33">
         <v>1.03</v>
       </c>
       <c r="AF33">
-        <v>2.25</v>
+        <v>1.84</v>
       </c>
       <c r="AG33">
-        <v>1.6</v>
+        <v>1.84</v>
       </c>
       <c r="AH33" t="inlineStr">
         <is>
@@ -5758,10 +5758,10 @@
         </is>
       </c>
       <c r="AJ33">
-        <v>1.31</v>
+        <v>1.4</v>
       </c>
       <c r="AK33">
-        <v>1.4</v>
+        <v>1.52</v>
       </c>
       <c r="AL33">
         <v>0</v>
@@ -5809,7 +5809,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -5819,12 +5819,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Volga Ulyanovsk</t>
+          <t>Sigma Olomouc</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Chelyabinsk</t>
+          <t>Mladá Boleslav</t>
         </is>
       </c>
       <c r="G34">
@@ -5851,64 +5851,64 @@
         </is>
       </c>
       <c r="N34">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="O34">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="P34">
-        <v>0</v>
+        <v>4.03</v>
       </c>
       <c r="Q34">
-        <v>3.18</v>
+        <v>2.2</v>
       </c>
       <c r="R34">
-        <v>1.95</v>
+        <v>2.3</v>
       </c>
       <c r="S34">
-        <v>1.43</v>
+        <v>1.28</v>
       </c>
       <c r="T34">
-        <v>2.53</v>
+        <v>3.6</v>
       </c>
       <c r="U34">
-        <v>3.1</v>
+        <v>2.45</v>
       </c>
       <c r="V34">
-        <v>1.32</v>
+        <v>1.52</v>
       </c>
       <c r="W34">
-        <v>1.02</v>
+        <v>1.1</v>
       </c>
       <c r="X34">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y34">
-        <v>1.33</v>
+        <v>1.14</v>
       </c>
       <c r="Z34">
-        <v>2.81</v>
+        <v>4.4</v>
       </c>
       <c r="AA34">
-        <v>2.19</v>
+        <v>1.59</v>
       </c>
       <c r="AB34">
-        <v>1.66</v>
+        <v>2.1</v>
       </c>
       <c r="AC34">
-        <v>3.94</v>
+        <v>2.38</v>
       </c>
       <c r="AD34">
-        <v>1.19</v>
+        <v>1.46</v>
       </c>
       <c r="AE34">
-        <v>1.03</v>
+        <v>1.17</v>
       </c>
       <c r="AF34">
-        <v>1.84</v>
+        <v>1.56</v>
       </c>
       <c r="AG34">
-        <v>1.84</v>
+        <v>2.28</v>
       </c>
       <c r="AH34" t="inlineStr">
         <is>
@@ -5921,10 +5921,10 @@
         </is>
       </c>
       <c r="AJ34">
-        <v>1.4</v>
+        <v>1.17</v>
       </c>
       <c r="AK34">
-        <v>1.52</v>
+        <v>2</v>
       </c>
       <c r="AL34">
         <v>0</v>
@@ -5972,22 +5972,22 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Sigma Olomouc</t>
+          <t>United Nordic</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Mladá Boleslav</t>
+          <t>Ljungskile</t>
         </is>
       </c>
       <c r="G35">
@@ -6014,64 +6014,64 @@
         </is>
       </c>
       <c r="N35">
-        <v>1.75</v>
+        <v>2.18</v>
       </c>
       <c r="O35">
-        <v>3.7</v>
+        <v>3.5</v>
       </c>
       <c r="P35">
-        <v>4.03</v>
+        <v>2.98</v>
       </c>
       <c r="Q35">
-        <v>2.2</v>
+        <v>2.65</v>
       </c>
       <c r="R35">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="S35">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="T35">
-        <v>3.6</v>
+        <v>3.36</v>
       </c>
       <c r="U35">
-        <v>2.45</v>
+        <v>2.31</v>
       </c>
       <c r="V35">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="W35">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="X35">
         <v>1.04</v>
       </c>
       <c r="Y35">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="Z35">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="AA35">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="AB35">
-        <v>2.1</v>
+        <v>2.3</v>
       </c>
       <c r="AC35">
-        <v>2.38</v>
+        <v>2.33</v>
       </c>
       <c r="AD35">
-        <v>1.46</v>
+        <v>1.53</v>
       </c>
       <c r="AE35">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="AF35">
-        <v>1.56</v>
+        <v>1.48</v>
       </c>
       <c r="AG35">
-        <v>2.28</v>
+        <v>2.4</v>
       </c>
       <c r="AH35" t="inlineStr">
         <is>
@@ -6084,10 +6084,10 @@
         </is>
       </c>
       <c r="AJ35">
-        <v>1.17</v>
+        <v>1.25</v>
       </c>
       <c r="AK35">
-        <v>2</v>
+        <v>1.63</v>
       </c>
       <c r="AL35">
         <v>0</v>
@@ -6135,7 +6135,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -6145,12 +6145,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>United Nordic</t>
+          <t>Häcken W</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Ljungskile</t>
+          <t>Eskilstuna United</t>
         </is>
       </c>
       <c r="G36">
@@ -6177,64 +6177,64 @@
         </is>
       </c>
       <c r="N36">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="O36">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="P36">
-        <v>2.98</v>
+        <v>0</v>
       </c>
       <c r="Q36">
-        <v>2.65</v>
+        <v>1.52</v>
       </c>
       <c r="R36">
-        <v>2.28</v>
+        <v>2.88</v>
       </c>
       <c r="S36">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="T36">
-        <v>3.36</v>
+        <v>4</v>
       </c>
       <c r="U36">
+        <v>2.13</v>
+      </c>
+      <c r="V36">
+        <v>1.62</v>
+      </c>
+      <c r="W36">
+        <v>1.14</v>
+      </c>
+      <c r="X36">
+        <v>1.02</v>
+      </c>
+      <c r="Y36">
+        <v>1.11</v>
+      </c>
+      <c r="Z36">
+        <v>5.2</v>
+      </c>
+      <c r="AA36">
+        <v>1.42</v>
+      </c>
+      <c r="AB36">
+        <v>2.49</v>
+      </c>
+      <c r="AC36">
+        <v>2.14</v>
+      </c>
+      <c r="AD36">
+        <v>1.62</v>
+      </c>
+      <c r="AE36">
+        <v>1.19</v>
+      </c>
+      <c r="AF36">
         <v>2.25</v>
       </c>
-      <c r="V36">
-        <v>1.56</v>
-      </c>
-      <c r="W36">
-        <v>1.11</v>
-      </c>
-      <c r="X36">
-        <v>1.04</v>
-      </c>
-      <c r="Y36">
-        <v>1.13</v>
-      </c>
-      <c r="Z36">
-        <v>4.2</v>
-      </c>
-      <c r="AA36">
-        <v>1.57</v>
-      </c>
-      <c r="AB36">
-        <v>2.35</v>
-      </c>
-      <c r="AC36">
-        <v>2.5</v>
-      </c>
-      <c r="AD36">
-        <v>1.48</v>
-      </c>
-      <c r="AE36">
-        <v>1.16</v>
-      </c>
-      <c r="AF36">
-        <v>1.5</v>
-      </c>
       <c r="AG36">
-        <v>2.4</v>
+        <v>1.53</v>
       </c>
       <c r="AH36" t="inlineStr">
         <is>
@@ -6247,10 +6247,10 @@
         </is>
       </c>
       <c r="AJ36">
-        <v>1.24</v>
+        <v>1.01</v>
       </c>
       <c r="AK36">
-        <v>1.64</v>
+        <v>4</v>
       </c>
       <c r="AL36">
         <v>0</v>
@@ -6298,7 +6298,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -6308,12 +6308,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Häcken W</t>
+          <t>Tukums</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Eskilstuna United</t>
+          <t>Liepāja</t>
         </is>
       </c>
       <c r="G37">
@@ -6340,64 +6340,64 @@
         </is>
       </c>
       <c r="N37">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="O37">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="P37">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="Q37">
-        <v>1.57</v>
+        <v>3.85</v>
       </c>
       <c r="R37">
-        <v>2.76</v>
+        <v>2.43</v>
       </c>
       <c r="S37">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="T37">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="U37">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="V37">
-        <v>1.66</v>
+        <v>1.55</v>
       </c>
       <c r="W37">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="X37">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y37">
-        <v>1.11</v>
+        <v>1.15</v>
       </c>
       <c r="Z37">
-        <v>5.2</v>
+        <v>4.3</v>
       </c>
       <c r="AA37">
-        <v>1.42</v>
+        <v>1.52</v>
       </c>
       <c r="AB37">
-        <v>2.49</v>
+        <v>2.23</v>
       </c>
       <c r="AC37">
-        <v>2.14</v>
+        <v>2.3</v>
       </c>
       <c r="AD37">
-        <v>1.62</v>
+        <v>1.5</v>
       </c>
       <c r="AE37">
-        <v>1.22</v>
+        <v>1.19</v>
       </c>
       <c r="AF37">
-        <v>1.93</v>
+        <v>1.49</v>
       </c>
       <c r="AG37">
-        <v>1.78</v>
+        <v>2.28</v>
       </c>
       <c r="AH37" t="inlineStr">
         <is>
@@ -6410,10 +6410,10 @@
         </is>
       </c>
       <c r="AJ37">
-        <v>1.05</v>
+        <v>1.8</v>
       </c>
       <c r="AK37">
-        <v>4</v>
+        <v>1.18</v>
       </c>
       <c r="AL37">
         <v>0</v>
@@ -6461,22 +6461,22 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Tukums</t>
+          <t>Orenburg</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Liepāja</t>
+          <t>Zenit</t>
         </is>
       </c>
       <c r="G38">
@@ -6503,64 +6503,64 @@
         </is>
       </c>
       <c r="N38">
-        <v>3.5</v>
+        <v>7.6</v>
       </c>
       <c r="O38">
-        <v>3.7</v>
+        <v>4.4</v>
       </c>
       <c r="P38">
-        <v>1.86</v>
+        <v>1.37</v>
       </c>
       <c r="Q38">
-        <v>3.85</v>
+        <v>7.1</v>
       </c>
       <c r="R38">
-        <v>2.43</v>
+        <v>2.47</v>
       </c>
       <c r="S38">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="T38">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="U38">
-        <v>2.14</v>
+        <v>2.6</v>
       </c>
       <c r="V38">
-        <v>1.55</v>
+        <v>1.45</v>
       </c>
       <c r="W38">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X38">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y38">
-        <v>1.15</v>
+        <v>1.23</v>
       </c>
       <c r="Z38">
-        <v>4.3</v>
+        <v>3.74</v>
       </c>
       <c r="AA38">
-        <v>1.52</v>
+        <v>1.85</v>
       </c>
       <c r="AB38">
-        <v>2.23</v>
+        <v>2.11</v>
       </c>
       <c r="AC38">
-        <v>2.3</v>
+        <v>2.86</v>
       </c>
       <c r="AD38">
-        <v>1.5</v>
+        <v>1.39</v>
       </c>
       <c r="AE38">
-        <v>1.19</v>
+        <v>1.1</v>
       </c>
       <c r="AF38">
-        <v>1.49</v>
+        <v>2.02</v>
       </c>
       <c r="AG38">
-        <v>2.28</v>
+        <v>1.71</v>
       </c>
       <c r="AH38" t="inlineStr">
         <is>
@@ -6573,10 +6573,10 @@
         </is>
       </c>
       <c r="AJ38">
-        <v>1.8</v>
+        <v>3.08</v>
       </c>
       <c r="AK38">
-        <v>1.18</v>
+        <v>1.1</v>
       </c>
       <c r="AL38">
         <v>0</v>
@@ -6624,7 +6624,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -6634,12 +6634,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Orenburg</t>
+          <t>St. Johnstone</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Zenit</t>
+          <t>Kilmarnock</t>
         </is>
       </c>
       <c r="G39">
@@ -6666,64 +6666,64 @@
         </is>
       </c>
       <c r="N39">
-        <v>7.6</v>
+        <v>2.17</v>
       </c>
       <c r="O39">
-        <v>4.4</v>
+        <v>3.4</v>
       </c>
       <c r="P39">
-        <v>1.37</v>
+        <v>3.15</v>
       </c>
       <c r="Q39">
-        <v>7.1</v>
+        <v>2.75</v>
       </c>
       <c r="R39">
-        <v>2.47</v>
+        <v>2.12</v>
       </c>
       <c r="S39">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="T39">
-        <v>3.2</v>
+        <v>2.94</v>
       </c>
       <c r="U39">
-        <v>2.6</v>
+        <v>2.75</v>
       </c>
       <c r="V39">
         <v>1.45</v>
       </c>
       <c r="W39">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="X39">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y39">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="Z39">
-        <v>3.74</v>
+        <v>3.85</v>
       </c>
       <c r="AA39">
-        <v>1.85</v>
+        <v>1.79</v>
       </c>
       <c r="AB39">
-        <v>2.11</v>
+        <v>1.97</v>
       </c>
       <c r="AC39">
-        <v>2.86</v>
+        <v>2.95</v>
       </c>
       <c r="AD39">
-        <v>1.39</v>
+        <v>1.34</v>
       </c>
       <c r="AE39">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="AF39">
-        <v>2.02</v>
+        <v>1.61</v>
       </c>
       <c r="AG39">
-        <v>1.71</v>
+        <v>2.2</v>
       </c>
       <c r="AH39" t="inlineStr">
         <is>
@@ -6736,10 +6736,10 @@
         </is>
       </c>
       <c r="AJ39">
-        <v>3.08</v>
+        <v>1.24</v>
       </c>
       <c r="AK39">
-        <v>1.1</v>
+        <v>1.65</v>
       </c>
       <c r="AL39">
         <v>0</v>
@@ -6787,22 +6787,22 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>St. Johnstone</t>
+          <t>Ulytau</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Kilmarnock</t>
+          <t>Astana</t>
         </is>
       </c>
       <c r="G40">
@@ -6829,31 +6829,31 @@
         </is>
       </c>
       <c r="N40">
-        <v>2.17</v>
+        <v>4.43</v>
       </c>
       <c r="O40">
-        <v>3.4</v>
+        <v>3.42</v>
       </c>
       <c r="P40">
-        <v>3.15</v>
+        <v>1.83</v>
       </c>
       <c r="Q40">
-        <v>2.75</v>
+        <v>4.9</v>
       </c>
       <c r="R40">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="S40">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="T40">
-        <v>2.94</v>
+        <v>3</v>
       </c>
       <c r="U40">
         <v>2.75</v>
       </c>
       <c r="V40">
-        <v>1.45</v>
+        <v>1.4</v>
       </c>
       <c r="W40">
         <v>1.06</v>
@@ -6862,31 +6862,31 @@
         <v>1.02</v>
       </c>
       <c r="Y40">
-        <v>1.21</v>
+        <v>1.3</v>
       </c>
       <c r="Z40">
-        <v>3.85</v>
+        <v>3.55</v>
       </c>
       <c r="AA40">
-        <v>1.79</v>
+        <v>1.9</v>
       </c>
       <c r="AB40">
-        <v>1.97</v>
+        <v>1.87</v>
       </c>
       <c r="AC40">
         <v>2.95</v>
       </c>
       <c r="AD40">
-        <v>1.34</v>
+        <v>1.27</v>
       </c>
       <c r="AE40">
-        <v>1.11</v>
+        <v>1.06</v>
       </c>
       <c r="AF40">
-        <v>1.61</v>
+        <v>1.9</v>
       </c>
       <c r="AG40">
-        <v>2.2</v>
+        <v>1.82</v>
       </c>
       <c r="AH40" t="inlineStr">
         <is>
@@ -6899,10 +6899,10 @@
         </is>
       </c>
       <c r="AJ40">
-        <v>1.24</v>
+        <v>1.91</v>
       </c>
       <c r="AK40">
-        <v>1.65</v>
+        <v>1.18</v>
       </c>
       <c r="AL40">
         <v>0</v>
@@ -7327,13 +7327,13 @@
         <v>2.03</v>
       </c>
       <c r="Q43">
-        <v>3.6</v>
+        <v>3.58</v>
       </c>
       <c r="R43">
-        <v>2.23</v>
+        <v>2.21</v>
       </c>
       <c r="S43">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="T43">
         <v>3.2</v>
@@ -7345,19 +7345,19 @@
         <v>1.5</v>
       </c>
       <c r="W43">
-        <v>1.08</v>
+        <v>1.12</v>
       </c>
       <c r="X43">
         <v>1.02</v>
       </c>
       <c r="Y43">
-        <v>1.16</v>
+        <v>1.2</v>
       </c>
       <c r="Z43">
-        <v>4.2</v>
+        <v>4.15</v>
       </c>
       <c r="AA43">
-        <v>1.68</v>
+        <v>1.66</v>
       </c>
       <c r="AB43">
         <v>2.05</v>
@@ -7366,16 +7366,16 @@
         <v>2.7</v>
       </c>
       <c r="AD43">
-        <v>1.45</v>
+        <v>1.41</v>
       </c>
       <c r="AE43">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="AF43">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="AG43">
-        <v>2.24</v>
+        <v>2.3</v>
       </c>
       <c r="AH43" t="inlineStr">
         <is>
@@ -7388,10 +7388,10 @@
         </is>
       </c>
       <c r="AJ43">
-        <v>1.22</v>
+        <v>1.27</v>
       </c>
       <c r="AK43">
-        <v>1.29</v>
+        <v>1.35</v>
       </c>
       <c r="AL43">
         <v>0</v>
@@ -7928,7 +7928,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -7938,12 +7938,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AB</t>
+          <t>ÍA</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Skála</t>
+          <t>Víkingur Reykjavík</t>
         </is>
       </c>
       <c r="G47">
@@ -7970,64 +7970,64 @@
         </is>
       </c>
       <c r="N47">
-        <v>2.28</v>
+        <v>5.78</v>
       </c>
       <c r="O47">
+        <v>4.85</v>
+      </c>
+      <c r="P47">
+        <v>1.44</v>
+      </c>
+      <c r="Q47">
+        <v>4.78</v>
+      </c>
+      <c r="R47">
+        <v>2.53</v>
+      </c>
+      <c r="S47">
+        <v>1.14</v>
+      </c>
+      <c r="T47">
+        <v>4.6</v>
+      </c>
+      <c r="U47">
+        <v>1.73</v>
+      </c>
+      <c r="V47">
+        <v>2</v>
+      </c>
+      <c r="W47">
+        <v>1.25</v>
+      </c>
+      <c r="X47">
+        <v>1.01</v>
+      </c>
+      <c r="Y47">
+        <v>1.03</v>
+      </c>
+      <c r="Z47">
+        <v>7.4</v>
+      </c>
+      <c r="AA47">
+        <v>1.24</v>
+      </c>
+      <c r="AB47">
         <v>3.4</v>
       </c>
-      <c r="P47">
-        <v>2.79</v>
-      </c>
-      <c r="Q47">
-        <v>2.8</v>
-      </c>
-      <c r="R47">
-        <v>2.18</v>
-      </c>
-      <c r="S47">
-        <v>1.31</v>
-      </c>
-      <c r="T47">
-        <v>3.02</v>
-      </c>
-      <c r="U47">
-        <v>2.44</v>
-      </c>
-      <c r="V47">
-        <v>1.46</v>
-      </c>
-      <c r="W47">
-        <v>1.08</v>
-      </c>
-      <c r="X47">
-        <v>1</v>
-      </c>
-      <c r="Y47">
-        <v>1.18</v>
-      </c>
-      <c r="Z47">
-        <v>3.84</v>
-      </c>
-      <c r="AA47">
-        <v>1.68</v>
-      </c>
-      <c r="AB47">
-        <v>2.06</v>
-      </c>
       <c r="AC47">
-        <v>2.59</v>
+        <v>1.71</v>
       </c>
       <c r="AD47">
-        <v>1.39</v>
+        <v>2</v>
       </c>
       <c r="AE47">
-        <v>1.12</v>
+        <v>1.43</v>
       </c>
       <c r="AF47">
-        <v>1.56</v>
+        <v>1.35</v>
       </c>
       <c r="AG47">
-        <v>2.25</v>
+        <v>2.88</v>
       </c>
       <c r="AH47" t="inlineStr">
         <is>
@@ -8040,10 +8040,10 @@
         </is>
       </c>
       <c r="AJ47">
-        <v>1.35</v>
+        <v>1.16</v>
       </c>
       <c r="AK47">
-        <v>1.48</v>
+        <v>1.14</v>
       </c>
       <c r="AL47">
         <v>0</v>
@@ -8101,12 +8101,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>KÍ</t>
+          <t>AB</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>B36</t>
+          <t>Skála</t>
         </is>
       </c>
       <c r="G48">
@@ -8133,80 +8133,80 @@
         </is>
       </c>
       <c r="N48">
-        <v>1.59</v>
+        <v>2.28</v>
       </c>
       <c r="O48">
-        <v>3.8</v>
+        <v>3.4</v>
       </c>
       <c r="P48">
-        <v>5.02</v>
+        <v>2.79</v>
       </c>
       <c r="Q48">
-        <v>2.15</v>
+        <v>2.8</v>
       </c>
       <c r="R48">
-        <v>2.17</v>
+        <v>2.2</v>
       </c>
       <c r="S48">
-        <v>1.34</v>
+        <v>1.31</v>
       </c>
       <c r="T48">
-        <v>2.88</v>
+        <v>3.02</v>
       </c>
       <c r="U48">
-        <v>2.63</v>
+        <v>2.5</v>
       </c>
       <c r="V48">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="W48">
-        <v>1.06</v>
+        <v>1.11</v>
       </c>
       <c r="X48">
         <v>1</v>
       </c>
       <c r="Y48">
+        <v>1.18</v>
+      </c>
+      <c r="Z48">
+        <v>3.84</v>
+      </c>
+      <c r="AA48">
+        <v>1.68</v>
+      </c>
+      <c r="AB48">
+        <v>2.06</v>
+      </c>
+      <c r="AC48">
+        <v>2.6</v>
+      </c>
+      <c r="AD48">
+        <v>1.38</v>
+      </c>
+      <c r="AE48">
+        <v>1.12</v>
+      </c>
+      <c r="AF48">
+        <v>1.56</v>
+      </c>
+      <c r="AG48">
+        <v>2.25</v>
+      </c>
+      <c r="AH48" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI48" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ48">
         <v>1.22</v>
       </c>
-      <c r="Z48">
-        <v>3.5</v>
-      </c>
-      <c r="AA48">
-        <v>1.79</v>
-      </c>
-      <c r="AB48">
-        <v>1.92</v>
-      </c>
-      <c r="AC48">
-        <v>2.88</v>
-      </c>
-      <c r="AD48">
-        <v>1.32</v>
-      </c>
-      <c r="AE48">
-        <v>1.09</v>
-      </c>
-      <c r="AF48">
-        <v>1.81</v>
-      </c>
-      <c r="AG48">
-        <v>1.88</v>
-      </c>
-      <c r="AH48" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI48" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ48">
-        <v>1.09</v>
-      </c>
       <c r="AK48">
-        <v>2.3</v>
+        <v>1.48</v>
       </c>
       <c r="AL48">
         <v>0</v>
@@ -8264,12 +8264,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>EB - Streymur</t>
+          <t>KÍ</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Víkingur</t>
+          <t>B36</t>
         </is>
       </c>
       <c r="G49">
@@ -8296,64 +8296,64 @@
         </is>
       </c>
       <c r="N49">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="O49">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="P49">
-        <v>0</v>
+        <v>5.02</v>
       </c>
       <c r="Q49">
-        <v>5.75</v>
+        <v>2.15</v>
       </c>
       <c r="R49">
-        <v>2.36</v>
+        <v>2.28</v>
       </c>
       <c r="S49">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="T49">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="U49">
-        <v>2.25</v>
+        <v>2.45</v>
       </c>
       <c r="V49">
-        <v>1.57</v>
+        <v>1.4</v>
       </c>
       <c r="W49">
-        <v>1.14</v>
+        <v>1.06</v>
       </c>
       <c r="X49">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y49">
-        <v>1.12</v>
+        <v>1.23</v>
       </c>
       <c r="Z49">
-        <v>4.65</v>
+        <v>3.45</v>
       </c>
       <c r="AA49">
-        <v>1.55</v>
+        <v>1.8</v>
       </c>
       <c r="AB49">
-        <v>2.29</v>
+        <v>1.9</v>
       </c>
       <c r="AC49">
-        <v>2.28</v>
+        <v>2.92</v>
       </c>
       <c r="AD49">
-        <v>1.5</v>
+        <v>1.31</v>
       </c>
       <c r="AE49">
-        <v>1.19</v>
+        <v>1.08</v>
       </c>
       <c r="AF49">
-        <v>1.72</v>
+        <v>1.81</v>
       </c>
       <c r="AG49">
-        <v>1.98</v>
+        <v>1.88</v>
       </c>
       <c r="AH49" t="inlineStr">
         <is>
@@ -8369,7 +8369,7 @@
         <v>1.13</v>
       </c>
       <c r="AK49">
-        <v>1.06</v>
+        <v>2.3</v>
       </c>
       <c r="AL49">
         <v>0</v>
@@ -8417,22 +8417,22 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Brøndby</t>
+          <t>EB - Streymur</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Viborg</t>
+          <t>Víkingur</t>
         </is>
       </c>
       <c r="G50">
@@ -8459,80 +8459,80 @@
         </is>
       </c>
       <c r="N50">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="O50">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="P50">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="Q50">
-        <v>2.38</v>
+        <v>5.75</v>
       </c>
       <c r="R50">
-        <v>2.22</v>
+        <v>2.36</v>
       </c>
       <c r="S50">
-        <v>1.32</v>
+        <v>1.27</v>
       </c>
       <c r="T50">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="U50">
-        <v>2.4</v>
+        <v>2.27</v>
       </c>
       <c r="V50">
+        <v>1.53</v>
+      </c>
+      <c r="W50">
+        <v>1.09</v>
+      </c>
+      <c r="X50">
+        <v>1.01</v>
+      </c>
+      <c r="Y50">
+        <v>1.15</v>
+      </c>
+      <c r="Z50">
+        <v>4.65</v>
+      </c>
+      <c r="AA50">
+        <v>1.55</v>
+      </c>
+      <c r="AB50">
+        <v>2.29</v>
+      </c>
+      <c r="AC50">
+        <v>2.28</v>
+      </c>
+      <c r="AD50">
         <v>1.5</v>
       </c>
-      <c r="W50">
-        <v>1.11</v>
-      </c>
-      <c r="X50">
-        <v>1.04</v>
-      </c>
-      <c r="Y50">
-        <v>1.22</v>
-      </c>
-      <c r="Z50">
-        <v>4.28</v>
-      </c>
-      <c r="AA50">
-        <v>1.71</v>
-      </c>
-      <c r="AB50">
-        <v>2.16</v>
-      </c>
-      <c r="AC50">
-        <v>2.65</v>
-      </c>
-      <c r="AD50">
-        <v>1.46</v>
-      </c>
       <c r="AE50">
+        <v>1.19</v>
+      </c>
+      <c r="AF50">
+        <v>1.72</v>
+      </c>
+      <c r="AG50">
+        <v>1.96</v>
+      </c>
+      <c r="AH50" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI50" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ50">
         <v>1.13</v>
       </c>
-      <c r="AF50">
-        <v>1.55</v>
-      </c>
-      <c r="AG50">
-        <v>2.28</v>
-      </c>
-      <c r="AH50" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI50" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ50">
-        <v>1.29</v>
-      </c>
       <c r="AK50">
-        <v>1.92</v>
+        <v>1.06</v>
       </c>
       <c r="AL50">
         <v>0</v>
@@ -8580,22 +8580,22 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Kyzyl-Zhar</t>
+          <t>Brøndby</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Aktobe</t>
+          <t>Viborg</t>
         </is>
       </c>
       <c r="G51">
@@ -8622,64 +8622,64 @@
         </is>
       </c>
       <c r="N51">
-        <v>4.4</v>
+        <v>1.85</v>
       </c>
       <c r="O51">
-        <v>3.2</v>
+        <v>3.65</v>
       </c>
       <c r="P51">
-        <v>1.9</v>
+        <v>3.4</v>
       </c>
       <c r="Q51">
-        <v>5</v>
+        <v>2.38</v>
       </c>
       <c r="R51">
-        <v>1.98</v>
+        <v>2.22</v>
       </c>
       <c r="S51">
-        <v>1.4</v>
+        <v>1.32</v>
       </c>
       <c r="T51">
-        <v>2.75</v>
+        <v>3.1</v>
       </c>
       <c r="U51">
-        <v>2.9</v>
+        <v>2.4</v>
       </c>
       <c r="V51">
-        <v>1.35</v>
+        <v>1.5</v>
       </c>
       <c r="W51">
+        <v>1.11</v>
+      </c>
+      <c r="X51">
         <v>1.04</v>
       </c>
-      <c r="X51">
-        <v>1.03</v>
-      </c>
       <c r="Y51">
-        <v>1.36</v>
+        <v>1.22</v>
       </c>
       <c r="Z51">
-        <v>2.95</v>
+        <v>4.28</v>
       </c>
       <c r="AA51">
-        <v>2.06</v>
+        <v>1.71</v>
       </c>
       <c r="AB51">
-        <v>1.67</v>
+        <v>2.16</v>
       </c>
       <c r="AC51">
-        <v>4.1</v>
+        <v>2.65</v>
       </c>
       <c r="AD51">
-        <v>1.24</v>
+        <v>1.46</v>
       </c>
       <c r="AE51">
-        <v>1.04</v>
+        <v>1.13</v>
       </c>
       <c r="AF51">
-        <v>2</v>
+        <v>1.55</v>
       </c>
       <c r="AG51">
-        <v>1.73</v>
+        <v>2.28</v>
       </c>
       <c r="AH51" t="inlineStr">
         <is>
@@ -8692,10 +8692,10 @@
         </is>
       </c>
       <c r="AJ51">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="AK51">
-        <v>1.19</v>
+        <v>1.92</v>
       </c>
       <c r="AL51">
         <v>0</v>
@@ -9277,10 +9277,10 @@
         <v>1.42</v>
       </c>
       <c r="O55">
-        <v>4.45</v>
+        <v>4.2</v>
       </c>
       <c r="P55">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="Q55">
         <v>1.94</v>
@@ -9289,16 +9289,16 @@
         <v>2.5</v>
       </c>
       <c r="S55">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="T55">
-        <v>3.58</v>
+        <v>3.55</v>
       </c>
       <c r="U55">
-        <v>2.18</v>
+        <v>2.15</v>
       </c>
       <c r="V55">
-        <v>1.58</v>
+        <v>1.62</v>
       </c>
       <c r="W55">
         <v>1.12</v>
@@ -9307,31 +9307,31 @@
         <v>1.02</v>
       </c>
       <c r="Y55">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="Z55">
-        <v>4.8</v>
+        <v>5.09</v>
       </c>
       <c r="AA55">
         <v>1.57</v>
       </c>
       <c r="AB55">
-        <v>2.35</v>
+        <v>2.33</v>
       </c>
       <c r="AC55">
-        <v>2.33</v>
+        <v>2.28</v>
       </c>
       <c r="AD55">
-        <v>1.58</v>
+        <v>1.53</v>
       </c>
       <c r="AE55">
         <v>1.19</v>
       </c>
       <c r="AF55">
-        <v>1.63</v>
+        <v>1.65</v>
       </c>
       <c r="AG55">
-        <v>2.14</v>
+        <v>2.04</v>
       </c>
       <c r="AH55" t="inlineStr">
         <is>
@@ -9344,10 +9344,10 @@
         </is>
       </c>
       <c r="AJ55">
-        <v>1.17</v>
+        <v>1.13</v>
       </c>
       <c r="AK55">
-        <v>2.7</v>
+        <v>2.59</v>
       </c>
       <c r="AL55">
         <v>0</v>
@@ -9763,43 +9763,43 @@
         </is>
       </c>
       <c r="N58">
-        <v>3.4</v>
+        <v>3.7</v>
       </c>
       <c r="O58">
-        <v>3.5</v>
+        <v>3.7</v>
       </c>
       <c r="P58">
         <v>1.87</v>
       </c>
       <c r="Q58">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="R58">
-        <v>2.24</v>
+        <v>2.25</v>
       </c>
       <c r="S58">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="T58">
         <v>3.3</v>
       </c>
       <c r="U58">
-        <v>2.52</v>
+        <v>2.4</v>
       </c>
       <c r="V58">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="W58">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="X58">
         <v>1.04</v>
       </c>
       <c r="Y58">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="Z58">
-        <v>4.44</v>
+        <v>4.1</v>
       </c>
       <c r="AA58">
         <v>1.66</v>
@@ -9808,19 +9808,19 @@
         <v>2.15</v>
       </c>
       <c r="AC58">
-        <v>2.57</v>
+        <v>2.68</v>
       </c>
       <c r="AD58">
-        <v>1.41</v>
+        <v>1.47</v>
       </c>
       <c r="AE58">
-        <v>1.12</v>
+        <v>1.18</v>
       </c>
       <c r="AF58">
         <v>1.58</v>
       </c>
       <c r="AG58">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="AH58" t="inlineStr">
         <is>
@@ -9833,7 +9833,7 @@
         </is>
       </c>
       <c r="AJ58">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="AK58">
         <v>1.25</v>
@@ -9926,28 +9926,28 @@
         </is>
       </c>
       <c r="N59">
-        <v>1.62</v>
+        <v>1.72</v>
       </c>
       <c r="O59">
-        <v>3.78</v>
+        <v>3.9</v>
       </c>
       <c r="P59">
-        <v>4.1</v>
+        <v>4.5</v>
       </c>
       <c r="Q59">
-        <v>2.04</v>
+        <v>2.19</v>
       </c>
       <c r="R59">
-        <v>2.21</v>
+        <v>2.46</v>
       </c>
       <c r="S59">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="T59">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="U59">
-        <v>2.39</v>
+        <v>2.4</v>
       </c>
       <c r="V59">
         <v>1.45</v>
@@ -9956,10 +9956,10 @@
         <v>1.08</v>
       </c>
       <c r="X59">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y59">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="Z59">
         <v>4.1</v>
@@ -9968,22 +9968,22 @@
         <v>1.7</v>
       </c>
       <c r="AB59">
-        <v>2.04</v>
+        <v>2.1</v>
       </c>
       <c r="AC59">
-        <v>2.8</v>
+        <v>2.57</v>
       </c>
       <c r="AD59">
         <v>1.4</v>
       </c>
       <c r="AE59">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="AF59">
-        <v>1.67</v>
+        <v>1.74</v>
       </c>
       <c r="AG59">
-        <v>2.08</v>
+        <v>1.93</v>
       </c>
       <c r="AH59" t="inlineStr">
         <is>
@@ -9996,7 +9996,7 @@
         </is>
       </c>
       <c r="AJ59">
-        <v>1.2</v>
+        <v>1.16</v>
       </c>
       <c r="AK59">
         <v>2.1</v>
@@ -10098,13 +10098,13 @@
         <v>4.43</v>
       </c>
       <c r="Q60">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="R60">
-        <v>2.38</v>
+        <v>2.71</v>
       </c>
       <c r="S60">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="T60">
         <v>4</v>
@@ -10119,7 +10119,7 @@
         <v>1.17</v>
       </c>
       <c r="X60">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y60">
         <v>1.08</v>
@@ -10131,22 +10131,22 @@
         <v>1.4</v>
       </c>
       <c r="AB60">
-        <v>2.75</v>
+        <v>2.78</v>
       </c>
       <c r="AC60">
         <v>2.12</v>
       </c>
       <c r="AD60">
-        <v>1.69</v>
+        <v>1.74</v>
       </c>
       <c r="AE60">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="AF60">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="AG60">
-        <v>2.5</v>
+        <v>2.55</v>
       </c>
       <c r="AH60" t="inlineStr">
         <is>
@@ -10162,7 +10162,7 @@
         <v>1.17</v>
       </c>
       <c r="AK60">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="AL60">
         <v>0</v>
@@ -11758,10 +11758,10 @@
         <v>2.9</v>
       </c>
       <c r="AA70">
+        <v>1.87</v>
+      </c>
+      <c r="AB70">
         <v>1.9</v>
-      </c>
-      <c r="AB70">
-        <v>1.87</v>
       </c>
       <c r="AC70">
         <v>3.5</v>
@@ -11773,10 +11773,10 @@
         <v>1.15</v>
       </c>
       <c r="AF70">
-        <v>2.15</v>
+        <v>1.65</v>
       </c>
       <c r="AG70">
-        <v>1.64</v>
+        <v>1.96</v>
       </c>
       <c r="AH70" t="inlineStr">
         <is>
@@ -11792,7 +11792,7 @@
         <v>1.27</v>
       </c>
       <c r="AK70">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="AL70">
         <v>0</v>
@@ -13693,13 +13693,13 @@
         <v>1.36</v>
       </c>
       <c r="T82">
-        <v>2.8</v>
+        <v>2.75</v>
       </c>
       <c r="U82">
-        <v>2.99</v>
+        <v>2.88</v>
       </c>
       <c r="V82">
-        <v>1.34</v>
+        <v>1.38</v>
       </c>
       <c r="W82">
         <v>1.08</v>
@@ -13708,10 +13708,10 @@
         <v>1.01</v>
       </c>
       <c r="Y82">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="Z82">
-        <v>3.2</v>
+        <v>3.22</v>
       </c>
       <c r="AA82">
         <v>2.03</v>
@@ -13723,7 +13723,7 @@
         <v>3.55</v>
       </c>
       <c r="AD82">
-        <v>1.28</v>
+        <v>1.23</v>
       </c>
       <c r="AE82">
         <v>1.04</v>
@@ -13732,7 +13732,7 @@
         <v>1.89</v>
       </c>
       <c r="AG82">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="AH82" t="inlineStr">
         <is>
@@ -13748,7 +13748,7 @@
         <v>1.17</v>
       </c>
       <c r="AK82">
-        <v>2.02</v>
+        <v>1.88</v>
       </c>
       <c r="AL82">
         <v>0</v>
@@ -14132,12 +14132,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Vaprus</t>
+          <t>Tallinna FC Flora</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Tallinna FC Levadia</t>
+          <t>Harju Jalgpallikool</t>
         </is>
       </c>
       <c r="G85">
@@ -14164,64 +14164,64 @@
         </is>
       </c>
       <c r="N85">
-        <v>11.7</v>
+        <v>1.48</v>
       </c>
       <c r="O85">
-        <v>5.75</v>
+        <v>4.2</v>
       </c>
       <c r="P85">
-        <v>1.22</v>
+        <v>5.25</v>
       </c>
       <c r="Q85">
-        <v>8.91</v>
+        <v>1.83</v>
       </c>
       <c r="R85">
-        <v>3.02</v>
+        <v>2.8</v>
       </c>
       <c r="S85">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="T85">
-        <v>3.9</v>
+        <v>3.58</v>
       </c>
       <c r="U85">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="V85">
-        <v>1.71</v>
+        <v>1.69</v>
       </c>
       <c r="W85">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="X85">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y85">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="Z85">
-        <v>5.25</v>
+        <v>5.5</v>
       </c>
       <c r="AA85">
-        <v>1.41</v>
+        <v>1.44</v>
       </c>
       <c r="AB85">
-        <v>2.52</v>
+        <v>2.7</v>
       </c>
       <c r="AC85">
         <v>2.11</v>
       </c>
       <c r="AD85">
-        <v>1.65</v>
+        <v>1.73</v>
       </c>
       <c r="AE85">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="AF85">
-        <v>1.85</v>
+        <v>1.5</v>
       </c>
       <c r="AG85">
-        <v>1.85</v>
+        <v>2.3</v>
       </c>
       <c r="AH85" t="inlineStr">
         <is>
@@ -14234,10 +14234,10 @@
         </is>
       </c>
       <c r="AJ85">
-        <v>3.66</v>
+        <v>1.14</v>
       </c>
       <c r="AK85">
-        <v>1.05</v>
+        <v>2.63</v>
       </c>
       <c r="AL85">
         <v>0</v>
@@ -14295,12 +14295,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Tallinna FC Flora</t>
+          <t>Vaprus</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Harju Jalgpallikool</t>
+          <t>Tallinna FC Levadia</t>
         </is>
       </c>
       <c r="G86">
@@ -14327,64 +14327,64 @@
         </is>
       </c>
       <c r="N86">
-        <v>1.48</v>
+        <v>11.7</v>
       </c>
       <c r="O86">
-        <v>4.2</v>
+        <v>5.75</v>
       </c>
       <c r="P86">
+        <v>1.22</v>
+      </c>
+      <c r="Q86">
+        <v>8.91</v>
+      </c>
+      <c r="R86">
+        <v>3.02</v>
+      </c>
+      <c r="S86">
+        <v>1.2</v>
+      </c>
+      <c r="T86">
+        <v>3.9</v>
+      </c>
+      <c r="U86">
+        <v>2.05</v>
+      </c>
+      <c r="V86">
+        <v>1.71</v>
+      </c>
+      <c r="W86">
+        <v>1.18</v>
+      </c>
+      <c r="X86">
+        <v>1.01</v>
+      </c>
+      <c r="Y86">
+        <v>1.1</v>
+      </c>
+      <c r="Z86">
         <v>5.25</v>
       </c>
-      <c r="Q86">
-        <v>1.83</v>
-      </c>
-      <c r="R86">
-        <v>2.8</v>
-      </c>
-      <c r="S86">
-        <v>1.21</v>
-      </c>
-      <c r="T86">
-        <v>3.58</v>
-      </c>
-      <c r="U86">
-        <v>2.1</v>
-      </c>
-      <c r="V86">
-        <v>1.69</v>
-      </c>
-      <c r="W86">
-        <v>1.17</v>
-      </c>
-      <c r="X86">
-        <v>1.02</v>
-      </c>
-      <c r="Y86">
-        <v>1.09</v>
-      </c>
-      <c r="Z86">
-        <v>5.5</v>
-      </c>
       <c r="AA86">
-        <v>1.44</v>
+        <v>1.41</v>
       </c>
       <c r="AB86">
-        <v>2.7</v>
+        <v>2.52</v>
       </c>
       <c r="AC86">
         <v>2.11</v>
       </c>
       <c r="AD86">
-        <v>1.73</v>
+        <v>1.65</v>
       </c>
       <c r="AE86">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="AF86">
-        <v>1.5</v>
+        <v>1.85</v>
       </c>
       <c r="AG86">
-        <v>2.3</v>
+        <v>1.85</v>
       </c>
       <c r="AH86" t="inlineStr">
         <is>
@@ -14397,10 +14397,10 @@
         </is>
       </c>
       <c r="AJ86">
-        <v>1.14</v>
+        <v>3.66</v>
       </c>
       <c r="AK86">
-        <v>2.63</v>
+        <v>1.05</v>
       </c>
       <c r="AL86">
         <v>0</v>
@@ -14825,10 +14825,10 @@
         <v>0</v>
       </c>
       <c r="Q89">
-        <v>2.6</v>
+        <v>2.61</v>
       </c>
       <c r="R89">
-        <v>2.3</v>
+        <v>2.22</v>
       </c>
       <c r="S89">
         <v>1.27</v>
@@ -14849,28 +14849,28 @@
         <v>1.02</v>
       </c>
       <c r="Y89">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="Z89">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="AA89">
-        <v>1.57</v>
+        <v>1.61</v>
       </c>
       <c r="AB89">
-        <v>2.16</v>
+        <v>2.17</v>
       </c>
       <c r="AC89">
-        <v>2.43</v>
+        <v>2.49</v>
       </c>
       <c r="AD89">
         <v>1.45</v>
       </c>
       <c r="AE89">
-        <v>1.13</v>
+        <v>1.16</v>
       </c>
       <c r="AF89">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
       <c r="AG89">
         <v>2.3</v>
@@ -14886,10 +14886,10 @@
         </is>
       </c>
       <c r="AJ89">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="AK89">
-        <v>1.61</v>
+        <v>1.67</v>
       </c>
       <c r="AL89">
         <v>0</v>
@@ -15142,13 +15142,13 @@
         </is>
       </c>
       <c r="N91">
-        <v>3.08</v>
+        <v>3.25</v>
       </c>
       <c r="O91">
         <v>3.5</v>
       </c>
       <c r="P91">
-        <v>1.98</v>
+        <v>2.03</v>
       </c>
       <c r="Q91">
         <v>3.8</v>
@@ -15157,46 +15157,46 @@
         <v>2.28</v>
       </c>
       <c r="S91">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="T91">
         <v>3.2</v>
       </c>
       <c r="U91">
-        <v>2.55</v>
+        <v>2.75</v>
       </c>
       <c r="V91">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="W91">
         <v>1.1</v>
       </c>
       <c r="X91">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y91">
-        <v>1.27</v>
+        <v>1.22</v>
       </c>
       <c r="Z91">
-        <v>3.71</v>
+        <v>3.5</v>
       </c>
       <c r="AA91">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="AB91">
-        <v>1.95</v>
+        <v>1.9</v>
       </c>
       <c r="AC91">
         <v>3</v>
       </c>
       <c r="AD91">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="AE91">
         <v>1.13</v>
       </c>
       <c r="AF91">
-        <v>1.7</v>
+        <v>1.68</v>
       </c>
       <c r="AG91">
         <v>2.05</v>
@@ -16283,22 +16283,22 @@
         </is>
       </c>
       <c r="N98">
-        <v>1.83</v>
+        <v>1.9</v>
       </c>
       <c r="O98">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="P98">
-        <v>3.3</v>
+        <v>3.76</v>
       </c>
       <c r="Q98">
         <v>2.2</v>
       </c>
       <c r="R98">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="S98">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="T98">
         <v>3.75</v>
@@ -16316,10 +16316,10 @@
         <v>1.02</v>
       </c>
       <c r="Y98">
-        <v>1.13</v>
+        <v>1.1</v>
       </c>
       <c r="Z98">
-        <v>5.25</v>
+        <v>5.15</v>
       </c>
       <c r="AA98">
         <v>1.5</v>
@@ -16328,13 +16328,13 @@
         <v>2.55</v>
       </c>
       <c r="AC98">
-        <v>2.24</v>
+        <v>2.25</v>
       </c>
       <c r="AD98">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="AE98">
-        <v>1.26</v>
+        <v>1.22</v>
       </c>
       <c r="AF98">
         <v>1.44</v>
@@ -16353,7 +16353,7 @@
         </is>
       </c>
       <c r="AJ98">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AK98">
         <v>1.95</v>
@@ -16778,58 +16778,58 @@
         <v>4.2</v>
       </c>
       <c r="P101">
-        <v>4.75</v>
+        <v>4.9</v>
       </c>
       <c r="Q101">
-        <v>2.01</v>
+        <v>2.08</v>
       </c>
       <c r="R101">
+        <v>2.21</v>
+      </c>
+      <c r="S101">
+        <v>1.28</v>
+      </c>
+      <c r="T101">
+        <v>3.3</v>
+      </c>
+      <c r="U101">
         <v>2.38</v>
       </c>
-      <c r="S101">
-        <v>1.25</v>
-      </c>
-      <c r="T101">
-        <v>3.6</v>
-      </c>
-      <c r="U101">
-        <v>2.25</v>
-      </c>
       <c r="V101">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="W101">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="X101">
         <v>1.01</v>
       </c>
       <c r="Y101">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="Z101">
-        <v>4.69</v>
+        <v>4.4</v>
       </c>
       <c r="AA101">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="AB101">
-        <v>2.25</v>
+        <v>2.05</v>
       </c>
       <c r="AC101">
-        <v>2.6</v>
+        <v>2.48</v>
       </c>
       <c r="AD101">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="AE101">
-        <v>1.18</v>
+        <v>1.14</v>
       </c>
       <c r="AF101">
-        <v>1.68</v>
+        <v>1.73</v>
       </c>
       <c r="AG101">
-        <v>2.06</v>
+        <v>1.92</v>
       </c>
       <c r="AH101" t="inlineStr">
         <is>
@@ -16842,10 +16842,10 @@
         </is>
       </c>
       <c r="AJ101">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="AK101">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="AL101">
         <v>0</v>
@@ -17261,7 +17261,7 @@
         </is>
       </c>
       <c r="N104">
-        <v>2.17</v>
+        <v>2.23</v>
       </c>
       <c r="O104">
         <v>2.7</v>
@@ -17424,7 +17424,7 @@
         </is>
       </c>
       <c r="N105">
-        <v>2.65</v>
+        <v>2.55</v>
       </c>
       <c r="O105">
         <v>2.65</v>
@@ -17463,10 +17463,10 @@
         <v>2.1</v>
       </c>
       <c r="AA105">
-        <v>2.87</v>
+        <v>3.1</v>
       </c>
       <c r="AB105">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AC105">
         <v>0</v>
@@ -17590,16 +17590,16 @@
         <v>2.3</v>
       </c>
       <c r="O106">
-        <v>2.5</v>
+        <v>2.45</v>
       </c>
       <c r="P106">
-        <v>3.6</v>
+        <v>3.85</v>
       </c>
       <c r="Q106">
-        <v>3.3</v>
+        <v>3.29</v>
       </c>
       <c r="R106">
-        <v>1.73</v>
+        <v>1.62</v>
       </c>
       <c r="S106">
         <v>1.8</v>
@@ -17608,10 +17608,10 @@
         <v>1.9</v>
       </c>
       <c r="U106">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="V106">
-        <v>1.13</v>
+        <v>1.17</v>
       </c>
       <c r="W106">
         <v>1.02</v>
@@ -17626,7 +17626,7 @@
         <v>1.98</v>
       </c>
       <c r="AA106">
-        <v>3.5</v>
+        <v>3.28</v>
       </c>
       <c r="AB106">
         <v>1.27</v>
@@ -17657,7 +17657,7 @@
         </is>
       </c>
       <c r="AJ106">
-        <v>1.25</v>
+        <v>1.42</v>
       </c>
       <c r="AK106">
         <v>1.49</v>
@@ -17753,58 +17753,58 @@
         <v>2.17</v>
       </c>
       <c r="O107">
-        <v>2.7</v>
+        <v>2.75</v>
       </c>
       <c r="P107">
-        <v>3.3</v>
+        <v>3.7</v>
       </c>
       <c r="Q107">
-        <v>3.01</v>
+        <v>2.9</v>
       </c>
       <c r="R107">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="S107">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="T107">
-        <v>2.19</v>
+        <v>2.21</v>
       </c>
       <c r="U107">
         <v>3.9</v>
       </c>
       <c r="V107">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="W107">
         <v>1.03</v>
       </c>
       <c r="X107">
-        <v>1.13</v>
+        <v>1.1</v>
       </c>
       <c r="Y107">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="Z107">
-        <v>2.17</v>
+        <v>2.19</v>
       </c>
       <c r="AA107">
-        <v>2.78</v>
+        <v>2.74</v>
       </c>
       <c r="AB107">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="AC107">
-        <v>6.12</v>
+        <v>6.5</v>
       </c>
       <c r="AD107">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="AE107">
         <v>1.03</v>
       </c>
       <c r="AF107">
-        <v>2.3</v>
+        <v>2.23</v>
       </c>
       <c r="AG107">
         <v>1.57</v>
@@ -17820,10 +17820,10 @@
         </is>
       </c>
       <c r="AJ107">
-        <v>1.33</v>
+        <v>1.19</v>
       </c>
       <c r="AK107">
-        <v>1.53</v>
+        <v>1.59</v>
       </c>
       <c r="AL107">
         <v>0</v>
@@ -18094,7 +18094,7 @@
         <v>1.31</v>
       </c>
       <c r="T109">
-        <v>3.02</v>
+        <v>3.26</v>
       </c>
       <c r="U109">
         <v>2.63</v>
@@ -18103,13 +18103,13 @@
         <v>1.46</v>
       </c>
       <c r="W109">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="X109">
         <v>1.03</v>
       </c>
       <c r="Y109">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="Z109">
         <v>4</v>
@@ -18133,7 +18133,7 @@
         <v>2.12</v>
       </c>
       <c r="AG109">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="AH109" t="inlineStr">
         <is>
@@ -18207,12 +18207,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Sutjeska</t>
+          <t>FK Jezero Plav</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Budućnost</t>
+          <t>Mornar</t>
         </is>
       </c>
       <c r="G110">
@@ -18239,13 +18239,13 @@
         </is>
       </c>
       <c r="N110">
-        <v>1.91</v>
+        <v>4.6</v>
       </c>
       <c r="O110">
-        <v>3.25</v>
+        <v>3.08</v>
       </c>
       <c r="P110">
-        <v>3.6</v>
+        <v>1.8</v>
       </c>
       <c r="Q110">
         <v>0</v>
@@ -18278,10 +18278,10 @@
         <v>0</v>
       </c>
       <c r="AA110">
-        <v>2.15</v>
+        <v>2.35</v>
       </c>
       <c r="AB110">
-        <v>1.66</v>
+        <v>1.57</v>
       </c>
       <c r="AC110">
         <v>0</v>
@@ -18370,12 +18370,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>FK Jezero Plav</t>
+          <t>Dečić</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Mornar</t>
+          <t>Arsenal Tivat</t>
         </is>
       </c>
       <c r="G111">
@@ -18402,13 +18402,13 @@
         </is>
       </c>
       <c r="N111">
-        <v>4.6</v>
+        <v>1.76</v>
       </c>
       <c r="O111">
-        <v>3.08</v>
+        <v>3.2</v>
       </c>
       <c r="P111">
-        <v>1.8</v>
+        <v>4.3</v>
       </c>
       <c r="Q111">
         <v>0</v>
@@ -18533,12 +18533,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Dečić</t>
+          <t>Mladost DG</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Arsenal Tivat</t>
+          <t>Otrant-Olympic</t>
         </is>
       </c>
       <c r="G112">
@@ -18565,13 +18565,13 @@
         </is>
       </c>
       <c r="N112">
-        <v>1.76</v>
+        <v>2.12</v>
       </c>
       <c r="O112">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="P112">
-        <v>4.3</v>
+        <v>3.32</v>
       </c>
       <c r="Q112">
         <v>0</v>
@@ -18604,10 +18604,10 @@
         <v>0</v>
       </c>
       <c r="AA112">
-        <v>2.35</v>
+        <v>1.95</v>
       </c>
       <c r="AB112">
-        <v>1.57</v>
+        <v>1.85</v>
       </c>
       <c r="AC112">
         <v>0</v>
@@ -18681,12 +18681,12 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -18696,12 +18696,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Mladost DG</t>
+          <t>Olimpija</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Otrant-Olympic</t>
+          <t>Aluminij</t>
         </is>
       </c>
       <c r="G113">
@@ -18728,65 +18728,65 @@
         </is>
       </c>
       <c r="N113">
-        <v>2.12</v>
+        <v>1.63</v>
       </c>
       <c r="O113">
-        <v>3.3</v>
+        <v>3.8</v>
       </c>
       <c r="P113">
-        <v>3.32</v>
+        <v>4.4</v>
       </c>
       <c r="Q113">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="R113">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="S113">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="T113">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="U113">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="V113">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="W113">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X113">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y113">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z113">
-        <v>0</v>
+        <v>4.06</v>
       </c>
       <c r="AA113">
+        <v>1.72</v>
+      </c>
+      <c r="AB113">
+        <v>2.09</v>
+      </c>
+      <c r="AC113">
+        <v>2.69</v>
+      </c>
+      <c r="AD113">
+        <v>1.4</v>
+      </c>
+      <c r="AE113">
+        <v>1.1</v>
+      </c>
+      <c r="AF113">
+        <v>1.7</v>
+      </c>
+      <c r="AG113">
         <v>1.95</v>
       </c>
-      <c r="AB113">
-        <v>1.85</v>
-      </c>
-      <c r="AC113">
-        <v>0</v>
-      </c>
-      <c r="AD113">
-        <v>0</v>
-      </c>
-      <c r="AE113">
-        <v>0</v>
-      </c>
-      <c r="AF113">
-        <v>0</v>
-      </c>
-      <c r="AG113">
-        <v>0</v>
-      </c>
       <c r="AH113" t="inlineStr">
         <is>
           <t>[]</t>
@@ -18798,10 +18798,10 @@
         </is>
       </c>
       <c r="AJ113">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AK113">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AL113">
         <v>0</v>
@@ -18832,7 +18832,7 @@
       </c>
       <c r="AU113" t="inlineStr">
         <is>
-          <t>2026-08-02 15:00:00</t>
+          <t>2026-08-02 15:15:00</t>
         </is>
       </c>
     </row>
@@ -18859,12 +18859,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Olimpija</t>
+          <t>Brinje-Grosuplje</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Aluminij</t>
+          <t>Koper</t>
         </is>
       </c>
       <c r="G114">
@@ -18891,64 +18891,64 @@
         </is>
       </c>
       <c r="N114">
-        <v>1.63</v>
+        <v>3.85</v>
       </c>
       <c r="O114">
-        <v>3.8</v>
+        <v>3.4</v>
       </c>
       <c r="P114">
-        <v>4.4</v>
+        <v>1.89</v>
       </c>
       <c r="Q114">
-        <v>2.15</v>
+        <v>4.49</v>
       </c>
       <c r="R114">
-        <v>2.28</v>
+        <v>2.2</v>
       </c>
       <c r="S114">
-        <v>1.28</v>
+        <v>1.35</v>
       </c>
       <c r="T114">
-        <v>3.4</v>
+        <v>2.95</v>
       </c>
       <c r="U114">
-        <v>2.5</v>
+        <v>2.63</v>
       </c>
       <c r="V114">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="W114">
-        <v>1.12</v>
+        <v>1.1</v>
       </c>
       <c r="X114">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y114">
         <v>1.22</v>
       </c>
       <c r="Z114">
-        <v>4.06</v>
+        <v>3.69</v>
       </c>
       <c r="AA114">
-        <v>1.72</v>
+        <v>1.83</v>
       </c>
       <c r="AB114">
-        <v>2.09</v>
+        <v>1.89</v>
       </c>
       <c r="AC114">
-        <v>2.69</v>
+        <v>3</v>
       </c>
       <c r="AD114">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="AE114">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="AF114">
         <v>1.7</v>
       </c>
       <c r="AG114">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="AH114" t="inlineStr">
         <is>
@@ -18961,10 +18961,10 @@
         </is>
       </c>
       <c r="AJ114">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="AK114">
-        <v>2.16</v>
+        <v>1.17</v>
       </c>
       <c r="AL114">
         <v>0</v>
@@ -19012,7 +19012,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -19022,12 +19022,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Brinje-Grosuplje</t>
+          <t>GKS Katowice</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Koper</t>
+          <t>Radomiak Radom</t>
         </is>
       </c>
       <c r="G115">
@@ -19054,64 +19054,64 @@
         </is>
       </c>
       <c r="N115">
-        <v>3.85</v>
+        <v>1.94</v>
       </c>
       <c r="O115">
-        <v>3.4</v>
+        <v>3.44</v>
       </c>
       <c r="P115">
-        <v>1.89</v>
+        <v>3.74</v>
       </c>
       <c r="Q115">
-        <v>4.49</v>
+        <v>2.47</v>
       </c>
       <c r="R115">
-        <v>2.2</v>
+        <v>2.11</v>
       </c>
       <c r="S115">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="T115">
-        <v>2.95</v>
+        <v>2.88</v>
       </c>
       <c r="U115">
-        <v>2.63</v>
+        <v>2.62</v>
       </c>
       <c r="V115">
-        <v>1.48</v>
+        <v>1.44</v>
       </c>
       <c r="W115">
         <v>1.1</v>
       </c>
       <c r="X115">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y115">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="Z115">
-        <v>3.69</v>
+        <v>3.76</v>
       </c>
       <c r="AA115">
         <v>1.83</v>
       </c>
       <c r="AB115">
-        <v>1.89</v>
+        <v>1.97</v>
       </c>
       <c r="AC115">
-        <v>3</v>
+        <v>2.88</v>
       </c>
       <c r="AD115">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="AE115">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="AF115">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="AG115">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="AH115" t="inlineStr">
         <is>
@@ -19124,10 +19124,10 @@
         </is>
       </c>
       <c r="AJ115">
-        <v>1.22</v>
+        <v>1.27</v>
       </c>
       <c r="AK115">
-        <v>1.17</v>
+        <v>1.75</v>
       </c>
       <c r="AL115">
         <v>0</v>
@@ -19175,7 +19175,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -19185,12 +19185,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>GKS Katowice</t>
+          <t>Ferencváros</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Radomiak Radom</t>
+          <t>Vasas</t>
         </is>
       </c>
       <c r="G116">
@@ -19217,64 +19217,64 @@
         </is>
       </c>
       <c r="N116">
-        <v>1.94</v>
+        <v>1.44</v>
       </c>
       <c r="O116">
-        <v>3.44</v>
+        <v>4.3</v>
       </c>
       <c r="P116">
-        <v>3.74</v>
+        <v>5.79</v>
       </c>
       <c r="Q116">
-        <v>2.47</v>
+        <v>1.95</v>
       </c>
       <c r="R116">
-        <v>2.11</v>
+        <v>2.5</v>
       </c>
       <c r="S116">
-        <v>1.36</v>
+        <v>1.27</v>
       </c>
       <c r="T116">
-        <v>2.88</v>
+        <v>3.25</v>
       </c>
       <c r="U116">
-        <v>2.62</v>
+        <v>2.25</v>
       </c>
       <c r="V116">
-        <v>1.44</v>
+        <v>1.6</v>
       </c>
       <c r="W116">
-        <v>1.1</v>
+        <v>1.15</v>
       </c>
       <c r="X116">
         <v>1.01</v>
       </c>
       <c r="Y116">
-        <v>1.24</v>
+        <v>1.14</v>
       </c>
       <c r="Z116">
-        <v>3.76</v>
+        <v>4.4</v>
       </c>
       <c r="AA116">
-        <v>1.83</v>
+        <v>1.6</v>
       </c>
       <c r="AB116">
-        <v>1.97</v>
+        <v>2.14</v>
       </c>
       <c r="AC116">
-        <v>2.88</v>
+        <v>2.43</v>
       </c>
       <c r="AD116">
-        <v>1.32</v>
+        <v>1.45</v>
       </c>
       <c r="AE116">
-        <v>1.09</v>
+        <v>1.14</v>
       </c>
       <c r="AF116">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="AG116">
-        <v>2.05</v>
+        <v>2.01</v>
       </c>
       <c r="AH116" t="inlineStr">
         <is>
@@ -19287,10 +19287,10 @@
         </is>
       </c>
       <c r="AJ116">
-        <v>1.27</v>
+        <v>1.07</v>
       </c>
       <c r="AK116">
-        <v>1.75</v>
+        <v>2.4</v>
       </c>
       <c r="AL116">
         <v>0</v>
@@ -19338,7 +19338,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -19348,12 +19348,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Ferencváros</t>
+          <t>CSKA Sofia</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Vasas</t>
+          <t>Dunav 2010</t>
         </is>
       </c>
       <c r="G117">
@@ -19380,64 +19380,64 @@
         </is>
       </c>
       <c r="N117">
-        <v>1.44</v>
+        <v>1.17</v>
       </c>
       <c r="O117">
-        <v>4.3</v>
+        <v>5.5</v>
       </c>
       <c r="P117">
-        <v>5.79</v>
+        <v>9.5</v>
       </c>
       <c r="Q117">
-        <v>1.95</v>
+        <v>1.68</v>
       </c>
       <c r="R117">
         <v>2.5</v>
       </c>
       <c r="S117">
+        <v>1.35</v>
+      </c>
+      <c r="T117">
+        <v>3.1</v>
+      </c>
+      <c r="U117">
+        <v>2.59</v>
+      </c>
+      <c r="V117">
+        <v>1.44</v>
+      </c>
+      <c r="W117">
+        <v>1.1</v>
+      </c>
+      <c r="X117">
+        <v>1</v>
+      </c>
+      <c r="Y117">
         <v>1.27</v>
       </c>
-      <c r="T117">
-        <v>3.25</v>
-      </c>
-      <c r="U117">
-        <v>2.25</v>
-      </c>
-      <c r="V117">
-        <v>1.6</v>
-      </c>
-      <c r="W117">
-        <v>1.15</v>
-      </c>
-      <c r="X117">
-        <v>1.01</v>
-      </c>
-      <c r="Y117">
-        <v>1.14</v>
-      </c>
       <c r="Z117">
-        <v>4.4</v>
+        <v>3.56</v>
       </c>
       <c r="AA117">
-        <v>1.6</v>
+        <v>1.72</v>
       </c>
       <c r="AB117">
-        <v>2.14</v>
+        <v>1.96</v>
       </c>
       <c r="AC117">
-        <v>2.43</v>
+        <v>2.8</v>
       </c>
       <c r="AD117">
-        <v>1.45</v>
+        <v>1.36</v>
       </c>
       <c r="AE117">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="AF117">
-        <v>1.7</v>
+        <v>2.49</v>
       </c>
       <c r="AG117">
-        <v>2.01</v>
+        <v>1.48</v>
       </c>
       <c r="AH117" t="inlineStr">
         <is>
@@ -19450,10 +19450,10 @@
         </is>
       </c>
       <c r="AJ117">
-        <v>1.07</v>
+        <v>1.03</v>
       </c>
       <c r="AK117">
-        <v>2.4</v>
+        <v>3.68</v>
       </c>
       <c r="AL117">
         <v>0</v>
@@ -19496,27 +19496,27 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>CSKA Sofia</t>
+          <t>Temperley</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Dunav 2010</t>
+          <t>Gimnasia y Tiro</t>
         </is>
       </c>
       <c r="G118">
@@ -19543,80 +19543,80 @@
         </is>
       </c>
       <c r="N118">
-        <v>1.17</v>
+        <v>2.05</v>
       </c>
       <c r="O118">
-        <v>5.5</v>
+        <v>2.75</v>
       </c>
       <c r="P118">
-        <v>9.5</v>
+        <v>4</v>
       </c>
       <c r="Q118">
-        <v>1.68</v>
+        <v>3</v>
       </c>
       <c r="R118">
-        <v>2.5</v>
+        <v>1.85</v>
       </c>
       <c r="S118">
-        <v>1.35</v>
+        <v>1.69</v>
       </c>
       <c r="T118">
-        <v>3.1</v>
+        <v>1.99</v>
       </c>
       <c r="U118">
-        <v>2.59</v>
+        <v>4</v>
       </c>
       <c r="V118">
-        <v>1.44</v>
+        <v>1.15</v>
       </c>
       <c r="W118">
+        <v>1.03</v>
+      </c>
+      <c r="X118">
+        <v>1.15</v>
+      </c>
+      <c r="Y118">
+        <v>1.67</v>
+      </c>
+      <c r="Z118">
+        <v>2.08</v>
+      </c>
+      <c r="AA118">
+        <v>2.97</v>
+      </c>
+      <c r="AB118">
+        <v>1.32</v>
+      </c>
+      <c r="AC118">
+        <v>6.39</v>
+      </c>
+      <c r="AD118">
         <v>1.1</v>
       </c>
-      <c r="X118">
-        <v>1</v>
-      </c>
-      <c r="Y118">
-        <v>1.27</v>
-      </c>
-      <c r="Z118">
-        <v>3.56</v>
-      </c>
-      <c r="AA118">
-        <v>1.72</v>
-      </c>
-      <c r="AB118">
-        <v>1.96</v>
-      </c>
-      <c r="AC118">
-        <v>2.8</v>
-      </c>
-      <c r="AD118">
+      <c r="AE118">
+        <v>1.02</v>
+      </c>
+      <c r="AF118">
+        <v>2.3</v>
+      </c>
+      <c r="AG118">
+        <v>1.5</v>
+      </c>
+      <c r="AH118" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI118" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ118">
         <v>1.36</v>
       </c>
-      <c r="AE118">
-        <v>1.12</v>
-      </c>
-      <c r="AF118">
-        <v>2.49</v>
-      </c>
-      <c r="AG118">
-        <v>1.48</v>
-      </c>
-      <c r="AH118" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI118" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ118">
-        <v>1.03</v>
-      </c>
       <c r="AK118">
-        <v>3.68</v>
+        <v>1.63</v>
       </c>
       <c r="AL118">
         <v>0</v>
@@ -19647,7 +19647,7 @@
       </c>
       <c r="AU118" t="inlineStr">
         <is>
-          <t>2026-08-02 15:15:00</t>
+          <t>2026-08-02 15:30:00</t>
         </is>
       </c>
     </row>
@@ -19674,12 +19674,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Temperley</t>
+          <t>Deportivo Maipú</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Gimnasia y Tiro</t>
+          <t>Atlanta</t>
         </is>
       </c>
       <c r="G119">
@@ -19706,64 +19706,64 @@
         </is>
       </c>
       <c r="N119">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="O119">
-        <v>2.75</v>
+        <v>2.9</v>
       </c>
       <c r="P119">
-        <v>3.9</v>
+        <v>2.9</v>
       </c>
       <c r="Q119">
-        <v>3</v>
+        <v>3.4</v>
       </c>
       <c r="R119">
-        <v>1.7</v>
+        <v>1.79</v>
       </c>
       <c r="S119">
-        <v>1.58</v>
+        <v>1.53</v>
       </c>
       <c r="T119">
-        <v>1.99</v>
+        <v>2.2</v>
       </c>
       <c r="U119">
-        <v>4</v>
+        <v>3.58</v>
       </c>
       <c r="V119">
-        <v>1.15</v>
+        <v>1.21</v>
       </c>
       <c r="W119">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="X119">
-        <v>1.15</v>
+        <v>1.12</v>
       </c>
       <c r="Y119">
-        <v>1.69</v>
+        <v>1.54</v>
       </c>
       <c r="Z119">
-        <v>2.13</v>
+        <v>2.42</v>
       </c>
       <c r="AA119">
-        <v>2.88</v>
+        <v>2.7</v>
       </c>
       <c r="AB119">
-        <v>1.32</v>
+        <v>1.45</v>
       </c>
       <c r="AC119">
-        <v>6.15</v>
+        <v>4.6</v>
       </c>
       <c r="AD119">
         <v>1.1</v>
       </c>
       <c r="AE119">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="AF119">
-        <v>2.3</v>
+        <v>2.04</v>
       </c>
       <c r="AG119">
-        <v>1.48</v>
+        <v>1.62</v>
       </c>
       <c r="AH119" t="inlineStr">
         <is>
@@ -19776,10 +19776,10 @@
         </is>
       </c>
       <c r="AJ119">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="AK119">
-        <v>1.58</v>
+        <v>1.4</v>
       </c>
       <c r="AL119">
         <v>0</v>
@@ -19827,22 +19827,22 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Deportivo Maipú</t>
+          <t>Rapid Bucureşti</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Atlanta</t>
+          <t>CFR Cluj</t>
         </is>
       </c>
       <c r="G120">
@@ -19869,80 +19869,80 @@
         </is>
       </c>
       <c r="N120">
-        <v>2.46</v>
+        <v>2.03</v>
       </c>
       <c r="O120">
+        <v>3.1</v>
+      </c>
+      <c r="P120">
+        <v>3.31</v>
+      </c>
+      <c r="Q120">
+        <v>2.64</v>
+      </c>
+      <c r="R120">
+        <v>2.15</v>
+      </c>
+      <c r="S120">
+        <v>1.41</v>
+      </c>
+      <c r="T120">
         <v>2.8</v>
       </c>
-      <c r="P120">
-        <v>2.73</v>
-      </c>
-      <c r="Q120">
-        <v>3.51</v>
-      </c>
-      <c r="R120">
-        <v>1.91</v>
-      </c>
-      <c r="S120">
-        <v>1.57</v>
-      </c>
-      <c r="T120">
-        <v>2.2</v>
-      </c>
       <c r="U120">
-        <v>3.75</v>
+        <v>2.88</v>
       </c>
       <c r="V120">
+        <v>1.34</v>
+      </c>
+      <c r="W120">
+        <v>1.05</v>
+      </c>
+      <c r="X120">
+        <v>1.05</v>
+      </c>
+      <c r="Y120">
+        <v>1.3</v>
+      </c>
+      <c r="Z120">
+        <v>2.92</v>
+      </c>
+      <c r="AA120">
+        <v>2</v>
+      </c>
+      <c r="AB120">
+        <v>1.77</v>
+      </c>
+      <c r="AC120">
+        <v>3.42</v>
+      </c>
+      <c r="AD120">
+        <v>1.28</v>
+      </c>
+      <c r="AE120">
+        <v>1.05</v>
+      </c>
+      <c r="AF120">
+        <v>1.83</v>
+      </c>
+      <c r="AG120">
+        <v>1.85</v>
+      </c>
+      <c r="AH120" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI120" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ120">
         <v>1.22</v>
       </c>
-      <c r="W120">
-        <v>1.03</v>
-      </c>
-      <c r="X120">
-        <v>1.12</v>
-      </c>
-      <c r="Y120">
-        <v>1.52</v>
-      </c>
-      <c r="Z120">
-        <v>2.36</v>
-      </c>
-      <c r="AA120">
-        <v>2.56</v>
-      </c>
-      <c r="AB120">
-        <v>1.44</v>
-      </c>
-      <c r="AC120">
-        <v>5.44</v>
-      </c>
-      <c r="AD120">
-        <v>1.1</v>
-      </c>
-      <c r="AE120">
-        <v>1.01</v>
-      </c>
-      <c r="AF120">
-        <v>2.1</v>
-      </c>
-      <c r="AG120">
-        <v>1.65</v>
-      </c>
-      <c r="AH120" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI120" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ120">
-        <v>1.4</v>
-      </c>
       <c r="AK120">
-        <v>1.4</v>
+        <v>1.77</v>
       </c>
       <c r="AL120">
         <v>0</v>
@@ -19985,27 +19985,27 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Rapid Bucureşti</t>
+          <t>Recoleta</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>CFR Cluj</t>
+          <t>Puerto Montt</t>
         </is>
       </c>
       <c r="G121">
@@ -20032,80 +20032,80 @@
         </is>
       </c>
       <c r="N121">
-        <v>2.03</v>
+        <v>2.12</v>
       </c>
       <c r="O121">
         <v>3.1</v>
       </c>
       <c r="P121">
-        <v>3.31</v>
+        <v>3.05</v>
       </c>
       <c r="Q121">
-        <v>2.64</v>
+        <v>2.84</v>
       </c>
       <c r="R121">
-        <v>2.15</v>
+        <v>1.97</v>
       </c>
       <c r="S121">
-        <v>1.41</v>
+        <v>1.44</v>
       </c>
       <c r="T121">
-        <v>2.8</v>
+        <v>2.48</v>
       </c>
       <c r="U121">
-        <v>2.88</v>
+        <v>3.09</v>
       </c>
       <c r="V121">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="W121">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="X121">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="Y121">
-        <v>1.3</v>
+        <v>1.35</v>
       </c>
       <c r="Z121">
-        <v>2.92</v>
+        <v>2.74</v>
       </c>
       <c r="AA121">
+        <v>2.18</v>
+      </c>
+      <c r="AB121">
+        <v>1.62</v>
+      </c>
+      <c r="AC121">
+        <v>4.2</v>
+      </c>
+      <c r="AD121">
+        <v>1.19</v>
+      </c>
+      <c r="AE121">
+        <v>1.03</v>
+      </c>
+      <c r="AF121">
         <v>2</v>
       </c>
-      <c r="AB121">
-        <v>1.77</v>
-      </c>
-      <c r="AC121">
-        <v>3.42</v>
-      </c>
-      <c r="AD121">
+      <c r="AG121">
+        <v>1.68</v>
+      </c>
+      <c r="AH121" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI121" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ121">
         <v>1.28</v>
       </c>
-      <c r="AE121">
-        <v>1.05</v>
-      </c>
-      <c r="AF121">
-        <v>1.83</v>
-      </c>
-      <c r="AG121">
-        <v>1.85</v>
-      </c>
-      <c r="AH121" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI121" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ121">
-        <v>1.22</v>
-      </c>
       <c r="AK121">
-        <v>1.77</v>
+        <v>1.55</v>
       </c>
       <c r="AL121">
         <v>0</v>
@@ -20136,7 +20136,7 @@
       </c>
       <c r="AU121" t="inlineStr">
         <is>
-          <t>2026-08-02 15:30:00</t>
+          <t>2026-08-02 16:00:00</t>
         </is>
       </c>
     </row>
@@ -20153,7 +20153,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -20163,12 +20163,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Recoleta</t>
+          <t>La Serena</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Puerto Montt</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="G122">
@@ -20195,64 +20195,64 @@
         </is>
       </c>
       <c r="N122">
-        <v>2.12</v>
+        <v>2.37</v>
       </c>
       <c r="O122">
+        <v>3.45</v>
+      </c>
+      <c r="P122">
+        <v>2.55</v>
+      </c>
+      <c r="Q122">
+        <v>2.95</v>
+      </c>
+      <c r="R122">
+        <v>2.25</v>
+      </c>
+      <c r="S122">
+        <v>1.31</v>
+      </c>
+      <c r="T122">
         <v>3.1</v>
       </c>
-      <c r="P122">
-        <v>3.05</v>
-      </c>
-      <c r="Q122">
-        <v>2.84</v>
-      </c>
-      <c r="R122">
-        <v>1.97</v>
-      </c>
-      <c r="S122">
-        <v>1.44</v>
-      </c>
-      <c r="T122">
-        <v>2.48</v>
-      </c>
       <c r="U122">
-        <v>3.09</v>
+        <v>2.65</v>
       </c>
       <c r="V122">
-        <v>1.35</v>
+        <v>1.48</v>
       </c>
       <c r="W122">
-        <v>1.07</v>
+        <v>1.09</v>
       </c>
       <c r="X122">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y122">
-        <v>1.35</v>
+        <v>1.24</v>
       </c>
       <c r="Z122">
-        <v>2.74</v>
+        <v>3.96</v>
       </c>
       <c r="AA122">
-        <v>2.18</v>
+        <v>1.78</v>
       </c>
       <c r="AB122">
-        <v>1.62</v>
+        <v>2.02</v>
       </c>
       <c r="AC122">
-        <v>4.2</v>
+        <v>2.94</v>
       </c>
       <c r="AD122">
-        <v>1.19</v>
+        <v>1.34</v>
       </c>
       <c r="AE122">
-        <v>1.03</v>
+        <v>1.11</v>
       </c>
       <c r="AF122">
-        <v>2</v>
+        <v>1.6</v>
       </c>
       <c r="AG122">
-        <v>1.68</v>
+        <v>2.22</v>
       </c>
       <c r="AH122" t="inlineStr">
         <is>
@@ -20265,10 +20265,10 @@
         </is>
       </c>
       <c r="AJ122">
-        <v>1.28</v>
+        <v>1.22</v>
       </c>
       <c r="AK122">
-        <v>1.55</v>
+        <v>1.45</v>
       </c>
       <c r="AL122">
         <v>0</v>
@@ -20316,7 +20316,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -20326,12 +20326,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>La Serena</t>
+          <t>Real Potosí</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Gualberto Villarroel SJ</t>
         </is>
       </c>
       <c r="G123">
@@ -20358,64 +20358,64 @@
         </is>
       </c>
       <c r="N123">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="O123">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="P123">
-        <v>2.54</v>
+        <v>0</v>
       </c>
       <c r="Q123">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="R123">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="S123">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="T123">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="U123">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="V123">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="W123">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="X123">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y123">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="Z123">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="AA123">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AB123">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC123">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="AD123">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AE123">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AF123">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AG123">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AH123" t="inlineStr">
         <is>
@@ -20428,10 +20428,10 @@
         </is>
       </c>
       <c r="AJ123">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AK123">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="AL123">
         <v>0</v>
@@ -20479,7 +20479,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -20489,12 +20489,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Real Potosí</t>
+          <t>Deportivo Madryn</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Gualberto Villarroel SJ</t>
+          <t>All Boys</t>
         </is>
       </c>
       <c r="G124">
@@ -20521,64 +20521,64 @@
         </is>
       </c>
       <c r="N124">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="O124">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="P124">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="Q124">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="R124">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="S124">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="T124">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="U124">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="V124">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="W124">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X124">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="Y124">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="Z124">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AA124">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AB124">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AC124">
-        <v>0</v>
+        <v>5.95</v>
       </c>
       <c r="AD124">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AE124">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AF124">
-        <v>0</v>
+        <v>2.51</v>
       </c>
       <c r="AG124">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AH124" t="inlineStr">
         <is>
@@ -20591,10 +20591,10 @@
         </is>
       </c>
       <c r="AJ124">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AK124">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AL124">
         <v>0</v>
@@ -20652,12 +20652,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Deportivo Madryn</t>
+          <t>Chaco For Ever</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>All Boys</t>
+          <t>Deportivo Morón</t>
         </is>
       </c>
       <c r="G125">
@@ -20684,64 +20684,64 @@
         </is>
       </c>
       <c r="N125">
-        <v>1.91</v>
+        <v>2.8</v>
       </c>
       <c r="O125">
-        <v>2.8</v>
+        <v>2.7</v>
       </c>
       <c r="P125">
-        <v>4.2</v>
+        <v>2.5</v>
       </c>
       <c r="Q125">
-        <v>2.7</v>
+        <v>3.98</v>
       </c>
       <c r="R125">
         <v>1.83</v>
       </c>
       <c r="S125">
-        <v>1.72</v>
+        <v>1.57</v>
       </c>
       <c r="T125">
-        <v>2.25</v>
+        <v>2.07</v>
       </c>
       <c r="U125">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="V125">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="W125">
         <v>1.03</v>
       </c>
       <c r="X125">
-        <v>1.16</v>
+        <v>1.1</v>
       </c>
       <c r="Y125">
-        <v>1.68</v>
+        <v>1.65</v>
       </c>
       <c r="Z125">
-        <v>2.09</v>
+        <v>2.15</v>
       </c>
       <c r="AA125">
-        <v>3.4</v>
+        <v>2.75</v>
       </c>
       <c r="AB125">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="AC125">
-        <v>4.9</v>
+        <v>5.3</v>
       </c>
       <c r="AD125">
-        <v>1.1</v>
+        <v>1.07</v>
       </c>
       <c r="AE125">
         <v>1.02</v>
       </c>
       <c r="AF125">
-        <v>2.51</v>
+        <v>2.2</v>
       </c>
       <c r="AG125">
-        <v>1.46</v>
+        <v>1.57</v>
       </c>
       <c r="AH125" t="inlineStr">
         <is>
@@ -20754,10 +20754,10 @@
         </is>
       </c>
       <c r="AJ125">
-        <v>1.35</v>
+        <v>1.44</v>
       </c>
       <c r="AK125">
-        <v>1.8</v>
+        <v>1.31</v>
       </c>
       <c r="AL125">
         <v>0</v>
@@ -20805,22 +20805,22 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Chaco For Ever</t>
+          <t>Rijeka</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Deportivo Morón</t>
+          <t>Rudeš</t>
         </is>
       </c>
       <c r="G126">
@@ -20847,64 +20847,64 @@
         </is>
       </c>
       <c r="N126">
-        <v>2.91</v>
+        <v>0</v>
       </c>
       <c r="O126">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="P126">
-        <v>2.44</v>
+        <v>0</v>
       </c>
       <c r="Q126">
-        <v>4.15</v>
+        <v>0</v>
       </c>
       <c r="R126">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="S126">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="T126">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="U126">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="V126">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="W126">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="X126">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="Y126">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="Z126">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AA126">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="AB126">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AC126">
-        <v>5.9</v>
+        <v>0</v>
       </c>
       <c r="AD126">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AE126">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AF126">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="AG126">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AH126" t="inlineStr">
         <is>
@@ -20917,10 +20917,10 @@
         </is>
       </c>
       <c r="AJ126">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AK126">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AL126">
         <v>0</v>
@@ -20963,27 +20963,27 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Rijeka</t>
+          <t>Central Norte</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Rudeš</t>
+          <t>Los Andes</t>
         </is>
       </c>
       <c r="G127">
@@ -21010,13 +21010,13 @@
         </is>
       </c>
       <c r="N127">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="O127">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="P127">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="Q127">
         <v>0</v>
@@ -21043,16 +21043,16 @@
         <v>0</v>
       </c>
       <c r="Y127">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="Z127">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AA127">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AB127">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AC127">
         <v>0</v>
@@ -21114,7 +21114,7 @@
       </c>
       <c r="AU127" t="inlineStr">
         <is>
-          <t>2026-08-02 16:00:00</t>
+          <t>2026-08-02 16:30:00</t>
         </is>
       </c>
     </row>
@@ -21126,12 +21126,12 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -21141,12 +21141,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Central Norte</t>
+          <t>Washington Spirit</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Los Andes</t>
+          <t>San Diego Wave</t>
         </is>
       </c>
       <c r="G128">
@@ -21173,64 +21173,64 @@
         </is>
       </c>
       <c r="N128">
-        <v>2.87</v>
+        <v>2.05</v>
       </c>
       <c r="O128">
-        <v>2.5</v>
+        <v>3.28</v>
       </c>
       <c r="P128">
-        <v>2.87</v>
+        <v>3.25</v>
       </c>
       <c r="Q128">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="R128">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="S128">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="T128">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="U128">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="V128">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="W128">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X128">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y128">
-        <v>1.83</v>
+        <v>1.33</v>
       </c>
       <c r="Z128">
-        <v>1.84</v>
+        <v>3.11</v>
       </c>
       <c r="AA128">
-        <v>4</v>
+        <v>1.96</v>
       </c>
       <c r="AB128">
-        <v>1.25</v>
+        <v>1.76</v>
       </c>
       <c r="AC128">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="AD128">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AE128">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AF128">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AG128">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AH128" t="inlineStr">
         <is>
@@ -21243,10 +21243,10 @@
         </is>
       </c>
       <c r="AJ128">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AK128">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AL128">
         <v>0</v>
@@ -21277,7 +21277,7 @@
       </c>
       <c r="AU128" t="inlineStr">
         <is>
-          <t>2026-08-02 16:30:00</t>
+          <t>2026-08-02 17:00:00</t>
         </is>
       </c>
     </row>
@@ -21289,12 +21289,12 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -21304,12 +21304,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Washington Spirit</t>
+          <t>Macará</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>San Diego Wave</t>
+          <t>Guayaquil City FC</t>
         </is>
       </c>
       <c r="G129">
@@ -21336,31 +21336,31 @@
         </is>
       </c>
       <c r="N129">
-        <v>2.05</v>
+        <v>1.55</v>
       </c>
       <c r="O129">
-        <v>3.28</v>
+        <v>3.6</v>
       </c>
       <c r="P129">
+        <v>5.25</v>
+      </c>
+      <c r="Q129">
+        <v>2.08</v>
+      </c>
+      <c r="R129">
+        <v>2.07</v>
+      </c>
+      <c r="S129">
+        <v>1.44</v>
+      </c>
+      <c r="T129">
+        <v>2.69</v>
+      </c>
+      <c r="U129">
         <v>3.25</v>
       </c>
-      <c r="Q129">
-        <v>2.43</v>
-      </c>
-      <c r="R129">
-        <v>2.25</v>
-      </c>
-      <c r="S129">
-        <v>1.36</v>
-      </c>
-      <c r="T129">
-        <v>2.73</v>
-      </c>
-      <c r="U129">
-        <v>2.45</v>
-      </c>
       <c r="V129">
-        <v>1.42</v>
+        <v>1.32</v>
       </c>
       <c r="W129">
         <v>1.04</v>
@@ -21369,31 +21369,31 @@
         <v>1.03</v>
       </c>
       <c r="Y129">
-        <v>1.33</v>
+        <v>1.42</v>
       </c>
       <c r="Z129">
-        <v>3.11</v>
+        <v>2.74</v>
       </c>
       <c r="AA129">
-        <v>1.96</v>
+        <v>2.2</v>
       </c>
       <c r="AB129">
-        <v>1.76</v>
+        <v>1.62</v>
       </c>
       <c r="AC129">
-        <v>3.34</v>
+        <v>3.84</v>
       </c>
       <c r="AD129">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="AE129">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="AF129">
-        <v>1.75</v>
+        <v>2.17</v>
       </c>
       <c r="AG129">
-        <v>1.95</v>
+        <v>1.65</v>
       </c>
       <c r="AH129" t="inlineStr">
         <is>
@@ -21406,10 +21406,10 @@
         </is>
       </c>
       <c r="AJ129">
-        <v>1.1</v>
+        <v>1.06</v>
       </c>
       <c r="AK129">
-        <v>1.58</v>
+        <v>2.38</v>
       </c>
       <c r="AL129">
         <v>0</v>
@@ -21440,7 +21440,7 @@
       </c>
       <c r="AU129" t="inlineStr">
         <is>
-          <t>2026-08-02 17:00:00</t>
+          <t>2026-08-02 17:30:00</t>
         </is>
       </c>
     </row>
@@ -21452,12 +21452,12 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>18:15</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -21467,12 +21467,12 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Macará</t>
+          <t>Club Always Ready</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Guayaquil City FC</t>
+          <t>Bolívar</t>
         </is>
       </c>
       <c r="G130">
@@ -21499,64 +21499,64 @@
         </is>
       </c>
       <c r="N130">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="O130">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="P130">
-        <v>5.25</v>
+        <v>0</v>
       </c>
       <c r="Q130">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="R130">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="S130">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="T130">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="U130">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="V130">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="W130">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="X130">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y130">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="Z130">
-        <v>2.74</v>
+        <v>0</v>
       </c>
       <c r="AA130">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AB130">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AC130">
-        <v>3.84</v>
+        <v>0</v>
       </c>
       <c r="AD130">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AE130">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AF130">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="AG130">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="AH130" t="inlineStr">
         <is>
@@ -21569,10 +21569,10 @@
         </is>
       </c>
       <c r="AJ130">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AK130">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="AL130">
         <v>0</v>
@@ -21603,7 +21603,7 @@
       </c>
       <c r="AU130" t="inlineStr">
         <is>
-          <t>2026-08-02 17:30:00</t>
+          <t>2026-08-02 18:15:00</t>
         </is>
       </c>
     </row>
@@ -21615,12 +21615,12 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>18:15</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -21630,12 +21630,12 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Club Always Ready</t>
+          <t>Deportes Santa Cruz</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Bolívar</t>
+          <t>Santiago Wanderers</t>
         </is>
       </c>
       <c r="G131">
@@ -21662,64 +21662,64 @@
         </is>
       </c>
       <c r="N131">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="O131">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="P131">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="Q131">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="R131">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="S131">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="T131">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="U131">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="V131">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="W131">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X131">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y131">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z131">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AA131">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AB131">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AC131">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="AD131">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AE131">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AF131">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AG131">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AH131" t="inlineStr">
         <is>
@@ -21732,10 +21732,10 @@
         </is>
       </c>
       <c r="AJ131">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK131">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AL131">
         <v>0</v>
@@ -21766,7 +21766,7 @@
       </c>
       <c r="AU131" t="inlineStr">
         <is>
-          <t>2026-08-02 18:15:00</t>
+          <t>2026-08-02 18:30:00</t>
         </is>
       </c>
     </row>
@@ -21783,7 +21783,7 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -21793,12 +21793,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Deportes Santa Cruz</t>
+          <t>Universidad Chile</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Santiago Wanderers</t>
+          <t>Huachipato</t>
         </is>
       </c>
       <c r="G132">
@@ -21825,64 +21825,64 @@
         </is>
       </c>
       <c r="N132">
-        <v>2.35</v>
+        <v>1.57</v>
       </c>
       <c r="O132">
-        <v>3.45</v>
+        <v>3.7</v>
       </c>
       <c r="P132">
-        <v>2.45</v>
+        <v>5</v>
       </c>
       <c r="Q132">
-        <v>3.05</v>
+        <v>2.09</v>
       </c>
       <c r="R132">
-        <v>2.13</v>
+        <v>2.25</v>
       </c>
       <c r="S132">
-        <v>1.32</v>
+        <v>1.35</v>
       </c>
       <c r="T132">
-        <v>2.96</v>
+        <v>3.07</v>
       </c>
       <c r="U132">
-        <v>2.66</v>
+        <v>2.6</v>
       </c>
       <c r="V132">
-        <v>1.39</v>
+        <v>1.44</v>
       </c>
       <c r="W132">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="X132">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y132">
-        <v>1.22</v>
+        <v>1.28</v>
       </c>
       <c r="Z132">
         <v>3.5</v>
       </c>
       <c r="AA132">
+        <v>1.85</v>
+      </c>
+      <c r="AB132">
+        <v>1.87</v>
+      </c>
+      <c r="AC132">
+        <v>3.19</v>
+      </c>
+      <c r="AD132">
+        <v>1.34</v>
+      </c>
+      <c r="AE132">
+        <v>1.08</v>
+      </c>
+      <c r="AF132">
         <v>1.83</v>
       </c>
-      <c r="AB132">
-        <v>1.96</v>
-      </c>
-      <c r="AC132">
-        <v>3.04</v>
-      </c>
-      <c r="AD132">
-        <v>1.29</v>
-      </c>
-      <c r="AE132">
-        <v>1.07</v>
-      </c>
-      <c r="AF132">
-        <v>1.64</v>
-      </c>
       <c r="AG132">
-        <v>2.1</v>
+        <v>1.8</v>
       </c>
       <c r="AH132" t="inlineStr">
         <is>
@@ -21895,10 +21895,10 @@
         </is>
       </c>
       <c r="AJ132">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="AK132">
-        <v>1.44</v>
+        <v>2.19</v>
       </c>
       <c r="AL132">
         <v>0</v>
@@ -21941,12 +21941,12 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -21956,12 +21956,12 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Universidad Chile</t>
+          <t>HFX Wanderers FC</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Huachipato</t>
+          <t>Forge FC</t>
         </is>
       </c>
       <c r="G133">
@@ -21988,64 +21988,64 @@
         </is>
       </c>
       <c r="N133">
-        <v>1.57</v>
+        <v>4.37</v>
       </c>
       <c r="O133">
-        <v>3.7</v>
+        <v>3.72</v>
       </c>
       <c r="P133">
-        <v>5.17</v>
+        <v>1.66</v>
       </c>
       <c r="Q133">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="R133">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="S133">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="T133">
-        <v>3.07</v>
+        <v>0</v>
       </c>
       <c r="U133">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="V133">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="W133">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="X133">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y133">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="Z133">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="AA133">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="AB133">
-        <v>1.87</v>
+        <v>2</v>
       </c>
       <c r="AC133">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="AD133">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AE133">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="AF133">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AG133">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AH133" t="inlineStr">
         <is>
@@ -22058,10 +22058,10 @@
         </is>
       </c>
       <c r="AJ133">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AK133">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="AL133">
         <v>0</v>
@@ -22092,7 +22092,7 @@
       </c>
       <c r="AU133" t="inlineStr">
         <is>
-          <t>2026-08-02 18:30:00</t>
+          <t>2026-08-02 19:00:00</t>
         </is>
       </c>
     </row>
@@ -22104,12 +22104,12 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -22119,12 +22119,12 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>HFX Wanderers FC</t>
+          <t>Utah Royals</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Forge FC</t>
+          <t>Portland Thorns</t>
         </is>
       </c>
       <c r="G134">
@@ -22151,64 +22151,64 @@
         </is>
       </c>
       <c r="N134">
-        <v>4.37</v>
+        <v>1.95</v>
       </c>
       <c r="O134">
-        <v>3.72</v>
+        <v>3.54</v>
       </c>
       <c r="P134">
-        <v>1.66</v>
+        <v>3.27</v>
       </c>
       <c r="Q134">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="R134">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S134">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="T134">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="U134">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="V134">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="W134">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X134">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y134">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="Z134">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AA134">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="AB134">
-        <v>2</v>
+        <v>1.94</v>
       </c>
       <c r="AC134">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AD134">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AE134">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AF134">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AG134">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AH134" t="inlineStr">
         <is>
@@ -22221,10 +22221,10 @@
         </is>
       </c>
       <c r="AJ134">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK134">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AL134">
         <v>0</v>
@@ -22255,7 +22255,7 @@
       </c>
       <c r="AU134" t="inlineStr">
         <is>
-          <t>2026-08-02 19:00:00</t>
+          <t>2026-08-02 20:00:00</t>
         </is>
       </c>
     </row>
@@ -22267,12 +22267,12 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>20:10</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -22282,12 +22282,12 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Utah Royals</t>
+          <t>Leones del Norte</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Portland Thorns</t>
+          <t>Barcelona</t>
         </is>
       </c>
       <c r="G135">
@@ -22314,64 +22314,64 @@
         </is>
       </c>
       <c r="N135">
+        <v>0</v>
+      </c>
+      <c r="O135">
+        <v>0</v>
+      </c>
+      <c r="P135">
+        <v>0</v>
+      </c>
+      <c r="Q135">
+        <v>3.6</v>
+      </c>
+      <c r="R135">
         <v>1.95</v>
       </c>
-      <c r="O135">
-        <v>3.54</v>
-      </c>
-      <c r="P135">
-        <v>3.27</v>
-      </c>
-      <c r="Q135">
-        <v>2.49</v>
-      </c>
-      <c r="R135">
+      <c r="S135">
+        <v>1.48</v>
+      </c>
+      <c r="T135">
+        <v>2.63</v>
+      </c>
+      <c r="U135">
+        <v>3</v>
+      </c>
+      <c r="V135">
+        <v>1.27</v>
+      </c>
+      <c r="W135">
+        <v>1.06</v>
+      </c>
+      <c r="X135">
+        <v>1.09</v>
+      </c>
+      <c r="Y135">
+        <v>1.49</v>
+      </c>
+      <c r="Z135">
+        <v>2.62</v>
+      </c>
+      <c r="AA135">
         <v>2.3</v>
       </c>
-      <c r="S135">
-        <v>1.28</v>
-      </c>
-      <c r="T135">
-        <v>3.14</v>
-      </c>
-      <c r="U135">
-        <v>2.48</v>
-      </c>
-      <c r="V135">
-        <v>1.5</v>
-      </c>
-      <c r="W135">
-        <v>1.11</v>
-      </c>
-      <c r="X135">
-        <v>1.04</v>
-      </c>
-      <c r="Y135">
-        <v>1.21</v>
-      </c>
-      <c r="Z135">
-        <v>3.6</v>
-      </c>
-      <c r="AA135">
-        <v>1.7</v>
-      </c>
       <c r="AB135">
-        <v>1.94</v>
+        <v>1.58</v>
       </c>
       <c r="AC135">
-        <v>2.62</v>
+        <v>4.2</v>
       </c>
       <c r="AD135">
-        <v>1.36</v>
+        <v>1.17</v>
       </c>
       <c r="AE135">
-        <v>1.12</v>
+        <v>1.02</v>
       </c>
       <c r="AF135">
-        <v>1.55</v>
+        <v>1.91</v>
       </c>
       <c r="AG135">
-        <v>2.1</v>
+        <v>1.64</v>
       </c>
       <c r="AH135" t="inlineStr">
         <is>
@@ -22384,10 +22384,10 @@
         </is>
       </c>
       <c r="AJ135">
-        <v>1.25</v>
+        <v>1.32</v>
       </c>
       <c r="AK135">
-        <v>1.7</v>
+        <v>1.33</v>
       </c>
       <c r="AL135">
         <v>0</v>
@@ -22418,7 +22418,7 @@
       </c>
       <c r="AU135" t="inlineStr">
         <is>
-          <t>2026-08-02 20:00:00</t>
+          <t>2026-08-02 20:10:00</t>
         </is>
       </c>
     </row>
@@ -22430,12 +22430,12 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>20:10</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
@@ -22445,12 +22445,12 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Leones del Norte</t>
+          <t>Oriente Petrolero</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Barcelona</t>
+          <t>Nacional Potosí</t>
         </is>
       </c>
       <c r="G136">
@@ -22486,55 +22486,55 @@
         <v>0</v>
       </c>
       <c r="Q136">
-        <v>3.71</v>
+        <v>0</v>
       </c>
       <c r="R136">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="S136">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="T136">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="U136">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="V136">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="W136">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="X136">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="Y136">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="Z136">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="AA136">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AB136">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AC136">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="AD136">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AE136">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AF136">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AG136">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="AH136" t="inlineStr">
         <is>
@@ -22547,10 +22547,10 @@
         </is>
       </c>
       <c r="AJ136">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AK136">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AL136">
         <v>0</v>
@@ -22581,7 +22581,7 @@
       </c>
       <c r="AU136" t="inlineStr">
         <is>
-          <t>2026-08-02 20:10:00</t>
+          <t>2026-08-02 20:30:00</t>
         </is>
       </c>
     </row>
@@ -22593,12 +22593,12 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>22:00</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
@@ -22608,12 +22608,12 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Oriente Petrolero</t>
+          <t>Denver Summit W</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Nacional Potosí</t>
+          <t>Boston Legacy W</t>
         </is>
       </c>
       <c r="G137">
@@ -22640,13 +22640,13 @@
         </is>
       </c>
       <c r="N137">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="O137">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="P137">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="Q137">
         <v>0</v>
@@ -22743,169 +22743,6 @@
         <v>0</v>
       </c>
       <c r="AU137" t="inlineStr">
-        <is>
-          <t>2026-08-02 20:30:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="138">
-      <c r="A138" t="inlineStr">
-        <is>
-          <t>2026-08-02</t>
-        </is>
-      </c>
-      <c r="B138" t="inlineStr">
-        <is>
-          <t>22:00</t>
-        </is>
-      </c>
-      <c r="C138" t="inlineStr">
-        <is>
-          <t>USA NWSL</t>
-        </is>
-      </c>
-      <c r="D138" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="E138" t="inlineStr">
-        <is>
-          <t>Denver Summit W</t>
-        </is>
-      </c>
-      <c r="F138" t="inlineStr">
-        <is>
-          <t>Boston Legacy W</t>
-        </is>
-      </c>
-      <c r="G138">
-        <v>0</v>
-      </c>
-      <c r="H138">
-        <v>0</v>
-      </c>
-      <c r="I138">
-        <v>0</v>
-      </c>
-      <c r="J138">
-        <v>0</v>
-      </c>
-      <c r="K138">
-        <v>0</v>
-      </c>
-      <c r="L138">
-        <v>0</v>
-      </c>
-      <c r="M138" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="N138">
-        <v>1.9</v>
-      </c>
-      <c r="O138">
-        <v>3.45</v>
-      </c>
-      <c r="P138">
-        <v>3.25</v>
-      </c>
-      <c r="Q138">
-        <v>0</v>
-      </c>
-      <c r="R138">
-        <v>0</v>
-      </c>
-      <c r="S138">
-        <v>0</v>
-      </c>
-      <c r="T138">
-        <v>0</v>
-      </c>
-      <c r="U138">
-        <v>0</v>
-      </c>
-      <c r="V138">
-        <v>0</v>
-      </c>
-      <c r="W138">
-        <v>0</v>
-      </c>
-      <c r="X138">
-        <v>0</v>
-      </c>
-      <c r="Y138">
-        <v>0</v>
-      </c>
-      <c r="Z138">
-        <v>0</v>
-      </c>
-      <c r="AA138">
-        <v>0</v>
-      </c>
-      <c r="AB138">
-        <v>0</v>
-      </c>
-      <c r="AC138">
-        <v>0</v>
-      </c>
-      <c r="AD138">
-        <v>0</v>
-      </c>
-      <c r="AE138">
-        <v>0</v>
-      </c>
-      <c r="AF138">
-        <v>0</v>
-      </c>
-      <c r="AG138">
-        <v>0</v>
-      </c>
-      <c r="AH138" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI138" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ138">
-        <v>0</v>
-      </c>
-      <c r="AK138">
-        <v>0</v>
-      </c>
-      <c r="AL138">
-        <v>0</v>
-      </c>
-      <c r="AM138">
-        <v>-1</v>
-      </c>
-      <c r="AN138">
-        <v>-1</v>
-      </c>
-      <c r="AO138">
-        <v>-1</v>
-      </c>
-      <c r="AP138">
-        <v>-1</v>
-      </c>
-      <c r="AQ138">
-        <v>0</v>
-      </c>
-      <c r="AR138">
-        <v>0</v>
-      </c>
-      <c r="AS138">
-        <v>0</v>
-      </c>
-      <c r="AT138">
-        <v>0</v>
-      </c>
-      <c r="AU138" t="inlineStr">
         <is>
           <t>2026-08-02 22:00:00</t>
         </is>

--- a/jogos_2026-08-02.xlsx
+++ b/jogos_2026-08-02.xlsx
@@ -2722,12 +2722,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Busan I'Park</t>
+          <t>Ansan Greeners</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Seoul E-Land</t>
+          <t>Gimhae City</t>
         </is>
       </c>
       <c r="G15">
@@ -2754,64 +2754,64 @@
         </is>
       </c>
       <c r="N15">
-        <v>2.65</v>
+        <v>2.91</v>
       </c>
       <c r="O15">
-        <v>3.5</v>
+        <v>3.38</v>
       </c>
       <c r="P15">
+        <v>2.18</v>
+      </c>
+      <c r="Q15">
+        <v>3.4</v>
+      </c>
+      <c r="R15">
         <v>2.2</v>
       </c>
-      <c r="Q15">
-        <v>3.1</v>
-      </c>
-      <c r="R15">
-        <v>2.36</v>
-      </c>
       <c r="S15">
-        <v>1.3</v>
+        <v>1.35</v>
       </c>
       <c r="T15">
-        <v>3.25</v>
+        <v>2.82</v>
       </c>
       <c r="U15">
-        <v>2.5</v>
+        <v>2.75</v>
       </c>
       <c r="V15">
-        <v>1.45</v>
+        <v>1.4</v>
       </c>
       <c r="W15">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="X15">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="Y15">
-        <v>1.21</v>
+        <v>1.29</v>
       </c>
       <c r="Z15">
-        <v>4.23</v>
+        <v>3.28</v>
       </c>
       <c r="AA15">
-        <v>1.7</v>
+        <v>1.87</v>
       </c>
       <c r="AB15">
-        <v>2.1</v>
+        <v>1.87</v>
       </c>
       <c r="AC15">
-        <v>2.66</v>
+        <v>3.2</v>
       </c>
       <c r="AD15">
-        <v>1.37</v>
+        <v>1.31</v>
       </c>
       <c r="AE15">
         <v>1.11</v>
       </c>
       <c r="AF15">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="AG15">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2824,10 +2824,10 @@
         </is>
       </c>
       <c r="AJ15">
-        <v>1.51</v>
+        <v>1.62</v>
       </c>
       <c r="AK15">
-        <v>1.4</v>
+        <v>1.32</v>
       </c>
       <c r="AL15">
         <v>0</v>
@@ -2885,12 +2885,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Ansan Greeners</t>
+          <t>Gimpo Citizen</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Gimhae City</t>
+          <t>Gyeongnam</t>
         </is>
       </c>
       <c r="G16">
@@ -2917,64 +2917,64 @@
         </is>
       </c>
       <c r="N16">
-        <v>2.91</v>
+        <v>1.95</v>
       </c>
       <c r="O16">
-        <v>3.38</v>
+        <v>3.2</v>
       </c>
       <c r="P16">
+        <v>3.5</v>
+      </c>
+      <c r="Q16">
+        <v>2.62</v>
+      </c>
+      <c r="R16">
         <v>2.18</v>
       </c>
-      <c r="Q16">
-        <v>3.4</v>
-      </c>
-      <c r="R16">
-        <v>2.2</v>
-      </c>
       <c r="S16">
-        <v>1.35</v>
+        <v>1.4</v>
       </c>
       <c r="T16">
-        <v>2.82</v>
+        <v>2.47</v>
       </c>
       <c r="U16">
-        <v>2.75</v>
+        <v>3.12</v>
       </c>
       <c r="V16">
-        <v>1.4</v>
+        <v>1.29</v>
       </c>
       <c r="W16">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="X16">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="Y16">
-        <v>1.29</v>
+        <v>1.39</v>
       </c>
       <c r="Z16">
-        <v>3.28</v>
+        <v>2.95</v>
       </c>
       <c r="AA16">
-        <v>1.87</v>
+        <v>2.12</v>
       </c>
       <c r="AB16">
-        <v>1.87</v>
+        <v>1.62</v>
       </c>
       <c r="AC16">
         <v>3.2</v>
       </c>
       <c r="AD16">
-        <v>1.31</v>
+        <v>1.21</v>
       </c>
       <c r="AE16">
-        <v>1.11</v>
+        <v>1.03</v>
       </c>
       <c r="AF16">
-        <v>1.67</v>
+        <v>1.92</v>
       </c>
       <c r="AG16">
-        <v>2.1</v>
+        <v>1.8</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -2987,10 +2987,10 @@
         </is>
       </c>
       <c r="AJ16">
-        <v>1.62</v>
+        <v>1.22</v>
       </c>
       <c r="AK16">
-        <v>1.32</v>
+        <v>1.84</v>
       </c>
       <c r="AL16">
         <v>0</v>
@@ -3048,12 +3048,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Gimpo Citizen</t>
+          <t>Busan I'Park</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Gyeongnam</t>
+          <t>Seoul E-Land</t>
         </is>
       </c>
       <c r="G17">
@@ -3080,64 +3080,64 @@
         </is>
       </c>
       <c r="N17">
-        <v>1.95</v>
+        <v>2.65</v>
       </c>
       <c r="O17">
-        <v>3.2</v>
+        <v>3.5</v>
       </c>
       <c r="P17">
-        <v>3.5</v>
+        <v>2.2</v>
       </c>
       <c r="Q17">
-        <v>2.62</v>
+        <v>3.1</v>
       </c>
       <c r="R17">
-        <v>2.18</v>
+        <v>2.36</v>
       </c>
       <c r="S17">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="T17">
-        <v>2.47</v>
+        <v>3.25</v>
       </c>
       <c r="U17">
-        <v>3.12</v>
+        <v>2.5</v>
       </c>
       <c r="V17">
-        <v>1.29</v>
+        <v>1.45</v>
       </c>
       <c r="W17">
-        <v>1.06</v>
+        <v>1.11</v>
       </c>
       <c r="X17">
         <v>1.04</v>
       </c>
       <c r="Y17">
-        <v>1.39</v>
+        <v>1.21</v>
       </c>
       <c r="Z17">
-        <v>2.95</v>
+        <v>4.23</v>
       </c>
       <c r="AA17">
-        <v>2.12</v>
+        <v>1.7</v>
       </c>
       <c r="AB17">
-        <v>1.62</v>
+        <v>2.1</v>
       </c>
       <c r="AC17">
-        <v>3.2</v>
+        <v>2.66</v>
       </c>
       <c r="AD17">
-        <v>1.21</v>
+        <v>1.37</v>
       </c>
       <c r="AE17">
-        <v>1.03</v>
+        <v>1.11</v>
       </c>
       <c r="AF17">
-        <v>1.92</v>
+        <v>1.57</v>
       </c>
       <c r="AG17">
-        <v>1.8</v>
+        <v>2.2</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3150,10 +3150,10 @@
         </is>
       </c>
       <c r="AJ17">
-        <v>1.22</v>
+        <v>1.51</v>
       </c>
       <c r="AK17">
-        <v>1.84</v>
+        <v>1.4</v>
       </c>
       <c r="AL17">
         <v>0</v>
@@ -5525,13 +5525,13 @@
         </is>
       </c>
       <c r="N32">
+        <v>2.6</v>
+      </c>
+      <c r="O32">
         <v>2.7</v>
       </c>
-      <c r="O32">
-        <v>2.6</v>
-      </c>
       <c r="P32">
-        <v>2.8</v>
+        <v>2.75</v>
       </c>
       <c r="Q32">
         <v>3.45</v>
@@ -5543,46 +5543,46 @@
         <v>1.6</v>
       </c>
       <c r="T32">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="U32">
         <v>3.82</v>
       </c>
       <c r="V32">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="W32">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="X32">
-        <v>1.15</v>
+        <v>1.1</v>
       </c>
       <c r="Y32">
-        <v>1.67</v>
+        <v>1.61</v>
       </c>
       <c r="Z32">
-        <v>2.15</v>
+        <v>2.17</v>
       </c>
       <c r="AA32">
         <v>2.78</v>
       </c>
       <c r="AB32">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="AC32">
         <v>6.25</v>
       </c>
       <c r="AD32">
-        <v>1.11</v>
+        <v>1.07</v>
       </c>
       <c r="AE32">
         <v>1.03</v>
       </c>
       <c r="AF32">
-        <v>2.25</v>
+        <v>2.23</v>
       </c>
       <c r="AG32">
-        <v>1.6</v>
+        <v>1.53</v>
       </c>
       <c r="AH32" t="inlineStr">
         <is>
@@ -12371,10 +12371,10 @@
         </is>
       </c>
       <c r="N74">
-        <v>2.1</v>
+        <v>2.18</v>
       </c>
       <c r="O74">
-        <v>2.99</v>
+        <v>2.85</v>
       </c>
       <c r="P74">
         <v>3.25</v>
@@ -12398,7 +12398,7 @@
         <v>1.22</v>
       </c>
       <c r="W74">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="X74">
         <v>1.06</v>
@@ -12413,7 +12413,7 @@
         <v>2.59</v>
       </c>
       <c r="AB74">
-        <v>1.5</v>
+        <v>1.43</v>
       </c>
       <c r="AC74">
         <v>5.25</v>
@@ -20489,12 +20489,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Deportivo Madryn</t>
+          <t>Chaco For Ever</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>All Boys</t>
+          <t>Deportivo Morón</t>
         </is>
       </c>
       <c r="G124">
@@ -20521,52 +20521,52 @@
         </is>
       </c>
       <c r="N124">
-        <v>1.91</v>
+        <v>2.8</v>
       </c>
       <c r="O124">
-        <v>2.8</v>
+        <v>2.7</v>
       </c>
       <c r="P124">
-        <v>4.33</v>
+        <v>2.5</v>
       </c>
       <c r="Q124">
-        <v>2.7</v>
+        <v>3.98</v>
       </c>
       <c r="R124">
         <v>1.83</v>
       </c>
       <c r="S124">
-        <v>1.7</v>
+        <v>1.57</v>
       </c>
       <c r="T124">
-        <v>2.25</v>
+        <v>2.07</v>
       </c>
       <c r="U124">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="V124">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="W124">
         <v>1.03</v>
       </c>
       <c r="X124">
-        <v>1.12</v>
+        <v>1.1</v>
       </c>
       <c r="Y124">
-        <v>1.71</v>
+        <v>1.65</v>
       </c>
       <c r="Z124">
-        <v>2.06</v>
+        <v>2.15</v>
       </c>
       <c r="AA124">
-        <v>3.4</v>
+        <v>2.75</v>
       </c>
       <c r="AB124">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="AC124">
-        <v>5.95</v>
+        <v>5.3</v>
       </c>
       <c r="AD124">
         <v>1.07</v>
@@ -20575,26 +20575,26 @@
         <v>1.02</v>
       </c>
       <c r="AF124">
-        <v>2.51</v>
+        <v>2.2</v>
       </c>
       <c r="AG124">
+        <v>1.57</v>
+      </c>
+      <c r="AH124" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI124" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ124">
         <v>1.44</v>
       </c>
-      <c r="AH124" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI124" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ124">
-        <v>1.35</v>
-      </c>
       <c r="AK124">
-        <v>1.8</v>
+        <v>1.31</v>
       </c>
       <c r="AL124">
         <v>0</v>
@@ -20652,12 +20652,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Chaco For Ever</t>
+          <t>Deportivo Madryn</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Deportivo Morón</t>
+          <t>All Boys</t>
         </is>
       </c>
       <c r="G125">
@@ -20684,52 +20684,52 @@
         </is>
       </c>
       <c r="N125">
+        <v>1.91</v>
+      </c>
+      <c r="O125">
         <v>2.8</v>
       </c>
-      <c r="O125">
+      <c r="P125">
+        <v>4.33</v>
+      </c>
+      <c r="Q125">
         <v>2.7</v>
-      </c>
-      <c r="P125">
-        <v>2.5</v>
-      </c>
-      <c r="Q125">
-        <v>3.98</v>
       </c>
       <c r="R125">
         <v>1.83</v>
       </c>
       <c r="S125">
-        <v>1.57</v>
+        <v>1.7</v>
       </c>
       <c r="T125">
-        <v>2.07</v>
+        <v>2.25</v>
       </c>
       <c r="U125">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="V125">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="W125">
         <v>1.03</v>
       </c>
       <c r="X125">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="Y125">
-        <v>1.65</v>
+        <v>1.71</v>
       </c>
       <c r="Z125">
-        <v>2.15</v>
+        <v>2.06</v>
       </c>
       <c r="AA125">
-        <v>2.75</v>
+        <v>3.4</v>
       </c>
       <c r="AB125">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="AC125">
-        <v>5.3</v>
+        <v>5.95</v>
       </c>
       <c r="AD125">
         <v>1.07</v>
@@ -20738,10 +20738,10 @@
         <v>1.02</v>
       </c>
       <c r="AF125">
-        <v>2.2</v>
+        <v>2.51</v>
       </c>
       <c r="AG125">
-        <v>1.57</v>
+        <v>1.44</v>
       </c>
       <c r="AH125" t="inlineStr">
         <is>
@@ -20754,10 +20754,10 @@
         </is>
       </c>
       <c r="AJ125">
-        <v>1.44</v>
+        <v>1.35</v>
       </c>
       <c r="AK125">
-        <v>1.31</v>
+        <v>1.8</v>
       </c>
       <c r="AL125">
         <v>0</v>

--- a/jogos_2026-08-02.xlsx
+++ b/jogos_2026-08-02.xlsx
@@ -1939,16 +1939,16 @@
         </is>
       </c>
       <c r="N10">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="O10">
-        <v>0</v>
+        <v>3.33</v>
       </c>
       <c r="P10">
-        <v>0</v>
+        <v>3.21</v>
       </c>
       <c r="Q10">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="R10">
         <v>2.38</v>
@@ -1957,7 +1957,7 @@
         <v>1.28</v>
       </c>
       <c r="T10">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="U10">
         <v>2.33</v>
@@ -1972,22 +1972,22 @@
         <v>1.03</v>
       </c>
       <c r="Y10">
-        <v>1.13</v>
+        <v>1.2</v>
       </c>
       <c r="Z10">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="AA10">
-        <v>1.62</v>
+        <v>1.58</v>
       </c>
       <c r="AB10">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="AC10">
-        <v>2.37</v>
+        <v>2.48</v>
       </c>
       <c r="AD10">
-        <v>1.48</v>
+        <v>1.53</v>
       </c>
       <c r="AE10">
         <v>1.17</v>
@@ -1996,7 +1996,7 @@
         <v>1.57</v>
       </c>
       <c r="AG10">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2009,7 +2009,7 @@
         </is>
       </c>
       <c r="AJ10">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AK10">
         <v>2.09</v>
@@ -2722,12 +2722,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Ansan Greeners</t>
+          <t>Busan I'Park</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Gimhae City</t>
+          <t>Seoul E-Land</t>
         </is>
       </c>
       <c r="G15">
@@ -2754,64 +2754,64 @@
         </is>
       </c>
       <c r="N15">
-        <v>2.91</v>
+        <v>2.65</v>
       </c>
       <c r="O15">
-        <v>3.38</v>
+        <v>3.5</v>
       </c>
       <c r="P15">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="Q15">
-        <v>3.4</v>
+        <v>3.1</v>
       </c>
       <c r="R15">
-        <v>2.2</v>
+        <v>2.36</v>
       </c>
       <c r="S15">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="T15">
-        <v>2.82</v>
+        <v>3.25</v>
       </c>
       <c r="U15">
-        <v>2.75</v>
+        <v>2.5</v>
       </c>
       <c r="V15">
-        <v>1.4</v>
+        <v>1.45</v>
       </c>
       <c r="W15">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="X15">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="Y15">
-        <v>1.29</v>
+        <v>1.21</v>
       </c>
       <c r="Z15">
-        <v>3.28</v>
+        <v>4.23</v>
       </c>
       <c r="AA15">
-        <v>1.87</v>
+        <v>1.7</v>
       </c>
       <c r="AB15">
-        <v>1.87</v>
+        <v>2.1</v>
       </c>
       <c r="AC15">
-        <v>3.2</v>
+        <v>2.66</v>
       </c>
       <c r="AD15">
-        <v>1.31</v>
+        <v>1.37</v>
       </c>
       <c r="AE15">
         <v>1.11</v>
       </c>
       <c r="AF15">
-        <v>1.67</v>
+        <v>1.57</v>
       </c>
       <c r="AG15">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2824,10 +2824,10 @@
         </is>
       </c>
       <c r="AJ15">
-        <v>1.62</v>
+        <v>1.51</v>
       </c>
       <c r="AK15">
-        <v>1.32</v>
+        <v>1.4</v>
       </c>
       <c r="AL15">
         <v>0</v>
@@ -3048,12 +3048,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Busan I'Park</t>
+          <t>Ansan Greeners</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Seoul E-Land</t>
+          <t>Gimhae City</t>
         </is>
       </c>
       <c r="G17">
@@ -3080,64 +3080,64 @@
         </is>
       </c>
       <c r="N17">
-        <v>2.65</v>
+        <v>2.91</v>
       </c>
       <c r="O17">
-        <v>3.5</v>
+        <v>3.38</v>
       </c>
       <c r="P17">
+        <v>2.18</v>
+      </c>
+      <c r="Q17">
+        <v>3.4</v>
+      </c>
+      <c r="R17">
         <v>2.2</v>
       </c>
-      <c r="Q17">
-        <v>3.1</v>
-      </c>
-      <c r="R17">
-        <v>2.36</v>
-      </c>
       <c r="S17">
-        <v>1.3</v>
+        <v>1.35</v>
       </c>
       <c r="T17">
-        <v>3.25</v>
+        <v>2.82</v>
       </c>
       <c r="U17">
-        <v>2.5</v>
+        <v>2.75</v>
       </c>
       <c r="V17">
-        <v>1.45</v>
+        <v>1.4</v>
       </c>
       <c r="W17">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="X17">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="Y17">
-        <v>1.21</v>
+        <v>1.29</v>
       </c>
       <c r="Z17">
-        <v>4.23</v>
+        <v>3.28</v>
       </c>
       <c r="AA17">
-        <v>1.7</v>
+        <v>1.87</v>
       </c>
       <c r="AB17">
-        <v>2.1</v>
+        <v>1.87</v>
       </c>
       <c r="AC17">
-        <v>2.66</v>
+        <v>3.2</v>
       </c>
       <c r="AD17">
-        <v>1.37</v>
+        <v>1.31</v>
       </c>
       <c r="AE17">
         <v>1.11</v>
       </c>
       <c r="AF17">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="AG17">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3150,10 +3150,10 @@
         </is>
       </c>
       <c r="AJ17">
-        <v>1.51</v>
+        <v>1.62</v>
       </c>
       <c r="AK17">
-        <v>1.4</v>
+        <v>1.32</v>
       </c>
       <c r="AL17">
         <v>0</v>
@@ -3732,25 +3732,25 @@
         </is>
       </c>
       <c r="N21">
-        <v>3.46</v>
+        <v>3.3</v>
       </c>
       <c r="O21">
-        <v>3.92</v>
+        <v>3.8</v>
       </c>
       <c r="P21">
-        <v>1.99</v>
+        <v>1.74</v>
       </c>
       <c r="Q21">
-        <v>3.81</v>
+        <v>3.7</v>
       </c>
       <c r="R21">
-        <v>2.49</v>
+        <v>2.51</v>
       </c>
       <c r="S21">
         <v>1.2</v>
       </c>
       <c r="T21">
-        <v>4.05</v>
+        <v>3.9</v>
       </c>
       <c r="U21">
         <v>2.1</v>
@@ -3765,28 +3765,28 @@
         <v>1.02</v>
       </c>
       <c r="Y21">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="Z21">
-        <v>5.5</v>
+        <v>5.34</v>
       </c>
       <c r="AA21">
-        <v>1.43</v>
+        <v>1.48</v>
       </c>
       <c r="AB21">
-        <v>2.6</v>
+        <v>2.58</v>
       </c>
       <c r="AC21">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="AD21">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="AE21">
-        <v>1.25</v>
+        <v>1.21</v>
       </c>
       <c r="AF21">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="AG21">
         <v>2.63</v>
@@ -3805,7 +3805,7 @@
         <v>1.22</v>
       </c>
       <c r="AK21">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="AL21">
         <v>0</v>
@@ -3895,16 +3895,16 @@
         </is>
       </c>
       <c r="N22">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="O22">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="P22">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="Q22">
-        <v>2.69</v>
+        <v>2.7</v>
       </c>
       <c r="R22">
         <v>2.07</v>
@@ -3916,7 +3916,7 @@
         <v>2.77</v>
       </c>
       <c r="U22">
-        <v>2.86</v>
+        <v>2.7</v>
       </c>
       <c r="V22">
         <v>1.4</v>
@@ -3925,28 +3925,28 @@
         <v>1.06</v>
       </c>
       <c r="X22">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y22">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="Z22">
-        <v>3.5</v>
+        <v>3.26</v>
       </c>
       <c r="AA22">
         <v>1.89</v>
       </c>
       <c r="AB22">
-        <v>1.86</v>
+        <v>1.83</v>
       </c>
       <c r="AC22">
-        <v>3.4</v>
+        <v>3.08</v>
       </c>
       <c r="AD22">
-        <v>1.29</v>
+        <v>1.31</v>
       </c>
       <c r="AE22">
-        <v>1.07</v>
+        <v>1.11</v>
       </c>
       <c r="AF22">
         <v>1.71</v>
@@ -3965,10 +3965,10 @@
         </is>
       </c>
       <c r="AJ22">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="AK22">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="AL22">
         <v>0</v>
@@ -14132,12 +14132,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Tallinna FC Flora</t>
+          <t>Vaprus</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Harju Jalgpallikool</t>
+          <t>Tallinna FC Levadia</t>
         </is>
       </c>
       <c r="G85">
@@ -14164,64 +14164,64 @@
         </is>
       </c>
       <c r="N85">
-        <v>1.48</v>
+        <v>11.7</v>
       </c>
       <c r="O85">
-        <v>4.2</v>
+        <v>5.75</v>
       </c>
       <c r="P85">
+        <v>1.22</v>
+      </c>
+      <c r="Q85">
+        <v>8.91</v>
+      </c>
+      <c r="R85">
+        <v>3.02</v>
+      </c>
+      <c r="S85">
+        <v>1.2</v>
+      </c>
+      <c r="T85">
+        <v>3.9</v>
+      </c>
+      <c r="U85">
+        <v>2.05</v>
+      </c>
+      <c r="V85">
+        <v>1.71</v>
+      </c>
+      <c r="W85">
+        <v>1.18</v>
+      </c>
+      <c r="X85">
+        <v>1.01</v>
+      </c>
+      <c r="Y85">
+        <v>1.1</v>
+      </c>
+      <c r="Z85">
         <v>5.25</v>
       </c>
-      <c r="Q85">
-        <v>1.83</v>
-      </c>
-      <c r="R85">
-        <v>2.8</v>
-      </c>
-      <c r="S85">
-        <v>1.21</v>
-      </c>
-      <c r="T85">
-        <v>3.58</v>
-      </c>
-      <c r="U85">
-        <v>2.1</v>
-      </c>
-      <c r="V85">
-        <v>1.69</v>
-      </c>
-      <c r="W85">
-        <v>1.17</v>
-      </c>
-      <c r="X85">
-        <v>1.02</v>
-      </c>
-      <c r="Y85">
-        <v>1.09</v>
-      </c>
-      <c r="Z85">
-        <v>5.5</v>
-      </c>
       <c r="AA85">
-        <v>1.44</v>
+        <v>1.41</v>
       </c>
       <c r="AB85">
-        <v>2.7</v>
+        <v>2.52</v>
       </c>
       <c r="AC85">
         <v>2.11</v>
       </c>
       <c r="AD85">
-        <v>1.73</v>
+        <v>1.65</v>
       </c>
       <c r="AE85">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="AF85">
-        <v>1.5</v>
+        <v>1.85</v>
       </c>
       <c r="AG85">
-        <v>2.3</v>
+        <v>1.85</v>
       </c>
       <c r="AH85" t="inlineStr">
         <is>
@@ -14234,10 +14234,10 @@
         </is>
       </c>
       <c r="AJ85">
-        <v>1.14</v>
+        <v>3.66</v>
       </c>
       <c r="AK85">
-        <v>2.63</v>
+        <v>1.05</v>
       </c>
       <c r="AL85">
         <v>0</v>
@@ -14295,12 +14295,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Vaprus</t>
+          <t>Tallinna FC Flora</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Tallinna FC Levadia</t>
+          <t>Harju Jalgpallikool</t>
         </is>
       </c>
       <c r="G86">
@@ -14327,64 +14327,64 @@
         </is>
       </c>
       <c r="N86">
-        <v>11.7</v>
+        <v>1.48</v>
       </c>
       <c r="O86">
-        <v>5.75</v>
+        <v>4.2</v>
       </c>
       <c r="P86">
-        <v>1.22</v>
+        <v>5.25</v>
       </c>
       <c r="Q86">
-        <v>8.91</v>
+        <v>1.83</v>
       </c>
       <c r="R86">
-        <v>3.02</v>
+        <v>2.8</v>
       </c>
       <c r="S86">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="T86">
-        <v>3.9</v>
+        <v>3.58</v>
       </c>
       <c r="U86">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="V86">
-        <v>1.71</v>
+        <v>1.69</v>
       </c>
       <c r="W86">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="X86">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y86">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="Z86">
-        <v>5.25</v>
+        <v>5.5</v>
       </c>
       <c r="AA86">
-        <v>1.41</v>
+        <v>1.44</v>
       </c>
       <c r="AB86">
-        <v>2.52</v>
+        <v>2.7</v>
       </c>
       <c r="AC86">
         <v>2.11</v>
       </c>
       <c r="AD86">
-        <v>1.65</v>
+        <v>1.73</v>
       </c>
       <c r="AE86">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="AF86">
-        <v>1.85</v>
+        <v>1.5</v>
       </c>
       <c r="AG86">
-        <v>1.85</v>
+        <v>2.3</v>
       </c>
       <c r="AH86" t="inlineStr">
         <is>
@@ -14397,10 +14397,10 @@
         </is>
       </c>
       <c r="AJ86">
-        <v>3.66</v>
+        <v>1.14</v>
       </c>
       <c r="AK86">
-        <v>1.05</v>
+        <v>2.63</v>
       </c>
       <c r="AL86">
         <v>0</v>
@@ -20489,12 +20489,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Chaco For Ever</t>
+          <t>Deportivo Madryn</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Deportivo Morón</t>
+          <t>All Boys</t>
         </is>
       </c>
       <c r="G124">
@@ -20521,52 +20521,52 @@
         </is>
       </c>
       <c r="N124">
+        <v>1.91</v>
+      </c>
+      <c r="O124">
         <v>2.8</v>
       </c>
-      <c r="O124">
+      <c r="P124">
+        <v>4.33</v>
+      </c>
+      <c r="Q124">
         <v>2.7</v>
-      </c>
-      <c r="P124">
-        <v>2.5</v>
-      </c>
-      <c r="Q124">
-        <v>3.98</v>
       </c>
       <c r="R124">
         <v>1.83</v>
       </c>
       <c r="S124">
-        <v>1.57</v>
+        <v>1.7</v>
       </c>
       <c r="T124">
-        <v>2.07</v>
+        <v>2.25</v>
       </c>
       <c r="U124">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="V124">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="W124">
         <v>1.03</v>
       </c>
       <c r="X124">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="Y124">
-        <v>1.65</v>
+        <v>1.71</v>
       </c>
       <c r="Z124">
-        <v>2.15</v>
+        <v>2.06</v>
       </c>
       <c r="AA124">
-        <v>2.75</v>
+        <v>3.4</v>
       </c>
       <c r="AB124">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="AC124">
-        <v>5.3</v>
+        <v>5.95</v>
       </c>
       <c r="AD124">
         <v>1.07</v>
@@ -20575,10 +20575,10 @@
         <v>1.02</v>
       </c>
       <c r="AF124">
-        <v>2.2</v>
+        <v>2.51</v>
       </c>
       <c r="AG124">
-        <v>1.57</v>
+        <v>1.44</v>
       </c>
       <c r="AH124" t="inlineStr">
         <is>
@@ -20591,10 +20591,10 @@
         </is>
       </c>
       <c r="AJ124">
-        <v>1.44</v>
+        <v>1.35</v>
       </c>
       <c r="AK124">
-        <v>1.31</v>
+        <v>1.8</v>
       </c>
       <c r="AL124">
         <v>0</v>
@@ -20652,12 +20652,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Deportivo Madryn</t>
+          <t>Chaco For Ever</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>All Boys</t>
+          <t>Deportivo Morón</t>
         </is>
       </c>
       <c r="G125">
@@ -20684,52 +20684,52 @@
         </is>
       </c>
       <c r="N125">
-        <v>1.91</v>
+        <v>2.8</v>
       </c>
       <c r="O125">
-        <v>2.8</v>
+        <v>2.7</v>
       </c>
       <c r="P125">
-        <v>4.33</v>
+        <v>2.5</v>
       </c>
       <c r="Q125">
-        <v>2.7</v>
+        <v>3.98</v>
       </c>
       <c r="R125">
         <v>1.83</v>
       </c>
       <c r="S125">
-        <v>1.7</v>
+        <v>1.57</v>
       </c>
       <c r="T125">
-        <v>2.25</v>
+        <v>2.07</v>
       </c>
       <c r="U125">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="V125">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="W125">
         <v>1.03</v>
       </c>
       <c r="X125">
-        <v>1.12</v>
+        <v>1.1</v>
       </c>
       <c r="Y125">
-        <v>1.71</v>
+        <v>1.65</v>
       </c>
       <c r="Z125">
-        <v>2.06</v>
+        <v>2.15</v>
       </c>
       <c r="AA125">
-        <v>3.4</v>
+        <v>2.75</v>
       </c>
       <c r="AB125">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="AC125">
-        <v>5.95</v>
+        <v>5.3</v>
       </c>
       <c r="AD125">
         <v>1.07</v>
@@ -20738,26 +20738,26 @@
         <v>1.02</v>
       </c>
       <c r="AF125">
-        <v>2.51</v>
+        <v>2.2</v>
       </c>
       <c r="AG125">
+        <v>1.57</v>
+      </c>
+      <c r="AH125" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI125" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ125">
         <v>1.44</v>
       </c>
-      <c r="AH125" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI125" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ125">
-        <v>1.35</v>
-      </c>
       <c r="AK125">
-        <v>1.8</v>
+        <v>1.31</v>
       </c>
       <c r="AL125">
         <v>0</v>

--- a/jogos_2026-08-02.xlsx
+++ b/jogos_2026-08-02.xlsx
@@ -1613,13 +1613,13 @@
         </is>
       </c>
       <c r="N8">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="O8">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="P8">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="Q8">
         <v>5</v>
@@ -1649,10 +1649,10 @@
         <v>1.3</v>
       </c>
       <c r="Z8">
-        <v>2.97</v>
+        <v>3.06</v>
       </c>
       <c r="AA8">
-        <v>2.09</v>
+        <v>2.11</v>
       </c>
       <c r="AB8">
         <v>1.7</v>
@@ -1683,7 +1683,7 @@
         </is>
       </c>
       <c r="AJ8">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="AK8">
         <v>1.2</v>
@@ -1776,10 +1776,10 @@
         </is>
       </c>
       <c r="N9">
-        <v>2.36</v>
+        <v>2.37</v>
       </c>
       <c r="O9">
-        <v>3.7</v>
+        <v>3.25</v>
       </c>
       <c r="P9">
         <v>2.6</v>
@@ -1815,10 +1815,10 @@
         <v>0</v>
       </c>
       <c r="AA9">
-        <v>1.94</v>
+        <v>1.8</v>
       </c>
       <c r="AB9">
-        <v>1.75</v>
+        <v>2</v>
       </c>
       <c r="AC9">
         <v>0</v>
@@ -1948,7 +1948,7 @@
         <v>3.21</v>
       </c>
       <c r="Q10">
-        <v>2.25</v>
+        <v>2.22</v>
       </c>
       <c r="R10">
         <v>2.38</v>
@@ -1972,19 +1972,19 @@
         <v>1.03</v>
       </c>
       <c r="Y10">
-        <v>1.2</v>
+        <v>1.14</v>
       </c>
       <c r="Z10">
         <v>4.6</v>
       </c>
       <c r="AA10">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="AB10">
-        <v>2.3</v>
+        <v>2.29</v>
       </c>
       <c r="AC10">
-        <v>2.48</v>
+        <v>2.44</v>
       </c>
       <c r="AD10">
         <v>1.53</v>
@@ -1996,7 +1996,7 @@
         <v>1.57</v>
       </c>
       <c r="AG10">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2591,16 +2591,16 @@
         </is>
       </c>
       <c r="N14">
-        <v>1.97</v>
+        <v>1.96</v>
       </c>
       <c r="O14">
-        <v>3.32</v>
+        <v>3.28</v>
       </c>
       <c r="P14">
-        <v>3.45</v>
+        <v>2.77</v>
       </c>
       <c r="Q14">
-        <v>2.66</v>
+        <v>2.63</v>
       </c>
       <c r="R14">
         <v>2.09</v>
@@ -2612,10 +2612,10 @@
         <v>2.9</v>
       </c>
       <c r="U14">
-        <v>2.71</v>
+        <v>2.62</v>
       </c>
       <c r="V14">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="W14">
         <v>1.05</v>
@@ -2624,25 +2624,25 @@
         <v>1</v>
       </c>
       <c r="Y14">
-        <v>1.21</v>
+        <v>1.26</v>
       </c>
       <c r="Z14">
-        <v>3.58</v>
+        <v>3.71</v>
       </c>
       <c r="AA14">
-        <v>1.68</v>
+        <v>1.8</v>
       </c>
       <c r="AB14">
-        <v>1.95</v>
+        <v>1.9</v>
       </c>
       <c r="AC14">
-        <v>2.92</v>
+        <v>3.05</v>
       </c>
       <c r="AD14">
-        <v>1.31</v>
+        <v>1.36</v>
       </c>
       <c r="AE14">
-        <v>1.13</v>
+        <v>1.08</v>
       </c>
       <c r="AF14">
         <v>1.65</v>
@@ -2661,7 +2661,7 @@
         </is>
       </c>
       <c r="AJ14">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AK14">
         <v>1.7</v>
@@ -2754,25 +2754,25 @@
         </is>
       </c>
       <c r="N15">
-        <v>2.65</v>
+        <v>2.42</v>
       </c>
       <c r="O15">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="P15">
-        <v>2.2</v>
+        <v>2.17</v>
       </c>
       <c r="Q15">
         <v>3.1</v>
       </c>
       <c r="R15">
-        <v>2.36</v>
+        <v>2.23</v>
       </c>
       <c r="S15">
         <v>1.3</v>
       </c>
       <c r="T15">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="U15">
         <v>2.5</v>
@@ -2781,10 +2781,10 @@
         <v>1.45</v>
       </c>
       <c r="W15">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="X15">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y15">
         <v>1.21</v>
@@ -2793,7 +2793,7 @@
         <v>4.23</v>
       </c>
       <c r="AA15">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="AB15">
         <v>2.1</v>
@@ -2811,7 +2811,7 @@
         <v>1.57</v>
       </c>
       <c r="AG15">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2827,7 +2827,7 @@
         <v>1.51</v>
       </c>
       <c r="AK15">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AL15">
         <v>0</v>
@@ -2885,12 +2885,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Gimpo Citizen</t>
+          <t>Ansan Greeners</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Gyeongnam</t>
+          <t>Gimhae City</t>
         </is>
       </c>
       <c r="G16">
@@ -2917,64 +2917,64 @@
         </is>
       </c>
       <c r="N16">
-        <v>1.95</v>
+        <v>2.65</v>
       </c>
       <c r="O16">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="P16">
-        <v>3.5</v>
+        <v>2.15</v>
       </c>
       <c r="Q16">
-        <v>2.62</v>
+        <v>3.4</v>
       </c>
       <c r="R16">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="S16">
+        <v>1.35</v>
+      </c>
+      <c r="T16">
+        <v>2.82</v>
+      </c>
+      <c r="U16">
+        <v>2.84</v>
+      </c>
+      <c r="V16">
         <v>1.4</v>
       </c>
-      <c r="T16">
-        <v>2.47</v>
-      </c>
-      <c r="U16">
-        <v>3.12</v>
-      </c>
-      <c r="V16">
-        <v>1.29</v>
-      </c>
       <c r="W16">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="X16">
         <v>1.04</v>
       </c>
       <c r="Y16">
-        <v>1.39</v>
+        <v>1.29</v>
       </c>
       <c r="Z16">
-        <v>2.95</v>
+        <v>3.28</v>
       </c>
       <c r="AA16">
-        <v>2.12</v>
+        <v>1.87</v>
       </c>
       <c r="AB16">
-        <v>1.62</v>
+        <v>1.87</v>
       </c>
       <c r="AC16">
         <v>3.2</v>
       </c>
       <c r="AD16">
-        <v>1.21</v>
+        <v>1.27</v>
       </c>
       <c r="AE16">
-        <v>1.03</v>
+        <v>1.11</v>
       </c>
       <c r="AF16">
-        <v>1.92</v>
+        <v>1.67</v>
       </c>
       <c r="AG16">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -2987,10 +2987,10 @@
         </is>
       </c>
       <c r="AJ16">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AK16">
-        <v>1.84</v>
+        <v>1.35</v>
       </c>
       <c r="AL16">
         <v>0</v>
@@ -3048,12 +3048,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Ansan Greeners</t>
+          <t>Gimpo Citizen</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Gimhae City</t>
+          <t>Gyeongnam</t>
         </is>
       </c>
       <c r="G17">
@@ -3080,64 +3080,64 @@
         </is>
       </c>
       <c r="N17">
-        <v>2.91</v>
+        <v>1.94</v>
       </c>
       <c r="O17">
-        <v>3.38</v>
+        <v>2.98</v>
       </c>
       <c r="P17">
-        <v>2.18</v>
+        <v>3.5</v>
       </c>
       <c r="Q17">
-        <v>3.4</v>
+        <v>2.62</v>
       </c>
       <c r="R17">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="S17">
-        <v>1.35</v>
+        <v>1.4</v>
       </c>
       <c r="T17">
-        <v>2.82</v>
+        <v>2.5</v>
       </c>
       <c r="U17">
-        <v>2.75</v>
+        <v>3.12</v>
       </c>
       <c r="V17">
-        <v>1.4</v>
+        <v>1.29</v>
       </c>
       <c r="W17">
-        <v>1.08</v>
+        <v>1.02</v>
       </c>
       <c r="X17">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="Y17">
-        <v>1.29</v>
+        <v>1.39</v>
       </c>
       <c r="Z17">
-        <v>3.28</v>
+        <v>2.9</v>
       </c>
       <c r="AA17">
-        <v>1.87</v>
+        <v>2.28</v>
       </c>
       <c r="AB17">
-        <v>1.87</v>
+        <v>1.62</v>
       </c>
       <c r="AC17">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="AD17">
-        <v>1.31</v>
+        <v>1.18</v>
       </c>
       <c r="AE17">
-        <v>1.11</v>
+        <v>1.03</v>
       </c>
       <c r="AF17">
-        <v>1.67</v>
+        <v>1.93</v>
       </c>
       <c r="AG17">
-        <v>2.1</v>
+        <v>1.8</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3150,10 +3150,10 @@
         </is>
       </c>
       <c r="AJ17">
-        <v>1.62</v>
+        <v>1.24</v>
       </c>
       <c r="AK17">
-        <v>1.32</v>
+        <v>1.72</v>
       </c>
       <c r="AL17">
         <v>0</v>
@@ -3243,64 +3243,64 @@
         </is>
       </c>
       <c r="N18">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="O18">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P18">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="Q18">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="R18">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="S18">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="T18">
-        <v>0</v>
+        <v>2.67</v>
       </c>
       <c r="U18">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="V18">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W18">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X18">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y18">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z18">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="AA18">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AB18">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AC18">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="AD18">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AE18">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AF18">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AG18">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3313,10 +3313,10 @@
         </is>
       </c>
       <c r="AJ18">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AK18">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AL18">
         <v>0</v>
@@ -3374,12 +3374,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Shenzhen Juniors</t>
+          <t>Suzhou Dongwu</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Wuxi Wugou</t>
+          <t>Meizhou Hakka</t>
         </is>
       </c>
       <c r="G19">
@@ -3406,64 +3406,64 @@
         </is>
       </c>
       <c r="N19">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="O19">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="P19">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Q19">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="R19">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="S19">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="T19">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="U19">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="V19">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W19">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X19">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y19">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="Z19">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="AA19">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AB19">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AC19">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AD19">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AE19">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AF19">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AG19">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3476,10 +3476,10 @@
         </is>
       </c>
       <c r="AJ19">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AK19">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AL19">
         <v>0</v>
@@ -3537,12 +3537,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Suzhou Dongwu</t>
+          <t>Shenzhen Juniors</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Meizhou Hakka</t>
+          <t>Wuxi Wugou</t>
         </is>
       </c>
       <c r="G20">
@@ -3569,64 +3569,64 @@
         </is>
       </c>
       <c r="N20">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="O20">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="P20">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="Q20">
-        <v>0</v>
+        <v>2.67</v>
       </c>
       <c r="R20">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="S20">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="T20">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="U20">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="V20">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="W20">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X20">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y20">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="Z20">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="AA20">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AB20">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="AC20">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AD20">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AE20">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AF20">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AG20">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
@@ -3639,10 +3639,10 @@
         </is>
       </c>
       <c r="AJ20">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AK20">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AL20">
         <v>0</v>
@@ -3732,19 +3732,19 @@
         </is>
       </c>
       <c r="N21">
-        <v>3.3</v>
+        <v>3.6</v>
       </c>
       <c r="O21">
         <v>3.8</v>
       </c>
       <c r="P21">
-        <v>1.74</v>
+        <v>1.72</v>
       </c>
       <c r="Q21">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="R21">
-        <v>2.51</v>
+        <v>2.5</v>
       </c>
       <c r="S21">
         <v>1.2</v>
@@ -3762,34 +3762,34 @@
         <v>1.14</v>
       </c>
       <c r="X21">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y21">
         <v>1.09</v>
       </c>
       <c r="Z21">
-        <v>5.34</v>
+        <v>6.71</v>
       </c>
       <c r="AA21">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="AB21">
-        <v>2.58</v>
+        <v>2.62</v>
       </c>
       <c r="AC21">
-        <v>2.2</v>
+        <v>2.21</v>
       </c>
       <c r="AD21">
-        <v>1.62</v>
+        <v>1.66</v>
       </c>
       <c r="AE21">
-        <v>1.21</v>
+        <v>1.28</v>
       </c>
       <c r="AF21">
         <v>1.44</v>
       </c>
       <c r="AG21">
-        <v>2.63</v>
+        <v>2.6</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
@@ -3805,7 +3805,7 @@
         <v>1.22</v>
       </c>
       <c r="AK21">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="AL21">
         <v>0</v>
@@ -3898,13 +3898,13 @@
         <v>2.03</v>
       </c>
       <c r="O22">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="P22">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="Q22">
-        <v>2.7</v>
+        <v>2.69</v>
       </c>
       <c r="R22">
         <v>2.07</v>
@@ -3916,7 +3916,7 @@
         <v>2.77</v>
       </c>
       <c r="U22">
-        <v>2.7</v>
+        <v>2.69</v>
       </c>
       <c r="V22">
         <v>1.4</v>
@@ -3931,22 +3931,22 @@
         <v>1.29</v>
       </c>
       <c r="Z22">
-        <v>3.26</v>
+        <v>3.5</v>
       </c>
       <c r="AA22">
         <v>1.89</v>
       </c>
       <c r="AB22">
-        <v>1.83</v>
+        <v>1.88</v>
       </c>
       <c r="AC22">
-        <v>3.08</v>
+        <v>3.4</v>
       </c>
       <c r="AD22">
         <v>1.31</v>
       </c>
       <c r="AE22">
-        <v>1.11</v>
+        <v>1.07</v>
       </c>
       <c r="AF22">
         <v>1.71</v>
@@ -4058,61 +4058,61 @@
         </is>
       </c>
       <c r="N23">
-        <v>2.95</v>
+        <v>3.2</v>
       </c>
       <c r="O23">
-        <v>3.8</v>
+        <v>3.61</v>
       </c>
       <c r="P23">
-        <v>2.2</v>
+        <v>2.03</v>
       </c>
       <c r="Q23">
-        <v>3.25</v>
+        <v>3.04</v>
       </c>
       <c r="R23">
-        <v>2.38</v>
+        <v>2.31</v>
       </c>
       <c r="S23">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="T23">
-        <v>3.5</v>
+        <v>3.58</v>
       </c>
       <c r="U23">
-        <v>2.18</v>
+        <v>2.14</v>
       </c>
       <c r="V23">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="W23">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="X23">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y23">
-        <v>1.12</v>
+        <v>1.15</v>
       </c>
       <c r="Z23">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="AA23">
-        <v>1.46</v>
+        <v>1.5</v>
       </c>
       <c r="AB23">
-        <v>2.39</v>
+        <v>2.58</v>
       </c>
       <c r="AC23">
-        <v>2.17</v>
+        <v>2.16</v>
       </c>
       <c r="AD23">
-        <v>1.64</v>
+        <v>1.62</v>
       </c>
       <c r="AE23">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="AF23">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AG23">
         <v>2.63</v>
@@ -4128,10 +4128,10 @@
         </is>
       </c>
       <c r="AJ23">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="AK23">
-        <v>1.36</v>
+        <v>1.32</v>
       </c>
       <c r="AL23">
         <v>0</v>
@@ -4221,25 +4221,25 @@
         </is>
       </c>
       <c r="N24">
-        <v>2.82</v>
+        <v>2.8</v>
       </c>
       <c r="O24">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="P24">
-        <v>2.25</v>
+        <v>2.4</v>
       </c>
       <c r="Q24">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="R24">
         <v>1.95</v>
       </c>
       <c r="S24">
-        <v>1.49</v>
+        <v>1.45</v>
       </c>
       <c r="T24">
-        <v>2.41</v>
+        <v>2.65</v>
       </c>
       <c r="U24">
         <v>3.29</v>
@@ -4254,7 +4254,7 @@
         <v>1.04</v>
       </c>
       <c r="Y24">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="Z24">
         <v>2.7</v>
@@ -4291,10 +4291,10 @@
         </is>
       </c>
       <c r="AJ24">
-        <v>1.52</v>
+        <v>1.27</v>
       </c>
       <c r="AK24">
-        <v>1.39</v>
+        <v>1.37</v>
       </c>
       <c r="AL24">
         <v>0</v>
@@ -4710,34 +4710,34 @@
         </is>
       </c>
       <c r="N27">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="O27">
         <v>4.8</v>
       </c>
       <c r="P27">
-        <v>6.8</v>
+        <v>7.3</v>
       </c>
       <c r="Q27">
-        <v>1.77</v>
+        <v>1.71</v>
       </c>
       <c r="R27">
-        <v>2.55</v>
+        <v>2.47</v>
       </c>
       <c r="S27">
         <v>1.24</v>
       </c>
       <c r="T27">
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="U27">
-        <v>2.23</v>
+        <v>2.25</v>
       </c>
       <c r="V27">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="W27">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="X27">
         <v>1.02</v>
@@ -4752,22 +4752,22 @@
         <v>1.55</v>
       </c>
       <c r="AB27">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="AC27">
-        <v>2.21</v>
+        <v>2.25</v>
       </c>
       <c r="AD27">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="AE27">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="AF27">
         <v>1.8</v>
       </c>
       <c r="AG27">
-        <v>1.92</v>
+        <v>1.94</v>
       </c>
       <c r="AH27" t="inlineStr">
         <is>
@@ -4783,7 +4783,7 @@
         <v>1.05</v>
       </c>
       <c r="AK27">
-        <v>3.2</v>
+        <v>2.97</v>
       </c>
       <c r="AL27">
         <v>0</v>
@@ -4873,28 +4873,28 @@
         </is>
       </c>
       <c r="N28">
-        <v>1.72</v>
+        <v>1.68</v>
       </c>
       <c r="O28">
         <v>3.75</v>
       </c>
       <c r="P28">
-        <v>3.8</v>
+        <v>4.7</v>
       </c>
       <c r="Q28">
         <v>2.1</v>
       </c>
       <c r="R28">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="S28">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="T28">
-        <v>3.6</v>
+        <v>3.28</v>
       </c>
       <c r="U28">
-        <v>2.45</v>
+        <v>2.44</v>
       </c>
       <c r="V28">
         <v>1.55</v>
@@ -4903,34 +4903,34 @@
         <v>1.11</v>
       </c>
       <c r="X28">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y28">
-        <v>1.2</v>
+        <v>1.16</v>
       </c>
       <c r="Z28">
-        <v>4.15</v>
+        <v>4.2</v>
       </c>
       <c r="AA28">
         <v>1.63</v>
       </c>
       <c r="AB28">
-        <v>2.23</v>
+        <v>2.29</v>
       </c>
       <c r="AC28">
-        <v>2.63</v>
+        <v>2.58</v>
       </c>
       <c r="AD28">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="AE28">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="AF28">
-        <v>1.57</v>
+        <v>1.65</v>
       </c>
       <c r="AG28">
-        <v>2.23</v>
+        <v>2.15</v>
       </c>
       <c r="AH28" t="inlineStr">
         <is>
@@ -4943,10 +4943,10 @@
         </is>
       </c>
       <c r="AJ28">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="AK28">
-        <v>2.12</v>
+        <v>2.17</v>
       </c>
       <c r="AL28">
         <v>0</v>
@@ -5036,13 +5036,13 @@
         </is>
       </c>
       <c r="N29">
-        <v>1.65</v>
+        <v>1.7</v>
       </c>
       <c r="O29">
-        <v>3.52</v>
+        <v>3.67</v>
       </c>
       <c r="P29">
-        <v>7.24</v>
+        <v>4.9</v>
       </c>
       <c r="Q29">
         <v>0</v>
@@ -5199,16 +5199,16 @@
         </is>
       </c>
       <c r="N30">
-        <v>2.04</v>
+        <v>1.99</v>
       </c>
       <c r="O30">
         <v>3.4</v>
       </c>
       <c r="P30">
-        <v>3.15</v>
+        <v>3</v>
       </c>
       <c r="Q30">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="R30">
         <v>2.19</v>
@@ -5217,7 +5217,7 @@
         <v>1.3</v>
       </c>
       <c r="T30">
-        <v>3.12</v>
+        <v>3.2</v>
       </c>
       <c r="U30">
         <v>2.5</v>
@@ -5229,25 +5229,25 @@
         <v>1.08</v>
       </c>
       <c r="X30">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y30">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="Z30">
-        <v>3.86</v>
+        <v>4.2</v>
       </c>
       <c r="AA30">
-        <v>1.74</v>
+        <v>1.72</v>
       </c>
       <c r="AB30">
         <v>2</v>
       </c>
       <c r="AC30">
-        <v>2.74</v>
+        <v>2.88</v>
       </c>
       <c r="AD30">
-        <v>1.35</v>
+        <v>1.4</v>
       </c>
       <c r="AE30">
         <v>1.09</v>
@@ -5362,7 +5362,7 @@
         </is>
       </c>
       <c r="N31">
-        <v>1.6</v>
+        <v>1.43</v>
       </c>
       <c r="O31">
         <v>3.7</v>
@@ -5371,55 +5371,55 @@
         <v>4.7</v>
       </c>
       <c r="Q31">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="R31">
-        <v>2.37</v>
+        <v>2.15</v>
       </c>
       <c r="S31">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="T31">
-        <v>2.9</v>
+        <v>2.85</v>
       </c>
       <c r="U31">
-        <v>2.55</v>
+        <v>2.73</v>
       </c>
       <c r="V31">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="W31">
         <v>1.05</v>
       </c>
       <c r="X31">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y31">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="Z31">
-        <v>3.42</v>
+        <v>3.34</v>
       </c>
       <c r="AA31">
-        <v>1.88</v>
+        <v>1.92</v>
       </c>
       <c r="AB31">
-        <v>1.94</v>
+        <v>1.9</v>
       </c>
       <c r="AC31">
-        <v>2.97</v>
+        <v>3.05</v>
       </c>
       <c r="AD31">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="AE31">
         <v>1.1</v>
       </c>
       <c r="AF31">
-        <v>1.91</v>
+        <v>1.87</v>
       </c>
       <c r="AG31">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="AH31" t="inlineStr">
         <is>
@@ -5432,10 +5432,10 @@
         </is>
       </c>
       <c r="AJ31">
-        <v>1.22</v>
+        <v>1.12</v>
       </c>
       <c r="AK31">
-        <v>2.31</v>
+        <v>2.27</v>
       </c>
       <c r="AL31">
         <v>0</v>
@@ -5534,7 +5534,7 @@
         <v>2.75</v>
       </c>
       <c r="Q32">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="R32">
         <v>1.85</v>
@@ -5543,19 +5543,19 @@
         <v>1.6</v>
       </c>
       <c r="T32">
-        <v>2.2</v>
+        <v>2.14</v>
       </c>
       <c r="U32">
         <v>3.82</v>
       </c>
       <c r="V32">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="W32">
         <v>1.03</v>
       </c>
       <c r="X32">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="Y32">
         <v>1.61</v>
@@ -5576,7 +5576,7 @@
         <v>1.07</v>
       </c>
       <c r="AE32">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AF32">
         <v>2.23</v>
@@ -5688,19 +5688,19 @@
         </is>
       </c>
       <c r="N33">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="O33">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P33">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="Q33">
-        <v>3.18</v>
+        <v>3.24</v>
       </c>
       <c r="R33">
-        <v>1.95</v>
+        <v>1.98</v>
       </c>
       <c r="S33">
         <v>1.43</v>
@@ -5709,10 +5709,10 @@
         <v>2.53</v>
       </c>
       <c r="U33">
-        <v>3.1</v>
+        <v>3.22</v>
       </c>
       <c r="V33">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="W33">
         <v>1.02</v>
@@ -5721,10 +5721,10 @@
         <v>1.03</v>
       </c>
       <c r="Y33">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="Z33">
-        <v>2.81</v>
+        <v>2.98</v>
       </c>
       <c r="AA33">
         <v>2.19</v>
@@ -5733,7 +5733,7 @@
         <v>1.66</v>
       </c>
       <c r="AC33">
-        <v>3.94</v>
+        <v>3.8</v>
       </c>
       <c r="AD33">
         <v>1.19</v>
@@ -5758,7 +5758,7 @@
         </is>
       </c>
       <c r="AJ33">
-        <v>1.4</v>
+        <v>1.35</v>
       </c>
       <c r="AK33">
         <v>1.52</v>
@@ -5854,46 +5854,46 @@
         <v>1.75</v>
       </c>
       <c r="O34">
-        <v>3.7</v>
+        <v>3.9</v>
       </c>
       <c r="P34">
-        <v>4.03</v>
+        <v>4.08</v>
       </c>
       <c r="Q34">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="R34">
         <v>2.3</v>
       </c>
       <c r="S34">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="T34">
-        <v>3.6</v>
+        <v>3.11</v>
       </c>
       <c r="U34">
-        <v>2.45</v>
+        <v>2.32</v>
       </c>
       <c r="V34">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="W34">
         <v>1.1</v>
       </c>
       <c r="X34">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y34">
         <v>1.14</v>
       </c>
       <c r="Z34">
-        <v>4.4</v>
+        <v>4.42</v>
       </c>
       <c r="AA34">
-        <v>1.59</v>
+        <v>1.65</v>
       </c>
       <c r="AB34">
-        <v>2.1</v>
+        <v>2.11</v>
       </c>
       <c r="AC34">
         <v>2.38</v>
@@ -5902,7 +5902,7 @@
         <v>1.46</v>
       </c>
       <c r="AE34">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="AF34">
         <v>1.56</v>
@@ -5921,7 +5921,7 @@
         </is>
       </c>
       <c r="AJ34">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="AK34">
         <v>2</v>
@@ -6340,13 +6340,13 @@
         </is>
       </c>
       <c r="N37">
-        <v>3.5</v>
+        <v>3.25</v>
       </c>
       <c r="O37">
-        <v>3.7</v>
+        <v>3.55</v>
       </c>
       <c r="P37">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="Q37">
         <v>3.85</v>
@@ -6503,64 +6503,64 @@
         </is>
       </c>
       <c r="N38">
-        <v>7.6</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="O38">
-        <v>4.4</v>
+        <v>5.25</v>
       </c>
       <c r="P38">
-        <v>1.37</v>
+        <v>1.31</v>
       </c>
       <c r="Q38">
-        <v>7.1</v>
+        <v>7.3</v>
       </c>
       <c r="R38">
-        <v>2.47</v>
+        <v>2.54</v>
       </c>
       <c r="S38">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="T38">
-        <v>3.2</v>
+        <v>3.32</v>
       </c>
       <c r="U38">
-        <v>2.6</v>
+        <v>2.51</v>
       </c>
       <c r="V38">
-        <v>1.45</v>
+        <v>1.5</v>
       </c>
       <c r="W38">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="X38">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y38">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="Z38">
-        <v>3.74</v>
+        <v>3.94</v>
       </c>
       <c r="AA38">
-        <v>1.85</v>
+        <v>1.78</v>
       </c>
       <c r="AB38">
-        <v>2.11</v>
+        <v>2.2</v>
       </c>
       <c r="AC38">
-        <v>2.86</v>
+        <v>2.74</v>
       </c>
       <c r="AD38">
-        <v>1.39</v>
+        <v>1.43</v>
       </c>
       <c r="AE38">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="AF38">
         <v>2.02</v>
       </c>
       <c r="AG38">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="AH38" t="inlineStr">
         <is>
@@ -6573,10 +6573,10 @@
         </is>
       </c>
       <c r="AJ38">
-        <v>3.08</v>
+        <v>3.28</v>
       </c>
       <c r="AK38">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="AL38">
         <v>0</v>
@@ -6666,40 +6666,40 @@
         </is>
       </c>
       <c r="N39">
-        <v>2.17</v>
+        <v>2.18</v>
       </c>
       <c r="O39">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="P39">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="Q39">
-        <v>2.75</v>
+        <v>2.49</v>
       </c>
       <c r="R39">
-        <v>2.12</v>
+        <v>2.11</v>
       </c>
       <c r="S39">
-        <v>1.35</v>
+        <v>1.37</v>
       </c>
       <c r="T39">
-        <v>2.94</v>
+        <v>2.85</v>
       </c>
       <c r="U39">
         <v>2.75</v>
       </c>
       <c r="V39">
-        <v>1.45</v>
+        <v>1.42</v>
       </c>
       <c r="W39">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="X39">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="Y39">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="Z39">
         <v>3.85</v>
@@ -6714,16 +6714,16 @@
         <v>2.95</v>
       </c>
       <c r="AD39">
-        <v>1.34</v>
+        <v>1.37</v>
       </c>
       <c r="AE39">
         <v>1.11</v>
       </c>
       <c r="AF39">
-        <v>1.61</v>
+        <v>1.57</v>
       </c>
       <c r="AG39">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="AH39" t="inlineStr">
         <is>
@@ -6736,7 +6736,7 @@
         </is>
       </c>
       <c r="AJ39">
-        <v>1.24</v>
+        <v>1.36</v>
       </c>
       <c r="AK39">
         <v>1.65</v>
@@ -6829,64 +6829,64 @@
         </is>
       </c>
       <c r="N40">
-        <v>4.43</v>
+        <v>3.7</v>
       </c>
       <c r="O40">
-        <v>3.42</v>
+        <v>3.3</v>
       </c>
       <c r="P40">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="Q40">
-        <v>4.9</v>
+        <v>4.55</v>
       </c>
       <c r="R40">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="S40">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="T40">
-        <v>3</v>
+        <v>2.77</v>
       </c>
       <c r="U40">
-        <v>2.75</v>
+        <v>2.77</v>
       </c>
       <c r="V40">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="W40">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="X40">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y40">
-        <v>1.3</v>
+        <v>1.24</v>
       </c>
       <c r="Z40">
-        <v>3.55</v>
+        <v>3.34</v>
       </c>
       <c r="AA40">
         <v>1.9</v>
       </c>
       <c r="AB40">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="AC40">
-        <v>2.95</v>
+        <v>3.14</v>
       </c>
       <c r="AD40">
         <v>1.27</v>
       </c>
       <c r="AE40">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="AF40">
-        <v>1.9</v>
+        <v>1.75</v>
       </c>
       <c r="AG40">
-        <v>1.82</v>
+        <v>1.95</v>
       </c>
       <c r="AH40" t="inlineStr">
         <is>
@@ -6899,10 +6899,10 @@
         </is>
       </c>
       <c r="AJ40">
-        <v>1.91</v>
+        <v>1.86</v>
       </c>
       <c r="AK40">
-        <v>1.18</v>
+        <v>1.21</v>
       </c>
       <c r="AL40">
         <v>0</v>
@@ -6992,13 +6992,13 @@
         </is>
       </c>
       <c r="N41">
-        <v>3.22</v>
+        <v>2.85</v>
       </c>
       <c r="O41">
-        <v>3.02</v>
+        <v>3.1</v>
       </c>
       <c r="P41">
-        <v>2.37</v>
+        <v>2.2</v>
       </c>
       <c r="Q41">
         <v>3.75</v>
@@ -7019,13 +7019,13 @@
         <v>1.33</v>
       </c>
       <c r="W41">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="X41">
         <v>1.02</v>
       </c>
       <c r="Y41">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="Z41">
         <v>2.8</v>
@@ -7037,13 +7037,13 @@
         <v>1.73</v>
       </c>
       <c r="AC41">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="AD41">
-        <v>1.27</v>
+        <v>1.22</v>
       </c>
       <c r="AE41">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="AF41">
         <v>1.81</v>
@@ -7065,7 +7065,7 @@
         <v>1.45</v>
       </c>
       <c r="AK41">
-        <v>1.25</v>
+        <v>1.34</v>
       </c>
       <c r="AL41">
         <v>0</v>
@@ -7161,7 +7161,7 @@
         <v>3.4</v>
       </c>
       <c r="P42">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="Q42">
         <v>2.47</v>
@@ -7173,25 +7173,25 @@
         <v>1.3</v>
       </c>
       <c r="T42">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="U42">
-        <v>2.55</v>
+        <v>2.4</v>
       </c>
       <c r="V42">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="W42">
         <v>1.06</v>
       </c>
       <c r="X42">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y42">
         <v>1.17</v>
       </c>
       <c r="Z42">
-        <v>3.8</v>
+        <v>4.1</v>
       </c>
       <c r="AA42">
         <v>1.66</v>
@@ -7520,7 +7520,7 @@
         <v>2.74</v>
       </c>
       <c r="AA44">
-        <v>2.17</v>
+        <v>2.21</v>
       </c>
       <c r="AB44">
         <v>1.65</v>
@@ -7554,7 +7554,7 @@
         <v>1.24</v>
       </c>
       <c r="AK44">
-        <v>2.16</v>
+        <v>2.19</v>
       </c>
       <c r="AL44">
         <v>0</v>
@@ -7644,25 +7644,25 @@
         </is>
       </c>
       <c r="N45">
-        <v>1.53</v>
+        <v>1.49</v>
       </c>
       <c r="O45">
-        <v>4</v>
+        <v>4.33</v>
       </c>
       <c r="P45">
         <v>4.6</v>
       </c>
       <c r="Q45">
-        <v>2.02</v>
+        <v>1.91</v>
       </c>
       <c r="R45">
-        <v>2.36</v>
+        <v>2.39</v>
       </c>
       <c r="S45">
         <v>1.25</v>
       </c>
       <c r="T45">
-        <v>3.5</v>
+        <v>3.28</v>
       </c>
       <c r="U45">
         <v>2.25</v>
@@ -7674,34 +7674,34 @@
         <v>1.11</v>
       </c>
       <c r="X45">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y45">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="Z45">
-        <v>4.4</v>
+        <v>4.45</v>
       </c>
       <c r="AA45">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="AB45">
-        <v>2.45</v>
+        <v>2.32</v>
       </c>
       <c r="AC45">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="AD45">
-        <v>1.49</v>
+        <v>1.53</v>
       </c>
       <c r="AE45">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="AF45">
         <v>1.56</v>
       </c>
       <c r="AG45">
-        <v>2.18</v>
+        <v>2.1</v>
       </c>
       <c r="AH45" t="inlineStr">
         <is>
@@ -7714,10 +7714,10 @@
         </is>
       </c>
       <c r="AJ45">
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
       <c r="AK45">
-        <v>2.31</v>
+        <v>2.63</v>
       </c>
       <c r="AL45">
         <v>0</v>
@@ -7807,7 +7807,7 @@
         </is>
       </c>
       <c r="N46">
-        <v>1.37</v>
+        <v>1.48</v>
       </c>
       <c r="O46">
         <v>4.2</v>
@@ -7816,25 +7816,25 @@
         <v>5</v>
       </c>
       <c r="Q46">
-        <v>1.93</v>
+        <v>1.96</v>
       </c>
       <c r="R46">
-        <v>2.6</v>
+        <v>2.55</v>
       </c>
       <c r="S46">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="T46">
-        <v>3.42</v>
+        <v>3.75</v>
       </c>
       <c r="U46">
-        <v>2.2</v>
+        <v>2.26</v>
       </c>
       <c r="V46">
         <v>1.59</v>
       </c>
       <c r="W46">
-        <v>1.17</v>
+        <v>1.1</v>
       </c>
       <c r="X46">
         <v>1.02</v>
@@ -7843,28 +7843,28 @@
         <v>1.14</v>
       </c>
       <c r="Z46">
-        <v>5.05</v>
+        <v>5.5</v>
       </c>
       <c r="AA46">
-        <v>1.5</v>
+        <v>1.55</v>
       </c>
       <c r="AB46">
-        <v>2.48</v>
+        <v>2.3</v>
       </c>
       <c r="AC46">
-        <v>2.25</v>
+        <v>2.35</v>
       </c>
       <c r="AD46">
-        <v>1.6</v>
+        <v>1.56</v>
       </c>
       <c r="AE46">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AF46">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="AG46">
-        <v>2.19</v>
+        <v>2.1</v>
       </c>
       <c r="AH46" t="inlineStr">
         <is>
@@ -7970,31 +7970,31 @@
         </is>
       </c>
       <c r="N47">
-        <v>5.78</v>
+        <v>4.85</v>
       </c>
       <c r="O47">
-        <v>4.85</v>
+        <v>4.3</v>
       </c>
       <c r="P47">
-        <v>1.44</v>
+        <v>1.52</v>
       </c>
       <c r="Q47">
         <v>4.78</v>
       </c>
       <c r="R47">
-        <v>2.53</v>
+        <v>2.63</v>
       </c>
       <c r="S47">
         <v>1.14</v>
       </c>
       <c r="T47">
-        <v>4.6</v>
+        <v>5</v>
       </c>
       <c r="U47">
-        <v>1.73</v>
+        <v>1.82</v>
       </c>
       <c r="V47">
-        <v>2</v>
+        <v>1.96</v>
       </c>
       <c r="W47">
         <v>1.25</v>
@@ -8006,28 +8006,28 @@
         <v>1.03</v>
       </c>
       <c r="Z47">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="AA47">
         <v>1.24</v>
       </c>
       <c r="AB47">
-        <v>3.4</v>
+        <v>3.34</v>
       </c>
       <c r="AC47">
-        <v>1.71</v>
+        <v>1.91</v>
       </c>
       <c r="AD47">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AE47">
-        <v>1.43</v>
+        <v>1.47</v>
       </c>
       <c r="AF47">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="AG47">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="AH47" t="inlineStr">
         <is>
@@ -8622,7 +8622,7 @@
         </is>
       </c>
       <c r="N51">
-        <v>1.85</v>
+        <v>1.87</v>
       </c>
       <c r="O51">
         <v>3.65</v>
@@ -8631,28 +8631,28 @@
         <v>3.4</v>
       </c>
       <c r="Q51">
-        <v>2.38</v>
+        <v>2.41</v>
       </c>
       <c r="R51">
-        <v>2.22</v>
+        <v>2.23</v>
       </c>
       <c r="S51">
-        <v>1.32</v>
+        <v>1.29</v>
       </c>
       <c r="T51">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="U51">
         <v>2.4</v>
       </c>
       <c r="V51">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="W51">
         <v>1.11</v>
       </c>
       <c r="X51">
-        <v>1.04</v>
+        <v>1</v>
       </c>
       <c r="Y51">
         <v>1.22</v>
@@ -8673,13 +8673,13 @@
         <v>1.46</v>
       </c>
       <c r="AE51">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="AF51">
-        <v>1.55</v>
+        <v>1.59</v>
       </c>
       <c r="AG51">
-        <v>2.28</v>
+        <v>2.25</v>
       </c>
       <c r="AH51" t="inlineStr">
         <is>
@@ -8695,7 +8695,7 @@
         <v>1.29</v>
       </c>
       <c r="AK51">
-        <v>1.92</v>
+        <v>1.86</v>
       </c>
       <c r="AL51">
         <v>0</v>
@@ -8948,16 +8948,16 @@
         </is>
       </c>
       <c r="N53">
-        <v>2.01</v>
+        <v>2</v>
       </c>
       <c r="O53">
-        <v>3.95</v>
+        <v>3.75</v>
       </c>
       <c r="P53">
-        <v>3.05</v>
+        <v>2.8</v>
       </c>
       <c r="Q53">
-        <v>2.54</v>
+        <v>2.6</v>
       </c>
       <c r="R53">
         <v>2.5</v>
@@ -8966,31 +8966,31 @@
         <v>1.24</v>
       </c>
       <c r="T53">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="U53">
-        <v>2.2</v>
+        <v>2.32</v>
       </c>
       <c r="V53">
-        <v>1.62</v>
+        <v>1.55</v>
       </c>
       <c r="W53">
-        <v>1.17</v>
+        <v>1.13</v>
       </c>
       <c r="X53">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y53">
         <v>1.13</v>
       </c>
       <c r="Z53">
-        <v>4.25</v>
+        <v>4.8</v>
       </c>
       <c r="AA53">
-        <v>1.56</v>
+        <v>1.54</v>
       </c>
       <c r="AB53">
-        <v>2.28</v>
+        <v>2.23</v>
       </c>
       <c r="AC53">
         <v>2.27</v>
@@ -9005,7 +9005,7 @@
         <v>1.48</v>
       </c>
       <c r="AG53">
-        <v>2.47</v>
+        <v>2.45</v>
       </c>
       <c r="AH53" t="inlineStr">
         <is>
@@ -9021,7 +9021,7 @@
         <v>1.24</v>
       </c>
       <c r="AK53">
-        <v>1.75</v>
+        <v>1.72</v>
       </c>
       <c r="AL53">
         <v>0</v>
@@ -9111,10 +9111,10 @@
         </is>
       </c>
       <c r="N54">
+        <v>3.61</v>
+      </c>
+      <c r="O54">
         <v>3.5</v>
-      </c>
-      <c r="O54">
-        <v>3.55</v>
       </c>
       <c r="P54">
         <v>1.85</v>
@@ -9123,13 +9123,13 @@
         <v>3.85</v>
       </c>
       <c r="R54">
-        <v>2.38</v>
+        <v>2.25</v>
       </c>
       <c r="S54">
         <v>1.3</v>
       </c>
       <c r="T54">
-        <v>3.23</v>
+        <v>3.15</v>
       </c>
       <c r="U54">
         <v>2.47</v>
@@ -9141,34 +9141,34 @@
         <v>1.08</v>
       </c>
       <c r="X54">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y54">
         <v>1.22</v>
       </c>
       <c r="Z54">
-        <v>4</v>
+        <v>4.21</v>
       </c>
       <c r="AA54">
         <v>1.73</v>
       </c>
       <c r="AB54">
+        <v>2.13</v>
+      </c>
+      <c r="AC54">
+        <v>2.75</v>
+      </c>
+      <c r="AD54">
+        <v>1.38</v>
+      </c>
+      <c r="AE54">
+        <v>1.15</v>
+      </c>
+      <c r="AF54">
+        <v>1.63</v>
+      </c>
+      <c r="AG54">
         <v>2.1</v>
-      </c>
-      <c r="AC54">
-        <v>2.8</v>
-      </c>
-      <c r="AD54">
-        <v>1.44</v>
-      </c>
-      <c r="AE54">
-        <v>1.13</v>
-      </c>
-      <c r="AF54">
-        <v>1.6</v>
-      </c>
-      <c r="AG54">
-        <v>2.18</v>
       </c>
       <c r="AH54" t="inlineStr">
         <is>
@@ -9437,7 +9437,7 @@
         </is>
       </c>
       <c r="N56">
-        <v>2.41</v>
+        <v>2.5</v>
       </c>
       <c r="O56">
         <v>3.5</v>
@@ -9446,10 +9446,10 @@
         <v>2.39</v>
       </c>
       <c r="Q56">
-        <v>3.04</v>
+        <v>2.78</v>
       </c>
       <c r="R56">
-        <v>2.3</v>
+        <v>2.18</v>
       </c>
       <c r="S56">
         <v>1.29</v>
@@ -9458,56 +9458,56 @@
         <v>3.3</v>
       </c>
       <c r="U56">
-        <v>2.31</v>
+        <v>2.33</v>
       </c>
       <c r="V56">
         <v>1.53</v>
       </c>
       <c r="W56">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="X56">
         <v>1.02</v>
       </c>
       <c r="Y56">
-        <v>1.18</v>
+        <v>1.14</v>
       </c>
       <c r="Z56">
         <v>4.33</v>
       </c>
       <c r="AA56">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="AB56">
         <v>2.3</v>
       </c>
       <c r="AC56">
-        <v>2.6</v>
+        <v>2.46</v>
       </c>
       <c r="AD56">
+        <v>1.43</v>
+      </c>
+      <c r="AE56">
+        <v>1.15</v>
+      </c>
+      <c r="AF56">
+        <v>1.5</v>
+      </c>
+      <c r="AG56">
+        <v>2.4</v>
+      </c>
+      <c r="AH56" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI56" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ56">
         <v>1.44</v>
-      </c>
-      <c r="AE56">
-        <v>1.19</v>
-      </c>
-      <c r="AF56">
-        <v>1.49</v>
-      </c>
-      <c r="AG56">
-        <v>2.42</v>
-      </c>
-      <c r="AH56" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI56" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ56">
-        <v>1.25</v>
       </c>
       <c r="AK56">
         <v>1.47</v>
@@ -10252,31 +10252,31 @@
         </is>
       </c>
       <c r="N61">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="O61">
         <v>7.5</v>
       </c>
       <c r="P61">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="Q61">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="R61">
-        <v>2.85</v>
+        <v>2.83</v>
       </c>
       <c r="S61">
-        <v>1.21</v>
+        <v>1.14</v>
       </c>
       <c r="T61">
-        <v>3.58</v>
+        <v>5</v>
       </c>
       <c r="U61">
-        <v>1.92</v>
+        <v>1.77</v>
       </c>
       <c r="V61">
-        <v>1.77</v>
+        <v>1.75</v>
       </c>
       <c r="W61">
         <v>1.25</v>
@@ -10291,7 +10291,7 @@
         <v>5.3</v>
       </c>
       <c r="AA61">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="AB61">
         <v>3.5</v>
@@ -10300,16 +10300,16 @@
         <v>1.94</v>
       </c>
       <c r="AD61">
-        <v>1.92</v>
+        <v>1.88</v>
       </c>
       <c r="AE61">
-        <v>1.39</v>
+        <v>1.37</v>
       </c>
       <c r="AF61">
-        <v>2.01</v>
+        <v>2.03</v>
       </c>
       <c r="AG61">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="AH61" t="inlineStr">
         <is>
@@ -10415,10 +10415,10 @@
         </is>
       </c>
       <c r="N62">
-        <v>2.62</v>
+        <v>2.6</v>
       </c>
       <c r="O62">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="P62">
         <v>2.45</v>
@@ -10430,10 +10430,10 @@
         <v>2.05</v>
       </c>
       <c r="S62">
-        <v>1.41</v>
+        <v>1.38</v>
       </c>
       <c r="T62">
-        <v>2.56</v>
+        <v>2.69</v>
       </c>
       <c r="U62">
         <v>2.88</v>
@@ -10442,13 +10442,13 @@
         <v>1.36</v>
       </c>
       <c r="W62">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="X62">
         <v>1.02</v>
       </c>
       <c r="Y62">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="Z62">
         <v>2.99</v>
@@ -10457,13 +10457,13 @@
         <v>2.08</v>
       </c>
       <c r="AB62">
-        <v>1.76</v>
+        <v>1.68</v>
       </c>
       <c r="AC62">
         <v>3.38</v>
       </c>
       <c r="AD62">
-        <v>1.24</v>
+        <v>1.27</v>
       </c>
       <c r="AE62">
         <v>1.06</v>
@@ -10485,10 +10485,10 @@
         </is>
       </c>
       <c r="AJ62">
-        <v>1.29</v>
+        <v>1.32</v>
       </c>
       <c r="AK62">
-        <v>1.45</v>
+        <v>1.4</v>
       </c>
       <c r="AL62">
         <v>0</v>
@@ -10578,25 +10578,25 @@
         </is>
       </c>
       <c r="N63">
-        <v>2.3</v>
+        <v>2.22</v>
       </c>
       <c r="O63">
         <v>3.2</v>
       </c>
       <c r="P63">
-        <v>2.85</v>
+        <v>2.63</v>
       </c>
       <c r="Q63">
-        <v>2.9</v>
+        <v>2.88</v>
       </c>
       <c r="R63">
-        <v>2.13</v>
+        <v>2.14</v>
       </c>
       <c r="S63">
         <v>1.3</v>
       </c>
       <c r="T63">
-        <v>2.89</v>
+        <v>3.2</v>
       </c>
       <c r="U63">
         <v>2.5</v>
@@ -10614,16 +10614,16 @@
         <v>1.25</v>
       </c>
       <c r="Z63">
-        <v>3.44</v>
+        <v>3.8</v>
       </c>
       <c r="AA63">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="AB63">
-        <v>1.87</v>
+        <v>1.94</v>
       </c>
       <c r="AC63">
-        <v>3.14</v>
+        <v>3.02</v>
       </c>
       <c r="AD63">
         <v>1.33</v>
@@ -10635,7 +10635,7 @@
         <v>1.67</v>
       </c>
       <c r="AG63">
-        <v>2.13</v>
+        <v>2.08</v>
       </c>
       <c r="AH63" t="inlineStr">
         <is>
@@ -10651,7 +10651,7 @@
         <v>1.34</v>
       </c>
       <c r="AK63">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="AL63">
         <v>0</v>
@@ -10741,10 +10741,10 @@
         </is>
       </c>
       <c r="N64">
-        <v>1.31</v>
+        <v>1.28</v>
       </c>
       <c r="O64">
-        <v>5.55</v>
+        <v>4.75</v>
       </c>
       <c r="P64">
         <v>5.8</v>
@@ -10756,13 +10756,13 @@
         <v>2.88</v>
       </c>
       <c r="S64">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="T64">
-        <v>4.75</v>
+        <v>4.6</v>
       </c>
       <c r="U64">
-        <v>1.85</v>
+        <v>1.77</v>
       </c>
       <c r="V64">
         <v>1.88</v>
@@ -10780,16 +10780,16 @@
         <v>6.5</v>
       </c>
       <c r="AA64">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="AB64">
-        <v>3.25</v>
+        <v>3.14</v>
       </c>
       <c r="AC64">
-        <v>1.77</v>
+        <v>1.73</v>
       </c>
       <c r="AD64">
-        <v>1.95</v>
+        <v>1.98</v>
       </c>
       <c r="AE64">
         <v>1.39</v>
@@ -10904,16 +10904,16 @@
         </is>
       </c>
       <c r="N65">
-        <v>2</v>
+        <v>1.93</v>
       </c>
       <c r="O65">
         <v>3.75</v>
       </c>
       <c r="P65">
-        <v>3.35</v>
+        <v>3.05</v>
       </c>
       <c r="Q65">
-        <v>2.28</v>
+        <v>2.38</v>
       </c>
       <c r="R65">
         <v>2.5</v>
@@ -10940,25 +10940,25 @@
         <v>1.12</v>
       </c>
       <c r="Z65">
-        <v>5.25</v>
+        <v>5.5</v>
       </c>
       <c r="AA65">
-        <v>1.48</v>
+        <v>1.51</v>
       </c>
       <c r="AB65">
-        <v>2.45</v>
+        <v>2.47</v>
       </c>
       <c r="AC65">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="AD65">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="AE65">
-        <v>1.23</v>
+        <v>1.2</v>
       </c>
       <c r="AF65">
-        <v>1.43</v>
+        <v>1.5</v>
       </c>
       <c r="AG65">
         <v>2.5</v>
@@ -10974,7 +10974,7 @@
         </is>
       </c>
       <c r="AJ65">
-        <v>1.21</v>
+        <v>1.23</v>
       </c>
       <c r="AK65">
         <v>1.83</v>
@@ -11067,13 +11067,13 @@
         </is>
       </c>
       <c r="N66">
-        <v>2.21</v>
+        <v>2.32</v>
       </c>
       <c r="O66">
-        <v>3.73</v>
+        <v>3.75</v>
       </c>
       <c r="P66">
-        <v>2.18</v>
+        <v>2.32</v>
       </c>
       <c r="Q66">
         <v>2.8</v>
@@ -11082,46 +11082,46 @@
         <v>2.45</v>
       </c>
       <c r="S66">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="T66">
-        <v>4.5</v>
+        <v>3.95</v>
       </c>
       <c r="U66">
-        <v>1.9</v>
+        <v>1.92</v>
       </c>
       <c r="V66">
-        <v>1.78</v>
+        <v>1.84</v>
       </c>
       <c r="W66">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="X66">
         <v>1.01</v>
       </c>
       <c r="Y66">
-        <v>1.1</v>
+        <v>1.06</v>
       </c>
       <c r="Z66">
-        <v>6.59</v>
+        <v>7.5</v>
       </c>
       <c r="AA66">
         <v>1.32</v>
       </c>
       <c r="AB66">
-        <v>2.75</v>
+        <v>3.25</v>
       </c>
       <c r="AC66">
         <v>1.94</v>
       </c>
       <c r="AD66">
-        <v>1.84</v>
+        <v>1.93</v>
       </c>
       <c r="AE66">
         <v>1.3</v>
       </c>
       <c r="AF66">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="AG66">
         <v>3.08</v>
@@ -11239,7 +11239,7 @@
         <v>2.75</v>
       </c>
       <c r="Q67">
-        <v>2.55</v>
+        <v>2.64</v>
       </c>
       <c r="R67">
         <v>2.38</v>
@@ -11275,7 +11275,7 @@
         <v>2.52</v>
       </c>
       <c r="AC67">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="AD67">
         <v>1.68</v>
@@ -11287,7 +11287,7 @@
         <v>1.39</v>
       </c>
       <c r="AG67">
-        <v>2.75</v>
+        <v>2.8</v>
       </c>
       <c r="AH67" t="inlineStr">
         <is>
@@ -11393,7 +11393,7 @@
         </is>
       </c>
       <c r="N68">
-        <v>1.39</v>
+        <v>1.33</v>
       </c>
       <c r="O68">
         <v>4.55</v>
@@ -11408,7 +11408,7 @@
         <v>2.8</v>
       </c>
       <c r="S68">
-        <v>1.18</v>
+        <v>1.15</v>
       </c>
       <c r="T68">
         <v>4.33</v>
@@ -11420,7 +11420,7 @@
         <v>1.83</v>
       </c>
       <c r="W68">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="X68">
         <v>1.01</v>
@@ -11429,16 +11429,16 @@
         <v>1.1</v>
       </c>
       <c r="Z68">
-        <v>5.6</v>
+        <v>6.6</v>
       </c>
       <c r="AA68">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="AB68">
         <v>2.85</v>
       </c>
       <c r="AC68">
-        <v>1.88</v>
+        <v>1.92</v>
       </c>
       <c r="AD68">
         <v>1.87</v>
@@ -11447,7 +11447,7 @@
         <v>1.3</v>
       </c>
       <c r="AF68">
-        <v>1.47</v>
+        <v>1.52</v>
       </c>
       <c r="AG68">
         <v>2.44</v>
@@ -11463,7 +11463,7 @@
         </is>
       </c>
       <c r="AJ68">
-        <v>1.14</v>
+        <v>1.08</v>
       </c>
       <c r="AK68">
         <v>2.7</v>
@@ -11556,7 +11556,7 @@
         </is>
       </c>
       <c r="N69">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="O69">
         <v>4</v>
@@ -11565,10 +11565,10 @@
         <v>1.54</v>
       </c>
       <c r="Q69">
-        <v>4.78</v>
+        <v>4.5</v>
       </c>
       <c r="R69">
-        <v>2.79</v>
+        <v>2.7</v>
       </c>
       <c r="S69">
         <v>1.17</v>
@@ -11577,10 +11577,10 @@
         <v>4.15</v>
       </c>
       <c r="U69">
-        <v>1.92</v>
+        <v>1.94</v>
       </c>
       <c r="V69">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="W69">
         <v>1.18</v>
@@ -11598,22 +11598,22 @@
         <v>1.38</v>
       </c>
       <c r="AB69">
-        <v>2.92</v>
+        <v>2.7</v>
       </c>
       <c r="AC69">
-        <v>1.98</v>
+        <v>1.96</v>
       </c>
       <c r="AD69">
         <v>1.71</v>
       </c>
       <c r="AE69">
-        <v>1.31</v>
+        <v>1.36</v>
       </c>
       <c r="AF69">
         <v>1.4</v>
       </c>
       <c r="AG69">
-        <v>2.55</v>
+        <v>2.73</v>
       </c>
       <c r="AH69" t="inlineStr">
         <is>
@@ -11626,10 +11626,10 @@
         </is>
       </c>
       <c r="AJ69">
-        <v>1.18</v>
+        <v>1.14</v>
       </c>
       <c r="AK69">
-        <v>1.16</v>
+        <v>1.14</v>
       </c>
       <c r="AL69">
         <v>0</v>
@@ -11722,7 +11722,7 @@
         <v>1.57</v>
       </c>
       <c r="O70">
-        <v>3.51</v>
+        <v>3.9</v>
       </c>
       <c r="P70">
         <v>6.83</v>
@@ -11734,49 +11734,49 @@
         <v>2.1</v>
       </c>
       <c r="S70">
-        <v>1.42</v>
+        <v>1.33</v>
       </c>
       <c r="T70">
-        <v>2.65</v>
+        <v>2.91</v>
       </c>
       <c r="U70">
-        <v>2.75</v>
+        <v>2.9</v>
       </c>
       <c r="V70">
         <v>1.35</v>
       </c>
       <c r="W70">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="X70">
         <v>1.03</v>
       </c>
       <c r="Y70">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="Z70">
-        <v>2.9</v>
+        <v>3.6</v>
       </c>
       <c r="AA70">
-        <v>1.87</v>
+        <v>1.8</v>
       </c>
       <c r="AB70">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="AC70">
-        <v>3.5</v>
+        <v>3</v>
       </c>
       <c r="AD70">
-        <v>1.24</v>
+        <v>1.41</v>
       </c>
       <c r="AE70">
         <v>1.15</v>
       </c>
       <c r="AF70">
-        <v>1.65</v>
+        <v>1.8</v>
       </c>
       <c r="AG70">
-        <v>1.96</v>
+        <v>1.91</v>
       </c>
       <c r="AH70" t="inlineStr">
         <is>
@@ -11789,10 +11789,10 @@
         </is>
       </c>
       <c r="AJ70">
-        <v>1.27</v>
+        <v>1.12</v>
       </c>
       <c r="AK70">
-        <v>2.25</v>
+        <v>2.02</v>
       </c>
       <c r="AL70">
         <v>0</v>
@@ -11882,43 +11882,43 @@
         </is>
       </c>
       <c r="N71">
-        <v>1.34</v>
+        <v>1.28</v>
       </c>
       <c r="O71">
-        <v>5.44</v>
+        <v>4.6</v>
       </c>
       <c r="P71">
-        <v>11.4</v>
+        <v>7.9</v>
       </c>
       <c r="Q71">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="R71">
-        <v>2.4</v>
+        <v>2.46</v>
       </c>
       <c r="S71">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="T71">
-        <v>3.02</v>
+        <v>3.08</v>
       </c>
       <c r="U71">
-        <v>2.77</v>
+        <v>2.68</v>
       </c>
       <c r="V71">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="W71">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="X71">
         <v>1</v>
       </c>
       <c r="Y71">
-        <v>1.27</v>
+        <v>1.24</v>
       </c>
       <c r="Z71">
-        <v>3.42</v>
+        <v>3.65</v>
       </c>
       <c r="AA71">
         <v>1.86</v>
@@ -11927,19 +11927,19 @@
         <v>1.98</v>
       </c>
       <c r="AC71">
-        <v>3.28</v>
+        <v>3.09</v>
       </c>
       <c r="AD71">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AE71">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="AF71">
-        <v>2.27</v>
+        <v>2.19</v>
       </c>
       <c r="AG71">
-        <v>1.58</v>
+        <v>1.62</v>
       </c>
       <c r="AH71" t="inlineStr">
         <is>
@@ -12051,10 +12051,10 @@
         <v>3.4</v>
       </c>
       <c r="P72">
-        <v>2.55</v>
+        <v>2.47</v>
       </c>
       <c r="Q72">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="R72">
         <v>2.25</v>
@@ -12084,7 +12084,7 @@
         <v>3.8</v>
       </c>
       <c r="AA72">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="AB72">
         <v>2</v>
@@ -12371,10 +12371,10 @@
         </is>
       </c>
       <c r="N74">
-        <v>2.18</v>
+        <v>2.1</v>
       </c>
       <c r="O74">
-        <v>2.85</v>
+        <v>2.99</v>
       </c>
       <c r="P74">
         <v>3.25</v>
@@ -12386,7 +12386,7 @@
         <v>1.83</v>
       </c>
       <c r="S74">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="T74">
         <v>2.5</v>
@@ -12401,22 +12401,22 @@
         <v>1.04</v>
       </c>
       <c r="X74">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="Y74">
         <v>1.5</v>
       </c>
       <c r="Z74">
-        <v>2.44</v>
+        <v>2.52</v>
       </c>
       <c r="AA74">
         <v>2.59</v>
       </c>
       <c r="AB74">
-        <v>1.43</v>
+        <v>1.5</v>
       </c>
       <c r="AC74">
-        <v>5.25</v>
+        <v>4.75</v>
       </c>
       <c r="AD74">
         <v>1.12</v>
@@ -12425,7 +12425,7 @@
         <v>1.04</v>
       </c>
       <c r="AF74">
-        <v>2.1</v>
+        <v>2.09</v>
       </c>
       <c r="AG74">
         <v>1.63</v>
@@ -12444,7 +12444,7 @@
         <v>1.22</v>
       </c>
       <c r="AK74">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="AL74">
         <v>0</v>
@@ -12534,31 +12534,31 @@
         </is>
       </c>
       <c r="N75">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="O75">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="P75">
-        <v>2.7</v>
+        <v>2.62</v>
       </c>
       <c r="Q75">
-        <v>2.76</v>
+        <v>3.14</v>
       </c>
       <c r="R75">
         <v>2.1</v>
       </c>
       <c r="S75">
-        <v>1.3</v>
+        <v>1.34</v>
       </c>
       <c r="T75">
         <v>2.99</v>
       </c>
       <c r="U75">
-        <v>2.55</v>
+        <v>2.59</v>
       </c>
       <c r="V75">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="W75">
         <v>1.1</v>
@@ -12579,19 +12579,19 @@
         <v>1.95</v>
       </c>
       <c r="AC75">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="AD75">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AE75">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="AF75">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="AG75">
-        <v>2.18</v>
+        <v>2.05</v>
       </c>
       <c r="AH75" t="inlineStr">
         <is>
@@ -12607,7 +12607,7 @@
         <v>1.27</v>
       </c>
       <c r="AK75">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="AL75">
         <v>0</v>
@@ -12697,61 +12697,61 @@
         </is>
       </c>
       <c r="N76">
-        <v>2.75</v>
+        <v>2.5</v>
       </c>
       <c r="O76">
         <v>3.1</v>
       </c>
       <c r="P76">
-        <v>2.45</v>
+        <v>2.4</v>
       </c>
       <c r="Q76">
-        <v>3.35</v>
+        <v>3.54</v>
       </c>
       <c r="R76">
-        <v>2.1</v>
+        <v>2.04</v>
       </c>
       <c r="S76">
         <v>1.37</v>
       </c>
       <c r="T76">
-        <v>2.95</v>
+        <v>2.73</v>
       </c>
       <c r="U76">
-        <v>2.95</v>
+        <v>2.9</v>
       </c>
       <c r="V76">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="W76">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="X76">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y76">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="Z76">
-        <v>3.35</v>
+        <v>3.46</v>
       </c>
       <c r="AA76">
-        <v>2</v>
+        <v>2.04</v>
       </c>
       <c r="AB76">
-        <v>1.76</v>
+        <v>1.85</v>
       </c>
       <c r="AC76">
         <v>3.6</v>
       </c>
       <c r="AD76">
-        <v>1.23</v>
+        <v>1.26</v>
       </c>
       <c r="AE76">
-        <v>1.06</v>
+        <v>1.11</v>
       </c>
       <c r="AF76">
-        <v>1.75</v>
+        <v>1.72</v>
       </c>
       <c r="AG76">
         <v>2</v>
@@ -12767,10 +12767,10 @@
         </is>
       </c>
       <c r="AJ76">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="AK76">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="AL76">
         <v>0</v>
@@ -12866,7 +12866,7 @@
         <v>3.43</v>
       </c>
       <c r="P77">
-        <v>3</v>
+        <v>2.73</v>
       </c>
       <c r="Q77">
         <v>2.81</v>
@@ -12878,7 +12878,7 @@
         <v>1.33</v>
       </c>
       <c r="T77">
-        <v>2.89</v>
+        <v>3.17</v>
       </c>
       <c r="U77">
         <v>2.62</v>
@@ -12893,13 +12893,13 @@
         <v>1.01</v>
       </c>
       <c r="Y77">
-        <v>1.25</v>
+        <v>1.21</v>
       </c>
       <c r="Z77">
-        <v>3.7</v>
+        <v>3.62</v>
       </c>
       <c r="AA77">
-        <v>1.81</v>
+        <v>1.78</v>
       </c>
       <c r="AB77">
         <v>2</v>
@@ -12914,7 +12914,7 @@
         <v>1.08</v>
       </c>
       <c r="AF77">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="AG77">
         <v>2.14</v>
@@ -12930,10 +12930,10 @@
         </is>
       </c>
       <c r="AJ77">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AK77">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="AL77">
         <v>0</v>
@@ -13023,13 +13023,13 @@
         </is>
       </c>
       <c r="N78">
-        <v>2.21</v>
+        <v>2.2</v>
       </c>
       <c r="O78">
         <v>3.2</v>
       </c>
       <c r="P78">
-        <v>3.24</v>
+        <v>3.25</v>
       </c>
       <c r="Q78">
         <v>2.8</v>
@@ -13044,10 +13044,10 @@
         <v>2.75</v>
       </c>
       <c r="U78">
-        <v>2.95</v>
+        <v>3.1</v>
       </c>
       <c r="V78">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
       <c r="W78">
         <v>1.02</v>
@@ -13056,19 +13056,19 @@
         <v>1.04</v>
       </c>
       <c r="Y78">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="Z78">
-        <v>2.75</v>
+        <v>2.62</v>
       </c>
       <c r="AA78">
-        <v>2.25</v>
+        <v>2.38</v>
       </c>
       <c r="AB78">
         <v>1.61</v>
       </c>
       <c r="AC78">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="AD78">
         <v>1.16</v>
@@ -13080,7 +13080,7 @@
         <v>1.9</v>
       </c>
       <c r="AG78">
-        <v>1.76</v>
+        <v>1.78</v>
       </c>
       <c r="AH78" t="inlineStr">
         <is>
@@ -13096,7 +13096,7 @@
         <v>1.34</v>
       </c>
       <c r="AK78">
-        <v>1.58</v>
+        <v>1.62</v>
       </c>
       <c r="AL78">
         <v>0</v>
@@ -13210,7 +13210,7 @@
         <v>2.92</v>
       </c>
       <c r="V79">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="W79">
         <v>1.05</v>
@@ -13512,19 +13512,19 @@
         </is>
       </c>
       <c r="N81">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="O81">
         <v>3.4</v>
       </c>
       <c r="P81">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="Q81">
-        <v>4.25</v>
+        <v>4.6</v>
       </c>
       <c r="R81">
-        <v>2.26</v>
+        <v>2.11</v>
       </c>
       <c r="S81">
         <v>1.33</v>
@@ -13545,7 +13545,7 @@
         <v>1</v>
       </c>
       <c r="Y81">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="Z81">
         <v>3.3</v>
@@ -13554,7 +13554,7 @@
         <v>1.86</v>
       </c>
       <c r="AB81">
-        <v>1.81</v>
+        <v>1.94</v>
       </c>
       <c r="AC81">
         <v>2.97</v>
@@ -13566,7 +13566,7 @@
         <v>1.07</v>
       </c>
       <c r="AF81">
-        <v>1.7</v>
+        <v>1.68</v>
       </c>
       <c r="AG81">
         <v>2</v>
@@ -13838,19 +13838,19 @@
         </is>
       </c>
       <c r="N83">
-        <v>3.2</v>
+        <v>2.98</v>
       </c>
       <c r="O83">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="P83">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="Q83">
-        <v>3.81</v>
+        <v>3.28</v>
       </c>
       <c r="R83">
-        <v>2.22</v>
+        <v>2.23</v>
       </c>
       <c r="S83">
         <v>1.28</v>
@@ -13859,34 +13859,34 @@
         <v>3.18</v>
       </c>
       <c r="U83">
-        <v>2.43</v>
+        <v>2.44</v>
       </c>
       <c r="V83">
-        <v>1.51</v>
+        <v>1.55</v>
       </c>
       <c r="W83">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="X83">
         <v>1.03</v>
       </c>
       <c r="Y83">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="Z83">
-        <v>4.45</v>
+        <v>4.3</v>
       </c>
       <c r="AA83">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="AB83">
-        <v>2.15</v>
+        <v>2.14</v>
       </c>
       <c r="AC83">
-        <v>2.55</v>
+        <v>2.5</v>
       </c>
       <c r="AD83">
-        <v>1.49</v>
+        <v>1.47</v>
       </c>
       <c r="AE83">
         <v>1.15</v>
@@ -13908,10 +13908,10 @@
         </is>
       </c>
       <c r="AJ83">
-        <v>1.73</v>
+        <v>1.3</v>
       </c>
       <c r="AK83">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="AL83">
         <v>0</v>
@@ -14001,64 +14001,64 @@
         </is>
       </c>
       <c r="N84">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="O84">
-        <v>4.2</v>
+        <v>3.85</v>
       </c>
       <c r="P84">
-        <v>5.25</v>
+        <v>4.4</v>
       </c>
       <c r="Q84">
-        <v>1.83</v>
+        <v>2.05</v>
       </c>
       <c r="R84">
-        <v>2.5</v>
+        <v>2.38</v>
       </c>
       <c r="S84">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="T84">
-        <v>3.28</v>
+        <v>3.32</v>
       </c>
       <c r="U84">
         <v>2.25</v>
       </c>
       <c r="V84">
-        <v>1.56</v>
+        <v>1.52</v>
       </c>
       <c r="W84">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="X84">
         <v>1.03</v>
       </c>
       <c r="Y84">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="Z84">
-        <v>4.6</v>
+        <v>4.51</v>
       </c>
       <c r="AA84">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="AB84">
         <v>2.38</v>
       </c>
       <c r="AC84">
-        <v>2.4</v>
+        <v>2.54</v>
       </c>
       <c r="AD84">
         <v>1.54</v>
       </c>
       <c r="AE84">
-        <v>1.19</v>
+        <v>1.16</v>
       </c>
       <c r="AF84">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="AG84">
-        <v>2.05</v>
+        <v>2.12</v>
       </c>
       <c r="AH84" t="inlineStr">
         <is>
@@ -14071,10 +14071,10 @@
         </is>
       </c>
       <c r="AJ84">
-        <v>1.14</v>
+        <v>1.16</v>
       </c>
       <c r="AK84">
-        <v>2.62</v>
+        <v>2.22</v>
       </c>
       <c r="AL84">
         <v>0</v>
@@ -14170,58 +14170,58 @@
         <v>5.75</v>
       </c>
       <c r="P85">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="Q85">
-        <v>8.91</v>
+        <v>7.61</v>
       </c>
       <c r="R85">
-        <v>3.02</v>
+        <v>2.82</v>
       </c>
       <c r="S85">
         <v>1.2</v>
       </c>
       <c r="T85">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="U85">
-        <v>2.05</v>
+        <v>2.17</v>
       </c>
       <c r="V85">
-        <v>1.71</v>
+        <v>1.65</v>
       </c>
       <c r="W85">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="X85">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y85">
         <v>1.1</v>
       </c>
       <c r="Z85">
-        <v>5.25</v>
+        <v>5.15</v>
       </c>
       <c r="AA85">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="AB85">
-        <v>2.52</v>
+        <v>2.49</v>
       </c>
       <c r="AC85">
-        <v>2.11</v>
+        <v>2.14</v>
       </c>
       <c r="AD85">
-        <v>1.65</v>
+        <v>1.63</v>
       </c>
       <c r="AE85">
         <v>1.24</v>
       </c>
       <c r="AF85">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="AG85">
-        <v>1.85</v>
+        <v>1.88</v>
       </c>
       <c r="AH85" t="inlineStr">
         <is>
@@ -14234,10 +14234,10 @@
         </is>
       </c>
       <c r="AJ85">
-        <v>3.66</v>
+        <v>1.11</v>
       </c>
       <c r="AK85">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="AL85">
         <v>0</v>
@@ -14327,61 +14327,61 @@
         </is>
       </c>
       <c r="N86">
-        <v>1.48</v>
+        <v>1.53</v>
       </c>
       <c r="O86">
-        <v>4.2</v>
+        <v>4.55</v>
       </c>
       <c r="P86">
-        <v>5.25</v>
+        <v>4.8</v>
       </c>
       <c r="Q86">
-        <v>1.83</v>
+        <v>1.93</v>
       </c>
       <c r="R86">
-        <v>2.8</v>
+        <v>2.65</v>
       </c>
       <c r="S86">
-        <v>1.21</v>
+        <v>1.23</v>
       </c>
       <c r="T86">
-        <v>3.58</v>
+        <v>3.42</v>
       </c>
       <c r="U86">
-        <v>2.1</v>
+        <v>2.18</v>
       </c>
       <c r="V86">
-        <v>1.69</v>
+        <v>1.67</v>
       </c>
       <c r="W86">
-        <v>1.17</v>
+        <v>1.12</v>
       </c>
       <c r="X86">
         <v>1.02</v>
       </c>
       <c r="Y86">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="Z86">
-        <v>5.5</v>
+        <v>4.95</v>
       </c>
       <c r="AA86">
-        <v>1.44</v>
+        <v>1.49</v>
       </c>
       <c r="AB86">
-        <v>2.7</v>
+        <v>2.51</v>
       </c>
       <c r="AC86">
-        <v>2.11</v>
+        <v>2.24</v>
       </c>
       <c r="AD86">
-        <v>1.73</v>
+        <v>1.63</v>
       </c>
       <c r="AE86">
-        <v>1.25</v>
+        <v>1.21</v>
       </c>
       <c r="AF86">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="AG86">
         <v>2.3</v>
@@ -14397,10 +14397,10 @@
         </is>
       </c>
       <c r="AJ86">
-        <v>1.14</v>
+        <v>1.22</v>
       </c>
       <c r="AK86">
-        <v>2.63</v>
+        <v>2.25</v>
       </c>
       <c r="AL86">
         <v>0</v>
@@ -14490,13 +14490,13 @@
         </is>
       </c>
       <c r="N87">
-        <v>4.3</v>
+        <v>3.8</v>
       </c>
       <c r="O87">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="P87">
-        <v>1.68</v>
+        <v>1.64</v>
       </c>
       <c r="Q87">
         <v>4.4</v>
@@ -14505,43 +14505,43 @@
         <v>2.4</v>
       </c>
       <c r="S87">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="T87">
-        <v>3.34</v>
+        <v>3.42</v>
       </c>
       <c r="U87">
-        <v>2.31</v>
+        <v>2.29</v>
       </c>
       <c r="V87">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="W87">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="X87">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y87">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="Z87">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="AA87">
-        <v>1.65</v>
+        <v>1.55</v>
       </c>
       <c r="AB87">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="AC87">
-        <v>2.42</v>
+        <v>2.35</v>
       </c>
       <c r="AD87">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="AE87">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="AF87">
         <v>1.57</v>
@@ -14563,7 +14563,7 @@
         <v>2.1</v>
       </c>
       <c r="AK87">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AL87">
         <v>0</v>
@@ -14653,13 +14653,13 @@
         </is>
       </c>
       <c r="N88">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="O88">
-        <v>4.8</v>
+        <v>4.3</v>
       </c>
       <c r="P88">
-        <v>7.75</v>
+        <v>6.8</v>
       </c>
       <c r="Q88">
         <v>1.7</v>
@@ -14668,19 +14668,19 @@
         <v>2.29</v>
       </c>
       <c r="S88">
-        <v>1.3</v>
+        <v>1.35</v>
       </c>
       <c r="T88">
-        <v>3.2</v>
+        <v>2.95</v>
       </c>
       <c r="U88">
-        <v>2.54</v>
+        <v>2.66</v>
       </c>
       <c r="V88">
         <v>1.41</v>
       </c>
       <c r="W88">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="X88">
         <v>1</v>
@@ -14689,25 +14689,25 @@
         <v>1.27</v>
       </c>
       <c r="Z88">
-        <v>3.5</v>
+        <v>3.52</v>
       </c>
       <c r="AA88">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="AB88">
-        <v>1.93</v>
+        <v>2</v>
       </c>
       <c r="AC88">
-        <v>3.1</v>
+        <v>3.08</v>
       </c>
       <c r="AD88">
         <v>1.3</v>
       </c>
       <c r="AE88">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="AF88">
-        <v>2.18</v>
+        <v>2.15</v>
       </c>
       <c r="AG88">
         <v>1.61</v>
@@ -14726,7 +14726,7 @@
         <v>1.05</v>
       </c>
       <c r="AK88">
-        <v>3.12</v>
+        <v>2.91</v>
       </c>
       <c r="AL88">
         <v>0</v>
@@ -14979,19 +14979,19 @@
         </is>
       </c>
       <c r="N90">
-        <v>2.16</v>
+        <v>2.15</v>
       </c>
       <c r="O90">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="P90">
         <v>2.7</v>
       </c>
       <c r="Q90">
-        <v>2.7</v>
+        <v>2.76</v>
       </c>
       <c r="R90">
-        <v>2.22</v>
+        <v>2.3</v>
       </c>
       <c r="S90">
         <v>1.27</v>
@@ -15003,40 +15003,40 @@
         <v>2.25</v>
       </c>
       <c r="V90">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="W90">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="X90">
         <v>1.01</v>
       </c>
       <c r="Y90">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="Z90">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="AA90">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="AB90">
-        <v>2.31</v>
+        <v>2.35</v>
       </c>
       <c r="AC90">
-        <v>2.38</v>
+        <v>2.37</v>
       </c>
       <c r="AD90">
+        <v>1.53</v>
+      </c>
+      <c r="AE90">
+        <v>1.16</v>
+      </c>
+      <c r="AF90">
         <v>1.46</v>
       </c>
-      <c r="AE90">
-        <v>1.2</v>
-      </c>
-      <c r="AF90">
-        <v>1.48</v>
-      </c>
       <c r="AG90">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="AH90" t="inlineStr">
         <is>
@@ -15049,10 +15049,10 @@
         </is>
       </c>
       <c r="AJ90">
-        <v>1.36</v>
+        <v>1.22</v>
       </c>
       <c r="AK90">
-        <v>1.68</v>
+        <v>1.53</v>
       </c>
       <c r="AL90">
         <v>0</v>
@@ -15468,7 +15468,7 @@
         </is>
       </c>
       <c r="N93">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="O93">
         <v>3.3</v>
@@ -15480,49 +15480,49 @@
         <v>3.75</v>
       </c>
       <c r="R93">
-        <v>2.1</v>
+        <v>1.95</v>
       </c>
       <c r="S93">
-        <v>1.36</v>
+        <v>1.41</v>
       </c>
       <c r="T93">
         <v>2.9</v>
       </c>
       <c r="U93">
-        <v>2.62</v>
+        <v>2.59</v>
       </c>
       <c r="V93">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="W93">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="X93">
         <v>1.01</v>
       </c>
       <c r="Y93">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="Z93">
-        <v>3.5</v>
+        <v>3.58</v>
       </c>
       <c r="AA93">
-        <v>1.86</v>
+        <v>1.84</v>
       </c>
       <c r="AB93">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="AC93">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="AD93">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="AE93">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="AF93">
-        <v>1.65</v>
+        <v>1.63</v>
       </c>
       <c r="AG93">
         <v>2.11</v>
@@ -15538,10 +15538,10 @@
         </is>
       </c>
       <c r="AJ93">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="AK93">
-        <v>1.28</v>
+        <v>1.23</v>
       </c>
       <c r="AL93">
         <v>0</v>
@@ -15812,10 +15812,10 @@
         <v>1.39</v>
       </c>
       <c r="T95">
-        <v>2.9</v>
+        <v>2.77</v>
       </c>
       <c r="U95">
-        <v>2.7</v>
+        <v>2.72</v>
       </c>
       <c r="V95">
         <v>1.37</v>
@@ -15830,10 +15830,10 @@
         <v>1.3</v>
       </c>
       <c r="Z95">
-        <v>3.25</v>
+        <v>3.36</v>
       </c>
       <c r="AA95">
-        <v>1.92</v>
+        <v>2.02</v>
       </c>
       <c r="AB95">
         <v>1.8</v>
@@ -15842,7 +15842,7 @@
         <v>3.5</v>
       </c>
       <c r="AD95">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AE95">
         <v>1.05</v>
@@ -16120,10 +16120,10 @@
         </is>
       </c>
       <c r="N97">
-        <v>2.25</v>
+        <v>2.29</v>
       </c>
       <c r="O97">
-        <v>3.5</v>
+        <v>3.44</v>
       </c>
       <c r="P97">
         <v>2.6</v>
@@ -16446,31 +16446,31 @@
         </is>
       </c>
       <c r="N99">
-        <v>2.6</v>
+        <v>2.19</v>
       </c>
       <c r="O99">
-        <v>3.05</v>
+        <v>3.3</v>
       </c>
       <c r="P99">
-        <v>2.5</v>
+        <v>2.77</v>
       </c>
       <c r="Q99">
-        <v>3</v>
+        <v>2.94</v>
       </c>
       <c r="R99">
         <v>2.11</v>
       </c>
       <c r="S99">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="T99">
         <v>3.09</v>
       </c>
       <c r="U99">
-        <v>2.45</v>
+        <v>2.41</v>
       </c>
       <c r="V99">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="W99">
         <v>1.1</v>
@@ -16488,22 +16488,22 @@
         <v>1.7</v>
       </c>
       <c r="AB99">
-        <v>2</v>
+        <v>2.03</v>
       </c>
       <c r="AC99">
         <v>2.59</v>
       </c>
       <c r="AD99">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="AE99">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="AF99">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="AG99">
-        <v>2.21</v>
+        <v>2.25</v>
       </c>
       <c r="AH99" t="inlineStr">
         <is>
@@ -16612,10 +16612,10 @@
         <v>3.7</v>
       </c>
       <c r="O100">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="P100">
-        <v>1.94</v>
+        <v>1.88</v>
       </c>
       <c r="Q100">
         <v>4.33</v>
@@ -16624,7 +16624,7 @@
         <v>2.19</v>
       </c>
       <c r="S100">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="T100">
         <v>2.93</v>
@@ -16633,7 +16633,7 @@
         <v>2.77</v>
       </c>
       <c r="V100">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="W100">
         <v>1.07</v>
@@ -16642,7 +16642,7 @@
         <v>1.01</v>
       </c>
       <c r="Y100">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="Z100">
         <v>3.42</v>
@@ -16651,16 +16651,16 @@
         <v>1.91</v>
       </c>
       <c r="AB100">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="AC100">
         <v>3.1</v>
       </c>
       <c r="AD100">
-        <v>1.34</v>
+        <v>1.32</v>
       </c>
       <c r="AE100">
-        <v>1.12</v>
+        <v>1.08</v>
       </c>
       <c r="AF100">
         <v>1.74</v>
@@ -16935,34 +16935,34 @@
         </is>
       </c>
       <c r="N102">
-        <v>2.46</v>
+        <v>3.4</v>
       </c>
       <c r="O102">
-        <v>3.14</v>
+        <v>3.15</v>
       </c>
       <c r="P102">
-        <v>2.59</v>
+        <v>1.97</v>
       </c>
       <c r="Q102">
-        <v>4.1</v>
+        <v>4.26</v>
       </c>
       <c r="R102">
         <v>2</v>
       </c>
       <c r="S102">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="T102">
         <v>2.62</v>
       </c>
       <c r="U102">
-        <v>2.85</v>
+        <v>2.91</v>
       </c>
       <c r="V102">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="W102">
-        <v>1.07</v>
+        <v>1.02</v>
       </c>
       <c r="X102">
         <v>1.01</v>
@@ -16974,19 +16974,19 @@
         <v>3.08</v>
       </c>
       <c r="AA102">
-        <v>2</v>
+        <v>1.82</v>
       </c>
       <c r="AB102">
-        <v>1.72</v>
+        <v>1.54</v>
       </c>
       <c r="AC102">
         <v>3.5</v>
       </c>
       <c r="AD102">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AE102">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="AF102">
         <v>1.79</v>
@@ -17005,7 +17005,7 @@
         </is>
       </c>
       <c r="AJ102">
-        <v>1.26</v>
+        <v>1.64</v>
       </c>
       <c r="AK102">
         <v>1.3</v>
@@ -17098,13 +17098,13 @@
         </is>
       </c>
       <c r="N103">
-        <v>1.58</v>
+        <v>1.62</v>
       </c>
       <c r="O103">
-        <v>4</v>
+        <v>3.75</v>
       </c>
       <c r="P103">
-        <v>4.2</v>
+        <v>4.25</v>
       </c>
       <c r="Q103">
         <v>2.1</v>
@@ -17113,13 +17113,13 @@
         <v>2.3</v>
       </c>
       <c r="S103">
-        <v>1.29</v>
+        <v>1.32</v>
       </c>
       <c r="T103">
-        <v>3.3</v>
+        <v>3.08</v>
       </c>
       <c r="U103">
-        <v>2.54</v>
+        <v>2.44</v>
       </c>
       <c r="V103">
         <v>1.46</v>
@@ -17131,31 +17131,31 @@
         <v>1.04</v>
       </c>
       <c r="Y103">
-        <v>1.22</v>
+        <v>1.15</v>
       </c>
       <c r="Z103">
-        <v>3.95</v>
+        <v>3</v>
       </c>
       <c r="AA103">
         <v>1.73</v>
       </c>
       <c r="AB103">
-        <v>2.09</v>
+        <v>2.05</v>
       </c>
       <c r="AC103">
-        <v>2.62</v>
+        <v>2.8</v>
       </c>
       <c r="AD103">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="AE103">
         <v>1.11</v>
       </c>
       <c r="AF103">
-        <v>1.68</v>
+        <v>1.73</v>
       </c>
       <c r="AG103">
-        <v>2</v>
+        <v>2.04</v>
       </c>
       <c r="AH103" t="inlineStr">
         <is>
@@ -17168,10 +17168,10 @@
         </is>
       </c>
       <c r="AJ103">
-        <v>1.16</v>
+        <v>1.12</v>
       </c>
       <c r="AK103">
-        <v>2.3</v>
+        <v>2.05</v>
       </c>
       <c r="AL103">
         <v>0</v>
@@ -17916,10 +17916,10 @@
         <v>2.4</v>
       </c>
       <c r="O108">
-        <v>3.32</v>
+        <v>3.3</v>
       </c>
       <c r="P108">
-        <v>2.81</v>
+        <v>2.8</v>
       </c>
       <c r="Q108">
         <v>2.81</v>
@@ -17928,10 +17928,10 @@
         <v>2.04</v>
       </c>
       <c r="S108">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="T108">
-        <v>2.85</v>
+        <v>2.88</v>
       </c>
       <c r="U108">
         <v>2.85</v>
@@ -17943,7 +17943,7 @@
         <v>1.05</v>
       </c>
       <c r="X108">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y108">
         <v>1.28</v>
@@ -17952,10 +17952,10 @@
         <v>3.5</v>
       </c>
       <c r="AA108">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="AB108">
-        <v>1.89</v>
+        <v>1.85</v>
       </c>
       <c r="AC108">
         <v>3.4</v>
@@ -17964,13 +17964,13 @@
         <v>1.29</v>
       </c>
       <c r="AE108">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="AF108">
         <v>1.66</v>
       </c>
       <c r="AG108">
-        <v>2.09</v>
+        <v>2</v>
       </c>
       <c r="AH108" t="inlineStr">
         <is>
@@ -17983,10 +17983,10 @@
         </is>
       </c>
       <c r="AJ108">
-        <v>1.39</v>
+        <v>1.33</v>
       </c>
       <c r="AK108">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="AL108">
         <v>0</v>
@@ -18079,25 +18079,25 @@
         <v>1.29</v>
       </c>
       <c r="O109">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="P109">
-        <v>8.4</v>
+        <v>7.5</v>
       </c>
       <c r="Q109">
-        <v>1.74</v>
+        <v>1.72</v>
       </c>
       <c r="R109">
         <v>2.63</v>
       </c>
       <c r="S109">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="T109">
-        <v>3.26</v>
+        <v>3.2</v>
       </c>
       <c r="U109">
-        <v>2.63</v>
+        <v>2.5</v>
       </c>
       <c r="V109">
         <v>1.46</v>
@@ -18115,13 +18115,13 @@
         <v>4</v>
       </c>
       <c r="AA109">
-        <v>1.75</v>
+        <v>1.63</v>
       </c>
       <c r="AB109">
         <v>2.04</v>
       </c>
       <c r="AC109">
-        <v>2.7</v>
+        <v>2.76</v>
       </c>
       <c r="AD109">
         <v>1.43</v>
@@ -18130,10 +18130,10 @@
         <v>1.15</v>
       </c>
       <c r="AF109">
-        <v>2.12</v>
+        <v>1.98</v>
       </c>
       <c r="AG109">
-        <v>1.63</v>
+        <v>1.7</v>
       </c>
       <c r="AH109" t="inlineStr">
         <is>
@@ -18146,10 +18146,10 @@
         </is>
       </c>
       <c r="AJ109">
-        <v>1.1</v>
+        <v>1.17</v>
       </c>
       <c r="AK109">
-        <v>3.18</v>
+        <v>3</v>
       </c>
       <c r="AL109">
         <v>0</v>
@@ -18245,7 +18245,7 @@
         <v>3.08</v>
       </c>
       <c r="P110">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="Q110">
         <v>0</v>
@@ -18402,13 +18402,13 @@
         </is>
       </c>
       <c r="N111">
-        <v>1.76</v>
+        <v>1.61</v>
       </c>
       <c r="O111">
-        <v>3.2</v>
+        <v>3.5</v>
       </c>
       <c r="P111">
-        <v>4.3</v>
+        <v>5.5</v>
       </c>
       <c r="Q111">
         <v>0</v>
@@ -18565,13 +18565,13 @@
         </is>
       </c>
       <c r="N112">
-        <v>2.12</v>
+        <v>2.09</v>
       </c>
       <c r="O112">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="P112">
-        <v>3.32</v>
+        <v>3.21</v>
       </c>
       <c r="Q112">
         <v>0</v>
@@ -18731,7 +18731,7 @@
         <v>1.63</v>
       </c>
       <c r="O113">
-        <v>3.8</v>
+        <v>3.65</v>
       </c>
       <c r="P113">
         <v>4.4</v>
@@ -18740,13 +18740,13 @@
         <v>2.15</v>
       </c>
       <c r="R113">
-        <v>2.28</v>
+        <v>2.38</v>
       </c>
       <c r="S113">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="T113">
-        <v>3.4</v>
+        <v>3.28</v>
       </c>
       <c r="U113">
         <v>2.5</v>
@@ -18755,25 +18755,25 @@
         <v>1.5</v>
       </c>
       <c r="W113">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="X113">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y113">
         <v>1.22</v>
       </c>
       <c r="Z113">
-        <v>4.06</v>
+        <v>4</v>
       </c>
       <c r="AA113">
-        <v>1.72</v>
+        <v>1.7</v>
       </c>
       <c r="AB113">
-        <v>2.09</v>
+        <v>2.2</v>
       </c>
       <c r="AC113">
-        <v>2.69</v>
+        <v>2.7</v>
       </c>
       <c r="AD113">
         <v>1.4</v>
@@ -18785,7 +18785,7 @@
         <v>1.7</v>
       </c>
       <c r="AG113">
-        <v>1.95</v>
+        <v>2.01</v>
       </c>
       <c r="AH113" t="inlineStr">
         <is>
@@ -18801,7 +18801,7 @@
         <v>1.18</v>
       </c>
       <c r="AK113">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="AL113">
         <v>0</v>
@@ -18891,16 +18891,16 @@
         </is>
       </c>
       <c r="N114">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="O114">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="P114">
-        <v>1.89</v>
+        <v>1.84</v>
       </c>
       <c r="Q114">
-        <v>4.49</v>
+        <v>4.82</v>
       </c>
       <c r="R114">
         <v>2.2</v>
@@ -18909,43 +18909,43 @@
         <v>1.35</v>
       </c>
       <c r="T114">
-        <v>2.95</v>
+        <v>3.16</v>
       </c>
       <c r="U114">
-        <v>2.63</v>
+        <v>2.68</v>
       </c>
       <c r="V114">
-        <v>1.48</v>
+        <v>1.44</v>
       </c>
       <c r="W114">
         <v>1.1</v>
       </c>
       <c r="X114">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="Y114">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="Z114">
-        <v>3.69</v>
+        <v>3.6</v>
       </c>
       <c r="AA114">
-        <v>1.83</v>
+        <v>1.76</v>
       </c>
       <c r="AB114">
-        <v>1.89</v>
+        <v>1.92</v>
       </c>
       <c r="AC114">
-        <v>3</v>
+        <v>2.95</v>
       </c>
       <c r="AD114">
         <v>1.33</v>
       </c>
       <c r="AE114">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="AF114">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="AG114">
         <v>2</v>
@@ -18961,7 +18961,7 @@
         </is>
       </c>
       <c r="AJ114">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="AK114">
         <v>1.17</v>
@@ -19054,64 +19054,64 @@
         </is>
       </c>
       <c r="N115">
-        <v>1.94</v>
+        <v>1.8</v>
       </c>
       <c r="O115">
-        <v>3.44</v>
+        <v>3.52</v>
       </c>
       <c r="P115">
-        <v>3.74</v>
+        <v>3.8</v>
       </c>
       <c r="Q115">
-        <v>2.47</v>
+        <v>2.4</v>
       </c>
       <c r="R115">
-        <v>2.11</v>
+        <v>2.28</v>
       </c>
       <c r="S115">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="T115">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="U115">
-        <v>2.62</v>
+        <v>2.6</v>
       </c>
       <c r="V115">
         <v>1.44</v>
       </c>
       <c r="W115">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="X115">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y115">
         <v>1.24</v>
       </c>
       <c r="Z115">
-        <v>3.76</v>
+        <v>3.99</v>
       </c>
       <c r="AA115">
-        <v>1.83</v>
+        <v>1.78</v>
       </c>
       <c r="AB115">
         <v>1.97</v>
       </c>
       <c r="AC115">
-        <v>2.88</v>
+        <v>3</v>
       </c>
       <c r="AD115">
-        <v>1.32</v>
+        <v>1.38</v>
       </c>
       <c r="AE115">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="AF115">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="AG115">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="AH115" t="inlineStr">
         <is>
@@ -19124,10 +19124,10 @@
         </is>
       </c>
       <c r="AJ115">
-        <v>1.27</v>
+        <v>1.23</v>
       </c>
       <c r="AK115">
-        <v>1.75</v>
+        <v>1.84</v>
       </c>
       <c r="AL115">
         <v>0</v>
@@ -19217,19 +19217,19 @@
         </is>
       </c>
       <c r="N116">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="O116">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="P116">
-        <v>5.79</v>
+        <v>5.75</v>
       </c>
       <c r="Q116">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="R116">
-        <v>2.5</v>
+        <v>2.35</v>
       </c>
       <c r="S116">
         <v>1.27</v>
@@ -19241,31 +19241,31 @@
         <v>2.25</v>
       </c>
       <c r="V116">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="W116">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="X116">
         <v>1.01</v>
       </c>
       <c r="Y116">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="Z116">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="AA116">
-        <v>1.6</v>
+        <v>1.58</v>
       </c>
       <c r="AB116">
-        <v>2.14</v>
+        <v>2.3</v>
       </c>
       <c r="AC116">
-        <v>2.43</v>
+        <v>2.41</v>
       </c>
       <c r="AD116">
-        <v>1.45</v>
+        <v>1.52</v>
       </c>
       <c r="AE116">
         <v>1.14</v>
@@ -19274,7 +19274,7 @@
         <v>1.7</v>
       </c>
       <c r="AG116">
-        <v>2.01</v>
+        <v>1.98</v>
       </c>
       <c r="AH116" t="inlineStr">
         <is>
@@ -19287,10 +19287,10 @@
         </is>
       </c>
       <c r="AJ116">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="AK116">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="AL116">
         <v>0</v>
@@ -19380,16 +19380,16 @@
         </is>
       </c>
       <c r="N117">
-        <v>1.17</v>
+        <v>1.23</v>
       </c>
       <c r="O117">
-        <v>5.5</v>
+        <v>4.85</v>
       </c>
       <c r="P117">
-        <v>9.5</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="Q117">
-        <v>1.68</v>
+        <v>1.65</v>
       </c>
       <c r="R117">
         <v>2.5</v>
@@ -19401,7 +19401,7 @@
         <v>3.1</v>
       </c>
       <c r="U117">
-        <v>2.59</v>
+        <v>2.62</v>
       </c>
       <c r="V117">
         <v>1.44</v>
@@ -19410,16 +19410,16 @@
         <v>1.1</v>
       </c>
       <c r="X117">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="Y117">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="Z117">
-        <v>3.56</v>
+        <v>3.51</v>
       </c>
       <c r="AA117">
-        <v>1.72</v>
+        <v>1.8</v>
       </c>
       <c r="AB117">
         <v>1.96</v>
@@ -19434,7 +19434,7 @@
         <v>1.12</v>
       </c>
       <c r="AF117">
-        <v>2.49</v>
+        <v>2.46</v>
       </c>
       <c r="AG117">
         <v>1.48</v>
@@ -19450,10 +19450,10 @@
         </is>
       </c>
       <c r="AJ117">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AK117">
-        <v>3.68</v>
+        <v>3.52</v>
       </c>
       <c r="AL117">
         <v>0</v>
@@ -19869,31 +19869,31 @@
         </is>
       </c>
       <c r="N120">
-        <v>2.03</v>
+        <v>1.95</v>
       </c>
       <c r="O120">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="P120">
-        <v>3.31</v>
+        <v>3.4</v>
       </c>
       <c r="Q120">
-        <v>2.64</v>
+        <v>2.6</v>
       </c>
       <c r="R120">
-        <v>2.15</v>
+        <v>2.17</v>
       </c>
       <c r="S120">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="T120">
-        <v>2.8</v>
+        <v>2.81</v>
       </c>
       <c r="U120">
-        <v>2.88</v>
+        <v>3.05</v>
       </c>
       <c r="V120">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="W120">
         <v>1.05</v>
@@ -19905,16 +19905,16 @@
         <v>1.3</v>
       </c>
       <c r="Z120">
-        <v>2.92</v>
+        <v>2.97</v>
       </c>
       <c r="AA120">
         <v>2</v>
       </c>
       <c r="AB120">
-        <v>1.77</v>
+        <v>1.71</v>
       </c>
       <c r="AC120">
-        <v>3.42</v>
+        <v>3.34</v>
       </c>
       <c r="AD120">
         <v>1.28</v>
@@ -19926,7 +19926,7 @@
         <v>1.83</v>
       </c>
       <c r="AG120">
-        <v>1.85</v>
+        <v>1.87</v>
       </c>
       <c r="AH120" t="inlineStr">
         <is>
@@ -19939,7 +19939,7 @@
         </is>
       </c>
       <c r="AJ120">
-        <v>1.22</v>
+        <v>1.28</v>
       </c>
       <c r="AK120">
         <v>1.77</v>
@@ -20032,28 +20032,28 @@
         </is>
       </c>
       <c r="N121">
-        <v>2.12</v>
+        <v>2.25</v>
       </c>
       <c r="O121">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="P121">
-        <v>3.05</v>
+        <v>2.89</v>
       </c>
       <c r="Q121">
-        <v>2.84</v>
+        <v>2.9</v>
       </c>
       <c r="R121">
-        <v>1.97</v>
+        <v>1.96</v>
       </c>
       <c r="S121">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="T121">
-        <v>2.48</v>
+        <v>2.33</v>
       </c>
       <c r="U121">
-        <v>3.09</v>
+        <v>3.2</v>
       </c>
       <c r="V121">
         <v>1.35</v>
@@ -20071,22 +20071,22 @@
         <v>2.74</v>
       </c>
       <c r="AA121">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="AB121">
         <v>1.62</v>
       </c>
       <c r="AC121">
-        <v>4.2</v>
+        <v>3.82</v>
       </c>
       <c r="AD121">
-        <v>1.19</v>
+        <v>1.16</v>
       </c>
       <c r="AE121">
         <v>1.03</v>
       </c>
       <c r="AF121">
-        <v>2</v>
+        <v>1.86</v>
       </c>
       <c r="AG121">
         <v>1.68</v>
@@ -20105,7 +20105,7 @@
         <v>1.28</v>
       </c>
       <c r="AK121">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="AL121">
         <v>0</v>
@@ -21339,22 +21339,22 @@
         <v>1.55</v>
       </c>
       <c r="O129">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="P129">
         <v>5.25</v>
       </c>
       <c r="Q129">
+        <v>2.07</v>
+      </c>
+      <c r="R129">
         <v>2.08</v>
-      </c>
-      <c r="R129">
-        <v>2.07</v>
       </c>
       <c r="S129">
         <v>1.44</v>
       </c>
       <c r="T129">
-        <v>2.69</v>
+        <v>2.75</v>
       </c>
       <c r="U129">
         <v>3.25</v>
@@ -21363,7 +21363,7 @@
         <v>1.32</v>
       </c>
       <c r="W129">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="X129">
         <v>1.03</v>
@@ -21372,25 +21372,25 @@
         <v>1.42</v>
       </c>
       <c r="Z129">
-        <v>2.74</v>
+        <v>2.77</v>
       </c>
       <c r="AA129">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="AB129">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="AC129">
         <v>3.84</v>
       </c>
       <c r="AD129">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="AE129">
         <v>1.06</v>
       </c>
       <c r="AF129">
-        <v>2.17</v>
+        <v>2.19</v>
       </c>
       <c r="AG129">
         <v>1.65</v>
@@ -21662,64 +21662,64 @@
         </is>
       </c>
       <c r="N131">
+        <v>2.52</v>
+      </c>
+      <c r="O131">
+        <v>3.35</v>
+      </c>
+      <c r="P131">
         <v>2.35</v>
       </c>
-      <c r="O131">
-        <v>3.45</v>
-      </c>
-      <c r="P131">
-        <v>2.45</v>
-      </c>
       <c r="Q131">
-        <v>3.05</v>
+        <v>3.2</v>
       </c>
       <c r="R131">
-        <v>2.13</v>
+        <v>2.2</v>
       </c>
       <c r="S131">
-        <v>1.32</v>
+        <v>1.28</v>
       </c>
       <c r="T131">
-        <v>2.96</v>
+        <v>3.15</v>
       </c>
       <c r="U131">
-        <v>2.66</v>
+        <v>2.53</v>
       </c>
       <c r="V131">
-        <v>1.39</v>
+        <v>1.43</v>
       </c>
       <c r="W131">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="X131">
         <v>1.01</v>
       </c>
       <c r="Y131">
-        <v>1.22</v>
+        <v>1.26</v>
       </c>
       <c r="Z131">
-        <v>3.5</v>
+        <v>3.25</v>
       </c>
       <c r="AA131">
-        <v>1.83</v>
+        <v>1.72</v>
       </c>
       <c r="AB131">
-        <v>1.96</v>
+        <v>2.07</v>
       </c>
       <c r="AC131">
-        <v>3.04</v>
+        <v>2.78</v>
       </c>
       <c r="AD131">
-        <v>1.29</v>
+        <v>1.34</v>
       </c>
       <c r="AE131">
-        <v>1.07</v>
+        <v>1.09</v>
       </c>
       <c r="AF131">
-        <v>1.64</v>
+        <v>1.67</v>
       </c>
       <c r="AG131">
-        <v>2.1</v>
+        <v>2.02</v>
       </c>
       <c r="AH131" t="inlineStr">
         <is>
@@ -21732,10 +21732,10 @@
         </is>
       </c>
       <c r="AJ131">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="AK131">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="AL131">
         <v>0</v>
@@ -21988,13 +21988,13 @@
         </is>
       </c>
       <c r="N133">
-        <v>4.37</v>
+        <v>4.85</v>
       </c>
       <c r="O133">
-        <v>3.72</v>
+        <v>3.8</v>
       </c>
       <c r="P133">
-        <v>1.66</v>
+        <v>1.54</v>
       </c>
       <c r="Q133">
         <v>0</v>
@@ -22314,16 +22314,16 @@
         </is>
       </c>
       <c r="N135">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="O135">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="P135">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Q135">
-        <v>3.6</v>
+        <v>3.75</v>
       </c>
       <c r="R135">
         <v>1.95</v>
@@ -22341,7 +22341,7 @@
         <v>1.27</v>
       </c>
       <c r="W135">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="X135">
         <v>1.09</v>
@@ -22359,7 +22359,7 @@
         <v>1.58</v>
       </c>
       <c r="AC135">
-        <v>4.2</v>
+        <v>4.19</v>
       </c>
       <c r="AD135">
         <v>1.17</v>

--- a/jogos_2026-08-02.xlsx
+++ b/jogos_2026-08-02.xlsx
@@ -641,25 +641,25 @@
         <v>4.75</v>
       </c>
       <c r="P2">
-        <v>7.95</v>
+        <v>7</v>
       </c>
       <c r="Q2">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="R2">
-        <v>2.77</v>
+        <v>2.63</v>
       </c>
       <c r="S2">
         <v>1.22</v>
       </c>
       <c r="T2">
-        <v>3.75</v>
+        <v>3.5</v>
       </c>
       <c r="U2">
-        <v>2.29</v>
+        <v>2.06</v>
       </c>
       <c r="V2">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="W2">
         <v>1.12</v>
@@ -668,7 +668,7 @@
         <v>1.01</v>
       </c>
       <c r="Y2">
-        <v>1.15</v>
+        <v>1.13</v>
       </c>
       <c r="Z2">
         <v>4.55</v>
@@ -677,19 +677,19 @@
         <v>1.5</v>
       </c>
       <c r="AB2">
-        <v>2.51</v>
+        <v>2.28</v>
       </c>
       <c r="AC2">
         <v>2.34</v>
       </c>
       <c r="AD2">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="AE2">
         <v>1.2</v>
       </c>
       <c r="AF2">
-        <v>1.73</v>
+        <v>1.82</v>
       </c>
       <c r="AG2">
         <v>1.87</v>
@@ -798,7 +798,7 @@
         </is>
       </c>
       <c r="N3">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="O3">
         <v>3.13</v>
@@ -807,16 +807,16 @@
         <v>3.52</v>
       </c>
       <c r="Q3">
-        <v>2.45</v>
+        <v>2.47</v>
       </c>
       <c r="R3">
         <v>2.1</v>
       </c>
       <c r="S3">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="T3">
-        <v>2.75</v>
+        <v>2.83</v>
       </c>
       <c r="U3">
         <v>2.73</v>
@@ -837,10 +837,10 @@
         <v>3.2</v>
       </c>
       <c r="AA3">
-        <v>1.95</v>
+        <v>1.88</v>
       </c>
       <c r="AB3">
-        <v>1.81</v>
+        <v>1.85</v>
       </c>
       <c r="AC3">
         <v>3.14</v>
@@ -852,10 +852,10 @@
         <v>1.07</v>
       </c>
       <c r="AF3">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="AG3">
-        <v>1.9</v>
+        <v>1.94</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -868,7 +868,7 @@
         </is>
       </c>
       <c r="AJ3">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="AK3">
         <v>1.83</v>
@@ -929,12 +929,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Rockdale City Suns</t>
+          <t>Blacktown City</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Manly United</t>
+          <t>Sydney II</t>
         </is>
       </c>
       <c r="G4">
@@ -961,64 +961,64 @@
         </is>
       </c>
       <c r="N4">
-        <v>1.76</v>
+        <v>1.92</v>
       </c>
       <c r="O4">
-        <v>3.8</v>
+        <v>3.21</v>
       </c>
       <c r="P4">
-        <v>3.55</v>
+        <v>3.24</v>
       </c>
       <c r="Q4">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="R4">
-        <v>2.25</v>
+        <v>2.18</v>
       </c>
       <c r="S4">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="T4">
-        <v>3.28</v>
+        <v>3.25</v>
       </c>
       <c r="U4">
-        <v>2.37</v>
+        <v>2.44</v>
       </c>
       <c r="V4">
-        <v>1.57</v>
+        <v>1.45</v>
       </c>
       <c r="W4">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="X4">
         <v>1.02</v>
       </c>
       <c r="Y4">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="Z4">
-        <v>4.35</v>
+        <v>3.92</v>
       </c>
       <c r="AA4">
-        <v>1.6</v>
+        <v>1.67</v>
       </c>
       <c r="AB4">
-        <v>2.25</v>
+        <v>2.08</v>
       </c>
       <c r="AC4">
-        <v>2.28</v>
+        <v>2.62</v>
       </c>
       <c r="AD4">
-        <v>1.48</v>
+        <v>1.41</v>
       </c>
       <c r="AE4">
-        <v>1.14</v>
+        <v>1.11</v>
       </c>
       <c r="AF4">
-        <v>1.54</v>
+        <v>1.62</v>
       </c>
       <c r="AG4">
-        <v>2.26</v>
+        <v>2.19</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1031,10 +1031,10 @@
         </is>
       </c>
       <c r="AJ4">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="AK4">
-        <v>1.91</v>
+        <v>1.73</v>
       </c>
       <c r="AL4">
         <v>0</v>
@@ -1092,12 +1092,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Marconi Stallions</t>
+          <t>Rockdale City Suns</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>St George City FA</t>
+          <t>Manly United</t>
         </is>
       </c>
       <c r="G5">
@@ -1124,64 +1124,64 @@
         </is>
       </c>
       <c r="N5">
-        <v>1.32</v>
+        <v>1.71</v>
       </c>
       <c r="O5">
-        <v>4.65</v>
+        <v>3.7</v>
       </c>
       <c r="P5">
-        <v>6.7</v>
+        <v>3.55</v>
       </c>
       <c r="Q5">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="R5">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="S5">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T5">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="U5">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="V5">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="W5">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="X5">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y5">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="Z5">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="AA5">
-        <v>1.72</v>
+        <v>1.54</v>
       </c>
       <c r="AB5">
-        <v>2.07</v>
+        <v>2.19</v>
       </c>
       <c r="AC5">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="AD5">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AE5">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AF5">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AG5">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1194,10 +1194,10 @@
         </is>
       </c>
       <c r="AJ5">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AK5">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AL5">
         <v>0</v>
@@ -1255,12 +1255,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Blacktown City</t>
+          <t>Marconi Stallions</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Sydney II</t>
+          <t>St George City FA</t>
         </is>
       </c>
       <c r="G6">
@@ -1287,64 +1287,64 @@
         </is>
       </c>
       <c r="N6">
-        <v>1.85</v>
+        <v>1.32</v>
       </c>
       <c r="O6">
-        <v>3.5</v>
+        <v>4.45</v>
       </c>
       <c r="P6">
-        <v>3.2</v>
+        <v>6.7</v>
       </c>
       <c r="Q6">
-        <v>2.44</v>
+        <v>1.76</v>
       </c>
       <c r="R6">
-        <v>2.18</v>
+        <v>2.47</v>
       </c>
       <c r="S6">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="T6">
-        <v>3.04</v>
+        <v>3.14</v>
       </c>
       <c r="U6">
-        <v>2.44</v>
+        <v>2.41</v>
       </c>
       <c r="V6">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="W6">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="X6">
         <v>1.02</v>
       </c>
       <c r="Y6">
-        <v>1.16</v>
+        <v>1.19</v>
       </c>
       <c r="Z6">
-        <v>3.92</v>
+        <v>3.86</v>
       </c>
       <c r="AA6">
         <v>1.67</v>
       </c>
       <c r="AB6">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="AC6">
         <v>2.62</v>
       </c>
       <c r="AD6">
-        <v>1.41</v>
+        <v>1.38</v>
       </c>
       <c r="AE6">
-        <v>1.17</v>
+        <v>1.12</v>
       </c>
       <c r="AF6">
-        <v>1.62</v>
+        <v>1.99</v>
       </c>
       <c r="AG6">
-        <v>2.15</v>
+        <v>1.7</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1357,10 +1357,10 @@
         </is>
       </c>
       <c r="AJ6">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="AK6">
-        <v>1.73</v>
+        <v>3.04</v>
       </c>
       <c r="AL6">
         <v>0</v>
@@ -1450,25 +1450,25 @@
         </is>
       </c>
       <c r="N7">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="O7">
-        <v>4.39</v>
+        <v>4.5</v>
       </c>
       <c r="P7">
-        <v>1.36</v>
+        <v>1.39</v>
       </c>
       <c r="Q7">
-        <v>5.79</v>
+        <v>5.1</v>
       </c>
       <c r="R7">
-        <v>2.55</v>
+        <v>2.54</v>
       </c>
       <c r="S7">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="T7">
-        <v>3.74</v>
+        <v>4</v>
       </c>
       <c r="U7">
         <v>2.1</v>
@@ -1477,7 +1477,7 @@
         <v>1.64</v>
       </c>
       <c r="W7">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="X7">
         <v>1.02</v>
@@ -1486,28 +1486,28 @@
         <v>1.09</v>
       </c>
       <c r="Z7">
-        <v>5.35</v>
+        <v>5.3</v>
       </c>
       <c r="AA7">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="AB7">
-        <v>2.56</v>
+        <v>2.52</v>
       </c>
       <c r="AC7">
         <v>2.15</v>
       </c>
       <c r="AD7">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="AE7">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="AF7">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="AG7">
-        <v>2.1</v>
+        <v>2.16</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1520,7 +1520,7 @@
         </is>
       </c>
       <c r="AJ7">
-        <v>2.66</v>
+        <v>1.13</v>
       </c>
       <c r="AK7">
         <v>1.06</v>
@@ -2070,12 +2070,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Ulsan</t>
+          <t>Daejeon Citizen</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Anyang</t>
+          <t>Gwangju</t>
         </is>
       </c>
       <c r="G11">
@@ -2102,64 +2102,64 @@
         </is>
       </c>
       <c r="N11">
-        <v>1.91</v>
+        <v>1.48</v>
       </c>
       <c r="O11">
-        <v>3.55</v>
+        <v>4.3</v>
       </c>
       <c r="P11">
-        <v>3.81</v>
+        <v>5.75</v>
       </c>
       <c r="Q11">
-        <v>2.38</v>
+        <v>2</v>
       </c>
       <c r="R11">
-        <v>2.25</v>
+        <v>2.29</v>
       </c>
       <c r="S11">
-        <v>1.35</v>
+        <v>1.37</v>
       </c>
       <c r="T11">
-        <v>2.94</v>
+        <v>2.77</v>
       </c>
       <c r="U11">
         <v>2.65</v>
       </c>
       <c r="V11">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="W11">
-        <v>1.1</v>
+        <v>1.06</v>
       </c>
       <c r="X11">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y11">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="Z11">
-        <v>3.82</v>
+        <v>3.8</v>
       </c>
       <c r="AA11">
-        <v>1.89</v>
+        <v>1.81</v>
       </c>
       <c r="AB11">
-        <v>1.94</v>
+        <v>1.97</v>
       </c>
       <c r="AC11">
-        <v>2.94</v>
+        <v>2.89</v>
       </c>
       <c r="AD11">
-        <v>1.37</v>
+        <v>1.32</v>
       </c>
       <c r="AE11">
         <v>1.08</v>
       </c>
       <c r="AF11">
-        <v>1.7</v>
+        <v>1.91</v>
       </c>
       <c r="AG11">
-        <v>2.04</v>
+        <v>1.77</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2172,10 +2172,10 @@
         </is>
       </c>
       <c r="AJ11">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="AK11">
-        <v>1.87</v>
+        <v>2.5</v>
       </c>
       <c r="AL11">
         <v>0</v>
@@ -2233,12 +2233,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Daejeon Citizen</t>
+          <t>Jeju United</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Gwangju</t>
+          <t>Incheon United</t>
         </is>
       </c>
       <c r="G12">
@@ -2265,80 +2265,80 @@
         </is>
       </c>
       <c r="N12">
-        <v>1.46</v>
+        <v>2.88</v>
       </c>
       <c r="O12">
-        <v>4.2</v>
+        <v>2.88</v>
       </c>
       <c r="P12">
-        <v>5.1</v>
+        <v>2.33</v>
       </c>
       <c r="Q12">
-        <v>2</v>
+        <v>3.2</v>
       </c>
       <c r="R12">
-        <v>2.28</v>
+        <v>1.98</v>
       </c>
       <c r="S12">
+        <v>1.53</v>
+      </c>
+      <c r="T12">
+        <v>2.34</v>
+      </c>
+      <c r="U12">
+        <v>3.4</v>
+      </c>
+      <c r="V12">
+        <v>1.27</v>
+      </c>
+      <c r="W12">
+        <v>1.01</v>
+      </c>
+      <c r="X12">
+        <v>1.07</v>
+      </c>
+      <c r="Y12">
+        <v>1.4</v>
+      </c>
+      <c r="Z12">
+        <v>2.57</v>
+      </c>
+      <c r="AA12">
+        <v>2.38</v>
+      </c>
+      <c r="AB12">
+        <v>1.56</v>
+      </c>
+      <c r="AC12">
+        <v>4.5</v>
+      </c>
+      <c r="AD12">
+        <v>1.19</v>
+      </c>
+      <c r="AE12">
+        <v>1.01</v>
+      </c>
+      <c r="AF12">
+        <v>1.97</v>
+      </c>
+      <c r="AG12">
+        <v>1.75</v>
+      </c>
+      <c r="AH12" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI12" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ12">
         <v>1.36</v>
       </c>
-      <c r="T12">
-        <v>2.77</v>
-      </c>
-      <c r="U12">
-        <v>2.65</v>
-      </c>
-      <c r="V12">
-        <v>1.4</v>
-      </c>
-      <c r="W12">
-        <v>1.06</v>
-      </c>
-      <c r="X12">
-        <v>1</v>
-      </c>
-      <c r="Y12">
-        <v>1.22</v>
-      </c>
-      <c r="Z12">
-        <v>3.8</v>
-      </c>
-      <c r="AA12">
-        <v>1.89</v>
-      </c>
-      <c r="AB12">
-        <v>1.93</v>
-      </c>
-      <c r="AC12">
-        <v>2.89</v>
-      </c>
-      <c r="AD12">
-        <v>1.32</v>
-      </c>
-      <c r="AE12">
-        <v>1.08</v>
-      </c>
-      <c r="AF12">
-        <v>1.91</v>
-      </c>
-      <c r="AG12">
-        <v>1.77</v>
-      </c>
-      <c r="AH12" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI12" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ12">
-        <v>1.16</v>
-      </c>
       <c r="AK12">
-        <v>2.5</v>
+        <v>1.34</v>
       </c>
       <c r="AL12">
         <v>0</v>
@@ -2396,12 +2396,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Jeju United</t>
+          <t>Ulsan</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Incheon United</t>
+          <t>Anyang</t>
         </is>
       </c>
       <c r="G13">
@@ -2428,64 +2428,64 @@
         </is>
       </c>
       <c r="N13">
-        <v>2.88</v>
+        <v>1.86</v>
       </c>
       <c r="O13">
-        <v>2.88</v>
+        <v>3.45</v>
       </c>
       <c r="P13">
-        <v>2.4</v>
+        <v>3.35</v>
       </c>
       <c r="Q13">
-        <v>3.2</v>
+        <v>2.38</v>
       </c>
       <c r="R13">
-        <v>1.98</v>
+        <v>2.25</v>
       </c>
       <c r="S13">
-        <v>1.53</v>
+        <v>1.35</v>
       </c>
       <c r="T13">
-        <v>2.34</v>
+        <v>2.75</v>
       </c>
       <c r="U13">
-        <v>3.4</v>
+        <v>2.65</v>
       </c>
       <c r="V13">
-        <v>1.27</v>
+        <v>1.42</v>
       </c>
       <c r="W13">
+        <v>1.1</v>
+      </c>
+      <c r="X13">
         <v>1.01</v>
       </c>
-      <c r="X13">
-        <v>1.1</v>
-      </c>
       <c r="Y13">
-        <v>1.4</v>
+        <v>1.22</v>
       </c>
       <c r="Z13">
-        <v>2.57</v>
+        <v>3.82</v>
       </c>
       <c r="AA13">
-        <v>2.38</v>
+        <v>1.89</v>
       </c>
       <c r="AB13">
-        <v>1.56</v>
+        <v>2.01</v>
       </c>
       <c r="AC13">
-        <v>4.5</v>
+        <v>3.05</v>
       </c>
       <c r="AD13">
-        <v>1.19</v>
+        <v>1.37</v>
       </c>
       <c r="AE13">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="AF13">
-        <v>1.97</v>
+        <v>1.7</v>
       </c>
       <c r="AG13">
-        <v>1.73</v>
+        <v>2.04</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2498,10 +2498,10 @@
         </is>
       </c>
       <c r="AJ13">
-        <v>1.31</v>
+        <v>1.25</v>
       </c>
       <c r="AK13">
-        <v>1.36</v>
+        <v>1.9</v>
       </c>
       <c r="AL13">
         <v>0</v>
@@ -2722,12 +2722,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Busan I'Park</t>
+          <t>Ansan Greeners</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Seoul E-Land</t>
+          <t>Gimhae City</t>
         </is>
       </c>
       <c r="G15">
@@ -2754,64 +2754,64 @@
         </is>
       </c>
       <c r="N15">
-        <v>2.42</v>
+        <v>2.65</v>
       </c>
       <c r="O15">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="P15">
-        <v>2.17</v>
+        <v>2.15</v>
       </c>
       <c r="Q15">
-        <v>3.1</v>
+        <v>3.4</v>
       </c>
       <c r="R15">
-        <v>2.23</v>
+        <v>2.2</v>
       </c>
       <c r="S15">
-        <v>1.3</v>
+        <v>1.35</v>
       </c>
       <c r="T15">
-        <v>3.3</v>
+        <v>2.82</v>
       </c>
       <c r="U15">
-        <v>2.5</v>
+        <v>2.84</v>
       </c>
       <c r="V15">
-        <v>1.45</v>
+        <v>1.4</v>
       </c>
       <c r="W15">
-        <v>1.12</v>
+        <v>1.08</v>
       </c>
       <c r="X15">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y15">
-        <v>1.21</v>
+        <v>1.29</v>
       </c>
       <c r="Z15">
-        <v>4.23</v>
+        <v>3.28</v>
       </c>
       <c r="AA15">
-        <v>1.67</v>
+        <v>1.87</v>
       </c>
       <c r="AB15">
-        <v>2.1</v>
+        <v>1.87</v>
       </c>
       <c r="AC15">
-        <v>2.66</v>
+        <v>3.2</v>
       </c>
       <c r="AD15">
-        <v>1.37</v>
+        <v>1.27</v>
       </c>
       <c r="AE15">
         <v>1.11</v>
       </c>
       <c r="AF15">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="AG15">
-        <v>2.25</v>
+        <v>2</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2824,10 +2824,10 @@
         </is>
       </c>
       <c r="AJ15">
-        <v>1.51</v>
+        <v>1.25</v>
       </c>
       <c r="AK15">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="AL15">
         <v>0</v>
@@ -2885,12 +2885,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Ansan Greeners</t>
+          <t>Busan I'Park</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Gimhae City</t>
+          <t>Seoul E-Land</t>
         </is>
       </c>
       <c r="G16">
@@ -2917,64 +2917,64 @@
         </is>
       </c>
       <c r="N16">
-        <v>2.65</v>
+        <v>2.42</v>
       </c>
       <c r="O16">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="P16">
-        <v>2.15</v>
+        <v>2.17</v>
       </c>
       <c r="Q16">
-        <v>3.4</v>
+        <v>3.1</v>
       </c>
       <c r="R16">
-        <v>2.2</v>
+        <v>2.23</v>
       </c>
       <c r="S16">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="T16">
-        <v>2.82</v>
+        <v>3.3</v>
       </c>
       <c r="U16">
-        <v>2.84</v>
+        <v>2.5</v>
       </c>
       <c r="V16">
-        <v>1.4</v>
+        <v>1.45</v>
       </c>
       <c r="W16">
-        <v>1.08</v>
+        <v>1.12</v>
       </c>
       <c r="X16">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y16">
-        <v>1.29</v>
+        <v>1.21</v>
       </c>
       <c r="Z16">
-        <v>3.28</v>
+        <v>4.23</v>
       </c>
       <c r="AA16">
-        <v>1.87</v>
+        <v>1.67</v>
       </c>
       <c r="AB16">
-        <v>1.87</v>
+        <v>2.1</v>
       </c>
       <c r="AC16">
-        <v>3.2</v>
+        <v>2.66</v>
       </c>
       <c r="AD16">
-        <v>1.27</v>
+        <v>1.37</v>
       </c>
       <c r="AE16">
         <v>1.11</v>
       </c>
       <c r="AF16">
-        <v>1.67</v>
+        <v>1.57</v>
       </c>
       <c r="AG16">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -2987,10 +2987,10 @@
         </is>
       </c>
       <c r="AJ16">
-        <v>1.25</v>
+        <v>1.51</v>
       </c>
       <c r="AK16">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="AL16">
         <v>0</v>
@@ -3211,12 +3211,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Changchun Yatai</t>
+          <t>Suzhou Dongwu</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Hebei Kungfu</t>
+          <t>Meizhou Hakka</t>
         </is>
       </c>
       <c r="G18">
@@ -3243,64 +3243,64 @@
         </is>
       </c>
       <c r="N18">
-        <v>1.71</v>
+        <v>2.25</v>
       </c>
       <c r="O18">
-        <v>3.4</v>
+        <v>3.05</v>
       </c>
       <c r="P18">
-        <v>4.4</v>
+        <v>3</v>
       </c>
       <c r="Q18">
-        <v>2.29</v>
+        <v>2.94</v>
       </c>
       <c r="R18">
-        <v>2.05</v>
+        <v>1.95</v>
       </c>
       <c r="S18">
-        <v>1.35</v>
+        <v>1.41</v>
       </c>
       <c r="T18">
-        <v>2.67</v>
+        <v>2.72</v>
       </c>
       <c r="U18">
-        <v>2.75</v>
+        <v>2.95</v>
       </c>
       <c r="V18">
         <v>1.36</v>
       </c>
       <c r="W18">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="X18">
         <v>1.01</v>
       </c>
       <c r="Y18">
-        <v>1.25</v>
+        <v>1.35</v>
       </c>
       <c r="Z18">
-        <v>3.28</v>
+        <v>3.05</v>
       </c>
       <c r="AA18">
-        <v>1.94</v>
+        <v>2.08</v>
       </c>
       <c r="AB18">
-        <v>1.86</v>
+        <v>1.73</v>
       </c>
       <c r="AC18">
-        <v>3.25</v>
+        <v>3.5</v>
       </c>
       <c r="AD18">
-        <v>1.28</v>
+        <v>1.22</v>
       </c>
       <c r="AE18">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="AF18">
-        <v>1.77</v>
+        <v>1.73</v>
       </c>
       <c r="AG18">
-        <v>1.85</v>
+        <v>1.91</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3313,10 +3313,10 @@
         </is>
       </c>
       <c r="AJ18">
-        <v>1.14</v>
+        <v>1.29</v>
       </c>
       <c r="AK18">
-        <v>1.96</v>
+        <v>1.57</v>
       </c>
       <c r="AL18">
         <v>0</v>
@@ -3374,12 +3374,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Suzhou Dongwu</t>
+          <t>Shenzhen Juniors</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Meizhou Hakka</t>
+          <t>Wuxi Wugou</t>
         </is>
       </c>
       <c r="G19">
@@ -3406,64 +3406,64 @@
         </is>
       </c>
       <c r="N19">
-        <v>2.25</v>
+        <v>2.12</v>
       </c>
       <c r="O19">
-        <v>3.05</v>
+        <v>3.5</v>
       </c>
       <c r="P19">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="Q19">
-        <v>2.94</v>
+        <v>2.67</v>
       </c>
       <c r="R19">
-        <v>1.95</v>
+        <v>2.34</v>
       </c>
       <c r="S19">
-        <v>1.41</v>
+        <v>1.34</v>
       </c>
       <c r="T19">
-        <v>2.72</v>
+        <v>3.04</v>
       </c>
       <c r="U19">
-        <v>2.95</v>
+        <v>2.39</v>
       </c>
       <c r="V19">
-        <v>1.36</v>
+        <v>1.53</v>
       </c>
       <c r="W19">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="X19">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y19">
-        <v>1.35</v>
+        <v>1.2</v>
       </c>
       <c r="Z19">
-        <v>3.05</v>
+        <v>4.33</v>
       </c>
       <c r="AA19">
-        <v>2.08</v>
+        <v>1.75</v>
       </c>
       <c r="AB19">
-        <v>1.73</v>
+        <v>2.19</v>
       </c>
       <c r="AC19">
-        <v>3.5</v>
+        <v>2.88</v>
       </c>
       <c r="AD19">
-        <v>1.22</v>
+        <v>1.4</v>
       </c>
       <c r="AE19">
-        <v>1.08</v>
+        <v>1.13</v>
       </c>
       <c r="AF19">
-        <v>1.73</v>
+        <v>1.53</v>
       </c>
       <c r="AG19">
-        <v>1.91</v>
+        <v>2.29</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3476,10 +3476,10 @@
         </is>
       </c>
       <c r="AJ19">
-        <v>1.29</v>
+        <v>1.24</v>
       </c>
       <c r="AK19">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="AL19">
         <v>0</v>
@@ -3537,12 +3537,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Shenzhen Juniors</t>
+          <t>Changchun Yatai</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Wuxi Wugou</t>
+          <t>Hebei Kungfu</t>
         </is>
       </c>
       <c r="G20">
@@ -3569,64 +3569,64 @@
         </is>
       </c>
       <c r="N20">
-        <v>2.12</v>
+        <v>1.71</v>
       </c>
       <c r="O20">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="P20">
-        <v>2.9</v>
+        <v>4.4</v>
       </c>
       <c r="Q20">
+        <v>2.29</v>
+      </c>
+      <c r="R20">
+        <v>2.05</v>
+      </c>
+      <c r="S20">
+        <v>1.35</v>
+      </c>
+      <c r="T20">
         <v>2.67</v>
       </c>
-      <c r="R20">
-        <v>2.34</v>
-      </c>
-      <c r="S20">
-        <v>1.34</v>
-      </c>
-      <c r="T20">
-        <v>3.04</v>
-      </c>
       <c r="U20">
-        <v>2.39</v>
+        <v>2.75</v>
       </c>
       <c r="V20">
-        <v>1.53</v>
+        <v>1.36</v>
       </c>
       <c r="W20">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="X20">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y20">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="Z20">
-        <v>4.33</v>
+        <v>3.28</v>
       </c>
       <c r="AA20">
-        <v>1.75</v>
+        <v>1.94</v>
       </c>
       <c r="AB20">
-        <v>2.19</v>
+        <v>1.86</v>
       </c>
       <c r="AC20">
-        <v>2.88</v>
+        <v>3.25</v>
       </c>
       <c r="AD20">
-        <v>1.4</v>
+        <v>1.28</v>
       </c>
       <c r="AE20">
-        <v>1.13</v>
+        <v>1.1</v>
       </c>
       <c r="AF20">
-        <v>1.53</v>
+        <v>1.77</v>
       </c>
       <c r="AG20">
-        <v>2.29</v>
+        <v>1.85</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
@@ -3639,10 +3639,10 @@
         </is>
       </c>
       <c r="AJ20">
-        <v>1.24</v>
+        <v>1.14</v>
       </c>
       <c r="AK20">
-        <v>1.6</v>
+        <v>1.96</v>
       </c>
       <c r="AL20">
         <v>0</v>
@@ -4384,43 +4384,43 @@
         </is>
       </c>
       <c r="N25">
-        <v>1.74</v>
+        <v>1.68</v>
       </c>
       <c r="O25">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="P25">
-        <v>4.35</v>
+        <v>4.33</v>
       </c>
       <c r="Q25">
-        <v>2.28</v>
+        <v>2.29</v>
       </c>
       <c r="R25">
-        <v>2.39</v>
+        <v>2.38</v>
       </c>
       <c r="S25">
         <v>1.29</v>
       </c>
       <c r="T25">
-        <v>3.3</v>
+        <v>3.04</v>
       </c>
       <c r="U25">
-        <v>2.47</v>
+        <v>2.61</v>
       </c>
       <c r="V25">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="W25">
         <v>1.08</v>
       </c>
       <c r="X25">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="Y25">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="Z25">
-        <v>3.8</v>
+        <v>3.82</v>
       </c>
       <c r="AA25">
         <v>1.8</v>
@@ -4432,7 +4432,7 @@
         <v>2.88</v>
       </c>
       <c r="AD25">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AE25">
         <v>1.09</v>
@@ -4454,10 +4454,10 @@
         </is>
       </c>
       <c r="AJ25">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AK25">
-        <v>2.04</v>
+        <v>2</v>
       </c>
       <c r="AL25">
         <v>0</v>
@@ -4550,22 +4550,22 @@
         <v>3</v>
       </c>
       <c r="O26">
-        <v>3.4</v>
+        <v>3.61</v>
       </c>
       <c r="P26">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="Q26">
         <v>3.23</v>
       </c>
       <c r="R26">
-        <v>2.3</v>
+        <v>2.42</v>
       </c>
       <c r="S26">
         <v>1.3</v>
       </c>
       <c r="T26">
-        <v>3.6</v>
+        <v>3.22</v>
       </c>
       <c r="U26">
         <v>2.4</v>
@@ -4574,7 +4574,7 @@
         <v>1.56</v>
       </c>
       <c r="W26">
-        <v>1.12</v>
+        <v>1.1</v>
       </c>
       <c r="X26">
         <v>1.04</v>
@@ -4583,13 +4583,13 @@
         <v>1.15</v>
       </c>
       <c r="Z26">
-        <v>4.25</v>
+        <v>4.5</v>
       </c>
       <c r="AA26">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="AB26">
-        <v>2.25</v>
+        <v>2.26</v>
       </c>
       <c r="AC26">
         <v>2.3</v>
@@ -4604,7 +4604,7 @@
         <v>1.5</v>
       </c>
       <c r="AG26">
-        <v>2.45</v>
+        <v>2.4</v>
       </c>
       <c r="AH26" t="inlineStr">
         <is>
@@ -4617,10 +4617,10 @@
         </is>
       </c>
       <c r="AJ26">
-        <v>1.23</v>
+        <v>1.27</v>
       </c>
       <c r="AK26">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="AL26">
         <v>0</v>
@@ -6014,13 +6014,13 @@
         </is>
       </c>
       <c r="N35">
-        <v>2.18</v>
+        <v>2.05</v>
       </c>
       <c r="O35">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="P35">
-        <v>2.98</v>
+        <v>2.81</v>
       </c>
       <c r="Q35">
         <v>2.65</v>
@@ -6029,46 +6029,46 @@
         <v>2.28</v>
       </c>
       <c r="S35">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="T35">
-        <v>3.36</v>
+        <v>3.8</v>
       </c>
       <c r="U35">
         <v>2.31</v>
       </c>
       <c r="V35">
-        <v>1.53</v>
+        <v>1.56</v>
       </c>
       <c r="W35">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="X35">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y35">
-        <v>1.13</v>
+        <v>1.2</v>
       </c>
       <c r="Z35">
-        <v>4.5</v>
+        <v>4.55</v>
       </c>
       <c r="AA35">
         <v>1.58</v>
       </c>
       <c r="AB35">
-        <v>2.3</v>
+        <v>2.33</v>
       </c>
       <c r="AC35">
         <v>2.33</v>
       </c>
       <c r="AD35">
-        <v>1.53</v>
+        <v>1.48</v>
       </c>
       <c r="AE35">
         <v>1.16</v>
       </c>
       <c r="AF35">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="AG35">
         <v>2.4</v>
@@ -6177,19 +6177,19 @@
         </is>
       </c>
       <c r="N36">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="O36">
-        <v>0</v>
+        <v>6.15</v>
       </c>
       <c r="P36">
-        <v>0</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="Q36">
         <v>1.52</v>
       </c>
       <c r="R36">
-        <v>2.88</v>
+        <v>2.75</v>
       </c>
       <c r="S36">
         <v>1.2</v>
@@ -6204,19 +6204,19 @@
         <v>1.62</v>
       </c>
       <c r="W36">
-        <v>1.14</v>
+        <v>1.16</v>
       </c>
       <c r="X36">
         <v>1.02</v>
       </c>
       <c r="Y36">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="Z36">
-        <v>5.2</v>
+        <v>4.4</v>
       </c>
       <c r="AA36">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="AB36">
         <v>2.49</v>
@@ -6225,7 +6225,7 @@
         <v>2.14</v>
       </c>
       <c r="AD36">
-        <v>1.62</v>
+        <v>1.5</v>
       </c>
       <c r="AE36">
         <v>1.19</v>
@@ -6675,10 +6675,10 @@
         <v>3.1</v>
       </c>
       <c r="Q39">
-        <v>2.49</v>
+        <v>2.75</v>
       </c>
       <c r="R39">
-        <v>2.11</v>
+        <v>2.28</v>
       </c>
       <c r="S39">
         <v>1.37</v>
@@ -6696,31 +6696,31 @@
         <v>1.05</v>
       </c>
       <c r="X39">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="Y39">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="Z39">
-        <v>3.85</v>
+        <v>3.44</v>
       </c>
       <c r="AA39">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="AB39">
-        <v>1.97</v>
+        <v>1.86</v>
       </c>
       <c r="AC39">
-        <v>2.95</v>
+        <v>3</v>
       </c>
       <c r="AD39">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="AE39">
         <v>1.11</v>
       </c>
       <c r="AF39">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="AG39">
         <v>2.1</v>
@@ -7158,7 +7158,7 @@
         <v>2.1</v>
       </c>
       <c r="O42">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="P42">
         <v>3.05</v>
@@ -7170,16 +7170,16 @@
         <v>2.18</v>
       </c>
       <c r="S42">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="T42">
-        <v>3.3</v>
+        <v>3.02</v>
       </c>
       <c r="U42">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="V42">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="W42">
         <v>1.06</v>
@@ -7194,10 +7194,10 @@
         <v>4.1</v>
       </c>
       <c r="AA42">
-        <v>1.66</v>
+        <v>1.69</v>
       </c>
       <c r="AB42">
-        <v>2.04</v>
+        <v>2.09</v>
       </c>
       <c r="AC42">
         <v>2.63</v>
@@ -7206,7 +7206,7 @@
         <v>1.37</v>
       </c>
       <c r="AE42">
-        <v>1.14</v>
+        <v>1.11</v>
       </c>
       <c r="AF42">
         <v>1.56</v>
@@ -7318,34 +7318,34 @@
         </is>
       </c>
       <c r="N43">
-        <v>3.15</v>
+        <v>2.8</v>
       </c>
       <c r="O43">
         <v>3.55</v>
       </c>
       <c r="P43">
-        <v>2.03</v>
+        <v>2.2</v>
       </c>
       <c r="Q43">
-        <v>3.58</v>
+        <v>3.33</v>
       </c>
       <c r="R43">
-        <v>2.21</v>
+        <v>2.3</v>
       </c>
       <c r="S43">
         <v>1.3</v>
       </c>
       <c r="T43">
-        <v>3.2</v>
+        <v>3.22</v>
       </c>
       <c r="U43">
-        <v>2.55</v>
+        <v>2.4</v>
       </c>
       <c r="V43">
         <v>1.5</v>
       </c>
       <c r="W43">
-        <v>1.12</v>
+        <v>1.08</v>
       </c>
       <c r="X43">
         <v>1.02</v>
@@ -7366,13 +7366,13 @@
         <v>2.7</v>
       </c>
       <c r="AD43">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="AE43">
-        <v>1.11</v>
+        <v>1.16</v>
       </c>
       <c r="AF43">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="AG43">
         <v>2.3</v>
@@ -7391,7 +7391,7 @@
         <v>1.27</v>
       </c>
       <c r="AK43">
-        <v>1.35</v>
+        <v>1.38</v>
       </c>
       <c r="AL43">
         <v>0</v>
@@ -8142,16 +8142,16 @@
         <v>2.79</v>
       </c>
       <c r="Q48">
-        <v>2.8</v>
+        <v>2.81</v>
       </c>
       <c r="R48">
         <v>2.2</v>
       </c>
       <c r="S48">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="T48">
-        <v>3.02</v>
+        <v>3.2</v>
       </c>
       <c r="U48">
         <v>2.5</v>
@@ -8160,22 +8160,22 @@
         <v>1.46</v>
       </c>
       <c r="W48">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="X48">
         <v>1</v>
       </c>
       <c r="Y48">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="Z48">
-        <v>3.84</v>
+        <v>3.85</v>
       </c>
       <c r="AA48">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="AB48">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="AC48">
         <v>2.6</v>
@@ -8187,7 +8187,7 @@
         <v>1.12</v>
       </c>
       <c r="AF48">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="AG48">
         <v>2.25</v>
@@ -8203,10 +8203,10 @@
         </is>
       </c>
       <c r="AJ48">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="AK48">
-        <v>1.48</v>
+        <v>1.57</v>
       </c>
       <c r="AL48">
         <v>0</v>
@@ -8308,13 +8308,13 @@
         <v>2.15</v>
       </c>
       <c r="R49">
-        <v>2.28</v>
+        <v>2.17</v>
       </c>
       <c r="S49">
-        <v>1.3</v>
+        <v>1.34</v>
       </c>
       <c r="T49">
-        <v>3.2</v>
+        <v>2.88</v>
       </c>
       <c r="U49">
         <v>2.45</v>
@@ -8323,7 +8323,7 @@
         <v>1.4</v>
       </c>
       <c r="W49">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="X49">
         <v>1</v>
@@ -8338,13 +8338,13 @@
         <v>1.8</v>
       </c>
       <c r="AB49">
-        <v>1.9</v>
+        <v>1.93</v>
       </c>
       <c r="AC49">
-        <v>2.92</v>
+        <v>3</v>
       </c>
       <c r="AD49">
-        <v>1.31</v>
+        <v>1.35</v>
       </c>
       <c r="AE49">
         <v>1.08</v>
@@ -8366,7 +8366,7 @@
         </is>
       </c>
       <c r="AJ49">
-        <v>1.13</v>
+        <v>1.2</v>
       </c>
       <c r="AK49">
         <v>2.3</v>
@@ -8468,7 +8468,7 @@
         <v>0</v>
       </c>
       <c r="Q50">
-        <v>5.75</v>
+        <v>6.25</v>
       </c>
       <c r="R50">
         <v>2.36</v>
@@ -8480,7 +8480,7 @@
         <v>3.25</v>
       </c>
       <c r="U50">
-        <v>2.27</v>
+        <v>2.25</v>
       </c>
       <c r="V50">
         <v>1.53</v>
@@ -8492,25 +8492,25 @@
         <v>1.01</v>
       </c>
       <c r="Y50">
-        <v>1.15</v>
+        <v>1.18</v>
       </c>
       <c r="Z50">
         <v>4.65</v>
       </c>
       <c r="AA50">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="AB50">
-        <v>2.29</v>
+        <v>2.3</v>
       </c>
       <c r="AC50">
-        <v>2.28</v>
+        <v>2.38</v>
       </c>
       <c r="AD50">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="AE50">
-        <v>1.19</v>
+        <v>1.16</v>
       </c>
       <c r="AF50">
         <v>1.72</v>
@@ -9274,25 +9274,25 @@
         </is>
       </c>
       <c r="N55">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="O55">
-        <v>4.2</v>
+        <v>4.8</v>
       </c>
       <c r="P55">
-        <v>5</v>
+        <v>5.55</v>
       </c>
       <c r="Q55">
-        <v>1.94</v>
+        <v>1.91</v>
       </c>
       <c r="R55">
-        <v>2.5</v>
+        <v>2.53</v>
       </c>
       <c r="S55">
         <v>1.22</v>
       </c>
       <c r="T55">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="U55">
         <v>2.15</v>
@@ -9310,10 +9310,10 @@
         <v>1.14</v>
       </c>
       <c r="Z55">
-        <v>5.09</v>
+        <v>5.13</v>
       </c>
       <c r="AA55">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="AB55">
         <v>2.33</v>
@@ -9328,10 +9328,10 @@
         <v>1.19</v>
       </c>
       <c r="AF55">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="AG55">
-        <v>2.04</v>
+        <v>2.15</v>
       </c>
       <c r="AH55" t="inlineStr">
         <is>
@@ -9344,10 +9344,10 @@
         </is>
       </c>
       <c r="AJ55">
-        <v>1.13</v>
+        <v>1.16</v>
       </c>
       <c r="AK55">
-        <v>2.59</v>
+        <v>2.66</v>
       </c>
       <c r="AL55">
         <v>0</v>
@@ -9763,43 +9763,43 @@
         </is>
       </c>
       <c r="N58">
-        <v>3.7</v>
+        <v>3.31</v>
       </c>
       <c r="O58">
-        <v>3.7</v>
+        <v>3.5</v>
       </c>
       <c r="P58">
-        <v>1.87</v>
+        <v>2</v>
       </c>
       <c r="Q58">
-        <v>4.1</v>
+        <v>3.75</v>
       </c>
       <c r="R58">
-        <v>2.25</v>
+        <v>2.23</v>
       </c>
       <c r="S58">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="T58">
-        <v>3.3</v>
+        <v>3.15</v>
       </c>
       <c r="U58">
-        <v>2.4</v>
+        <v>2.44</v>
       </c>
       <c r="V58">
         <v>1.49</v>
       </c>
       <c r="W58">
-        <v>1.12</v>
+        <v>1.08</v>
       </c>
       <c r="X58">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y58">
         <v>1.17</v>
       </c>
       <c r="Z58">
-        <v>4.1</v>
+        <v>4.05</v>
       </c>
       <c r="AA58">
         <v>1.66</v>
@@ -9808,7 +9808,7 @@
         <v>2.15</v>
       </c>
       <c r="AC58">
-        <v>2.68</v>
+        <v>2.69</v>
       </c>
       <c r="AD58">
         <v>1.47</v>
@@ -9817,7 +9817,7 @@
         <v>1.18</v>
       </c>
       <c r="AF58">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="AG58">
         <v>2.2</v>
@@ -9833,7 +9833,7 @@
         </is>
       </c>
       <c r="AJ58">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AK58">
         <v>1.25</v>
@@ -9929,22 +9929,22 @@
         <v>1.72</v>
       </c>
       <c r="O59">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="P59">
-        <v>4.5</v>
+        <v>4.2</v>
       </c>
       <c r="Q59">
-        <v>2.19</v>
+        <v>2.2</v>
       </c>
       <c r="R59">
         <v>2.46</v>
       </c>
       <c r="S59">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="T59">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="U59">
         <v>2.4</v>
@@ -9956,10 +9956,10 @@
         <v>1.08</v>
       </c>
       <c r="X59">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y59">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="Z59">
         <v>4.1</v>
@@ -9971,19 +9971,19 @@
         <v>2.1</v>
       </c>
       <c r="AC59">
-        <v>2.57</v>
+        <v>2.7</v>
       </c>
       <c r="AD59">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="AE59">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AF59">
-        <v>1.74</v>
+        <v>1.67</v>
       </c>
       <c r="AG59">
-        <v>1.93</v>
+        <v>2.08</v>
       </c>
       <c r="AH59" t="inlineStr">
         <is>
@@ -10089,34 +10089,34 @@
         </is>
       </c>
       <c r="N60">
-        <v>1.7</v>
+        <v>1.57</v>
       </c>
       <c r="O60">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="P60">
-        <v>4.43</v>
+        <v>4</v>
       </c>
       <c r="Q60">
         <v>2.1</v>
       </c>
       <c r="R60">
-        <v>2.71</v>
+        <v>2.63</v>
       </c>
       <c r="S60">
         <v>1.23</v>
       </c>
       <c r="T60">
-        <v>4</v>
+        <v>3.58</v>
       </c>
       <c r="U60">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="V60">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="W60">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="X60">
         <v>1.02</v>
@@ -10131,16 +10131,16 @@
         <v>1.4</v>
       </c>
       <c r="AB60">
-        <v>2.78</v>
+        <v>2.77</v>
       </c>
       <c r="AC60">
-        <v>2.12</v>
+        <v>2.08</v>
       </c>
       <c r="AD60">
-        <v>1.74</v>
+        <v>1.76</v>
       </c>
       <c r="AE60">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="AF60">
         <v>1.45</v>
@@ -10159,7 +10159,7 @@
         </is>
       </c>
       <c r="AJ60">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="AK60">
         <v>2.2</v>
@@ -12860,10 +12860,10 @@
         </is>
       </c>
       <c r="N77">
-        <v>2.15</v>
+        <v>2.3</v>
       </c>
       <c r="O77">
-        <v>3.43</v>
+        <v>3.5</v>
       </c>
       <c r="P77">
         <v>2.73</v>
@@ -12878,7 +12878,7 @@
         <v>1.33</v>
       </c>
       <c r="T77">
-        <v>3.17</v>
+        <v>2.89</v>
       </c>
       <c r="U77">
         <v>2.62</v>
@@ -12893,31 +12893,31 @@
         <v>1.01</v>
       </c>
       <c r="Y77">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="Z77">
         <v>3.62</v>
       </c>
       <c r="AA77">
-        <v>1.78</v>
+        <v>1.81</v>
       </c>
       <c r="AB77">
         <v>2</v>
       </c>
       <c r="AC77">
-        <v>3</v>
+        <v>2.85</v>
       </c>
       <c r="AD77">
         <v>1.33</v>
       </c>
       <c r="AE77">
-        <v>1.08</v>
+        <v>1.14</v>
       </c>
       <c r="AF77">
         <v>1.62</v>
       </c>
       <c r="AG77">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="AH77" t="inlineStr">
         <is>
@@ -12930,10 +12930,10 @@
         </is>
       </c>
       <c r="AJ77">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AK77">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="AL77">
         <v>0</v>
@@ -13023,16 +13023,16 @@
         </is>
       </c>
       <c r="N78">
-        <v>2.2</v>
+        <v>2.12</v>
       </c>
       <c r="O78">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="P78">
         <v>3.25</v>
       </c>
       <c r="Q78">
-        <v>2.8</v>
+        <v>2.9</v>
       </c>
       <c r="R78">
         <v>2.05</v>
@@ -13044,25 +13044,25 @@
         <v>2.75</v>
       </c>
       <c r="U78">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="V78">
         <v>1.28</v>
       </c>
       <c r="W78">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="X78">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="Y78">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="Z78">
         <v>2.62</v>
       </c>
       <c r="AA78">
-        <v>2.38</v>
+        <v>2.25</v>
       </c>
       <c r="AB78">
         <v>1.61</v>
@@ -13678,7 +13678,7 @@
         <v>1.79</v>
       </c>
       <c r="O82">
-        <v>3.45</v>
+        <v>3.35</v>
       </c>
       <c r="P82">
         <v>4.46</v>
@@ -13690,49 +13690,49 @@
         <v>2.1</v>
       </c>
       <c r="S82">
+        <v>1.43</v>
+      </c>
+      <c r="T82">
+        <v>2.56</v>
+      </c>
+      <c r="U82">
+        <v>2.8</v>
+      </c>
+      <c r="V82">
+        <v>1.31</v>
+      </c>
+      <c r="W82">
+        <v>1.01</v>
+      </c>
+      <c r="X82">
+        <v>1.06</v>
+      </c>
+      <c r="Y82">
         <v>1.36</v>
       </c>
-      <c r="T82">
-        <v>2.75</v>
-      </c>
-      <c r="U82">
-        <v>2.88</v>
-      </c>
-      <c r="V82">
-        <v>1.38</v>
-      </c>
-      <c r="W82">
-        <v>1.08</v>
-      </c>
-      <c r="X82">
-        <v>1.01</v>
-      </c>
-      <c r="Y82">
-        <v>1.33</v>
-      </c>
       <c r="Z82">
-        <v>3.22</v>
+        <v>2.97</v>
       </c>
       <c r="AA82">
-        <v>2.03</v>
+        <v>2.14</v>
       </c>
       <c r="AB82">
-        <v>1.76</v>
+        <v>1.7</v>
       </c>
       <c r="AC82">
-        <v>3.55</v>
+        <v>3.85</v>
       </c>
       <c r="AD82">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="AE82">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="AF82">
-        <v>1.89</v>
+        <v>1.97</v>
       </c>
       <c r="AG82">
-        <v>1.81</v>
+        <v>1.75</v>
       </c>
       <c r="AH82" t="inlineStr">
         <is>
@@ -13745,7 +13745,7 @@
         </is>
       </c>
       <c r="AJ82">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="AK82">
         <v>1.88</v>
@@ -14001,25 +14001,25 @@
         </is>
       </c>
       <c r="N84">
-        <v>1.5</v>
+        <v>1.58</v>
       </c>
       <c r="O84">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="P84">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="Q84">
-        <v>2.05</v>
+        <v>2.08</v>
       </c>
       <c r="R84">
-        <v>2.38</v>
+        <v>2.36</v>
       </c>
       <c r="S84">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="T84">
-        <v>3.32</v>
+        <v>3.25</v>
       </c>
       <c r="U84">
         <v>2.25</v>
@@ -14031,34 +14031,34 @@
         <v>1.14</v>
       </c>
       <c r="X84">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y84">
         <v>1.15</v>
       </c>
       <c r="Z84">
-        <v>4.51</v>
+        <v>4.47</v>
       </c>
       <c r="AA84">
         <v>1.53</v>
       </c>
       <c r="AB84">
-        <v>2.38</v>
+        <v>2.26</v>
       </c>
       <c r="AC84">
-        <v>2.54</v>
+        <v>2.56</v>
       </c>
       <c r="AD84">
         <v>1.54</v>
       </c>
       <c r="AE84">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="AF84">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="AG84">
-        <v>2.12</v>
+        <v>2.25</v>
       </c>
       <c r="AH84" t="inlineStr">
         <is>
@@ -14071,10 +14071,10 @@
         </is>
       </c>
       <c r="AJ84">
-        <v>1.16</v>
+        <v>1.11</v>
       </c>
       <c r="AK84">
-        <v>2.22</v>
+        <v>2.46</v>
       </c>
       <c r="AL84">
         <v>0</v>
@@ -14653,13 +14653,13 @@
         </is>
       </c>
       <c r="N88">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="O88">
-        <v>4.3</v>
+        <v>5.35</v>
       </c>
       <c r="P88">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="Q88">
         <v>1.7</v>
@@ -14671,46 +14671,46 @@
         <v>1.35</v>
       </c>
       <c r="T88">
-        <v>2.95</v>
+        <v>2.82</v>
       </c>
       <c r="U88">
-        <v>2.66</v>
+        <v>2.63</v>
       </c>
       <c r="V88">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="W88">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="X88">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="Y88">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="Z88">
-        <v>3.52</v>
+        <v>3.35</v>
       </c>
       <c r="AA88">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="AB88">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="AC88">
-        <v>3.08</v>
+        <v>3.1</v>
       </c>
       <c r="AD88">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="AE88">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="AF88">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="AG88">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="AH88" t="inlineStr">
         <is>
@@ -14723,10 +14723,10 @@
         </is>
       </c>
       <c r="AJ88">
-        <v>1.05</v>
+        <v>1.16</v>
       </c>
       <c r="AK88">
-        <v>2.91</v>
+        <v>3.12</v>
       </c>
       <c r="AL88">
         <v>0</v>
@@ -14825,22 +14825,22 @@
         <v>0</v>
       </c>
       <c r="Q89">
-        <v>2.61</v>
+        <v>2.63</v>
       </c>
       <c r="R89">
         <v>2.22</v>
       </c>
       <c r="S89">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="T89">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="U89">
         <v>2.38</v>
       </c>
       <c r="V89">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="W89">
         <v>1.13</v>
@@ -14849,10 +14849,10 @@
         <v>1.02</v>
       </c>
       <c r="Y89">
-        <v>1.15</v>
+        <v>1.2</v>
       </c>
       <c r="Z89">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="AA89">
         <v>1.61</v>
@@ -14864,13 +14864,13 @@
         <v>2.49</v>
       </c>
       <c r="AD89">
-        <v>1.45</v>
+        <v>1.48</v>
       </c>
       <c r="AE89">
         <v>1.16</v>
       </c>
       <c r="AF89">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="AG89">
         <v>2.3</v>
@@ -14886,10 +14886,10 @@
         </is>
       </c>
       <c r="AJ89">
-        <v>1.3</v>
+        <v>1.22</v>
       </c>
       <c r="AK89">
-        <v>1.67</v>
+        <v>1.61</v>
       </c>
       <c r="AL89">
         <v>0</v>
@@ -15145,55 +15145,55 @@
         <v>3.25</v>
       </c>
       <c r="O91">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="P91">
-        <v>2.03</v>
+        <v>1.95</v>
       </c>
       <c r="Q91">
-        <v>3.8</v>
+        <v>3.93</v>
       </c>
       <c r="R91">
-        <v>2.28</v>
+        <v>2.25</v>
       </c>
       <c r="S91">
         <v>1.34</v>
       </c>
       <c r="T91">
-        <v>3.2</v>
+        <v>3.09</v>
       </c>
       <c r="U91">
-        <v>2.75</v>
+        <v>2.55</v>
       </c>
       <c r="V91">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="W91">
         <v>1.1</v>
       </c>
       <c r="X91">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y91">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="Z91">
         <v>3.5</v>
       </c>
       <c r="AA91">
-        <v>1.8</v>
+        <v>1.88</v>
       </c>
       <c r="AB91">
-        <v>1.9</v>
+        <v>1.95</v>
       </c>
       <c r="AC91">
-        <v>3</v>
+        <v>2.97</v>
       </c>
       <c r="AD91">
-        <v>1.3</v>
+        <v>1.35</v>
       </c>
       <c r="AE91">
-        <v>1.13</v>
+        <v>1.09</v>
       </c>
       <c r="AF91">
         <v>1.68</v>
@@ -15212,7 +15212,7 @@
         </is>
       </c>
       <c r="AJ91">
-        <v>1.67</v>
+        <v>1.73</v>
       </c>
       <c r="AK91">
         <v>1.25</v>
@@ -15495,7 +15495,7 @@
         <v>1.43</v>
       </c>
       <c r="W93">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="X93">
         <v>1.01</v>
@@ -15504,10 +15504,10 @@
         <v>1.21</v>
       </c>
       <c r="Z93">
-        <v>3.58</v>
+        <v>3.85</v>
       </c>
       <c r="AA93">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="AB93">
         <v>1.85</v>
@@ -15522,10 +15522,10 @@
         <v>1.1</v>
       </c>
       <c r="AF93">
-        <v>1.63</v>
+        <v>1.7</v>
       </c>
       <c r="AG93">
-        <v>2.11</v>
+        <v>2</v>
       </c>
       <c r="AH93" t="inlineStr">
         <is>
@@ -15538,7 +15538,7 @@
         </is>
       </c>
       <c r="AJ93">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="AK93">
         <v>1.23</v>
@@ -16301,7 +16301,7 @@
         <v>1.24</v>
       </c>
       <c r="T98">
-        <v>3.75</v>
+        <v>3.5</v>
       </c>
       <c r="U98">
         <v>2.05</v>
@@ -16310,34 +16310,34 @@
         <v>1.62</v>
       </c>
       <c r="W98">
-        <v>1.17</v>
+        <v>1.12</v>
       </c>
       <c r="X98">
         <v>1.02</v>
       </c>
       <c r="Y98">
-        <v>1.1</v>
+        <v>1.15</v>
       </c>
       <c r="Z98">
-        <v>5.15</v>
+        <v>5.6</v>
       </c>
       <c r="AA98">
         <v>1.5</v>
       </c>
       <c r="AB98">
-        <v>2.55</v>
+        <v>2.5</v>
       </c>
       <c r="AC98">
-        <v>2.25</v>
+        <v>2.26</v>
       </c>
       <c r="AD98">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
       <c r="AE98">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AF98">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AG98">
         <v>2.5</v>
@@ -16353,7 +16353,7 @@
         </is>
       </c>
       <c r="AJ98">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="AK98">
         <v>1.95</v>
@@ -16772,31 +16772,31 @@
         </is>
       </c>
       <c r="N101">
-        <v>1.54</v>
+        <v>1.56</v>
       </c>
       <c r="O101">
-        <v>4.2</v>
+        <v>4.15</v>
       </c>
       <c r="P101">
         <v>4.9</v>
       </c>
       <c r="Q101">
-        <v>2.08</v>
+        <v>2.07</v>
       </c>
       <c r="R101">
-        <v>2.21</v>
+        <v>2.52</v>
       </c>
       <c r="S101">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="T101">
-        <v>3.3</v>
+        <v>3.6</v>
       </c>
       <c r="U101">
-        <v>2.38</v>
+        <v>2.39</v>
       </c>
       <c r="V101">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="W101">
         <v>1.08</v>
@@ -16808,7 +16808,7 @@
         <v>1.2</v>
       </c>
       <c r="Z101">
-        <v>4.4</v>
+        <v>4.59</v>
       </c>
       <c r="AA101">
         <v>1.63</v>
@@ -16842,10 +16842,10 @@
         </is>
       </c>
       <c r="AJ101">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="AK101">
-        <v>2.4</v>
+        <v>2.33</v>
       </c>
       <c r="AL101">
         <v>0</v>
@@ -17261,7 +17261,7 @@
         </is>
       </c>
       <c r="N104">
-        <v>2.23</v>
+        <v>2.17</v>
       </c>
       <c r="O104">
         <v>2.7</v>
@@ -17270,55 +17270,55 @@
         <v>3.65</v>
       </c>
       <c r="Q104">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="R104">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="S104">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="T104">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="U104">
-        <v>0</v>
+        <v>4.45</v>
       </c>
       <c r="V104">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="W104">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X104">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="Y104">
-        <v>1.65</v>
+        <v>1.75</v>
       </c>
       <c r="Z104">
-        <v>2.1</v>
+        <v>1.96</v>
       </c>
       <c r="AA104">
         <v>3.5</v>
       </c>
       <c r="AB104">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="AC104">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="AD104">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AE104">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AF104">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="AG104">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AH104" t="inlineStr">
         <is>
@@ -17331,10 +17331,10 @@
         </is>
       </c>
       <c r="AJ104">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK104">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AL104">
         <v>0</v>
@@ -17427,10 +17427,10 @@
         <v>2.55</v>
       </c>
       <c r="O105">
-        <v>2.65</v>
+        <v>2.75</v>
       </c>
       <c r="P105">
-        <v>2.87</v>
+        <v>2.9</v>
       </c>
       <c r="Q105">
         <v>0</v>
@@ -17590,43 +17590,43 @@
         <v>2.3</v>
       </c>
       <c r="O106">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="P106">
         <v>3.85</v>
       </c>
       <c r="Q106">
-        <v>3.29</v>
+        <v>3.1</v>
       </c>
       <c r="R106">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="S106">
-        <v>1.8</v>
+        <v>1.67</v>
       </c>
       <c r="T106">
-        <v>1.9</v>
+        <v>2.1</v>
       </c>
       <c r="U106">
-        <v>4.5</v>
+        <v>4.33</v>
       </c>
       <c r="V106">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="W106">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="X106">
         <v>1.18</v>
       </c>
       <c r="Y106">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="Z106">
-        <v>1.98</v>
+        <v>1.96</v>
       </c>
       <c r="AA106">
-        <v>3.28</v>
+        <v>3.52</v>
       </c>
       <c r="AB106">
         <v>1.27</v>
@@ -17657,10 +17657,10 @@
         </is>
       </c>
       <c r="AJ106">
-        <v>1.42</v>
+        <v>1.18</v>
       </c>
       <c r="AK106">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="AL106">
         <v>0</v>
@@ -17750,28 +17750,28 @@
         </is>
       </c>
       <c r="N107">
-        <v>2.17</v>
+        <v>2.25</v>
       </c>
       <c r="O107">
-        <v>2.75</v>
+        <v>2.7</v>
       </c>
       <c r="P107">
-        <v>3.7</v>
+        <v>3.3</v>
       </c>
       <c r="Q107">
         <v>2.9</v>
       </c>
       <c r="R107">
-        <v>1.83</v>
+        <v>1.91</v>
       </c>
       <c r="S107">
         <v>1.64</v>
       </c>
       <c r="T107">
-        <v>2.21</v>
+        <v>2.2</v>
       </c>
       <c r="U107">
-        <v>3.9</v>
+        <v>3.75</v>
       </c>
       <c r="V107">
         <v>1.22</v>
@@ -17804,10 +17804,10 @@
         <v>1.03</v>
       </c>
       <c r="AF107">
-        <v>2.23</v>
+        <v>2.3</v>
       </c>
       <c r="AG107">
-        <v>1.57</v>
+        <v>1.54</v>
       </c>
       <c r="AH107" t="inlineStr">
         <is>
@@ -17820,10 +17820,10 @@
         </is>
       </c>
       <c r="AJ107">
-        <v>1.19</v>
+        <v>1.21</v>
       </c>
       <c r="AK107">
-        <v>1.59</v>
+        <v>1.54</v>
       </c>
       <c r="AL107">
         <v>0</v>
@@ -18696,12 +18696,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Olimpija</t>
+          <t>Brinje-Grosuplje</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Aluminij</t>
+          <t>Koper</t>
         </is>
       </c>
       <c r="G113">
@@ -18728,64 +18728,64 @@
         </is>
       </c>
       <c r="N113">
-        <v>1.63</v>
+        <v>3.9</v>
       </c>
       <c r="O113">
-        <v>3.65</v>
+        <v>3.45</v>
       </c>
       <c r="P113">
-        <v>4.4</v>
+        <v>1.84</v>
       </c>
       <c r="Q113">
-        <v>2.15</v>
+        <v>4.82</v>
       </c>
       <c r="R113">
-        <v>2.38</v>
+        <v>2.2</v>
       </c>
       <c r="S113">
-        <v>1.3</v>
+        <v>1.35</v>
       </c>
       <c r="T113">
-        <v>3.28</v>
+        <v>3.16</v>
       </c>
       <c r="U113">
-        <v>2.5</v>
+        <v>2.68</v>
       </c>
       <c r="V113">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="W113">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="X113">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="Y113">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="Z113">
-        <v>4</v>
+        <v>3.6</v>
       </c>
       <c r="AA113">
-        <v>1.7</v>
+        <v>1.76</v>
       </c>
       <c r="AB113">
-        <v>2.2</v>
+        <v>1.92</v>
       </c>
       <c r="AC113">
-        <v>2.7</v>
+        <v>2.95</v>
       </c>
       <c r="AD113">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="AE113">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="AF113">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="AG113">
-        <v>2.01</v>
+        <v>2</v>
       </c>
       <c r="AH113" t="inlineStr">
         <is>
@@ -18798,10 +18798,10 @@
         </is>
       </c>
       <c r="AJ113">
-        <v>1.18</v>
+        <v>1.21</v>
       </c>
       <c r="AK113">
-        <v>2.14</v>
+        <v>1.17</v>
       </c>
       <c r="AL113">
         <v>0</v>
@@ -18859,12 +18859,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Brinje-Grosuplje</t>
+          <t>Olimpija</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Koper</t>
+          <t>Aluminij</t>
         </is>
       </c>
       <c r="G114">
@@ -18891,64 +18891,64 @@
         </is>
       </c>
       <c r="N114">
-        <v>3.9</v>
+        <v>1.63</v>
       </c>
       <c r="O114">
-        <v>3.45</v>
+        <v>3.65</v>
       </c>
       <c r="P114">
-        <v>1.84</v>
+        <v>4.4</v>
       </c>
       <c r="Q114">
-        <v>4.82</v>
+        <v>2.15</v>
       </c>
       <c r="R114">
+        <v>2.38</v>
+      </c>
+      <c r="S114">
+        <v>1.3</v>
+      </c>
+      <c r="T114">
+        <v>3.28</v>
+      </c>
+      <c r="U114">
+        <v>2.5</v>
+      </c>
+      <c r="V114">
+        <v>1.5</v>
+      </c>
+      <c r="W114">
+        <v>1.11</v>
+      </c>
+      <c r="X114">
+        <v>1.01</v>
+      </c>
+      <c r="Y114">
+        <v>1.22</v>
+      </c>
+      <c r="Z114">
+        <v>4</v>
+      </c>
+      <c r="AA114">
+        <v>1.7</v>
+      </c>
+      <c r="AB114">
         <v>2.2</v>
       </c>
-      <c r="S114">
-        <v>1.35</v>
-      </c>
-      <c r="T114">
-        <v>3.16</v>
-      </c>
-      <c r="U114">
-        <v>2.68</v>
-      </c>
-      <c r="V114">
-        <v>1.44</v>
-      </c>
-      <c r="W114">
+      <c r="AC114">
+        <v>2.7</v>
+      </c>
+      <c r="AD114">
+        <v>1.4</v>
+      </c>
+      <c r="AE114">
         <v>1.1</v>
       </c>
-      <c r="X114">
-        <v>1.05</v>
-      </c>
-      <c r="Y114">
-        <v>1.25</v>
-      </c>
-      <c r="Z114">
-        <v>3.6</v>
-      </c>
-      <c r="AA114">
-        <v>1.76</v>
-      </c>
-      <c r="AB114">
-        <v>1.92</v>
-      </c>
-      <c r="AC114">
-        <v>2.95</v>
-      </c>
-      <c r="AD114">
-        <v>1.33</v>
-      </c>
-      <c r="AE114">
-        <v>1.09</v>
-      </c>
       <c r="AF114">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="AG114">
-        <v>2</v>
+        <v>2.01</v>
       </c>
       <c r="AH114" t="inlineStr">
         <is>
@@ -18961,10 +18961,10 @@
         </is>
       </c>
       <c r="AJ114">
-        <v>1.21</v>
+        <v>1.18</v>
       </c>
       <c r="AK114">
-        <v>1.17</v>
+        <v>2.14</v>
       </c>
       <c r="AL114">
         <v>0</v>
@@ -19217,25 +19217,25 @@
         </is>
       </c>
       <c r="N116">
-        <v>1.43</v>
+        <v>1.48</v>
       </c>
       <c r="O116">
         <v>4.4</v>
       </c>
       <c r="P116">
-        <v>5.75</v>
+        <v>5.25</v>
       </c>
       <c r="Q116">
-        <v>1.94</v>
+        <v>1.91</v>
       </c>
       <c r="R116">
-        <v>2.35</v>
+        <v>2.59</v>
       </c>
       <c r="S116">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="T116">
-        <v>3.25</v>
+        <v>3.5</v>
       </c>
       <c r="U116">
         <v>2.25</v>
@@ -19250,7 +19250,7 @@
         <v>1.01</v>
       </c>
       <c r="Y116">
-        <v>1.13</v>
+        <v>1.18</v>
       </c>
       <c r="Z116">
         <v>4.5</v>
@@ -19259,7 +19259,7 @@
         <v>1.58</v>
       </c>
       <c r="AB116">
-        <v>2.3</v>
+        <v>2.23</v>
       </c>
       <c r="AC116">
         <v>2.41</v>
@@ -19383,13 +19383,13 @@
         <v>1.23</v>
       </c>
       <c r="O117">
-        <v>4.85</v>
+        <v>5.3</v>
       </c>
       <c r="P117">
-        <v>8.800000000000001</v>
+        <v>8.1</v>
       </c>
       <c r="Q117">
-        <v>1.65</v>
+        <v>1.69</v>
       </c>
       <c r="R117">
         <v>2.5</v>
@@ -19407,34 +19407,34 @@
         <v>1.44</v>
       </c>
       <c r="W117">
-        <v>1.1</v>
+        <v>1.07</v>
       </c>
       <c r="X117">
         <v>1.02</v>
       </c>
       <c r="Y117">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="Z117">
-        <v>3.51</v>
+        <v>3.56</v>
       </c>
       <c r="AA117">
         <v>1.8</v>
       </c>
       <c r="AB117">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="AC117">
         <v>2.8</v>
       </c>
       <c r="AD117">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AE117">
         <v>1.12</v>
       </c>
       <c r="AF117">
-        <v>2.46</v>
+        <v>2.49</v>
       </c>
       <c r="AG117">
         <v>1.48</v>
@@ -19453,7 +19453,7 @@
         <v>1.01</v>
       </c>
       <c r="AK117">
-        <v>3.52</v>
+        <v>3.6</v>
       </c>
       <c r="AL117">
         <v>0</v>
@@ -19543,7 +19543,7 @@
         </is>
       </c>
       <c r="N118">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="O118">
         <v>2.75</v>
@@ -19552,19 +19552,19 @@
         <v>4</v>
       </c>
       <c r="Q118">
-        <v>3</v>
+        <v>2.93</v>
       </c>
       <c r="R118">
-        <v>1.85</v>
+        <v>1.7</v>
       </c>
       <c r="S118">
-        <v>1.69</v>
+        <v>1.58</v>
       </c>
       <c r="T118">
         <v>1.99</v>
       </c>
       <c r="U118">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="V118">
         <v>1.15</v>
@@ -19576,7 +19576,7 @@
         <v>1.15</v>
       </c>
       <c r="Y118">
-        <v>1.67</v>
+        <v>1.69</v>
       </c>
       <c r="Z118">
         <v>2.08</v>
@@ -19585,7 +19585,7 @@
         <v>2.97</v>
       </c>
       <c r="AB118">
-        <v>1.32</v>
+        <v>1.35</v>
       </c>
       <c r="AC118">
         <v>6.39</v>
@@ -19613,7 +19613,7 @@
         </is>
       </c>
       <c r="AJ118">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="AK118">
         <v>1.63</v>
@@ -19706,22 +19706,22 @@
         </is>
       </c>
       <c r="N119">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="O119">
-        <v>2.9</v>
+        <v>2.87</v>
       </c>
       <c r="P119">
-        <v>2.9</v>
+        <v>2.6</v>
       </c>
       <c r="Q119">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="R119">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="S119">
-        <v>1.53</v>
+        <v>1.59</v>
       </c>
       <c r="T119">
         <v>2.2</v>
@@ -19733,19 +19733,19 @@
         <v>1.21</v>
       </c>
       <c r="W119">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="X119">
         <v>1.12</v>
       </c>
       <c r="Y119">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="Z119">
-        <v>2.42</v>
+        <v>2.43</v>
       </c>
       <c r="AA119">
-        <v>2.7</v>
+        <v>2.48</v>
       </c>
       <c r="AB119">
         <v>1.45</v>
@@ -19754,16 +19754,16 @@
         <v>4.6</v>
       </c>
       <c r="AD119">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="AE119">
         <v>1.01</v>
       </c>
       <c r="AF119">
-        <v>2.04</v>
+        <v>2.09</v>
       </c>
       <c r="AG119">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="AH119" t="inlineStr">
         <is>
@@ -19869,7 +19869,7 @@
         </is>
       </c>
       <c r="N120">
-        <v>1.95</v>
+        <v>1.98</v>
       </c>
       <c r="O120">
         <v>3.25</v>
@@ -19902,19 +19902,19 @@
         <v>1.05</v>
       </c>
       <c r="Y120">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="Z120">
         <v>2.97</v>
       </c>
       <c r="AA120">
-        <v>2</v>
+        <v>2.04</v>
       </c>
       <c r="AB120">
-        <v>1.71</v>
+        <v>1.74</v>
       </c>
       <c r="AC120">
-        <v>3.34</v>
+        <v>3.45</v>
       </c>
       <c r="AD120">
         <v>1.28</v>
@@ -19923,10 +19923,10 @@
         <v>1.05</v>
       </c>
       <c r="AF120">
-        <v>1.83</v>
+        <v>1.87</v>
       </c>
       <c r="AG120">
-        <v>1.87</v>
+        <v>1.9</v>
       </c>
       <c r="AH120" t="inlineStr">
         <is>
@@ -20201,7 +20201,7 @@
         <v>3.45</v>
       </c>
       <c r="P122">
-        <v>2.55</v>
+        <v>2.6</v>
       </c>
       <c r="Q122">
         <v>2.95</v>
@@ -20213,7 +20213,7 @@
         <v>1.31</v>
       </c>
       <c r="T122">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="U122">
         <v>2.65</v>
@@ -20228,22 +20228,22 @@
         <v>1.02</v>
       </c>
       <c r="Y122">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="Z122">
-        <v>3.96</v>
+        <v>3.7</v>
       </c>
       <c r="AA122">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="AB122">
-        <v>2.02</v>
+        <v>1.98</v>
       </c>
       <c r="AC122">
-        <v>2.94</v>
+        <v>2.95</v>
       </c>
       <c r="AD122">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="AE122">
         <v>1.11</v>
@@ -20252,7 +20252,7 @@
         <v>1.6</v>
       </c>
       <c r="AG122">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="AH122" t="inlineStr">
         <is>
@@ -20265,7 +20265,7 @@
         </is>
       </c>
       <c r="AJ122">
-        <v>1.22</v>
+        <v>1.4</v>
       </c>
       <c r="AK122">
         <v>1.45</v>
@@ -20489,12 +20489,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Deportivo Madryn</t>
+          <t>Chaco For Ever</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>All Boys</t>
+          <t>Deportivo Morón</t>
         </is>
       </c>
       <c r="G124">
@@ -20521,52 +20521,52 @@
         </is>
       </c>
       <c r="N124">
-        <v>1.91</v>
+        <v>2.8</v>
       </c>
       <c r="O124">
-        <v>2.8</v>
+        <v>2.7</v>
       </c>
       <c r="P124">
-        <v>4.33</v>
+        <v>2.44</v>
       </c>
       <c r="Q124">
-        <v>2.7</v>
+        <v>3.98</v>
       </c>
       <c r="R124">
-        <v>1.83</v>
+        <v>1.74</v>
       </c>
       <c r="S124">
-        <v>1.7</v>
+        <v>1.58</v>
       </c>
       <c r="T124">
-        <v>2.25</v>
+        <v>2.07</v>
       </c>
       <c r="U124">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="V124">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="W124">
         <v>1.03</v>
       </c>
       <c r="X124">
-        <v>1.12</v>
+        <v>1.1</v>
       </c>
       <c r="Y124">
-        <v>1.71</v>
+        <v>1.65</v>
       </c>
       <c r="Z124">
-        <v>2.06</v>
+        <v>2.15</v>
       </c>
       <c r="AA124">
-        <v>3.4</v>
+        <v>2.75</v>
       </c>
       <c r="AB124">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AC124">
-        <v>5.95</v>
+        <v>5.3</v>
       </c>
       <c r="AD124">
         <v>1.07</v>
@@ -20575,10 +20575,10 @@
         <v>1.02</v>
       </c>
       <c r="AF124">
-        <v>2.51</v>
+        <v>2.2</v>
       </c>
       <c r="AG124">
-        <v>1.44</v>
+        <v>1.55</v>
       </c>
       <c r="AH124" t="inlineStr">
         <is>
@@ -20591,10 +20591,10 @@
         </is>
       </c>
       <c r="AJ124">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="AK124">
-        <v>1.8</v>
+        <v>1.31</v>
       </c>
       <c r="AL124">
         <v>0</v>
@@ -20652,12 +20652,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Chaco For Ever</t>
+          <t>Deportivo Madryn</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Deportivo Morón</t>
+          <t>All Boys</t>
         </is>
       </c>
       <c r="G125">
@@ -20684,52 +20684,52 @@
         </is>
       </c>
       <c r="N125">
-        <v>2.8</v>
+        <v>1.91</v>
       </c>
       <c r="O125">
-        <v>2.7</v>
+        <v>2.87</v>
       </c>
       <c r="P125">
-        <v>2.5</v>
+        <v>4.8</v>
       </c>
       <c r="Q125">
-        <v>3.98</v>
+        <v>2.78</v>
       </c>
       <c r="R125">
-        <v>1.83</v>
+        <v>1.72</v>
       </c>
       <c r="S125">
-        <v>1.57</v>
+        <v>1.7</v>
       </c>
       <c r="T125">
-        <v>2.07</v>
+        <v>2.25</v>
       </c>
       <c r="U125">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="V125">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="W125">
         <v>1.03</v>
       </c>
       <c r="X125">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="Y125">
-        <v>1.65</v>
+        <v>1.71</v>
       </c>
       <c r="Z125">
-        <v>2.15</v>
+        <v>2.06</v>
       </c>
       <c r="AA125">
-        <v>2.75</v>
+        <v>3.4</v>
       </c>
       <c r="AB125">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="AC125">
-        <v>5.3</v>
+        <v>5.95</v>
       </c>
       <c r="AD125">
         <v>1.07</v>
@@ -20738,10 +20738,10 @@
         <v>1.02</v>
       </c>
       <c r="AF125">
-        <v>2.2</v>
+        <v>2.51</v>
       </c>
       <c r="AG125">
-        <v>1.57</v>
+        <v>1.44</v>
       </c>
       <c r="AH125" t="inlineStr">
         <is>
@@ -20754,10 +20754,10 @@
         </is>
       </c>
       <c r="AJ125">
-        <v>1.44</v>
+        <v>1.35</v>
       </c>
       <c r="AK125">
-        <v>1.31</v>
+        <v>1.8</v>
       </c>
       <c r="AL125">
         <v>0</v>
@@ -21010,13 +21010,13 @@
         </is>
       </c>
       <c r="N127">
-        <v>2.87</v>
+        <v>2.81</v>
       </c>
       <c r="O127">
-        <v>2.65</v>
+        <v>2.45</v>
       </c>
       <c r="P127">
-        <v>2.9</v>
+        <v>2.95</v>
       </c>
       <c r="Q127">
         <v>0</v>
@@ -21173,49 +21173,49 @@
         </is>
       </c>
       <c r="N128">
-        <v>2.05</v>
+        <v>2.45</v>
       </c>
       <c r="O128">
-        <v>3.28</v>
+        <v>3.55</v>
       </c>
       <c r="P128">
-        <v>3.25</v>
+        <v>2.3</v>
       </c>
       <c r="Q128">
-        <v>2.43</v>
+        <v>2.9</v>
       </c>
       <c r="R128">
-        <v>2.25</v>
+        <v>2.1</v>
       </c>
       <c r="S128">
         <v>1.36</v>
       </c>
       <c r="T128">
-        <v>2.73</v>
+        <v>2.75</v>
       </c>
       <c r="U128">
-        <v>2.45</v>
+        <v>2.29</v>
       </c>
       <c r="V128">
-        <v>1.42</v>
+        <v>1.31</v>
       </c>
       <c r="W128">
         <v>1.04</v>
       </c>
       <c r="X128">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y128">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
       <c r="Z128">
-        <v>3.11</v>
+        <v>3.08</v>
       </c>
       <c r="AA128">
-        <v>1.96</v>
+        <v>1.94</v>
       </c>
       <c r="AB128">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="AC128">
         <v>3.34</v>
@@ -21224,13 +21224,13 @@
         <v>1.24</v>
       </c>
       <c r="AE128">
-        <v>1.08</v>
+        <v>1.04</v>
       </c>
       <c r="AF128">
         <v>1.75</v>
       </c>
       <c r="AG128">
-        <v>1.95</v>
+        <v>1.78</v>
       </c>
       <c r="AH128" t="inlineStr">
         <is>
@@ -21246,7 +21246,7 @@
         <v>1.1</v>
       </c>
       <c r="AK128">
-        <v>1.58</v>
+        <v>1.39</v>
       </c>
       <c r="AL128">
         <v>0</v>
@@ -21825,64 +21825,64 @@
         </is>
       </c>
       <c r="N132">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="O132">
-        <v>3.7</v>
+        <v>3.9</v>
       </c>
       <c r="P132">
         <v>5</v>
       </c>
       <c r="Q132">
-        <v>2.09</v>
+        <v>2.07</v>
       </c>
       <c r="R132">
         <v>2.25</v>
       </c>
       <c r="S132">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="T132">
-        <v>3.07</v>
+        <v>3.16</v>
       </c>
       <c r="U132">
-        <v>2.6</v>
+        <v>2.59</v>
       </c>
       <c r="V132">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="W132">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="X132">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y132">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="Z132">
         <v>3.5</v>
       </c>
       <c r="AA132">
-        <v>1.85</v>
+        <v>1.87</v>
       </c>
       <c r="AB132">
         <v>1.87</v>
       </c>
       <c r="AC132">
-        <v>3.19</v>
+        <v>3.05</v>
       </c>
       <c r="AD132">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="AE132">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="AF132">
-        <v>1.83</v>
+        <v>1.79</v>
       </c>
       <c r="AG132">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="AH132" t="inlineStr">
         <is>
@@ -21898,7 +21898,7 @@
         <v>1.15</v>
       </c>
       <c r="AK132">
-        <v>2.19</v>
+        <v>2.06</v>
       </c>
       <c r="AL132">
         <v>0</v>
@@ -22151,61 +22151,61 @@
         </is>
       </c>
       <c r="N134">
-        <v>1.95</v>
+        <v>1.79</v>
       </c>
       <c r="O134">
-        <v>3.54</v>
+        <v>3.55</v>
       </c>
       <c r="P134">
-        <v>3.27</v>
+        <v>3.55</v>
       </c>
       <c r="Q134">
-        <v>2.49</v>
+        <v>2.35</v>
       </c>
       <c r="R134">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="S134">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="T134">
-        <v>3.14</v>
+        <v>3.2</v>
       </c>
       <c r="U134">
-        <v>2.48</v>
+        <v>2.36</v>
       </c>
       <c r="V134">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="W134">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="X134">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y134">
-        <v>1.21</v>
+        <v>1.17</v>
       </c>
       <c r="Z134">
-        <v>3.6</v>
+        <v>4.05</v>
       </c>
       <c r="AA134">
-        <v>1.7</v>
+        <v>1.65</v>
       </c>
       <c r="AB134">
-        <v>1.94</v>
+        <v>2.16</v>
       </c>
       <c r="AC134">
-        <v>2.62</v>
+        <v>2.63</v>
       </c>
       <c r="AD134">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="AE134">
         <v>1.12</v>
       </c>
       <c r="AF134">
-        <v>1.55</v>
+        <v>1.6</v>
       </c>
       <c r="AG134">
         <v>2.1</v>
@@ -22221,10 +22221,10 @@
         </is>
       </c>
       <c r="AJ134">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AK134">
-        <v>1.7</v>
+        <v>1.79</v>
       </c>
       <c r="AL134">
         <v>0</v>
@@ -22640,13 +22640,13 @@
         </is>
       </c>
       <c r="N137">
-        <v>1.9</v>
+        <v>1.83</v>
       </c>
       <c r="O137">
-        <v>3.45</v>
+        <v>3.64</v>
       </c>
       <c r="P137">
-        <v>3.25</v>
+        <v>3.56</v>
       </c>
       <c r="Q137">
         <v>0</v>

--- a/jogos_2026-08-02.xlsx
+++ b/jogos_2026-08-02.xlsx
@@ -1092,12 +1092,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Rockdale City Suns</t>
+          <t>Marconi Stallions</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Manly United</t>
+          <t>St George City FA</t>
         </is>
       </c>
       <c r="G5">
@@ -1124,64 +1124,64 @@
         </is>
       </c>
       <c r="N5">
-        <v>1.71</v>
+        <v>1.32</v>
       </c>
       <c r="O5">
-        <v>3.7</v>
+        <v>4.45</v>
       </c>
       <c r="P5">
-        <v>3.55</v>
+        <v>6.7</v>
       </c>
       <c r="Q5">
-        <v>2.2</v>
+        <v>1.76</v>
       </c>
       <c r="R5">
-        <v>2.25</v>
+        <v>2.47</v>
       </c>
       <c r="S5">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="T5">
-        <v>3.28</v>
+        <v>3.14</v>
       </c>
       <c r="U5">
-        <v>2.31</v>
+        <v>2.41</v>
       </c>
       <c r="V5">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="W5">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="X5">
         <v>1.02</v>
       </c>
       <c r="Y5">
-        <v>1.13</v>
+        <v>1.19</v>
       </c>
       <c r="Z5">
-        <v>4.5</v>
+        <v>3.86</v>
       </c>
       <c r="AA5">
-        <v>1.54</v>
+        <v>1.67</v>
       </c>
       <c r="AB5">
-        <v>2.19</v>
+        <v>2.06</v>
       </c>
       <c r="AC5">
-        <v>2.44</v>
+        <v>2.62</v>
       </c>
       <c r="AD5">
-        <v>1.48</v>
+        <v>1.38</v>
       </c>
       <c r="AE5">
-        <v>1.19</v>
+        <v>1.12</v>
       </c>
       <c r="AF5">
-        <v>1.54</v>
+        <v>1.99</v>
       </c>
       <c r="AG5">
-        <v>2.26</v>
+        <v>1.7</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1194,10 +1194,10 @@
         </is>
       </c>
       <c r="AJ5">
-        <v>1.16</v>
+        <v>1.1</v>
       </c>
       <c r="AK5">
-        <v>1.91</v>
+        <v>3.04</v>
       </c>
       <c r="AL5">
         <v>0</v>
@@ -1255,12 +1255,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Marconi Stallions</t>
+          <t>Rockdale City Suns</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>St George City FA</t>
+          <t>Manly United</t>
         </is>
       </c>
       <c r="G6">
@@ -1287,64 +1287,64 @@
         </is>
       </c>
       <c r="N6">
-        <v>1.32</v>
+        <v>1.71</v>
       </c>
       <c r="O6">
-        <v>4.45</v>
+        <v>3.7</v>
       </c>
       <c r="P6">
-        <v>6.7</v>
+        <v>3.55</v>
       </c>
       <c r="Q6">
-        <v>1.76</v>
+        <v>2.2</v>
       </c>
       <c r="R6">
-        <v>2.47</v>
+        <v>2.25</v>
       </c>
       <c r="S6">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="T6">
-        <v>3.14</v>
+        <v>3.28</v>
       </c>
       <c r="U6">
-        <v>2.41</v>
+        <v>2.31</v>
       </c>
       <c r="V6">
-        <v>1.46</v>
+        <v>1.5</v>
       </c>
       <c r="W6">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="X6">
         <v>1.02</v>
       </c>
       <c r="Y6">
+        <v>1.13</v>
+      </c>
+      <c r="Z6">
+        <v>4.5</v>
+      </c>
+      <c r="AA6">
+        <v>1.54</v>
+      </c>
+      <c r="AB6">
+        <v>2.19</v>
+      </c>
+      <c r="AC6">
+        <v>2.44</v>
+      </c>
+      <c r="AD6">
+        <v>1.48</v>
+      </c>
+      <c r="AE6">
         <v>1.19</v>
       </c>
-      <c r="Z6">
-        <v>3.86</v>
-      </c>
-      <c r="AA6">
-        <v>1.67</v>
-      </c>
-      <c r="AB6">
-        <v>2.06</v>
-      </c>
-      <c r="AC6">
-        <v>2.62</v>
-      </c>
-      <c r="AD6">
-        <v>1.38</v>
-      </c>
-      <c r="AE6">
-        <v>1.12</v>
-      </c>
       <c r="AF6">
-        <v>1.99</v>
+        <v>1.54</v>
       </c>
       <c r="AG6">
-        <v>1.7</v>
+        <v>2.26</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1357,10 +1357,10 @@
         </is>
       </c>
       <c r="AJ6">
-        <v>1.1</v>
+        <v>1.16</v>
       </c>
       <c r="AK6">
-        <v>3.04</v>
+        <v>1.91</v>
       </c>
       <c r="AL6">
         <v>0</v>
@@ -1779,10 +1779,10 @@
         <v>2.37</v>
       </c>
       <c r="O9">
-        <v>3.25</v>
+        <v>3.44</v>
       </c>
       <c r="P9">
-        <v>2.6</v>
+        <v>2.67</v>
       </c>
       <c r="Q9">
         <v>0</v>
@@ -2722,12 +2722,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Ansan Greeners</t>
+          <t>Busan I'Park</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Gimhae City</t>
+          <t>Seoul E-Land</t>
         </is>
       </c>
       <c r="G15">
@@ -2754,64 +2754,64 @@
         </is>
       </c>
       <c r="N15">
-        <v>2.65</v>
+        <v>2.42</v>
       </c>
       <c r="O15">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="P15">
-        <v>2.15</v>
+        <v>2.17</v>
       </c>
       <c r="Q15">
-        <v>3.4</v>
+        <v>3.1</v>
       </c>
       <c r="R15">
-        <v>2.2</v>
+        <v>2.23</v>
       </c>
       <c r="S15">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="T15">
-        <v>2.82</v>
+        <v>3.3</v>
       </c>
       <c r="U15">
-        <v>2.84</v>
+        <v>2.5</v>
       </c>
       <c r="V15">
-        <v>1.4</v>
+        <v>1.45</v>
       </c>
       <c r="W15">
-        <v>1.08</v>
+        <v>1.12</v>
       </c>
       <c r="X15">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y15">
-        <v>1.29</v>
+        <v>1.21</v>
       </c>
       <c r="Z15">
-        <v>3.28</v>
+        <v>4.23</v>
       </c>
       <c r="AA15">
-        <v>1.87</v>
+        <v>1.67</v>
       </c>
       <c r="AB15">
-        <v>1.87</v>
+        <v>2.1</v>
       </c>
       <c r="AC15">
-        <v>3.2</v>
+        <v>2.66</v>
       </c>
       <c r="AD15">
-        <v>1.27</v>
+        <v>1.37</v>
       </c>
       <c r="AE15">
         <v>1.11</v>
       </c>
       <c r="AF15">
-        <v>1.67</v>
+        <v>1.57</v>
       </c>
       <c r="AG15">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2824,10 +2824,10 @@
         </is>
       </c>
       <c r="AJ15">
-        <v>1.25</v>
+        <v>1.51</v>
       </c>
       <c r="AK15">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="AL15">
         <v>0</v>
@@ -2885,12 +2885,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Busan I'Park</t>
+          <t>Gimpo Citizen</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Seoul E-Land</t>
+          <t>Gyeongnam</t>
         </is>
       </c>
       <c r="G16">
@@ -2917,64 +2917,64 @@
         </is>
       </c>
       <c r="N16">
-        <v>2.42</v>
+        <v>1.94</v>
       </c>
       <c r="O16">
+        <v>2.98</v>
+      </c>
+      <c r="P16">
+        <v>3.5</v>
+      </c>
+      <c r="Q16">
+        <v>2.62</v>
+      </c>
+      <c r="R16">
+        <v>2.15</v>
+      </c>
+      <c r="S16">
+        <v>1.4</v>
+      </c>
+      <c r="T16">
+        <v>2.5</v>
+      </c>
+      <c r="U16">
+        <v>3.12</v>
+      </c>
+      <c r="V16">
+        <v>1.29</v>
+      </c>
+      <c r="W16">
+        <v>1.02</v>
+      </c>
+      <c r="X16">
+        <v>1.06</v>
+      </c>
+      <c r="Y16">
+        <v>1.39</v>
+      </c>
+      <c r="Z16">
+        <v>2.9</v>
+      </c>
+      <c r="AA16">
+        <v>2.28</v>
+      </c>
+      <c r="AB16">
+        <v>1.62</v>
+      </c>
+      <c r="AC16">
         <v>3.3</v>
       </c>
-      <c r="P16">
-        <v>2.17</v>
-      </c>
-      <c r="Q16">
-        <v>3.1</v>
-      </c>
-      <c r="R16">
-        <v>2.23</v>
-      </c>
-      <c r="S16">
-        <v>1.3</v>
-      </c>
-      <c r="T16">
-        <v>3.3</v>
-      </c>
-      <c r="U16">
-        <v>2.5</v>
-      </c>
-      <c r="V16">
-        <v>1.45</v>
-      </c>
-      <c r="W16">
-        <v>1.12</v>
-      </c>
-      <c r="X16">
+      <c r="AD16">
+        <v>1.18</v>
+      </c>
+      <c r="AE16">
         <v>1.03</v>
       </c>
-      <c r="Y16">
-        <v>1.21</v>
-      </c>
-      <c r="Z16">
-        <v>4.23</v>
-      </c>
-      <c r="AA16">
-        <v>1.67</v>
-      </c>
-      <c r="AB16">
-        <v>2.1</v>
-      </c>
-      <c r="AC16">
-        <v>2.66</v>
-      </c>
-      <c r="AD16">
-        <v>1.37</v>
-      </c>
-      <c r="AE16">
-        <v>1.11</v>
-      </c>
       <c r="AF16">
-        <v>1.57</v>
+        <v>1.93</v>
       </c>
       <c r="AG16">
-        <v>2.25</v>
+        <v>1.8</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -2987,10 +2987,10 @@
         </is>
       </c>
       <c r="AJ16">
-        <v>1.51</v>
+        <v>1.24</v>
       </c>
       <c r="AK16">
-        <v>1.36</v>
+        <v>1.72</v>
       </c>
       <c r="AL16">
         <v>0</v>
@@ -3048,12 +3048,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Gimpo Citizen</t>
+          <t>Ansan Greeners</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Gyeongnam</t>
+          <t>Gimhae City</t>
         </is>
       </c>
       <c r="G17">
@@ -3080,64 +3080,64 @@
         </is>
       </c>
       <c r="N17">
-        <v>1.94</v>
+        <v>2.65</v>
       </c>
       <c r="O17">
-        <v>2.98</v>
+        <v>3.25</v>
       </c>
       <c r="P17">
-        <v>3.5</v>
+        <v>2.15</v>
       </c>
       <c r="Q17">
-        <v>2.62</v>
+        <v>3.4</v>
       </c>
       <c r="R17">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="S17">
+        <v>1.35</v>
+      </c>
+      <c r="T17">
+        <v>2.82</v>
+      </c>
+      <c r="U17">
+        <v>2.84</v>
+      </c>
+      <c r="V17">
         <v>1.4</v>
       </c>
-      <c r="T17">
-        <v>2.5</v>
-      </c>
-      <c r="U17">
-        <v>3.12</v>
-      </c>
-      <c r="V17">
+      <c r="W17">
+        <v>1.08</v>
+      </c>
+      <c r="X17">
+        <v>1.04</v>
+      </c>
+      <c r="Y17">
         <v>1.29</v>
       </c>
-      <c r="W17">
-        <v>1.02</v>
-      </c>
-      <c r="X17">
-        <v>1.06</v>
-      </c>
-      <c r="Y17">
-        <v>1.39</v>
-      </c>
       <c r="Z17">
-        <v>2.9</v>
+        <v>3.28</v>
       </c>
       <c r="AA17">
-        <v>2.28</v>
+        <v>1.87</v>
       </c>
       <c r="AB17">
-        <v>1.62</v>
+        <v>1.87</v>
       </c>
       <c r="AC17">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="AD17">
-        <v>1.18</v>
+        <v>1.27</v>
       </c>
       <c r="AE17">
-        <v>1.03</v>
+        <v>1.11</v>
       </c>
       <c r="AF17">
-        <v>1.93</v>
+        <v>1.67</v>
       </c>
       <c r="AG17">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3150,10 +3150,10 @@
         </is>
       </c>
       <c r="AJ17">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="AK17">
-        <v>1.72</v>
+        <v>1.35</v>
       </c>
       <c r="AL17">
         <v>0</v>
@@ -5199,10 +5199,10 @@
         </is>
       </c>
       <c r="N30">
-        <v>1.99</v>
+        <v>2.05</v>
       </c>
       <c r="O30">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="P30">
         <v>3</v>
@@ -5214,16 +5214,16 @@
         <v>2.19</v>
       </c>
       <c r="S30">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="T30">
-        <v>3.2</v>
+        <v>3.12</v>
       </c>
       <c r="U30">
         <v>2.5</v>
       </c>
       <c r="V30">
-        <v>1.49</v>
+        <v>1.44</v>
       </c>
       <c r="W30">
         <v>1.08</v>
@@ -5232,22 +5232,22 @@
         <v>1.02</v>
       </c>
       <c r="Y30">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="Z30">
-        <v>4.2</v>
+        <v>3.86</v>
       </c>
       <c r="AA30">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="AB30">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="AC30">
         <v>2.88</v>
       </c>
       <c r="AD30">
-        <v>1.4</v>
+        <v>1.35</v>
       </c>
       <c r="AE30">
         <v>1.09</v>
@@ -5371,25 +5371,25 @@
         <v>4.7</v>
       </c>
       <c r="Q31">
-        <v>2.14</v>
+        <v>2.01</v>
       </c>
       <c r="R31">
         <v>2.15</v>
       </c>
       <c r="S31">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="T31">
-        <v>2.85</v>
+        <v>3.2</v>
       </c>
       <c r="U31">
-        <v>2.73</v>
+        <v>2.83</v>
       </c>
       <c r="V31">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="W31">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="X31">
         <v>1.01</v>
@@ -5407,19 +5407,19 @@
         <v>1.9</v>
       </c>
       <c r="AC31">
-        <v>3.05</v>
+        <v>3.25</v>
       </c>
       <c r="AD31">
         <v>1.28</v>
       </c>
       <c r="AE31">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="AF31">
         <v>1.87</v>
       </c>
       <c r="AG31">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="AH31" t="inlineStr">
         <is>
@@ -5432,10 +5432,10 @@
         </is>
       </c>
       <c r="AJ31">
-        <v>1.12</v>
+        <v>1.18</v>
       </c>
       <c r="AK31">
-        <v>2.27</v>
+        <v>2.3</v>
       </c>
       <c r="AL31">
         <v>0</v>
@@ -7318,19 +7318,19 @@
         </is>
       </c>
       <c r="N43">
-        <v>2.8</v>
+        <v>2.7</v>
       </c>
       <c r="O43">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="P43">
+        <v>2.25</v>
+      </c>
+      <c r="Q43">
+        <v>3.35</v>
+      </c>
+      <c r="R43">
         <v>2.2</v>
-      </c>
-      <c r="Q43">
-        <v>3.33</v>
-      </c>
-      <c r="R43">
-        <v>2.3</v>
       </c>
       <c r="S43">
         <v>1.3</v>
@@ -7351,7 +7351,7 @@
         <v>1.02</v>
       </c>
       <c r="Y43">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="Z43">
         <v>4.15</v>
@@ -7363,16 +7363,16 @@
         <v>2.05</v>
       </c>
       <c r="AC43">
-        <v>2.7</v>
+        <v>2.65</v>
       </c>
       <c r="AD43">
         <v>1.4</v>
       </c>
       <c r="AE43">
-        <v>1.16</v>
+        <v>1.11</v>
       </c>
       <c r="AF43">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="AG43">
         <v>2.3</v>
@@ -7388,10 +7388,10 @@
         </is>
       </c>
       <c r="AJ43">
-        <v>1.27</v>
+        <v>1.57</v>
       </c>
       <c r="AK43">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="AL43">
         <v>0</v>
@@ -9437,19 +9437,19 @@
         </is>
       </c>
       <c r="N56">
-        <v>2.5</v>
+        <v>2.45</v>
       </c>
       <c r="O56">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="P56">
-        <v>2.39</v>
+        <v>2.45</v>
       </c>
       <c r="Q56">
         <v>2.78</v>
       </c>
       <c r="R56">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="S56">
         <v>1.29</v>
@@ -9470,19 +9470,19 @@
         <v>1.02</v>
       </c>
       <c r="Y56">
-        <v>1.14</v>
+        <v>1.18</v>
       </c>
       <c r="Z56">
-        <v>4.33</v>
+        <v>4.5</v>
       </c>
       <c r="AA56">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="AB56">
         <v>2.3</v>
       </c>
       <c r="AC56">
-        <v>2.46</v>
+        <v>2.51</v>
       </c>
       <c r="AD56">
         <v>1.43</v>
@@ -9494,7 +9494,7 @@
         <v>1.5</v>
       </c>
       <c r="AG56">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="AH56" t="inlineStr">
         <is>
@@ -9510,7 +9510,7 @@
         <v>1.44</v>
       </c>
       <c r="AK56">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="AL56">
         <v>0</v>
@@ -9766,25 +9766,25 @@
         <v>3.31</v>
       </c>
       <c r="O58">
-        <v>3.5</v>
+        <v>3.7</v>
       </c>
       <c r="P58">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="Q58">
-        <v>3.75</v>
+        <v>3.94</v>
       </c>
       <c r="R58">
-        <v>2.23</v>
+        <v>2.24</v>
       </c>
       <c r="S58">
-        <v>1.31</v>
+        <v>1.25</v>
       </c>
       <c r="T58">
-        <v>3.15</v>
+        <v>3.22</v>
       </c>
       <c r="U58">
-        <v>2.44</v>
+        <v>2.5</v>
       </c>
       <c r="V58">
         <v>1.49</v>
@@ -9793,7 +9793,7 @@
         <v>1.08</v>
       </c>
       <c r="X58">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y58">
         <v>1.17</v>
@@ -9805,10 +9805,10 @@
         <v>1.66</v>
       </c>
       <c r="AB58">
-        <v>2.15</v>
+        <v>2.19</v>
       </c>
       <c r="AC58">
-        <v>2.69</v>
+        <v>2.67</v>
       </c>
       <c r="AD58">
         <v>1.47</v>
@@ -9817,10 +9817,10 @@
         <v>1.18</v>
       </c>
       <c r="AF58">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="AG58">
-        <v>2.2</v>
+        <v>2.26</v>
       </c>
       <c r="AH58" t="inlineStr">
         <is>
@@ -9833,10 +9833,10 @@
         </is>
       </c>
       <c r="AJ58">
-        <v>1.22</v>
+        <v>1.27</v>
       </c>
       <c r="AK58">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="AL58">
         <v>0</v>
@@ -9932,19 +9932,19 @@
         <v>3.85</v>
       </c>
       <c r="P59">
-        <v>4.2</v>
+        <v>4.72</v>
       </c>
       <c r="Q59">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="R59">
-        <v>2.46</v>
+        <v>2.45</v>
       </c>
       <c r="S59">
-        <v>1.29</v>
+        <v>1.35</v>
       </c>
       <c r="T59">
-        <v>3.25</v>
+        <v>2.94</v>
       </c>
       <c r="U59">
         <v>2.4</v>
@@ -9977,13 +9977,13 @@
         <v>1.42</v>
       </c>
       <c r="AE59">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="AF59">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="AG59">
-        <v>2.08</v>
+        <v>2.09</v>
       </c>
       <c r="AH59" t="inlineStr">
         <is>
@@ -9996,7 +9996,7 @@
         </is>
       </c>
       <c r="AJ59">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="AK59">
         <v>2.1</v>
@@ -10089,19 +10089,19 @@
         </is>
       </c>
       <c r="N60">
-        <v>1.57</v>
+        <v>1.61</v>
       </c>
       <c r="O60">
-        <v>4.2</v>
+        <v>3.9</v>
       </c>
       <c r="P60">
         <v>4</v>
       </c>
       <c r="Q60">
-        <v>2.1</v>
+        <v>2.11</v>
       </c>
       <c r="R60">
-        <v>2.63</v>
+        <v>2.36</v>
       </c>
       <c r="S60">
         <v>1.23</v>
@@ -10110,13 +10110,13 @@
         <v>3.58</v>
       </c>
       <c r="U60">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="V60">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="W60">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="X60">
         <v>1.02</v>
@@ -10140,10 +10140,10 @@
         <v>1.76</v>
       </c>
       <c r="AE60">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="AF60">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="AG60">
         <v>2.55</v>
@@ -12700,10 +12700,10 @@
         <v>2.5</v>
       </c>
       <c r="O76">
-        <v>3.1</v>
+        <v>3.13</v>
       </c>
       <c r="P76">
-        <v>2.4</v>
+        <v>2.37</v>
       </c>
       <c r="Q76">
         <v>3.54</v>
@@ -12712,7 +12712,7 @@
         <v>2.04</v>
       </c>
       <c r="S76">
-        <v>1.37</v>
+        <v>1.39</v>
       </c>
       <c r="T76">
         <v>2.73</v>
@@ -12721,40 +12721,40 @@
         <v>2.9</v>
       </c>
       <c r="V76">
-        <v>1.39</v>
+        <v>1.34</v>
       </c>
       <c r="W76">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="X76">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y76">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="Z76">
-        <v>3.46</v>
+        <v>3.2</v>
       </c>
       <c r="AA76">
         <v>2.04</v>
       </c>
       <c r="AB76">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="AC76">
         <v>3.6</v>
       </c>
       <c r="AD76">
-        <v>1.26</v>
+        <v>1.23</v>
       </c>
       <c r="AE76">
-        <v>1.11</v>
+        <v>1.07</v>
       </c>
       <c r="AF76">
         <v>1.72</v>
       </c>
       <c r="AG76">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AH76" t="inlineStr">
         <is>
@@ -13678,7 +13678,7 @@
         <v>1.79</v>
       </c>
       <c r="O82">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="P82">
         <v>4.46</v>
@@ -13690,31 +13690,31 @@
         <v>2.1</v>
       </c>
       <c r="S82">
-        <v>1.43</v>
+        <v>1.45</v>
       </c>
       <c r="T82">
         <v>2.56</v>
       </c>
       <c r="U82">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
       <c r="V82">
-        <v>1.31</v>
+        <v>1.36</v>
       </c>
       <c r="W82">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="X82">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="Y82">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="Z82">
-        <v>2.97</v>
+        <v>3</v>
       </c>
       <c r="AA82">
-        <v>2.14</v>
+        <v>2.1</v>
       </c>
       <c r="AB82">
         <v>1.7</v>
@@ -13723,10 +13723,10 @@
         <v>3.85</v>
       </c>
       <c r="AD82">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AE82">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="AF82">
         <v>1.97</v>
@@ -14132,12 +14132,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Vaprus</t>
+          <t>Tallinna FC Flora</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Tallinna FC Levadia</t>
+          <t>Harju Jalgpallikool</t>
         </is>
       </c>
       <c r="G85">
@@ -14164,64 +14164,64 @@
         </is>
       </c>
       <c r="N85">
-        <v>11.7</v>
+        <v>1.53</v>
       </c>
       <c r="O85">
-        <v>5.75</v>
+        <v>4.55</v>
       </c>
       <c r="P85">
-        <v>1.24</v>
+        <v>4.8</v>
       </c>
       <c r="Q85">
-        <v>7.61</v>
+        <v>1.93</v>
       </c>
       <c r="R85">
-        <v>2.82</v>
+        <v>2.65</v>
       </c>
       <c r="S85">
-        <v>1.2</v>
+        <v>1.23</v>
       </c>
       <c r="T85">
-        <v>3.8</v>
+        <v>3.42</v>
       </c>
       <c r="U85">
-        <v>2.17</v>
+        <v>2.18</v>
       </c>
       <c r="V85">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="W85">
-        <v>1.17</v>
+        <v>1.12</v>
       </c>
       <c r="X85">
         <v>1.02</v>
       </c>
       <c r="Y85">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="Z85">
-        <v>5.15</v>
+        <v>4.95</v>
       </c>
       <c r="AA85">
-        <v>1.42</v>
+        <v>1.49</v>
       </c>
       <c r="AB85">
-        <v>2.49</v>
+        <v>2.51</v>
       </c>
       <c r="AC85">
-        <v>2.14</v>
+        <v>2.24</v>
       </c>
       <c r="AD85">
         <v>1.63</v>
       </c>
       <c r="AE85">
-        <v>1.24</v>
+        <v>1.21</v>
       </c>
       <c r="AF85">
-        <v>1.8</v>
+        <v>1.53</v>
       </c>
       <c r="AG85">
-        <v>1.88</v>
+        <v>2.3</v>
       </c>
       <c r="AH85" t="inlineStr">
         <is>
@@ -14234,10 +14234,10 @@
         </is>
       </c>
       <c r="AJ85">
-        <v>1.11</v>
+        <v>1.22</v>
       </c>
       <c r="AK85">
-        <v>1.03</v>
+        <v>2.25</v>
       </c>
       <c r="AL85">
         <v>0</v>
@@ -14295,12 +14295,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Tallinna FC Flora</t>
+          <t>Vaprus</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Harju Jalgpallikool</t>
+          <t>Tallinna FC Levadia</t>
         </is>
       </c>
       <c r="G86">
@@ -14327,64 +14327,64 @@
         </is>
       </c>
       <c r="N86">
-        <v>1.53</v>
+        <v>11.7</v>
       </c>
       <c r="O86">
-        <v>4.55</v>
+        <v>5.75</v>
       </c>
       <c r="P86">
-        <v>4.8</v>
+        <v>1.24</v>
       </c>
       <c r="Q86">
-        <v>1.93</v>
+        <v>7.61</v>
       </c>
       <c r="R86">
-        <v>2.65</v>
+        <v>2.82</v>
       </c>
       <c r="S86">
-        <v>1.23</v>
+        <v>1.2</v>
       </c>
       <c r="T86">
-        <v>3.42</v>
+        <v>3.8</v>
       </c>
       <c r="U86">
-        <v>2.18</v>
+        <v>2.17</v>
       </c>
       <c r="V86">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="W86">
-        <v>1.12</v>
+        <v>1.17</v>
       </c>
       <c r="X86">
         <v>1.02</v>
       </c>
       <c r="Y86">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="Z86">
-        <v>4.95</v>
+        <v>5.15</v>
       </c>
       <c r="AA86">
-        <v>1.49</v>
+        <v>1.42</v>
       </c>
       <c r="AB86">
-        <v>2.51</v>
+        <v>2.49</v>
       </c>
       <c r="AC86">
-        <v>2.24</v>
+        <v>2.14</v>
       </c>
       <c r="AD86">
         <v>1.63</v>
       </c>
       <c r="AE86">
-        <v>1.21</v>
+        <v>1.24</v>
       </c>
       <c r="AF86">
-        <v>1.53</v>
+        <v>1.8</v>
       </c>
       <c r="AG86">
-        <v>2.3</v>
+        <v>1.88</v>
       </c>
       <c r="AH86" t="inlineStr">
         <is>
@@ -14397,10 +14397,10 @@
         </is>
       </c>
       <c r="AJ86">
-        <v>1.22</v>
+        <v>1.11</v>
       </c>
       <c r="AK86">
-        <v>2.25</v>
+        <v>1.03</v>
       </c>
       <c r="AL86">
         <v>0</v>
@@ -16283,13 +16283,13 @@
         </is>
       </c>
       <c r="N98">
-        <v>1.9</v>
+        <v>1.88</v>
       </c>
       <c r="O98">
-        <v>3.8</v>
+        <v>3.6</v>
       </c>
       <c r="P98">
-        <v>3.76</v>
+        <v>3.4</v>
       </c>
       <c r="Q98">
         <v>2.2</v>
@@ -16307,10 +16307,10 @@
         <v>2.05</v>
       </c>
       <c r="V98">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="W98">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="X98">
         <v>1.02</v>
@@ -16319,22 +16319,22 @@
         <v>1.15</v>
       </c>
       <c r="Z98">
-        <v>5.6</v>
+        <v>5.25</v>
       </c>
       <c r="AA98">
         <v>1.5</v>
       </c>
       <c r="AB98">
-        <v>2.5</v>
+        <v>2.62</v>
       </c>
       <c r="AC98">
-        <v>2.26</v>
+        <v>2.22</v>
       </c>
       <c r="AD98">
         <v>1.67</v>
       </c>
       <c r="AE98">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="AF98">
         <v>1.4</v>
@@ -16446,13 +16446,13 @@
         </is>
       </c>
       <c r="N99">
-        <v>2.19</v>
+        <v>2.37</v>
       </c>
       <c r="O99">
         <v>3.3</v>
       </c>
       <c r="P99">
-        <v>2.77</v>
+        <v>2.6</v>
       </c>
       <c r="Q99">
         <v>2.94</v>
@@ -16461,13 +16461,13 @@
         <v>2.11</v>
       </c>
       <c r="S99">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="T99">
-        <v>3.09</v>
+        <v>2.91</v>
       </c>
       <c r="U99">
-        <v>2.41</v>
+        <v>2.56</v>
       </c>
       <c r="V99">
         <v>1.47</v>
@@ -16491,7 +16491,7 @@
         <v>2.03</v>
       </c>
       <c r="AC99">
-        <v>2.59</v>
+        <v>2.77</v>
       </c>
       <c r="AD99">
         <v>1.39</v>
@@ -16516,7 +16516,7 @@
         </is>
       </c>
       <c r="AJ99">
-        <v>1.36</v>
+        <v>1.26</v>
       </c>
       <c r="AK99">
         <v>1.5</v>
@@ -16772,13 +16772,13 @@
         </is>
       </c>
       <c r="N101">
-        <v>1.56</v>
+        <v>1.53</v>
       </c>
       <c r="O101">
         <v>4.15</v>
       </c>
       <c r="P101">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="Q101">
         <v>2.07</v>
@@ -16790,22 +16790,22 @@
         <v>1.25</v>
       </c>
       <c r="T101">
-        <v>3.6</v>
+        <v>3.34</v>
       </c>
       <c r="U101">
         <v>2.39</v>
       </c>
       <c r="V101">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="W101">
         <v>1.08</v>
       </c>
       <c r="X101">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y101">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="Z101">
         <v>4.59</v>
@@ -16814,7 +16814,7 @@
         <v>1.63</v>
       </c>
       <c r="AB101">
-        <v>2.05</v>
+        <v>2.25</v>
       </c>
       <c r="AC101">
         <v>2.48</v>
@@ -17229,12 +17229,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Ciudad de Bolívar</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Club Atlético Mitre</t>
+          <t>San Miguel</t>
         </is>
       </c>
       <c r="G104">
@@ -17261,64 +17261,64 @@
         </is>
       </c>
       <c r="N104">
-        <v>2.17</v>
+        <v>2.55</v>
       </c>
       <c r="O104">
-        <v>2.7</v>
+        <v>2.75</v>
       </c>
       <c r="P104">
-        <v>3.65</v>
+        <v>2.9</v>
       </c>
       <c r="Q104">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="R104">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="S104">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="T104">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="U104">
-        <v>4.45</v>
+        <v>0</v>
       </c>
       <c r="V104">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="W104">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="X104">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="Y104">
-        <v>1.75</v>
+        <v>1.63</v>
       </c>
       <c r="Z104">
-        <v>1.96</v>
+        <v>2.1</v>
       </c>
       <c r="AA104">
-        <v>3.5</v>
+        <v>3.1</v>
       </c>
       <c r="AB104">
         <v>1.36</v>
       </c>
       <c r="AC104">
-        <v>5.4</v>
+        <v>0</v>
       </c>
       <c r="AD104">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AE104">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AF104">
-        <v>2.54</v>
+        <v>0</v>
       </c>
       <c r="AG104">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AH104" t="inlineStr">
         <is>
@@ -17331,10 +17331,10 @@
         </is>
       </c>
       <c r="AJ104">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AK104">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AL104">
         <v>0</v>
@@ -17392,12 +17392,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Almirante Brown</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>San Miguel</t>
+          <t>Racing Córdoba</t>
         </is>
       </c>
       <c r="G105">
@@ -17424,64 +17424,64 @@
         </is>
       </c>
       <c r="N105">
-        <v>2.55</v>
+        <v>2.3</v>
       </c>
       <c r="O105">
-        <v>2.75</v>
+        <v>2.5</v>
       </c>
       <c r="P105">
-        <v>2.9</v>
+        <v>3.85</v>
       </c>
       <c r="Q105">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R105">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="S105">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="T105">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="U105">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="V105">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="W105">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X105">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Y105">
-        <v>1.63</v>
+        <v>1.75</v>
       </c>
       <c r="Z105">
-        <v>2.1</v>
+        <v>1.96</v>
       </c>
       <c r="AA105">
-        <v>3.1</v>
+        <v>3.52</v>
       </c>
       <c r="AB105">
-        <v>1.36</v>
+        <v>1.27</v>
       </c>
       <c r="AC105">
-        <v>0</v>
+        <v>7.1</v>
       </c>
       <c r="AD105">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AE105">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AF105">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="AG105">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AH105" t="inlineStr">
         <is>
@@ -17494,10 +17494,10 @@
         </is>
       </c>
       <c r="AJ105">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AK105">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AL105">
         <v>0</v>
@@ -17555,12 +17555,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Almirante Brown</t>
+          <t>Chacarita Juniors</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Racing Córdoba</t>
+          <t>Agropecuario</t>
         </is>
       </c>
       <c r="G106">
@@ -17587,64 +17587,64 @@
         </is>
       </c>
       <c r="N106">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="O106">
-        <v>2.5</v>
+        <v>2.7</v>
       </c>
       <c r="P106">
-        <v>3.85</v>
+        <v>3.3</v>
       </c>
       <c r="Q106">
-        <v>3.1</v>
+        <v>2.9</v>
       </c>
       <c r="R106">
-        <v>1.61</v>
+        <v>1.91</v>
       </c>
       <c r="S106">
-        <v>1.67</v>
+        <v>1.64</v>
       </c>
       <c r="T106">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="U106">
-        <v>4.33</v>
+        <v>3.75</v>
       </c>
       <c r="V106">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="W106">
         <v>1.03</v>
       </c>
       <c r="X106">
-        <v>1.18</v>
+        <v>1.1</v>
       </c>
       <c r="Y106">
-        <v>1.75</v>
+        <v>1.6</v>
       </c>
       <c r="Z106">
-        <v>1.96</v>
+        <v>2.19</v>
       </c>
       <c r="AA106">
-        <v>3.52</v>
+        <v>2.74</v>
       </c>
       <c r="AB106">
-        <v>1.27</v>
+        <v>1.37</v>
       </c>
       <c r="AC106">
-        <v>7.1</v>
+        <v>6.5</v>
       </c>
       <c r="AD106">
-        <v>1.04</v>
+        <v>1.1</v>
       </c>
       <c r="AE106">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="AF106">
-        <v>2.54</v>
+        <v>2.3</v>
       </c>
       <c r="AG106">
-        <v>1.45</v>
+        <v>1.54</v>
       </c>
       <c r="AH106" t="inlineStr">
         <is>
@@ -17657,10 +17657,10 @@
         </is>
       </c>
       <c r="AJ106">
-        <v>1.18</v>
+        <v>1.21</v>
       </c>
       <c r="AK106">
-        <v>1.5</v>
+        <v>1.54</v>
       </c>
       <c r="AL106">
         <v>0</v>
@@ -17718,12 +17718,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Chacarita Juniors</t>
+          <t>Ciudad de Bolívar</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Agropecuario</t>
+          <t>Club Atlético Mitre</t>
         </is>
       </c>
       <c r="G107">
@@ -17750,64 +17750,64 @@
         </is>
       </c>
       <c r="N107">
-        <v>2.25</v>
+        <v>2.17</v>
       </c>
       <c r="O107">
         <v>2.7</v>
       </c>
       <c r="P107">
-        <v>3.3</v>
+        <v>3.65</v>
       </c>
       <c r="Q107">
-        <v>2.9</v>
+        <v>3.05</v>
       </c>
       <c r="R107">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="S107">
-        <v>1.64</v>
+        <v>1.58</v>
       </c>
       <c r="T107">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="U107">
-        <v>3.75</v>
+        <v>4.45</v>
       </c>
       <c r="V107">
-        <v>1.22</v>
+        <v>1.14</v>
       </c>
       <c r="W107">
         <v>1.03</v>
       </c>
       <c r="X107">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="Y107">
-        <v>1.6</v>
+        <v>1.75</v>
       </c>
       <c r="Z107">
-        <v>2.19</v>
+        <v>1.96</v>
       </c>
       <c r="AA107">
-        <v>2.74</v>
+        <v>3.5</v>
       </c>
       <c r="AB107">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="AC107">
-        <v>6.5</v>
+        <v>5.4</v>
       </c>
       <c r="AD107">
         <v>1.1</v>
       </c>
       <c r="AE107">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AF107">
-        <v>2.3</v>
+        <v>2.54</v>
       </c>
       <c r="AG107">
-        <v>1.54</v>
+        <v>1.44</v>
       </c>
       <c r="AH107" t="inlineStr">
         <is>
@@ -17820,10 +17820,10 @@
         </is>
       </c>
       <c r="AJ107">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="AK107">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="AL107">
         <v>0</v>
@@ -19054,7 +19054,7 @@
         </is>
       </c>
       <c r="N115">
-        <v>1.8</v>
+        <v>1.93</v>
       </c>
       <c r="O115">
         <v>3.52</v>
@@ -19063,10 +19063,10 @@
         <v>3.8</v>
       </c>
       <c r="Q115">
-        <v>2.4</v>
+        <v>2.44</v>
       </c>
       <c r="R115">
-        <v>2.28</v>
+        <v>2.14</v>
       </c>
       <c r="S115">
         <v>1.35</v>
@@ -19075,7 +19075,7 @@
         <v>2.9</v>
       </c>
       <c r="U115">
-        <v>2.6</v>
+        <v>2.56</v>
       </c>
       <c r="V115">
         <v>1.44</v>
@@ -19090,13 +19090,13 @@
         <v>1.24</v>
       </c>
       <c r="Z115">
-        <v>3.99</v>
+        <v>3.75</v>
       </c>
       <c r="AA115">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="AB115">
-        <v>1.97</v>
+        <v>2</v>
       </c>
       <c r="AC115">
         <v>3</v>
@@ -19108,10 +19108,10 @@
         <v>1.1</v>
       </c>
       <c r="AF115">
-        <v>1.7</v>
+        <v>1.66</v>
       </c>
       <c r="AG115">
-        <v>2</v>
+        <v>2.09</v>
       </c>
       <c r="AH115" t="inlineStr">
         <is>
@@ -19124,10 +19124,10 @@
         </is>
       </c>
       <c r="AJ115">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="AK115">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="AL115">
         <v>0</v>
@@ -20489,12 +20489,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Chaco For Ever</t>
+          <t>Deportivo Madryn</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Deportivo Morón</t>
+          <t>All Boys</t>
         </is>
       </c>
       <c r="G124">
@@ -20521,52 +20521,52 @@
         </is>
       </c>
       <c r="N124">
-        <v>2.8</v>
+        <v>1.91</v>
       </c>
       <c r="O124">
-        <v>2.7</v>
+        <v>2.87</v>
       </c>
       <c r="P124">
-        <v>2.44</v>
+        <v>4.8</v>
       </c>
       <c r="Q124">
-        <v>3.98</v>
+        <v>2.78</v>
       </c>
       <c r="R124">
-        <v>1.74</v>
+        <v>1.72</v>
       </c>
       <c r="S124">
-        <v>1.58</v>
+        <v>1.7</v>
       </c>
       <c r="T124">
-        <v>2.07</v>
+        <v>2.25</v>
       </c>
       <c r="U124">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="V124">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="W124">
         <v>1.03</v>
       </c>
       <c r="X124">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="Y124">
-        <v>1.65</v>
+        <v>1.71</v>
       </c>
       <c r="Z124">
-        <v>2.15</v>
+        <v>2.06</v>
       </c>
       <c r="AA124">
-        <v>2.75</v>
+        <v>3.4</v>
       </c>
       <c r="AB124">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="AC124">
-        <v>5.3</v>
+        <v>5.95</v>
       </c>
       <c r="AD124">
         <v>1.07</v>
@@ -20575,10 +20575,10 @@
         <v>1.02</v>
       </c>
       <c r="AF124">
-        <v>2.2</v>
+        <v>2.51</v>
       </c>
       <c r="AG124">
-        <v>1.55</v>
+        <v>1.44</v>
       </c>
       <c r="AH124" t="inlineStr">
         <is>
@@ -20591,10 +20591,10 @@
         </is>
       </c>
       <c r="AJ124">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="AK124">
-        <v>1.31</v>
+        <v>1.8</v>
       </c>
       <c r="AL124">
         <v>0</v>
@@ -20652,12 +20652,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Deportivo Madryn</t>
+          <t>Chaco For Ever</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>All Boys</t>
+          <t>Deportivo Morón</t>
         </is>
       </c>
       <c r="G125">
@@ -20684,52 +20684,52 @@
         </is>
       </c>
       <c r="N125">
-        <v>1.91</v>
+        <v>2.8</v>
       </c>
       <c r="O125">
-        <v>2.87</v>
+        <v>2.7</v>
       </c>
       <c r="P125">
-        <v>4.8</v>
+        <v>2.44</v>
       </c>
       <c r="Q125">
-        <v>2.78</v>
+        <v>3.98</v>
       </c>
       <c r="R125">
-        <v>1.72</v>
+        <v>1.74</v>
       </c>
       <c r="S125">
-        <v>1.7</v>
+        <v>1.58</v>
       </c>
       <c r="T125">
-        <v>2.25</v>
+        <v>2.07</v>
       </c>
       <c r="U125">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="V125">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="W125">
         <v>1.03</v>
       </c>
       <c r="X125">
-        <v>1.12</v>
+        <v>1.1</v>
       </c>
       <c r="Y125">
-        <v>1.71</v>
+        <v>1.65</v>
       </c>
       <c r="Z125">
-        <v>2.06</v>
+        <v>2.15</v>
       </c>
       <c r="AA125">
-        <v>3.4</v>
+        <v>2.75</v>
       </c>
       <c r="AB125">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="AC125">
-        <v>5.95</v>
+        <v>5.3</v>
       </c>
       <c r="AD125">
         <v>1.07</v>
@@ -20738,10 +20738,10 @@
         <v>1.02</v>
       </c>
       <c r="AF125">
-        <v>2.51</v>
+        <v>2.2</v>
       </c>
       <c r="AG125">
-        <v>1.44</v>
+        <v>1.55</v>
       </c>
       <c r="AH125" t="inlineStr">
         <is>
@@ -20754,10 +20754,10 @@
         </is>
       </c>
       <c r="AJ125">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="AK125">
-        <v>1.8</v>
+        <v>1.31</v>
       </c>
       <c r="AL125">
         <v>0</v>
@@ -21499,13 +21499,13 @@
         </is>
       </c>
       <c r="N130">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="O130">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="P130">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="Q130">
         <v>0</v>
@@ -22477,13 +22477,13 @@
         </is>
       </c>
       <c r="N136">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="O136">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="P136">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="Q136">
         <v>0</v>

--- a/jogos_2026-08-02.xlsx
+++ b/jogos_2026-08-02.xlsx
@@ -635,28 +635,28 @@
         </is>
       </c>
       <c r="N2">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="O2">
         <v>4.75</v>
       </c>
       <c r="P2">
-        <v>7</v>
+        <v>6.9</v>
       </c>
       <c r="Q2">
-        <v>1.73</v>
+        <v>1.69</v>
       </c>
       <c r="R2">
-        <v>2.63</v>
+        <v>2.62</v>
       </c>
       <c r="S2">
         <v>1.22</v>
       </c>
       <c r="T2">
-        <v>3.5</v>
+        <v>3.75</v>
       </c>
       <c r="U2">
-        <v>2.06</v>
+        <v>2.19</v>
       </c>
       <c r="V2">
         <v>1.58</v>
@@ -668,31 +668,31 @@
         <v>1.01</v>
       </c>
       <c r="Y2">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="Z2">
-        <v>4.55</v>
+        <v>5</v>
       </c>
       <c r="AA2">
-        <v>1.5</v>
+        <v>1.54</v>
       </c>
       <c r="AB2">
-        <v>2.28</v>
+        <v>2.27</v>
       </c>
       <c r="AC2">
-        <v>2.34</v>
+        <v>2.18</v>
       </c>
       <c r="AD2">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="AE2">
         <v>1.2</v>
       </c>
       <c r="AF2">
-        <v>1.82</v>
+        <v>1.84</v>
       </c>
       <c r="AG2">
-        <v>1.87</v>
+        <v>1.95</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
@@ -705,10 +705,10 @@
         </is>
       </c>
       <c r="AJ2">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="AK2">
-        <v>3.05</v>
+        <v>2.65</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -1092,12 +1092,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Marconi Stallions</t>
+          <t>Rockdale City Suns</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>St George City FA</t>
+          <t>Manly United</t>
         </is>
       </c>
       <c r="G5">
@@ -1124,64 +1124,64 @@
         </is>
       </c>
       <c r="N5">
-        <v>1.32</v>
+        <v>1.71</v>
       </c>
       <c r="O5">
-        <v>4.45</v>
+        <v>3.7</v>
       </c>
       <c r="P5">
-        <v>6.7</v>
+        <v>3.55</v>
       </c>
       <c r="Q5">
-        <v>1.76</v>
+        <v>2.2</v>
       </c>
       <c r="R5">
-        <v>2.47</v>
+        <v>2.25</v>
       </c>
       <c r="S5">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="T5">
-        <v>3.14</v>
+        <v>3.28</v>
       </c>
       <c r="U5">
-        <v>2.41</v>
+        <v>2.31</v>
       </c>
       <c r="V5">
-        <v>1.46</v>
+        <v>1.5</v>
       </c>
       <c r="W5">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="X5">
         <v>1.02</v>
       </c>
       <c r="Y5">
+        <v>1.13</v>
+      </c>
+      <c r="Z5">
+        <v>4.5</v>
+      </c>
+      <c r="AA5">
+        <v>1.54</v>
+      </c>
+      <c r="AB5">
+        <v>2.19</v>
+      </c>
+      <c r="AC5">
+        <v>2.44</v>
+      </c>
+      <c r="AD5">
+        <v>1.48</v>
+      </c>
+      <c r="AE5">
         <v>1.19</v>
       </c>
-      <c r="Z5">
-        <v>3.86</v>
-      </c>
-      <c r="AA5">
-        <v>1.67</v>
-      </c>
-      <c r="AB5">
-        <v>2.06</v>
-      </c>
-      <c r="AC5">
-        <v>2.62</v>
-      </c>
-      <c r="AD5">
-        <v>1.38</v>
-      </c>
-      <c r="AE5">
-        <v>1.12</v>
-      </c>
       <c r="AF5">
-        <v>1.99</v>
+        <v>1.54</v>
       </c>
       <c r="AG5">
-        <v>1.7</v>
+        <v>2.26</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1194,10 +1194,10 @@
         </is>
       </c>
       <c r="AJ5">
-        <v>1.1</v>
+        <v>1.16</v>
       </c>
       <c r="AK5">
-        <v>3.04</v>
+        <v>1.91</v>
       </c>
       <c r="AL5">
         <v>0</v>
@@ -1255,12 +1255,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Rockdale City Suns</t>
+          <t>Marconi Stallions</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Manly United</t>
+          <t>St George City FA</t>
         </is>
       </c>
       <c r="G6">
@@ -1287,64 +1287,64 @@
         </is>
       </c>
       <c r="N6">
-        <v>1.71</v>
+        <v>1.32</v>
       </c>
       <c r="O6">
-        <v>3.7</v>
+        <v>4.45</v>
       </c>
       <c r="P6">
-        <v>3.55</v>
+        <v>6.7</v>
       </c>
       <c r="Q6">
-        <v>2.2</v>
+        <v>1.76</v>
       </c>
       <c r="R6">
-        <v>2.25</v>
+        <v>2.47</v>
       </c>
       <c r="S6">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="T6">
-        <v>3.28</v>
+        <v>3.14</v>
       </c>
       <c r="U6">
-        <v>2.31</v>
+        <v>2.41</v>
       </c>
       <c r="V6">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="W6">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="X6">
         <v>1.02</v>
       </c>
       <c r="Y6">
-        <v>1.13</v>
+        <v>1.19</v>
       </c>
       <c r="Z6">
-        <v>4.5</v>
+        <v>3.86</v>
       </c>
       <c r="AA6">
-        <v>1.54</v>
+        <v>1.67</v>
       </c>
       <c r="AB6">
-        <v>2.19</v>
+        <v>2.06</v>
       </c>
       <c r="AC6">
-        <v>2.44</v>
+        <v>2.62</v>
       </c>
       <c r="AD6">
-        <v>1.48</v>
+        <v>1.38</v>
       </c>
       <c r="AE6">
-        <v>1.19</v>
+        <v>1.12</v>
       </c>
       <c r="AF6">
-        <v>1.54</v>
+        <v>1.99</v>
       </c>
       <c r="AG6">
-        <v>2.26</v>
+        <v>1.7</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1357,10 +1357,10 @@
         </is>
       </c>
       <c r="AJ6">
-        <v>1.16</v>
+        <v>1.1</v>
       </c>
       <c r="AK6">
-        <v>1.91</v>
+        <v>3.04</v>
       </c>
       <c r="AL6">
         <v>0</v>
@@ -2233,12 +2233,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Jeju United</t>
+          <t>Ulsan</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Incheon United</t>
+          <t>Anyang</t>
         </is>
       </c>
       <c r="G12">
@@ -2265,64 +2265,64 @@
         </is>
       </c>
       <c r="N12">
-        <v>2.88</v>
+        <v>1.86</v>
       </c>
       <c r="O12">
-        <v>2.88</v>
+        <v>3.45</v>
       </c>
       <c r="P12">
-        <v>2.33</v>
+        <v>3.35</v>
       </c>
       <c r="Q12">
-        <v>3.2</v>
+        <v>2.38</v>
       </c>
       <c r="R12">
-        <v>1.98</v>
+        <v>2.25</v>
       </c>
       <c r="S12">
-        <v>1.53</v>
+        <v>1.35</v>
       </c>
       <c r="T12">
-        <v>2.34</v>
+        <v>2.75</v>
       </c>
       <c r="U12">
-        <v>3.4</v>
+        <v>2.65</v>
       </c>
       <c r="V12">
-        <v>1.27</v>
+        <v>1.42</v>
       </c>
       <c r="W12">
+        <v>1.1</v>
+      </c>
+      <c r="X12">
         <v>1.01</v>
       </c>
-      <c r="X12">
-        <v>1.07</v>
-      </c>
       <c r="Y12">
-        <v>1.4</v>
+        <v>1.22</v>
       </c>
       <c r="Z12">
-        <v>2.57</v>
+        <v>3.82</v>
       </c>
       <c r="AA12">
-        <v>2.38</v>
+        <v>1.89</v>
       </c>
       <c r="AB12">
-        <v>1.56</v>
+        <v>2.01</v>
       </c>
       <c r="AC12">
-        <v>4.5</v>
+        <v>3.05</v>
       </c>
       <c r="AD12">
-        <v>1.19</v>
+        <v>1.37</v>
       </c>
       <c r="AE12">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="AF12">
-        <v>1.97</v>
+        <v>1.7</v>
       </c>
       <c r="AG12">
-        <v>1.75</v>
+        <v>2.04</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2335,10 +2335,10 @@
         </is>
       </c>
       <c r="AJ12">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="AK12">
-        <v>1.34</v>
+        <v>1.9</v>
       </c>
       <c r="AL12">
         <v>0</v>
@@ -2396,12 +2396,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Ulsan</t>
+          <t>Jeju United</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Anyang</t>
+          <t>Incheon United</t>
         </is>
       </c>
       <c r="G13">
@@ -2428,64 +2428,64 @@
         </is>
       </c>
       <c r="N13">
-        <v>1.86</v>
+        <v>2.88</v>
       </c>
       <c r="O13">
-        <v>3.45</v>
+        <v>2.88</v>
       </c>
       <c r="P13">
-        <v>3.35</v>
+        <v>2.33</v>
       </c>
       <c r="Q13">
+        <v>3.2</v>
+      </c>
+      <c r="R13">
+        <v>1.98</v>
+      </c>
+      <c r="S13">
+        <v>1.53</v>
+      </c>
+      <c r="T13">
+        <v>2.34</v>
+      </c>
+      <c r="U13">
+        <v>3.4</v>
+      </c>
+      <c r="V13">
+        <v>1.27</v>
+      </c>
+      <c r="W13">
+        <v>1.01</v>
+      </c>
+      <c r="X13">
+        <v>1.07</v>
+      </c>
+      <c r="Y13">
+        <v>1.4</v>
+      </c>
+      <c r="Z13">
+        <v>2.57</v>
+      </c>
+      <c r="AA13">
         <v>2.38</v>
       </c>
-      <c r="R13">
-        <v>2.25</v>
-      </c>
-      <c r="S13">
-        <v>1.35</v>
-      </c>
-      <c r="T13">
-        <v>2.75</v>
-      </c>
-      <c r="U13">
-        <v>2.65</v>
-      </c>
-      <c r="V13">
-        <v>1.42</v>
-      </c>
-      <c r="W13">
-        <v>1.1</v>
-      </c>
-      <c r="X13">
+      <c r="AB13">
+        <v>1.56</v>
+      </c>
+      <c r="AC13">
+        <v>4.5</v>
+      </c>
+      <c r="AD13">
+        <v>1.19</v>
+      </c>
+      <c r="AE13">
         <v>1.01</v>
       </c>
-      <c r="Y13">
-        <v>1.22</v>
-      </c>
-      <c r="Z13">
-        <v>3.82</v>
-      </c>
-      <c r="AA13">
-        <v>1.89</v>
-      </c>
-      <c r="AB13">
-        <v>2.01</v>
-      </c>
-      <c r="AC13">
-        <v>3.05</v>
-      </c>
-      <c r="AD13">
-        <v>1.37</v>
-      </c>
-      <c r="AE13">
-        <v>1.08</v>
-      </c>
       <c r="AF13">
-        <v>1.7</v>
+        <v>1.97</v>
       </c>
       <c r="AG13">
-        <v>2.04</v>
+        <v>1.75</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2498,10 +2498,10 @@
         </is>
       </c>
       <c r="AJ13">
-        <v>1.25</v>
+        <v>1.36</v>
       </c>
       <c r="AK13">
-        <v>1.9</v>
+        <v>1.34</v>
       </c>
       <c r="AL13">
         <v>0</v>
@@ -2722,12 +2722,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Busan I'Park</t>
+          <t>Gimpo Citizen</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Seoul E-Land</t>
+          <t>Gyeongnam</t>
         </is>
       </c>
       <c r="G15">
@@ -2754,64 +2754,64 @@
         </is>
       </c>
       <c r="N15">
-        <v>2.42</v>
+        <v>1.94</v>
       </c>
       <c r="O15">
+        <v>2.98</v>
+      </c>
+      <c r="P15">
+        <v>3.5</v>
+      </c>
+      <c r="Q15">
+        <v>2.62</v>
+      </c>
+      <c r="R15">
+        <v>2.15</v>
+      </c>
+      <c r="S15">
+        <v>1.4</v>
+      </c>
+      <c r="T15">
+        <v>2.5</v>
+      </c>
+      <c r="U15">
+        <v>3.12</v>
+      </c>
+      <c r="V15">
+        <v>1.29</v>
+      </c>
+      <c r="W15">
+        <v>1.02</v>
+      </c>
+      <c r="X15">
+        <v>1.06</v>
+      </c>
+      <c r="Y15">
+        <v>1.39</v>
+      </c>
+      <c r="Z15">
+        <v>2.9</v>
+      </c>
+      <c r="AA15">
+        <v>2.28</v>
+      </c>
+      <c r="AB15">
+        <v>1.62</v>
+      </c>
+      <c r="AC15">
         <v>3.3</v>
       </c>
-      <c r="P15">
-        <v>2.17</v>
-      </c>
-      <c r="Q15">
-        <v>3.1</v>
-      </c>
-      <c r="R15">
-        <v>2.23</v>
-      </c>
-      <c r="S15">
-        <v>1.3</v>
-      </c>
-      <c r="T15">
-        <v>3.3</v>
-      </c>
-      <c r="U15">
-        <v>2.5</v>
-      </c>
-      <c r="V15">
-        <v>1.45</v>
-      </c>
-      <c r="W15">
-        <v>1.12</v>
-      </c>
-      <c r="X15">
+      <c r="AD15">
+        <v>1.18</v>
+      </c>
+      <c r="AE15">
         <v>1.03</v>
       </c>
-      <c r="Y15">
-        <v>1.21</v>
-      </c>
-      <c r="Z15">
-        <v>4.23</v>
-      </c>
-      <c r="AA15">
-        <v>1.67</v>
-      </c>
-      <c r="AB15">
-        <v>2.1</v>
-      </c>
-      <c r="AC15">
-        <v>2.66</v>
-      </c>
-      <c r="AD15">
-        <v>1.37</v>
-      </c>
-      <c r="AE15">
-        <v>1.11</v>
-      </c>
       <c r="AF15">
-        <v>1.57</v>
+        <v>1.93</v>
       </c>
       <c r="AG15">
-        <v>2.25</v>
+        <v>1.8</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2824,10 +2824,10 @@
         </is>
       </c>
       <c r="AJ15">
-        <v>1.51</v>
+        <v>1.24</v>
       </c>
       <c r="AK15">
-        <v>1.36</v>
+        <v>1.72</v>
       </c>
       <c r="AL15">
         <v>0</v>
@@ -2885,12 +2885,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Gimpo Citizen</t>
+          <t>Ansan Greeners</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Gyeongnam</t>
+          <t>Gimhae City</t>
         </is>
       </c>
       <c r="G16">
@@ -2917,64 +2917,64 @@
         </is>
       </c>
       <c r="N16">
-        <v>1.94</v>
+        <v>2.65</v>
       </c>
       <c r="O16">
-        <v>2.98</v>
+        <v>3.25</v>
       </c>
       <c r="P16">
-        <v>3.5</v>
+        <v>2.15</v>
       </c>
       <c r="Q16">
-        <v>2.62</v>
+        <v>3.4</v>
       </c>
       <c r="R16">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="S16">
+        <v>1.35</v>
+      </c>
+      <c r="T16">
+        <v>2.82</v>
+      </c>
+      <c r="U16">
+        <v>2.84</v>
+      </c>
+      <c r="V16">
         <v>1.4</v>
       </c>
-      <c r="T16">
-        <v>2.5</v>
-      </c>
-      <c r="U16">
-        <v>3.12</v>
-      </c>
-      <c r="V16">
+      <c r="W16">
+        <v>1.08</v>
+      </c>
+      <c r="X16">
+        <v>1.04</v>
+      </c>
+      <c r="Y16">
         <v>1.29</v>
       </c>
-      <c r="W16">
-        <v>1.02</v>
-      </c>
-      <c r="X16">
-        <v>1.06</v>
-      </c>
-      <c r="Y16">
-        <v>1.39</v>
-      </c>
       <c r="Z16">
-        <v>2.9</v>
+        <v>3.28</v>
       </c>
       <c r="AA16">
-        <v>2.28</v>
+        <v>1.87</v>
       </c>
       <c r="AB16">
-        <v>1.62</v>
+        <v>1.87</v>
       </c>
       <c r="AC16">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="AD16">
-        <v>1.18</v>
+        <v>1.27</v>
       </c>
       <c r="AE16">
-        <v>1.03</v>
+        <v>1.11</v>
       </c>
       <c r="AF16">
-        <v>1.93</v>
+        <v>1.67</v>
       </c>
       <c r="AG16">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -2987,10 +2987,10 @@
         </is>
       </c>
       <c r="AJ16">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="AK16">
-        <v>1.72</v>
+        <v>1.35</v>
       </c>
       <c r="AL16">
         <v>0</v>
@@ -3048,12 +3048,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Ansan Greeners</t>
+          <t>Busan I'Park</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Gimhae City</t>
+          <t>Seoul E-Land</t>
         </is>
       </c>
       <c r="G17">
@@ -3080,64 +3080,64 @@
         </is>
       </c>
       <c r="N17">
-        <v>2.65</v>
+        <v>2.42</v>
       </c>
       <c r="O17">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="P17">
-        <v>2.15</v>
+        <v>2.17</v>
       </c>
       <c r="Q17">
-        <v>3.4</v>
+        <v>3.1</v>
       </c>
       <c r="R17">
-        <v>2.2</v>
+        <v>2.23</v>
       </c>
       <c r="S17">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="T17">
-        <v>2.82</v>
+        <v>3.3</v>
       </c>
       <c r="U17">
-        <v>2.84</v>
+        <v>2.5</v>
       </c>
       <c r="V17">
-        <v>1.4</v>
+        <v>1.45</v>
       </c>
       <c r="W17">
-        <v>1.08</v>
+        <v>1.12</v>
       </c>
       <c r="X17">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y17">
-        <v>1.29</v>
+        <v>1.21</v>
       </c>
       <c r="Z17">
-        <v>3.28</v>
+        <v>4.23</v>
       </c>
       <c r="AA17">
-        <v>1.87</v>
+        <v>1.67</v>
       </c>
       <c r="AB17">
-        <v>1.87</v>
+        <v>2.1</v>
       </c>
       <c r="AC17">
-        <v>3.2</v>
+        <v>2.66</v>
       </c>
       <c r="AD17">
-        <v>1.27</v>
+        <v>1.37</v>
       </c>
       <c r="AE17">
         <v>1.11</v>
       </c>
       <c r="AF17">
-        <v>1.67</v>
+        <v>1.57</v>
       </c>
       <c r="AG17">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3150,10 +3150,10 @@
         </is>
       </c>
       <c r="AJ17">
-        <v>1.25</v>
+        <v>1.51</v>
       </c>
       <c r="AK17">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="AL17">
         <v>0</v>
@@ -5036,7 +5036,7 @@
         </is>
       </c>
       <c r="N29">
-        <v>1.7</v>
+        <v>1.66</v>
       </c>
       <c r="O29">
         <v>3.67</v>
@@ -5371,25 +5371,25 @@
         <v>4.7</v>
       </c>
       <c r="Q31">
-        <v>2.01</v>
+        <v>2.15</v>
       </c>
       <c r="R31">
-        <v>2.15</v>
+        <v>2.17</v>
       </c>
       <c r="S31">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="T31">
-        <v>3.2</v>
+        <v>2.85</v>
       </c>
       <c r="U31">
-        <v>2.83</v>
+        <v>2.73</v>
       </c>
       <c r="V31">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="W31">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="X31">
         <v>1.01</v>
@@ -5398,7 +5398,7 @@
         <v>1.24</v>
       </c>
       <c r="Z31">
-        <v>3.34</v>
+        <v>3.8</v>
       </c>
       <c r="AA31">
         <v>1.92</v>
@@ -5410,16 +5410,16 @@
         <v>3.25</v>
       </c>
       <c r="AD31">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="AE31">
         <v>1.11</v>
       </c>
       <c r="AF31">
-        <v>1.87</v>
+        <v>1.9</v>
       </c>
       <c r="AG31">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="AH31" t="inlineStr">
         <is>
@@ -5432,10 +5432,10 @@
         </is>
       </c>
       <c r="AJ31">
-        <v>1.18</v>
+        <v>1.21</v>
       </c>
       <c r="AK31">
-        <v>2.3</v>
+        <v>2.27</v>
       </c>
       <c r="AL31">
         <v>0</v>
@@ -6506,7 +6506,7 @@
         <v>8.699999999999999</v>
       </c>
       <c r="O38">
-        <v>5.25</v>
+        <v>4.4</v>
       </c>
       <c r="P38">
         <v>1.31</v>
@@ -6527,7 +6527,7 @@
         <v>2.51</v>
       </c>
       <c r="V38">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="W38">
         <v>1.09</v>
@@ -6666,19 +6666,19 @@
         </is>
       </c>
       <c r="N39">
-        <v>2.18</v>
+        <v>2.22</v>
       </c>
       <c r="O39">
         <v>3.5</v>
       </c>
       <c r="P39">
-        <v>3.1</v>
+        <v>2.83</v>
       </c>
       <c r="Q39">
-        <v>2.75</v>
+        <v>2.8</v>
       </c>
       <c r="R39">
-        <v>2.28</v>
+        <v>2.11</v>
       </c>
       <c r="S39">
         <v>1.37</v>
@@ -6687,10 +6687,10 @@
         <v>2.85</v>
       </c>
       <c r="U39">
-        <v>2.75</v>
+        <v>2.55</v>
       </c>
       <c r="V39">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="W39">
         <v>1.05</v>
@@ -6699,31 +6699,31 @@
         <v>1.02</v>
       </c>
       <c r="Y39">
-        <v>1.23</v>
+        <v>1.28</v>
       </c>
       <c r="Z39">
-        <v>3.44</v>
+        <v>3.65</v>
       </c>
       <c r="AA39">
         <v>1.8</v>
       </c>
       <c r="AB39">
-        <v>1.86</v>
+        <v>2</v>
       </c>
       <c r="AC39">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="AD39">
         <v>1.36</v>
       </c>
       <c r="AE39">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="AF39">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
       <c r="AG39">
-        <v>2.1</v>
+        <v>2.09</v>
       </c>
       <c r="AH39" t="inlineStr">
         <is>
@@ -6829,16 +6829,16 @@
         </is>
       </c>
       <c r="N40">
-        <v>3.7</v>
+        <v>4.09</v>
       </c>
       <c r="O40">
-        <v>3.3</v>
+        <v>3.48</v>
       </c>
       <c r="P40">
-        <v>1.82</v>
+        <v>1.87</v>
       </c>
       <c r="Q40">
-        <v>4.55</v>
+        <v>3.95</v>
       </c>
       <c r="R40">
         <v>2.2</v>
@@ -6847,13 +6847,13 @@
         <v>1.36</v>
       </c>
       <c r="T40">
-        <v>2.77</v>
+        <v>2.74</v>
       </c>
       <c r="U40">
-        <v>2.77</v>
+        <v>2.65</v>
       </c>
       <c r="V40">
-        <v>1.36</v>
+        <v>1.42</v>
       </c>
       <c r="W40">
         <v>1.04</v>
@@ -6868,22 +6868,22 @@
         <v>3.34</v>
       </c>
       <c r="AA40">
-        <v>1.9</v>
+        <v>1.95</v>
       </c>
       <c r="AB40">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="AC40">
-        <v>3.14</v>
+        <v>3.2</v>
       </c>
       <c r="AD40">
-        <v>1.27</v>
+        <v>1.33</v>
       </c>
       <c r="AE40">
         <v>1.1</v>
       </c>
       <c r="AF40">
-        <v>1.75</v>
+        <v>1.64</v>
       </c>
       <c r="AG40">
         <v>1.95</v>
@@ -6998,25 +6998,25 @@
         <v>3.1</v>
       </c>
       <c r="P41">
-        <v>2.2</v>
+        <v>2.26</v>
       </c>
       <c r="Q41">
-        <v>3.75</v>
+        <v>3.6</v>
       </c>
       <c r="R41">
-        <v>2.04</v>
+        <v>2.1</v>
       </c>
       <c r="S41">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="T41">
-        <v>2.45</v>
+        <v>2.56</v>
       </c>
       <c r="U41">
-        <v>3</v>
+        <v>2.96</v>
       </c>
       <c r="V41">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="W41">
         <v>1.03</v>
@@ -7025,13 +7025,13 @@
         <v>1.02</v>
       </c>
       <c r="Y41">
-        <v>1.36</v>
+        <v>1.32</v>
       </c>
       <c r="Z41">
-        <v>2.8</v>
+        <v>2.88</v>
       </c>
       <c r="AA41">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="AB41">
         <v>1.73</v>
@@ -7043,13 +7043,13 @@
         <v>1.22</v>
       </c>
       <c r="AE41">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="AF41">
         <v>1.81</v>
       </c>
       <c r="AG41">
-        <v>1.78</v>
+        <v>1.85</v>
       </c>
       <c r="AH41" t="inlineStr">
         <is>
@@ -7065,7 +7065,7 @@
         <v>1.45</v>
       </c>
       <c r="AK41">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="AL41">
         <v>0</v>
@@ -11725,7 +11725,7 @@
         <v>3.9</v>
       </c>
       <c r="P70">
-        <v>6.83</v>
+        <v>5.58</v>
       </c>
       <c r="Q70">
         <v>2.1</v>
@@ -11734,10 +11734,10 @@
         <v>2.1</v>
       </c>
       <c r="S70">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="T70">
-        <v>2.91</v>
+        <v>3.2</v>
       </c>
       <c r="U70">
         <v>2.9</v>
@@ -11752,31 +11752,31 @@
         <v>1.03</v>
       </c>
       <c r="Y70">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="Z70">
         <v>3.6</v>
       </c>
       <c r="AA70">
-        <v>1.8</v>
+        <v>2.11</v>
       </c>
       <c r="AB70">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="AC70">
-        <v>3</v>
+        <v>3.5</v>
       </c>
       <c r="AD70">
         <v>1.41</v>
       </c>
       <c r="AE70">
-        <v>1.15</v>
+        <v>1.09</v>
       </c>
       <c r="AF70">
         <v>1.8</v>
       </c>
       <c r="AG70">
-        <v>1.91</v>
+        <v>1.83</v>
       </c>
       <c r="AH70" t="inlineStr">
         <is>
@@ -11789,10 +11789,10 @@
         </is>
       </c>
       <c r="AJ70">
-        <v>1.12</v>
+        <v>1.2</v>
       </c>
       <c r="AK70">
-        <v>2.02</v>
+        <v>2.29</v>
       </c>
       <c r="AL70">
         <v>0</v>
@@ -11882,19 +11882,19 @@
         </is>
       </c>
       <c r="N71">
-        <v>1.28</v>
+        <v>1.31</v>
       </c>
       <c r="O71">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="P71">
         <v>7.9</v>
       </c>
       <c r="Q71">
-        <v>1.8</v>
+        <v>1.77</v>
       </c>
       <c r="R71">
-        <v>2.46</v>
+        <v>2.47</v>
       </c>
       <c r="S71">
         <v>1.35</v>
@@ -11903,10 +11903,10 @@
         <v>3.08</v>
       </c>
       <c r="U71">
-        <v>2.68</v>
+        <v>2.66</v>
       </c>
       <c r="V71">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="W71">
         <v>1.08</v>
@@ -11921,16 +11921,16 @@
         <v>3.65</v>
       </c>
       <c r="AA71">
-        <v>1.86</v>
+        <v>1.82</v>
       </c>
       <c r="AB71">
-        <v>1.98</v>
+        <v>2.03</v>
       </c>
       <c r="AC71">
-        <v>3.09</v>
+        <v>2.9</v>
       </c>
       <c r="AD71">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="AE71">
         <v>1.1</v>
@@ -11952,7 +11952,7 @@
         </is>
       </c>
       <c r="AJ71">
-        <v>1.07</v>
+        <v>1.18</v>
       </c>
       <c r="AK71">
         <v>3.08</v>
@@ -12045,19 +12045,19 @@
         </is>
       </c>
       <c r="N72">
-        <v>2.37</v>
+        <v>2.4</v>
       </c>
       <c r="O72">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="P72">
-        <v>2.47</v>
+        <v>2.5</v>
       </c>
       <c r="Q72">
-        <v>3.1</v>
+        <v>3.02</v>
       </c>
       <c r="R72">
-        <v>2.25</v>
+        <v>2.1</v>
       </c>
       <c r="S72">
         <v>1.3</v>
@@ -12066,16 +12066,16 @@
         <v>3.2</v>
       </c>
       <c r="U72">
-        <v>2.54</v>
+        <v>2.5</v>
       </c>
       <c r="V72">
-        <v>1.49</v>
+        <v>1.44</v>
       </c>
       <c r="W72">
         <v>1.07</v>
       </c>
       <c r="X72">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="Y72">
         <v>1.19</v>
@@ -12090,13 +12090,13 @@
         <v>2</v>
       </c>
       <c r="AC72">
-        <v>2.7</v>
+        <v>2.75</v>
       </c>
       <c r="AD72">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="AE72">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="AF72">
         <v>1.56</v>
@@ -12118,7 +12118,7 @@
         <v>1.4</v>
       </c>
       <c r="AK72">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="AL72">
         <v>0</v>
@@ -12706,55 +12706,55 @@
         <v>2.37</v>
       </c>
       <c r="Q76">
-        <v>3.54</v>
+        <v>3.35</v>
       </c>
       <c r="R76">
         <v>2.04</v>
       </c>
       <c r="S76">
-        <v>1.39</v>
+        <v>1.41</v>
       </c>
       <c r="T76">
-        <v>2.73</v>
+        <v>2.75</v>
       </c>
       <c r="U76">
         <v>2.9</v>
       </c>
       <c r="V76">
-        <v>1.34</v>
+        <v>1.4</v>
       </c>
       <c r="W76">
-        <v>1.08</v>
+        <v>1.04</v>
       </c>
       <c r="X76">
         <v>1.03</v>
       </c>
       <c r="Y76">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="Z76">
-        <v>3.2</v>
+        <v>3.46</v>
       </c>
       <c r="AA76">
-        <v>2.04</v>
+        <v>1.98</v>
       </c>
       <c r="AB76">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="AC76">
         <v>3.6</v>
       </c>
       <c r="AD76">
-        <v>1.23</v>
+        <v>1.31</v>
       </c>
       <c r="AE76">
-        <v>1.07</v>
+        <v>1.11</v>
       </c>
       <c r="AF76">
         <v>1.72</v>
       </c>
       <c r="AG76">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="AH76" t="inlineStr">
         <is>
@@ -12767,7 +12767,7 @@
         </is>
       </c>
       <c r="AJ76">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="AK76">
         <v>1.4</v>
@@ -12860,10 +12860,10 @@
         </is>
       </c>
       <c r="N77">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="O77">
-        <v>3.5</v>
+        <v>3.36</v>
       </c>
       <c r="P77">
         <v>2.73</v>
@@ -12878,7 +12878,7 @@
         <v>1.33</v>
       </c>
       <c r="T77">
-        <v>2.89</v>
+        <v>3.05</v>
       </c>
       <c r="U77">
         <v>2.62</v>
@@ -12893,25 +12893,25 @@
         <v>1.01</v>
       </c>
       <c r="Y77">
-        <v>1.25</v>
+        <v>1.21</v>
       </c>
       <c r="Z77">
-        <v>3.62</v>
+        <v>3.6</v>
       </c>
       <c r="AA77">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="AB77">
         <v>2</v>
       </c>
       <c r="AC77">
-        <v>2.85</v>
+        <v>3.1</v>
       </c>
       <c r="AD77">
         <v>1.33</v>
       </c>
       <c r="AE77">
-        <v>1.14</v>
+        <v>1.09</v>
       </c>
       <c r="AF77">
         <v>1.62</v>
@@ -12930,7 +12930,7 @@
         </is>
       </c>
       <c r="AJ77">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="AK77">
         <v>1.61</v>
@@ -13186,13 +13186,13 @@
         </is>
       </c>
       <c r="N79">
-        <v>2.34</v>
+        <v>2.37</v>
       </c>
       <c r="O79">
-        <v>3.14</v>
+        <v>3.2</v>
       </c>
       <c r="P79">
-        <v>2.72</v>
+        <v>2.59</v>
       </c>
       <c r="Q79">
         <v>3.06</v>
@@ -13204,7 +13204,7 @@
         <v>1.4</v>
       </c>
       <c r="T79">
-        <v>2.88</v>
+        <v>2.6</v>
       </c>
       <c r="U79">
         <v>2.92</v>
@@ -13225,10 +13225,10 @@
         <v>2.92</v>
       </c>
       <c r="AA79">
-        <v>2.1</v>
+        <v>2.04</v>
       </c>
       <c r="AB79">
-        <v>1.7</v>
+        <v>1.68</v>
       </c>
       <c r="AC79">
         <v>3.58</v>
@@ -13256,10 +13256,10 @@
         </is>
       </c>
       <c r="AJ79">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="AK79">
-        <v>1.44</v>
+        <v>1.53</v>
       </c>
       <c r="AL79">
         <v>0</v>
@@ -14132,12 +14132,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Tallinna FC Flora</t>
+          <t>Vaprus</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Harju Jalgpallikool</t>
+          <t>Tallinna FC Levadia</t>
         </is>
       </c>
       <c r="G85">
@@ -14164,64 +14164,64 @@
         </is>
       </c>
       <c r="N85">
-        <v>1.53</v>
+        <v>11.7</v>
       </c>
       <c r="O85">
-        <v>4.55</v>
+        <v>5.75</v>
       </c>
       <c r="P85">
-        <v>4.8</v>
+        <v>1.24</v>
       </c>
       <c r="Q85">
-        <v>1.93</v>
+        <v>7.61</v>
       </c>
       <c r="R85">
-        <v>2.65</v>
+        <v>2.82</v>
       </c>
       <c r="S85">
-        <v>1.23</v>
+        <v>1.2</v>
       </c>
       <c r="T85">
-        <v>3.42</v>
+        <v>3.8</v>
       </c>
       <c r="U85">
-        <v>2.18</v>
+        <v>2.17</v>
       </c>
       <c r="V85">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="W85">
-        <v>1.12</v>
+        <v>1.17</v>
       </c>
       <c r="X85">
         <v>1.02</v>
       </c>
       <c r="Y85">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="Z85">
-        <v>4.95</v>
+        <v>5.15</v>
       </c>
       <c r="AA85">
-        <v>1.49</v>
+        <v>1.42</v>
       </c>
       <c r="AB85">
-        <v>2.51</v>
+        <v>2.49</v>
       </c>
       <c r="AC85">
-        <v>2.24</v>
+        <v>2.14</v>
       </c>
       <c r="AD85">
         <v>1.63</v>
       </c>
       <c r="AE85">
-        <v>1.21</v>
+        <v>1.24</v>
       </c>
       <c r="AF85">
-        <v>1.53</v>
+        <v>1.8</v>
       </c>
       <c r="AG85">
-        <v>2.3</v>
+        <v>1.88</v>
       </c>
       <c r="AH85" t="inlineStr">
         <is>
@@ -14234,10 +14234,10 @@
         </is>
       </c>
       <c r="AJ85">
-        <v>1.22</v>
+        <v>1.11</v>
       </c>
       <c r="AK85">
-        <v>2.25</v>
+        <v>1.03</v>
       </c>
       <c r="AL85">
         <v>0</v>
@@ -14295,12 +14295,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Vaprus</t>
+          <t>Tallinna FC Flora</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Tallinna FC Levadia</t>
+          <t>Harju Jalgpallikool</t>
         </is>
       </c>
       <c r="G86">
@@ -14327,64 +14327,64 @@
         </is>
       </c>
       <c r="N86">
-        <v>11.7</v>
+        <v>1.53</v>
       </c>
       <c r="O86">
-        <v>5.75</v>
+        <v>4.55</v>
       </c>
       <c r="P86">
-        <v>1.24</v>
+        <v>4.8</v>
       </c>
       <c r="Q86">
-        <v>7.61</v>
+        <v>1.93</v>
       </c>
       <c r="R86">
-        <v>2.82</v>
+        <v>2.65</v>
       </c>
       <c r="S86">
-        <v>1.2</v>
+        <v>1.23</v>
       </c>
       <c r="T86">
-        <v>3.8</v>
+        <v>3.42</v>
       </c>
       <c r="U86">
-        <v>2.17</v>
+        <v>2.18</v>
       </c>
       <c r="V86">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="W86">
-        <v>1.17</v>
+        <v>1.12</v>
       </c>
       <c r="X86">
         <v>1.02</v>
       </c>
       <c r="Y86">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="Z86">
-        <v>5.15</v>
+        <v>4.95</v>
       </c>
       <c r="AA86">
-        <v>1.42</v>
+        <v>1.49</v>
       </c>
       <c r="AB86">
-        <v>2.49</v>
+        <v>2.51</v>
       </c>
       <c r="AC86">
-        <v>2.14</v>
+        <v>2.24</v>
       </c>
       <c r="AD86">
         <v>1.63</v>
       </c>
       <c r="AE86">
-        <v>1.24</v>
+        <v>1.21</v>
       </c>
       <c r="AF86">
-        <v>1.8</v>
+        <v>1.53</v>
       </c>
       <c r="AG86">
-        <v>1.88</v>
+        <v>2.3</v>
       </c>
       <c r="AH86" t="inlineStr">
         <is>
@@ -14397,10 +14397,10 @@
         </is>
       </c>
       <c r="AJ86">
-        <v>1.11</v>
+        <v>1.22</v>
       </c>
       <c r="AK86">
-        <v>1.03</v>
+        <v>2.25</v>
       </c>
       <c r="AL86">
         <v>0</v>
@@ -14979,25 +14979,25 @@
         </is>
       </c>
       <c r="N90">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="O90">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="P90">
         <v>2.7</v>
       </c>
       <c r="Q90">
-        <v>2.76</v>
+        <v>2.6</v>
       </c>
       <c r="R90">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="S90">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="T90">
-        <v>3.25</v>
+        <v>3.5</v>
       </c>
       <c r="U90">
         <v>2.25</v>
@@ -15012,10 +15012,10 @@
         <v>1.01</v>
       </c>
       <c r="Y90">
-        <v>1.12</v>
+        <v>1.17</v>
       </c>
       <c r="Z90">
-        <v>4.7</v>
+        <v>3.5</v>
       </c>
       <c r="AA90">
         <v>1.57</v>
@@ -15024,19 +15024,19 @@
         <v>2.35</v>
       </c>
       <c r="AC90">
-        <v>2.37</v>
+        <v>2.3</v>
       </c>
       <c r="AD90">
-        <v>1.53</v>
+        <v>1.49</v>
       </c>
       <c r="AE90">
         <v>1.16</v>
       </c>
       <c r="AF90">
-        <v>1.46</v>
+        <v>1.63</v>
       </c>
       <c r="AG90">
-        <v>2.5</v>
+        <v>2.1</v>
       </c>
       <c r="AH90" t="inlineStr">
         <is>
@@ -15142,13 +15142,13 @@
         </is>
       </c>
       <c r="N91">
-        <v>3.25</v>
+        <v>3.08</v>
       </c>
       <c r="O91">
         <v>3.3</v>
       </c>
       <c r="P91">
-        <v>1.95</v>
+        <v>1.98</v>
       </c>
       <c r="Q91">
         <v>3.93</v>
@@ -15163,34 +15163,34 @@
         <v>3.09</v>
       </c>
       <c r="U91">
-        <v>2.55</v>
+        <v>2.6</v>
       </c>
       <c r="V91">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="W91">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="X91">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y91">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="Z91">
-        <v>3.5</v>
+        <v>3.8</v>
       </c>
       <c r="AA91">
-        <v>1.88</v>
+        <v>1.81</v>
       </c>
       <c r="AB91">
-        <v>1.95</v>
+        <v>1.9</v>
       </c>
       <c r="AC91">
-        <v>2.97</v>
+        <v>3.1</v>
       </c>
       <c r="AD91">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="AE91">
         <v>1.09</v>
@@ -15212,10 +15212,10 @@
         </is>
       </c>
       <c r="AJ91">
-        <v>1.73</v>
+        <v>1.2</v>
       </c>
       <c r="AK91">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="AL91">
         <v>0</v>
@@ -16120,13 +16120,13 @@
         </is>
       </c>
       <c r="N97">
-        <v>2.29</v>
+        <v>2.3</v>
       </c>
       <c r="O97">
-        <v>3.44</v>
+        <v>3.42</v>
       </c>
       <c r="P97">
-        <v>2.6</v>
+        <v>2.59</v>
       </c>
       <c r="Q97">
         <v>0</v>
@@ -16609,25 +16609,25 @@
         </is>
       </c>
       <c r="N100">
-        <v>3.7</v>
+        <v>4</v>
       </c>
       <c r="O100">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="P100">
-        <v>1.88</v>
+        <v>1.93</v>
       </c>
       <c r="Q100">
-        <v>4.33</v>
+        <v>4.37</v>
       </c>
       <c r="R100">
-        <v>2.19</v>
+        <v>2.08</v>
       </c>
       <c r="S100">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="T100">
-        <v>2.93</v>
+        <v>3.03</v>
       </c>
       <c r="U100">
         <v>2.77</v>
@@ -16642,7 +16642,7 @@
         <v>1.01</v>
       </c>
       <c r="Y100">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="Z100">
         <v>3.42</v>
@@ -16654,7 +16654,7 @@
         <v>1.93</v>
       </c>
       <c r="AC100">
-        <v>3.1</v>
+        <v>3.24</v>
       </c>
       <c r="AD100">
         <v>1.32</v>
@@ -16663,10 +16663,10 @@
         <v>1.08</v>
       </c>
       <c r="AF100">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="AG100">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="AH100" t="inlineStr">
         <is>
@@ -16679,10 +16679,10 @@
         </is>
       </c>
       <c r="AJ100">
-        <v>1.22</v>
+        <v>1.32</v>
       </c>
       <c r="AK100">
-        <v>1.29</v>
+        <v>1.18</v>
       </c>
       <c r="AL100">
         <v>0</v>
@@ -18085,10 +18085,10 @@
         <v>7.5</v>
       </c>
       <c r="Q109">
-        <v>1.72</v>
+        <v>1.75</v>
       </c>
       <c r="R109">
-        <v>2.63</v>
+        <v>2.4</v>
       </c>
       <c r="S109">
         <v>1.3</v>
@@ -18097,43 +18097,43 @@
         <v>3.2</v>
       </c>
       <c r="U109">
-        <v>2.5</v>
+        <v>2.47</v>
       </c>
       <c r="V109">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="W109">
         <v>1.11</v>
       </c>
       <c r="X109">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y109">
         <v>1.22</v>
       </c>
       <c r="Z109">
-        <v>4</v>
+        <v>3.98</v>
       </c>
       <c r="AA109">
-        <v>1.63</v>
+        <v>1.68</v>
       </c>
       <c r="AB109">
-        <v>2.04</v>
+        <v>2.08</v>
       </c>
       <c r="AC109">
-        <v>2.76</v>
+        <v>2.66</v>
       </c>
       <c r="AD109">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="AE109">
-        <v>1.15</v>
+        <v>1.12</v>
       </c>
       <c r="AF109">
-        <v>1.98</v>
+        <v>2.09</v>
       </c>
       <c r="AG109">
-        <v>1.7</v>
+        <v>1.65</v>
       </c>
       <c r="AH109" t="inlineStr">
         <is>
@@ -18146,7 +18146,7 @@
         </is>
       </c>
       <c r="AJ109">
-        <v>1.17</v>
+        <v>1.13</v>
       </c>
       <c r="AK109">
         <v>3</v>
@@ -18239,64 +18239,64 @@
         </is>
       </c>
       <c r="N110">
-        <v>4.6</v>
+        <v>4.24</v>
       </c>
       <c r="O110">
-        <v>3.08</v>
+        <v>3</v>
       </c>
       <c r="P110">
-        <v>1.79</v>
+        <v>1.75</v>
       </c>
       <c r="Q110">
-        <v>0</v>
+        <v>5.77</v>
       </c>
       <c r="R110">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="S110">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="T110">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="U110">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="V110">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="W110">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X110">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="Y110">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="Z110">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AA110">
-        <v>2.35</v>
+        <v>2.37</v>
       </c>
       <c r="AB110">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="AC110">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="AD110">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AE110">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AF110">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AG110">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AH110" t="inlineStr">
         <is>
@@ -18309,10 +18309,10 @@
         </is>
       </c>
       <c r="AJ110">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AK110">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AL110">
         <v>0</v>
@@ -18402,7 +18402,7 @@
         </is>
       </c>
       <c r="N111">
-        <v>1.61</v>
+        <v>1.54</v>
       </c>
       <c r="O111">
         <v>3.5</v>
@@ -18411,55 +18411,55 @@
         <v>5.5</v>
       </c>
       <c r="Q111">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="R111">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="S111">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="T111">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="U111">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="V111">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="W111">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X111">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y111">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="Z111">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AA111">
-        <v>2.35</v>
+        <v>2.1</v>
       </c>
       <c r="AB111">
-        <v>1.57</v>
+        <v>1.7</v>
       </c>
       <c r="AC111">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="AD111">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AE111">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AF111">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AG111">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AH111" t="inlineStr">
         <is>
@@ -18472,10 +18472,10 @@
         </is>
       </c>
       <c r="AJ111">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK111">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="AL111">
         <v>0</v>
@@ -18565,43 +18565,43 @@
         </is>
       </c>
       <c r="N112">
-        <v>2.09</v>
+        <v>2</v>
       </c>
       <c r="O112">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="P112">
-        <v>3.21</v>
+        <v>3.15</v>
       </c>
       <c r="Q112">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="R112">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="S112">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="T112">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="U112">
-        <v>0</v>
+        <v>2.79</v>
       </c>
       <c r="V112">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="W112">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X112">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y112">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z112">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="AA112">
         <v>1.95</v>
@@ -18610,19 +18610,19 @@
         <v>1.85</v>
       </c>
       <c r="AC112">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AD112">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AE112">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AF112">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AG112">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AH112" t="inlineStr">
         <is>
@@ -18635,10 +18635,10 @@
         </is>
       </c>
       <c r="AJ112">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK112">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AL112">
         <v>0</v>
@@ -19054,16 +19054,16 @@
         </is>
       </c>
       <c r="N115">
-        <v>1.93</v>
+        <v>1.85</v>
       </c>
       <c r="O115">
         <v>3.52</v>
       </c>
       <c r="P115">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="Q115">
-        <v>2.44</v>
+        <v>2.42</v>
       </c>
       <c r="R115">
         <v>2.14</v>
@@ -19075,7 +19075,7 @@
         <v>2.9</v>
       </c>
       <c r="U115">
-        <v>2.56</v>
+        <v>2.6</v>
       </c>
       <c r="V115">
         <v>1.44</v>
@@ -19090,13 +19090,13 @@
         <v>1.24</v>
       </c>
       <c r="Z115">
-        <v>3.75</v>
+        <v>4.1</v>
       </c>
       <c r="AA115">
-        <v>1.8</v>
+        <v>1.78</v>
       </c>
       <c r="AB115">
-        <v>2</v>
+        <v>1.89</v>
       </c>
       <c r="AC115">
         <v>3</v>
@@ -19108,10 +19108,10 @@
         <v>1.1</v>
       </c>
       <c r="AF115">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="AG115">
-        <v>2.09</v>
+        <v>2.1</v>
       </c>
       <c r="AH115" t="inlineStr">
         <is>
@@ -20032,10 +20032,10 @@
         </is>
       </c>
       <c r="N121">
-        <v>2.25</v>
+        <v>2.22</v>
       </c>
       <c r="O121">
-        <v>3.05</v>
+        <v>3.15</v>
       </c>
       <c r="P121">
         <v>2.89</v>
@@ -20044,52 +20044,52 @@
         <v>2.9</v>
       </c>
       <c r="R121">
-        <v>1.96</v>
+        <v>2</v>
       </c>
       <c r="S121">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="T121">
-        <v>2.33</v>
+        <v>2.63</v>
       </c>
       <c r="U121">
-        <v>3.2</v>
+        <v>3.09</v>
       </c>
       <c r="V121">
-        <v>1.35</v>
+        <v>1.32</v>
       </c>
       <c r="W121">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="X121">
         <v>1.03</v>
       </c>
       <c r="Y121">
-        <v>1.35</v>
+        <v>1.38</v>
       </c>
       <c r="Z121">
-        <v>2.74</v>
+        <v>2.85</v>
       </c>
       <c r="AA121">
-        <v>2.16</v>
+        <v>2.15</v>
       </c>
       <c r="AB121">
         <v>1.62</v>
       </c>
       <c r="AC121">
-        <v>3.82</v>
+        <v>3.9</v>
       </c>
       <c r="AD121">
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
       <c r="AE121">
         <v>1.03</v>
       </c>
       <c r="AF121">
-        <v>1.86</v>
+        <v>2</v>
       </c>
       <c r="AG121">
-        <v>1.68</v>
+        <v>1.73</v>
       </c>
       <c r="AH121" t="inlineStr">
         <is>
@@ -20102,10 +20102,10 @@
         </is>
       </c>
       <c r="AJ121">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="AK121">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="AL121">
         <v>0</v>
@@ -20201,7 +20201,7 @@
         <v>3.45</v>
       </c>
       <c r="P122">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="Q122">
         <v>2.95</v>
@@ -20210,40 +20210,40 @@
         <v>2.25</v>
       </c>
       <c r="S122">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="T122">
         <v>3.2</v>
       </c>
       <c r="U122">
-        <v>2.65</v>
+        <v>2.63</v>
       </c>
       <c r="V122">
         <v>1.48</v>
       </c>
       <c r="W122">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="X122">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y122">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="Z122">
-        <v>3.7</v>
+        <v>4.1</v>
       </c>
       <c r="AA122">
         <v>1.8</v>
       </c>
       <c r="AB122">
-        <v>1.98</v>
+        <v>1.9</v>
       </c>
       <c r="AC122">
-        <v>2.95</v>
+        <v>2.8</v>
       </c>
       <c r="AD122">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="AE122">
         <v>1.11</v>
@@ -20252,7 +20252,7 @@
         <v>1.6</v>
       </c>
       <c r="AG122">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="AH122" t="inlineStr">
         <is>
@@ -20265,7 +20265,7 @@
         </is>
       </c>
       <c r="AJ122">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="AK122">
         <v>1.45</v>
@@ -20358,13 +20358,13 @@
         </is>
       </c>
       <c r="N123">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="O123">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="P123">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="Q123">
         <v>0</v>
@@ -21182,25 +21182,25 @@
         <v>2.3</v>
       </c>
       <c r="Q128">
-        <v>2.9</v>
+        <v>3.25</v>
       </c>
       <c r="R128">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="S128">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="T128">
-        <v>2.75</v>
+        <v>2.23</v>
       </c>
       <c r="U128">
-        <v>2.29</v>
+        <v>2.62</v>
       </c>
       <c r="V128">
-        <v>1.31</v>
+        <v>1.42</v>
       </c>
       <c r="W128">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="X128">
         <v>1.02</v>
@@ -21209,28 +21209,28 @@
         <v>1.28</v>
       </c>
       <c r="Z128">
-        <v>3.08</v>
+        <v>3.35</v>
       </c>
       <c r="AA128">
-        <v>1.94</v>
+        <v>1.93</v>
       </c>
       <c r="AB128">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="AC128">
-        <v>3.34</v>
+        <v>3.35</v>
       </c>
       <c r="AD128">
-        <v>1.24</v>
+        <v>1.28</v>
       </c>
       <c r="AE128">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="AF128">
-        <v>1.75</v>
+        <v>1.7</v>
       </c>
       <c r="AG128">
-        <v>1.78</v>
+        <v>1.95</v>
       </c>
       <c r="AH128" t="inlineStr">
         <is>
@@ -21243,10 +21243,10 @@
         </is>
       </c>
       <c r="AJ128">
-        <v>1.1</v>
+        <v>1.45</v>
       </c>
       <c r="AK128">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="AL128">
         <v>0</v>
@@ -21336,10 +21336,10 @@
         </is>
       </c>
       <c r="N129">
-        <v>1.55</v>
+        <v>1.49</v>
       </c>
       <c r="O129">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="P129">
         <v>5.25</v>
@@ -21351,19 +21351,19 @@
         <v>2.08</v>
       </c>
       <c r="S129">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="T129">
         <v>2.75</v>
       </c>
       <c r="U129">
-        <v>3.25</v>
+        <v>2.9</v>
       </c>
       <c r="V129">
-        <v>1.32</v>
+        <v>1.36</v>
       </c>
       <c r="W129">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="X129">
         <v>1.03</v>
@@ -21372,22 +21372,22 @@
         <v>1.42</v>
       </c>
       <c r="Z129">
-        <v>2.77</v>
+        <v>2.8</v>
       </c>
       <c r="AA129">
-        <v>2.1</v>
+        <v>2.25</v>
       </c>
       <c r="AB129">
         <v>1.65</v>
       </c>
       <c r="AC129">
-        <v>3.84</v>
+        <v>3.95</v>
       </c>
       <c r="AD129">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="AE129">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="AF129">
         <v>2.19</v>
@@ -21406,7 +21406,7 @@
         </is>
       </c>
       <c r="AJ129">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="AK129">
         <v>2.38</v>
@@ -21499,10 +21499,10 @@
         </is>
       </c>
       <c r="N130">
-        <v>1.87</v>
+        <v>1.89</v>
       </c>
       <c r="O130">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="P130">
         <v>3.45</v>
@@ -21671,28 +21671,28 @@
         <v>2.35</v>
       </c>
       <c r="Q131">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="R131">
-        <v>2.2</v>
+        <v>2.21</v>
       </c>
       <c r="S131">
-        <v>1.28</v>
+        <v>1.32</v>
       </c>
       <c r="T131">
-        <v>3.15</v>
+        <v>3.11</v>
       </c>
       <c r="U131">
         <v>2.53</v>
       </c>
       <c r="V131">
-        <v>1.43</v>
+        <v>1.47</v>
       </c>
       <c r="W131">
         <v>1.09</v>
       </c>
       <c r="X131">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y131">
         <v>1.26</v>
@@ -21701,16 +21701,16 @@
         <v>3.25</v>
       </c>
       <c r="AA131">
-        <v>1.72</v>
+        <v>1.84</v>
       </c>
       <c r="AB131">
-        <v>2.07</v>
+        <v>1.79</v>
       </c>
       <c r="AC131">
-        <v>2.78</v>
+        <v>3.1</v>
       </c>
       <c r="AD131">
-        <v>1.34</v>
+        <v>1.29</v>
       </c>
       <c r="AE131">
         <v>1.09</v>
@@ -21732,10 +21732,10 @@
         </is>
       </c>
       <c r="AJ131">
-        <v>1.24</v>
+        <v>1.5</v>
       </c>
       <c r="AK131">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="AL131">
         <v>0</v>
@@ -21825,19 +21825,19 @@
         </is>
       </c>
       <c r="N132">
-        <v>1.6</v>
+        <v>1.63</v>
       </c>
       <c r="O132">
         <v>3.9</v>
       </c>
       <c r="P132">
-        <v>5</v>
+        <v>4.65</v>
       </c>
       <c r="Q132">
         <v>2.07</v>
       </c>
       <c r="R132">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="S132">
         <v>1.33</v>
@@ -21846,13 +21846,13 @@
         <v>3.16</v>
       </c>
       <c r="U132">
-        <v>2.59</v>
+        <v>2.6</v>
       </c>
       <c r="V132">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="W132">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="X132">
         <v>1.01</v>
@@ -21864,22 +21864,22 @@
         <v>3.5</v>
       </c>
       <c r="AA132">
-        <v>1.87</v>
+        <v>1.8</v>
       </c>
       <c r="AB132">
         <v>1.87</v>
       </c>
       <c r="AC132">
-        <v>3.05</v>
+        <v>2.78</v>
       </c>
       <c r="AD132">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="AE132">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="AF132">
-        <v>1.79</v>
+        <v>1.85</v>
       </c>
       <c r="AG132">
         <v>1.85</v>
@@ -21898,7 +21898,7 @@
         <v>1.15</v>
       </c>
       <c r="AK132">
-        <v>2.06</v>
+        <v>2.2</v>
       </c>
       <c r="AL132">
         <v>0</v>
@@ -22160,7 +22160,7 @@
         <v>3.55</v>
       </c>
       <c r="Q134">
-        <v>2.35</v>
+        <v>2.45</v>
       </c>
       <c r="R134">
         <v>2.25</v>
@@ -22172,13 +22172,13 @@
         <v>3.2</v>
       </c>
       <c r="U134">
-        <v>2.36</v>
+        <v>2.44</v>
       </c>
       <c r="V134">
-        <v>1.48</v>
+        <v>1.52</v>
       </c>
       <c r="W134">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="X134">
         <v>1.03</v>
@@ -22193,7 +22193,7 @@
         <v>1.65</v>
       </c>
       <c r="AB134">
-        <v>2.16</v>
+        <v>2.08</v>
       </c>
       <c r="AC134">
         <v>2.63</v>
@@ -22221,7 +22221,7 @@
         </is>
       </c>
       <c r="AJ134">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="AK134">
         <v>1.79</v>
@@ -22326,10 +22326,10 @@
         <v>3.75</v>
       </c>
       <c r="R135">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="S135">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="T135">
         <v>2.63</v>
@@ -22350,25 +22350,25 @@
         <v>1.49</v>
       </c>
       <c r="Z135">
-        <v>2.62</v>
+        <v>2.52</v>
       </c>
       <c r="AA135">
-        <v>2.3</v>
+        <v>2.34</v>
       </c>
       <c r="AB135">
-        <v>1.58</v>
+        <v>1.56</v>
       </c>
       <c r="AC135">
-        <v>4.19</v>
+        <v>4.29</v>
       </c>
       <c r="AD135">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="AE135">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="AF135">
-        <v>1.91</v>
+        <v>1.98</v>
       </c>
       <c r="AG135">
         <v>1.64</v>
@@ -22477,13 +22477,13 @@
         </is>
       </c>
       <c r="N136">
-        <v>2.26</v>
+        <v>2.05</v>
       </c>
       <c r="O136">
-        <v>3.7</v>
+        <v>3.4</v>
       </c>
       <c r="P136">
-        <v>2.7</v>
+        <v>2.9</v>
       </c>
       <c r="Q136">
         <v>0</v>
@@ -22640,13 +22640,13 @@
         </is>
       </c>
       <c r="N137">
-        <v>1.83</v>
+        <v>1.86</v>
       </c>
       <c r="O137">
-        <v>3.64</v>
+        <v>3.5</v>
       </c>
       <c r="P137">
-        <v>3.56</v>
+        <v>3.25</v>
       </c>
       <c r="Q137">
         <v>0</v>

--- a/jogos_2026-08-02.xlsx
+++ b/jogos_2026-08-02.xlsx
@@ -635,13 +635,13 @@
         </is>
       </c>
       <c r="N2">
-        <v>1.29</v>
+        <v>1.22</v>
       </c>
       <c r="O2">
         <v>4.75</v>
       </c>
       <c r="P2">
-        <v>6.9</v>
+        <v>8.4</v>
       </c>
       <c r="Q2">
         <v>1.69</v>
@@ -798,52 +798,52 @@
         </is>
       </c>
       <c r="N3">
-        <v>1.87</v>
+        <v>1.83</v>
       </c>
       <c r="O3">
-        <v>3.13</v>
+        <v>3.35</v>
       </c>
       <c r="P3">
-        <v>3.52</v>
+        <v>3.72</v>
       </c>
       <c r="Q3">
-        <v>2.47</v>
+        <v>2.43</v>
       </c>
       <c r="R3">
-        <v>2.1</v>
+        <v>2.25</v>
       </c>
       <c r="S3">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="T3">
-        <v>2.83</v>
+        <v>2.75</v>
       </c>
       <c r="U3">
-        <v>2.73</v>
+        <v>2.43</v>
       </c>
       <c r="V3">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="W3">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="X3">
         <v>1.01</v>
       </c>
       <c r="Y3">
-        <v>1.26</v>
+        <v>1.22</v>
       </c>
       <c r="Z3">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="AA3">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="AB3">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="AC3">
-        <v>3.14</v>
+        <v>3.4</v>
       </c>
       <c r="AD3">
         <v>1.27</v>
@@ -852,10 +852,10 @@
         <v>1.07</v>
       </c>
       <c r="AF3">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="AG3">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -868,7 +868,7 @@
         </is>
       </c>
       <c r="AJ3">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="AK3">
         <v>1.83</v>
@@ -961,22 +961,22 @@
         </is>
       </c>
       <c r="N4">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="O4">
-        <v>3.21</v>
+        <v>3.5</v>
       </c>
       <c r="P4">
-        <v>3.24</v>
+        <v>3.4</v>
       </c>
       <c r="Q4">
-        <v>2.3</v>
+        <v>2.5</v>
       </c>
       <c r="R4">
-        <v>2.18</v>
+        <v>2.38</v>
       </c>
       <c r="S4">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="T4">
         <v>3.25</v>
@@ -988,7 +988,7 @@
         <v>1.45</v>
       </c>
       <c r="W4">
-        <v>1.11</v>
+        <v>1.07</v>
       </c>
       <c r="X4">
         <v>1.02</v>
@@ -1003,22 +1003,22 @@
         <v>1.67</v>
       </c>
       <c r="AB4">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="AC4">
         <v>2.62</v>
       </c>
       <c r="AD4">
-        <v>1.41</v>
+        <v>1.45</v>
       </c>
       <c r="AE4">
-        <v>1.11</v>
+        <v>1.17</v>
       </c>
       <c r="AF4">
         <v>1.62</v>
       </c>
       <c r="AG4">
-        <v>2.19</v>
+        <v>2.25</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1124,13 +1124,13 @@
         </is>
       </c>
       <c r="N5">
-        <v>1.71</v>
+        <v>1.75</v>
       </c>
       <c r="O5">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="P5">
-        <v>3.55</v>
+        <v>3.63</v>
       </c>
       <c r="Q5">
         <v>2.2</v>
@@ -1142,7 +1142,7 @@
         <v>1.25</v>
       </c>
       <c r="T5">
-        <v>3.28</v>
+        <v>3.4</v>
       </c>
       <c r="U5">
         <v>2.31</v>
@@ -1160,44 +1160,44 @@
         <v>1.13</v>
       </c>
       <c r="Z5">
-        <v>4.5</v>
+        <v>4.35</v>
       </c>
       <c r="AA5">
-        <v>1.54</v>
+        <v>1.6</v>
       </c>
       <c r="AB5">
         <v>2.19</v>
       </c>
       <c r="AC5">
-        <v>2.44</v>
+        <v>2.5</v>
       </c>
       <c r="AD5">
-        <v>1.48</v>
+        <v>1.53</v>
       </c>
       <c r="AE5">
+        <v>1.22</v>
+      </c>
+      <c r="AF5">
+        <v>1.57</v>
+      </c>
+      <c r="AG5">
+        <v>2.25</v>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ5">
         <v>1.19</v>
       </c>
-      <c r="AF5">
-        <v>1.54</v>
-      </c>
-      <c r="AG5">
-        <v>2.26</v>
-      </c>
-      <c r="AH5" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI5" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ5">
-        <v>1.16</v>
-      </c>
       <c r="AK5">
-        <v>1.91</v>
+        <v>1.94</v>
       </c>
       <c r="AL5">
         <v>0</v>
@@ -1290,28 +1290,28 @@
         <v>1.32</v>
       </c>
       <c r="O6">
-        <v>4.45</v>
+        <v>5</v>
       </c>
       <c r="P6">
         <v>6.7</v>
       </c>
       <c r="Q6">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="R6">
         <v>2.47</v>
       </c>
       <c r="S6">
-        <v>1.28</v>
+        <v>1.32</v>
       </c>
       <c r="T6">
-        <v>3.14</v>
+        <v>3.11</v>
       </c>
       <c r="U6">
-        <v>2.41</v>
+        <v>2.51</v>
       </c>
       <c r="V6">
-        <v>1.46</v>
+        <v>1.49</v>
       </c>
       <c r="W6">
         <v>1.08</v>
@@ -1320,16 +1320,16 @@
         <v>1.02</v>
       </c>
       <c r="Y6">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="Z6">
         <v>3.86</v>
       </c>
       <c r="AA6">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="AB6">
-        <v>2.06</v>
+        <v>2.02</v>
       </c>
       <c r="AC6">
         <v>2.62</v>
@@ -1338,13 +1338,13 @@
         <v>1.38</v>
       </c>
       <c r="AE6">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="AF6">
-        <v>1.99</v>
+        <v>1.82</v>
       </c>
       <c r="AG6">
-        <v>1.7</v>
+        <v>1.85</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1450,25 +1450,25 @@
         </is>
       </c>
       <c r="N7">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="O7">
         <v>4.5</v>
       </c>
       <c r="P7">
-        <v>1.39</v>
+        <v>1.36</v>
       </c>
       <c r="Q7">
-        <v>5.1</v>
+        <v>6</v>
       </c>
       <c r="R7">
         <v>2.54</v>
       </c>
       <c r="S7">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="T7">
-        <v>4</v>
+        <v>3.74</v>
       </c>
       <c r="U7">
         <v>2.1</v>
@@ -1489,7 +1489,7 @@
         <v>5.3</v>
       </c>
       <c r="AA7">
-        <v>1.41</v>
+        <v>1.43</v>
       </c>
       <c r="AB7">
         <v>2.52</v>
@@ -1520,10 +1520,10 @@
         </is>
       </c>
       <c r="AJ7">
+        <v>2.75</v>
+      </c>
+      <c r="AK7">
         <v>1.13</v>
-      </c>
-      <c r="AK7">
-        <v>1.06</v>
       </c>
       <c r="AL7">
         <v>0</v>
@@ -1616,25 +1616,25 @@
         <v>3.6</v>
       </c>
       <c r="O8">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="P8">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="Q8">
-        <v>5</v>
+        <v>4.95</v>
       </c>
       <c r="R8">
-        <v>2.01</v>
+        <v>2.02</v>
       </c>
       <c r="S8">
         <v>1.43</v>
       </c>
       <c r="T8">
-        <v>2.59</v>
+        <v>2.76</v>
       </c>
       <c r="U8">
-        <v>3.05</v>
+        <v>3.15</v>
       </c>
       <c r="V8">
         <v>1.32</v>
@@ -1649,19 +1649,19 @@
         <v>1.3</v>
       </c>
       <c r="Z8">
-        <v>3.06</v>
+        <v>2.97</v>
       </c>
       <c r="AA8">
-        <v>2.11</v>
+        <v>2.12</v>
       </c>
       <c r="AB8">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="AC8">
-        <v>3.68</v>
+        <v>3.58</v>
       </c>
       <c r="AD8">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="AE8">
         <v>1.03</v>
@@ -1683,7 +1683,7 @@
         </is>
       </c>
       <c r="AJ8">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="AK8">
         <v>1.2</v>
@@ -1776,13 +1776,13 @@
         </is>
       </c>
       <c r="N9">
-        <v>2.37</v>
+        <v>2.41</v>
       </c>
       <c r="O9">
-        <v>3.44</v>
+        <v>3.5</v>
       </c>
       <c r="P9">
-        <v>2.67</v>
+        <v>2.63</v>
       </c>
       <c r="Q9">
         <v>0</v>
@@ -1939,25 +1939,25 @@
         </is>
       </c>
       <c r="N10">
-        <v>1.77</v>
+        <v>1.7</v>
       </c>
       <c r="O10">
-        <v>3.33</v>
+        <v>3.75</v>
       </c>
       <c r="P10">
-        <v>3.21</v>
+        <v>3.8</v>
       </c>
       <c r="Q10">
-        <v>2.22</v>
+        <v>2.3</v>
       </c>
       <c r="R10">
         <v>2.38</v>
       </c>
       <c r="S10">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="T10">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="U10">
         <v>2.33</v>
@@ -1972,31 +1972,31 @@
         <v>1.03</v>
       </c>
       <c r="Y10">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="Z10">
-        <v>4.6</v>
+        <v>4.75</v>
       </c>
       <c r="AA10">
-        <v>1.59</v>
+        <v>1.62</v>
       </c>
       <c r="AB10">
-        <v>2.29</v>
+        <v>2.2</v>
       </c>
       <c r="AC10">
-        <v>2.44</v>
+        <v>2.5</v>
       </c>
       <c r="AD10">
-        <v>1.53</v>
+        <v>1.43</v>
       </c>
       <c r="AE10">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="AF10">
         <v>1.57</v>
       </c>
       <c r="AG10">
-        <v>2.25</v>
+        <v>2.06</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2009,10 +2009,10 @@
         </is>
       </c>
       <c r="AJ10">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AK10">
-        <v>2.09</v>
+        <v>1.84</v>
       </c>
       <c r="AL10">
         <v>0</v>
@@ -2105,43 +2105,43 @@
         <v>1.48</v>
       </c>
       <c r="O11">
-        <v>4.3</v>
+        <v>4</v>
       </c>
       <c r="P11">
-        <v>5.75</v>
+        <v>5.25</v>
       </c>
       <c r="Q11">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="R11">
         <v>2.29</v>
       </c>
       <c r="S11">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="T11">
-        <v>2.77</v>
+        <v>3.3</v>
       </c>
       <c r="U11">
-        <v>2.65</v>
+        <v>2.63</v>
       </c>
       <c r="V11">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="W11">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="X11">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="Y11">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="Z11">
-        <v>3.8</v>
+        <v>3.54</v>
       </c>
       <c r="AA11">
-        <v>1.81</v>
+        <v>1.85</v>
       </c>
       <c r="AB11">
         <v>1.97</v>
@@ -2156,7 +2156,7 @@
         <v>1.08</v>
       </c>
       <c r="AF11">
-        <v>1.91</v>
+        <v>2.05</v>
       </c>
       <c r="AG11">
         <v>1.77</v>
@@ -2172,7 +2172,7 @@
         </is>
       </c>
       <c r="AJ11">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AK11">
         <v>2.5</v>
@@ -2233,12 +2233,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Ulsan</t>
+          <t>Jeju United</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Anyang</t>
+          <t>Incheon United</t>
         </is>
       </c>
       <c r="G12">
@@ -2265,64 +2265,64 @@
         </is>
       </c>
       <c r="N12">
-        <v>1.86</v>
+        <v>2.87</v>
       </c>
       <c r="O12">
-        <v>3.45</v>
+        <v>2.97</v>
       </c>
       <c r="P12">
-        <v>3.35</v>
+        <v>2.4</v>
       </c>
       <c r="Q12">
+        <v>3.55</v>
+      </c>
+      <c r="R12">
+        <v>1.87</v>
+      </c>
+      <c r="S12">
+        <v>1.44</v>
+      </c>
+      <c r="T12">
+        <v>2.6</v>
+      </c>
+      <c r="U12">
+        <v>3.2</v>
+      </c>
+      <c r="V12">
+        <v>1.3</v>
+      </c>
+      <c r="W12">
+        <v>1.06</v>
+      </c>
+      <c r="X12">
+        <v>1.07</v>
+      </c>
+      <c r="Y12">
+        <v>1.4</v>
+      </c>
+      <c r="Z12">
+        <v>2.57</v>
+      </c>
+      <c r="AA12">
         <v>2.38</v>
       </c>
-      <c r="R12">
-        <v>2.25</v>
-      </c>
-      <c r="S12">
-        <v>1.35</v>
-      </c>
-      <c r="T12">
-        <v>2.75</v>
-      </c>
-      <c r="U12">
-        <v>2.65</v>
-      </c>
-      <c r="V12">
-        <v>1.42</v>
-      </c>
-      <c r="W12">
-        <v>1.1</v>
-      </c>
-      <c r="X12">
-        <v>1.01</v>
-      </c>
-      <c r="Y12">
-        <v>1.22</v>
-      </c>
-      <c r="Z12">
-        <v>3.82</v>
-      </c>
-      <c r="AA12">
-        <v>1.89</v>
-      </c>
       <c r="AB12">
-        <v>2.01</v>
+        <v>1.56</v>
       </c>
       <c r="AC12">
-        <v>3.05</v>
+        <v>4.5</v>
       </c>
       <c r="AD12">
-        <v>1.37</v>
+        <v>1.2</v>
       </c>
       <c r="AE12">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="AF12">
-        <v>1.7</v>
+        <v>1.93</v>
       </c>
       <c r="AG12">
-        <v>2.04</v>
+        <v>1.75</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2335,10 +2335,10 @@
         </is>
       </c>
       <c r="AJ12">
-        <v>1.25</v>
+        <v>1.36</v>
       </c>
       <c r="AK12">
-        <v>1.9</v>
+        <v>1.34</v>
       </c>
       <c r="AL12">
         <v>0</v>
@@ -2396,12 +2396,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Jeju United</t>
+          <t>Ulsan</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Incheon United</t>
+          <t>Anyang</t>
         </is>
       </c>
       <c r="G13">
@@ -2428,64 +2428,64 @@
         </is>
       </c>
       <c r="N13">
-        <v>2.88</v>
+        <v>1.85</v>
       </c>
       <c r="O13">
-        <v>2.88</v>
+        <v>3.4</v>
       </c>
       <c r="P13">
-        <v>2.33</v>
+        <v>3.5</v>
       </c>
       <c r="Q13">
-        <v>3.2</v>
+        <v>2.28</v>
       </c>
       <c r="R13">
-        <v>1.98</v>
+        <v>2.15</v>
       </c>
       <c r="S13">
-        <v>1.53</v>
+        <v>1.36</v>
       </c>
       <c r="T13">
-        <v>2.34</v>
+        <v>3.1</v>
       </c>
       <c r="U13">
-        <v>3.4</v>
+        <v>2.65</v>
       </c>
       <c r="V13">
-        <v>1.27</v>
+        <v>1.42</v>
       </c>
       <c r="W13">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="X13">
-        <v>1.07</v>
+        <v>1.02</v>
       </c>
       <c r="Y13">
-        <v>1.4</v>
+        <v>1.22</v>
       </c>
       <c r="Z13">
-        <v>2.57</v>
+        <v>3.86</v>
       </c>
       <c r="AA13">
-        <v>2.38</v>
+        <v>1.89</v>
       </c>
       <c r="AB13">
-        <v>1.56</v>
+        <v>1.89</v>
       </c>
       <c r="AC13">
-        <v>4.5</v>
+        <v>3.05</v>
       </c>
       <c r="AD13">
-        <v>1.19</v>
+        <v>1.38</v>
       </c>
       <c r="AE13">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="AF13">
-        <v>1.97</v>
+        <v>1.7</v>
       </c>
       <c r="AG13">
-        <v>1.75</v>
+        <v>2.04</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2498,10 +2498,10 @@
         </is>
       </c>
       <c r="AJ13">
-        <v>1.36</v>
+        <v>1.18</v>
       </c>
       <c r="AK13">
-        <v>1.34</v>
+        <v>1.87</v>
       </c>
       <c r="AL13">
         <v>0</v>
@@ -2591,19 +2591,19 @@
         </is>
       </c>
       <c r="N14">
-        <v>1.96</v>
+        <v>2</v>
       </c>
       <c r="O14">
-        <v>3.28</v>
+        <v>3.3</v>
       </c>
       <c r="P14">
-        <v>2.77</v>
+        <v>3.1</v>
       </c>
       <c r="Q14">
-        <v>2.63</v>
+        <v>2.66</v>
       </c>
       <c r="R14">
-        <v>2.09</v>
+        <v>2.2</v>
       </c>
       <c r="S14">
         <v>1.33</v>
@@ -2612,7 +2612,7 @@
         <v>2.9</v>
       </c>
       <c r="U14">
-        <v>2.62</v>
+        <v>2.73</v>
       </c>
       <c r="V14">
         <v>1.4</v>
@@ -2627,16 +2627,16 @@
         <v>1.26</v>
       </c>
       <c r="Z14">
-        <v>3.71</v>
+        <v>3.76</v>
       </c>
       <c r="AA14">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="AB14">
-        <v>1.9</v>
+        <v>1.92</v>
       </c>
       <c r="AC14">
-        <v>3.05</v>
+        <v>2.92</v>
       </c>
       <c r="AD14">
         <v>1.36</v>
@@ -2645,10 +2645,10 @@
         <v>1.08</v>
       </c>
       <c r="AF14">
-        <v>1.65</v>
+        <v>1.58</v>
       </c>
       <c r="AG14">
-        <v>2.1</v>
+        <v>2.17</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2757,7 +2757,7 @@
         <v>1.94</v>
       </c>
       <c r="O15">
-        <v>2.98</v>
+        <v>3.2</v>
       </c>
       <c r="P15">
         <v>3.5</v>
@@ -2772,7 +2772,7 @@
         <v>1.4</v>
       </c>
       <c r="T15">
-        <v>2.5</v>
+        <v>2.48</v>
       </c>
       <c r="U15">
         <v>3.12</v>
@@ -2784,34 +2784,34 @@
         <v>1.02</v>
       </c>
       <c r="X15">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="Y15">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="Z15">
-        <v>2.9</v>
+        <v>3.05</v>
       </c>
       <c r="AA15">
-        <v>2.28</v>
+        <v>2.29</v>
       </c>
       <c r="AB15">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="AC15">
         <v>3.3</v>
       </c>
       <c r="AD15">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="AE15">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="AF15">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="AG15">
-        <v>1.8</v>
+        <v>1.77</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2824,10 +2824,10 @@
         </is>
       </c>
       <c r="AJ15">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="AK15">
-        <v>1.72</v>
+        <v>1.83</v>
       </c>
       <c r="AL15">
         <v>0</v>
@@ -2885,12 +2885,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Ansan Greeners</t>
+          <t>Busan I'Park</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Gimhae City</t>
+          <t>Seoul E-Land</t>
         </is>
       </c>
       <c r="G16">
@@ -2917,64 +2917,64 @@
         </is>
       </c>
       <c r="N16">
-        <v>2.65</v>
+        <v>2.62</v>
       </c>
       <c r="O16">
+        <v>3.5</v>
+      </c>
+      <c r="P16">
+        <v>2.2</v>
+      </c>
+      <c r="Q16">
+        <v>3.1</v>
+      </c>
+      <c r="R16">
+        <v>2.16</v>
+      </c>
+      <c r="S16">
+        <v>1.3</v>
+      </c>
+      <c r="T16">
         <v>3.25</v>
       </c>
-      <c r="P16">
-        <v>2.15</v>
-      </c>
-      <c r="Q16">
-        <v>3.4</v>
-      </c>
-      <c r="R16">
-        <v>2.2</v>
-      </c>
-      <c r="S16">
-        <v>1.35</v>
-      </c>
-      <c r="T16">
-        <v>2.82</v>
-      </c>
       <c r="U16">
-        <v>2.84</v>
+        <v>2.5</v>
       </c>
       <c r="V16">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="W16">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="X16">
         <v>1.04</v>
       </c>
       <c r="Y16">
-        <v>1.29</v>
+        <v>1.21</v>
       </c>
       <c r="Z16">
-        <v>3.28</v>
+        <v>4.26</v>
       </c>
       <c r="AA16">
-        <v>1.87</v>
+        <v>1.67</v>
       </c>
       <c r="AB16">
-        <v>1.87</v>
+        <v>2.1</v>
       </c>
       <c r="AC16">
-        <v>3.2</v>
+        <v>2.66</v>
       </c>
       <c r="AD16">
-        <v>1.27</v>
+        <v>1.37</v>
       </c>
       <c r="AE16">
         <v>1.11</v>
       </c>
       <c r="AF16">
-        <v>1.67</v>
+        <v>1.57</v>
       </c>
       <c r="AG16">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -2987,10 +2987,10 @@
         </is>
       </c>
       <c r="AJ16">
-        <v>1.25</v>
+        <v>1.5</v>
       </c>
       <c r="AK16">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="AL16">
         <v>0</v>
@@ -3048,12 +3048,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Busan I'Park</t>
+          <t>Ansan Greeners</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Seoul E-Land</t>
+          <t>Gimhae City</t>
         </is>
       </c>
       <c r="G17">
@@ -3080,64 +3080,64 @@
         </is>
       </c>
       <c r="N17">
-        <v>2.42</v>
+        <v>2.65</v>
       </c>
       <c r="O17">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="P17">
-        <v>2.17</v>
+        <v>2.1</v>
       </c>
       <c r="Q17">
-        <v>3.1</v>
+        <v>3.4</v>
       </c>
       <c r="R17">
-        <v>2.23</v>
+        <v>2.12</v>
       </c>
       <c r="S17">
-        <v>1.3</v>
+        <v>1.34</v>
       </c>
       <c r="T17">
-        <v>3.3</v>
+        <v>3.01</v>
       </c>
       <c r="U17">
-        <v>2.5</v>
+        <v>2.74</v>
       </c>
       <c r="V17">
-        <v>1.45</v>
+        <v>1.37</v>
       </c>
       <c r="W17">
-        <v>1.12</v>
+        <v>1.08</v>
       </c>
       <c r="X17">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="Y17">
-        <v>1.21</v>
+        <v>1.29</v>
       </c>
       <c r="Z17">
-        <v>4.23</v>
+        <v>3.4</v>
       </c>
       <c r="AA17">
-        <v>1.67</v>
+        <v>1.9</v>
       </c>
       <c r="AB17">
-        <v>2.1</v>
+        <v>1.87</v>
       </c>
       <c r="AC17">
-        <v>2.66</v>
+        <v>3.2</v>
       </c>
       <c r="AD17">
-        <v>1.37</v>
+        <v>1.33</v>
       </c>
       <c r="AE17">
         <v>1.11</v>
       </c>
       <c r="AF17">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="AG17">
-        <v>2.25</v>
+        <v>2.03</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3150,10 +3150,10 @@
         </is>
       </c>
       <c r="AJ17">
-        <v>1.51</v>
+        <v>1.24</v>
       </c>
       <c r="AK17">
-        <v>1.36</v>
+        <v>1.32</v>
       </c>
       <c r="AL17">
         <v>0</v>
@@ -3252,40 +3252,40 @@
         <v>3</v>
       </c>
       <c r="Q18">
-        <v>2.94</v>
+        <v>2.89</v>
       </c>
       <c r="R18">
-        <v>1.95</v>
+        <v>2.1</v>
       </c>
       <c r="S18">
         <v>1.41</v>
       </c>
       <c r="T18">
-        <v>2.72</v>
+        <v>2.65</v>
       </c>
       <c r="U18">
-        <v>2.95</v>
+        <v>2.88</v>
       </c>
       <c r="V18">
         <v>1.36</v>
       </c>
       <c r="W18">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="X18">
         <v>1.01</v>
       </c>
       <c r="Y18">
-        <v>1.35</v>
+        <v>1.28</v>
       </c>
       <c r="Z18">
         <v>3.05</v>
       </c>
       <c r="AA18">
-        <v>2.08</v>
+        <v>2</v>
       </c>
       <c r="AB18">
-        <v>1.73</v>
+        <v>1.8</v>
       </c>
       <c r="AC18">
         <v>3.5</v>
@@ -3294,7 +3294,7 @@
         <v>1.22</v>
       </c>
       <c r="AE18">
-        <v>1.08</v>
+        <v>1.03</v>
       </c>
       <c r="AF18">
         <v>1.73</v>
@@ -3313,7 +3313,7 @@
         </is>
       </c>
       <c r="AJ18">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="AK18">
         <v>1.57</v>
@@ -3415,46 +3415,46 @@
         <v>2.9</v>
       </c>
       <c r="Q19">
-        <v>2.67</v>
+        <v>2.55</v>
       </c>
       <c r="R19">
-        <v>2.34</v>
+        <v>2.25</v>
       </c>
       <c r="S19">
         <v>1.34</v>
       </c>
       <c r="T19">
-        <v>3.04</v>
+        <v>3.1</v>
       </c>
       <c r="U19">
         <v>2.39</v>
       </c>
       <c r="V19">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="W19">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="X19">
         <v>1.02</v>
       </c>
       <c r="Y19">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="Z19">
         <v>4.33</v>
       </c>
       <c r="AA19">
-        <v>1.75</v>
+        <v>1.64</v>
       </c>
       <c r="AB19">
         <v>2.19</v>
       </c>
       <c r="AC19">
-        <v>2.88</v>
+        <v>2.64</v>
       </c>
       <c r="AD19">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="AE19">
         <v>1.13</v>
@@ -3476,10 +3476,10 @@
         </is>
       </c>
       <c r="AJ19">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="AK19">
-        <v>1.6</v>
+        <v>1.65</v>
       </c>
       <c r="AL19">
         <v>0</v>
@@ -3578,43 +3578,43 @@
         <v>4.4</v>
       </c>
       <c r="Q20">
-        <v>2.29</v>
+        <v>2.27</v>
       </c>
       <c r="R20">
-        <v>2.05</v>
+        <v>2.25</v>
       </c>
       <c r="S20">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="T20">
         <v>2.67</v>
       </c>
       <c r="U20">
-        <v>2.75</v>
+        <v>2.62</v>
       </c>
       <c r="V20">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="W20">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="X20">
         <v>1.01</v>
       </c>
       <c r="Y20">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="Z20">
-        <v>3.28</v>
+        <v>3.25</v>
       </c>
       <c r="AA20">
-        <v>1.94</v>
+        <v>1.93</v>
       </c>
       <c r="AB20">
-        <v>1.86</v>
+        <v>1.8</v>
       </c>
       <c r="AC20">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="AD20">
         <v>1.28</v>
@@ -3623,10 +3623,10 @@
         <v>1.1</v>
       </c>
       <c r="AF20">
-        <v>1.77</v>
+        <v>1.87</v>
       </c>
       <c r="AG20">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
@@ -3639,10 +3639,10 @@
         </is>
       </c>
       <c r="AJ20">
-        <v>1.14</v>
+        <v>1.25</v>
       </c>
       <c r="AK20">
-        <v>1.96</v>
+        <v>2</v>
       </c>
       <c r="AL20">
         <v>0</v>
@@ -3732,16 +3732,16 @@
         </is>
       </c>
       <c r="N21">
-        <v>3.6</v>
+        <v>3.75</v>
       </c>
       <c r="O21">
         <v>3.8</v>
       </c>
       <c r="P21">
-        <v>1.72</v>
+        <v>1.66</v>
       </c>
       <c r="Q21">
-        <v>3.6</v>
+        <v>3.96</v>
       </c>
       <c r="R21">
         <v>2.5</v>
@@ -3750,46 +3750,46 @@
         <v>1.2</v>
       </c>
       <c r="T21">
-        <v>3.9</v>
+        <v>4.1</v>
       </c>
       <c r="U21">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="V21">
         <v>1.63</v>
       </c>
       <c r="W21">
-        <v>1.14</v>
+        <v>1.18</v>
       </c>
       <c r="X21">
         <v>1.01</v>
       </c>
       <c r="Y21">
-        <v>1.09</v>
+        <v>1.13</v>
       </c>
       <c r="Z21">
-        <v>6.71</v>
+        <v>5.48</v>
       </c>
       <c r="AA21">
-        <v>1.47</v>
+        <v>1.4</v>
       </c>
       <c r="AB21">
-        <v>2.62</v>
+        <v>2.7</v>
       </c>
       <c r="AC21">
-        <v>2.21</v>
+        <v>2.22</v>
       </c>
       <c r="AD21">
         <v>1.66</v>
       </c>
       <c r="AE21">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="AF21">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="AG21">
-        <v>2.6</v>
+        <v>2.55</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
@@ -3802,10 +3802,10 @@
         </is>
       </c>
       <c r="AJ21">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="AK21">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="AL21">
         <v>0</v>
@@ -3895,16 +3895,16 @@
         </is>
       </c>
       <c r="N22">
-        <v>2.03</v>
+        <v>2.12</v>
       </c>
       <c r="O22">
-        <v>3.25</v>
+        <v>3.17</v>
       </c>
       <c r="P22">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="Q22">
-        <v>2.69</v>
+        <v>2.68</v>
       </c>
       <c r="R22">
         <v>2.07</v>
@@ -3925,22 +3925,22 @@
         <v>1.06</v>
       </c>
       <c r="X22">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="Y22">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="Z22">
-        <v>3.5</v>
+        <v>3.2</v>
       </c>
       <c r="AA22">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="AB22">
-        <v>1.88</v>
+        <v>1.85</v>
       </c>
       <c r="AC22">
-        <v>3.4</v>
+        <v>3.51</v>
       </c>
       <c r="AD22">
         <v>1.31</v>
@@ -3949,7 +3949,7 @@
         <v>1.07</v>
       </c>
       <c r="AF22">
-        <v>1.71</v>
+        <v>1.64</v>
       </c>
       <c r="AG22">
         <v>2</v>
@@ -3968,7 +3968,7 @@
         <v>1.32</v>
       </c>
       <c r="AK22">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="AL22">
         <v>0</v>
@@ -4058,22 +4058,22 @@
         </is>
       </c>
       <c r="N23">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="O23">
-        <v>3.61</v>
+        <v>3.6</v>
       </c>
       <c r="P23">
-        <v>2.03</v>
+        <v>2</v>
       </c>
       <c r="Q23">
-        <v>3.04</v>
+        <v>3.4</v>
       </c>
       <c r="R23">
-        <v>2.31</v>
+        <v>2.58</v>
       </c>
       <c r="S23">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="T23">
         <v>3.58</v>
@@ -4082,7 +4082,7 @@
         <v>2.14</v>
       </c>
       <c r="V23">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="W23">
         <v>1.13</v>
@@ -4091,22 +4091,22 @@
         <v>1.01</v>
       </c>
       <c r="Y23">
-        <v>1.15</v>
+        <v>1.13</v>
       </c>
       <c r="Z23">
-        <v>4.9</v>
+        <v>5.25</v>
       </c>
       <c r="AA23">
         <v>1.5</v>
       </c>
       <c r="AB23">
-        <v>2.58</v>
+        <v>2.55</v>
       </c>
       <c r="AC23">
-        <v>2.16</v>
+        <v>2.15</v>
       </c>
       <c r="AD23">
-        <v>1.62</v>
+        <v>1.58</v>
       </c>
       <c r="AE23">
         <v>1.22</v>
@@ -4128,10 +4128,10 @@
         </is>
       </c>
       <c r="AJ23">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="AK23">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="AL23">
         <v>0</v>
@@ -4221,10 +4221,10 @@
         </is>
       </c>
       <c r="N24">
-        <v>2.8</v>
+        <v>2.43</v>
       </c>
       <c r="O24">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="P24">
         <v>2.4</v>
@@ -4236,13 +4236,13 @@
         <v>1.95</v>
       </c>
       <c r="S24">
-        <v>1.45</v>
+        <v>1.49</v>
       </c>
       <c r="T24">
-        <v>2.65</v>
+        <v>2.41</v>
       </c>
       <c r="U24">
-        <v>3.29</v>
+        <v>3.31</v>
       </c>
       <c r="V24">
         <v>1.3</v>
@@ -4257,7 +4257,7 @@
         <v>1.36</v>
       </c>
       <c r="Z24">
-        <v>2.7</v>
+        <v>2.95</v>
       </c>
       <c r="AA24">
         <v>2.23</v>
@@ -4266,7 +4266,7 @@
         <v>1.62</v>
       </c>
       <c r="AC24">
-        <v>4.04</v>
+        <v>4.07</v>
       </c>
       <c r="AD24">
         <v>1.22</v>
@@ -4384,7 +4384,7 @@
         </is>
       </c>
       <c r="N25">
-        <v>1.68</v>
+        <v>1.73</v>
       </c>
       <c r="O25">
         <v>3.6</v>
@@ -4399,28 +4399,28 @@
         <v>2.38</v>
       </c>
       <c r="S25">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="T25">
         <v>3.04</v>
       </c>
       <c r="U25">
-        <v>2.61</v>
+        <v>2.6</v>
       </c>
       <c r="V25">
-        <v>1.44</v>
+        <v>1.48</v>
       </c>
       <c r="W25">
         <v>1.08</v>
       </c>
       <c r="X25">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="Y25">
         <v>1.22</v>
       </c>
       <c r="Z25">
-        <v>3.82</v>
+        <v>3.8</v>
       </c>
       <c r="AA25">
         <v>1.8</v>
@@ -4432,13 +4432,13 @@
         <v>2.88</v>
       </c>
       <c r="AD25">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="AE25">
         <v>1.09</v>
       </c>
       <c r="AF25">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="AG25">
         <v>2.05</v>
@@ -4454,10 +4454,10 @@
         </is>
       </c>
       <c r="AJ25">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="AK25">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="AL25">
         <v>0</v>
@@ -4559,25 +4559,25 @@
         <v>3.23</v>
       </c>
       <c r="R26">
-        <v>2.42</v>
+        <v>2.25</v>
       </c>
       <c r="S26">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="T26">
-        <v>3.22</v>
+        <v>3.4</v>
       </c>
       <c r="U26">
-        <v>2.4</v>
+        <v>2.34</v>
       </c>
       <c r="V26">
         <v>1.56</v>
       </c>
       <c r="W26">
-        <v>1.1</v>
+        <v>1.14</v>
       </c>
       <c r="X26">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y26">
         <v>1.15</v>
@@ -4589,7 +4589,7 @@
         <v>1.62</v>
       </c>
       <c r="AB26">
-        <v>2.26</v>
+        <v>2.25</v>
       </c>
       <c r="AC26">
         <v>2.3</v>
@@ -4620,7 +4620,7 @@
         <v>1.27</v>
       </c>
       <c r="AK26">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="AL26">
         <v>0</v>
@@ -4710,10 +4710,10 @@
         </is>
       </c>
       <c r="N27">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="O27">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="P27">
         <v>7.3</v>
@@ -4731,10 +4731,10 @@
         <v>3.5</v>
       </c>
       <c r="U27">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="V27">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="W27">
         <v>1.15</v>
@@ -4761,13 +4761,13 @@
         <v>1.55</v>
       </c>
       <c r="AE27">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="AF27">
-        <v>1.8</v>
+        <v>1.77</v>
       </c>
       <c r="AG27">
-        <v>1.94</v>
+        <v>1.91</v>
       </c>
       <c r="AH27" t="inlineStr">
         <is>
@@ -4783,7 +4783,7 @@
         <v>1.05</v>
       </c>
       <c r="AK27">
-        <v>2.97</v>
+        <v>3.15</v>
       </c>
       <c r="AL27">
         <v>0</v>
@@ -4873,55 +4873,55 @@
         </is>
       </c>
       <c r="N28">
-        <v>1.68</v>
+        <v>1.72</v>
       </c>
       <c r="O28">
-        <v>3.75</v>
+        <v>3.9</v>
       </c>
       <c r="P28">
-        <v>4.7</v>
+        <v>3.8</v>
       </c>
       <c r="Q28">
         <v>2.1</v>
       </c>
       <c r="R28">
+        <v>2.24</v>
+      </c>
+      <c r="S28">
+        <v>1.28</v>
+      </c>
+      <c r="T28">
+        <v>3.3</v>
+      </c>
+      <c r="U28">
         <v>2.4</v>
-      </c>
-      <c r="S28">
-        <v>1.29</v>
-      </c>
-      <c r="T28">
-        <v>3.28</v>
-      </c>
-      <c r="U28">
-        <v>2.44</v>
       </c>
       <c r="V28">
         <v>1.55</v>
       </c>
       <c r="W28">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="X28">
         <v>1.01</v>
       </c>
       <c r="Y28">
-        <v>1.16</v>
+        <v>1.2</v>
       </c>
       <c r="Z28">
-        <v>4.2</v>
+        <v>4.25</v>
       </c>
       <c r="AA28">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="AB28">
-        <v>2.29</v>
+        <v>2.26</v>
       </c>
       <c r="AC28">
-        <v>2.58</v>
+        <v>2.55</v>
       </c>
       <c r="AD28">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="AE28">
         <v>1.15</v>
@@ -4930,7 +4930,7 @@
         <v>1.65</v>
       </c>
       <c r="AG28">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="AH28" t="inlineStr">
         <is>
@@ -4943,7 +4943,7 @@
         </is>
       </c>
       <c r="AJ28">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="AK28">
         <v>2.17</v>
@@ -5202,7 +5202,7 @@
         <v>2.05</v>
       </c>
       <c r="O30">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="P30">
         <v>3</v>
@@ -5214,19 +5214,19 @@
         <v>2.19</v>
       </c>
       <c r="S30">
-        <v>1.29</v>
+        <v>1.32</v>
       </c>
       <c r="T30">
-        <v>3.12</v>
+        <v>3.25</v>
       </c>
       <c r="U30">
-        <v>2.5</v>
+        <v>2.48</v>
       </c>
       <c r="V30">
-        <v>1.44</v>
+        <v>1.48</v>
       </c>
       <c r="W30">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="X30">
         <v>1.02</v>
@@ -5238,16 +5238,16 @@
         <v>3.86</v>
       </c>
       <c r="AA30">
-        <v>1.71</v>
+        <v>1.73</v>
       </c>
       <c r="AB30">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="AC30">
-        <v>2.88</v>
+        <v>2.84</v>
       </c>
       <c r="AD30">
-        <v>1.35</v>
+        <v>1.4</v>
       </c>
       <c r="AE30">
         <v>1.09</v>
@@ -5269,7 +5269,7 @@
         </is>
       </c>
       <c r="AJ30">
-        <v>1.22</v>
+        <v>1.29</v>
       </c>
       <c r="AK30">
         <v>1.63</v>
@@ -5362,19 +5362,19 @@
         </is>
       </c>
       <c r="N31">
-        <v>1.43</v>
+        <v>1.56</v>
       </c>
       <c r="O31">
         <v>3.7</v>
       </c>
       <c r="P31">
-        <v>4.7</v>
+        <v>5.5</v>
       </c>
       <c r="Q31">
         <v>2.15</v>
       </c>
       <c r="R31">
-        <v>2.17</v>
+        <v>2.18</v>
       </c>
       <c r="S31">
         <v>1.36</v>
@@ -5401,10 +5401,10 @@
         <v>3.8</v>
       </c>
       <c r="AA31">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="AB31">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="AC31">
         <v>3.25</v>
@@ -5413,7 +5413,7 @@
         <v>1.33</v>
       </c>
       <c r="AE31">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="AF31">
         <v>1.9</v>
@@ -5531,55 +5531,55 @@
         <v>2.7</v>
       </c>
       <c r="P32">
-        <v>2.75</v>
+        <v>2.88</v>
       </c>
       <c r="Q32">
-        <v>3.4</v>
+        <v>3.58</v>
       </c>
       <c r="R32">
-        <v>1.85</v>
+        <v>1.7</v>
       </c>
       <c r="S32">
         <v>1.6</v>
       </c>
       <c r="T32">
-        <v>2.14</v>
+        <v>2.2</v>
       </c>
       <c r="U32">
-        <v>3.82</v>
+        <v>3.96</v>
       </c>
       <c r="V32">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="W32">
+        <v>1.02</v>
+      </c>
+      <c r="X32">
+        <v>1.15</v>
+      </c>
+      <c r="Y32">
+        <v>1.66</v>
+      </c>
+      <c r="Z32">
+        <v>2.09</v>
+      </c>
+      <c r="AA32">
+        <v>2.92</v>
+      </c>
+      <c r="AB32">
+        <v>1.36</v>
+      </c>
+      <c r="AC32">
+        <v>5.8</v>
+      </c>
+      <c r="AD32">
+        <v>1.11</v>
+      </c>
+      <c r="AE32">
         <v>1.03</v>
       </c>
-      <c r="X32">
-        <v>1.12</v>
-      </c>
-      <c r="Y32">
-        <v>1.61</v>
-      </c>
-      <c r="Z32">
-        <v>2.17</v>
-      </c>
-      <c r="AA32">
-        <v>2.78</v>
-      </c>
-      <c r="AB32">
-        <v>1.4</v>
-      </c>
-      <c r="AC32">
-        <v>6.25</v>
-      </c>
-      <c r="AD32">
-        <v>1.07</v>
-      </c>
-      <c r="AE32">
-        <v>1.01</v>
-      </c>
       <c r="AF32">
-        <v>2.23</v>
+        <v>2.3</v>
       </c>
       <c r="AG32">
         <v>1.53</v>
@@ -5595,10 +5595,10 @@
         </is>
       </c>
       <c r="AJ32">
-        <v>1.31</v>
+        <v>1.38</v>
       </c>
       <c r="AK32">
-        <v>1.4</v>
+        <v>1.37</v>
       </c>
       <c r="AL32">
         <v>0</v>
@@ -5688,28 +5688,28 @@
         </is>
       </c>
       <c r="N33">
-        <v>2.07</v>
+        <v>2.2</v>
       </c>
       <c r="O33">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="P33">
         <v>2.75</v>
       </c>
       <c r="Q33">
-        <v>3.24</v>
+        <v>2.7</v>
       </c>
       <c r="R33">
-        <v>1.98</v>
+        <v>1.95</v>
       </c>
       <c r="S33">
-        <v>1.43</v>
+        <v>1.45</v>
       </c>
       <c r="T33">
         <v>2.53</v>
       </c>
       <c r="U33">
-        <v>3.22</v>
+        <v>3.1</v>
       </c>
       <c r="V33">
         <v>1.31</v>
@@ -5721,19 +5721,19 @@
         <v>1.03</v>
       </c>
       <c r="Y33">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="Z33">
-        <v>2.98</v>
+        <v>2.81</v>
       </c>
       <c r="AA33">
-        <v>2.19</v>
+        <v>2.2</v>
       </c>
       <c r="AB33">
         <v>1.66</v>
       </c>
       <c r="AC33">
-        <v>3.8</v>
+        <v>3.97</v>
       </c>
       <c r="AD33">
         <v>1.19</v>
@@ -5761,7 +5761,7 @@
         <v>1.35</v>
       </c>
       <c r="AK33">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
       <c r="AL33">
         <v>0</v>
@@ -5851,28 +5851,28 @@
         </is>
       </c>
       <c r="N34">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="O34">
-        <v>3.9</v>
+        <v>3.6</v>
       </c>
       <c r="P34">
         <v>4.08</v>
       </c>
       <c r="Q34">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="R34">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="S34">
-        <v>1.27</v>
+        <v>1.33</v>
       </c>
       <c r="T34">
         <v>3.11</v>
       </c>
       <c r="U34">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="V34">
         <v>1.53</v>
@@ -5884,13 +5884,13 @@
         <v>1.01</v>
       </c>
       <c r="Y34">
-        <v>1.14</v>
+        <v>1.19</v>
       </c>
       <c r="Z34">
-        <v>4.42</v>
+        <v>4</v>
       </c>
       <c r="AA34">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="AB34">
         <v>2.11</v>
@@ -5899,16 +5899,16 @@
         <v>2.38</v>
       </c>
       <c r="AD34">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="AE34">
         <v>1.16</v>
       </c>
       <c r="AF34">
-        <v>1.56</v>
+        <v>1.62</v>
       </c>
       <c r="AG34">
-        <v>2.28</v>
+        <v>2.25</v>
       </c>
       <c r="AH34" t="inlineStr">
         <is>
@@ -5921,7 +5921,7 @@
         </is>
       </c>
       <c r="AJ34">
-        <v>1.15</v>
+        <v>1.2</v>
       </c>
       <c r="AK34">
         <v>2</v>
@@ -6014,19 +6014,19 @@
         </is>
       </c>
       <c r="N35">
-        <v>2.05</v>
+        <v>2.13</v>
       </c>
       <c r="O35">
         <v>3.6</v>
       </c>
       <c r="P35">
-        <v>2.81</v>
+        <v>2.85</v>
       </c>
       <c r="Q35">
-        <v>2.65</v>
+        <v>2.66</v>
       </c>
       <c r="R35">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="S35">
         <v>1.25</v>
@@ -6047,16 +6047,16 @@
         <v>1.01</v>
       </c>
       <c r="Y35">
-        <v>1.2</v>
+        <v>1.13</v>
       </c>
       <c r="Z35">
-        <v>4.55</v>
+        <v>4.5</v>
       </c>
       <c r="AA35">
         <v>1.58</v>
       </c>
       <c r="AB35">
-        <v>2.33</v>
+        <v>2.35</v>
       </c>
       <c r="AC35">
         <v>2.33</v>
@@ -6068,10 +6068,10 @@
         <v>1.16</v>
       </c>
       <c r="AF35">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="AG35">
-        <v>2.4</v>
+        <v>2.47</v>
       </c>
       <c r="AH35" t="inlineStr">
         <is>
@@ -6084,10 +6084,10 @@
         </is>
       </c>
       <c r="AJ35">
-        <v>1.25</v>
+        <v>1.21</v>
       </c>
       <c r="AK35">
-        <v>1.63</v>
+        <v>1.65</v>
       </c>
       <c r="AL35">
         <v>0</v>
@@ -6183,7 +6183,7 @@
         <v>6.15</v>
       </c>
       <c r="P36">
-        <v>9.300000000000001</v>
+        <v>8.470000000000001</v>
       </c>
       <c r="Q36">
         <v>1.52</v>
@@ -6192,16 +6192,16 @@
         <v>2.75</v>
       </c>
       <c r="S36">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="T36">
-        <v>4</v>
+        <v>3.8</v>
       </c>
       <c r="U36">
         <v>2.13</v>
       </c>
       <c r="V36">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
       <c r="W36">
         <v>1.16</v>
@@ -6210,13 +6210,13 @@
         <v>1.02</v>
       </c>
       <c r="Y36">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="Z36">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="AA36">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="AB36">
         <v>2.49</v>
@@ -6225,16 +6225,16 @@
         <v>2.14</v>
       </c>
       <c r="AD36">
-        <v>1.5</v>
+        <v>1.62</v>
       </c>
       <c r="AE36">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="AF36">
-        <v>2.25</v>
+        <v>1.95</v>
       </c>
       <c r="AG36">
-        <v>1.53</v>
+        <v>1.7</v>
       </c>
       <c r="AH36" t="inlineStr">
         <is>
@@ -6247,10 +6247,10 @@
         </is>
       </c>
       <c r="AJ36">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="AK36">
-        <v>4</v>
+        <v>4.05</v>
       </c>
       <c r="AL36">
         <v>0</v>
@@ -6340,13 +6340,13 @@
         </is>
       </c>
       <c r="N37">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="O37">
         <v>3.55</v>
       </c>
       <c r="P37">
-        <v>1.87</v>
+        <v>1.94</v>
       </c>
       <c r="Q37">
         <v>3.85</v>
@@ -6355,10 +6355,10 @@
         <v>2.43</v>
       </c>
       <c r="S37">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T37">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="U37">
         <v>2.14</v>
@@ -6367,19 +6367,19 @@
         <v>1.55</v>
       </c>
       <c r="W37">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X37">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y37">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="Z37">
         <v>4.3</v>
       </c>
       <c r="AA37">
-        <v>1.52</v>
+        <v>1.58</v>
       </c>
       <c r="AB37">
         <v>2.23</v>
@@ -6506,10 +6506,10 @@
         <v>8.699999999999999</v>
       </c>
       <c r="O38">
-        <v>4.4</v>
+        <v>5.25</v>
       </c>
       <c r="P38">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="Q38">
         <v>7.3</v>
@@ -6527,7 +6527,7 @@
         <v>2.51</v>
       </c>
       <c r="V38">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="W38">
         <v>1.09</v>
@@ -6548,7 +6548,7 @@
         <v>2.2</v>
       </c>
       <c r="AC38">
-        <v>2.74</v>
+        <v>2.7</v>
       </c>
       <c r="AD38">
         <v>1.43</v>
@@ -6672,10 +6672,10 @@
         <v>3.5</v>
       </c>
       <c r="P39">
-        <v>2.83</v>
+        <v>3.1</v>
       </c>
       <c r="Q39">
-        <v>2.8</v>
+        <v>2.49</v>
       </c>
       <c r="R39">
         <v>2.11</v>
@@ -6702,13 +6702,13 @@
         <v>1.28</v>
       </c>
       <c r="Z39">
-        <v>3.65</v>
+        <v>3.55</v>
       </c>
       <c r="AA39">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="AB39">
-        <v>2</v>
+        <v>1.86</v>
       </c>
       <c r="AC39">
         <v>3.1</v>
@@ -6739,7 +6739,7 @@
         <v>1.36</v>
       </c>
       <c r="AK39">
-        <v>1.65</v>
+        <v>1.63</v>
       </c>
       <c r="AL39">
         <v>0</v>
@@ -6829,13 +6829,13 @@
         </is>
       </c>
       <c r="N40">
-        <v>4.09</v>
+        <v>3.7</v>
       </c>
       <c r="O40">
-        <v>3.48</v>
+        <v>3.3</v>
       </c>
       <c r="P40">
-        <v>1.87</v>
+        <v>1.82</v>
       </c>
       <c r="Q40">
         <v>3.95</v>
@@ -6847,7 +6847,7 @@
         <v>1.36</v>
       </c>
       <c r="T40">
-        <v>2.74</v>
+        <v>2.77</v>
       </c>
       <c r="U40">
         <v>2.65</v>
@@ -6868,10 +6868,10 @@
         <v>3.34</v>
       </c>
       <c r="AA40">
-        <v>1.95</v>
+        <v>1.87</v>
       </c>
       <c r="AB40">
-        <v>1.85</v>
+        <v>1.9</v>
       </c>
       <c r="AC40">
         <v>3.2</v>
@@ -6998,7 +6998,7 @@
         <v>3.1</v>
       </c>
       <c r="P41">
-        <v>2.26</v>
+        <v>2.2</v>
       </c>
       <c r="Q41">
         <v>3.6</v>
@@ -7007,16 +7007,16 @@
         <v>2.1</v>
       </c>
       <c r="S41">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="T41">
         <v>2.56</v>
       </c>
       <c r="U41">
-        <v>2.96</v>
+        <v>2.8</v>
       </c>
       <c r="V41">
-        <v>1.32</v>
+        <v>1.38</v>
       </c>
       <c r="W41">
         <v>1.03</v>
@@ -7031,7 +7031,7 @@
         <v>2.88</v>
       </c>
       <c r="AA41">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="AB41">
         <v>1.73</v>
@@ -7043,7 +7043,7 @@
         <v>1.22</v>
       </c>
       <c r="AE41">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="AF41">
         <v>1.81</v>
@@ -7158,61 +7158,61 @@
         <v>2.1</v>
       </c>
       <c r="O42">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="P42">
-        <v>3.05</v>
+        <v>2.95</v>
       </c>
       <c r="Q42">
-        <v>2.47</v>
+        <v>2.7</v>
       </c>
       <c r="R42">
-        <v>2.18</v>
+        <v>2.35</v>
       </c>
       <c r="S42">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="T42">
-        <v>3.02</v>
+        <v>3.3</v>
       </c>
       <c r="U42">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="V42">
-        <v>1.44</v>
+        <v>1.47</v>
       </c>
       <c r="W42">
-        <v>1.06</v>
+        <v>1.11</v>
       </c>
       <c r="X42">
         <v>1.02</v>
       </c>
       <c r="Y42">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="Z42">
-        <v>4.1</v>
+        <v>4.22</v>
       </c>
       <c r="AA42">
-        <v>1.69</v>
+        <v>1.66</v>
       </c>
       <c r="AB42">
-        <v>2.09</v>
+        <v>2.08</v>
       </c>
       <c r="AC42">
-        <v>2.63</v>
+        <v>2.62</v>
       </c>
       <c r="AD42">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="AE42">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="AF42">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="AG42">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="AH42" t="inlineStr">
         <is>
@@ -7318,25 +7318,25 @@
         </is>
       </c>
       <c r="N43">
-        <v>2.7</v>
+        <v>2.65</v>
       </c>
       <c r="O43">
         <v>3.5</v>
       </c>
       <c r="P43">
+        <v>2.3</v>
+      </c>
+      <c r="Q43">
+        <v>3.3</v>
+      </c>
+      <c r="R43">
         <v>2.25</v>
-      </c>
-      <c r="Q43">
-        <v>3.35</v>
-      </c>
-      <c r="R43">
-        <v>2.2</v>
       </c>
       <c r="S43">
         <v>1.3</v>
       </c>
       <c r="T43">
-        <v>3.22</v>
+        <v>3.25</v>
       </c>
       <c r="U43">
         <v>2.4</v>
@@ -7345,25 +7345,25 @@
         <v>1.5</v>
       </c>
       <c r="W43">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="X43">
         <v>1.02</v>
       </c>
       <c r="Y43">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="Z43">
-        <v>4.15</v>
+        <v>4.2</v>
       </c>
       <c r="AA43">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="AB43">
         <v>2.05</v>
       </c>
       <c r="AC43">
-        <v>2.65</v>
+        <v>2.7</v>
       </c>
       <c r="AD43">
         <v>1.4</v>
@@ -7372,10 +7372,10 @@
         <v>1.11</v>
       </c>
       <c r="AF43">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="AG43">
-        <v>2.3</v>
+        <v>2.38</v>
       </c>
       <c r="AH43" t="inlineStr">
         <is>
@@ -7388,10 +7388,10 @@
         </is>
       </c>
       <c r="AJ43">
-        <v>1.57</v>
+        <v>1.27</v>
       </c>
       <c r="AK43">
-        <v>1.39</v>
+        <v>1.41</v>
       </c>
       <c r="AL43">
         <v>0</v>
@@ -7481,64 +7481,64 @@
         </is>
       </c>
       <c r="N44">
-        <v>1.83</v>
+        <v>1.7</v>
       </c>
       <c r="O44">
-        <v>3.52</v>
+        <v>3.4</v>
       </c>
       <c r="P44">
-        <v>4.59</v>
+        <v>4.85</v>
       </c>
       <c r="Q44">
-        <v>2.17</v>
+        <v>2.3</v>
       </c>
       <c r="R44">
-        <v>2.13</v>
+        <v>2.04</v>
       </c>
       <c r="S44">
-        <v>1.41</v>
+        <v>1.45</v>
       </c>
       <c r="T44">
-        <v>2.66</v>
+        <v>2.53</v>
       </c>
       <c r="U44">
-        <v>3.1</v>
+        <v>3.16</v>
       </c>
       <c r="V44">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="W44">
+        <v>1.02</v>
+      </c>
+      <c r="X44">
         <v>1.03</v>
       </c>
-      <c r="X44">
-        <v>1.02</v>
-      </c>
       <c r="Y44">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="Z44">
-        <v>2.74</v>
+        <v>2.69</v>
       </c>
       <c r="AA44">
-        <v>2.21</v>
+        <v>2.28</v>
       </c>
       <c r="AB44">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="AC44">
-        <v>3.88</v>
+        <v>3.95</v>
       </c>
       <c r="AD44">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AE44">
         <v>1.03</v>
       </c>
       <c r="AF44">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="AG44">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="AH44" t="inlineStr">
         <is>
@@ -7551,10 +7551,10 @@
         </is>
       </c>
       <c r="AJ44">
-        <v>1.24</v>
+        <v>1.26</v>
       </c>
       <c r="AK44">
-        <v>2.19</v>
+        <v>2.03</v>
       </c>
       <c r="AL44">
         <v>0</v>
@@ -7647,7 +7647,7 @@
         <v>1.49</v>
       </c>
       <c r="O45">
-        <v>4.33</v>
+        <v>4.2</v>
       </c>
       <c r="P45">
         <v>4.6</v>
@@ -7656,7 +7656,7 @@
         <v>1.91</v>
       </c>
       <c r="R45">
-        <v>2.39</v>
+        <v>2.5</v>
       </c>
       <c r="S45">
         <v>1.25</v>
@@ -7671,13 +7671,13 @@
         <v>1.57</v>
       </c>
       <c r="W45">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="X45">
         <v>1</v>
       </c>
       <c r="Y45">
-        <v>1.17</v>
+        <v>1.12</v>
       </c>
       <c r="Z45">
         <v>4.45</v>
@@ -7686,22 +7686,22 @@
         <v>1.54</v>
       </c>
       <c r="AB45">
-        <v>2.32</v>
+        <v>2.35</v>
       </c>
       <c r="AC45">
         <v>2.28</v>
       </c>
       <c r="AD45">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="AE45">
         <v>1.18</v>
       </c>
       <c r="AF45">
-        <v>1.56</v>
+        <v>1.65</v>
       </c>
       <c r="AG45">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="AH45" t="inlineStr">
         <is>
@@ -7714,7 +7714,7 @@
         </is>
       </c>
       <c r="AJ45">
-        <v>1.18</v>
+        <v>1.15</v>
       </c>
       <c r="AK45">
         <v>2.63</v>
@@ -7807,7 +7807,7 @@
         </is>
       </c>
       <c r="N46">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="O46">
         <v>4.2</v>
@@ -7816,71 +7816,71 @@
         <v>5</v>
       </c>
       <c r="Q46">
-        <v>1.96</v>
+        <v>1.98</v>
       </c>
       <c r="R46">
-        <v>2.55</v>
+        <v>2.54</v>
       </c>
       <c r="S46">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="T46">
-        <v>3.75</v>
+        <v>3.28</v>
       </c>
       <c r="U46">
         <v>2.26</v>
       </c>
       <c r="V46">
-        <v>1.59</v>
+        <v>1.56</v>
       </c>
       <c r="W46">
-        <v>1.1</v>
+        <v>1.15</v>
       </c>
       <c r="X46">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y46">
+        <v>1.12</v>
+      </c>
+      <c r="Z46">
+        <v>4.75</v>
+      </c>
+      <c r="AA46">
+        <v>1.53</v>
+      </c>
+      <c r="AB46">
+        <v>2.38</v>
+      </c>
+      <c r="AC46">
+        <v>2.36</v>
+      </c>
+      <c r="AD46">
+        <v>1.55</v>
+      </c>
+      <c r="AE46">
+        <v>1.17</v>
+      </c>
+      <c r="AF46">
+        <v>1.62</v>
+      </c>
+      <c r="AG46">
+        <v>2.2</v>
+      </c>
+      <c r="AH46" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI46" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ46">
         <v>1.14</v>
       </c>
-      <c r="Z46">
-        <v>5.5</v>
-      </c>
-      <c r="AA46">
-        <v>1.55</v>
-      </c>
-      <c r="AB46">
-        <v>2.3</v>
-      </c>
-      <c r="AC46">
-        <v>2.35</v>
-      </c>
-      <c r="AD46">
-        <v>1.56</v>
-      </c>
-      <c r="AE46">
-        <v>1.22</v>
-      </c>
-      <c r="AF46">
-        <v>1.67</v>
-      </c>
-      <c r="AG46">
-        <v>2.1</v>
-      </c>
-      <c r="AH46" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI46" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ46">
-        <v>1.08</v>
-      </c>
       <c r="AK46">
-        <v>2.4</v>
+        <v>2.43</v>
       </c>
       <c r="AL46">
         <v>0</v>
@@ -7973,16 +7973,16 @@
         <v>4.85</v>
       </c>
       <c r="O47">
-        <v>4.3</v>
+        <v>4.7</v>
       </c>
       <c r="P47">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="Q47">
-        <v>4.78</v>
+        <v>3.67</v>
       </c>
       <c r="R47">
-        <v>2.63</v>
+        <v>2.56</v>
       </c>
       <c r="S47">
         <v>1.14</v>
@@ -8015,10 +8015,10 @@
         <v>3.34</v>
       </c>
       <c r="AC47">
-        <v>1.91</v>
+        <v>1.75</v>
       </c>
       <c r="AD47">
-        <v>2.1</v>
+        <v>2.03</v>
       </c>
       <c r="AE47">
         <v>1.47</v>
@@ -8040,10 +8040,10 @@
         </is>
       </c>
       <c r="AJ47">
-        <v>1.16</v>
+        <v>2.43</v>
       </c>
       <c r="AK47">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="AL47">
         <v>0</v>
@@ -8133,19 +8133,19 @@
         </is>
       </c>
       <c r="N48">
+        <v>2.2</v>
+      </c>
+      <c r="O48">
+        <v>3.35</v>
+      </c>
+      <c r="P48">
+        <v>2.73</v>
+      </c>
+      <c r="Q48">
+        <v>2.8</v>
+      </c>
+      <c r="R48">
         <v>2.28</v>
-      </c>
-      <c r="O48">
-        <v>3.4</v>
-      </c>
-      <c r="P48">
-        <v>2.79</v>
-      </c>
-      <c r="Q48">
-        <v>2.81</v>
-      </c>
-      <c r="R48">
-        <v>2.2</v>
       </c>
       <c r="S48">
         <v>1.3</v>
@@ -8160,28 +8160,28 @@
         <v>1.46</v>
       </c>
       <c r="W48">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="X48">
         <v>1</v>
       </c>
       <c r="Y48">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="Z48">
-        <v>3.85</v>
+        <v>3.84</v>
       </c>
       <c r="AA48">
-        <v>1.7</v>
+        <v>1.68</v>
       </c>
       <c r="AB48">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="AC48">
-        <v>2.6</v>
+        <v>2.59</v>
       </c>
       <c r="AD48">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="AE48">
         <v>1.12</v>
@@ -8206,7 +8206,7 @@
         <v>1.23</v>
       </c>
       <c r="AK48">
-        <v>1.57</v>
+        <v>1.48</v>
       </c>
       <c r="AL48">
         <v>0</v>
@@ -8296,34 +8296,34 @@
         </is>
       </c>
       <c r="N49">
-        <v>1.59</v>
+        <v>1.55</v>
       </c>
       <c r="O49">
-        <v>3.8</v>
+        <v>3.65</v>
       </c>
       <c r="P49">
-        <v>5.02</v>
+        <v>4.98</v>
       </c>
       <c r="Q49">
-        <v>2.15</v>
+        <v>2.13</v>
       </c>
       <c r="R49">
-        <v>2.17</v>
+        <v>2.2</v>
       </c>
       <c r="S49">
         <v>1.34</v>
       </c>
       <c r="T49">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="U49">
         <v>2.45</v>
       </c>
       <c r="V49">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="W49">
-        <v>1.1</v>
+        <v>1.06</v>
       </c>
       <c r="X49">
         <v>1</v>
@@ -8335,16 +8335,16 @@
         <v>3.45</v>
       </c>
       <c r="AA49">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="AB49">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="AC49">
-        <v>3</v>
+        <v>2.85</v>
       </c>
       <c r="AD49">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="AE49">
         <v>1.08</v>
@@ -8366,10 +8366,10 @@
         </is>
       </c>
       <c r="AJ49">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="AK49">
-        <v>2.3</v>
+        <v>2.18</v>
       </c>
       <c r="AL49">
         <v>0</v>
@@ -8459,31 +8459,31 @@
         </is>
       </c>
       <c r="N50">
-        <v>0</v>
+        <v>6.14</v>
       </c>
       <c r="O50">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="P50">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="Q50">
-        <v>6.25</v>
+        <v>5.75</v>
       </c>
       <c r="R50">
-        <v>2.36</v>
+        <v>2.6</v>
       </c>
       <c r="S50">
         <v>1.27</v>
       </c>
       <c r="T50">
-        <v>3.25</v>
+        <v>3.75</v>
       </c>
       <c r="U50">
-        <v>2.25</v>
+        <v>2.12</v>
       </c>
       <c r="V50">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="W50">
         <v>1.09</v>
@@ -8492,16 +8492,16 @@
         <v>1.01</v>
       </c>
       <c r="Y50">
-        <v>1.18</v>
+        <v>1.12</v>
       </c>
       <c r="Z50">
         <v>4.65</v>
       </c>
       <c r="AA50">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="AB50">
-        <v>2.3</v>
+        <v>2.29</v>
       </c>
       <c r="AC50">
         <v>2.38</v>
@@ -8622,31 +8622,31 @@
         </is>
       </c>
       <c r="N51">
-        <v>1.87</v>
+        <v>1.94</v>
       </c>
       <c r="O51">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="P51">
-        <v>3.4</v>
+        <v>3.71</v>
       </c>
       <c r="Q51">
         <v>2.41</v>
       </c>
       <c r="R51">
-        <v>2.23</v>
+        <v>2.22</v>
       </c>
       <c r="S51">
-        <v>1.29</v>
+        <v>1.32</v>
       </c>
       <c r="T51">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="U51">
         <v>2.4</v>
       </c>
       <c r="V51">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="W51">
         <v>1.11</v>
@@ -8655,16 +8655,16 @@
         <v>1</v>
       </c>
       <c r="Y51">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="Z51">
-        <v>4.28</v>
+        <v>4.4</v>
       </c>
       <c r="AA51">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="AB51">
-        <v>2.16</v>
+        <v>2.17</v>
       </c>
       <c r="AC51">
         <v>2.65</v>
@@ -8673,7 +8673,7 @@
         <v>1.46</v>
       </c>
       <c r="AE51">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="AF51">
         <v>1.59</v>
@@ -8692,7 +8692,7 @@
         </is>
       </c>
       <c r="AJ51">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AK51">
         <v>1.86</v>
@@ -8951,13 +8951,13 @@
         <v>2</v>
       </c>
       <c r="O53">
-        <v>3.75</v>
+        <v>3.5</v>
       </c>
       <c r="P53">
         <v>2.8</v>
       </c>
       <c r="Q53">
-        <v>2.6</v>
+        <v>2.56</v>
       </c>
       <c r="R53">
         <v>2.5</v>
@@ -8969,7 +8969,7 @@
         <v>3.5</v>
       </c>
       <c r="U53">
-        <v>2.32</v>
+        <v>2.2</v>
       </c>
       <c r="V53">
         <v>1.55</v>
@@ -9005,7 +9005,7 @@
         <v>1.48</v>
       </c>
       <c r="AG53">
-        <v>2.45</v>
+        <v>2.47</v>
       </c>
       <c r="AH53" t="inlineStr">
         <is>
@@ -9021,7 +9021,7 @@
         <v>1.24</v>
       </c>
       <c r="AK53">
-        <v>1.72</v>
+        <v>1.75</v>
       </c>
       <c r="AL53">
         <v>0</v>
@@ -9111,13 +9111,13 @@
         </is>
       </c>
       <c r="N54">
-        <v>3.61</v>
+        <v>3.4</v>
       </c>
       <c r="O54">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="P54">
-        <v>1.85</v>
+        <v>1.97</v>
       </c>
       <c r="Q54">
         <v>3.85</v>
@@ -9126,49 +9126,49 @@
         <v>2.25</v>
       </c>
       <c r="S54">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="T54">
-        <v>3.15</v>
+        <v>3.3</v>
       </c>
       <c r="U54">
-        <v>2.47</v>
+        <v>2.57</v>
       </c>
       <c r="V54">
-        <v>1.48</v>
+        <v>1.45</v>
       </c>
       <c r="W54">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="X54">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y54">
         <v>1.22</v>
       </c>
       <c r="Z54">
-        <v>4.21</v>
+        <v>4.25</v>
       </c>
       <c r="AA54">
         <v>1.73</v>
       </c>
       <c r="AB54">
-        <v>2.13</v>
+        <v>2.14</v>
       </c>
       <c r="AC54">
-        <v>2.75</v>
+        <v>2.88</v>
       </c>
       <c r="AD54">
-        <v>1.38</v>
+        <v>1.44</v>
       </c>
       <c r="AE54">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="AF54">
         <v>1.63</v>
       </c>
       <c r="AG54">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="AH54" t="inlineStr">
         <is>
@@ -9274,19 +9274,19 @@
         </is>
       </c>
       <c r="N55">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="O55">
-        <v>4.8</v>
+        <v>4.45</v>
       </c>
       <c r="P55">
-        <v>5.55</v>
+        <v>6</v>
       </c>
       <c r="Q55">
-        <v>1.91</v>
+        <v>1.85</v>
       </c>
       <c r="R55">
-        <v>2.53</v>
+        <v>2.37</v>
       </c>
       <c r="S55">
         <v>1.22</v>
@@ -9295,10 +9295,10 @@
         <v>3.6</v>
       </c>
       <c r="U55">
-        <v>2.15</v>
+        <v>2.28</v>
       </c>
       <c r="V55">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="W55">
         <v>1.12</v>
@@ -9307,28 +9307,28 @@
         <v>1.02</v>
       </c>
       <c r="Y55">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="Z55">
-        <v>5.13</v>
+        <v>5.14</v>
       </c>
       <c r="AA55">
         <v>1.53</v>
       </c>
       <c r="AB55">
-        <v>2.33</v>
+        <v>2.52</v>
       </c>
       <c r="AC55">
-        <v>2.28</v>
+        <v>2.2</v>
       </c>
       <c r="AD55">
-        <v>1.53</v>
+        <v>1.56</v>
       </c>
       <c r="AE55">
         <v>1.19</v>
       </c>
       <c r="AF55">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
       <c r="AG55">
         <v>2.15</v>
@@ -9344,7 +9344,7 @@
         </is>
       </c>
       <c r="AJ55">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="AK55">
         <v>2.66</v>
@@ -9437,13 +9437,13 @@
         </is>
       </c>
       <c r="N56">
-        <v>2.45</v>
+        <v>2.4</v>
       </c>
       <c r="O56">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="P56">
-        <v>2.45</v>
+        <v>2.43</v>
       </c>
       <c r="Q56">
         <v>2.78</v>
@@ -9458,37 +9458,37 @@
         <v>3.3</v>
       </c>
       <c r="U56">
-        <v>2.33</v>
+        <v>2.38</v>
       </c>
       <c r="V56">
         <v>1.53</v>
       </c>
       <c r="W56">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="X56">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y56">
         <v>1.18</v>
       </c>
       <c r="Z56">
-        <v>4.5</v>
+        <v>4.33</v>
       </c>
       <c r="AA56">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="AB56">
-        <v>2.3</v>
+        <v>2.13</v>
       </c>
       <c r="AC56">
-        <v>2.51</v>
+        <v>2.46</v>
       </c>
       <c r="AD56">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="AE56">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="AF56">
         <v>1.5</v>
@@ -9763,13 +9763,13 @@
         </is>
       </c>
       <c r="N58">
-        <v>3.31</v>
+        <v>3.5</v>
       </c>
       <c r="O58">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="P58">
-        <v>1.98</v>
+        <v>1.99</v>
       </c>
       <c r="Q58">
         <v>3.94</v>
@@ -9778,7 +9778,7 @@
         <v>2.24</v>
       </c>
       <c r="S58">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="T58">
         <v>3.22</v>
@@ -9793,19 +9793,19 @@
         <v>1.08</v>
       </c>
       <c r="X58">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y58">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="Z58">
-        <v>4.05</v>
+        <v>4.33</v>
       </c>
       <c r="AA58">
         <v>1.66</v>
       </c>
       <c r="AB58">
-        <v>2.19</v>
+        <v>2.08</v>
       </c>
       <c r="AC58">
         <v>2.67</v>
@@ -9817,10 +9817,10 @@
         <v>1.18</v>
       </c>
       <c r="AF58">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="AG58">
-        <v>2.26</v>
+        <v>2.25</v>
       </c>
       <c r="AH58" t="inlineStr">
         <is>
@@ -9833,7 +9833,7 @@
         </is>
       </c>
       <c r="AJ58">
-        <v>1.27</v>
+        <v>1.22</v>
       </c>
       <c r="AK58">
         <v>1.29</v>
@@ -9935,34 +9935,34 @@
         <v>4.72</v>
       </c>
       <c r="Q59">
+        <v>2.14</v>
+      </c>
+      <c r="R59">
         <v>2.22</v>
       </c>
-      <c r="R59">
-        <v>2.45</v>
-      </c>
       <c r="S59">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="T59">
-        <v>2.94</v>
+        <v>3.3</v>
       </c>
       <c r="U59">
-        <v>2.4</v>
+        <v>2.55</v>
       </c>
       <c r="V59">
-        <v>1.45</v>
+        <v>1.49</v>
       </c>
       <c r="W59">
         <v>1.08</v>
       </c>
       <c r="X59">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y59">
-        <v>1.19</v>
+        <v>1.21</v>
       </c>
       <c r="Z59">
-        <v>4.1</v>
+        <v>3.82</v>
       </c>
       <c r="AA59">
         <v>1.7</v>
@@ -9971,19 +9971,19 @@
         <v>2.1</v>
       </c>
       <c r="AC59">
-        <v>2.7</v>
+        <v>2.75</v>
       </c>
       <c r="AD59">
         <v>1.42</v>
       </c>
       <c r="AE59">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AF59">
-        <v>1.66</v>
+        <v>1.73</v>
       </c>
       <c r="AG59">
-        <v>2.09</v>
+        <v>1.95</v>
       </c>
       <c r="AH59" t="inlineStr">
         <is>
@@ -10092,31 +10092,31 @@
         <v>1.61</v>
       </c>
       <c r="O60">
-        <v>3.9</v>
+        <v>4.2</v>
       </c>
       <c r="P60">
         <v>4</v>
       </c>
       <c r="Q60">
+        <v>2</v>
+      </c>
+      <c r="R60">
+        <v>2.44</v>
+      </c>
+      <c r="S60">
+        <v>1.22</v>
+      </c>
+      <c r="T60">
+        <v>4</v>
+      </c>
+      <c r="U60">
         <v>2.11</v>
       </c>
-      <c r="R60">
-        <v>2.36</v>
-      </c>
-      <c r="S60">
-        <v>1.23</v>
-      </c>
-      <c r="T60">
-        <v>3.58</v>
-      </c>
-      <c r="U60">
-        <v>2</v>
-      </c>
       <c r="V60">
-        <v>1.73</v>
+        <v>1.68</v>
       </c>
       <c r="W60">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="X60">
         <v>1.02</v>
@@ -10131,19 +10131,19 @@
         <v>1.4</v>
       </c>
       <c r="AB60">
-        <v>2.77</v>
+        <v>2.64</v>
       </c>
       <c r="AC60">
-        <v>2.08</v>
+        <v>2.12</v>
       </c>
       <c r="AD60">
-        <v>1.76</v>
+        <v>1.73</v>
       </c>
       <c r="AE60">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="AF60">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="AG60">
         <v>2.55</v>
@@ -10255,13 +10255,13 @@
         <v>1.14</v>
       </c>
       <c r="O61">
-        <v>7.5</v>
+        <v>7.75</v>
       </c>
       <c r="P61">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="Q61">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="R61">
         <v>2.83</v>
@@ -10273,10 +10273,10 @@
         <v>5</v>
       </c>
       <c r="U61">
-        <v>1.77</v>
+        <v>1.94</v>
       </c>
       <c r="V61">
-        <v>1.75</v>
+        <v>1.9</v>
       </c>
       <c r="W61">
         <v>1.25</v>
@@ -10285,31 +10285,31 @@
         <v>1.01</v>
       </c>
       <c r="Y61">
-        <v>1.1</v>
+        <v>1.07</v>
       </c>
       <c r="Z61">
-        <v>5.3</v>
+        <v>5.95</v>
       </c>
       <c r="AA61">
-        <v>1.29</v>
+        <v>1.36</v>
       </c>
       <c r="AB61">
-        <v>3.5</v>
+        <v>2.75</v>
       </c>
       <c r="AC61">
         <v>1.94</v>
       </c>
       <c r="AD61">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="AE61">
-        <v>1.37</v>
+        <v>1.42</v>
       </c>
       <c r="AF61">
-        <v>2.03</v>
+        <v>2.1</v>
       </c>
       <c r="AG61">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="AH61" t="inlineStr">
         <is>
@@ -10322,10 +10322,10 @@
         </is>
       </c>
       <c r="AJ61">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="AK61">
-        <v>4</v>
+        <v>4.85</v>
       </c>
       <c r="AL61">
         <v>0</v>
@@ -10430,10 +10430,10 @@
         <v>2.05</v>
       </c>
       <c r="S62">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="T62">
-        <v>2.69</v>
+        <v>2.56</v>
       </c>
       <c r="U62">
         <v>2.88</v>
@@ -10442,13 +10442,13 @@
         <v>1.36</v>
       </c>
       <c r="W62">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="X62">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="Y62">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="Z62">
         <v>2.99</v>
@@ -10457,16 +10457,16 @@
         <v>2.08</v>
       </c>
       <c r="AB62">
-        <v>1.68</v>
+        <v>1.75</v>
       </c>
       <c r="AC62">
-        <v>3.38</v>
+        <v>3.5</v>
       </c>
       <c r="AD62">
-        <v>1.27</v>
+        <v>1.24</v>
       </c>
       <c r="AE62">
-        <v>1.06</v>
+        <v>1.09</v>
       </c>
       <c r="AF62">
         <v>1.75</v>
@@ -10578,25 +10578,25 @@
         </is>
       </c>
       <c r="N63">
-        <v>2.22</v>
+        <v>2.29</v>
       </c>
       <c r="O63">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="P63">
-        <v>2.63</v>
+        <v>2.85</v>
       </c>
       <c r="Q63">
-        <v>2.88</v>
+        <v>2.75</v>
       </c>
       <c r="R63">
-        <v>2.14</v>
+        <v>2.25</v>
       </c>
       <c r="S63">
         <v>1.3</v>
       </c>
       <c r="T63">
-        <v>3.2</v>
+        <v>2.8</v>
       </c>
       <c r="U63">
         <v>2.5</v>
@@ -10608,28 +10608,28 @@
         <v>1.07</v>
       </c>
       <c r="X63">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y63">
         <v>1.25</v>
       </c>
       <c r="Z63">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="AA63">
         <v>1.79</v>
       </c>
       <c r="AB63">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="AC63">
         <v>3.02</v>
       </c>
       <c r="AD63">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AE63">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="AF63">
         <v>1.67</v>
@@ -10741,13 +10741,13 @@
         </is>
       </c>
       <c r="N64">
-        <v>1.28</v>
+        <v>1.34</v>
       </c>
       <c r="O64">
-        <v>4.75</v>
+        <v>5</v>
       </c>
       <c r="P64">
-        <v>5.8</v>
+        <v>5.75</v>
       </c>
       <c r="Q64">
         <v>1.67</v>
@@ -10756,25 +10756,25 @@
         <v>2.88</v>
       </c>
       <c r="S64">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="T64">
-        <v>4.6</v>
+        <v>4.75</v>
       </c>
       <c r="U64">
-        <v>1.77</v>
+        <v>1.85</v>
       </c>
       <c r="V64">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="W64">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="X64">
         <v>1.01</v>
       </c>
       <c r="Y64">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="Z64">
         <v>6.5</v>
@@ -10783,16 +10783,16 @@
         <v>1.29</v>
       </c>
       <c r="AB64">
-        <v>3.14</v>
+        <v>3.25</v>
       </c>
       <c r="AC64">
-        <v>1.73</v>
+        <v>1.77</v>
       </c>
       <c r="AD64">
-        <v>1.98</v>
+        <v>1.95</v>
       </c>
       <c r="AE64">
-        <v>1.39</v>
+        <v>1.43</v>
       </c>
       <c r="AF64">
         <v>1.47</v>
@@ -10907,61 +10907,61 @@
         <v>1.93</v>
       </c>
       <c r="O65">
-        <v>3.75</v>
+        <v>3.33</v>
       </c>
       <c r="P65">
-        <v>3.05</v>
+        <v>2.78</v>
       </c>
       <c r="Q65">
-        <v>2.38</v>
+        <v>2.33</v>
       </c>
       <c r="R65">
         <v>2.5</v>
       </c>
       <c r="S65">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="T65">
         <v>3.44</v>
       </c>
       <c r="U65">
-        <v>2.2</v>
+        <v>2.17</v>
       </c>
       <c r="V65">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="W65">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="X65">
         <v>1.01</v>
       </c>
       <c r="Y65">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="Z65">
-        <v>5.5</v>
+        <v>4.75</v>
       </c>
       <c r="AA65">
-        <v>1.51</v>
+        <v>1.45</v>
       </c>
       <c r="AB65">
-        <v>2.47</v>
+        <v>2.5</v>
       </c>
       <c r="AC65">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="AD65">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="AE65">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="AF65">
         <v>1.5</v>
       </c>
       <c r="AG65">
-        <v>2.5</v>
+        <v>2.47</v>
       </c>
       <c r="AH65" t="inlineStr">
         <is>
@@ -10974,10 +10974,10 @@
         </is>
       </c>
       <c r="AJ65">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="AK65">
-        <v>1.83</v>
+        <v>1.76</v>
       </c>
       <c r="AL65">
         <v>0</v>
@@ -11067,16 +11067,16 @@
         </is>
       </c>
       <c r="N66">
-        <v>2.32</v>
+        <v>2.45</v>
       </c>
       <c r="O66">
-        <v>3.75</v>
+        <v>3.73</v>
       </c>
       <c r="P66">
-        <v>2.32</v>
+        <v>2.4</v>
       </c>
       <c r="Q66">
-        <v>2.8</v>
+        <v>2.64</v>
       </c>
       <c r="R66">
         <v>2.45</v>
@@ -11088,13 +11088,13 @@
         <v>3.95</v>
       </c>
       <c r="U66">
-        <v>1.92</v>
+        <v>1.9</v>
       </c>
       <c r="V66">
-        <v>1.84</v>
+        <v>1.78</v>
       </c>
       <c r="W66">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="X66">
         <v>1.01</v>
@@ -11109,22 +11109,22 @@
         <v>1.32</v>
       </c>
       <c r="AB66">
-        <v>3.25</v>
+        <v>3.13</v>
       </c>
       <c r="AC66">
         <v>1.94</v>
       </c>
       <c r="AD66">
-        <v>1.93</v>
+        <v>1.88</v>
       </c>
       <c r="AE66">
         <v>1.3</v>
       </c>
       <c r="AF66">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="AG66">
-        <v>3.08</v>
+        <v>2.88</v>
       </c>
       <c r="AH66" t="inlineStr">
         <is>
@@ -11230,16 +11230,16 @@
         </is>
       </c>
       <c r="N67">
-        <v>2.15</v>
+        <v>2</v>
       </c>
       <c r="O67">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="P67">
-        <v>2.75</v>
+        <v>3</v>
       </c>
       <c r="Q67">
-        <v>2.64</v>
+        <v>2.55</v>
       </c>
       <c r="R67">
         <v>2.38</v>
@@ -11251,7 +11251,7 @@
         <v>3.9</v>
       </c>
       <c r="U67">
-        <v>2.13</v>
+        <v>2.04</v>
       </c>
       <c r="V67">
         <v>1.67</v>
@@ -11263,31 +11263,31 @@
         <v>1.02</v>
       </c>
       <c r="Y67">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="Z67">
         <v>5.75</v>
       </c>
       <c r="AA67">
-        <v>1.46</v>
+        <v>1.42</v>
       </c>
       <c r="AB67">
-        <v>2.52</v>
+        <v>2.63</v>
       </c>
       <c r="AC67">
-        <v>2.14</v>
+        <v>2.15</v>
       </c>
       <c r="AD67">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="AE67">
-        <v>1.24</v>
+        <v>1.29</v>
       </c>
       <c r="AF67">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="AG67">
-        <v>2.8</v>
+        <v>2.7</v>
       </c>
       <c r="AH67" t="inlineStr">
         <is>
@@ -11300,10 +11300,10 @@
         </is>
       </c>
       <c r="AJ67">
-        <v>1.24</v>
+        <v>1.36</v>
       </c>
       <c r="AK67">
-        <v>1.6</v>
+        <v>1.56</v>
       </c>
       <c r="AL67">
         <v>0</v>
@@ -11393,13 +11393,13 @@
         </is>
       </c>
       <c r="N68">
-        <v>1.33</v>
+        <v>1.39</v>
       </c>
       <c r="O68">
-        <v>4.55</v>
+        <v>5</v>
       </c>
       <c r="P68">
-        <v>4.85</v>
+        <v>5.25</v>
       </c>
       <c r="Q68">
         <v>1.77</v>
@@ -11408,19 +11408,19 @@
         <v>2.8</v>
       </c>
       <c r="S68">
-        <v>1.15</v>
+        <v>1.18</v>
       </c>
       <c r="T68">
-        <v>4.33</v>
+        <v>4.4</v>
       </c>
       <c r="U68">
         <v>1.99</v>
       </c>
       <c r="V68">
-        <v>1.83</v>
+        <v>1.78</v>
       </c>
       <c r="W68">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="X68">
         <v>1.01</v>
@@ -11429,7 +11429,7 @@
         <v>1.1</v>
       </c>
       <c r="Z68">
-        <v>6.6</v>
+        <v>6.45</v>
       </c>
       <c r="AA68">
         <v>1.3</v>
@@ -11444,10 +11444,10 @@
         <v>1.87</v>
       </c>
       <c r="AE68">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AF68">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
       <c r="AG68">
         <v>2.44</v>
@@ -11463,10 +11463,10 @@
         </is>
       </c>
       <c r="AJ68">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="AK68">
-        <v>2.7</v>
+        <v>2.88</v>
       </c>
       <c r="AL68">
         <v>0</v>
@@ -11556,19 +11556,19 @@
         </is>
       </c>
       <c r="N69">
-        <v>4.5</v>
+        <v>3.97</v>
       </c>
       <c r="O69">
-        <v>4</v>
+        <v>4.33</v>
       </c>
       <c r="P69">
         <v>1.54</v>
       </c>
       <c r="Q69">
-        <v>4.5</v>
+        <v>4.2</v>
       </c>
       <c r="R69">
-        <v>2.7</v>
+        <v>2.65</v>
       </c>
       <c r="S69">
         <v>1.17</v>
@@ -11580,25 +11580,25 @@
         <v>1.94</v>
       </c>
       <c r="V69">
-        <v>1.75</v>
+        <v>1.79</v>
       </c>
       <c r="W69">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="X69">
         <v>1.01</v>
       </c>
       <c r="Y69">
-        <v>1.1</v>
+        <v>1.05</v>
       </c>
       <c r="Z69">
-        <v>6.47</v>
+        <v>6.5</v>
       </c>
       <c r="AA69">
-        <v>1.38</v>
+        <v>1.31</v>
       </c>
       <c r="AB69">
-        <v>2.7</v>
+        <v>2.92</v>
       </c>
       <c r="AC69">
         <v>1.96</v>
@@ -11610,10 +11610,10 @@
         <v>1.36</v>
       </c>
       <c r="AF69">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="AG69">
-        <v>2.73</v>
+        <v>2.65</v>
       </c>
       <c r="AH69" t="inlineStr">
         <is>
@@ -11626,10 +11626,10 @@
         </is>
       </c>
       <c r="AJ69">
-        <v>1.14</v>
+        <v>1.18</v>
       </c>
       <c r="AK69">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="AL69">
         <v>0</v>
@@ -11719,7 +11719,7 @@
         </is>
       </c>
       <c r="N70">
-        <v>1.57</v>
+        <v>1.48</v>
       </c>
       <c r="O70">
         <v>3.9</v>
@@ -11767,10 +11767,10 @@
         <v>3.5</v>
       </c>
       <c r="AD70">
-        <v>1.41</v>
+        <v>1.36</v>
       </c>
       <c r="AE70">
-        <v>1.09</v>
+        <v>1.13</v>
       </c>
       <c r="AF70">
         <v>1.8</v>
@@ -11882,13 +11882,13 @@
         </is>
       </c>
       <c r="N71">
-        <v>1.31</v>
+        <v>1.28</v>
       </c>
       <c r="O71">
-        <v>4.8</v>
+        <v>4.6</v>
       </c>
       <c r="P71">
-        <v>7.9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="Q71">
         <v>1.77</v>
@@ -12371,64 +12371,64 @@
         </is>
       </c>
       <c r="N74">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="O74">
-        <v>2.99</v>
+        <v>2.94</v>
       </c>
       <c r="P74">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="Q74">
-        <v>2.9</v>
+        <v>2.8</v>
       </c>
       <c r="R74">
-        <v>1.83</v>
+        <v>1.95</v>
       </c>
       <c r="S74">
         <v>1.5</v>
       </c>
       <c r="T74">
-        <v>2.5</v>
+        <v>2.33</v>
       </c>
       <c r="U74">
-        <v>3.48</v>
+        <v>3.35</v>
       </c>
       <c r="V74">
         <v>1.22</v>
       </c>
       <c r="W74">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="X74">
-        <v>1.07</v>
+        <v>1.11</v>
       </c>
       <c r="Y74">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="Z74">
-        <v>2.52</v>
+        <v>2.4</v>
       </c>
       <c r="AA74">
-        <v>2.59</v>
+        <v>2.46</v>
       </c>
       <c r="AB74">
-        <v>1.5</v>
+        <v>1.43</v>
       </c>
       <c r="AC74">
-        <v>4.75</v>
+        <v>5.5</v>
       </c>
       <c r="AD74">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="AE74">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="AF74">
         <v>2.09</v>
       </c>
       <c r="AG74">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="AH74" t="inlineStr">
         <is>
@@ -12441,10 +12441,10 @@
         </is>
       </c>
       <c r="AJ74">
-        <v>1.22</v>
+        <v>1.32</v>
       </c>
       <c r="AK74">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="AL74">
         <v>0</v>
@@ -12534,49 +12534,49 @@
         </is>
       </c>
       <c r="N75">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="O75">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="P75">
-        <v>2.62</v>
+        <v>2.55</v>
       </c>
       <c r="Q75">
-        <v>3.14</v>
+        <v>3.1</v>
       </c>
       <c r="R75">
         <v>2.1</v>
       </c>
       <c r="S75">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="T75">
-        <v>2.99</v>
+        <v>2.8</v>
       </c>
       <c r="U75">
-        <v>2.59</v>
+        <v>2.65</v>
       </c>
       <c r="V75">
-        <v>1.43</v>
+        <v>1.38</v>
       </c>
       <c r="W75">
-        <v>1.1</v>
+        <v>1.07</v>
       </c>
       <c r="X75">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="Y75">
         <v>1.26</v>
       </c>
       <c r="Z75">
-        <v>3.58</v>
+        <v>3.15</v>
       </c>
       <c r="AA75">
         <v>1.86</v>
       </c>
       <c r="AB75">
-        <v>1.95</v>
+        <v>1.91</v>
       </c>
       <c r="AC75">
         <v>3.1</v>
@@ -12585,13 +12585,13 @@
         <v>1.33</v>
       </c>
       <c r="AE75">
-        <v>1.12</v>
+        <v>1.1</v>
       </c>
       <c r="AF75">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="AG75">
-        <v>2.05</v>
+        <v>2.15</v>
       </c>
       <c r="AH75" t="inlineStr">
         <is>
@@ -12697,13 +12697,13 @@
         </is>
       </c>
       <c r="N76">
-        <v>2.5</v>
+        <v>2.8</v>
       </c>
       <c r="O76">
-        <v>3.13</v>
+        <v>3.1</v>
       </c>
       <c r="P76">
-        <v>2.37</v>
+        <v>2.4</v>
       </c>
       <c r="Q76">
         <v>3.35</v>
@@ -12742,7 +12742,7 @@
         <v>1.83</v>
       </c>
       <c r="AC76">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="AD76">
         <v>1.31</v>
@@ -12860,16 +12860,16 @@
         </is>
       </c>
       <c r="N77">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="O77">
-        <v>3.36</v>
+        <v>3.5</v>
       </c>
       <c r="P77">
-        <v>2.73</v>
+        <v>3</v>
       </c>
       <c r="Q77">
-        <v>2.81</v>
+        <v>2.82</v>
       </c>
       <c r="R77">
         <v>2.2</v>
@@ -12930,10 +12930,10 @@
         </is>
       </c>
       <c r="AJ77">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="AK77">
-        <v>1.61</v>
+        <v>1.56</v>
       </c>
       <c r="AL77">
         <v>0</v>
@@ -13023,10 +13023,10 @@
         </is>
       </c>
       <c r="N78">
-        <v>2.12</v>
+        <v>2.2</v>
       </c>
       <c r="O78">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="P78">
         <v>3.25</v>
@@ -13044,28 +13044,28 @@
         <v>2.75</v>
       </c>
       <c r="U78">
-        <v>3.3</v>
+        <v>2.88</v>
       </c>
       <c r="V78">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="W78">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="X78">
-        <v>1.08</v>
+        <v>1.04</v>
       </c>
       <c r="Y78">
-        <v>1.38</v>
+        <v>1.42</v>
       </c>
       <c r="Z78">
         <v>2.62</v>
       </c>
       <c r="AA78">
-        <v>2.25</v>
+        <v>2.34</v>
       </c>
       <c r="AB78">
-        <v>1.61</v>
+        <v>1.57</v>
       </c>
       <c r="AC78">
         <v>4</v>
@@ -13080,7 +13080,7 @@
         <v>1.9</v>
       </c>
       <c r="AG78">
-        <v>1.78</v>
+        <v>1.76</v>
       </c>
       <c r="AH78" t="inlineStr">
         <is>
@@ -13096,7 +13096,7 @@
         <v>1.34</v>
       </c>
       <c r="AK78">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="AL78">
         <v>0</v>
@@ -13512,64 +13512,64 @@
         </is>
       </c>
       <c r="N81">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="O81">
         <v>3.4</v>
       </c>
       <c r="P81">
-        <v>1.84</v>
+        <v>1.8</v>
       </c>
       <c r="Q81">
-        <v>4.6</v>
+        <v>4</v>
       </c>
       <c r="R81">
-        <v>2.11</v>
+        <v>2.25</v>
       </c>
       <c r="S81">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="T81">
-        <v>2.98</v>
+        <v>3.04</v>
       </c>
       <c r="U81">
-        <v>2.63</v>
+        <v>2.5</v>
       </c>
       <c r="V81">
-        <v>1.38</v>
+        <v>1.44</v>
       </c>
       <c r="W81">
         <v>1.09</v>
       </c>
       <c r="X81">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y81">
-        <v>1.22</v>
+        <v>1.19</v>
       </c>
       <c r="Z81">
-        <v>3.3</v>
+        <v>3.8</v>
       </c>
       <c r="AA81">
-        <v>1.86</v>
+        <v>1.75</v>
       </c>
       <c r="AB81">
-        <v>1.94</v>
+        <v>2.05</v>
       </c>
       <c r="AC81">
-        <v>2.97</v>
+        <v>2.78</v>
       </c>
       <c r="AD81">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="AE81">
-        <v>1.07</v>
+        <v>1.14</v>
       </c>
       <c r="AF81">
         <v>1.68</v>
       </c>
       <c r="AG81">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="AH81" t="inlineStr">
         <is>
@@ -13582,10 +13582,10 @@
         </is>
       </c>
       <c r="AJ81">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="AK81">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="AL81">
         <v>0</v>
@@ -13678,7 +13678,7 @@
         <v>1.79</v>
       </c>
       <c r="O82">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="P82">
         <v>4.46</v>
@@ -13690,37 +13690,37 @@
         <v>2.1</v>
       </c>
       <c r="S82">
-        <v>1.45</v>
+        <v>1.43</v>
       </c>
       <c r="T82">
-        <v>2.56</v>
+        <v>2.53</v>
       </c>
       <c r="U82">
-        <v>2.82</v>
+        <v>2.84</v>
       </c>
       <c r="V82">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="W82">
-        <v>1.07</v>
+        <v>1.02</v>
       </c>
       <c r="X82">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y82">
         <v>1.33</v>
       </c>
       <c r="Z82">
-        <v>3</v>
+        <v>3.01</v>
       </c>
       <c r="AA82">
         <v>2.1</v>
       </c>
       <c r="AB82">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="AC82">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="AD82">
         <v>1.22</v>
@@ -13729,10 +13729,10 @@
         <v>1.05</v>
       </c>
       <c r="AF82">
-        <v>1.97</v>
+        <v>1.85</v>
       </c>
       <c r="AG82">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="AH82" t="inlineStr">
         <is>
@@ -13748,7 +13748,7 @@
         <v>1.2</v>
       </c>
       <c r="AK82">
-        <v>1.88</v>
+        <v>2.04</v>
       </c>
       <c r="AL82">
         <v>0</v>
@@ -13838,13 +13838,13 @@
         </is>
       </c>
       <c r="N83">
-        <v>2.98</v>
+        <v>3</v>
       </c>
       <c r="O83">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="P83">
-        <v>2.02</v>
+        <v>2.05</v>
       </c>
       <c r="Q83">
         <v>3.28</v>
@@ -13859,22 +13859,22 @@
         <v>3.18</v>
       </c>
       <c r="U83">
-        <v>2.44</v>
+        <v>2.3</v>
       </c>
       <c r="V83">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="W83">
         <v>1.13</v>
       </c>
       <c r="X83">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y83">
         <v>1.15</v>
       </c>
       <c r="Z83">
-        <v>4.3</v>
+        <v>4.33</v>
       </c>
       <c r="AA83">
         <v>1.57</v>
@@ -13883,7 +13883,7 @@
         <v>2.14</v>
       </c>
       <c r="AC83">
-        <v>2.5</v>
+        <v>2.55</v>
       </c>
       <c r="AD83">
         <v>1.47</v>
@@ -13895,7 +13895,7 @@
         <v>1.5</v>
       </c>
       <c r="AG83">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="AH83" t="inlineStr">
         <is>
@@ -13908,7 +13908,7 @@
         </is>
       </c>
       <c r="AJ83">
-        <v>1.3</v>
+        <v>1.22</v>
       </c>
       <c r="AK83">
         <v>1.33</v>
@@ -14001,22 +14001,22 @@
         </is>
       </c>
       <c r="N84">
-        <v>1.58</v>
+        <v>1.53</v>
       </c>
       <c r="O84">
-        <v>3.8</v>
+        <v>4.1</v>
       </c>
       <c r="P84">
-        <v>4.3</v>
+        <v>4.8</v>
       </c>
       <c r="Q84">
-        <v>2.08</v>
+        <v>1.95</v>
       </c>
       <c r="R84">
         <v>2.36</v>
       </c>
       <c r="S84">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="T84">
         <v>3.25</v>
@@ -14025,56 +14025,56 @@
         <v>2.25</v>
       </c>
       <c r="V84">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="W84">
-        <v>1.14</v>
+        <v>1.1</v>
       </c>
       <c r="X84">
         <v>1.01</v>
       </c>
       <c r="Y84">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="Z84">
-        <v>4.47</v>
+        <v>4.6</v>
       </c>
       <c r="AA84">
         <v>1.53</v>
       </c>
       <c r="AB84">
-        <v>2.26</v>
+        <v>2.15</v>
       </c>
       <c r="AC84">
-        <v>2.56</v>
+        <v>2.45</v>
       </c>
       <c r="AD84">
         <v>1.54</v>
       </c>
       <c r="AE84">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="AF84">
         <v>1.6</v>
       </c>
       <c r="AG84">
+        <v>2.12</v>
+      </c>
+      <c r="AH84" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI84" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ84">
+        <v>1.16</v>
+      </c>
+      <c r="AK84">
         <v>2.25</v>
-      </c>
-      <c r="AH84" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI84" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ84">
-        <v>1.11</v>
-      </c>
-      <c r="AK84">
-        <v>2.46</v>
       </c>
       <c r="AL84">
         <v>0</v>
@@ -14167,10 +14167,10 @@
         <v>11.7</v>
       </c>
       <c r="O85">
-        <v>5.75</v>
+        <v>5.7</v>
       </c>
       <c r="P85">
-        <v>1.24</v>
+        <v>1.19</v>
       </c>
       <c r="Q85">
         <v>7.61</v>
@@ -14182,46 +14182,46 @@
         <v>1.2</v>
       </c>
       <c r="T85">
-        <v>3.8</v>
+        <v>3.58</v>
       </c>
       <c r="U85">
-        <v>2.17</v>
+        <v>2.05</v>
       </c>
       <c r="V85">
         <v>1.65</v>
       </c>
       <c r="W85">
-        <v>1.17</v>
+        <v>1.13</v>
       </c>
       <c r="X85">
         <v>1.02</v>
       </c>
       <c r="Y85">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="Z85">
-        <v>5.15</v>
+        <v>5.1</v>
       </c>
       <c r="AA85">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="AB85">
-        <v>2.49</v>
+        <v>2.55</v>
       </c>
       <c r="AC85">
-        <v>2.14</v>
+        <v>2.07</v>
       </c>
       <c r="AD85">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="AE85">
-        <v>1.24</v>
+        <v>1.29</v>
       </c>
       <c r="AF85">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="AG85">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="AH85" t="inlineStr">
         <is>
@@ -14237,7 +14237,7 @@
         <v>1.11</v>
       </c>
       <c r="AK85">
-        <v>1.03</v>
+        <v>1</v>
       </c>
       <c r="AL85">
         <v>0</v>
@@ -14327,49 +14327,49 @@
         </is>
       </c>
       <c r="N86">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="O86">
-        <v>4.55</v>
+        <v>3.9</v>
       </c>
       <c r="P86">
         <v>4.8</v>
       </c>
       <c r="Q86">
-        <v>1.93</v>
+        <v>1.95</v>
       </c>
       <c r="R86">
-        <v>2.65</v>
+        <v>2.6</v>
       </c>
       <c r="S86">
-        <v>1.23</v>
+        <v>1.2</v>
       </c>
       <c r="T86">
-        <v>3.42</v>
+        <v>3.8</v>
       </c>
       <c r="U86">
         <v>2.18</v>
       </c>
       <c r="V86">
-        <v>1.67</v>
+        <v>1.64</v>
       </c>
       <c r="W86">
         <v>1.12</v>
       </c>
       <c r="X86">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y86">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="Z86">
         <v>4.95</v>
       </c>
       <c r="AA86">
-        <v>1.49</v>
+        <v>1.47</v>
       </c>
       <c r="AB86">
-        <v>2.51</v>
+        <v>2.63</v>
       </c>
       <c r="AC86">
         <v>2.24</v>
@@ -14381,10 +14381,10 @@
         <v>1.21</v>
       </c>
       <c r="AF86">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="AG86">
-        <v>2.3</v>
+        <v>2.31</v>
       </c>
       <c r="AH86" t="inlineStr">
         <is>
@@ -14397,10 +14397,10 @@
         </is>
       </c>
       <c r="AJ86">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="AK86">
-        <v>2.25</v>
+        <v>2.35</v>
       </c>
       <c r="AL86">
         <v>0</v>
@@ -14505,7 +14505,7 @@
         <v>2.4</v>
       </c>
       <c r="S87">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="T87">
         <v>3.42</v>
@@ -14517,10 +14517,10 @@
         <v>1.58</v>
       </c>
       <c r="W87">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="X87">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y87">
         <v>1.14</v>
@@ -14529,16 +14529,16 @@
         <v>4.8</v>
       </c>
       <c r="AA87">
-        <v>1.55</v>
+        <v>1.49</v>
       </c>
       <c r="AB87">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="AC87">
         <v>2.35</v>
       </c>
       <c r="AD87">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="AE87">
         <v>1.2</v>
@@ -14653,61 +14653,61 @@
         </is>
       </c>
       <c r="N88">
-        <v>1.22</v>
+        <v>1.33</v>
       </c>
       <c r="O88">
-        <v>5.35</v>
+        <v>4.8</v>
       </c>
       <c r="P88">
-        <v>7</v>
+        <v>7.75</v>
       </c>
       <c r="Q88">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
       <c r="R88">
-        <v>2.29</v>
+        <v>2.4</v>
       </c>
       <c r="S88">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="T88">
-        <v>2.82</v>
+        <v>3</v>
       </c>
       <c r="U88">
-        <v>2.63</v>
+        <v>2.62</v>
       </c>
       <c r="V88">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="W88">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="X88">
         <v>1.02</v>
       </c>
       <c r="Y88">
-        <v>1.26</v>
+        <v>1.22</v>
       </c>
       <c r="Z88">
-        <v>3.35</v>
+        <v>3.5</v>
       </c>
       <c r="AA88">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="AB88">
         <v>1.95</v>
       </c>
       <c r="AC88">
-        <v>3.1</v>
+        <v>2.9</v>
       </c>
       <c r="AD88">
         <v>1.36</v>
       </c>
       <c r="AE88">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="AF88">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="AG88">
         <v>1.62</v>
@@ -14816,19 +14816,19 @@
         </is>
       </c>
       <c r="N89">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="O89">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="P89">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="Q89">
-        <v>2.63</v>
+        <v>2.6</v>
       </c>
       <c r="R89">
-        <v>2.22</v>
+        <v>2.25</v>
       </c>
       <c r="S89">
         <v>1.28</v>
@@ -14849,31 +14849,31 @@
         <v>1.02</v>
       </c>
       <c r="Y89">
-        <v>1.2</v>
+        <v>1.15</v>
       </c>
       <c r="Z89">
-        <v>4.2</v>
+        <v>4.25</v>
       </c>
       <c r="AA89">
-        <v>1.61</v>
+        <v>1.63</v>
       </c>
       <c r="AB89">
-        <v>2.17</v>
+        <v>2.14</v>
       </c>
       <c r="AC89">
-        <v>2.49</v>
+        <v>2.52</v>
       </c>
       <c r="AD89">
         <v>1.48</v>
       </c>
       <c r="AE89">
-        <v>1.16</v>
+        <v>1.12</v>
       </c>
       <c r="AF89">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="AG89">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="AH89" t="inlineStr">
         <is>
@@ -14886,10 +14886,10 @@
         </is>
       </c>
       <c r="AJ89">
-        <v>1.22</v>
+        <v>1.26</v>
       </c>
       <c r="AK89">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="AL89">
         <v>0</v>
@@ -14979,7 +14979,7 @@
         </is>
       </c>
       <c r="N90">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="O90">
         <v>3.5</v>
@@ -14991,19 +14991,19 @@
         <v>2.6</v>
       </c>
       <c r="R90">
-        <v>2.25</v>
+        <v>2.45</v>
       </c>
       <c r="S90">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="T90">
-        <v>3.5</v>
+        <v>3.25</v>
       </c>
       <c r="U90">
-        <v>2.25</v>
+        <v>2.21</v>
       </c>
       <c r="V90">
-        <v>1.43</v>
+        <v>1.57</v>
       </c>
       <c r="W90">
         <v>1.13</v>
@@ -15015,13 +15015,13 @@
         <v>1.17</v>
       </c>
       <c r="Z90">
-        <v>3.5</v>
+        <v>4.5</v>
       </c>
       <c r="AA90">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="AB90">
-        <v>2.35</v>
+        <v>2.38</v>
       </c>
       <c r="AC90">
         <v>2.3</v>
@@ -15033,7 +15033,7 @@
         <v>1.16</v>
       </c>
       <c r="AF90">
-        <v>1.63</v>
+        <v>1.46</v>
       </c>
       <c r="AG90">
         <v>2.1</v>
@@ -15142,13 +15142,13 @@
         </is>
       </c>
       <c r="N91">
-        <v>3.08</v>
+        <v>3.3</v>
       </c>
       <c r="O91">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="P91">
-        <v>1.98</v>
+        <v>2.03</v>
       </c>
       <c r="Q91">
         <v>3.93</v>
@@ -15181,7 +15181,7 @@
         <v>3.8</v>
       </c>
       <c r="AA91">
-        <v>1.81</v>
+        <v>1.88</v>
       </c>
       <c r="AB91">
         <v>1.9</v>
@@ -15468,22 +15468,22 @@
         </is>
       </c>
       <c r="N93">
-        <v>3.35</v>
+        <v>3.9</v>
       </c>
       <c r="O93">
-        <v>3.3</v>
+        <v>2.8</v>
       </c>
       <c r="P93">
-        <v>1.91</v>
+        <v>2.08</v>
       </c>
       <c r="Q93">
         <v>3.75</v>
       </c>
       <c r="R93">
-        <v>1.95</v>
+        <v>2.27</v>
       </c>
       <c r="S93">
-        <v>1.41</v>
+        <v>1.34</v>
       </c>
       <c r="T93">
         <v>2.9</v>
@@ -15504,13 +15504,13 @@
         <v>1.21</v>
       </c>
       <c r="Z93">
-        <v>3.85</v>
+        <v>3.5</v>
       </c>
       <c r="AA93">
         <v>1.83</v>
       </c>
       <c r="AB93">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="AC93">
         <v>3.25</v>
@@ -15522,10 +15522,10 @@
         <v>1.1</v>
       </c>
       <c r="AF93">
-        <v>1.7</v>
+        <v>1.63</v>
       </c>
       <c r="AG93">
-        <v>2</v>
+        <v>2.14</v>
       </c>
       <c r="AH93" t="inlineStr">
         <is>
@@ -15541,7 +15541,7 @@
         <v>1.23</v>
       </c>
       <c r="AK93">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="AL93">
         <v>0</v>
@@ -15794,10 +15794,10 @@
         </is>
       </c>
       <c r="N95">
-        <v>1.78</v>
+        <v>1.81</v>
       </c>
       <c r="O95">
-        <v>3.35</v>
+        <v>3.54</v>
       </c>
       <c r="P95">
         <v>4.3</v>
@@ -15806,52 +15806,52 @@
         <v>2.4</v>
       </c>
       <c r="R95">
-        <v>2.11</v>
+        <v>2.15</v>
       </c>
       <c r="S95">
-        <v>1.39</v>
+        <v>1.36</v>
       </c>
       <c r="T95">
-        <v>2.77</v>
+        <v>2.88</v>
       </c>
       <c r="U95">
-        <v>2.72</v>
+        <v>2.96</v>
       </c>
       <c r="V95">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="W95">
         <v>1.05</v>
       </c>
       <c r="X95">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="Y95">
         <v>1.3</v>
       </c>
       <c r="Z95">
-        <v>3.36</v>
+        <v>3.12</v>
       </c>
       <c r="AA95">
-        <v>2.02</v>
+        <v>2.01</v>
       </c>
       <c r="AB95">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="AC95">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="AD95">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="AE95">
-        <v>1.05</v>
+        <v>1.1</v>
       </c>
       <c r="AF95">
         <v>1.84</v>
       </c>
       <c r="AG95">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="AH95" t="inlineStr">
         <is>
@@ -16283,34 +16283,34 @@
         </is>
       </c>
       <c r="N98">
-        <v>1.88</v>
+        <v>1.79</v>
       </c>
       <c r="O98">
-        <v>3.6</v>
+        <v>3.8</v>
       </c>
       <c r="P98">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="Q98">
         <v>2.2</v>
       </c>
       <c r="R98">
-        <v>2.4</v>
+        <v>2.31</v>
       </c>
       <c r="S98">
         <v>1.24</v>
       </c>
       <c r="T98">
-        <v>3.5</v>
+        <v>3.7</v>
       </c>
       <c r="U98">
-        <v>2.05</v>
+        <v>2.17</v>
       </c>
       <c r="V98">
-        <v>1.63</v>
+        <v>1.58</v>
       </c>
       <c r="W98">
-        <v>1.13</v>
+        <v>1.17</v>
       </c>
       <c r="X98">
         <v>1.02</v>
@@ -16325,16 +16325,16 @@
         <v>1.5</v>
       </c>
       <c r="AB98">
-        <v>2.62</v>
+        <v>2.55</v>
       </c>
       <c r="AC98">
         <v>2.22</v>
       </c>
       <c r="AD98">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="AE98">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="AF98">
         <v>1.4</v>
@@ -16353,7 +16353,7 @@
         </is>
       </c>
       <c r="AJ98">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="AK98">
         <v>1.95</v>
@@ -16455,49 +16455,49 @@
         <v>2.6</v>
       </c>
       <c r="Q99">
-        <v>2.94</v>
+        <v>2.98</v>
       </c>
       <c r="R99">
-        <v>2.11</v>
+        <v>2.14</v>
       </c>
       <c r="S99">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="T99">
-        <v>2.91</v>
+        <v>3.2</v>
       </c>
       <c r="U99">
-        <v>2.56</v>
+        <v>2.39</v>
       </c>
       <c r="V99">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="W99">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="X99">
         <v>1</v>
       </c>
       <c r="Y99">
-        <v>1.19</v>
+        <v>1.21</v>
       </c>
       <c r="Z99">
         <v>3.78</v>
       </c>
       <c r="AA99">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="AB99">
-        <v>2.03</v>
+        <v>2.08</v>
       </c>
       <c r="AC99">
-        <v>2.77</v>
+        <v>2.59</v>
       </c>
       <c r="AD99">
         <v>1.39</v>
       </c>
       <c r="AE99">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="AF99">
         <v>1.56</v>
@@ -16519,7 +16519,7 @@
         <v>1.26</v>
       </c>
       <c r="AK99">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="AL99">
         <v>0</v>
@@ -16618,7 +16618,7 @@
         <v>1.93</v>
       </c>
       <c r="Q100">
-        <v>4.37</v>
+        <v>4.59</v>
       </c>
       <c r="R100">
         <v>2.08</v>
@@ -16654,7 +16654,7 @@
         <v>1.93</v>
       </c>
       <c r="AC100">
-        <v>3.24</v>
+        <v>3.23</v>
       </c>
       <c r="AD100">
         <v>1.32</v>
@@ -16663,7 +16663,7 @@
         <v>1.08</v>
       </c>
       <c r="AF100">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="AG100">
         <v>1.95</v>
@@ -16778,7 +16778,7 @@
         <v>4.15</v>
       </c>
       <c r="P101">
-        <v>4.8</v>
+        <v>5.33</v>
       </c>
       <c r="Q101">
         <v>2.07</v>
@@ -16787,28 +16787,28 @@
         <v>2.52</v>
       </c>
       <c r="S101">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="T101">
-        <v>3.34</v>
+        <v>3.6</v>
       </c>
       <c r="U101">
-        <v>2.39</v>
+        <v>2.45</v>
       </c>
       <c r="V101">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="W101">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="X101">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y101">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="Z101">
-        <v>4.59</v>
+        <v>5</v>
       </c>
       <c r="AA101">
         <v>1.63</v>
@@ -16823,7 +16823,7 @@
         <v>1.43</v>
       </c>
       <c r="AE101">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="AF101">
         <v>1.73</v>
@@ -16842,10 +16842,10 @@
         </is>
       </c>
       <c r="AJ101">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="AK101">
-        <v>2.33</v>
+        <v>2.4</v>
       </c>
       <c r="AL101">
         <v>0</v>
@@ -16944,7 +16944,7 @@
         <v>1.97</v>
       </c>
       <c r="Q102">
-        <v>4.26</v>
+        <v>3.75</v>
       </c>
       <c r="R102">
         <v>2</v>
@@ -16953,46 +16953,46 @@
         <v>1.4</v>
       </c>
       <c r="T102">
-        <v>2.62</v>
+        <v>2.56</v>
       </c>
       <c r="U102">
-        <v>2.91</v>
+        <v>2.88</v>
       </c>
       <c r="V102">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="W102">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="X102">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="Y102">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="Z102">
-        <v>3.08</v>
+        <v>2.45</v>
       </c>
       <c r="AA102">
-        <v>1.82</v>
+        <v>2.1</v>
       </c>
       <c r="AB102">
-        <v>1.54</v>
+        <v>1.73</v>
       </c>
       <c r="AC102">
-        <v>3.5</v>
+        <v>3.8</v>
       </c>
       <c r="AD102">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AE102">
         <v>1.03</v>
       </c>
       <c r="AF102">
-        <v>1.79</v>
+        <v>1.67</v>
       </c>
       <c r="AG102">
-        <v>1.9</v>
+        <v>1.67</v>
       </c>
       <c r="AH102" t="inlineStr">
         <is>
@@ -17005,10 +17005,10 @@
         </is>
       </c>
       <c r="AJ102">
-        <v>1.64</v>
+        <v>1.25</v>
       </c>
       <c r="AK102">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AL102">
         <v>0</v>
@@ -17101,10 +17101,10 @@
         <v>1.62</v>
       </c>
       <c r="O103">
-        <v>3.75</v>
+        <v>4</v>
       </c>
       <c r="P103">
-        <v>4.25</v>
+        <v>4.2</v>
       </c>
       <c r="Q103">
         <v>2.1</v>
@@ -17113,16 +17113,16 @@
         <v>2.3</v>
       </c>
       <c r="S103">
-        <v>1.32</v>
+        <v>1.29</v>
       </c>
       <c r="T103">
-        <v>3.08</v>
+        <v>2.63</v>
       </c>
       <c r="U103">
-        <v>2.44</v>
+        <v>2.38</v>
       </c>
       <c r="V103">
-        <v>1.46</v>
+        <v>1.52</v>
       </c>
       <c r="W103">
         <v>1.07</v>
@@ -17131,31 +17131,31 @@
         <v>1.04</v>
       </c>
       <c r="Y103">
-        <v>1.15</v>
+        <v>1.22</v>
       </c>
       <c r="Z103">
-        <v>3</v>
+        <v>3.95</v>
       </c>
       <c r="AA103">
-        <v>1.73</v>
+        <v>1.66</v>
       </c>
       <c r="AB103">
-        <v>2.05</v>
+        <v>1.79</v>
       </c>
       <c r="AC103">
-        <v>2.8</v>
+        <v>2.88</v>
       </c>
       <c r="AD103">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="AE103">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="AF103">
-        <v>1.73</v>
+        <v>1.55</v>
       </c>
       <c r="AG103">
-        <v>2.04</v>
+        <v>2</v>
       </c>
       <c r="AH103" t="inlineStr">
         <is>
@@ -17168,10 +17168,10 @@
         </is>
       </c>
       <c r="AJ103">
-        <v>1.12</v>
+        <v>1.16</v>
       </c>
       <c r="AK103">
-        <v>2.05</v>
+        <v>2.16</v>
       </c>
       <c r="AL103">
         <v>0</v>
@@ -17261,13 +17261,13 @@
         </is>
       </c>
       <c r="N104">
-        <v>2.55</v>
+        <v>2.4</v>
       </c>
       <c r="O104">
-        <v>2.75</v>
+        <v>2.7</v>
       </c>
       <c r="P104">
-        <v>2.9</v>
+        <v>3.05</v>
       </c>
       <c r="Q104">
         <v>0</v>
@@ -17430,58 +17430,58 @@
         <v>2.5</v>
       </c>
       <c r="P105">
-        <v>3.85</v>
+        <v>3.5</v>
       </c>
       <c r="Q105">
         <v>3.1</v>
       </c>
       <c r="R105">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="S105">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="T105">
         <v>2.1</v>
       </c>
       <c r="U105">
-        <v>4.33</v>
+        <v>4.5</v>
       </c>
       <c r="V105">
-        <v>1.2</v>
+        <v>1.12</v>
       </c>
       <c r="W105">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="X105">
         <v>1.18</v>
       </c>
       <c r="Y105">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="Z105">
-        <v>1.96</v>
+        <v>1.94</v>
       </c>
       <c r="AA105">
-        <v>3.52</v>
+        <v>3.57</v>
       </c>
       <c r="AB105">
-        <v>1.27</v>
+        <v>1.24</v>
       </c>
       <c r="AC105">
-        <v>7.1</v>
+        <v>7.3</v>
       </c>
       <c r="AD105">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="AE105">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="AF105">
-        <v>2.54</v>
+        <v>2.5</v>
       </c>
       <c r="AG105">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="AH105" t="inlineStr">
         <is>
@@ -17494,10 +17494,10 @@
         </is>
       </c>
       <c r="AJ105">
-        <v>1.18</v>
+        <v>1.44</v>
       </c>
       <c r="AK105">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="AL105">
         <v>0</v>
@@ -17596,10 +17596,10 @@
         <v>3.3</v>
       </c>
       <c r="Q106">
-        <v>2.9</v>
+        <v>3.05</v>
       </c>
       <c r="R106">
-        <v>1.91</v>
+        <v>1.76</v>
       </c>
       <c r="S106">
         <v>1.64</v>
@@ -17617,13 +17617,13 @@
         <v>1.03</v>
       </c>
       <c r="X106">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="Y106">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="Z106">
-        <v>2.19</v>
+        <v>2.17</v>
       </c>
       <c r="AA106">
         <v>2.74</v>
@@ -17632,10 +17632,10 @@
         <v>1.37</v>
       </c>
       <c r="AC106">
-        <v>6.5</v>
+        <v>6.1</v>
       </c>
       <c r="AD106">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="AE106">
         <v>1.03</v>
@@ -17660,7 +17660,7 @@
         <v>1.21</v>
       </c>
       <c r="AK106">
-        <v>1.54</v>
+        <v>1.57</v>
       </c>
       <c r="AL106">
         <v>0</v>
@@ -17750,52 +17750,52 @@
         </is>
       </c>
       <c r="N107">
-        <v>2.17</v>
+        <v>2.2</v>
       </c>
       <c r="O107">
-        <v>2.7</v>
+        <v>2.65</v>
       </c>
       <c r="P107">
-        <v>3.65</v>
+        <v>3.4</v>
       </c>
       <c r="Q107">
-        <v>3.05</v>
+        <v>2.94</v>
       </c>
       <c r="R107">
-        <v>1.9</v>
+        <v>1.7</v>
       </c>
       <c r="S107">
         <v>1.58</v>
       </c>
       <c r="T107">
-        <v>2.18</v>
+        <v>2.04</v>
       </c>
       <c r="U107">
-        <v>4.45</v>
+        <v>4.5</v>
       </c>
       <c r="V107">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="W107">
         <v>1.03</v>
       </c>
       <c r="X107">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="Y107">
-        <v>1.75</v>
+        <v>1.67</v>
       </c>
       <c r="Z107">
-        <v>1.96</v>
+        <v>2.15</v>
       </c>
       <c r="AA107">
-        <v>3.5</v>
+        <v>3.2</v>
       </c>
       <c r="AB107">
-        <v>1.36</v>
+        <v>1.28</v>
       </c>
       <c r="AC107">
-        <v>5.4</v>
+        <v>6.5</v>
       </c>
       <c r="AD107">
         <v>1.1</v>
@@ -17804,7 +17804,7 @@
         <v>1.02</v>
       </c>
       <c r="AF107">
-        <v>2.54</v>
+        <v>2.5</v>
       </c>
       <c r="AG107">
         <v>1.44</v>
@@ -17820,10 +17820,10 @@
         </is>
       </c>
       <c r="AJ107">
-        <v>1.25</v>
+        <v>1.38</v>
       </c>
       <c r="AK107">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="AL107">
         <v>0</v>
@@ -17913,31 +17913,31 @@
         </is>
       </c>
       <c r="N108">
-        <v>2.4</v>
+        <v>2.25</v>
       </c>
       <c r="O108">
         <v>3.3</v>
       </c>
       <c r="P108">
-        <v>2.8</v>
+        <v>2.95</v>
       </c>
       <c r="Q108">
         <v>2.81</v>
       </c>
       <c r="R108">
-        <v>2.04</v>
+        <v>2.09</v>
       </c>
       <c r="S108">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="T108">
         <v>2.88</v>
       </c>
       <c r="U108">
-        <v>2.85</v>
+        <v>2.84</v>
       </c>
       <c r="V108">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="W108">
         <v>1.05</v>
@@ -17949,16 +17949,16 @@
         <v>1.28</v>
       </c>
       <c r="Z108">
-        <v>3.5</v>
+        <v>3.51</v>
       </c>
       <c r="AA108">
-        <v>1.87</v>
+        <v>1.95</v>
       </c>
       <c r="AB108">
-        <v>1.85</v>
+        <v>1.89</v>
       </c>
       <c r="AC108">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="AD108">
         <v>1.29</v>
@@ -17967,10 +17967,10 @@
         <v>1.08</v>
       </c>
       <c r="AF108">
-        <v>1.66</v>
+        <v>1.7</v>
       </c>
       <c r="AG108">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AH108" t="inlineStr">
         <is>
@@ -17983,10 +17983,10 @@
         </is>
       </c>
       <c r="AJ108">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="AK108">
-        <v>1.53</v>
+        <v>1.49</v>
       </c>
       <c r="AL108">
         <v>0</v>
@@ -18076,13 +18076,13 @@
         </is>
       </c>
       <c r="N109">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="O109">
         <v>4.8</v>
       </c>
       <c r="P109">
-        <v>7.5</v>
+        <v>7.1</v>
       </c>
       <c r="Q109">
         <v>1.75</v>
@@ -18112,7 +18112,7 @@
         <v>1.22</v>
       </c>
       <c r="Z109">
-        <v>3.98</v>
+        <v>4</v>
       </c>
       <c r="AA109">
         <v>1.68</v>
@@ -18728,58 +18728,58 @@
         </is>
       </c>
       <c r="N113">
-        <v>3.9</v>
+        <v>3.5</v>
       </c>
       <c r="O113">
         <v>3.45</v>
       </c>
       <c r="P113">
-        <v>1.84</v>
+        <v>1.78</v>
       </c>
       <c r="Q113">
-        <v>4.82</v>
+        <v>4.93</v>
       </c>
       <c r="R113">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="S113">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="T113">
-        <v>3.16</v>
+        <v>2.82</v>
       </c>
       <c r="U113">
-        <v>2.68</v>
+        <v>2.63</v>
       </c>
       <c r="V113">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="W113">
         <v>1.1</v>
       </c>
       <c r="X113">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="Y113">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="Z113">
-        <v>3.6</v>
+        <v>3.76</v>
       </c>
       <c r="AA113">
-        <v>1.76</v>
+        <v>1.8</v>
       </c>
       <c r="AB113">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AC113">
-        <v>2.95</v>
+        <v>3.1</v>
       </c>
       <c r="AD113">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AE113">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="AF113">
         <v>1.71</v>
@@ -18801,7 +18801,7 @@
         <v>1.21</v>
       </c>
       <c r="AK113">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="AL113">
         <v>0</v>
@@ -18891,10 +18891,10 @@
         </is>
       </c>
       <c r="N114">
-        <v>1.63</v>
+        <v>1.61</v>
       </c>
       <c r="O114">
-        <v>3.65</v>
+        <v>3.9</v>
       </c>
       <c r="P114">
         <v>4.4</v>
@@ -18903,10 +18903,10 @@
         <v>2.15</v>
       </c>
       <c r="R114">
-        <v>2.38</v>
+        <v>2.24</v>
       </c>
       <c r="S114">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="T114">
         <v>3.28</v>
@@ -18918,28 +18918,28 @@
         <v>1.5</v>
       </c>
       <c r="W114">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="X114">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y114">
         <v>1.22</v>
       </c>
       <c r="Z114">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="AA114">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="AB114">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="AC114">
         <v>2.7</v>
       </c>
       <c r="AD114">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="AE114">
         <v>1.1</v>
@@ -18948,7 +18948,7 @@
         <v>1.7</v>
       </c>
       <c r="AG114">
-        <v>2.01</v>
+        <v>1.95</v>
       </c>
       <c r="AH114" t="inlineStr">
         <is>
@@ -19054,13 +19054,13 @@
         </is>
       </c>
       <c r="N115">
-        <v>1.85</v>
+        <v>1.93</v>
       </c>
       <c r="O115">
-        <v>3.52</v>
+        <v>3.5</v>
       </c>
       <c r="P115">
-        <v>3.85</v>
+        <v>3.82</v>
       </c>
       <c r="Q115">
         <v>2.42</v>
@@ -19084,25 +19084,25 @@
         <v>1.09</v>
       </c>
       <c r="X115">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y115">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="Z115">
         <v>4.1</v>
       </c>
       <c r="AA115">
-        <v>1.78</v>
+        <v>1.76</v>
       </c>
       <c r="AB115">
-        <v>1.89</v>
+        <v>1.97</v>
       </c>
       <c r="AC115">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="AD115">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="AE115">
         <v>1.1</v>
@@ -19111,7 +19111,7 @@
         <v>1.67</v>
       </c>
       <c r="AG115">
-        <v>2.1</v>
+        <v>2.09</v>
       </c>
       <c r="AH115" t="inlineStr">
         <is>
@@ -19217,25 +19217,25 @@
         </is>
       </c>
       <c r="N116">
-        <v>1.48</v>
+        <v>1.43</v>
       </c>
       <c r="O116">
         <v>4.4</v>
       </c>
       <c r="P116">
-        <v>5.25</v>
+        <v>5.75</v>
       </c>
       <c r="Q116">
-        <v>1.91</v>
+        <v>1.96</v>
       </c>
       <c r="R116">
-        <v>2.59</v>
+        <v>2.35</v>
       </c>
       <c r="S116">
         <v>1.25</v>
       </c>
       <c r="T116">
-        <v>3.5</v>
+        <v>3.25</v>
       </c>
       <c r="U116">
         <v>2.25</v>
@@ -19244,13 +19244,13 @@
         <v>1.57</v>
       </c>
       <c r="W116">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="X116">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y116">
-        <v>1.18</v>
+        <v>1.13</v>
       </c>
       <c r="Z116">
         <v>4.5</v>
@@ -19262,10 +19262,10 @@
         <v>2.23</v>
       </c>
       <c r="AC116">
-        <v>2.41</v>
+        <v>2.48</v>
       </c>
       <c r="AD116">
-        <v>1.52</v>
+        <v>1.45</v>
       </c>
       <c r="AE116">
         <v>1.14</v>
@@ -19274,7 +19274,7 @@
         <v>1.7</v>
       </c>
       <c r="AG116">
-        <v>1.98</v>
+        <v>2.01</v>
       </c>
       <c r="AH116" t="inlineStr">
         <is>
@@ -19380,16 +19380,16 @@
         </is>
       </c>
       <c r="N117">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="O117">
-        <v>5.3</v>
+        <v>5.25</v>
       </c>
       <c r="P117">
-        <v>8.1</v>
+        <v>9.5</v>
       </c>
       <c r="Q117">
-        <v>1.69</v>
+        <v>1.58</v>
       </c>
       <c r="R117">
         <v>2.5</v>
@@ -19410,34 +19410,34 @@
         <v>1.07</v>
       </c>
       <c r="X117">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y117">
-        <v>1.27</v>
+        <v>1.22</v>
       </c>
       <c r="Z117">
-        <v>3.56</v>
+        <v>4.1</v>
       </c>
       <c r="AA117">
         <v>1.8</v>
       </c>
       <c r="AB117">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="AC117">
-        <v>2.8</v>
+        <v>3.1</v>
       </c>
       <c r="AD117">
         <v>1.33</v>
       </c>
       <c r="AE117">
-        <v>1.12</v>
+        <v>1.09</v>
       </c>
       <c r="AF117">
         <v>2.49</v>
       </c>
       <c r="AG117">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="AH117" t="inlineStr">
         <is>
@@ -19543,25 +19543,25 @@
         </is>
       </c>
       <c r="N118">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="O118">
-        <v>2.75</v>
+        <v>2.8</v>
       </c>
       <c r="P118">
         <v>4</v>
       </c>
       <c r="Q118">
-        <v>2.93</v>
+        <v>2.85</v>
       </c>
       <c r="R118">
-        <v>1.7</v>
+        <v>1.83</v>
       </c>
       <c r="S118">
         <v>1.58</v>
       </c>
       <c r="T118">
-        <v>1.99</v>
+        <v>2.16</v>
       </c>
       <c r="U118">
         <v>4.2</v>
@@ -19573,28 +19573,28 @@
         <v>1.03</v>
       </c>
       <c r="X118">
-        <v>1.15</v>
+        <v>1.1</v>
       </c>
       <c r="Y118">
-        <v>1.69</v>
+        <v>1.62</v>
       </c>
       <c r="Z118">
         <v>2.08</v>
       </c>
       <c r="AA118">
-        <v>2.97</v>
+        <v>3.2</v>
       </c>
       <c r="AB118">
         <v>1.35</v>
       </c>
       <c r="AC118">
-        <v>6.39</v>
+        <v>6.5</v>
       </c>
       <c r="AD118">
         <v>1.1</v>
       </c>
       <c r="AE118">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="AF118">
         <v>2.3</v>
@@ -19712,46 +19712,46 @@
         <v>2.87</v>
       </c>
       <c r="P119">
-        <v>2.6</v>
+        <v>2.59</v>
       </c>
       <c r="Q119">
-        <v>3.3</v>
+        <v>3.45</v>
       </c>
       <c r="R119">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="S119">
-        <v>1.59</v>
+        <v>1.55</v>
       </c>
       <c r="T119">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="U119">
-        <v>3.58</v>
+        <v>3.45</v>
       </c>
       <c r="V119">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="W119">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="X119">
-        <v>1.12</v>
+        <v>1.07</v>
       </c>
       <c r="Y119">
         <v>1.53</v>
       </c>
       <c r="Z119">
-        <v>2.43</v>
+        <v>2.45</v>
       </c>
       <c r="AA119">
-        <v>2.48</v>
+        <v>2.7</v>
       </c>
       <c r="AB119">
-        <v>1.45</v>
+        <v>1.41</v>
       </c>
       <c r="AC119">
-        <v>4.6</v>
+        <v>4.95</v>
       </c>
       <c r="AD119">
         <v>1.11</v>
@@ -19760,10 +19760,10 @@
         <v>1.01</v>
       </c>
       <c r="AF119">
-        <v>2.09</v>
+        <v>2.04</v>
       </c>
       <c r="AG119">
-        <v>1.63</v>
+        <v>1.65</v>
       </c>
       <c r="AH119" t="inlineStr">
         <is>
@@ -19776,10 +19776,10 @@
         </is>
       </c>
       <c r="AJ119">
-        <v>1.4</v>
+        <v>1.35</v>
       </c>
       <c r="AK119">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="AL119">
         <v>0</v>
@@ -19869,7 +19869,7 @@
         </is>
       </c>
       <c r="N120">
-        <v>1.98</v>
+        <v>1.95</v>
       </c>
       <c r="O120">
         <v>3.25</v>
@@ -19878,25 +19878,25 @@
         <v>3.4</v>
       </c>
       <c r="Q120">
-        <v>2.6</v>
+        <v>2.67</v>
       </c>
       <c r="R120">
-        <v>2.17</v>
+        <v>2.03</v>
       </c>
       <c r="S120">
         <v>1.4</v>
       </c>
       <c r="T120">
-        <v>2.81</v>
+        <v>2.57</v>
       </c>
       <c r="U120">
-        <v>3.05</v>
+        <v>2.75</v>
       </c>
       <c r="V120">
-        <v>1.35</v>
+        <v>1.4</v>
       </c>
       <c r="W120">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="X120">
         <v>1.05</v>
@@ -19905,7 +19905,7 @@
         <v>1.33</v>
       </c>
       <c r="Z120">
-        <v>2.97</v>
+        <v>3.25</v>
       </c>
       <c r="AA120">
         <v>2.04</v>
@@ -19923,10 +19923,10 @@
         <v>1.05</v>
       </c>
       <c r="AF120">
-        <v>1.87</v>
+        <v>1.83</v>
       </c>
       <c r="AG120">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="AH120" t="inlineStr">
         <is>
@@ -19942,7 +19942,7 @@
         <v>1.28</v>
       </c>
       <c r="AK120">
-        <v>1.77</v>
+        <v>1.73</v>
       </c>
       <c r="AL120">
         <v>0</v>
@@ -20038,10 +20038,10 @@
         <v>3.15</v>
       </c>
       <c r="P121">
-        <v>2.89</v>
+        <v>2.8</v>
       </c>
       <c r="Q121">
-        <v>2.9</v>
+        <v>2.97</v>
       </c>
       <c r="R121">
         <v>2</v>
@@ -20065,7 +20065,7 @@
         <v>1.03</v>
       </c>
       <c r="Y121">
-        <v>1.38</v>
+        <v>1.35</v>
       </c>
       <c r="Z121">
         <v>2.85</v>
@@ -20102,7 +20102,7 @@
         </is>
       </c>
       <c r="AJ121">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="AK121">
         <v>1.5</v>
@@ -20198,7 +20198,7 @@
         <v>2.37</v>
       </c>
       <c r="O122">
-        <v>3.45</v>
+        <v>3.3</v>
       </c>
       <c r="P122">
         <v>2.5</v>
@@ -20213,13 +20213,13 @@
         <v>1.32</v>
       </c>
       <c r="T122">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="U122">
         <v>2.63</v>
       </c>
       <c r="V122">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="W122">
         <v>1.1</v>
@@ -20237,10 +20237,10 @@
         <v>1.8</v>
       </c>
       <c r="AB122">
-        <v>1.9</v>
+        <v>1.96</v>
       </c>
       <c r="AC122">
-        <v>2.8</v>
+        <v>3</v>
       </c>
       <c r="AD122">
         <v>1.4</v>
@@ -20265,7 +20265,7 @@
         </is>
       </c>
       <c r="AJ122">
-        <v>1.3</v>
+        <v>1.38</v>
       </c>
       <c r="AK122">
         <v>1.45</v>
@@ -20358,64 +20358,64 @@
         </is>
       </c>
       <c r="N123">
-        <v>1.51</v>
+        <v>1.49</v>
       </c>
       <c r="O123">
-        <v>4.4</v>
+        <v>4</v>
       </c>
       <c r="P123">
-        <v>5.6</v>
+        <v>5</v>
       </c>
       <c r="Q123">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="R123">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="S123">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="T123">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="U123">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="V123">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="W123">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X123">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y123">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="Z123">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="AA123">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AB123">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AC123">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AD123">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AE123">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AF123">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AG123">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AH123" t="inlineStr">
         <is>
@@ -20428,10 +20428,10 @@
         </is>
       </c>
       <c r="AJ123">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AK123">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="AL123">
         <v>0</v>
@@ -20521,16 +20521,16 @@
         </is>
       </c>
       <c r="N124">
-        <v>1.91</v>
+        <v>1.86</v>
       </c>
       <c r="O124">
-        <v>2.87</v>
+        <v>2.8</v>
       </c>
       <c r="P124">
-        <v>4.8</v>
+        <v>4.2</v>
       </c>
       <c r="Q124">
-        <v>2.78</v>
+        <v>2.77</v>
       </c>
       <c r="R124">
         <v>1.72</v>
@@ -20554,7 +20554,7 @@
         <v>1.12</v>
       </c>
       <c r="Y124">
-        <v>1.71</v>
+        <v>1.68</v>
       </c>
       <c r="Z124">
         <v>2.06</v>
@@ -20563,13 +20563,13 @@
         <v>3.4</v>
       </c>
       <c r="AB124">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AC124">
         <v>5.95</v>
       </c>
       <c r="AD124">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="AE124">
         <v>1.02</v>
@@ -20591,10 +20591,10 @@
         </is>
       </c>
       <c r="AJ124">
-        <v>1.35</v>
+        <v>1.4</v>
       </c>
       <c r="AK124">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="AL124">
         <v>0</v>
@@ -20684,31 +20684,31 @@
         </is>
       </c>
       <c r="N125">
-        <v>2.8</v>
+        <v>2.81</v>
       </c>
       <c r="O125">
-        <v>2.7</v>
+        <v>2.64</v>
       </c>
       <c r="P125">
-        <v>2.44</v>
+        <v>2.45</v>
       </c>
       <c r="Q125">
-        <v>3.98</v>
+        <v>4.15</v>
       </c>
       <c r="R125">
         <v>1.74</v>
       </c>
       <c r="S125">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="T125">
-        <v>2.07</v>
+        <v>2.25</v>
       </c>
       <c r="U125">
         <v>4</v>
       </c>
       <c r="V125">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="W125">
         <v>1.03</v>
@@ -20723,13 +20723,13 @@
         <v>2.15</v>
       </c>
       <c r="AA125">
-        <v>2.75</v>
+        <v>2.88</v>
       </c>
       <c r="AB125">
-        <v>1.36</v>
+        <v>1.32</v>
       </c>
       <c r="AC125">
-        <v>5.3</v>
+        <v>5.9</v>
       </c>
       <c r="AD125">
         <v>1.07</v>
@@ -20738,10 +20738,10 @@
         <v>1.02</v>
       </c>
       <c r="AF125">
-        <v>2.2</v>
+        <v>2.32</v>
       </c>
       <c r="AG125">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="AH125" t="inlineStr">
         <is>
@@ -20757,7 +20757,7 @@
         <v>1.36</v>
       </c>
       <c r="AK125">
-        <v>1.31</v>
+        <v>1.38</v>
       </c>
       <c r="AL125">
         <v>0</v>
@@ -20847,64 +20847,64 @@
         </is>
       </c>
       <c r="N126">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="O126">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="P126">
-        <v>0</v>
+        <v>9.75</v>
       </c>
       <c r="Q126">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="R126">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="S126">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="T126">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="U126">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="V126">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="W126">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="X126">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y126">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="Z126">
-        <v>0</v>
+        <v>4.51</v>
       </c>
       <c r="AA126">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AB126">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AC126">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="AD126">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AE126">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AF126">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AG126">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AH126" t="inlineStr">
         <is>
@@ -20917,10 +20917,10 @@
         </is>
       </c>
       <c r="AJ126">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AK126">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="AL126">
         <v>0</v>
@@ -21013,10 +21013,10 @@
         <v>2.81</v>
       </c>
       <c r="O127">
-        <v>2.45</v>
+        <v>2.6</v>
       </c>
       <c r="P127">
-        <v>2.95</v>
+        <v>2.81</v>
       </c>
       <c r="Q127">
         <v>0</v>
@@ -21173,7 +21173,7 @@
         </is>
       </c>
       <c r="N128">
-        <v>2.45</v>
+        <v>2.25</v>
       </c>
       <c r="O128">
         <v>3.55</v>
@@ -21336,7 +21336,7 @@
         </is>
       </c>
       <c r="N129">
-        <v>1.49</v>
+        <v>1.55</v>
       </c>
       <c r="O129">
         <v>3.6</v>
@@ -21499,64 +21499,64 @@
         </is>
       </c>
       <c r="N130">
-        <v>1.89</v>
+        <v>1.83</v>
       </c>
       <c r="O130">
-        <v>4</v>
+        <v>3.75</v>
       </c>
       <c r="P130">
-        <v>3.45</v>
+        <v>3.25</v>
       </c>
       <c r="Q130">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="R130">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="S130">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="T130">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="U130">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="V130">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="W130">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="X130">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y130">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Z130">
-        <v>0</v>
+        <v>6.05</v>
       </c>
       <c r="AA130">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AB130">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="AC130">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AD130">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AE130">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AF130">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AG130">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="AH130" t="inlineStr">
         <is>
@@ -21569,10 +21569,10 @@
         </is>
       </c>
       <c r="AJ130">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AK130">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AL130">
         <v>0</v>
@@ -21668,7 +21668,7 @@
         <v>3.35</v>
       </c>
       <c r="P131">
-        <v>2.35</v>
+        <v>2.3</v>
       </c>
       <c r="Q131">
         <v>3.15</v>
@@ -21825,13 +21825,13 @@
         </is>
       </c>
       <c r="N132">
-        <v>1.63</v>
+        <v>1.57</v>
       </c>
       <c r="O132">
         <v>3.9</v>
       </c>
       <c r="P132">
-        <v>4.65</v>
+        <v>5</v>
       </c>
       <c r="Q132">
         <v>2.07</v>
@@ -21855,7 +21855,7 @@
         <v>1.1</v>
       </c>
       <c r="X132">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y132">
         <v>1.25</v>
@@ -21895,7 +21895,7 @@
         </is>
       </c>
       <c r="AJ132">
-        <v>1.15</v>
+        <v>1.18</v>
       </c>
       <c r="AK132">
         <v>2.2</v>
@@ -21988,64 +21988,64 @@
         </is>
       </c>
       <c r="N133">
-        <v>4.85</v>
+        <v>5.15</v>
       </c>
       <c r="O133">
         <v>3.8</v>
       </c>
       <c r="P133">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="Q133">
-        <v>0</v>
+        <v>5.84</v>
       </c>
       <c r="R133">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="S133">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="T133">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="U133">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="V133">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="W133">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="X133">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y133">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="Z133">
-        <v>0</v>
+        <v>3.72</v>
       </c>
       <c r="AA133">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="AB133">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="AC133">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="AD133">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AE133">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AF133">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AG133">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AH133" t="inlineStr">
         <is>
@@ -22058,10 +22058,10 @@
         </is>
       </c>
       <c r="AJ133">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AK133">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AL133">
         <v>0</v>
@@ -22184,7 +22184,7 @@
         <v>1.03</v>
       </c>
       <c r="Y134">
-        <v>1.17</v>
+        <v>1.21</v>
       </c>
       <c r="Z134">
         <v>4.05</v>
@@ -22314,19 +22314,19 @@
         </is>
       </c>
       <c r="N135">
-        <v>2.8</v>
+        <v>2.85</v>
       </c>
       <c r="O135">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="P135">
-        <v>2.3</v>
+        <v>2.29</v>
       </c>
       <c r="Q135">
         <v>3.75</v>
       </c>
       <c r="R135">
-        <v>1.94</v>
+        <v>1.93</v>
       </c>
       <c r="S135">
         <v>1.5</v>
@@ -22338,7 +22338,7 @@
         <v>3</v>
       </c>
       <c r="V135">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="W135">
         <v>1.03</v>
@@ -22353,13 +22353,13 @@
         <v>2.52</v>
       </c>
       <c r="AA135">
-        <v>2.34</v>
+        <v>2.37</v>
       </c>
       <c r="AB135">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="AC135">
-        <v>4.29</v>
+        <v>4.38</v>
       </c>
       <c r="AD135">
         <v>1.16</v>
@@ -22486,55 +22486,55 @@
         <v>2.9</v>
       </c>
       <c r="Q136">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="R136">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="S136">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="T136">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="U136">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="V136">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="W136">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="X136">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y136">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="Z136">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="AA136">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AB136">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="AC136">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AD136">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AE136">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AF136">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AG136">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="AH136" t="inlineStr">
         <is>
@@ -22547,10 +22547,10 @@
         </is>
       </c>
       <c r="AJ136">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AK136">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AL136">
         <v>0</v>
@@ -22640,13 +22640,13 @@
         </is>
       </c>
       <c r="N137">
-        <v>1.86</v>
+        <v>1.94</v>
       </c>
       <c r="O137">
-        <v>3.5</v>
+        <v>3.64</v>
       </c>
       <c r="P137">
-        <v>3.25</v>
+        <v>3.56</v>
       </c>
       <c r="Q137">
         <v>0</v>

--- a/jogos_2026-08-02.xlsx
+++ b/jogos_2026-08-02.xlsx
@@ -1658,7 +1658,7 @@
         <v>1.73</v>
       </c>
       <c r="AC8">
-        <v>3.58</v>
+        <v>3.78</v>
       </c>
       <c r="AD8">
         <v>1.21</v>
@@ -1782,7 +1782,7 @@
         <v>3.5</v>
       </c>
       <c r="P9">
-        <v>2.63</v>
+        <v>2.72</v>
       </c>
       <c r="Q9">
         <v>0</v>
@@ -2722,12 +2722,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Gimpo Citizen</t>
+          <t>Busan I'Park</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Gyeongnam</t>
+          <t>Seoul E-Land</t>
         </is>
       </c>
       <c r="G15">
@@ -2754,64 +2754,64 @@
         </is>
       </c>
       <c r="N15">
-        <v>1.94</v>
+        <v>2.62</v>
       </c>
       <c r="O15">
-        <v>3.2</v>
+        <v>3.5</v>
       </c>
       <c r="P15">
-        <v>3.5</v>
+        <v>2.2</v>
       </c>
       <c r="Q15">
-        <v>2.62</v>
+        <v>3.1</v>
       </c>
       <c r="R15">
-        <v>2.15</v>
+        <v>2.16</v>
       </c>
       <c r="S15">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="T15">
-        <v>2.48</v>
+        <v>3.25</v>
       </c>
       <c r="U15">
-        <v>3.12</v>
+        <v>2.5</v>
       </c>
       <c r="V15">
-        <v>1.29</v>
+        <v>1.5</v>
       </c>
       <c r="W15">
-        <v>1.02</v>
+        <v>1.11</v>
       </c>
       <c r="X15">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="Y15">
-        <v>1.4</v>
+        <v>1.21</v>
       </c>
       <c r="Z15">
-        <v>3.05</v>
+        <v>4.26</v>
       </c>
       <c r="AA15">
-        <v>2.29</v>
+        <v>1.67</v>
       </c>
       <c r="AB15">
-        <v>1.61</v>
+        <v>2.1</v>
       </c>
       <c r="AC15">
-        <v>3.3</v>
+        <v>2.66</v>
       </c>
       <c r="AD15">
-        <v>1.2</v>
+        <v>1.37</v>
       </c>
       <c r="AE15">
-        <v>1.04</v>
+        <v>1.11</v>
       </c>
       <c r="AF15">
-        <v>1.92</v>
+        <v>1.57</v>
       </c>
       <c r="AG15">
-        <v>1.77</v>
+        <v>2.2</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2824,10 +2824,10 @@
         </is>
       </c>
       <c r="AJ15">
-        <v>1.25</v>
+        <v>1.5</v>
       </c>
       <c r="AK15">
-        <v>1.83</v>
+        <v>1.36</v>
       </c>
       <c r="AL15">
         <v>0</v>
@@ -2885,12 +2885,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Busan I'Park</t>
+          <t>Ansan Greeners</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Seoul E-Land</t>
+          <t>Gimhae City</t>
         </is>
       </c>
       <c r="G16">
@@ -2917,64 +2917,64 @@
         </is>
       </c>
       <c r="N16">
-        <v>2.62</v>
+        <v>2.65</v>
       </c>
       <c r="O16">
-        <v>3.5</v>
+        <v>3.1</v>
       </c>
       <c r="P16">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="Q16">
-        <v>3.1</v>
+        <v>3.4</v>
       </c>
       <c r="R16">
-        <v>2.16</v>
+        <v>2.12</v>
       </c>
       <c r="S16">
-        <v>1.3</v>
+        <v>1.34</v>
       </c>
       <c r="T16">
-        <v>3.25</v>
+        <v>3.01</v>
       </c>
       <c r="U16">
-        <v>2.5</v>
+        <v>2.74</v>
       </c>
       <c r="V16">
-        <v>1.5</v>
+        <v>1.37</v>
       </c>
       <c r="W16">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="X16">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="Y16">
-        <v>1.21</v>
+        <v>1.29</v>
       </c>
       <c r="Z16">
-        <v>4.26</v>
+        <v>3.4</v>
       </c>
       <c r="AA16">
-        <v>1.67</v>
+        <v>1.9</v>
       </c>
       <c r="AB16">
-        <v>2.1</v>
+        <v>1.87</v>
       </c>
       <c r="AC16">
-        <v>2.66</v>
+        <v>3.2</v>
       </c>
       <c r="AD16">
-        <v>1.37</v>
+        <v>1.33</v>
       </c>
       <c r="AE16">
         <v>1.11</v>
       </c>
       <c r="AF16">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="AG16">
-        <v>2.2</v>
+        <v>2.03</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -2987,10 +2987,10 @@
         </is>
       </c>
       <c r="AJ16">
-        <v>1.5</v>
+        <v>1.24</v>
       </c>
       <c r="AK16">
-        <v>1.36</v>
+        <v>1.32</v>
       </c>
       <c r="AL16">
         <v>0</v>
@@ -3048,12 +3048,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Ansan Greeners</t>
+          <t>Gimpo Citizen</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Gimhae City</t>
+          <t>Gyeongnam</t>
         </is>
       </c>
       <c r="G17">
@@ -3080,64 +3080,64 @@
         </is>
       </c>
       <c r="N17">
-        <v>2.65</v>
+        <v>1.94</v>
       </c>
       <c r="O17">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="P17">
-        <v>2.1</v>
+        <v>3.5</v>
       </c>
       <c r="Q17">
-        <v>3.4</v>
+        <v>2.62</v>
       </c>
       <c r="R17">
-        <v>2.12</v>
+        <v>2.15</v>
       </c>
       <c r="S17">
-        <v>1.34</v>
+        <v>1.4</v>
       </c>
       <c r="T17">
-        <v>3.01</v>
+        <v>2.48</v>
       </c>
       <c r="U17">
-        <v>2.74</v>
+        <v>3.12</v>
       </c>
       <c r="V17">
-        <v>1.37</v>
+        <v>1.29</v>
       </c>
       <c r="W17">
-        <v>1.08</v>
+        <v>1.02</v>
       </c>
       <c r="X17">
         <v>1.05</v>
       </c>
       <c r="Y17">
-        <v>1.29</v>
+        <v>1.4</v>
       </c>
       <c r="Z17">
-        <v>3.4</v>
+        <v>3.05</v>
       </c>
       <c r="AA17">
-        <v>1.9</v>
+        <v>2.29</v>
       </c>
       <c r="AB17">
-        <v>1.87</v>
+        <v>1.61</v>
       </c>
       <c r="AC17">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="AD17">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="AE17">
-        <v>1.11</v>
+        <v>1.04</v>
       </c>
       <c r="AF17">
-        <v>1.67</v>
+        <v>1.92</v>
       </c>
       <c r="AG17">
-        <v>2.03</v>
+        <v>1.77</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3150,10 +3150,10 @@
         </is>
       </c>
       <c r="AJ17">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="AK17">
-        <v>1.32</v>
+        <v>1.83</v>
       </c>
       <c r="AL17">
         <v>0</v>
@@ -4224,16 +4224,16 @@
         <v>2.43</v>
       </c>
       <c r="O24">
+        <v>3.1</v>
+      </c>
+      <c r="P24">
+        <v>2.27</v>
+      </c>
+      <c r="Q24">
         <v>3</v>
       </c>
-      <c r="P24">
-        <v>2.4</v>
-      </c>
-      <c r="Q24">
-        <v>3.75</v>
-      </c>
       <c r="R24">
-        <v>1.95</v>
+        <v>1.92</v>
       </c>
       <c r="S24">
         <v>1.49</v>
@@ -5362,7 +5362,7 @@
         </is>
       </c>
       <c r="N31">
-        <v>1.56</v>
+        <v>1.6</v>
       </c>
       <c r="O31">
         <v>3.7</v>
@@ -5371,10 +5371,10 @@
         <v>5.5</v>
       </c>
       <c r="Q31">
+        <v>2.01</v>
+      </c>
+      <c r="R31">
         <v>2.15</v>
-      </c>
-      <c r="R31">
-        <v>2.18</v>
       </c>
       <c r="S31">
         <v>1.36</v>
@@ -5395,7 +5395,7 @@
         <v>1.01</v>
       </c>
       <c r="Y31">
-        <v>1.24</v>
+        <v>1.28</v>
       </c>
       <c r="Z31">
         <v>3.8</v>
@@ -5419,7 +5419,7 @@
         <v>1.9</v>
       </c>
       <c r="AG31">
-        <v>1.83</v>
+        <v>1.87</v>
       </c>
       <c r="AH31" t="inlineStr">
         <is>
@@ -6503,10 +6503,10 @@
         </is>
       </c>
       <c r="N38">
-        <v>8.699999999999999</v>
+        <v>7.6</v>
       </c>
       <c r="O38">
-        <v>5.25</v>
+        <v>5</v>
       </c>
       <c r="P38">
         <v>1.33</v>
@@ -6536,7 +6536,7 @@
         <v>1</v>
       </c>
       <c r="Y38">
-        <v>1.21</v>
+        <v>1.23</v>
       </c>
       <c r="Z38">
         <v>3.94</v>
@@ -6675,10 +6675,10 @@
         <v>3.1</v>
       </c>
       <c r="Q39">
-        <v>2.49</v>
+        <v>2.75</v>
       </c>
       <c r="R39">
-        <v>2.11</v>
+        <v>2.15</v>
       </c>
       <c r="S39">
         <v>1.37</v>
@@ -6687,7 +6687,7 @@
         <v>2.85</v>
       </c>
       <c r="U39">
-        <v>2.55</v>
+        <v>2.56</v>
       </c>
       <c r="V39">
         <v>1.4</v>
@@ -6702,7 +6702,7 @@
         <v>1.28</v>
       </c>
       <c r="Z39">
-        <v>3.55</v>
+        <v>3.44</v>
       </c>
       <c r="AA39">
         <v>1.81</v>
@@ -6736,7 +6736,7 @@
         </is>
       </c>
       <c r="AJ39">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="AK39">
         <v>1.63</v>
@@ -7665,19 +7665,19 @@
         <v>3.28</v>
       </c>
       <c r="U45">
-        <v>2.25</v>
+        <v>2.26</v>
       </c>
       <c r="V45">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="W45">
         <v>1.14</v>
       </c>
       <c r="X45">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y45">
-        <v>1.12</v>
+        <v>1.17</v>
       </c>
       <c r="Z45">
         <v>4.45</v>
@@ -7689,13 +7689,13 @@
         <v>2.35</v>
       </c>
       <c r="AC45">
-        <v>2.28</v>
+        <v>2.38</v>
       </c>
       <c r="AD45">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="AE45">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="AF45">
         <v>1.65</v>
@@ -7714,7 +7714,7 @@
         </is>
       </c>
       <c r="AJ45">
-        <v>1.15</v>
+        <v>1.08</v>
       </c>
       <c r="AK45">
         <v>2.63</v>
@@ -7807,43 +7807,43 @@
         </is>
       </c>
       <c r="N46">
-        <v>1.5</v>
+        <v>1.37</v>
       </c>
       <c r="O46">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="P46">
         <v>5</v>
       </c>
       <c r="Q46">
-        <v>1.98</v>
+        <v>2.02</v>
       </c>
       <c r="R46">
-        <v>2.54</v>
+        <v>2.32</v>
       </c>
       <c r="S46">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="T46">
         <v>3.28</v>
       </c>
       <c r="U46">
-        <v>2.26</v>
+        <v>2.17</v>
       </c>
       <c r="V46">
         <v>1.56</v>
       </c>
       <c r="W46">
-        <v>1.15</v>
+        <v>1.1</v>
       </c>
       <c r="X46">
         <v>1.01</v>
       </c>
       <c r="Y46">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="Z46">
-        <v>4.75</v>
+        <v>5.5</v>
       </c>
       <c r="AA46">
         <v>1.53</v>
@@ -7979,10 +7979,10 @@
         <v>1.51</v>
       </c>
       <c r="Q47">
-        <v>3.67</v>
+        <v>4.78</v>
       </c>
       <c r="R47">
-        <v>2.56</v>
+        <v>2.94</v>
       </c>
       <c r="S47">
         <v>1.14</v>
@@ -7991,10 +7991,10 @@
         <v>5</v>
       </c>
       <c r="U47">
-        <v>1.82</v>
+        <v>1.9</v>
       </c>
       <c r="V47">
-        <v>1.96</v>
+        <v>1.7</v>
       </c>
       <c r="W47">
         <v>1.25</v>
@@ -8009,19 +8009,19 @@
         <v>7.3</v>
       </c>
       <c r="AA47">
-        <v>1.24</v>
+        <v>1.3</v>
       </c>
       <c r="AB47">
-        <v>3.34</v>
+        <v>3.4</v>
       </c>
       <c r="AC47">
-        <v>1.75</v>
+        <v>1.91</v>
       </c>
       <c r="AD47">
         <v>2.03</v>
       </c>
       <c r="AE47">
-        <v>1.47</v>
+        <v>1.42</v>
       </c>
       <c r="AF47">
         <v>1.36</v>
@@ -8040,10 +8040,10 @@
         </is>
       </c>
       <c r="AJ47">
-        <v>2.43</v>
+        <v>1.16</v>
       </c>
       <c r="AK47">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="AL47">
         <v>0</v>
@@ -12697,13 +12697,13 @@
         </is>
       </c>
       <c r="N76">
-        <v>2.8</v>
+        <v>2.7</v>
       </c>
       <c r="O76">
         <v>3.1</v>
       </c>
       <c r="P76">
-        <v>2.4</v>
+        <v>2.18</v>
       </c>
       <c r="Q76">
         <v>3.35</v>
@@ -12718,7 +12718,7 @@
         <v>2.75</v>
       </c>
       <c r="U76">
-        <v>2.9</v>
+        <v>2.91</v>
       </c>
       <c r="V76">
         <v>1.4</v>
@@ -12727,16 +12727,16 @@
         <v>1.04</v>
       </c>
       <c r="X76">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="Y76">
         <v>1.3</v>
       </c>
       <c r="Z76">
-        <v>3.46</v>
+        <v>3.35</v>
       </c>
       <c r="AA76">
-        <v>1.98</v>
+        <v>1.95</v>
       </c>
       <c r="AB76">
         <v>1.83</v>
@@ -12748,7 +12748,7 @@
         <v>1.31</v>
       </c>
       <c r="AE76">
-        <v>1.11</v>
+        <v>1.06</v>
       </c>
       <c r="AF76">
         <v>1.72</v>
@@ -13512,19 +13512,19 @@
         </is>
       </c>
       <c r="N81">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="O81">
         <v>3.4</v>
       </c>
       <c r="P81">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="Q81">
         <v>4</v>
       </c>
       <c r="R81">
-        <v>2.25</v>
+        <v>2.18</v>
       </c>
       <c r="S81">
         <v>1.3</v>
@@ -13539,10 +13539,10 @@
         <v>1.44</v>
       </c>
       <c r="W81">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="X81">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y81">
         <v>1.19</v>
@@ -13566,10 +13566,10 @@
         <v>1.14</v>
       </c>
       <c r="AF81">
-        <v>1.68</v>
+        <v>1.62</v>
       </c>
       <c r="AG81">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="AH81" t="inlineStr">
         <is>
@@ -13675,13 +13675,13 @@
         </is>
       </c>
       <c r="N82">
-        <v>1.79</v>
+        <v>1.7</v>
       </c>
       <c r="O82">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="P82">
-        <v>4.46</v>
+        <v>4.05</v>
       </c>
       <c r="Q82">
         <v>2.38</v>
@@ -13693,25 +13693,25 @@
         <v>1.43</v>
       </c>
       <c r="T82">
-        <v>2.53</v>
+        <v>2.65</v>
       </c>
       <c r="U82">
-        <v>2.84</v>
+        <v>2.9</v>
       </c>
       <c r="V82">
-        <v>1.35</v>
+        <v>1.32</v>
       </c>
       <c r="W82">
         <v>1.02</v>
       </c>
       <c r="X82">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y82">
         <v>1.33</v>
       </c>
       <c r="Z82">
-        <v>3.01</v>
+        <v>3.03</v>
       </c>
       <c r="AA82">
         <v>2.1</v>
@@ -13729,10 +13729,10 @@
         <v>1.05</v>
       </c>
       <c r="AF82">
-        <v>1.85</v>
+        <v>2</v>
       </c>
       <c r="AG82">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="AH82" t="inlineStr">
         <is>
@@ -13745,10 +13745,10 @@
         </is>
       </c>
       <c r="AJ82">
-        <v>1.2</v>
+        <v>1.27</v>
       </c>
       <c r="AK82">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="AL82">
         <v>0</v>
@@ -14132,12 +14132,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Vaprus</t>
+          <t>Tallinna FC Flora</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Tallinna FC Levadia</t>
+          <t>Harju Jalgpallikool</t>
         </is>
       </c>
       <c r="G85">
@@ -14164,64 +14164,64 @@
         </is>
       </c>
       <c r="N85">
-        <v>11.7</v>
+        <v>1.52</v>
       </c>
       <c r="O85">
-        <v>5.7</v>
+        <v>4.05</v>
       </c>
       <c r="P85">
-        <v>1.19</v>
+        <v>6.59</v>
       </c>
       <c r="Q85">
-        <v>7.61</v>
+        <v>2</v>
       </c>
       <c r="R85">
-        <v>2.82</v>
+        <v>2.5</v>
       </c>
       <c r="S85">
-        <v>1.2</v>
+        <v>1.23</v>
       </c>
       <c r="T85">
-        <v>3.58</v>
+        <v>3.42</v>
       </c>
       <c r="U85">
-        <v>2.05</v>
+        <v>2.18</v>
       </c>
       <c r="V85">
-        <v>1.65</v>
+        <v>1.63</v>
       </c>
       <c r="W85">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="X85">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y85">
-        <v>1.13</v>
+        <v>1.1</v>
       </c>
       <c r="Z85">
-        <v>5.1</v>
+        <v>6</v>
       </c>
       <c r="AA85">
-        <v>1.44</v>
+        <v>1.47</v>
       </c>
       <c r="AB85">
-        <v>2.55</v>
+        <v>2.63</v>
       </c>
       <c r="AC85">
-        <v>2.07</v>
+        <v>2.2</v>
       </c>
       <c r="AD85">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="AE85">
-        <v>1.29</v>
+        <v>1.21</v>
       </c>
       <c r="AF85">
-        <v>1.81</v>
+        <v>1.53</v>
       </c>
       <c r="AG85">
-        <v>1.89</v>
+        <v>2.32</v>
       </c>
       <c r="AH85" t="inlineStr">
         <is>
@@ -14234,10 +14234,10 @@
         </is>
       </c>
       <c r="AJ85">
-        <v>1.11</v>
+        <v>1.17</v>
       </c>
       <c r="AK85">
-        <v>1</v>
+        <v>2.3</v>
       </c>
       <c r="AL85">
         <v>0</v>
@@ -14295,12 +14295,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Tallinna FC Flora</t>
+          <t>Vaprus</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Harju Jalgpallikool</t>
+          <t>Tallinna FC Levadia</t>
         </is>
       </c>
       <c r="G86">
@@ -14327,64 +14327,64 @@
         </is>
       </c>
       <c r="N86">
-        <v>1.52</v>
+        <v>11.7</v>
       </c>
       <c r="O86">
-        <v>3.9</v>
+        <v>5.5</v>
       </c>
       <c r="P86">
-        <v>4.8</v>
+        <v>1.25</v>
       </c>
       <c r="Q86">
-        <v>1.95</v>
+        <v>7.61</v>
       </c>
       <c r="R86">
-        <v>2.6</v>
+        <v>2.82</v>
       </c>
       <c r="S86">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="T86">
-        <v>3.8</v>
+        <v>3.58</v>
       </c>
       <c r="U86">
-        <v>2.18</v>
+        <v>2.13</v>
       </c>
       <c r="V86">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="W86">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="X86">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y86">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="Z86">
-        <v>4.95</v>
+        <v>6</v>
       </c>
       <c r="AA86">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="AB86">
-        <v>2.63</v>
+        <v>2.7</v>
       </c>
       <c r="AC86">
-        <v>2.24</v>
+        <v>2.15</v>
       </c>
       <c r="AD86">
-        <v>1.63</v>
+        <v>1.67</v>
       </c>
       <c r="AE86">
-        <v>1.21</v>
+        <v>1.29</v>
       </c>
       <c r="AF86">
-        <v>1.5</v>
+        <v>1.81</v>
       </c>
       <c r="AG86">
-        <v>2.31</v>
+        <v>1.89</v>
       </c>
       <c r="AH86" t="inlineStr">
         <is>
@@ -14397,10 +14397,10 @@
         </is>
       </c>
       <c r="AJ86">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="AK86">
-        <v>2.35</v>
+        <v>1</v>
       </c>
       <c r="AL86">
         <v>0</v>
@@ -15468,13 +15468,13 @@
         </is>
       </c>
       <c r="N93">
-        <v>3.9</v>
+        <v>3.3</v>
       </c>
       <c r="O93">
-        <v>2.8</v>
+        <v>3.2</v>
       </c>
       <c r="P93">
-        <v>2.08</v>
+        <v>2</v>
       </c>
       <c r="Q93">
         <v>3.75</v>
@@ -15483,7 +15483,7 @@
         <v>2.27</v>
       </c>
       <c r="S93">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="T93">
         <v>2.9</v>
@@ -15504,16 +15504,16 @@
         <v>1.21</v>
       </c>
       <c r="Z93">
-        <v>3.5</v>
+        <v>3.58</v>
       </c>
       <c r="AA93">
-        <v>1.83</v>
+        <v>1.81</v>
       </c>
       <c r="AB93">
         <v>1.84</v>
       </c>
       <c r="AC93">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="AD93">
         <v>1.35</v>
@@ -16781,19 +16781,19 @@
         <v>5.33</v>
       </c>
       <c r="Q101">
-        <v>2.07</v>
+        <v>1.95</v>
       </c>
       <c r="R101">
-        <v>2.52</v>
+        <v>2.34</v>
       </c>
       <c r="S101">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="T101">
         <v>3.6</v>
       </c>
       <c r="U101">
-        <v>2.45</v>
+        <v>2.46</v>
       </c>
       <c r="V101">
         <v>1.57</v>
@@ -16814,7 +16814,7 @@
         <v>1.63</v>
       </c>
       <c r="AB101">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="AC101">
         <v>2.48</v>
@@ -18207,12 +18207,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>FK Jezero Plav</t>
+          <t>Dečić</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Mornar</t>
+          <t>Arsenal Tivat</t>
         </is>
       </c>
       <c r="G110">
@@ -18239,64 +18239,64 @@
         </is>
       </c>
       <c r="N110">
-        <v>4.24</v>
+        <v>1.54</v>
       </c>
       <c r="O110">
-        <v>3</v>
+        <v>3.5</v>
       </c>
       <c r="P110">
-        <v>1.75</v>
+        <v>5.5</v>
       </c>
       <c r="Q110">
-        <v>5.77</v>
+        <v>2.15</v>
       </c>
       <c r="R110">
-        <v>1.86</v>
+        <v>2.01</v>
       </c>
       <c r="S110">
-        <v>1.53</v>
+        <v>1.43</v>
       </c>
       <c r="T110">
-        <v>2.31</v>
+        <v>2.5</v>
       </c>
       <c r="U110">
-        <v>3.48</v>
+        <v>2.97</v>
       </c>
       <c r="V110">
-        <v>1.22</v>
+        <v>1.31</v>
       </c>
       <c r="W110">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="X110">
-        <v>1.07</v>
+        <v>1.03</v>
       </c>
       <c r="Y110">
-        <v>1.47</v>
+        <v>1.32</v>
       </c>
       <c r="Z110">
-        <v>2.6</v>
+        <v>2.88</v>
       </c>
       <c r="AA110">
-        <v>2.37</v>
+        <v>2.1</v>
       </c>
       <c r="AB110">
-        <v>1.53</v>
+        <v>1.7</v>
       </c>
       <c r="AC110">
-        <v>4.7</v>
+        <v>3.58</v>
       </c>
       <c r="AD110">
-        <v>1.12</v>
+        <v>1.21</v>
       </c>
       <c r="AE110">
         <v>1.04</v>
       </c>
       <c r="AF110">
-        <v>2.16</v>
+        <v>2.06</v>
       </c>
       <c r="AG110">
-        <v>1.59</v>
+        <v>1.65</v>
       </c>
       <c r="AH110" t="inlineStr">
         <is>
@@ -18309,10 +18309,10 @@
         </is>
       </c>
       <c r="AJ110">
-        <v>1.27</v>
+        <v>1.22</v>
       </c>
       <c r="AK110">
-        <v>1.12</v>
+        <v>2.19</v>
       </c>
       <c r="AL110">
         <v>0</v>
@@ -18370,12 +18370,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Dečić</t>
+          <t>FK Jezero Plav</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Arsenal Tivat</t>
+          <t>Mornar</t>
         </is>
       </c>
       <c r="G111">
@@ -18402,64 +18402,64 @@
         </is>
       </c>
       <c r="N111">
-        <v>1.54</v>
+        <v>4.24</v>
       </c>
       <c r="O111">
-        <v>3.5</v>
+        <v>3</v>
       </c>
       <c r="P111">
-        <v>5.5</v>
+        <v>1.75</v>
       </c>
       <c r="Q111">
-        <v>2.15</v>
+        <v>5.77</v>
       </c>
       <c r="R111">
-        <v>2.01</v>
+        <v>1.86</v>
       </c>
       <c r="S111">
-        <v>1.43</v>
+        <v>1.53</v>
       </c>
       <c r="T111">
-        <v>2.5</v>
+        <v>2.31</v>
       </c>
       <c r="U111">
-        <v>2.97</v>
+        <v>3.48</v>
       </c>
       <c r="V111">
-        <v>1.31</v>
+        <v>1.22</v>
       </c>
       <c r="W111">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="X111">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="Y111">
-        <v>1.32</v>
+        <v>1.47</v>
       </c>
       <c r="Z111">
-        <v>2.88</v>
+        <v>2.6</v>
       </c>
       <c r="AA111">
-        <v>2.1</v>
+        <v>2.37</v>
       </c>
       <c r="AB111">
-        <v>1.7</v>
+        <v>1.53</v>
       </c>
       <c r="AC111">
-        <v>3.58</v>
+        <v>4.7</v>
       </c>
       <c r="AD111">
-        <v>1.21</v>
+        <v>1.12</v>
       </c>
       <c r="AE111">
         <v>1.04</v>
       </c>
       <c r="AF111">
-        <v>2.06</v>
+        <v>2.16</v>
       </c>
       <c r="AG111">
-        <v>1.65</v>
+        <v>1.59</v>
       </c>
       <c r="AH111" t="inlineStr">
         <is>
@@ -18472,10 +18472,10 @@
         </is>
       </c>
       <c r="AJ111">
-        <v>1.22</v>
+        <v>1.27</v>
       </c>
       <c r="AK111">
-        <v>2.19</v>
+        <v>1.12</v>
       </c>
       <c r="AL111">
         <v>0</v>
@@ -19054,16 +19054,16 @@
         </is>
       </c>
       <c r="N115">
-        <v>1.93</v>
+        <v>1.8</v>
       </c>
       <c r="O115">
-        <v>3.5</v>
+        <v>3.52</v>
       </c>
       <c r="P115">
-        <v>3.82</v>
+        <v>3.8</v>
       </c>
       <c r="Q115">
-        <v>2.42</v>
+        <v>2.4</v>
       </c>
       <c r="R115">
         <v>2.14</v>
@@ -19093,7 +19093,7 @@
         <v>4.1</v>
       </c>
       <c r="AA115">
-        <v>1.76</v>
+        <v>1.8</v>
       </c>
       <c r="AB115">
         <v>1.97</v>
@@ -19108,10 +19108,10 @@
         <v>1.1</v>
       </c>
       <c r="AF115">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="AG115">
-        <v>2.09</v>
+        <v>2.1</v>
       </c>
       <c r="AH115" t="inlineStr">
         <is>
@@ -20489,12 +20489,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Deportivo Madryn</t>
+          <t>Chaco For Ever</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>All Boys</t>
+          <t>Deportivo Morón</t>
         </is>
       </c>
       <c r="G124">
@@ -20521,64 +20521,64 @@
         </is>
       </c>
       <c r="N124">
-        <v>1.86</v>
+        <v>2.81</v>
       </c>
       <c r="O124">
-        <v>2.8</v>
+        <v>2.64</v>
       </c>
       <c r="P124">
-        <v>4.2</v>
+        <v>2.45</v>
       </c>
       <c r="Q124">
-        <v>2.77</v>
+        <v>4.15</v>
       </c>
       <c r="R124">
-        <v>1.72</v>
+        <v>1.74</v>
       </c>
       <c r="S124">
-        <v>1.7</v>
+        <v>1.57</v>
       </c>
       <c r="T124">
         <v>2.25</v>
       </c>
       <c r="U124">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="V124">
-        <v>1.16</v>
+        <v>1.2</v>
       </c>
       <c r="W124">
         <v>1.03</v>
       </c>
       <c r="X124">
-        <v>1.12</v>
+        <v>1.1</v>
       </c>
       <c r="Y124">
-        <v>1.68</v>
+        <v>1.65</v>
       </c>
       <c r="Z124">
-        <v>2.06</v>
+        <v>2.15</v>
       </c>
       <c r="AA124">
-        <v>3.4</v>
+        <v>2.88</v>
       </c>
       <c r="AB124">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="AC124">
-        <v>5.95</v>
+        <v>5.9</v>
       </c>
       <c r="AD124">
-        <v>1.1</v>
+        <v>1.07</v>
       </c>
       <c r="AE124">
         <v>1.02</v>
       </c>
       <c r="AF124">
-        <v>2.51</v>
+        <v>2.32</v>
       </c>
       <c r="AG124">
-        <v>1.44</v>
+        <v>1.53</v>
       </c>
       <c r="AH124" t="inlineStr">
         <is>
@@ -20591,10 +20591,10 @@
         </is>
       </c>
       <c r="AJ124">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AK124">
-        <v>1.7</v>
+        <v>1.38</v>
       </c>
       <c r="AL124">
         <v>0</v>
@@ -20652,12 +20652,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Chaco For Ever</t>
+          <t>Deportivo Madryn</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Deportivo Morón</t>
+          <t>All Boys</t>
         </is>
       </c>
       <c r="G125">
@@ -20684,64 +20684,64 @@
         </is>
       </c>
       <c r="N125">
-        <v>2.81</v>
+        <v>1.86</v>
       </c>
       <c r="O125">
-        <v>2.64</v>
+        <v>2.8</v>
       </c>
       <c r="P125">
-        <v>2.45</v>
+        <v>4.2</v>
       </c>
       <c r="Q125">
-        <v>4.15</v>
+        <v>2.77</v>
       </c>
       <c r="R125">
-        <v>1.74</v>
+        <v>1.72</v>
       </c>
       <c r="S125">
-        <v>1.57</v>
+        <v>1.7</v>
       </c>
       <c r="T125">
         <v>2.25</v>
       </c>
       <c r="U125">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="V125">
-        <v>1.2</v>
+        <v>1.16</v>
       </c>
       <c r="W125">
         <v>1.03</v>
       </c>
       <c r="X125">
+        <v>1.12</v>
+      </c>
+      <c r="Y125">
+        <v>1.68</v>
+      </c>
+      <c r="Z125">
+        <v>2.06</v>
+      </c>
+      <c r="AA125">
+        <v>3.4</v>
+      </c>
+      <c r="AB125">
+        <v>1.33</v>
+      </c>
+      <c r="AC125">
+        <v>5.95</v>
+      </c>
+      <c r="AD125">
         <v>1.1</v>
-      </c>
-      <c r="Y125">
-        <v>1.65</v>
-      </c>
-      <c r="Z125">
-        <v>2.15</v>
-      </c>
-      <c r="AA125">
-        <v>2.88</v>
-      </c>
-      <c r="AB125">
-        <v>1.32</v>
-      </c>
-      <c r="AC125">
-        <v>5.9</v>
-      </c>
-      <c r="AD125">
-        <v>1.07</v>
       </c>
       <c r="AE125">
         <v>1.02</v>
       </c>
       <c r="AF125">
-        <v>2.32</v>
+        <v>2.51</v>
       </c>
       <c r="AG125">
-        <v>1.53</v>
+        <v>1.44</v>
       </c>
       <c r="AH125" t="inlineStr">
         <is>
@@ -20754,10 +20754,10 @@
         </is>
       </c>
       <c r="AJ125">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="AK125">
-        <v>1.38</v>
+        <v>1.7</v>
       </c>
       <c r="AL125">
         <v>0</v>
@@ -20847,64 +20847,64 @@
         </is>
       </c>
       <c r="N126">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="O126">
-        <v>5.5</v>
+        <v>6</v>
       </c>
       <c r="P126">
-        <v>9.75</v>
+        <v>11</v>
       </c>
       <c r="Q126">
+        <v>1.72</v>
+      </c>
+      <c r="R126">
+        <v>2.35</v>
+      </c>
+      <c r="S126">
+        <v>1.25</v>
+      </c>
+      <c r="T126">
+        <v>3.45</v>
+      </c>
+      <c r="U126">
+        <v>2.2</v>
+      </c>
+      <c r="V126">
         <v>1.6</v>
-      </c>
-      <c r="R126">
-        <v>2.78</v>
-      </c>
-      <c r="S126">
-        <v>1.22</v>
-      </c>
-      <c r="T126">
-        <v>3.6</v>
-      </c>
-      <c r="U126">
-        <v>2.33</v>
-      </c>
-      <c r="V126">
-        <v>1.54</v>
       </c>
       <c r="W126">
         <v>1.14</v>
       </c>
       <c r="X126">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y126">
-        <v>1.11</v>
+        <v>1.18</v>
       </c>
       <c r="Z126">
-        <v>4.51</v>
+        <v>4.5</v>
       </c>
       <c r="AA126">
-        <v>1.61</v>
+        <v>1.57</v>
       </c>
       <c r="AB126">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="AC126">
-        <v>2.33</v>
+        <v>2.4</v>
       </c>
       <c r="AD126">
-        <v>1.38</v>
+        <v>1.53</v>
       </c>
       <c r="AE126">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="AF126">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="AG126">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="AH126" t="inlineStr">
         <is>
@@ -20917,10 +20917,10 @@
         </is>
       </c>
       <c r="AJ126">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="AK126">
-        <v>3.7</v>
+        <v>3.2</v>
       </c>
       <c r="AL126">
         <v>0</v>
@@ -22018,7 +22018,7 @@
         <v>1.09</v>
       </c>
       <c r="X133">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y133">
         <v>1.2</v>
@@ -22033,10 +22033,10 @@
         <v>2.05</v>
       </c>
       <c r="AC133">
-        <v>2.74</v>
+        <v>2.8</v>
       </c>
       <c r="AD133">
-        <v>1.35</v>
+        <v>1.39</v>
       </c>
       <c r="AE133">
         <v>1.1</v>
@@ -22058,7 +22058,7 @@
         </is>
       </c>
       <c r="AJ133">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="AK133">
         <v>1.08</v>

--- a/jogos_2026-08-02.xlsx
+++ b/jogos_2026-08-02.xlsx
@@ -813,37 +813,37 @@
         <v>2.25</v>
       </c>
       <c r="S3">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="T3">
+        <v>2.9</v>
+      </c>
+      <c r="U3">
         <v>2.75</v>
-      </c>
-      <c r="U3">
-        <v>2.43</v>
       </c>
       <c r="V3">
         <v>1.4</v>
       </c>
       <c r="W3">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="X3">
         <v>1.01</v>
       </c>
       <c r="Y3">
-        <v>1.22</v>
+        <v>1.29</v>
       </c>
       <c r="Z3">
         <v>3.4</v>
       </c>
       <c r="AA3">
-        <v>1.87</v>
+        <v>1.74</v>
       </c>
       <c r="AB3">
-        <v>1.8</v>
+        <v>1.89</v>
       </c>
       <c r="AC3">
-        <v>3.4</v>
+        <v>2.8</v>
       </c>
       <c r="AD3">
         <v>1.27</v>
@@ -855,7 +855,7 @@
         <v>1.75</v>
       </c>
       <c r="AG3">
-        <v>1.95</v>
+        <v>1.93</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -970,7 +970,7 @@
         <v>3.4</v>
       </c>
       <c r="Q4">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
       <c r="R4">
         <v>2.38</v>
@@ -994,7 +994,7 @@
         <v>1.02</v>
       </c>
       <c r="Y4">
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
       <c r="Z4">
         <v>3.92</v>
@@ -1003,7 +1003,7 @@
         <v>1.67</v>
       </c>
       <c r="AB4">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="AC4">
         <v>2.62</v>
@@ -1018,7 +1018,7 @@
         <v>1.62</v>
       </c>
       <c r="AG4">
-        <v>2.25</v>
+        <v>2.19</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1034,7 +1034,7 @@
         <v>1.22</v>
       </c>
       <c r="AK4">
-        <v>1.73</v>
+        <v>1.8</v>
       </c>
       <c r="AL4">
         <v>0</v>
@@ -1142,13 +1142,13 @@
         <v>1.25</v>
       </c>
       <c r="T5">
-        <v>3.4</v>
+        <v>3.28</v>
       </c>
       <c r="U5">
-        <v>2.31</v>
+        <v>2.37</v>
       </c>
       <c r="V5">
-        <v>1.5</v>
+        <v>1.55</v>
       </c>
       <c r="W5">
         <v>1.09</v>
@@ -1287,13 +1287,13 @@
         </is>
       </c>
       <c r="N6">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="O6">
-        <v>5</v>
+        <v>4.6</v>
       </c>
       <c r="P6">
-        <v>6.7</v>
+        <v>6.4</v>
       </c>
       <c r="Q6">
         <v>1.75</v>
@@ -1308,43 +1308,43 @@
         <v>3.11</v>
       </c>
       <c r="U6">
-        <v>2.51</v>
+        <v>2.48</v>
       </c>
       <c r="V6">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="W6">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="X6">
         <v>1.02</v>
       </c>
       <c r="Y6">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="Z6">
-        <v>3.86</v>
+        <v>3.94</v>
       </c>
       <c r="AA6">
-        <v>1.68</v>
+        <v>1.64</v>
       </c>
       <c r="AB6">
-        <v>2.02</v>
+        <v>2.08</v>
       </c>
       <c r="AC6">
-        <v>2.62</v>
+        <v>2.56</v>
       </c>
       <c r="AD6">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="AE6">
         <v>1.14</v>
       </c>
       <c r="AF6">
-        <v>1.82</v>
+        <v>1.93</v>
       </c>
       <c r="AG6">
-        <v>1.85</v>
+        <v>1.75</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1357,10 +1357,10 @@
         </is>
       </c>
       <c r="AJ6">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="AK6">
-        <v>3.04</v>
+        <v>2.92</v>
       </c>
       <c r="AL6">
         <v>0</v>
@@ -1450,13 +1450,13 @@
         </is>
       </c>
       <c r="N7">
-        <v>5.7</v>
+        <v>5.5</v>
       </c>
       <c r="O7">
-        <v>4.5</v>
+        <v>4.75</v>
       </c>
       <c r="P7">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="Q7">
         <v>6</v>
@@ -1471,13 +1471,13 @@
         <v>3.74</v>
       </c>
       <c r="U7">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="V7">
-        <v>1.64</v>
+        <v>1.67</v>
       </c>
       <c r="W7">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="X7">
         <v>1.02</v>
@@ -1489,10 +1489,10 @@
         <v>5.3</v>
       </c>
       <c r="AA7">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="AB7">
-        <v>2.52</v>
+        <v>2.6</v>
       </c>
       <c r="AC7">
         <v>2.15</v>
@@ -2070,12 +2070,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Daejeon Citizen</t>
+          <t>Ulsan</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Gwangju</t>
+          <t>Anyang</t>
         </is>
       </c>
       <c r="G11">
@@ -2102,64 +2102,64 @@
         </is>
       </c>
       <c r="N11">
-        <v>1.48</v>
+        <v>1.85</v>
       </c>
       <c r="O11">
-        <v>4</v>
+        <v>3.4</v>
       </c>
       <c r="P11">
-        <v>5.25</v>
+        <v>3.5</v>
       </c>
       <c r="Q11">
-        <v>1.98</v>
+        <v>2.28</v>
       </c>
       <c r="R11">
-        <v>2.29</v>
+        <v>2.15</v>
       </c>
       <c r="S11">
         <v>1.36</v>
       </c>
       <c r="T11">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="U11">
-        <v>2.63</v>
+        <v>2.65</v>
       </c>
       <c r="V11">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="W11">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="X11">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="Y11">
         <v>1.22</v>
       </c>
       <c r="Z11">
-        <v>3.54</v>
+        <v>3.86</v>
       </c>
       <c r="AA11">
-        <v>1.85</v>
+        <v>1.89</v>
       </c>
       <c r="AB11">
-        <v>1.97</v>
+        <v>1.89</v>
       </c>
       <c r="AC11">
-        <v>2.89</v>
+        <v>3.05</v>
       </c>
       <c r="AD11">
-        <v>1.32</v>
+        <v>1.38</v>
       </c>
       <c r="AE11">
         <v>1.08</v>
       </c>
       <c r="AF11">
-        <v>2.05</v>
+        <v>1.7</v>
       </c>
       <c r="AG11">
-        <v>1.77</v>
+        <v>2.04</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2172,10 +2172,10 @@
         </is>
       </c>
       <c r="AJ11">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="AK11">
-        <v>2.5</v>
+        <v>1.87</v>
       </c>
       <c r="AL11">
         <v>0</v>
@@ -2396,12 +2396,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Ulsan</t>
+          <t>Daejeon Citizen</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Anyang</t>
+          <t>Gwangju</t>
         </is>
       </c>
       <c r="G13">
@@ -2428,64 +2428,64 @@
         </is>
       </c>
       <c r="N13">
-        <v>1.85</v>
+        <v>1.48</v>
       </c>
       <c r="O13">
-        <v>3.4</v>
+        <v>4</v>
       </c>
       <c r="P13">
-        <v>3.5</v>
+        <v>5.25</v>
       </c>
       <c r="Q13">
-        <v>2.28</v>
+        <v>1.98</v>
       </c>
       <c r="R13">
-        <v>2.15</v>
+        <v>2.29</v>
       </c>
       <c r="S13">
         <v>1.36</v>
       </c>
       <c r="T13">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="U13">
-        <v>2.65</v>
+        <v>2.63</v>
       </c>
       <c r="V13">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="W13">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="X13">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="Y13">
         <v>1.22</v>
       </c>
       <c r="Z13">
-        <v>3.86</v>
+        <v>3.54</v>
       </c>
       <c r="AA13">
-        <v>1.89</v>
+        <v>1.85</v>
       </c>
       <c r="AB13">
-        <v>1.89</v>
+        <v>1.97</v>
       </c>
       <c r="AC13">
-        <v>3.05</v>
+        <v>2.89</v>
       </c>
       <c r="AD13">
-        <v>1.38</v>
+        <v>1.32</v>
       </c>
       <c r="AE13">
         <v>1.08</v>
       </c>
       <c r="AF13">
-        <v>1.7</v>
+        <v>2.05</v>
       </c>
       <c r="AG13">
-        <v>2.04</v>
+        <v>1.77</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2498,10 +2498,10 @@
         </is>
       </c>
       <c r="AJ13">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="AK13">
-        <v>1.87</v>
+        <v>2.5</v>
       </c>
       <c r="AL13">
         <v>0</v>
@@ -2885,12 +2885,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Ansan Greeners</t>
+          <t>Gimpo Citizen</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Gimhae City</t>
+          <t>Gyeongnam</t>
         </is>
       </c>
       <c r="G16">
@@ -2917,64 +2917,64 @@
         </is>
       </c>
       <c r="N16">
-        <v>2.65</v>
+        <v>1.94</v>
       </c>
       <c r="O16">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="P16">
-        <v>2.1</v>
+        <v>3.5</v>
       </c>
       <c r="Q16">
-        <v>3.4</v>
+        <v>2.62</v>
       </c>
       <c r="R16">
-        <v>2.12</v>
+        <v>2.15</v>
       </c>
       <c r="S16">
-        <v>1.34</v>
+        <v>1.4</v>
       </c>
       <c r="T16">
-        <v>3.01</v>
+        <v>2.48</v>
       </c>
       <c r="U16">
-        <v>2.74</v>
+        <v>3.12</v>
       </c>
       <c r="V16">
-        <v>1.37</v>
+        <v>1.29</v>
       </c>
       <c r="W16">
-        <v>1.08</v>
+        <v>1.02</v>
       </c>
       <c r="X16">
         <v>1.05</v>
       </c>
       <c r="Y16">
-        <v>1.29</v>
+        <v>1.4</v>
       </c>
       <c r="Z16">
-        <v>3.4</v>
+        <v>3.05</v>
       </c>
       <c r="AA16">
-        <v>1.9</v>
+        <v>2.29</v>
       </c>
       <c r="AB16">
-        <v>1.87</v>
+        <v>1.61</v>
       </c>
       <c r="AC16">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="AD16">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="AE16">
-        <v>1.11</v>
+        <v>1.04</v>
       </c>
       <c r="AF16">
-        <v>1.67</v>
+        <v>1.92</v>
       </c>
       <c r="AG16">
-        <v>2.03</v>
+        <v>1.77</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -2987,10 +2987,10 @@
         </is>
       </c>
       <c r="AJ16">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="AK16">
-        <v>1.32</v>
+        <v>1.83</v>
       </c>
       <c r="AL16">
         <v>0</v>
@@ -3048,12 +3048,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Gimpo Citizen</t>
+          <t>Ansan Greeners</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Gyeongnam</t>
+          <t>Gimhae City</t>
         </is>
       </c>
       <c r="G17">
@@ -3080,64 +3080,64 @@
         </is>
       </c>
       <c r="N17">
-        <v>1.94</v>
+        <v>2.65</v>
       </c>
       <c r="O17">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="P17">
-        <v>3.5</v>
+        <v>2.1</v>
       </c>
       <c r="Q17">
-        <v>2.62</v>
+        <v>3.4</v>
       </c>
       <c r="R17">
-        <v>2.15</v>
+        <v>2.12</v>
       </c>
       <c r="S17">
-        <v>1.4</v>
+        <v>1.34</v>
       </c>
       <c r="T17">
-        <v>2.48</v>
+        <v>3.01</v>
       </c>
       <c r="U17">
-        <v>3.12</v>
+        <v>2.74</v>
       </c>
       <c r="V17">
-        <v>1.29</v>
+        <v>1.37</v>
       </c>
       <c r="W17">
-        <v>1.02</v>
+        <v>1.08</v>
       </c>
       <c r="X17">
         <v>1.05</v>
       </c>
       <c r="Y17">
-        <v>1.4</v>
+        <v>1.29</v>
       </c>
       <c r="Z17">
-        <v>3.05</v>
+        <v>3.4</v>
       </c>
       <c r="AA17">
-        <v>2.29</v>
+        <v>1.9</v>
       </c>
       <c r="AB17">
-        <v>1.61</v>
+        <v>1.87</v>
       </c>
       <c r="AC17">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="AD17">
-        <v>1.2</v>
+        <v>1.33</v>
       </c>
       <c r="AE17">
-        <v>1.04</v>
+        <v>1.11</v>
       </c>
       <c r="AF17">
-        <v>1.92</v>
+        <v>1.67</v>
       </c>
       <c r="AG17">
-        <v>1.77</v>
+        <v>2.03</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3150,10 +3150,10 @@
         </is>
       </c>
       <c r="AJ17">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="AK17">
-        <v>1.83</v>
+        <v>1.32</v>
       </c>
       <c r="AL17">
         <v>0</v>
@@ -3211,12 +3211,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Suzhou Dongwu</t>
+          <t>Shenzhen Juniors</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Meizhou Hakka</t>
+          <t>Wuxi Wugou</t>
         </is>
       </c>
       <c r="G18">
@@ -3243,80 +3243,80 @@
         </is>
       </c>
       <c r="N18">
+        <v>2.12</v>
+      </c>
+      <c r="O18">
+        <v>3.5</v>
+      </c>
+      <c r="P18">
+        <v>2.9</v>
+      </c>
+      <c r="Q18">
+        <v>2.55</v>
+      </c>
+      <c r="R18">
         <v>2.25</v>
       </c>
-      <c r="O18">
-        <v>3.05</v>
-      </c>
-      <c r="P18">
-        <v>3</v>
-      </c>
-      <c r="Q18">
-        <v>2.89</v>
-      </c>
-      <c r="R18">
-        <v>2.1</v>
-      </c>
       <c r="S18">
-        <v>1.41</v>
+        <v>1.34</v>
       </c>
       <c r="T18">
-        <v>2.65</v>
+        <v>3.1</v>
       </c>
       <c r="U18">
-        <v>2.88</v>
+        <v>2.39</v>
       </c>
       <c r="V18">
-        <v>1.36</v>
+        <v>1.5</v>
       </c>
       <c r="W18">
-        <v>1.07</v>
+        <v>1.11</v>
       </c>
       <c r="X18">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y18">
-        <v>1.28</v>
+        <v>1.22</v>
       </c>
       <c r="Z18">
-        <v>3.05</v>
+        <v>4.33</v>
       </c>
       <c r="AA18">
-        <v>2</v>
+        <v>1.64</v>
       </c>
       <c r="AB18">
-        <v>1.8</v>
+        <v>2.19</v>
       </c>
       <c r="AC18">
-        <v>3.5</v>
+        <v>2.64</v>
       </c>
       <c r="AD18">
+        <v>1.44</v>
+      </c>
+      <c r="AE18">
+        <v>1.13</v>
+      </c>
+      <c r="AF18">
+        <v>1.53</v>
+      </c>
+      <c r="AG18">
+        <v>2.29</v>
+      </c>
+      <c r="AH18" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI18" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ18">
         <v>1.22</v>
       </c>
-      <c r="AE18">
-        <v>1.03</v>
-      </c>
-      <c r="AF18">
-        <v>1.73</v>
-      </c>
-      <c r="AG18">
-        <v>1.91</v>
-      </c>
-      <c r="AH18" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI18" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ18">
-        <v>1.27</v>
-      </c>
       <c r="AK18">
-        <v>1.57</v>
+        <v>1.65</v>
       </c>
       <c r="AL18">
         <v>0</v>
@@ -3374,12 +3374,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Shenzhen Juniors</t>
+          <t>Suzhou Dongwu</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Wuxi Wugou</t>
+          <t>Meizhou Hakka</t>
         </is>
       </c>
       <c r="G19">
@@ -3406,64 +3406,64 @@
         </is>
       </c>
       <c r="N19">
-        <v>2.12</v>
+        <v>2.25</v>
       </c>
       <c r="O19">
+        <v>3.05</v>
+      </c>
+      <c r="P19">
+        <v>3</v>
+      </c>
+      <c r="Q19">
+        <v>2.89</v>
+      </c>
+      <c r="R19">
+        <v>2.1</v>
+      </c>
+      <c r="S19">
+        <v>1.41</v>
+      </c>
+      <c r="T19">
+        <v>2.65</v>
+      </c>
+      <c r="U19">
+        <v>2.88</v>
+      </c>
+      <c r="V19">
+        <v>1.36</v>
+      </c>
+      <c r="W19">
+        <v>1.07</v>
+      </c>
+      <c r="X19">
+        <v>1.01</v>
+      </c>
+      <c r="Y19">
+        <v>1.28</v>
+      </c>
+      <c r="Z19">
+        <v>3.05</v>
+      </c>
+      <c r="AA19">
+        <v>2</v>
+      </c>
+      <c r="AB19">
+        <v>1.8</v>
+      </c>
+      <c r="AC19">
         <v>3.5</v>
       </c>
-      <c r="P19">
-        <v>2.9</v>
-      </c>
-      <c r="Q19">
-        <v>2.55</v>
-      </c>
-      <c r="R19">
-        <v>2.25</v>
-      </c>
-      <c r="S19">
-        <v>1.34</v>
-      </c>
-      <c r="T19">
-        <v>3.1</v>
-      </c>
-      <c r="U19">
-        <v>2.39</v>
-      </c>
-      <c r="V19">
-        <v>1.5</v>
-      </c>
-      <c r="W19">
-        <v>1.11</v>
-      </c>
-      <c r="X19">
-        <v>1.02</v>
-      </c>
-      <c r="Y19">
+      <c r="AD19">
         <v>1.22</v>
       </c>
-      <c r="Z19">
-        <v>4.33</v>
-      </c>
-      <c r="AA19">
-        <v>1.64</v>
-      </c>
-      <c r="AB19">
-        <v>2.19</v>
-      </c>
-      <c r="AC19">
-        <v>2.64</v>
-      </c>
-      <c r="AD19">
-        <v>1.44</v>
-      </c>
       <c r="AE19">
-        <v>1.13</v>
+        <v>1.03</v>
       </c>
       <c r="AF19">
-        <v>1.53</v>
+        <v>1.73</v>
       </c>
       <c r="AG19">
-        <v>2.29</v>
+        <v>1.91</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3476,10 +3476,10 @@
         </is>
       </c>
       <c r="AJ19">
-        <v>1.22</v>
+        <v>1.27</v>
       </c>
       <c r="AK19">
-        <v>1.65</v>
+        <v>1.57</v>
       </c>
       <c r="AL19">
         <v>0</v>
@@ -14132,12 +14132,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Tallinna FC Flora</t>
+          <t>Vaprus</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Harju Jalgpallikool</t>
+          <t>Tallinna FC Levadia</t>
         </is>
       </c>
       <c r="G85">
@@ -14164,64 +14164,64 @@
         </is>
       </c>
       <c r="N85">
-        <v>1.52</v>
+        <v>11.7</v>
       </c>
       <c r="O85">
-        <v>4.05</v>
+        <v>5.5</v>
       </c>
       <c r="P85">
-        <v>6.59</v>
+        <v>1.25</v>
       </c>
       <c r="Q85">
-        <v>2</v>
+        <v>7.61</v>
       </c>
       <c r="R85">
-        <v>2.5</v>
+        <v>2.82</v>
       </c>
       <c r="S85">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="T85">
-        <v>3.42</v>
+        <v>3.58</v>
       </c>
       <c r="U85">
-        <v>2.18</v>
+        <v>2.13</v>
       </c>
       <c r="V85">
-        <v>1.63</v>
+        <v>1.65</v>
       </c>
       <c r="W85">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="X85">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y85">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="Z85">
         <v>6</v>
       </c>
       <c r="AA85">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="AB85">
-        <v>2.63</v>
+        <v>2.7</v>
       </c>
       <c r="AC85">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="AD85">
-        <v>1.63</v>
+        <v>1.67</v>
       </c>
       <c r="AE85">
-        <v>1.21</v>
+        <v>1.29</v>
       </c>
       <c r="AF85">
-        <v>1.53</v>
+        <v>1.81</v>
       </c>
       <c r="AG85">
-        <v>2.32</v>
+        <v>1.89</v>
       </c>
       <c r="AH85" t="inlineStr">
         <is>
@@ -14234,10 +14234,10 @@
         </is>
       </c>
       <c r="AJ85">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="AK85">
-        <v>2.3</v>
+        <v>1</v>
       </c>
       <c r="AL85">
         <v>0</v>
@@ -14295,12 +14295,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Vaprus</t>
+          <t>Tallinna FC Flora</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Tallinna FC Levadia</t>
+          <t>Harju Jalgpallikool</t>
         </is>
       </c>
       <c r="G86">
@@ -14327,64 +14327,64 @@
         </is>
       </c>
       <c r="N86">
-        <v>11.7</v>
+        <v>1.52</v>
       </c>
       <c r="O86">
-        <v>5.5</v>
+        <v>4.05</v>
       </c>
       <c r="P86">
-        <v>1.25</v>
+        <v>6.59</v>
       </c>
       <c r="Q86">
-        <v>7.61</v>
+        <v>2</v>
       </c>
       <c r="R86">
-        <v>2.82</v>
+        <v>2.5</v>
       </c>
       <c r="S86">
-        <v>1.21</v>
+        <v>1.23</v>
       </c>
       <c r="T86">
-        <v>3.58</v>
+        <v>3.42</v>
       </c>
       <c r="U86">
-        <v>2.13</v>
+        <v>2.18</v>
       </c>
       <c r="V86">
-        <v>1.65</v>
+        <v>1.63</v>
       </c>
       <c r="W86">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="X86">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y86">
-        <v>1.13</v>
+        <v>1.1</v>
       </c>
       <c r="Z86">
         <v>6</v>
       </c>
       <c r="AA86">
-        <v>1.44</v>
+        <v>1.47</v>
       </c>
       <c r="AB86">
-        <v>2.7</v>
+        <v>2.63</v>
       </c>
       <c r="AC86">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="AD86">
-        <v>1.67</v>
+        <v>1.63</v>
       </c>
       <c r="AE86">
-        <v>1.29</v>
+        <v>1.21</v>
       </c>
       <c r="AF86">
-        <v>1.81</v>
+        <v>1.53</v>
       </c>
       <c r="AG86">
-        <v>1.89</v>
+        <v>2.32</v>
       </c>
       <c r="AH86" t="inlineStr">
         <is>
@@ -14397,10 +14397,10 @@
         </is>
       </c>
       <c r="AJ86">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="AK86">
-        <v>1</v>
+        <v>2.3</v>
       </c>
       <c r="AL86">
         <v>0</v>
@@ -19511,12 +19511,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Temperley</t>
+          <t>Deportivo Maipú</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Gimnasia y Tiro</t>
+          <t>Atlanta</t>
         </is>
       </c>
       <c r="G118">
@@ -19543,64 +19543,64 @@
         </is>
       </c>
       <c r="N118">
-        <v>2.05</v>
+        <v>2.6</v>
       </c>
       <c r="O118">
-        <v>2.8</v>
+        <v>2.87</v>
       </c>
       <c r="P118">
-        <v>4</v>
+        <v>2.59</v>
       </c>
       <c r="Q118">
-        <v>2.85</v>
+        <v>3.45</v>
       </c>
       <c r="R118">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="S118">
-        <v>1.58</v>
+        <v>1.55</v>
       </c>
       <c r="T118">
-        <v>2.16</v>
+        <v>2.25</v>
       </c>
       <c r="U118">
-        <v>4.2</v>
+        <v>3.45</v>
       </c>
       <c r="V118">
-        <v>1.15</v>
+        <v>1.25</v>
       </c>
       <c r="W118">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="X118">
-        <v>1.1</v>
+        <v>1.07</v>
       </c>
       <c r="Y118">
-        <v>1.62</v>
+        <v>1.53</v>
       </c>
       <c r="Z118">
-        <v>2.08</v>
+        <v>2.45</v>
       </c>
       <c r="AA118">
-        <v>3.2</v>
+        <v>2.7</v>
       </c>
       <c r="AB118">
-        <v>1.35</v>
+        <v>1.41</v>
       </c>
       <c r="AC118">
-        <v>6.5</v>
+        <v>4.95</v>
       </c>
       <c r="AD118">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="AE118">
         <v>1.01</v>
       </c>
       <c r="AF118">
-        <v>2.3</v>
+        <v>2.04</v>
       </c>
       <c r="AG118">
-        <v>1.5</v>
+        <v>1.65</v>
       </c>
       <c r="AH118" t="inlineStr">
         <is>
@@ -19613,10 +19613,10 @@
         </is>
       </c>
       <c r="AJ118">
-        <v>1.37</v>
+        <v>1.35</v>
       </c>
       <c r="AK118">
-        <v>1.63</v>
+        <v>1.42</v>
       </c>
       <c r="AL118">
         <v>0</v>
@@ -19674,12 +19674,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Deportivo Maipú</t>
+          <t>Temperley</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Atlanta</t>
+          <t>Gimnasia y Tiro</t>
         </is>
       </c>
       <c r="G119">
@@ -19706,64 +19706,64 @@
         </is>
       </c>
       <c r="N119">
-        <v>2.6</v>
+        <v>2.05</v>
       </c>
       <c r="O119">
-        <v>2.87</v>
+        <v>2.8</v>
       </c>
       <c r="P119">
-        <v>2.59</v>
+        <v>4</v>
       </c>
       <c r="Q119">
-        <v>3.45</v>
+        <v>2.85</v>
       </c>
       <c r="R119">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="S119">
-        <v>1.55</v>
+        <v>1.58</v>
       </c>
       <c r="T119">
-        <v>2.25</v>
+        <v>2.16</v>
       </c>
       <c r="U119">
-        <v>3.45</v>
+        <v>4.2</v>
       </c>
       <c r="V119">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="W119">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="X119">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="Y119">
-        <v>1.53</v>
+        <v>1.62</v>
       </c>
       <c r="Z119">
-        <v>2.45</v>
+        <v>2.08</v>
       </c>
       <c r="AA119">
-        <v>2.7</v>
+        <v>3.2</v>
       </c>
       <c r="AB119">
-        <v>1.41</v>
+        <v>1.35</v>
       </c>
       <c r="AC119">
-        <v>4.95</v>
+        <v>6.5</v>
       </c>
       <c r="AD119">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="AE119">
         <v>1.01</v>
       </c>
       <c r="AF119">
-        <v>2.04</v>
+        <v>2.3</v>
       </c>
       <c r="AG119">
-        <v>1.65</v>
+        <v>1.5</v>
       </c>
       <c r="AH119" t="inlineStr">
         <is>
@@ -19776,10 +19776,10 @@
         </is>
       </c>
       <c r="AJ119">
-        <v>1.35</v>
+        <v>1.37</v>
       </c>
       <c r="AK119">
-        <v>1.42</v>
+        <v>1.63</v>
       </c>
       <c r="AL119">
         <v>0</v>

--- a/jogos_2026-08-02.xlsx
+++ b/jogos_2026-08-02.xlsx
@@ -1092,12 +1092,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Rockdale City Suns</t>
+          <t>Marconi Stallions</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Manly United</t>
+          <t>St George City FA</t>
         </is>
       </c>
       <c r="G5">
@@ -1124,31 +1124,31 @@
         </is>
       </c>
       <c r="N5">
+        <v>1.33</v>
+      </c>
+      <c r="O5">
+        <v>4.6</v>
+      </c>
+      <c r="P5">
+        <v>6.4</v>
+      </c>
+      <c r="Q5">
         <v>1.75</v>
       </c>
-      <c r="O5">
-        <v>3.8</v>
-      </c>
-      <c r="P5">
-        <v>3.63</v>
-      </c>
-      <c r="Q5">
-        <v>2.2</v>
-      </c>
       <c r="R5">
-        <v>2.25</v>
+        <v>2.47</v>
       </c>
       <c r="S5">
-        <v>1.25</v>
+        <v>1.32</v>
       </c>
       <c r="T5">
-        <v>3.28</v>
+        <v>3.11</v>
       </c>
       <c r="U5">
-        <v>2.37</v>
+        <v>2.48</v>
       </c>
       <c r="V5">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="W5">
         <v>1.09</v>
@@ -1157,31 +1157,31 @@
         <v>1.02</v>
       </c>
       <c r="Y5">
-        <v>1.13</v>
+        <v>1.17</v>
       </c>
       <c r="Z5">
-        <v>4.35</v>
+        <v>3.94</v>
       </c>
       <c r="AA5">
-        <v>1.6</v>
+        <v>1.64</v>
       </c>
       <c r="AB5">
-        <v>2.19</v>
+        <v>2.08</v>
       </c>
       <c r="AC5">
-        <v>2.5</v>
+        <v>2.56</v>
       </c>
       <c r="AD5">
-        <v>1.53</v>
+        <v>1.4</v>
       </c>
       <c r="AE5">
-        <v>1.22</v>
+        <v>1.14</v>
       </c>
       <c r="AF5">
-        <v>1.57</v>
+        <v>1.93</v>
       </c>
       <c r="AG5">
-        <v>2.25</v>
+        <v>1.75</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1194,10 +1194,10 @@
         </is>
       </c>
       <c r="AJ5">
-        <v>1.19</v>
+        <v>1.11</v>
       </c>
       <c r="AK5">
-        <v>1.94</v>
+        <v>2.92</v>
       </c>
       <c r="AL5">
         <v>0</v>
@@ -1255,12 +1255,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Marconi Stallions</t>
+          <t>Rockdale City Suns</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>St George City FA</t>
+          <t>Manly United</t>
         </is>
       </c>
       <c r="G6">
@@ -1287,31 +1287,31 @@
         </is>
       </c>
       <c r="N6">
-        <v>1.33</v>
+        <v>1.75</v>
       </c>
       <c r="O6">
-        <v>4.6</v>
+        <v>3.8</v>
       </c>
       <c r="P6">
-        <v>6.4</v>
+        <v>3.63</v>
       </c>
       <c r="Q6">
-        <v>1.75</v>
+        <v>2.2</v>
       </c>
       <c r="R6">
-        <v>2.47</v>
+        <v>2.25</v>
       </c>
       <c r="S6">
-        <v>1.32</v>
+        <v>1.25</v>
       </c>
       <c r="T6">
-        <v>3.11</v>
+        <v>3.28</v>
       </c>
       <c r="U6">
-        <v>2.48</v>
+        <v>2.37</v>
       </c>
       <c r="V6">
-        <v>1.5</v>
+        <v>1.55</v>
       </c>
       <c r="W6">
         <v>1.09</v>
@@ -1320,31 +1320,31 @@
         <v>1.02</v>
       </c>
       <c r="Y6">
-        <v>1.17</v>
+        <v>1.13</v>
       </c>
       <c r="Z6">
-        <v>3.94</v>
+        <v>4.35</v>
       </c>
       <c r="AA6">
-        <v>1.64</v>
+        <v>1.6</v>
       </c>
       <c r="AB6">
-        <v>2.08</v>
+        <v>2.19</v>
       </c>
       <c r="AC6">
-        <v>2.56</v>
+        <v>2.5</v>
       </c>
       <c r="AD6">
-        <v>1.4</v>
+        <v>1.53</v>
       </c>
       <c r="AE6">
-        <v>1.14</v>
+        <v>1.22</v>
       </c>
       <c r="AF6">
-        <v>1.93</v>
+        <v>1.57</v>
       </c>
       <c r="AG6">
-        <v>1.75</v>
+        <v>2.25</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1357,10 +1357,10 @@
         </is>
       </c>
       <c r="AJ6">
-        <v>1.11</v>
+        <v>1.19</v>
       </c>
       <c r="AK6">
-        <v>2.92</v>
+        <v>1.94</v>
       </c>
       <c r="AL6">
         <v>0</v>
@@ -1613,28 +1613,28 @@
         </is>
       </c>
       <c r="N8">
-        <v>3.6</v>
+        <v>4.45</v>
       </c>
       <c r="O8">
-        <v>3.35</v>
+        <v>3.25</v>
       </c>
       <c r="P8">
-        <v>1.84</v>
+        <v>1.78</v>
       </c>
       <c r="Q8">
-        <v>4.95</v>
+        <v>5</v>
       </c>
       <c r="R8">
-        <v>2.02</v>
+        <v>2.01</v>
       </c>
       <c r="S8">
         <v>1.43</v>
       </c>
       <c r="T8">
-        <v>2.76</v>
+        <v>2.59</v>
       </c>
       <c r="U8">
-        <v>3.15</v>
+        <v>3.05</v>
       </c>
       <c r="V8">
         <v>1.32</v>
@@ -1652,16 +1652,16 @@
         <v>2.97</v>
       </c>
       <c r="AA8">
-        <v>2.12</v>
+        <v>2.13</v>
       </c>
       <c r="AB8">
         <v>1.73</v>
       </c>
       <c r="AC8">
-        <v>3.78</v>
+        <v>3.68</v>
       </c>
       <c r="AD8">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="AE8">
         <v>1.03</v>
@@ -1683,10 +1683,10 @@
         </is>
       </c>
       <c r="AJ8">
-        <v>1.3</v>
+        <v>1.85</v>
       </c>
       <c r="AK8">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AL8">
         <v>0</v>
@@ -1954,16 +1954,16 @@
         <v>2.38</v>
       </c>
       <c r="S10">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="T10">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="U10">
         <v>2.33</v>
       </c>
       <c r="V10">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="W10">
         <v>1.09</v>
@@ -1972,31 +1972,31 @@
         <v>1.03</v>
       </c>
       <c r="Y10">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="Z10">
-        <v>4.75</v>
+        <v>4.6</v>
       </c>
       <c r="AA10">
         <v>1.62</v>
       </c>
       <c r="AB10">
-        <v>2.2</v>
+        <v>2.19</v>
       </c>
       <c r="AC10">
-        <v>2.5</v>
+        <v>2.43</v>
       </c>
       <c r="AD10">
-        <v>1.43</v>
+        <v>1.5</v>
       </c>
       <c r="AE10">
-        <v>1.16</v>
+        <v>1.21</v>
       </c>
       <c r="AF10">
         <v>1.57</v>
       </c>
       <c r="AG10">
-        <v>2.06</v>
+        <v>2.22</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2009,7 +2009,7 @@
         </is>
       </c>
       <c r="AJ10">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="AK10">
         <v>1.84</v>
@@ -2070,12 +2070,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Ulsan</t>
+          <t>Daejeon Citizen</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Anyang</t>
+          <t>Gwangju</t>
         </is>
       </c>
       <c r="G11">
@@ -2102,64 +2102,64 @@
         </is>
       </c>
       <c r="N11">
-        <v>1.85</v>
+        <v>1.38</v>
       </c>
       <c r="O11">
-        <v>3.4</v>
+        <v>4.25</v>
       </c>
       <c r="P11">
-        <v>3.5</v>
+        <v>5.9</v>
       </c>
       <c r="Q11">
-        <v>2.28</v>
+        <v>1.98</v>
       </c>
       <c r="R11">
-        <v>2.15</v>
+        <v>2.29</v>
       </c>
       <c r="S11">
         <v>1.36</v>
       </c>
       <c r="T11">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="U11">
-        <v>2.65</v>
+        <v>2.63</v>
       </c>
       <c r="V11">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="W11">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="X11">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="Y11">
         <v>1.22</v>
       </c>
       <c r="Z11">
-        <v>3.86</v>
+        <v>3.54</v>
       </c>
       <c r="AA11">
-        <v>1.89</v>
+        <v>1.85</v>
       </c>
       <c r="AB11">
-        <v>1.89</v>
+        <v>1.97</v>
       </c>
       <c r="AC11">
-        <v>3.05</v>
+        <v>2.89</v>
       </c>
       <c r="AD11">
-        <v>1.38</v>
+        <v>1.32</v>
       </c>
       <c r="AE11">
         <v>1.08</v>
       </c>
       <c r="AF11">
-        <v>1.7</v>
+        <v>2.05</v>
       </c>
       <c r="AG11">
-        <v>2.04</v>
+        <v>1.77</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2172,10 +2172,10 @@
         </is>
       </c>
       <c r="AJ11">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="AK11">
-        <v>1.87</v>
+        <v>2.5</v>
       </c>
       <c r="AL11">
         <v>0</v>
@@ -2277,7 +2277,7 @@
         <v>3.55</v>
       </c>
       <c r="R12">
-        <v>1.87</v>
+        <v>1.96</v>
       </c>
       <c r="S12">
         <v>1.44</v>
@@ -2289,7 +2289,7 @@
         <v>3.2</v>
       </c>
       <c r="V12">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="W12">
         <v>1.06</v>
@@ -2298,10 +2298,10 @@
         <v>1.07</v>
       </c>
       <c r="Y12">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="Z12">
-        <v>2.57</v>
+        <v>2.7</v>
       </c>
       <c r="AA12">
         <v>2.38</v>
@@ -2316,10 +2316,10 @@
         <v>1.2</v>
       </c>
       <c r="AE12">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="AF12">
-        <v>1.93</v>
+        <v>1.95</v>
       </c>
       <c r="AG12">
         <v>1.75</v>
@@ -2396,12 +2396,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Daejeon Citizen</t>
+          <t>Ulsan</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Gwangju</t>
+          <t>Anyang</t>
         </is>
       </c>
       <c r="G13">
@@ -2428,64 +2428,64 @@
         </is>
       </c>
       <c r="N13">
-        <v>1.48</v>
+        <v>1.89</v>
       </c>
       <c r="O13">
-        <v>4</v>
+        <v>3.6</v>
       </c>
       <c r="P13">
-        <v>5.25</v>
+        <v>3.8</v>
       </c>
       <c r="Q13">
-        <v>1.98</v>
+        <v>2.41</v>
       </c>
       <c r="R13">
-        <v>2.29</v>
+        <v>2.08</v>
       </c>
       <c r="S13">
         <v>1.36</v>
       </c>
       <c r="T13">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="U13">
-        <v>2.63</v>
+        <v>2.65</v>
       </c>
       <c r="V13">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="W13">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="X13">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="Y13">
         <v>1.22</v>
       </c>
       <c r="Z13">
-        <v>3.54</v>
+        <v>3.86</v>
       </c>
       <c r="AA13">
-        <v>1.85</v>
+        <v>1.89</v>
       </c>
       <c r="AB13">
-        <v>1.97</v>
+        <v>1.89</v>
       </c>
       <c r="AC13">
-        <v>2.89</v>
+        <v>3.09</v>
       </c>
       <c r="AD13">
-        <v>1.32</v>
+        <v>1.38</v>
       </c>
       <c r="AE13">
         <v>1.08</v>
       </c>
       <c r="AF13">
-        <v>2.05</v>
+        <v>1.7</v>
       </c>
       <c r="AG13">
-        <v>1.77</v>
+        <v>2.04</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2498,10 +2498,10 @@
         </is>
       </c>
       <c r="AJ13">
-        <v>1.22</v>
+        <v>1.19</v>
       </c>
       <c r="AK13">
-        <v>2.5</v>
+        <v>1.87</v>
       </c>
       <c r="AL13">
         <v>0</v>
@@ -2594,25 +2594,25 @@
         <v>2</v>
       </c>
       <c r="O14">
-        <v>3.3</v>
+        <v>3.28</v>
       </c>
       <c r="P14">
-        <v>3.1</v>
+        <v>2.77</v>
       </c>
       <c r="Q14">
-        <v>2.66</v>
+        <v>2.69</v>
       </c>
       <c r="R14">
         <v>2.2</v>
       </c>
       <c r="S14">
-        <v>1.33</v>
+        <v>1.38</v>
       </c>
       <c r="T14">
         <v>2.9</v>
       </c>
       <c r="U14">
-        <v>2.73</v>
+        <v>2.74</v>
       </c>
       <c r="V14">
         <v>1.4</v>
@@ -2621,22 +2621,22 @@
         <v>1.05</v>
       </c>
       <c r="X14">
-        <v>1</v>
+        <v>1.04</v>
       </c>
       <c r="Y14">
-        <v>1.26</v>
+        <v>1.2</v>
       </c>
       <c r="Z14">
-        <v>3.76</v>
+        <v>3.7</v>
       </c>
       <c r="AA14">
-        <v>1.79</v>
+        <v>1.68</v>
       </c>
       <c r="AB14">
-        <v>1.92</v>
+        <v>1.9</v>
       </c>
       <c r="AC14">
-        <v>2.92</v>
+        <v>3.08</v>
       </c>
       <c r="AD14">
         <v>1.36</v>
@@ -2645,10 +2645,10 @@
         <v>1.08</v>
       </c>
       <c r="AF14">
-        <v>1.58</v>
+        <v>1.64</v>
       </c>
       <c r="AG14">
-        <v>2.17</v>
+        <v>2.1</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2781,10 +2781,10 @@
         <v>1.5</v>
       </c>
       <c r="W15">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="X15">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y15">
         <v>1.21</v>
@@ -2793,7 +2793,7 @@
         <v>4.26</v>
       </c>
       <c r="AA15">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="AB15">
         <v>2.1</v>
@@ -2802,16 +2802,16 @@
         <v>2.66</v>
       </c>
       <c r="AD15">
-        <v>1.37</v>
+        <v>1.44</v>
       </c>
       <c r="AE15">
         <v>1.11</v>
       </c>
       <c r="AF15">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="AG15">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2827,7 +2827,7 @@
         <v>1.5</v>
       </c>
       <c r="AK15">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="AL15">
         <v>0</v>
@@ -2920,43 +2920,43 @@
         <v>1.94</v>
       </c>
       <c r="O16">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="P16">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="Q16">
-        <v>2.62</v>
+        <v>2.69</v>
       </c>
       <c r="R16">
-        <v>2.15</v>
+        <v>2.07</v>
       </c>
       <c r="S16">
         <v>1.4</v>
       </c>
       <c r="T16">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="U16">
         <v>3.12</v>
       </c>
       <c r="V16">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="W16">
         <v>1.02</v>
       </c>
       <c r="X16">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="Y16">
-        <v>1.4</v>
+        <v>1.29</v>
       </c>
       <c r="Z16">
         <v>3.05</v>
       </c>
       <c r="AA16">
-        <v>2.29</v>
+        <v>1.95</v>
       </c>
       <c r="AB16">
         <v>1.61</v>
@@ -2965,16 +2965,16 @@
         <v>3.3</v>
       </c>
       <c r="AD16">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="AE16">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="AF16">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="AG16">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -2990,7 +2990,7 @@
         <v>1.25</v>
       </c>
       <c r="AK16">
-        <v>1.83</v>
+        <v>1.76</v>
       </c>
       <c r="AL16">
         <v>0</v>
@@ -3080,13 +3080,13 @@
         </is>
       </c>
       <c r="N17">
-        <v>2.65</v>
+        <v>2.87</v>
       </c>
       <c r="O17">
-        <v>3.1</v>
+        <v>3.45</v>
       </c>
       <c r="P17">
-        <v>2.1</v>
+        <v>2.3</v>
       </c>
       <c r="Q17">
         <v>3.4</v>
@@ -3098,19 +3098,19 @@
         <v>1.34</v>
       </c>
       <c r="T17">
-        <v>3.01</v>
+        <v>3</v>
       </c>
       <c r="U17">
-        <v>2.74</v>
+        <v>2.62</v>
       </c>
       <c r="V17">
-        <v>1.37</v>
+        <v>1.41</v>
       </c>
       <c r="W17">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="X17">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="Y17">
         <v>1.29</v>
@@ -3119,16 +3119,16 @@
         <v>3.4</v>
       </c>
       <c r="AA17">
-        <v>1.9</v>
+        <v>1.93</v>
       </c>
       <c r="AB17">
         <v>1.87</v>
       </c>
       <c r="AC17">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="AD17">
-        <v>1.33</v>
+        <v>1.27</v>
       </c>
       <c r="AE17">
         <v>1.11</v>
@@ -3150,10 +3150,10 @@
         </is>
       </c>
       <c r="AJ17">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="AK17">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="AL17">
         <v>0</v>
@@ -3243,16 +3243,16 @@
         </is>
       </c>
       <c r="N18">
-        <v>2.12</v>
+        <v>2.05</v>
       </c>
       <c r="O18">
-        <v>3.5</v>
+        <v>3.23</v>
       </c>
       <c r="P18">
-        <v>2.9</v>
+        <v>2.65</v>
       </c>
       <c r="Q18">
-        <v>2.55</v>
+        <v>2.67</v>
       </c>
       <c r="R18">
         <v>2.25</v>
@@ -3276,7 +3276,7 @@
         <v>1.02</v>
       </c>
       <c r="Y18">
-        <v>1.22</v>
+        <v>1.16</v>
       </c>
       <c r="Z18">
         <v>4.33</v>
@@ -3285,7 +3285,7 @@
         <v>1.64</v>
       </c>
       <c r="AB18">
-        <v>2.19</v>
+        <v>2.1</v>
       </c>
       <c r="AC18">
         <v>2.64</v>
@@ -3313,10 +3313,10 @@
         </is>
       </c>
       <c r="AJ18">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="AK18">
-        <v>1.65</v>
+        <v>1.6</v>
       </c>
       <c r="AL18">
         <v>0</v>
@@ -3424,16 +3424,16 @@
         <v>1.41</v>
       </c>
       <c r="T19">
-        <v>2.65</v>
+        <v>2.72</v>
       </c>
       <c r="U19">
-        <v>2.88</v>
+        <v>2.95</v>
       </c>
       <c r="V19">
         <v>1.36</v>
       </c>
       <c r="W19">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="X19">
         <v>1.01</v>
@@ -3445,10 +3445,10 @@
         <v>3.05</v>
       </c>
       <c r="AA19">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="AB19">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="AC19">
         <v>3.5</v>
@@ -3457,13 +3457,13 @@
         <v>1.22</v>
       </c>
       <c r="AE19">
-        <v>1.03</v>
+        <v>1.1</v>
       </c>
       <c r="AF19">
         <v>1.73</v>
       </c>
       <c r="AG19">
-        <v>1.91</v>
+        <v>1.93</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3476,10 +3476,10 @@
         </is>
       </c>
       <c r="AJ19">
-        <v>1.27</v>
+        <v>1.35</v>
       </c>
       <c r="AK19">
-        <v>1.57</v>
+        <v>1.51</v>
       </c>
       <c r="AL19">
         <v>0</v>
@@ -3569,28 +3569,28 @@
         </is>
       </c>
       <c r="N20">
-        <v>1.71</v>
+        <v>1.82</v>
       </c>
       <c r="O20">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="P20">
-        <v>4.4</v>
+        <v>4</v>
       </c>
       <c r="Q20">
-        <v>2.27</v>
+        <v>2.33</v>
       </c>
       <c r="R20">
-        <v>2.25</v>
+        <v>2.23</v>
       </c>
       <c r="S20">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="T20">
-        <v>2.67</v>
+        <v>2.63</v>
       </c>
       <c r="U20">
-        <v>2.62</v>
+        <v>2.7</v>
       </c>
       <c r="V20">
         <v>1.4</v>
@@ -3602,32 +3602,32 @@
         <v>1.01</v>
       </c>
       <c r="Y20">
-        <v>1.3</v>
+        <v>1.26</v>
       </c>
       <c r="Z20">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="AA20">
-        <v>1.93</v>
+        <v>1.9</v>
       </c>
       <c r="AB20">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="AC20">
         <v>3.3</v>
       </c>
       <c r="AD20">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="AE20">
-        <v>1.1</v>
+        <v>1.06</v>
       </c>
       <c r="AF20">
+        <v>1.8</v>
+      </c>
+      <c r="AG20">
         <v>1.87</v>
       </c>
-      <c r="AG20">
-        <v>1.86</v>
-      </c>
       <c r="AH20" t="inlineStr">
         <is>
           <t>[]</t>
@@ -3639,10 +3639,10 @@
         </is>
       </c>
       <c r="AJ20">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AK20">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="AL20">
         <v>0</v>
@@ -3732,34 +3732,34 @@
         </is>
       </c>
       <c r="N21">
-        <v>3.75</v>
+        <v>3.9</v>
       </c>
       <c r="O21">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="P21">
         <v>1.66</v>
       </c>
       <c r="Q21">
-        <v>3.96</v>
+        <v>3.9</v>
       </c>
       <c r="R21">
-        <v>2.5</v>
+        <v>2.55</v>
       </c>
       <c r="S21">
         <v>1.2</v>
       </c>
       <c r="T21">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="U21">
-        <v>2.05</v>
+        <v>2.02</v>
       </c>
       <c r="V21">
-        <v>1.63</v>
+        <v>1.65</v>
       </c>
       <c r="W21">
-        <v>1.18</v>
+        <v>1.16</v>
       </c>
       <c r="X21">
         <v>1.01</v>
@@ -3768,22 +3768,22 @@
         <v>1.13</v>
       </c>
       <c r="Z21">
-        <v>5.48</v>
+        <v>5.75</v>
       </c>
       <c r="AA21">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AB21">
         <v>2.7</v>
       </c>
       <c r="AC21">
-        <v>2.22</v>
+        <v>2.11</v>
       </c>
       <c r="AD21">
-        <v>1.66</v>
+        <v>1.73</v>
       </c>
       <c r="AE21">
-        <v>1.29</v>
+        <v>1.32</v>
       </c>
       <c r="AF21">
         <v>1.5</v>
@@ -3895,25 +3895,25 @@
         </is>
       </c>
       <c r="N22">
-        <v>2.12</v>
+        <v>2.16</v>
       </c>
       <c r="O22">
-        <v>3.17</v>
+        <v>3.3</v>
       </c>
       <c r="P22">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="Q22">
-        <v>2.68</v>
+        <v>2.72</v>
       </c>
       <c r="R22">
         <v>2.07</v>
       </c>
       <c r="S22">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="T22">
-        <v>2.77</v>
+        <v>2.73</v>
       </c>
       <c r="U22">
         <v>2.69</v>
@@ -3925,13 +3925,13 @@
         <v>1.06</v>
       </c>
       <c r="X22">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="Y22">
         <v>1.28</v>
       </c>
       <c r="Z22">
-        <v>3.2</v>
+        <v>3.51</v>
       </c>
       <c r="AA22">
         <v>1.9</v>
@@ -3949,7 +3949,7 @@
         <v>1.07</v>
       </c>
       <c r="AF22">
-        <v>1.64</v>
+        <v>1.71</v>
       </c>
       <c r="AG22">
         <v>2</v>
@@ -3965,10 +3965,10 @@
         </is>
       </c>
       <c r="AJ22">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="AK22">
-        <v>1.69</v>
+        <v>1.67</v>
       </c>
       <c r="AL22">
         <v>0</v>
@@ -4221,16 +4221,16 @@
         </is>
       </c>
       <c r="N24">
-        <v>2.43</v>
+        <v>2.76</v>
       </c>
       <c r="O24">
-        <v>3.1</v>
+        <v>2.95</v>
       </c>
       <c r="P24">
-        <v>2.27</v>
+        <v>2.4</v>
       </c>
       <c r="Q24">
-        <v>3</v>
+        <v>3.07</v>
       </c>
       <c r="R24">
         <v>1.92</v>
@@ -4384,7 +4384,7 @@
         </is>
       </c>
       <c r="N25">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="O25">
         <v>3.6</v>
@@ -4393,7 +4393,7 @@
         <v>4.33</v>
       </c>
       <c r="Q25">
-        <v>2.29</v>
+        <v>2.28</v>
       </c>
       <c r="R25">
         <v>2.38</v>
@@ -4405,13 +4405,13 @@
         <v>3.04</v>
       </c>
       <c r="U25">
-        <v>2.6</v>
+        <v>2.45</v>
       </c>
       <c r="V25">
         <v>1.48</v>
       </c>
       <c r="W25">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="X25">
         <v>1.03</v>
@@ -4429,10 +4429,10 @@
         <v>1.91</v>
       </c>
       <c r="AC25">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="AD25">
-        <v>1.34</v>
+        <v>1.4</v>
       </c>
       <c r="AE25">
         <v>1.09</v>
@@ -4454,7 +4454,7 @@
         </is>
       </c>
       <c r="AJ25">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="AK25">
         <v>1.98</v>
@@ -4550,10 +4550,10 @@
         <v>3</v>
       </c>
       <c r="O26">
-        <v>3.61</v>
+        <v>3.4</v>
       </c>
       <c r="P26">
-        <v>2.08</v>
+        <v>2.19</v>
       </c>
       <c r="Q26">
         <v>3.23</v>
@@ -4574,37 +4574,37 @@
         <v>1.56</v>
       </c>
       <c r="W26">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="X26">
         <v>1.01</v>
       </c>
       <c r="Y26">
-        <v>1.15</v>
+        <v>1.2</v>
       </c>
       <c r="Z26">
         <v>4.5</v>
       </c>
       <c r="AA26">
-        <v>1.62</v>
+        <v>1.59</v>
       </c>
       <c r="AB26">
         <v>2.25</v>
       </c>
       <c r="AC26">
-        <v>2.3</v>
+        <v>2.33</v>
       </c>
       <c r="AD26">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
       <c r="AE26">
         <v>1.16</v>
       </c>
       <c r="AF26">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="AG26">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="AH26" t="inlineStr">
         <is>
@@ -4617,10 +4617,10 @@
         </is>
       </c>
       <c r="AJ26">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="AK26">
-        <v>1.29</v>
+        <v>1.36</v>
       </c>
       <c r="AL26">
         <v>0</v>
@@ -5036,13 +5036,13 @@
         </is>
       </c>
       <c r="N29">
-        <v>1.66</v>
+        <v>1.6</v>
       </c>
       <c r="O29">
-        <v>3.67</v>
+        <v>3.75</v>
       </c>
       <c r="P29">
-        <v>4.9</v>
+        <v>4.85</v>
       </c>
       <c r="Q29">
         <v>0</v>
@@ -5075,10 +5075,10 @@
         <v>0</v>
       </c>
       <c r="AA29">
-        <v>1.8</v>
+        <v>1.9</v>
       </c>
       <c r="AB29">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="AC29">
         <v>0</v>
@@ -5368,31 +5368,31 @@
         <v>3.7</v>
       </c>
       <c r="P31">
-        <v>5.5</v>
+        <v>4.8</v>
       </c>
       <c r="Q31">
-        <v>2.01</v>
+        <v>2.13</v>
       </c>
       <c r="R31">
-        <v>2.15</v>
+        <v>2.25</v>
       </c>
       <c r="S31">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="T31">
-        <v>2.85</v>
+        <v>2.73</v>
       </c>
       <c r="U31">
-        <v>2.73</v>
+        <v>2.55</v>
       </c>
       <c r="V31">
-        <v>1.4</v>
+        <v>1.43</v>
       </c>
       <c r="W31">
+        <v>1.1</v>
+      </c>
+      <c r="X31">
         <v>1.05</v>
-      </c>
-      <c r="X31">
-        <v>1.01</v>
       </c>
       <c r="Y31">
         <v>1.28</v>
@@ -5410,7 +5410,7 @@
         <v>3.25</v>
       </c>
       <c r="AD31">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
       <c r="AE31">
         <v>1.12</v>
@@ -5528,10 +5528,10 @@
         <v>2.6</v>
       </c>
       <c r="O32">
-        <v>2.7</v>
+        <v>2.62</v>
       </c>
       <c r="P32">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="Q32">
         <v>3.58</v>
@@ -5543,10 +5543,10 @@
         <v>1.6</v>
       </c>
       <c r="T32">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="U32">
-        <v>3.96</v>
+        <v>3.98</v>
       </c>
       <c r="V32">
         <v>1.17</v>
@@ -5555,34 +5555,34 @@
         <v>1.02</v>
       </c>
       <c r="X32">
-        <v>1.15</v>
+        <v>1.11</v>
       </c>
       <c r="Y32">
-        <v>1.66</v>
+        <v>1.62</v>
       </c>
       <c r="Z32">
-        <v>2.09</v>
+        <v>2.17</v>
       </c>
       <c r="AA32">
-        <v>2.92</v>
+        <v>2.88</v>
       </c>
       <c r="AB32">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="AC32">
         <v>5.8</v>
       </c>
       <c r="AD32">
-        <v>1.11</v>
+        <v>1.07</v>
       </c>
       <c r="AE32">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AF32">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="AG32">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="AH32" t="inlineStr">
         <is>
@@ -5598,7 +5598,7 @@
         <v>1.38</v>
       </c>
       <c r="AK32">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="AL32">
         <v>0</v>
@@ -5697,10 +5697,10 @@
         <v>2.75</v>
       </c>
       <c r="Q33">
-        <v>2.7</v>
+        <v>3.18</v>
       </c>
       <c r="R33">
-        <v>1.95</v>
+        <v>2.09</v>
       </c>
       <c r="S33">
         <v>1.45</v>
@@ -5745,7 +5745,7 @@
         <v>1.84</v>
       </c>
       <c r="AG33">
-        <v>1.84</v>
+        <v>1.86</v>
       </c>
       <c r="AH33" t="inlineStr">
         <is>
@@ -5758,7 +5758,7 @@
         </is>
       </c>
       <c r="AJ33">
-        <v>1.35</v>
+        <v>1.4</v>
       </c>
       <c r="AK33">
         <v>1.5</v>
@@ -6014,28 +6014,28 @@
         </is>
       </c>
       <c r="N35">
-        <v>2.13</v>
+        <v>2.14</v>
       </c>
       <c r="O35">
         <v>3.6</v>
       </c>
       <c r="P35">
-        <v>2.85</v>
+        <v>2.79</v>
       </c>
       <c r="Q35">
-        <v>2.66</v>
+        <v>2.48</v>
       </c>
       <c r="R35">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="S35">
         <v>1.25</v>
       </c>
       <c r="T35">
-        <v>3.8</v>
+        <v>3.36</v>
       </c>
       <c r="U35">
-        <v>2.31</v>
+        <v>2.38</v>
       </c>
       <c r="V35">
         <v>1.56</v>
@@ -6050,13 +6050,13 @@
         <v>1.13</v>
       </c>
       <c r="Z35">
-        <v>4.5</v>
+        <v>4.2</v>
       </c>
       <c r="AA35">
         <v>1.58</v>
       </c>
       <c r="AB35">
-        <v>2.35</v>
+        <v>2.18</v>
       </c>
       <c r="AC35">
         <v>2.33</v>
@@ -6065,13 +6065,13 @@
         <v>1.48</v>
       </c>
       <c r="AE35">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="AF35">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="AG35">
-        <v>2.47</v>
+        <v>2.4</v>
       </c>
       <c r="AH35" t="inlineStr">
         <is>
@@ -6084,10 +6084,10 @@
         </is>
       </c>
       <c r="AJ35">
-        <v>1.21</v>
+        <v>1.36</v>
       </c>
       <c r="AK35">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="AL35">
         <v>0</v>
@@ -6177,64 +6177,64 @@
         </is>
       </c>
       <c r="N36">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="O36">
-        <v>6.15</v>
+        <v>6.25</v>
       </c>
       <c r="P36">
-        <v>8.470000000000001</v>
+        <v>9.449999999999999</v>
       </c>
       <c r="Q36">
-        <v>1.52</v>
+        <v>1.57</v>
       </c>
       <c r="R36">
         <v>2.75</v>
       </c>
       <c r="S36">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="T36">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="U36">
-        <v>2.13</v>
+        <v>2</v>
       </c>
       <c r="V36">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="W36">
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
       <c r="X36">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y36">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="Z36">
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="AA36">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="AB36">
-        <v>2.49</v>
+        <v>2.3</v>
       </c>
       <c r="AC36">
-        <v>2.14</v>
+        <v>2.08</v>
       </c>
       <c r="AD36">
-        <v>1.62</v>
+        <v>1.68</v>
       </c>
       <c r="AE36">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="AF36">
-        <v>1.95</v>
+        <v>1.93</v>
       </c>
       <c r="AG36">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="AH36" t="inlineStr">
         <is>
@@ -6250,7 +6250,7 @@
         <v>1.1</v>
       </c>
       <c r="AK36">
-        <v>4.05</v>
+        <v>4.1</v>
       </c>
       <c r="AL36">
         <v>0</v>
@@ -6340,13 +6340,13 @@
         </is>
       </c>
       <c r="N37">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="O37">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="P37">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="Q37">
         <v>3.85</v>
@@ -6361,10 +6361,10 @@
         <v>3.34</v>
       </c>
       <c r="U37">
-        <v>2.14</v>
+        <v>2.31</v>
       </c>
       <c r="V37">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="W37">
         <v>1.08</v>
@@ -6373,16 +6373,16 @@
         <v>1.01</v>
       </c>
       <c r="Y37">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="Z37">
         <v>4.3</v>
       </c>
       <c r="AA37">
-        <v>1.58</v>
+        <v>1.52</v>
       </c>
       <c r="AB37">
-        <v>2.23</v>
+        <v>2.21</v>
       </c>
       <c r="AC37">
         <v>2.3</v>
@@ -6506,22 +6506,22 @@
         <v>7.6</v>
       </c>
       <c r="O38">
-        <v>5</v>
+        <v>5.05</v>
       </c>
       <c r="P38">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="Q38">
-        <v>7.3</v>
+        <v>8.35</v>
       </c>
       <c r="R38">
-        <v>2.54</v>
+        <v>2.55</v>
       </c>
       <c r="S38">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="T38">
-        <v>3.32</v>
+        <v>3.24</v>
       </c>
       <c r="U38">
         <v>2.51</v>
@@ -6530,7 +6530,7 @@
         <v>1.49</v>
       </c>
       <c r="W38">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="X38">
         <v>1</v>
@@ -6542,22 +6542,22 @@
         <v>3.94</v>
       </c>
       <c r="AA38">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="AB38">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="AC38">
         <v>2.7</v>
       </c>
       <c r="AD38">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="AE38">
         <v>1.12</v>
       </c>
       <c r="AF38">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="AG38">
         <v>1.72</v>
@@ -6576,7 +6576,7 @@
         <v>3.28</v>
       </c>
       <c r="AK38">
-        <v>1.08</v>
+        <v>1.03</v>
       </c>
       <c r="AL38">
         <v>0</v>
@@ -6829,13 +6829,13 @@
         </is>
       </c>
       <c r="N40">
-        <v>3.7</v>
+        <v>4.33</v>
       </c>
       <c r="O40">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="P40">
-        <v>1.82</v>
+        <v>1.66</v>
       </c>
       <c r="Q40">
         <v>3.95</v>
@@ -6847,7 +6847,7 @@
         <v>1.36</v>
       </c>
       <c r="T40">
-        <v>2.77</v>
+        <v>2.88</v>
       </c>
       <c r="U40">
         <v>2.65</v>
@@ -6862,16 +6862,16 @@
         <v>1.04</v>
       </c>
       <c r="Y40">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="Z40">
-        <v>3.34</v>
+        <v>3.5</v>
       </c>
       <c r="AA40">
+        <v>1.83</v>
+      </c>
+      <c r="AB40">
         <v>1.87</v>
-      </c>
-      <c r="AB40">
-        <v>1.9</v>
       </c>
       <c r="AC40">
         <v>3.2</v>
@@ -6880,13 +6880,13 @@
         <v>1.33</v>
       </c>
       <c r="AE40">
-        <v>1.1</v>
+        <v>1.07</v>
       </c>
       <c r="AF40">
-        <v>1.64</v>
+        <v>1.77</v>
       </c>
       <c r="AG40">
-        <v>1.95</v>
+        <v>1.98</v>
       </c>
       <c r="AH40" t="inlineStr">
         <is>
@@ -6899,10 +6899,10 @@
         </is>
       </c>
       <c r="AJ40">
-        <v>1.86</v>
+        <v>1.22</v>
       </c>
       <c r="AK40">
-        <v>1.21</v>
+        <v>1.12</v>
       </c>
       <c r="AL40">
         <v>0</v>
@@ -6995,61 +6995,61 @@
         <v>2.85</v>
       </c>
       <c r="O41">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="P41">
         <v>2.2</v>
       </c>
       <c r="Q41">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="R41">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="S41">
-        <v>1.4</v>
+        <v>1.43</v>
       </c>
       <c r="T41">
-        <v>2.56</v>
+        <v>2.53</v>
       </c>
       <c r="U41">
-        <v>2.8</v>
+        <v>2.96</v>
       </c>
       <c r="V41">
-        <v>1.38</v>
+        <v>1.32</v>
       </c>
       <c r="W41">
         <v>1.03</v>
       </c>
       <c r="X41">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="Y41">
-        <v>1.32</v>
+        <v>1.36</v>
       </c>
       <c r="Z41">
-        <v>2.88</v>
+        <v>3.1</v>
       </c>
       <c r="AA41">
         <v>2.15</v>
       </c>
       <c r="AB41">
-        <v>1.73</v>
+        <v>1.65</v>
       </c>
       <c r="AC41">
-        <v>3.5</v>
+        <v>4.1</v>
       </c>
       <c r="AD41">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="AE41">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="AF41">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="AG41">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="AH41" t="inlineStr">
         <is>
@@ -7065,7 +7065,7 @@
         <v>1.45</v>
       </c>
       <c r="AK41">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="AL41">
         <v>0</v>
@@ -7481,31 +7481,31 @@
         </is>
       </c>
       <c r="N44">
-        <v>1.7</v>
+        <v>1.65</v>
       </c>
       <c r="O44">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="P44">
-        <v>4.85</v>
+        <v>4.67</v>
       </c>
       <c r="Q44">
-        <v>2.3</v>
+        <v>2.31</v>
       </c>
       <c r="R44">
-        <v>2.04</v>
+        <v>2.03</v>
       </c>
       <c r="S44">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="T44">
-        <v>2.53</v>
+        <v>2.64</v>
       </c>
       <c r="U44">
         <v>3.16</v>
       </c>
       <c r="V44">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="W44">
         <v>1.02</v>
@@ -7523,13 +7523,13 @@
         <v>2.28</v>
       </c>
       <c r="AB44">
-        <v>1.62</v>
+        <v>1.64</v>
       </c>
       <c r="AC44">
-        <v>3.95</v>
+        <v>3.92</v>
       </c>
       <c r="AD44">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="AE44">
         <v>1.03</v>
@@ -7551,7 +7551,7 @@
         </is>
       </c>
       <c r="AJ44">
-        <v>1.26</v>
+        <v>1.15</v>
       </c>
       <c r="AK44">
         <v>2.03</v>
@@ -9277,10 +9277,10 @@
         <v>1.44</v>
       </c>
       <c r="O55">
-        <v>4.45</v>
+        <v>4.2</v>
       </c>
       <c r="P55">
-        <v>6</v>
+        <v>5.49</v>
       </c>
       <c r="Q55">
         <v>1.85</v>
@@ -9295,7 +9295,7 @@
         <v>3.6</v>
       </c>
       <c r="U55">
-        <v>2.28</v>
+        <v>2.2</v>
       </c>
       <c r="V55">
         <v>1.61</v>
@@ -9304,13 +9304,13 @@
         <v>1.12</v>
       </c>
       <c r="X55">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y55">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="Z55">
-        <v>5.14</v>
+        <v>5.5</v>
       </c>
       <c r="AA55">
         <v>1.53</v>
@@ -9319,10 +9319,10 @@
         <v>2.52</v>
       </c>
       <c r="AC55">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="AD55">
-        <v>1.56</v>
+        <v>1.6</v>
       </c>
       <c r="AE55">
         <v>1.19</v>
@@ -9347,7 +9347,7 @@
         <v>1.15</v>
       </c>
       <c r="AK55">
-        <v>2.66</v>
+        <v>2.64</v>
       </c>
       <c r="AL55">
         <v>0</v>
@@ -10255,16 +10255,16 @@
         <v>1.14</v>
       </c>
       <c r="O61">
-        <v>7.75</v>
+        <v>7.5</v>
       </c>
       <c r="P61">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="Q61">
         <v>1.48</v>
       </c>
       <c r="R61">
-        <v>2.83</v>
+        <v>2.82</v>
       </c>
       <c r="S61">
         <v>1.14</v>
@@ -10273,13 +10273,13 @@
         <v>5</v>
       </c>
       <c r="U61">
-        <v>1.94</v>
+        <v>1.8</v>
       </c>
       <c r="V61">
-        <v>1.9</v>
+        <v>1.74</v>
       </c>
       <c r="W61">
-        <v>1.25</v>
+        <v>1.19</v>
       </c>
       <c r="X61">
         <v>1.01</v>
@@ -10288,28 +10288,28 @@
         <v>1.07</v>
       </c>
       <c r="Z61">
-        <v>5.95</v>
+        <v>5.9</v>
       </c>
       <c r="AA61">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="AB61">
-        <v>2.75</v>
+        <v>3.2</v>
       </c>
       <c r="AC61">
         <v>1.94</v>
       </c>
       <c r="AD61">
-        <v>1.89</v>
+        <v>2</v>
       </c>
       <c r="AE61">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="AF61">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="AG61">
-        <v>1.65</v>
+        <v>1.7</v>
       </c>
       <c r="AH61" t="inlineStr">
         <is>
@@ -10322,10 +10322,10 @@
         </is>
       </c>
       <c r="AJ61">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AK61">
-        <v>4.85</v>
+        <v>4</v>
       </c>
       <c r="AL61">
         <v>0</v>
@@ -11719,61 +11719,61 @@
         </is>
       </c>
       <c r="N70">
-        <v>1.48</v>
+        <v>1.54</v>
       </c>
       <c r="O70">
-        <v>3.9</v>
+        <v>3.75</v>
       </c>
       <c r="P70">
-        <v>5.58</v>
+        <v>4.85</v>
       </c>
       <c r="Q70">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="R70">
-        <v>2.1</v>
+        <v>2.25</v>
       </c>
       <c r="S70">
-        <v>1.3</v>
+        <v>1.35</v>
       </c>
       <c r="T70">
         <v>3.2</v>
       </c>
       <c r="U70">
-        <v>2.9</v>
+        <v>2.55</v>
       </c>
       <c r="V70">
-        <v>1.35</v>
+        <v>1.45</v>
       </c>
       <c r="W70">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="X70">
         <v>1.03</v>
       </c>
       <c r="Y70">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="Z70">
-        <v>3.6</v>
+        <v>3.8</v>
       </c>
       <c r="AA70">
-        <v>2.11</v>
+        <v>1.75</v>
       </c>
       <c r="AB70">
-        <v>2.05</v>
+        <v>1.87</v>
       </c>
       <c r="AC70">
-        <v>3.5</v>
+        <v>3</v>
       </c>
       <c r="AD70">
         <v>1.36</v>
       </c>
       <c r="AE70">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="AF70">
-        <v>1.8</v>
+        <v>1.87</v>
       </c>
       <c r="AG70">
         <v>1.83</v>
@@ -11789,10 +11789,10 @@
         </is>
       </c>
       <c r="AJ70">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="AK70">
-        <v>2.29</v>
+        <v>2.38</v>
       </c>
       <c r="AL70">
         <v>0</v>
@@ -11891,22 +11891,22 @@
         <v>8.800000000000001</v>
       </c>
       <c r="Q71">
-        <v>1.77</v>
+        <v>1.74</v>
       </c>
       <c r="R71">
-        <v>2.47</v>
+        <v>2.25</v>
       </c>
       <c r="S71">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="T71">
-        <v>3.08</v>
+        <v>3.14</v>
       </c>
       <c r="U71">
-        <v>2.66</v>
+        <v>2.62</v>
       </c>
       <c r="V71">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="W71">
         <v>1.08</v>
@@ -11915,31 +11915,31 @@
         <v>1</v>
       </c>
       <c r="Y71">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="Z71">
-        <v>3.65</v>
+        <v>3.83</v>
       </c>
       <c r="AA71">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="AB71">
-        <v>2.03</v>
+        <v>2.05</v>
       </c>
       <c r="AC71">
-        <v>2.9</v>
+        <v>2.89</v>
       </c>
       <c r="AD71">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="AE71">
         <v>1.1</v>
       </c>
       <c r="AF71">
-        <v>2.19</v>
+        <v>2.17</v>
       </c>
       <c r="AG71">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="AH71" t="inlineStr">
         <is>
@@ -12371,28 +12371,28 @@
         </is>
       </c>
       <c r="N74">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="O74">
-        <v>2.94</v>
+        <v>3</v>
       </c>
       <c r="P74">
-        <v>3.3</v>
+        <v>3.24</v>
       </c>
       <c r="Q74">
-        <v>2.8</v>
+        <v>3</v>
       </c>
       <c r="R74">
-        <v>1.95</v>
+        <v>1.87</v>
       </c>
       <c r="S74">
-        <v>1.5</v>
+        <v>1.58</v>
       </c>
       <c r="T74">
-        <v>2.33</v>
+        <v>2.22</v>
       </c>
       <c r="U74">
-        <v>3.35</v>
+        <v>3.8</v>
       </c>
       <c r="V74">
         <v>1.22</v>
@@ -12401,34 +12401,34 @@
         <v>1.03</v>
       </c>
       <c r="X74">
-        <v>1.11</v>
+        <v>1.07</v>
       </c>
       <c r="Y74">
         <v>1.53</v>
       </c>
       <c r="Z74">
-        <v>2.4</v>
+        <v>2.36</v>
       </c>
       <c r="AA74">
-        <v>2.46</v>
+        <v>2.56</v>
       </c>
       <c r="AB74">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="AC74">
         <v>5.5</v>
       </c>
       <c r="AD74">
-        <v>1.14</v>
+        <v>1.11</v>
       </c>
       <c r="AE74">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="AF74">
-        <v>2.09</v>
+        <v>2.14</v>
       </c>
       <c r="AG74">
-        <v>1.64</v>
+        <v>1.62</v>
       </c>
       <c r="AH74" t="inlineStr">
         <is>
@@ -12444,7 +12444,7 @@
         <v>1.32</v>
       </c>
       <c r="AK74">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="AL74">
         <v>0</v>
@@ -12700,7 +12700,7 @@
         <v>2.7</v>
       </c>
       <c r="O76">
-        <v>3.1</v>
+        <v>3.13</v>
       </c>
       <c r="P76">
         <v>2.18</v>
@@ -12709,7 +12709,7 @@
         <v>3.35</v>
       </c>
       <c r="R76">
-        <v>2.04</v>
+        <v>2.1</v>
       </c>
       <c r="S76">
         <v>1.41</v>
@@ -12718,7 +12718,7 @@
         <v>2.75</v>
       </c>
       <c r="U76">
-        <v>2.91</v>
+        <v>2.9</v>
       </c>
       <c r="V76">
         <v>1.4</v>
@@ -12727,31 +12727,31 @@
         <v>1.04</v>
       </c>
       <c r="X76">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="Y76">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="Z76">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="AA76">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="AB76">
-        <v>1.83</v>
+        <v>1.86</v>
       </c>
       <c r="AC76">
-        <v>3.4</v>
+        <v>3.39</v>
       </c>
       <c r="AD76">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="AE76">
         <v>1.06</v>
       </c>
       <c r="AF76">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="AG76">
         <v>2</v>
@@ -13195,7 +13195,7 @@
         <v>2.59</v>
       </c>
       <c r="Q79">
-        <v>3.06</v>
+        <v>3.04</v>
       </c>
       <c r="R79">
         <v>2</v>
@@ -13210,7 +13210,7 @@
         <v>2.92</v>
       </c>
       <c r="V79">
-        <v>1.32</v>
+        <v>1.29</v>
       </c>
       <c r="W79">
         <v>1.05</v>
@@ -13225,10 +13225,10 @@
         <v>2.92</v>
       </c>
       <c r="AA79">
-        <v>2.04</v>
+        <v>2.1</v>
       </c>
       <c r="AB79">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="AC79">
         <v>3.58</v>
@@ -13256,10 +13256,10 @@
         </is>
       </c>
       <c r="AJ79">
-        <v>1.3</v>
+        <v>1.26</v>
       </c>
       <c r="AK79">
-        <v>1.53</v>
+        <v>1.45</v>
       </c>
       <c r="AL79">
         <v>0</v>
@@ -16120,13 +16120,13 @@
         </is>
       </c>
       <c r="N97">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="O97">
-        <v>3.42</v>
+        <v>3.44</v>
       </c>
       <c r="P97">
-        <v>2.59</v>
+        <v>2.6</v>
       </c>
       <c r="Q97">
         <v>0</v>
@@ -16612,22 +16612,22 @@
         <v>4</v>
       </c>
       <c r="O100">
-        <v>3.5</v>
+        <v>3.58</v>
       </c>
       <c r="P100">
-        <v>1.93</v>
+        <v>1.88</v>
       </c>
       <c r="Q100">
         <v>4.59</v>
       </c>
       <c r="R100">
-        <v>2.08</v>
+        <v>2.09</v>
       </c>
       <c r="S100">
         <v>1.36</v>
       </c>
       <c r="T100">
-        <v>3.03</v>
+        <v>2.85</v>
       </c>
       <c r="U100">
         <v>2.77</v>
@@ -16642,31 +16642,31 @@
         <v>1.01</v>
       </c>
       <c r="Y100">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="Z100">
         <v>3.42</v>
       </c>
       <c r="AA100">
-        <v>1.91</v>
+        <v>1.97</v>
       </c>
       <c r="AB100">
         <v>1.93</v>
       </c>
       <c r="AC100">
-        <v>3.23</v>
+        <v>3.1</v>
       </c>
       <c r="AD100">
         <v>1.32</v>
       </c>
       <c r="AE100">
-        <v>1.08</v>
+        <v>1.12</v>
       </c>
       <c r="AF100">
         <v>1.76</v>
       </c>
       <c r="AG100">
-        <v>1.95</v>
+        <v>1.97</v>
       </c>
       <c r="AH100" t="inlineStr">
         <is>
@@ -19063,7 +19063,7 @@
         <v>3.8</v>
       </c>
       <c r="Q115">
-        <v>2.4</v>
+        <v>2.43</v>
       </c>
       <c r="R115">
         <v>2.14</v>
@@ -19075,13 +19075,13 @@
         <v>2.9</v>
       </c>
       <c r="U115">
-        <v>2.6</v>
+        <v>2.65</v>
       </c>
       <c r="V115">
         <v>1.44</v>
       </c>
       <c r="W115">
-        <v>1.09</v>
+        <v>1.07</v>
       </c>
       <c r="X115">
         <v>1.04</v>
@@ -19108,10 +19108,10 @@
         <v>1.1</v>
       </c>
       <c r="AF115">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="AG115">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="AH115" t="inlineStr">
         <is>
@@ -19124,7 +19124,7 @@
         </is>
       </c>
       <c r="AJ115">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="AK115">
         <v>1.83</v>
@@ -20489,12 +20489,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Chaco For Ever</t>
+          <t>Deportivo Madryn</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Deportivo Morón</t>
+          <t>All Boys</t>
         </is>
       </c>
       <c r="G124">
@@ -20521,64 +20521,64 @@
         </is>
       </c>
       <c r="N124">
-        <v>2.81</v>
+        <v>1.86</v>
       </c>
       <c r="O124">
-        <v>2.64</v>
+        <v>2.8</v>
       </c>
       <c r="P124">
-        <v>2.45</v>
+        <v>4.2</v>
       </c>
       <c r="Q124">
-        <v>4.15</v>
+        <v>2.77</v>
       </c>
       <c r="R124">
-        <v>1.74</v>
+        <v>1.72</v>
       </c>
       <c r="S124">
-        <v>1.57</v>
+        <v>1.7</v>
       </c>
       <c r="T124">
         <v>2.25</v>
       </c>
       <c r="U124">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="V124">
-        <v>1.2</v>
+        <v>1.16</v>
       </c>
       <c r="W124">
         <v>1.03</v>
       </c>
       <c r="X124">
+        <v>1.12</v>
+      </c>
+      <c r="Y124">
+        <v>1.68</v>
+      </c>
+      <c r="Z124">
+        <v>2.06</v>
+      </c>
+      <c r="AA124">
+        <v>3.4</v>
+      </c>
+      <c r="AB124">
+        <v>1.33</v>
+      </c>
+      <c r="AC124">
+        <v>5.95</v>
+      </c>
+      <c r="AD124">
         <v>1.1</v>
-      </c>
-      <c r="Y124">
-        <v>1.65</v>
-      </c>
-      <c r="Z124">
-        <v>2.15</v>
-      </c>
-      <c r="AA124">
-        <v>2.88</v>
-      </c>
-      <c r="AB124">
-        <v>1.32</v>
-      </c>
-      <c r="AC124">
-        <v>5.9</v>
-      </c>
-      <c r="AD124">
-        <v>1.07</v>
       </c>
       <c r="AE124">
         <v>1.02</v>
       </c>
       <c r="AF124">
-        <v>2.32</v>
+        <v>2.51</v>
       </c>
       <c r="AG124">
-        <v>1.53</v>
+        <v>1.44</v>
       </c>
       <c r="AH124" t="inlineStr">
         <is>
@@ -20591,10 +20591,10 @@
         </is>
       </c>
       <c r="AJ124">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="AK124">
-        <v>1.38</v>
+        <v>1.7</v>
       </c>
       <c r="AL124">
         <v>0</v>
@@ -20652,12 +20652,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Deportivo Madryn</t>
+          <t>Chaco For Ever</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>All Boys</t>
+          <t>Deportivo Morón</t>
         </is>
       </c>
       <c r="G125">
@@ -20684,64 +20684,64 @@
         </is>
       </c>
       <c r="N125">
-        <v>1.86</v>
+        <v>2.81</v>
       </c>
       <c r="O125">
-        <v>2.8</v>
+        <v>2.64</v>
       </c>
       <c r="P125">
-        <v>4.2</v>
+        <v>2.45</v>
       </c>
       <c r="Q125">
-        <v>2.77</v>
+        <v>4.15</v>
       </c>
       <c r="R125">
-        <v>1.72</v>
+        <v>1.74</v>
       </c>
       <c r="S125">
-        <v>1.7</v>
+        <v>1.57</v>
       </c>
       <c r="T125">
         <v>2.25</v>
       </c>
       <c r="U125">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="V125">
-        <v>1.16</v>
+        <v>1.2</v>
       </c>
       <c r="W125">
         <v>1.03</v>
       </c>
       <c r="X125">
-        <v>1.12</v>
+        <v>1.1</v>
       </c>
       <c r="Y125">
-        <v>1.68</v>
+        <v>1.65</v>
       </c>
       <c r="Z125">
-        <v>2.06</v>
+        <v>2.15</v>
       </c>
       <c r="AA125">
-        <v>3.4</v>
+        <v>2.88</v>
       </c>
       <c r="AB125">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="AC125">
-        <v>5.95</v>
+        <v>5.9</v>
       </c>
       <c r="AD125">
-        <v>1.1</v>
+        <v>1.07</v>
       </c>
       <c r="AE125">
         <v>1.02</v>
       </c>
       <c r="AF125">
-        <v>2.51</v>
+        <v>2.32</v>
       </c>
       <c r="AG125">
-        <v>1.44</v>
+        <v>1.53</v>
       </c>
       <c r="AH125" t="inlineStr">
         <is>
@@ -20754,10 +20754,10 @@
         </is>
       </c>
       <c r="AJ125">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AK125">
-        <v>1.7</v>
+        <v>1.38</v>
       </c>
       <c r="AL125">
         <v>0</v>

--- a/jogos_2026-08-02.xlsx
+++ b/jogos_2026-08-02.xlsx
@@ -635,16 +635,16 @@
         </is>
       </c>
       <c r="N2">
-        <v>1.22</v>
+        <v>1.31</v>
       </c>
       <c r="O2">
-        <v>4.75</v>
+        <v>5</v>
       </c>
       <c r="P2">
-        <v>8.4</v>
+        <v>7</v>
       </c>
       <c r="Q2">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="R2">
         <v>2.62</v>
@@ -668,10 +668,10 @@
         <v>1.01</v>
       </c>
       <c r="Y2">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="Z2">
-        <v>5</v>
+        <v>4.5</v>
       </c>
       <c r="AA2">
         <v>1.54</v>
@@ -680,10 +680,10 @@
         <v>2.27</v>
       </c>
       <c r="AC2">
-        <v>2.18</v>
+        <v>2.36</v>
       </c>
       <c r="AD2">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="AE2">
         <v>1.2</v>
@@ -798,19 +798,19 @@
         </is>
       </c>
       <c r="N3">
-        <v>1.83</v>
+        <v>1.91</v>
       </c>
       <c r="O3">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="P3">
-        <v>3.72</v>
+        <v>3.5</v>
       </c>
       <c r="Q3">
-        <v>2.43</v>
+        <v>2.5</v>
       </c>
       <c r="R3">
-        <v>2.25</v>
+        <v>2.09</v>
       </c>
       <c r="S3">
         <v>1.38</v>
@@ -822,7 +822,7 @@
         <v>2.75</v>
       </c>
       <c r="V3">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="W3">
         <v>1.08</v>
@@ -852,26 +852,26 @@
         <v>1.07</v>
       </c>
       <c r="AF3">
+        <v>1.74</v>
+      </c>
+      <c r="AG3">
+        <v>1.94</v>
+      </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ3">
+        <v>1.22</v>
+      </c>
+      <c r="AK3">
         <v>1.75</v>
-      </c>
-      <c r="AG3">
-        <v>1.93</v>
-      </c>
-      <c r="AH3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ3">
-        <v>1.25</v>
-      </c>
-      <c r="AK3">
-        <v>1.83</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -929,12 +929,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Blacktown City</t>
+          <t>Marconi Stallions</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Sydney II</t>
+          <t>St George City FA</t>
         </is>
       </c>
       <c r="G4">
@@ -961,64 +961,64 @@
         </is>
       </c>
       <c r="N4">
-        <v>1.91</v>
+        <v>1.33</v>
       </c>
       <c r="O4">
-        <v>3.5</v>
+        <v>4.65</v>
       </c>
       <c r="P4">
-        <v>3.4</v>
+        <v>7.9</v>
       </c>
       <c r="Q4">
-        <v>2.3</v>
+        <v>1.75</v>
       </c>
       <c r="R4">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="S4">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="T4">
-        <v>3.25</v>
+        <v>3.11</v>
       </c>
       <c r="U4">
-        <v>2.44</v>
+        <v>2.48</v>
       </c>
       <c r="V4">
-        <v>1.45</v>
+        <v>1.5</v>
       </c>
       <c r="W4">
-        <v>1.07</v>
+        <v>1.09</v>
       </c>
       <c r="X4">
         <v>1.02</v>
       </c>
       <c r="Y4">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="Z4">
-        <v>3.92</v>
+        <v>3.94</v>
       </c>
       <c r="AA4">
-        <v>1.67</v>
+        <v>1.64</v>
       </c>
       <c r="AB4">
-        <v>2.05</v>
+        <v>2.08</v>
       </c>
       <c r="AC4">
-        <v>2.62</v>
+        <v>2.56</v>
       </c>
       <c r="AD4">
-        <v>1.45</v>
+        <v>1.4</v>
       </c>
       <c r="AE4">
-        <v>1.17</v>
+        <v>1.13</v>
       </c>
       <c r="AF4">
-        <v>1.62</v>
+        <v>1.93</v>
       </c>
       <c r="AG4">
-        <v>2.19</v>
+        <v>1.7</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1031,10 +1031,10 @@
         </is>
       </c>
       <c r="AJ4">
-        <v>1.22</v>
+        <v>1.11</v>
       </c>
       <c r="AK4">
-        <v>1.8</v>
+        <v>2.92</v>
       </c>
       <c r="AL4">
         <v>0</v>
@@ -1092,12 +1092,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Marconi Stallions</t>
+          <t>Rockdale City Suns</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>St George City FA</t>
+          <t>Manly United</t>
         </is>
       </c>
       <c r="G5">
@@ -1124,31 +1124,31 @@
         </is>
       </c>
       <c r="N5">
-        <v>1.33</v>
+        <v>1.75</v>
       </c>
       <c r="O5">
-        <v>4.6</v>
+        <v>3.7</v>
       </c>
       <c r="P5">
-        <v>6.4</v>
+        <v>3.63</v>
       </c>
       <c r="Q5">
-        <v>1.75</v>
+        <v>2.25</v>
       </c>
       <c r="R5">
-        <v>2.47</v>
+        <v>2.38</v>
       </c>
       <c r="S5">
-        <v>1.32</v>
+        <v>1.25</v>
       </c>
       <c r="T5">
-        <v>3.11</v>
+        <v>3.4</v>
       </c>
       <c r="U5">
-        <v>2.48</v>
+        <v>2.37</v>
       </c>
       <c r="V5">
-        <v>1.5</v>
+        <v>1.55</v>
       </c>
       <c r="W5">
         <v>1.09</v>
@@ -1157,31 +1157,31 @@
         <v>1.02</v>
       </c>
       <c r="Y5">
-        <v>1.17</v>
+        <v>1.13</v>
       </c>
       <c r="Z5">
-        <v>3.94</v>
+        <v>4.35</v>
       </c>
       <c r="AA5">
-        <v>1.64</v>
+        <v>1.6</v>
       </c>
       <c r="AB5">
-        <v>2.08</v>
+        <v>2.19</v>
       </c>
       <c r="AC5">
-        <v>2.56</v>
+        <v>2.5</v>
       </c>
       <c r="AD5">
-        <v>1.4</v>
+        <v>1.53</v>
       </c>
       <c r="AE5">
-        <v>1.14</v>
+        <v>1.22</v>
       </c>
       <c r="AF5">
-        <v>1.93</v>
+        <v>1.57</v>
       </c>
       <c r="AG5">
-        <v>1.75</v>
+        <v>2.25</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1194,10 +1194,10 @@
         </is>
       </c>
       <c r="AJ5">
-        <v>1.11</v>
+        <v>1.19</v>
       </c>
       <c r="AK5">
-        <v>2.92</v>
+        <v>1.94</v>
       </c>
       <c r="AL5">
         <v>0</v>
@@ -1255,12 +1255,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Rockdale City Suns</t>
+          <t>Blacktown City</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Manly United</t>
+          <t>Sydney II</t>
         </is>
       </c>
       <c r="G6">
@@ -1287,80 +1287,80 @@
         </is>
       </c>
       <c r="N6">
-        <v>1.75</v>
+        <v>1.91</v>
       </c>
       <c r="O6">
-        <v>3.8</v>
+        <v>3.4</v>
       </c>
       <c r="P6">
-        <v>3.63</v>
+        <v>3.4</v>
       </c>
       <c r="Q6">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="R6">
-        <v>2.25</v>
+        <v>2.18</v>
       </c>
       <c r="S6">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="T6">
-        <v>3.28</v>
+        <v>3.25</v>
       </c>
       <c r="U6">
-        <v>2.37</v>
+        <v>2.44</v>
       </c>
       <c r="V6">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="W6">
-        <v>1.09</v>
+        <v>1.07</v>
       </c>
       <c r="X6">
         <v>1.02</v>
       </c>
       <c r="Y6">
-        <v>1.13</v>
+        <v>1.18</v>
       </c>
       <c r="Z6">
-        <v>4.35</v>
+        <v>4.2</v>
       </c>
       <c r="AA6">
-        <v>1.6</v>
+        <v>1.67</v>
       </c>
       <c r="AB6">
+        <v>2.05</v>
+      </c>
+      <c r="AC6">
+        <v>2.74</v>
+      </c>
+      <c r="AD6">
+        <v>1.41</v>
+      </c>
+      <c r="AE6">
+        <v>1.17</v>
+      </c>
+      <c r="AF6">
+        <v>1.58</v>
+      </c>
+      <c r="AG6">
         <v>2.19</v>
       </c>
-      <c r="AC6">
-        <v>2.5</v>
-      </c>
-      <c r="AD6">
-        <v>1.53</v>
-      </c>
-      <c r="AE6">
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ6">
         <v>1.22</v>
       </c>
-      <c r="AF6">
-        <v>1.57</v>
-      </c>
-      <c r="AG6">
-        <v>2.25</v>
-      </c>
-      <c r="AH6" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI6" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ6">
-        <v>1.19</v>
-      </c>
       <c r="AK6">
-        <v>1.94</v>
+        <v>1.8</v>
       </c>
       <c r="AL6">
         <v>0</v>
@@ -1450,34 +1450,34 @@
         </is>
       </c>
       <c r="N7">
-        <v>5.5</v>
+        <v>5.05</v>
       </c>
       <c r="O7">
-        <v>4.75</v>
+        <v>4.6</v>
       </c>
       <c r="P7">
-        <v>1.35</v>
+        <v>1.44</v>
       </c>
       <c r="Q7">
-        <v>6</v>
+        <v>5.1</v>
       </c>
       <c r="R7">
-        <v>2.54</v>
+        <v>2.49</v>
       </c>
       <c r="S7">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="T7">
-        <v>3.74</v>
+        <v>3.85</v>
       </c>
       <c r="U7">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="V7">
         <v>1.67</v>
       </c>
       <c r="W7">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="X7">
         <v>1.02</v>
@@ -1486,28 +1486,28 @@
         <v>1.09</v>
       </c>
       <c r="Z7">
-        <v>5.3</v>
+        <v>5.25</v>
       </c>
       <c r="AA7">
         <v>1.44</v>
       </c>
       <c r="AB7">
-        <v>2.6</v>
+        <v>2.63</v>
       </c>
       <c r="AC7">
-        <v>2.15</v>
+        <v>2.12</v>
       </c>
       <c r="AD7">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="AE7">
         <v>1.23</v>
       </c>
       <c r="AF7">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="AG7">
-        <v>2.16</v>
+        <v>2.3</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1520,10 +1520,10 @@
         </is>
       </c>
       <c r="AJ7">
-        <v>2.75</v>
+        <v>2.45</v>
       </c>
       <c r="AK7">
-        <v>1.13</v>
+        <v>1.09</v>
       </c>
       <c r="AL7">
         <v>0</v>
@@ -1616,7 +1616,7 @@
         <v>4.45</v>
       </c>
       <c r="O8">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="P8">
         <v>1.78</v>
@@ -1649,7 +1649,7 @@
         <v>1.3</v>
       </c>
       <c r="Z8">
-        <v>2.97</v>
+        <v>3.11</v>
       </c>
       <c r="AA8">
         <v>2.13</v>
@@ -1661,7 +1661,7 @@
         <v>3.68</v>
       </c>
       <c r="AD8">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="AE8">
         <v>1.03</v>
@@ -1683,10 +1683,10 @@
         </is>
       </c>
       <c r="AJ8">
-        <v>1.85</v>
+        <v>1.3</v>
       </c>
       <c r="AK8">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="AL8">
         <v>0</v>
@@ -1779,10 +1779,10 @@
         <v>2.41</v>
       </c>
       <c r="O9">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="P9">
-        <v>2.72</v>
+        <v>2.67</v>
       </c>
       <c r="Q9">
         <v>0</v>
@@ -1945,58 +1945,58 @@
         <v>3.75</v>
       </c>
       <c r="P10">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="Q10">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="R10">
         <v>2.38</v>
       </c>
       <c r="S10">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="T10">
         <v>3.35</v>
       </c>
       <c r="U10">
-        <v>2.33</v>
+        <v>2.38</v>
       </c>
       <c r="V10">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="W10">
-        <v>1.09</v>
+        <v>1.14</v>
       </c>
       <c r="X10">
         <v>1.03</v>
       </c>
       <c r="Y10">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="Z10">
-        <v>4.6</v>
+        <v>4.75</v>
       </c>
       <c r="AA10">
-        <v>1.62</v>
+        <v>1.64</v>
       </c>
       <c r="AB10">
-        <v>2.19</v>
+        <v>2.08</v>
       </c>
       <c r="AC10">
-        <v>2.43</v>
+        <v>2.53</v>
       </c>
       <c r="AD10">
         <v>1.5</v>
       </c>
       <c r="AE10">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="AF10">
         <v>1.57</v>
       </c>
       <c r="AG10">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2012,7 +2012,7 @@
         <v>1.2</v>
       </c>
       <c r="AK10">
-        <v>1.84</v>
+        <v>2.1</v>
       </c>
       <c r="AL10">
         <v>0</v>
@@ -2102,13 +2102,13 @@
         </is>
       </c>
       <c r="N11">
-        <v>1.38</v>
+        <v>1.45</v>
       </c>
       <c r="O11">
-        <v>4.25</v>
+        <v>4.2</v>
       </c>
       <c r="P11">
-        <v>5.9</v>
+        <v>5.2</v>
       </c>
       <c r="Q11">
         <v>1.98</v>
@@ -2120,7 +2120,7 @@
         <v>1.36</v>
       </c>
       <c r="T11">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="U11">
         <v>2.63</v>
@@ -2141,7 +2141,7 @@
         <v>3.54</v>
       </c>
       <c r="AA11">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="AB11">
         <v>1.97</v>
@@ -2153,10 +2153,10 @@
         <v>1.32</v>
       </c>
       <c r="AE11">
-        <v>1.08</v>
+        <v>1.12</v>
       </c>
       <c r="AF11">
-        <v>2.05</v>
+        <v>1.9</v>
       </c>
       <c r="AG11">
         <v>1.77</v>
@@ -2268,16 +2268,16 @@
         <v>2.87</v>
       </c>
       <c r="O12">
-        <v>2.97</v>
+        <v>2.9</v>
       </c>
       <c r="P12">
-        <v>2.4</v>
+        <v>2.2</v>
       </c>
       <c r="Q12">
         <v>3.55</v>
       </c>
       <c r="R12">
-        <v>1.96</v>
+        <v>1.98</v>
       </c>
       <c r="S12">
         <v>1.44</v>
@@ -2310,7 +2310,7 @@
         <v>1.56</v>
       </c>
       <c r="AC12">
-        <v>4.5</v>
+        <v>4.3</v>
       </c>
       <c r="AD12">
         <v>1.2</v>
@@ -2338,7 +2338,7 @@
         <v>1.36</v>
       </c>
       <c r="AK12">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="AL12">
         <v>0</v>
@@ -2428,7 +2428,7 @@
         </is>
       </c>
       <c r="N13">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="O13">
         <v>3.6</v>
@@ -2440,13 +2440,13 @@
         <v>2.41</v>
       </c>
       <c r="R13">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="S13">
         <v>1.36</v>
       </c>
       <c r="T13">
-        <v>3.1</v>
+        <v>2.94</v>
       </c>
       <c r="U13">
         <v>2.65</v>
@@ -2464,7 +2464,7 @@
         <v>1.22</v>
       </c>
       <c r="Z13">
-        <v>3.86</v>
+        <v>3.9</v>
       </c>
       <c r="AA13">
         <v>1.89</v>
@@ -2473,7 +2473,7 @@
         <v>1.89</v>
       </c>
       <c r="AC13">
-        <v>3.09</v>
+        <v>3.11</v>
       </c>
       <c r="AD13">
         <v>1.38</v>
@@ -2498,10 +2498,10 @@
         </is>
       </c>
       <c r="AJ13">
-        <v>1.19</v>
+        <v>1.21</v>
       </c>
       <c r="AK13">
-        <v>1.87</v>
+        <v>1.9</v>
       </c>
       <c r="AL13">
         <v>0</v>
@@ -2591,13 +2591,13 @@
         </is>
       </c>
       <c r="N14">
-        <v>2</v>
+        <v>1.96</v>
       </c>
       <c r="O14">
-        <v>3.28</v>
+        <v>3.4</v>
       </c>
       <c r="P14">
-        <v>2.77</v>
+        <v>3.15</v>
       </c>
       <c r="Q14">
         <v>2.69</v>
@@ -2606,13 +2606,13 @@
         <v>2.2</v>
       </c>
       <c r="S14">
-        <v>1.38</v>
+        <v>1.35</v>
       </c>
       <c r="T14">
         <v>2.9</v>
       </c>
       <c r="U14">
-        <v>2.74</v>
+        <v>2.75</v>
       </c>
       <c r="V14">
         <v>1.4</v>
@@ -2630,16 +2630,16 @@
         <v>3.7</v>
       </c>
       <c r="AA14">
-        <v>1.68</v>
+        <v>1.85</v>
       </c>
       <c r="AB14">
         <v>1.9</v>
       </c>
       <c r="AC14">
-        <v>3.08</v>
+        <v>3.1</v>
       </c>
       <c r="AD14">
-        <v>1.36</v>
+        <v>1.31</v>
       </c>
       <c r="AE14">
         <v>1.08</v>
@@ -2760,7 +2760,7 @@
         <v>3.5</v>
       </c>
       <c r="P15">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="Q15">
         <v>3.1</v>
@@ -2787,10 +2787,10 @@
         <v>1.02</v>
       </c>
       <c r="Y15">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="Z15">
-        <v>4.26</v>
+        <v>4.3</v>
       </c>
       <c r="AA15">
         <v>1.7</v>
@@ -2805,13 +2805,13 @@
         <v>1.44</v>
       </c>
       <c r="AE15">
-        <v>1.11</v>
+        <v>1.17</v>
       </c>
       <c r="AF15">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="AG15">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2929,13 +2929,13 @@
         <v>2.69</v>
       </c>
       <c r="R16">
-        <v>2.07</v>
+        <v>2.1</v>
       </c>
       <c r="S16">
         <v>1.4</v>
       </c>
       <c r="T16">
-        <v>2.5</v>
+        <v>2.64</v>
       </c>
       <c r="U16">
         <v>3.12</v>
@@ -2950,13 +2950,13 @@
         <v>1.04</v>
       </c>
       <c r="Y16">
-        <v>1.29</v>
+        <v>1.36</v>
       </c>
       <c r="Z16">
         <v>3.05</v>
       </c>
       <c r="AA16">
-        <v>1.95</v>
+        <v>2.03</v>
       </c>
       <c r="AB16">
         <v>1.61</v>
@@ -3080,10 +3080,10 @@
         </is>
       </c>
       <c r="N17">
-        <v>2.87</v>
+        <v>2.78</v>
       </c>
       <c r="O17">
-        <v>3.45</v>
+        <v>3.55</v>
       </c>
       <c r="P17">
         <v>2.3</v>
@@ -3101,16 +3101,16 @@
         <v>3</v>
       </c>
       <c r="U17">
-        <v>2.62</v>
+        <v>2.89</v>
       </c>
       <c r="V17">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="W17">
         <v>1.06</v>
       </c>
       <c r="X17">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y17">
         <v>1.29</v>
@@ -3122,7 +3122,7 @@
         <v>1.93</v>
       </c>
       <c r="AB17">
-        <v>1.87</v>
+        <v>1.85</v>
       </c>
       <c r="AC17">
         <v>3.25</v>
@@ -3243,25 +3243,25 @@
         </is>
       </c>
       <c r="N18">
-        <v>2.05</v>
+        <v>2.15</v>
       </c>
       <c r="O18">
-        <v>3.23</v>
+        <v>3.4</v>
       </c>
       <c r="P18">
-        <v>2.65</v>
+        <v>2.68</v>
       </c>
       <c r="Q18">
-        <v>2.67</v>
+        <v>2.69</v>
       </c>
       <c r="R18">
-        <v>2.25</v>
+        <v>2.16</v>
       </c>
       <c r="S18">
         <v>1.34</v>
       </c>
       <c r="T18">
-        <v>3.1</v>
+        <v>3.08</v>
       </c>
       <c r="U18">
         <v>2.39</v>
@@ -3270,7 +3270,7 @@
         <v>1.5</v>
       </c>
       <c r="W18">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="X18">
         <v>1.02</v>
@@ -3291,7 +3291,7 @@
         <v>2.64</v>
       </c>
       <c r="AD18">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="AE18">
         <v>1.13</v>
@@ -3300,7 +3300,7 @@
         <v>1.53</v>
       </c>
       <c r="AG18">
-        <v>2.29</v>
+        <v>2.3</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3313,10 +3313,10 @@
         </is>
       </c>
       <c r="AJ18">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="AK18">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="AL18">
         <v>0</v>
@@ -3374,12 +3374,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Suzhou Dongwu</t>
+          <t>Changchun Yatai</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Meizhou Hakka</t>
+          <t>Hebei Kungfu</t>
         </is>
       </c>
       <c r="G19">
@@ -3406,65 +3406,65 @@
         </is>
       </c>
       <c r="N19">
-        <v>2.25</v>
+        <v>1.8</v>
       </c>
       <c r="O19">
-        <v>3.05</v>
+        <v>3.3</v>
       </c>
       <c r="P19">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Q19">
-        <v>2.89</v>
+        <v>2.4</v>
       </c>
       <c r="R19">
-        <v>2.1</v>
+        <v>2.21</v>
       </c>
       <c r="S19">
-        <v>1.41</v>
+        <v>1.36</v>
       </c>
       <c r="T19">
-        <v>2.72</v>
+        <v>2.63</v>
       </c>
       <c r="U19">
-        <v>2.95</v>
+        <v>2.7</v>
       </c>
       <c r="V19">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="W19">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="X19">
         <v>1.01</v>
       </c>
       <c r="Y19">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="Z19">
-        <v>3.05</v>
+        <v>3.4</v>
       </c>
       <c r="AA19">
-        <v>1.95</v>
+        <v>1.91</v>
       </c>
       <c r="AB19">
-        <v>1.75</v>
+        <v>1.78</v>
       </c>
       <c r="AC19">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="AD19">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="AE19">
-        <v>1.1</v>
+        <v>1.06</v>
       </c>
       <c r="AF19">
+        <v>1.79</v>
+      </c>
+      <c r="AG19">
         <v>1.73</v>
       </c>
-      <c r="AG19">
-        <v>1.93</v>
-      </c>
       <c r="AH19" t="inlineStr">
         <is>
           <t>[]</t>
@@ -3476,10 +3476,10 @@
         </is>
       </c>
       <c r="AJ19">
-        <v>1.35</v>
+        <v>1.15</v>
       </c>
       <c r="AK19">
-        <v>1.51</v>
+        <v>1.84</v>
       </c>
       <c r="AL19">
         <v>0</v>
@@ -3537,12 +3537,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Changchun Yatai</t>
+          <t>Suzhou Dongwu</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Hebei Kungfu</t>
+          <t>Meizhou Hakka</t>
         </is>
       </c>
       <c r="G20">
@@ -3569,64 +3569,64 @@
         </is>
       </c>
       <c r="N20">
-        <v>1.82</v>
+        <v>2.25</v>
       </c>
       <c r="O20">
-        <v>3.3</v>
+        <v>3.05</v>
       </c>
       <c r="P20">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="Q20">
-        <v>2.33</v>
+        <v>2.96</v>
       </c>
       <c r="R20">
-        <v>2.23</v>
+        <v>1.95</v>
       </c>
       <c r="S20">
-        <v>1.35</v>
+        <v>1.41</v>
       </c>
       <c r="T20">
-        <v>2.63</v>
+        <v>2.72</v>
       </c>
       <c r="U20">
-        <v>2.7</v>
+        <v>2.95</v>
       </c>
       <c r="V20">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="W20">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="X20">
         <v>1.01</v>
       </c>
       <c r="Y20">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="Z20">
-        <v>3.2</v>
+        <v>3.05</v>
       </c>
       <c r="AA20">
-        <v>1.9</v>
+        <v>1.87</v>
       </c>
       <c r="AB20">
-        <v>1.75</v>
+        <v>1.7</v>
       </c>
       <c r="AC20">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="AD20">
-        <v>1.3</v>
+        <v>1.22</v>
       </c>
       <c r="AE20">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="AF20">
-        <v>1.8</v>
+        <v>1.73</v>
       </c>
       <c r="AG20">
-        <v>1.87</v>
+        <v>1.93</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
@@ -3639,10 +3639,10 @@
         </is>
       </c>
       <c r="AJ20">
-        <v>1.22</v>
+        <v>1.35</v>
       </c>
       <c r="AK20">
-        <v>1.9</v>
+        <v>1.42</v>
       </c>
       <c r="AL20">
         <v>0</v>
@@ -3738,7 +3738,7 @@
         <v>3.9</v>
       </c>
       <c r="P21">
-        <v>1.66</v>
+        <v>1.68</v>
       </c>
       <c r="Q21">
         <v>3.9</v>
@@ -3753,13 +3753,13 @@
         <v>4.3</v>
       </c>
       <c r="U21">
-        <v>2.02</v>
+        <v>2.05</v>
       </c>
       <c r="V21">
-        <v>1.65</v>
+        <v>1.71</v>
       </c>
       <c r="W21">
-        <v>1.16</v>
+        <v>1.14</v>
       </c>
       <c r="X21">
         <v>1.01</v>
@@ -3777,10 +3777,10 @@
         <v>2.7</v>
       </c>
       <c r="AC21">
-        <v>2.11</v>
+        <v>2.12</v>
       </c>
       <c r="AD21">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="AE21">
         <v>1.32</v>
@@ -3789,7 +3789,7 @@
         <v>1.5</v>
       </c>
       <c r="AG21">
-        <v>2.55</v>
+        <v>2.45</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
@@ -3802,7 +3802,7 @@
         </is>
       </c>
       <c r="AJ21">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AK21">
         <v>1.25</v>
@@ -3904,7 +3904,7 @@
         <v>3</v>
       </c>
       <c r="Q22">
-        <v>2.72</v>
+        <v>2.55</v>
       </c>
       <c r="R22">
         <v>2.07</v>
@@ -3916,7 +3916,7 @@
         <v>2.73</v>
       </c>
       <c r="U22">
-        <v>2.69</v>
+        <v>2.89</v>
       </c>
       <c r="V22">
         <v>1.4</v>
@@ -3928,10 +3928,10 @@
         <v>1.01</v>
       </c>
       <c r="Y22">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="Z22">
-        <v>3.51</v>
+        <v>3.54</v>
       </c>
       <c r="AA22">
         <v>1.9</v>
@@ -3940,10 +3940,10 @@
         <v>1.85</v>
       </c>
       <c r="AC22">
-        <v>3.51</v>
+        <v>3.25</v>
       </c>
       <c r="AD22">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="AE22">
         <v>1.07</v>
@@ -3965,10 +3965,10 @@
         </is>
       </c>
       <c r="AJ22">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="AK22">
-        <v>1.67</v>
+        <v>1.6</v>
       </c>
       <c r="AL22">
         <v>0</v>
@@ -4061,16 +4061,16 @@
         <v>3.3</v>
       </c>
       <c r="O23">
-        <v>3.6</v>
+        <v>3.61</v>
       </c>
       <c r="P23">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="Q23">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="R23">
-        <v>2.58</v>
+        <v>2.45</v>
       </c>
       <c r="S23">
         <v>1.22</v>
@@ -4082,7 +4082,7 @@
         <v>2.14</v>
       </c>
       <c r="V23">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="W23">
         <v>1.13</v>
@@ -4097,25 +4097,25 @@
         <v>5.25</v>
       </c>
       <c r="AA23">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="AB23">
         <v>2.55</v>
       </c>
       <c r="AC23">
-        <v>2.15</v>
+        <v>2.13</v>
       </c>
       <c r="AD23">
-        <v>1.58</v>
+        <v>1.68</v>
       </c>
       <c r="AE23">
         <v>1.22</v>
       </c>
       <c r="AF23">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="AG23">
-        <v>2.63</v>
+        <v>2.6</v>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
@@ -4128,10 +4128,10 @@
         </is>
       </c>
       <c r="AJ23">
-        <v>1.25</v>
+        <v>1.73</v>
       </c>
       <c r="AK23">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AL23">
         <v>0</v>
@@ -4227,13 +4227,13 @@
         <v>2.95</v>
       </c>
       <c r="P24">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="Q24">
         <v>3.07</v>
       </c>
       <c r="R24">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="S24">
         <v>1.49</v>
@@ -4242,7 +4242,7 @@
         <v>2.41</v>
       </c>
       <c r="U24">
-        <v>3.31</v>
+        <v>3.32</v>
       </c>
       <c r="V24">
         <v>1.3</v>
@@ -4257,7 +4257,7 @@
         <v>1.36</v>
       </c>
       <c r="Z24">
-        <v>2.95</v>
+        <v>2.97</v>
       </c>
       <c r="AA24">
         <v>2.23</v>
@@ -4266,19 +4266,19 @@
         <v>1.62</v>
       </c>
       <c r="AC24">
-        <v>4.07</v>
+        <v>4.11</v>
       </c>
       <c r="AD24">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="AE24">
         <v>1.03</v>
       </c>
       <c r="AF24">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="AG24">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="AH24" t="inlineStr">
         <is>
@@ -4294,7 +4294,7 @@
         <v>1.27</v>
       </c>
       <c r="AK24">
-        <v>1.37</v>
+        <v>1.34</v>
       </c>
       <c r="AL24">
         <v>0</v>
@@ -4387,22 +4387,22 @@
         <v>1.74</v>
       </c>
       <c r="O25">
-        <v>3.6</v>
+        <v>3.61</v>
       </c>
       <c r="P25">
         <v>4.33</v>
       </c>
       <c r="Q25">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="R25">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="S25">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="T25">
-        <v>3.04</v>
+        <v>2.99</v>
       </c>
       <c r="U25">
         <v>2.45</v>
@@ -4426,10 +4426,10 @@
         <v>1.8</v>
       </c>
       <c r="AB25">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="AC25">
-        <v>2.9</v>
+        <v>2.88</v>
       </c>
       <c r="AD25">
         <v>1.4</v>
@@ -4454,7 +4454,7 @@
         </is>
       </c>
       <c r="AJ25">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="AK25">
         <v>1.98</v>
@@ -4550,10 +4550,10 @@
         <v>3</v>
       </c>
       <c r="O26">
-        <v>3.4</v>
+        <v>3.54</v>
       </c>
       <c r="P26">
-        <v>2.19</v>
+        <v>2.05</v>
       </c>
       <c r="Q26">
         <v>3.23</v>
@@ -4580,7 +4580,7 @@
         <v>1.01</v>
       </c>
       <c r="Y26">
-        <v>1.2</v>
+        <v>1.15</v>
       </c>
       <c r="Z26">
         <v>4.5</v>
@@ -4710,37 +4710,37 @@
         </is>
       </c>
       <c r="N27">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="O27">
-        <v>5</v>
+        <v>4.6</v>
       </c>
       <c r="P27">
-        <v>7.3</v>
+        <v>7.5</v>
       </c>
       <c r="Q27">
-        <v>1.71</v>
+        <v>1.75</v>
       </c>
       <c r="R27">
-        <v>2.47</v>
+        <v>2.7</v>
       </c>
       <c r="S27">
         <v>1.24</v>
       </c>
       <c r="T27">
-        <v>3.5</v>
+        <v>3.8</v>
       </c>
       <c r="U27">
-        <v>2.2</v>
+        <v>2.31</v>
       </c>
       <c r="V27">
-        <v>1.61</v>
+        <v>1.57</v>
       </c>
       <c r="W27">
-        <v>1.15</v>
+        <v>1.13</v>
       </c>
       <c r="X27">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y27">
         <v>1.18</v>
@@ -4749,13 +4749,13 @@
         <v>4.75</v>
       </c>
       <c r="AA27">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="AB27">
-        <v>2.4</v>
+        <v>2.51</v>
       </c>
       <c r="AC27">
-        <v>2.25</v>
+        <v>2.24</v>
       </c>
       <c r="AD27">
         <v>1.55</v>
@@ -4767,7 +4767,7 @@
         <v>1.77</v>
       </c>
       <c r="AG27">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="AH27" t="inlineStr">
         <is>
@@ -4780,7 +4780,7 @@
         </is>
       </c>
       <c r="AJ27">
-        <v>1.05</v>
+        <v>1.15</v>
       </c>
       <c r="AK27">
         <v>3.15</v>
@@ -4873,19 +4873,19 @@
         </is>
       </c>
       <c r="N28">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="O28">
-        <v>3.9</v>
+        <v>4.15</v>
       </c>
       <c r="P28">
-        <v>3.8</v>
+        <v>4.81</v>
       </c>
       <c r="Q28">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="R28">
-        <v>2.24</v>
+        <v>2.4</v>
       </c>
       <c r="S28">
         <v>1.28</v>
@@ -4906,22 +4906,22 @@
         <v>1.01</v>
       </c>
       <c r="Y28">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="Z28">
-        <v>4.25</v>
+        <v>4.71</v>
       </c>
       <c r="AA28">
         <v>1.62</v>
       </c>
       <c r="AB28">
-        <v>2.26</v>
+        <v>2.25</v>
       </c>
       <c r="AC28">
-        <v>2.55</v>
+        <v>2.63</v>
       </c>
       <c r="AD28">
-        <v>1.46</v>
+        <v>1.5</v>
       </c>
       <c r="AE28">
         <v>1.15</v>
@@ -5199,10 +5199,10 @@
         </is>
       </c>
       <c r="N30">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="O30">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="P30">
         <v>3</v>
@@ -5211,22 +5211,22 @@
         <v>2.62</v>
       </c>
       <c r="R30">
-        <v>2.19</v>
+        <v>2.2</v>
       </c>
       <c r="S30">
-        <v>1.32</v>
+        <v>1.28</v>
       </c>
       <c r="T30">
-        <v>3.25</v>
+        <v>3.15</v>
       </c>
       <c r="U30">
-        <v>2.48</v>
+        <v>2.47</v>
       </c>
       <c r="V30">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="W30">
-        <v>1.11</v>
+        <v>1.09</v>
       </c>
       <c r="X30">
         <v>1.02</v>
@@ -5235,28 +5235,28 @@
         <v>1.18</v>
       </c>
       <c r="Z30">
-        <v>3.86</v>
+        <v>3.9</v>
       </c>
       <c r="AA30">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="AB30">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="AC30">
-        <v>2.84</v>
+        <v>2.74</v>
       </c>
       <c r="AD30">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="AE30">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="AF30">
         <v>1.59</v>
       </c>
       <c r="AG30">
-        <v>2.2</v>
+        <v>2.19</v>
       </c>
       <c r="AH30" t="inlineStr">
         <is>
@@ -5269,7 +5269,7 @@
         </is>
       </c>
       <c r="AJ30">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="AK30">
         <v>1.63</v>
@@ -5368,7 +5368,7 @@
         <v>3.7</v>
       </c>
       <c r="P31">
-        <v>4.8</v>
+        <v>5.25</v>
       </c>
       <c r="Q31">
         <v>2.13</v>
@@ -5377,43 +5377,43 @@
         <v>2.25</v>
       </c>
       <c r="S31">
-        <v>1.38</v>
+        <v>1.35</v>
       </c>
       <c r="T31">
-        <v>2.73</v>
+        <v>2.95</v>
       </c>
       <c r="U31">
         <v>2.55</v>
       </c>
       <c r="V31">
-        <v>1.43</v>
+        <v>1.39</v>
       </c>
       <c r="W31">
         <v>1.1</v>
       </c>
       <c r="X31">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="Y31">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="Z31">
-        <v>3.8</v>
+        <v>3.34</v>
       </c>
       <c r="AA31">
         <v>1.93</v>
       </c>
       <c r="AB31">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="AC31">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="AD31">
         <v>1.28</v>
       </c>
       <c r="AE31">
-        <v>1.12</v>
+        <v>1.1</v>
       </c>
       <c r="AF31">
         <v>1.9</v>
@@ -5432,7 +5432,7 @@
         </is>
       </c>
       <c r="AJ31">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="AK31">
         <v>2.27</v>
@@ -5531,7 +5531,7 @@
         <v>2.62</v>
       </c>
       <c r="P32">
-        <v>2.9</v>
+        <v>2.92</v>
       </c>
       <c r="Q32">
         <v>3.58</v>
@@ -5552,7 +5552,7 @@
         <v>1.17</v>
       </c>
       <c r="W32">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="X32">
         <v>1.11</v>
@@ -5567,7 +5567,7 @@
         <v>2.88</v>
       </c>
       <c r="AB32">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AC32">
         <v>5.8</v>
@@ -5579,7 +5579,7 @@
         <v>1.02</v>
       </c>
       <c r="AF32">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="AG32">
         <v>1.5</v>
@@ -5598,7 +5598,7 @@
         <v>1.38</v>
       </c>
       <c r="AK32">
-        <v>1.4</v>
+        <v>1.37</v>
       </c>
       <c r="AL32">
         <v>0</v>
@@ -5691,16 +5691,16 @@
         <v>2.2</v>
       </c>
       <c r="O33">
-        <v>3.1</v>
+        <v>2.9</v>
       </c>
       <c r="P33">
-        <v>2.75</v>
+        <v>2.63</v>
       </c>
       <c r="Q33">
         <v>3.18</v>
       </c>
       <c r="R33">
-        <v>2.09</v>
+        <v>2.11</v>
       </c>
       <c r="S33">
         <v>1.45</v>
@@ -5727,13 +5727,13 @@
         <v>2.81</v>
       </c>
       <c r="AA33">
-        <v>2.2</v>
+        <v>2.21</v>
       </c>
       <c r="AB33">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="AC33">
-        <v>3.97</v>
+        <v>4.01</v>
       </c>
       <c r="AD33">
         <v>1.19</v>
@@ -5761,7 +5761,7 @@
         <v>1.4</v>
       </c>
       <c r="AK33">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="AL33">
         <v>0</v>
@@ -5851,19 +5851,19 @@
         </is>
       </c>
       <c r="N34">
-        <v>1.76</v>
+        <v>1.78</v>
       </c>
       <c r="O34">
         <v>3.6</v>
       </c>
       <c r="P34">
-        <v>4.08</v>
+        <v>4.13</v>
       </c>
       <c r="Q34">
         <v>2.2</v>
       </c>
       <c r="R34">
-        <v>2.2</v>
+        <v>2.19</v>
       </c>
       <c r="S34">
         <v>1.33</v>
@@ -5872,10 +5872,10 @@
         <v>3.11</v>
       </c>
       <c r="U34">
-        <v>2.3</v>
+        <v>2.41</v>
       </c>
       <c r="V34">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="W34">
         <v>1.1</v>
@@ -5884,19 +5884,19 @@
         <v>1.01</v>
       </c>
       <c r="Y34">
-        <v>1.19</v>
+        <v>1.14</v>
       </c>
       <c r="Z34">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="AA34">
-        <v>1.62</v>
+        <v>1.59</v>
       </c>
       <c r="AB34">
-        <v>2.11</v>
+        <v>2.12</v>
       </c>
       <c r="AC34">
-        <v>2.38</v>
+        <v>2.35</v>
       </c>
       <c r="AD34">
         <v>1.47</v>
@@ -5908,7 +5908,7 @@
         <v>1.62</v>
       </c>
       <c r="AG34">
-        <v>2.25</v>
+        <v>2.1</v>
       </c>
       <c r="AH34" t="inlineStr">
         <is>
@@ -5924,7 +5924,7 @@
         <v>1.2</v>
       </c>
       <c r="AK34">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="AL34">
         <v>0</v>
@@ -6014,19 +6014,19 @@
         </is>
       </c>
       <c r="N35">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="O35">
         <v>3.6</v>
       </c>
       <c r="P35">
-        <v>2.79</v>
+        <v>2.8</v>
       </c>
       <c r="Q35">
         <v>2.48</v>
       </c>
       <c r="R35">
-        <v>2.28</v>
+        <v>2.37</v>
       </c>
       <c r="S35">
         <v>1.25</v>
@@ -6050,13 +6050,13 @@
         <v>1.13</v>
       </c>
       <c r="Z35">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="AA35">
         <v>1.58</v>
       </c>
       <c r="AB35">
-        <v>2.18</v>
+        <v>2.3</v>
       </c>
       <c r="AC35">
         <v>2.33</v>
@@ -6065,7 +6065,7 @@
         <v>1.48</v>
       </c>
       <c r="AE35">
-        <v>1.17</v>
+        <v>1.21</v>
       </c>
       <c r="AF35">
         <v>1.5</v>
@@ -6177,13 +6177,13 @@
         </is>
       </c>
       <c r="N36">
-        <v>1.2</v>
+        <v>1.13</v>
       </c>
       <c r="O36">
-        <v>6.25</v>
+        <v>6.95</v>
       </c>
       <c r="P36">
-        <v>9.449999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="Q36">
         <v>1.57</v>
@@ -6192,49 +6192,49 @@
         <v>2.75</v>
       </c>
       <c r="S36">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="T36">
-        <v>4</v>
+        <v>3.8</v>
       </c>
       <c r="U36">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="V36">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="W36">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="X36">
         <v>1.01</v>
       </c>
       <c r="Y36">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="Z36">
-        <v>5</v>
+        <v>4.4</v>
       </c>
       <c r="AA36">
-        <v>1.41</v>
+        <v>1.44</v>
       </c>
       <c r="AB36">
-        <v>2.3</v>
+        <v>2.59</v>
       </c>
       <c r="AC36">
-        <v>2.08</v>
+        <v>2.18</v>
       </c>
       <c r="AD36">
-        <v>1.68</v>
+        <v>1.64</v>
       </c>
       <c r="AE36">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="AF36">
-        <v>1.93</v>
+        <v>2</v>
       </c>
       <c r="AG36">
-        <v>1.72</v>
+        <v>1.64</v>
       </c>
       <c r="AH36" t="inlineStr">
         <is>
@@ -6250,7 +6250,7 @@
         <v>1.1</v>
       </c>
       <c r="AK36">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="AL36">
         <v>0</v>
@@ -6340,19 +6340,19 @@
         </is>
       </c>
       <c r="N37">
-        <v>3.05</v>
+        <v>2.95</v>
       </c>
       <c r="O37">
-        <v>3.5</v>
+        <v>3.8</v>
       </c>
       <c r="P37">
         <v>1.95</v>
       </c>
       <c r="Q37">
-        <v>3.85</v>
+        <v>3.61</v>
       </c>
       <c r="R37">
-        <v>2.43</v>
+        <v>2.25</v>
       </c>
       <c r="S37">
         <v>1.25</v>
@@ -6382,7 +6382,7 @@
         <v>1.52</v>
       </c>
       <c r="AB37">
-        <v>2.21</v>
+        <v>2.35</v>
       </c>
       <c r="AC37">
         <v>2.3</v>
@@ -6391,13 +6391,13 @@
         <v>1.5</v>
       </c>
       <c r="AE37">
-        <v>1.19</v>
+        <v>1.14</v>
       </c>
       <c r="AF37">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="AG37">
-        <v>2.28</v>
+        <v>2.39</v>
       </c>
       <c r="AH37" t="inlineStr">
         <is>
@@ -6410,10 +6410,10 @@
         </is>
       </c>
       <c r="AJ37">
-        <v>1.8</v>
+        <v>1.63</v>
       </c>
       <c r="AK37">
-        <v>1.18</v>
+        <v>1.3</v>
       </c>
       <c r="AL37">
         <v>0</v>
@@ -6506,28 +6506,28 @@
         <v>7.6</v>
       </c>
       <c r="O38">
-        <v>5.05</v>
+        <v>5.15</v>
       </c>
       <c r="P38">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="Q38">
-        <v>8.35</v>
+        <v>7.3</v>
       </c>
       <c r="R38">
         <v>2.55</v>
       </c>
       <c r="S38">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="T38">
-        <v>3.24</v>
+        <v>3.32</v>
       </c>
       <c r="U38">
         <v>2.51</v>
       </c>
       <c r="V38">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="W38">
         <v>1.1</v>
@@ -6539,7 +6539,7 @@
         <v>1.23</v>
       </c>
       <c r="Z38">
-        <v>3.94</v>
+        <v>3.98</v>
       </c>
       <c r="AA38">
         <v>1.77</v>
@@ -6548,7 +6548,7 @@
         <v>2.22</v>
       </c>
       <c r="AC38">
-        <v>2.7</v>
+        <v>2.65</v>
       </c>
       <c r="AD38">
         <v>1.44</v>
@@ -6576,7 +6576,7 @@
         <v>3.28</v>
       </c>
       <c r="AK38">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="AL38">
         <v>0</v>
@@ -6666,19 +6666,19 @@
         </is>
       </c>
       <c r="N39">
-        <v>2.22</v>
+        <v>2.26</v>
       </c>
       <c r="O39">
-        <v>3.5</v>
+        <v>3.47</v>
       </c>
       <c r="P39">
         <v>3.1</v>
       </c>
       <c r="Q39">
-        <v>2.75</v>
+        <v>2.84</v>
       </c>
       <c r="R39">
-        <v>2.15</v>
+        <v>2.29</v>
       </c>
       <c r="S39">
         <v>1.37</v>
@@ -6696,7 +6696,7 @@
         <v>1.05</v>
       </c>
       <c r="X39">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="Y39">
         <v>1.28</v>
@@ -6705,25 +6705,25 @@
         <v>3.44</v>
       </c>
       <c r="AA39">
-        <v>1.81</v>
+        <v>1.9</v>
       </c>
       <c r="AB39">
-        <v>1.86</v>
+        <v>1.97</v>
       </c>
       <c r="AC39">
         <v>3.1</v>
       </c>
       <c r="AD39">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AE39">
         <v>1.08</v>
       </c>
       <c r="AF39">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="AG39">
-        <v>2.09</v>
+        <v>2.11</v>
       </c>
       <c r="AH39" t="inlineStr">
         <is>
@@ -6736,10 +6736,10 @@
         </is>
       </c>
       <c r="AJ39">
-        <v>1.25</v>
+        <v>1.34</v>
       </c>
       <c r="AK39">
-        <v>1.63</v>
+        <v>1.6</v>
       </c>
       <c r="AL39">
         <v>0</v>
@@ -7155,64 +7155,64 @@
         </is>
       </c>
       <c r="N42">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="O42">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="P42">
-        <v>2.95</v>
+        <v>3</v>
       </c>
       <c r="Q42">
-        <v>2.7</v>
+        <v>2.9</v>
       </c>
       <c r="R42">
-        <v>2.35</v>
+        <v>2.17</v>
       </c>
       <c r="S42">
+        <v>1.36</v>
+      </c>
+      <c r="T42">
+        <v>3</v>
+      </c>
+      <c r="U42">
+        <v>2.93</v>
+      </c>
+      <c r="V42">
+        <v>1.42</v>
+      </c>
+      <c r="W42">
+        <v>1.1</v>
+      </c>
+      <c r="X42">
+        <v>1.01</v>
+      </c>
+      <c r="Y42">
+        <v>1.22</v>
+      </c>
+      <c r="Z42">
+        <v>3.58</v>
+      </c>
+      <c r="AA42">
+        <v>1.72</v>
+      </c>
+      <c r="AB42">
+        <v>1.88</v>
+      </c>
+      <c r="AC42">
+        <v>3.16</v>
+      </c>
+      <c r="AD42">
         <v>1.3</v>
       </c>
-      <c r="T42">
-        <v>3.3</v>
-      </c>
-      <c r="U42">
-        <v>2.4</v>
-      </c>
-      <c r="V42">
-        <v>1.47</v>
-      </c>
-      <c r="W42">
-        <v>1.11</v>
-      </c>
-      <c r="X42">
-        <v>1.02</v>
-      </c>
-      <c r="Y42">
-        <v>1.16</v>
-      </c>
-      <c r="Z42">
-        <v>4.22</v>
-      </c>
-      <c r="AA42">
-        <v>1.66</v>
-      </c>
-      <c r="AB42">
-        <v>2.08</v>
-      </c>
-      <c r="AC42">
-        <v>2.62</v>
-      </c>
-      <c r="AD42">
-        <v>1.38</v>
-      </c>
       <c r="AE42">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AF42">
-        <v>1.55</v>
+        <v>1.65</v>
       </c>
       <c r="AG42">
-        <v>2.2</v>
+        <v>2.05</v>
       </c>
       <c r="AH42" t="inlineStr">
         <is>
@@ -7321,22 +7321,22 @@
         <v>2.65</v>
       </c>
       <c r="O43">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="P43">
-        <v>2.3</v>
+        <v>2.35</v>
       </c>
       <c r="Q43">
-        <v>3.3</v>
+        <v>3.02</v>
       </c>
       <c r="R43">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="S43">
         <v>1.3</v>
       </c>
       <c r="T43">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="U43">
         <v>2.4</v>
@@ -7354,10 +7354,10 @@
         <v>1.2</v>
       </c>
       <c r="Z43">
-        <v>4.2</v>
+        <v>4.15</v>
       </c>
       <c r="AA43">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="AB43">
         <v>2.05</v>
@@ -7369,7 +7369,7 @@
         <v>1.4</v>
       </c>
       <c r="AE43">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="AF43">
         <v>1.57</v>
@@ -7481,16 +7481,16 @@
         </is>
       </c>
       <c r="N44">
-        <v>1.65</v>
+        <v>1.68</v>
       </c>
       <c r="O44">
         <v>3.45</v>
       </c>
       <c r="P44">
-        <v>4.67</v>
+        <v>5.05</v>
       </c>
       <c r="Q44">
-        <v>2.31</v>
+        <v>2.28</v>
       </c>
       <c r="R44">
         <v>2.03</v>
@@ -7499,13 +7499,13 @@
         <v>1.46</v>
       </c>
       <c r="T44">
-        <v>2.64</v>
+        <v>2.5</v>
       </c>
       <c r="U44">
         <v>3.16</v>
       </c>
       <c r="V44">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="W44">
         <v>1.02</v>
@@ -7517,16 +7517,16 @@
         <v>1.36</v>
       </c>
       <c r="Z44">
-        <v>2.69</v>
+        <v>2.7</v>
       </c>
       <c r="AA44">
-        <v>2.28</v>
+        <v>2.25</v>
       </c>
       <c r="AB44">
-        <v>1.64</v>
+        <v>1.66</v>
       </c>
       <c r="AC44">
-        <v>3.92</v>
+        <v>3.9</v>
       </c>
       <c r="AD44">
         <v>1.18</v>
@@ -7551,10 +7551,10 @@
         </is>
       </c>
       <c r="AJ44">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="AK44">
-        <v>2.03</v>
+        <v>2.06</v>
       </c>
       <c r="AL44">
         <v>0</v>
@@ -7612,12 +7612,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Nõmme Kalju</t>
+          <t>Paide</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Tammeka</t>
+          <t>Kuressaare</t>
         </is>
       </c>
       <c r="G45">
@@ -7644,64 +7644,64 @@
         </is>
       </c>
       <c r="N45">
-        <v>1.49</v>
+        <v>1.57</v>
       </c>
       <c r="O45">
-        <v>4.2</v>
+        <v>3.9</v>
       </c>
       <c r="P45">
-        <v>4.6</v>
+        <v>4.57</v>
       </c>
       <c r="Q45">
-        <v>1.91</v>
+        <v>2.11</v>
       </c>
       <c r="R45">
-        <v>2.5</v>
+        <v>2.28</v>
       </c>
       <c r="S45">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="T45">
-        <v>3.28</v>
+        <v>3.25</v>
       </c>
       <c r="U45">
-        <v>2.26</v>
+        <v>2.27</v>
       </c>
       <c r="V45">
-        <v>1.56</v>
+        <v>1.53</v>
       </c>
       <c r="W45">
-        <v>1.14</v>
+        <v>1.09</v>
       </c>
       <c r="X45">
         <v>1.01</v>
       </c>
       <c r="Y45">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="Z45">
-        <v>4.45</v>
+        <v>4.2</v>
       </c>
       <c r="AA45">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="AB45">
-        <v>2.35</v>
+        <v>2.38</v>
       </c>
       <c r="AC45">
-        <v>2.38</v>
+        <v>2.41</v>
       </c>
       <c r="AD45">
         <v>1.53</v>
       </c>
       <c r="AE45">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AF45">
-        <v>1.65</v>
+        <v>1.58</v>
       </c>
       <c r="AG45">
-        <v>2.05</v>
+        <v>2.25</v>
       </c>
       <c r="AH45" t="inlineStr">
         <is>
@@ -7714,10 +7714,10 @@
         </is>
       </c>
       <c r="AJ45">
-        <v>1.08</v>
+        <v>1.17</v>
       </c>
       <c r="AK45">
-        <v>2.63</v>
+        <v>2.23</v>
       </c>
       <c r="AL45">
         <v>0</v>
@@ -7775,12 +7775,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Paide</t>
+          <t>Nõmme Kalju</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Kuressaare</t>
+          <t>Tammeka</t>
         </is>
       </c>
       <c r="G46">
@@ -7807,7 +7807,7 @@
         </is>
       </c>
       <c r="N46">
-        <v>1.37</v>
+        <v>1.5</v>
       </c>
       <c r="O46">
         <v>4</v>
@@ -7816,55 +7816,55 @@
         <v>5</v>
       </c>
       <c r="Q46">
-        <v>2.02</v>
+        <v>1.91</v>
       </c>
       <c r="R46">
-        <v>2.32</v>
+        <v>2.6</v>
       </c>
       <c r="S46">
-        <v>1.22</v>
+        <v>1.26</v>
       </c>
       <c r="T46">
-        <v>3.28</v>
+        <v>3.2</v>
       </c>
       <c r="U46">
-        <v>2.17</v>
+        <v>2.2</v>
       </c>
       <c r="V46">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="W46">
-        <v>1.1</v>
+        <v>1.14</v>
       </c>
       <c r="X46">
         <v>1.01</v>
       </c>
       <c r="Y46">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="Z46">
-        <v>5.5</v>
+        <v>4.45</v>
       </c>
       <c r="AA46">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="AB46">
+        <v>2.35</v>
+      </c>
+      <c r="AC46">
         <v>2.38</v>
       </c>
-      <c r="AC46">
-        <v>2.36</v>
-      </c>
       <c r="AD46">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="AE46">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="AF46">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="AG46">
-        <v>2.2</v>
+        <v>2.05</v>
       </c>
       <c r="AH46" t="inlineStr">
         <is>
@@ -7877,10 +7877,10 @@
         </is>
       </c>
       <c r="AJ46">
-        <v>1.14</v>
+        <v>1.08</v>
       </c>
       <c r="AK46">
-        <v>2.43</v>
+        <v>2.63</v>
       </c>
       <c r="AL46">
         <v>0</v>
@@ -7970,61 +7970,61 @@
         </is>
       </c>
       <c r="N47">
-        <v>4.85</v>
+        <v>4.5</v>
       </c>
       <c r="O47">
-        <v>4.7</v>
+        <v>4.4</v>
       </c>
       <c r="P47">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="Q47">
-        <v>4.78</v>
+        <v>3.64</v>
       </c>
       <c r="R47">
-        <v>2.94</v>
+        <v>2.57</v>
       </c>
       <c r="S47">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="T47">
-        <v>5</v>
+        <v>4.35</v>
       </c>
       <c r="U47">
-        <v>1.9</v>
+        <v>1.85</v>
       </c>
       <c r="V47">
-        <v>1.7</v>
+        <v>1.88</v>
       </c>
       <c r="W47">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="X47">
         <v>1.01</v>
       </c>
       <c r="Y47">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Z47">
-        <v>7.3</v>
+        <v>7</v>
       </c>
       <c r="AA47">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="AB47">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="AC47">
-        <v>1.91</v>
+        <v>1.77</v>
       </c>
       <c r="AD47">
-        <v>2.03</v>
+        <v>2.05</v>
       </c>
       <c r="AE47">
-        <v>1.42</v>
+        <v>1.39</v>
       </c>
       <c r="AF47">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="AG47">
         <v>2.9</v>
@@ -8043,7 +8043,7 @@
         <v>1.16</v>
       </c>
       <c r="AK47">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="AL47">
         <v>0</v>
@@ -8133,58 +8133,58 @@
         </is>
       </c>
       <c r="N48">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="O48">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="P48">
-        <v>2.73</v>
+        <v>2.72</v>
       </c>
       <c r="Q48">
-        <v>2.8</v>
+        <v>2.88</v>
       </c>
       <c r="R48">
-        <v>2.28</v>
+        <v>2.26</v>
       </c>
       <c r="S48">
         <v>1.3</v>
       </c>
       <c r="T48">
-        <v>3.2</v>
+        <v>3.08</v>
       </c>
       <c r="U48">
-        <v>2.5</v>
+        <v>2.75</v>
       </c>
       <c r="V48">
         <v>1.46</v>
       </c>
       <c r="W48">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="X48">
         <v>1</v>
       </c>
       <c r="Y48">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="Z48">
-        <v>3.84</v>
+        <v>3.42</v>
       </c>
       <c r="AA48">
-        <v>1.68</v>
+        <v>1.81</v>
       </c>
       <c r="AB48">
-        <v>2.06</v>
+        <v>2</v>
       </c>
       <c r="AC48">
-        <v>2.59</v>
+        <v>2.97</v>
       </c>
       <c r="AD48">
-        <v>1.39</v>
+        <v>1.3</v>
       </c>
       <c r="AE48">
-        <v>1.12</v>
+        <v>1.08</v>
       </c>
       <c r="AF48">
         <v>1.55</v>
@@ -8203,7 +8203,7 @@
         </is>
       </c>
       <c r="AJ48">
-        <v>1.23</v>
+        <v>1.41</v>
       </c>
       <c r="AK48">
         <v>1.48</v>
@@ -8296,64 +8296,64 @@
         </is>
       </c>
       <c r="N49">
-        <v>1.55</v>
+        <v>1.42</v>
       </c>
       <c r="O49">
-        <v>3.65</v>
+        <v>4.45</v>
       </c>
       <c r="P49">
-        <v>4.98</v>
+        <v>5.23</v>
       </c>
       <c r="Q49">
-        <v>2.13</v>
+        <v>1.93</v>
       </c>
       <c r="R49">
-        <v>2.2</v>
+        <v>2.45</v>
       </c>
       <c r="S49">
-        <v>1.34</v>
+        <v>1.27</v>
       </c>
       <c r="T49">
-        <v>2.9</v>
+        <v>3.4</v>
       </c>
       <c r="U49">
-        <v>2.45</v>
+        <v>2.3</v>
       </c>
       <c r="V49">
-        <v>1.44</v>
+        <v>1.52</v>
       </c>
       <c r="W49">
-        <v>1.06</v>
+        <v>1.14</v>
       </c>
       <c r="X49">
         <v>1</v>
       </c>
       <c r="Y49">
-        <v>1.23</v>
+        <v>1.14</v>
       </c>
       <c r="Z49">
-        <v>3.45</v>
+        <v>4.4</v>
       </c>
       <c r="AA49">
-        <v>1.79</v>
+        <v>1.53</v>
       </c>
       <c r="AB49">
-        <v>1.92</v>
+        <v>2.25</v>
       </c>
       <c r="AC49">
-        <v>2.85</v>
+        <v>2.41</v>
       </c>
       <c r="AD49">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
       <c r="AE49">
-        <v>1.08</v>
+        <v>1.16</v>
       </c>
       <c r="AF49">
-        <v>1.81</v>
+        <v>1.69</v>
       </c>
       <c r="AG49">
-        <v>1.88</v>
+        <v>2</v>
       </c>
       <c r="AH49" t="inlineStr">
         <is>
@@ -8366,10 +8366,10 @@
         </is>
       </c>
       <c r="AJ49">
-        <v>1.19</v>
+        <v>1.14</v>
       </c>
       <c r="AK49">
-        <v>2.18</v>
+        <v>2.8</v>
       </c>
       <c r="AL49">
         <v>0</v>
@@ -8459,61 +8459,61 @@
         </is>
       </c>
       <c r="N50">
-        <v>6.14</v>
+        <v>5.52</v>
       </c>
       <c r="O50">
-        <v>4.3</v>
+        <v>5.35</v>
       </c>
       <c r="P50">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="Q50">
         <v>5.75</v>
       </c>
       <c r="R50">
-        <v>2.6</v>
+        <v>2.52</v>
       </c>
       <c r="S50">
-        <v>1.27</v>
+        <v>1.21</v>
       </c>
       <c r="T50">
-        <v>3.75</v>
+        <v>3.5</v>
       </c>
       <c r="U50">
-        <v>2.12</v>
+        <v>2.25</v>
       </c>
       <c r="V50">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="W50">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="X50">
         <v>1.01</v>
       </c>
       <c r="Y50">
-        <v>1.12</v>
+        <v>1.17</v>
       </c>
       <c r="Z50">
-        <v>4.65</v>
+        <v>4.5</v>
       </c>
       <c r="AA50">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="AB50">
-        <v>2.29</v>
+        <v>2.45</v>
       </c>
       <c r="AC50">
-        <v>2.38</v>
+        <v>2.34</v>
       </c>
       <c r="AD50">
         <v>1.53</v>
       </c>
       <c r="AE50">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="AF50">
-        <v>1.72</v>
+        <v>1.66</v>
       </c>
       <c r="AG50">
         <v>1.96</v>
@@ -8529,7 +8529,7 @@
         </is>
       </c>
       <c r="AJ50">
-        <v>1.13</v>
+        <v>1.17</v>
       </c>
       <c r="AK50">
         <v>1.06</v>
@@ -8622,19 +8622,19 @@
         </is>
       </c>
       <c r="N51">
-        <v>1.94</v>
+        <v>1.85</v>
       </c>
       <c r="O51">
-        <v>3.7</v>
+        <v>3.55</v>
       </c>
       <c r="P51">
-        <v>3.71</v>
+        <v>3.4</v>
       </c>
       <c r="Q51">
-        <v>2.41</v>
+        <v>2.47</v>
       </c>
       <c r="R51">
-        <v>2.22</v>
+        <v>2.23</v>
       </c>
       <c r="S51">
         <v>1.32</v>
@@ -8652,28 +8652,28 @@
         <v>1.11</v>
       </c>
       <c r="X51">
-        <v>1</v>
+        <v>1.04</v>
       </c>
       <c r="Y51">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="Z51">
-        <v>4.4</v>
+        <v>3.92</v>
       </c>
       <c r="AA51">
         <v>1.72</v>
       </c>
       <c r="AB51">
-        <v>2.17</v>
+        <v>2.18</v>
       </c>
       <c r="AC51">
-        <v>2.65</v>
+        <v>2.69</v>
       </c>
       <c r="AD51">
         <v>1.46</v>
       </c>
       <c r="AE51">
-        <v>1.17</v>
+        <v>1.13</v>
       </c>
       <c r="AF51">
         <v>1.59</v>
@@ -8692,7 +8692,7 @@
         </is>
       </c>
       <c r="AJ51">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="AK51">
         <v>1.86</v>
@@ -8785,64 +8785,64 @@
         </is>
       </c>
       <c r="N52">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="O52">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="P52">
-        <v>0</v>
+        <v>6.71</v>
       </c>
       <c r="Q52">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="R52">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="S52">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="T52">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="U52">
-        <v>0</v>
+        <v>2.93</v>
       </c>
       <c r="V52">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W52">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X52">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y52">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="Z52">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AA52">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AB52">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AC52">
-        <v>0</v>
+        <v>3.31</v>
       </c>
       <c r="AD52">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AE52">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AF52">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AG52">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AH52" t="inlineStr">
         <is>
@@ -8855,10 +8855,10 @@
         </is>
       </c>
       <c r="AJ52">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AK52">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AL52">
         <v>0</v>
@@ -8951,16 +8951,16 @@
         <v>2</v>
       </c>
       <c r="O53">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="P53">
-        <v>2.8</v>
+        <v>3.25</v>
       </c>
       <c r="Q53">
-        <v>2.56</v>
+        <v>2.58</v>
       </c>
       <c r="R53">
-        <v>2.5</v>
+        <v>2.53</v>
       </c>
       <c r="S53">
         <v>1.24</v>
@@ -9002,10 +9002,10 @@
         <v>1.18</v>
       </c>
       <c r="AF53">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="AG53">
-        <v>2.47</v>
+        <v>2.63</v>
       </c>
       <c r="AH53" t="inlineStr">
         <is>
@@ -9111,13 +9111,13 @@
         </is>
       </c>
       <c r="N54">
-        <v>3.4</v>
+        <v>3.62</v>
       </c>
       <c r="O54">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="P54">
-        <v>1.97</v>
+        <v>1.92</v>
       </c>
       <c r="Q54">
         <v>3.85</v>
@@ -9126,16 +9126,16 @@
         <v>2.25</v>
       </c>
       <c r="S54">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="T54">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="U54">
-        <v>2.57</v>
+        <v>2.45</v>
       </c>
       <c r="V54">
-        <v>1.45</v>
+        <v>1.48</v>
       </c>
       <c r="W54">
         <v>1.11</v>
@@ -9147,22 +9147,22 @@
         <v>1.22</v>
       </c>
       <c r="Z54">
-        <v>4.25</v>
+        <v>4.2</v>
       </c>
       <c r="AA54">
         <v>1.73</v>
       </c>
       <c r="AB54">
-        <v>2.14</v>
+        <v>1.96</v>
       </c>
       <c r="AC54">
         <v>2.88</v>
       </c>
       <c r="AD54">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AE54">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="AF54">
         <v>1.63</v>
@@ -9184,7 +9184,7 @@
         <v>1.85</v>
       </c>
       <c r="AK54">
-        <v>1.26</v>
+        <v>1.21</v>
       </c>
       <c r="AL54">
         <v>0</v>
@@ -9274,13 +9274,13 @@
         </is>
       </c>
       <c r="N55">
-        <v>1.44</v>
+        <v>1.47</v>
       </c>
       <c r="O55">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="P55">
-        <v>5.49</v>
+        <v>5.7</v>
       </c>
       <c r="Q55">
         <v>1.85</v>
@@ -9289,7 +9289,7 @@
         <v>2.37</v>
       </c>
       <c r="S55">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="T55">
         <v>3.6</v>
@@ -9298,28 +9298,28 @@
         <v>2.2</v>
       </c>
       <c r="V55">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="W55">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="X55">
         <v>1.01</v>
       </c>
       <c r="Y55">
-        <v>1.15</v>
+        <v>1.13</v>
       </c>
       <c r="Z55">
-        <v>5.5</v>
+        <v>5</v>
       </c>
       <c r="AA55">
         <v>1.53</v>
       </c>
       <c r="AB55">
-        <v>2.52</v>
+        <v>2.53</v>
       </c>
       <c r="AC55">
-        <v>2.3</v>
+        <v>2.23</v>
       </c>
       <c r="AD55">
         <v>1.6</v>
@@ -9347,7 +9347,7 @@
         <v>1.15</v>
       </c>
       <c r="AK55">
-        <v>2.64</v>
+        <v>2.66</v>
       </c>
       <c r="AL55">
         <v>0</v>
@@ -9437,19 +9437,19 @@
         </is>
       </c>
       <c r="N56">
-        <v>2.4</v>
+        <v>2.41</v>
       </c>
       <c r="O56">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="P56">
-        <v>2.43</v>
+        <v>2.45</v>
       </c>
       <c r="Q56">
-        <v>2.78</v>
+        <v>2.9</v>
       </c>
       <c r="R56">
-        <v>2.16</v>
+        <v>2.3</v>
       </c>
       <c r="S56">
         <v>1.29</v>
@@ -9464,37 +9464,37 @@
         <v>1.53</v>
       </c>
       <c r="W56">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="X56">
         <v>1.01</v>
       </c>
       <c r="Y56">
-        <v>1.18</v>
+        <v>1.14</v>
       </c>
       <c r="Z56">
-        <v>4.33</v>
+        <v>4.3</v>
       </c>
       <c r="AA56">
-        <v>1.61</v>
+        <v>1.65</v>
       </c>
       <c r="AB56">
-        <v>2.13</v>
+        <v>2.23</v>
       </c>
       <c r="AC56">
-        <v>2.46</v>
+        <v>2.6</v>
       </c>
       <c r="AD56">
         <v>1.44</v>
       </c>
       <c r="AE56">
-        <v>1.14</v>
+        <v>1.2</v>
       </c>
       <c r="AF56">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="AG56">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="AH56" t="inlineStr">
         <is>
@@ -9507,10 +9507,10 @@
         </is>
       </c>
       <c r="AJ56">
-        <v>1.44</v>
+        <v>1.25</v>
       </c>
       <c r="AK56">
-        <v>1.44</v>
+        <v>1.47</v>
       </c>
       <c r="AL56">
         <v>0</v>
@@ -9600,64 +9600,64 @@
         </is>
       </c>
       <c r="N57">
-        <v>0</v>
+        <v>4.74</v>
       </c>
       <c r="O57">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="P57">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="Q57">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="R57">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S57">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="T57">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="U57">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="V57">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="W57">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X57">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="Y57">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="Z57">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AA57">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="AB57">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AC57">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AD57">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AE57">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AF57">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AG57">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AH57" t="inlineStr">
         <is>
@@ -9670,10 +9670,10 @@
         </is>
       </c>
       <c r="AJ57">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AK57">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AL57">
         <v>0</v>
@@ -9763,31 +9763,31 @@
         </is>
       </c>
       <c r="N58">
+        <v>3.3</v>
+      </c>
+      <c r="O58">
         <v>3.5</v>
       </c>
-      <c r="O58">
-        <v>3.65</v>
-      </c>
       <c r="P58">
-        <v>1.99</v>
+        <v>1.91</v>
       </c>
       <c r="Q58">
-        <v>3.94</v>
+        <v>3.92</v>
       </c>
       <c r="R58">
-        <v>2.24</v>
+        <v>2.3</v>
       </c>
       <c r="S58">
         <v>1.3</v>
       </c>
       <c r="T58">
-        <v>3.22</v>
+        <v>3.2</v>
       </c>
       <c r="U58">
-        <v>2.5</v>
+        <v>2.45</v>
       </c>
       <c r="V58">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="W58">
         <v>1.08</v>
@@ -9796,19 +9796,19 @@
         <v>1.01</v>
       </c>
       <c r="Y58">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="Z58">
-        <v>4.33</v>
+        <v>4.5</v>
       </c>
       <c r="AA58">
         <v>1.66</v>
       </c>
       <c r="AB58">
-        <v>2.08</v>
+        <v>2.2</v>
       </c>
       <c r="AC58">
-        <v>2.67</v>
+        <v>2.69</v>
       </c>
       <c r="AD58">
         <v>1.47</v>
@@ -9817,7 +9817,7 @@
         <v>1.18</v>
       </c>
       <c r="AF58">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="AG58">
         <v>2.25</v>
@@ -9833,7 +9833,7 @@
         </is>
       </c>
       <c r="AJ58">
-        <v>1.22</v>
+        <v>1.78</v>
       </c>
       <c r="AK58">
         <v>1.29</v>
@@ -9926,43 +9926,43 @@
         </is>
       </c>
       <c r="N59">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="O59">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="P59">
-        <v>4.72</v>
+        <v>4.2</v>
       </c>
       <c r="Q59">
-        <v>2.14</v>
+        <v>2.23</v>
       </c>
       <c r="R59">
-        <v>2.22</v>
+        <v>2.19</v>
       </c>
       <c r="S59">
         <v>1.3</v>
       </c>
       <c r="T59">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="U59">
-        <v>2.55</v>
+        <v>2.56</v>
       </c>
       <c r="V59">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="W59">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="X59">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y59">
         <v>1.21</v>
       </c>
       <c r="Z59">
-        <v>3.82</v>
+        <v>4.2</v>
       </c>
       <c r="AA59">
         <v>1.7</v>
@@ -9974,10 +9974,10 @@
         <v>2.75</v>
       </c>
       <c r="AD59">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="AE59">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="AF59">
         <v>1.73</v>
@@ -10089,34 +10089,34 @@
         </is>
       </c>
       <c r="N60">
-        <v>1.61</v>
+        <v>1.57</v>
       </c>
       <c r="O60">
         <v>4.2</v>
       </c>
       <c r="P60">
-        <v>4</v>
+        <v>4.92</v>
       </c>
       <c r="Q60">
         <v>2</v>
       </c>
       <c r="R60">
-        <v>2.44</v>
+        <v>2.41</v>
       </c>
       <c r="S60">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="T60">
         <v>4</v>
       </c>
       <c r="U60">
-        <v>2.11</v>
+        <v>2.12</v>
       </c>
       <c r="V60">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="W60">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="X60">
         <v>1.02</v>
@@ -10140,10 +10140,10 @@
         <v>1.73</v>
       </c>
       <c r="AE60">
-        <v>1.3</v>
+        <v>1.26</v>
       </c>
       <c r="AF60">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="AG60">
         <v>2.55</v>
@@ -10252,34 +10252,34 @@
         </is>
       </c>
       <c r="N61">
-        <v>1.14</v>
+        <v>1.16</v>
       </c>
       <c r="O61">
-        <v>7.5</v>
+        <v>7.25</v>
       </c>
       <c r="P61">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="Q61">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="R61">
-        <v>2.82</v>
+        <v>2.78</v>
       </c>
       <c r="S61">
-        <v>1.14</v>
+        <v>1.21</v>
       </c>
       <c r="T61">
-        <v>5</v>
+        <v>3.58</v>
       </c>
       <c r="U61">
         <v>1.8</v>
       </c>
       <c r="V61">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="W61">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="X61">
         <v>1.01</v>
@@ -10288,7 +10288,7 @@
         <v>1.07</v>
       </c>
       <c r="Z61">
-        <v>5.9</v>
+        <v>8</v>
       </c>
       <c r="AA61">
         <v>1.3</v>
@@ -10300,16 +10300,16 @@
         <v>1.94</v>
       </c>
       <c r="AD61">
-        <v>2</v>
+        <v>1.93</v>
       </c>
       <c r="AE61">
         <v>1.4</v>
       </c>
       <c r="AF61">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="AG61">
-        <v>1.7</v>
+        <v>1.65</v>
       </c>
       <c r="AH61" t="inlineStr">
         <is>
@@ -10418,7 +10418,7 @@
         <v>2.6</v>
       </c>
       <c r="O62">
-        <v>3.15</v>
+        <v>3.18</v>
       </c>
       <c r="P62">
         <v>2.45</v>
@@ -10430,10 +10430,10 @@
         <v>2.05</v>
       </c>
       <c r="S62">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="T62">
-        <v>2.56</v>
+        <v>2.88</v>
       </c>
       <c r="U62">
         <v>2.88</v>
@@ -10445,7 +10445,7 @@
         <v>1.05</v>
       </c>
       <c r="X62">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="Y62">
         <v>1.33</v>
@@ -10454,7 +10454,7 @@
         <v>2.99</v>
       </c>
       <c r="AA62">
-        <v>2.08</v>
+        <v>2.09</v>
       </c>
       <c r="AB62">
         <v>1.75</v>
@@ -10578,25 +10578,25 @@
         </is>
       </c>
       <c r="N63">
-        <v>2.29</v>
+        <v>2.35</v>
       </c>
       <c r="O63">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="P63">
-        <v>2.85</v>
+        <v>3</v>
       </c>
       <c r="Q63">
-        <v>2.75</v>
+        <v>2.88</v>
       </c>
       <c r="R63">
-        <v>2.25</v>
+        <v>2.1</v>
       </c>
       <c r="S63">
-        <v>1.3</v>
+        <v>1.35</v>
       </c>
       <c r="T63">
-        <v>2.8</v>
+        <v>2.78</v>
       </c>
       <c r="U63">
         <v>2.5</v>
@@ -10608,13 +10608,13 @@
         <v>1.07</v>
       </c>
       <c r="X63">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="Y63">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="Z63">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="AA63">
         <v>1.79</v>
@@ -10623,19 +10623,19 @@
         <v>1.95</v>
       </c>
       <c r="AC63">
-        <v>3.02</v>
+        <v>3.04</v>
       </c>
       <c r="AD63">
-        <v>1.3</v>
+        <v>1.38</v>
       </c>
       <c r="AE63">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="AF63">
         <v>1.67</v>
       </c>
       <c r="AG63">
-        <v>2.08</v>
+        <v>2.15</v>
       </c>
       <c r="AH63" t="inlineStr">
         <is>
@@ -10741,13 +10741,13 @@
         </is>
       </c>
       <c r="N64">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="O64">
         <v>5</v>
       </c>
       <c r="P64">
-        <v>5.75</v>
+        <v>6.75</v>
       </c>
       <c r="Q64">
         <v>1.67</v>
@@ -10762,7 +10762,7 @@
         <v>4.75</v>
       </c>
       <c r="U64">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="V64">
         <v>1.87</v>
@@ -10780,25 +10780,25 @@
         <v>6.5</v>
       </c>
       <c r="AA64">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="AB64">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="AC64">
         <v>1.77</v>
       </c>
       <c r="AD64">
-        <v>1.95</v>
+        <v>1.98</v>
       </c>
       <c r="AE64">
         <v>1.43</v>
       </c>
       <c r="AF64">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="AG64">
-        <v>2.5</v>
+        <v>2.47</v>
       </c>
       <c r="AH64" t="inlineStr">
         <is>
@@ -10907,13 +10907,13 @@
         <v>1.93</v>
       </c>
       <c r="O65">
-        <v>3.33</v>
+        <v>3.7</v>
       </c>
       <c r="P65">
-        <v>2.78</v>
+        <v>3.25</v>
       </c>
       <c r="Q65">
-        <v>2.33</v>
+        <v>2.3</v>
       </c>
       <c r="R65">
         <v>2.5</v>
@@ -10925,10 +10925,10 @@
         <v>3.44</v>
       </c>
       <c r="U65">
-        <v>2.17</v>
+        <v>2.2</v>
       </c>
       <c r="V65">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="W65">
         <v>1.14</v>
@@ -10946,13 +10946,13 @@
         <v>1.45</v>
       </c>
       <c r="AB65">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="AC65">
-        <v>2.28</v>
+        <v>2.26</v>
       </c>
       <c r="AD65">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="AE65">
         <v>1.21</v>
@@ -10977,7 +10977,7 @@
         <v>1.25</v>
       </c>
       <c r="AK65">
-        <v>1.76</v>
+        <v>1.92</v>
       </c>
       <c r="AL65">
         <v>0</v>
@@ -11067,31 +11067,31 @@
         </is>
       </c>
       <c r="N66">
-        <v>2.45</v>
+        <v>2.4</v>
       </c>
       <c r="O66">
-        <v>3.73</v>
+        <v>3.85</v>
       </c>
       <c r="P66">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="Q66">
-        <v>2.64</v>
+        <v>2.79</v>
       </c>
       <c r="R66">
-        <v>2.45</v>
+        <v>2.48</v>
       </c>
       <c r="S66">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="T66">
-        <v>3.95</v>
+        <v>4.5</v>
       </c>
       <c r="U66">
-        <v>1.9</v>
+        <v>1.88</v>
       </c>
       <c r="V66">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="W66">
         <v>1.22</v>
@@ -11103,19 +11103,19 @@
         <v>1.06</v>
       </c>
       <c r="Z66">
-        <v>7.5</v>
+        <v>5.4</v>
       </c>
       <c r="AA66">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="AB66">
-        <v>3.13</v>
+        <v>3.09</v>
       </c>
       <c r="AC66">
         <v>1.94</v>
       </c>
       <c r="AD66">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="AE66">
         <v>1.3</v>
@@ -11137,7 +11137,7 @@
         </is>
       </c>
       <c r="AJ66">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AK66">
         <v>1.49</v>
@@ -11230,19 +11230,19 @@
         </is>
       </c>
       <c r="N67">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="O67">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="P67">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="Q67">
-        <v>2.55</v>
+        <v>2.6</v>
       </c>
       <c r="R67">
-        <v>2.38</v>
+        <v>2.5</v>
       </c>
       <c r="S67">
         <v>1.2</v>
@@ -11269,16 +11269,16 @@
         <v>5.75</v>
       </c>
       <c r="AA67">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="AB67">
         <v>2.63</v>
       </c>
       <c r="AC67">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="AD67">
-        <v>1.67</v>
+        <v>1.73</v>
       </c>
       <c r="AE67">
         <v>1.29</v>
@@ -11287,7 +11287,7 @@
         <v>1.4</v>
       </c>
       <c r="AG67">
-        <v>2.7</v>
+        <v>2.75</v>
       </c>
       <c r="AH67" t="inlineStr">
         <is>
@@ -11300,10 +11300,10 @@
         </is>
       </c>
       <c r="AJ67">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="AK67">
-        <v>1.56</v>
+        <v>1.71</v>
       </c>
       <c r="AL67">
         <v>0</v>
@@ -11396,10 +11396,10 @@
         <v>1.39</v>
       </c>
       <c r="O68">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="P68">
-        <v>5.25</v>
+        <v>4.85</v>
       </c>
       <c r="Q68">
         <v>1.77</v>
@@ -11417,7 +11417,7 @@
         <v>1.99</v>
       </c>
       <c r="V68">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="W68">
         <v>1.22</v>
@@ -11435,13 +11435,13 @@
         <v>1.3</v>
       </c>
       <c r="AB68">
-        <v>2.85</v>
+        <v>3.21</v>
       </c>
       <c r="AC68">
-        <v>1.92</v>
+        <v>1.88</v>
       </c>
       <c r="AD68">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="AE68">
         <v>1.33</v>
@@ -11450,7 +11450,7 @@
         <v>1.5</v>
       </c>
       <c r="AG68">
-        <v>2.44</v>
+        <v>2.25</v>
       </c>
       <c r="AH68" t="inlineStr">
         <is>
@@ -11463,10 +11463,10 @@
         </is>
       </c>
       <c r="AJ68">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="AK68">
-        <v>2.88</v>
+        <v>2.83</v>
       </c>
       <c r="AL68">
         <v>0</v>
@@ -11556,16 +11556,16 @@
         </is>
       </c>
       <c r="N69">
-        <v>3.97</v>
+        <v>4.2</v>
       </c>
       <c r="O69">
+        <v>4.4</v>
+      </c>
+      <c r="P69">
+        <v>1.57</v>
+      </c>
+      <c r="Q69">
         <v>4.33</v>
-      </c>
-      <c r="P69">
-        <v>1.54</v>
-      </c>
-      <c r="Q69">
-        <v>4.2</v>
       </c>
       <c r="R69">
         <v>2.65</v>
@@ -11577,7 +11577,7 @@
         <v>4.15</v>
       </c>
       <c r="U69">
-        <v>1.94</v>
+        <v>1.98</v>
       </c>
       <c r="V69">
         <v>1.79</v>
@@ -11589,10 +11589,10 @@
         <v>1.01</v>
       </c>
       <c r="Y69">
-        <v>1.05</v>
+        <v>1.11</v>
       </c>
       <c r="Z69">
-        <v>6.5</v>
+        <v>6.57</v>
       </c>
       <c r="AA69">
         <v>1.31</v>
@@ -11601,19 +11601,19 @@
         <v>2.92</v>
       </c>
       <c r="AC69">
-        <v>1.96</v>
+        <v>1.89</v>
       </c>
       <c r="AD69">
         <v>1.71</v>
       </c>
       <c r="AE69">
-        <v>1.36</v>
+        <v>1.31</v>
       </c>
       <c r="AF69">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="AG69">
-        <v>2.65</v>
+        <v>2.7</v>
       </c>
       <c r="AH69" t="inlineStr">
         <is>
@@ -11626,7 +11626,7 @@
         </is>
       </c>
       <c r="AJ69">
-        <v>1.18</v>
+        <v>1.13</v>
       </c>
       <c r="AK69">
         <v>1.15</v>
@@ -11885,16 +11885,16 @@
         <v>1.28</v>
       </c>
       <c r="O71">
-        <v>4.6</v>
+        <v>5.25</v>
       </c>
       <c r="P71">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="Q71">
-        <v>1.74</v>
+        <v>1.78</v>
       </c>
       <c r="R71">
-        <v>2.25</v>
+        <v>2.59</v>
       </c>
       <c r="S71">
         <v>1.34</v>
@@ -11903,7 +11903,7 @@
         <v>3.14</v>
       </c>
       <c r="U71">
-        <v>2.62</v>
+        <v>2.7</v>
       </c>
       <c r="V71">
         <v>1.46</v>
@@ -11915,22 +11915,22 @@
         <v>1</v>
       </c>
       <c r="Y71">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="Z71">
-        <v>3.83</v>
+        <v>3.68</v>
       </c>
       <c r="AA71">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="AB71">
-        <v>2.05</v>
+        <v>2.02</v>
       </c>
       <c r="AC71">
-        <v>2.89</v>
+        <v>2.85</v>
       </c>
       <c r="AD71">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="AE71">
         <v>1.1</v>
@@ -11952,10 +11952,10 @@
         </is>
       </c>
       <c r="AJ71">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AK71">
-        <v>3.08</v>
+        <v>3.42</v>
       </c>
       <c r="AL71">
         <v>0</v>
@@ -12054,10 +12054,10 @@
         <v>2.5</v>
       </c>
       <c r="Q72">
-        <v>3.02</v>
+        <v>2.95</v>
       </c>
       <c r="R72">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="S72">
         <v>1.3</v>
@@ -12084,19 +12084,19 @@
         <v>3.8</v>
       </c>
       <c r="AA72">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="AB72">
         <v>2</v>
       </c>
       <c r="AC72">
-        <v>2.75</v>
+        <v>2.7</v>
       </c>
       <c r="AD72">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AE72">
-        <v>1.14</v>
+        <v>1.11</v>
       </c>
       <c r="AF72">
         <v>1.56</v>
@@ -12118,7 +12118,7 @@
         <v>1.4</v>
       </c>
       <c r="AK72">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="AL72">
         <v>0</v>
@@ -12208,13 +12208,13 @@
         </is>
       </c>
       <c r="N73">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="O73">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="P73">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="Q73">
         <v>0</v>
@@ -12377,7 +12377,7 @@
         <v>3</v>
       </c>
       <c r="P74">
-        <v>3.24</v>
+        <v>3.25</v>
       </c>
       <c r="Q74">
         <v>3</v>
@@ -12386,28 +12386,28 @@
         <v>1.87</v>
       </c>
       <c r="S74">
-        <v>1.58</v>
+        <v>1.5</v>
       </c>
       <c r="T74">
-        <v>2.22</v>
+        <v>2.33</v>
       </c>
       <c r="U74">
-        <v>3.8</v>
+        <v>3.58</v>
       </c>
       <c r="V74">
         <v>1.22</v>
       </c>
       <c r="W74">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="X74">
         <v>1.07</v>
       </c>
       <c r="Y74">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="Z74">
-        <v>2.36</v>
+        <v>2.34</v>
       </c>
       <c r="AA74">
         <v>2.56</v>
@@ -12425,10 +12425,10 @@
         <v>1.04</v>
       </c>
       <c r="AF74">
-        <v>2.14</v>
+        <v>2.15</v>
       </c>
       <c r="AG74">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="AH74" t="inlineStr">
         <is>
@@ -12534,19 +12534,19 @@
         </is>
       </c>
       <c r="N75">
-        <v>2.45</v>
+        <v>2.3</v>
       </c>
       <c r="O75">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="P75">
-        <v>2.55</v>
+        <v>2.62</v>
       </c>
       <c r="Q75">
         <v>3.1</v>
       </c>
       <c r="R75">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="S75">
         <v>1.33</v>
@@ -12564,28 +12564,28 @@
         <v>1.07</v>
       </c>
       <c r="X75">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="Y75">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="Z75">
         <v>3.15</v>
       </c>
       <c r="AA75">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="AB75">
-        <v>1.91</v>
+        <v>1.98</v>
       </c>
       <c r="AC75">
         <v>3.1</v>
       </c>
       <c r="AD75">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="AE75">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="AF75">
         <v>1.65</v>
@@ -12700,10 +12700,10 @@
         <v>2.7</v>
       </c>
       <c r="O76">
-        <v>3.13</v>
+        <v>3.25</v>
       </c>
       <c r="P76">
-        <v>2.18</v>
+        <v>2.4</v>
       </c>
       <c r="Q76">
         <v>3.35</v>
@@ -12748,7 +12748,7 @@
         <v>1.32</v>
       </c>
       <c r="AE76">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="AF76">
         <v>1.71</v>
@@ -12860,7 +12860,7 @@
         </is>
       </c>
       <c r="N77">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="O77">
         <v>3.5</v>
@@ -12890,13 +12890,13 @@
         <v>1.11</v>
       </c>
       <c r="X77">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y77">
         <v>1.21</v>
       </c>
       <c r="Z77">
-        <v>3.6</v>
+        <v>3.8</v>
       </c>
       <c r="AA77">
         <v>1.8</v>
@@ -12930,10 +12930,10 @@
         </is>
       </c>
       <c r="AJ77">
-        <v>1.27</v>
+        <v>1.33</v>
       </c>
       <c r="AK77">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="AL77">
         <v>0</v>
@@ -13026,16 +13026,16 @@
         <v>2.2</v>
       </c>
       <c r="O78">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="P78">
         <v>3.25</v>
       </c>
       <c r="Q78">
-        <v>2.9</v>
+        <v>2.98</v>
       </c>
       <c r="R78">
-        <v>2.05</v>
+        <v>1.89</v>
       </c>
       <c r="S78">
         <v>1.4</v>
@@ -13050,25 +13050,25 @@
         <v>1.33</v>
       </c>
       <c r="W78">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="X78">
         <v>1.04</v>
       </c>
       <c r="Y78">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="Z78">
         <v>2.62</v>
       </c>
       <c r="AA78">
-        <v>2.34</v>
+        <v>2.35</v>
       </c>
       <c r="AB78">
-        <v>1.57</v>
+        <v>1.61</v>
       </c>
       <c r="AC78">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="AD78">
         <v>1.16</v>
@@ -13077,7 +13077,7 @@
         <v>1.02</v>
       </c>
       <c r="AF78">
-        <v>1.9</v>
+        <v>1.85</v>
       </c>
       <c r="AG78">
         <v>1.76</v>
@@ -13093,7 +13093,7 @@
         </is>
       </c>
       <c r="AJ78">
-        <v>1.34</v>
+        <v>1.23</v>
       </c>
       <c r="AK78">
         <v>1.57</v>
@@ -13530,7 +13530,7 @@
         <v>1.3</v>
       </c>
       <c r="T81">
-        <v>3.04</v>
+        <v>3.1</v>
       </c>
       <c r="U81">
         <v>2.5</v>
@@ -13539,7 +13539,7 @@
         <v>1.44</v>
       </c>
       <c r="W81">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="X81">
         <v>1.03</v>
@@ -13548,13 +13548,13 @@
         <v>1.19</v>
       </c>
       <c r="Z81">
-        <v>3.8</v>
+        <v>4.2</v>
       </c>
       <c r="AA81">
         <v>1.75</v>
       </c>
       <c r="AB81">
-        <v>2.05</v>
+        <v>1.97</v>
       </c>
       <c r="AC81">
         <v>2.78</v>
@@ -13563,10 +13563,10 @@
         <v>1.4</v>
       </c>
       <c r="AE81">
-        <v>1.14</v>
+        <v>1.09</v>
       </c>
       <c r="AF81">
-        <v>1.62</v>
+        <v>1.64</v>
       </c>
       <c r="AG81">
         <v>2</v>
@@ -13582,7 +13582,7 @@
         </is>
       </c>
       <c r="AJ81">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="AK81">
         <v>1.18</v>
@@ -13681,7 +13681,7 @@
         <v>3.4</v>
       </c>
       <c r="P82">
-        <v>4.05</v>
+        <v>4.46</v>
       </c>
       <c r="Q82">
         <v>2.38</v>
@@ -13693,7 +13693,7 @@
         <v>1.43</v>
       </c>
       <c r="T82">
-        <v>2.65</v>
+        <v>2.53</v>
       </c>
       <c r="U82">
         <v>2.9</v>
@@ -13705,34 +13705,34 @@
         <v>1.02</v>
       </c>
       <c r="X82">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="Y82">
-        <v>1.33</v>
+        <v>1.38</v>
       </c>
       <c r="Z82">
-        <v>3.03</v>
+        <v>2.94</v>
       </c>
       <c r="AA82">
         <v>2.1</v>
       </c>
       <c r="AB82">
-        <v>1.67</v>
+        <v>1.71</v>
       </c>
       <c r="AC82">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="AD82">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AE82">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="AF82">
         <v>2</v>
       </c>
       <c r="AG82">
-        <v>1.83</v>
+        <v>1.74</v>
       </c>
       <c r="AH82" t="inlineStr">
         <is>
@@ -13748,7 +13748,7 @@
         <v>1.27</v>
       </c>
       <c r="AK82">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="AL82">
         <v>0</v>
@@ -13841,16 +13841,16 @@
         <v>3</v>
       </c>
       <c r="O83">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="P83">
         <v>2.05</v>
       </c>
       <c r="Q83">
-        <v>3.28</v>
+        <v>3.57</v>
       </c>
       <c r="R83">
-        <v>2.23</v>
+        <v>2.21</v>
       </c>
       <c r="S83">
         <v>1.28</v>
@@ -13862,10 +13862,10 @@
         <v>2.3</v>
       </c>
       <c r="V83">
-        <v>1.5</v>
+        <v>1.55</v>
       </c>
       <c r="W83">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="X83">
         <v>1.01</v>
@@ -13874,7 +13874,7 @@
         <v>1.15</v>
       </c>
       <c r="Z83">
-        <v>4.33</v>
+        <v>4.3</v>
       </c>
       <c r="AA83">
         <v>1.57</v>
@@ -13889,7 +13889,7 @@
         <v>1.47</v>
       </c>
       <c r="AE83">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="AF83">
         <v>1.5</v>
@@ -13908,10 +13908,10 @@
         </is>
       </c>
       <c r="AJ83">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="AK83">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="AL83">
         <v>0</v>
@@ -14001,61 +14001,61 @@
         </is>
       </c>
       <c r="N84">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="O84">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="P84">
-        <v>4.8</v>
+        <v>4.6</v>
       </c>
       <c r="Q84">
-        <v>1.95</v>
+        <v>2.1</v>
       </c>
       <c r="R84">
-        <v>2.36</v>
+        <v>2.32</v>
       </c>
       <c r="S84">
         <v>1.25</v>
       </c>
       <c r="T84">
-        <v>3.25</v>
+        <v>3.5</v>
       </c>
       <c r="U84">
-        <v>2.25</v>
+        <v>2.47</v>
       </c>
       <c r="V84">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="W84">
         <v>1.1</v>
       </c>
       <c r="X84">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y84">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="Z84">
-        <v>4.6</v>
+        <v>4.33</v>
       </c>
       <c r="AA84">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="AB84">
-        <v>2.15</v>
+        <v>2.14</v>
       </c>
       <c r="AC84">
-        <v>2.45</v>
+        <v>2.49</v>
       </c>
       <c r="AD84">
-        <v>1.54</v>
+        <v>1.47</v>
       </c>
       <c r="AE84">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="AF84">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="AG84">
         <v>2.12</v>
@@ -14071,10 +14071,10 @@
         </is>
       </c>
       <c r="AJ84">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="AK84">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="AL84">
         <v>0</v>
@@ -14132,12 +14132,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Vaprus</t>
+          <t>Tallinna FC Flora</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Tallinna FC Levadia</t>
+          <t>Harju Jalgpallikool</t>
         </is>
       </c>
       <c r="G85">
@@ -14164,64 +14164,64 @@
         </is>
       </c>
       <c r="N85">
-        <v>11.7</v>
+        <v>1.54</v>
       </c>
       <c r="O85">
-        <v>5.5</v>
+        <v>4.55</v>
       </c>
       <c r="P85">
-        <v>1.25</v>
+        <v>6.59</v>
       </c>
       <c r="Q85">
-        <v>7.61</v>
+        <v>2</v>
       </c>
       <c r="R85">
-        <v>2.82</v>
+        <v>2.5</v>
       </c>
       <c r="S85">
-        <v>1.21</v>
+        <v>1.23</v>
       </c>
       <c r="T85">
-        <v>3.58</v>
+        <v>3.42</v>
       </c>
       <c r="U85">
-        <v>2.13</v>
+        <v>2.18</v>
       </c>
       <c r="V85">
-        <v>1.65</v>
+        <v>1.63</v>
       </c>
       <c r="W85">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="X85">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y85">
-        <v>1.13</v>
+        <v>1.1</v>
       </c>
       <c r="Z85">
         <v>6</v>
       </c>
       <c r="AA85">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="AB85">
-        <v>2.7</v>
+        <v>2.5</v>
       </c>
       <c r="AC85">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="AD85">
-        <v>1.67</v>
+        <v>1.63</v>
       </c>
       <c r="AE85">
-        <v>1.29</v>
+        <v>1.21</v>
       </c>
       <c r="AF85">
-        <v>1.81</v>
+        <v>1.53</v>
       </c>
       <c r="AG85">
-        <v>1.89</v>
+        <v>2.28</v>
       </c>
       <c r="AH85" t="inlineStr">
         <is>
@@ -14234,10 +14234,10 @@
         </is>
       </c>
       <c r="AJ85">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="AK85">
-        <v>1</v>
+        <v>2.3</v>
       </c>
       <c r="AL85">
         <v>0</v>
@@ -14295,12 +14295,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Tallinna FC Flora</t>
+          <t>Vaprus</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Harju Jalgpallikool</t>
+          <t>Tallinna FC Levadia</t>
         </is>
       </c>
       <c r="G86">
@@ -14327,64 +14327,64 @@
         </is>
       </c>
       <c r="N86">
-        <v>1.52</v>
+        <v>11.7</v>
       </c>
       <c r="O86">
-        <v>4.05</v>
+        <v>5.25</v>
       </c>
       <c r="P86">
-        <v>6.59</v>
+        <v>1.28</v>
       </c>
       <c r="Q86">
-        <v>2</v>
+        <v>7.44</v>
       </c>
       <c r="R86">
-        <v>2.5</v>
+        <v>2.83</v>
       </c>
       <c r="S86">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="T86">
-        <v>3.42</v>
+        <v>3.58</v>
       </c>
       <c r="U86">
-        <v>2.18</v>
+        <v>2.11</v>
       </c>
       <c r="V86">
-        <v>1.63</v>
+        <v>1.67</v>
       </c>
       <c r="W86">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="X86">
         <v>1.01</v>
       </c>
       <c r="Y86">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="Z86">
         <v>6</v>
       </c>
       <c r="AA86">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="AB86">
-        <v>2.63</v>
+        <v>2.66</v>
       </c>
       <c r="AC86">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="AD86">
-        <v>1.63</v>
+        <v>1.65</v>
       </c>
       <c r="AE86">
-        <v>1.21</v>
+        <v>1.23</v>
       </c>
       <c r="AF86">
-        <v>1.53</v>
+        <v>1.75</v>
       </c>
       <c r="AG86">
-        <v>2.32</v>
+        <v>1.91</v>
       </c>
       <c r="AH86" t="inlineStr">
         <is>
@@ -14397,10 +14397,10 @@
         </is>
       </c>
       <c r="AJ86">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="AK86">
-        <v>2.3</v>
+        <v>1.01</v>
       </c>
       <c r="AL86">
         <v>0</v>
@@ -14490,13 +14490,13 @@
         </is>
       </c>
       <c r="N87">
-        <v>3.8</v>
+        <v>4.4</v>
       </c>
       <c r="O87">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="P87">
-        <v>1.64</v>
+        <v>1.66</v>
       </c>
       <c r="Q87">
         <v>4.4</v>
@@ -14505,19 +14505,19 @@
         <v>2.4</v>
       </c>
       <c r="S87">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="T87">
         <v>3.42</v>
       </c>
       <c r="U87">
-        <v>2.29</v>
+        <v>2.27</v>
       </c>
       <c r="V87">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="W87">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="X87">
         <v>1.01</v>
@@ -14526,28 +14526,28 @@
         <v>1.14</v>
       </c>
       <c r="Z87">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="AA87">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="AB87">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="AC87">
-        <v>2.35</v>
+        <v>2.33</v>
       </c>
       <c r="AD87">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="AE87">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AF87">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="AG87">
-        <v>2.1</v>
+        <v>2.25</v>
       </c>
       <c r="AH87" t="inlineStr">
         <is>
@@ -14560,10 +14560,10 @@
         </is>
       </c>
       <c r="AJ87">
-        <v>2.1</v>
+        <v>2.17</v>
       </c>
       <c r="AK87">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AL87">
         <v>0</v>
@@ -14653,31 +14653,31 @@
         </is>
       </c>
       <c r="N88">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="O88">
-        <v>4.8</v>
+        <v>4.6</v>
       </c>
       <c r="P88">
-        <v>7.75</v>
+        <v>7</v>
       </c>
       <c r="Q88">
         <v>1.8</v>
       </c>
       <c r="R88">
-        <v>2.4</v>
+        <v>2.25</v>
       </c>
       <c r="S88">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="T88">
-        <v>3</v>
+        <v>2.8</v>
       </c>
       <c r="U88">
         <v>2.62</v>
       </c>
       <c r="V88">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="W88">
         <v>1.1</v>
@@ -14686,31 +14686,31 @@
         <v>1.02</v>
       </c>
       <c r="Y88">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="Z88">
         <v>3.5</v>
       </c>
       <c r="AA88">
+        <v>1.89</v>
+      </c>
+      <c r="AB88">
         <v>1.85</v>
       </c>
-      <c r="AB88">
-        <v>1.95</v>
-      </c>
       <c r="AC88">
-        <v>2.9</v>
+        <v>3.1</v>
       </c>
       <c r="AD88">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AE88">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="AF88">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="AG88">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
       <c r="AH88" t="inlineStr">
         <is>
@@ -14723,10 +14723,10 @@
         </is>
       </c>
       <c r="AJ88">
-        <v>1.16</v>
+        <v>1.01</v>
       </c>
       <c r="AK88">
-        <v>3.12</v>
+        <v>2.91</v>
       </c>
       <c r="AL88">
         <v>0</v>
@@ -14816,64 +14816,64 @@
         </is>
       </c>
       <c r="N89">
-        <v>2.02</v>
+        <v>1.71</v>
       </c>
       <c r="O89">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="P89">
-        <v>2.95</v>
+        <v>3.8</v>
       </c>
       <c r="Q89">
-        <v>2.6</v>
+        <v>2.3</v>
       </c>
       <c r="R89">
         <v>2.25</v>
       </c>
       <c r="S89">
-        <v>1.28</v>
+        <v>1.32</v>
       </c>
       <c r="T89">
-        <v>3.2</v>
+        <v>2.96</v>
       </c>
       <c r="U89">
-        <v>2.38</v>
+        <v>2.63</v>
       </c>
       <c r="V89">
-        <v>1.55</v>
+        <v>1.41</v>
       </c>
       <c r="W89">
+        <v>1.11</v>
+      </c>
+      <c r="X89">
+        <v>1.04</v>
+      </c>
+      <c r="Y89">
+        <v>1.19</v>
+      </c>
+      <c r="Z89">
+        <v>3.74</v>
+      </c>
+      <c r="AA89">
+        <v>1.75</v>
+      </c>
+      <c r="AB89">
+        <v>1.96</v>
+      </c>
+      <c r="AC89">
+        <v>2.83</v>
+      </c>
+      <c r="AD89">
+        <v>1.36</v>
+      </c>
+      <c r="AE89">
         <v>1.13</v>
       </c>
-      <c r="X89">
-        <v>1.02</v>
-      </c>
-      <c r="Y89">
-        <v>1.15</v>
-      </c>
-      <c r="Z89">
-        <v>4.25</v>
-      </c>
-      <c r="AA89">
-        <v>1.63</v>
-      </c>
-      <c r="AB89">
-        <v>2.14</v>
-      </c>
-      <c r="AC89">
-        <v>2.52</v>
-      </c>
-      <c r="AD89">
-        <v>1.48</v>
-      </c>
-      <c r="AE89">
-        <v>1.12</v>
-      </c>
       <c r="AF89">
-        <v>1.53</v>
+        <v>1.66</v>
       </c>
       <c r="AG89">
-        <v>2.28</v>
+        <v>2.07</v>
       </c>
       <c r="AH89" t="inlineStr">
         <is>
@@ -14886,10 +14886,10 @@
         </is>
       </c>
       <c r="AJ89">
-        <v>1.26</v>
+        <v>1.22</v>
       </c>
       <c r="AK89">
-        <v>1.6</v>
+        <v>1.83</v>
       </c>
       <c r="AL89">
         <v>0</v>
@@ -14982,7 +14982,7 @@
         <v>2.15</v>
       </c>
       <c r="O90">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="P90">
         <v>2.7</v>
@@ -14991,22 +14991,22 @@
         <v>2.6</v>
       </c>
       <c r="R90">
-        <v>2.45</v>
+        <v>2.25</v>
       </c>
       <c r="S90">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="T90">
-        <v>3.25</v>
+        <v>3.32</v>
       </c>
       <c r="U90">
-        <v>2.21</v>
+        <v>2.43</v>
       </c>
       <c r="V90">
-        <v>1.57</v>
+        <v>1.43</v>
       </c>
       <c r="W90">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="X90">
         <v>1.01</v>
@@ -15018,16 +15018,16 @@
         <v>4.5</v>
       </c>
       <c r="AA90">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="AB90">
         <v>2.38</v>
       </c>
       <c r="AC90">
-        <v>2.3</v>
+        <v>2.33</v>
       </c>
       <c r="AD90">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="AE90">
         <v>1.16</v>
@@ -15148,7 +15148,7 @@
         <v>3.5</v>
       </c>
       <c r="P91">
-        <v>2.03</v>
+        <v>2.02</v>
       </c>
       <c r="Q91">
         <v>3.93</v>
@@ -15160,10 +15160,10 @@
         <v>1.34</v>
       </c>
       <c r="T91">
-        <v>3.09</v>
+        <v>3.1</v>
       </c>
       <c r="U91">
-        <v>2.6</v>
+        <v>2.69</v>
       </c>
       <c r="V91">
         <v>1.4</v>
@@ -15193,7 +15193,7 @@
         <v>1.36</v>
       </c>
       <c r="AE91">
-        <v>1.09</v>
+        <v>1.07</v>
       </c>
       <c r="AF91">
         <v>1.68</v>
@@ -15215,7 +15215,7 @@
         <v>1.2</v>
       </c>
       <c r="AK91">
-        <v>1.18</v>
+        <v>1.24</v>
       </c>
       <c r="AL91">
         <v>0</v>
@@ -15471,10 +15471,10 @@
         <v>3.3</v>
       </c>
       <c r="O93">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="P93">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="Q93">
         <v>3.75</v>
@@ -15504,13 +15504,13 @@
         <v>1.21</v>
       </c>
       <c r="Z93">
-        <v>3.58</v>
+        <v>3.6</v>
       </c>
       <c r="AA93">
         <v>1.81</v>
       </c>
       <c r="AB93">
-        <v>1.84</v>
+        <v>1.95</v>
       </c>
       <c r="AC93">
         <v>3.3</v>
@@ -15538,10 +15538,10 @@
         </is>
       </c>
       <c r="AJ93">
-        <v>1.23</v>
+        <v>1.33</v>
       </c>
       <c r="AK93">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="AL93">
         <v>0</v>
@@ -15794,19 +15794,19 @@
         </is>
       </c>
       <c r="N95">
-        <v>1.81</v>
+        <v>1.84</v>
       </c>
       <c r="O95">
-        <v>3.54</v>
+        <v>3.6</v>
       </c>
       <c r="P95">
-        <v>4.3</v>
+        <v>4.1</v>
       </c>
       <c r="Q95">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="R95">
-        <v>2.15</v>
+        <v>2.18</v>
       </c>
       <c r="S95">
         <v>1.36</v>
@@ -15815,40 +15815,40 @@
         <v>2.88</v>
       </c>
       <c r="U95">
-        <v>2.96</v>
+        <v>2.88</v>
       </c>
       <c r="V95">
         <v>1.36</v>
       </c>
       <c r="W95">
+        <v>1.06</v>
+      </c>
+      <c r="X95">
         <v>1.05</v>
       </c>
-      <c r="X95">
-        <v>1.06</v>
-      </c>
       <c r="Y95">
+        <v>1.23</v>
+      </c>
+      <c r="Z95">
+        <v>3.05</v>
+      </c>
+      <c r="AA95">
+        <v>1.96</v>
+      </c>
+      <c r="AB95">
+        <v>1.88</v>
+      </c>
+      <c r="AC95">
+        <v>3.25</v>
+      </c>
+      <c r="AD95">
         <v>1.3</v>
       </c>
-      <c r="Z95">
-        <v>3.12</v>
-      </c>
-      <c r="AA95">
-        <v>2.01</v>
-      </c>
-      <c r="AB95">
-        <v>1.83</v>
-      </c>
-      <c r="AC95">
-        <v>3.6</v>
-      </c>
-      <c r="AD95">
-        <v>1.28</v>
-      </c>
       <c r="AE95">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="AF95">
-        <v>1.84</v>
+        <v>1.75</v>
       </c>
       <c r="AG95">
         <v>1.85</v>
@@ -15864,10 +15864,10 @@
         </is>
       </c>
       <c r="AJ95">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="AK95">
-        <v>1.95</v>
+        <v>1.98</v>
       </c>
       <c r="AL95">
         <v>0</v>
@@ -15957,64 +15957,64 @@
         </is>
       </c>
       <c r="N96">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="O96">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="P96">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="Q96">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="R96">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="S96">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="T96">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="U96">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="V96">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="W96">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X96">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y96">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="Z96">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="AA96">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AB96">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AC96">
-        <v>0</v>
+        <v>3.98</v>
       </c>
       <c r="AD96">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AE96">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF96">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AG96">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AH96" t="inlineStr">
         <is>
@@ -16027,10 +16027,10 @@
         </is>
       </c>
       <c r="AJ96">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AK96">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="AL96">
         <v>0</v>
@@ -16283,13 +16283,13 @@
         </is>
       </c>
       <c r="N98">
-        <v>1.79</v>
+        <v>1.95</v>
       </c>
       <c r="O98">
         <v>3.8</v>
       </c>
       <c r="P98">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="Q98">
         <v>2.2</v>
@@ -16304,10 +16304,10 @@
         <v>3.7</v>
       </c>
       <c r="U98">
-        <v>2.17</v>
+        <v>2.2</v>
       </c>
       <c r="V98">
-        <v>1.58</v>
+        <v>1.63</v>
       </c>
       <c r="W98">
         <v>1.17</v>
@@ -16316,7 +16316,7 @@
         <v>1.02</v>
       </c>
       <c r="Y98">
-        <v>1.15</v>
+        <v>1.11</v>
       </c>
       <c r="Z98">
         <v>5.25</v>
@@ -16325,16 +16325,16 @@
         <v>1.5</v>
       </c>
       <c r="AB98">
-        <v>2.55</v>
+        <v>2.63</v>
       </c>
       <c r="AC98">
         <v>2.22</v>
       </c>
       <c r="AD98">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="AE98">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AF98">
         <v>1.4</v>
@@ -16356,7 +16356,7 @@
         <v>1.25</v>
       </c>
       <c r="AK98">
-        <v>1.95</v>
+        <v>1.88</v>
       </c>
       <c r="AL98">
         <v>0</v>
@@ -16461,16 +16461,16 @@
         <v>2.14</v>
       </c>
       <c r="S99">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="T99">
-        <v>3.2</v>
+        <v>2.91</v>
       </c>
       <c r="U99">
-        <v>2.39</v>
+        <v>2.57</v>
       </c>
       <c r="V99">
-        <v>1.44</v>
+        <v>1.47</v>
       </c>
       <c r="W99">
         <v>1.11</v>
@@ -16479,16 +16479,16 @@
         <v>1</v>
       </c>
       <c r="Y99">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="Z99">
         <v>3.78</v>
       </c>
       <c r="AA99">
-        <v>1.69</v>
+        <v>1.73</v>
       </c>
       <c r="AB99">
-        <v>2.08</v>
+        <v>2.09</v>
       </c>
       <c r="AC99">
         <v>2.59</v>
@@ -16497,10 +16497,10 @@
         <v>1.39</v>
       </c>
       <c r="AE99">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="AF99">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="AG99">
         <v>2.25</v>
@@ -16519,7 +16519,7 @@
         <v>1.26</v>
       </c>
       <c r="AK99">
-        <v>1.46</v>
+        <v>1.5</v>
       </c>
       <c r="AL99">
         <v>0</v>
@@ -16612,7 +16612,7 @@
         <v>4</v>
       </c>
       <c r="O100">
-        <v>3.58</v>
+        <v>3.6</v>
       </c>
       <c r="P100">
         <v>1.88</v>
@@ -16621,7 +16621,7 @@
         <v>4.59</v>
       </c>
       <c r="R100">
-        <v>2.09</v>
+        <v>2.15</v>
       </c>
       <c r="S100">
         <v>1.36</v>
@@ -16633,7 +16633,7 @@
         <v>2.77</v>
       </c>
       <c r="V100">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="W100">
         <v>1.07</v>
@@ -16642,25 +16642,25 @@
         <v>1.01</v>
       </c>
       <c r="Y100">
-        <v>1.29</v>
+        <v>1.26</v>
       </c>
       <c r="Z100">
-        <v>3.42</v>
+        <v>3.36</v>
       </c>
       <c r="AA100">
         <v>1.97</v>
       </c>
       <c r="AB100">
-        <v>1.93</v>
+        <v>1.97</v>
       </c>
       <c r="AC100">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="AD100">
-        <v>1.32</v>
+        <v>1.34</v>
       </c>
       <c r="AE100">
-        <v>1.12</v>
+        <v>1.08</v>
       </c>
       <c r="AF100">
         <v>1.76</v>
@@ -16679,7 +16679,7 @@
         </is>
       </c>
       <c r="AJ100">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="AK100">
         <v>1.18</v>
@@ -16775,13 +16775,13 @@
         <v>1.53</v>
       </c>
       <c r="O101">
-        <v>4.15</v>
+        <v>3.85</v>
       </c>
       <c r="P101">
         <v>5.33</v>
       </c>
       <c r="Q101">
-        <v>1.95</v>
+        <v>2.07</v>
       </c>
       <c r="R101">
         <v>2.34</v>
@@ -16808,7 +16808,7 @@
         <v>1.2</v>
       </c>
       <c r="Z101">
-        <v>5</v>
+        <v>4.35</v>
       </c>
       <c r="AA101">
         <v>1.63</v>
@@ -16826,10 +16826,10 @@
         <v>1.17</v>
       </c>
       <c r="AF101">
-        <v>1.73</v>
+        <v>1.65</v>
       </c>
       <c r="AG101">
-        <v>1.92</v>
+        <v>2.1</v>
       </c>
       <c r="AH101" t="inlineStr">
         <is>
@@ -16935,19 +16935,19 @@
         </is>
       </c>
       <c r="N102">
-        <v>3.4</v>
+        <v>3.13</v>
       </c>
       <c r="O102">
         <v>3.15</v>
       </c>
       <c r="P102">
-        <v>1.97</v>
+        <v>2.05</v>
       </c>
       <c r="Q102">
-        <v>3.75</v>
+        <v>3.6</v>
       </c>
       <c r="R102">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="S102">
         <v>1.4</v>
@@ -16956,16 +16956,16 @@
         <v>2.56</v>
       </c>
       <c r="U102">
-        <v>2.88</v>
+        <v>3</v>
       </c>
       <c r="V102">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="W102">
         <v>1.05</v>
       </c>
       <c r="X102">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="Y102">
         <v>1.25</v>
@@ -16974,25 +16974,25 @@
         <v>2.45</v>
       </c>
       <c r="AA102">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="AB102">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="AC102">
         <v>3.8</v>
       </c>
       <c r="AD102">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AE102">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="AF102">
-        <v>1.67</v>
+        <v>1.8</v>
       </c>
       <c r="AG102">
-        <v>1.67</v>
+        <v>1.89</v>
       </c>
       <c r="AH102" t="inlineStr">
         <is>
@@ -17098,64 +17098,64 @@
         </is>
       </c>
       <c r="N103">
-        <v>1.62</v>
+        <v>1.54</v>
       </c>
       <c r="O103">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="P103">
-        <v>4.2</v>
+        <v>4.8</v>
       </c>
       <c r="Q103">
-        <v>2.1</v>
+        <v>2.01</v>
       </c>
       <c r="R103">
-        <v>2.3</v>
+        <v>2.39</v>
       </c>
       <c r="S103">
-        <v>1.29</v>
+        <v>1.32</v>
       </c>
       <c r="T103">
         <v>2.63</v>
       </c>
       <c r="U103">
-        <v>2.38</v>
+        <v>2.39</v>
       </c>
       <c r="V103">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
       <c r="W103">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="X103">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y103">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="Z103">
-        <v>3.95</v>
+        <v>4.33</v>
       </c>
       <c r="AA103">
-        <v>1.66</v>
+        <v>1.71</v>
       </c>
       <c r="AB103">
-        <v>1.79</v>
+        <v>2.05</v>
       </c>
       <c r="AC103">
         <v>2.88</v>
       </c>
       <c r="AD103">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="AE103">
         <v>1.14</v>
       </c>
       <c r="AF103">
-        <v>1.55</v>
+        <v>1.7</v>
       </c>
       <c r="AG103">
-        <v>2</v>
+        <v>2.01</v>
       </c>
       <c r="AH103" t="inlineStr">
         <is>
@@ -17168,10 +17168,10 @@
         </is>
       </c>
       <c r="AJ103">
-        <v>1.16</v>
+        <v>1.14</v>
       </c>
       <c r="AK103">
-        <v>2.16</v>
+        <v>2.31</v>
       </c>
       <c r="AL103">
         <v>0</v>
@@ -17264,10 +17264,10 @@
         <v>2.4</v>
       </c>
       <c r="O104">
-        <v>2.7</v>
+        <v>2.75</v>
       </c>
       <c r="P104">
-        <v>3.05</v>
+        <v>2.9</v>
       </c>
       <c r="Q104">
         <v>0</v>
@@ -17424,61 +17424,61 @@
         </is>
       </c>
       <c r="N105">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="O105">
-        <v>2.5</v>
+        <v>2.55</v>
       </c>
       <c r="P105">
-        <v>3.5</v>
+        <v>3.32</v>
       </c>
       <c r="Q105">
-        <v>3.1</v>
+        <v>3.21</v>
       </c>
       <c r="R105">
-        <v>1.6</v>
+        <v>1.64</v>
       </c>
       <c r="S105">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="T105">
-        <v>2.1</v>
+        <v>1.92</v>
       </c>
       <c r="U105">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="V105">
-        <v>1.12</v>
+        <v>1.17</v>
       </c>
       <c r="W105">
         <v>1.02</v>
       </c>
       <c r="X105">
-        <v>1.18</v>
+        <v>1.15</v>
       </c>
       <c r="Y105">
-        <v>1.77</v>
+        <v>1.7</v>
       </c>
       <c r="Z105">
-        <v>1.94</v>
+        <v>2</v>
       </c>
       <c r="AA105">
-        <v>3.57</v>
+        <v>3.6</v>
       </c>
       <c r="AB105">
         <v>1.24</v>
       </c>
       <c r="AC105">
-        <v>7.3</v>
+        <v>7.4</v>
       </c>
       <c r="AD105">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="AE105">
         <v>1.01</v>
       </c>
       <c r="AF105">
-        <v>2.5</v>
+        <v>2.57</v>
       </c>
       <c r="AG105">
         <v>1.44</v>
@@ -17494,7 +17494,7 @@
         </is>
       </c>
       <c r="AJ105">
-        <v>1.44</v>
+        <v>1.22</v>
       </c>
       <c r="AK105">
         <v>1.57</v>
@@ -17587,16 +17587,16 @@
         </is>
       </c>
       <c r="N106">
-        <v>2.25</v>
+        <v>2.17</v>
       </c>
       <c r="O106">
-        <v>2.7</v>
+        <v>2.75</v>
       </c>
       <c r="P106">
         <v>3.3</v>
       </c>
       <c r="Q106">
-        <v>3.05</v>
+        <v>2.96</v>
       </c>
       <c r="R106">
         <v>1.76</v>
@@ -17605,13 +17605,13 @@
         <v>1.64</v>
       </c>
       <c r="T106">
-        <v>2.2</v>
+        <v>2.23</v>
       </c>
       <c r="U106">
         <v>3.75</v>
       </c>
       <c r="V106">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="W106">
         <v>1.03</v>
@@ -17620,22 +17620,22 @@
         <v>1.09</v>
       </c>
       <c r="Y106">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="Z106">
-        <v>2.17</v>
+        <v>2.19</v>
       </c>
       <c r="AA106">
         <v>2.74</v>
       </c>
       <c r="AB106">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="AC106">
-        <v>6.1</v>
+        <v>5.5</v>
       </c>
       <c r="AD106">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="AE106">
         <v>1.03</v>
@@ -17750,25 +17750,25 @@
         </is>
       </c>
       <c r="N107">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="O107">
-        <v>2.65</v>
+        <v>2.85</v>
       </c>
       <c r="P107">
-        <v>3.4</v>
+        <v>3.44</v>
       </c>
       <c r="Q107">
-        <v>2.94</v>
+        <v>3.1</v>
       </c>
       <c r="R107">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
       <c r="S107">
-        <v>1.58</v>
+        <v>1.62</v>
       </c>
       <c r="T107">
-        <v>2.04</v>
+        <v>2.05</v>
       </c>
       <c r="U107">
         <v>4.5</v>
@@ -17777,28 +17777,28 @@
         <v>1.17</v>
       </c>
       <c r="W107">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="X107">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="Y107">
-        <v>1.67</v>
+        <v>1.79</v>
       </c>
       <c r="Z107">
-        <v>2.15</v>
+        <v>2.02</v>
       </c>
       <c r="AA107">
         <v>3.2</v>
       </c>
       <c r="AB107">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="AC107">
-        <v>6.5</v>
+        <v>7</v>
       </c>
       <c r="AD107">
-        <v>1.1</v>
+        <v>1.05</v>
       </c>
       <c r="AE107">
         <v>1.02</v>
@@ -17807,7 +17807,7 @@
         <v>2.5</v>
       </c>
       <c r="AG107">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="AH107" t="inlineStr">
         <is>
@@ -17820,10 +17820,10 @@
         </is>
       </c>
       <c r="AJ107">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="AK107">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="AL107">
         <v>0</v>
@@ -17916,46 +17916,46 @@
         <v>2.25</v>
       </c>
       <c r="O108">
-        <v>3.3</v>
+        <v>3.34</v>
       </c>
       <c r="P108">
-        <v>2.95</v>
+        <v>2.8</v>
       </c>
       <c r="Q108">
-        <v>2.81</v>
+        <v>2.66</v>
       </c>
       <c r="R108">
         <v>2.09</v>
       </c>
       <c r="S108">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="T108">
-        <v>2.88</v>
+        <v>2.7</v>
       </c>
       <c r="U108">
-        <v>2.84</v>
+        <v>2.87</v>
       </c>
       <c r="V108">
         <v>1.36</v>
       </c>
       <c r="W108">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="X108">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y108">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="Z108">
-        <v>3.51</v>
+        <v>3.52</v>
       </c>
       <c r="AA108">
-        <v>1.95</v>
+        <v>1.99</v>
       </c>
       <c r="AB108">
-        <v>1.89</v>
+        <v>1.83</v>
       </c>
       <c r="AC108">
         <v>3.35</v>
@@ -17967,7 +17967,7 @@
         <v>1.08</v>
       </c>
       <c r="AF108">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="AG108">
         <v>2.1</v>
@@ -17983,10 +17983,10 @@
         </is>
       </c>
       <c r="AJ108">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="AK108">
-        <v>1.49</v>
+        <v>1.57</v>
       </c>
       <c r="AL108">
         <v>0</v>
@@ -18079,34 +18079,34 @@
         <v>1.28</v>
       </c>
       <c r="O109">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="P109">
-        <v>7.1</v>
+        <v>7.5</v>
       </c>
       <c r="Q109">
-        <v>1.75</v>
+        <v>1.69</v>
       </c>
       <c r="R109">
-        <v>2.4</v>
+        <v>2.43</v>
       </c>
       <c r="S109">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="T109">
-        <v>3.2</v>
+        <v>3.08</v>
       </c>
       <c r="U109">
-        <v>2.47</v>
+        <v>2.44</v>
       </c>
       <c r="V109">
-        <v>1.44</v>
+        <v>1.55</v>
       </c>
       <c r="W109">
-        <v>1.11</v>
+        <v>1.06</v>
       </c>
       <c r="X109">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y109">
         <v>1.22</v>
@@ -18115,25 +18115,25 @@
         <v>4</v>
       </c>
       <c r="AA109">
-        <v>1.68</v>
+        <v>1.66</v>
       </c>
       <c r="AB109">
-        <v>2.08</v>
+        <v>2.11</v>
       </c>
       <c r="AC109">
-        <v>2.66</v>
+        <v>2.56</v>
       </c>
       <c r="AD109">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="AE109">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="AF109">
-        <v>2.09</v>
+        <v>1.85</v>
       </c>
       <c r="AG109">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="AH109" t="inlineStr">
         <is>
@@ -18146,10 +18146,10 @@
         </is>
       </c>
       <c r="AJ109">
-        <v>1.13</v>
+        <v>1.17</v>
       </c>
       <c r="AK109">
-        <v>3</v>
+        <v>2.92</v>
       </c>
       <c r="AL109">
         <v>0</v>
@@ -18239,64 +18239,64 @@
         </is>
       </c>
       <c r="N110">
-        <v>1.54</v>
+        <v>1.68</v>
       </c>
       <c r="O110">
-        <v>3.5</v>
+        <v>3.25</v>
       </c>
       <c r="P110">
-        <v>5.5</v>
+        <v>4.65</v>
       </c>
       <c r="Q110">
+        <v>2.32</v>
+      </c>
+      <c r="R110">
+        <v>1.95</v>
+      </c>
+      <c r="S110">
+        <v>1.4</v>
+      </c>
+      <c r="T110">
+        <v>2.44</v>
+      </c>
+      <c r="U110">
+        <v>2.9</v>
+      </c>
+      <c r="V110">
+        <v>1.29</v>
+      </c>
+      <c r="W110">
+        <v>1.05</v>
+      </c>
+      <c r="X110">
+        <v>1.05</v>
+      </c>
+      <c r="Y110">
+        <v>1.37</v>
+      </c>
+      <c r="Z110">
+        <v>2.91</v>
+      </c>
+      <c r="AA110">
         <v>2.15</v>
       </c>
-      <c r="R110">
+      <c r="AB110">
+        <v>1.62</v>
+      </c>
+      <c r="AC110">
+        <v>3.78</v>
+      </c>
+      <c r="AD110">
+        <v>1.19</v>
+      </c>
+      <c r="AE110">
+        <v>1.05</v>
+      </c>
+      <c r="AF110">
         <v>2.01</v>
       </c>
-      <c r="S110">
-        <v>1.43</v>
-      </c>
-      <c r="T110">
-        <v>2.5</v>
-      </c>
-      <c r="U110">
-        <v>2.97</v>
-      </c>
-      <c r="V110">
-        <v>1.31</v>
-      </c>
-      <c r="W110">
-        <v>1.04</v>
-      </c>
-      <c r="X110">
-        <v>1.03</v>
-      </c>
-      <c r="Y110">
-        <v>1.32</v>
-      </c>
-      <c r="Z110">
-        <v>2.88</v>
-      </c>
-      <c r="AA110">
-        <v>2.1</v>
-      </c>
-      <c r="AB110">
-        <v>1.7</v>
-      </c>
-      <c r="AC110">
-        <v>3.58</v>
-      </c>
-      <c r="AD110">
-        <v>1.21</v>
-      </c>
-      <c r="AE110">
-        <v>1.04</v>
-      </c>
-      <c r="AF110">
-        <v>2.06</v>
-      </c>
       <c r="AG110">
-        <v>1.65</v>
+        <v>1.68</v>
       </c>
       <c r="AH110" t="inlineStr">
         <is>
@@ -18309,10 +18309,10 @@
         </is>
       </c>
       <c r="AJ110">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="AK110">
-        <v>2.19</v>
+        <v>2</v>
       </c>
       <c r="AL110">
         <v>0</v>
@@ -18402,7 +18402,7 @@
         </is>
       </c>
       <c r="N111">
-        <v>4.24</v>
+        <v>4.6</v>
       </c>
       <c r="O111">
         <v>3</v>
@@ -18411,52 +18411,52 @@
         <v>1.75</v>
       </c>
       <c r="Q111">
-        <v>5.77</v>
+        <v>5</v>
       </c>
       <c r="R111">
-        <v>1.86</v>
+        <v>1.91</v>
       </c>
       <c r="S111">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="T111">
-        <v>2.31</v>
+        <v>2.4</v>
       </c>
       <c r="U111">
         <v>3.48</v>
       </c>
       <c r="V111">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="W111">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X111">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="Y111">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="Z111">
         <v>2.6</v>
       </c>
       <c r="AA111">
-        <v>2.37</v>
+        <v>2.4</v>
       </c>
       <c r="AB111">
-        <v>1.53</v>
+        <v>1.49</v>
       </c>
       <c r="AC111">
-        <v>4.7</v>
+        <v>5.2</v>
       </c>
       <c r="AD111">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="AE111">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="AF111">
-        <v>2.16</v>
+        <v>2.2</v>
       </c>
       <c r="AG111">
         <v>1.59</v>
@@ -18472,10 +18472,10 @@
         </is>
       </c>
       <c r="AJ111">
-        <v>1.27</v>
+        <v>1.84</v>
       </c>
       <c r="AK111">
-        <v>1.12</v>
+        <v>1.17</v>
       </c>
       <c r="AL111">
         <v>0</v>
@@ -18604,10 +18604,10 @@
         <v>3.28</v>
       </c>
       <c r="AA112">
-        <v>1.95</v>
+        <v>1.89</v>
       </c>
       <c r="AB112">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="AC112">
         <v>3.2</v>
@@ -18635,7 +18635,7 @@
         </is>
       </c>
       <c r="AJ112">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AK112">
         <v>1.61</v>
@@ -18728,80 +18728,80 @@
         </is>
       </c>
       <c r="N113">
-        <v>3.5</v>
+        <v>4.05</v>
       </c>
       <c r="O113">
-        <v>3.45</v>
+        <v>3.65</v>
       </c>
       <c r="P113">
         <v>1.78</v>
       </c>
       <c r="Q113">
-        <v>4.93</v>
+        <v>4.6</v>
       </c>
       <c r="R113">
-        <v>2.18</v>
+        <v>2.17</v>
       </c>
       <c r="S113">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="T113">
         <v>2.82</v>
       </c>
       <c r="U113">
-        <v>2.63</v>
+        <v>2.7</v>
       </c>
       <c r="V113">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="W113">
         <v>1.1</v>
       </c>
       <c r="X113">
-        <v>1.04</v>
+        <v>1</v>
       </c>
       <c r="Y113">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="Z113">
-        <v>3.76</v>
+        <v>3.58</v>
       </c>
       <c r="AA113">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="AB113">
+        <v>1.93</v>
+      </c>
+      <c r="AC113">
+        <v>2.99</v>
+      </c>
+      <c r="AD113">
+        <v>1.37</v>
+      </c>
+      <c r="AE113">
+        <v>1.09</v>
+      </c>
+      <c r="AF113">
+        <v>1.7</v>
+      </c>
+      <c r="AG113">
+        <v>1.95</v>
+      </c>
+      <c r="AH113" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI113" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ113">
         <v>2</v>
       </c>
-      <c r="AC113">
-        <v>3.1</v>
-      </c>
-      <c r="AD113">
-        <v>1.36</v>
-      </c>
-      <c r="AE113">
-        <v>1.1</v>
-      </c>
-      <c r="AF113">
-        <v>1.71</v>
-      </c>
-      <c r="AG113">
-        <v>2</v>
-      </c>
-      <c r="AH113" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI113" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ113">
-        <v>1.21</v>
-      </c>
       <c r="AK113">
-        <v>1.14</v>
+        <v>1.16</v>
       </c>
       <c r="AL113">
         <v>0</v>
@@ -18894,7 +18894,7 @@
         <v>1.61</v>
       </c>
       <c r="O114">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="P114">
         <v>4.4</v>
@@ -18903,31 +18903,31 @@
         <v>2.15</v>
       </c>
       <c r="R114">
-        <v>2.24</v>
+        <v>2.23</v>
       </c>
       <c r="S114">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="T114">
-        <v>3.28</v>
+        <v>3.08</v>
       </c>
       <c r="U114">
         <v>2.5</v>
       </c>
       <c r="V114">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="W114">
         <v>1.1</v>
       </c>
       <c r="X114">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y114">
         <v>1.22</v>
       </c>
       <c r="Z114">
-        <v>4.5</v>
+        <v>3.92</v>
       </c>
       <c r="AA114">
         <v>1.72</v>
@@ -18939,7 +18939,7 @@
         <v>2.7</v>
       </c>
       <c r="AD114">
-        <v>1.44</v>
+        <v>1.41</v>
       </c>
       <c r="AE114">
         <v>1.1</v>
@@ -18964,7 +18964,7 @@
         <v>1.18</v>
       </c>
       <c r="AK114">
-        <v>2.14</v>
+        <v>2.1</v>
       </c>
       <c r="AL114">
         <v>0</v>
@@ -19057,28 +19057,28 @@
         <v>1.8</v>
       </c>
       <c r="O115">
-        <v>3.52</v>
+        <v>3.54</v>
       </c>
       <c r="P115">
-        <v>3.8</v>
+        <v>3.78</v>
       </c>
       <c r="Q115">
         <v>2.43</v>
       </c>
       <c r="R115">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="S115">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="T115">
-        <v>2.9</v>
+        <v>2.95</v>
       </c>
       <c r="U115">
         <v>2.65</v>
       </c>
       <c r="V115">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="W115">
         <v>1.07</v>
@@ -19087,31 +19087,31 @@
         <v>1.04</v>
       </c>
       <c r="Y115">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="Z115">
-        <v>4.1</v>
+        <v>4.03</v>
       </c>
       <c r="AA115">
-        <v>1.8</v>
+        <v>1.78</v>
       </c>
       <c r="AB115">
         <v>1.97</v>
       </c>
       <c r="AC115">
-        <v>3.1</v>
+        <v>2.95</v>
       </c>
       <c r="AD115">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AE115">
         <v>1.1</v>
       </c>
       <c r="AF115">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="AG115">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="AH115" t="inlineStr">
         <is>
@@ -19217,16 +19217,16 @@
         </is>
       </c>
       <c r="N116">
-        <v>1.43</v>
+        <v>1.48</v>
       </c>
       <c r="O116">
-        <v>4.4</v>
+        <v>4.2</v>
       </c>
       <c r="P116">
-        <v>5.75</v>
+        <v>5.25</v>
       </c>
       <c r="Q116">
-        <v>1.96</v>
+        <v>1.94</v>
       </c>
       <c r="R116">
         <v>2.35</v>
@@ -19235,7 +19235,7 @@
         <v>1.25</v>
       </c>
       <c r="T116">
-        <v>3.25</v>
+        <v>3.32</v>
       </c>
       <c r="U116">
         <v>2.25</v>
@@ -19250,25 +19250,25 @@
         <v>1.03</v>
       </c>
       <c r="Y116">
-        <v>1.13</v>
+        <v>1.18</v>
       </c>
       <c r="Z116">
         <v>4.5</v>
       </c>
       <c r="AA116">
-        <v>1.58</v>
+        <v>1.6</v>
       </c>
       <c r="AB116">
         <v>2.23</v>
       </c>
       <c r="AC116">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="AD116">
         <v>1.45</v>
       </c>
       <c r="AE116">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="AF116">
         <v>1.7</v>
@@ -19380,22 +19380,22 @@
         </is>
       </c>
       <c r="N117">
-        <v>1.24</v>
+        <v>1.26</v>
       </c>
       <c r="O117">
-        <v>5.25</v>
+        <v>4.8</v>
       </c>
       <c r="P117">
-        <v>9.5</v>
+        <v>9.75</v>
       </c>
       <c r="Q117">
-        <v>1.58</v>
+        <v>1.72</v>
       </c>
       <c r="R117">
         <v>2.5</v>
       </c>
       <c r="S117">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="T117">
         <v>3.1</v>
@@ -19404,13 +19404,13 @@
         <v>2.62</v>
       </c>
       <c r="V117">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="W117">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="X117">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y117">
         <v>1.22</v>
@@ -19419,25 +19419,25 @@
         <v>4.1</v>
       </c>
       <c r="AA117">
-        <v>1.8</v>
+        <v>1.72</v>
       </c>
       <c r="AB117">
-        <v>1.94</v>
+        <v>1.93</v>
       </c>
       <c r="AC117">
-        <v>3.1</v>
+        <v>3.12</v>
       </c>
       <c r="AD117">
         <v>1.33</v>
       </c>
       <c r="AE117">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="AF117">
-        <v>2.49</v>
+        <v>2.43</v>
       </c>
       <c r="AG117">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="AH117" t="inlineStr">
         <is>
@@ -19450,10 +19450,10 @@
         </is>
       </c>
       <c r="AJ117">
-        <v>1.01</v>
+        <v>1.14</v>
       </c>
       <c r="AK117">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="AL117">
         <v>0</v>
@@ -19543,31 +19543,31 @@
         </is>
       </c>
       <c r="N118">
+        <v>2.58</v>
+      </c>
+      <c r="O118">
+        <v>2.88</v>
+      </c>
+      <c r="P118">
         <v>2.6</v>
       </c>
-      <c r="O118">
-        <v>2.87</v>
-      </c>
-      <c r="P118">
-        <v>2.59</v>
-      </c>
       <c r="Q118">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="R118">
-        <v>1.85</v>
+        <v>1.9</v>
       </c>
       <c r="S118">
-        <v>1.55</v>
+        <v>1.58</v>
       </c>
       <c r="T118">
-        <v>2.25</v>
+        <v>2.33</v>
       </c>
       <c r="U118">
-        <v>3.45</v>
+        <v>3.58</v>
       </c>
       <c r="V118">
-        <v>1.25</v>
+        <v>1.21</v>
       </c>
       <c r="W118">
         <v>1.04</v>
@@ -19576,13 +19576,13 @@
         <v>1.07</v>
       </c>
       <c r="Y118">
-        <v>1.53</v>
+        <v>1.47</v>
       </c>
       <c r="Z118">
-        <v>2.45</v>
+        <v>2.39</v>
       </c>
       <c r="AA118">
-        <v>2.7</v>
+        <v>2.74</v>
       </c>
       <c r="AB118">
         <v>1.41</v>
@@ -19613,7 +19613,7 @@
         </is>
       </c>
       <c r="AJ118">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="AK118">
         <v>1.42</v>
@@ -19706,22 +19706,22 @@
         </is>
       </c>
       <c r="N119">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="O119">
         <v>2.8</v>
       </c>
       <c r="P119">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="Q119">
-        <v>2.85</v>
+        <v>2.88</v>
       </c>
       <c r="R119">
         <v>1.83</v>
       </c>
       <c r="S119">
-        <v>1.58</v>
+        <v>1.72</v>
       </c>
       <c r="T119">
         <v>2.16</v>
@@ -19736,34 +19736,34 @@
         <v>1.03</v>
       </c>
       <c r="X119">
-        <v>1.1</v>
+        <v>1.16</v>
       </c>
       <c r="Y119">
-        <v>1.62</v>
+        <v>1.7</v>
       </c>
       <c r="Z119">
         <v>2.08</v>
       </c>
       <c r="AA119">
-        <v>3.2</v>
+        <v>3.22</v>
       </c>
       <c r="AB119">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="AC119">
-        <v>6.5</v>
+        <v>6.39</v>
       </c>
       <c r="AD119">
         <v>1.1</v>
       </c>
       <c r="AE119">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="AF119">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="AG119">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="AH119" t="inlineStr">
         <is>
@@ -19869,34 +19869,34 @@
         </is>
       </c>
       <c r="N120">
-        <v>1.95</v>
+        <v>2.16</v>
       </c>
       <c r="O120">
-        <v>3.25</v>
+        <v>3.05</v>
       </c>
       <c r="P120">
         <v>3.4</v>
       </c>
       <c r="Q120">
-        <v>2.67</v>
+        <v>2.6</v>
       </c>
       <c r="R120">
-        <v>2.03</v>
+        <v>2.15</v>
       </c>
       <c r="S120">
         <v>1.4</v>
       </c>
       <c r="T120">
-        <v>2.57</v>
+        <v>2.56</v>
       </c>
       <c r="U120">
-        <v>2.75</v>
+        <v>2.95</v>
       </c>
       <c r="V120">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="W120">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="X120">
         <v>1.05</v>
@@ -19905,22 +19905,22 @@
         <v>1.33</v>
       </c>
       <c r="Z120">
-        <v>3.25</v>
+        <v>3.24</v>
       </c>
       <c r="AA120">
-        <v>2.04</v>
+        <v>1.98</v>
       </c>
       <c r="AB120">
-        <v>1.74</v>
+        <v>1.71</v>
       </c>
       <c r="AC120">
-        <v>3.45</v>
+        <v>3.34</v>
       </c>
       <c r="AD120">
         <v>1.28</v>
       </c>
       <c r="AE120">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="AF120">
         <v>1.83</v>
@@ -19942,7 +19942,7 @@
         <v>1.28</v>
       </c>
       <c r="AK120">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="AL120">
         <v>0</v>
@@ -20032,10 +20032,10 @@
         </is>
       </c>
       <c r="N121">
-        <v>2.22</v>
+        <v>2.3</v>
       </c>
       <c r="O121">
-        <v>3.15</v>
+        <v>3.05</v>
       </c>
       <c r="P121">
         <v>2.8</v>
@@ -20065,22 +20065,22 @@
         <v>1.03</v>
       </c>
       <c r="Y121">
-        <v>1.35</v>
+        <v>1.42</v>
       </c>
       <c r="Z121">
-        <v>2.85</v>
+        <v>2.5</v>
       </c>
       <c r="AA121">
-        <v>2.15</v>
+        <v>2.3</v>
       </c>
       <c r="AB121">
-        <v>1.62</v>
+        <v>1.66</v>
       </c>
       <c r="AC121">
-        <v>3.9</v>
+        <v>3.82</v>
       </c>
       <c r="AD121">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="AE121">
         <v>1.03</v>
@@ -20195,34 +20195,34 @@
         </is>
       </c>
       <c r="N122">
-        <v>2.37</v>
+        <v>2.24</v>
       </c>
       <c r="O122">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="P122">
-        <v>2.5</v>
+        <v>2.65</v>
       </c>
       <c r="Q122">
-        <v>2.95</v>
+        <v>2.85</v>
       </c>
       <c r="R122">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="S122">
-        <v>1.32</v>
+        <v>1.35</v>
       </c>
       <c r="T122">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="U122">
-        <v>2.63</v>
+        <v>2.65</v>
       </c>
       <c r="V122">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="W122">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="X122">
         <v>1.03</v>
@@ -20234,10 +20234,10 @@
         <v>4.1</v>
       </c>
       <c r="AA122">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="AB122">
-        <v>1.96</v>
+        <v>1.93</v>
       </c>
       <c r="AC122">
         <v>3</v>
@@ -20246,7 +20246,7 @@
         <v>1.4</v>
       </c>
       <c r="AE122">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="AF122">
         <v>1.6</v>
@@ -20265,10 +20265,10 @@
         </is>
       </c>
       <c r="AJ122">
-        <v>1.38</v>
+        <v>1.26</v>
       </c>
       <c r="AK122">
-        <v>1.45</v>
+        <v>1.48</v>
       </c>
       <c r="AL122">
         <v>0</v>
@@ -20364,58 +20364,58 @@
         <v>4</v>
       </c>
       <c r="P123">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="Q123">
-        <v>2.01</v>
+        <v>2.05</v>
       </c>
       <c r="R123">
-        <v>2.34</v>
+        <v>2.35</v>
       </c>
       <c r="S123">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="T123">
-        <v>3.18</v>
+        <v>3.25</v>
       </c>
       <c r="U123">
-        <v>2.29</v>
+        <v>2.21</v>
       </c>
       <c r="V123">
-        <v>1.52</v>
+        <v>1.57</v>
       </c>
       <c r="W123">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="X123">
         <v>1.01</v>
       </c>
       <c r="Y123">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="Z123">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="AA123">
-        <v>1.58</v>
+        <v>1.53</v>
       </c>
       <c r="AB123">
-        <v>2.23</v>
+        <v>2.4</v>
       </c>
       <c r="AC123">
-        <v>2.35</v>
+        <v>2.3</v>
       </c>
       <c r="AD123">
-        <v>1.47</v>
+        <v>1.49</v>
       </c>
       <c r="AE123">
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
       <c r="AF123">
-        <v>1.66</v>
+        <v>1.62</v>
       </c>
       <c r="AG123">
-        <v>2.07</v>
+        <v>2.14</v>
       </c>
       <c r="AH123" t="inlineStr">
         <is>
@@ -20431,7 +20431,7 @@
         <v>1.16</v>
       </c>
       <c r="AK123">
-        <v>2.33</v>
+        <v>2.29</v>
       </c>
       <c r="AL123">
         <v>0</v>
@@ -20521,13 +20521,13 @@
         </is>
       </c>
       <c r="N124">
-        <v>1.86</v>
+        <v>1.97</v>
       </c>
       <c r="O124">
-        <v>2.8</v>
+        <v>2.9</v>
       </c>
       <c r="P124">
-        <v>4.2</v>
+        <v>4.6</v>
       </c>
       <c r="Q124">
         <v>2.77</v>
@@ -20539,7 +20539,7 @@
         <v>1.7</v>
       </c>
       <c r="T124">
-        <v>2.25</v>
+        <v>2.1</v>
       </c>
       <c r="U124">
         <v>4.1</v>
@@ -20569,7 +20569,7 @@
         <v>5.95</v>
       </c>
       <c r="AD124">
-        <v>1.1</v>
+        <v>1.07</v>
       </c>
       <c r="AE124">
         <v>1.02</v>
@@ -20578,7 +20578,7 @@
         <v>2.51</v>
       </c>
       <c r="AG124">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="AH124" t="inlineStr">
         <is>
@@ -20690,7 +20690,7 @@
         <v>2.64</v>
       </c>
       <c r="P125">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="Q125">
         <v>4.15</v>
@@ -20702,7 +20702,7 @@
         <v>1.57</v>
       </c>
       <c r="T125">
-        <v>2.25</v>
+        <v>2.18</v>
       </c>
       <c r="U125">
         <v>4</v>
@@ -20723,7 +20723,7 @@
         <v>2.15</v>
       </c>
       <c r="AA125">
-        <v>2.88</v>
+        <v>2.75</v>
       </c>
       <c r="AB125">
         <v>1.32</v>
@@ -20741,7 +20741,7 @@
         <v>2.32</v>
       </c>
       <c r="AG125">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="AH125" t="inlineStr">
         <is>
@@ -20757,7 +20757,7 @@
         <v>1.36</v>
       </c>
       <c r="AK125">
-        <v>1.38</v>
+        <v>1.31</v>
       </c>
       <c r="AL125">
         <v>0</v>
@@ -20847,19 +20847,19 @@
         </is>
       </c>
       <c r="N126">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="O126">
-        <v>6</v>
+        <v>5.55</v>
       </c>
       <c r="P126">
-        <v>11</v>
+        <v>10.02</v>
       </c>
       <c r="Q126">
-        <v>1.72</v>
+        <v>1.58</v>
       </c>
       <c r="R126">
-        <v>2.35</v>
+        <v>2.74</v>
       </c>
       <c r="S126">
         <v>1.25</v>
@@ -20868,40 +20868,40 @@
         <v>3.45</v>
       </c>
       <c r="U126">
-        <v>2.2</v>
+        <v>2.24</v>
       </c>
       <c r="V126">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="W126">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="X126">
         <v>1.03</v>
       </c>
       <c r="Y126">
+        <v>1.17</v>
+      </c>
+      <c r="Z126">
+        <v>5</v>
+      </c>
+      <c r="AA126">
+        <v>1.58</v>
+      </c>
+      <c r="AB126">
+        <v>2.29</v>
+      </c>
+      <c r="AC126">
+        <v>2.31</v>
+      </c>
+      <c r="AD126">
+        <v>1.54</v>
+      </c>
+      <c r="AE126">
         <v>1.18</v>
       </c>
-      <c r="Z126">
-        <v>4.5</v>
-      </c>
-      <c r="AA126">
-        <v>1.57</v>
-      </c>
-      <c r="AB126">
-        <v>2.3</v>
-      </c>
-      <c r="AC126">
-        <v>2.4</v>
-      </c>
-      <c r="AD126">
-        <v>1.53</v>
-      </c>
-      <c r="AE126">
-        <v>1.2</v>
-      </c>
       <c r="AF126">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AG126">
         <v>1.67</v>
@@ -21010,13 +21010,13 @@
         </is>
       </c>
       <c r="N127">
-        <v>2.81</v>
+        <v>2.72</v>
       </c>
       <c r="O127">
-        <v>2.6</v>
+        <v>2.45</v>
       </c>
       <c r="P127">
-        <v>2.81</v>
+        <v>2.8</v>
       </c>
       <c r="Q127">
         <v>0</v>
@@ -21173,19 +21173,19 @@
         </is>
       </c>
       <c r="N128">
-        <v>2.25</v>
+        <v>2.14</v>
       </c>
       <c r="O128">
-        <v>3.55</v>
+        <v>3.08</v>
       </c>
       <c r="P128">
-        <v>2.3</v>
+        <v>2.6</v>
       </c>
       <c r="Q128">
-        <v>3.25</v>
+        <v>2.75</v>
       </c>
       <c r="R128">
-        <v>2.2</v>
+        <v>1.95</v>
       </c>
       <c r="S128">
         <v>1.33</v>
@@ -21194,40 +21194,40 @@
         <v>2.23</v>
       </c>
       <c r="U128">
-        <v>2.62</v>
+        <v>2.79</v>
       </c>
       <c r="V128">
-        <v>1.42</v>
+        <v>1.35</v>
       </c>
       <c r="W128">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="X128">
         <v>1.02</v>
       </c>
       <c r="Y128">
-        <v>1.28</v>
+        <v>1.22</v>
       </c>
       <c r="Z128">
-        <v>3.35</v>
+        <v>3.14</v>
       </c>
       <c r="AA128">
-        <v>1.93</v>
+        <v>2.01</v>
       </c>
       <c r="AB128">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="AC128">
-        <v>3.35</v>
+        <v>2.95</v>
       </c>
       <c r="AD128">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="AE128">
         <v>1.06</v>
       </c>
       <c r="AF128">
-        <v>1.7</v>
+        <v>1.57</v>
       </c>
       <c r="AG128">
         <v>1.95</v>
@@ -21243,10 +21243,10 @@
         </is>
       </c>
       <c r="AJ128">
-        <v>1.45</v>
+        <v>1.33</v>
       </c>
       <c r="AK128">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="AL128">
         <v>0</v>
@@ -21336,19 +21336,19 @@
         </is>
       </c>
       <c r="N129">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="O129">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="P129">
-        <v>5.25</v>
+        <v>5.5</v>
       </c>
       <c r="Q129">
+        <v>2.06</v>
+      </c>
+      <c r="R129">
         <v>2.07</v>
-      </c>
-      <c r="R129">
-        <v>2.08</v>
       </c>
       <c r="S129">
         <v>1.4</v>
@@ -21357,43 +21357,43 @@
         <v>2.75</v>
       </c>
       <c r="U129">
+        <v>3.12</v>
+      </c>
+      <c r="V129">
+        <v>1.29</v>
+      </c>
+      <c r="W129">
+        <v>1.06</v>
+      </c>
+      <c r="X129">
+        <v>1.06</v>
+      </c>
+      <c r="Y129">
+        <v>1.4</v>
+      </c>
+      <c r="Z129">
         <v>2.9</v>
       </c>
-      <c r="V129">
-        <v>1.36</v>
-      </c>
-      <c r="W129">
-        <v>1.05</v>
-      </c>
-      <c r="X129">
-        <v>1.03</v>
-      </c>
-      <c r="Y129">
-        <v>1.42</v>
-      </c>
-      <c r="Z129">
-        <v>2.8</v>
-      </c>
       <c r="AA129">
+        <v>2.2</v>
+      </c>
+      <c r="AB129">
+        <v>1.49</v>
+      </c>
+      <c r="AC129">
+        <v>3.92</v>
+      </c>
+      <c r="AD129">
+        <v>1.19</v>
+      </c>
+      <c r="AE129">
+        <v>1.07</v>
+      </c>
+      <c r="AF129">
         <v>2.25</v>
       </c>
-      <c r="AB129">
-        <v>1.65</v>
-      </c>
-      <c r="AC129">
-        <v>3.95</v>
-      </c>
-      <c r="AD129">
-        <v>1.22</v>
-      </c>
-      <c r="AE129">
-        <v>1.03</v>
-      </c>
-      <c r="AF129">
-        <v>2.19</v>
-      </c>
       <c r="AG129">
-        <v>1.65</v>
+        <v>1.57</v>
       </c>
       <c r="AH129" t="inlineStr">
         <is>
@@ -21406,10 +21406,10 @@
         </is>
       </c>
       <c r="AJ129">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="AK129">
-        <v>2.38</v>
+        <v>2.3</v>
       </c>
       <c r="AL129">
         <v>0</v>
@@ -21499,13 +21499,13 @@
         </is>
       </c>
       <c r="N130">
-        <v>1.83</v>
+        <v>1.86</v>
       </c>
       <c r="O130">
-        <v>3.75</v>
+        <v>3.9</v>
       </c>
       <c r="P130">
-        <v>3.25</v>
+        <v>3.17</v>
       </c>
       <c r="Q130">
         <v>2.35</v>
@@ -21520,10 +21520,10 @@
         <v>4.2</v>
       </c>
       <c r="U130">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="V130">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="W130">
         <v>1.2</v>
@@ -21547,10 +21547,10 @@
         <v>1.96</v>
       </c>
       <c r="AD130">
-        <v>1.75</v>
+        <v>1.71</v>
       </c>
       <c r="AE130">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="AF130">
         <v>1.36</v>
@@ -21572,7 +21572,7 @@
         <v>1.19</v>
       </c>
       <c r="AK130">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="AL130">
         <v>0</v>
@@ -21662,13 +21662,13 @@
         </is>
       </c>
       <c r="N131">
-        <v>2.52</v>
+        <v>2.53</v>
       </c>
       <c r="O131">
         <v>3.35</v>
       </c>
       <c r="P131">
-        <v>2.3</v>
+        <v>2.35</v>
       </c>
       <c r="Q131">
         <v>3.15</v>
@@ -21683,7 +21683,7 @@
         <v>3.11</v>
       </c>
       <c r="U131">
-        <v>2.53</v>
+        <v>2.51</v>
       </c>
       <c r="V131">
         <v>1.47</v>
@@ -21692,34 +21692,34 @@
         <v>1.09</v>
       </c>
       <c r="X131">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y131">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="Z131">
         <v>3.25</v>
       </c>
       <c r="AA131">
-        <v>1.84</v>
+        <v>1.77</v>
       </c>
       <c r="AB131">
-        <v>1.79</v>
+        <v>2.06</v>
       </c>
       <c r="AC131">
-        <v>3.1</v>
+        <v>2.81</v>
       </c>
       <c r="AD131">
-        <v>1.29</v>
+        <v>1.34</v>
       </c>
       <c r="AE131">
         <v>1.09</v>
       </c>
       <c r="AF131">
-        <v>1.67</v>
+        <v>1.57</v>
       </c>
       <c r="AG131">
-        <v>2.02</v>
+        <v>2.25</v>
       </c>
       <c r="AH131" t="inlineStr">
         <is>
@@ -21732,7 +21732,7 @@
         </is>
       </c>
       <c r="AJ131">
-        <v>1.5</v>
+        <v>1.22</v>
       </c>
       <c r="AK131">
         <v>1.4</v>
@@ -21828,7 +21828,7 @@
         <v>1.57</v>
       </c>
       <c r="O132">
-        <v>3.9</v>
+        <v>3.7</v>
       </c>
       <c r="P132">
         <v>5</v>
@@ -21840,13 +21840,13 @@
         <v>2.3</v>
       </c>
       <c r="S132">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="T132">
-        <v>3.16</v>
+        <v>3.17</v>
       </c>
       <c r="U132">
-        <v>2.6</v>
+        <v>2.59</v>
       </c>
       <c r="V132">
         <v>1.44</v>
@@ -21855,13 +21855,13 @@
         <v>1.1</v>
       </c>
       <c r="X132">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y132">
         <v>1.25</v>
       </c>
       <c r="Z132">
-        <v>3.5</v>
+        <v>3.65</v>
       </c>
       <c r="AA132">
         <v>1.8</v>
@@ -21870,13 +21870,13 @@
         <v>1.87</v>
       </c>
       <c r="AC132">
-        <v>2.78</v>
+        <v>3</v>
       </c>
       <c r="AD132">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="AE132">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="AF132">
         <v>1.85</v>
@@ -21895,10 +21895,10 @@
         </is>
       </c>
       <c r="AJ132">
-        <v>1.18</v>
+        <v>1.25</v>
       </c>
       <c r="AK132">
-        <v>2.2</v>
+        <v>2.21</v>
       </c>
       <c r="AL132">
         <v>0</v>
@@ -21988,19 +21988,19 @@
         </is>
       </c>
       <c r="N133">
-        <v>5.15</v>
+        <v>4.9</v>
       </c>
       <c r="O133">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="P133">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="Q133">
-        <v>5.84</v>
+        <v>6</v>
       </c>
       <c r="R133">
-        <v>2.19</v>
+        <v>2.4</v>
       </c>
       <c r="S133">
         <v>1.32</v>
@@ -22009,10 +22009,10 @@
         <v>2.92</v>
       </c>
       <c r="U133">
-        <v>2.53</v>
+        <v>2.5</v>
       </c>
       <c r="V133">
-        <v>1.42</v>
+        <v>1.5</v>
       </c>
       <c r="W133">
         <v>1.09</v>
@@ -22021,31 +22021,31 @@
         <v>1.01</v>
       </c>
       <c r="Y133">
-        <v>1.2</v>
+        <v>1.26</v>
       </c>
       <c r="Z133">
-        <v>3.72</v>
+        <v>3.45</v>
       </c>
       <c r="AA133">
         <v>1.75</v>
       </c>
       <c r="AB133">
-        <v>2.05</v>
+        <v>1.98</v>
       </c>
       <c r="AC133">
-        <v>2.8</v>
+        <v>2.88</v>
       </c>
       <c r="AD133">
-        <v>1.39</v>
+        <v>1.36</v>
       </c>
       <c r="AE133">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="AF133">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="AG133">
-        <v>1.89</v>
+        <v>1.88</v>
       </c>
       <c r="AH133" t="inlineStr">
         <is>
@@ -22058,10 +22058,10 @@
         </is>
       </c>
       <c r="AJ133">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="AK133">
-        <v>1.08</v>
+        <v>1.12</v>
       </c>
       <c r="AL133">
         <v>0</v>
@@ -22151,19 +22151,19 @@
         </is>
       </c>
       <c r="N134">
-        <v>1.79</v>
+        <v>1.83</v>
       </c>
       <c r="O134">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="P134">
-        <v>3.55</v>
+        <v>3.05</v>
       </c>
       <c r="Q134">
-        <v>2.45</v>
+        <v>2.4</v>
       </c>
       <c r="R134">
-        <v>2.25</v>
+        <v>2.1</v>
       </c>
       <c r="S134">
         <v>1.27</v>
@@ -22172,10 +22172,10 @@
         <v>3.2</v>
       </c>
       <c r="U134">
-        <v>2.44</v>
+        <v>2.3</v>
       </c>
       <c r="V134">
-        <v>1.52</v>
+        <v>1.41</v>
       </c>
       <c r="W134">
         <v>1.08</v>
@@ -22184,7 +22184,7 @@
         <v>1.03</v>
       </c>
       <c r="Y134">
-        <v>1.21</v>
+        <v>1.17</v>
       </c>
       <c r="Z134">
         <v>4.05</v>
@@ -22196,13 +22196,13 @@
         <v>2.08</v>
       </c>
       <c r="AC134">
-        <v>2.63</v>
+        <v>2.56</v>
       </c>
       <c r="AD134">
         <v>1.4</v>
       </c>
       <c r="AE134">
-        <v>1.12</v>
+        <v>1.1</v>
       </c>
       <c r="AF134">
         <v>1.6</v>
@@ -22224,7 +22224,7 @@
         <v>1.21</v>
       </c>
       <c r="AK134">
-        <v>1.79</v>
+        <v>1.75</v>
       </c>
       <c r="AL134">
         <v>0</v>
@@ -22314,22 +22314,22 @@
         </is>
       </c>
       <c r="N135">
-        <v>2.85</v>
+        <v>2.8</v>
       </c>
       <c r="O135">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="P135">
-        <v>2.29</v>
+        <v>2.32</v>
       </c>
       <c r="Q135">
-        <v>3.75</v>
+        <v>3.66</v>
       </c>
       <c r="R135">
-        <v>1.93</v>
+        <v>1.9</v>
       </c>
       <c r="S135">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="T135">
         <v>2.63</v>
@@ -22338,37 +22338,37 @@
         <v>3</v>
       </c>
       <c r="V135">
-        <v>1.26</v>
+        <v>1.2</v>
       </c>
       <c r="W135">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="X135">
-        <v>1.09</v>
+        <v>1.04</v>
       </c>
       <c r="Y135">
         <v>1.49</v>
       </c>
       <c r="Z135">
-        <v>2.52</v>
+        <v>2.49</v>
       </c>
       <c r="AA135">
-        <v>2.37</v>
+        <v>2.42</v>
       </c>
       <c r="AB135">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="AC135">
-        <v>4.38</v>
+        <v>4.8</v>
       </c>
       <c r="AD135">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="AE135">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="AF135">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="AG135">
         <v>1.64</v>
@@ -22384,7 +22384,7 @@
         </is>
       </c>
       <c r="AJ135">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="AK135">
         <v>1.33</v>
@@ -22477,64 +22477,64 @@
         </is>
       </c>
       <c r="N136">
-        <v>2.05</v>
+        <v>1.83</v>
       </c>
       <c r="O136">
-        <v>3.4</v>
+        <v>3.75</v>
       </c>
       <c r="P136">
         <v>2.9</v>
       </c>
       <c r="Q136">
-        <v>2.47</v>
+        <v>2.29</v>
       </c>
       <c r="R136">
-        <v>2.32</v>
+        <v>2.38</v>
       </c>
       <c r="S136">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="T136">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="U136">
-        <v>2.16</v>
+        <v>2.12</v>
       </c>
       <c r="V136">
         <v>1.62</v>
       </c>
       <c r="W136">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="X136">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y136">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="Z136">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="AA136">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="AB136">
-        <v>2.49</v>
+        <v>2.6</v>
       </c>
       <c r="AC136">
-        <v>2.16</v>
+        <v>2.09</v>
       </c>
       <c r="AD136">
-        <v>1.62</v>
+        <v>1.66</v>
       </c>
       <c r="AE136">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="AF136">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="AG136">
-        <v>2.66</v>
+        <v>2.75</v>
       </c>
       <c r="AH136" t="inlineStr">
         <is>
@@ -22547,10 +22547,10 @@
         </is>
       </c>
       <c r="AJ136">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="AK136">
-        <v>1.7</v>
+        <v>1.87</v>
       </c>
       <c r="AL136">
         <v>0</v>
@@ -22640,10 +22640,10 @@
         </is>
       </c>
       <c r="N137">
-        <v>1.94</v>
+        <v>1.9</v>
       </c>
       <c r="O137">
-        <v>3.64</v>
+        <v>3.6</v>
       </c>
       <c r="P137">
         <v>3.56</v>

--- a/jogos_2026-08-02.xlsx
+++ b/jogos_2026-08-02.xlsx
@@ -1092,12 +1092,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Rockdale City Suns</t>
+          <t>Blacktown City</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Manly United</t>
+          <t>Sydney II</t>
         </is>
       </c>
       <c r="G5">
@@ -1124,80 +1124,80 @@
         </is>
       </c>
       <c r="N5">
-        <v>1.75</v>
+        <v>1.91</v>
       </c>
       <c r="O5">
-        <v>3.7</v>
+        <v>3.4</v>
       </c>
       <c r="P5">
-        <v>3.63</v>
+        <v>3.4</v>
       </c>
       <c r="Q5">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="R5">
-        <v>2.38</v>
+        <v>2.18</v>
       </c>
       <c r="S5">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="T5">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="U5">
-        <v>2.37</v>
+        <v>2.44</v>
       </c>
       <c r="V5">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="W5">
-        <v>1.09</v>
+        <v>1.07</v>
       </c>
       <c r="X5">
         <v>1.02</v>
       </c>
       <c r="Y5">
-        <v>1.13</v>
+        <v>1.18</v>
       </c>
       <c r="Z5">
-        <v>4.35</v>
+        <v>4.2</v>
       </c>
       <c r="AA5">
-        <v>1.6</v>
+        <v>1.67</v>
       </c>
       <c r="AB5">
+        <v>2.05</v>
+      </c>
+      <c r="AC5">
+        <v>2.74</v>
+      </c>
+      <c r="AD5">
+        <v>1.41</v>
+      </c>
+      <c r="AE5">
+        <v>1.17</v>
+      </c>
+      <c r="AF5">
+        <v>1.58</v>
+      </c>
+      <c r="AG5">
         <v>2.19</v>
       </c>
-      <c r="AC5">
-        <v>2.5</v>
-      </c>
-      <c r="AD5">
-        <v>1.53</v>
-      </c>
-      <c r="AE5">
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ5">
         <v>1.22</v>
       </c>
-      <c r="AF5">
-        <v>1.57</v>
-      </c>
-      <c r="AG5">
-        <v>2.25</v>
-      </c>
-      <c r="AH5" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI5" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ5">
-        <v>1.19</v>
-      </c>
       <c r="AK5">
-        <v>1.94</v>
+        <v>1.8</v>
       </c>
       <c r="AL5">
         <v>0</v>
@@ -1255,12 +1255,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Blacktown City</t>
+          <t>Rockdale City Suns</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Sydney II</t>
+          <t>Manly United</t>
         </is>
       </c>
       <c r="G6">
@@ -1287,64 +1287,64 @@
         </is>
       </c>
       <c r="N6">
-        <v>1.91</v>
+        <v>1.75</v>
       </c>
       <c r="O6">
+        <v>3.7</v>
+      </c>
+      <c r="P6">
+        <v>3.63</v>
+      </c>
+      <c r="Q6">
+        <v>2.25</v>
+      </c>
+      <c r="R6">
+        <v>2.38</v>
+      </c>
+      <c r="S6">
+        <v>1.25</v>
+      </c>
+      <c r="T6">
         <v>3.4</v>
       </c>
-      <c r="P6">
-        <v>3.4</v>
-      </c>
-      <c r="Q6">
-        <v>2.3</v>
-      </c>
-      <c r="R6">
-        <v>2.18</v>
-      </c>
-      <c r="S6">
-        <v>1.28</v>
-      </c>
-      <c r="T6">
-        <v>3.25</v>
-      </c>
       <c r="U6">
-        <v>2.44</v>
+        <v>2.37</v>
       </c>
       <c r="V6">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="W6">
-        <v>1.07</v>
+        <v>1.09</v>
       </c>
       <c r="X6">
         <v>1.02</v>
       </c>
       <c r="Y6">
-        <v>1.18</v>
+        <v>1.13</v>
       </c>
       <c r="Z6">
-        <v>4.2</v>
+        <v>4.35</v>
       </c>
       <c r="AA6">
-        <v>1.67</v>
+        <v>1.6</v>
       </c>
       <c r="AB6">
-        <v>2.05</v>
+        <v>2.19</v>
       </c>
       <c r="AC6">
-        <v>2.74</v>
+        <v>2.5</v>
       </c>
       <c r="AD6">
-        <v>1.41</v>
+        <v>1.53</v>
       </c>
       <c r="AE6">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="AF6">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="AG6">
-        <v>2.19</v>
+        <v>2.25</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1357,10 +1357,10 @@
         </is>
       </c>
       <c r="AJ6">
-        <v>1.22</v>
+        <v>1.19</v>
       </c>
       <c r="AK6">
-        <v>1.8</v>
+        <v>1.94</v>
       </c>
       <c r="AL6">
         <v>0</v>
@@ -1782,7 +1782,7 @@
         <v>3.3</v>
       </c>
       <c r="P9">
-        <v>2.67</v>
+        <v>2.6</v>
       </c>
       <c r="Q9">
         <v>0</v>
@@ -2070,12 +2070,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Daejeon Citizen</t>
+          <t>Ulsan</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Gwangju</t>
+          <t>Anyang</t>
         </is>
       </c>
       <c r="G11">
@@ -2102,80 +2102,80 @@
         </is>
       </c>
       <c r="N11">
-        <v>1.45</v>
+        <v>1.9</v>
       </c>
       <c r="O11">
-        <v>4.2</v>
+        <v>3.6</v>
       </c>
       <c r="P11">
-        <v>5.2</v>
+        <v>3.8</v>
       </c>
       <c r="Q11">
-        <v>1.98</v>
+        <v>2.41</v>
       </c>
       <c r="R11">
-        <v>2.29</v>
+        <v>2.1</v>
       </c>
       <c r="S11">
         <v>1.36</v>
       </c>
       <c r="T11">
-        <v>3.2</v>
+        <v>2.94</v>
       </c>
       <c r="U11">
-        <v>2.63</v>
+        <v>2.65</v>
       </c>
       <c r="V11">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="W11">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="X11">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="Y11">
         <v>1.22</v>
       </c>
       <c r="Z11">
-        <v>3.54</v>
+        <v>3.9</v>
       </c>
       <c r="AA11">
-        <v>1.83</v>
+        <v>1.89</v>
       </c>
       <c r="AB11">
-        <v>1.97</v>
+        <v>1.89</v>
       </c>
       <c r="AC11">
-        <v>2.89</v>
+        <v>3.11</v>
       </c>
       <c r="AD11">
-        <v>1.32</v>
+        <v>1.38</v>
       </c>
       <c r="AE11">
-        <v>1.12</v>
+        <v>1.08</v>
       </c>
       <c r="AF11">
+        <v>1.7</v>
+      </c>
+      <c r="AG11">
+        <v>2.04</v>
+      </c>
+      <c r="AH11" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI11" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ11">
+        <v>1.21</v>
+      </c>
+      <c r="AK11">
         <v>1.9</v>
-      </c>
-      <c r="AG11">
-        <v>1.77</v>
-      </c>
-      <c r="AH11" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI11" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ11">
-        <v>1.22</v>
-      </c>
-      <c r="AK11">
-        <v>2.5</v>
       </c>
       <c r="AL11">
         <v>0</v>
@@ -2233,12 +2233,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Jeju United</t>
+          <t>Daejeon Citizen</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Incheon United</t>
+          <t>Gwangju</t>
         </is>
       </c>
       <c r="G12">
@@ -2265,64 +2265,64 @@
         </is>
       </c>
       <c r="N12">
-        <v>2.87</v>
+        <v>1.45</v>
       </c>
       <c r="O12">
-        <v>2.9</v>
+        <v>4.2</v>
       </c>
       <c r="P12">
-        <v>2.2</v>
+        <v>5.2</v>
       </c>
       <c r="Q12">
-        <v>3.55</v>
+        <v>1.98</v>
       </c>
       <c r="R12">
-        <v>1.98</v>
+        <v>2.29</v>
       </c>
       <c r="S12">
-        <v>1.44</v>
+        <v>1.36</v>
       </c>
       <c r="T12">
-        <v>2.6</v>
+        <v>3.2</v>
       </c>
       <c r="U12">
-        <v>3.2</v>
+        <v>2.63</v>
       </c>
       <c r="V12">
-        <v>1.27</v>
+        <v>1.41</v>
       </c>
       <c r="W12">
         <v>1.06</v>
       </c>
       <c r="X12">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="Y12">
-        <v>1.44</v>
+        <v>1.22</v>
       </c>
       <c r="Z12">
-        <v>2.7</v>
+        <v>3.54</v>
       </c>
       <c r="AA12">
-        <v>2.38</v>
+        <v>1.83</v>
       </c>
       <c r="AB12">
-        <v>1.56</v>
+        <v>1.97</v>
       </c>
       <c r="AC12">
-        <v>4.3</v>
+        <v>2.89</v>
       </c>
       <c r="AD12">
-        <v>1.2</v>
+        <v>1.32</v>
       </c>
       <c r="AE12">
-        <v>1.03</v>
+        <v>1.12</v>
       </c>
       <c r="AF12">
-        <v>1.95</v>
+        <v>1.9</v>
       </c>
       <c r="AG12">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2335,10 +2335,10 @@
         </is>
       </c>
       <c r="AJ12">
-        <v>1.36</v>
+        <v>1.22</v>
       </c>
       <c r="AK12">
-        <v>1.36</v>
+        <v>2.5</v>
       </c>
       <c r="AL12">
         <v>0</v>
@@ -2396,12 +2396,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Ulsan</t>
+          <t>Jeju United</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Anyang</t>
+          <t>Incheon United</t>
         </is>
       </c>
       <c r="G13">
@@ -2428,80 +2428,80 @@
         </is>
       </c>
       <c r="N13">
-        <v>1.9</v>
+        <v>2.87</v>
       </c>
       <c r="O13">
-        <v>3.6</v>
+        <v>2.9</v>
       </c>
       <c r="P13">
-        <v>3.8</v>
+        <v>2.2</v>
       </c>
       <c r="Q13">
-        <v>2.41</v>
+        <v>3.55</v>
       </c>
       <c r="R13">
-        <v>2.1</v>
+        <v>1.98</v>
       </c>
       <c r="S13">
+        <v>1.44</v>
+      </c>
+      <c r="T13">
+        <v>2.6</v>
+      </c>
+      <c r="U13">
+        <v>3.2</v>
+      </c>
+      <c r="V13">
+        <v>1.27</v>
+      </c>
+      <c r="W13">
+        <v>1.06</v>
+      </c>
+      <c r="X13">
+        <v>1.07</v>
+      </c>
+      <c r="Y13">
+        <v>1.44</v>
+      </c>
+      <c r="Z13">
+        <v>2.7</v>
+      </c>
+      <c r="AA13">
+        <v>2.38</v>
+      </c>
+      <c r="AB13">
+        <v>1.56</v>
+      </c>
+      <c r="AC13">
+        <v>4.3</v>
+      </c>
+      <c r="AD13">
+        <v>1.2</v>
+      </c>
+      <c r="AE13">
+        <v>1.03</v>
+      </c>
+      <c r="AF13">
+        <v>1.95</v>
+      </c>
+      <c r="AG13">
+        <v>1.75</v>
+      </c>
+      <c r="AH13" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI13" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ13">
         <v>1.36</v>
       </c>
-      <c r="T13">
-        <v>2.94</v>
-      </c>
-      <c r="U13">
-        <v>2.65</v>
-      </c>
-      <c r="V13">
-        <v>1.42</v>
-      </c>
-      <c r="W13">
-        <v>1.05</v>
-      </c>
-      <c r="X13">
-        <v>1.02</v>
-      </c>
-      <c r="Y13">
-        <v>1.22</v>
-      </c>
-      <c r="Z13">
-        <v>3.9</v>
-      </c>
-      <c r="AA13">
-        <v>1.89</v>
-      </c>
-      <c r="AB13">
-        <v>1.89</v>
-      </c>
-      <c r="AC13">
-        <v>3.11</v>
-      </c>
-      <c r="AD13">
-        <v>1.38</v>
-      </c>
-      <c r="AE13">
-        <v>1.08</v>
-      </c>
-      <c r="AF13">
-        <v>1.7</v>
-      </c>
-      <c r="AG13">
-        <v>2.04</v>
-      </c>
-      <c r="AH13" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI13" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ13">
-        <v>1.21</v>
-      </c>
       <c r="AK13">
-        <v>1.9</v>
+        <v>1.36</v>
       </c>
       <c r="AL13">
         <v>0</v>
@@ -2559,12 +2559,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Jeonnam Dragons</t>
+          <t>Ansan Greeners</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Paju Citizen</t>
+          <t>Gimhae City</t>
         </is>
       </c>
       <c r="G14">
@@ -2591,64 +2591,64 @@
         </is>
       </c>
       <c r="N14">
-        <v>1.96</v>
+        <v>2.78</v>
       </c>
       <c r="O14">
+        <v>3.55</v>
+      </c>
+      <c r="P14">
+        <v>2.3</v>
+      </c>
+      <c r="Q14">
         <v>3.4</v>
       </c>
-      <c r="P14">
-        <v>3.15</v>
-      </c>
-      <c r="Q14">
-        <v>2.69</v>
-      </c>
       <c r="R14">
-        <v>2.2</v>
+        <v>2.12</v>
       </c>
       <c r="S14">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="T14">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="U14">
-        <v>2.75</v>
+        <v>2.89</v>
       </c>
       <c r="V14">
         <v>1.4</v>
       </c>
       <c r="W14">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="X14">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y14">
-        <v>1.2</v>
+        <v>1.29</v>
       </c>
       <c r="Z14">
-        <v>3.7</v>
+        <v>3.4</v>
       </c>
       <c r="AA14">
+        <v>1.93</v>
+      </c>
+      <c r="AB14">
         <v>1.85</v>
       </c>
-      <c r="AB14">
-        <v>1.9</v>
-      </c>
       <c r="AC14">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="AD14">
-        <v>1.31</v>
+        <v>1.27</v>
       </c>
       <c r="AE14">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="AF14">
-        <v>1.64</v>
+        <v>1.67</v>
       </c>
       <c r="AG14">
-        <v>2.1</v>
+        <v>2.03</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2661,10 +2661,10 @@
         </is>
       </c>
       <c r="AJ14">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AK14">
-        <v>1.7</v>
+        <v>1.33</v>
       </c>
       <c r="AL14">
         <v>0</v>
@@ -3048,12 +3048,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Ansan Greeners</t>
+          <t>Jeonnam Dragons</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Gimhae City</t>
+          <t>Paju Citizen</t>
         </is>
       </c>
       <c r="G17">
@@ -3080,64 +3080,64 @@
         </is>
       </c>
       <c r="N17">
-        <v>2.78</v>
+        <v>1.96</v>
       </c>
       <c r="O17">
-        <v>3.55</v>
+        <v>3.4</v>
       </c>
       <c r="P17">
-        <v>2.3</v>
+        <v>3.15</v>
       </c>
       <c r="Q17">
-        <v>3.4</v>
+        <v>2.69</v>
       </c>
       <c r="R17">
-        <v>2.12</v>
+        <v>2.2</v>
       </c>
       <c r="S17">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="T17">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="U17">
-        <v>2.89</v>
+        <v>2.75</v>
       </c>
       <c r="V17">
         <v>1.4</v>
       </c>
       <c r="W17">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="X17">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y17">
-        <v>1.29</v>
+        <v>1.2</v>
       </c>
       <c r="Z17">
-        <v>3.4</v>
+        <v>3.7</v>
       </c>
       <c r="AA17">
-        <v>1.93</v>
+        <v>1.85</v>
       </c>
       <c r="AB17">
-        <v>1.85</v>
+        <v>1.9</v>
       </c>
       <c r="AC17">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="AD17">
-        <v>1.27</v>
+        <v>1.31</v>
       </c>
       <c r="AE17">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="AF17">
-        <v>1.67</v>
+        <v>1.64</v>
       </c>
       <c r="AG17">
-        <v>2.03</v>
+        <v>2.1</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3150,10 +3150,10 @@
         </is>
       </c>
       <c r="AJ17">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AK17">
-        <v>1.33</v>
+        <v>1.7</v>
       </c>
       <c r="AL17">
         <v>0</v>
@@ -3374,12 +3374,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Changchun Yatai</t>
+          <t>Suzhou Dongwu</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Hebei Kungfu</t>
+          <t>Meizhou Hakka</t>
         </is>
       </c>
       <c r="G19">
@@ -3406,64 +3406,64 @@
         </is>
       </c>
       <c r="N19">
-        <v>1.8</v>
+        <v>2.25</v>
       </c>
       <c r="O19">
-        <v>3.3</v>
+        <v>3.05</v>
       </c>
       <c r="P19">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="Q19">
-        <v>2.4</v>
+        <v>2.96</v>
       </c>
       <c r="R19">
-        <v>2.21</v>
+        <v>1.95</v>
       </c>
       <c r="S19">
+        <v>1.41</v>
+      </c>
+      <c r="T19">
+        <v>2.72</v>
+      </c>
+      <c r="U19">
+        <v>2.95</v>
+      </c>
+      <c r="V19">
         <v>1.36</v>
       </c>
-      <c r="T19">
-        <v>2.63</v>
-      </c>
-      <c r="U19">
-        <v>2.7</v>
-      </c>
-      <c r="V19">
-        <v>1.4</v>
-      </c>
       <c r="W19">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="X19">
         <v>1.01</v>
       </c>
       <c r="Y19">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="Z19">
-        <v>3.4</v>
+        <v>3.05</v>
       </c>
       <c r="AA19">
-        <v>1.91</v>
+        <v>1.87</v>
       </c>
       <c r="AB19">
-        <v>1.78</v>
+        <v>1.7</v>
       </c>
       <c r="AC19">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="AD19">
-        <v>1.3</v>
+        <v>1.22</v>
       </c>
       <c r="AE19">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="AF19">
-        <v>1.79</v>
+        <v>1.73</v>
       </c>
       <c r="AG19">
-        <v>1.73</v>
+        <v>1.93</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3476,10 +3476,10 @@
         </is>
       </c>
       <c r="AJ19">
-        <v>1.15</v>
+        <v>1.35</v>
       </c>
       <c r="AK19">
-        <v>1.84</v>
+        <v>1.42</v>
       </c>
       <c r="AL19">
         <v>0</v>
@@ -3537,12 +3537,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Suzhou Dongwu</t>
+          <t>Changchun Yatai</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Meizhou Hakka</t>
+          <t>Hebei Kungfu</t>
         </is>
       </c>
       <c r="G20">
@@ -3569,65 +3569,65 @@
         </is>
       </c>
       <c r="N20">
-        <v>2.25</v>
+        <v>1.8</v>
       </c>
       <c r="O20">
-        <v>3.05</v>
+        <v>3.3</v>
       </c>
       <c r="P20">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Q20">
-        <v>2.96</v>
+        <v>2.4</v>
       </c>
       <c r="R20">
-        <v>1.95</v>
+        <v>2.21</v>
       </c>
       <c r="S20">
-        <v>1.41</v>
+        <v>1.36</v>
       </c>
       <c r="T20">
-        <v>2.72</v>
+        <v>2.63</v>
       </c>
       <c r="U20">
-        <v>2.95</v>
+        <v>2.7</v>
       </c>
       <c r="V20">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="W20">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="X20">
         <v>1.01</v>
       </c>
       <c r="Y20">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="Z20">
-        <v>3.05</v>
+        <v>3.4</v>
       </c>
       <c r="AA20">
-        <v>1.87</v>
+        <v>1.91</v>
       </c>
       <c r="AB20">
-        <v>1.7</v>
+        <v>1.78</v>
       </c>
       <c r="AC20">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="AD20">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="AE20">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="AF20">
+        <v>1.79</v>
+      </c>
+      <c r="AG20">
         <v>1.73</v>
       </c>
-      <c r="AG20">
-        <v>1.93</v>
-      </c>
       <c r="AH20" t="inlineStr">
         <is>
           <t>[]</t>
@@ -3639,10 +3639,10 @@
         </is>
       </c>
       <c r="AJ20">
-        <v>1.35</v>
+        <v>1.15</v>
       </c>
       <c r="AK20">
-        <v>1.42</v>
+        <v>1.84</v>
       </c>
       <c r="AL20">
         <v>0</v>
@@ -4061,19 +4061,19 @@
         <v>3.3</v>
       </c>
       <c r="O23">
-        <v>3.61</v>
+        <v>3.6</v>
       </c>
       <c r="P23">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="Q23">
         <v>3.25</v>
       </c>
       <c r="R23">
-        <v>2.45</v>
+        <v>2.6</v>
       </c>
       <c r="S23">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="T23">
         <v>3.58</v>
@@ -4085,10 +4085,10 @@
         <v>1.67</v>
       </c>
       <c r="W23">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="X23">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y23">
         <v>1.13</v>
@@ -4115,7 +4115,7 @@
         <v>1.44</v>
       </c>
       <c r="AG23">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
@@ -4128,10 +4128,10 @@
         </is>
       </c>
       <c r="AJ23">
-        <v>1.73</v>
+        <v>1.79</v>
       </c>
       <c r="AK23">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AL23">
         <v>0</v>
@@ -5199,10 +5199,10 @@
         </is>
       </c>
       <c r="N30">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="O30">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="P30">
         <v>3</v>
@@ -5214,49 +5214,49 @@
         <v>2.2</v>
       </c>
       <c r="S30">
-        <v>1.28</v>
+        <v>1.32</v>
       </c>
       <c r="T30">
-        <v>3.15</v>
+        <v>3.25</v>
       </c>
       <c r="U30">
-        <v>2.47</v>
+        <v>2.39</v>
       </c>
       <c r="V30">
         <v>1.49</v>
       </c>
       <c r="W30">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="X30">
         <v>1.02</v>
       </c>
       <c r="Y30">
-        <v>1.18</v>
+        <v>1.23</v>
       </c>
       <c r="Z30">
         <v>3.9</v>
       </c>
       <c r="AA30">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="AB30">
-        <v>2.02</v>
+        <v>2.07</v>
       </c>
       <c r="AC30">
-        <v>2.74</v>
+        <v>2.8</v>
       </c>
       <c r="AD30">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="AE30">
-        <v>1.1</v>
+        <v>1.14</v>
       </c>
       <c r="AF30">
-        <v>1.59</v>
+        <v>1.62</v>
       </c>
       <c r="AG30">
-        <v>2.19</v>
+        <v>2.15</v>
       </c>
       <c r="AH30" t="inlineStr">
         <is>
@@ -5269,10 +5269,10 @@
         </is>
       </c>
       <c r="AJ30">
-        <v>1.28</v>
+        <v>1.22</v>
       </c>
       <c r="AK30">
-        <v>1.63</v>
+        <v>1.65</v>
       </c>
       <c r="AL30">
         <v>0</v>
@@ -5368,7 +5368,7 @@
         <v>3.7</v>
       </c>
       <c r="P31">
-        <v>5.25</v>
+        <v>5.5</v>
       </c>
       <c r="Q31">
         <v>2.13</v>
@@ -5377,25 +5377,25 @@
         <v>2.25</v>
       </c>
       <c r="S31">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="T31">
-        <v>2.95</v>
+        <v>3.05</v>
       </c>
       <c r="U31">
-        <v>2.55</v>
+        <v>2.73</v>
       </c>
       <c r="V31">
         <v>1.39</v>
       </c>
       <c r="W31">
-        <v>1.1</v>
+        <v>1.05</v>
       </c>
       <c r="X31">
-        <v>1.03</v>
+        <v>1</v>
       </c>
       <c r="Y31">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="Z31">
         <v>3.34</v>
@@ -5407,19 +5407,19 @@
         <v>1.92</v>
       </c>
       <c r="AC31">
-        <v>3.2</v>
+        <v>3.08</v>
       </c>
       <c r="AD31">
         <v>1.28</v>
       </c>
       <c r="AE31">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="AF31">
-        <v>1.9</v>
+        <v>1.87</v>
       </c>
       <c r="AG31">
-        <v>1.87</v>
+        <v>1.83</v>
       </c>
       <c r="AH31" t="inlineStr">
         <is>
@@ -5432,7 +5432,7 @@
         </is>
       </c>
       <c r="AJ31">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AK31">
         <v>2.27</v>
@@ -5528,77 +5528,77 @@
         <v>2.6</v>
       </c>
       <c r="O32">
-        <v>2.62</v>
+        <v>2.68</v>
       </c>
       <c r="P32">
         <v>2.92</v>
       </c>
       <c r="Q32">
-        <v>3.58</v>
+        <v>3.64</v>
       </c>
       <c r="R32">
-        <v>1.7</v>
+        <v>1.68</v>
       </c>
       <c r="S32">
         <v>1.6</v>
       </c>
       <c r="T32">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="U32">
-        <v>3.98</v>
+        <v>4.15</v>
       </c>
       <c r="V32">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="W32">
         <v>1.01</v>
       </c>
       <c r="X32">
-        <v>1.11</v>
+        <v>1.17</v>
       </c>
       <c r="Y32">
-        <v>1.62</v>
+        <v>1.7</v>
       </c>
       <c r="Z32">
-        <v>2.17</v>
+        <v>2.03</v>
       </c>
       <c r="AA32">
-        <v>2.88</v>
+        <v>3.1</v>
       </c>
       <c r="AB32">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AC32">
-        <v>5.8</v>
+        <v>6.15</v>
       </c>
       <c r="AD32">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="AE32">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="AF32">
-        <v>2.3</v>
+        <v>2.38</v>
       </c>
       <c r="AG32">
+        <v>1.47</v>
+      </c>
+      <c r="AH32" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI32" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ32">
         <v>1.5</v>
       </c>
-      <c r="AH32" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI32" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ32">
-        <v>1.38</v>
-      </c>
       <c r="AK32">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="AL32">
         <v>0</v>
@@ -5851,13 +5851,13 @@
         </is>
       </c>
       <c r="N34">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="O34">
-        <v>3.6</v>
+        <v>3.78</v>
       </c>
       <c r="P34">
-        <v>4.13</v>
+        <v>4.09</v>
       </c>
       <c r="Q34">
         <v>2.2</v>
@@ -5872,10 +5872,10 @@
         <v>3.11</v>
       </c>
       <c r="U34">
-        <v>2.41</v>
+        <v>2.32</v>
       </c>
       <c r="V34">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="W34">
         <v>1.1</v>
@@ -5908,7 +5908,7 @@
         <v>1.62</v>
       </c>
       <c r="AG34">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="AH34" t="inlineStr">
         <is>
@@ -5924,7 +5924,7 @@
         <v>1.2</v>
       </c>
       <c r="AK34">
-        <v>1.99</v>
+        <v>1.98</v>
       </c>
       <c r="AL34">
         <v>0</v>
@@ -6506,10 +6506,10 @@
         <v>7.6</v>
       </c>
       <c r="O38">
-        <v>5.15</v>
+        <v>4.4</v>
       </c>
       <c r="P38">
-        <v>1.36</v>
+        <v>1.31</v>
       </c>
       <c r="Q38">
         <v>7.3</v>
@@ -6518,10 +6518,10 @@
         <v>2.55</v>
       </c>
       <c r="S38">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="T38">
-        <v>3.32</v>
+        <v>3.24</v>
       </c>
       <c r="U38">
         <v>2.51</v>
@@ -6539,13 +6539,13 @@
         <v>1.23</v>
       </c>
       <c r="Z38">
-        <v>3.98</v>
+        <v>3.96</v>
       </c>
       <c r="AA38">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="AB38">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="AC38">
         <v>2.65</v>
@@ -6675,7 +6675,7 @@
         <v>3.1</v>
       </c>
       <c r="Q39">
-        <v>2.84</v>
+        <v>2.82</v>
       </c>
       <c r="R39">
         <v>2.29</v>
@@ -6705,7 +6705,7 @@
         <v>3.44</v>
       </c>
       <c r="AA39">
-        <v>1.9</v>
+        <v>1.8</v>
       </c>
       <c r="AB39">
         <v>1.97</v>
@@ -6720,7 +6720,7 @@
         <v>1.08</v>
       </c>
       <c r="AF39">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="AG39">
         <v>2.11</v>
@@ -7161,10 +7161,10 @@
         <v>3.25</v>
       </c>
       <c r="P42">
-        <v>3</v>
+        <v>3.01</v>
       </c>
       <c r="Q42">
-        <v>2.9</v>
+        <v>2.7</v>
       </c>
       <c r="R42">
         <v>2.17</v>
@@ -7173,10 +7173,10 @@
         <v>1.36</v>
       </c>
       <c r="T42">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="U42">
-        <v>2.93</v>
+        <v>2.66</v>
       </c>
       <c r="V42">
         <v>1.42</v>
@@ -7185,34 +7185,34 @@
         <v>1.1</v>
       </c>
       <c r="X42">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="Y42">
         <v>1.22</v>
       </c>
       <c r="Z42">
-        <v>3.58</v>
+        <v>3.75</v>
       </c>
       <c r="AA42">
-        <v>1.72</v>
+        <v>1.8</v>
       </c>
       <c r="AB42">
-        <v>1.88</v>
+        <v>1.95</v>
       </c>
       <c r="AC42">
-        <v>3.16</v>
+        <v>2.9</v>
       </c>
       <c r="AD42">
         <v>1.3</v>
       </c>
       <c r="AE42">
-        <v>1.13</v>
+        <v>1.07</v>
       </c>
       <c r="AF42">
         <v>1.65</v>
       </c>
       <c r="AG42">
-        <v>2.05</v>
+        <v>2.15</v>
       </c>
       <c r="AH42" t="inlineStr">
         <is>
@@ -7318,25 +7318,25 @@
         </is>
       </c>
       <c r="N43">
-        <v>2.65</v>
+        <v>2.7</v>
       </c>
       <c r="O43">
-        <v>3.55</v>
+        <v>3.65</v>
       </c>
       <c r="P43">
-        <v>2.35</v>
+        <v>1.86</v>
       </c>
       <c r="Q43">
         <v>3.02</v>
       </c>
       <c r="R43">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="S43">
         <v>1.3</v>
       </c>
       <c r="T43">
-        <v>3.2</v>
+        <v>3.22</v>
       </c>
       <c r="U43">
         <v>2.4</v>
@@ -7391,7 +7391,7 @@
         <v>1.27</v>
       </c>
       <c r="AK43">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="AL43">
         <v>0</v>
@@ -8951,10 +8951,10 @@
         <v>2</v>
       </c>
       <c r="O53">
-        <v>4</v>
+        <v>3.65</v>
       </c>
       <c r="P53">
-        <v>3.25</v>
+        <v>3.19</v>
       </c>
       <c r="Q53">
         <v>2.58</v>
@@ -8972,16 +8972,16 @@
         <v>2.2</v>
       </c>
       <c r="V53">
-        <v>1.55</v>
+        <v>1.6</v>
       </c>
       <c r="W53">
         <v>1.13</v>
       </c>
       <c r="X53">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y53">
-        <v>1.13</v>
+        <v>1.17</v>
       </c>
       <c r="Z53">
         <v>4.8</v>
@@ -8990,7 +8990,7 @@
         <v>1.54</v>
       </c>
       <c r="AB53">
-        <v>2.23</v>
+        <v>2.4</v>
       </c>
       <c r="AC53">
         <v>2.27</v>
@@ -9002,10 +9002,10 @@
         <v>1.18</v>
       </c>
       <c r="AF53">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="AG53">
-        <v>2.63</v>
+        <v>2.45</v>
       </c>
       <c r="AH53" t="inlineStr">
         <is>
@@ -9111,31 +9111,31 @@
         </is>
       </c>
       <c r="N54">
-        <v>3.62</v>
+        <v>3.68</v>
       </c>
       <c r="O54">
         <v>3.7</v>
       </c>
       <c r="P54">
-        <v>1.92</v>
+        <v>1.9</v>
       </c>
       <c r="Q54">
-        <v>3.85</v>
+        <v>4</v>
       </c>
       <c r="R54">
         <v>2.25</v>
       </c>
       <c r="S54">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="T54">
         <v>3.2</v>
       </c>
       <c r="U54">
-        <v>2.45</v>
+        <v>2.55</v>
       </c>
       <c r="V54">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="W54">
         <v>1.11</v>
@@ -9147,7 +9147,7 @@
         <v>1.22</v>
       </c>
       <c r="Z54">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="AA54">
         <v>1.73</v>
@@ -9156,13 +9156,13 @@
         <v>1.96</v>
       </c>
       <c r="AC54">
-        <v>2.88</v>
+        <v>2.75</v>
       </c>
       <c r="AD54">
         <v>1.4</v>
       </c>
       <c r="AE54">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="AF54">
         <v>1.63</v>
@@ -9184,7 +9184,7 @@
         <v>1.85</v>
       </c>
       <c r="AK54">
-        <v>1.21</v>
+        <v>1.26</v>
       </c>
       <c r="AL54">
         <v>0</v>
@@ -9437,7 +9437,7 @@
         </is>
       </c>
       <c r="N56">
-        <v>2.41</v>
+        <v>2.55</v>
       </c>
       <c r="O56">
         <v>3.4</v>
@@ -9467,7 +9467,7 @@
         <v>1.1</v>
       </c>
       <c r="X56">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y56">
         <v>1.14</v>
@@ -9479,7 +9479,7 @@
         <v>1.65</v>
       </c>
       <c r="AB56">
-        <v>2.23</v>
+        <v>2.2</v>
       </c>
       <c r="AC56">
         <v>2.6</v>
@@ -9491,7 +9491,7 @@
         <v>1.2</v>
       </c>
       <c r="AF56">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="AG56">
         <v>2.4</v>
@@ -9763,13 +9763,13 @@
         </is>
       </c>
       <c r="N58">
-        <v>3.3</v>
+        <v>3.31</v>
       </c>
       <c r="O58">
-        <v>3.5</v>
+        <v>3.61</v>
       </c>
       <c r="P58">
-        <v>1.91</v>
+        <v>1.83</v>
       </c>
       <c r="Q58">
         <v>3.92</v>
@@ -9793,7 +9793,7 @@
         <v>1.08</v>
       </c>
       <c r="X58">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y58">
         <v>1.2</v>
@@ -9808,19 +9808,19 @@
         <v>2.2</v>
       </c>
       <c r="AC58">
-        <v>2.69</v>
+        <v>2.71</v>
       </c>
       <c r="AD58">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="AE58">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="AF58">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="AG58">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="AH58" t="inlineStr">
         <is>
@@ -9833,7 +9833,7 @@
         </is>
       </c>
       <c r="AJ58">
-        <v>1.78</v>
+        <v>1.29</v>
       </c>
       <c r="AK58">
         <v>1.29</v>
@@ -9944,7 +9944,7 @@
         <v>1.3</v>
       </c>
       <c r="T59">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="U59">
         <v>2.56</v>
@@ -9953,13 +9953,13 @@
         <v>1.5</v>
       </c>
       <c r="W59">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="X59">
-        <v>1</v>
+        <v>1.04</v>
       </c>
       <c r="Y59">
-        <v>1.21</v>
+        <v>1.23</v>
       </c>
       <c r="Z59">
         <v>4.2</v>
@@ -9968,7 +9968,7 @@
         <v>1.7</v>
       </c>
       <c r="AB59">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="AC59">
         <v>2.75</v>
@@ -9980,10 +9980,10 @@
         <v>1.15</v>
       </c>
       <c r="AF59">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="AG59">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="AH59" t="inlineStr">
         <is>
@@ -10095,7 +10095,7 @@
         <v>4.2</v>
       </c>
       <c r="P60">
-        <v>4.92</v>
+        <v>4</v>
       </c>
       <c r="Q60">
         <v>2</v>
@@ -10113,13 +10113,13 @@
         <v>2.12</v>
       </c>
       <c r="V60">
-        <v>1.7</v>
+        <v>1.68</v>
       </c>
       <c r="W60">
         <v>1.17</v>
       </c>
       <c r="X60">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y60">
         <v>1.08</v>
@@ -10131,16 +10131,16 @@
         <v>1.4</v>
       </c>
       <c r="AB60">
-        <v>2.64</v>
+        <v>2.7</v>
       </c>
       <c r="AC60">
-        <v>2.12</v>
+        <v>2.02</v>
       </c>
       <c r="AD60">
-        <v>1.73</v>
+        <v>1.68</v>
       </c>
       <c r="AE60">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="AF60">
         <v>1.44</v>
@@ -10159,7 +10159,7 @@
         </is>
       </c>
       <c r="AJ60">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="AK60">
         <v>2.2</v>
@@ -10418,7 +10418,7 @@
         <v>2.6</v>
       </c>
       <c r="O62">
-        <v>3.18</v>
+        <v>3.22</v>
       </c>
       <c r="P62">
         <v>2.45</v>
@@ -10454,7 +10454,7 @@
         <v>2.99</v>
       </c>
       <c r="AA62">
-        <v>2.09</v>
+        <v>2.1</v>
       </c>
       <c r="AB62">
         <v>1.75</v>
@@ -10463,7 +10463,7 @@
         <v>3.5</v>
       </c>
       <c r="AD62">
-        <v>1.24</v>
+        <v>1.28</v>
       </c>
       <c r="AE62">
         <v>1.09</v>
@@ -10488,7 +10488,7 @@
         <v>1.32</v>
       </c>
       <c r="AK62">
-        <v>1.4</v>
+        <v>1.45</v>
       </c>
       <c r="AL62">
         <v>0</v>
@@ -10581,10 +10581,10 @@
         <v>2.35</v>
       </c>
       <c r="O63">
-        <v>3.2</v>
+        <v>3.42</v>
       </c>
       <c r="P63">
-        <v>3</v>
+        <v>2.63</v>
       </c>
       <c r="Q63">
         <v>2.88</v>
@@ -10593,10 +10593,10 @@
         <v>2.1</v>
       </c>
       <c r="S63">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="T63">
-        <v>2.78</v>
+        <v>3.19</v>
       </c>
       <c r="U63">
         <v>2.5</v>
@@ -10611,10 +10611,10 @@
         <v>1.05</v>
       </c>
       <c r="Y63">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="Z63">
-        <v>3.65</v>
+        <v>3.44</v>
       </c>
       <c r="AA63">
         <v>1.79</v>
@@ -10623,19 +10623,19 @@
         <v>1.95</v>
       </c>
       <c r="AC63">
-        <v>3.04</v>
+        <v>3.06</v>
       </c>
       <c r="AD63">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="AE63">
-        <v>1.09</v>
+        <v>1.13</v>
       </c>
       <c r="AF63">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="AG63">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="AH63" t="inlineStr">
         <is>
@@ -11888,13 +11888,13 @@
         <v>5.25</v>
       </c>
       <c r="P71">
-        <v>9</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="Q71">
-        <v>1.78</v>
+        <v>1.74</v>
       </c>
       <c r="R71">
-        <v>2.59</v>
+        <v>2.25</v>
       </c>
       <c r="S71">
         <v>1.34</v>
@@ -11903,7 +11903,7 @@
         <v>3.14</v>
       </c>
       <c r="U71">
-        <v>2.7</v>
+        <v>2.62</v>
       </c>
       <c r="V71">
         <v>1.46</v>
@@ -11921,25 +11921,25 @@
         <v>3.68</v>
       </c>
       <c r="AA71">
-        <v>1.8</v>
+        <v>1.86</v>
       </c>
       <c r="AB71">
-        <v>2.02</v>
+        <v>2.09</v>
       </c>
       <c r="AC71">
         <v>2.85</v>
       </c>
       <c r="AD71">
-        <v>1.38</v>
+        <v>1.35</v>
       </c>
       <c r="AE71">
         <v>1.1</v>
       </c>
       <c r="AF71">
-        <v>2.17</v>
+        <v>2.19</v>
       </c>
       <c r="AG71">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="AH71" t="inlineStr">
         <is>
@@ -11955,7 +11955,7 @@
         <v>1.17</v>
       </c>
       <c r="AK71">
-        <v>3.42</v>
+        <v>3.08</v>
       </c>
       <c r="AL71">
         <v>0</v>
@@ -12377,31 +12377,31 @@
         <v>3</v>
       </c>
       <c r="P74">
-        <v>3.25</v>
+        <v>3.6</v>
       </c>
       <c r="Q74">
-        <v>3</v>
+        <v>3.07</v>
       </c>
       <c r="R74">
-        <v>1.87</v>
+        <v>1.93</v>
       </c>
       <c r="S74">
-        <v>1.5</v>
+        <v>1.59</v>
       </c>
       <c r="T74">
-        <v>2.33</v>
+        <v>2.2</v>
       </c>
       <c r="U74">
-        <v>3.58</v>
+        <v>3.8</v>
       </c>
       <c r="V74">
         <v>1.22</v>
       </c>
       <c r="W74">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X74">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="Y74">
         <v>1.54</v>
@@ -12410,10 +12410,10 @@
         <v>2.34</v>
       </c>
       <c r="AA74">
-        <v>2.56</v>
+        <v>2.59</v>
       </c>
       <c r="AB74">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="AC74">
         <v>5.5</v>
@@ -12534,16 +12534,16 @@
         </is>
       </c>
       <c r="N75">
-        <v>2.3</v>
+        <v>2.37</v>
       </c>
       <c r="O75">
-        <v>3.25</v>
+        <v>3.44</v>
       </c>
       <c r="P75">
-        <v>2.62</v>
+        <v>2.65</v>
       </c>
       <c r="Q75">
-        <v>3.1</v>
+        <v>2.95</v>
       </c>
       <c r="R75">
         <v>2.2</v>
@@ -12573,10 +12573,10 @@
         <v>3.15</v>
       </c>
       <c r="AA75">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="AB75">
-        <v>1.98</v>
+        <v>1.95</v>
       </c>
       <c r="AC75">
         <v>3.1</v>
@@ -12585,10 +12585,10 @@
         <v>1.34</v>
       </c>
       <c r="AE75">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="AF75">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="AG75">
         <v>2.15</v>
@@ -12700,10 +12700,10 @@
         <v>2.7</v>
       </c>
       <c r="O76">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="P76">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="Q76">
         <v>3.35</v>
@@ -12718,7 +12718,7 @@
         <v>2.75</v>
       </c>
       <c r="U76">
-        <v>2.9</v>
+        <v>2.91</v>
       </c>
       <c r="V76">
         <v>1.4</v>
@@ -12736,22 +12736,22 @@
         <v>3.3</v>
       </c>
       <c r="AA76">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="AB76">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="AC76">
-        <v>3.39</v>
+        <v>3.42</v>
       </c>
       <c r="AD76">
         <v>1.32</v>
       </c>
       <c r="AE76">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="AF76">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="AG76">
         <v>2</v>
@@ -12896,7 +12896,7 @@
         <v>1.21</v>
       </c>
       <c r="Z77">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="AA77">
         <v>1.8</v>
@@ -12911,10 +12911,10 @@
         <v>1.33</v>
       </c>
       <c r="AE77">
-        <v>1.09</v>
+        <v>1.13</v>
       </c>
       <c r="AF77">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="AG77">
         <v>2.16</v>
@@ -13023,16 +13023,16 @@
         </is>
       </c>
       <c r="N78">
-        <v>2.2</v>
+        <v>2.23</v>
       </c>
       <c r="O78">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="P78">
-        <v>3.25</v>
+        <v>3.21</v>
       </c>
       <c r="Q78">
-        <v>2.98</v>
+        <v>2.96</v>
       </c>
       <c r="R78">
         <v>1.89</v>
@@ -13044,7 +13044,7 @@
         <v>2.75</v>
       </c>
       <c r="U78">
-        <v>2.88</v>
+        <v>3.28</v>
       </c>
       <c r="V78">
         <v>1.33</v>
@@ -13053,7 +13053,7 @@
         <v>1.01</v>
       </c>
       <c r="X78">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="Y78">
         <v>1.38</v>
@@ -13062,7 +13062,7 @@
         <v>2.62</v>
       </c>
       <c r="AA78">
-        <v>2.35</v>
+        <v>2.36</v>
       </c>
       <c r="AB78">
         <v>1.61</v>
@@ -13093,10 +13093,10 @@
         </is>
       </c>
       <c r="AJ78">
-        <v>1.23</v>
+        <v>1.36</v>
       </c>
       <c r="AK78">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="AL78">
         <v>0</v>
@@ -13681,7 +13681,7 @@
         <v>3.4</v>
       </c>
       <c r="P82">
-        <v>4.46</v>
+        <v>4.2</v>
       </c>
       <c r="Q82">
         <v>2.38</v>
@@ -13693,10 +13693,10 @@
         <v>1.43</v>
       </c>
       <c r="T82">
-        <v>2.53</v>
+        <v>2.78</v>
       </c>
       <c r="U82">
-        <v>2.9</v>
+        <v>3.19</v>
       </c>
       <c r="V82">
         <v>1.32</v>
@@ -13705,7 +13705,7 @@
         <v>1.02</v>
       </c>
       <c r="X82">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="Y82">
         <v>1.38</v>
@@ -13717,13 +13717,13 @@
         <v>2.1</v>
       </c>
       <c r="AB82">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="AC82">
         <v>3.85</v>
       </c>
       <c r="AD82">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="AE82">
         <v>1.02</v>
@@ -13732,7 +13732,7 @@
         <v>2</v>
       </c>
       <c r="AG82">
-        <v>1.74</v>
+        <v>1.83</v>
       </c>
       <c r="AH82" t="inlineStr">
         <is>
@@ -13748,7 +13748,7 @@
         <v>1.27</v>
       </c>
       <c r="AK82">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="AL82">
         <v>0</v>
@@ -13850,7 +13850,7 @@
         <v>3.57</v>
       </c>
       <c r="R83">
-        <v>2.21</v>
+        <v>2.3</v>
       </c>
       <c r="S83">
         <v>1.28</v>
@@ -13868,13 +13868,13 @@
         <v>1.11</v>
       </c>
       <c r="X83">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y83">
         <v>1.15</v>
       </c>
       <c r="Z83">
-        <v>4.3</v>
+        <v>4.52</v>
       </c>
       <c r="AA83">
         <v>1.57</v>
@@ -13886,13 +13886,13 @@
         <v>2.55</v>
       </c>
       <c r="AD83">
-        <v>1.47</v>
+        <v>1.49</v>
       </c>
       <c r="AE83">
-        <v>1.14</v>
+        <v>1.18</v>
       </c>
       <c r="AF83">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="AG83">
         <v>2.34</v>
@@ -14010,22 +14010,22 @@
         <v>4.6</v>
       </c>
       <c r="Q84">
-        <v>2.1</v>
+        <v>1.99</v>
       </c>
       <c r="R84">
-        <v>2.32</v>
+        <v>2.31</v>
       </c>
       <c r="S84">
         <v>1.25</v>
       </c>
       <c r="T84">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="U84">
-        <v>2.47</v>
+        <v>2.33</v>
       </c>
       <c r="V84">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="W84">
         <v>1.1</v>
@@ -14037,28 +14037,28 @@
         <v>1.2</v>
       </c>
       <c r="Z84">
-        <v>4.33</v>
+        <v>4.2</v>
       </c>
       <c r="AA84">
         <v>1.57</v>
       </c>
       <c r="AB84">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="AC84">
-        <v>2.49</v>
+        <v>2.5</v>
       </c>
       <c r="AD84">
         <v>1.47</v>
       </c>
       <c r="AE84">
-        <v>1.15</v>
+        <v>1.18</v>
       </c>
       <c r="AF84">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="AG84">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="AH84" t="inlineStr">
         <is>
@@ -14071,10 +14071,10 @@
         </is>
       </c>
       <c r="AJ84">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="AK84">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="AL84">
         <v>0</v>
@@ -14653,64 +14653,64 @@
         </is>
       </c>
       <c r="N88">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="O88">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="P88">
-        <v>7</v>
+        <v>7.5</v>
       </c>
       <c r="Q88">
         <v>1.8</v>
       </c>
       <c r="R88">
-        <v>2.25</v>
+        <v>2.28</v>
       </c>
       <c r="S88">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="T88">
-        <v>2.8</v>
+        <v>2.9</v>
       </c>
       <c r="U88">
-        <v>2.62</v>
+        <v>2.66</v>
       </c>
       <c r="V88">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="W88">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="X88">
         <v>1.02</v>
       </c>
       <c r="Y88">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="Z88">
-        <v>3.5</v>
+        <v>3.8</v>
       </c>
       <c r="AA88">
-        <v>1.89</v>
+        <v>1.87</v>
       </c>
       <c r="AB88">
-        <v>1.85</v>
+        <v>1.87</v>
       </c>
       <c r="AC88">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="AD88">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AE88">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="AF88">
-        <v>2.1</v>
+        <v>2.25</v>
       </c>
       <c r="AG88">
-        <v>1.67</v>
+        <v>1.6</v>
       </c>
       <c r="AH88" t="inlineStr">
         <is>
@@ -14979,7 +14979,7 @@
         </is>
       </c>
       <c r="N90">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="O90">
         <v>3.45</v>
@@ -14988,28 +14988,28 @@
         <v>2.7</v>
       </c>
       <c r="Q90">
-        <v>2.6</v>
+        <v>2.63</v>
       </c>
       <c r="R90">
+        <v>2.45</v>
+      </c>
+      <c r="S90">
+        <v>1.27</v>
+      </c>
+      <c r="T90">
+        <v>3.25</v>
+      </c>
+      <c r="U90">
         <v>2.25</v>
       </c>
-      <c r="S90">
-        <v>1.26</v>
-      </c>
-      <c r="T90">
-        <v>3.32</v>
-      </c>
-      <c r="U90">
-        <v>2.43</v>
-      </c>
       <c r="V90">
-        <v>1.43</v>
+        <v>1.57</v>
       </c>
       <c r="W90">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="X90">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y90">
         <v>1.17</v>
@@ -15021,22 +15021,22 @@
         <v>1.57</v>
       </c>
       <c r="AB90">
+        <v>2.25</v>
+      </c>
+      <c r="AC90">
         <v>2.38</v>
       </c>
-      <c r="AC90">
-        <v>2.33</v>
-      </c>
       <c r="AD90">
-        <v>1.48</v>
+        <v>1.46</v>
       </c>
       <c r="AE90">
-        <v>1.16</v>
+        <v>1.2</v>
       </c>
       <c r="AF90">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="AG90">
-        <v>2.1</v>
+        <v>2.5</v>
       </c>
       <c r="AH90" t="inlineStr">
         <is>
@@ -15471,19 +15471,19 @@
         <v>3.3</v>
       </c>
       <c r="O93">
-        <v>3.3</v>
+        <v>2.95</v>
       </c>
       <c r="P93">
-        <v>1.9</v>
+        <v>2.06</v>
       </c>
       <c r="Q93">
         <v>3.75</v>
       </c>
       <c r="R93">
-        <v>2.27</v>
+        <v>2.2</v>
       </c>
       <c r="S93">
-        <v>1.35</v>
+        <v>1.39</v>
       </c>
       <c r="T93">
         <v>2.9</v>
@@ -15504,19 +15504,19 @@
         <v>1.21</v>
       </c>
       <c r="Z93">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="AA93">
         <v>1.81</v>
       </c>
       <c r="AB93">
-        <v>1.95</v>
+        <v>1.85</v>
       </c>
       <c r="AC93">
         <v>3.3</v>
       </c>
       <c r="AD93">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="AE93">
         <v>1.1</v>
@@ -15525,7 +15525,7 @@
         <v>1.63</v>
       </c>
       <c r="AG93">
-        <v>2.14</v>
+        <v>1.95</v>
       </c>
       <c r="AH93" t="inlineStr">
         <is>
@@ -15794,28 +15794,28 @@
         </is>
       </c>
       <c r="N95">
-        <v>1.84</v>
+        <v>1.82</v>
       </c>
       <c r="O95">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="P95">
-        <v>4.1</v>
+        <v>4.32</v>
       </c>
       <c r="Q95">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="R95">
-        <v>2.18</v>
+        <v>2.19</v>
       </c>
       <c r="S95">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="T95">
-        <v>2.88</v>
+        <v>3</v>
       </c>
       <c r="U95">
-        <v>2.88</v>
+        <v>2.89</v>
       </c>
       <c r="V95">
         <v>1.36</v>
@@ -15827,31 +15827,31 @@
         <v>1.05</v>
       </c>
       <c r="Y95">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="Z95">
-        <v>3.05</v>
+        <v>3.6</v>
       </c>
       <c r="AA95">
-        <v>1.96</v>
+        <v>1.91</v>
       </c>
       <c r="AB95">
-        <v>1.88</v>
+        <v>1.93</v>
       </c>
       <c r="AC95">
-        <v>3.25</v>
+        <v>3.13</v>
       </c>
       <c r="AD95">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AE95">
         <v>1.13</v>
       </c>
       <c r="AF95">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="AG95">
-        <v>1.85</v>
+        <v>1.93</v>
       </c>
       <c r="AH95" t="inlineStr">
         <is>
@@ -15966,13 +15966,13 @@
         <v>6</v>
       </c>
       <c r="Q96">
-        <v>2.07</v>
+        <v>2.15</v>
       </c>
       <c r="R96">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="S96">
-        <v>1.43</v>
+        <v>1.47</v>
       </c>
       <c r="T96">
         <v>2.5</v>
@@ -15990,13 +15990,13 @@
         <v>1.05</v>
       </c>
       <c r="Y96">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="Z96">
-        <v>2.74</v>
+        <v>2.88</v>
       </c>
       <c r="AA96">
-        <v>2.17</v>
+        <v>2.25</v>
       </c>
       <c r="AB96">
         <v>1.6</v>
@@ -16011,10 +16011,10 @@
         <v>1.03</v>
       </c>
       <c r="AF96">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="AG96">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="AH96" t="inlineStr">
         <is>
@@ -16027,10 +16027,10 @@
         </is>
       </c>
       <c r="AJ96">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="AK96">
-        <v>2.39</v>
+        <v>2.45</v>
       </c>
       <c r="AL96">
         <v>0</v>
@@ -16283,31 +16283,31 @@
         </is>
       </c>
       <c r="N98">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="O98">
-        <v>3.8</v>
+        <v>3.6</v>
       </c>
       <c r="P98">
-        <v>3.5</v>
+        <v>3.2</v>
       </c>
       <c r="Q98">
         <v>2.2</v>
       </c>
       <c r="R98">
-        <v>2.31</v>
+        <v>2.34</v>
       </c>
       <c r="S98">
         <v>1.24</v>
       </c>
       <c r="T98">
-        <v>3.7</v>
+        <v>3.5</v>
       </c>
       <c r="U98">
         <v>2.2</v>
       </c>
       <c r="V98">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="W98">
         <v>1.17</v>
@@ -16325,16 +16325,16 @@
         <v>1.5</v>
       </c>
       <c r="AB98">
-        <v>2.63</v>
+        <v>2.5</v>
       </c>
       <c r="AC98">
         <v>2.22</v>
       </c>
       <c r="AD98">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="AE98">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AF98">
         <v>1.4</v>
@@ -16353,10 +16353,10 @@
         </is>
       </c>
       <c r="AJ98">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AK98">
-        <v>1.88</v>
+        <v>1.85</v>
       </c>
       <c r="AL98">
         <v>0</v>
@@ -16452,43 +16452,43 @@
         <v>3.3</v>
       </c>
       <c r="P99">
-        <v>2.6</v>
+        <v>2.56</v>
       </c>
       <c r="Q99">
-        <v>2.98</v>
+        <v>3.01</v>
       </c>
       <c r="R99">
-        <v>2.14</v>
+        <v>2.25</v>
       </c>
       <c r="S99">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="T99">
-        <v>2.91</v>
+        <v>3.25</v>
       </c>
       <c r="U99">
-        <v>2.57</v>
+        <v>2.39</v>
       </c>
       <c r="V99">
         <v>1.47</v>
       </c>
       <c r="W99">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="X99">
         <v>1</v>
       </c>
       <c r="Y99">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="Z99">
         <v>3.78</v>
       </c>
       <c r="AA99">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="AB99">
-        <v>2.09</v>
+        <v>2.1</v>
       </c>
       <c r="AC99">
         <v>2.59</v>
@@ -16497,7 +16497,7 @@
         <v>1.39</v>
       </c>
       <c r="AE99">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="AF99">
         <v>1.57</v>
@@ -16519,7 +16519,7 @@
         <v>1.26</v>
       </c>
       <c r="AK99">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="AL99">
         <v>0</v>
@@ -16609,22 +16609,22 @@
         </is>
       </c>
       <c r="N100">
-        <v>4</v>
+        <v>4.05</v>
       </c>
       <c r="O100">
-        <v>3.6</v>
+        <v>3.58</v>
       </c>
       <c r="P100">
         <v>1.88</v>
       </c>
       <c r="Q100">
-        <v>4.59</v>
+        <v>4.65</v>
       </c>
       <c r="R100">
-        <v>2.15</v>
+        <v>2.09</v>
       </c>
       <c r="S100">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="T100">
         <v>2.85</v>
@@ -16633,7 +16633,7 @@
         <v>2.77</v>
       </c>
       <c r="V100">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="W100">
         <v>1.07</v>
@@ -16642,7 +16642,7 @@
         <v>1.01</v>
       </c>
       <c r="Y100">
-        <v>1.26</v>
+        <v>1.29</v>
       </c>
       <c r="Z100">
         <v>3.36</v>
@@ -16657,16 +16657,16 @@
         <v>3.05</v>
       </c>
       <c r="AD100">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="AE100">
         <v>1.08</v>
       </c>
       <c r="AF100">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="AG100">
-        <v>1.97</v>
+        <v>1.98</v>
       </c>
       <c r="AH100" t="inlineStr">
         <is>
@@ -16781,7 +16781,7 @@
         <v>5.33</v>
       </c>
       <c r="Q101">
-        <v>2.07</v>
+        <v>1.95</v>
       </c>
       <c r="R101">
         <v>2.34</v>
@@ -16793,7 +16793,7 @@
         <v>3.6</v>
       </c>
       <c r="U101">
-        <v>2.46</v>
+        <v>2.47</v>
       </c>
       <c r="V101">
         <v>1.57</v>
@@ -16808,7 +16808,7 @@
         <v>1.2</v>
   